--- a/Data_ERP/Pedidos Transmicion.xlsx
+++ b/Data_ERP/Pedidos Transmicion.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Mi unidad\Sistema_Logistico_Peirano\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sistema_Logistico_Peirano\Data_ERP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{851FEC6E-DDF9-4BD8-8A79-6D1A8DC6B5E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{14300C14-2A70-45F4-9399-A5B218D879C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{854DF19A-0C24-49C2-95F1-3828B168A7C8}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{F35A25CB-1CCD-4BDC-8526-8C916F45A488}"/>
   </bookViews>
   <sheets>
     <sheet name="transmicion" sheetId="1" r:id="rId1"/>
@@ -4256,7 +4256,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2915D8BF-EE4A-485E-9370-060D7A960B73}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{288ACFD6-C0B7-4E80-B429-B6C0F4CA9C3D}">
   <dimension ref="A1:H453"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="10.5" x14ac:dyDescent="0.15"/>
   <cols>

--- a/Data_ERP/Pedidos Transmicion.xlsx
+++ b/Data_ERP/Pedidos Transmicion.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sistema_Logistico_Peirano\Data_ERP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D02FDEB0-1335-4FED-AD23-E06A801D3F3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F3A058EB-AA6E-4184-822C-4D5A4A0A0049}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{E7BDC0C5-A6F9-4DEC-ABBD-E83A56431198}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{A13A846E-569D-4C42-B442-80B4CE7712B4}"/>
   </bookViews>
   <sheets>
     <sheet name="transmicion" sheetId="1" r:id="rId1"/>
@@ -4169,7 +4169,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3335470-EC2C-4671-A2FF-CB64DA8FE0D2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3789995-99B4-4516-AD4E-7C386CEEC013}">
   <dimension ref="A1:H441"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="10.5" x14ac:dyDescent="0.15"/>
   <cols>

--- a/Data_ERP/Pedidos Transmicion.xlsx
+++ b/Data_ERP/Pedidos Transmicion.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sistema_Logistico_Peirano\Data_ERP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E1F559A7-F50D-4D24-9481-368263BBE645}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1ED107C3-D8DA-41F8-9FE5-EA715B590F07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{CBD33827-AADC-4FB9-914F-F1204A984410}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{2322D428-2DDC-494B-867A-A2B9B2D2D7F9}"/>
   </bookViews>
   <sheets>
     <sheet name="transmicion" sheetId="1" r:id="rId1"/>
@@ -4388,7 +4388,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF3F844A-5B17-4C25-BFAD-7A3855511305}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD668B2E-7616-4EBD-9EA7-A62A586B40D1}">
   <dimension ref="A1:H469"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="10.5" x14ac:dyDescent="0.15"/>
   <cols>

--- a/Data_ERP/Pedidos Transmicion.xlsx
+++ b/Data_ERP/Pedidos Transmicion.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sistema_Logistico_Peirano\Data_ERP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9012DDAC-05ED-4943-AA72-A4BAD7739B90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{567F6933-0584-49C4-B011-7E07290C3500}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{ED228632-3AC8-4C80-BDCA-011C11B6EFD0}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{2CF6C55C-860C-4E62-8CFF-825E9AE082C8}"/>
   </bookViews>
   <sheets>
     <sheet name="transmicion" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1508" uniqueCount="571">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1672" uniqueCount="629">
   <si>
     <t>0001</t>
   </si>
@@ -574,9 +574,6 @@
     <t>SEIP SERGIO MARCELO Y RODRIGUEZ PABLO MARTIN</t>
   </si>
   <si>
-    <t xml:space="preserve">  213084</t>
-  </si>
-  <si>
     <t xml:space="preserve">  213097</t>
   </si>
   <si>
@@ -589,6 +586,9 @@
     <t xml:space="preserve">  213101</t>
   </si>
   <si>
+    <t xml:space="preserve">  213109</t>
+  </si>
+  <si>
     <t xml:space="preserve">  213132</t>
   </si>
   <si>
@@ -601,6 +601,9 @@
     <t xml:space="preserve">  213162</t>
   </si>
   <si>
+    <t xml:space="preserve">  213170</t>
+  </si>
+  <si>
     <t xml:space="preserve">  213176</t>
   </si>
   <si>
@@ -715,6 +718,9 @@
     <t xml:space="preserve">  213364</t>
   </si>
   <si>
+    <t>1. Enviado para armado</t>
+  </si>
+  <si>
     <t>CYNETH SRL -CYNETH SANITARIOS</t>
   </si>
   <si>
@@ -751,6 +757,12 @@
     <t>CONSTRUDISENO S.A.</t>
   </si>
   <si>
+    <t xml:space="preserve">  213485</t>
+  </si>
+  <si>
+    <t>DIDIO HERMANOS S.A.</t>
+  </si>
+  <si>
     <t xml:space="preserve">  213498</t>
   </si>
   <si>
@@ -805,21 +817,6 @@
     <t xml:space="preserve">  213571</t>
   </si>
   <si>
-    <t xml:space="preserve">  213572</t>
-  </si>
-  <si>
-    <t>BETOMAT S.R.L.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213575</t>
-  </si>
-  <si>
-    <t>BRUNETTI ADRIANA NOEMI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213576</t>
-  </si>
-  <si>
     <t xml:space="preserve">  213588</t>
   </si>
   <si>
@@ -832,15 +829,12 @@
     <t xml:space="preserve">  213595</t>
   </si>
   <si>
-    <t xml:space="preserve">  213602</t>
+    <t xml:space="preserve">  213603</t>
   </si>
   <si>
     <t>DOMINGO RESTA Y CIA. SA</t>
   </si>
   <si>
-    <t xml:space="preserve">  213603</t>
-  </si>
-  <si>
     <t xml:space="preserve">  213606</t>
   </si>
   <si>
@@ -868,18 +862,6 @@
     <t xml:space="preserve">  213637</t>
   </si>
   <si>
-    <t xml:space="preserve">  213645</t>
-  </si>
-  <si>
-    <t>ANSBOR S.R.L.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213646</t>
-  </si>
-  <si>
-    <t>MAYOR S.A.</t>
-  </si>
-  <si>
     <t xml:space="preserve">  213647</t>
   </si>
   <si>
@@ -889,27 +871,12 @@
     <t xml:space="preserve">  213648</t>
   </si>
   <si>
-    <t xml:space="preserve">  213649</t>
-  </si>
-  <si>
-    <t>DADDONA S.A.</t>
-  </si>
-  <si>
     <t xml:space="preserve">  213651</t>
   </si>
   <si>
     <t>DISTRIBUIDORA GAY S.R.L.</t>
   </si>
   <si>
-    <t xml:space="preserve">  213654</t>
-  </si>
-  <si>
-    <t>SANITARIOS CAMPANA S.R.L.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213656</t>
-  </si>
-  <si>
     <t xml:space="preserve">  213663</t>
   </si>
   <si>
@@ -997,21 +964,12 @@
     <t xml:space="preserve">  213719</t>
   </si>
   <si>
-    <t xml:space="preserve">  213720</t>
-  </si>
-  <si>
-    <t>MATERIALES GUEMES SRL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213722</t>
+    <t xml:space="preserve">  213723</t>
   </si>
   <si>
     <t>ABELSON S.A.</t>
   </si>
   <si>
-    <t xml:space="preserve">  213723</t>
-  </si>
-  <si>
     <t xml:space="preserve">  213724</t>
   </si>
   <si>
@@ -1021,502 +979,706 @@
     <t xml:space="preserve">  213727</t>
   </si>
   <si>
-    <t xml:space="preserve">  213728</t>
-  </si>
-  <si>
-    <t>FORTUNATO RIZZI E HIJOS S.A.</t>
-  </si>
-  <si>
     <t xml:space="preserve">  213729</t>
   </si>
   <si>
     <t>ANDRES LUIS DE FRANCESCO S.A.</t>
   </si>
   <si>
-    <t xml:space="preserve">  213731</t>
+    <t xml:space="preserve">  213732</t>
+  </si>
+  <si>
+    <t>ISKANDAR SRL - GRUPO NEXOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213734</t>
+  </si>
+  <si>
+    <t>UCCELI GABRIEL A.-SANITARIOS GABRIEL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213735</t>
+  </si>
+  <si>
+    <t>DOMANI DECO S.R.L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213736</t>
+  </si>
+  <si>
+    <t>DE FREITA BRAIAN O- DF HOGAR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213739</t>
+  </si>
+  <si>
+    <t>SANITARIOS LUGANO S.R.L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213740</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213744</t>
+  </si>
+  <si>
+    <t>CONCORPLAST S.R.L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213745</t>
+  </si>
+  <si>
+    <t>BODEN CERAMICS S.R.L. -SYRIA CERAMICOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213747</t>
+  </si>
+  <si>
+    <t>MASIELLO MATIAS A. -MATEO SANITARIOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213751</t>
+  </si>
+  <si>
+    <t>GRUPO GALU S.A.  - SANITARIOS MITRE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213754</t>
+  </si>
+  <si>
+    <t>CASA BOUCIGUEZ S.A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213755</t>
+  </si>
+  <si>
+    <t>HEREDIA LEONARDO A - FERRETERIA HEREDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213757</t>
+  </si>
+  <si>
+    <t>DI STABILE E HIJOS S.A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213760</t>
+  </si>
+  <si>
+    <t>FRAU ARIEL- EL SALVADOR DE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213762</t>
+  </si>
+  <si>
+    <t>GUERRERO EMILIO G. Y GUERRERO MATIA SH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213765</t>
+  </si>
+  <si>
+    <t>TOBA S.R.L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213766</t>
+  </si>
+  <si>
+    <t>DEKKO GUALEGUAYCHU SRL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213770</t>
+  </si>
+  <si>
+    <t>SUCESION DE MARCHAL JUAN HECTOR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213771</t>
+  </si>
+  <si>
+    <t>MADERSA S.R.L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213772</t>
+  </si>
+  <si>
+    <t>CORDA SANITARIOS SRL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213773</t>
+  </si>
+  <si>
+    <t>JORGE N. FLORES E HIJOS S.A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213778</t>
+  </si>
+  <si>
+    <t>SAIZ ARIEL A.-HERRAJES SAIZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213780</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213781</t>
+  </si>
+  <si>
+    <t>CATUS S.A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213783</t>
+  </si>
+  <si>
+    <t>WALTER CARLOS A. -EL FUERTE MATERIALES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213784</t>
+  </si>
+  <si>
+    <t>ROMANO FABIAN ANDRES -COMAR DESIGN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213785</t>
+  </si>
+  <si>
+    <t>GALBAHIA S.R.L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213786</t>
+  </si>
+  <si>
+    <t>CASA FERRALIC SRL - MARMOLERIA PATAGONICA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213787</t>
+  </si>
+  <si>
+    <t>CORRALON COMAHUE S.A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213789</t>
+  </si>
+  <si>
+    <t>ZINGALV GALVANIZADOS Y ZINC S.R.L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213790</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213793</t>
+  </si>
+  <si>
+    <t>SANITARIOS JULICAM SRL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213794</t>
+  </si>
+  <si>
+    <t>ALVEAR SANITARIOS S.R.L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213796</t>
+  </si>
+  <si>
+    <t>CARLOS CARTIER M Y ROSANA GERARDI SH-SANITARIOS RC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213797</t>
+  </si>
+  <si>
+    <t>BAEZ RAMON ANTONIO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213800</t>
+  </si>
+  <si>
+    <t>SANCHEZ M. Y NUÑEZ M. S.H. - SANITARIOS NUSAN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213801</t>
+  </si>
+  <si>
+    <t>NEO MATERIALES S.A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213803</t>
+  </si>
+  <si>
+    <t>PLASTISUR S.R.L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213804</t>
+  </si>
+  <si>
+    <t>SANITARIOS CORTESE SRL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213805</t>
+  </si>
+  <si>
+    <t>NOVA FUSION SRL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213807</t>
+  </si>
+  <si>
+    <t>DAPESOL S.A. -MATERIALES ACON</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213809</t>
+  </si>
+  <si>
+    <t>FEDAN S.A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213810</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213812</t>
+  </si>
+  <si>
+    <t>FERNANDEZ GUILLERMO S. -SANITARIOS FAM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213813</t>
+  </si>
+  <si>
+    <t>PONSVILL S.A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213814</t>
+  </si>
+  <si>
+    <t>COLADONATO FEDERICO N.-SANITARIOS CARUPA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213817</t>
+  </si>
+  <si>
+    <t>HIPERCAÑO S.A.S.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213820</t>
+  </si>
+  <si>
+    <t>PREMOLCHACO S.R.L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213822</t>
+  </si>
+  <si>
+    <t>CERAMICOS PELLEGRINI S.R.L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213823</t>
+  </si>
+  <si>
+    <t>ALLEGRA S.R.L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213827</t>
+  </si>
+  <si>
+    <t>VIESTI HNOS. SANITARIOS S. R. L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213828</t>
+  </si>
+  <si>
+    <t>SANITARIOS ADUCCI ADROGUE S.R.L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213829</t>
+  </si>
+  <si>
+    <t>ROCAS DEL SUR S.A. -CORTES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213830</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213840</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213844</t>
+  </si>
+  <si>
+    <t>PORAL S.A.C.I.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213848</t>
+  </si>
+  <si>
+    <t>EDEN SANITARIOS S.R.L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213850</t>
+  </si>
+  <si>
+    <t>ALVARENGA VILLAR LUIS F.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213851</t>
+  </si>
+  <si>
+    <t>SANTIANO LILIANA NOEMI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213852</t>
+  </si>
+  <si>
+    <t>BALCARCE 54 S.A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213853</t>
+  </si>
+  <si>
+    <t>SNEUBER SANITARIOS S.A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213857</t>
+  </si>
+  <si>
+    <t>SAMOT S.A.S.  -SANIPLAST</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213863</t>
+  </si>
+  <si>
+    <t>SANITARIOS GAONA S.A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213864</t>
+  </si>
+  <si>
+    <t>GILI Y CIA SRL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213870</t>
+  </si>
+  <si>
+    <t>VILANOVA DE MEIA S.R.L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213872</t>
+  </si>
+  <si>
+    <t>FERNANDEZ GONZALO M.-SANITARIOS FERNANDEZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213873</t>
+  </si>
+  <si>
+    <t>FIUMANI MATIAS EZEQUIEL - SANITARIOS MARQUEZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213874</t>
+  </si>
+  <si>
+    <t>COSTA CALCAGNO SRL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213876</t>
+  </si>
+  <si>
+    <t>ARDISSONE MARIO JAVIER -SANIT. ARDISSONE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213877</t>
+  </si>
+  <si>
+    <t>LISOTTO ROQUE Y LISOTTO ROBERTO SH -LISOTTO SANIT.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213878</t>
+  </si>
+  <si>
+    <t>DARSIE Y CIA. SACI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213879</t>
+  </si>
+  <si>
+    <t>TOTAL 25 SANITARIOS S.A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213880</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213881</t>
+  </si>
+  <si>
+    <t>EL IMPERIO DEL CERAMICO S.R.L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213886</t>
+  </si>
+  <si>
+    <t>MIGUEL MUKDISE HNOS SRL  -CORRALON MUKDISE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213887</t>
+  </si>
+  <si>
+    <t>VEGA DEL ESLA S.A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213888</t>
+  </si>
+  <si>
+    <t>BRASIL CERAMICAS S.R.L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213889</t>
+  </si>
+  <si>
+    <t>SACE SRL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213890</t>
+  </si>
+  <si>
+    <t>VICTOR NADIA ANTONELA -SANTIANO CONSTRUCCIONES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213891</t>
   </si>
   <si>
     <t>GILLI FAUDIN LUIS V. -GILCOMAT</t>
   </si>
   <si>
-    <t xml:space="preserve">  213732</t>
-  </si>
-  <si>
-    <t>ISKANDAR SRL - GRUPO NEXOS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213734</t>
-  </si>
-  <si>
-    <t>UCCELI GABRIEL A.-SANITARIOS GABRIEL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213735</t>
-  </si>
-  <si>
-    <t>DOMANI DECO S.R.L.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213736</t>
-  </si>
-  <si>
-    <t>DE FREITA BRAIAN O- DF HOGAR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213738</t>
-  </si>
-  <si>
-    <t>KALFAIAN HNOS. S.R.L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213739</t>
-  </si>
-  <si>
-    <t>SANITARIOS LUGANO S.R.L.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213740</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213744</t>
-  </si>
-  <si>
-    <t>CONCORPLAST S.R.L.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213745</t>
-  </si>
-  <si>
-    <t>BODEN CERAMICS S.R.L. -SYRIA CERAMICOS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213747</t>
-  </si>
-  <si>
-    <t>MASIELLO MATIAS A. -MATEO SANITARIOS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213750</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213751</t>
-  </si>
-  <si>
-    <t>GRUPO GALU S.A.  - SANITARIOS MITRE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213754</t>
-  </si>
-  <si>
-    <t>CASA BOUCIGUEZ S.A.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213755</t>
-  </si>
-  <si>
-    <t>HEREDIA LEONARDO A - FERRETERIA HEREDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213757</t>
-  </si>
-  <si>
-    <t>DI STABILE E HIJOS S.A.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213760</t>
-  </si>
-  <si>
-    <t>FRAU ARIEL- EL SALVADOR DE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213761</t>
-  </si>
-  <si>
-    <t>SANI 3 S.R.L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213762</t>
-  </si>
-  <si>
-    <t>GUERRERO EMILIO G. Y GUERRERO MATIA SH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213765</t>
-  </si>
-  <si>
-    <t>TOBA S.R.L.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213766</t>
-  </si>
-  <si>
-    <t>DEKKO GUALEGUAYCHU SRL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213770</t>
-  </si>
-  <si>
-    <t>SUCESION DE MARCHAL JUAN HECTOR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213771</t>
-  </si>
-  <si>
-    <t>MADERSA S.R.L.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213772</t>
-  </si>
-  <si>
-    <t>CORDA SANITARIOS SRL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213773</t>
-  </si>
-  <si>
-    <t>JORGE N. FLORES E HIJOS S.A.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213778</t>
-  </si>
-  <si>
-    <t>SAIZ ARIEL A.-HERRAJES SAIZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213780</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213781</t>
-  </si>
-  <si>
-    <t>CATUS S.A.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213783</t>
-  </si>
-  <si>
-    <t>WALTER CARLOS A. -EL FUERTE MATERIALES</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213785</t>
-  </si>
-  <si>
-    <t>GALBAHIA S.R.L.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213786</t>
-  </si>
-  <si>
-    <t>CASA FERRALIC SRL - MARMOLERIA PATAGONICA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213787</t>
-  </si>
-  <si>
-    <t>CORRALON COMAHUE S.A.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213789</t>
-  </si>
-  <si>
-    <t>ZINGALV GALVANIZADOS Y ZINC S.R.L.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213790</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213793</t>
-  </si>
-  <si>
-    <t>SANITARIOS JULICAM SRL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213794</t>
-  </si>
-  <si>
-    <t>ALVEAR SANITARIOS S.R.L.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213795</t>
-  </si>
-  <si>
-    <t>NESGAMET S.A.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213796</t>
-  </si>
-  <si>
-    <t>CARLOS CARTIER M Y ROSANA GERARDI SH-SANITARIOS RC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213797</t>
-  </si>
-  <si>
-    <t>BAEZ RAMON ANTONIO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213800</t>
-  </si>
-  <si>
-    <t>SANCHEZ M. Y NUÑEZ M. S.H. - SANITARIOS NUSAN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213801</t>
-  </si>
-  <si>
-    <t>NEO MATERIALES S.A.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213803</t>
-  </si>
-  <si>
-    <t>PLASTISUR S.R.L.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213804</t>
-  </si>
-  <si>
-    <t>SANITARIOS CORTESE SRL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213805</t>
-  </si>
-  <si>
-    <t>NOVA FUSION SRL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213807</t>
-  </si>
-  <si>
-    <t>DAPESOL S.A. -MATERIALES ACON</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213809</t>
-  </si>
-  <si>
-    <t>FEDAN S.A.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213810</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213812</t>
-  </si>
-  <si>
-    <t>FERNANDEZ GUILLERMO S. -SANITARIOS FAM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213813</t>
-  </si>
-  <si>
-    <t>PONSVILL S.A.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213814</t>
-  </si>
-  <si>
-    <t>COLADONATO FEDERICO N.-SANITARIOS CARUPA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213817</t>
-  </si>
-  <si>
-    <t>HIPERCAÑO S.A.S.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213820</t>
-  </si>
-  <si>
-    <t>PREMOLCHACO S.R.L.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213822</t>
-  </si>
-  <si>
-    <t>CERAMICOS PELLEGRINI S.R.L.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213823</t>
-  </si>
-  <si>
-    <t>ALLEGRA S.R.L.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213827</t>
-  </si>
-  <si>
-    <t>VIESTI HNOS. SANITARIOS S. R. L.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213828</t>
-  </si>
-  <si>
-    <t>SANITARIOS ADUCCI ADROGUE S.R.L.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213829</t>
-  </si>
-  <si>
-    <t>ROCAS DEL SUR S.A. -CORTES</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213830</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213840</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213848</t>
-  </si>
-  <si>
-    <t>EDEN SANITARIOS S.R.L.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213849</t>
-  </si>
-  <si>
-    <t>PORAL S.A.C.I.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213850</t>
-  </si>
-  <si>
-    <t>ALVARENGA VILLAR LUIS F.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213851</t>
-  </si>
-  <si>
-    <t>SANTIANO LILIANA NOEMI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213852</t>
-  </si>
-  <si>
-    <t>BALCARCE 54 S.A.</t>
+    <t xml:space="preserve">  213892</t>
+  </si>
+  <si>
+    <t>VALDEZ HUGO A -DEL SUR MATERIALES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213895</t>
+  </si>
+  <si>
+    <t>COMERCIALIZADORA Y CONSTRUCTORA LANUS SA  CYCLA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213896</t>
+  </si>
+  <si>
+    <t>TRIPOLI ARNALDO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213898</t>
+  </si>
+  <si>
+    <t>ABATEDAGA PABLO D.J.-CONECTANDO INST. SANIT.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213900</t>
+  </si>
+  <si>
+    <t>PIGNATARO M,PIGNATARO P,PIGNATARO D S.H.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213902</t>
+  </si>
+  <si>
+    <t>MERMOZ S.A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213904</t>
+  </si>
+  <si>
+    <t>SANITARIOS PLASTICOS S.R.L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213906</t>
   </si>
   <si>
     <t>0004</t>
@@ -1597,7 +1759,22 @@
     <t xml:space="preserve">    2804</t>
   </si>
   <si>
-    <t xml:space="preserve">    2805</t>
+    <t xml:space="preserve">    2806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    2807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    2808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    2809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    2810</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    2811</t>
   </si>
   <si>
     <t>4444</t>
@@ -1669,10 +1846,10 @@
     <t xml:space="preserve">    2074</t>
   </si>
   <si>
-    <t xml:space="preserve">    2192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    2198</t>
+    <t xml:space="preserve">    2204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    2206</t>
   </si>
   <si>
     <t>9999</t>
@@ -1706,9 +1883,6 @@
   </si>
   <si>
     <t xml:space="preserve">      81</t>
-  </si>
-  <si>
-    <t xml:space="preserve">      82</t>
   </si>
   <si>
     <t>Puesto</t>
@@ -2182,34 +2356,34 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5032884E-3461-46D0-B25A-2F52B71A50A2}">
-  <dimension ref="A1:H376"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FBBF4EDC-88C7-4B8F-A47F-C4CA13359FD9}">
+  <dimension ref="A1:H417"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
-        <v>563</v>
+        <v>621</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>564</v>
+        <v>622</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>565</v>
+        <v>623</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>566</v>
+        <v>624</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>567</v>
+        <v>625</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>568</v>
+        <v>626</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>569</v>
+        <v>627</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>570</v>
+        <v>628</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
@@ -3676,10 +3850,10 @@
         <v>105</v>
       </c>
       <c r="C58">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D58" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E58" t="s">
         <v>106</v>
@@ -3688,7 +3862,7 @@
         <v>46217</v>
       </c>
       <c r="G58" s="1">
-        <v>46232</v>
+        <v>46252</v>
       </c>
       <c r="H58">
         <v>0</v>
@@ -3962,10 +4136,10 @@
         <v>125</v>
       </c>
       <c r="C69">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D69" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E69" t="s">
         <v>59</v>
@@ -3974,7 +4148,7 @@
         <v>46225</v>
       </c>
       <c r="G69" s="1">
-        <v>46239</v>
+        <v>46252</v>
       </c>
       <c r="H69">
         <v>0</v>
@@ -4040,10 +4214,10 @@
         <v>129</v>
       </c>
       <c r="C72">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D72" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E72" t="s">
         <v>130</v>
@@ -4052,10 +4226,10 @@
         <v>46226</v>
       </c>
       <c r="G72" s="1">
-        <v>46232</v>
+        <v>46252</v>
       </c>
       <c r="H72">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.2">
@@ -4404,10 +4578,10 @@
         <v>153</v>
       </c>
       <c r="C86">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D86" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E86" t="s">
         <v>154</v>
@@ -4416,10 +4590,10 @@
         <v>46233</v>
       </c>
       <c r="G86" s="1">
-        <v>46244</v>
+        <v>46252</v>
       </c>
       <c r="H86">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.2">
@@ -4638,10 +4812,10 @@
         <v>166</v>
       </c>
       <c r="C95">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D95" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E95" t="s">
         <v>138</v>
@@ -4650,10 +4824,10 @@
         <v>46234</v>
       </c>
       <c r="G95" s="1">
-        <v>46238</v>
+        <v>46252</v>
       </c>
       <c r="H95">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.2">
@@ -4936,10 +5110,10 @@
         <v>46238</v>
       </c>
       <c r="G106" s="1">
-        <v>46239</v>
+        <v>46238</v>
       </c>
       <c r="H106">
-        <v>25</v>
+        <v>44</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.2">
@@ -4965,7 +5139,7 @@
         <v>46238</v>
       </c>
       <c r="H107">
-        <v>44</v>
+        <v>73</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.2">
@@ -4991,7 +5165,7 @@
         <v>46238</v>
       </c>
       <c r="H108">
-        <v>73</v>
+        <v>78</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.2">
@@ -5014,10 +5188,10 @@
         <v>46238</v>
       </c>
       <c r="G109" s="1">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="H109">
-        <v>78</v>
+        <v>118</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.2">
@@ -5031,19 +5205,19 @@
         <v>1</v>
       </c>
       <c r="D110" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E110" t="s">
-        <v>27</v>
+        <v>89</v>
       </c>
       <c r="F110" s="1">
         <v>46238</v>
       </c>
       <c r="G110" s="1">
-        <v>46239</v>
+        <v>46252</v>
       </c>
       <c r="H110">
-        <v>118</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.2">
@@ -5054,10 +5228,10 @@
         <v>189</v>
       </c>
       <c r="C111">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D111" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E111" t="s">
         <v>190</v>
@@ -5066,10 +5240,10 @@
         <v>46238</v>
       </c>
       <c r="G111" s="1">
-        <v>46240</v>
+        <v>46252</v>
       </c>
       <c r="H111">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.2">
@@ -5138,10 +5312,10 @@
         <v>12</v>
       </c>
       <c r="E114" t="s">
-        <v>27</v>
+        <v>138</v>
       </c>
       <c r="F114" s="1">
-        <v>46239</v>
+        <v>46238</v>
       </c>
       <c r="G114" s="1">
         <v>46252</v>
@@ -5170,10 +5344,10 @@
         <v>46239</v>
       </c>
       <c r="G115" s="1">
-        <v>46239</v>
+        <v>46252</v>
       </c>
       <c r="H115">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.2">
@@ -5190,16 +5364,16 @@
         <v>2</v>
       </c>
       <c r="E116" t="s">
-        <v>196</v>
+        <v>27</v>
       </c>
       <c r="F116" s="1">
         <v>46239</v>
       </c>
       <c r="G116" s="1">
-        <v>46240</v>
+        <v>46239</v>
       </c>
       <c r="H116">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.2">
@@ -5207,16 +5381,16 @@
         <v>0</v>
       </c>
       <c r="B117" t="s">
+        <v>196</v>
+      </c>
+      <c r="C117">
+        <v>1</v>
+      </c>
+      <c r="D117" t="s">
+        <v>2</v>
+      </c>
+      <c r="E117" t="s">
         <v>197</v>
-      </c>
-      <c r="C117">
-        <v>1</v>
-      </c>
-      <c r="D117" t="s">
-        <v>2</v>
-      </c>
-      <c r="E117" t="s">
-        <v>198</v>
       </c>
       <c r="F117" s="1">
         <v>46239</v>
@@ -5225,7 +5399,7 @@
         <v>46240</v>
       </c>
       <c r="H117">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.2">
@@ -5233,16 +5407,16 @@
         <v>0</v>
       </c>
       <c r="B118" t="s">
+        <v>198</v>
+      </c>
+      <c r="C118">
+        <v>1</v>
+      </c>
+      <c r="D118" t="s">
+        <v>2</v>
+      </c>
+      <c r="E118" t="s">
         <v>199</v>
-      </c>
-      <c r="C118">
-        <v>1</v>
-      </c>
-      <c r="D118" t="s">
-        <v>2</v>
-      </c>
-      <c r="E118" t="s">
-        <v>200</v>
       </c>
       <c r="F118" s="1">
         <v>46239</v>
@@ -5251,7 +5425,7 @@
         <v>46240</v>
       </c>
       <c r="H118">
-        <v>2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.2">
@@ -5259,22 +5433,22 @@
         <v>0</v>
       </c>
       <c r="B119" t="s">
+        <v>200</v>
+      </c>
+      <c r="C119">
+        <v>1</v>
+      </c>
+      <c r="D119" t="s">
+        <v>2</v>
+      </c>
+      <c r="E119" t="s">
         <v>201</v>
-      </c>
-      <c r="C119">
-        <v>1</v>
-      </c>
-      <c r="D119" t="s">
-        <v>2</v>
-      </c>
-      <c r="E119" t="s">
-        <v>202</v>
       </c>
       <c r="F119" s="1">
         <v>46239</v>
       </c>
       <c r="G119" s="1">
-        <v>46241</v>
+        <v>46240</v>
       </c>
       <c r="H119">
         <v>2</v>
@@ -5285,25 +5459,25 @@
         <v>0</v>
       </c>
       <c r="B120" t="s">
+        <v>202</v>
+      </c>
+      <c r="C120">
+        <v>1</v>
+      </c>
+      <c r="D120" t="s">
+        <v>2</v>
+      </c>
+      <c r="E120" t="s">
         <v>203</v>
-      </c>
-      <c r="C120">
-        <v>1</v>
-      </c>
-      <c r="D120" t="s">
-        <v>12</v>
-      </c>
-      <c r="E120" t="s">
-        <v>23</v>
       </c>
       <c r="F120" s="1">
         <v>46239</v>
       </c>
       <c r="G120" s="1">
-        <v>46252</v>
+        <v>46241</v>
       </c>
       <c r="H120">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.2">
@@ -5317,19 +5491,19 @@
         <v>1</v>
       </c>
       <c r="D121" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E121" t="s">
-        <v>120</v>
+        <v>23</v>
       </c>
       <c r="F121" s="1">
-        <v>46240</v>
+        <v>46239</v>
       </c>
       <c r="G121" s="1">
-        <v>46244</v>
+        <v>46252</v>
       </c>
       <c r="H121">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.2">
@@ -5340,22 +5514,22 @@
         <v>205</v>
       </c>
       <c r="C122">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D122" t="s">
         <v>2</v>
       </c>
       <c r="E122" t="s">
-        <v>27</v>
+        <v>120</v>
       </c>
       <c r="F122" s="1">
         <v>46240</v>
       </c>
       <c r="G122" s="1">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="H122">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.2">
@@ -5366,10 +5540,10 @@
         <v>206</v>
       </c>
       <c r="C123">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D123" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E123" t="s">
         <v>27</v>
@@ -5378,10 +5552,10 @@
         <v>46240</v>
       </c>
       <c r="G123" s="1">
-        <v>46252</v>
+        <v>46241</v>
       </c>
       <c r="H123">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.2">
@@ -5395,7 +5569,7 @@
         <v>1</v>
       </c>
       <c r="D124" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E124" t="s">
         <v>27</v>
@@ -5407,7 +5581,7 @@
         <v>46252</v>
       </c>
       <c r="H124">
-        <v>0</v>
+        <v>39</v>
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.2">
@@ -5421,7 +5595,7 @@
         <v>1</v>
       </c>
       <c r="D125" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E125" t="s">
         <v>27</v>
@@ -5433,7 +5607,7 @@
         <v>46252</v>
       </c>
       <c r="H125">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.2">
@@ -5447,7 +5621,7 @@
         <v>1</v>
       </c>
       <c r="D126" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E126" t="s">
         <v>27</v>
@@ -5456,10 +5630,10 @@
         <v>46240</v>
       </c>
       <c r="G126" s="1">
-        <v>46240</v>
+        <v>46252</v>
       </c>
       <c r="H126">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.2">
@@ -5473,7 +5647,7 @@
         <v>1</v>
       </c>
       <c r="D127" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E127" t="s">
         <v>27</v>
@@ -5482,10 +5656,10 @@
         <v>46240</v>
       </c>
       <c r="G127" s="1">
-        <v>46252</v>
+        <v>46240</v>
       </c>
       <c r="H127">
-        <v>0</v>
+        <v>24</v>
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.2">
@@ -5499,7 +5673,7 @@
         <v>1</v>
       </c>
       <c r="D128" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E128" t="s">
         <v>27</v>
@@ -5511,7 +5685,7 @@
         <v>46252</v>
       </c>
       <c r="H128">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.2">
@@ -5525,7 +5699,7 @@
         <v>1</v>
       </c>
       <c r="D129" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E129" t="s">
         <v>27</v>
@@ -5537,7 +5711,7 @@
         <v>46252</v>
       </c>
       <c r="H129">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.2">
@@ -5551,7 +5725,7 @@
         <v>1</v>
       </c>
       <c r="D130" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E130" t="s">
         <v>27</v>
@@ -5563,7 +5737,7 @@
         <v>46252</v>
       </c>
       <c r="H130">
-        <v>0</v>
+        <v>19</v>
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.2">
@@ -5577,7 +5751,7 @@
         <v>1</v>
       </c>
       <c r="D131" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E131" t="s">
         <v>27</v>
@@ -5589,7 +5763,7 @@
         <v>46252</v>
       </c>
       <c r="H131">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.2">
@@ -5603,7 +5777,7 @@
         <v>1</v>
       </c>
       <c r="D132" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E132" t="s">
         <v>27</v>
@@ -5615,7 +5789,7 @@
         <v>46252</v>
       </c>
       <c r="H132">
-        <v>0</v>
+        <v>19</v>
       </c>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.2">
@@ -5655,10 +5829,10 @@
         <v>1</v>
       </c>
       <c r="D134" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E134" t="s">
-        <v>218</v>
+        <v>27</v>
       </c>
       <c r="F134" s="1">
         <v>46240</v>
@@ -5667,7 +5841,7 @@
         <v>46252</v>
       </c>
       <c r="H134">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.2">
@@ -5675,25 +5849,25 @@
         <v>0</v>
       </c>
       <c r="B135" t="s">
+        <v>218</v>
+      </c>
+      <c r="C135">
+        <v>1</v>
+      </c>
+      <c r="D135" t="s">
+        <v>12</v>
+      </c>
+      <c r="E135" t="s">
         <v>219</v>
-      </c>
-      <c r="C135">
-        <v>1</v>
-      </c>
-      <c r="D135" t="s">
-        <v>2</v>
-      </c>
-      <c r="E135" t="s">
-        <v>220</v>
       </c>
       <c r="F135" s="1">
         <v>46240</v>
       </c>
       <c r="G135" s="1">
-        <v>46241</v>
+        <v>46252</v>
       </c>
       <c r="H135">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.2">
@@ -5701,25 +5875,25 @@
         <v>0</v>
       </c>
       <c r="B136" t="s">
+        <v>220</v>
+      </c>
+      <c r="C136">
+        <v>1</v>
+      </c>
+      <c r="D136" t="s">
+        <v>2</v>
+      </c>
+      <c r="E136" t="s">
         <v>221</v>
       </c>
-      <c r="C136">
-        <v>1</v>
-      </c>
-      <c r="D136" t="s">
-        <v>12</v>
-      </c>
-      <c r="E136" t="s">
-        <v>27</v>
-      </c>
       <c r="F136" s="1">
+        <v>46240</v>
+      </c>
+      <c r="G136" s="1">
         <v>46241</v>
       </c>
-      <c r="G136" s="1">
-        <v>46252</v>
-      </c>
       <c r="H136">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.2">
@@ -5742,10 +5916,10 @@
         <v>46241</v>
       </c>
       <c r="G137" s="1">
-        <v>46241</v>
+        <v>46252</v>
       </c>
       <c r="H137">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.2">
@@ -5756,7 +5930,7 @@
         <v>223</v>
       </c>
       <c r="C138">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D138" t="s">
         <v>2</v>
@@ -5768,10 +5942,10 @@
         <v>46241</v>
       </c>
       <c r="G138" s="1">
-        <v>46245</v>
+        <v>46241</v>
       </c>
       <c r="H138">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.2">
@@ -5782,22 +5956,22 @@
         <v>224</v>
       </c>
       <c r="C139">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D139" t="s">
         <v>2</v>
       </c>
       <c r="E139" t="s">
-        <v>124</v>
+        <v>27</v>
       </c>
       <c r="F139" s="1">
         <v>46241</v>
       </c>
       <c r="G139" s="1">
-        <v>46241</v>
+        <v>46245</v>
       </c>
       <c r="H139">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.2">
@@ -5814,16 +5988,16 @@
         <v>2</v>
       </c>
       <c r="E140" t="s">
-        <v>226</v>
+        <v>124</v>
       </c>
       <c r="F140" s="1">
         <v>46241</v>
       </c>
       <c r="G140" s="1">
-        <v>46244</v>
+        <v>46241</v>
       </c>
       <c r="H140">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.2">
@@ -5831,22 +6005,22 @@
         <v>0</v>
       </c>
       <c r="B141" t="s">
+        <v>226</v>
+      </c>
+      <c r="C141">
+        <v>1</v>
+      </c>
+      <c r="D141" t="s">
+        <v>2</v>
+      </c>
+      <c r="E141" t="s">
         <v>227</v>
-      </c>
-      <c r="C141">
-        <v>1</v>
-      </c>
-      <c r="D141" t="s">
-        <v>2</v>
-      </c>
-      <c r="E141" t="s">
-        <v>124</v>
       </c>
       <c r="F141" s="1">
         <v>46241</v>
       </c>
       <c r="G141" s="1">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="H141">
         <v>2</v>
@@ -5866,13 +6040,13 @@
         <v>2</v>
       </c>
       <c r="E142" t="s">
-        <v>229</v>
+        <v>124</v>
       </c>
       <c r="F142" s="1">
         <v>46241</v>
       </c>
       <c r="G142" s="1">
-        <v>46244</v>
+        <v>46241</v>
       </c>
       <c r="H142">
         <v>2</v>
@@ -5883,25 +6057,25 @@
         <v>0</v>
       </c>
       <c r="B143" t="s">
+        <v>229</v>
+      </c>
+      <c r="C143">
+        <v>2</v>
+      </c>
+      <c r="D143" t="s">
+        <v>12</v>
+      </c>
+      <c r="E143" t="s">
         <v>230</v>
-      </c>
-      <c r="C143">
-        <v>1</v>
-      </c>
-      <c r="D143" t="s">
-        <v>2</v>
-      </c>
-      <c r="E143" t="s">
-        <v>231</v>
       </c>
       <c r="F143" s="1">
         <v>46241</v>
       </c>
       <c r="G143" s="1">
-        <v>46245</v>
+        <v>46252</v>
       </c>
       <c r="H143">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.2">
@@ -5909,25 +6083,25 @@
         <v>0</v>
       </c>
       <c r="B144" t="s">
+        <v>231</v>
+      </c>
+      <c r="C144">
+        <v>2</v>
+      </c>
+      <c r="D144" t="s">
         <v>232</v>
       </c>
-      <c r="C144">
-        <v>1</v>
-      </c>
-      <c r="D144" t="s">
-        <v>2</v>
-      </c>
       <c r="E144" t="s">
-        <v>27</v>
+        <v>233</v>
       </c>
       <c r="F144" s="1">
         <v>46241</v>
       </c>
       <c r="G144" s="1">
-        <v>46241</v>
+        <v>46252</v>
       </c>
       <c r="H144">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.2">
@@ -5935,7 +6109,7 @@
         <v>0</v>
       </c>
       <c r="B145" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C145">
         <v>1</v>
@@ -5961,7 +6135,7 @@
         <v>0</v>
       </c>
       <c r="B146" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C146">
         <v>1</v>
@@ -5970,16 +6144,16 @@
         <v>2</v>
       </c>
       <c r="E146" t="s">
-        <v>130</v>
+        <v>27</v>
       </c>
       <c r="F146" s="1">
         <v>46241</v>
       </c>
       <c r="G146" s="1">
-        <v>46245</v>
+        <v>46241</v>
       </c>
       <c r="H146">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.2">
@@ -5987,7 +6161,7 @@
         <v>0</v>
       </c>
       <c r="B147" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C147">
         <v>1</v>
@@ -5996,16 +6170,16 @@
         <v>2</v>
       </c>
       <c r="E147" t="s">
-        <v>236</v>
+        <v>130</v>
       </c>
       <c r="F147" s="1">
         <v>46241</v>
       </c>
       <c r="G147" s="1">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="H147">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.2">
@@ -6025,13 +6199,13 @@
         <v>238</v>
       </c>
       <c r="F148" s="1">
-        <v>46242</v>
+        <v>46241</v>
       </c>
       <c r="G148" s="1">
         <v>46244</v>
       </c>
       <c r="H148">
-        <v>2</v>
+        <v>21</v>
       </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.2">
@@ -6045,19 +6219,19 @@
         <v>1</v>
       </c>
       <c r="D149" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E149" t="s">
         <v>240</v>
       </c>
       <c r="F149" s="1">
+        <v>46242</v>
+      </c>
+      <c r="G149" s="1">
         <v>46244</v>
       </c>
-      <c r="G149" s="1">
-        <v>46252</v>
-      </c>
       <c r="H149">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.2">
@@ -6071,7 +6245,7 @@
         <v>1</v>
       </c>
       <c r="D150" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E150" t="s">
         <v>242</v>
@@ -6080,10 +6254,10 @@
         <v>46244</v>
       </c>
       <c r="G150" s="1">
-        <v>46244</v>
+        <v>46252</v>
       </c>
       <c r="H150">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.2">
@@ -6100,7 +6274,7 @@
         <v>2</v>
       </c>
       <c r="E151" t="s">
-        <v>27</v>
+        <v>244</v>
       </c>
       <c r="F151" s="1">
         <v>46244</v>
@@ -6109,7 +6283,7 @@
         <v>46244</v>
       </c>
       <c r="H151">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.2">
@@ -6117,25 +6291,25 @@
         <v>0</v>
       </c>
       <c r="B152" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C152">
         <v>1</v>
       </c>
       <c r="D152" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E152" t="s">
-        <v>27</v>
+        <v>246</v>
       </c>
       <c r="F152" s="1">
         <v>46244</v>
       </c>
       <c r="G152" s="1">
-        <v>46244</v>
+        <v>46252</v>
       </c>
       <c r="H152">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.2">
@@ -6143,16 +6317,16 @@
         <v>0</v>
       </c>
       <c r="B153" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C153">
         <v>1</v>
       </c>
       <c r="D153" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E153" t="s">
-        <v>112</v>
+        <v>27</v>
       </c>
       <c r="F153" s="1">
         <v>46244</v>
@@ -6161,7 +6335,7 @@
         <v>46244</v>
       </c>
       <c r="H153">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.2">
@@ -6169,7 +6343,7 @@
         <v>0</v>
       </c>
       <c r="B154" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="C154">
         <v>1</v>
@@ -6178,16 +6352,16 @@
         <v>2</v>
       </c>
       <c r="E154" t="s">
-        <v>247</v>
+        <v>27</v>
       </c>
       <c r="F154" s="1">
         <v>46244</v>
       </c>
       <c r="G154" s="1">
-        <v>46246</v>
+        <v>46244</v>
       </c>
       <c r="H154">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.2">
@@ -6195,25 +6369,25 @@
         <v>0</v>
       </c>
       <c r="B155" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C155">
         <v>1</v>
       </c>
       <c r="D155" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E155" t="s">
-        <v>249</v>
+        <v>112</v>
       </c>
       <c r="F155" s="1">
         <v>46244</v>
       </c>
       <c r="G155" s="1">
-        <v>46245</v>
+        <v>46244</v>
       </c>
       <c r="H155">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.2">
@@ -6227,19 +6401,19 @@
         <v>1</v>
       </c>
       <c r="D156" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E156" t="s">
-        <v>61</v>
+        <v>251</v>
       </c>
       <c r="F156" s="1">
-        <v>46245</v>
+        <v>46244</v>
       </c>
       <c r="G156" s="1">
-        <v>46252</v>
+        <v>46246</v>
       </c>
       <c r="H156">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.2">
@@ -6247,25 +6421,25 @@
         <v>0</v>
       </c>
       <c r="B157" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C157">
         <v>1</v>
       </c>
       <c r="D157" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E157" t="s">
-        <v>61</v>
+        <v>253</v>
       </c>
       <c r="F157" s="1">
+        <v>46244</v>
+      </c>
+      <c r="G157" s="1">
         <v>46245</v>
       </c>
-      <c r="G157" s="1">
-        <v>46252</v>
-      </c>
       <c r="H157">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.2">
@@ -6273,25 +6447,25 @@
         <v>0</v>
       </c>
       <c r="B158" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C158">
         <v>1</v>
       </c>
       <c r="D158" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E158" t="s">
-        <v>253</v>
+        <v>61</v>
       </c>
       <c r="F158" s="1">
         <v>46245</v>
       </c>
       <c r="G158" s="1">
-        <v>46247</v>
+        <v>46252</v>
       </c>
       <c r="H158">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.2">
@@ -6299,7 +6473,7 @@
         <v>0</v>
       </c>
       <c r="B159" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C159">
         <v>1</v>
@@ -6308,7 +6482,7 @@
         <v>12</v>
       </c>
       <c r="E159" t="s">
-        <v>255</v>
+        <v>61</v>
       </c>
       <c r="F159" s="1">
         <v>46245</v>
@@ -6331,7 +6505,7 @@
         <v>1</v>
       </c>
       <c r="D160" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E160" t="s">
         <v>257</v>
@@ -6340,10 +6514,10 @@
         <v>46245</v>
       </c>
       <c r="G160" s="1">
-        <v>46252</v>
+        <v>46247</v>
       </c>
       <c r="H160">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.2">
@@ -6357,16 +6531,16 @@
         <v>1</v>
       </c>
       <c r="D161" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E161" t="s">
-        <v>85</v>
+        <v>259</v>
       </c>
       <c r="F161" s="1">
         <v>46245</v>
       </c>
       <c r="G161" s="1">
-        <v>46246</v>
+        <v>46252</v>
       </c>
       <c r="H161">
         <v>0</v>
@@ -6377,22 +6551,22 @@
         <v>0</v>
       </c>
       <c r="B162" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C162">
         <v>1</v>
       </c>
       <c r="D162" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E162" t="s">
-        <v>85</v>
+        <v>261</v>
       </c>
       <c r="F162" s="1">
         <v>46245</v>
       </c>
       <c r="G162" s="1">
-        <v>46245</v>
+        <v>46252</v>
       </c>
       <c r="H162">
         <v>0</v>
@@ -6403,7 +6577,7 @@
         <v>0</v>
       </c>
       <c r="B163" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="C163">
         <v>1</v>
@@ -6418,7 +6592,7 @@
         <v>46245</v>
       </c>
       <c r="G163" s="1">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="H163">
         <v>0</v>
@@ -6429,16 +6603,16 @@
         <v>0</v>
       </c>
       <c r="B164" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C164">
         <v>1</v>
       </c>
       <c r="D164" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E164" t="s">
-        <v>262</v>
+        <v>85</v>
       </c>
       <c r="F164" s="1">
         <v>46245</v>
@@ -6447,7 +6621,7 @@
         <v>46245</v>
       </c>
       <c r="H164">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.2">
@@ -6455,16 +6629,16 @@
         <v>0</v>
       </c>
       <c r="B165" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C165">
         <v>1</v>
       </c>
       <c r="D165" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E165" t="s">
-        <v>264</v>
+        <v>85</v>
       </c>
       <c r="F165" s="1">
         <v>46245</v>
@@ -6473,7 +6647,7 @@
         <v>46245</v>
       </c>
       <c r="H165">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.2">
@@ -6487,19 +6661,19 @@
         <v>1</v>
       </c>
       <c r="D166" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E166" t="s">
-        <v>264</v>
+        <v>39</v>
       </c>
       <c r="F166" s="1">
         <v>46245</v>
       </c>
       <c r="G166" s="1">
-        <v>46252</v>
+        <v>46246</v>
       </c>
       <c r="H166">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.2">
@@ -6516,7 +6690,7 @@
         <v>2</v>
       </c>
       <c r="E167" t="s">
-        <v>39</v>
+        <v>267</v>
       </c>
       <c r="F167" s="1">
         <v>46245</v>
@@ -6525,7 +6699,7 @@
         <v>46246</v>
       </c>
       <c r="H167">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="168" spans="1:8" x14ac:dyDescent="0.2">
@@ -6533,25 +6707,25 @@
         <v>0</v>
       </c>
       <c r="B168" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C168">
         <v>1</v>
       </c>
       <c r="D168" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E168" t="s">
-        <v>268</v>
+        <v>70</v>
       </c>
       <c r="F168" s="1">
         <v>46245</v>
       </c>
       <c r="G168" s="1">
-        <v>46246</v>
+        <v>46252</v>
       </c>
       <c r="H168">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.2">
@@ -6568,7 +6742,7 @@
         <v>12</v>
       </c>
       <c r="E169" t="s">
-        <v>70</v>
+        <v>270</v>
       </c>
       <c r="F169" s="1">
         <v>46245</v>
@@ -6585,7 +6759,7 @@
         <v>0</v>
       </c>
       <c r="B170" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C170">
         <v>1</v>
@@ -6594,7 +6768,7 @@
         <v>2</v>
       </c>
       <c r="E170" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F170" s="1">
         <v>46245</v>
@@ -6603,7 +6777,7 @@
         <v>46246</v>
       </c>
       <c r="H170">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.2">
@@ -6611,25 +6785,25 @@
         <v>0</v>
       </c>
       <c r="B171" t="s">
+        <v>273</v>
+      </c>
+      <c r="C171">
+        <v>1</v>
+      </c>
+      <c r="D171" t="s">
+        <v>2</v>
+      </c>
+      <c r="E171" t="s">
         <v>272</v>
-      </c>
-      <c r="C171">
-        <v>1</v>
-      </c>
-      <c r="D171" t="s">
-        <v>12</v>
-      </c>
-      <c r="E171" t="s">
-        <v>271</v>
       </c>
       <c r="F171" s="1">
         <v>46245</v>
       </c>
       <c r="G171" s="1">
-        <v>46252</v>
+        <v>46246</v>
       </c>
       <c r="H171">
-        <v>0</v>
+        <v>22</v>
       </c>
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.2">
@@ -6637,25 +6811,25 @@
         <v>0</v>
       </c>
       <c r="B172" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C172">
         <v>1</v>
       </c>
       <c r="D172" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E172" t="s">
-        <v>274</v>
+        <v>70</v>
       </c>
       <c r="F172" s="1">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="G172" s="1">
-        <v>46246</v>
+        <v>46252</v>
       </c>
       <c r="H172">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.2">
@@ -6672,16 +6846,16 @@
         <v>2</v>
       </c>
       <c r="E173" t="s">
-        <v>274</v>
+        <v>27</v>
       </c>
       <c r="F173" s="1">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="G173" s="1">
         <v>46246</v>
       </c>
       <c r="H173">
-        <v>22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="174" spans="1:8" x14ac:dyDescent="0.2">
@@ -6698,7 +6872,7 @@
         <v>12</v>
       </c>
       <c r="E174" t="s">
-        <v>70</v>
+        <v>27</v>
       </c>
       <c r="F174" s="1">
         <v>46246</v>
@@ -6721,19 +6895,19 @@
         <v>1</v>
       </c>
       <c r="D175" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E175" t="s">
-        <v>27</v>
+        <v>197</v>
       </c>
       <c r="F175" s="1">
         <v>46246</v>
       </c>
       <c r="G175" s="1">
-        <v>46246</v>
+        <v>46252</v>
       </c>
       <c r="H175">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="176" spans="1:8" x14ac:dyDescent="0.2">
@@ -6747,19 +6921,19 @@
         <v>1</v>
       </c>
       <c r="D176" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E176" t="s">
-        <v>27</v>
+        <v>66</v>
       </c>
       <c r="F176" s="1">
         <v>46246</v>
       </c>
       <c r="G176" s="1">
-        <v>46252</v>
+        <v>46247</v>
       </c>
       <c r="H176">
-        <v>0</v>
+        <v>21</v>
       </c>
     </row>
     <row r="177" spans="1:8" x14ac:dyDescent="0.2">
@@ -6770,13 +6944,13 @@
         <v>279</v>
       </c>
       <c r="C177">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D177" t="s">
         <v>12</v>
       </c>
       <c r="E177" t="s">
-        <v>196</v>
+        <v>66</v>
       </c>
       <c r="F177" s="1">
         <v>46246</v>
@@ -6799,19 +6973,19 @@
         <v>1</v>
       </c>
       <c r="D178" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E178" t="s">
-        <v>66</v>
+        <v>281</v>
       </c>
       <c r="F178" s="1">
         <v>46246</v>
       </c>
       <c r="G178" s="1">
-        <v>46247</v>
+        <v>46252</v>
       </c>
       <c r="H178">
-        <v>21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="179" spans="1:8" x14ac:dyDescent="0.2">
@@ -6819,25 +6993,25 @@
         <v>0</v>
       </c>
       <c r="B179" t="s">
+        <v>282</v>
+      </c>
+      <c r="C179">
+        <v>1</v>
+      </c>
+      <c r="D179" t="s">
+        <v>12</v>
+      </c>
+      <c r="E179" t="s">
         <v>281</v>
-      </c>
-      <c r="C179">
-        <v>1</v>
-      </c>
-      <c r="D179" t="s">
-        <v>2</v>
-      </c>
-      <c r="E179" t="s">
-        <v>66</v>
       </c>
       <c r="F179" s="1">
         <v>46246</v>
       </c>
       <c r="G179" s="1">
-        <v>46247</v>
+        <v>46252</v>
       </c>
       <c r="H179">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="180" spans="1:8" x14ac:dyDescent="0.2">
@@ -6845,25 +7019,25 @@
         <v>0</v>
       </c>
       <c r="B180" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C180">
         <v>1</v>
       </c>
       <c r="D180" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E180" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F180" s="1">
         <v>46246</v>
       </c>
       <c r="G180" s="1">
-        <v>46249</v>
+        <v>46252</v>
       </c>
       <c r="H180">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="181" spans="1:8" x14ac:dyDescent="0.2">
@@ -6871,7 +7045,7 @@
         <v>0</v>
       </c>
       <c r="B181" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C181">
         <v>1</v>
@@ -6880,7 +7054,7 @@
         <v>12</v>
       </c>
       <c r="E181" t="s">
-        <v>285</v>
+        <v>233</v>
       </c>
       <c r="F181" s="1">
         <v>46246</v>
@@ -6903,7 +7077,7 @@
         <v>1</v>
       </c>
       <c r="D182" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E182" t="s">
         <v>287</v>
@@ -6912,10 +7086,10 @@
         <v>46246</v>
       </c>
       <c r="G182" s="1">
-        <v>46252</v>
+        <v>46247</v>
       </c>
       <c r="H182">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="183" spans="1:8" x14ac:dyDescent="0.2">
@@ -6932,7 +7106,7 @@
         <v>12</v>
       </c>
       <c r="E183" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="F183" s="1">
         <v>46246</v>
@@ -6949,25 +7123,25 @@
         <v>0</v>
       </c>
       <c r="B184" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C184">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D184" t="s">
         <v>2</v>
       </c>
       <c r="E184" t="s">
-        <v>290</v>
+        <v>104</v>
       </c>
       <c r="F184" s="1">
         <v>46246</v>
       </c>
       <c r="G184" s="1">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="H184">
-        <v>168</v>
+        <v>46</v>
       </c>
     </row>
     <row r="185" spans="1:8" x14ac:dyDescent="0.2">
@@ -6984,7 +7158,7 @@
         <v>12</v>
       </c>
       <c r="E185" t="s">
-        <v>292</v>
+        <v>233</v>
       </c>
       <c r="F185" s="1">
         <v>46246</v>
@@ -7001,25 +7175,25 @@
         <v>0</v>
       </c>
       <c r="B186" t="s">
+        <v>292</v>
+      </c>
+      <c r="C186">
+        <v>1</v>
+      </c>
+      <c r="D186" t="s">
+        <v>12</v>
+      </c>
+      <c r="E186" t="s">
         <v>293</v>
-      </c>
-      <c r="C186">
-        <v>1</v>
-      </c>
-      <c r="D186" t="s">
-        <v>2</v>
-      </c>
-      <c r="E186" t="s">
-        <v>294</v>
       </c>
       <c r="F186" s="1">
         <v>46246</v>
       </c>
       <c r="G186" s="1">
-        <v>46246</v>
+        <v>46252</v>
       </c>
       <c r="H186">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="187" spans="1:8" x14ac:dyDescent="0.2">
@@ -7027,25 +7201,25 @@
         <v>0</v>
       </c>
       <c r="B187" t="s">
+        <v>294</v>
+      </c>
+      <c r="C187">
+        <v>1</v>
+      </c>
+      <c r="D187" t="s">
+        <v>12</v>
+      </c>
+      <c r="E187" t="s">
         <v>295</v>
-      </c>
-      <c r="C187">
-        <v>1</v>
-      </c>
-      <c r="D187" t="s">
-        <v>2</v>
-      </c>
-      <c r="E187" t="s">
-        <v>294</v>
       </c>
       <c r="F187" s="1">
         <v>46246</v>
       </c>
       <c r="G187" s="1">
-        <v>46246</v>
+        <v>46252</v>
       </c>
       <c r="H187">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="188" spans="1:8" x14ac:dyDescent="0.2">
@@ -7062,7 +7236,7 @@
         <v>12</v>
       </c>
       <c r="E188" t="s">
-        <v>231</v>
+        <v>295</v>
       </c>
       <c r="F188" s="1">
         <v>46246</v>
@@ -7085,7 +7259,7 @@
         <v>1</v>
       </c>
       <c r="D189" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E189" t="s">
         <v>298</v>
@@ -7094,10 +7268,10 @@
         <v>46246</v>
       </c>
       <c r="G189" s="1">
-        <v>46247</v>
+        <v>46252</v>
       </c>
       <c r="H189">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="190" spans="1:8" x14ac:dyDescent="0.2">
@@ -7114,7 +7288,7 @@
         <v>12</v>
       </c>
       <c r="E190" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="F190" s="1">
         <v>46246</v>
@@ -7131,25 +7305,25 @@
         <v>0</v>
       </c>
       <c r="B191" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C191">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D191" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E191" t="s">
-        <v>104</v>
+        <v>70</v>
       </c>
       <c r="F191" s="1">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="G191" s="1">
-        <v>46247</v>
+        <v>46252</v>
       </c>
       <c r="H191">
-        <v>46</v>
+        <v>0</v>
       </c>
     </row>
     <row r="192" spans="1:8" x14ac:dyDescent="0.2">
@@ -7157,7 +7331,7 @@
         <v>0</v>
       </c>
       <c r="B192" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C192">
         <v>1</v>
@@ -7166,10 +7340,10 @@
         <v>12</v>
       </c>
       <c r="E192" t="s">
-        <v>231</v>
+        <v>27</v>
       </c>
       <c r="F192" s="1">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="G192" s="1">
         <v>46252</v>
@@ -7183,7 +7357,7 @@
         <v>0</v>
       </c>
       <c r="B193" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C193">
         <v>1</v>
@@ -7192,10 +7366,10 @@
         <v>12</v>
       </c>
       <c r="E193" t="s">
-        <v>304</v>
+        <v>27</v>
       </c>
       <c r="F193" s="1">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="G193" s="1">
         <v>46252</v>
@@ -7209,7 +7383,7 @@
         <v>0</v>
       </c>
       <c r="B194" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C194">
         <v>1</v>
@@ -7218,10 +7392,10 @@
         <v>12</v>
       </c>
       <c r="E194" t="s">
-        <v>306</v>
+        <v>27</v>
       </c>
       <c r="F194" s="1">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="G194" s="1">
         <v>46252</v>
@@ -7235,7 +7409,7 @@
         <v>0</v>
       </c>
       <c r="B195" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="C195">
         <v>1</v>
@@ -7244,10 +7418,10 @@
         <v>12</v>
       </c>
       <c r="E195" t="s">
-        <v>306</v>
+        <v>27</v>
       </c>
       <c r="F195" s="1">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="G195" s="1">
         <v>46252</v>
@@ -7261,7 +7435,7 @@
         <v>0</v>
       </c>
       <c r="B196" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="C196">
         <v>1</v>
@@ -7270,10 +7444,10 @@
         <v>12</v>
       </c>
       <c r="E196" t="s">
-        <v>309</v>
+        <v>27</v>
       </c>
       <c r="F196" s="1">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="G196" s="1">
         <v>46252</v>
@@ -7287,7 +7461,7 @@
         <v>0</v>
       </c>
       <c r="B197" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="C197">
         <v>1</v>
@@ -7296,10 +7470,10 @@
         <v>12</v>
       </c>
       <c r="E197" t="s">
-        <v>309</v>
+        <v>27</v>
       </c>
       <c r="F197" s="1">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="G197" s="1">
         <v>46252</v>
@@ -7313,7 +7487,7 @@
         <v>0</v>
       </c>
       <c r="B198" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="C198">
         <v>1</v>
@@ -7322,7 +7496,7 @@
         <v>12</v>
       </c>
       <c r="E198" t="s">
-        <v>70</v>
+        <v>27</v>
       </c>
       <c r="F198" s="1">
         <v>46247</v>
@@ -7339,7 +7513,7 @@
         <v>0</v>
       </c>
       <c r="B199" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="C199">
         <v>1</v>
@@ -7365,10 +7539,10 @@
         <v>0</v>
       </c>
       <c r="B200" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="C200">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D200" t="s">
         <v>12</v>
@@ -7391,7 +7565,7 @@
         <v>0</v>
       </c>
       <c r="B201" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="C201">
         <v>1</v>
@@ -7417,7 +7591,7 @@
         <v>0</v>
       </c>
       <c r="B202" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="C202">
         <v>1</v>
@@ -7443,7 +7617,7 @@
         <v>0</v>
       </c>
       <c r="B203" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="C203">
         <v>1</v>
@@ -7452,7 +7626,7 @@
         <v>12</v>
       </c>
       <c r="E203" t="s">
-        <v>27</v>
+        <v>295</v>
       </c>
       <c r="F203" s="1">
         <v>46247</v>
@@ -7469,7 +7643,7 @@
         <v>0</v>
       </c>
       <c r="B204" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="C204">
         <v>1</v>
@@ -7478,7 +7652,7 @@
         <v>12</v>
       </c>
       <c r="E204" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F204" s="1">
         <v>46247</v>
@@ -7495,16 +7669,16 @@
         <v>0</v>
       </c>
       <c r="B205" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="C205">
         <v>1</v>
       </c>
       <c r="D205" t="s">
-        <v>12</v>
+        <v>68</v>
       </c>
       <c r="E205" t="s">
-        <v>27</v>
+        <v>315</v>
       </c>
       <c r="F205" s="1">
         <v>46247</v>
@@ -7513,7 +7687,7 @@
         <v>46252</v>
       </c>
       <c r="H205">
-        <v>0</v>
+        <v>36</v>
       </c>
     </row>
     <row r="206" spans="1:8" x14ac:dyDescent="0.2">
@@ -7521,7 +7695,7 @@
         <v>0</v>
       </c>
       <c r="B206" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="C206">
         <v>1</v>
@@ -7530,7 +7704,7 @@
         <v>12</v>
       </c>
       <c r="E206" t="s">
-        <v>27</v>
+        <v>66</v>
       </c>
       <c r="F206" s="1">
         <v>46247</v>
@@ -7547,16 +7721,16 @@
         <v>0</v>
       </c>
       <c r="B207" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="C207">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D207" t="s">
         <v>12</v>
       </c>
       <c r="E207" t="s">
-        <v>27</v>
+        <v>134</v>
       </c>
       <c r="F207" s="1">
         <v>46247</v>
@@ -7573,7 +7747,7 @@
         <v>0</v>
       </c>
       <c r="B208" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="C208">
         <v>1</v>
@@ -7582,7 +7756,7 @@
         <v>12</v>
       </c>
       <c r="E208" t="s">
-        <v>27</v>
+        <v>244</v>
       </c>
       <c r="F208" s="1">
         <v>46247</v>
@@ -7599,7 +7773,7 @@
         <v>0</v>
       </c>
       <c r="B209" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="C209">
         <v>1</v>
@@ -7608,7 +7782,7 @@
         <v>12</v>
       </c>
       <c r="E209" t="s">
-        <v>27</v>
+        <v>320</v>
       </c>
       <c r="F209" s="1">
         <v>46247</v>
@@ -7625,7 +7799,7 @@
         <v>0</v>
       </c>
       <c r="B210" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C210">
         <v>1</v>
@@ -7634,7 +7808,7 @@
         <v>12</v>
       </c>
       <c r="E210" t="s">
-        <v>306</v>
+        <v>322</v>
       </c>
       <c r="F210" s="1">
         <v>46247</v>
@@ -7651,16 +7825,16 @@
         <v>0</v>
       </c>
       <c r="B211" t="s">
+        <v>323</v>
+      </c>
+      <c r="C211">
+        <v>1</v>
+      </c>
+      <c r="D211" t="s">
+        <v>12</v>
+      </c>
+      <c r="E211" t="s">
         <v>324</v>
-      </c>
-      <c r="C211">
-        <v>1</v>
-      </c>
-      <c r="D211" t="s">
-        <v>12</v>
-      </c>
-      <c r="E211" t="s">
-        <v>30</v>
       </c>
       <c r="F211" s="1">
         <v>46247</v>
@@ -7683,7 +7857,7 @@
         <v>1</v>
       </c>
       <c r="D212" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E212" t="s">
         <v>326</v>
@@ -7695,7 +7869,7 @@
         <v>46247</v>
       </c>
       <c r="H212">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="213" spans="1:8" x14ac:dyDescent="0.2">
@@ -7709,7 +7883,7 @@
         <v>1</v>
       </c>
       <c r="D213" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E213" t="s">
         <v>328</v>
@@ -7718,10 +7892,10 @@
         <v>46247</v>
       </c>
       <c r="G213" s="1">
-        <v>46247</v>
+        <v>46252</v>
       </c>
       <c r="H213">
-        <v>75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="214" spans="1:8" x14ac:dyDescent="0.2">
@@ -7732,13 +7906,13 @@
         <v>329</v>
       </c>
       <c r="C214">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D214" t="s">
         <v>12</v>
       </c>
       <c r="E214" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="F214" s="1">
         <v>46247</v>
@@ -7755,16 +7929,16 @@
         <v>0</v>
       </c>
       <c r="B215" t="s">
+        <v>331</v>
+      </c>
+      <c r="C215">
+        <v>1</v>
+      </c>
+      <c r="D215" t="s">
+        <v>12</v>
+      </c>
+      <c r="E215" t="s">
         <v>330</v>
-      </c>
-      <c r="C215">
-        <v>1</v>
-      </c>
-      <c r="D215" t="s">
-        <v>12</v>
-      </c>
-      <c r="E215" t="s">
-        <v>66</v>
       </c>
       <c r="F215" s="1">
         <v>46247</v>
@@ -7781,7 +7955,7 @@
         <v>0</v>
       </c>
       <c r="B216" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C216">
         <v>1</v>
@@ -7790,7 +7964,7 @@
         <v>12</v>
       </c>
       <c r="E216" t="s">
-        <v>134</v>
+        <v>66</v>
       </c>
       <c r="F216" s="1">
         <v>46247</v>
@@ -7807,7 +7981,7 @@
         <v>0</v>
       </c>
       <c r="B217" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C217">
         <v>1</v>
@@ -7816,7 +7990,7 @@
         <v>12</v>
       </c>
       <c r="E217" t="s">
-        <v>242</v>
+        <v>334</v>
       </c>
       <c r="F217" s="1">
         <v>46247</v>
@@ -7833,25 +8007,25 @@
         <v>0</v>
       </c>
       <c r="B218" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="C218">
         <v>1</v>
       </c>
       <c r="D218" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E218" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="F218" s="1">
         <v>46247</v>
       </c>
       <c r="G218" s="1">
-        <v>46247</v>
+        <v>46252</v>
       </c>
       <c r="H218">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="219" spans="1:8" x14ac:dyDescent="0.2">
@@ -7859,16 +8033,16 @@
         <v>0</v>
       </c>
       <c r="B219" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C219">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D219" t="s">
         <v>12</v>
       </c>
       <c r="E219" t="s">
-        <v>336</v>
+        <v>145</v>
       </c>
       <c r="F219" s="1">
         <v>46247</v>
@@ -7885,25 +8059,25 @@
         <v>0</v>
       </c>
       <c r="B220" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C220">
         <v>1</v>
       </c>
       <c r="D220" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E220" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F220" s="1">
         <v>46247</v>
       </c>
       <c r="G220" s="1">
-        <v>46247</v>
+        <v>46252</v>
       </c>
       <c r="H220">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="221" spans="1:8" x14ac:dyDescent="0.2">
@@ -7911,7 +8085,7 @@
         <v>0</v>
       </c>
       <c r="B221" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C221">
         <v>1</v>
@@ -7920,7 +8094,7 @@
         <v>12</v>
       </c>
       <c r="E221" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="F221" s="1">
         <v>46247</v>
@@ -7937,7 +8111,7 @@
         <v>0</v>
       </c>
       <c r="B222" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C222">
         <v>1</v>
@@ -7946,7 +8120,7 @@
         <v>12</v>
       </c>
       <c r="E222" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="F222" s="1">
         <v>46247</v>
@@ -7963,22 +8137,22 @@
         <v>0</v>
       </c>
       <c r="B223" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C223">
         <v>1</v>
       </c>
       <c r="D223" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E223" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="F223" s="1">
         <v>46247</v>
       </c>
       <c r="G223" s="1">
-        <v>46247</v>
+        <v>46252</v>
       </c>
       <c r="H223">
         <v>0</v>
@@ -7989,16 +8163,16 @@
         <v>0</v>
       </c>
       <c r="B224" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C224">
         <v>1</v>
       </c>
       <c r="D224" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E224" t="s">
-        <v>346</v>
+        <v>173</v>
       </c>
       <c r="F224" s="1">
         <v>46247</v>
@@ -8007,7 +8181,7 @@
         <v>46252</v>
       </c>
       <c r="H224">
-        <v>0</v>
+        <v>32</v>
       </c>
     </row>
     <row r="225" spans="1:8" x14ac:dyDescent="0.2">
@@ -8030,10 +8204,10 @@
         <v>46247</v>
       </c>
       <c r="G225" s="1">
-        <v>46249</v>
+        <v>46252</v>
       </c>
       <c r="H225">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="226" spans="1:8" x14ac:dyDescent="0.2">
@@ -8044,13 +8218,13 @@
         <v>349</v>
       </c>
       <c r="C226">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D226" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E226" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="F226" s="1">
         <v>46247</v>
@@ -8059,7 +8233,7 @@
         <v>46252</v>
       </c>
       <c r="H226">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="227" spans="1:8" x14ac:dyDescent="0.2">
@@ -8067,7 +8241,7 @@
         <v>0</v>
       </c>
       <c r="B227" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C227">
         <v>1</v>
@@ -8076,7 +8250,7 @@
         <v>12</v>
       </c>
       <c r="E227" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="F227" s="1">
         <v>46247</v>
@@ -8093,16 +8267,16 @@
         <v>0</v>
       </c>
       <c r="B228" t="s">
+        <v>351</v>
+      </c>
+      <c r="C228">
+        <v>1</v>
+      </c>
+      <c r="D228" t="s">
+        <v>12</v>
+      </c>
+      <c r="E228" t="s">
         <v>352</v>
-      </c>
-      <c r="C228">
-        <v>1</v>
-      </c>
-      <c r="D228" t="s">
-        <v>12</v>
-      </c>
-      <c r="E228" t="s">
-        <v>66</v>
       </c>
       <c r="F228" s="1">
         <v>46247</v>
@@ -8151,19 +8325,19 @@
         <v>1</v>
       </c>
       <c r="D230" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E230" t="s">
-        <v>356</v>
+        <v>326</v>
       </c>
       <c r="F230" s="1">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="G230" s="1">
         <v>46252</v>
       </c>
       <c r="H230">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="231" spans="1:8" x14ac:dyDescent="0.2">
@@ -8171,19 +8345,19 @@
         <v>0</v>
       </c>
       <c r="B231" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C231">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D231" t="s">
         <v>12</v>
       </c>
       <c r="E231" t="s">
-        <v>145</v>
+        <v>27</v>
       </c>
       <c r="F231" s="1">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="G231" s="1">
         <v>46252</v>
@@ -8197,19 +8371,19 @@
         <v>0</v>
       </c>
       <c r="B232" t="s">
+        <v>357</v>
+      </c>
+      <c r="C232">
+        <v>1</v>
+      </c>
+      <c r="D232" t="s">
+        <v>12</v>
+      </c>
+      <c r="E232" t="s">
         <v>358</v>
       </c>
-      <c r="C232">
-        <v>1</v>
-      </c>
-      <c r="D232" t="s">
-        <v>12</v>
-      </c>
-      <c r="E232" t="s">
-        <v>359</v>
-      </c>
       <c r="F232" s="1">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="G232" s="1">
         <v>46252</v>
@@ -8223,25 +8397,25 @@
         <v>0</v>
       </c>
       <c r="B233" t="s">
+        <v>359</v>
+      </c>
+      <c r="C233">
+        <v>1</v>
+      </c>
+      <c r="D233" t="s">
+        <v>2</v>
+      </c>
+      <c r="E233" t="s">
         <v>360</v>
       </c>
-      <c r="C233">
-        <v>1</v>
-      </c>
-      <c r="D233" t="s">
-        <v>12</v>
-      </c>
-      <c r="E233" t="s">
-        <v>262</v>
-      </c>
       <c r="F233" s="1">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="G233" s="1">
         <v>46252</v>
       </c>
       <c r="H233">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="234" spans="1:8" x14ac:dyDescent="0.2">
@@ -8258,10 +8432,10 @@
         <v>12</v>
       </c>
       <c r="E234" t="s">
-        <v>362</v>
+        <v>70</v>
       </c>
       <c r="F234" s="1">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="G234" s="1">
         <v>46252</v>
@@ -8275,7 +8449,7 @@
         <v>0</v>
       </c>
       <c r="B235" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C235">
         <v>1</v>
@@ -8284,10 +8458,10 @@
         <v>12</v>
       </c>
       <c r="E235" t="s">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="F235" s="1">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="G235" s="1">
         <v>46252</v>
@@ -8301,7 +8475,7 @@
         <v>0</v>
       </c>
       <c r="B236" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C236">
         <v>1</v>
@@ -8310,10 +8484,10 @@
         <v>12</v>
       </c>
       <c r="E236" t="s">
-        <v>365</v>
+        <v>261</v>
       </c>
       <c r="F236" s="1">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="G236" s="1">
         <v>46252</v>
@@ -8327,7 +8501,7 @@
         <v>0</v>
       </c>
       <c r="B237" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C237">
         <v>1</v>
@@ -8336,10 +8510,10 @@
         <v>12</v>
       </c>
       <c r="E237" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="F237" s="1">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="G237" s="1">
         <v>46252</v>
@@ -8353,7 +8527,7 @@
         <v>0</v>
       </c>
       <c r="B238" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C238">
         <v>1</v>
@@ -8362,10 +8536,10 @@
         <v>12</v>
       </c>
       <c r="E238" t="s">
-        <v>173</v>
+        <v>367</v>
       </c>
       <c r="F238" s="1">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="G238" s="1">
         <v>46252</v>
@@ -8379,19 +8553,19 @@
         <v>0</v>
       </c>
       <c r="B239" t="s">
+        <v>368</v>
+      </c>
+      <c r="C239">
+        <v>1</v>
+      </c>
+      <c r="D239" t="s">
+        <v>12</v>
+      </c>
+      <c r="E239" t="s">
         <v>369</v>
       </c>
-      <c r="C239">
-        <v>1</v>
-      </c>
-      <c r="D239" t="s">
-        <v>12</v>
-      </c>
-      <c r="E239" t="s">
-        <v>370</v>
-      </c>
       <c r="F239" s="1">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="G239" s="1">
         <v>46252</v>
@@ -8405,25 +8579,25 @@
         <v>0</v>
       </c>
       <c r="B240" t="s">
+        <v>370</v>
+      </c>
+      <c r="C240">
+        <v>1</v>
+      </c>
+      <c r="D240" t="s">
+        <v>2</v>
+      </c>
+      <c r="E240" t="s">
         <v>371</v>
       </c>
-      <c r="C240">
-        <v>1</v>
-      </c>
-      <c r="D240" t="s">
-        <v>12</v>
-      </c>
-      <c r="E240" t="s">
-        <v>370</v>
-      </c>
       <c r="F240" s="1">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="G240" s="1">
         <v>46252</v>
       </c>
       <c r="H240">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="241" spans="1:8" x14ac:dyDescent="0.2">
@@ -8440,10 +8614,10 @@
         <v>12</v>
       </c>
       <c r="E241" t="s">
-        <v>370</v>
+        <v>345</v>
       </c>
       <c r="F241" s="1">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="G241" s="1">
         <v>46252</v>
@@ -8469,7 +8643,7 @@
         <v>374</v>
       </c>
       <c r="F242" s="1">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="G242" s="1">
         <v>46252</v>
@@ -8492,10 +8666,10 @@
         <v>12</v>
       </c>
       <c r="E243" t="s">
-        <v>376</v>
+        <v>39</v>
       </c>
       <c r="F243" s="1">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="G243" s="1">
         <v>46252</v>
@@ -8509,7 +8683,7 @@
         <v>0</v>
       </c>
       <c r="B244" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C244">
         <v>1</v>
@@ -8518,10 +8692,10 @@
         <v>12</v>
       </c>
       <c r="E244" t="s">
-        <v>378</v>
+        <v>3</v>
       </c>
       <c r="F244" s="1">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="G244" s="1">
         <v>46252</v>
@@ -8535,16 +8709,16 @@
         <v>0</v>
       </c>
       <c r="B245" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="C245">
         <v>1</v>
       </c>
       <c r="D245" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E245" t="s">
-        <v>344</v>
+        <v>378</v>
       </c>
       <c r="F245" s="1">
         <v>46248</v>
@@ -8553,7 +8727,7 @@
         <v>46252</v>
       </c>
       <c r="H245">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="246" spans="1:8" x14ac:dyDescent="0.2">
@@ -8561,16 +8735,16 @@
         <v>0</v>
       </c>
       <c r="B246" t="s">
+        <v>379</v>
+      </c>
+      <c r="C246">
+        <v>1</v>
+      </c>
+      <c r="D246" t="s">
+        <v>12</v>
+      </c>
+      <c r="E246" t="s">
         <v>380</v>
-      </c>
-      <c r="C246">
-        <v>1</v>
-      </c>
-      <c r="D246" t="s">
-        <v>12</v>
-      </c>
-      <c r="E246" t="s">
-        <v>27</v>
       </c>
       <c r="F246" s="1">
         <v>46248</v>
@@ -8648,7 +8822,7 @@
         <v>12</v>
       </c>
       <c r="E249" t="s">
-        <v>70</v>
+        <v>386</v>
       </c>
       <c r="F249" s="1">
         <v>46248</v>
@@ -8665,7 +8839,7 @@
         <v>0</v>
       </c>
       <c r="B250" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C250">
         <v>1</v>
@@ -8674,7 +8848,7 @@
         <v>12</v>
       </c>
       <c r="E250" t="s">
-        <v>257</v>
+        <v>388</v>
       </c>
       <c r="F250" s="1">
         <v>46248</v>
@@ -8691,16 +8865,16 @@
         <v>0</v>
       </c>
       <c r="B251" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="C251">
         <v>1</v>
       </c>
       <c r="D251" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E251" t="s">
-        <v>257</v>
+        <v>390</v>
       </c>
       <c r="F251" s="1">
         <v>46248</v>
@@ -8709,7 +8883,7 @@
         <v>46252</v>
       </c>
       <c r="H251">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="252" spans="1:8" x14ac:dyDescent="0.2">
@@ -8717,7 +8891,7 @@
         <v>0</v>
       </c>
       <c r="B252" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="C252">
         <v>1</v>
@@ -8726,7 +8900,7 @@
         <v>12</v>
       </c>
       <c r="E252" t="s">
-        <v>389</v>
+        <v>72</v>
       </c>
       <c r="F252" s="1">
         <v>46248</v>
@@ -8743,7 +8917,7 @@
         <v>0</v>
       </c>
       <c r="B253" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C253">
         <v>1</v>
@@ -8752,7 +8926,7 @@
         <v>12</v>
       </c>
       <c r="E253" t="s">
-        <v>391</v>
+        <v>72</v>
       </c>
       <c r="F253" s="1">
         <v>46248</v>
@@ -8769,7 +8943,7 @@
         <v>0</v>
       </c>
       <c r="B254" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C254">
         <v>1</v>
@@ -8778,7 +8952,7 @@
         <v>12</v>
       </c>
       <c r="E254" t="s">
-        <v>393</v>
+        <v>72</v>
       </c>
       <c r="F254" s="1">
         <v>46248</v>
@@ -8830,7 +9004,7 @@
         <v>12</v>
       </c>
       <c r="E256" t="s">
-        <v>367</v>
+        <v>397</v>
       </c>
       <c r="F256" s="1">
         <v>46248</v>
@@ -8847,7 +9021,7 @@
         <v>0</v>
       </c>
       <c r="B257" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C257">
         <v>1</v>
@@ -8856,7 +9030,7 @@
         <v>12</v>
       </c>
       <c r="E257" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="F257" s="1">
         <v>46248</v>
@@ -8873,7 +9047,7 @@
         <v>0</v>
       </c>
       <c r="B258" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C258">
         <v>1</v>
@@ -8882,7 +9056,7 @@
         <v>12</v>
       </c>
       <c r="E258" t="s">
-        <v>39</v>
+        <v>401</v>
       </c>
       <c r="F258" s="1">
         <v>46248</v>
@@ -8899,7 +9073,7 @@
         <v>0</v>
       </c>
       <c r="B259" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="C259">
         <v>1</v>
@@ -8908,7 +9082,7 @@
         <v>12</v>
       </c>
       <c r="E259" t="s">
-        <v>3</v>
+        <v>127</v>
       </c>
       <c r="F259" s="1">
         <v>46248</v>
@@ -8925,7 +9099,7 @@
         <v>0</v>
       </c>
       <c r="B260" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C260">
         <v>1</v>
@@ -8934,7 +9108,7 @@
         <v>12</v>
       </c>
       <c r="E260" t="s">
-        <v>402</v>
+        <v>127</v>
       </c>
       <c r="F260" s="1">
         <v>46248</v>
@@ -8951,7 +9125,7 @@
         <v>0</v>
       </c>
       <c r="B261" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C261">
         <v>1</v>
@@ -8960,7 +9134,7 @@
         <v>12</v>
       </c>
       <c r="E261" t="s">
-        <v>294</v>
+        <v>405</v>
       </c>
       <c r="F261" s="1">
         <v>46248</v>
@@ -8977,7 +9151,7 @@
         <v>0</v>
       </c>
       <c r="B262" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="C262">
         <v>1</v>
@@ -8986,7 +9160,7 @@
         <v>12</v>
       </c>
       <c r="E262" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="F262" s="1">
         <v>46248</v>
@@ -9003,7 +9177,7 @@
         <v>0</v>
       </c>
       <c r="B263" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C263">
         <v>1</v>
@@ -9012,7 +9186,7 @@
         <v>12</v>
       </c>
       <c r="E263" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="F263" s="1">
         <v>46248</v>
@@ -9029,7 +9203,7 @@
         <v>0</v>
       </c>
       <c r="B264" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="C264">
         <v>1</v>
@@ -9038,7 +9212,7 @@
         <v>12</v>
       </c>
       <c r="E264" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="F264" s="1">
         <v>46248</v>
@@ -9055,7 +9229,7 @@
         <v>0</v>
       </c>
       <c r="B265" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C265">
         <v>1</v>
@@ -9064,7 +9238,7 @@
         <v>12</v>
       </c>
       <c r="E265" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="F265" s="1">
         <v>46248</v>
@@ -9081,7 +9255,7 @@
         <v>0</v>
       </c>
       <c r="B266" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="C266">
         <v>1</v>
@@ -9090,7 +9264,7 @@
         <v>12</v>
       </c>
       <c r="E266" t="s">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="F266" s="1">
         <v>46248</v>
@@ -9107,7 +9281,7 @@
         <v>0</v>
       </c>
       <c r="B267" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="C267">
         <v>1</v>
@@ -9116,7 +9290,7 @@
         <v>12</v>
       </c>
       <c r="E267" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="F267" s="1">
         <v>46248</v>
@@ -9133,7 +9307,7 @@
         <v>0</v>
       </c>
       <c r="B268" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="C268">
         <v>1</v>
@@ -9142,7 +9316,7 @@
         <v>12</v>
       </c>
       <c r="E268" t="s">
-        <v>72</v>
+        <v>330</v>
       </c>
       <c r="F268" s="1">
         <v>46248</v>
@@ -9159,7 +9333,7 @@
         <v>0</v>
       </c>
       <c r="B269" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="C269">
         <v>1</v>
@@ -9168,7 +9342,7 @@
         <v>12</v>
       </c>
       <c r="E269" t="s">
-        <v>72</v>
+        <v>419</v>
       </c>
       <c r="F269" s="1">
         <v>46248</v>
@@ -9185,16 +9359,16 @@
         <v>0</v>
       </c>
       <c r="B270" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="C270">
         <v>1</v>
       </c>
       <c r="D270" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E270" t="s">
-        <v>72</v>
+        <v>145</v>
       </c>
       <c r="F270" s="1">
         <v>46248</v>
@@ -9203,7 +9377,7 @@
         <v>46252</v>
       </c>
       <c r="H270">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="271" spans="1:8" x14ac:dyDescent="0.2">
@@ -9211,7 +9385,7 @@
         <v>0</v>
       </c>
       <c r="B271" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="C271">
         <v>1</v>
@@ -9220,7 +9394,7 @@
         <v>12</v>
       </c>
       <c r="E271" t="s">
-        <v>419</v>
+        <v>85</v>
       </c>
       <c r="F271" s="1">
         <v>46248</v>
@@ -9237,7 +9411,7 @@
         <v>0</v>
       </c>
       <c r="B272" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="C272">
         <v>1</v>
@@ -9246,7 +9420,7 @@
         <v>12</v>
       </c>
       <c r="E272" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="F272" s="1">
         <v>46248</v>
@@ -9263,7 +9437,7 @@
         <v>0</v>
       </c>
       <c r="B273" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="C273">
         <v>1</v>
@@ -9272,7 +9446,7 @@
         <v>12</v>
       </c>
       <c r="E273" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="F273" s="1">
         <v>46248</v>
@@ -9289,16 +9463,16 @@
         <v>0</v>
       </c>
       <c r="B274" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="C274">
         <v>1</v>
       </c>
       <c r="D274" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E274" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="F274" s="1">
         <v>46248</v>
@@ -9307,7 +9481,7 @@
         <v>46252</v>
       </c>
       <c r="H274">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="275" spans="1:8" x14ac:dyDescent="0.2">
@@ -9315,7 +9489,7 @@
         <v>0</v>
       </c>
       <c r="B275" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="C275">
         <v>1</v>
@@ -9324,7 +9498,7 @@
         <v>12</v>
       </c>
       <c r="E275" t="s">
-        <v>427</v>
+        <v>358</v>
       </c>
       <c r="F275" s="1">
         <v>46248</v>
@@ -9341,7 +9515,7 @@
         <v>0</v>
       </c>
       <c r="B276" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C276">
         <v>1</v>
@@ -9350,7 +9524,7 @@
         <v>12</v>
       </c>
       <c r="E276" t="s">
-        <v>127</v>
+        <v>324</v>
       </c>
       <c r="F276" s="1">
         <v>46248</v>
@@ -9367,16 +9541,16 @@
         <v>0</v>
       </c>
       <c r="B277" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C277">
         <v>1</v>
       </c>
       <c r="D277" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E277" t="s">
-        <v>127</v>
+        <v>431</v>
       </c>
       <c r="F277" s="1">
         <v>46248</v>
@@ -9385,7 +9559,7 @@
         <v>46252</v>
       </c>
       <c r="H277">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="278" spans="1:8" x14ac:dyDescent="0.2">
@@ -9393,7 +9567,7 @@
         <v>0</v>
       </c>
       <c r="B278" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="C278">
         <v>1</v>
@@ -9402,7 +9576,7 @@
         <v>12</v>
       </c>
       <c r="E278" t="s">
-        <v>431</v>
+        <v>35</v>
       </c>
       <c r="F278" s="1">
         <v>46248</v>
@@ -9419,7 +9593,7 @@
         <v>0</v>
       </c>
       <c r="B279" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C279">
         <v>1</v>
@@ -9428,7 +9602,7 @@
         <v>12</v>
       </c>
       <c r="E279" t="s">
-        <v>433</v>
+        <v>35</v>
       </c>
       <c r="F279" s="1">
         <v>46248</v>
@@ -9480,7 +9654,7 @@
         <v>12</v>
       </c>
       <c r="E281" t="s">
-        <v>437</v>
+        <v>230</v>
       </c>
       <c r="F281" s="1">
         <v>46248</v>
@@ -9497,16 +9671,16 @@
         <v>0</v>
       </c>
       <c r="B282" t="s">
+        <v>437</v>
+      </c>
+      <c r="C282">
+        <v>1</v>
+      </c>
+      <c r="D282" t="s">
+        <v>12</v>
+      </c>
+      <c r="E282" t="s">
         <v>438</v>
-      </c>
-      <c r="C282">
-        <v>1</v>
-      </c>
-      <c r="D282" t="s">
-        <v>12</v>
-      </c>
-      <c r="E282" t="s">
-        <v>439</v>
       </c>
       <c r="F282" s="1">
         <v>46248</v>
@@ -9523,16 +9697,16 @@
         <v>0</v>
       </c>
       <c r="B283" t="s">
+        <v>439</v>
+      </c>
+      <c r="C283">
+        <v>1</v>
+      </c>
+      <c r="D283" t="s">
+        <v>12</v>
+      </c>
+      <c r="E283" t="s">
         <v>440</v>
-      </c>
-      <c r="C283">
-        <v>1</v>
-      </c>
-      <c r="D283" t="s">
-        <v>12</v>
-      </c>
-      <c r="E283" t="s">
-        <v>72</v>
       </c>
       <c r="F283" s="1">
         <v>46248</v>
@@ -9558,7 +9732,7 @@
         <v>12</v>
       </c>
       <c r="E284" t="s">
-        <v>442</v>
+        <v>21</v>
       </c>
       <c r="F284" s="1">
         <v>46248</v>
@@ -9575,7 +9749,7 @@
         <v>0</v>
       </c>
       <c r="B285" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C285">
         <v>1</v>
@@ -9584,7 +9758,7 @@
         <v>12</v>
       </c>
       <c r="E285" t="s">
-        <v>350</v>
+        <v>72</v>
       </c>
       <c r="F285" s="1">
         <v>46248</v>
@@ -9601,16 +9775,16 @@
         <v>0</v>
       </c>
       <c r="B286" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C286">
         <v>1</v>
       </c>
       <c r="D286" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E286" t="s">
-        <v>445</v>
+        <v>89</v>
       </c>
       <c r="F286" s="1">
         <v>46248</v>
@@ -9619,7 +9793,7 @@
         <v>46252</v>
       </c>
       <c r="H286">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="287" spans="1:8" x14ac:dyDescent="0.2">
@@ -9627,7 +9801,7 @@
         <v>0</v>
       </c>
       <c r="B287" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="C287">
         <v>1</v>
@@ -9636,7 +9810,7 @@
         <v>12</v>
       </c>
       <c r="E287" t="s">
-        <v>145</v>
+        <v>445</v>
       </c>
       <c r="F287" s="1">
         <v>46248</v>
@@ -9653,16 +9827,16 @@
         <v>0</v>
       </c>
       <c r="B288" t="s">
+        <v>446</v>
+      </c>
+      <c r="C288">
+        <v>1</v>
+      </c>
+      <c r="D288" t="s">
+        <v>12</v>
+      </c>
+      <c r="E288" t="s">
         <v>447</v>
-      </c>
-      <c r="C288">
-        <v>1</v>
-      </c>
-      <c r="D288" t="s">
-        <v>12</v>
-      </c>
-      <c r="E288" t="s">
-        <v>448</v>
       </c>
       <c r="F288" s="1">
         <v>46248</v>
@@ -9679,16 +9853,16 @@
         <v>0</v>
       </c>
       <c r="B289" t="s">
+        <v>448</v>
+      </c>
+      <c r="C289">
+        <v>1</v>
+      </c>
+      <c r="D289" t="s">
+        <v>12</v>
+      </c>
+      <c r="E289" t="s">
         <v>449</v>
-      </c>
-      <c r="C289">
-        <v>1</v>
-      </c>
-      <c r="D289" t="s">
-        <v>12</v>
-      </c>
-      <c r="E289" t="s">
-        <v>450</v>
       </c>
       <c r="F289" s="1">
         <v>46248</v>
@@ -9705,16 +9879,16 @@
         <v>0</v>
       </c>
       <c r="B290" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C290">
         <v>1</v>
       </c>
       <c r="D290" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E290" t="s">
-        <v>452</v>
+        <v>89</v>
       </c>
       <c r="F290" s="1">
         <v>46248</v>
@@ -9723,7 +9897,7 @@
         <v>46252</v>
       </c>
       <c r="H290">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="291" spans="1:8" x14ac:dyDescent="0.2">
@@ -9731,7 +9905,7 @@
         <v>0</v>
       </c>
       <c r="B291" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C291">
         <v>1</v>
@@ -9740,7 +9914,7 @@
         <v>12</v>
       </c>
       <c r="E291" t="s">
-        <v>382</v>
+        <v>449</v>
       </c>
       <c r="F291" s="1">
         <v>46248</v>
@@ -9757,16 +9931,16 @@
         <v>0</v>
       </c>
       <c r="B292" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="C292">
         <v>1</v>
       </c>
       <c r="D292" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E292" t="s">
-        <v>342</v>
+        <v>89</v>
       </c>
       <c r="F292" s="1">
         <v>46248</v>
@@ -9775,7 +9949,7 @@
         <v>46252</v>
       </c>
       <c r="H292">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="293" spans="1:8" x14ac:dyDescent="0.2">
@@ -9783,16 +9957,16 @@
         <v>0</v>
       </c>
       <c r="B293" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="C293">
         <v>1</v>
       </c>
       <c r="D293" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E293" t="s">
-        <v>456</v>
+        <v>89</v>
       </c>
       <c r="F293" s="1">
         <v>46248</v>
@@ -9801,7 +9975,7 @@
         <v>46252</v>
       </c>
       <c r="H293">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="294" spans="1:8" x14ac:dyDescent="0.2">
@@ -9809,16 +9983,16 @@
         <v>0</v>
       </c>
       <c r="B294" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="C294">
         <v>1</v>
       </c>
       <c r="D294" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E294" t="s">
-        <v>35</v>
+        <v>89</v>
       </c>
       <c r="F294" s="1">
         <v>46248</v>
@@ -9827,7 +10001,7 @@
         <v>46252</v>
       </c>
       <c r="H294">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="295" spans="1:8" x14ac:dyDescent="0.2">
@@ -9835,16 +10009,16 @@
         <v>0</v>
       </c>
       <c r="B295" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="C295">
         <v>1</v>
       </c>
       <c r="D295" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E295" t="s">
-        <v>459</v>
+        <v>89</v>
       </c>
       <c r="F295" s="1">
         <v>46248</v>
@@ -9853,7 +10027,7 @@
         <v>46252</v>
       </c>
       <c r="H295">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="296" spans="1:8" x14ac:dyDescent="0.2">
@@ -9861,16 +10035,16 @@
         <v>0</v>
       </c>
       <c r="B296" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="C296">
         <v>1</v>
       </c>
       <c r="D296" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E296" t="s">
-        <v>229</v>
+        <v>89</v>
       </c>
       <c r="F296" s="1">
         <v>46248</v>
@@ -9879,7 +10053,7 @@
         <v>46252</v>
       </c>
       <c r="H296">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="297" spans="1:8" x14ac:dyDescent="0.2">
@@ -9887,16 +10061,16 @@
         <v>0</v>
       </c>
       <c r="B297" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="C297">
         <v>1</v>
       </c>
       <c r="D297" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E297" t="s">
-        <v>462</v>
+        <v>89</v>
       </c>
       <c r="F297" s="1">
         <v>46248</v>
@@ -9905,7 +10079,7 @@
         <v>46252</v>
       </c>
       <c r="H297">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="298" spans="1:8" x14ac:dyDescent="0.2">
@@ -9913,16 +10087,16 @@
         <v>0</v>
       </c>
       <c r="B298" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
       <c r="C298">
         <v>1</v>
       </c>
       <c r="D298" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E298" t="s">
-        <v>464</v>
+        <v>89</v>
       </c>
       <c r="F298" s="1">
         <v>46248</v>
@@ -9931,7 +10105,7 @@
         <v>46252</v>
       </c>
       <c r="H298">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="299" spans="1:8" x14ac:dyDescent="0.2">
@@ -9939,16 +10113,16 @@
         <v>0</v>
       </c>
       <c r="B299" t="s">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="C299">
         <v>1</v>
       </c>
       <c r="D299" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E299" t="s">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="F299" s="1">
         <v>46248</v>
@@ -9957,7 +10131,7 @@
         <v>46252</v>
       </c>
       <c r="H299">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="300" spans="1:8" x14ac:dyDescent="0.2">
@@ -9965,16 +10139,16 @@
         <v>0</v>
       </c>
       <c r="B300" t="s">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="C300">
         <v>1</v>
       </c>
       <c r="D300" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E300" t="s">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="F300" s="1">
         <v>46248</v>
@@ -9983,7 +10157,7 @@
         <v>46252</v>
       </c>
       <c r="H300">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="301" spans="1:8" x14ac:dyDescent="0.2">
@@ -9991,13 +10165,13 @@
         <v>0</v>
       </c>
       <c r="B301" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="C301">
         <v>1</v>
       </c>
       <c r="D301" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E301" t="s">
         <v>89</v>
@@ -10009,7 +10183,7 @@
         <v>46252</v>
       </c>
       <c r="H301">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="302" spans="1:8" x14ac:dyDescent="0.2">
@@ -10017,16 +10191,16 @@
         <v>0</v>
       </c>
       <c r="B302" t="s">
-        <v>468</v>
+        <v>462</v>
       </c>
       <c r="C302">
         <v>1</v>
       </c>
       <c r="D302" t="s">
-        <v>12</v>
+        <v>232</v>
       </c>
       <c r="E302" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="F302" s="1">
         <v>46248</v>
@@ -10043,16 +10217,16 @@
         <v>0</v>
       </c>
       <c r="B303" t="s">
-        <v>470</v>
+        <v>464</v>
       </c>
       <c r="C303">
         <v>1</v>
       </c>
       <c r="D303" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E303" t="s">
-        <v>471</v>
+        <v>360</v>
       </c>
       <c r="F303" s="1">
         <v>46248</v>
@@ -10061,7 +10235,7 @@
         <v>46252</v>
       </c>
       <c r="H303">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="304" spans="1:8" x14ac:dyDescent="0.2">
@@ -10069,7 +10243,7 @@
         <v>0</v>
       </c>
       <c r="B304" t="s">
-        <v>472</v>
+        <v>465</v>
       </c>
       <c r="C304">
         <v>1</v>
@@ -10078,7 +10252,7 @@
         <v>12</v>
       </c>
       <c r="E304" t="s">
-        <v>473</v>
+        <v>117</v>
       </c>
       <c r="F304" s="1">
         <v>46248</v>
@@ -10095,7 +10269,7 @@
         <v>0</v>
       </c>
       <c r="B305" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="C305">
         <v>1</v>
@@ -10104,7 +10278,7 @@
         <v>12</v>
       </c>
       <c r="E305" t="s">
-        <v>89</v>
+        <v>467</v>
       </c>
       <c r="F305" s="1">
         <v>46248</v>
@@ -10121,7 +10295,7 @@
         <v>0</v>
       </c>
       <c r="B306" t="s">
-        <v>475</v>
+        <v>468</v>
       </c>
       <c r="C306">
         <v>1</v>
@@ -10130,7 +10304,7 @@
         <v>12</v>
       </c>
       <c r="E306" t="s">
-        <v>473</v>
+        <v>463</v>
       </c>
       <c r="F306" s="1">
         <v>46248</v>
@@ -10147,7 +10321,7 @@
         <v>0</v>
       </c>
       <c r="B307" t="s">
-        <v>476</v>
+        <v>469</v>
       </c>
       <c r="C307">
         <v>1</v>
@@ -10156,7 +10330,7 @@
         <v>12</v>
       </c>
       <c r="E307" t="s">
-        <v>89</v>
+        <v>470</v>
       </c>
       <c r="F307" s="1">
         <v>46248</v>
@@ -10173,7 +10347,7 @@
         <v>0</v>
       </c>
       <c r="B308" t="s">
-        <v>477</v>
+        <v>471</v>
       </c>
       <c r="C308">
         <v>1</v>
@@ -10182,7 +10356,7 @@
         <v>12</v>
       </c>
       <c r="E308" t="s">
-        <v>89</v>
+        <v>472</v>
       </c>
       <c r="F308" s="1">
         <v>46248</v>
@@ -10199,7 +10373,7 @@
         <v>0</v>
       </c>
       <c r="B309" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
       <c r="C309">
         <v>1</v>
@@ -10208,7 +10382,7 @@
         <v>12</v>
       </c>
       <c r="E309" t="s">
-        <v>89</v>
+        <v>474</v>
       </c>
       <c r="F309" s="1">
         <v>46248</v>
@@ -10225,7 +10399,7 @@
         <v>0</v>
       </c>
       <c r="B310" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="C310">
         <v>1</v>
@@ -10234,7 +10408,7 @@
         <v>12</v>
       </c>
       <c r="E310" t="s">
-        <v>89</v>
+        <v>476</v>
       </c>
       <c r="F310" s="1">
         <v>46248</v>
@@ -10251,7 +10425,7 @@
         <v>0</v>
       </c>
       <c r="B311" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="C311">
         <v>1</v>
@@ -10260,7 +10434,7 @@
         <v>12</v>
       </c>
       <c r="E311" t="s">
-        <v>89</v>
+        <v>145</v>
       </c>
       <c r="F311" s="1">
         <v>46248</v>
@@ -10277,7 +10451,7 @@
         <v>0</v>
       </c>
       <c r="B312" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="C312">
         <v>1</v>
@@ -10286,7 +10460,7 @@
         <v>12</v>
       </c>
       <c r="E312" t="s">
-        <v>89</v>
+        <v>476</v>
       </c>
       <c r="F312" s="1">
         <v>46248</v>
@@ -10303,7 +10477,7 @@
         <v>0</v>
       </c>
       <c r="B313" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="C313">
         <v>1</v>
@@ -10312,7 +10486,7 @@
         <v>12</v>
       </c>
       <c r="E313" t="s">
-        <v>89</v>
+        <v>476</v>
       </c>
       <c r="F313" s="1">
         <v>46248</v>
@@ -10329,7 +10503,7 @@
         <v>0</v>
       </c>
       <c r="B314" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="C314">
         <v>1</v>
@@ -10338,7 +10512,7 @@
         <v>12</v>
       </c>
       <c r="E314" t="s">
-        <v>89</v>
+        <v>481</v>
       </c>
       <c r="F314" s="1">
         <v>46248</v>
@@ -10355,7 +10529,7 @@
         <v>0</v>
       </c>
       <c r="B315" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="C315">
         <v>1</v>
@@ -10364,7 +10538,7 @@
         <v>12</v>
       </c>
       <c r="E315" t="s">
-        <v>89</v>
+        <v>476</v>
       </c>
       <c r="F315" s="1">
         <v>46248</v>
@@ -10381,7 +10555,7 @@
         <v>0</v>
       </c>
       <c r="B316" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="C316">
         <v>1</v>
@@ -10390,7 +10564,7 @@
         <v>12</v>
       </c>
       <c r="E316" t="s">
-        <v>89</v>
+        <v>476</v>
       </c>
       <c r="F316" s="1">
         <v>46248</v>
@@ -10407,7 +10581,7 @@
         <v>0</v>
       </c>
       <c r="B317" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="C317">
         <v>1</v>
@@ -10416,7 +10590,7 @@
         <v>12</v>
       </c>
       <c r="E317" t="s">
-        <v>89</v>
+        <v>159</v>
       </c>
       <c r="F317" s="1">
         <v>46248</v>
@@ -10433,7 +10607,7 @@
         <v>0</v>
       </c>
       <c r="B318" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="C318">
         <v>1</v>
@@ -10442,7 +10616,7 @@
         <v>12</v>
       </c>
       <c r="E318" t="s">
-        <v>89</v>
+        <v>486</v>
       </c>
       <c r="F318" s="1">
         <v>46248</v>
@@ -10459,16 +10633,16 @@
         <v>0</v>
       </c>
       <c r="B319" t="s">
+        <v>487</v>
+      </c>
+      <c r="C319">
+        <v>1</v>
+      </c>
+      <c r="D319" t="s">
+        <v>12</v>
+      </c>
+      <c r="E319" t="s">
         <v>488</v>
-      </c>
-      <c r="C319">
-        <v>1</v>
-      </c>
-      <c r="D319" t="s">
-        <v>12</v>
-      </c>
-      <c r="E319" t="s">
-        <v>384</v>
       </c>
       <c r="F319" s="1">
         <v>46248</v>
@@ -10494,7 +10668,7 @@
         <v>12</v>
       </c>
       <c r="E320" t="s">
-        <v>490</v>
+        <v>397</v>
       </c>
       <c r="F320" s="1">
         <v>46248</v>
@@ -10511,7 +10685,7 @@
         <v>0</v>
       </c>
       <c r="B321" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C321">
         <v>1</v>
@@ -10520,7 +10694,7 @@
         <v>12</v>
       </c>
       <c r="E321" t="s">
-        <v>492</v>
+        <v>390</v>
       </c>
       <c r="F321" s="1">
         <v>46248</v>
@@ -10537,7 +10711,7 @@
         <v>0</v>
       </c>
       <c r="B322" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="C322">
         <v>1</v>
@@ -10546,7 +10720,7 @@
         <v>12</v>
       </c>
       <c r="E322" t="s">
-        <v>494</v>
+        <v>486</v>
       </c>
       <c r="F322" s="1">
         <v>46248</v>
@@ -10563,7 +10737,7 @@
         <v>0</v>
       </c>
       <c r="B323" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="C323">
         <v>1</v>
@@ -10572,7 +10746,7 @@
         <v>12</v>
       </c>
       <c r="E323" t="s">
-        <v>496</v>
+        <v>486</v>
       </c>
       <c r="F323" s="1">
         <v>46248</v>
@@ -10589,7 +10763,7 @@
         <v>0</v>
       </c>
       <c r="B324" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="C324">
         <v>1</v>
@@ -10598,7 +10772,7 @@
         <v>12</v>
       </c>
       <c r="E324" t="s">
-        <v>498</v>
+        <v>348</v>
       </c>
       <c r="F324" s="1">
         <v>46248</v>
@@ -10612,51 +10786,51 @@
     </row>
     <row r="325" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A325" t="s">
-        <v>499</v>
+        <v>0</v>
       </c>
       <c r="B325" t="s">
-        <v>500</v>
+        <v>494</v>
       </c>
       <c r="C325">
         <v>1</v>
       </c>
       <c r="D325" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E325" t="s">
-        <v>473</v>
+        <v>495</v>
       </c>
       <c r="F325" s="1">
-        <v>46148</v>
+        <v>46249</v>
       </c>
       <c r="G325" s="1">
-        <v>46149</v>
+        <v>46252</v>
       </c>
       <c r="H325">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="326" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A326" t="s">
-        <v>501</v>
+        <v>0</v>
       </c>
       <c r="B326" t="s">
-        <v>502</v>
+        <v>496</v>
       </c>
       <c r="C326">
         <v>1</v>
       </c>
       <c r="D326" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E326" t="s">
-        <v>30</v>
+        <v>79</v>
       </c>
       <c r="F326" s="1">
-        <v>46133</v>
+        <v>46249</v>
       </c>
       <c r="G326" s="1">
-        <v>46134</v>
+        <v>46252</v>
       </c>
       <c r="H326">
         <v>0</v>
@@ -10664,25 +10838,25 @@
     </row>
     <row r="327" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A327" t="s">
-        <v>501</v>
+        <v>0</v>
       </c>
       <c r="B327" t="s">
-        <v>503</v>
+        <v>497</v>
       </c>
       <c r="C327">
         <v>1</v>
       </c>
       <c r="D327" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E327" t="s">
-        <v>30</v>
+        <v>498</v>
       </c>
       <c r="F327" s="1">
-        <v>46134</v>
+        <v>46249</v>
       </c>
       <c r="G327" s="1">
-        <v>46134</v>
+        <v>46252</v>
       </c>
       <c r="H327">
         <v>0</v>
@@ -10690,25 +10864,25 @@
     </row>
     <row r="328" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A328" t="s">
-        <v>501</v>
+        <v>0</v>
       </c>
       <c r="B328" t="s">
-        <v>504</v>
+        <v>499</v>
       </c>
       <c r="C328">
         <v>1</v>
       </c>
       <c r="D328" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E328" t="s">
-        <v>15</v>
+        <v>500</v>
       </c>
       <c r="F328" s="1">
-        <v>46156</v>
+        <v>46249</v>
       </c>
       <c r="G328" s="1">
-        <v>46156</v>
+        <v>46252</v>
       </c>
       <c r="H328">
         <v>0</v>
@@ -10716,48 +10890,48 @@
     </row>
     <row r="329" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A329" t="s">
+        <v>0</v>
+      </c>
+      <c r="B329" t="s">
         <v>501</v>
       </c>
-      <c r="B329" t="s">
-        <v>505</v>
-      </c>
       <c r="C329">
         <v>1</v>
       </c>
       <c r="D329" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E329" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="F329" s="1">
-        <v>46195</v>
+        <v>46249</v>
       </c>
       <c r="G329" s="1">
-        <v>46195</v>
+        <v>46252</v>
       </c>
       <c r="H329">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="330" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A330" t="s">
-        <v>501</v>
+        <v>0</v>
       </c>
       <c r="B330" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="C330">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D330" t="s">
         <v>12</v>
       </c>
       <c r="E330" t="s">
-        <v>508</v>
+        <v>502</v>
       </c>
       <c r="F330" s="1">
-        <v>46206</v>
+        <v>46249</v>
       </c>
       <c r="G330" s="1">
         <v>46252</v>
@@ -10768,51 +10942,51 @@
     </row>
     <row r="331" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A331" t="s">
-        <v>501</v>
+        <v>0</v>
       </c>
       <c r="B331" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="C331">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D331" t="s">
-        <v>68</v>
+        <v>12</v>
       </c>
       <c r="E331" t="s">
-        <v>510</v>
+        <v>505</v>
       </c>
       <c r="F331" s="1">
-        <v>46209</v>
+        <v>46249</v>
       </c>
       <c r="G331" s="1">
-        <v>46218</v>
+        <v>46252</v>
       </c>
       <c r="H331">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="332" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A332" t="s">
-        <v>501</v>
+        <v>0</v>
       </c>
       <c r="B332" t="s">
-        <v>511</v>
+        <v>506</v>
       </c>
       <c r="C332">
         <v>1</v>
       </c>
       <c r="D332" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E332" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="F332" s="1">
-        <v>46213</v>
+        <v>46249</v>
       </c>
       <c r="G332" s="1">
-        <v>46213</v>
+        <v>46252</v>
       </c>
       <c r="H332">
         <v>0</v>
@@ -10820,230 +10994,230 @@
     </row>
     <row r="333" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A333" t="s">
-        <v>501</v>
+        <v>0</v>
       </c>
       <c r="B333" t="s">
-        <v>513</v>
+        <v>508</v>
       </c>
       <c r="C333">
         <v>1</v>
       </c>
       <c r="D333" t="s">
-        <v>68</v>
+        <v>12</v>
       </c>
       <c r="E333" t="s">
-        <v>242</v>
+        <v>509</v>
       </c>
       <c r="F333" s="1">
-        <v>46213</v>
+        <v>46249</v>
       </c>
       <c r="G333" s="1">
-        <v>46216</v>
+        <v>46252</v>
       </c>
       <c r="H333">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="334" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A334" t="s">
-        <v>501</v>
+        <v>0</v>
       </c>
       <c r="B334" t="s">
-        <v>514</v>
+        <v>510</v>
       </c>
       <c r="C334">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D334" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E334" t="s">
-        <v>96</v>
+        <v>511</v>
       </c>
       <c r="F334" s="1">
-        <v>46220</v>
+        <v>46249</v>
       </c>
       <c r="G334" s="1">
-        <v>46231</v>
+        <v>46252</v>
       </c>
       <c r="H334">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="335" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A335" t="s">
-        <v>501</v>
+        <v>0</v>
       </c>
       <c r="B335" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="C335">
         <v>1</v>
       </c>
       <c r="D335" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E335" t="s">
-        <v>506</v>
+        <v>106</v>
       </c>
       <c r="F335" s="1">
-        <v>46223</v>
+        <v>46249</v>
       </c>
       <c r="G335" s="1">
-        <v>46223</v>
+        <v>46252</v>
       </c>
       <c r="H335">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="336" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A336" t="s">
-        <v>501</v>
+        <v>0</v>
       </c>
       <c r="B336" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="C336">
         <v>1</v>
       </c>
       <c r="D336" t="s">
-        <v>68</v>
+        <v>12</v>
       </c>
       <c r="E336" t="s">
-        <v>242</v>
+        <v>514</v>
       </c>
       <c r="F336" s="1">
-        <v>46224</v>
+        <v>46249</v>
       </c>
       <c r="G336" s="1">
-        <v>46224</v>
+        <v>46252</v>
       </c>
       <c r="H336">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="337" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A337" t="s">
-        <v>501</v>
+        <v>0</v>
       </c>
       <c r="B337" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="C337">
         <v>1</v>
       </c>
       <c r="D337" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E337" t="s">
-        <v>506</v>
+        <v>242</v>
       </c>
       <c r="F337" s="1">
-        <v>46230</v>
+        <v>46249</v>
       </c>
       <c r="G337" s="1">
-        <v>46231</v>
+        <v>46252</v>
       </c>
       <c r="H337">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="338" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A338" t="s">
-        <v>501</v>
+        <v>0</v>
       </c>
       <c r="B338" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="C338">
         <v>1</v>
       </c>
       <c r="D338" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E338" t="s">
-        <v>96</v>
+        <v>242</v>
       </c>
       <c r="F338" s="1">
-        <v>46232</v>
+        <v>46249</v>
       </c>
       <c r="G338" s="1">
-        <v>46233</v>
+        <v>46252</v>
       </c>
       <c r="H338">
-        <v>126</v>
+        <v>0</v>
       </c>
     </row>
     <row r="339" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A339" t="s">
-        <v>501</v>
+        <v>0</v>
       </c>
       <c r="B339" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="C339">
         <v>1</v>
       </c>
       <c r="D339" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E339" t="s">
-        <v>96</v>
+        <v>165</v>
       </c>
       <c r="F339" s="1">
-        <v>46232</v>
+        <v>46251</v>
       </c>
       <c r="G339" s="1">
-        <v>46233</v>
+        <v>46252</v>
       </c>
       <c r="H339">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="340" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A340" t="s">
-        <v>501</v>
+        <v>0</v>
       </c>
       <c r="B340" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="C340">
         <v>1</v>
       </c>
       <c r="D340" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E340" t="s">
-        <v>242</v>
+        <v>261</v>
       </c>
       <c r="F340" s="1">
-        <v>46238</v>
+        <v>46252</v>
       </c>
       <c r="G340" s="1">
-        <v>46239</v>
+        <v>46252</v>
       </c>
       <c r="H340">
-        <v>117</v>
+        <v>0</v>
       </c>
     </row>
     <row r="341" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A341" t="s">
-        <v>501</v>
+        <v>0</v>
       </c>
       <c r="B341" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C341">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D341" t="s">
         <v>12</v>
       </c>
       <c r="E341" t="s">
-        <v>508</v>
+        <v>520</v>
       </c>
       <c r="F341" s="1">
-        <v>46239</v>
+        <v>46252</v>
       </c>
       <c r="G341" s="1">
         <v>46252</v>
@@ -11054,22 +11228,22 @@
     </row>
     <row r="342" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A342" t="s">
-        <v>501</v>
+        <v>0</v>
       </c>
       <c r="B342" t="s">
+        <v>521</v>
+      </c>
+      <c r="C342">
+        <v>1</v>
+      </c>
+      <c r="D342" t="s">
+        <v>12</v>
+      </c>
+      <c r="E342" t="s">
         <v>522</v>
       </c>
-      <c r="C342">
-        <v>2</v>
-      </c>
-      <c r="D342" t="s">
-        <v>12</v>
-      </c>
-      <c r="E342" t="s">
-        <v>508</v>
-      </c>
       <c r="F342" s="1">
-        <v>46239</v>
+        <v>46252</v>
       </c>
       <c r="G342" s="1">
         <v>46252</v>
@@ -11080,7 +11254,7 @@
     </row>
     <row r="343" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A343" t="s">
-        <v>501</v>
+        <v>0</v>
       </c>
       <c r="B343" t="s">
         <v>523</v>
@@ -11092,10 +11266,10 @@
         <v>12</v>
       </c>
       <c r="E343" t="s">
-        <v>30</v>
+        <v>524</v>
       </c>
       <c r="F343" s="1">
-        <v>46247</v>
+        <v>46252</v>
       </c>
       <c r="G343" s="1">
         <v>46252</v>
@@ -11106,10 +11280,10 @@
     </row>
     <row r="344" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A344" t="s">
-        <v>501</v>
+        <v>0</v>
       </c>
       <c r="B344" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C344">
         <v>1</v>
@@ -11118,10 +11292,10 @@
         <v>12</v>
       </c>
       <c r="E344" t="s">
-        <v>374</v>
+        <v>526</v>
       </c>
       <c r="F344" s="1">
-        <v>46247</v>
+        <v>46252</v>
       </c>
       <c r="G344" s="1">
         <v>46252</v>
@@ -11132,10 +11306,10 @@
     </row>
     <row r="345" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A345" t="s">
-        <v>501</v>
+        <v>0</v>
       </c>
       <c r="B345" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="C345">
         <v>1</v>
@@ -11144,10 +11318,10 @@
         <v>12</v>
       </c>
       <c r="E345" t="s">
-        <v>376</v>
+        <v>528</v>
       </c>
       <c r="F345" s="1">
-        <v>46247</v>
+        <v>46252</v>
       </c>
       <c r="G345" s="1">
         <v>46252</v>
@@ -11158,51 +11332,51 @@
     </row>
     <row r="346" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A346" t="s">
-        <v>526</v>
+        <v>0</v>
       </c>
       <c r="B346" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="C346">
         <v>1</v>
       </c>
       <c r="D346" t="s">
-        <v>68</v>
+        <v>12</v>
       </c>
       <c r="E346" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="F346" s="1">
-        <v>46063</v>
+        <v>46252</v>
       </c>
       <c r="G346" s="1">
-        <v>46064</v>
+        <v>46252</v>
       </c>
       <c r="H346">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="347" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A347" t="s">
-        <v>526</v>
+        <v>0</v>
       </c>
       <c r="B347" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="C347">
         <v>1</v>
       </c>
       <c r="D347" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E347" t="s">
-        <v>41</v>
+        <v>532</v>
       </c>
       <c r="F347" s="1">
-        <v>46113</v>
+        <v>46252</v>
       </c>
       <c r="G347" s="1">
-        <v>46125</v>
+        <v>46252</v>
       </c>
       <c r="H347">
         <v>0</v>
@@ -11210,129 +11384,129 @@
     </row>
     <row r="348" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A348" t="s">
-        <v>526</v>
+        <v>0</v>
       </c>
       <c r="B348" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="C348">
         <v>1</v>
       </c>
       <c r="D348" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E348" t="s">
-        <v>41</v>
+        <v>532</v>
       </c>
       <c r="F348" s="1">
-        <v>46125</v>
+        <v>46252</v>
       </c>
       <c r="G348" s="1">
-        <v>46125</v>
+        <v>46252</v>
       </c>
       <c r="H348">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="349" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A349" t="s">
-        <v>526</v>
+        <v>0</v>
       </c>
       <c r="B349" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="C349">
         <v>1</v>
       </c>
       <c r="D349" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E349" t="s">
-        <v>41</v>
+        <v>514</v>
       </c>
       <c r="F349" s="1">
-        <v>46126</v>
+        <v>46252</v>
       </c>
       <c r="G349" s="1">
-        <v>46126</v>
+        <v>46252</v>
       </c>
       <c r="H349">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="350" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A350" t="s">
-        <v>526</v>
+        <v>0</v>
       </c>
       <c r="B350" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="C350">
         <v>1</v>
       </c>
       <c r="D350" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E350" t="s">
-        <v>41</v>
+        <v>536</v>
       </c>
       <c r="F350" s="1">
-        <v>46126</v>
+        <v>46252</v>
       </c>
       <c r="G350" s="1">
-        <v>46126</v>
+        <v>46252</v>
       </c>
       <c r="H350">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="351" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A351" t="s">
-        <v>526</v>
+        <v>0</v>
       </c>
       <c r="B351" t="s">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="C351">
         <v>1</v>
       </c>
       <c r="D351" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E351" t="s">
-        <v>41</v>
+        <v>538</v>
       </c>
       <c r="F351" s="1">
-        <v>46128</v>
+        <v>46252</v>
       </c>
       <c r="G351" s="1">
-        <v>46128</v>
+        <v>46252</v>
       </c>
       <c r="H351">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="352" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A352" t="s">
-        <v>526</v>
+        <v>0</v>
       </c>
       <c r="B352" t="s">
-        <v>534</v>
+        <v>539</v>
       </c>
       <c r="C352">
         <v>1</v>
       </c>
       <c r="D352" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E352" t="s">
-        <v>41</v>
+        <v>474</v>
       </c>
       <c r="F352" s="1">
-        <v>46132</v>
+        <v>46252</v>
       </c>
       <c r="G352" s="1">
-        <v>46132</v>
+        <v>46252</v>
       </c>
       <c r="H352">
         <v>0</v>
@@ -11340,88 +11514,88 @@
     </row>
     <row r="353" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A353" t="s">
-        <v>526</v>
+        <v>0</v>
       </c>
       <c r="B353" t="s">
-        <v>535</v>
+        <v>540</v>
       </c>
       <c r="C353">
         <v>1</v>
       </c>
       <c r="D353" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E353" t="s">
-        <v>41</v>
+        <v>541</v>
       </c>
       <c r="F353" s="1">
-        <v>46161</v>
+        <v>46252</v>
       </c>
       <c r="G353" s="1">
-        <v>46161</v>
+        <v>46252</v>
       </c>
       <c r="H353">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="354" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A354" t="s">
-        <v>526</v>
+        <v>0</v>
       </c>
       <c r="B354" t="s">
-        <v>536</v>
+        <v>542</v>
       </c>
       <c r="C354">
         <v>1</v>
       </c>
       <c r="D354" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E354" t="s">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="F354" s="1">
-        <v>46174</v>
+        <v>46252</v>
       </c>
       <c r="G354" s="1">
-        <v>46174</v>
+        <v>46252</v>
       </c>
       <c r="H354">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="355" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A355" t="s">
-        <v>526</v>
+        <v>0</v>
       </c>
       <c r="B355" t="s">
-        <v>537</v>
+        <v>543</v>
       </c>
       <c r="C355">
         <v>1</v>
       </c>
       <c r="D355" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E355" t="s">
-        <v>41</v>
+        <v>544</v>
       </c>
       <c r="F355" s="1">
-        <v>46174</v>
+        <v>46252</v>
       </c>
       <c r="G355" s="1">
-        <v>46174</v>
+        <v>46252</v>
       </c>
       <c r="H355">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="356" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A356" t="s">
-        <v>526</v>
+        <v>0</v>
       </c>
       <c r="B356" t="s">
-        <v>538</v>
+        <v>545</v>
       </c>
       <c r="C356">
         <v>1</v>
@@ -11430,10 +11604,10 @@
         <v>12</v>
       </c>
       <c r="E356" t="s">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="F356" s="1">
-        <v>46195</v>
+        <v>46252</v>
       </c>
       <c r="G356" s="1">
         <v>46252</v>
@@ -11444,25 +11618,25 @@
     </row>
     <row r="357" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A357" t="s">
-        <v>526</v>
+        <v>0</v>
       </c>
       <c r="B357" t="s">
-        <v>539</v>
+        <v>546</v>
       </c>
       <c r="C357">
         <v>1</v>
       </c>
       <c r="D357" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E357" t="s">
-        <v>41</v>
+        <v>547</v>
       </c>
       <c r="F357" s="1">
-        <v>46210</v>
+        <v>46252</v>
       </c>
       <c r="G357" s="1">
-        <v>46210</v>
+        <v>46252</v>
       </c>
       <c r="H357">
         <v>0</v>
@@ -11470,36 +11644,36 @@
     </row>
     <row r="358" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A358" t="s">
-        <v>526</v>
+        <v>0</v>
       </c>
       <c r="B358" t="s">
-        <v>540</v>
+        <v>548</v>
       </c>
       <c r="C358">
         <v>1</v>
       </c>
       <c r="D358" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E358" t="s">
-        <v>41</v>
+        <v>242</v>
       </c>
       <c r="F358" s="1">
-        <v>46213</v>
+        <v>46252</v>
       </c>
       <c r="G358" s="1">
-        <v>46213</v>
+        <v>46252</v>
       </c>
       <c r="H358">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="359" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A359" t="s">
-        <v>526</v>
+        <v>0</v>
       </c>
       <c r="B359" t="s">
-        <v>541</v>
+        <v>549</v>
       </c>
       <c r="C359">
         <v>1</v>
@@ -11508,10 +11682,10 @@
         <v>12</v>
       </c>
       <c r="E359" t="s">
-        <v>41</v>
+        <v>550</v>
       </c>
       <c r="F359" s="1">
-        <v>46218</v>
+        <v>46252</v>
       </c>
       <c r="G359" s="1">
         <v>46252</v>
@@ -11522,25 +11696,25 @@
     </row>
     <row r="360" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A360" t="s">
-        <v>526</v>
+        <v>0</v>
       </c>
       <c r="B360" t="s">
-        <v>542</v>
+        <v>551</v>
       </c>
       <c r="C360">
         <v>1</v>
       </c>
       <c r="D360" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E360" t="s">
-        <v>55</v>
+        <v>117</v>
       </c>
       <c r="F360" s="1">
-        <v>46226</v>
+        <v>46252</v>
       </c>
       <c r="G360" s="1">
-        <v>46226</v>
+        <v>46252</v>
       </c>
       <c r="H360">
         <v>0</v>
@@ -11548,10 +11722,10 @@
     </row>
     <row r="361" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A361" t="s">
-        <v>526</v>
+        <v>0</v>
       </c>
       <c r="B361" t="s">
-        <v>543</v>
+        <v>552</v>
       </c>
       <c r="C361">
         <v>1</v>
@@ -11560,10 +11734,10 @@
         <v>12</v>
       </c>
       <c r="E361" t="s">
-        <v>41</v>
+        <v>66</v>
       </c>
       <c r="F361" s="1">
-        <v>46227</v>
+        <v>46252</v>
       </c>
       <c r="G361" s="1">
         <v>46252</v>
@@ -11574,36 +11748,36 @@
     </row>
     <row r="362" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A362" t="s">
-        <v>526</v>
+        <v>553</v>
       </c>
       <c r="B362" t="s">
-        <v>544</v>
+        <v>554</v>
       </c>
       <c r="C362">
         <v>1</v>
       </c>
       <c r="D362" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E362" t="s">
-        <v>41</v>
+        <v>449</v>
       </c>
       <c r="F362" s="1">
-        <v>46227</v>
+        <v>46148</v>
       </c>
       <c r="G362" s="1">
-        <v>46252</v>
+        <v>46149</v>
       </c>
       <c r="H362">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="363" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A363" t="s">
-        <v>526</v>
+        <v>555</v>
       </c>
       <c r="B363" t="s">
-        <v>545</v>
+        <v>556</v>
       </c>
       <c r="C363">
         <v>1</v>
@@ -11612,13 +11786,13 @@
         <v>5</v>
       </c>
       <c r="E363" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="F363" s="1">
-        <v>46227</v>
+        <v>46133</v>
       </c>
       <c r="G363" s="1">
-        <v>46228</v>
+        <v>46134</v>
       </c>
       <c r="H363">
         <v>0</v>
@@ -11626,25 +11800,25 @@
     </row>
     <row r="364" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A364" t="s">
-        <v>526</v>
+        <v>555</v>
       </c>
       <c r="B364" t="s">
-        <v>546</v>
+        <v>557</v>
       </c>
       <c r="C364">
         <v>1</v>
       </c>
       <c r="D364" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E364" t="s">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="F364" s="1">
-        <v>46230</v>
+        <v>46134</v>
       </c>
       <c r="G364" s="1">
-        <v>46252</v>
+        <v>46134</v>
       </c>
       <c r="H364">
         <v>0</v>
@@ -11652,10 +11826,10 @@
     </row>
     <row r="365" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A365" t="s">
-        <v>526</v>
+        <v>555</v>
       </c>
       <c r="B365" t="s">
-        <v>547</v>
+        <v>558</v>
       </c>
       <c r="C365">
         <v>1</v>
@@ -11664,13 +11838,13 @@
         <v>5</v>
       </c>
       <c r="E365" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="F365" s="1">
-        <v>46231</v>
+        <v>46156</v>
       </c>
       <c r="G365" s="1">
-        <v>46231</v>
+        <v>46156</v>
       </c>
       <c r="H365">
         <v>0</v>
@@ -11678,48 +11852,48 @@
     </row>
     <row r="366" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A366" t="s">
-        <v>526</v>
+        <v>555</v>
       </c>
       <c r="B366" t="s">
-        <v>548</v>
+        <v>559</v>
       </c>
       <c r="C366">
         <v>1</v>
       </c>
       <c r="D366" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E366" t="s">
-        <v>41</v>
+        <v>560</v>
       </c>
       <c r="F366" s="1">
-        <v>46237</v>
+        <v>46195</v>
       </c>
       <c r="G366" s="1">
-        <v>46237</v>
+        <v>46195</v>
       </c>
       <c r="H366">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="367" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A367" t="s">
-        <v>526</v>
+        <v>555</v>
       </c>
       <c r="B367" t="s">
-        <v>549</v>
+        <v>561</v>
       </c>
       <c r="C367">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D367" t="s">
         <v>12</v>
       </c>
       <c r="E367" t="s">
-        <v>41</v>
+        <v>562</v>
       </c>
       <c r="F367" s="1">
-        <v>46248</v>
+        <v>46206</v>
       </c>
       <c r="G367" s="1">
         <v>46252</v>
@@ -11730,114 +11904,114 @@
     </row>
     <row r="368" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A368" t="s">
-        <v>526</v>
+        <v>555</v>
       </c>
       <c r="B368" t="s">
-        <v>550</v>
+        <v>563</v>
       </c>
       <c r="C368">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D368" t="s">
-        <v>12</v>
+        <v>68</v>
       </c>
       <c r="E368" t="s">
-        <v>41</v>
+        <v>564</v>
       </c>
       <c r="F368" s="1">
-        <v>46248</v>
+        <v>46209</v>
       </c>
       <c r="G368" s="1">
-        <v>46252</v>
+        <v>46218</v>
       </c>
       <c r="H368">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="369" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A369" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="B369" t="s">
-        <v>552</v>
+        <v>565</v>
       </c>
       <c r="C369">
         <v>1</v>
       </c>
       <c r="D369" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E369" t="s">
-        <v>553</v>
+        <v>566</v>
       </c>
       <c r="F369" s="1">
-        <v>46083</v>
+        <v>46213</v>
       </c>
       <c r="G369" s="1">
-        <v>46084</v>
+        <v>46213</v>
       </c>
       <c r="H369">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="370" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A370" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="B370" t="s">
-        <v>554</v>
+        <v>567</v>
       </c>
       <c r="C370">
         <v>1</v>
       </c>
       <c r="D370" t="s">
-        <v>2</v>
+        <v>68</v>
       </c>
       <c r="E370" t="s">
-        <v>553</v>
+        <v>244</v>
       </c>
       <c r="F370" s="1">
-        <v>46132</v>
+        <v>46213</v>
       </c>
       <c r="G370" s="1">
-        <v>46133</v>
+        <v>46216</v>
       </c>
       <c r="H370">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="371" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A371" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="B371" t="s">
-        <v>555</v>
+        <v>568</v>
       </c>
       <c r="C371">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D371" t="s">
         <v>2</v>
       </c>
       <c r="E371" t="s">
-        <v>556</v>
+        <v>96</v>
       </c>
       <c r="F371" s="1">
-        <v>46157</v>
+        <v>46220</v>
       </c>
       <c r="G371" s="1">
-        <v>46157</v>
+        <v>46231</v>
       </c>
       <c r="H371">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="372" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A372" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="B372" t="s">
-        <v>557</v>
+        <v>569</v>
       </c>
       <c r="C372">
         <v>1</v>
@@ -11846,76 +12020,76 @@
         <v>2</v>
       </c>
       <c r="E372" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="F372" s="1">
-        <v>46168</v>
+        <v>46223</v>
       </c>
       <c r="G372" s="1">
-        <v>46170</v>
+        <v>46223</v>
       </c>
       <c r="H372">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="373" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A373" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="B373" t="s">
-        <v>559</v>
+        <v>570</v>
       </c>
       <c r="C373">
         <v>1</v>
       </c>
       <c r="D373" t="s">
-        <v>2</v>
+        <v>68</v>
       </c>
       <c r="E373" t="s">
-        <v>556</v>
+        <v>244</v>
       </c>
       <c r="F373" s="1">
-        <v>46244</v>
+        <v>46224</v>
       </c>
       <c r="G373" s="1">
-        <v>46244</v>
+        <v>46224</v>
       </c>
       <c r="H373">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="374" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A374" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="B374" t="s">
+        <v>571</v>
+      </c>
+      <c r="C374">
+        <v>1</v>
+      </c>
+      <c r="D374" t="s">
+        <v>2</v>
+      </c>
+      <c r="E374" t="s">
         <v>560</v>
       </c>
-      <c r="C374">
-        <v>1</v>
-      </c>
-      <c r="D374" t="s">
-        <v>2</v>
-      </c>
-      <c r="E374" t="s">
-        <v>556</v>
-      </c>
       <c r="F374" s="1">
-        <v>46247</v>
+        <v>46230</v>
       </c>
       <c r="G374" s="1">
-        <v>46247</v>
+        <v>46231</v>
       </c>
       <c r="H374">
-        <v>7</v>
+        <v>18</v>
       </c>
     </row>
     <row r="375" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A375" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="B375" t="s">
-        <v>561</v>
+        <v>572</v>
       </c>
       <c r="C375">
         <v>1</v>
@@ -11924,42 +12098,1108 @@
         <v>2</v>
       </c>
       <c r="E375" t="s">
-        <v>553</v>
+        <v>96</v>
       </c>
       <c r="F375" s="1">
-        <v>46247</v>
+        <v>46232</v>
       </c>
       <c r="G375" s="1">
-        <v>46247</v>
+        <v>46233</v>
       </c>
       <c r="H375">
-        <v>1</v>
+        <v>126</v>
       </c>
     </row>
     <row r="376" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A376" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="B376" t="s">
+        <v>573</v>
+      </c>
+      <c r="C376">
+        <v>1</v>
+      </c>
+      <c r="D376" t="s">
+        <v>2</v>
+      </c>
+      <c r="E376" t="s">
+        <v>96</v>
+      </c>
+      <c r="F376" s="1">
+        <v>46232</v>
+      </c>
+      <c r="G376" s="1">
+        <v>46233</v>
+      </c>
+      <c r="H376">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="377" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A377" t="s">
+        <v>555</v>
+      </c>
+      <c r="B377" t="s">
+        <v>574</v>
+      </c>
+      <c r="C377">
+        <v>1</v>
+      </c>
+      <c r="D377" t="s">
+        <v>2</v>
+      </c>
+      <c r="E377" t="s">
+        <v>244</v>
+      </c>
+      <c r="F377" s="1">
+        <v>46238</v>
+      </c>
+      <c r="G377" s="1">
+        <v>46239</v>
+      </c>
+      <c r="H377">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="378" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A378" t="s">
+        <v>555</v>
+      </c>
+      <c r="B378" t="s">
+        <v>575</v>
+      </c>
+      <c r="C378">
+        <v>2</v>
+      </c>
+      <c r="D378" t="s">
+        <v>12</v>
+      </c>
+      <c r="E378" t="s">
         <v>562</v>
       </c>
-      <c r="C376">
-        <v>1</v>
-      </c>
-      <c r="D376" t="s">
-        <v>12</v>
-      </c>
-      <c r="E376" t="s">
-        <v>553</v>
-      </c>
-      <c r="F376" s="1">
+      <c r="F378" s="1">
+        <v>46239</v>
+      </c>
+      <c r="G378" s="1">
+        <v>46252</v>
+      </c>
+      <c r="H378">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="379" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A379" t="s">
+        <v>555</v>
+      </c>
+      <c r="B379" t="s">
+        <v>576</v>
+      </c>
+      <c r="C379">
+        <v>2</v>
+      </c>
+      <c r="D379" t="s">
+        <v>12</v>
+      </c>
+      <c r="E379" t="s">
+        <v>562</v>
+      </c>
+      <c r="F379" s="1">
+        <v>46239</v>
+      </c>
+      <c r="G379" s="1">
+        <v>46252</v>
+      </c>
+      <c r="H379">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="380" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A380" t="s">
+        <v>555</v>
+      </c>
+      <c r="B380" t="s">
+        <v>577</v>
+      </c>
+      <c r="C380">
+        <v>1</v>
+      </c>
+      <c r="D380" t="s">
+        <v>12</v>
+      </c>
+      <c r="E380" t="s">
+        <v>30</v>
+      </c>
+      <c r="F380" s="1">
+        <v>46247</v>
+      </c>
+      <c r="G380" s="1">
+        <v>46252</v>
+      </c>
+      <c r="H380">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="381" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A381" t="s">
+        <v>555</v>
+      </c>
+      <c r="B381" t="s">
+        <v>578</v>
+      </c>
+      <c r="C381">
+        <v>1</v>
+      </c>
+      <c r="D381" t="s">
+        <v>12</v>
+      </c>
+      <c r="E381" t="s">
+        <v>352</v>
+      </c>
+      <c r="F381" s="1">
+        <v>46247</v>
+      </c>
+      <c r="G381" s="1">
+        <v>46252</v>
+      </c>
+      <c r="H381">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="382" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A382" t="s">
+        <v>555</v>
+      </c>
+      <c r="B382" t="s">
+        <v>579</v>
+      </c>
+      <c r="C382">
+        <v>1</v>
+      </c>
+      <c r="D382" t="s">
+        <v>12</v>
+      </c>
+      <c r="E382" t="s">
+        <v>136</v>
+      </c>
+      <c r="F382" s="1">
         <v>46248</v>
       </c>
-      <c r="G376" s="1">
-        <v>46252</v>
-      </c>
-      <c r="H376">
-        <v>0</v>
+      <c r="G382" s="1">
+        <v>46252</v>
+      </c>
+      <c r="H382">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="383" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A383" t="s">
+        <v>555</v>
+      </c>
+      <c r="B383" t="s">
+        <v>580</v>
+      </c>
+      <c r="C383">
+        <v>1</v>
+      </c>
+      <c r="D383" t="s">
+        <v>12</v>
+      </c>
+      <c r="E383" t="s">
+        <v>242</v>
+      </c>
+      <c r="F383" s="1">
+        <v>46249</v>
+      </c>
+      <c r="G383" s="1">
+        <v>46252</v>
+      </c>
+      <c r="H383">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="384" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A384" t="s">
+        <v>555</v>
+      </c>
+      <c r="B384" t="s">
+        <v>581</v>
+      </c>
+      <c r="C384">
+        <v>1</v>
+      </c>
+      <c r="D384" t="s">
+        <v>12</v>
+      </c>
+      <c r="E384" t="s">
+        <v>242</v>
+      </c>
+      <c r="F384" s="1">
+        <v>46249</v>
+      </c>
+      <c r="G384" s="1">
+        <v>46252</v>
+      </c>
+      <c r="H384">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="385" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A385" t="s">
+        <v>555</v>
+      </c>
+      <c r="B385" t="s">
+        <v>582</v>
+      </c>
+      <c r="C385">
+        <v>1</v>
+      </c>
+      <c r="D385" t="s">
+        <v>12</v>
+      </c>
+      <c r="E385" t="s">
+        <v>560</v>
+      </c>
+      <c r="F385" s="1">
+        <v>46252</v>
+      </c>
+      <c r="G385" s="1">
+        <v>46252</v>
+      </c>
+      <c r="H385">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="386" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A386" t="s">
+        <v>555</v>
+      </c>
+      <c r="B386" t="s">
+        <v>583</v>
+      </c>
+      <c r="C386">
+        <v>1</v>
+      </c>
+      <c r="D386" t="s">
+        <v>12</v>
+      </c>
+      <c r="E386" t="s">
+        <v>560</v>
+      </c>
+      <c r="F386" s="1">
+        <v>46252</v>
+      </c>
+      <c r="G386" s="1">
+        <v>46252</v>
+      </c>
+      <c r="H386">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="387" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A387" t="s">
+        <v>555</v>
+      </c>
+      <c r="B387" t="s">
+        <v>584</v>
+      </c>
+      <c r="C387">
+        <v>1</v>
+      </c>
+      <c r="D387" t="s">
+        <v>12</v>
+      </c>
+      <c r="E387" t="s">
+        <v>547</v>
+      </c>
+      <c r="F387" s="1">
+        <v>46252</v>
+      </c>
+      <c r="G387" s="1">
+        <v>46252</v>
+      </c>
+      <c r="H387">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="388" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A388" t="s">
+        <v>585</v>
+      </c>
+      <c r="B388" t="s">
+        <v>586</v>
+      </c>
+      <c r="C388">
+        <v>1</v>
+      </c>
+      <c r="D388" t="s">
+        <v>68</v>
+      </c>
+      <c r="E388" t="s">
+        <v>587</v>
+      </c>
+      <c r="F388" s="1">
+        <v>46063</v>
+      </c>
+      <c r="G388" s="1">
+        <v>46064</v>
+      </c>
+      <c r="H388">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="389" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A389" t="s">
+        <v>585</v>
+      </c>
+      <c r="B389" t="s">
+        <v>588</v>
+      </c>
+      <c r="C389">
+        <v>1</v>
+      </c>
+      <c r="D389" t="s">
+        <v>5</v>
+      </c>
+      <c r="E389" t="s">
+        <v>41</v>
+      </c>
+      <c r="F389" s="1">
+        <v>46113</v>
+      </c>
+      <c r="G389" s="1">
+        <v>46125</v>
+      </c>
+      <c r="H389">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="390" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A390" t="s">
+        <v>585</v>
+      </c>
+      <c r="B390" t="s">
+        <v>589</v>
+      </c>
+      <c r="C390">
+        <v>1</v>
+      </c>
+      <c r="D390" t="s">
+        <v>2</v>
+      </c>
+      <c r="E390" t="s">
+        <v>41</v>
+      </c>
+      <c r="F390" s="1">
+        <v>46125</v>
+      </c>
+      <c r="G390" s="1">
+        <v>46125</v>
+      </c>
+      <c r="H390">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="391" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A391" t="s">
+        <v>585</v>
+      </c>
+      <c r="B391" t="s">
+        <v>590</v>
+      </c>
+      <c r="C391">
+        <v>1</v>
+      </c>
+      <c r="D391" t="s">
+        <v>2</v>
+      </c>
+      <c r="E391" t="s">
+        <v>41</v>
+      </c>
+      <c r="F391" s="1">
+        <v>46126</v>
+      </c>
+      <c r="G391" s="1">
+        <v>46126</v>
+      </c>
+      <c r="H391">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="392" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A392" t="s">
+        <v>585</v>
+      </c>
+      <c r="B392" t="s">
+        <v>591</v>
+      </c>
+      <c r="C392">
+        <v>1</v>
+      </c>
+      <c r="D392" t="s">
+        <v>2</v>
+      </c>
+      <c r="E392" t="s">
+        <v>41</v>
+      </c>
+      <c r="F392" s="1">
+        <v>46126</v>
+      </c>
+      <c r="G392" s="1">
+        <v>46126</v>
+      </c>
+      <c r="H392">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="393" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A393" t="s">
+        <v>585</v>
+      </c>
+      <c r="B393" t="s">
+        <v>592</v>
+      </c>
+      <c r="C393">
+        <v>1</v>
+      </c>
+      <c r="D393" t="s">
+        <v>2</v>
+      </c>
+      <c r="E393" t="s">
+        <v>41</v>
+      </c>
+      <c r="F393" s="1">
+        <v>46128</v>
+      </c>
+      <c r="G393" s="1">
+        <v>46128</v>
+      </c>
+      <c r="H393">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="394" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A394" t="s">
+        <v>585</v>
+      </c>
+      <c r="B394" t="s">
+        <v>593</v>
+      </c>
+      <c r="C394">
+        <v>1</v>
+      </c>
+      <c r="D394" t="s">
+        <v>5</v>
+      </c>
+      <c r="E394" t="s">
+        <v>41</v>
+      </c>
+      <c r="F394" s="1">
+        <v>46132</v>
+      </c>
+      <c r="G394" s="1">
+        <v>46132</v>
+      </c>
+      <c r="H394">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="395" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A395" t="s">
+        <v>585</v>
+      </c>
+      <c r="B395" t="s">
+        <v>594</v>
+      </c>
+      <c r="C395">
+        <v>1</v>
+      </c>
+      <c r="D395" t="s">
+        <v>2</v>
+      </c>
+      <c r="E395" t="s">
+        <v>41</v>
+      </c>
+      <c r="F395" s="1">
+        <v>46161</v>
+      </c>
+      <c r="G395" s="1">
+        <v>46161</v>
+      </c>
+      <c r="H395">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="396" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A396" t="s">
+        <v>585</v>
+      </c>
+      <c r="B396" t="s">
+        <v>595</v>
+      </c>
+      <c r="C396">
+        <v>1</v>
+      </c>
+      <c r="D396" t="s">
+        <v>2</v>
+      </c>
+      <c r="E396" t="s">
+        <v>41</v>
+      </c>
+      <c r="F396" s="1">
+        <v>46174</v>
+      </c>
+      <c r="G396" s="1">
+        <v>46174</v>
+      </c>
+      <c r="H396">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="397" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A397" t="s">
+        <v>585</v>
+      </c>
+      <c r="B397" t="s">
+        <v>596</v>
+      </c>
+      <c r="C397">
+        <v>1</v>
+      </c>
+      <c r="D397" t="s">
+        <v>2</v>
+      </c>
+      <c r="E397" t="s">
+        <v>41</v>
+      </c>
+      <c r="F397" s="1">
+        <v>46174</v>
+      </c>
+      <c r="G397" s="1">
+        <v>46174</v>
+      </c>
+      <c r="H397">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="398" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A398" t="s">
+        <v>585</v>
+      </c>
+      <c r="B398" t="s">
+        <v>597</v>
+      </c>
+      <c r="C398">
+        <v>1</v>
+      </c>
+      <c r="D398" t="s">
+        <v>12</v>
+      </c>
+      <c r="E398" t="s">
+        <v>41</v>
+      </c>
+      <c r="F398" s="1">
+        <v>46195</v>
+      </c>
+      <c r="G398" s="1">
+        <v>46252</v>
+      </c>
+      <c r="H398">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="399" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A399" t="s">
+        <v>585</v>
+      </c>
+      <c r="B399" t="s">
+        <v>598</v>
+      </c>
+      <c r="C399">
+        <v>1</v>
+      </c>
+      <c r="D399" t="s">
+        <v>5</v>
+      </c>
+      <c r="E399" t="s">
+        <v>41</v>
+      </c>
+      <c r="F399" s="1">
+        <v>46210</v>
+      </c>
+      <c r="G399" s="1">
+        <v>46210</v>
+      </c>
+      <c r="H399">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="400" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A400" t="s">
+        <v>585</v>
+      </c>
+      <c r="B400" t="s">
+        <v>599</v>
+      </c>
+      <c r="C400">
+        <v>1</v>
+      </c>
+      <c r="D400" t="s">
+        <v>2</v>
+      </c>
+      <c r="E400" t="s">
+        <v>41</v>
+      </c>
+      <c r="F400" s="1">
+        <v>46213</v>
+      </c>
+      <c r="G400" s="1">
+        <v>46213</v>
+      </c>
+      <c r="H400">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="401" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A401" t="s">
+        <v>585</v>
+      </c>
+      <c r="B401" t="s">
+        <v>600</v>
+      </c>
+      <c r="C401">
+        <v>1</v>
+      </c>
+      <c r="D401" t="s">
+        <v>12</v>
+      </c>
+      <c r="E401" t="s">
+        <v>41</v>
+      </c>
+      <c r="F401" s="1">
+        <v>46218</v>
+      </c>
+      <c r="G401" s="1">
+        <v>46252</v>
+      </c>
+      <c r="H401">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="402" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A402" t="s">
+        <v>585</v>
+      </c>
+      <c r="B402" t="s">
+        <v>601</v>
+      </c>
+      <c r="C402">
+        <v>1</v>
+      </c>
+      <c r="D402" t="s">
+        <v>5</v>
+      </c>
+      <c r="E402" t="s">
+        <v>55</v>
+      </c>
+      <c r="F402" s="1">
+        <v>46226</v>
+      </c>
+      <c r="G402" s="1">
+        <v>46226</v>
+      </c>
+      <c r="H402">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="403" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A403" t="s">
+        <v>585</v>
+      </c>
+      <c r="B403" t="s">
+        <v>602</v>
+      </c>
+      <c r="C403">
+        <v>1</v>
+      </c>
+      <c r="D403" t="s">
+        <v>12</v>
+      </c>
+      <c r="E403" t="s">
+        <v>41</v>
+      </c>
+      <c r="F403" s="1">
+        <v>46227</v>
+      </c>
+      <c r="G403" s="1">
+        <v>46252</v>
+      </c>
+      <c r="H403">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="404" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A404" t="s">
+        <v>585</v>
+      </c>
+      <c r="B404" t="s">
+        <v>603</v>
+      </c>
+      <c r="C404">
+        <v>1</v>
+      </c>
+      <c r="D404" t="s">
+        <v>12</v>
+      </c>
+      <c r="E404" t="s">
+        <v>41</v>
+      </c>
+      <c r="F404" s="1">
+        <v>46227</v>
+      </c>
+      <c r="G404" s="1">
+        <v>46252</v>
+      </c>
+      <c r="H404">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="405" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A405" t="s">
+        <v>585</v>
+      </c>
+      <c r="B405" t="s">
+        <v>604</v>
+      </c>
+      <c r="C405">
+        <v>1</v>
+      </c>
+      <c r="D405" t="s">
+        <v>5</v>
+      </c>
+      <c r="E405" t="s">
+        <v>41</v>
+      </c>
+      <c r="F405" s="1">
+        <v>46227</v>
+      </c>
+      <c r="G405" s="1">
+        <v>46228</v>
+      </c>
+      <c r="H405">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="406" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A406" t="s">
+        <v>585</v>
+      </c>
+      <c r="B406" t="s">
+        <v>605</v>
+      </c>
+      <c r="C406">
+        <v>1</v>
+      </c>
+      <c r="D406" t="s">
+        <v>12</v>
+      </c>
+      <c r="E406" t="s">
+        <v>55</v>
+      </c>
+      <c r="F406" s="1">
+        <v>46230</v>
+      </c>
+      <c r="G406" s="1">
+        <v>46252</v>
+      </c>
+      <c r="H406">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="407" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A407" t="s">
+        <v>585</v>
+      </c>
+      <c r="B407" t="s">
+        <v>606</v>
+      </c>
+      <c r="C407">
+        <v>1</v>
+      </c>
+      <c r="D407" t="s">
+        <v>5</v>
+      </c>
+      <c r="E407" t="s">
+        <v>41</v>
+      </c>
+      <c r="F407" s="1">
+        <v>46231</v>
+      </c>
+      <c r="G407" s="1">
+        <v>46231</v>
+      </c>
+      <c r="H407">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="408" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A408" t="s">
+        <v>585</v>
+      </c>
+      <c r="B408" t="s">
+        <v>607</v>
+      </c>
+      <c r="C408">
+        <v>1</v>
+      </c>
+      <c r="D408" t="s">
+        <v>5</v>
+      </c>
+      <c r="E408" t="s">
+        <v>41</v>
+      </c>
+      <c r="F408" s="1">
+        <v>46237</v>
+      </c>
+      <c r="G408" s="1">
+        <v>46237</v>
+      </c>
+      <c r="H408">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="409" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A409" t="s">
+        <v>585</v>
+      </c>
+      <c r="B409" t="s">
+        <v>608</v>
+      </c>
+      <c r="C409">
+        <v>1</v>
+      </c>
+      <c r="D409" t="s">
+        <v>232</v>
+      </c>
+      <c r="E409" t="s">
+        <v>41</v>
+      </c>
+      <c r="F409" s="1">
+        <v>46252</v>
+      </c>
+      <c r="G409" s="1">
+        <v>46252</v>
+      </c>
+      <c r="H409">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="410" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A410" t="s">
+        <v>585</v>
+      </c>
+      <c r="B410" t="s">
+        <v>609</v>
+      </c>
+      <c r="C410">
+        <v>1</v>
+      </c>
+      <c r="D410" t="s">
+        <v>232</v>
+      </c>
+      <c r="E410" t="s">
+        <v>41</v>
+      </c>
+      <c r="F410" s="1">
+        <v>46252</v>
+      </c>
+      <c r="G410" s="1">
+        <v>46252</v>
+      </c>
+      <c r="H410">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="411" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A411" t="s">
+        <v>610</v>
+      </c>
+      <c r="B411" t="s">
+        <v>611</v>
+      </c>
+      <c r="C411">
+        <v>1</v>
+      </c>
+      <c r="D411" t="s">
+        <v>2</v>
+      </c>
+      <c r="E411" t="s">
+        <v>612</v>
+      </c>
+      <c r="F411" s="1">
+        <v>46083</v>
+      </c>
+      <c r="G411" s="1">
+        <v>46084</v>
+      </c>
+      <c r="H411">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="412" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A412" t="s">
+        <v>610</v>
+      </c>
+      <c r="B412" t="s">
+        <v>613</v>
+      </c>
+      <c r="C412">
+        <v>1</v>
+      </c>
+      <c r="D412" t="s">
+        <v>2</v>
+      </c>
+      <c r="E412" t="s">
+        <v>612</v>
+      </c>
+      <c r="F412" s="1">
+        <v>46132</v>
+      </c>
+      <c r="G412" s="1">
+        <v>46133</v>
+      </c>
+      <c r="H412">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="413" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A413" t="s">
+        <v>610</v>
+      </c>
+      <c r="B413" t="s">
+        <v>614</v>
+      </c>
+      <c r="C413">
+        <v>1</v>
+      </c>
+      <c r="D413" t="s">
+        <v>2</v>
+      </c>
+      <c r="E413" t="s">
+        <v>615</v>
+      </c>
+      <c r="F413" s="1">
+        <v>46157</v>
+      </c>
+      <c r="G413" s="1">
+        <v>46157</v>
+      </c>
+      <c r="H413">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="414" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A414" t="s">
+        <v>610</v>
+      </c>
+      <c r="B414" t="s">
+        <v>616</v>
+      </c>
+      <c r="C414">
+        <v>1</v>
+      </c>
+      <c r="D414" t="s">
+        <v>2</v>
+      </c>
+      <c r="E414" t="s">
+        <v>617</v>
+      </c>
+      <c r="F414" s="1">
+        <v>46168</v>
+      </c>
+      <c r="G414" s="1">
+        <v>46170</v>
+      </c>
+      <c r="H414">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="415" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A415" t="s">
+        <v>610</v>
+      </c>
+      <c r="B415" t="s">
+        <v>618</v>
+      </c>
+      <c r="C415">
+        <v>1</v>
+      </c>
+      <c r="D415" t="s">
+        <v>2</v>
+      </c>
+      <c r="E415" t="s">
+        <v>615</v>
+      </c>
+      <c r="F415" s="1">
+        <v>46244</v>
+      </c>
+      <c r="G415" s="1">
+        <v>46244</v>
+      </c>
+      <c r="H415">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="416" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A416" t="s">
+        <v>610</v>
+      </c>
+      <c r="B416" t="s">
+        <v>619</v>
+      </c>
+      <c r="C416">
+        <v>1</v>
+      </c>
+      <c r="D416" t="s">
+        <v>2</v>
+      </c>
+      <c r="E416" t="s">
+        <v>615</v>
+      </c>
+      <c r="F416" s="1">
+        <v>46247</v>
+      </c>
+      <c r="G416" s="1">
+        <v>46247</v>
+      </c>
+      <c r="H416">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="417" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A417" t="s">
+        <v>610</v>
+      </c>
+      <c r="B417" t="s">
+        <v>620</v>
+      </c>
+      <c r="C417">
+        <v>1</v>
+      </c>
+      <c r="D417" t="s">
+        <v>2</v>
+      </c>
+      <c r="E417" t="s">
+        <v>612</v>
+      </c>
+      <c r="F417" s="1">
+        <v>46247</v>
+      </c>
+      <c r="G417" s="1">
+        <v>46247</v>
+      </c>
+      <c r="H417">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/Data_ERP/Pedidos Transmicion.xlsx
+++ b/Data_ERP/Pedidos Transmicion.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sistema_Logistico_Peirano\Data_ERP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DF493AF4-F41B-4B11-B48A-1A3C46833535}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4253136C-6637-4B90-ABD3-BC686DA02DD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{390F19CB-F997-45BC-8983-03492B63BBCC}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{34F05A7A-5E3A-4627-B954-A6E5D5A3580F}"/>
   </bookViews>
   <sheets>
     <sheet name="transmicion" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1544" uniqueCount="585">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1636" uniqueCount="619">
   <si>
     <t>0001</t>
   </si>
@@ -475,6 +475,12 @@
     <t>DISTRIBUIDORA CEM SRL.</t>
   </si>
   <si>
+    <t xml:space="preserve">  212706</t>
+  </si>
+  <si>
+    <t>MARTINO S.A.</t>
+  </si>
+  <si>
     <t xml:space="preserve">  212782</t>
   </si>
   <si>
@@ -934,6 +940,12 @@
     <t>GRUPO GALU S.A.  - SANITARIOS MITRE</t>
   </si>
   <si>
+    <t xml:space="preserve">  213753</t>
+  </si>
+  <si>
+    <t>VENTURA LEANDRO ARIEL</t>
+  </si>
+  <si>
     <t xml:space="preserve">  213754</t>
   </si>
   <si>
@@ -1435,12 +1447,18 @@
     <t>SANICENTRO S.A. SANITARIOS</t>
   </si>
   <si>
+    <t xml:space="preserve">  213933</t>
+  </si>
+  <si>
     <t xml:space="preserve">  213936</t>
   </si>
   <si>
     <t>SUPERFICIES S.R.L.</t>
   </si>
   <si>
+    <t xml:space="preserve">  213938</t>
+  </si>
+  <si>
     <t xml:space="preserve">  213939</t>
   </si>
   <si>
@@ -1492,12 +1510,30 @@
     <t>GARABITO MATERIALES S.R.L.</t>
   </si>
   <si>
+    <t xml:space="preserve">  213952</t>
+  </si>
+  <si>
+    <t>LEIRO JOAQUIN C. - EL GASIFICADOR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213954</t>
+  </si>
+  <si>
+    <t>ARNALDO BUYATTI E HIJOS S.A. -BUYATTI MATERIALES</t>
+  </si>
+  <si>
     <t xml:space="preserve">  213955</t>
   </si>
   <si>
     <t xml:space="preserve">  213956</t>
   </si>
   <si>
+    <t xml:space="preserve">  213957</t>
+  </si>
+  <si>
+    <t>SANITARIOS AXANTRA S.R.L.</t>
+  </si>
+  <si>
     <t xml:space="preserve">  213959</t>
   </si>
   <si>
@@ -1543,6 +1579,75 @@
     <t xml:space="preserve">  213970</t>
   </si>
   <si>
+    <t xml:space="preserve">  213974</t>
+  </si>
+  <si>
+    <t>BERGIA SEBASTIAN R Y BERGIA S.R. SH -HIDRONORTE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213976</t>
+  </si>
+  <si>
+    <t>GRUPO GRIFO LINC.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213977</t>
+  </si>
+  <si>
+    <t>PRIATEL PISOS S.R.L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213984</t>
+  </si>
+  <si>
+    <t>EL CAÑADON  S.R.L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213987</t>
+  </si>
+  <si>
+    <t>EMPRESA MAYORISTA INDUSTRIAL SRL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213988</t>
+  </si>
+  <si>
+    <t>SANTIANO LILIANA NOEMI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213990</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213996</t>
+  </si>
+  <si>
     <t>0004</t>
   </si>
   <si>
@@ -1624,30 +1729,24 @@
     <t xml:space="preserve">    2806</t>
   </si>
   <si>
-    <t xml:space="preserve">    2807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    2809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    2810</t>
-  </si>
-  <si>
     <t xml:space="preserve">    2811</t>
   </si>
   <si>
-    <t xml:space="preserve">    2812</t>
-  </si>
-  <si>
-    <t>VARIOS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    2813</t>
-  </si>
-  <si>
     <t xml:space="preserve">    2814</t>
   </si>
   <si>
+    <t xml:space="preserve">    2815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    2816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    2817</t>
+  </si>
+  <si>
+    <t>PITA EPPER NICOLAS</t>
+  </si>
+  <si>
     <t>4444</t>
   </si>
   <si>
@@ -1717,7 +1816,10 @@
     <t xml:space="preserve">    2074</t>
   </si>
   <si>
-    <t xml:space="preserve">    2213</t>
+    <t xml:space="preserve">    2216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    2220</t>
   </si>
   <si>
     <t>9999</t>
@@ -2224,34 +2326,34 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2FF379F8-1EA4-4E01-B2EB-E18BF39F7A2A}">
-  <dimension ref="A1:H385"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1742E12D-5A2B-4BD6-9493-B75A248B4705}">
+  <dimension ref="A1:H408"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
-        <v>577</v>
+        <v>611</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>578</v>
+        <v>612</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>579</v>
+        <v>613</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>580</v>
+        <v>614</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>581</v>
+        <v>615</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>582</v>
+        <v>616</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>583</v>
+        <v>617</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>584</v>
+        <v>618</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
@@ -4085,7 +4187,7 @@
         <v>4</v>
       </c>
       <c r="D72" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E72" t="s">
         <v>130</v>
@@ -4097,7 +4199,7 @@
         <v>46252</v>
       </c>
       <c r="H72">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.2">
@@ -4400,13 +4502,13 @@
         <v>12</v>
       </c>
       <c r="E84" t="s">
-        <v>72</v>
+        <v>152</v>
       </c>
       <c r="F84" s="1">
-        <v>46232</v>
+        <v>46231</v>
       </c>
       <c r="G84" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="H84">
         <v>0</v>
@@ -4417,19 +4519,19 @@
         <v>0</v>
       </c>
       <c r="B85" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C85">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D85" t="s">
         <v>12</v>
       </c>
       <c r="E85" t="s">
-        <v>153</v>
+        <v>72</v>
       </c>
       <c r="F85" s="1">
-        <v>46233</v>
+        <v>46232</v>
       </c>
       <c r="G85" s="1">
         <v>46252</v>
@@ -4446,13 +4548,13 @@
         <v>154</v>
       </c>
       <c r="C86">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D86" t="s">
         <v>12</v>
       </c>
       <c r="E86" t="s">
-        <v>23</v>
+        <v>155</v>
       </c>
       <c r="F86" s="1">
         <v>46233</v>
@@ -4469,7 +4571,7 @@
         <v>0</v>
       </c>
       <c r="B87" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C87">
         <v>1</v>
@@ -4478,16 +4580,16 @@
         <v>2</v>
       </c>
       <c r="E87" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F87" s="1">
         <v>46233</v>
       </c>
       <c r="G87" s="1">
-        <v>46238</v>
+        <v>46252</v>
       </c>
       <c r="H87">
-        <v>23</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.2">
@@ -4495,7 +4597,7 @@
         <v>0</v>
       </c>
       <c r="B88" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C88">
         <v>1</v>
@@ -4504,7 +4606,7 @@
         <v>2</v>
       </c>
       <c r="E88" t="s">
-        <v>136</v>
+        <v>30</v>
       </c>
       <c r="F88" s="1">
         <v>46233</v>
@@ -4513,7 +4615,7 @@
         <v>46238</v>
       </c>
       <c r="H88">
-        <v>8</v>
+        <v>23</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.2">
@@ -4521,25 +4623,25 @@
         <v>0</v>
       </c>
       <c r="B89" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C89">
         <v>1</v>
       </c>
       <c r="D89" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E89" t="s">
-        <v>158</v>
+        <v>136</v>
       </c>
       <c r="F89" s="1">
         <v>46233</v>
       </c>
       <c r="G89" s="1">
-        <v>46233</v>
+        <v>46238</v>
       </c>
       <c r="H89">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.2">
@@ -4553,7 +4655,7 @@
         <v>1</v>
       </c>
       <c r="D90" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E90" t="s">
         <v>160</v>
@@ -4562,10 +4664,10 @@
         <v>46233</v>
       </c>
       <c r="G90" s="1">
-        <v>46239</v>
+        <v>46233</v>
       </c>
       <c r="H90">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.2">
@@ -4582,16 +4684,16 @@
         <v>2</v>
       </c>
       <c r="E91" t="s">
-        <v>13</v>
+        <v>162</v>
       </c>
       <c r="F91" s="1">
-        <v>46234</v>
+        <v>46233</v>
       </c>
       <c r="G91" s="1">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="H91">
-        <v>35</v>
+        <v>10</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.2">
@@ -4599,25 +4701,25 @@
         <v>0</v>
       </c>
       <c r="B92" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C92">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D92" t="s">
         <v>2</v>
       </c>
       <c r="E92" t="s">
-        <v>138</v>
+        <v>13</v>
       </c>
       <c r="F92" s="1">
         <v>46234</v>
       </c>
       <c r="G92" s="1">
-        <v>46244</v>
+        <v>46238</v>
       </c>
       <c r="H92">
-        <v>1</v>
+        <v>35</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.2">
@@ -4625,22 +4727,22 @@
         <v>0</v>
       </c>
       <c r="B93" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C93">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D93" t="s">
         <v>2</v>
       </c>
       <c r="E93" t="s">
-        <v>164</v>
+        <v>138</v>
       </c>
       <c r="F93" s="1">
         <v>46234</v>
       </c>
       <c r="G93" s="1">
-        <v>46252</v>
+        <v>46244</v>
       </c>
       <c r="H93">
         <v>1</v>
@@ -4663,13 +4765,13 @@
         <v>166</v>
       </c>
       <c r="F94" s="1">
-        <v>46237</v>
+        <v>46234</v>
       </c>
       <c r="G94" s="1">
-        <v>46241</v>
+        <v>46252</v>
       </c>
       <c r="H94">
-        <v>28</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.2">
@@ -4692,10 +4794,10 @@
         <v>46237</v>
       </c>
       <c r="G95" s="1">
-        <v>46244</v>
+        <v>46241</v>
       </c>
       <c r="H95">
-        <v>3</v>
+        <v>28</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.2">
@@ -4712,16 +4814,16 @@
         <v>2</v>
       </c>
       <c r="E96" t="s">
-        <v>35</v>
+        <v>170</v>
       </c>
       <c r="F96" s="1">
         <v>46237</v>
       </c>
       <c r="G96" s="1">
-        <v>46238</v>
+        <v>46244</v>
       </c>
       <c r="H96">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.2">
@@ -4729,25 +4831,25 @@
         <v>0</v>
       </c>
       <c r="B97" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C97">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D97" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E97" t="s">
-        <v>171</v>
+        <v>35</v>
       </c>
       <c r="F97" s="1">
         <v>46237</v>
       </c>
       <c r="G97" s="1">
-        <v>46240</v>
+        <v>46238</v>
       </c>
       <c r="H97">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.2">
@@ -4770,7 +4872,7 @@
         <v>46237</v>
       </c>
       <c r="G98" s="1">
-        <v>46238</v>
+        <v>46240</v>
       </c>
       <c r="H98">
         <v>0</v>
@@ -4810,22 +4912,22 @@
         <v>176</v>
       </c>
       <c r="C100">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D100" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E100" t="s">
-        <v>130</v>
+        <v>177</v>
       </c>
       <c r="F100" s="1">
         <v>46237</v>
       </c>
       <c r="G100" s="1">
-        <v>46240</v>
+        <v>46238</v>
       </c>
       <c r="H100">
-        <v>28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.2">
@@ -4833,7 +4935,7 @@
         <v>0</v>
       </c>
       <c r="B101" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C101">
         <v>1</v>
@@ -4842,13 +4944,13 @@
         <v>2</v>
       </c>
       <c r="E101" t="s">
-        <v>178</v>
+        <v>130</v>
       </c>
       <c r="F101" s="1">
         <v>46237</v>
       </c>
       <c r="G101" s="1">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="H101">
         <v>28</v>
@@ -4868,16 +4970,16 @@
         <v>2</v>
       </c>
       <c r="E102" t="s">
-        <v>164</v>
+        <v>180</v>
       </c>
       <c r="F102" s="1">
-        <v>46238</v>
+        <v>46237</v>
       </c>
       <c r="G102" s="1">
-        <v>46244</v>
+        <v>46239</v>
       </c>
       <c r="H102">
-        <v>3</v>
+        <v>28</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.2">
@@ -4885,7 +4987,7 @@
         <v>0</v>
       </c>
       <c r="B103" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C103">
         <v>1</v>
@@ -4894,16 +4996,16 @@
         <v>2</v>
       </c>
       <c r="E103" t="s">
-        <v>27</v>
+        <v>166</v>
       </c>
       <c r="F103" s="1">
         <v>46238</v>
       </c>
       <c r="G103" s="1">
-        <v>46238</v>
+        <v>46244</v>
       </c>
       <c r="H103">
-        <v>44</v>
+        <v>3</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.2">
@@ -4911,7 +5013,7 @@
         <v>0</v>
       </c>
       <c r="B104" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C104">
         <v>1</v>
@@ -4929,7 +5031,7 @@
         <v>46238</v>
       </c>
       <c r="H104">
-        <v>73</v>
+        <v>44</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.2">
@@ -4937,7 +5039,7 @@
         <v>0</v>
       </c>
       <c r="B105" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C105">
         <v>1</v>
@@ -4955,7 +5057,7 @@
         <v>46238</v>
       </c>
       <c r="H105">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.2">
@@ -4963,7 +5065,7 @@
         <v>0</v>
       </c>
       <c r="B106" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C106">
         <v>1</v>
@@ -4978,10 +5080,10 @@
         <v>46238</v>
       </c>
       <c r="G106" s="1">
-        <v>46239</v>
+        <v>46238</v>
       </c>
       <c r="H106">
-        <v>118</v>
+        <v>78</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.2">
@@ -4989,25 +5091,25 @@
         <v>0</v>
       </c>
       <c r="B107" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C107">
         <v>1</v>
       </c>
       <c r="D107" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E107" t="s">
-        <v>89</v>
+        <v>27</v>
       </c>
       <c r="F107" s="1">
         <v>46238</v>
       </c>
       <c r="G107" s="1">
-        <v>46252</v>
+        <v>46239</v>
       </c>
       <c r="H107">
-        <v>0</v>
+        <v>118</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.2">
@@ -5015,25 +5117,25 @@
         <v>0</v>
       </c>
       <c r="B108" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C108">
         <v>1</v>
       </c>
       <c r="D108" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E108" t="s">
-        <v>122</v>
+        <v>89</v>
       </c>
       <c r="F108" s="1">
         <v>46238</v>
       </c>
       <c r="G108" s="1">
-        <v>46240</v>
+        <v>46252</v>
       </c>
       <c r="H108">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.2">
@@ -5041,7 +5143,7 @@
         <v>0</v>
       </c>
       <c r="B109" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C109">
         <v>1</v>
@@ -5059,7 +5161,7 @@
         <v>46240</v>
       </c>
       <c r="H109">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.2">
@@ -5067,7 +5169,7 @@
         <v>0</v>
       </c>
       <c r="B110" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C110">
         <v>1</v>
@@ -5076,16 +5178,16 @@
         <v>2</v>
       </c>
       <c r="E110" t="s">
-        <v>27</v>
+        <v>122</v>
       </c>
       <c r="F110" s="1">
-        <v>46239</v>
+        <v>46238</v>
       </c>
       <c r="G110" s="1">
-        <v>46252</v>
+        <v>46240</v>
       </c>
       <c r="H110">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.2">
@@ -5093,7 +5195,7 @@
         <v>0</v>
       </c>
       <c r="B111" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C111">
         <v>1</v>
@@ -5108,10 +5210,10 @@
         <v>46239</v>
       </c>
       <c r="G111" s="1">
-        <v>46239</v>
+        <v>46252</v>
       </c>
       <c r="H111">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.2">
@@ -5119,7 +5221,7 @@
         <v>0</v>
       </c>
       <c r="B112" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C112">
         <v>1</v>
@@ -5128,16 +5230,16 @@
         <v>2</v>
       </c>
       <c r="E112" t="s">
-        <v>190</v>
+        <v>27</v>
       </c>
       <c r="F112" s="1">
         <v>46239</v>
       </c>
       <c r="G112" s="1">
-        <v>46240</v>
+        <v>46239</v>
       </c>
       <c r="H112">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.2">
@@ -5163,7 +5265,7 @@
         <v>46240</v>
       </c>
       <c r="H113">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.2">
@@ -5189,7 +5291,7 @@
         <v>46240</v>
       </c>
       <c r="H114">
-        <v>2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.2">
@@ -5212,7 +5314,7 @@
         <v>46239</v>
       </c>
       <c r="G115" s="1">
-        <v>46241</v>
+        <v>46240</v>
       </c>
       <c r="H115">
         <v>2</v>
@@ -5229,19 +5331,19 @@
         <v>1</v>
       </c>
       <c r="D116" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E116" t="s">
-        <v>23</v>
+        <v>198</v>
       </c>
       <c r="F116" s="1">
         <v>46239</v>
       </c>
       <c r="G116" s="1">
-        <v>46252</v>
+        <v>46241</v>
       </c>
       <c r="H116">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.2">
@@ -5249,7 +5351,7 @@
         <v>0</v>
       </c>
       <c r="B117" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C117">
         <v>1</v>
@@ -5258,16 +5360,16 @@
         <v>2</v>
       </c>
       <c r="E117" t="s">
-        <v>120</v>
+        <v>23</v>
       </c>
       <c r="F117" s="1">
-        <v>46240</v>
+        <v>46239</v>
       </c>
       <c r="G117" s="1">
-        <v>46244</v>
+        <v>46252</v>
       </c>
       <c r="H117">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.2">
@@ -5275,7 +5377,7 @@
         <v>0</v>
       </c>
       <c r="B118" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C118">
         <v>1</v>
@@ -5284,16 +5386,16 @@
         <v>2</v>
       </c>
       <c r="E118" t="s">
-        <v>27</v>
+        <v>120</v>
       </c>
       <c r="F118" s="1">
         <v>46240</v>
       </c>
       <c r="G118" s="1">
-        <v>46252</v>
+        <v>46244</v>
       </c>
       <c r="H118">
-        <v>39</v>
+        <v>2</v>
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.2">
@@ -5301,7 +5403,7 @@
         <v>0</v>
       </c>
       <c r="B119" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C119">
         <v>1</v>
@@ -5319,7 +5421,7 @@
         <v>46252</v>
       </c>
       <c r="H119">
-        <v>2</v>
+        <v>39</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.2">
@@ -5327,7 +5429,7 @@
         <v>0</v>
       </c>
       <c r="B120" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C120">
         <v>1</v>
@@ -5345,7 +5447,7 @@
         <v>46252</v>
       </c>
       <c r="H120">
-        <v>31</v>
+        <v>2</v>
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.2">
@@ -5353,7 +5455,7 @@
         <v>0</v>
       </c>
       <c r="B121" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C121">
         <v>1</v>
@@ -5371,7 +5473,7 @@
         <v>46252</v>
       </c>
       <c r="H121">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.2">
@@ -5379,7 +5481,7 @@
         <v>0</v>
       </c>
       <c r="B122" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C122">
         <v>1</v>
@@ -5397,7 +5499,7 @@
         <v>46252</v>
       </c>
       <c r="H122">
-        <v>17</v>
+        <v>29</v>
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.2">
@@ -5405,7 +5507,7 @@
         <v>0</v>
       </c>
       <c r="B123" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C123">
         <v>1</v>
@@ -5423,7 +5525,7 @@
         <v>46252</v>
       </c>
       <c r="H123">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.2">
@@ -5431,7 +5533,7 @@
         <v>0</v>
       </c>
       <c r="B124" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C124">
         <v>1</v>
@@ -5449,7 +5551,7 @@
         <v>46252</v>
       </c>
       <c r="H124">
-        <v>29</v>
+        <v>19</v>
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.2">
@@ -5457,7 +5559,7 @@
         <v>0</v>
       </c>
       <c r="B125" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C125">
         <v>1</v>
@@ -5475,7 +5577,7 @@
         <v>46252</v>
       </c>
       <c r="H125">
-        <v>19</v>
+        <v>29</v>
       </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.2">
@@ -5483,7 +5585,7 @@
         <v>0</v>
       </c>
       <c r="B126" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C126">
         <v>1</v>
@@ -5501,7 +5603,7 @@
         <v>46252</v>
       </c>
       <c r="H126">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.2">
@@ -5509,7 +5611,7 @@
         <v>0</v>
       </c>
       <c r="B127" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C127">
         <v>1</v>
@@ -5527,7 +5629,7 @@
         <v>46252</v>
       </c>
       <c r="H127">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.2">
@@ -5535,16 +5637,16 @@
         <v>0</v>
       </c>
       <c r="B128" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C128">
         <v>1</v>
       </c>
       <c r="D128" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E128" t="s">
-        <v>210</v>
+        <v>27</v>
       </c>
       <c r="F128" s="1">
         <v>46240</v>
@@ -5553,7 +5655,7 @@
         <v>46252</v>
       </c>
       <c r="H128">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.2">
@@ -5567,7 +5669,7 @@
         <v>1</v>
       </c>
       <c r="D129" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E129" t="s">
         <v>212</v>
@@ -5576,10 +5678,10 @@
         <v>46240</v>
       </c>
       <c r="G129" s="1">
-        <v>46241</v>
+        <v>46252</v>
       </c>
       <c r="H129">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.2">
@@ -5596,13 +5698,13 @@
         <v>2</v>
       </c>
       <c r="E130" t="s">
-        <v>27</v>
+        <v>214</v>
       </c>
       <c r="F130" s="1">
+        <v>46240</v>
+      </c>
+      <c r="G130" s="1">
         <v>46241</v>
-      </c>
-      <c r="G130" s="1">
-        <v>46252</v>
       </c>
       <c r="H130">
         <v>2</v>
@@ -5613,10 +5715,10 @@
         <v>0</v>
       </c>
       <c r="B131" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C131">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D131" t="s">
         <v>2</v>
@@ -5628,10 +5730,10 @@
         <v>46241</v>
       </c>
       <c r="G131" s="1">
-        <v>46245</v>
+        <v>46252</v>
       </c>
       <c r="H131">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.2">
@@ -5639,25 +5741,25 @@
         <v>0</v>
       </c>
       <c r="B132" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C132">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D132" t="s">
         <v>2</v>
       </c>
       <c r="E132" t="s">
-        <v>216</v>
+        <v>27</v>
       </c>
       <c r="F132" s="1">
         <v>46241</v>
       </c>
       <c r="G132" s="1">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="H132">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.2">
@@ -5674,16 +5776,16 @@
         <v>2</v>
       </c>
       <c r="E133" t="s">
-        <v>27</v>
+        <v>218</v>
       </c>
       <c r="F133" s="1">
         <v>46241</v>
       </c>
       <c r="G133" s="1">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="H133">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.2">
@@ -5691,7 +5793,7 @@
         <v>0</v>
       </c>
       <c r="B134" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C134">
         <v>1</v>
@@ -5700,16 +5802,16 @@
         <v>2</v>
       </c>
       <c r="E134" t="s">
-        <v>130</v>
+        <v>27</v>
       </c>
       <c r="F134" s="1">
         <v>46241</v>
       </c>
       <c r="G134" s="1">
-        <v>46245</v>
+        <v>46241</v>
       </c>
       <c r="H134">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.2">
@@ -5717,7 +5819,7 @@
         <v>0</v>
       </c>
       <c r="B135" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C135">
         <v>1</v>
@@ -5726,16 +5828,16 @@
         <v>2</v>
       </c>
       <c r="E135" t="s">
-        <v>220</v>
+        <v>130</v>
       </c>
       <c r="F135" s="1">
         <v>46241</v>
       </c>
       <c r="G135" s="1">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="H135">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.2">
@@ -5755,13 +5857,13 @@
         <v>222</v>
       </c>
       <c r="F136" s="1">
-        <v>46242</v>
+        <v>46241</v>
       </c>
       <c r="G136" s="1">
         <v>46244</v>
       </c>
       <c r="H136">
-        <v>2</v>
+        <v>21</v>
       </c>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.2">
@@ -5781,13 +5883,13 @@
         <v>224</v>
       </c>
       <c r="F137" s="1">
-        <v>46244</v>
+        <v>46242</v>
       </c>
       <c r="G137" s="1">
         <v>46244</v>
       </c>
       <c r="H137">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.2">
@@ -5801,7 +5903,7 @@
         <v>1</v>
       </c>
       <c r="D138" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E138" t="s">
         <v>226</v>
@@ -5810,10 +5912,10 @@
         <v>46244</v>
       </c>
       <c r="G138" s="1">
-        <v>46252</v>
+        <v>46244</v>
       </c>
       <c r="H138">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.2">
@@ -5827,16 +5929,16 @@
         <v>1</v>
       </c>
       <c r="D139" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E139" t="s">
-        <v>112</v>
+        <v>228</v>
       </c>
       <c r="F139" s="1">
         <v>46244</v>
       </c>
       <c r="G139" s="1">
-        <v>46244</v>
+        <v>46252</v>
       </c>
       <c r="H139">
         <v>0</v>
@@ -5847,25 +5949,25 @@
         <v>0</v>
       </c>
       <c r="B140" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C140">
         <v>1</v>
       </c>
       <c r="D140" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E140" t="s">
-        <v>229</v>
+        <v>112</v>
       </c>
       <c r="F140" s="1">
         <v>46244</v>
       </c>
       <c r="G140" s="1">
-        <v>46246</v>
+        <v>46244</v>
       </c>
       <c r="H140">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.2">
@@ -5888,10 +5990,10 @@
         <v>46244</v>
       </c>
       <c r="G141" s="1">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="H141">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.2">
@@ -5911,10 +6013,10 @@
         <v>233</v>
       </c>
       <c r="F142" s="1">
+        <v>46244</v>
+      </c>
+      <c r="G142" s="1">
         <v>46245</v>
-      </c>
-      <c r="G142" s="1">
-        <v>46247</v>
       </c>
       <c r="H142">
         <v>1</v>
@@ -5931,7 +6033,7 @@
         <v>1</v>
       </c>
       <c r="D143" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E143" t="s">
         <v>235</v>
@@ -5940,10 +6042,10 @@
         <v>46245</v>
       </c>
       <c r="G143" s="1">
-        <v>46252</v>
+        <v>46247</v>
       </c>
       <c r="H143">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.2">
@@ -5983,16 +6085,16 @@
         <v>1</v>
       </c>
       <c r="D145" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E145" t="s">
-        <v>85</v>
+        <v>239</v>
       </c>
       <c r="F145" s="1">
         <v>46245</v>
       </c>
       <c r="G145" s="1">
-        <v>46246</v>
+        <v>46252</v>
       </c>
       <c r="H145">
         <v>0</v>
@@ -6003,7 +6105,7 @@
         <v>0</v>
       </c>
       <c r="B146" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C146">
         <v>1</v>
@@ -6018,7 +6120,7 @@
         <v>46245</v>
       </c>
       <c r="G146" s="1">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="H146">
         <v>0</v>
@@ -6029,7 +6131,7 @@
         <v>0</v>
       </c>
       <c r="B147" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C147">
         <v>1</v>
@@ -6055,25 +6157,25 @@
         <v>0</v>
       </c>
       <c r="B148" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C148">
         <v>1</v>
       </c>
       <c r="D148" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E148" t="s">
-        <v>39</v>
+        <v>85</v>
       </c>
       <c r="F148" s="1">
         <v>46245</v>
       </c>
       <c r="G148" s="1">
-        <v>46246</v>
+        <v>46245</v>
       </c>
       <c r="H148">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.2">
@@ -6081,7 +6183,7 @@
         <v>0</v>
       </c>
       <c r="B149" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C149">
         <v>1</v>
@@ -6090,7 +6192,7 @@
         <v>2</v>
       </c>
       <c r="E149" t="s">
-        <v>243</v>
+        <v>39</v>
       </c>
       <c r="F149" s="1">
         <v>46245</v>
@@ -6099,7 +6201,7 @@
         <v>46246</v>
       </c>
       <c r="H149">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.2">
@@ -6125,7 +6227,7 @@
         <v>46246</v>
       </c>
       <c r="H150">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.2">
@@ -6142,7 +6244,7 @@
         <v>2</v>
       </c>
       <c r="E151" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="F151" s="1">
         <v>46245</v>
@@ -6151,7 +6253,7 @@
         <v>46246</v>
       </c>
       <c r="H151">
-        <v>22</v>
+        <v>4</v>
       </c>
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.2">
@@ -6159,25 +6261,25 @@
         <v>0</v>
       </c>
       <c r="B152" t="s">
+        <v>248</v>
+      </c>
+      <c r="C152">
+        <v>1</v>
+      </c>
+      <c r="D152" t="s">
+        <v>2</v>
+      </c>
+      <c r="E152" t="s">
         <v>247</v>
       </c>
-      <c r="C152">
-        <v>1</v>
-      </c>
-      <c r="D152" t="s">
-        <v>12</v>
-      </c>
-      <c r="E152" t="s">
-        <v>27</v>
-      </c>
       <c r="F152" s="1">
+        <v>46245</v>
+      </c>
+      <c r="G152" s="1">
         <v>46246</v>
       </c>
-      <c r="G152" s="1">
-        <v>46252</v>
-      </c>
       <c r="H152">
-        <v>0</v>
+        <v>22</v>
       </c>
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.2">
@@ -6185,7 +6287,7 @@
         <v>0</v>
       </c>
       <c r="B153" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C153">
         <v>1</v>
@@ -6194,7 +6296,7 @@
         <v>12</v>
       </c>
       <c r="E153" t="s">
-        <v>190</v>
+        <v>27</v>
       </c>
       <c r="F153" s="1">
         <v>46246</v>
@@ -6211,25 +6313,25 @@
         <v>0</v>
       </c>
       <c r="B154" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C154">
         <v>1</v>
       </c>
       <c r="D154" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E154" t="s">
-        <v>66</v>
+        <v>192</v>
       </c>
       <c r="F154" s="1">
         <v>46246</v>
       </c>
       <c r="G154" s="1">
-        <v>46247</v>
+        <v>46252</v>
       </c>
       <c r="H154">
-        <v>21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.2">
@@ -6237,13 +6339,13 @@
         <v>0</v>
       </c>
       <c r="B155" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C155">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D155" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E155" t="s">
         <v>66</v>
@@ -6252,10 +6354,10 @@
         <v>46246</v>
       </c>
       <c r="G155" s="1">
-        <v>46252</v>
+        <v>46247</v>
       </c>
       <c r="H155">
-        <v>0</v>
+        <v>21</v>
       </c>
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.2">
@@ -6263,16 +6365,16 @@
         <v>0</v>
       </c>
       <c r="B156" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C156">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D156" t="s">
         <v>2</v>
       </c>
       <c r="E156" t="s">
-        <v>252</v>
+        <v>66</v>
       </c>
       <c r="F156" s="1">
         <v>46246</v>
@@ -6281,7 +6383,7 @@
         <v>46252</v>
       </c>
       <c r="H156">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.2">
@@ -6298,7 +6400,7 @@
         <v>2</v>
       </c>
       <c r="E157" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="F157" s="1">
         <v>46246</v>
@@ -6307,7 +6409,7 @@
         <v>46252</v>
       </c>
       <c r="H157">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.2">
@@ -6315,25 +6417,25 @@
         <v>0</v>
       </c>
       <c r="B158" t="s">
+        <v>255</v>
+      </c>
+      <c r="C158">
+        <v>1</v>
+      </c>
+      <c r="D158" t="s">
+        <v>2</v>
+      </c>
+      <c r="E158" t="s">
         <v>254</v>
-      </c>
-      <c r="C158">
-        <v>1</v>
-      </c>
-      <c r="D158" t="s">
-        <v>2</v>
-      </c>
-      <c r="E158" t="s">
-        <v>255</v>
       </c>
       <c r="F158" s="1">
         <v>46246</v>
       </c>
       <c r="G158" s="1">
-        <v>46247</v>
+        <v>46252</v>
       </c>
       <c r="H158">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.2">
@@ -6356,7 +6458,7 @@
         <v>46246</v>
       </c>
       <c r="G159" s="1">
-        <v>46252</v>
+        <v>46247</v>
       </c>
       <c r="H159">
         <v>4</v>
@@ -6370,22 +6472,22 @@
         <v>258</v>
       </c>
       <c r="C160">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D160" t="s">
         <v>2</v>
       </c>
       <c r="E160" t="s">
-        <v>104</v>
+        <v>259</v>
       </c>
       <c r="F160" s="1">
         <v>46246</v>
       </c>
       <c r="G160" s="1">
-        <v>46247</v>
+        <v>46252</v>
       </c>
       <c r="H160">
-        <v>46</v>
+        <v>4</v>
       </c>
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.2">
@@ -6393,25 +6495,25 @@
         <v>0</v>
       </c>
       <c r="B161" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C161">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D161" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E161" t="s">
-        <v>260</v>
+        <v>104</v>
       </c>
       <c r="F161" s="1">
         <v>46246</v>
       </c>
       <c r="G161" s="1">
-        <v>46252</v>
+        <v>46247</v>
       </c>
       <c r="H161">
-        <v>0</v>
+        <v>46</v>
       </c>
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.2">
@@ -6454,7 +6556,7 @@
         <v>12</v>
       </c>
       <c r="E163" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="F163" s="1">
         <v>46246</v>
@@ -6471,16 +6573,16 @@
         <v>0</v>
       </c>
       <c r="B164" t="s">
+        <v>265</v>
+      </c>
+      <c r="C164">
+        <v>1</v>
+      </c>
+      <c r="D164" t="s">
+        <v>12</v>
+      </c>
+      <c r="E164" t="s">
         <v>264</v>
-      </c>
-      <c r="C164">
-        <v>1</v>
-      </c>
-      <c r="D164" t="s">
-        <v>12</v>
-      </c>
-      <c r="E164" t="s">
-        <v>265</v>
       </c>
       <c r="F164" s="1">
         <v>46246</v>
@@ -6503,10 +6605,10 @@
         <v>1</v>
       </c>
       <c r="D165" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E165" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="F165" s="1">
         <v>46246</v>
@@ -6515,7 +6617,7 @@
         <v>46252</v>
       </c>
       <c r="H165">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.2">
@@ -6523,25 +6625,25 @@
         <v>0</v>
       </c>
       <c r="B166" t="s">
+        <v>268</v>
+      </c>
+      <c r="C166">
+        <v>1</v>
+      </c>
+      <c r="D166" t="s">
+        <v>2</v>
+      </c>
+      <c r="E166" t="s">
         <v>267</v>
       </c>
-      <c r="C166">
-        <v>1</v>
-      </c>
-      <c r="D166" t="s">
-        <v>12</v>
-      </c>
-      <c r="E166" t="s">
-        <v>27</v>
-      </c>
       <c r="F166" s="1">
-        <v>46247</v>
+        <v>46246</v>
       </c>
       <c r="G166" s="1">
         <v>46252</v>
       </c>
       <c r="H166">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.2">
@@ -6549,7 +6651,7 @@
         <v>0</v>
       </c>
       <c r="B167" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C167">
         <v>1</v>
@@ -6575,7 +6677,7 @@
         <v>0</v>
       </c>
       <c r="B168" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C168">
         <v>1</v>
@@ -6601,7 +6703,7 @@
         <v>0</v>
       </c>
       <c r="B169" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C169">
         <v>1</v>
@@ -6627,7 +6729,7 @@
         <v>0</v>
       </c>
       <c r="B170" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C170">
         <v>1</v>
@@ -6653,7 +6755,7 @@
         <v>0</v>
       </c>
       <c r="B171" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C171">
         <v>1</v>
@@ -6679,7 +6781,7 @@
         <v>0</v>
       </c>
       <c r="B172" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C172">
         <v>1</v>
@@ -6705,7 +6807,7 @@
         <v>0</v>
       </c>
       <c r="B173" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C173">
         <v>1</v>
@@ -6731,10 +6833,10 @@
         <v>0</v>
       </c>
       <c r="B174" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C174">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D174" t="s">
         <v>12</v>
@@ -6757,10 +6859,10 @@
         <v>0</v>
       </c>
       <c r="B175" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C175">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D175" t="s">
         <v>12</v>
@@ -6783,7 +6885,7 @@
         <v>0</v>
       </c>
       <c r="B176" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C176">
         <v>1</v>
@@ -6809,7 +6911,7 @@
         <v>0</v>
       </c>
       <c r="B177" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C177">
         <v>1</v>
@@ -6818,7 +6920,7 @@
         <v>12</v>
       </c>
       <c r="E177" t="s">
-        <v>262</v>
+        <v>27</v>
       </c>
       <c r="F177" s="1">
         <v>46247</v>
@@ -6835,7 +6937,7 @@
         <v>0</v>
       </c>
       <c r="B178" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C178">
         <v>1</v>
@@ -6844,7 +6946,7 @@
         <v>12</v>
       </c>
       <c r="E178" t="s">
-        <v>30</v>
+        <v>264</v>
       </c>
       <c r="F178" s="1">
         <v>46247</v>
@@ -6861,7 +6963,7 @@
         <v>0</v>
       </c>
       <c r="B179" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C179">
         <v>1</v>
@@ -6870,7 +6972,7 @@
         <v>2</v>
       </c>
       <c r="E179" t="s">
-        <v>281</v>
+        <v>30</v>
       </c>
       <c r="F179" s="1">
         <v>46247</v>
@@ -6879,7 +6981,7 @@
         <v>46252</v>
       </c>
       <c r="H179">
-        <v>36</v>
+        <v>86</v>
       </c>
     </row>
     <row r="180" spans="1:8" x14ac:dyDescent="0.2">
@@ -6893,10 +6995,10 @@
         <v>1</v>
       </c>
       <c r="D180" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E180" t="s">
-        <v>66</v>
+        <v>283</v>
       </c>
       <c r="F180" s="1">
         <v>46247</v>
@@ -6905,7 +7007,7 @@
         <v>46252</v>
       </c>
       <c r="H180">
-        <v>0</v>
+        <v>36</v>
       </c>
     </row>
     <row r="181" spans="1:8" x14ac:dyDescent="0.2">
@@ -6913,16 +7015,16 @@
         <v>0</v>
       </c>
       <c r="B181" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C181">
         <v>1</v>
       </c>
       <c r="D181" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E181" t="s">
-        <v>134</v>
+        <v>66</v>
       </c>
       <c r="F181" s="1">
         <v>46247</v>
@@ -6931,7 +7033,7 @@
         <v>46252</v>
       </c>
       <c r="H181">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="182" spans="1:8" x14ac:dyDescent="0.2">
@@ -6939,7 +7041,7 @@
         <v>0</v>
       </c>
       <c r="B182" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C182">
         <v>1</v>
@@ -6948,7 +7050,7 @@
         <v>12</v>
       </c>
       <c r="E182" t="s">
-        <v>224</v>
+        <v>134</v>
       </c>
       <c r="F182" s="1">
         <v>46247</v>
@@ -6965,7 +7067,7 @@
         <v>0</v>
       </c>
       <c r="B183" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C183">
         <v>1</v>
@@ -6974,7 +7076,7 @@
         <v>12</v>
       </c>
       <c r="E183" t="s">
-        <v>286</v>
+        <v>226</v>
       </c>
       <c r="F183" s="1">
         <v>46247</v>
@@ -7023,7 +7125,7 @@
         <v>1</v>
       </c>
       <c r="D185" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E185" t="s">
         <v>290</v>
@@ -7035,7 +7137,7 @@
         <v>46252</v>
       </c>
       <c r="H185">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="186" spans="1:8" x14ac:dyDescent="0.2">
@@ -7049,7 +7151,7 @@
         <v>1</v>
       </c>
       <c r="D186" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E186" t="s">
         <v>292</v>
@@ -7058,10 +7160,10 @@
         <v>46247</v>
       </c>
       <c r="G186" s="1">
-        <v>46247</v>
+        <v>46252</v>
       </c>
       <c r="H186">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="187" spans="1:8" x14ac:dyDescent="0.2">
@@ -7072,10 +7174,10 @@
         <v>293</v>
       </c>
       <c r="C187">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D187" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E187" t="s">
         <v>294</v>
@@ -7084,7 +7186,7 @@
         <v>46247</v>
       </c>
       <c r="G187" s="1">
-        <v>46252</v>
+        <v>46247</v>
       </c>
       <c r="H187">
         <v>0</v>
@@ -7098,13 +7200,13 @@
         <v>295</v>
       </c>
       <c r="C188">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D188" t="s">
         <v>12</v>
       </c>
       <c r="E188" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="F188" s="1">
         <v>46247</v>
@@ -7121,16 +7223,16 @@
         <v>0</v>
       </c>
       <c r="B189" t="s">
+        <v>297</v>
+      </c>
+      <c r="C189">
+        <v>1</v>
+      </c>
+      <c r="D189" t="s">
+        <v>12</v>
+      </c>
+      <c r="E189" t="s">
         <v>296</v>
-      </c>
-      <c r="C189">
-        <v>1</v>
-      </c>
-      <c r="D189" t="s">
-        <v>12</v>
-      </c>
-      <c r="E189" t="s">
-        <v>66</v>
       </c>
       <c r="F189" s="1">
         <v>46247</v>
@@ -7147,16 +7249,16 @@
         <v>0</v>
       </c>
       <c r="B190" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C190">
         <v>1</v>
       </c>
       <c r="D190" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E190" t="s">
-        <v>298</v>
+        <v>66</v>
       </c>
       <c r="F190" s="1">
         <v>46247</v>
@@ -7165,7 +7267,7 @@
         <v>46252</v>
       </c>
       <c r="H190">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="191" spans="1:8" x14ac:dyDescent="0.2">
@@ -7176,13 +7278,13 @@
         <v>299</v>
       </c>
       <c r="C191">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D191" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E191" t="s">
-        <v>145</v>
+        <v>300</v>
       </c>
       <c r="F191" s="1">
         <v>46247</v>
@@ -7199,16 +7301,16 @@
         <v>0</v>
       </c>
       <c r="B192" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C192">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D192" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E192" t="s">
-        <v>301</v>
+        <v>145</v>
       </c>
       <c r="F192" s="1">
         <v>46247</v>
@@ -7292,7 +7394,7 @@
         <v>46247</v>
       </c>
       <c r="G195" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="H195">
         <v>0</v>
@@ -7309,7 +7411,7 @@
         <v>1</v>
       </c>
       <c r="D196" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E196" t="s">
         <v>309</v>
@@ -7321,7 +7423,7 @@
         <v>46252</v>
       </c>
       <c r="H196">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="197" spans="1:8" x14ac:dyDescent="0.2">
@@ -7361,19 +7463,19 @@
         <v>1</v>
       </c>
       <c r="D198" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E198" t="s">
-        <v>27</v>
+        <v>313</v>
       </c>
       <c r="F198" s="1">
-        <v>46248</v>
+        <v>46247</v>
       </c>
       <c r="G198" s="1">
         <v>46252</v>
       </c>
       <c r="H198">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="199" spans="1:8" x14ac:dyDescent="0.2">
@@ -7381,25 +7483,25 @@
         <v>0</v>
       </c>
       <c r="B199" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C199">
         <v>1</v>
       </c>
       <c r="D199" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E199" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F199" s="1">
-        <v>46248</v>
+        <v>46247</v>
       </c>
       <c r="G199" s="1">
         <v>46252</v>
       </c>
       <c r="H199">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="200" spans="1:8" x14ac:dyDescent="0.2">
@@ -7407,7 +7509,7 @@
         <v>0</v>
       </c>
       <c r="B200" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C200">
         <v>1</v>
@@ -7416,7 +7518,7 @@
         <v>12</v>
       </c>
       <c r="E200" t="s">
-        <v>307</v>
+        <v>27</v>
       </c>
       <c r="F200" s="1">
         <v>46248</v>
@@ -7433,16 +7535,16 @@
         <v>0</v>
       </c>
       <c r="B201" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C201">
         <v>1</v>
       </c>
       <c r="D201" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E201" t="s">
-        <v>13</v>
+        <v>318</v>
       </c>
       <c r="F201" s="1">
         <v>46248</v>
@@ -7451,7 +7553,7 @@
         <v>46252</v>
       </c>
       <c r="H201">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="202" spans="1:8" x14ac:dyDescent="0.2">
@@ -7459,16 +7561,16 @@
         <v>0</v>
       </c>
       <c r="B202" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="C202">
         <v>1</v>
       </c>
       <c r="D202" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E202" t="s">
-        <v>13</v>
+        <v>311</v>
       </c>
       <c r="F202" s="1">
         <v>46248</v>
@@ -7477,7 +7579,7 @@
         <v>46252</v>
       </c>
       <c r="H202">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="203" spans="1:8" x14ac:dyDescent="0.2">
@@ -7485,7 +7587,7 @@
         <v>0</v>
       </c>
       <c r="B203" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C203">
         <v>1</v>
@@ -7494,7 +7596,7 @@
         <v>12</v>
       </c>
       <c r="E203" t="s">
-        <v>319</v>
+        <v>13</v>
       </c>
       <c r="F203" s="1">
         <v>46248</v>
@@ -7511,7 +7613,7 @@
         <v>0</v>
       </c>
       <c r="B204" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C204">
         <v>1</v>
@@ -7520,7 +7622,7 @@
         <v>12</v>
       </c>
       <c r="E204" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="F204" s="1">
         <v>46248</v>
@@ -7537,7 +7639,7 @@
         <v>0</v>
       </c>
       <c r="B205" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C205">
         <v>1</v>
@@ -7546,7 +7648,7 @@
         <v>12</v>
       </c>
       <c r="E205" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="F205" s="1">
         <v>46248</v>
@@ -7563,16 +7665,16 @@
         <v>0</v>
       </c>
       <c r="B206" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C206">
         <v>1</v>
       </c>
       <c r="D206" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E206" t="s">
-        <v>324</v>
+        <v>39</v>
       </c>
       <c r="F206" s="1">
         <v>46248</v>
@@ -7581,7 +7683,7 @@
         <v>46252</v>
       </c>
       <c r="H206">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="207" spans="1:8" x14ac:dyDescent="0.2">
@@ -7595,7 +7697,7 @@
         <v>1</v>
       </c>
       <c r="D207" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E207" t="s">
         <v>326</v>
@@ -7607,7 +7709,7 @@
         <v>46252</v>
       </c>
       <c r="H207">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="208" spans="1:8" x14ac:dyDescent="0.2">
@@ -7624,7 +7726,7 @@
         <v>12</v>
       </c>
       <c r="E208" t="s">
-        <v>72</v>
+        <v>328</v>
       </c>
       <c r="F208" s="1">
         <v>46248</v>
@@ -7641,16 +7743,16 @@
         <v>0</v>
       </c>
       <c r="B209" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C209">
         <v>1</v>
       </c>
       <c r="D209" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E209" t="s">
-        <v>72</v>
+        <v>330</v>
       </c>
       <c r="F209" s="1">
         <v>46248</v>
@@ -7659,7 +7761,7 @@
         <v>46252</v>
       </c>
       <c r="H209">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="210" spans="1:8" x14ac:dyDescent="0.2">
@@ -7667,7 +7769,7 @@
         <v>0</v>
       </c>
       <c r="B210" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C210">
         <v>1</v>
@@ -7693,7 +7795,7 @@
         <v>0</v>
       </c>
       <c r="B211" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C211">
         <v>1</v>
@@ -7702,7 +7804,7 @@
         <v>12</v>
       </c>
       <c r="E211" t="s">
-        <v>331</v>
+        <v>72</v>
       </c>
       <c r="F211" s="1">
         <v>46248</v>
@@ -7719,7 +7821,7 @@
         <v>0</v>
       </c>
       <c r="B212" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C212">
         <v>1</v>
@@ -7728,7 +7830,7 @@
         <v>12</v>
       </c>
       <c r="E212" t="s">
-        <v>333</v>
+        <v>72</v>
       </c>
       <c r="F212" s="1">
         <v>46248</v>
@@ -7751,7 +7853,7 @@
         <v>1</v>
       </c>
       <c r="D213" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E213" t="s">
         <v>335</v>
@@ -7763,7 +7865,7 @@
         <v>46252</v>
       </c>
       <c r="H213">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="214" spans="1:8" x14ac:dyDescent="0.2">
@@ -7806,7 +7908,7 @@
         <v>12</v>
       </c>
       <c r="E215" t="s">
-        <v>127</v>
+        <v>339</v>
       </c>
       <c r="F215" s="1">
         <v>46248</v>
@@ -7823,7 +7925,7 @@
         <v>0</v>
       </c>
       <c r="B216" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C216">
         <v>1</v>
@@ -7832,7 +7934,7 @@
         <v>12</v>
       </c>
       <c r="E216" t="s">
-        <v>127</v>
+        <v>341</v>
       </c>
       <c r="F216" s="1">
         <v>46248</v>
@@ -7849,7 +7951,7 @@
         <v>0</v>
       </c>
       <c r="B217" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="C217">
         <v>1</v>
@@ -7858,7 +7960,7 @@
         <v>12</v>
       </c>
       <c r="E217" t="s">
-        <v>341</v>
+        <v>127</v>
       </c>
       <c r="F217" s="1">
         <v>46248</v>
@@ -7875,7 +7977,7 @@
         <v>0</v>
       </c>
       <c r="B218" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C218">
         <v>1</v>
@@ -7884,7 +7986,7 @@
         <v>12</v>
       </c>
       <c r="E218" t="s">
-        <v>343</v>
+        <v>127</v>
       </c>
       <c r="F218" s="1">
         <v>46248</v>
@@ -7907,10 +8009,10 @@
         <v>1</v>
       </c>
       <c r="D219" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E219" t="s">
-        <v>72</v>
+        <v>345</v>
       </c>
       <c r="F219" s="1">
         <v>46248</v>
@@ -7919,7 +8021,7 @@
         <v>46252</v>
       </c>
       <c r="H219">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="220" spans="1:8" x14ac:dyDescent="0.2">
@@ -7927,7 +8029,7 @@
         <v>0</v>
       </c>
       <c r="B220" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C220">
         <v>1</v>
@@ -7936,7 +8038,7 @@
         <v>12</v>
       </c>
       <c r="E220" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F220" s="1">
         <v>46248</v>
@@ -7953,7 +8055,7 @@
         <v>0</v>
       </c>
       <c r="B221" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C221">
         <v>1</v>
@@ -7962,7 +8064,7 @@
         <v>12</v>
       </c>
       <c r="E221" t="s">
-        <v>294</v>
+        <v>72</v>
       </c>
       <c r="F221" s="1">
         <v>46248</v>
@@ -7979,7 +8081,7 @@
         <v>0</v>
       </c>
       <c r="B222" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C222">
         <v>1</v>
@@ -7988,7 +8090,7 @@
         <v>12</v>
       </c>
       <c r="E222" t="s">
-        <v>85</v>
+        <v>350</v>
       </c>
       <c r="F222" s="1">
         <v>46248</v>
@@ -8005,7 +8107,7 @@
         <v>0</v>
       </c>
       <c r="B223" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="C223">
         <v>1</v>
@@ -8014,7 +8116,7 @@
         <v>12</v>
       </c>
       <c r="E223" t="s">
-        <v>350</v>
+        <v>296</v>
       </c>
       <c r="F223" s="1">
         <v>46248</v>
@@ -8031,7 +8133,7 @@
         <v>0</v>
       </c>
       <c r="B224" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C224">
         <v>1</v>
@@ -8040,7 +8142,7 @@
         <v>12</v>
       </c>
       <c r="E224" t="s">
-        <v>352</v>
+        <v>85</v>
       </c>
       <c r="F224" s="1">
         <v>46248</v>
@@ -8066,7 +8168,7 @@
         <v>12</v>
       </c>
       <c r="E225" t="s">
-        <v>290</v>
+        <v>354</v>
       </c>
       <c r="F225" s="1">
         <v>46248</v>
@@ -8083,7 +8185,7 @@
         <v>0</v>
       </c>
       <c r="B226" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C226">
         <v>1</v>
@@ -8092,7 +8194,7 @@
         <v>12</v>
       </c>
       <c r="E226" t="s">
-        <v>35</v>
+        <v>356</v>
       </c>
       <c r="F226" s="1">
         <v>46248</v>
@@ -8109,7 +8211,7 @@
         <v>0</v>
       </c>
       <c r="B227" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C227">
         <v>1</v>
@@ -8118,7 +8220,7 @@
         <v>12</v>
       </c>
       <c r="E227" t="s">
-        <v>35</v>
+        <v>292</v>
       </c>
       <c r="F227" s="1">
         <v>46248</v>
@@ -8135,7 +8237,7 @@
         <v>0</v>
       </c>
       <c r="B228" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="C228">
         <v>1</v>
@@ -8144,7 +8246,7 @@
         <v>12</v>
       </c>
       <c r="E228" t="s">
-        <v>357</v>
+        <v>35</v>
       </c>
       <c r="F228" s="1">
         <v>46248</v>
@@ -8161,7 +8263,7 @@
         <v>0</v>
       </c>
       <c r="B229" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C229">
         <v>1</v>
@@ -8170,7 +8272,7 @@
         <v>12</v>
       </c>
       <c r="E229" t="s">
-        <v>72</v>
+        <v>35</v>
       </c>
       <c r="F229" s="1">
         <v>46248</v>
@@ -8187,16 +8289,16 @@
         <v>0</v>
       </c>
       <c r="B230" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C230">
         <v>1</v>
       </c>
       <c r="D230" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E230" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="F230" s="1">
         <v>46248</v>
@@ -8205,7 +8307,7 @@
         <v>46252</v>
       </c>
       <c r="H230">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="231" spans="1:8" x14ac:dyDescent="0.2">
@@ -8213,7 +8315,7 @@
         <v>0</v>
       </c>
       <c r="B231" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C231">
         <v>1</v>
@@ -8222,7 +8324,7 @@
         <v>12</v>
       </c>
       <c r="E231" t="s">
-        <v>362</v>
+        <v>72</v>
       </c>
       <c r="F231" s="1">
         <v>46248</v>
@@ -8245,10 +8347,10 @@
         <v>1</v>
       </c>
       <c r="D232" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E232" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="F232" s="1">
         <v>46248</v>
@@ -8265,16 +8367,16 @@
         <v>0</v>
       </c>
       <c r="B233" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C233">
         <v>1</v>
       </c>
       <c r="D233" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E233" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="F233" s="1">
         <v>46248</v>
@@ -8283,7 +8385,7 @@
         <v>46252</v>
       </c>
       <c r="H233">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="234" spans="1:8" x14ac:dyDescent="0.2">
@@ -8291,16 +8393,16 @@
         <v>0</v>
       </c>
       <c r="B234" t="s">
+        <v>367</v>
+      </c>
+      <c r="C234">
+        <v>1</v>
+      </c>
+      <c r="D234" t="s">
+        <v>5</v>
+      </c>
+      <c r="E234" t="s">
         <v>366</v>
-      </c>
-      <c r="C234">
-        <v>1</v>
-      </c>
-      <c r="D234" t="s">
-        <v>12</v>
-      </c>
-      <c r="E234" t="s">
-        <v>117</v>
       </c>
       <c r="F234" s="1">
         <v>46248</v>
@@ -8317,16 +8419,16 @@
         <v>0</v>
       </c>
       <c r="B235" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C235">
         <v>1</v>
       </c>
       <c r="D235" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E235" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="F235" s="1">
         <v>46248</v>
@@ -8335,7 +8437,7 @@
         <v>46252</v>
       </c>
       <c r="H235">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="236" spans="1:8" x14ac:dyDescent="0.2">
@@ -8343,7 +8445,7 @@
         <v>0</v>
       </c>
       <c r="B236" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C236">
         <v>1</v>
@@ -8352,7 +8454,7 @@
         <v>12</v>
       </c>
       <c r="E236" t="s">
-        <v>370</v>
+        <v>117</v>
       </c>
       <c r="F236" s="1">
         <v>46248</v>
@@ -8375,7 +8477,7 @@
         <v>1</v>
       </c>
       <c r="D237" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E237" t="s">
         <v>372</v>
@@ -8387,7 +8489,7 @@
         <v>46252</v>
       </c>
       <c r="H237">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="238" spans="1:8" x14ac:dyDescent="0.2">
@@ -8404,7 +8506,7 @@
         <v>12</v>
       </c>
       <c r="E238" t="s">
-        <v>145</v>
+        <v>374</v>
       </c>
       <c r="F238" s="1">
         <v>46248</v>
@@ -8421,16 +8523,16 @@
         <v>0</v>
       </c>
       <c r="B239" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C239">
         <v>1</v>
       </c>
       <c r="D239" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E239" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="F239" s="1">
         <v>46248</v>
@@ -8439,7 +8541,7 @@
         <v>46252</v>
       </c>
       <c r="H239">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="240" spans="1:8" x14ac:dyDescent="0.2">
@@ -8447,7 +8549,7 @@
         <v>0</v>
       </c>
       <c r="B240" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="C240">
         <v>1</v>
@@ -8456,7 +8558,7 @@
         <v>12</v>
       </c>
       <c r="E240" t="s">
-        <v>372</v>
+        <v>145</v>
       </c>
       <c r="F240" s="1">
         <v>46248</v>
@@ -8473,16 +8575,16 @@
         <v>0</v>
       </c>
       <c r="B241" t="s">
+        <v>378</v>
+      </c>
+      <c r="C241">
+        <v>1</v>
+      </c>
+      <c r="D241" t="s">
+        <v>12</v>
+      </c>
+      <c r="E241" t="s">
         <v>376</v>
-      </c>
-      <c r="C241">
-        <v>1</v>
-      </c>
-      <c r="D241" t="s">
-        <v>12</v>
-      </c>
-      <c r="E241" t="s">
-        <v>377</v>
       </c>
       <c r="F241" s="1">
         <v>46248</v>
@@ -8499,16 +8601,16 @@
         <v>0</v>
       </c>
       <c r="B242" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C242">
         <v>1</v>
       </c>
       <c r="D242" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E242" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="F242" s="1">
         <v>46248</v>
@@ -8517,7 +8619,7 @@
         <v>46252</v>
       </c>
       <c r="H242">
-        <v>0</v>
+        <v>32</v>
       </c>
     </row>
     <row r="243" spans="1:8" x14ac:dyDescent="0.2">
@@ -8525,7 +8627,7 @@
         <v>0</v>
       </c>
       <c r="B243" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C243">
         <v>1</v>
@@ -8534,7 +8636,7 @@
         <v>12</v>
       </c>
       <c r="E243" t="s">
-        <v>372</v>
+        <v>381</v>
       </c>
       <c r="F243" s="1">
         <v>46248</v>
@@ -8551,7 +8653,7 @@
         <v>0</v>
       </c>
       <c r="B244" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="C244">
         <v>1</v>
@@ -8560,7 +8662,7 @@
         <v>12</v>
       </c>
       <c r="E244" t="s">
-        <v>158</v>
+        <v>376</v>
       </c>
       <c r="F244" s="1">
         <v>46248</v>
@@ -8577,16 +8679,16 @@
         <v>0</v>
       </c>
       <c r="B245" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="C245">
         <v>1</v>
       </c>
       <c r="D245" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E245" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="F245" s="1">
         <v>46248</v>
@@ -8595,7 +8697,7 @@
         <v>46252</v>
       </c>
       <c r="H245">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="246" spans="1:8" x14ac:dyDescent="0.2">
@@ -8603,7 +8705,7 @@
         <v>0</v>
       </c>
       <c r="B246" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C246">
         <v>1</v>
@@ -8612,7 +8714,7 @@
         <v>12</v>
       </c>
       <c r="E246" t="s">
-        <v>384</v>
+        <v>160</v>
       </c>
       <c r="F246" s="1">
         <v>46248</v>
@@ -8635,10 +8737,10 @@
         <v>1</v>
       </c>
       <c r="D247" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E247" t="s">
-        <v>333</v>
+        <v>386</v>
       </c>
       <c r="F247" s="1">
         <v>46248</v>
@@ -8647,7 +8749,7 @@
         <v>46252</v>
       </c>
       <c r="H247">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="248" spans="1:8" x14ac:dyDescent="0.2">
@@ -8655,7 +8757,7 @@
         <v>0</v>
       </c>
       <c r="B248" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C248">
         <v>1</v>
@@ -8664,7 +8766,7 @@
         <v>12</v>
       </c>
       <c r="E248" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F248" s="1">
         <v>46248</v>
@@ -8681,7 +8783,7 @@
         <v>0</v>
       </c>
       <c r="B249" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C249">
         <v>1</v>
@@ -8690,7 +8792,7 @@
         <v>12</v>
       </c>
       <c r="E249" t="s">
-        <v>382</v>
+        <v>337</v>
       </c>
       <c r="F249" s="1">
         <v>46248</v>
@@ -8707,7 +8809,7 @@
         <v>0</v>
       </c>
       <c r="B250" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C250">
         <v>1</v>
@@ -8716,7 +8818,7 @@
         <v>12</v>
       </c>
       <c r="E250" t="s">
-        <v>382</v>
+        <v>391</v>
       </c>
       <c r="F250" s="1">
         <v>46248</v>
@@ -8733,16 +8835,16 @@
         <v>0</v>
       </c>
       <c r="B251" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C251">
         <v>1</v>
       </c>
       <c r="D251" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E251" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="F251" s="1">
         <v>46248</v>
@@ -8751,7 +8853,7 @@
         <v>46252</v>
       </c>
       <c r="H251">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="252" spans="1:8" x14ac:dyDescent="0.2">
@@ -8759,25 +8861,25 @@
         <v>0</v>
       </c>
       <c r="B252" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C252">
         <v>1</v>
       </c>
       <c r="D252" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E252" t="s">
-        <v>393</v>
+        <v>386</v>
       </c>
       <c r="F252" s="1">
-        <v>46249</v>
+        <v>46248</v>
       </c>
       <c r="G252" s="1">
         <v>46252</v>
       </c>
       <c r="H252">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="253" spans="1:8" x14ac:dyDescent="0.2">
@@ -8794,10 +8896,10 @@
         <v>12</v>
       </c>
       <c r="E253" t="s">
-        <v>79</v>
+        <v>395</v>
       </c>
       <c r="F253" s="1">
-        <v>46249</v>
+        <v>46248</v>
       </c>
       <c r="G253" s="1">
         <v>46252</v>
@@ -8811,16 +8913,16 @@
         <v>0</v>
       </c>
       <c r="B254" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C254">
         <v>1</v>
       </c>
       <c r="D254" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E254" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="F254" s="1">
         <v>46249</v>
@@ -8829,7 +8931,7 @@
         <v>46252</v>
       </c>
       <c r="H254">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="255" spans="1:8" x14ac:dyDescent="0.2">
@@ -8837,7 +8939,7 @@
         <v>0</v>
       </c>
       <c r="B255" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C255">
         <v>1</v>
@@ -8846,7 +8948,7 @@
         <v>12</v>
       </c>
       <c r="E255" t="s">
-        <v>398</v>
+        <v>79</v>
       </c>
       <c r="F255" s="1">
         <v>46249</v>
@@ -8898,7 +9000,7 @@
         <v>12</v>
       </c>
       <c r="E257" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="F257" s="1">
         <v>46249</v>
@@ -8915,7 +9017,7 @@
         <v>0</v>
       </c>
       <c r="B258" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C258">
         <v>1</v>
@@ -8924,7 +9026,7 @@
         <v>12</v>
       </c>
       <c r="E258" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="F258" s="1">
         <v>46249</v>
@@ -8941,16 +9043,16 @@
         <v>0</v>
       </c>
       <c r="B259" t="s">
+        <v>405</v>
+      </c>
+      <c r="C259">
+        <v>1</v>
+      </c>
+      <c r="D259" t="s">
+        <v>12</v>
+      </c>
+      <c r="E259" t="s">
         <v>404</v>
-      </c>
-      <c r="C259">
-        <v>1</v>
-      </c>
-      <c r="D259" t="s">
-        <v>12</v>
-      </c>
-      <c r="E259" t="s">
-        <v>405</v>
       </c>
       <c r="F259" s="1">
         <v>46249</v>
@@ -9031,7 +9133,7 @@
         <v>411</v>
       </c>
       <c r="F262" s="1">
-        <v>46252</v>
+        <v>46249</v>
       </c>
       <c r="G262" s="1">
         <v>46252</v>
@@ -9057,7 +9159,7 @@
         <v>413</v>
       </c>
       <c r="F263" s="1">
-        <v>46252</v>
+        <v>46249</v>
       </c>
       <c r="G263" s="1">
         <v>46252</v>
@@ -9077,7 +9179,7 @@
         <v>1</v>
       </c>
       <c r="D264" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E264" t="s">
         <v>415</v>
@@ -9089,7 +9191,7 @@
         <v>46252</v>
       </c>
       <c r="H264">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="265" spans="1:8" x14ac:dyDescent="0.2">
@@ -9103,7 +9205,7 @@
         <v>1</v>
       </c>
       <c r="D265" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E265" t="s">
         <v>417</v>
@@ -9115,7 +9217,7 @@
         <v>46252</v>
       </c>
       <c r="H265">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="266" spans="1:8" x14ac:dyDescent="0.2">
@@ -9236,7 +9338,7 @@
         <v>12</v>
       </c>
       <c r="E270" t="s">
-        <v>370</v>
+        <v>427</v>
       </c>
       <c r="F270" s="1">
         <v>46252</v>
@@ -9253,16 +9355,16 @@
         <v>0</v>
       </c>
       <c r="B271" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C271">
         <v>1</v>
       </c>
       <c r="D271" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E271" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="F271" s="1">
         <v>46252</v>
@@ -9271,7 +9373,7 @@
         <v>46252</v>
       </c>
       <c r="H271">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="272" spans="1:8" x14ac:dyDescent="0.2">
@@ -9279,7 +9381,7 @@
         <v>0</v>
       </c>
       <c r="B272" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C272">
         <v>1</v>
@@ -9288,7 +9390,7 @@
         <v>12</v>
       </c>
       <c r="E272" t="s">
-        <v>13</v>
+        <v>374</v>
       </c>
       <c r="F272" s="1">
         <v>46252</v>
@@ -9305,7 +9407,7 @@
         <v>0</v>
       </c>
       <c r="B273" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C273">
         <v>1</v>
@@ -9314,7 +9416,7 @@
         <v>12</v>
       </c>
       <c r="E273" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="F273" s="1">
         <v>46252</v>
@@ -9331,13 +9433,13 @@
         <v>0</v>
       </c>
       <c r="B274" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C274">
         <v>1</v>
       </c>
       <c r="D274" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E274" t="s">
         <v>13</v>
@@ -9349,7 +9451,7 @@
         <v>46252</v>
       </c>
       <c r="H274">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="275" spans="1:8" x14ac:dyDescent="0.2">
@@ -9357,7 +9459,7 @@
         <v>0</v>
       </c>
       <c r="B275" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C275">
         <v>1</v>
@@ -9366,7 +9468,7 @@
         <v>12</v>
       </c>
       <c r="E275" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="F275" s="1">
         <v>46252</v>
@@ -9383,7 +9485,7 @@
         <v>0</v>
       </c>
       <c r="B276" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C276">
         <v>1</v>
@@ -9392,7 +9494,7 @@
         <v>12</v>
       </c>
       <c r="E276" t="s">
-        <v>436</v>
+        <v>13</v>
       </c>
       <c r="F276" s="1">
         <v>46252</v>
@@ -9418,7 +9520,7 @@
         <v>12</v>
       </c>
       <c r="E277" t="s">
-        <v>117</v>
+        <v>438</v>
       </c>
       <c r="F277" s="1">
         <v>46252</v>
@@ -9435,16 +9537,16 @@
         <v>0</v>
       </c>
       <c r="B278" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C278">
         <v>1</v>
       </c>
       <c r="D278" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E278" t="s">
-        <v>66</v>
+        <v>440</v>
       </c>
       <c r="F278" s="1">
         <v>46252</v>
@@ -9453,7 +9555,7 @@
         <v>46252</v>
       </c>
       <c r="H278">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="279" spans="1:8" x14ac:dyDescent="0.2">
@@ -9461,7 +9563,7 @@
         <v>0</v>
       </c>
       <c r="B279" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="C279">
         <v>1</v>
@@ -9470,7 +9572,7 @@
         <v>12</v>
       </c>
       <c r="E279" t="s">
-        <v>440</v>
+        <v>117</v>
       </c>
       <c r="F279" s="1">
         <v>46252</v>
@@ -9487,16 +9589,16 @@
         <v>0</v>
       </c>
       <c r="B280" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C280">
         <v>1</v>
       </c>
       <c r="D280" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E280" t="s">
-        <v>442</v>
+        <v>66</v>
       </c>
       <c r="F280" s="1">
         <v>46252</v>
@@ -9505,7 +9607,7 @@
         <v>46252</v>
       </c>
       <c r="H280">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="281" spans="1:8" x14ac:dyDescent="0.2">
@@ -9545,10 +9647,10 @@
         <v>1</v>
       </c>
       <c r="D282" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E282" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="F282" s="1">
         <v>46252</v>
@@ -9557,7 +9659,7 @@
         <v>46252</v>
       </c>
       <c r="H282">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="283" spans="1:8" x14ac:dyDescent="0.2">
@@ -9565,7 +9667,7 @@
         <v>0</v>
       </c>
       <c r="B283" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C283">
         <v>1</v>
@@ -9574,7 +9676,7 @@
         <v>12</v>
       </c>
       <c r="E283" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="F283" s="1">
         <v>46252</v>
@@ -9591,16 +9693,16 @@
         <v>0</v>
       </c>
       <c r="B284" t="s">
+        <v>449</v>
+      </c>
+      <c r="C284">
+        <v>1</v>
+      </c>
+      <c r="D284" t="s">
+        <v>12</v>
+      </c>
+      <c r="E284" t="s">
         <v>448</v>
-      </c>
-      <c r="C284">
-        <v>1</v>
-      </c>
-      <c r="D284" t="s">
-        <v>12</v>
-      </c>
-      <c r="E284" t="s">
-        <v>72</v>
       </c>
       <c r="F284" s="1">
         <v>46252</v>
@@ -9617,16 +9719,16 @@
         <v>0</v>
       </c>
       <c r="B285" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C285">
         <v>1</v>
       </c>
       <c r="D285" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E285" t="s">
-        <v>33</v>
+        <v>451</v>
       </c>
       <c r="F285" s="1">
         <v>46252</v>
@@ -9635,7 +9737,7 @@
         <v>46252</v>
       </c>
       <c r="H285">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="286" spans="1:8" x14ac:dyDescent="0.2">
@@ -9643,7 +9745,7 @@
         <v>0</v>
       </c>
       <c r="B286" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="C286">
         <v>1</v>
@@ -9652,7 +9754,7 @@
         <v>12</v>
       </c>
       <c r="E286" t="s">
-        <v>451</v>
+        <v>72</v>
       </c>
       <c r="F286" s="1">
         <v>46252</v>
@@ -9669,7 +9771,7 @@
         <v>0</v>
       </c>
       <c r="B287" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C287">
         <v>1</v>
@@ -9678,7 +9780,7 @@
         <v>12</v>
       </c>
       <c r="E287" t="s">
-        <v>451</v>
+        <v>33</v>
       </c>
       <c r="F287" s="1">
         <v>46252</v>
@@ -9695,7 +9797,7 @@
         <v>0</v>
       </c>
       <c r="B288" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C288">
         <v>1</v>
@@ -9704,7 +9806,7 @@
         <v>12</v>
       </c>
       <c r="E288" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="F288" s="1">
         <v>46252</v>
@@ -9721,7 +9823,7 @@
         <v>0</v>
       </c>
       <c r="B289" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="C289">
         <v>1</v>
@@ -9730,7 +9832,7 @@
         <v>12</v>
       </c>
       <c r="E289" t="s">
-        <v>243</v>
+        <v>455</v>
       </c>
       <c r="F289" s="1">
         <v>46252</v>
@@ -9747,16 +9849,16 @@
         <v>0</v>
       </c>
       <c r="B290" t="s">
+        <v>457</v>
+      </c>
+      <c r="C290">
+        <v>1</v>
+      </c>
+      <c r="D290" t="s">
+        <v>12</v>
+      </c>
+      <c r="E290" t="s">
         <v>455</v>
-      </c>
-      <c r="C290">
-        <v>1</v>
-      </c>
-      <c r="D290" t="s">
-        <v>12</v>
-      </c>
-      <c r="E290" t="s">
-        <v>456</v>
       </c>
       <c r="F290" s="1">
         <v>46252</v>
@@ -9773,7 +9875,7 @@
         <v>0</v>
       </c>
       <c r="B291" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C291">
         <v>1</v>
@@ -9782,7 +9884,7 @@
         <v>12</v>
       </c>
       <c r="E291" t="s">
-        <v>372</v>
+        <v>245</v>
       </c>
       <c r="F291" s="1">
         <v>46252</v>
@@ -9799,7 +9901,7 @@
         <v>0</v>
       </c>
       <c r="B292" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C292">
         <v>1</v>
@@ -9808,7 +9910,7 @@
         <v>12</v>
       </c>
       <c r="E292" t="s">
-        <v>281</v>
+        <v>460</v>
       </c>
       <c r="F292" s="1">
         <v>46252</v>
@@ -9825,16 +9927,16 @@
         <v>0</v>
       </c>
       <c r="B293" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="C293">
         <v>1</v>
       </c>
       <c r="D293" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E293" t="s">
-        <v>66</v>
+        <v>376</v>
       </c>
       <c r="F293" s="1">
         <v>46252</v>
@@ -9843,7 +9945,7 @@
         <v>46252</v>
       </c>
       <c r="H293">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="294" spans="1:8" x14ac:dyDescent="0.2">
@@ -9851,7 +9953,7 @@
         <v>0</v>
       </c>
       <c r="B294" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="C294">
         <v>1</v>
@@ -9860,7 +9962,7 @@
         <v>12</v>
       </c>
       <c r="E294" t="s">
-        <v>13</v>
+        <v>283</v>
       </c>
       <c r="F294" s="1">
         <v>46252</v>
@@ -9877,7 +9979,7 @@
         <v>0</v>
       </c>
       <c r="B295" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="C295">
         <v>1</v>
@@ -9886,7 +9988,7 @@
         <v>12</v>
       </c>
       <c r="E295" t="s">
-        <v>13</v>
+        <v>66</v>
       </c>
       <c r="F295" s="1">
         <v>46252</v>
@@ -9903,7 +10005,7 @@
         <v>0</v>
       </c>
       <c r="B296" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="C296">
         <v>1</v>
@@ -9929,7 +10031,7 @@
         <v>0</v>
       </c>
       <c r="B297" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="C297">
         <v>1</v>
@@ -9955,7 +10057,7 @@
         <v>0</v>
       </c>
       <c r="B298" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="C298">
         <v>1</v>
@@ -9964,7 +10066,7 @@
         <v>12</v>
       </c>
       <c r="E298" t="s">
-        <v>55</v>
+        <v>13</v>
       </c>
       <c r="F298" s="1">
         <v>46252</v>
@@ -9981,7 +10083,7 @@
         <v>0</v>
       </c>
       <c r="B299" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="C299">
         <v>1</v>
@@ -9990,7 +10092,7 @@
         <v>12</v>
       </c>
       <c r="E299" t="s">
-        <v>255</v>
+        <v>13</v>
       </c>
       <c r="F299" s="1">
         <v>46252</v>
@@ -10007,7 +10109,7 @@
         <v>0</v>
       </c>
       <c r="B300" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C300">
         <v>1</v>
@@ -10016,7 +10118,7 @@
         <v>12</v>
       </c>
       <c r="E300" t="s">
-        <v>467</v>
+        <v>55</v>
       </c>
       <c r="F300" s="1">
         <v>46252</v>
@@ -10033,7 +10135,7 @@
         <v>0</v>
       </c>
       <c r="B301" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C301">
         <v>1</v>
@@ -10042,7 +10144,7 @@
         <v>12</v>
       </c>
       <c r="E301" t="s">
-        <v>70</v>
+        <v>257</v>
       </c>
       <c r="F301" s="1">
         <v>46252</v>
@@ -10059,7 +10161,7 @@
         <v>0</v>
       </c>
       <c r="B302" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C302">
         <v>1</v>
@@ -10068,7 +10170,7 @@
         <v>12</v>
       </c>
       <c r="E302" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="F302" s="1">
         <v>46252</v>
@@ -10085,7 +10187,7 @@
         <v>0</v>
       </c>
       <c r="B303" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C303">
         <v>1</v>
@@ -10094,7 +10196,7 @@
         <v>12</v>
       </c>
       <c r="E303" t="s">
-        <v>472</v>
+        <v>70</v>
       </c>
       <c r="F303" s="1">
         <v>46252</v>
@@ -10120,7 +10222,7 @@
         <v>12</v>
       </c>
       <c r="E304" t="s">
-        <v>130</v>
+        <v>474</v>
       </c>
       <c r="F304" s="1">
         <v>46252</v>
@@ -10137,7 +10239,7 @@
         <v>0</v>
       </c>
       <c r="B305" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C305">
         <v>1</v>
@@ -10146,13 +10248,13 @@
         <v>12</v>
       </c>
       <c r="E305" t="s">
-        <v>130</v>
+        <v>85</v>
       </c>
       <c r="F305" s="1">
         <v>46252</v>
       </c>
       <c r="G305" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="H305">
         <v>0</v>
@@ -10163,7 +10265,7 @@
         <v>0</v>
       </c>
       <c r="B306" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C306">
         <v>1</v>
@@ -10172,7 +10274,7 @@
         <v>12</v>
       </c>
       <c r="E306" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="F306" s="1">
         <v>46252</v>
@@ -10189,7 +10291,7 @@
         <v>0</v>
       </c>
       <c r="B307" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C307">
         <v>1</v>
@@ -10198,13 +10300,13 @@
         <v>12</v>
       </c>
       <c r="E307" t="s">
-        <v>478</v>
+        <v>130</v>
       </c>
       <c r="F307" s="1">
         <v>46252</v>
       </c>
       <c r="G307" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="H307">
         <v>0</v>
@@ -10224,7 +10326,7 @@
         <v>12</v>
       </c>
       <c r="E308" t="s">
-        <v>178</v>
+        <v>130</v>
       </c>
       <c r="F308" s="1">
         <v>46252</v>
@@ -10250,7 +10352,7 @@
         <v>12</v>
       </c>
       <c r="E309" t="s">
-        <v>15</v>
+        <v>130</v>
       </c>
       <c r="F309" s="1">
         <v>46252</v>
@@ -10302,7 +10404,7 @@
         <v>12</v>
       </c>
       <c r="E311" t="s">
-        <v>136</v>
+        <v>484</v>
       </c>
       <c r="F311" s="1">
         <v>46252</v>
@@ -10319,7 +10421,7 @@
         <v>0</v>
       </c>
       <c r="B312" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C312">
         <v>1</v>
@@ -10328,7 +10430,7 @@
         <v>12</v>
       </c>
       <c r="E312" t="s">
-        <v>136</v>
+        <v>180</v>
       </c>
       <c r="F312" s="1">
         <v>46252</v>
@@ -10345,7 +10447,7 @@
         <v>0</v>
       </c>
       <c r="B313" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C313">
         <v>1</v>
@@ -10354,7 +10456,7 @@
         <v>12</v>
       </c>
       <c r="E313" t="s">
-        <v>309</v>
+        <v>15</v>
       </c>
       <c r="F313" s="1">
         <v>46252</v>
@@ -10371,7 +10473,7 @@
         <v>0</v>
       </c>
       <c r="B314" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C314">
         <v>1</v>
@@ -10380,7 +10482,7 @@
         <v>12</v>
       </c>
       <c r="E314" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="F314" s="1">
         <v>46252</v>
@@ -10397,7 +10499,7 @@
         <v>0</v>
       </c>
       <c r="B315" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C315">
         <v>1</v>
@@ -10406,7 +10508,7 @@
         <v>12</v>
       </c>
       <c r="E315" t="s">
-        <v>489</v>
+        <v>136</v>
       </c>
       <c r="F315" s="1">
         <v>46252</v>
@@ -10432,7 +10534,7 @@
         <v>12</v>
       </c>
       <c r="E316" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="F316" s="1">
         <v>46252</v>
@@ -10455,10 +10557,10 @@
         <v>1</v>
       </c>
       <c r="D317" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E317" t="s">
-        <v>333</v>
+        <v>313</v>
       </c>
       <c r="F317" s="1">
         <v>46252</v>
@@ -10467,7 +10569,7 @@
         <v>46252</v>
       </c>
       <c r="H317">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="318" spans="1:8" x14ac:dyDescent="0.2">
@@ -10484,7 +10586,7 @@
         <v>12</v>
       </c>
       <c r="E318" t="s">
-        <v>400</v>
+        <v>493</v>
       </c>
       <c r="F318" s="1">
         <v>46252</v>
@@ -10501,7 +10603,7 @@
         <v>0</v>
       </c>
       <c r="B319" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C319">
         <v>1</v>
@@ -10510,7 +10612,7 @@
         <v>12</v>
       </c>
       <c r="E319" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="F319" s="1">
         <v>46252</v>
@@ -10527,7 +10629,7 @@
         <v>0</v>
       </c>
       <c r="B320" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C320">
         <v>1</v>
@@ -10536,13 +10638,13 @@
         <v>12</v>
       </c>
       <c r="E320" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="F320" s="1">
         <v>46252</v>
       </c>
       <c r="G320" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="H320">
         <v>0</v>
@@ -10553,7 +10655,7 @@
         <v>0</v>
       </c>
       <c r="B321" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C321">
         <v>1</v>
@@ -10562,13 +10664,13 @@
         <v>12</v>
       </c>
       <c r="E321" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="F321" s="1">
         <v>46252</v>
       </c>
       <c r="G321" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="H321">
         <v>0</v>
@@ -10579,7 +10681,7 @@
         <v>0</v>
       </c>
       <c r="B322" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="C322">
         <v>1</v>
@@ -10588,7 +10690,7 @@
         <v>12</v>
       </c>
       <c r="E322" t="s">
-        <v>499</v>
+        <v>127</v>
       </c>
       <c r="F322" s="1">
         <v>46252</v>
@@ -10605,7 +10707,7 @@
         <v>0</v>
       </c>
       <c r="B323" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C323">
         <v>1</v>
@@ -10614,7 +10716,7 @@
         <v>12</v>
       </c>
       <c r="E323" t="s">
-        <v>499</v>
+        <v>337</v>
       </c>
       <c r="F323" s="1">
         <v>46252</v>
@@ -10631,7 +10733,7 @@
         <v>0</v>
       </c>
       <c r="B324" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C324">
         <v>1</v>
@@ -10640,13 +10742,13 @@
         <v>12</v>
       </c>
       <c r="E324" t="s">
-        <v>192</v>
+        <v>503</v>
       </c>
       <c r="F324" s="1">
         <v>46252</v>
       </c>
       <c r="G324" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="H324">
         <v>0</v>
@@ -10657,7 +10759,7 @@
         <v>0</v>
       </c>
       <c r="B325" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="C325">
         <v>1</v>
@@ -10666,7 +10768,7 @@
         <v>12</v>
       </c>
       <c r="E325" t="s">
-        <v>503</v>
+        <v>404</v>
       </c>
       <c r="F325" s="1">
         <v>46252</v>
@@ -10683,7 +10785,7 @@
         <v>0</v>
       </c>
       <c r="B326" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C326">
         <v>1</v>
@@ -10692,7 +10794,7 @@
         <v>12</v>
       </c>
       <c r="E326" t="s">
-        <v>496</v>
+        <v>506</v>
       </c>
       <c r="F326" s="1">
         <v>46252</v>
@@ -10709,7 +10811,7 @@
         <v>0</v>
       </c>
       <c r="B327" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="C327">
         <v>1</v>
@@ -10718,7 +10820,7 @@
         <v>12</v>
       </c>
       <c r="E327" t="s">
-        <v>496</v>
+        <v>508</v>
       </c>
       <c r="F327" s="1">
         <v>46252</v>
@@ -10735,7 +10837,7 @@
         <v>0</v>
       </c>
       <c r="B328" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="C328">
         <v>1</v>
@@ -10744,7 +10846,7 @@
         <v>12</v>
       </c>
       <c r="E328" t="s">
-        <v>496</v>
+        <v>508</v>
       </c>
       <c r="F328" s="1">
         <v>46252</v>
@@ -10758,77 +10860,77 @@
     </row>
     <row r="329" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A329" t="s">
-        <v>507</v>
+        <v>0</v>
       </c>
       <c r="B329" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="C329">
         <v>1</v>
       </c>
       <c r="D329" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E329" t="s">
-        <v>362</v>
+        <v>511</v>
       </c>
       <c r="F329" s="1">
-        <v>46148</v>
+        <v>46252</v>
       </c>
       <c r="G329" s="1">
-        <v>46149</v>
+        <v>46252</v>
       </c>
       <c r="H329">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="330" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A330" t="s">
-        <v>509</v>
+        <v>0</v>
       </c>
       <c r="B330" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="C330">
         <v>1</v>
       </c>
       <c r="D330" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E330" t="s">
-        <v>30</v>
+        <v>511</v>
       </c>
       <c r="F330" s="1">
-        <v>46133</v>
+        <v>46252</v>
       </c>
       <c r="G330" s="1">
-        <v>46134</v>
+        <v>46252</v>
       </c>
       <c r="H330">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="331" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A331" t="s">
-        <v>509</v>
+        <v>0</v>
       </c>
       <c r="B331" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="C331">
         <v>1</v>
       </c>
       <c r="D331" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E331" t="s">
-        <v>30</v>
+        <v>194</v>
       </c>
       <c r="F331" s="1">
-        <v>46134</v>
+        <v>46252</v>
       </c>
       <c r="G331" s="1">
-        <v>46134</v>
+        <v>46252</v>
       </c>
       <c r="H331">
         <v>0</v>
@@ -10836,25 +10938,25 @@
     </row>
     <row r="332" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A332" t="s">
-        <v>509</v>
+        <v>0</v>
       </c>
       <c r="B332" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="C332">
         <v>1</v>
       </c>
       <c r="D332" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E332" t="s">
-        <v>15</v>
+        <v>515</v>
       </c>
       <c r="F332" s="1">
-        <v>46156</v>
+        <v>46252</v>
       </c>
       <c r="G332" s="1">
-        <v>46156</v>
+        <v>46252</v>
       </c>
       <c r="H332">
         <v>0</v>
@@ -10862,48 +10964,48 @@
     </row>
     <row r="333" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A333" t="s">
-        <v>509</v>
+        <v>0</v>
       </c>
       <c r="B333" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="C333">
         <v>1</v>
       </c>
       <c r="D333" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E333" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="F333" s="1">
-        <v>46195</v>
+        <v>46252</v>
       </c>
       <c r="G333" s="1">
-        <v>46195</v>
+        <v>46252</v>
       </c>
       <c r="H333">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="334" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A334" t="s">
-        <v>509</v>
+        <v>0</v>
       </c>
       <c r="B334" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="C334">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D334" t="s">
         <v>12</v>
       </c>
       <c r="E334" t="s">
-        <v>516</v>
+        <v>508</v>
       </c>
       <c r="F334" s="1">
-        <v>46206</v>
+        <v>46252</v>
       </c>
       <c r="G334" s="1">
         <v>46252</v>
@@ -10914,33 +11016,33 @@
     </row>
     <row r="335" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A335" t="s">
-        <v>509</v>
+        <v>0</v>
       </c>
       <c r="B335" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C335">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D335" t="s">
-        <v>68</v>
+        <v>12</v>
       </c>
       <c r="E335" t="s">
-        <v>518</v>
+        <v>508</v>
       </c>
       <c r="F335" s="1">
-        <v>46209</v>
+        <v>46252</v>
       </c>
       <c r="G335" s="1">
-        <v>46218</v>
+        <v>46252</v>
       </c>
       <c r="H335">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="336" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A336" t="s">
-        <v>509</v>
+        <v>0</v>
       </c>
       <c r="B336" t="s">
         <v>519</v>
@@ -10949,16 +11051,16 @@
         <v>1</v>
       </c>
       <c r="D336" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E336" t="s">
         <v>520</v>
       </c>
       <c r="F336" s="1">
-        <v>46213</v>
+        <v>46252</v>
       </c>
       <c r="G336" s="1">
-        <v>46213</v>
+        <v>46253</v>
       </c>
       <c r="H336">
         <v>0</v>
@@ -10966,7 +11068,7 @@
     </row>
     <row r="337" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A337" t="s">
-        <v>509</v>
+        <v>0</v>
       </c>
       <c r="B337" t="s">
         <v>521</v>
@@ -10975,224 +11077,224 @@
         <v>1</v>
       </c>
       <c r="D337" t="s">
-        <v>68</v>
+        <v>12</v>
       </c>
       <c r="E337" t="s">
-        <v>224</v>
+        <v>522</v>
       </c>
       <c r="F337" s="1">
-        <v>46213</v>
+        <v>46252</v>
       </c>
       <c r="G337" s="1">
-        <v>46216</v>
+        <v>46253</v>
       </c>
       <c r="H337">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="338" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A338" t="s">
-        <v>509</v>
+        <v>0</v>
       </c>
       <c r="B338" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="C338">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D338" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E338" t="s">
-        <v>96</v>
+        <v>524</v>
       </c>
       <c r="F338" s="1">
-        <v>46220</v>
+        <v>46252</v>
       </c>
       <c r="G338" s="1">
-        <v>46231</v>
+        <v>46253</v>
       </c>
       <c r="H338">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="339" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A339" t="s">
-        <v>509</v>
+        <v>0</v>
       </c>
       <c r="B339" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="C339">
         <v>1</v>
       </c>
       <c r="D339" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E339" t="s">
-        <v>514</v>
+        <v>222</v>
       </c>
       <c r="F339" s="1">
-        <v>46223</v>
+        <v>46252</v>
       </c>
       <c r="G339" s="1">
-        <v>46223</v>
+        <v>46253</v>
       </c>
       <c r="H339">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="340" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A340" t="s">
-        <v>509</v>
+        <v>0</v>
       </c>
       <c r="B340" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="C340">
         <v>1</v>
       </c>
       <c r="D340" t="s">
-        <v>68</v>
+        <v>12</v>
       </c>
       <c r="E340" t="s">
-        <v>224</v>
+        <v>170</v>
       </c>
       <c r="F340" s="1">
-        <v>46224</v>
+        <v>46253</v>
       </c>
       <c r="G340" s="1">
-        <v>46224</v>
+        <v>46253</v>
       </c>
       <c r="H340">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="341" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A341" t="s">
-        <v>509</v>
+        <v>0</v>
       </c>
       <c r="B341" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="C341">
         <v>1</v>
       </c>
       <c r="D341" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E341" t="s">
-        <v>514</v>
+        <v>170</v>
       </c>
       <c r="F341" s="1">
-        <v>46230</v>
+        <v>46253</v>
       </c>
       <c r="G341" s="1">
-        <v>46231</v>
+        <v>46253</v>
       </c>
       <c r="H341">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="342" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A342" t="s">
-        <v>509</v>
+        <v>0</v>
       </c>
       <c r="B342" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="C342">
         <v>1</v>
       </c>
       <c r="D342" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E342" t="s">
-        <v>96</v>
+        <v>529</v>
       </c>
       <c r="F342" s="1">
-        <v>46232</v>
+        <v>46253</v>
       </c>
       <c r="G342" s="1">
-        <v>46233</v>
+        <v>46253</v>
       </c>
       <c r="H342">
-        <v>126</v>
+        <v>0</v>
       </c>
     </row>
     <row r="343" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A343" t="s">
-        <v>509</v>
+        <v>0</v>
       </c>
       <c r="B343" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="C343">
         <v>1</v>
       </c>
       <c r="D343" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E343" t="s">
-        <v>96</v>
+        <v>531</v>
       </c>
       <c r="F343" s="1">
-        <v>46232</v>
+        <v>46253</v>
       </c>
       <c r="G343" s="1">
-        <v>46233</v>
+        <v>46253</v>
       </c>
       <c r="H343">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="344" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A344" t="s">
-        <v>509</v>
+        <v>0</v>
       </c>
       <c r="B344" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="C344">
         <v>1</v>
       </c>
       <c r="D344" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E344" t="s">
-        <v>224</v>
+        <v>533</v>
       </c>
       <c r="F344" s="1">
-        <v>46238</v>
+        <v>46253</v>
       </c>
       <c r="G344" s="1">
-        <v>46239</v>
+        <v>46253</v>
       </c>
       <c r="H344">
-        <v>117</v>
+        <v>0</v>
       </c>
     </row>
     <row r="345" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A345" t="s">
-        <v>509</v>
+        <v>0</v>
       </c>
       <c r="B345" t="s">
-        <v>529</v>
+        <v>534</v>
       </c>
       <c r="C345">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D345" t="s">
         <v>12</v>
       </c>
       <c r="E345" t="s">
-        <v>516</v>
+        <v>27</v>
       </c>
       <c r="F345" s="1">
-        <v>46239</v>
+        <v>46253</v>
       </c>
       <c r="G345" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="H345">
         <v>0</v>
@@ -11200,25 +11302,25 @@
     </row>
     <row r="346" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A346" t="s">
-        <v>509</v>
+        <v>0</v>
       </c>
       <c r="B346" t="s">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="C346">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D346" t="s">
         <v>12</v>
       </c>
       <c r="E346" t="s">
-        <v>516</v>
+        <v>27</v>
       </c>
       <c r="F346" s="1">
-        <v>46239</v>
+        <v>46253</v>
       </c>
       <c r="G346" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="H346">
         <v>0</v>
@@ -11226,10 +11328,10 @@
     </row>
     <row r="347" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A347" t="s">
-        <v>509</v>
+        <v>0</v>
       </c>
       <c r="B347" t="s">
-        <v>531</v>
+        <v>536</v>
       </c>
       <c r="C347">
         <v>1</v>
@@ -11238,13 +11340,13 @@
         <v>12</v>
       </c>
       <c r="E347" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F347" s="1">
-        <v>46247</v>
+        <v>46253</v>
       </c>
       <c r="G347" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="H347">
         <v>0</v>
@@ -11252,10 +11354,10 @@
     </row>
     <row r="348" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A348" t="s">
-        <v>509</v>
+        <v>0</v>
       </c>
       <c r="B348" t="s">
-        <v>532</v>
+        <v>537</v>
       </c>
       <c r="C348">
         <v>1</v>
@@ -11264,13 +11366,13 @@
         <v>12</v>
       </c>
       <c r="E348" t="s">
-        <v>309</v>
+        <v>294</v>
       </c>
       <c r="F348" s="1">
-        <v>46247</v>
+        <v>46253</v>
       </c>
       <c r="G348" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="H348">
         <v>0</v>
@@ -11278,10 +11380,10 @@
     </row>
     <row r="349" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A349" t="s">
-        <v>509</v>
+        <v>0</v>
       </c>
       <c r="B349" t="s">
-        <v>533</v>
+        <v>538</v>
       </c>
       <c r="C349">
         <v>1</v>
@@ -11290,13 +11392,13 @@
         <v>12</v>
       </c>
       <c r="E349" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="F349" s="1">
-        <v>46248</v>
+        <v>46253</v>
       </c>
       <c r="G349" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="H349">
         <v>0</v>
@@ -11304,10 +11406,10 @@
     </row>
     <row r="350" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A350" t="s">
-        <v>509</v>
+        <v>0</v>
       </c>
       <c r="B350" t="s">
-        <v>534</v>
+        <v>539</v>
       </c>
       <c r="C350">
         <v>1</v>
@@ -11316,13 +11418,13 @@
         <v>12</v>
       </c>
       <c r="E350" t="s">
-        <v>470</v>
+        <v>124</v>
       </c>
       <c r="F350" s="1">
-        <v>46249</v>
+        <v>46253</v>
       </c>
       <c r="G350" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="H350">
         <v>0</v>
@@ -11330,10 +11432,10 @@
     </row>
     <row r="351" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A351" t="s">
-        <v>509</v>
+        <v>0</v>
       </c>
       <c r="B351" t="s">
-        <v>535</v>
+        <v>540</v>
       </c>
       <c r="C351">
         <v>1</v>
@@ -11342,13 +11444,13 @@
         <v>12</v>
       </c>
       <c r="E351" t="s">
-        <v>514</v>
+        <v>57</v>
       </c>
       <c r="F351" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="G351" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="H351">
         <v>0</v>
@@ -11356,10 +11458,10 @@
     </row>
     <row r="352" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A352" t="s">
-        <v>509</v>
+        <v>0</v>
       </c>
       <c r="B352" t="s">
-        <v>536</v>
+        <v>541</v>
       </c>
       <c r="C352">
         <v>1</v>
@@ -11368,13 +11470,13 @@
         <v>12</v>
       </c>
       <c r="E352" t="s">
-        <v>514</v>
+        <v>13</v>
       </c>
       <c r="F352" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="G352" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="H352">
         <v>0</v>
@@ -11382,51 +11484,51 @@
     </row>
     <row r="353" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A353" t="s">
-        <v>509</v>
+        <v>542</v>
       </c>
       <c r="B353" t="s">
-        <v>537</v>
+        <v>543</v>
       </c>
       <c r="C353">
         <v>1</v>
       </c>
       <c r="D353" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E353" t="s">
-        <v>434</v>
+        <v>366</v>
       </c>
       <c r="F353" s="1">
-        <v>46252</v>
+        <v>46148</v>
       </c>
       <c r="G353" s="1">
-        <v>46252</v>
+        <v>46149</v>
       </c>
       <c r="H353">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="354" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A354" t="s">
-        <v>509</v>
+        <v>544</v>
       </c>
       <c r="B354" t="s">
-        <v>538</v>
+        <v>545</v>
       </c>
       <c r="C354">
         <v>1</v>
       </c>
       <c r="D354" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E354" t="s">
-        <v>539</v>
+        <v>30</v>
       </c>
       <c r="F354" s="1">
-        <v>46252</v>
+        <v>46133</v>
       </c>
       <c r="G354" s="1">
-        <v>46252</v>
+        <v>46134</v>
       </c>
       <c r="H354">
         <v>0</v>
@@ -11434,25 +11536,25 @@
     </row>
     <row r="355" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A355" t="s">
-        <v>509</v>
+        <v>544</v>
       </c>
       <c r="B355" t="s">
-        <v>540</v>
+        <v>546</v>
       </c>
       <c r="C355">
         <v>1</v>
       </c>
       <c r="D355" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E355" t="s">
-        <v>539</v>
+        <v>30</v>
       </c>
       <c r="F355" s="1">
-        <v>46252</v>
+        <v>46134</v>
       </c>
       <c r="G355" s="1">
-        <v>46252</v>
+        <v>46134</v>
       </c>
       <c r="H355">
         <v>0</v>
@@ -11460,25 +11562,25 @@
     </row>
     <row r="356" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A356" t="s">
-        <v>509</v>
+        <v>544</v>
       </c>
       <c r="B356" t="s">
-        <v>541</v>
+        <v>547</v>
       </c>
       <c r="C356">
         <v>1</v>
       </c>
       <c r="D356" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E356" t="s">
-        <v>136</v>
+        <v>15</v>
       </c>
       <c r="F356" s="1">
-        <v>46252</v>
+        <v>46156</v>
       </c>
       <c r="G356" s="1">
-        <v>46252</v>
+        <v>46156</v>
       </c>
       <c r="H356">
         <v>0</v>
@@ -11486,51 +11588,51 @@
     </row>
     <row r="357" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A357" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="B357" t="s">
-        <v>543</v>
+        <v>548</v>
       </c>
       <c r="C357">
         <v>1</v>
       </c>
       <c r="D357" t="s">
-        <v>68</v>
+        <v>2</v>
       </c>
       <c r="E357" t="s">
-        <v>544</v>
+        <v>549</v>
       </c>
       <c r="F357" s="1">
-        <v>46063</v>
+        <v>46195</v>
       </c>
       <c r="G357" s="1">
-        <v>46064</v>
+        <v>46195</v>
       </c>
       <c r="H357">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="358" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A358" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="B358" t="s">
-        <v>545</v>
+        <v>550</v>
       </c>
       <c r="C358">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D358" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E358" t="s">
-        <v>41</v>
+        <v>551</v>
       </c>
       <c r="F358" s="1">
-        <v>46113</v>
+        <v>46206</v>
       </c>
       <c r="G358" s="1">
-        <v>46125</v>
+        <v>46252</v>
       </c>
       <c r="H358">
         <v>0</v>
@@ -11538,25 +11640,25 @@
     </row>
     <row r="359" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A359" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="B359" t="s">
-        <v>546</v>
+        <v>552</v>
       </c>
       <c r="C359">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D359" t="s">
-        <v>2</v>
+        <v>68</v>
       </c>
       <c r="E359" t="s">
-        <v>41</v>
+        <v>553</v>
       </c>
       <c r="F359" s="1">
-        <v>46125</v>
+        <v>46209</v>
       </c>
       <c r="G359" s="1">
-        <v>46125</v>
+        <v>46218</v>
       </c>
       <c r="H359">
         <v>1</v>
@@ -11564,140 +11666,140 @@
     </row>
     <row r="360" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A360" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="B360" t="s">
-        <v>547</v>
+        <v>554</v>
       </c>
       <c r="C360">
         <v>1</v>
       </c>
       <c r="D360" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E360" t="s">
-        <v>41</v>
+        <v>555</v>
       </c>
       <c r="F360" s="1">
-        <v>46126</v>
+        <v>46213</v>
       </c>
       <c r="G360" s="1">
-        <v>46126</v>
+        <v>46213</v>
       </c>
       <c r="H360">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="361" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A361" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="B361" t="s">
-        <v>548</v>
+        <v>556</v>
       </c>
       <c r="C361">
         <v>1</v>
       </c>
       <c r="D361" t="s">
-        <v>2</v>
+        <v>68</v>
       </c>
       <c r="E361" t="s">
-        <v>41</v>
+        <v>226</v>
       </c>
       <c r="F361" s="1">
-        <v>46126</v>
+        <v>46213</v>
       </c>
       <c r="G361" s="1">
-        <v>46126</v>
+        <v>46216</v>
       </c>
       <c r="H361">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="362" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A362" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="B362" t="s">
-        <v>549</v>
+        <v>557</v>
       </c>
       <c r="C362">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D362" t="s">
         <v>2</v>
       </c>
       <c r="E362" t="s">
-        <v>41</v>
+        <v>96</v>
       </c>
       <c r="F362" s="1">
-        <v>46128</v>
+        <v>46220</v>
       </c>
       <c r="G362" s="1">
-        <v>46128</v>
+        <v>46231</v>
       </c>
       <c r="H362">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="363" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A363" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="B363" t="s">
-        <v>550</v>
+        <v>558</v>
       </c>
       <c r="C363">
         <v>1</v>
       </c>
       <c r="D363" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E363" t="s">
-        <v>41</v>
+        <v>549</v>
       </c>
       <c r="F363" s="1">
-        <v>46132</v>
+        <v>46223</v>
       </c>
       <c r="G363" s="1">
-        <v>46132</v>
+        <v>46223</v>
       </c>
       <c r="H363">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="364" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A364" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="B364" t="s">
-        <v>551</v>
+        <v>559</v>
       </c>
       <c r="C364">
         <v>1</v>
       </c>
       <c r="D364" t="s">
-        <v>2</v>
+        <v>68</v>
       </c>
       <c r="E364" t="s">
-        <v>41</v>
+        <v>226</v>
       </c>
       <c r="F364" s="1">
-        <v>46161</v>
+        <v>46224</v>
       </c>
       <c r="G364" s="1">
-        <v>46161</v>
+        <v>46224</v>
       </c>
       <c r="H364">
-        <v>1</v>
+        <v>26</v>
       </c>
     </row>
     <row r="365" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A365" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="B365" t="s">
-        <v>552</v>
+        <v>560</v>
       </c>
       <c r="C365">
         <v>1</v>
@@ -11706,24 +11808,24 @@
         <v>2</v>
       </c>
       <c r="E365" t="s">
-        <v>41</v>
+        <v>549</v>
       </c>
       <c r="F365" s="1">
-        <v>46174</v>
+        <v>46230</v>
       </c>
       <c r="G365" s="1">
-        <v>46174</v>
+        <v>46231</v>
       </c>
       <c r="H365">
-        <v>1</v>
+        <v>18</v>
       </c>
     </row>
     <row r="366" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A366" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="B366" t="s">
-        <v>553</v>
+        <v>561</v>
       </c>
       <c r="C366">
         <v>1</v>
@@ -11732,114 +11834,114 @@
         <v>2</v>
       </c>
       <c r="E366" t="s">
-        <v>41</v>
+        <v>96</v>
       </c>
       <c r="F366" s="1">
-        <v>46174</v>
+        <v>46232</v>
       </c>
       <c r="G366" s="1">
-        <v>46174</v>
+        <v>46233</v>
       </c>
       <c r="H366">
-        <v>1</v>
+        <v>126</v>
       </c>
     </row>
     <row r="367" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A367" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="B367" t="s">
-        <v>554</v>
+        <v>562</v>
       </c>
       <c r="C367">
         <v>1</v>
       </c>
       <c r="D367" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E367" t="s">
-        <v>41</v>
+        <v>96</v>
       </c>
       <c r="F367" s="1">
-        <v>46195</v>
+        <v>46232</v>
       </c>
       <c r="G367" s="1">
-        <v>46252</v>
+        <v>46233</v>
       </c>
       <c r="H367">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="368" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A368" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="B368" t="s">
-        <v>555</v>
+        <v>563</v>
       </c>
       <c r="C368">
         <v>1</v>
       </c>
       <c r="D368" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E368" t="s">
-        <v>41</v>
+        <v>226</v>
       </c>
       <c r="F368" s="1">
-        <v>46210</v>
+        <v>46238</v>
       </c>
       <c r="G368" s="1">
-        <v>46210</v>
+        <v>46239</v>
       </c>
       <c r="H368">
-        <v>0</v>
+        <v>117</v>
       </c>
     </row>
     <row r="369" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A369" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="B369" t="s">
-        <v>556</v>
+        <v>564</v>
       </c>
       <c r="C369">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D369" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E369" t="s">
-        <v>41</v>
+        <v>551</v>
       </c>
       <c r="F369" s="1">
-        <v>46213</v>
+        <v>46239</v>
       </c>
       <c r="G369" s="1">
-        <v>46213</v>
+        <v>46252</v>
       </c>
       <c r="H369">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="370" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A370" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="B370" t="s">
-        <v>557</v>
+        <v>565</v>
       </c>
       <c r="C370">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D370" t="s">
         <v>12</v>
       </c>
       <c r="E370" t="s">
-        <v>41</v>
+        <v>551</v>
       </c>
       <c r="F370" s="1">
-        <v>46218</v>
+        <v>46239</v>
       </c>
       <c r="G370" s="1">
         <v>46252</v>
@@ -11850,36 +11952,36 @@
     </row>
     <row r="371" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A371" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="B371" t="s">
-        <v>558</v>
+        <v>566</v>
       </c>
       <c r="C371">
         <v>1</v>
       </c>
       <c r="D371" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E371" t="s">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="F371" s="1">
-        <v>46226</v>
+        <v>46247</v>
       </c>
       <c r="G371" s="1">
-        <v>46226</v>
+        <v>46252</v>
       </c>
       <c r="H371">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="372" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A372" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="B372" t="s">
-        <v>559</v>
+        <v>567</v>
       </c>
       <c r="C372">
         <v>1</v>
@@ -11888,10 +11990,10 @@
         <v>12</v>
       </c>
       <c r="E372" t="s">
-        <v>41</v>
+        <v>313</v>
       </c>
       <c r="F372" s="1">
-        <v>46227</v>
+        <v>46247</v>
       </c>
       <c r="G372" s="1">
         <v>46252</v>
@@ -11902,10 +12004,10 @@
     </row>
     <row r="373" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A373" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="B373" t="s">
-        <v>560</v>
+        <v>568</v>
       </c>
       <c r="C373">
         <v>1</v>
@@ -11914,10 +12016,10 @@
         <v>12</v>
       </c>
       <c r="E373" t="s">
-        <v>41</v>
+        <v>136</v>
       </c>
       <c r="F373" s="1">
-        <v>46227</v>
+        <v>46248</v>
       </c>
       <c r="G373" s="1">
         <v>46252</v>
@@ -11928,25 +12030,25 @@
     </row>
     <row r="374" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A374" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="B374" t="s">
-        <v>561</v>
+        <v>569</v>
       </c>
       <c r="C374">
         <v>1</v>
       </c>
       <c r="D374" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E374" t="s">
-        <v>41</v>
+        <v>438</v>
       </c>
       <c r="F374" s="1">
-        <v>46227</v>
+        <v>46252</v>
       </c>
       <c r="G374" s="1">
-        <v>46228</v>
+        <v>46252</v>
       </c>
       <c r="H374">
         <v>0</v>
@@ -11954,10 +12056,10 @@
     </row>
     <row r="375" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A375" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="B375" t="s">
-        <v>562</v>
+        <v>570</v>
       </c>
       <c r="C375">
         <v>1</v>
@@ -11966,10 +12068,10 @@
         <v>12</v>
       </c>
       <c r="E375" t="s">
-        <v>55</v>
+        <v>136</v>
       </c>
       <c r="F375" s="1">
-        <v>46230</v>
+        <v>46252</v>
       </c>
       <c r="G375" s="1">
         <v>46252</v>
@@ -11980,25 +12082,25 @@
     </row>
     <row r="376" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A376" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="B376" t="s">
-        <v>563</v>
+        <v>571</v>
       </c>
       <c r="C376">
         <v>1</v>
       </c>
       <c r="D376" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E376" t="s">
-        <v>41</v>
+        <v>553</v>
       </c>
       <c r="F376" s="1">
-        <v>46231</v>
+        <v>46253</v>
       </c>
       <c r="G376" s="1">
-        <v>46231</v>
+        <v>46253</v>
       </c>
       <c r="H376">
         <v>0</v>
@@ -12006,25 +12108,25 @@
     </row>
     <row r="377" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A377" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="B377" t="s">
-        <v>564</v>
+        <v>572</v>
       </c>
       <c r="C377">
         <v>1</v>
       </c>
       <c r="D377" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E377" t="s">
-        <v>41</v>
+        <v>553</v>
       </c>
       <c r="F377" s="1">
-        <v>46237</v>
+        <v>46253</v>
       </c>
       <c r="G377" s="1">
-        <v>46237</v>
+        <v>46253</v>
       </c>
       <c r="H377">
         <v>0</v>
@@ -12032,10 +12134,10 @@
     </row>
     <row r="378" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A378" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="B378" t="s">
-        <v>565</v>
+        <v>573</v>
       </c>
       <c r="C378">
         <v>1</v>
@@ -12044,13 +12146,13 @@
         <v>12</v>
       </c>
       <c r="E378" t="s">
-        <v>41</v>
+        <v>574</v>
       </c>
       <c r="F378" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="G378" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="H378">
         <v>0</v>
@@ -12058,62 +12160,62 @@
     </row>
     <row r="379" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A379" t="s">
-        <v>566</v>
+        <v>575</v>
       </c>
       <c r="B379" t="s">
-        <v>567</v>
+        <v>576</v>
       </c>
       <c r="C379">
         <v>1</v>
       </c>
       <c r="D379" t="s">
-        <v>2</v>
+        <v>68</v>
       </c>
       <c r="E379" t="s">
-        <v>568</v>
+        <v>577</v>
       </c>
       <c r="F379" s="1">
-        <v>46083</v>
+        <v>46063</v>
       </c>
       <c r="G379" s="1">
-        <v>46084</v>
+        <v>46064</v>
       </c>
       <c r="H379">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="380" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A380" t="s">
-        <v>566</v>
+        <v>575</v>
       </c>
       <c r="B380" t="s">
-        <v>569</v>
+        <v>578</v>
       </c>
       <c r="C380">
         <v>1</v>
       </c>
       <c r="D380" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E380" t="s">
-        <v>568</v>
+        <v>41</v>
       </c>
       <c r="F380" s="1">
-        <v>46132</v>
+        <v>46113</v>
       </c>
       <c r="G380" s="1">
-        <v>46133</v>
+        <v>46125</v>
       </c>
       <c r="H380">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="381" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A381" t="s">
-        <v>566</v>
+        <v>575</v>
       </c>
       <c r="B381" t="s">
-        <v>570</v>
+        <v>579</v>
       </c>
       <c r="C381">
         <v>1</v>
@@ -12122,24 +12224,24 @@
         <v>2</v>
       </c>
       <c r="E381" t="s">
-        <v>571</v>
+        <v>41</v>
       </c>
       <c r="F381" s="1">
-        <v>46157</v>
+        <v>46125</v>
       </c>
       <c r="G381" s="1">
-        <v>46157</v>
+        <v>46125</v>
       </c>
       <c r="H381">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="382" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A382" t="s">
-        <v>566</v>
+        <v>575</v>
       </c>
       <c r="B382" t="s">
-        <v>572</v>
+        <v>580</v>
       </c>
       <c r="C382">
         <v>1</v>
@@ -12148,13 +12250,13 @@
         <v>2</v>
       </c>
       <c r="E382" t="s">
-        <v>573</v>
+        <v>41</v>
       </c>
       <c r="F382" s="1">
-        <v>46168</v>
+        <v>46126</v>
       </c>
       <c r="G382" s="1">
-        <v>46170</v>
+        <v>46126</v>
       </c>
       <c r="H382">
         <v>1</v>
@@ -12162,10 +12264,10 @@
     </row>
     <row r="383" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A383" t="s">
-        <v>566</v>
+        <v>575</v>
       </c>
       <c r="B383" t="s">
-        <v>574</v>
+        <v>581</v>
       </c>
       <c r="C383">
         <v>1</v>
@@ -12174,24 +12276,24 @@
         <v>2</v>
       </c>
       <c r="E383" t="s">
-        <v>571</v>
+        <v>41</v>
       </c>
       <c r="F383" s="1">
-        <v>46244</v>
+        <v>46126</v>
       </c>
       <c r="G383" s="1">
-        <v>46244</v>
+        <v>46126</v>
       </c>
       <c r="H383">
-        <v>27</v>
+        <v>1</v>
       </c>
     </row>
     <row r="384" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A384" t="s">
-        <v>566</v>
+        <v>575</v>
       </c>
       <c r="B384" t="s">
-        <v>575</v>
+        <v>582</v>
       </c>
       <c r="C384">
         <v>1</v>
@@ -12200,41 +12302,639 @@
         <v>2</v>
       </c>
       <c r="E384" t="s">
-        <v>571</v>
+        <v>41</v>
       </c>
       <c r="F384" s="1">
-        <v>46247</v>
+        <v>46128</v>
       </c>
       <c r="G384" s="1">
-        <v>46247</v>
+        <v>46128</v>
       </c>
       <c r="H384">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="385" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A385" t="s">
-        <v>566</v>
+        <v>575</v>
       </c>
       <c r="B385" t="s">
-        <v>576</v>
+        <v>583</v>
       </c>
       <c r="C385">
         <v>1</v>
       </c>
       <c r="D385" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E385" t="s">
-        <v>568</v>
+        <v>41</v>
       </c>
       <c r="F385" s="1">
+        <v>46132</v>
+      </c>
+      <c r="G385" s="1">
+        <v>46132</v>
+      </c>
+      <c r="H385">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="386" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A386" t="s">
+        <v>575</v>
+      </c>
+      <c r="B386" t="s">
+        <v>584</v>
+      </c>
+      <c r="C386">
+        <v>1</v>
+      </c>
+      <c r="D386" t="s">
+        <v>2</v>
+      </c>
+      <c r="E386" t="s">
+        <v>41</v>
+      </c>
+      <c r="F386" s="1">
+        <v>46161</v>
+      </c>
+      <c r="G386" s="1">
+        <v>46161</v>
+      </c>
+      <c r="H386">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="387" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A387" t="s">
+        <v>575</v>
+      </c>
+      <c r="B387" t="s">
+        <v>585</v>
+      </c>
+      <c r="C387">
+        <v>1</v>
+      </c>
+      <c r="D387" t="s">
+        <v>2</v>
+      </c>
+      <c r="E387" t="s">
+        <v>41</v>
+      </c>
+      <c r="F387" s="1">
+        <v>46174</v>
+      </c>
+      <c r="G387" s="1">
+        <v>46174</v>
+      </c>
+      <c r="H387">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="388" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A388" t="s">
+        <v>575</v>
+      </c>
+      <c r="B388" t="s">
+        <v>586</v>
+      </c>
+      <c r="C388">
+        <v>1</v>
+      </c>
+      <c r="D388" t="s">
+        <v>2</v>
+      </c>
+      <c r="E388" t="s">
+        <v>41</v>
+      </c>
+      <c r="F388" s="1">
+        <v>46174</v>
+      </c>
+      <c r="G388" s="1">
+        <v>46174</v>
+      </c>
+      <c r="H388">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="389" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A389" t="s">
+        <v>575</v>
+      </c>
+      <c r="B389" t="s">
+        <v>587</v>
+      </c>
+      <c r="C389">
+        <v>1</v>
+      </c>
+      <c r="D389" t="s">
+        <v>12</v>
+      </c>
+      <c r="E389" t="s">
+        <v>41</v>
+      </c>
+      <c r="F389" s="1">
+        <v>46195</v>
+      </c>
+      <c r="G389" s="1">
+        <v>46252</v>
+      </c>
+      <c r="H389">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="390" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A390" t="s">
+        <v>575</v>
+      </c>
+      <c r="B390" t="s">
+        <v>588</v>
+      </c>
+      <c r="C390">
+        <v>1</v>
+      </c>
+      <c r="D390" t="s">
+        <v>5</v>
+      </c>
+      <c r="E390" t="s">
+        <v>41</v>
+      </c>
+      <c r="F390" s="1">
+        <v>46210</v>
+      </c>
+      <c r="G390" s="1">
+        <v>46210</v>
+      </c>
+      <c r="H390">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="391" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A391" t="s">
+        <v>575</v>
+      </c>
+      <c r="B391" t="s">
+        <v>589</v>
+      </c>
+      <c r="C391">
+        <v>1</v>
+      </c>
+      <c r="D391" t="s">
+        <v>2</v>
+      </c>
+      <c r="E391" t="s">
+        <v>41</v>
+      </c>
+      <c r="F391" s="1">
+        <v>46213</v>
+      </c>
+      <c r="G391" s="1">
+        <v>46213</v>
+      </c>
+      <c r="H391">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="392" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A392" t="s">
+        <v>575</v>
+      </c>
+      <c r="B392" t="s">
+        <v>590</v>
+      </c>
+      <c r="C392">
+        <v>1</v>
+      </c>
+      <c r="D392" t="s">
+        <v>12</v>
+      </c>
+      <c r="E392" t="s">
+        <v>41</v>
+      </c>
+      <c r="F392" s="1">
+        <v>46218</v>
+      </c>
+      <c r="G392" s="1">
+        <v>46252</v>
+      </c>
+      <c r="H392">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="393" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A393" t="s">
+        <v>575</v>
+      </c>
+      <c r="B393" t="s">
+        <v>591</v>
+      </c>
+      <c r="C393">
+        <v>1</v>
+      </c>
+      <c r="D393" t="s">
+        <v>5</v>
+      </c>
+      <c r="E393" t="s">
+        <v>55</v>
+      </c>
+      <c r="F393" s="1">
+        <v>46226</v>
+      </c>
+      <c r="G393" s="1">
+        <v>46226</v>
+      </c>
+      <c r="H393">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="394" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A394" t="s">
+        <v>575</v>
+      </c>
+      <c r="B394" t="s">
+        <v>592</v>
+      </c>
+      <c r="C394">
+        <v>1</v>
+      </c>
+      <c r="D394" t="s">
+        <v>12</v>
+      </c>
+      <c r="E394" t="s">
+        <v>41</v>
+      </c>
+      <c r="F394" s="1">
+        <v>46227</v>
+      </c>
+      <c r="G394" s="1">
+        <v>46252</v>
+      </c>
+      <c r="H394">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="395" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A395" t="s">
+        <v>575</v>
+      </c>
+      <c r="B395" t="s">
+        <v>593</v>
+      </c>
+      <c r="C395">
+        <v>1</v>
+      </c>
+      <c r="D395" t="s">
+        <v>12</v>
+      </c>
+      <c r="E395" t="s">
+        <v>41</v>
+      </c>
+      <c r="F395" s="1">
+        <v>46227</v>
+      </c>
+      <c r="G395" s="1">
+        <v>46252</v>
+      </c>
+      <c r="H395">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="396" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A396" t="s">
+        <v>575</v>
+      </c>
+      <c r="B396" t="s">
+        <v>594</v>
+      </c>
+      <c r="C396">
+        <v>1</v>
+      </c>
+      <c r="D396" t="s">
+        <v>5</v>
+      </c>
+      <c r="E396" t="s">
+        <v>41</v>
+      </c>
+      <c r="F396" s="1">
+        <v>46227</v>
+      </c>
+      <c r="G396" s="1">
+        <v>46228</v>
+      </c>
+      <c r="H396">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="397" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A397" t="s">
+        <v>575</v>
+      </c>
+      <c r="B397" t="s">
+        <v>595</v>
+      </c>
+      <c r="C397">
+        <v>1</v>
+      </c>
+      <c r="D397" t="s">
+        <v>12</v>
+      </c>
+      <c r="E397" t="s">
+        <v>55</v>
+      </c>
+      <c r="F397" s="1">
+        <v>46230</v>
+      </c>
+      <c r="G397" s="1">
+        <v>46252</v>
+      </c>
+      <c r="H397">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="398" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A398" t="s">
+        <v>575</v>
+      </c>
+      <c r="B398" t="s">
+        <v>596</v>
+      </c>
+      <c r="C398">
+        <v>1</v>
+      </c>
+      <c r="D398" t="s">
+        <v>5</v>
+      </c>
+      <c r="E398" t="s">
+        <v>41</v>
+      </c>
+      <c r="F398" s="1">
+        <v>46231</v>
+      </c>
+      <c r="G398" s="1">
+        <v>46231</v>
+      </c>
+      <c r="H398">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="399" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A399" t="s">
+        <v>575</v>
+      </c>
+      <c r="B399" t="s">
+        <v>597</v>
+      </c>
+      <c r="C399">
+        <v>1</v>
+      </c>
+      <c r="D399" t="s">
+        <v>5</v>
+      </c>
+      <c r="E399" t="s">
+        <v>41</v>
+      </c>
+      <c r="F399" s="1">
+        <v>46237</v>
+      </c>
+      <c r="G399" s="1">
+        <v>46237</v>
+      </c>
+      <c r="H399">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="400" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A400" t="s">
+        <v>575</v>
+      </c>
+      <c r="B400" t="s">
+        <v>598</v>
+      </c>
+      <c r="C400">
+        <v>1</v>
+      </c>
+      <c r="D400" t="s">
+        <v>12</v>
+      </c>
+      <c r="E400" t="s">
+        <v>41</v>
+      </c>
+      <c r="F400" s="1">
+        <v>46253</v>
+      </c>
+      <c r="G400" s="1">
+        <v>46253</v>
+      </c>
+      <c r="H400">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="401" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A401" t="s">
+        <v>575</v>
+      </c>
+      <c r="B401" t="s">
+        <v>599</v>
+      </c>
+      <c r="C401">
+        <v>1</v>
+      </c>
+      <c r="D401" t="s">
+        <v>12</v>
+      </c>
+      <c r="E401" t="s">
+        <v>41</v>
+      </c>
+      <c r="F401" s="1">
+        <v>46253</v>
+      </c>
+      <c r="G401" s="1">
+        <v>46253</v>
+      </c>
+      <c r="H401">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="402" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A402" t="s">
+        <v>600</v>
+      </c>
+      <c r="B402" t="s">
+        <v>601</v>
+      </c>
+      <c r="C402">
+        <v>1</v>
+      </c>
+      <c r="D402" t="s">
+        <v>2</v>
+      </c>
+      <c r="E402" t="s">
+        <v>602</v>
+      </c>
+      <c r="F402" s="1">
+        <v>46083</v>
+      </c>
+      <c r="G402" s="1">
+        <v>46084</v>
+      </c>
+      <c r="H402">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="403" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A403" t="s">
+        <v>600</v>
+      </c>
+      <c r="B403" t="s">
+        <v>603</v>
+      </c>
+      <c r="C403">
+        <v>1</v>
+      </c>
+      <c r="D403" t="s">
+        <v>2</v>
+      </c>
+      <c r="E403" t="s">
+        <v>602</v>
+      </c>
+      <c r="F403" s="1">
+        <v>46132</v>
+      </c>
+      <c r="G403" s="1">
+        <v>46133</v>
+      </c>
+      <c r="H403">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="404" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A404" t="s">
+        <v>600</v>
+      </c>
+      <c r="B404" t="s">
+        <v>604</v>
+      </c>
+      <c r="C404">
+        <v>1</v>
+      </c>
+      <c r="D404" t="s">
+        <v>2</v>
+      </c>
+      <c r="E404" t="s">
+        <v>605</v>
+      </c>
+      <c r="F404" s="1">
+        <v>46157</v>
+      </c>
+      <c r="G404" s="1">
+        <v>46157</v>
+      </c>
+      <c r="H404">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="405" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A405" t="s">
+        <v>600</v>
+      </c>
+      <c r="B405" t="s">
+        <v>606</v>
+      </c>
+      <c r="C405">
+        <v>1</v>
+      </c>
+      <c r="D405" t="s">
+        <v>2</v>
+      </c>
+      <c r="E405" t="s">
+        <v>607</v>
+      </c>
+      <c r="F405" s="1">
+        <v>46168</v>
+      </c>
+      <c r="G405" s="1">
+        <v>46170</v>
+      </c>
+      <c r="H405">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="406" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A406" t="s">
+        <v>600</v>
+      </c>
+      <c r="B406" t="s">
+        <v>608</v>
+      </c>
+      <c r="C406">
+        <v>1</v>
+      </c>
+      <c r="D406" t="s">
+        <v>2</v>
+      </c>
+      <c r="E406" t="s">
+        <v>605</v>
+      </c>
+      <c r="F406" s="1">
+        <v>46244</v>
+      </c>
+      <c r="G406" s="1">
+        <v>46244</v>
+      </c>
+      <c r="H406">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="407" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A407" t="s">
+        <v>600</v>
+      </c>
+      <c r="B407" t="s">
+        <v>609</v>
+      </c>
+      <c r="C407">
+        <v>1</v>
+      </c>
+      <c r="D407" t="s">
+        <v>2</v>
+      </c>
+      <c r="E407" t="s">
+        <v>605</v>
+      </c>
+      <c r="F407" s="1">
         <v>46247</v>
       </c>
-      <c r="G385" s="1">
+      <c r="G407" s="1">
         <v>46247</v>
       </c>
-      <c r="H385">
+      <c r="H407">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="408" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A408" t="s">
+        <v>600</v>
+      </c>
+      <c r="B408" t="s">
+        <v>610</v>
+      </c>
+      <c r="C408">
+        <v>1</v>
+      </c>
+      <c r="D408" t="s">
+        <v>2</v>
+      </c>
+      <c r="E408" t="s">
+        <v>602</v>
+      </c>
+      <c r="F408" s="1">
+        <v>46247</v>
+      </c>
+      <c r="G408" s="1">
+        <v>46247</v>
+      </c>
+      <c r="H408">
         <v>1</v>
       </c>
     </row>

--- a/Data_ERP/Pedidos Transmicion.xlsx
+++ b/Data_ERP/Pedidos Transmicion.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sistema_Logistico_Peirano\Data_ERP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2A7253D2-31EA-485F-B528-75CE7479F6AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{63925FA5-77F6-4EDC-B62F-C3F5DF83502A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25125" yWindow="2385" windowWidth="15375" windowHeight="8325" xr2:uid="{E19B347B-622F-4385-9E2A-9B946E5CDBEC}"/>
+    <workbookView xWindow="26160" yWindow="3420" windowWidth="15375" windowHeight="8325" xr2:uid="{77D8270B-20F4-4867-BB0B-AD0F6A92E940}"/>
   </bookViews>
   <sheets>
     <sheet name="transmicion" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1496" uniqueCount="566">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1532" uniqueCount="581">
   <si>
     <t>0001</t>
   </si>
@@ -694,12 +694,6 @@
     <t>CONSTRUDISENO S.A.</t>
   </si>
   <si>
-    <t xml:space="preserve">  213485</t>
-  </si>
-  <si>
-    <t>DIDIO HERMANOS S.A.</t>
-  </si>
-  <si>
     <t xml:space="preserve">  213501</t>
   </si>
   <si>
@@ -847,27 +841,12 @@
     <t xml:space="preserve">  213727</t>
   </si>
   <si>
-    <t xml:space="preserve">  213729</t>
-  </si>
-  <si>
-    <t>ANDRES LUIS DE FRANCESCO S.A.</t>
-  </si>
-  <si>
     <t xml:space="preserve">  213735</t>
   </si>
   <si>
     <t>DOMANI DECO S.R.L.</t>
   </si>
   <si>
-    <t xml:space="preserve">  213739</t>
-  </si>
-  <si>
-    <t>SANITARIOS LUGANO S.R.L.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213740</t>
-  </si>
-  <si>
     <t xml:space="preserve">  213745</t>
   </si>
   <si>
@@ -928,39 +907,24 @@
     <t xml:space="preserve">  213791</t>
   </si>
   <si>
-    <t xml:space="preserve">  213792</t>
-  </si>
-  <si>
     <t xml:space="preserve">  213794</t>
   </si>
   <si>
     <t>ALVEAR SANITARIOS S.R.L.</t>
   </si>
   <si>
-    <t xml:space="preserve">  213797</t>
-  </si>
-  <si>
-    <t>BAEZ RAMON ANTONIO</t>
-  </si>
-  <si>
     <t xml:space="preserve">  213798</t>
   </si>
   <si>
     <t xml:space="preserve">  213799</t>
   </si>
   <si>
-    <t xml:space="preserve">  213806</t>
-  </si>
-  <si>
     <t xml:space="preserve">  213807</t>
   </si>
   <si>
     <t>DAPESOL S.A. -MATERIALES ACON</t>
   </si>
   <si>
-    <t xml:space="preserve">  213808</t>
-  </si>
-  <si>
     <t xml:space="preserve">  213811</t>
   </si>
   <si>
@@ -982,9 +946,6 @@
     <t xml:space="preserve">  213819</t>
   </si>
   <si>
-    <t xml:space="preserve">  213825</t>
-  </si>
-  <si>
     <t xml:space="preserve">  213827</t>
   </si>
   <si>
@@ -1009,498 +970,567 @@
     <t xml:space="preserve">  213847</t>
   </si>
   <si>
-    <t xml:space="preserve">  213852</t>
+    <t xml:space="preserve">  213854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213857</t>
+  </si>
+  <si>
+    <t>SAMOT S.A.S.  -SANIPLAST</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213859</t>
+  </si>
+  <si>
+    <t>SNEUBER SANITARIOS S.A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213864</t>
+  </si>
+  <si>
+    <t>GILI Y CIA SRL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213866</t>
+  </si>
+  <si>
+    <t>ZINGALV GALVANIZADOS Y ZINC S.R.L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213869</t>
+  </si>
+  <si>
+    <t>DI STABILE E HIJOS S.A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213872</t>
+  </si>
+  <si>
+    <t>FERNANDEZ GONZALO M.-SANITARIOS FERNANDEZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213873</t>
+  </si>
+  <si>
+    <t>FIUMANI MATIAS EZEQUIEL - SANITARIOS MARQUEZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213874</t>
+  </si>
+  <si>
+    <t>COSTA CALCAGNO SRL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213876</t>
+  </si>
+  <si>
+    <t>ARDISSONE MARIO JAVIER -SANIT. ARDISSONE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213877</t>
+  </si>
+  <si>
+    <t>LISOTTO ROQUE Y LISOTTO ROBERTO SH -LISOTTO SANIT.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213878</t>
+  </si>
+  <si>
+    <t>DARSIE Y CIA. SACI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213879</t>
+  </si>
+  <si>
+    <t>TOTAL 25 SANITARIOS S.A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213888</t>
+  </si>
+  <si>
+    <t>BRASIL CERAMICAS S.R.L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213889</t>
+  </si>
+  <si>
+    <t>SACE SRL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213890</t>
+  </si>
+  <si>
+    <t>VICTOR NADIA ANTONELA -SANTIANO CONSTRUCCIONES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213891</t>
+  </si>
+  <si>
+    <t>GILLI FAUDIN LUIS V. -GILCOMAT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213895</t>
+  </si>
+  <si>
+    <t>COMERCIALIZADORA Y CONSTRUCTORA LANUS SA  CYCLA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213896</t>
+  </si>
+  <si>
+    <t>TRIPOLI ARNALDO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213898</t>
+  </si>
+  <si>
+    <t>ABATEDAGA PABLO D.J.-CONECTANDO INST. SANIT.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213900</t>
+  </si>
+  <si>
+    <t>PIGNATARO M,PIGNATARO P,PIGNATARO D S.H.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213902</t>
+  </si>
+  <si>
+    <t>MERMOZ S.A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213907</t>
+  </si>
+  <si>
+    <t>SAN MONTE ALMO SA - TEIXEIRA POCAS SANITARIOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213910</t>
+  </si>
+  <si>
+    <t>STM LOMAS DE CONCRETO SA - STM HOME</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213920</t>
+  </si>
+  <si>
+    <t>LA FERRETERIA S.A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213930</t>
+  </si>
+  <si>
+    <t>NUEVA CASA SA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213932</t>
+  </si>
+  <si>
+    <t>SANICENTRO S.A. SANITARIOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213936</t>
+  </si>
+  <si>
+    <t>SUPERFICIES S.R.L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213941</t>
+  </si>
+  <si>
+    <t>SUCESION DE ARMITANO ALBERTO JUAN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213946</t>
+  </si>
+  <si>
+    <t>BETOMAT S.R.L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213951</t>
+  </si>
+  <si>
+    <t>GARABITO MATERIALES S.R.L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213952</t>
+  </si>
+  <si>
+    <t>LEIRO JOAQUIN C. - EL GASIFICADOR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213954</t>
+  </si>
+  <si>
+    <t>ARNALDO BUYATTI E HIJOS S.A. -BUYATTI MATERIALES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213957</t>
+  </si>
+  <si>
+    <t>SANITARIOS AXANTRA S.R.L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213960</t>
+  </si>
+  <si>
+    <t>DOS RIZZO S. A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213961</t>
+  </si>
+  <si>
+    <t>SUPERMAT CENTRAL S.A.S.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213970</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213971</t>
+  </si>
+  <si>
+    <t>TODO CAÑO DE MIGUEL ESPECHE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213974</t>
+  </si>
+  <si>
+    <t>BERGIA SEBASTIAN R Y BERGIA S.R. SH -HIDRONORTE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213976</t>
+  </si>
+  <si>
+    <t>GRUPO GRIFO LINC.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213977</t>
+  </si>
+  <si>
+    <t>PRIATEL PISOS S.R.L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213984</t>
+  </si>
+  <si>
+    <t>EL CAÑADON  S.R.L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213987</t>
+  </si>
+  <si>
+    <t>EMPRESA MAYORISTA INDUSTRIAL SRL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213988</t>
+  </si>
+  <si>
+    <t>SANTIANO LILIANA NOEMI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213990</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213998</t>
+  </si>
+  <si>
+    <t>CMM ARGENTINA SA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214002</t>
+  </si>
+  <si>
+    <t>MG PINHEL S.R.L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214003</t>
+  </si>
+  <si>
+    <t>TUBONOR S.A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214004</t>
+  </si>
+  <si>
+    <t>SANITARIOS TARAGUI S.R.L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214005</t>
+  </si>
+  <si>
+    <t>CASA FERRALIC SRL - MARMOLERIA PATAGONICA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214008</t>
+  </si>
+  <si>
+    <t>FEDAN S.A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214009</t>
+  </si>
+  <si>
+    <t>ANSBOR S.R.L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214013</t>
+  </si>
+  <si>
+    <t>BRUNETTI ADRIANA NOEMI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214016</t>
+  </si>
+  <si>
+    <t>DIMA BAÑOS &amp; COCINAS S.R.L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214017</t>
+  </si>
+  <si>
+    <t>OCHIUZZO ALBINO JUAN - DISTRIMAR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214023</t>
+  </si>
+  <si>
+    <t>FLUIDOS PATAGONIA S.A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214024</t>
+  </si>
+  <si>
+    <t>BAIRESMAT S.R.L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214026</t>
+  </si>
+  <si>
+    <t>SURVALMEDA CONSTRUCCIONES S. A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214039</t>
+  </si>
+  <si>
+    <t>BENETTI HUGO D -CONSTRUCCIONES DEL OESTE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214040</t>
+  </si>
+  <si>
+    <t>JUAN H MARCHAL Y CIA S.R.L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214041</t>
+  </si>
+  <si>
+    <t>AQUA SANITARIOS TANDIL S. R. L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214042</t>
+  </si>
+  <si>
+    <t>MATERIALES BASUALDO S.A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214043</t>
+  </si>
+  <si>
+    <t>RUTENIA S.A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214044</t>
   </si>
   <si>
     <t>BALCARCE 54 S.A.</t>
   </si>
   <si>
-    <t xml:space="preserve">  213854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213857</t>
-  </si>
-  <si>
-    <t>SAMOT S.A.S.  -SANIPLAST</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213858</t>
-  </si>
-  <si>
-    <t>SNEUBER SANITARIOS S.A.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213864</t>
-  </si>
-  <si>
-    <t>GILI Y CIA SRL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213866</t>
-  </si>
-  <si>
-    <t>ZINGALV GALVANIZADOS Y ZINC S.R.L.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213869</t>
-  </si>
-  <si>
-    <t>DI STABILE E HIJOS S.A.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213872</t>
-  </si>
-  <si>
-    <t>FERNANDEZ GONZALO M.-SANITARIOS FERNANDEZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213873</t>
-  </si>
-  <si>
-    <t>FIUMANI MATIAS EZEQUIEL - SANITARIOS MARQUEZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213874</t>
-  </si>
-  <si>
-    <t>COSTA CALCAGNO SRL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213876</t>
-  </si>
-  <si>
-    <t>ARDISSONE MARIO JAVIER -SANIT. ARDISSONE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213877</t>
-  </si>
-  <si>
-    <t>LISOTTO ROQUE Y LISOTTO ROBERTO SH -LISOTTO SANIT.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213878</t>
-  </si>
-  <si>
-    <t>DARSIE Y CIA. SACI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213879</t>
-  </si>
-  <si>
-    <t>TOTAL 25 SANITARIOS S.A.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213888</t>
-  </si>
-  <si>
-    <t>BRASIL CERAMICAS S.R.L.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213889</t>
-  </si>
-  <si>
-    <t>SACE SRL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213890</t>
-  </si>
-  <si>
-    <t>VICTOR NADIA ANTONELA -SANTIANO CONSTRUCCIONES</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213891</t>
-  </si>
-  <si>
-    <t>GILLI FAUDIN LUIS V. -GILCOMAT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213895</t>
-  </si>
-  <si>
-    <t>COMERCIALIZADORA Y CONSTRUCTORA LANUS SA  CYCLA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213896</t>
-  </si>
-  <si>
-    <t>TRIPOLI ARNALDO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213898</t>
-  </si>
-  <si>
-    <t>ABATEDAGA PABLO D.J.-CONECTANDO INST. SANIT.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213900</t>
-  </si>
-  <si>
-    <t>PIGNATARO M,PIGNATARO P,PIGNATARO D S.H.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213902</t>
-  </si>
-  <si>
-    <t>MERMOZ S.A.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213907</t>
-  </si>
-  <si>
-    <t>SAN MONTE ALMO SA - TEIXEIRA POCAS SANITARIOS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213910</t>
-  </si>
-  <si>
-    <t>STM LOMAS DE CONCRETO SA - STM HOME</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213916</t>
-  </si>
-  <si>
-    <t>BRUNETTI ADRIANA NOEMI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213920</t>
-  </si>
-  <si>
-    <t>LA FERRETERIA S.A.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213930</t>
-  </si>
-  <si>
-    <t>NUEVA CASA SA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213932</t>
-  </si>
-  <si>
-    <t>SANICENTRO S.A. SANITARIOS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213936</t>
-  </si>
-  <si>
-    <t>SUPERFICIES S.R.L.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213940</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213941</t>
-  </si>
-  <si>
-    <t>SUCESION DE ARMITANO ALBERTO JUAN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213942</t>
-  </si>
-  <si>
-    <t>BARBOSA NESTOR AGUSTIN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213946</t>
-  </si>
-  <si>
-    <t>BETOMAT S.R.L.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213950</t>
-  </si>
-  <si>
-    <t>MG PINHEL S.R.L.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213951</t>
-  </si>
-  <si>
-    <t>GARABITO MATERIALES S.R.L.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213952</t>
-  </si>
-  <si>
-    <t>LEIRO JOAQUIN C. - EL GASIFICADOR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213954</t>
-  </si>
-  <si>
-    <t>ARNALDO BUYATTI E HIJOS S.A. -BUYATTI MATERIALES</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213957</t>
-  </si>
-  <si>
-    <t>SANITARIOS AXANTRA S.R.L.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213960</t>
-  </si>
-  <si>
-    <t>DOS RIZZO S. A.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213961</t>
-  </si>
-  <si>
-    <t>SUPERMAT CENTRAL S.A.S.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213963</t>
-  </si>
-  <si>
-    <t>SANITARIOS ALVAREZ SOC. LEY 19550 CAP. I SECCION I</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213967</t>
-  </si>
-  <si>
-    <t>MOENCA SRL -JAQUE MATE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213970</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213971</t>
-  </si>
-  <si>
-    <t>TODO CAÑO DE MIGUEL ESPECHE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213974</t>
-  </si>
-  <si>
-    <t>BERGIA SEBASTIAN R Y BERGIA S.R. SH -HIDRONORTE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213976</t>
-  </si>
-  <si>
-    <t>GRUPO GRIFO LINC.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213977</t>
-  </si>
-  <si>
-    <t>PRIATEL PISOS S.R.L.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213984</t>
-  </si>
-  <si>
-    <t>EL CAÑADON  S.R.L.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213987</t>
-  </si>
-  <si>
-    <t>EMPRESA MAYORISTA INDUSTRIAL SRL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213988</t>
-  </si>
-  <si>
-    <t>SANTIANO LILIANA NOEMI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213990</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213998</t>
-  </si>
-  <si>
-    <t>CMM ARGENTINA SA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214003</t>
-  </si>
-  <si>
-    <t>TUBONOR S.A.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214005</t>
-  </si>
-  <si>
-    <t>CASA FERRALIC SRL - MARMOLERIA PATAGONICA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214008</t>
-  </si>
-  <si>
-    <t>FEDAN S.A.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214010</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214011</t>
-  </si>
-  <si>
     <t>0004</t>
   </si>
   <si>
@@ -1586,6 +1616,21 @@
   </si>
   <si>
     <t>PITA EPPER NICOLAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    2819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    2820</t>
+  </si>
+  <si>
+    <t>VARIOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    2821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    2822</t>
   </si>
   <si>
     <t>4444</t>
@@ -2167,34 +2212,34 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F20B87C-5E20-4464-9F2F-F91F621AC409}">
-  <dimension ref="A1:H373"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AEC88125-5589-4C47-BA6D-41E117CE4BE9}">
+  <dimension ref="A1:H382"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
-        <v>558</v>
+        <v>573</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>559</v>
+        <v>574</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>560</v>
+        <v>575</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>561</v>
+        <v>576</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>562</v>
+        <v>577</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>563</v>
+        <v>578</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>564</v>
+        <v>579</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>565</v>
+        <v>580</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
@@ -5692,19 +5737,19 @@
         <v>1</v>
       </c>
       <c r="D136" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E136" t="s">
-        <v>225</v>
+        <v>112</v>
       </c>
       <c r="F136" s="1">
         <v>46244</v>
       </c>
       <c r="G136" s="1">
-        <v>46252</v>
+        <v>46244</v>
       </c>
       <c r="H136">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.2">
@@ -5712,25 +5757,25 @@
         <v>0</v>
       </c>
       <c r="B137" t="s">
+        <v>225</v>
+      </c>
+      <c r="C137">
+        <v>1</v>
+      </c>
+      <c r="D137" t="s">
+        <v>2</v>
+      </c>
+      <c r="E137" t="s">
         <v>226</v>
-      </c>
-      <c r="C137">
-        <v>1</v>
-      </c>
-      <c r="D137" t="s">
-        <v>5</v>
-      </c>
-      <c r="E137" t="s">
-        <v>112</v>
       </c>
       <c r="F137" s="1">
         <v>46244</v>
       </c>
       <c r="G137" s="1">
-        <v>46244</v>
+        <v>46246</v>
       </c>
       <c r="H137">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.2">
@@ -5753,10 +5798,10 @@
         <v>46244</v>
       </c>
       <c r="G138" s="1">
-        <v>46246</v>
+        <v>46245</v>
       </c>
       <c r="H138">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.2">
@@ -5776,10 +5821,10 @@
         <v>230</v>
       </c>
       <c r="F139" s="1">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="G139" s="1">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="H139">
         <v>1</v>
@@ -5796,7 +5841,7 @@
         <v>1</v>
       </c>
       <c r="D140" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E140" t="s">
         <v>232</v>
@@ -5805,10 +5850,10 @@
         <v>46245</v>
       </c>
       <c r="G140" s="1">
-        <v>46247</v>
+        <v>46252</v>
       </c>
       <c r="H140">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.2">
@@ -5848,16 +5893,16 @@
         <v>1</v>
       </c>
       <c r="D142" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E142" t="s">
-        <v>236</v>
+        <v>85</v>
       </c>
       <c r="F142" s="1">
         <v>46245</v>
       </c>
       <c r="G142" s="1">
-        <v>46252</v>
+        <v>46246</v>
       </c>
       <c r="H142">
         <v>0</v>
@@ -5868,7 +5913,7 @@
         <v>0</v>
       </c>
       <c r="B143" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C143">
         <v>1</v>
@@ -5883,7 +5928,7 @@
         <v>46245</v>
       </c>
       <c r="G143" s="1">
-        <v>46246</v>
+        <v>46245</v>
       </c>
       <c r="H143">
         <v>0</v>
@@ -5894,7 +5939,7 @@
         <v>0</v>
       </c>
       <c r="B144" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C144">
         <v>1</v>
@@ -5920,25 +5965,25 @@
         <v>0</v>
       </c>
       <c r="B145" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C145">
         <v>1</v>
       </c>
       <c r="D145" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E145" t="s">
-        <v>85</v>
+        <v>39</v>
       </c>
       <c r="F145" s="1">
         <v>46245</v>
       </c>
       <c r="G145" s="1">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="H145">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.2">
@@ -5946,16 +5991,16 @@
         <v>0</v>
       </c>
       <c r="B146" t="s">
+        <v>239</v>
+      </c>
+      <c r="C146">
+        <v>1</v>
+      </c>
+      <c r="D146" t="s">
+        <v>2</v>
+      </c>
+      <c r="E146" t="s">
         <v>240</v>
-      </c>
-      <c r="C146">
-        <v>1</v>
-      </c>
-      <c r="D146" t="s">
-        <v>2</v>
-      </c>
-      <c r="E146" t="s">
-        <v>39</v>
       </c>
       <c r="F146" s="1">
         <v>46245</v>
@@ -5964,7 +6009,7 @@
         <v>46246</v>
       </c>
       <c r="H146">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.2">
@@ -5981,16 +6026,16 @@
         <v>2</v>
       </c>
       <c r="E147" t="s">
-        <v>242</v>
+        <v>27</v>
       </c>
       <c r="F147" s="1">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="G147" s="1">
-        <v>46246</v>
+        <v>46252</v>
       </c>
       <c r="H147">
-        <v>8</v>
+        <v>19</v>
       </c>
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.2">
@@ -5998,7 +6043,7 @@
         <v>0</v>
       </c>
       <c r="B148" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C148">
         <v>1</v>
@@ -6007,7 +6052,7 @@
         <v>2</v>
       </c>
       <c r="E148" t="s">
-        <v>27</v>
+        <v>190</v>
       </c>
       <c r="F148" s="1">
         <v>46246</v>
@@ -6016,7 +6061,7 @@
         <v>46252</v>
       </c>
       <c r="H148">
-        <v>19</v>
+        <v>4</v>
       </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.2">
@@ -6024,7 +6069,7 @@
         <v>0</v>
       </c>
       <c r="B149" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C149">
         <v>1</v>
@@ -6033,16 +6078,16 @@
         <v>2</v>
       </c>
       <c r="E149" t="s">
-        <v>190</v>
+        <v>66</v>
       </c>
       <c r="F149" s="1">
         <v>46246</v>
       </c>
       <c r="G149" s="1">
-        <v>46252</v>
+        <v>46247</v>
       </c>
       <c r="H149">
-        <v>4</v>
+        <v>21</v>
       </c>
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.2">
@@ -6050,25 +6095,25 @@
         <v>0</v>
       </c>
       <c r="B150" t="s">
+        <v>244</v>
+      </c>
+      <c r="C150">
+        <v>1</v>
+      </c>
+      <c r="D150" t="s">
+        <v>2</v>
+      </c>
+      <c r="E150" t="s">
         <v>245</v>
-      </c>
-      <c r="C150">
-        <v>1</v>
-      </c>
-      <c r="D150" t="s">
-        <v>2</v>
-      </c>
-      <c r="E150" t="s">
-        <v>66</v>
       </c>
       <c r="F150" s="1">
         <v>46246</v>
       </c>
       <c r="G150" s="1">
-        <v>46247</v>
+        <v>46252</v>
       </c>
       <c r="H150">
-        <v>21</v>
+        <v>2</v>
       </c>
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.2">
@@ -6085,7 +6130,7 @@
         <v>2</v>
       </c>
       <c r="E151" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="F151" s="1">
         <v>46246</v>
@@ -6094,7 +6139,7 @@
         <v>46252</v>
       </c>
       <c r="H151">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.2">
@@ -6102,25 +6147,25 @@
         <v>0</v>
       </c>
       <c r="B152" t="s">
+        <v>247</v>
+      </c>
+      <c r="C152">
+        <v>1</v>
+      </c>
+      <c r="D152" t="s">
+        <v>2</v>
+      </c>
+      <c r="E152" t="s">
         <v>248</v>
-      </c>
-      <c r="C152">
-        <v>1</v>
-      </c>
-      <c r="D152" t="s">
-        <v>2</v>
-      </c>
-      <c r="E152" t="s">
-        <v>247</v>
       </c>
       <c r="F152" s="1">
         <v>46246</v>
       </c>
       <c r="G152" s="1">
-        <v>46252</v>
+        <v>46247</v>
       </c>
       <c r="H152">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.2">
@@ -6143,7 +6188,7 @@
         <v>46246</v>
       </c>
       <c r="G153" s="1">
-        <v>46247</v>
+        <v>46252</v>
       </c>
       <c r="H153">
         <v>4</v>
@@ -6157,22 +6202,22 @@
         <v>251</v>
       </c>
       <c r="C154">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D154" t="s">
         <v>2</v>
       </c>
       <c r="E154" t="s">
-        <v>252</v>
+        <v>104</v>
       </c>
       <c r="F154" s="1">
         <v>46246</v>
       </c>
       <c r="G154" s="1">
-        <v>46252</v>
+        <v>46247</v>
       </c>
       <c r="H154">
-        <v>4</v>
+        <v>46</v>
       </c>
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.2">
@@ -6180,25 +6225,25 @@
         <v>0</v>
       </c>
       <c r="B155" t="s">
+        <v>252</v>
+      </c>
+      <c r="C155">
+        <v>1</v>
+      </c>
+      <c r="D155" t="s">
+        <v>12</v>
+      </c>
+      <c r="E155" t="s">
         <v>253</v>
-      </c>
-      <c r="C155">
-        <v>2</v>
-      </c>
-      <c r="D155" t="s">
-        <v>2</v>
-      </c>
-      <c r="E155" t="s">
-        <v>104</v>
       </c>
       <c r="F155" s="1">
         <v>46246</v>
       </c>
       <c r="G155" s="1">
-        <v>46247</v>
+        <v>46252</v>
       </c>
       <c r="H155">
-        <v>46</v>
+        <v>0</v>
       </c>
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.2">
@@ -6241,7 +6286,7 @@
         <v>12</v>
       </c>
       <c r="E157" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F157" s="1">
         <v>46246</v>
@@ -6258,7 +6303,7 @@
         <v>0</v>
       </c>
       <c r="B158" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C158">
         <v>1</v>
@@ -6267,10 +6312,10 @@
         <v>12</v>
       </c>
       <c r="E158" t="s">
-        <v>257</v>
+        <v>27</v>
       </c>
       <c r="F158" s="1">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="G158" s="1">
         <v>46252</v>
@@ -6284,7 +6329,7 @@
         <v>0</v>
       </c>
       <c r="B159" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C159">
         <v>1</v>
@@ -6310,7 +6355,7 @@
         <v>0</v>
       </c>
       <c r="B160" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C160">
         <v>1</v>
@@ -6336,7 +6381,7 @@
         <v>0</v>
       </c>
       <c r="B161" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C161">
         <v>1</v>
@@ -6362,7 +6407,7 @@
         <v>0</v>
       </c>
       <c r="B162" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C162">
         <v>1</v>
@@ -6388,7 +6433,7 @@
         <v>0</v>
       </c>
       <c r="B163" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C163">
         <v>1</v>
@@ -6414,7 +6459,7 @@
         <v>0</v>
       </c>
       <c r="B164" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C164">
         <v>1</v>
@@ -6440,7 +6485,7 @@
         <v>0</v>
       </c>
       <c r="B165" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C165">
         <v>1</v>
@@ -6466,10 +6511,10 @@
         <v>0</v>
       </c>
       <c r="B166" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C166">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D166" t="s">
         <v>12</v>
@@ -6492,10 +6537,10 @@
         <v>0</v>
       </c>
       <c r="B167" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C167">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D167" t="s">
         <v>12</v>
@@ -6518,7 +6563,7 @@
         <v>0</v>
       </c>
       <c r="B168" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C168">
         <v>1</v>
@@ -6544,7 +6589,7 @@
         <v>0</v>
       </c>
       <c r="B169" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C169">
         <v>1</v>
@@ -6553,7 +6598,7 @@
         <v>12</v>
       </c>
       <c r="E169" t="s">
-        <v>27</v>
+        <v>255</v>
       </c>
       <c r="F169" s="1">
         <v>46247</v>
@@ -6570,16 +6615,16 @@
         <v>0</v>
       </c>
       <c r="B170" t="s">
+        <v>269</v>
+      </c>
+      <c r="C170">
+        <v>1</v>
+      </c>
+      <c r="D170" t="s">
+        <v>2</v>
+      </c>
+      <c r="E170" t="s">
         <v>270</v>
-      </c>
-      <c r="C170">
-        <v>1</v>
-      </c>
-      <c r="D170" t="s">
-        <v>12</v>
-      </c>
-      <c r="E170" t="s">
-        <v>257</v>
       </c>
       <c r="F170" s="1">
         <v>46247</v>
@@ -6588,7 +6633,7 @@
         <v>46252</v>
       </c>
       <c r="H170">
-        <v>0</v>
+        <v>36</v>
       </c>
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.2">
@@ -6602,10 +6647,10 @@
         <v>1</v>
       </c>
       <c r="D171" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E171" t="s">
-        <v>272</v>
+        <v>132</v>
       </c>
       <c r="F171" s="1">
         <v>46247</v>
@@ -6614,7 +6659,7 @@
         <v>46252</v>
       </c>
       <c r="H171">
-        <v>36</v>
+        <v>0</v>
       </c>
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.2">
@@ -6622,7 +6667,7 @@
         <v>0</v>
       </c>
       <c r="B172" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C172">
         <v>1</v>
@@ -6631,7 +6676,7 @@
         <v>12</v>
       </c>
       <c r="E172" t="s">
-        <v>132</v>
+        <v>223</v>
       </c>
       <c r="F172" s="1">
         <v>46247</v>
@@ -6648,22 +6693,22 @@
         <v>0</v>
       </c>
       <c r="B173" t="s">
+        <v>273</v>
+      </c>
+      <c r="C173">
+        <v>1</v>
+      </c>
+      <c r="D173" t="s">
+        <v>5</v>
+      </c>
+      <c r="E173" t="s">
         <v>274</v>
-      </c>
-      <c r="C173">
-        <v>1</v>
-      </c>
-      <c r="D173" t="s">
-        <v>12</v>
-      </c>
-      <c r="E173" t="s">
-        <v>223</v>
       </c>
       <c r="F173" s="1">
         <v>46247</v>
       </c>
       <c r="G173" s="1">
-        <v>46252</v>
+        <v>46247</v>
       </c>
       <c r="H173">
         <v>0</v>
@@ -6680,7 +6725,7 @@
         <v>1</v>
       </c>
       <c r="D174" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E174" t="s">
         <v>276</v>
@@ -6692,7 +6737,7 @@
         <v>46252</v>
       </c>
       <c r="H174">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="175" spans="1:8" x14ac:dyDescent="0.2">
@@ -6703,19 +6748,19 @@
         <v>277</v>
       </c>
       <c r="C175">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D175" t="s">
         <v>5</v>
       </c>
       <c r="E175" t="s">
-        <v>278</v>
+        <v>143</v>
       </c>
       <c r="F175" s="1">
         <v>46247</v>
       </c>
       <c r="G175" s="1">
-        <v>46247</v>
+        <v>46252</v>
       </c>
       <c r="H175">
         <v>0</v>
@@ -6726,16 +6771,16 @@
         <v>0</v>
       </c>
       <c r="B176" t="s">
+        <v>278</v>
+      </c>
+      <c r="C176">
+        <v>1</v>
+      </c>
+      <c r="D176" t="s">
+        <v>12</v>
+      </c>
+      <c r="E176" t="s">
         <v>279</v>
-      </c>
-      <c r="C176">
-        <v>2</v>
-      </c>
-      <c r="D176" t="s">
-        <v>2</v>
-      </c>
-      <c r="E176" t="s">
-        <v>280</v>
       </c>
       <c r="F176" s="1">
         <v>46247</v>
@@ -6744,7 +6789,7 @@
         <v>46252</v>
       </c>
       <c r="H176">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="177" spans="1:8" x14ac:dyDescent="0.2">
@@ -6752,25 +6797,25 @@
         <v>0</v>
       </c>
       <c r="B177" t="s">
+        <v>280</v>
+      </c>
+      <c r="C177">
+        <v>1</v>
+      </c>
+      <c r="D177" t="s">
+        <v>12</v>
+      </c>
+      <c r="E177" t="s">
         <v>281</v>
-      </c>
-      <c r="C177">
-        <v>1</v>
-      </c>
-      <c r="D177" t="s">
-        <v>2</v>
-      </c>
-      <c r="E177" t="s">
-        <v>280</v>
       </c>
       <c r="F177" s="1">
         <v>46247</v>
       </c>
       <c r="G177" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="H177">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="178" spans="1:8" x14ac:dyDescent="0.2">
@@ -6784,7 +6829,7 @@
         <v>1</v>
       </c>
       <c r="D178" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E178" t="s">
         <v>283</v>
@@ -6796,7 +6841,7 @@
         <v>46252</v>
       </c>
       <c r="H178">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="179" spans="1:8" x14ac:dyDescent="0.2">
@@ -6807,13 +6852,13 @@
         <v>284</v>
       </c>
       <c r="C179">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D179" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E179" t="s">
-        <v>143</v>
+        <v>285</v>
       </c>
       <c r="F179" s="1">
         <v>46247</v>
@@ -6822,7 +6867,7 @@
         <v>46252</v>
       </c>
       <c r="H179">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="180" spans="1:8" x14ac:dyDescent="0.2">
@@ -6830,25 +6875,25 @@
         <v>0</v>
       </c>
       <c r="B180" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C180">
         <v>1</v>
       </c>
       <c r="D180" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E180" t="s">
-        <v>286</v>
+        <v>27</v>
       </c>
       <c r="F180" s="1">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="G180" s="1">
         <v>46252</v>
       </c>
       <c r="H180">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="181" spans="1:8" x14ac:dyDescent="0.2">
@@ -6865,13 +6910,13 @@
         <v>12</v>
       </c>
       <c r="E181" t="s">
-        <v>288</v>
+        <v>13</v>
       </c>
       <c r="F181" s="1">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="G181" s="1">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="H181">
         <v>0</v>
@@ -6882,25 +6927,25 @@
         <v>0</v>
       </c>
       <c r="B182" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C182">
         <v>1</v>
       </c>
       <c r="D182" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E182" t="s">
-        <v>290</v>
+        <v>13</v>
       </c>
       <c r="F182" s="1">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="G182" s="1">
         <v>46252</v>
       </c>
       <c r="H182">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="183" spans="1:8" x14ac:dyDescent="0.2">
@@ -6908,25 +6953,25 @@
         <v>0</v>
       </c>
       <c r="B183" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C183">
         <v>1</v>
       </c>
       <c r="D183" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E183" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="F183" s="1">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="G183" s="1">
         <v>46252</v>
       </c>
       <c r="H183">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="184" spans="1:8" x14ac:dyDescent="0.2">
@@ -6934,16 +6979,16 @@
         <v>0</v>
       </c>
       <c r="B184" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C184">
         <v>1</v>
       </c>
       <c r="D184" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E184" t="s">
-        <v>27</v>
+        <v>292</v>
       </c>
       <c r="F184" s="1">
         <v>46248</v>
@@ -6952,7 +6997,7 @@
         <v>46252</v>
       </c>
       <c r="H184">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="185" spans="1:8" x14ac:dyDescent="0.2">
@@ -6960,7 +7005,7 @@
         <v>0</v>
       </c>
       <c r="B185" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C185">
         <v>1</v>
@@ -6969,7 +7014,7 @@
         <v>12</v>
       </c>
       <c r="E185" t="s">
-        <v>13</v>
+        <v>72</v>
       </c>
       <c r="F185" s="1">
         <v>46248</v>
@@ -6986,7 +7031,7 @@
         <v>0</v>
       </c>
       <c r="B186" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C186">
         <v>1</v>
@@ -6995,7 +7040,7 @@
         <v>12</v>
       </c>
       <c r="E186" t="s">
-        <v>13</v>
+        <v>72</v>
       </c>
       <c r="F186" s="1">
         <v>46248</v>
@@ -7012,16 +7057,16 @@
         <v>0</v>
       </c>
       <c r="B187" t="s">
+        <v>295</v>
+      </c>
+      <c r="C187">
+        <v>1</v>
+      </c>
+      <c r="D187" t="s">
+        <v>12</v>
+      </c>
+      <c r="E187" t="s">
         <v>296</v>
-      </c>
-      <c r="C187">
-        <v>1</v>
-      </c>
-      <c r="D187" t="s">
-        <v>12</v>
-      </c>
-      <c r="E187" t="s">
-        <v>297</v>
       </c>
       <c r="F187" s="1">
         <v>46248</v>
@@ -7038,7 +7083,7 @@
         <v>0</v>
       </c>
       <c r="B188" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C188">
         <v>1</v>
@@ -7047,7 +7092,7 @@
         <v>12</v>
       </c>
       <c r="E188" t="s">
-        <v>299</v>
+        <v>127</v>
       </c>
       <c r="F188" s="1">
         <v>46248</v>
@@ -7064,7 +7109,7 @@
         <v>0</v>
       </c>
       <c r="B189" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C189">
         <v>1</v>
@@ -7073,7 +7118,7 @@
         <v>12</v>
       </c>
       <c r="E189" t="s">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="F189" s="1">
         <v>46248</v>
@@ -7090,7 +7135,7 @@
         <v>0</v>
       </c>
       <c r="B190" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C190">
         <v>1</v>
@@ -7099,7 +7144,7 @@
         <v>12</v>
       </c>
       <c r="E190" t="s">
-        <v>72</v>
+        <v>300</v>
       </c>
       <c r="F190" s="1">
         <v>46248</v>
@@ -7116,16 +7161,16 @@
         <v>0</v>
       </c>
       <c r="B191" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C191">
         <v>1</v>
       </c>
       <c r="D191" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E191" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="F191" s="1">
         <v>46248</v>
@@ -7134,7 +7179,7 @@
         <v>46252</v>
       </c>
       <c r="H191">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="192" spans="1:8" x14ac:dyDescent="0.2">
@@ -7142,16 +7187,16 @@
         <v>0</v>
       </c>
       <c r="B192" t="s">
+        <v>302</v>
+      </c>
+      <c r="C192">
+        <v>1</v>
+      </c>
+      <c r="D192" t="s">
+        <v>12</v>
+      </c>
+      <c r="E192" t="s">
         <v>303</v>
-      </c>
-      <c r="C192">
-        <v>1</v>
-      </c>
-      <c r="D192" t="s">
-        <v>12</v>
-      </c>
-      <c r="E192" t="s">
-        <v>304</v>
       </c>
       <c r="F192" s="1">
         <v>46248</v>
@@ -7168,16 +7213,16 @@
         <v>0</v>
       </c>
       <c r="B193" t="s">
+        <v>304</v>
+      </c>
+      <c r="C193">
+        <v>1</v>
+      </c>
+      <c r="D193" t="s">
+        <v>12</v>
+      </c>
+      <c r="E193" t="s">
         <v>305</v>
-      </c>
-      <c r="C193">
-        <v>1</v>
-      </c>
-      <c r="D193" t="s">
-        <v>2</v>
-      </c>
-      <c r="E193" t="s">
-        <v>306</v>
       </c>
       <c r="F193" s="1">
         <v>46248</v>
@@ -7186,7 +7231,7 @@
         <v>46252</v>
       </c>
       <c r="H193">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="194" spans="1:8" x14ac:dyDescent="0.2">
@@ -7194,7 +7239,7 @@
         <v>0</v>
       </c>
       <c r="B194" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C194">
         <v>1</v>
@@ -7203,7 +7248,7 @@
         <v>12</v>
       </c>
       <c r="E194" t="s">
-        <v>127</v>
+        <v>35</v>
       </c>
       <c r="F194" s="1">
         <v>46248</v>
@@ -7220,7 +7265,7 @@
         <v>0</v>
       </c>
       <c r="B195" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C195">
         <v>1</v>
@@ -7229,7 +7274,7 @@
         <v>12</v>
       </c>
       <c r="E195" t="s">
-        <v>127</v>
+        <v>35</v>
       </c>
       <c r="F195" s="1">
         <v>46248</v>
@@ -7246,16 +7291,16 @@
         <v>0</v>
       </c>
       <c r="B196" t="s">
+        <v>308</v>
+      </c>
+      <c r="C196">
+        <v>1</v>
+      </c>
+      <c r="D196" t="s">
+        <v>12</v>
+      </c>
+      <c r="E196" t="s">
         <v>309</v>
-      </c>
-      <c r="C196">
-        <v>1</v>
-      </c>
-      <c r="D196" t="s">
-        <v>2</v>
-      </c>
-      <c r="E196" t="s">
-        <v>72</v>
       </c>
       <c r="F196" s="1">
         <v>46248</v>
@@ -7264,7 +7309,7 @@
         <v>46252</v>
       </c>
       <c r="H196">
-        <v>47</v>
+        <v>0</v>
       </c>
     </row>
     <row r="197" spans="1:8" x14ac:dyDescent="0.2">
@@ -7304,10 +7349,10 @@
         <v>1</v>
       </c>
       <c r="D198" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E198" t="s">
-        <v>280</v>
+        <v>311</v>
       </c>
       <c r="F198" s="1">
         <v>46248</v>
@@ -7316,7 +7361,7 @@
         <v>46252</v>
       </c>
       <c r="H198">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="199" spans="1:8" x14ac:dyDescent="0.2">
@@ -7330,10 +7375,10 @@
         <v>1</v>
       </c>
       <c r="D199" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E199" t="s">
-        <v>85</v>
+        <v>314</v>
       </c>
       <c r="F199" s="1">
         <v>46248</v>
@@ -7342,7 +7387,7 @@
         <v>46252</v>
       </c>
       <c r="H199">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="200" spans="1:8" x14ac:dyDescent="0.2">
@@ -7350,7 +7395,7 @@
         <v>0</v>
       </c>
       <c r="B200" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C200">
         <v>1</v>
@@ -7359,7 +7404,7 @@
         <v>12</v>
       </c>
       <c r="E200" t="s">
-        <v>315</v>
+        <v>117</v>
       </c>
       <c r="F200" s="1">
         <v>46248</v>
@@ -7385,7 +7430,7 @@
         <v>12</v>
       </c>
       <c r="E201" t="s">
-        <v>317</v>
+        <v>143</v>
       </c>
       <c r="F201" s="1">
         <v>46248</v>
@@ -7402,16 +7447,16 @@
         <v>0</v>
       </c>
       <c r="B202" t="s">
+        <v>317</v>
+      </c>
+      <c r="C202">
+        <v>1</v>
+      </c>
+      <c r="D202" t="s">
+        <v>12</v>
+      </c>
+      <c r="E202" t="s">
         <v>318</v>
-      </c>
-      <c r="C202">
-        <v>1</v>
-      </c>
-      <c r="D202" t="s">
-        <v>12</v>
-      </c>
-      <c r="E202" t="s">
-        <v>35</v>
       </c>
       <c r="F202" s="1">
         <v>46248</v>
@@ -7434,10 +7479,10 @@
         <v>1</v>
       </c>
       <c r="D203" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E203" t="s">
-        <v>35</v>
+        <v>320</v>
       </c>
       <c r="F203" s="1">
         <v>46248</v>
@@ -7446,7 +7491,7 @@
         <v>46252</v>
       </c>
       <c r="H203">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="204" spans="1:8" x14ac:dyDescent="0.2">
@@ -7454,16 +7499,16 @@
         <v>0</v>
       </c>
       <c r="B204" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C204">
         <v>1</v>
       </c>
       <c r="D204" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E204" t="s">
-        <v>72</v>
+        <v>157</v>
       </c>
       <c r="F204" s="1">
         <v>46248</v>
@@ -7472,7 +7517,7 @@
         <v>46252</v>
       </c>
       <c r="H204">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="205" spans="1:8" x14ac:dyDescent="0.2">
@@ -7480,7 +7525,7 @@
         <v>0</v>
       </c>
       <c r="B205" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C205">
         <v>1</v>
@@ -7489,7 +7534,7 @@
         <v>12</v>
       </c>
       <c r="E205" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="F205" s="1">
         <v>46248</v>
@@ -7506,7 +7551,7 @@
         <v>0</v>
       </c>
       <c r="B206" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C206">
         <v>1</v>
@@ -7515,7 +7560,7 @@
         <v>12</v>
       </c>
       <c r="E206" t="s">
-        <v>324</v>
+        <v>296</v>
       </c>
       <c r="F206" s="1">
         <v>46248</v>
@@ -7538,10 +7583,10 @@
         <v>1</v>
       </c>
       <c r="D207" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E207" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="F207" s="1">
         <v>46248</v>
@@ -7558,16 +7603,16 @@
         <v>0</v>
       </c>
       <c r="B208" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C208">
         <v>1</v>
       </c>
       <c r="D208" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E208" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="F208" s="1">
         <v>46248</v>
@@ -7576,7 +7621,7 @@
         <v>46252</v>
       </c>
       <c r="H208">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="209" spans="1:8" x14ac:dyDescent="0.2">
@@ -7584,7 +7629,7 @@
         <v>0</v>
       </c>
       <c r="B209" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C209">
         <v>1</v>
@@ -7593,10 +7638,10 @@
         <v>12</v>
       </c>
       <c r="E209" t="s">
-        <v>117</v>
+        <v>79</v>
       </c>
       <c r="F209" s="1">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="G209" s="1">
         <v>46252</v>
@@ -7610,25 +7655,25 @@
         <v>0</v>
       </c>
       <c r="B210" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C210">
         <v>1</v>
       </c>
       <c r="D210" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E210" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F210" s="1">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="G210" s="1">
         <v>46252</v>
       </c>
       <c r="H210">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="211" spans="1:8" x14ac:dyDescent="0.2">
@@ -7636,7 +7681,7 @@
         <v>0</v>
       </c>
       <c r="B211" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C211">
         <v>1</v>
@@ -7645,10 +7690,10 @@
         <v>12</v>
       </c>
       <c r="E211" t="s">
-        <v>143</v>
+        <v>333</v>
       </c>
       <c r="F211" s="1">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="G211" s="1">
         <v>46252</v>
@@ -7662,7 +7707,7 @@
         <v>0</v>
       </c>
       <c r="B212" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="C212">
         <v>1</v>
@@ -7671,10 +7716,10 @@
         <v>12</v>
       </c>
       <c r="E212" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="F212" s="1">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="G212" s="1">
         <v>46252</v>
@@ -7688,25 +7733,25 @@
         <v>0</v>
       </c>
       <c r="B213" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="C213">
         <v>1</v>
       </c>
       <c r="D213" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E213" t="s">
         <v>335</v>
       </c>
       <c r="F213" s="1">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="G213" s="1">
         <v>46252</v>
       </c>
       <c r="H213">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="214" spans="1:8" x14ac:dyDescent="0.2">
@@ -7714,25 +7759,25 @@
         <v>0</v>
       </c>
       <c r="B214" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C214">
         <v>1</v>
       </c>
       <c r="D214" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E214" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="F214" s="1">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="G214" s="1">
         <v>46252</v>
       </c>
       <c r="H214">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="215" spans="1:8" x14ac:dyDescent="0.2">
@@ -7740,7 +7785,7 @@
         <v>0</v>
       </c>
       <c r="B215" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C215">
         <v>1</v>
@@ -7749,10 +7794,10 @@
         <v>12</v>
       </c>
       <c r="E215" t="s">
-        <v>157</v>
+        <v>340</v>
       </c>
       <c r="F215" s="1">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="G215" s="1">
         <v>46252</v>
@@ -7766,7 +7811,7 @@
         <v>0</v>
       </c>
       <c r="B216" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="C216">
         <v>1</v>
@@ -7775,10 +7820,10 @@
         <v>12</v>
       </c>
       <c r="E216" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="F216" s="1">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="G216" s="1">
         <v>46252</v>
@@ -7792,7 +7837,7 @@
         <v>0</v>
       </c>
       <c r="B217" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="C217">
         <v>1</v>
@@ -7801,10 +7846,10 @@
         <v>12</v>
       </c>
       <c r="E217" t="s">
-        <v>304</v>
+        <v>344</v>
       </c>
       <c r="F217" s="1">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="G217" s="1">
         <v>46252</v>
@@ -7818,7 +7863,7 @@
         <v>0</v>
       </c>
       <c r="B218" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="C218">
         <v>1</v>
@@ -7827,10 +7872,10 @@
         <v>12</v>
       </c>
       <c r="E218" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="F218" s="1">
-        <v>46248</v>
+        <v>46252</v>
       </c>
       <c r="G218" s="1">
         <v>46252</v>
@@ -7844,7 +7889,7 @@
         <v>0</v>
       </c>
       <c r="B219" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="C219">
         <v>1</v>
@@ -7853,10 +7898,10 @@
         <v>12</v>
       </c>
       <c r="E219" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="F219" s="1">
-        <v>46248</v>
+        <v>46252</v>
       </c>
       <c r="G219" s="1">
         <v>46252</v>
@@ -7870,7 +7915,7 @@
         <v>0</v>
       </c>
       <c r="B220" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="C220">
         <v>1</v>
@@ -7879,10 +7924,10 @@
         <v>12</v>
       </c>
       <c r="E220" t="s">
-        <v>79</v>
+        <v>350</v>
       </c>
       <c r="F220" s="1">
-        <v>46249</v>
+        <v>46252</v>
       </c>
       <c r="G220" s="1">
         <v>46252</v>
@@ -7896,7 +7941,7 @@
         <v>0</v>
       </c>
       <c r="B221" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="C221">
         <v>1</v>
@@ -7905,10 +7950,10 @@
         <v>12</v>
       </c>
       <c r="E221" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="F221" s="1">
-        <v>46249</v>
+        <v>46252</v>
       </c>
       <c r="G221" s="1">
         <v>46252</v>
@@ -7922,7 +7967,7 @@
         <v>0</v>
       </c>
       <c r="B222" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="C222">
         <v>1</v>
@@ -7931,10 +7976,10 @@
         <v>12</v>
       </c>
       <c r="E222" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="F222" s="1">
-        <v>46249</v>
+        <v>46252</v>
       </c>
       <c r="G222" s="1">
         <v>46252</v>
@@ -7948,25 +7993,25 @@
         <v>0</v>
       </c>
       <c r="B223" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="C223">
         <v>1</v>
       </c>
       <c r="D223" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E223" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="F223" s="1">
-        <v>46249</v>
+        <v>46252</v>
       </c>
       <c r="G223" s="1">
         <v>46252</v>
       </c>
       <c r="H223">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="224" spans="1:8" x14ac:dyDescent="0.2">
@@ -7974,7 +8019,7 @@
         <v>0</v>
       </c>
       <c r="B224" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="C224">
         <v>1</v>
@@ -7983,10 +8028,10 @@
         <v>12</v>
       </c>
       <c r="E224" t="s">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="F224" s="1">
-        <v>46249</v>
+        <v>46252</v>
       </c>
       <c r="G224" s="1">
         <v>46252</v>
@@ -8000,7 +8045,7 @@
         <v>0</v>
       </c>
       <c r="B225" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="C225">
         <v>1</v>
@@ -8009,10 +8054,10 @@
         <v>12</v>
       </c>
       <c r="E225" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="F225" s="1">
-        <v>46249</v>
+        <v>46252</v>
       </c>
       <c r="G225" s="1">
         <v>46252</v>
@@ -8026,7 +8071,7 @@
         <v>0</v>
       </c>
       <c r="B226" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="C226">
         <v>1</v>
@@ -8035,10 +8080,10 @@
         <v>12</v>
       </c>
       <c r="E226" t="s">
-        <v>356</v>
+        <v>13</v>
       </c>
       <c r="F226" s="1">
-        <v>46249</v>
+        <v>46252</v>
       </c>
       <c r="G226" s="1">
         <v>46252</v>
@@ -8052,7 +8097,7 @@
         <v>0</v>
       </c>
       <c r="B227" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="C227">
         <v>1</v>
@@ -8061,10 +8106,10 @@
         <v>12</v>
       </c>
       <c r="E227" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="F227" s="1">
-        <v>46249</v>
+        <v>46252</v>
       </c>
       <c r="G227" s="1">
         <v>46252</v>
@@ -8078,7 +8123,7 @@
         <v>0</v>
       </c>
       <c r="B228" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="C228">
         <v>1</v>
@@ -8087,10 +8132,10 @@
         <v>12</v>
       </c>
       <c r="E228" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="F228" s="1">
-        <v>46249</v>
+        <v>46252</v>
       </c>
       <c r="G228" s="1">
         <v>46252</v>
@@ -8104,7 +8149,7 @@
         <v>0</v>
       </c>
       <c r="B229" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="C229">
         <v>1</v>
@@ -8113,7 +8158,7 @@
         <v>12</v>
       </c>
       <c r="E229" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="F229" s="1">
         <v>46252</v>
@@ -8130,7 +8175,7 @@
         <v>0</v>
       </c>
       <c r="B230" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="C230">
         <v>1</v>
@@ -8139,7 +8184,7 @@
         <v>12</v>
       </c>
       <c r="E230" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="F230" s="1">
         <v>46252</v>
@@ -8156,7 +8201,7 @@
         <v>0</v>
       </c>
       <c r="B231" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="C231">
         <v>1</v>
@@ -8165,7 +8210,7 @@
         <v>12</v>
       </c>
       <c r="E231" t="s">
-        <v>366</v>
+        <v>72</v>
       </c>
       <c r="F231" s="1">
         <v>46252</v>
@@ -8182,7 +8227,7 @@
         <v>0</v>
       </c>
       <c r="B232" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="C232">
         <v>1</v>
@@ -8191,7 +8236,7 @@
         <v>12</v>
       </c>
       <c r="E232" t="s">
-        <v>368</v>
+        <v>33</v>
       </c>
       <c r="F232" s="1">
         <v>46252</v>
@@ -8208,7 +8253,7 @@
         <v>0</v>
       </c>
       <c r="B233" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="C233">
         <v>1</v>
@@ -8217,7 +8262,7 @@
         <v>12</v>
       </c>
       <c r="E233" t="s">
-        <v>370</v>
+        <v>240</v>
       </c>
       <c r="F233" s="1">
         <v>46252</v>
@@ -8234,16 +8279,16 @@
         <v>0</v>
       </c>
       <c r="B234" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C234">
         <v>1</v>
       </c>
       <c r="D234" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E234" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F234" s="1">
         <v>46252</v>
@@ -8252,7 +8297,7 @@
         <v>46252</v>
       </c>
       <c r="H234">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="235" spans="1:8" x14ac:dyDescent="0.2">
@@ -8260,16 +8305,16 @@
         <v>0</v>
       </c>
       <c r="B235" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C235">
         <v>1</v>
       </c>
       <c r="D235" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E235" t="s">
-        <v>330</v>
+        <v>270</v>
       </c>
       <c r="F235" s="1">
         <v>46252</v>
@@ -8278,7 +8323,7 @@
         <v>46252</v>
       </c>
       <c r="H235">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="236" spans="1:8" x14ac:dyDescent="0.2">
@@ -8286,7 +8331,7 @@
         <v>0</v>
       </c>
       <c r="B236" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C236">
         <v>1</v>
@@ -8295,7 +8340,7 @@
         <v>12</v>
       </c>
       <c r="E236" t="s">
-        <v>375</v>
+        <v>66</v>
       </c>
       <c r="F236" s="1">
         <v>46252</v>
@@ -8321,7 +8366,7 @@
         <v>12</v>
       </c>
       <c r="E237" t="s">
-        <v>377</v>
+        <v>13</v>
       </c>
       <c r="F237" s="1">
         <v>46252</v>
@@ -8338,7 +8383,7 @@
         <v>0</v>
       </c>
       <c r="B238" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C238">
         <v>1</v>
@@ -8364,7 +8409,7 @@
         <v>0</v>
       </c>
       <c r="B239" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C239">
         <v>1</v>
@@ -8373,7 +8418,7 @@
         <v>12</v>
       </c>
       <c r="E239" t="s">
-        <v>380</v>
+        <v>13</v>
       </c>
       <c r="F239" s="1">
         <v>46252</v>
@@ -8390,16 +8435,16 @@
         <v>0</v>
       </c>
       <c r="B240" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="C240">
         <v>1</v>
       </c>
       <c r="D240" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E240" t="s">
-        <v>117</v>
+        <v>13</v>
       </c>
       <c r="F240" s="1">
         <v>46252</v>
@@ -8408,7 +8453,7 @@
         <v>46252</v>
       </c>
       <c r="H240">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="241" spans="1:8" x14ac:dyDescent="0.2">
@@ -8416,7 +8461,7 @@
         <v>0</v>
       </c>
       <c r="B241" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C241">
         <v>1</v>
@@ -8425,7 +8470,7 @@
         <v>12</v>
       </c>
       <c r="E241" t="s">
-        <v>383</v>
+        <v>55</v>
       </c>
       <c r="F241" s="1">
         <v>46252</v>
@@ -8442,7 +8487,7 @@
         <v>0</v>
       </c>
       <c r="B242" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="C242">
         <v>1</v>
@@ -8451,7 +8496,7 @@
         <v>12</v>
       </c>
       <c r="E242" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="F242" s="1">
         <v>46252</v>
@@ -8468,7 +8513,7 @@
         <v>0</v>
       </c>
       <c r="B243" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="C243">
         <v>1</v>
@@ -8477,7 +8522,7 @@
         <v>12</v>
       </c>
       <c r="E243" t="s">
-        <v>385</v>
+        <v>70</v>
       </c>
       <c r="F243" s="1">
         <v>46252</v>
@@ -8494,7 +8539,7 @@
         <v>0</v>
       </c>
       <c r="B244" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="C244">
         <v>1</v>
@@ -8503,7 +8548,7 @@
         <v>12</v>
       </c>
       <c r="E244" t="s">
-        <v>72</v>
+        <v>385</v>
       </c>
       <c r="F244" s="1">
         <v>46252</v>
@@ -8520,7 +8565,7 @@
         <v>0</v>
       </c>
       <c r="B245" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C245">
         <v>1</v>
@@ -8529,13 +8574,13 @@
         <v>12</v>
       </c>
       <c r="E245" t="s">
-        <v>33</v>
+        <v>85</v>
       </c>
       <c r="F245" s="1">
         <v>46252</v>
       </c>
       <c r="G245" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="H245">
         <v>0</v>
@@ -8546,25 +8591,25 @@
         <v>0</v>
       </c>
       <c r="B246" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C246">
         <v>1</v>
       </c>
       <c r="D246" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E246" t="s">
-        <v>390</v>
+        <v>283</v>
       </c>
       <c r="F246" s="1">
         <v>46252</v>
       </c>
       <c r="G246" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="H246">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="247" spans="1:8" x14ac:dyDescent="0.2">
@@ -8572,16 +8617,16 @@
         <v>0</v>
       </c>
       <c r="B247" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="C247">
         <v>1</v>
       </c>
       <c r="D247" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E247" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F247" s="1">
         <v>46252</v>
@@ -8590,7 +8635,7 @@
         <v>46252</v>
       </c>
       <c r="H247">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="248" spans="1:8" x14ac:dyDescent="0.2">
@@ -8598,7 +8643,7 @@
         <v>0</v>
       </c>
       <c r="B248" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C248">
         <v>1</v>
@@ -8607,16 +8652,16 @@
         <v>2</v>
       </c>
       <c r="E248" t="s">
-        <v>390</v>
+        <v>176</v>
       </c>
       <c r="F248" s="1">
         <v>46252</v>
       </c>
       <c r="G248" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="H248">
-        <v>2</v>
+        <v>20</v>
       </c>
     </row>
     <row r="249" spans="1:8" x14ac:dyDescent="0.2">
@@ -8624,7 +8669,7 @@
         <v>0</v>
       </c>
       <c r="B249" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="C249">
         <v>1</v>
@@ -8633,7 +8678,7 @@
         <v>12</v>
       </c>
       <c r="E249" t="s">
-        <v>242</v>
+        <v>392</v>
       </c>
       <c r="F249" s="1">
         <v>46252</v>
@@ -8650,7 +8695,7 @@
         <v>0</v>
       </c>
       <c r="B250" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C250">
         <v>1</v>
@@ -8659,7 +8704,7 @@
         <v>12</v>
       </c>
       <c r="E250" t="s">
-        <v>395</v>
+        <v>178</v>
       </c>
       <c r="F250" s="1">
         <v>46252</v>
@@ -8676,16 +8721,16 @@
         <v>0</v>
       </c>
       <c r="B251" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="C251">
         <v>1</v>
       </c>
       <c r="D251" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E251" t="s">
-        <v>272</v>
+        <v>15</v>
       </c>
       <c r="F251" s="1">
         <v>46252</v>
@@ -8694,7 +8739,7 @@
         <v>46252</v>
       </c>
       <c r="H251">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="252" spans="1:8" x14ac:dyDescent="0.2">
@@ -8702,7 +8747,7 @@
         <v>0</v>
       </c>
       <c r="B252" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C252">
         <v>1</v>
@@ -8711,7 +8756,7 @@
         <v>12</v>
       </c>
       <c r="E252" t="s">
-        <v>66</v>
+        <v>396</v>
       </c>
       <c r="F252" s="1">
         <v>46252</v>
@@ -8728,7 +8773,7 @@
         <v>0</v>
       </c>
       <c r="B253" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C253">
         <v>1</v>
@@ -8737,7 +8782,7 @@
         <v>12</v>
       </c>
       <c r="E253" t="s">
-        <v>13</v>
+        <v>134</v>
       </c>
       <c r="F253" s="1">
         <v>46252</v>
@@ -8754,7 +8799,7 @@
         <v>0</v>
       </c>
       <c r="B254" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C254">
         <v>1</v>
@@ -8763,7 +8808,7 @@
         <v>12</v>
       </c>
       <c r="E254" t="s">
-        <v>13</v>
+        <v>134</v>
       </c>
       <c r="F254" s="1">
         <v>46252</v>
@@ -8780,16 +8825,16 @@
         <v>0</v>
       </c>
       <c r="B255" t="s">
+        <v>399</v>
+      </c>
+      <c r="C255">
+        <v>1</v>
+      </c>
+      <c r="D255" t="s">
+        <v>12</v>
+      </c>
+      <c r="E255" t="s">
         <v>400</v>
-      </c>
-      <c r="C255">
-        <v>1</v>
-      </c>
-      <c r="D255" t="s">
-        <v>12</v>
-      </c>
-      <c r="E255" t="s">
-        <v>13</v>
       </c>
       <c r="F255" s="1">
         <v>46252</v>
@@ -8815,13 +8860,13 @@
         <v>12</v>
       </c>
       <c r="E256" t="s">
-        <v>13</v>
+        <v>402</v>
       </c>
       <c r="F256" s="1">
         <v>46252</v>
       </c>
       <c r="G256" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="H256">
         <v>0</v>
@@ -8832,7 +8877,7 @@
         <v>0</v>
       </c>
       <c r="B257" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C257">
         <v>1</v>
@@ -8841,13 +8886,13 @@
         <v>12</v>
       </c>
       <c r="E257" t="s">
-        <v>55</v>
+        <v>404</v>
       </c>
       <c r="F257" s="1">
         <v>46252</v>
       </c>
       <c r="G257" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="H257">
         <v>0</v>
@@ -8858,16 +8903,16 @@
         <v>0</v>
       </c>
       <c r="B258" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C258">
         <v>1</v>
       </c>
       <c r="D258" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E258" t="s">
-        <v>250</v>
+        <v>296</v>
       </c>
       <c r="F258" s="1">
         <v>46252</v>
@@ -8876,7 +8921,7 @@
         <v>46252</v>
       </c>
       <c r="H258">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="259" spans="1:8" x14ac:dyDescent="0.2">
@@ -8884,25 +8929,25 @@
         <v>0</v>
       </c>
       <c r="B259" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="C259">
         <v>1</v>
       </c>
       <c r="D259" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E259" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="F259" s="1">
         <v>46252</v>
       </c>
       <c r="G259" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="H259">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="260" spans="1:8" x14ac:dyDescent="0.2">
@@ -8910,7 +8955,7 @@
         <v>0</v>
       </c>
       <c r="B260" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C260">
         <v>1</v>
@@ -8919,7 +8964,7 @@
         <v>12</v>
       </c>
       <c r="E260" t="s">
-        <v>70</v>
+        <v>335</v>
       </c>
       <c r="F260" s="1">
         <v>46252</v>
@@ -8936,7 +8981,7 @@
         <v>0</v>
       </c>
       <c r="B261" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="C261">
         <v>1</v>
@@ -8945,7 +8990,7 @@
         <v>12</v>
       </c>
       <c r="E261" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="F261" s="1">
         <v>46252</v>
@@ -8962,7 +9007,7 @@
         <v>0</v>
       </c>
       <c r="B262" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="C262">
         <v>1</v>
@@ -8971,13 +9016,13 @@
         <v>12</v>
       </c>
       <c r="E262" t="s">
-        <v>85</v>
+        <v>412</v>
       </c>
       <c r="F262" s="1">
         <v>46252</v>
       </c>
       <c r="G262" s="1">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="H262">
         <v>0</v>
@@ -8988,7 +9033,7 @@
         <v>0</v>
       </c>
       <c r="B263" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="C263">
         <v>1</v>
@@ -8997,13 +9042,13 @@
         <v>12</v>
       </c>
       <c r="E263" t="s">
-        <v>290</v>
+        <v>412</v>
       </c>
       <c r="F263" s="1">
         <v>46252</v>
       </c>
       <c r="G263" s="1">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="H263">
         <v>0</v>
@@ -9014,7 +9059,7 @@
         <v>0</v>
       </c>
       <c r="B264" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="C264">
         <v>1</v>
@@ -9029,7 +9074,7 @@
         <v>46252</v>
       </c>
       <c r="G264" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="H264">
         <v>0</v>
@@ -9040,25 +9085,25 @@
         <v>0</v>
       </c>
       <c r="B265" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="C265">
         <v>1</v>
       </c>
       <c r="D265" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E265" t="s">
-        <v>176</v>
+        <v>192</v>
       </c>
       <c r="F265" s="1">
         <v>46252</v>
       </c>
       <c r="G265" s="1">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="H265">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="266" spans="1:8" x14ac:dyDescent="0.2">
@@ -9066,16 +9111,16 @@
         <v>0</v>
       </c>
       <c r="B266" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C266">
         <v>1</v>
       </c>
       <c r="D266" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E266" t="s">
-        <v>176</v>
+        <v>412</v>
       </c>
       <c r="F266" s="1">
         <v>46252</v>
@@ -9084,7 +9129,7 @@
         <v>46252</v>
       </c>
       <c r="H266">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="267" spans="1:8" x14ac:dyDescent="0.2">
@@ -9092,7 +9137,7 @@
         <v>0</v>
       </c>
       <c r="B267" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="C267">
         <v>1</v>
@@ -9101,7 +9146,7 @@
         <v>12</v>
       </c>
       <c r="E267" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="F267" s="1">
         <v>46252</v>
@@ -9118,16 +9163,16 @@
         <v>0</v>
       </c>
       <c r="B268" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C268">
         <v>1</v>
       </c>
       <c r="D268" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E268" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="F268" s="1">
         <v>46252</v>
@@ -9136,7 +9181,7 @@
         <v>46252</v>
       </c>
       <c r="H268">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="269" spans="1:8" x14ac:dyDescent="0.2">
@@ -9153,13 +9198,13 @@
         <v>12</v>
       </c>
       <c r="E269" t="s">
-        <v>178</v>
+        <v>420</v>
       </c>
       <c r="F269" s="1">
         <v>46252</v>
       </c>
       <c r="G269" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="H269">
         <v>0</v>
@@ -9170,25 +9215,25 @@
         <v>0</v>
       </c>
       <c r="B270" t="s">
+        <v>421</v>
+      </c>
+      <c r="C270">
+        <v>1</v>
+      </c>
+      <c r="D270" t="s">
+        <v>12</v>
+      </c>
+      <c r="E270" t="s">
         <v>420</v>
       </c>
-      <c r="C270">
-        <v>1</v>
-      </c>
-      <c r="D270" t="s">
-        <v>2</v>
-      </c>
-      <c r="E270" t="s">
-        <v>15</v>
-      </c>
       <c r="F270" s="1">
         <v>46252</v>
       </c>
       <c r="G270" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="H270">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="271" spans="1:8" x14ac:dyDescent="0.2">
@@ -9196,7 +9241,7 @@
         <v>0</v>
       </c>
       <c r="B271" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C271">
         <v>1</v>
@@ -9205,13 +9250,13 @@
         <v>12</v>
       </c>
       <c r="E271" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="F271" s="1">
         <v>46252</v>
       </c>
       <c r="G271" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="H271">
         <v>0</v>
@@ -9222,7 +9267,7 @@
         <v>0</v>
       </c>
       <c r="B272" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C272">
         <v>1</v>
@@ -9231,13 +9276,13 @@
         <v>12</v>
       </c>
       <c r="E272" t="s">
-        <v>134</v>
+        <v>425</v>
       </c>
       <c r="F272" s="1">
         <v>46252</v>
       </c>
       <c r="G272" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="H272">
         <v>0</v>
@@ -9248,7 +9293,7 @@
         <v>0</v>
       </c>
       <c r="B273" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="C273">
         <v>1</v>
@@ -9257,13 +9302,13 @@
         <v>12</v>
       </c>
       <c r="E273" t="s">
-        <v>134</v>
+        <v>427</v>
       </c>
       <c r="F273" s="1">
         <v>46252</v>
       </c>
       <c r="G273" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="H273">
         <v>0</v>
@@ -9274,25 +9319,25 @@
         <v>0</v>
       </c>
       <c r="B274" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="C274">
         <v>1</v>
       </c>
       <c r="D274" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E274" t="s">
-        <v>426</v>
+        <v>219</v>
       </c>
       <c r="F274" s="1">
         <v>46252</v>
       </c>
       <c r="G274" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="H274">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="275" spans="1:8" x14ac:dyDescent="0.2">
@@ -9300,7 +9345,7 @@
         <v>0</v>
       </c>
       <c r="B275" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C275">
         <v>1</v>
@@ -9309,13 +9354,13 @@
         <v>12</v>
       </c>
       <c r="E275" t="s">
-        <v>428</v>
+        <v>167</v>
       </c>
       <c r="F275" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="G275" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="H275">
         <v>0</v>
@@ -9326,7 +9371,7 @@
         <v>0</v>
       </c>
       <c r="B276" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C276">
         <v>1</v>
@@ -9335,10 +9380,10 @@
         <v>12</v>
       </c>
       <c r="E276" t="s">
-        <v>430</v>
+        <v>167</v>
       </c>
       <c r="F276" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="G276" s="1">
         <v>46253</v>
@@ -9364,7 +9409,7 @@
         <v>432</v>
       </c>
       <c r="F277" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="G277" s="1">
         <v>46253</v>
@@ -9384,19 +9429,19 @@
         <v>1</v>
       </c>
       <c r="D278" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E278" t="s">
-        <v>127</v>
+        <v>434</v>
       </c>
       <c r="F278" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="G278" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="H278">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="279" spans="1:8" x14ac:dyDescent="0.2">
@@ -9404,22 +9449,22 @@
         <v>0</v>
       </c>
       <c r="B279" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C279">
         <v>1</v>
       </c>
       <c r="D279" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E279" t="s">
-        <v>304</v>
+        <v>436</v>
       </c>
       <c r="F279" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="G279" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="H279">
         <v>0</v>
@@ -9430,25 +9475,25 @@
         <v>0</v>
       </c>
       <c r="B280" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="C280">
         <v>1</v>
       </c>
       <c r="D280" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E280" t="s">
-        <v>436</v>
+        <v>27</v>
       </c>
       <c r="F280" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="G280" s="1">
         <v>46253</v>
       </c>
       <c r="H280">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="281" spans="1:8" x14ac:dyDescent="0.2">
@@ -9456,7 +9501,7 @@
         <v>0</v>
       </c>
       <c r="B281" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C281">
         <v>1</v>
@@ -9465,13 +9510,13 @@
         <v>12</v>
       </c>
       <c r="E281" t="s">
-        <v>351</v>
+        <v>27</v>
       </c>
       <c r="F281" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="G281" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="H281">
         <v>0</v>
@@ -9482,7 +9527,7 @@
         <v>0</v>
       </c>
       <c r="B282" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C282">
         <v>1</v>
@@ -9491,13 +9536,13 @@
         <v>12</v>
       </c>
       <c r="E282" t="s">
-        <v>439</v>
+        <v>27</v>
       </c>
       <c r="F282" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="G282" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="H282">
         <v>0</v>
@@ -9517,13 +9562,13 @@
         <v>12</v>
       </c>
       <c r="E283" t="s">
-        <v>441</v>
+        <v>274</v>
       </c>
       <c r="F283" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="G283" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="H283">
         <v>0</v>
@@ -9534,25 +9579,25 @@
         <v>0</v>
       </c>
       <c r="B284" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C284">
         <v>1</v>
       </c>
       <c r="D284" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E284" t="s">
-        <v>441</v>
+        <v>124</v>
       </c>
       <c r="F284" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="G284" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="H284">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="285" spans="1:8" x14ac:dyDescent="0.2">
@@ -9560,7 +9605,7 @@
         <v>0</v>
       </c>
       <c r="B285" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C285">
         <v>1</v>
@@ -9569,16 +9614,16 @@
         <v>2</v>
       </c>
       <c r="E285" t="s">
-        <v>444</v>
+        <v>124</v>
       </c>
       <c r="F285" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="G285" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="H285">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="286" spans="1:8" x14ac:dyDescent="0.2">
@@ -9586,7 +9631,7 @@
         <v>0</v>
       </c>
       <c r="B286" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="C286">
         <v>1</v>
@@ -9595,10 +9640,10 @@
         <v>12</v>
       </c>
       <c r="E286" t="s">
-        <v>441</v>
+        <v>57</v>
       </c>
       <c r="F286" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="G286" s="1">
         <v>46253</v>
@@ -9612,7 +9657,7 @@
         <v>0</v>
       </c>
       <c r="B287" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="C287">
         <v>1</v>
@@ -9621,13 +9666,13 @@
         <v>12</v>
       </c>
       <c r="E287" t="s">
-        <v>192</v>
+        <v>13</v>
       </c>
       <c r="F287" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="G287" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="H287">
         <v>0</v>
@@ -9638,25 +9683,25 @@
         <v>0</v>
       </c>
       <c r="B288" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="C288">
         <v>1</v>
       </c>
       <c r="D288" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E288" t="s">
-        <v>448</v>
+        <v>10</v>
       </c>
       <c r="F288" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="G288" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="H288">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="289" spans="1:8" x14ac:dyDescent="0.2">
@@ -9664,7 +9709,7 @@
         <v>0</v>
       </c>
       <c r="B289" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="C289">
         <v>1</v>
@@ -9673,13 +9718,13 @@
         <v>12</v>
       </c>
       <c r="E289" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="F289" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="G289" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="H289">
         <v>0</v>
@@ -9690,7 +9735,7 @@
         <v>0</v>
       </c>
       <c r="B290" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="C290">
         <v>1</v>
@@ -9699,13 +9744,13 @@
         <v>12</v>
       </c>
       <c r="E290" t="s">
-        <v>441</v>
+        <v>66</v>
       </c>
       <c r="F290" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="G290" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="H290">
         <v>0</v>
@@ -9716,7 +9761,7 @@
         <v>0</v>
       </c>
       <c r="B291" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="C291">
         <v>1</v>
@@ -9725,13 +9770,13 @@
         <v>12</v>
       </c>
       <c r="E291" t="s">
-        <v>441</v>
+        <v>146</v>
       </c>
       <c r="F291" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="G291" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="H291">
         <v>0</v>
@@ -9742,7 +9787,7 @@
         <v>0</v>
       </c>
       <c r="B292" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="C292">
         <v>1</v>
@@ -9751,10 +9796,10 @@
         <v>12</v>
       </c>
       <c r="E292" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="F292" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="G292" s="1">
         <v>46253</v>
@@ -9768,7 +9813,7 @@
         <v>0</v>
       </c>
       <c r="B293" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="C293">
         <v>1</v>
@@ -9780,7 +9825,7 @@
         <v>453</v>
       </c>
       <c r="F293" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="G293" s="1">
         <v>46253</v>
@@ -9794,19 +9839,19 @@
         <v>0</v>
       </c>
       <c r="B294" t="s">
+        <v>454</v>
+      </c>
+      <c r="C294">
+        <v>1</v>
+      </c>
+      <c r="D294" t="s">
+        <v>12</v>
+      </c>
+      <c r="E294" t="s">
         <v>455</v>
       </c>
-      <c r="C294">
-        <v>1</v>
-      </c>
-      <c r="D294" t="s">
-        <v>12</v>
-      </c>
-      <c r="E294" t="s">
-        <v>456</v>
-      </c>
       <c r="F294" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="G294" s="1">
         <v>46253</v>
@@ -9820,19 +9865,19 @@
         <v>0</v>
       </c>
       <c r="B295" t="s">
+        <v>456</v>
+      </c>
+      <c r="C295">
+        <v>1</v>
+      </c>
+      <c r="D295" t="s">
+        <v>12</v>
+      </c>
+      <c r="E295" t="s">
         <v>457</v>
       </c>
-      <c r="C295">
-        <v>1</v>
-      </c>
-      <c r="D295" t="s">
-        <v>12</v>
-      </c>
-      <c r="E295" t="s">
-        <v>458</v>
-      </c>
       <c r="F295" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="G295" s="1">
         <v>46253</v>
@@ -9846,7 +9891,7 @@
         <v>0</v>
       </c>
       <c r="B296" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C296">
         <v>1</v>
@@ -9855,10 +9900,10 @@
         <v>12</v>
       </c>
       <c r="E296" t="s">
-        <v>460</v>
+        <v>292</v>
       </c>
       <c r="F296" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="G296" s="1">
         <v>46253</v>
@@ -9872,7 +9917,7 @@
         <v>0</v>
       </c>
       <c r="B297" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="C297">
         <v>1</v>
@@ -9881,10 +9926,10 @@
         <v>12</v>
       </c>
       <c r="E297" t="s">
-        <v>219</v>
+        <v>460</v>
       </c>
       <c r="F297" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="G297" s="1">
         <v>46253</v>
@@ -9898,16 +9943,16 @@
         <v>0</v>
       </c>
       <c r="B298" t="s">
+        <v>461</v>
+      </c>
+      <c r="C298">
+        <v>1</v>
+      </c>
+      <c r="D298" t="s">
+        <v>12</v>
+      </c>
+      <c r="E298" t="s">
         <v>462</v>
-      </c>
-      <c r="C298">
-        <v>1</v>
-      </c>
-      <c r="D298" t="s">
-        <v>12</v>
-      </c>
-      <c r="E298" t="s">
-        <v>167</v>
       </c>
       <c r="F298" s="1">
         <v>46253</v>
@@ -9933,7 +9978,7 @@
         <v>12</v>
       </c>
       <c r="E299" t="s">
-        <v>167</v>
+        <v>396</v>
       </c>
       <c r="F299" s="1">
         <v>46253</v>
@@ -9959,7 +10004,7 @@
         <v>12</v>
       </c>
       <c r="E300" t="s">
-        <v>465</v>
+        <v>122</v>
       </c>
       <c r="F300" s="1">
         <v>46253</v>
@@ -9976,16 +10021,16 @@
         <v>0</v>
       </c>
       <c r="B301" t="s">
+        <v>465</v>
+      </c>
+      <c r="C301">
+        <v>1</v>
+      </c>
+      <c r="D301" t="s">
+        <v>12</v>
+      </c>
+      <c r="E301" t="s">
         <v>466</v>
-      </c>
-      <c r="C301">
-        <v>1</v>
-      </c>
-      <c r="D301" t="s">
-        <v>12</v>
-      </c>
-      <c r="E301" t="s">
-        <v>467</v>
       </c>
       <c r="F301" s="1">
         <v>46253</v>
@@ -10002,16 +10047,16 @@
         <v>0</v>
       </c>
       <c r="B302" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C302">
         <v>1</v>
       </c>
       <c r="D302" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E302" t="s">
-        <v>469</v>
+        <v>296</v>
       </c>
       <c r="F302" s="1">
         <v>46253</v>
@@ -10028,7 +10073,7 @@
         <v>0</v>
       </c>
       <c r="B303" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="C303">
         <v>1</v>
@@ -10037,7 +10082,7 @@
         <v>12</v>
       </c>
       <c r="E303" t="s">
-        <v>27</v>
+        <v>469</v>
       </c>
       <c r="F303" s="1">
         <v>46253</v>
@@ -10054,16 +10099,16 @@
         <v>0</v>
       </c>
       <c r="B304" t="s">
+        <v>470</v>
+      </c>
+      <c r="C304">
+        <v>1</v>
+      </c>
+      <c r="D304" t="s">
+        <v>12</v>
+      </c>
+      <c r="E304" t="s">
         <v>471</v>
-      </c>
-      <c r="C304">
-        <v>1</v>
-      </c>
-      <c r="D304" t="s">
-        <v>12</v>
-      </c>
-      <c r="E304" t="s">
-        <v>27</v>
       </c>
       <c r="F304" s="1">
         <v>46253</v>
@@ -10089,7 +10134,7 @@
         <v>12</v>
       </c>
       <c r="E305" t="s">
-        <v>27</v>
+        <v>323</v>
       </c>
       <c r="F305" s="1">
         <v>46253</v>
@@ -10115,7 +10160,7 @@
         <v>12</v>
       </c>
       <c r="E306" t="s">
-        <v>278</v>
+        <v>335</v>
       </c>
       <c r="F306" s="1">
         <v>46253</v>
@@ -10138,10 +10183,10 @@
         <v>1</v>
       </c>
       <c r="D307" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E307" t="s">
-        <v>124</v>
+        <v>475</v>
       </c>
       <c r="F307" s="1">
         <v>46253</v>
@@ -10150,7 +10195,7 @@
         <v>46253</v>
       </c>
       <c r="H307">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="308" spans="1:8" x14ac:dyDescent="0.2">
@@ -10158,16 +10203,16 @@
         <v>0</v>
       </c>
       <c r="B308" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C308">
         <v>1</v>
       </c>
       <c r="D308" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E308" t="s">
-        <v>124</v>
+        <v>477</v>
       </c>
       <c r="F308" s="1">
         <v>46253</v>
@@ -10176,7 +10221,7 @@
         <v>46253</v>
       </c>
       <c r="H308">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="309" spans="1:8" x14ac:dyDescent="0.2">
@@ -10184,7 +10229,7 @@
         <v>0</v>
       </c>
       <c r="B309" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="C309">
         <v>1</v>
@@ -10193,7 +10238,7 @@
         <v>12</v>
       </c>
       <c r="E309" t="s">
-        <v>57</v>
+        <v>141</v>
       </c>
       <c r="F309" s="1">
         <v>46253</v>
@@ -10210,7 +10255,7 @@
         <v>0</v>
       </c>
       <c r="B310" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="C310">
         <v>1</v>
@@ -10219,7 +10264,7 @@
         <v>12</v>
       </c>
       <c r="E310" t="s">
-        <v>13</v>
+        <v>480</v>
       </c>
       <c r="F310" s="1">
         <v>46253</v>
@@ -10236,7 +10281,7 @@
         <v>0</v>
       </c>
       <c r="B311" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="C311">
         <v>1</v>
@@ -10245,7 +10290,7 @@
         <v>12</v>
       </c>
       <c r="E311" t="s">
-        <v>10</v>
+        <v>396</v>
       </c>
       <c r="F311" s="1">
         <v>46253</v>
@@ -10262,7 +10307,7 @@
         <v>0</v>
       </c>
       <c r="B312" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="C312">
         <v>1</v>
@@ -10271,7 +10316,7 @@
         <v>12</v>
       </c>
       <c r="E312" t="s">
-        <v>480</v>
+        <v>382</v>
       </c>
       <c r="F312" s="1">
         <v>46253</v>
@@ -10288,7 +10333,7 @@
         <v>0</v>
       </c>
       <c r="B313" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C313">
         <v>1</v>
@@ -10297,7 +10342,7 @@
         <v>12</v>
       </c>
       <c r="E313" t="s">
-        <v>66</v>
+        <v>27</v>
       </c>
       <c r="F313" s="1">
         <v>46253</v>
@@ -10314,7 +10359,7 @@
         <v>0</v>
       </c>
       <c r="B314" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="C314">
         <v>1</v>
@@ -10323,7 +10368,7 @@
         <v>12</v>
       </c>
       <c r="E314" t="s">
-        <v>146</v>
+        <v>27</v>
       </c>
       <c r="F314" s="1">
         <v>46253</v>
@@ -10340,7 +10385,7 @@
         <v>0</v>
       </c>
       <c r="B315" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="C315">
         <v>1</v>
@@ -10349,7 +10394,7 @@
         <v>12</v>
       </c>
       <c r="E315" t="s">
-        <v>426</v>
+        <v>27</v>
       </c>
       <c r="F315" s="1">
         <v>46253</v>
@@ -10366,7 +10411,7 @@
         <v>0</v>
       </c>
       <c r="B316" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="C316">
         <v>1</v>
@@ -10375,7 +10420,7 @@
         <v>12</v>
       </c>
       <c r="E316" t="s">
-        <v>485</v>
+        <v>27</v>
       </c>
       <c r="F316" s="1">
         <v>46253</v>
@@ -10392,7 +10437,7 @@
         <v>0</v>
       </c>
       <c r="B317" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C317">
         <v>1</v>
@@ -10401,7 +10446,7 @@
         <v>12</v>
       </c>
       <c r="E317" t="s">
-        <v>487</v>
+        <v>27</v>
       </c>
       <c r="F317" s="1">
         <v>46253</v>
@@ -10427,7 +10472,7 @@
         <v>12</v>
       </c>
       <c r="E318" t="s">
-        <v>299</v>
+        <v>27</v>
       </c>
       <c r="F318" s="1">
         <v>46253</v>
@@ -10453,7 +10498,7 @@
         <v>12</v>
       </c>
       <c r="E319" t="s">
-        <v>490</v>
+        <v>27</v>
       </c>
       <c r="F319" s="1">
         <v>46253</v>
@@ -10470,7 +10515,7 @@
         <v>0</v>
       </c>
       <c r="B320" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C320">
         <v>1</v>
@@ -10479,7 +10524,7 @@
         <v>12</v>
       </c>
       <c r="E320" t="s">
-        <v>422</v>
+        <v>27</v>
       </c>
       <c r="F320" s="1">
         <v>46253</v>
@@ -10496,16 +10541,16 @@
         <v>0</v>
       </c>
       <c r="B321" t="s">
+        <v>491</v>
+      </c>
+      <c r="C321">
+        <v>1</v>
+      </c>
+      <c r="D321" t="s">
+        <v>12</v>
+      </c>
+      <c r="E321" t="s">
         <v>492</v>
-      </c>
-      <c r="C321">
-        <v>1</v>
-      </c>
-      <c r="D321" t="s">
-        <v>12</v>
-      </c>
-      <c r="E321" t="s">
-        <v>122</v>
       </c>
       <c r="F321" s="1">
         <v>46253</v>
@@ -10519,51 +10564,51 @@
     </row>
     <row r="322" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A322" t="s">
+        <v>0</v>
+      </c>
+      <c r="B322" t="s">
         <v>493</v>
       </c>
-      <c r="B322" t="s">
+      <c r="C322">
+        <v>1</v>
+      </c>
+      <c r="D322" t="s">
+        <v>12</v>
+      </c>
+      <c r="E322" t="s">
         <v>494</v>
       </c>
-      <c r="C322">
-        <v>1</v>
-      </c>
-      <c r="D322" t="s">
-        <v>2</v>
-      </c>
-      <c r="E322" t="s">
-        <v>324</v>
-      </c>
       <c r="F322" s="1">
-        <v>46148</v>
+        <v>46253</v>
       </c>
       <c r="G322" s="1">
-        <v>46149</v>
+        <v>46253</v>
       </c>
       <c r="H322">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="323" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A323" t="s">
+        <v>0</v>
+      </c>
+      <c r="B323" t="s">
         <v>495</v>
       </c>
-      <c r="B323" t="s">
+      <c r="C323">
+        <v>1</v>
+      </c>
+      <c r="D323" t="s">
+        <v>12</v>
+      </c>
+      <c r="E323" t="s">
         <v>496</v>
       </c>
-      <c r="C323">
-        <v>1</v>
-      </c>
-      <c r="D323" t="s">
-        <v>5</v>
-      </c>
-      <c r="E323" t="s">
-        <v>30</v>
-      </c>
       <c r="F323" s="1">
-        <v>46133</v>
+        <v>46253</v>
       </c>
       <c r="G323" s="1">
-        <v>46134</v>
+        <v>46253</v>
       </c>
       <c r="H323">
         <v>0</v>
@@ -10571,7 +10616,7 @@
     </row>
     <row r="324" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A324" t="s">
-        <v>495</v>
+        <v>0</v>
       </c>
       <c r="B324" t="s">
         <v>497</v>
@@ -10580,16 +10625,16 @@
         <v>1</v>
       </c>
       <c r="D324" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E324" t="s">
-        <v>30</v>
+        <v>498</v>
       </c>
       <c r="F324" s="1">
-        <v>46134</v>
+        <v>46253</v>
       </c>
       <c r="G324" s="1">
-        <v>46134</v>
+        <v>46253</v>
       </c>
       <c r="H324">
         <v>0</v>
@@ -10597,25 +10642,25 @@
     </row>
     <row r="325" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A325" t="s">
-        <v>495</v>
+        <v>0</v>
       </c>
       <c r="B325" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C325">
         <v>1</v>
       </c>
       <c r="D325" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E325" t="s">
-        <v>15</v>
+        <v>500</v>
       </c>
       <c r="F325" s="1">
-        <v>46156</v>
+        <v>46253</v>
       </c>
       <c r="G325" s="1">
-        <v>46156</v>
+        <v>46253</v>
       </c>
       <c r="H325">
         <v>0</v>
@@ -10623,88 +10668,88 @@
     </row>
     <row r="326" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A326" t="s">
-        <v>495</v>
+        <v>0</v>
       </c>
       <c r="B326" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="C326">
         <v>1</v>
       </c>
       <c r="D326" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E326" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="F326" s="1">
-        <v>46195</v>
+        <v>46253</v>
       </c>
       <c r="G326" s="1">
-        <v>46195</v>
+        <v>46253</v>
       </c>
       <c r="H326">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="327" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A327" t="s">
-        <v>495</v>
+        <v>503</v>
       </c>
       <c r="B327" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="C327">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D327" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E327" t="s">
-        <v>502</v>
+        <v>311</v>
       </c>
       <c r="F327" s="1">
-        <v>46206</v>
+        <v>46148</v>
       </c>
       <c r="G327" s="1">
-        <v>46252</v>
+        <v>46149</v>
       </c>
       <c r="H327">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="328" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A328" t="s">
-        <v>495</v>
+        <v>505</v>
       </c>
       <c r="B328" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="C328">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D328" t="s">
-        <v>68</v>
+        <v>5</v>
       </c>
       <c r="E328" t="s">
-        <v>504</v>
+        <v>30</v>
       </c>
       <c r="F328" s="1">
-        <v>46209</v>
+        <v>46133</v>
       </c>
       <c r="G328" s="1">
-        <v>46218</v>
+        <v>46134</v>
       </c>
       <c r="H328">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="329" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A329" t="s">
-        <v>495</v>
+        <v>505</v>
       </c>
       <c r="B329" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="C329">
         <v>1</v>
@@ -10713,13 +10758,13 @@
         <v>5</v>
       </c>
       <c r="E329" t="s">
-        <v>506</v>
+        <v>30</v>
       </c>
       <c r="F329" s="1">
-        <v>46213</v>
+        <v>46134</v>
       </c>
       <c r="G329" s="1">
-        <v>46213</v>
+        <v>46134</v>
       </c>
       <c r="H329">
         <v>0</v>
@@ -10727,169 +10772,169 @@
     </row>
     <row r="330" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A330" t="s">
-        <v>495</v>
+        <v>505</v>
       </c>
       <c r="B330" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C330">
         <v>1</v>
       </c>
       <c r="D330" t="s">
-        <v>68</v>
+        <v>5</v>
       </c>
       <c r="E330" t="s">
-        <v>223</v>
+        <v>15</v>
       </c>
       <c r="F330" s="1">
-        <v>46213</v>
+        <v>46156</v>
       </c>
       <c r="G330" s="1">
-        <v>46216</v>
+        <v>46156</v>
       </c>
       <c r="H330">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="331" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A331" t="s">
-        <v>495</v>
+        <v>505</v>
       </c>
       <c r="B331" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C331">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D331" t="s">
         <v>2</v>
       </c>
       <c r="E331" t="s">
-        <v>96</v>
+        <v>510</v>
       </c>
       <c r="F331" s="1">
-        <v>46220</v>
+        <v>46195</v>
       </c>
       <c r="G331" s="1">
-        <v>46231</v>
+        <v>46195</v>
       </c>
       <c r="H331">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="332" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A332" t="s">
-        <v>495</v>
+        <v>505</v>
       </c>
       <c r="B332" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="C332">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D332" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E332" t="s">
-        <v>500</v>
+        <v>512</v>
       </c>
       <c r="F332" s="1">
-        <v>46223</v>
+        <v>46206</v>
       </c>
       <c r="G332" s="1">
-        <v>46223</v>
+        <v>46252</v>
       </c>
       <c r="H332">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="333" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A333" t="s">
-        <v>495</v>
+        <v>505</v>
       </c>
       <c r="B333" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="C333">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D333" t="s">
         <v>68</v>
       </c>
       <c r="E333" t="s">
-        <v>223</v>
+        <v>514</v>
       </c>
       <c r="F333" s="1">
-        <v>46224</v>
+        <v>46209</v>
       </c>
       <c r="G333" s="1">
-        <v>46224</v>
+        <v>46218</v>
       </c>
       <c r="H333">
-        <v>26</v>
+        <v>1</v>
       </c>
     </row>
     <row r="334" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A334" t="s">
-        <v>495</v>
+        <v>505</v>
       </c>
       <c r="B334" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="C334">
         <v>1</v>
       </c>
       <c r="D334" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E334" t="s">
-        <v>500</v>
+        <v>516</v>
       </c>
       <c r="F334" s="1">
-        <v>46230</v>
+        <v>46213</v>
       </c>
       <c r="G334" s="1">
-        <v>46231</v>
+        <v>46213</v>
       </c>
       <c r="H334">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="335" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A335" t="s">
-        <v>495</v>
+        <v>505</v>
       </c>
       <c r="B335" t="s">
-        <v>512</v>
+        <v>517</v>
       </c>
       <c r="C335">
         <v>1</v>
       </c>
       <c r="D335" t="s">
-        <v>2</v>
+        <v>68</v>
       </c>
       <c r="E335" t="s">
-        <v>96</v>
+        <v>223</v>
       </c>
       <c r="F335" s="1">
-        <v>46232</v>
+        <v>46213</v>
       </c>
       <c r="G335" s="1">
-        <v>46233</v>
+        <v>46216</v>
       </c>
       <c r="H335">
-        <v>126</v>
+        <v>7</v>
       </c>
     </row>
     <row r="336" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A336" t="s">
-        <v>495</v>
+        <v>505</v>
       </c>
       <c r="B336" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="C336">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D336" t="s">
         <v>2</v>
@@ -10898,21 +10943,21 @@
         <v>96</v>
       </c>
       <c r="F336" s="1">
-        <v>46232</v>
+        <v>46220</v>
       </c>
       <c r="G336" s="1">
-        <v>46233</v>
+        <v>46231</v>
       </c>
       <c r="H336">
-        <v>27</v>
+        <v>2</v>
       </c>
     </row>
     <row r="337" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A337" t="s">
-        <v>495</v>
+        <v>505</v>
       </c>
       <c r="B337" t="s">
-        <v>514</v>
+        <v>519</v>
       </c>
       <c r="C337">
         <v>1</v>
@@ -10921,76 +10966,76 @@
         <v>2</v>
       </c>
       <c r="E337" t="s">
-        <v>223</v>
+        <v>510</v>
       </c>
       <c r="F337" s="1">
-        <v>46238</v>
+        <v>46223</v>
       </c>
       <c r="G337" s="1">
-        <v>46239</v>
+        <v>46223</v>
       </c>
       <c r="H337">
-        <v>117</v>
+        <v>7</v>
       </c>
     </row>
     <row r="338" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A338" t="s">
-        <v>495</v>
+        <v>505</v>
       </c>
       <c r="B338" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="C338">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D338" t="s">
-        <v>12</v>
+        <v>68</v>
       </c>
       <c r="E338" t="s">
-        <v>502</v>
+        <v>223</v>
       </c>
       <c r="F338" s="1">
-        <v>46239</v>
+        <v>46224</v>
       </c>
       <c r="G338" s="1">
-        <v>46252</v>
+        <v>46224</v>
       </c>
       <c r="H338">
-        <v>0</v>
+        <v>26</v>
       </c>
     </row>
     <row r="339" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A339" t="s">
-        <v>495</v>
+        <v>505</v>
       </c>
       <c r="B339" t="s">
-        <v>516</v>
+        <v>521</v>
       </c>
       <c r="C339">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D339" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E339" t="s">
-        <v>502</v>
+        <v>510</v>
       </c>
       <c r="F339" s="1">
-        <v>46239</v>
+        <v>46230</v>
       </c>
       <c r="G339" s="1">
-        <v>46252</v>
+        <v>46231</v>
       </c>
       <c r="H339">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="340" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A340" t="s">
-        <v>495</v>
+        <v>505</v>
       </c>
       <c r="B340" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="C340">
         <v>1</v>
@@ -10999,91 +11044,91 @@
         <v>2</v>
       </c>
       <c r="E340" t="s">
-        <v>30</v>
+        <v>96</v>
       </c>
       <c r="F340" s="1">
-        <v>46247</v>
+        <v>46232</v>
       </c>
       <c r="G340" s="1">
-        <v>46252</v>
+        <v>46233</v>
       </c>
       <c r="H340">
-        <v>29</v>
+        <v>126</v>
       </c>
     </row>
     <row r="341" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A341" t="s">
-        <v>495</v>
+        <v>505</v>
       </c>
       <c r="B341" t="s">
-        <v>518</v>
+        <v>523</v>
       </c>
       <c r="C341">
         <v>1</v>
       </c>
       <c r="D341" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E341" t="s">
-        <v>380</v>
+        <v>96</v>
       </c>
       <c r="F341" s="1">
-        <v>46252</v>
+        <v>46232</v>
       </c>
       <c r="G341" s="1">
-        <v>46252</v>
+        <v>46233</v>
       </c>
       <c r="H341">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="342" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A342" t="s">
-        <v>495</v>
+        <v>505</v>
       </c>
       <c r="B342" t="s">
-        <v>519</v>
+        <v>524</v>
       </c>
       <c r="C342">
         <v>1</v>
       </c>
       <c r="D342" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E342" t="s">
-        <v>134</v>
+        <v>223</v>
       </c>
       <c r="F342" s="1">
-        <v>46252</v>
+        <v>46238</v>
       </c>
       <c r="G342" s="1">
-        <v>46252</v>
+        <v>46239</v>
       </c>
       <c r="H342">
-        <v>0</v>
+        <v>117</v>
       </c>
     </row>
     <row r="343" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A343" t="s">
-        <v>495</v>
+        <v>505</v>
       </c>
       <c r="B343" t="s">
-        <v>520</v>
+        <v>525</v>
       </c>
       <c r="C343">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D343" t="s">
         <v>12</v>
       </c>
       <c r="E343" t="s">
-        <v>521</v>
+        <v>512</v>
       </c>
       <c r="F343" s="1">
-        <v>46253</v>
+        <v>46239</v>
       </c>
       <c r="G343" s="1">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="H343">
         <v>0</v>
@@ -11091,181 +11136,181 @@
     </row>
     <row r="344" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A344" t="s">
-        <v>522</v>
+        <v>505</v>
       </c>
       <c r="B344" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="C344">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D344" t="s">
-        <v>68</v>
+        <v>12</v>
       </c>
       <c r="E344" t="s">
-        <v>524</v>
+        <v>512</v>
       </c>
       <c r="F344" s="1">
-        <v>46063</v>
+        <v>46239</v>
       </c>
       <c r="G344" s="1">
-        <v>46064</v>
+        <v>46252</v>
       </c>
       <c r="H344">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="345" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A345" t="s">
-        <v>522</v>
+        <v>505</v>
       </c>
       <c r="B345" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="C345">
         <v>1</v>
       </c>
       <c r="D345" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E345" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="F345" s="1">
-        <v>46113</v>
+        <v>46247</v>
       </c>
       <c r="G345" s="1">
-        <v>46125</v>
+        <v>46252</v>
       </c>
       <c r="H345">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="346" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A346" t="s">
-        <v>522</v>
+        <v>505</v>
       </c>
       <c r="B346" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="C346">
         <v>1</v>
       </c>
       <c r="D346" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E346" t="s">
-        <v>41</v>
+        <v>363</v>
       </c>
       <c r="F346" s="1">
-        <v>46125</v>
+        <v>46252</v>
       </c>
       <c r="G346" s="1">
-        <v>46125</v>
+        <v>46252</v>
       </c>
       <c r="H346">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="347" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A347" t="s">
-        <v>522</v>
+        <v>505</v>
       </c>
       <c r="B347" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="C347">
         <v>1</v>
       </c>
       <c r="D347" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E347" t="s">
-        <v>41</v>
+        <v>134</v>
       </c>
       <c r="F347" s="1">
-        <v>46126</v>
+        <v>46252</v>
       </c>
       <c r="G347" s="1">
-        <v>46126</v>
+        <v>46252</v>
       </c>
       <c r="H347">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="348" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A348" t="s">
-        <v>522</v>
+        <v>505</v>
       </c>
       <c r="B348" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="C348">
         <v>1</v>
       </c>
       <c r="D348" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E348" t="s">
-        <v>41</v>
+        <v>531</v>
       </c>
       <c r="F348" s="1">
-        <v>46126</v>
+        <v>46253</v>
       </c>
       <c r="G348" s="1">
-        <v>46126</v>
+        <v>46253</v>
       </c>
       <c r="H348">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="349" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A349" t="s">
-        <v>522</v>
+        <v>505</v>
       </c>
       <c r="B349" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="C349">
         <v>1</v>
       </c>
       <c r="D349" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E349" t="s">
-        <v>41</v>
+        <v>455</v>
       </c>
       <c r="F349" s="1">
-        <v>46128</v>
+        <v>46253</v>
       </c>
       <c r="G349" s="1">
-        <v>46128</v>
+        <v>46253</v>
       </c>
       <c r="H349">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="350" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A350" t="s">
-        <v>522</v>
+        <v>505</v>
       </c>
       <c r="B350" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="C350">
         <v>1</v>
       </c>
       <c r="D350" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E350" t="s">
-        <v>41</v>
+        <v>534</v>
       </c>
       <c r="F350" s="1">
-        <v>46132</v>
+        <v>46253</v>
       </c>
       <c r="G350" s="1">
-        <v>46132</v>
+        <v>46253</v>
       </c>
       <c r="H350">
         <v>0</v>
@@ -11273,77 +11318,77 @@
     </row>
     <row r="351" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A351" t="s">
-        <v>522</v>
+        <v>505</v>
       </c>
       <c r="B351" t="s">
+        <v>535</v>
+      </c>
+      <c r="C351">
+        <v>1</v>
+      </c>
+      <c r="D351" t="s">
+        <v>12</v>
+      </c>
+      <c r="E351" t="s">
         <v>531</v>
       </c>
-      <c r="C351">
-        <v>1</v>
-      </c>
-      <c r="D351" t="s">
-        <v>2</v>
-      </c>
-      <c r="E351" t="s">
-        <v>41</v>
-      </c>
       <c r="F351" s="1">
-        <v>46161</v>
+        <v>46253</v>
       </c>
       <c r="G351" s="1">
-        <v>46161</v>
+        <v>46253</v>
       </c>
       <c r="H351">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="352" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A352" t="s">
-        <v>522</v>
+        <v>505</v>
       </c>
       <c r="B352" t="s">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="C352">
         <v>1</v>
       </c>
       <c r="D352" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E352" t="s">
-        <v>41</v>
+        <v>141</v>
       </c>
       <c r="F352" s="1">
-        <v>46174</v>
+        <v>46253</v>
       </c>
       <c r="G352" s="1">
-        <v>46174</v>
+        <v>46253</v>
       </c>
       <c r="H352">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="353" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A353" t="s">
-        <v>522</v>
+        <v>537</v>
       </c>
       <c r="B353" t="s">
-        <v>533</v>
+        <v>538</v>
       </c>
       <c r="C353">
         <v>1</v>
       </c>
       <c r="D353" t="s">
-        <v>2</v>
+        <v>68</v>
       </c>
       <c r="E353" t="s">
-        <v>41</v>
+        <v>539</v>
       </c>
       <c r="F353" s="1">
-        <v>46174</v>
+        <v>46063</v>
       </c>
       <c r="G353" s="1">
-        <v>46174</v>
+        <v>46064</v>
       </c>
       <c r="H353">
         <v>1</v>
@@ -11351,25 +11396,25 @@
     </row>
     <row r="354" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A354" t="s">
-        <v>522</v>
+        <v>537</v>
       </c>
       <c r="B354" t="s">
-        <v>534</v>
+        <v>540</v>
       </c>
       <c r="C354">
         <v>1</v>
       </c>
       <c r="D354" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E354" t="s">
         <v>41</v>
       </c>
       <c r="F354" s="1">
-        <v>46195</v>
+        <v>46113</v>
       </c>
       <c r="G354" s="1">
-        <v>46252</v>
+        <v>46125</v>
       </c>
       <c r="H354">
         <v>0</v>
@@ -11377,36 +11422,36 @@
     </row>
     <row r="355" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A355" t="s">
-        <v>522</v>
+        <v>537</v>
       </c>
       <c r="B355" t="s">
-        <v>535</v>
+        <v>541</v>
       </c>
       <c r="C355">
         <v>1</v>
       </c>
       <c r="D355" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E355" t="s">
         <v>41</v>
       </c>
       <c r="F355" s="1">
-        <v>46210</v>
+        <v>46125</v>
       </c>
       <c r="G355" s="1">
-        <v>46210</v>
+        <v>46125</v>
       </c>
       <c r="H355">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="356" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A356" t="s">
-        <v>522</v>
+        <v>537</v>
       </c>
       <c r="B356" t="s">
-        <v>536</v>
+        <v>542</v>
       </c>
       <c r="C356">
         <v>1</v>
@@ -11418,10 +11463,10 @@
         <v>41</v>
       </c>
       <c r="F356" s="1">
-        <v>46213</v>
+        <v>46126</v>
       </c>
       <c r="G356" s="1">
-        <v>46213</v>
+        <v>46126</v>
       </c>
       <c r="H356">
         <v>1</v>
@@ -11429,77 +11474,77 @@
     </row>
     <row r="357" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A357" t="s">
-        <v>522</v>
+        <v>537</v>
       </c>
       <c r="B357" t="s">
-        <v>537</v>
+        <v>543</v>
       </c>
       <c r="C357">
         <v>1</v>
       </c>
       <c r="D357" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E357" t="s">
         <v>41</v>
       </c>
       <c r="F357" s="1">
-        <v>46218</v>
+        <v>46126</v>
       </c>
       <c r="G357" s="1">
-        <v>46252</v>
+        <v>46126</v>
       </c>
       <c r="H357">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="358" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A358" t="s">
-        <v>522</v>
+        <v>537</v>
       </c>
       <c r="B358" t="s">
-        <v>538</v>
+        <v>544</v>
       </c>
       <c r="C358">
         <v>1</v>
       </c>
       <c r="D358" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E358" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="F358" s="1">
-        <v>46226</v>
+        <v>46128</v>
       </c>
       <c r="G358" s="1">
-        <v>46226</v>
+        <v>46128</v>
       </c>
       <c r="H358">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="359" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A359" t="s">
-        <v>522</v>
+        <v>537</v>
       </c>
       <c r="B359" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="C359">
         <v>1</v>
       </c>
       <c r="D359" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E359" t="s">
         <v>41</v>
       </c>
       <c r="F359" s="1">
-        <v>46227</v>
+        <v>46132</v>
       </c>
       <c r="G359" s="1">
-        <v>46252</v>
+        <v>46132</v>
       </c>
       <c r="H359">
         <v>0</v>
@@ -11507,103 +11552,103 @@
     </row>
     <row r="360" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A360" t="s">
-        <v>522</v>
+        <v>537</v>
       </c>
       <c r="B360" t="s">
-        <v>540</v>
+        <v>546</v>
       </c>
       <c r="C360">
         <v>1</v>
       </c>
       <c r="D360" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E360" t="s">
         <v>41</v>
       </c>
       <c r="F360" s="1">
-        <v>46227</v>
+        <v>46161</v>
       </c>
       <c r="G360" s="1">
-        <v>46252</v>
+        <v>46161</v>
       </c>
       <c r="H360">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="361" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A361" t="s">
-        <v>522</v>
+        <v>537</v>
       </c>
       <c r="B361" t="s">
-        <v>541</v>
+        <v>547</v>
       </c>
       <c r="C361">
         <v>1</v>
       </c>
       <c r="D361" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E361" t="s">
         <v>41</v>
       </c>
       <c r="F361" s="1">
-        <v>46227</v>
+        <v>46174</v>
       </c>
       <c r="G361" s="1">
-        <v>46228</v>
+        <v>46174</v>
       </c>
       <c r="H361">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="362" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A362" t="s">
-        <v>522</v>
+        <v>537</v>
       </c>
       <c r="B362" t="s">
-        <v>542</v>
+        <v>548</v>
       </c>
       <c r="C362">
         <v>1</v>
       </c>
       <c r="D362" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E362" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="F362" s="1">
-        <v>46230</v>
+        <v>46174</v>
       </c>
       <c r="G362" s="1">
-        <v>46252</v>
+        <v>46174</v>
       </c>
       <c r="H362">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="363" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A363" t="s">
-        <v>522</v>
+        <v>537</v>
       </c>
       <c r="B363" t="s">
-        <v>543</v>
+        <v>549</v>
       </c>
       <c r="C363">
         <v>1</v>
       </c>
       <c r="D363" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E363" t="s">
         <v>41</v>
       </c>
       <c r="F363" s="1">
-        <v>46231</v>
+        <v>46195</v>
       </c>
       <c r="G363" s="1">
-        <v>46231</v>
+        <v>46252</v>
       </c>
       <c r="H363">
         <v>0</v>
@@ -11611,10 +11656,10 @@
     </row>
     <row r="364" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A364" t="s">
-        <v>522</v>
+        <v>537</v>
       </c>
       <c r="B364" t="s">
-        <v>544</v>
+        <v>550</v>
       </c>
       <c r="C364">
         <v>1</v>
@@ -11626,10 +11671,10 @@
         <v>41</v>
       </c>
       <c r="F364" s="1">
-        <v>46237</v>
+        <v>46210</v>
       </c>
       <c r="G364" s="1">
-        <v>46237</v>
+        <v>46210</v>
       </c>
       <c r="H364">
         <v>0</v>
@@ -11637,36 +11682,36 @@
     </row>
     <row r="365" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A365" t="s">
-        <v>522</v>
+        <v>537</v>
       </c>
       <c r="B365" t="s">
-        <v>545</v>
+        <v>551</v>
       </c>
       <c r="C365">
         <v>1</v>
       </c>
       <c r="D365" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E365" t="s">
         <v>41</v>
       </c>
       <c r="F365" s="1">
-        <v>46253</v>
+        <v>46213</v>
       </c>
       <c r="G365" s="1">
-        <v>46253</v>
+        <v>46213</v>
       </c>
       <c r="H365">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="366" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A366" t="s">
-        <v>522</v>
+        <v>537</v>
       </c>
       <c r="B366" t="s">
-        <v>546</v>
+        <v>552</v>
       </c>
       <c r="C366">
         <v>1</v>
@@ -11678,10 +11723,10 @@
         <v>41</v>
       </c>
       <c r="F366" s="1">
-        <v>46253</v>
+        <v>46218</v>
       </c>
       <c r="G366" s="1">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="H366">
         <v>0</v>
@@ -11689,183 +11734,417 @@
     </row>
     <row r="367" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A367" t="s">
-        <v>547</v>
+        <v>537</v>
       </c>
       <c r="B367" t="s">
-        <v>548</v>
+        <v>553</v>
       </c>
       <c r="C367">
         <v>1</v>
       </c>
       <c r="D367" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E367" t="s">
-        <v>549</v>
+        <v>55</v>
       </c>
       <c r="F367" s="1">
-        <v>46083</v>
+        <v>46226</v>
       </c>
       <c r="G367" s="1">
-        <v>46084</v>
+        <v>46226</v>
       </c>
       <c r="H367">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="368" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A368" t="s">
-        <v>547</v>
+        <v>537</v>
       </c>
       <c r="B368" t="s">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="C368">
         <v>1</v>
       </c>
       <c r="D368" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E368" t="s">
-        <v>549</v>
+        <v>41</v>
       </c>
       <c r="F368" s="1">
-        <v>46132</v>
+        <v>46227</v>
       </c>
       <c r="G368" s="1">
-        <v>46133</v>
+        <v>46252</v>
       </c>
       <c r="H368">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="369" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A369" t="s">
-        <v>547</v>
+        <v>537</v>
       </c>
       <c r="B369" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="C369">
         <v>1</v>
       </c>
       <c r="D369" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E369" t="s">
-        <v>552</v>
+        <v>41</v>
       </c>
       <c r="F369" s="1">
-        <v>46157</v>
+        <v>46227</v>
       </c>
       <c r="G369" s="1">
-        <v>46157</v>
+        <v>46252</v>
       </c>
       <c r="H369">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="370" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A370" t="s">
-        <v>547</v>
+        <v>537</v>
       </c>
       <c r="B370" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="C370">
         <v>1</v>
       </c>
       <c r="D370" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E370" t="s">
-        <v>554</v>
+        <v>41</v>
       </c>
       <c r="F370" s="1">
-        <v>46168</v>
+        <v>46227</v>
       </c>
       <c r="G370" s="1">
-        <v>46170</v>
+        <v>46228</v>
       </c>
       <c r="H370">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="371" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A371" t="s">
-        <v>547</v>
+        <v>537</v>
       </c>
       <c r="B371" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="C371">
         <v>1</v>
       </c>
       <c r="D371" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E371" t="s">
-        <v>552</v>
+        <v>55</v>
       </c>
       <c r="F371" s="1">
-        <v>46244</v>
+        <v>46230</v>
       </c>
       <c r="G371" s="1">
-        <v>46244</v>
+        <v>46252</v>
       </c>
       <c r="H371">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="372" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A372" t="s">
-        <v>547</v>
+        <v>537</v>
       </c>
       <c r="B372" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="C372">
         <v>1</v>
       </c>
       <c r="D372" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E372" t="s">
-        <v>552</v>
+        <v>41</v>
       </c>
       <c r="F372" s="1">
-        <v>46247</v>
+        <v>46231</v>
       </c>
       <c r="G372" s="1">
-        <v>46247</v>
+        <v>46231</v>
       </c>
       <c r="H372">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="373" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A373" t="s">
-        <v>547</v>
+        <v>537</v>
       </c>
       <c r="B373" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="C373">
         <v>1</v>
       </c>
       <c r="D373" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E373" t="s">
-        <v>549</v>
+        <v>41</v>
       </c>
       <c r="F373" s="1">
+        <v>46237</v>
+      </c>
+      <c r="G373" s="1">
+        <v>46237</v>
+      </c>
+      <c r="H373">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="374" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A374" t="s">
+        <v>537</v>
+      </c>
+      <c r="B374" t="s">
+        <v>560</v>
+      </c>
+      <c r="C374">
+        <v>1</v>
+      </c>
+      <c r="D374" t="s">
+        <v>12</v>
+      </c>
+      <c r="E374" t="s">
+        <v>41</v>
+      </c>
+      <c r="F374" s="1">
+        <v>46253</v>
+      </c>
+      <c r="G374" s="1">
+        <v>46253</v>
+      </c>
+      <c r="H374">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="375" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A375" t="s">
+        <v>537</v>
+      </c>
+      <c r="B375" t="s">
+        <v>561</v>
+      </c>
+      <c r="C375">
+        <v>1</v>
+      </c>
+      <c r="D375" t="s">
+        <v>12</v>
+      </c>
+      <c r="E375" t="s">
+        <v>41</v>
+      </c>
+      <c r="F375" s="1">
+        <v>46253</v>
+      </c>
+      <c r="G375" s="1">
+        <v>46253</v>
+      </c>
+      <c r="H375">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="376" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A376" t="s">
+        <v>562</v>
+      </c>
+      <c r="B376" t="s">
+        <v>563</v>
+      </c>
+      <c r="C376">
+        <v>1</v>
+      </c>
+      <c r="D376" t="s">
+        <v>2</v>
+      </c>
+      <c r="E376" t="s">
+        <v>564</v>
+      </c>
+      <c r="F376" s="1">
+        <v>46083</v>
+      </c>
+      <c r="G376" s="1">
+        <v>46084</v>
+      </c>
+      <c r="H376">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="377" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A377" t="s">
+        <v>562</v>
+      </c>
+      <c r="B377" t="s">
+        <v>565</v>
+      </c>
+      <c r="C377">
+        <v>1</v>
+      </c>
+      <c r="D377" t="s">
+        <v>2</v>
+      </c>
+      <c r="E377" t="s">
+        <v>564</v>
+      </c>
+      <c r="F377" s="1">
+        <v>46132</v>
+      </c>
+      <c r="G377" s="1">
+        <v>46133</v>
+      </c>
+      <c r="H377">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="378" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A378" t="s">
+        <v>562</v>
+      </c>
+      <c r="B378" t="s">
+        <v>566</v>
+      </c>
+      <c r="C378">
+        <v>1</v>
+      </c>
+      <c r="D378" t="s">
+        <v>2</v>
+      </c>
+      <c r="E378" t="s">
+        <v>567</v>
+      </c>
+      <c r="F378" s="1">
+        <v>46157</v>
+      </c>
+      <c r="G378" s="1">
+        <v>46157</v>
+      </c>
+      <c r="H378">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="379" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A379" t="s">
+        <v>562</v>
+      </c>
+      <c r="B379" t="s">
+        <v>568</v>
+      </c>
+      <c r="C379">
+        <v>1</v>
+      </c>
+      <c r="D379" t="s">
+        <v>2</v>
+      </c>
+      <c r="E379" t="s">
+        <v>569</v>
+      </c>
+      <c r="F379" s="1">
+        <v>46168</v>
+      </c>
+      <c r="G379" s="1">
+        <v>46170</v>
+      </c>
+      <c r="H379">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="380" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A380" t="s">
+        <v>562</v>
+      </c>
+      <c r="B380" t="s">
+        <v>570</v>
+      </c>
+      <c r="C380">
+        <v>1</v>
+      </c>
+      <c r="D380" t="s">
+        <v>2</v>
+      </c>
+      <c r="E380" t="s">
+        <v>567</v>
+      </c>
+      <c r="F380" s="1">
+        <v>46244</v>
+      </c>
+      <c r="G380" s="1">
+        <v>46244</v>
+      </c>
+      <c r="H380">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="381" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A381" t="s">
+        <v>562</v>
+      </c>
+      <c r="B381" t="s">
+        <v>571</v>
+      </c>
+      <c r="C381">
+        <v>1</v>
+      </c>
+      <c r="D381" t="s">
+        <v>2</v>
+      </c>
+      <c r="E381" t="s">
+        <v>567</v>
+      </c>
+      <c r="F381" s="1">
         <v>46247</v>
       </c>
-      <c r="G373" s="1">
+      <c r="G381" s="1">
         <v>46247</v>
       </c>
-      <c r="H373">
+      <c r="H381">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="382" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A382" t="s">
+        <v>562</v>
+      </c>
+      <c r="B382" t="s">
+        <v>572</v>
+      </c>
+      <c r="C382">
+        <v>1</v>
+      </c>
+      <c r="D382" t="s">
+        <v>2</v>
+      </c>
+      <c r="E382" t="s">
+        <v>564</v>
+      </c>
+      <c r="F382" s="1">
+        <v>46247</v>
+      </c>
+      <c r="G382" s="1">
+        <v>46247</v>
+      </c>
+      <c r="H382">
         <v>1</v>
       </c>
     </row>

--- a/Data_ERP/Pedidos Transmicion.xlsx
+++ b/Data_ERP/Pedidos Transmicion.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sistema_Logistico_Peirano\Data_ERP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{63925FA5-77F6-4EDC-B62F-C3F5DF83502A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B4EFB909-474F-4E10-BB73-C318614B7764}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="26160" yWindow="3420" windowWidth="15375" windowHeight="8325" xr2:uid="{77D8270B-20F4-4867-BB0B-AD0F6A92E940}"/>
+    <workbookView xWindow="26505" yWindow="3765" windowWidth="15375" windowHeight="8325" xr2:uid="{21F14381-FDC1-4C09-82D0-525EE40A7AFB}"/>
   </bookViews>
   <sheets>
     <sheet name="transmicion" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1532" uniqueCount="581">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1656" uniqueCount="619">
   <si>
     <t>0001</t>
   </si>
@@ -1192,6 +1192,9 @@
     <t>SUPERFICIES S.R.L.</t>
   </si>
   <si>
+    <t xml:space="preserve">  213937</t>
+  </si>
+  <si>
     <t xml:space="preserve">  213938</t>
   </si>
   <si>
@@ -1246,6 +1249,9 @@
     <t>SANITARIOS AXANTRA S.R.L.</t>
   </si>
   <si>
+    <t xml:space="preserve">  213958</t>
+  </si>
+  <si>
     <t xml:space="preserve">  213959</t>
   </si>
   <si>
@@ -1306,9 +1312,18 @@
     <t>PRIATEL PISOS S.R.L.</t>
   </si>
   <si>
+    <t xml:space="preserve">  213978</t>
+  </si>
+  <si>
     <t xml:space="preserve">  213979</t>
   </si>
   <si>
+    <t xml:space="preserve">  213980</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213981</t>
+  </si>
+  <si>
     <t xml:space="preserve">  213982</t>
   </si>
   <si>
@@ -1321,6 +1336,12 @@
     <t>EL CAÑADON  S.R.L.</t>
   </si>
   <si>
+    <t xml:space="preserve">  213985</t>
+  </si>
+  <si>
+    <t>BALCARCE 54 S.A.</t>
+  </si>
+  <si>
     <t xml:space="preserve">  213987</t>
   </si>
   <si>
@@ -1444,6 +1465,9 @@
     <t xml:space="preserve">  214021</t>
   </si>
   <si>
+    <t xml:space="preserve">  214022</t>
+  </si>
+  <si>
     <t xml:space="preserve">  214023</t>
   </si>
   <si>
@@ -1528,7 +1552,94 @@
     <t xml:space="preserve">  214044</t>
   </si>
   <si>
-    <t>BALCARCE 54 S.A.</t>
+    <t xml:space="preserve">  214046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214050</t>
+  </si>
+  <si>
+    <t>DELIACY S.R.L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214053</t>
+  </si>
+  <si>
+    <t>IMPORTADORA COMERCIAL FUEGUINA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214055</t>
+  </si>
+  <si>
+    <t>V.S.MATERIALES DE J.C.MOREIRA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214060</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214061</t>
+  </si>
+  <si>
+    <t>FERRETERIA CHEMES HNOS S.R.L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214062</t>
+  </si>
+  <si>
+    <t>HIPERCAÑO S.A.S.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214066</t>
+  </si>
+  <si>
+    <t>DI GREGORIO CESAR ALEJANDRO - MATTONELLA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214067</t>
+  </si>
+  <si>
+    <t>MARGARITA GUSTAVO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214068</t>
+  </si>
+  <si>
+    <t>GUIDOLI FLORIO S.R.L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214070</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214072</t>
   </si>
   <si>
     <t>0004</t>
@@ -1618,21 +1729,18 @@
     <t>PITA EPPER NICOLAS</t>
   </si>
   <si>
+    <t xml:space="preserve">    2818</t>
+  </si>
+  <si>
     <t xml:space="preserve">    2819</t>
   </si>
   <si>
-    <t xml:space="preserve">    2820</t>
-  </si>
-  <si>
-    <t>VARIOS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    2821</t>
-  </si>
-  <si>
     <t xml:space="preserve">    2822</t>
   </si>
   <si>
+    <t xml:space="preserve">    2823</t>
+  </si>
+  <si>
     <t>4444</t>
   </si>
   <si>
@@ -1702,10 +1810,16 @@
     <t xml:space="preserve">    2074</t>
   </si>
   <si>
-    <t xml:space="preserve">    2227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    2230</t>
+    <t xml:space="preserve">    2237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    2238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    2240</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    2241</t>
   </si>
   <si>
     <t>9999</t>
@@ -2212,34 +2326,34 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AEC88125-5589-4C47-BA6D-41E117CE4BE9}">
-  <dimension ref="A1:H382"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD0089AF-CB57-41EE-88AE-69B2B29B9461}">
+  <dimension ref="A1:H413"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
-        <v>573</v>
+        <v>611</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>574</v>
+        <v>612</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>575</v>
+        <v>613</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>576</v>
+        <v>614</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>577</v>
+        <v>615</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>578</v>
+        <v>616</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>579</v>
+        <v>617</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>580</v>
+        <v>618</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
@@ -3319,7 +3433,7 @@
         <v>2</v>
       </c>
       <c r="D43" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E43" t="s">
         <v>79</v>
@@ -3331,7 +3445,7 @@
         <v>46252</v>
       </c>
       <c r="H43">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.2">
@@ -4411,7 +4525,7 @@
         <v>2</v>
       </c>
       <c r="D85" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E85" t="s">
         <v>153</v>
@@ -4423,7 +4537,7 @@
         <v>46252</v>
       </c>
       <c r="H85">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.2">
@@ -5867,7 +5981,7 @@
         <v>1</v>
       </c>
       <c r="D141" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E141" t="s">
         <v>234</v>
@@ -5879,7 +5993,7 @@
         <v>46252</v>
       </c>
       <c r="H141">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.2">
@@ -6257,7 +6371,7 @@
         <v>1</v>
       </c>
       <c r="D156" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E156" t="s">
         <v>255</v>
@@ -6269,7 +6383,7 @@
         <v>46252</v>
       </c>
       <c r="H156">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.2">
@@ -6647,7 +6761,7 @@
         <v>1</v>
       </c>
       <c r="D171" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E171" t="s">
         <v>132</v>
@@ -6659,7 +6773,7 @@
         <v>46252</v>
       </c>
       <c r="H171">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.2">
@@ -6673,7 +6787,7 @@
         <v>1</v>
       </c>
       <c r="D172" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E172" t="s">
         <v>223</v>
@@ -6685,7 +6799,7 @@
         <v>46252</v>
       </c>
       <c r="H172">
-        <v>0</v>
+        <v>42</v>
       </c>
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.2">
@@ -6725,7 +6839,7 @@
         <v>1</v>
       </c>
       <c r="D174" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E174" t="s">
         <v>276</v>
@@ -6737,7 +6851,7 @@
         <v>46252</v>
       </c>
       <c r="H174">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="175" spans="1:8" x14ac:dyDescent="0.2">
@@ -6907,7 +7021,7 @@
         <v>1</v>
       </c>
       <c r="D181" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E181" t="s">
         <v>13</v>
@@ -6919,7 +7033,7 @@
         <v>46252</v>
       </c>
       <c r="H181">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="182" spans="1:8" x14ac:dyDescent="0.2">
@@ -6933,7 +7047,7 @@
         <v>1</v>
       </c>
       <c r="D182" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E182" t="s">
         <v>13</v>
@@ -6945,7 +7059,7 @@
         <v>46252</v>
       </c>
       <c r="H182">
-        <v>0</v>
+        <v>42</v>
       </c>
     </row>
     <row r="183" spans="1:8" x14ac:dyDescent="0.2">
@@ -6959,7 +7073,7 @@
         <v>1</v>
       </c>
       <c r="D183" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E183" t="s">
         <v>290</v>
@@ -6971,7 +7085,7 @@
         <v>46252</v>
       </c>
       <c r="H183">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="184" spans="1:8" x14ac:dyDescent="0.2">
@@ -6985,7 +7099,7 @@
         <v>1</v>
       </c>
       <c r="D184" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E184" t="s">
         <v>292</v>
@@ -6997,7 +7111,7 @@
         <v>46252</v>
       </c>
       <c r="H184">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="185" spans="1:8" x14ac:dyDescent="0.2">
@@ -7063,7 +7177,7 @@
         <v>1</v>
       </c>
       <c r="D187" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E187" t="s">
         <v>296</v>
@@ -7075,7 +7189,7 @@
         <v>46252</v>
       </c>
       <c r="H187">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="188" spans="1:8" x14ac:dyDescent="0.2">
@@ -7193,7 +7307,7 @@
         <v>1</v>
       </c>
       <c r="D192" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E192" t="s">
         <v>303</v>
@@ -7205,7 +7319,7 @@
         <v>46252</v>
       </c>
       <c r="H192">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="193" spans="1:8" x14ac:dyDescent="0.2">
@@ -7245,7 +7359,7 @@
         <v>1</v>
       </c>
       <c r="D194" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E194" t="s">
         <v>35</v>
@@ -7257,7 +7371,7 @@
         <v>46252</v>
       </c>
       <c r="H194">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="195" spans="1:8" x14ac:dyDescent="0.2">
@@ -7271,7 +7385,7 @@
         <v>1</v>
       </c>
       <c r="D195" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E195" t="s">
         <v>35</v>
@@ -7283,7 +7397,7 @@
         <v>46252</v>
       </c>
       <c r="H195">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="196" spans="1:8" x14ac:dyDescent="0.2">
@@ -7297,7 +7411,7 @@
         <v>1</v>
       </c>
       <c r="D196" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E196" t="s">
         <v>309</v>
@@ -7309,7 +7423,7 @@
         <v>46252</v>
       </c>
       <c r="H196">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="197" spans="1:8" x14ac:dyDescent="0.2">
@@ -7323,7 +7437,7 @@
         <v>1</v>
       </c>
       <c r="D197" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E197" t="s">
         <v>311</v>
@@ -7335,7 +7449,7 @@
         <v>46252</v>
       </c>
       <c r="H197">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="198" spans="1:8" x14ac:dyDescent="0.2">
@@ -7401,7 +7515,7 @@
         <v>1</v>
       </c>
       <c r="D200" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E200" t="s">
         <v>117</v>
@@ -7413,7 +7527,7 @@
         <v>46252</v>
       </c>
       <c r="H200">
-        <v>0</v>
+        <v>136</v>
       </c>
     </row>
     <row r="201" spans="1:8" x14ac:dyDescent="0.2">
@@ -7505,7 +7619,7 @@
         <v>1</v>
       </c>
       <c r="D204" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E204" t="s">
         <v>157</v>
@@ -7517,7 +7631,7 @@
         <v>46252</v>
       </c>
       <c r="H204">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="205" spans="1:8" x14ac:dyDescent="0.2">
@@ -7531,7 +7645,7 @@
         <v>1</v>
       </c>
       <c r="D205" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E205" t="s">
         <v>323</v>
@@ -7543,7 +7657,7 @@
         <v>46252</v>
       </c>
       <c r="H205">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="206" spans="1:8" x14ac:dyDescent="0.2">
@@ -7557,7 +7671,7 @@
         <v>1</v>
       </c>
       <c r="D206" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E206" t="s">
         <v>296</v>
@@ -7569,7 +7683,7 @@
         <v>46252</v>
       </c>
       <c r="H206">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="207" spans="1:8" x14ac:dyDescent="0.2">
@@ -7635,7 +7749,7 @@
         <v>1</v>
       </c>
       <c r="D209" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E209" t="s">
         <v>79</v>
@@ -7647,7 +7761,7 @@
         <v>46252</v>
       </c>
       <c r="H209">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="210" spans="1:8" x14ac:dyDescent="0.2">
@@ -7661,7 +7775,7 @@
         <v>1</v>
       </c>
       <c r="D210" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E210" t="s">
         <v>331</v>
@@ -7673,7 +7787,7 @@
         <v>46252</v>
       </c>
       <c r="H210">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="211" spans="1:8" x14ac:dyDescent="0.2">
@@ -7687,7 +7801,7 @@
         <v>1</v>
       </c>
       <c r="D211" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E211" t="s">
         <v>333</v>
@@ -7699,7 +7813,7 @@
         <v>46252</v>
       </c>
       <c r="H211">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="212" spans="1:8" x14ac:dyDescent="0.2">
@@ -7817,7 +7931,7 @@
         <v>1</v>
       </c>
       <c r="D216" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E216" t="s">
         <v>342</v>
@@ -7829,7 +7943,7 @@
         <v>46252</v>
       </c>
       <c r="H216">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="217" spans="1:8" x14ac:dyDescent="0.2">
@@ -7843,7 +7957,7 @@
         <v>1</v>
       </c>
       <c r="D217" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E217" t="s">
         <v>344</v>
@@ -7855,7 +7969,7 @@
         <v>46252</v>
       </c>
       <c r="H217">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="218" spans="1:8" x14ac:dyDescent="0.2">
@@ -7869,7 +7983,7 @@
         <v>1</v>
       </c>
       <c r="D218" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E218" t="s">
         <v>346</v>
@@ -7881,7 +7995,7 @@
         <v>46252</v>
       </c>
       <c r="H218">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="219" spans="1:8" x14ac:dyDescent="0.2">
@@ -7895,7 +8009,7 @@
         <v>1</v>
       </c>
       <c r="D219" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E219" t="s">
         <v>348</v>
@@ -7907,7 +8021,7 @@
         <v>46252</v>
       </c>
       <c r="H219">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="220" spans="1:8" x14ac:dyDescent="0.2">
@@ -7921,7 +8035,7 @@
         <v>1</v>
       </c>
       <c r="D220" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E220" t="s">
         <v>350</v>
@@ -7933,7 +8047,7 @@
         <v>46252</v>
       </c>
       <c r="H220">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="221" spans="1:8" x14ac:dyDescent="0.2">
@@ -7947,7 +8061,7 @@
         <v>1</v>
       </c>
       <c r="D221" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E221" t="s">
         <v>352</v>
@@ -7959,7 +8073,7 @@
         <v>46252</v>
       </c>
       <c r="H221">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="222" spans="1:8" x14ac:dyDescent="0.2">
@@ -8025,7 +8139,7 @@
         <v>1</v>
       </c>
       <c r="D224" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E224" t="s">
         <v>358</v>
@@ -8037,7 +8151,7 @@
         <v>46252</v>
       </c>
       <c r="H224">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="225" spans="1:8" x14ac:dyDescent="0.2">
@@ -8051,7 +8165,7 @@
         <v>1</v>
       </c>
       <c r="D225" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E225" t="s">
         <v>360</v>
@@ -8063,7 +8177,7 @@
         <v>46252</v>
       </c>
       <c r="H225">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="226" spans="1:8" x14ac:dyDescent="0.2">
@@ -8077,7 +8191,7 @@
         <v>1</v>
       </c>
       <c r="D226" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E226" t="s">
         <v>13</v>
@@ -8089,7 +8203,7 @@
         <v>46252</v>
       </c>
       <c r="H226">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="227" spans="1:8" x14ac:dyDescent="0.2">
@@ -8233,7 +8347,7 @@
         <v>1</v>
       </c>
       <c r="D232" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E232" t="s">
         <v>33</v>
@@ -8245,7 +8359,7 @@
         <v>46252</v>
       </c>
       <c r="H232">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="233" spans="1:8" x14ac:dyDescent="0.2">
@@ -8259,7 +8373,7 @@
         <v>1</v>
       </c>
       <c r="D233" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E233" t="s">
         <v>240</v>
@@ -8271,7 +8385,7 @@
         <v>46252</v>
       </c>
       <c r="H233">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="234" spans="1:8" x14ac:dyDescent="0.2">
@@ -8285,7 +8399,7 @@
         <v>1</v>
       </c>
       <c r="D234" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E234" t="s">
         <v>373</v>
@@ -8297,7 +8411,7 @@
         <v>46252</v>
       </c>
       <c r="H234">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="235" spans="1:8" x14ac:dyDescent="0.2">
@@ -8363,7 +8477,7 @@
         <v>1</v>
       </c>
       <c r="D237" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E237" t="s">
         <v>13</v>
@@ -8375,7 +8489,7 @@
         <v>46252</v>
       </c>
       <c r="H237">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="238" spans="1:8" x14ac:dyDescent="0.2">
@@ -8389,7 +8503,7 @@
         <v>1</v>
       </c>
       <c r="D238" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E238" t="s">
         <v>13</v>
@@ -8401,7 +8515,7 @@
         <v>46252</v>
       </c>
       <c r="H238">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="239" spans="1:8" x14ac:dyDescent="0.2">
@@ -8415,7 +8529,7 @@
         <v>1</v>
       </c>
       <c r="D239" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E239" t="s">
         <v>13</v>
@@ -8427,7 +8541,7 @@
         <v>46252</v>
       </c>
       <c r="H239">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="240" spans="1:8" x14ac:dyDescent="0.2">
@@ -8441,7 +8555,7 @@
         <v>1</v>
       </c>
       <c r="D240" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E240" t="s">
         <v>13</v>
@@ -8453,7 +8567,7 @@
         <v>46252</v>
       </c>
       <c r="H240">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="241" spans="1:8" x14ac:dyDescent="0.2">
@@ -8493,7 +8607,7 @@
         <v>1</v>
       </c>
       <c r="D242" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E242" t="s">
         <v>382</v>
@@ -8505,7 +8619,7 @@
         <v>46252</v>
       </c>
       <c r="H242">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="243" spans="1:8" x14ac:dyDescent="0.2">
@@ -8623,7 +8737,7 @@
         <v>1</v>
       </c>
       <c r="D247" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E247" t="s">
         <v>389</v>
@@ -8635,7 +8749,7 @@
         <v>46252</v>
       </c>
       <c r="H247">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="248" spans="1:8" x14ac:dyDescent="0.2">
@@ -8649,19 +8763,19 @@
         <v>1</v>
       </c>
       <c r="D248" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E248" t="s">
-        <v>176</v>
+        <v>163</v>
       </c>
       <c r="F248" s="1">
         <v>46252</v>
       </c>
       <c r="G248" s="1">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="H248">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="249" spans="1:8" x14ac:dyDescent="0.2">
@@ -8675,19 +8789,19 @@
         <v>1</v>
       </c>
       <c r="D249" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E249" t="s">
-        <v>392</v>
+        <v>176</v>
       </c>
       <c r="F249" s="1">
         <v>46252</v>
       </c>
       <c r="G249" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="H249">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="250" spans="1:8" x14ac:dyDescent="0.2">
@@ -8695,17 +8809,17 @@
         <v>0</v>
       </c>
       <c r="B250" t="s">
+        <v>392</v>
+      </c>
+      <c r="C250">
+        <v>1</v>
+      </c>
+      <c r="D250" t="s">
+        <v>2</v>
+      </c>
+      <c r="E250" t="s">
         <v>393</v>
       </c>
-      <c r="C250">
-        <v>1</v>
-      </c>
-      <c r="D250" t="s">
-        <v>12</v>
-      </c>
-      <c r="E250" t="s">
-        <v>178</v>
-      </c>
       <c r="F250" s="1">
         <v>46252</v>
       </c>
@@ -8713,7 +8827,7 @@
         <v>46252</v>
       </c>
       <c r="H250">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="251" spans="1:8" x14ac:dyDescent="0.2">
@@ -8730,7 +8844,7 @@
         <v>2</v>
       </c>
       <c r="E251" t="s">
-        <v>15</v>
+        <v>178</v>
       </c>
       <c r="F251" s="1">
         <v>46252</v>
@@ -8739,7 +8853,7 @@
         <v>46252</v>
       </c>
       <c r="H251">
-        <v>4</v>
+        <v>21</v>
       </c>
     </row>
     <row r="252" spans="1:8" x14ac:dyDescent="0.2">
@@ -8753,10 +8867,10 @@
         <v>1</v>
       </c>
       <c r="D252" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E252" t="s">
-        <v>396</v>
+        <v>15</v>
       </c>
       <c r="F252" s="1">
         <v>46252</v>
@@ -8765,7 +8879,7 @@
         <v>46252</v>
       </c>
       <c r="H252">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="253" spans="1:8" x14ac:dyDescent="0.2">
@@ -8773,16 +8887,16 @@
         <v>0</v>
       </c>
       <c r="B253" t="s">
+        <v>396</v>
+      </c>
+      <c r="C253">
+        <v>1</v>
+      </c>
+      <c r="D253" t="s">
+        <v>12</v>
+      </c>
+      <c r="E253" t="s">
         <v>397</v>
-      </c>
-      <c r="C253">
-        <v>1</v>
-      </c>
-      <c r="D253" t="s">
-        <v>12</v>
-      </c>
-      <c r="E253" t="s">
-        <v>134</v>
       </c>
       <c r="F253" s="1">
         <v>46252</v>
@@ -8834,7 +8948,7 @@
         <v>12</v>
       </c>
       <c r="E255" t="s">
-        <v>400</v>
+        <v>134</v>
       </c>
       <c r="F255" s="1">
         <v>46252</v>
@@ -8851,25 +8965,25 @@
         <v>0</v>
       </c>
       <c r="B256" t="s">
+        <v>400</v>
+      </c>
+      <c r="C256">
+        <v>1</v>
+      </c>
+      <c r="D256" t="s">
+        <v>2</v>
+      </c>
+      <c r="E256" t="s">
         <v>401</v>
       </c>
-      <c r="C256">
-        <v>1</v>
-      </c>
-      <c r="D256" t="s">
-        <v>12</v>
-      </c>
-      <c r="E256" t="s">
-        <v>402</v>
-      </c>
       <c r="F256" s="1">
         <v>46252</v>
       </c>
       <c r="G256" s="1">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="H256">
-        <v>0</v>
+        <v>24</v>
       </c>
     </row>
     <row r="257" spans="1:8" x14ac:dyDescent="0.2">
@@ -8877,16 +8991,16 @@
         <v>0</v>
       </c>
       <c r="B257" t="s">
+        <v>402</v>
+      </c>
+      <c r="C257">
+        <v>1</v>
+      </c>
+      <c r="D257" t="s">
+        <v>12</v>
+      </c>
+      <c r="E257" t="s">
         <v>403</v>
-      </c>
-      <c r="C257">
-        <v>1</v>
-      </c>
-      <c r="D257" t="s">
-        <v>12</v>
-      </c>
-      <c r="E257" t="s">
-        <v>404</v>
       </c>
       <c r="F257" s="1">
         <v>46252</v>
@@ -8903,25 +9017,25 @@
         <v>0</v>
       </c>
       <c r="B258" t="s">
+        <v>404</v>
+      </c>
+      <c r="C258">
+        <v>1</v>
+      </c>
+      <c r="D258" t="s">
+        <v>2</v>
+      </c>
+      <c r="E258" t="s">
         <v>405</v>
       </c>
-      <c r="C258">
-        <v>1</v>
-      </c>
-      <c r="D258" t="s">
-        <v>12</v>
-      </c>
-      <c r="E258" t="s">
-        <v>296</v>
-      </c>
       <c r="F258" s="1">
         <v>46252</v>
       </c>
       <c r="G258" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="H258">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="259" spans="1:8" x14ac:dyDescent="0.2">
@@ -8938,16 +9052,16 @@
         <v>2</v>
       </c>
       <c r="E259" t="s">
-        <v>407</v>
+        <v>296</v>
       </c>
       <c r="F259" s="1">
         <v>46252</v>
       </c>
       <c r="G259" s="1">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="H259">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="260" spans="1:8" x14ac:dyDescent="0.2">
@@ -8955,25 +9069,25 @@
         <v>0</v>
       </c>
       <c r="B260" t="s">
+        <v>407</v>
+      </c>
+      <c r="C260">
+        <v>1</v>
+      </c>
+      <c r="D260" t="s">
+        <v>2</v>
+      </c>
+      <c r="E260" t="s">
         <v>408</v>
       </c>
-      <c r="C260">
-        <v>1</v>
-      </c>
-      <c r="D260" t="s">
-        <v>12</v>
-      </c>
-      <c r="E260" t="s">
-        <v>335</v>
-      </c>
       <c r="F260" s="1">
         <v>46252</v>
       </c>
       <c r="G260" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="H260">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="261" spans="1:8" x14ac:dyDescent="0.2">
@@ -8990,13 +9104,13 @@
         <v>12</v>
       </c>
       <c r="E261" t="s">
-        <v>410</v>
+        <v>255</v>
       </c>
       <c r="F261" s="1">
         <v>46252</v>
       </c>
       <c r="G261" s="1">
-        <v>46252</v>
+        <v>46254</v>
       </c>
       <c r="H261">
         <v>0</v>
@@ -9007,16 +9121,16 @@
         <v>0</v>
       </c>
       <c r="B262" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C262">
         <v>1</v>
       </c>
       <c r="D262" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E262" t="s">
-        <v>412</v>
+        <v>335</v>
       </c>
       <c r="F262" s="1">
         <v>46252</v>
@@ -9025,7 +9139,7 @@
         <v>46252</v>
       </c>
       <c r="H262">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="263" spans="1:8" x14ac:dyDescent="0.2">
@@ -9033,13 +9147,13 @@
         <v>0</v>
       </c>
       <c r="B263" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C263">
         <v>1</v>
       </c>
       <c r="D263" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E263" t="s">
         <v>412</v>
@@ -9051,7 +9165,7 @@
         <v>46252</v>
       </c>
       <c r="H263">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="264" spans="1:8" x14ac:dyDescent="0.2">
@@ -9059,25 +9173,25 @@
         <v>0</v>
       </c>
       <c r="B264" t="s">
+        <v>413</v>
+      </c>
+      <c r="C264">
+        <v>1</v>
+      </c>
+      <c r="D264" t="s">
+        <v>2</v>
+      </c>
+      <c r="E264" t="s">
         <v>414</v>
       </c>
-      <c r="C264">
-        <v>1</v>
-      </c>
-      <c r="D264" t="s">
-        <v>12</v>
-      </c>
-      <c r="E264" t="s">
-        <v>412</v>
-      </c>
       <c r="F264" s="1">
         <v>46252</v>
       </c>
       <c r="G264" s="1">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="H264">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="265" spans="1:8" x14ac:dyDescent="0.2">
@@ -9091,10 +9205,10 @@
         <v>1</v>
       </c>
       <c r="D265" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E265" t="s">
-        <v>192</v>
+        <v>414</v>
       </c>
       <c r="F265" s="1">
         <v>46252</v>
@@ -9103,7 +9217,7 @@
         <v>46252</v>
       </c>
       <c r="H265">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="266" spans="1:8" x14ac:dyDescent="0.2">
@@ -9120,13 +9234,13 @@
         <v>12</v>
       </c>
       <c r="E266" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="F266" s="1">
         <v>46252</v>
       </c>
       <c r="G266" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="H266">
         <v>0</v>
@@ -9143,10 +9257,10 @@
         <v>1</v>
       </c>
       <c r="D267" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E267" t="s">
-        <v>412</v>
+        <v>192</v>
       </c>
       <c r="F267" s="1">
         <v>46252</v>
@@ -9155,7 +9269,7 @@
         <v>46252</v>
       </c>
       <c r="H267">
-        <v>0</v>
+        <v>26</v>
       </c>
     </row>
     <row r="268" spans="1:8" x14ac:dyDescent="0.2">
@@ -9169,10 +9283,10 @@
         <v>1</v>
       </c>
       <c r="D268" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E268" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="F268" s="1">
         <v>46252</v>
@@ -9181,7 +9295,7 @@
         <v>46252</v>
       </c>
       <c r="H268">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="269" spans="1:8" x14ac:dyDescent="0.2">
@@ -9195,19 +9309,19 @@
         <v>1</v>
       </c>
       <c r="D269" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E269" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="F269" s="1">
         <v>46252</v>
       </c>
       <c r="G269" s="1">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="H269">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="270" spans="1:8" x14ac:dyDescent="0.2">
@@ -9215,25 +9329,25 @@
         <v>0</v>
       </c>
       <c r="B270" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C270">
         <v>1</v>
       </c>
       <c r="D270" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E270" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="F270" s="1">
         <v>46252</v>
       </c>
       <c r="G270" s="1">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="H270">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="271" spans="1:8" x14ac:dyDescent="0.2">
@@ -9241,16 +9355,16 @@
         <v>0</v>
       </c>
       <c r="B271" t="s">
+        <v>421</v>
+      </c>
+      <c r="C271">
+        <v>1</v>
+      </c>
+      <c r="D271" t="s">
+        <v>12</v>
+      </c>
+      <c r="E271" t="s">
         <v>422</v>
-      </c>
-      <c r="C271">
-        <v>1</v>
-      </c>
-      <c r="D271" t="s">
-        <v>12</v>
-      </c>
-      <c r="E271" t="s">
-        <v>423</v>
       </c>
       <c r="F271" s="1">
         <v>46252</v>
@@ -9267,7 +9381,7 @@
         <v>0</v>
       </c>
       <c r="B272" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C272">
         <v>1</v>
@@ -9276,7 +9390,7 @@
         <v>12</v>
       </c>
       <c r="E272" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="F272" s="1">
         <v>46252</v>
@@ -9293,16 +9407,16 @@
         <v>0</v>
       </c>
       <c r="B273" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="C273">
         <v>1</v>
       </c>
       <c r="D273" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E273" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="F273" s="1">
         <v>46252</v>
@@ -9311,7 +9425,7 @@
         <v>46253</v>
       </c>
       <c r="H273">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="274" spans="1:8" x14ac:dyDescent="0.2">
@@ -9319,16 +9433,16 @@
         <v>0</v>
       </c>
       <c r="B274" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="C274">
         <v>1</v>
       </c>
       <c r="D274" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E274" t="s">
-        <v>219</v>
+        <v>427</v>
       </c>
       <c r="F274" s="1">
         <v>46252</v>
@@ -9337,7 +9451,7 @@
         <v>46253</v>
       </c>
       <c r="H274">
-        <v>0</v>
+        <v>33</v>
       </c>
     </row>
     <row r="275" spans="1:8" x14ac:dyDescent="0.2">
@@ -9345,19 +9459,19 @@
         <v>0</v>
       </c>
       <c r="B275" t="s">
+        <v>428</v>
+      </c>
+      <c r="C275">
+        <v>1</v>
+      </c>
+      <c r="D275" t="s">
+        <v>12</v>
+      </c>
+      <c r="E275" t="s">
         <v>429</v>
       </c>
-      <c r="C275">
-        <v>1</v>
-      </c>
-      <c r="D275" t="s">
-        <v>12</v>
-      </c>
-      <c r="E275" t="s">
-        <v>167</v>
-      </c>
       <c r="F275" s="1">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="G275" s="1">
         <v>46253</v>
@@ -9380,13 +9494,13 @@
         <v>12</v>
       </c>
       <c r="E276" t="s">
-        <v>167</v>
+        <v>219</v>
       </c>
       <c r="F276" s="1">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="G276" s="1">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="H276">
         <v>0</v>
@@ -9406,10 +9520,10 @@
         <v>12</v>
       </c>
       <c r="E277" t="s">
-        <v>432</v>
+        <v>219</v>
       </c>
       <c r="F277" s="1">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="G277" s="1">
         <v>46253</v>
@@ -9423,7 +9537,7 @@
         <v>0</v>
       </c>
       <c r="B278" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C278">
         <v>1</v>
@@ -9432,13 +9546,13 @@
         <v>12</v>
       </c>
       <c r="E278" t="s">
-        <v>434</v>
+        <v>136</v>
       </c>
       <c r="F278" s="1">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="G278" s="1">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="H278">
         <v>0</v>
@@ -9449,22 +9563,22 @@
         <v>0</v>
       </c>
       <c r="B279" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="C279">
         <v>1</v>
       </c>
       <c r="D279" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E279" t="s">
-        <v>436</v>
+        <v>136</v>
       </c>
       <c r="F279" s="1">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="G279" s="1">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="H279">
         <v>0</v>
@@ -9475,7 +9589,7 @@
         <v>0</v>
       </c>
       <c r="B280" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="C280">
         <v>1</v>
@@ -9484,7 +9598,7 @@
         <v>12</v>
       </c>
       <c r="E280" t="s">
-        <v>27</v>
+        <v>167</v>
       </c>
       <c r="F280" s="1">
         <v>46253</v>
@@ -9501,7 +9615,7 @@
         <v>0</v>
       </c>
       <c r="B281" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="C281">
         <v>1</v>
@@ -9510,7 +9624,7 @@
         <v>12</v>
       </c>
       <c r="E281" t="s">
-        <v>27</v>
+        <v>167</v>
       </c>
       <c r="F281" s="1">
         <v>46253</v>
@@ -9527,7 +9641,7 @@
         <v>0</v>
       </c>
       <c r="B282" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C282">
         <v>1</v>
@@ -9536,7 +9650,7 @@
         <v>12</v>
       </c>
       <c r="E282" t="s">
-        <v>27</v>
+        <v>437</v>
       </c>
       <c r="F282" s="1">
         <v>46253</v>
@@ -9553,7 +9667,7 @@
         <v>0</v>
       </c>
       <c r="B283" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="C283">
         <v>1</v>
@@ -9562,13 +9676,13 @@
         <v>12</v>
       </c>
       <c r="E283" t="s">
-        <v>274</v>
+        <v>439</v>
       </c>
       <c r="F283" s="1">
         <v>46253</v>
       </c>
       <c r="G283" s="1">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="H283">
         <v>0</v>
@@ -9579,17 +9693,17 @@
         <v>0</v>
       </c>
       <c r="B284" t="s">
+        <v>440</v>
+      </c>
+      <c r="C284">
+        <v>1</v>
+      </c>
+      <c r="D284" t="s">
+        <v>12</v>
+      </c>
+      <c r="E284" t="s">
         <v>441</v>
       </c>
-      <c r="C284">
-        <v>1</v>
-      </c>
-      <c r="D284" t="s">
-        <v>2</v>
-      </c>
-      <c r="E284" t="s">
-        <v>124</v>
-      </c>
       <c r="F284" s="1">
         <v>46253</v>
       </c>
@@ -9597,7 +9711,7 @@
         <v>46253</v>
       </c>
       <c r="H284">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="285" spans="1:8" x14ac:dyDescent="0.2">
@@ -9611,10 +9725,10 @@
         <v>1</v>
       </c>
       <c r="D285" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E285" t="s">
-        <v>124</v>
+        <v>443</v>
       </c>
       <c r="F285" s="1">
         <v>46253</v>
@@ -9623,7 +9737,7 @@
         <v>46253</v>
       </c>
       <c r="H285">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="286" spans="1:8" x14ac:dyDescent="0.2">
@@ -9631,7 +9745,7 @@
         <v>0</v>
       </c>
       <c r="B286" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C286">
         <v>1</v>
@@ -9640,7 +9754,7 @@
         <v>12</v>
       </c>
       <c r="E286" t="s">
-        <v>57</v>
+        <v>27</v>
       </c>
       <c r="F286" s="1">
         <v>46253</v>
@@ -9657,7 +9771,7 @@
         <v>0</v>
       </c>
       <c r="B287" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C287">
         <v>1</v>
@@ -9666,7 +9780,7 @@
         <v>12</v>
       </c>
       <c r="E287" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="F287" s="1">
         <v>46253</v>
@@ -9683,16 +9797,16 @@
         <v>0</v>
       </c>
       <c r="B288" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C288">
         <v>1</v>
       </c>
       <c r="D288" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E288" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="F288" s="1">
         <v>46253</v>
@@ -9701,7 +9815,7 @@
         <v>46253</v>
       </c>
       <c r="H288">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="289" spans="1:8" x14ac:dyDescent="0.2">
@@ -9709,16 +9823,16 @@
         <v>0</v>
       </c>
       <c r="B289" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C289">
         <v>1</v>
       </c>
       <c r="D289" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E289" t="s">
-        <v>447</v>
+        <v>274</v>
       </c>
       <c r="F289" s="1">
         <v>46253</v>
@@ -9727,7 +9841,7 @@
         <v>46253</v>
       </c>
       <c r="H289">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="290" spans="1:8" x14ac:dyDescent="0.2">
@@ -9741,10 +9855,10 @@
         <v>1</v>
       </c>
       <c r="D290" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E290" t="s">
-        <v>66</v>
+        <v>124</v>
       </c>
       <c r="F290" s="1">
         <v>46253</v>
@@ -9753,7 +9867,7 @@
         <v>46253</v>
       </c>
       <c r="H290">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="291" spans="1:8" x14ac:dyDescent="0.2">
@@ -9767,10 +9881,10 @@
         <v>1</v>
       </c>
       <c r="D291" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E291" t="s">
-        <v>146</v>
+        <v>124</v>
       </c>
       <c r="F291" s="1">
         <v>46253</v>
@@ -9779,7 +9893,7 @@
         <v>46253</v>
       </c>
       <c r="H291">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="292" spans="1:8" x14ac:dyDescent="0.2">
@@ -9793,10 +9907,10 @@
         <v>1</v>
       </c>
       <c r="D292" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E292" t="s">
-        <v>451</v>
+        <v>57</v>
       </c>
       <c r="F292" s="1">
         <v>46253</v>
@@ -9805,7 +9919,7 @@
         <v>46253</v>
       </c>
       <c r="H292">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="293" spans="1:8" x14ac:dyDescent="0.2">
@@ -9813,7 +9927,7 @@
         <v>0</v>
       </c>
       <c r="B293" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C293">
         <v>1</v>
@@ -9822,7 +9936,7 @@
         <v>12</v>
       </c>
       <c r="E293" t="s">
-        <v>453</v>
+        <v>13</v>
       </c>
       <c r="F293" s="1">
         <v>46253</v>
@@ -9839,16 +9953,16 @@
         <v>0</v>
       </c>
       <c r="B294" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="C294">
         <v>1</v>
       </c>
       <c r="D294" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E294" t="s">
-        <v>455</v>
+        <v>10</v>
       </c>
       <c r="F294" s="1">
         <v>46253</v>
@@ -9857,7 +9971,7 @@
         <v>46253</v>
       </c>
       <c r="H294">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="295" spans="1:8" x14ac:dyDescent="0.2">
@@ -9865,16 +9979,16 @@
         <v>0</v>
       </c>
       <c r="B295" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="C295">
         <v>1</v>
       </c>
       <c r="D295" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E295" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="F295" s="1">
         <v>46253</v>
@@ -9883,7 +9997,7 @@
         <v>46253</v>
       </c>
       <c r="H295">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="296" spans="1:8" x14ac:dyDescent="0.2">
@@ -9891,7 +10005,7 @@
         <v>0</v>
       </c>
       <c r="B296" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="C296">
         <v>1</v>
@@ -9900,7 +10014,7 @@
         <v>12</v>
       </c>
       <c r="E296" t="s">
-        <v>292</v>
+        <v>66</v>
       </c>
       <c r="F296" s="1">
         <v>46253</v>
@@ -9917,7 +10031,7 @@
         <v>0</v>
       </c>
       <c r="B297" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="C297">
         <v>1</v>
@@ -9926,7 +10040,7 @@
         <v>12</v>
       </c>
       <c r="E297" t="s">
-        <v>460</v>
+        <v>146</v>
       </c>
       <c r="F297" s="1">
         <v>46253</v>
@@ -9943,7 +10057,7 @@
         <v>0</v>
       </c>
       <c r="B298" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="C298">
         <v>1</v>
@@ -9952,7 +10066,7 @@
         <v>12</v>
       </c>
       <c r="E298" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="F298" s="1">
         <v>46253</v>
@@ -9969,7 +10083,7 @@
         <v>0</v>
       </c>
       <c r="B299" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="C299">
         <v>1</v>
@@ -9978,7 +10092,7 @@
         <v>12</v>
       </c>
       <c r="E299" t="s">
-        <v>396</v>
+        <v>460</v>
       </c>
       <c r="F299" s="1">
         <v>46253</v>
@@ -9995,7 +10109,7 @@
         <v>0</v>
       </c>
       <c r="B300" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="C300">
         <v>1</v>
@@ -10004,7 +10118,7 @@
         <v>12</v>
       </c>
       <c r="E300" t="s">
-        <v>122</v>
+        <v>462</v>
       </c>
       <c r="F300" s="1">
         <v>46253</v>
@@ -10021,7 +10135,7 @@
         <v>0</v>
       </c>
       <c r="B301" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="C301">
         <v>1</v>
@@ -10030,7 +10144,7 @@
         <v>12</v>
       </c>
       <c r="E301" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="F301" s="1">
         <v>46253</v>
@@ -10047,16 +10161,16 @@
         <v>0</v>
       </c>
       <c r="B302" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="C302">
         <v>1</v>
       </c>
       <c r="D302" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E302" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="F302" s="1">
         <v>46253</v>
@@ -10065,7 +10179,7 @@
         <v>46253</v>
       </c>
       <c r="H302">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="303" spans="1:8" x14ac:dyDescent="0.2">
@@ -10073,7 +10187,7 @@
         <v>0</v>
       </c>
       <c r="B303" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="C303">
         <v>1</v>
@@ -10082,7 +10196,7 @@
         <v>12</v>
       </c>
       <c r="E303" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="F303" s="1">
         <v>46253</v>
@@ -10099,7 +10213,7 @@
         <v>0</v>
       </c>
       <c r="B304" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="C304">
         <v>1</v>
@@ -10108,7 +10222,7 @@
         <v>12</v>
       </c>
       <c r="E304" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="F304" s="1">
         <v>46253</v>
@@ -10125,7 +10239,7 @@
         <v>0</v>
       </c>
       <c r="B305" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="C305">
         <v>1</v>
@@ -10134,7 +10248,7 @@
         <v>12</v>
       </c>
       <c r="E305" t="s">
-        <v>323</v>
+        <v>397</v>
       </c>
       <c r="F305" s="1">
         <v>46253</v>
@@ -10151,7 +10265,7 @@
         <v>0</v>
       </c>
       <c r="B306" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="C306">
         <v>1</v>
@@ -10160,7 +10274,7 @@
         <v>12</v>
       </c>
       <c r="E306" t="s">
-        <v>335</v>
+        <v>122</v>
       </c>
       <c r="F306" s="1">
         <v>46253</v>
@@ -10177,7 +10291,7 @@
         <v>0</v>
       </c>
       <c r="B307" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="C307">
         <v>1</v>
@@ -10186,7 +10300,7 @@
         <v>12</v>
       </c>
       <c r="E307" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="F307" s="1">
         <v>46253</v>
@@ -10203,16 +10317,16 @@
         <v>0</v>
       </c>
       <c r="B308" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="C308">
         <v>1</v>
       </c>
       <c r="D308" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E308" t="s">
-        <v>477</v>
+        <v>296</v>
       </c>
       <c r="F308" s="1">
         <v>46253</v>
@@ -10221,7 +10335,7 @@
         <v>46253</v>
       </c>
       <c r="H308">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="309" spans="1:8" x14ac:dyDescent="0.2">
@@ -10229,7 +10343,7 @@
         <v>0</v>
       </c>
       <c r="B309" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="C309">
         <v>1</v>
@@ -10238,7 +10352,7 @@
         <v>12</v>
       </c>
       <c r="E309" t="s">
-        <v>141</v>
+        <v>476</v>
       </c>
       <c r="F309" s="1">
         <v>46253</v>
@@ -10255,16 +10369,16 @@
         <v>0</v>
       </c>
       <c r="B310" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="C310">
         <v>1</v>
       </c>
       <c r="D310" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E310" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="F310" s="1">
         <v>46253</v>
@@ -10273,7 +10387,7 @@
         <v>46253</v>
       </c>
       <c r="H310">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="311" spans="1:8" x14ac:dyDescent="0.2">
@@ -10281,7 +10395,7 @@
         <v>0</v>
       </c>
       <c r="B311" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="C311">
         <v>1</v>
@@ -10290,7 +10404,7 @@
         <v>12</v>
       </c>
       <c r="E311" t="s">
-        <v>396</v>
+        <v>323</v>
       </c>
       <c r="F311" s="1">
         <v>46253</v>
@@ -10307,16 +10421,16 @@
         <v>0</v>
       </c>
       <c r="B312" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="C312">
         <v>1</v>
       </c>
       <c r="D312" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E312" t="s">
-        <v>382</v>
+        <v>335</v>
       </c>
       <c r="F312" s="1">
         <v>46253</v>
@@ -10325,7 +10439,7 @@
         <v>46253</v>
       </c>
       <c r="H312">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="313" spans="1:8" x14ac:dyDescent="0.2">
@@ -10333,7 +10447,7 @@
         <v>0</v>
       </c>
       <c r="B313" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="C313">
         <v>1</v>
@@ -10342,13 +10456,13 @@
         <v>12</v>
       </c>
       <c r="E313" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="F313" s="1">
         <v>46253</v>
       </c>
       <c r="G313" s="1">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="H313">
         <v>0</v>
@@ -10359,7 +10473,7 @@
         <v>0</v>
       </c>
       <c r="B314" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="C314">
         <v>1</v>
@@ -10368,7 +10482,7 @@
         <v>12</v>
       </c>
       <c r="E314" t="s">
-        <v>27</v>
+        <v>483</v>
       </c>
       <c r="F314" s="1">
         <v>46253</v>
@@ -10385,16 +10499,16 @@
         <v>0</v>
       </c>
       <c r="B315" t="s">
+        <v>484</v>
+      </c>
+      <c r="C315">
+        <v>1</v>
+      </c>
+      <c r="D315" t="s">
+        <v>12</v>
+      </c>
+      <c r="E315" t="s">
         <v>485</v>
-      </c>
-      <c r="C315">
-        <v>1</v>
-      </c>
-      <c r="D315" t="s">
-        <v>12</v>
-      </c>
-      <c r="E315" t="s">
-        <v>27</v>
       </c>
       <c r="F315" s="1">
         <v>46253</v>
@@ -10420,7 +10534,7 @@
         <v>12</v>
       </c>
       <c r="E316" t="s">
-        <v>27</v>
+        <v>141</v>
       </c>
       <c r="F316" s="1">
         <v>46253</v>
@@ -10443,10 +10557,10 @@
         <v>1</v>
       </c>
       <c r="D317" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E317" t="s">
-        <v>27</v>
+        <v>488</v>
       </c>
       <c r="F317" s="1">
         <v>46253</v>
@@ -10455,7 +10569,7 @@
         <v>46253</v>
       </c>
       <c r="H317">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="318" spans="1:8" x14ac:dyDescent="0.2">
@@ -10463,7 +10577,7 @@
         <v>0</v>
       </c>
       <c r="B318" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C318">
         <v>1</v>
@@ -10472,7 +10586,7 @@
         <v>12</v>
       </c>
       <c r="E318" t="s">
-        <v>27</v>
+        <v>397</v>
       </c>
       <c r="F318" s="1">
         <v>46253</v>
@@ -10489,16 +10603,16 @@
         <v>0</v>
       </c>
       <c r="B319" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C319">
         <v>1</v>
       </c>
       <c r="D319" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E319" t="s">
-        <v>27</v>
+        <v>382</v>
       </c>
       <c r="F319" s="1">
         <v>46253</v>
@@ -10507,7 +10621,7 @@
         <v>46253</v>
       </c>
       <c r="H319">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="320" spans="1:8" x14ac:dyDescent="0.2">
@@ -10515,7 +10629,7 @@
         <v>0</v>
       </c>
       <c r="B320" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C320">
         <v>1</v>
@@ -10541,7 +10655,7 @@
         <v>0</v>
       </c>
       <c r="B321" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C321">
         <v>1</v>
@@ -10550,7 +10664,7 @@
         <v>12</v>
       </c>
       <c r="E321" t="s">
-        <v>492</v>
+        <v>27</v>
       </c>
       <c r="F321" s="1">
         <v>46253</v>
@@ -10576,7 +10690,7 @@
         <v>12</v>
       </c>
       <c r="E322" t="s">
-        <v>494</v>
+        <v>27</v>
       </c>
       <c r="F322" s="1">
         <v>46253</v>
@@ -10593,7 +10707,7 @@
         <v>0</v>
       </c>
       <c r="B323" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C323">
         <v>1</v>
@@ -10602,7 +10716,7 @@
         <v>12</v>
       </c>
       <c r="E323" t="s">
-        <v>496</v>
+        <v>27</v>
       </c>
       <c r="F323" s="1">
         <v>46253</v>
@@ -10619,7 +10733,7 @@
         <v>0</v>
       </c>
       <c r="B324" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="C324">
         <v>1</v>
@@ -10628,7 +10742,7 @@
         <v>12</v>
       </c>
       <c r="E324" t="s">
-        <v>498</v>
+        <v>27</v>
       </c>
       <c r="F324" s="1">
         <v>46253</v>
@@ -10645,7 +10759,7 @@
         <v>0</v>
       </c>
       <c r="B325" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="C325">
         <v>1</v>
@@ -10654,7 +10768,7 @@
         <v>12</v>
       </c>
       <c r="E325" t="s">
-        <v>500</v>
+        <v>27</v>
       </c>
       <c r="F325" s="1">
         <v>46253</v>
@@ -10671,7 +10785,7 @@
         <v>0</v>
       </c>
       <c r="B326" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="C326">
         <v>1</v>
@@ -10680,7 +10794,7 @@
         <v>12</v>
       </c>
       <c r="E326" t="s">
-        <v>502</v>
+        <v>27</v>
       </c>
       <c r="F326" s="1">
         <v>46253</v>
@@ -10694,51 +10808,51 @@
     </row>
     <row r="327" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A327" t="s">
-        <v>503</v>
+        <v>0</v>
       </c>
       <c r="B327" t="s">
-        <v>504</v>
+        <v>498</v>
       </c>
       <c r="C327">
         <v>1</v>
       </c>
       <c r="D327" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E327" t="s">
-        <v>311</v>
+        <v>27</v>
       </c>
       <c r="F327" s="1">
-        <v>46148</v>
+        <v>46253</v>
       </c>
       <c r="G327" s="1">
-        <v>46149</v>
+        <v>46253</v>
       </c>
       <c r="H327">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="328" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A328" t="s">
-        <v>505</v>
+        <v>0</v>
       </c>
       <c r="B328" t="s">
-        <v>506</v>
+        <v>499</v>
       </c>
       <c r="C328">
         <v>1</v>
       </c>
       <c r="D328" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E328" t="s">
-        <v>30</v>
+        <v>500</v>
       </c>
       <c r="F328" s="1">
-        <v>46133</v>
+        <v>46253</v>
       </c>
       <c r="G328" s="1">
-        <v>46134</v>
+        <v>46253</v>
       </c>
       <c r="H328">
         <v>0</v>
@@ -10746,25 +10860,25 @@
     </row>
     <row r="329" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A329" t="s">
-        <v>505</v>
+        <v>0</v>
       </c>
       <c r="B329" t="s">
-        <v>507</v>
+        <v>501</v>
       </c>
       <c r="C329">
         <v>1</v>
       </c>
       <c r="D329" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E329" t="s">
-        <v>30</v>
+        <v>502</v>
       </c>
       <c r="F329" s="1">
-        <v>46134</v>
+        <v>46253</v>
       </c>
       <c r="G329" s="1">
-        <v>46134</v>
+        <v>46253</v>
       </c>
       <c r="H329">
         <v>0</v>
@@ -10772,25 +10886,25 @@
     </row>
     <row r="330" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A330" t="s">
-        <v>505</v>
+        <v>0</v>
       </c>
       <c r="B330" t="s">
-        <v>508</v>
+        <v>503</v>
       </c>
       <c r="C330">
         <v>1</v>
       </c>
       <c r="D330" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E330" t="s">
-        <v>15</v>
+        <v>504</v>
       </c>
       <c r="F330" s="1">
-        <v>46156</v>
+        <v>46253</v>
       </c>
       <c r="G330" s="1">
-        <v>46156</v>
+        <v>46253</v>
       </c>
       <c r="H330">
         <v>0</v>
@@ -10798,51 +10912,51 @@
     </row>
     <row r="331" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A331" t="s">
+        <v>0</v>
+      </c>
+      <c r="B331" t="s">
         <v>505</v>
       </c>
-      <c r="B331" t="s">
-        <v>509</v>
-      </c>
       <c r="C331">
         <v>1</v>
       </c>
       <c r="D331" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E331" t="s">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="F331" s="1">
-        <v>46195</v>
+        <v>46253</v>
       </c>
       <c r="G331" s="1">
-        <v>46195</v>
+        <v>46253</v>
       </c>
       <c r="H331">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="332" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A332" t="s">
-        <v>505</v>
+        <v>0</v>
       </c>
       <c r="B332" t="s">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="C332">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D332" t="s">
         <v>12</v>
       </c>
       <c r="E332" t="s">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="F332" s="1">
-        <v>46206</v>
+        <v>46253</v>
       </c>
       <c r="G332" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="H332">
         <v>0</v>
@@ -10850,285 +10964,285 @@
     </row>
     <row r="333" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A333" t="s">
-        <v>505</v>
+        <v>0</v>
       </c>
       <c r="B333" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="C333">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D333" t="s">
-        <v>68</v>
+        <v>12</v>
       </c>
       <c r="E333" t="s">
-        <v>514</v>
+        <v>439</v>
       </c>
       <c r="F333" s="1">
-        <v>46209</v>
+        <v>46253</v>
       </c>
       <c r="G333" s="1">
-        <v>46218</v>
+        <v>46253</v>
       </c>
       <c r="H333">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="334" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A334" t="s">
-        <v>505</v>
+        <v>0</v>
       </c>
       <c r="B334" t="s">
-        <v>515</v>
+        <v>510</v>
       </c>
       <c r="C334">
         <v>1</v>
       </c>
       <c r="D334" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E334" t="s">
-        <v>516</v>
+        <v>309</v>
       </c>
       <c r="F334" s="1">
-        <v>46213</v>
+        <v>46253</v>
       </c>
       <c r="G334" s="1">
-        <v>46213</v>
+        <v>46254</v>
       </c>
       <c r="H334">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="335" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A335" t="s">
-        <v>505</v>
+        <v>0</v>
       </c>
       <c r="B335" t="s">
-        <v>517</v>
+        <v>511</v>
       </c>
       <c r="C335">
         <v>1</v>
       </c>
       <c r="D335" t="s">
-        <v>68</v>
+        <v>12</v>
       </c>
       <c r="E335" t="s">
-        <v>223</v>
+        <v>512</v>
       </c>
       <c r="F335" s="1">
-        <v>46213</v>
+        <v>46253</v>
       </c>
       <c r="G335" s="1">
-        <v>46216</v>
+        <v>46254</v>
       </c>
       <c r="H335">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="336" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A336" t="s">
-        <v>505</v>
+        <v>0</v>
       </c>
       <c r="B336" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="C336">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D336" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E336" t="s">
-        <v>96</v>
+        <v>21</v>
       </c>
       <c r="F336" s="1">
-        <v>46220</v>
+        <v>46253</v>
       </c>
       <c r="G336" s="1">
-        <v>46231</v>
+        <v>46254</v>
       </c>
       <c r="H336">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="337" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A337" t="s">
-        <v>505</v>
+        <v>0</v>
       </c>
       <c r="B337" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="C337">
         <v>1</v>
       </c>
       <c r="D337" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E337" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="F337" s="1">
-        <v>46223</v>
+        <v>46253</v>
       </c>
       <c r="G337" s="1">
-        <v>46223</v>
+        <v>46254</v>
       </c>
       <c r="H337">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="338" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A338" t="s">
-        <v>505</v>
+        <v>0</v>
       </c>
       <c r="B338" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="C338">
         <v>1</v>
       </c>
       <c r="D338" t="s">
-        <v>68</v>
+        <v>12</v>
       </c>
       <c r="E338" t="s">
-        <v>223</v>
+        <v>515</v>
       </c>
       <c r="F338" s="1">
-        <v>46224</v>
+        <v>46253</v>
       </c>
       <c r="G338" s="1">
-        <v>46224</v>
+        <v>46254</v>
       </c>
       <c r="H338">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="339" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A339" t="s">
-        <v>505</v>
+        <v>0</v>
       </c>
       <c r="B339" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="C339">
         <v>1</v>
       </c>
       <c r="D339" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E339" t="s">
-        <v>510</v>
+        <v>518</v>
       </c>
       <c r="F339" s="1">
-        <v>46230</v>
+        <v>46253</v>
       </c>
       <c r="G339" s="1">
-        <v>46231</v>
+        <v>46254</v>
       </c>
       <c r="H339">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="340" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A340" t="s">
-        <v>505</v>
+        <v>0</v>
       </c>
       <c r="B340" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="C340">
         <v>1</v>
       </c>
       <c r="D340" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E340" t="s">
-        <v>96</v>
+        <v>53</v>
       </c>
       <c r="F340" s="1">
-        <v>46232</v>
+        <v>46253</v>
       </c>
       <c r="G340" s="1">
-        <v>46233</v>
+        <v>46254</v>
       </c>
       <c r="H340">
-        <v>126</v>
+        <v>0</v>
       </c>
     </row>
     <row r="341" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A341" t="s">
-        <v>505</v>
+        <v>0</v>
       </c>
       <c r="B341" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="C341">
         <v>1</v>
       </c>
       <c r="D341" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E341" t="s">
-        <v>96</v>
+        <v>53</v>
       </c>
       <c r="F341" s="1">
-        <v>46232</v>
+        <v>46253</v>
       </c>
       <c r="G341" s="1">
-        <v>46233</v>
+        <v>46254</v>
       </c>
       <c r="H341">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="342" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A342" t="s">
-        <v>505</v>
+        <v>0</v>
       </c>
       <c r="B342" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="C342">
         <v>1</v>
       </c>
       <c r="D342" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E342" t="s">
-        <v>223</v>
+        <v>53</v>
       </c>
       <c r="F342" s="1">
-        <v>46238</v>
+        <v>46253</v>
       </c>
       <c r="G342" s="1">
-        <v>46239</v>
+        <v>46254</v>
       </c>
       <c r="H342">
-        <v>117</v>
+        <v>0</v>
       </c>
     </row>
     <row r="343" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A343" t="s">
-        <v>505</v>
+        <v>0</v>
       </c>
       <c r="B343" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="C343">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D343" t="s">
         <v>12</v>
       </c>
       <c r="E343" t="s">
-        <v>512</v>
+        <v>19</v>
       </c>
       <c r="F343" s="1">
-        <v>46239</v>
+        <v>46253</v>
       </c>
       <c r="G343" s="1">
-        <v>46252</v>
+        <v>46254</v>
       </c>
       <c r="H343">
         <v>0</v>
@@ -11136,25 +11250,25 @@
     </row>
     <row r="344" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A344" t="s">
-        <v>505</v>
+        <v>0</v>
       </c>
       <c r="B344" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="C344">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D344" t="s">
         <v>12</v>
       </c>
       <c r="E344" t="s">
-        <v>512</v>
+        <v>524</v>
       </c>
       <c r="F344" s="1">
-        <v>46239</v>
+        <v>46253</v>
       </c>
       <c r="G344" s="1">
-        <v>46252</v>
+        <v>46254</v>
       </c>
       <c r="H344">
         <v>0</v>
@@ -11162,36 +11276,36 @@
     </row>
     <row r="345" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A345" t="s">
-        <v>505</v>
+        <v>0</v>
       </c>
       <c r="B345" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="C345">
         <v>1</v>
       </c>
       <c r="D345" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E345" t="s">
-        <v>30</v>
+        <v>526</v>
       </c>
       <c r="F345" s="1">
-        <v>46247</v>
+        <v>46253</v>
       </c>
       <c r="G345" s="1">
-        <v>46252</v>
+        <v>46254</v>
       </c>
       <c r="H345">
-        <v>29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="346" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A346" t="s">
-        <v>505</v>
+        <v>0</v>
       </c>
       <c r="B346" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C346">
         <v>1</v>
@@ -11200,13 +11314,13 @@
         <v>12</v>
       </c>
       <c r="E346" t="s">
-        <v>363</v>
+        <v>318</v>
       </c>
       <c r="F346" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="G346" s="1">
-        <v>46252</v>
+        <v>46254</v>
       </c>
       <c r="H346">
         <v>0</v>
@@ -11214,10 +11328,10 @@
     </row>
     <row r="347" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A347" t="s">
-        <v>505</v>
+        <v>0</v>
       </c>
       <c r="B347" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C347">
         <v>1</v>
@@ -11229,10 +11343,10 @@
         <v>134</v>
       </c>
       <c r="F347" s="1">
-        <v>46252</v>
+        <v>46254</v>
       </c>
       <c r="G347" s="1">
-        <v>46252</v>
+        <v>46254</v>
       </c>
       <c r="H347">
         <v>0</v>
@@ -11240,25 +11354,25 @@
     </row>
     <row r="348" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A348" t="s">
-        <v>505</v>
+        <v>0</v>
       </c>
       <c r="B348" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C348">
         <v>1</v>
       </c>
       <c r="D348" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E348" t="s">
-        <v>531</v>
+        <v>70</v>
       </c>
       <c r="F348" s="1">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="G348" s="1">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="H348">
         <v>0</v>
@@ -11266,10 +11380,10 @@
     </row>
     <row r="349" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A349" t="s">
-        <v>505</v>
+        <v>0</v>
       </c>
       <c r="B349" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="C349">
         <v>1</v>
@@ -11278,13 +11392,13 @@
         <v>12</v>
       </c>
       <c r="E349" t="s">
-        <v>455</v>
+        <v>531</v>
       </c>
       <c r="F349" s="1">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="G349" s="1">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="H349">
         <v>0</v>
@@ -11292,25 +11406,25 @@
     </row>
     <row r="350" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A350" t="s">
-        <v>505</v>
+        <v>0</v>
       </c>
       <c r="B350" t="s">
+        <v>532</v>
+      </c>
+      <c r="C350">
+        <v>1</v>
+      </c>
+      <c r="D350" t="s">
+        <v>12</v>
+      </c>
+      <c r="E350" t="s">
         <v>533</v>
       </c>
-      <c r="C350">
-        <v>1</v>
-      </c>
-      <c r="D350" t="s">
-        <v>12</v>
-      </c>
-      <c r="E350" t="s">
-        <v>534</v>
-      </c>
       <c r="F350" s="1">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="G350" s="1">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="H350">
         <v>0</v>
@@ -11318,25 +11432,25 @@
     </row>
     <row r="351" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A351" t="s">
-        <v>505</v>
+        <v>0</v>
       </c>
       <c r="B351" t="s">
+        <v>534</v>
+      </c>
+      <c r="C351">
+        <v>1</v>
+      </c>
+      <c r="D351" t="s">
+        <v>12</v>
+      </c>
+      <c r="E351" t="s">
         <v>535</v>
       </c>
-      <c r="C351">
-        <v>1</v>
-      </c>
-      <c r="D351" t="s">
-        <v>12</v>
-      </c>
-      <c r="E351" t="s">
-        <v>531</v>
-      </c>
       <c r="F351" s="1">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="G351" s="1">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="H351">
         <v>0</v>
@@ -11344,7 +11458,7 @@
     </row>
     <row r="352" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A352" t="s">
-        <v>505</v>
+        <v>0</v>
       </c>
       <c r="B352" t="s">
         <v>536</v>
@@ -11356,13 +11470,13 @@
         <v>12</v>
       </c>
       <c r="E352" t="s">
-        <v>141</v>
+        <v>124</v>
       </c>
       <c r="F352" s="1">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="G352" s="1">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="H352">
         <v>0</v>
@@ -11370,51 +11484,51 @@
     </row>
     <row r="353" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A353" t="s">
+        <v>0</v>
+      </c>
+      <c r="B353" t="s">
         <v>537</v>
       </c>
-      <c r="B353" t="s">
-        <v>538</v>
-      </c>
       <c r="C353">
         <v>1</v>
       </c>
       <c r="D353" t="s">
-        <v>68</v>
+        <v>12</v>
       </c>
       <c r="E353" t="s">
-        <v>539</v>
+        <v>27</v>
       </c>
       <c r="F353" s="1">
-        <v>46063</v>
+        <v>46254</v>
       </c>
       <c r="G353" s="1">
-        <v>46064</v>
+        <v>46254</v>
       </c>
       <c r="H353">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="354" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A354" t="s">
-        <v>537</v>
+        <v>0</v>
       </c>
       <c r="B354" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="C354">
         <v>1</v>
       </c>
       <c r="D354" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E354" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="F354" s="1">
-        <v>46113</v>
+        <v>46254</v>
       </c>
       <c r="G354" s="1">
-        <v>46125</v>
+        <v>46254</v>
       </c>
       <c r="H354">
         <v>0</v>
@@ -11422,36 +11536,36 @@
     </row>
     <row r="355" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A355" t="s">
-        <v>537</v>
+        <v>0</v>
       </c>
       <c r="B355" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="C355">
         <v>1</v>
       </c>
       <c r="D355" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E355" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="F355" s="1">
-        <v>46125</v>
+        <v>46254</v>
       </c>
       <c r="G355" s="1">
-        <v>46125</v>
+        <v>46254</v>
       </c>
       <c r="H355">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="356" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A356" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="B356" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="C356">
         <v>1</v>
@@ -11460,21 +11574,21 @@
         <v>2</v>
       </c>
       <c r="E356" t="s">
-        <v>41</v>
+        <v>311</v>
       </c>
       <c r="F356" s="1">
-        <v>46126</v>
+        <v>46148</v>
       </c>
       <c r="G356" s="1">
-        <v>46126</v>
+        <v>46149</v>
       </c>
       <c r="H356">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="357" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A357" t="s">
-        <v>537</v>
+        <v>542</v>
       </c>
       <c r="B357" t="s">
         <v>543</v>
@@ -11483,24 +11597,24 @@
         <v>1</v>
       </c>
       <c r="D357" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E357" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="F357" s="1">
-        <v>46126</v>
+        <v>46133</v>
       </c>
       <c r="G357" s="1">
-        <v>46126</v>
+        <v>46134</v>
       </c>
       <c r="H357">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="358" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A358" t="s">
-        <v>537</v>
+        <v>542</v>
       </c>
       <c r="B358" t="s">
         <v>544</v>
@@ -11509,24 +11623,24 @@
         <v>1</v>
       </c>
       <c r="D358" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E358" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="F358" s="1">
-        <v>46128</v>
+        <v>46134</v>
       </c>
       <c r="G358" s="1">
-        <v>46128</v>
+        <v>46134</v>
       </c>
       <c r="H358">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="359" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A359" t="s">
-        <v>537</v>
+        <v>542</v>
       </c>
       <c r="B359" t="s">
         <v>545</v>
@@ -11538,13 +11652,13 @@
         <v>5</v>
       </c>
       <c r="E359" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="F359" s="1">
-        <v>46132</v>
+        <v>46156</v>
       </c>
       <c r="G359" s="1">
-        <v>46132</v>
+        <v>46156</v>
       </c>
       <c r="H359">
         <v>0</v>
@@ -11552,7 +11666,7 @@
     </row>
     <row r="360" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A360" t="s">
-        <v>537</v>
+        <v>542</v>
       </c>
       <c r="B360" t="s">
         <v>546</v>
@@ -11564,65 +11678,65 @@
         <v>2</v>
       </c>
       <c r="E360" t="s">
-        <v>41</v>
+        <v>547</v>
       </c>
       <c r="F360" s="1">
-        <v>46161</v>
+        <v>46195</v>
       </c>
       <c r="G360" s="1">
-        <v>46161</v>
+        <v>46195</v>
       </c>
       <c r="H360">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="361" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A361" t="s">
-        <v>537</v>
+        <v>542</v>
       </c>
       <c r="B361" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C361">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D361" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E361" t="s">
-        <v>41</v>
+        <v>549</v>
       </c>
       <c r="F361" s="1">
-        <v>46174</v>
+        <v>46206</v>
       </c>
       <c r="G361" s="1">
-        <v>46174</v>
+        <v>46252</v>
       </c>
       <c r="H361">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="362" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A362" t="s">
-        <v>537</v>
+        <v>542</v>
       </c>
       <c r="B362" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="C362">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D362" t="s">
-        <v>2</v>
+        <v>68</v>
       </c>
       <c r="E362" t="s">
-        <v>41</v>
+        <v>551</v>
       </c>
       <c r="F362" s="1">
-        <v>46174</v>
+        <v>46209</v>
       </c>
       <c r="G362" s="1">
-        <v>46174</v>
+        <v>46218</v>
       </c>
       <c r="H362">
         <v>1</v>
@@ -11630,25 +11744,25 @@
     </row>
     <row r="363" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A363" t="s">
-        <v>537</v>
+        <v>542</v>
       </c>
       <c r="B363" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="C363">
         <v>1</v>
       </c>
       <c r="D363" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E363" t="s">
-        <v>41</v>
+        <v>553</v>
       </c>
       <c r="F363" s="1">
-        <v>46195</v>
+        <v>46213</v>
       </c>
       <c r="G363" s="1">
-        <v>46252</v>
+        <v>46213</v>
       </c>
       <c r="H363">
         <v>0</v>
@@ -11656,233 +11770,233 @@
     </row>
     <row r="364" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A364" t="s">
-        <v>537</v>
+        <v>542</v>
       </c>
       <c r="B364" t="s">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="C364">
         <v>1</v>
       </c>
       <c r="D364" t="s">
-        <v>5</v>
+        <v>68</v>
       </c>
       <c r="E364" t="s">
-        <v>41</v>
+        <v>223</v>
       </c>
       <c r="F364" s="1">
-        <v>46210</v>
+        <v>46213</v>
       </c>
       <c r="G364" s="1">
-        <v>46210</v>
+        <v>46216</v>
       </c>
       <c r="H364">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="365" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A365" t="s">
-        <v>537</v>
+        <v>542</v>
       </c>
       <c r="B365" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="C365">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D365" t="s">
         <v>2</v>
       </c>
       <c r="E365" t="s">
-        <v>41</v>
+        <v>96</v>
       </c>
       <c r="F365" s="1">
-        <v>46213</v>
+        <v>46220</v>
       </c>
       <c r="G365" s="1">
-        <v>46213</v>
+        <v>46231</v>
       </c>
       <c r="H365">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="366" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A366" t="s">
-        <v>537</v>
+        <v>542</v>
       </c>
       <c r="B366" t="s">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="C366">
         <v>1</v>
       </c>
       <c r="D366" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E366" t="s">
-        <v>41</v>
+        <v>547</v>
       </c>
       <c r="F366" s="1">
-        <v>46218</v>
+        <v>46223</v>
       </c>
       <c r="G366" s="1">
-        <v>46252</v>
+        <v>46223</v>
       </c>
       <c r="H366">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="367" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A367" t="s">
-        <v>537</v>
+        <v>542</v>
       </c>
       <c r="B367" t="s">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="C367">
         <v>1</v>
       </c>
       <c r="D367" t="s">
-        <v>5</v>
+        <v>68</v>
       </c>
       <c r="E367" t="s">
-        <v>55</v>
+        <v>223</v>
       </c>
       <c r="F367" s="1">
-        <v>46226</v>
+        <v>46224</v>
       </c>
       <c r="G367" s="1">
-        <v>46226</v>
+        <v>46224</v>
       </c>
       <c r="H367">
-        <v>0</v>
+        <v>26</v>
       </c>
     </row>
     <row r="368" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A368" t="s">
-        <v>537</v>
+        <v>542</v>
       </c>
       <c r="B368" t="s">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="C368">
         <v>1</v>
       </c>
       <c r="D368" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E368" t="s">
-        <v>41</v>
+        <v>547</v>
       </c>
       <c r="F368" s="1">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="G368" s="1">
-        <v>46252</v>
+        <v>46231</v>
       </c>
       <c r="H368">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="369" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A369" t="s">
-        <v>537</v>
+        <v>542</v>
       </c>
       <c r="B369" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="C369">
         <v>1</v>
       </c>
       <c r="D369" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E369" t="s">
-        <v>41</v>
+        <v>96</v>
       </c>
       <c r="F369" s="1">
-        <v>46227</v>
+        <v>46232</v>
       </c>
       <c r="G369" s="1">
-        <v>46252</v>
+        <v>46233</v>
       </c>
       <c r="H369">
-        <v>0</v>
+        <v>126</v>
       </c>
     </row>
     <row r="370" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A370" t="s">
-        <v>537</v>
+        <v>542</v>
       </c>
       <c r="B370" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="C370">
         <v>1</v>
       </c>
       <c r="D370" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E370" t="s">
-        <v>41</v>
+        <v>96</v>
       </c>
       <c r="F370" s="1">
-        <v>46227</v>
+        <v>46232</v>
       </c>
       <c r="G370" s="1">
-        <v>46228</v>
+        <v>46233</v>
       </c>
       <c r="H370">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="371" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A371" t="s">
-        <v>537</v>
+        <v>542</v>
       </c>
       <c r="B371" t="s">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="C371">
         <v>1</v>
       </c>
       <c r="D371" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E371" t="s">
-        <v>55</v>
+        <v>223</v>
       </c>
       <c r="F371" s="1">
-        <v>46230</v>
+        <v>46238</v>
       </c>
       <c r="G371" s="1">
-        <v>46252</v>
+        <v>46239</v>
       </c>
       <c r="H371">
-        <v>0</v>
+        <v>117</v>
       </c>
     </row>
     <row r="372" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A372" t="s">
-        <v>537</v>
+        <v>542</v>
       </c>
       <c r="B372" t="s">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="C372">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D372" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E372" t="s">
-        <v>41</v>
+        <v>549</v>
       </c>
       <c r="F372" s="1">
-        <v>46231</v>
+        <v>46239</v>
       </c>
       <c r="G372" s="1">
-        <v>46231</v>
+        <v>46252</v>
       </c>
       <c r="H372">
         <v>0</v>
@@ -11890,25 +12004,25 @@
     </row>
     <row r="373" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A373" t="s">
-        <v>537</v>
+        <v>542</v>
       </c>
       <c r="B373" t="s">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="C373">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D373" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E373" t="s">
-        <v>41</v>
+        <v>549</v>
       </c>
       <c r="F373" s="1">
-        <v>46237</v>
+        <v>46239</v>
       </c>
       <c r="G373" s="1">
-        <v>46237</v>
+        <v>46252</v>
       </c>
       <c r="H373">
         <v>0</v>
@@ -11916,36 +12030,36 @@
     </row>
     <row r="374" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A374" t="s">
-        <v>537</v>
+        <v>542</v>
       </c>
       <c r="B374" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="C374">
         <v>1</v>
       </c>
       <c r="D374" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E374" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="F374" s="1">
-        <v>46253</v>
+        <v>46247</v>
       </c>
       <c r="G374" s="1">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="H374">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="375" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A375" t="s">
-        <v>537</v>
+        <v>542</v>
       </c>
       <c r="B375" t="s">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="C375">
         <v>1</v>
@@ -11954,13 +12068,13 @@
         <v>12</v>
       </c>
       <c r="E375" t="s">
-        <v>41</v>
+        <v>363</v>
       </c>
       <c r="F375" s="1">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="G375" s="1">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="H375">
         <v>0</v>
@@ -11968,183 +12082,989 @@
     </row>
     <row r="376" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A376" t="s">
-        <v>562</v>
+        <v>542</v>
       </c>
       <c r="B376" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="C376">
         <v>1</v>
       </c>
       <c r="D376" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E376" t="s">
-        <v>564</v>
+        <v>134</v>
       </c>
       <c r="F376" s="1">
-        <v>46083</v>
+        <v>46252</v>
       </c>
       <c r="G376" s="1">
-        <v>46084</v>
+        <v>46252</v>
       </c>
       <c r="H376">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="377" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A377" t="s">
-        <v>562</v>
+        <v>542</v>
       </c>
       <c r="B377" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="C377">
         <v>1</v>
       </c>
       <c r="D377" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E377" t="s">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="F377" s="1">
-        <v>46132</v>
+        <v>46253</v>
       </c>
       <c r="G377" s="1">
-        <v>46133</v>
+        <v>46253</v>
       </c>
       <c r="H377">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="378" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A378" t="s">
-        <v>562</v>
+        <v>542</v>
       </c>
       <c r="B378" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="C378">
         <v>1</v>
       </c>
       <c r="D378" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E378" t="s">
-        <v>567</v>
+        <v>223</v>
       </c>
       <c r="F378" s="1">
-        <v>46157</v>
+        <v>46253</v>
       </c>
       <c r="G378" s="1">
-        <v>46157</v>
+        <v>46254</v>
       </c>
       <c r="H378">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="379" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A379" t="s">
-        <v>562</v>
+        <v>542</v>
       </c>
       <c r="B379" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="C379">
         <v>1</v>
       </c>
       <c r="D379" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E379" t="s">
-        <v>569</v>
+        <v>462</v>
       </c>
       <c r="F379" s="1">
-        <v>46168</v>
+        <v>46253</v>
       </c>
       <c r="G379" s="1">
-        <v>46170</v>
+        <v>46253</v>
       </c>
       <c r="H379">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="380" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A380" t="s">
-        <v>562</v>
+        <v>542</v>
       </c>
       <c r="B380" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C380">
         <v>1</v>
       </c>
       <c r="D380" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E380" t="s">
-        <v>567</v>
+        <v>141</v>
       </c>
       <c r="F380" s="1">
-        <v>46244</v>
+        <v>46253</v>
       </c>
       <c r="G380" s="1">
-        <v>46244</v>
+        <v>46253</v>
       </c>
       <c r="H380">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="381" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A381" t="s">
-        <v>562</v>
+        <v>542</v>
       </c>
       <c r="B381" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C381">
         <v>1</v>
       </c>
       <c r="D381" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E381" t="s">
-        <v>567</v>
+        <v>518</v>
       </c>
       <c r="F381" s="1">
-        <v>46247</v>
+        <v>46253</v>
       </c>
       <c r="G381" s="1">
-        <v>46247</v>
+        <v>46254</v>
       </c>
       <c r="H381">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="382" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A382" t="s">
-        <v>562</v>
+        <v>573</v>
       </c>
       <c r="B382" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="C382">
         <v>1</v>
       </c>
       <c r="D382" t="s">
-        <v>2</v>
+        <v>68</v>
       </c>
       <c r="E382" t="s">
-        <v>564</v>
+        <v>575</v>
       </c>
       <c r="F382" s="1">
+        <v>46063</v>
+      </c>
+      <c r="G382" s="1">
+        <v>46064</v>
+      </c>
+      <c r="H382">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="383" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A383" t="s">
+        <v>573</v>
+      </c>
+      <c r="B383" t="s">
+        <v>576</v>
+      </c>
+      <c r="C383">
+        <v>1</v>
+      </c>
+      <c r="D383" t="s">
+        <v>5</v>
+      </c>
+      <c r="E383" t="s">
+        <v>41</v>
+      </c>
+      <c r="F383" s="1">
+        <v>46113</v>
+      </c>
+      <c r="G383" s="1">
+        <v>46125</v>
+      </c>
+      <c r="H383">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="384" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A384" t="s">
+        <v>573</v>
+      </c>
+      <c r="B384" t="s">
+        <v>577</v>
+      </c>
+      <c r="C384">
+        <v>1</v>
+      </c>
+      <c r="D384" t="s">
+        <v>2</v>
+      </c>
+      <c r="E384" t="s">
+        <v>41</v>
+      </c>
+      <c r="F384" s="1">
+        <v>46125</v>
+      </c>
+      <c r="G384" s="1">
+        <v>46125</v>
+      </c>
+      <c r="H384">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="385" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A385" t="s">
+        <v>573</v>
+      </c>
+      <c r="B385" t="s">
+        <v>578</v>
+      </c>
+      <c r="C385">
+        <v>1</v>
+      </c>
+      <c r="D385" t="s">
+        <v>2</v>
+      </c>
+      <c r="E385" t="s">
+        <v>41</v>
+      </c>
+      <c r="F385" s="1">
+        <v>46126</v>
+      </c>
+      <c r="G385" s="1">
+        <v>46126</v>
+      </c>
+      <c r="H385">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="386" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A386" t="s">
+        <v>573</v>
+      </c>
+      <c r="B386" t="s">
+        <v>579</v>
+      </c>
+      <c r="C386">
+        <v>1</v>
+      </c>
+      <c r="D386" t="s">
+        <v>2</v>
+      </c>
+      <c r="E386" t="s">
+        <v>41</v>
+      </c>
+      <c r="F386" s="1">
+        <v>46126</v>
+      </c>
+      <c r="G386" s="1">
+        <v>46126</v>
+      </c>
+      <c r="H386">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="387" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A387" t="s">
+        <v>573</v>
+      </c>
+      <c r="B387" t="s">
+        <v>580</v>
+      </c>
+      <c r="C387">
+        <v>1</v>
+      </c>
+      <c r="D387" t="s">
+        <v>2</v>
+      </c>
+      <c r="E387" t="s">
+        <v>41</v>
+      </c>
+      <c r="F387" s="1">
+        <v>46128</v>
+      </c>
+      <c r="G387" s="1">
+        <v>46128</v>
+      </c>
+      <c r="H387">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="388" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A388" t="s">
+        <v>573</v>
+      </c>
+      <c r="B388" t="s">
+        <v>581</v>
+      </c>
+      <c r="C388">
+        <v>1</v>
+      </c>
+      <c r="D388" t="s">
+        <v>5</v>
+      </c>
+      <c r="E388" t="s">
+        <v>41</v>
+      </c>
+      <c r="F388" s="1">
+        <v>46132</v>
+      </c>
+      <c r="G388" s="1">
+        <v>46132</v>
+      </c>
+      <c r="H388">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="389" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A389" t="s">
+        <v>573</v>
+      </c>
+      <c r="B389" t="s">
+        <v>582</v>
+      </c>
+      <c r="C389">
+        <v>1</v>
+      </c>
+      <c r="D389" t="s">
+        <v>2</v>
+      </c>
+      <c r="E389" t="s">
+        <v>41</v>
+      </c>
+      <c r="F389" s="1">
+        <v>46161</v>
+      </c>
+      <c r="G389" s="1">
+        <v>46161</v>
+      </c>
+      <c r="H389">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="390" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A390" t="s">
+        <v>573</v>
+      </c>
+      <c r="B390" t="s">
+        <v>583</v>
+      </c>
+      <c r="C390">
+        <v>1</v>
+      </c>
+      <c r="D390" t="s">
+        <v>2</v>
+      </c>
+      <c r="E390" t="s">
+        <v>41</v>
+      </c>
+      <c r="F390" s="1">
+        <v>46174</v>
+      </c>
+      <c r="G390" s="1">
+        <v>46174</v>
+      </c>
+      <c r="H390">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="391" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A391" t="s">
+        <v>573</v>
+      </c>
+      <c r="B391" t="s">
+        <v>584</v>
+      </c>
+      <c r="C391">
+        <v>1</v>
+      </c>
+      <c r="D391" t="s">
+        <v>2</v>
+      </c>
+      <c r="E391" t="s">
+        <v>41</v>
+      </c>
+      <c r="F391" s="1">
+        <v>46174</v>
+      </c>
+      <c r="G391" s="1">
+        <v>46174</v>
+      </c>
+      <c r="H391">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="392" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A392" t="s">
+        <v>573</v>
+      </c>
+      <c r="B392" t="s">
+        <v>585</v>
+      </c>
+      <c r="C392">
+        <v>1</v>
+      </c>
+      <c r="D392" t="s">
+        <v>12</v>
+      </c>
+      <c r="E392" t="s">
+        <v>41</v>
+      </c>
+      <c r="F392" s="1">
+        <v>46195</v>
+      </c>
+      <c r="G392" s="1">
+        <v>46252</v>
+      </c>
+      <c r="H392">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="393" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A393" t="s">
+        <v>573</v>
+      </c>
+      <c r="B393" t="s">
+        <v>586</v>
+      </c>
+      <c r="C393">
+        <v>1</v>
+      </c>
+      <c r="D393" t="s">
+        <v>5</v>
+      </c>
+      <c r="E393" t="s">
+        <v>41</v>
+      </c>
+      <c r="F393" s="1">
+        <v>46210</v>
+      </c>
+      <c r="G393" s="1">
+        <v>46210</v>
+      </c>
+      <c r="H393">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="394" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A394" t="s">
+        <v>573</v>
+      </c>
+      <c r="B394" t="s">
+        <v>587</v>
+      </c>
+      <c r="C394">
+        <v>1</v>
+      </c>
+      <c r="D394" t="s">
+        <v>2</v>
+      </c>
+      <c r="E394" t="s">
+        <v>41</v>
+      </c>
+      <c r="F394" s="1">
+        <v>46213</v>
+      </c>
+      <c r="G394" s="1">
+        <v>46213</v>
+      </c>
+      <c r="H394">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="395" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A395" t="s">
+        <v>573</v>
+      </c>
+      <c r="B395" t="s">
+        <v>588</v>
+      </c>
+      <c r="C395">
+        <v>1</v>
+      </c>
+      <c r="D395" t="s">
+        <v>12</v>
+      </c>
+      <c r="E395" t="s">
+        <v>41</v>
+      </c>
+      <c r="F395" s="1">
+        <v>46218</v>
+      </c>
+      <c r="G395" s="1">
+        <v>46252</v>
+      </c>
+      <c r="H395">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="396" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A396" t="s">
+        <v>573</v>
+      </c>
+      <c r="B396" t="s">
+        <v>589</v>
+      </c>
+      <c r="C396">
+        <v>1</v>
+      </c>
+      <c r="D396" t="s">
+        <v>5</v>
+      </c>
+      <c r="E396" t="s">
+        <v>55</v>
+      </c>
+      <c r="F396" s="1">
+        <v>46226</v>
+      </c>
+      <c r="G396" s="1">
+        <v>46226</v>
+      </c>
+      <c r="H396">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="397" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A397" t="s">
+        <v>573</v>
+      </c>
+      <c r="B397" t="s">
+        <v>590</v>
+      </c>
+      <c r="C397">
+        <v>1</v>
+      </c>
+      <c r="D397" t="s">
+        <v>12</v>
+      </c>
+      <c r="E397" t="s">
+        <v>41</v>
+      </c>
+      <c r="F397" s="1">
+        <v>46227</v>
+      </c>
+      <c r="G397" s="1">
+        <v>46252</v>
+      </c>
+      <c r="H397">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="398" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A398" t="s">
+        <v>573</v>
+      </c>
+      <c r="B398" t="s">
+        <v>591</v>
+      </c>
+      <c r="C398">
+        <v>1</v>
+      </c>
+      <c r="D398" t="s">
+        <v>12</v>
+      </c>
+      <c r="E398" t="s">
+        <v>41</v>
+      </c>
+      <c r="F398" s="1">
+        <v>46227</v>
+      </c>
+      <c r="G398" s="1">
+        <v>46252</v>
+      </c>
+      <c r="H398">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="399" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A399" t="s">
+        <v>573</v>
+      </c>
+      <c r="B399" t="s">
+        <v>592</v>
+      </c>
+      <c r="C399">
+        <v>1</v>
+      </c>
+      <c r="D399" t="s">
+        <v>5</v>
+      </c>
+      <c r="E399" t="s">
+        <v>41</v>
+      </c>
+      <c r="F399" s="1">
+        <v>46227</v>
+      </c>
+      <c r="G399" s="1">
+        <v>46228</v>
+      </c>
+      <c r="H399">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="400" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A400" t="s">
+        <v>573</v>
+      </c>
+      <c r="B400" t="s">
+        <v>593</v>
+      </c>
+      <c r="C400">
+        <v>1</v>
+      </c>
+      <c r="D400" t="s">
+        <v>12</v>
+      </c>
+      <c r="E400" t="s">
+        <v>55</v>
+      </c>
+      <c r="F400" s="1">
+        <v>46230</v>
+      </c>
+      <c r="G400" s="1">
+        <v>46252</v>
+      </c>
+      <c r="H400">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="401" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A401" t="s">
+        <v>573</v>
+      </c>
+      <c r="B401" t="s">
+        <v>594</v>
+      </c>
+      <c r="C401">
+        <v>1</v>
+      </c>
+      <c r="D401" t="s">
+        <v>5</v>
+      </c>
+      <c r="E401" t="s">
+        <v>41</v>
+      </c>
+      <c r="F401" s="1">
+        <v>46231</v>
+      </c>
+      <c r="G401" s="1">
+        <v>46231</v>
+      </c>
+      <c r="H401">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="402" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A402" t="s">
+        <v>573</v>
+      </c>
+      <c r="B402" t="s">
+        <v>595</v>
+      </c>
+      <c r="C402">
+        <v>1</v>
+      </c>
+      <c r="D402" t="s">
+        <v>5</v>
+      </c>
+      <c r="E402" t="s">
+        <v>41</v>
+      </c>
+      <c r="F402" s="1">
+        <v>46237</v>
+      </c>
+      <c r="G402" s="1">
+        <v>46237</v>
+      </c>
+      <c r="H402">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="403" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A403" t="s">
+        <v>573</v>
+      </c>
+      <c r="B403" t="s">
+        <v>596</v>
+      </c>
+      <c r="C403">
+        <v>1</v>
+      </c>
+      <c r="D403" t="s">
+        <v>12</v>
+      </c>
+      <c r="E403" t="s">
+        <v>41</v>
+      </c>
+      <c r="F403" s="1">
+        <v>46254</v>
+      </c>
+      <c r="G403" s="1">
+        <v>46254</v>
+      </c>
+      <c r="H403">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="404" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A404" t="s">
+        <v>573</v>
+      </c>
+      <c r="B404" t="s">
+        <v>597</v>
+      </c>
+      <c r="C404">
+        <v>1</v>
+      </c>
+      <c r="D404" t="s">
+        <v>12</v>
+      </c>
+      <c r="E404" t="s">
+        <v>41</v>
+      </c>
+      <c r="F404" s="1">
+        <v>46254</v>
+      </c>
+      <c r="G404" s="1">
+        <v>46254</v>
+      </c>
+      <c r="H404">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="405" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A405" t="s">
+        <v>573</v>
+      </c>
+      <c r="B405" t="s">
+        <v>598</v>
+      </c>
+      <c r="C405">
+        <v>1</v>
+      </c>
+      <c r="D405" t="s">
+        <v>12</v>
+      </c>
+      <c r="E405" t="s">
+        <v>41</v>
+      </c>
+      <c r="F405" s="1">
+        <v>46254</v>
+      </c>
+      <c r="G405" s="1">
+        <v>46254</v>
+      </c>
+      <c r="H405">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="406" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A406" t="s">
+        <v>573</v>
+      </c>
+      <c r="B406" t="s">
+        <v>599</v>
+      </c>
+      <c r="C406">
+        <v>1</v>
+      </c>
+      <c r="D406" t="s">
+        <v>12</v>
+      </c>
+      <c r="E406" t="s">
+        <v>41</v>
+      </c>
+      <c r="F406" s="1">
+        <v>46254</v>
+      </c>
+      <c r="G406" s="1">
+        <v>46254</v>
+      </c>
+      <c r="H406">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="407" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A407" t="s">
+        <v>600</v>
+      </c>
+      <c r="B407" t="s">
+        <v>601</v>
+      </c>
+      <c r="C407">
+        <v>1</v>
+      </c>
+      <c r="D407" t="s">
+        <v>2</v>
+      </c>
+      <c r="E407" t="s">
+        <v>602</v>
+      </c>
+      <c r="F407" s="1">
+        <v>46083</v>
+      </c>
+      <c r="G407" s="1">
+        <v>46084</v>
+      </c>
+      <c r="H407">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="408" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A408" t="s">
+        <v>600</v>
+      </c>
+      <c r="B408" t="s">
+        <v>603</v>
+      </c>
+      <c r="C408">
+        <v>1</v>
+      </c>
+      <c r="D408" t="s">
+        <v>2</v>
+      </c>
+      <c r="E408" t="s">
+        <v>602</v>
+      </c>
+      <c r="F408" s="1">
+        <v>46132</v>
+      </c>
+      <c r="G408" s="1">
+        <v>46133</v>
+      </c>
+      <c r="H408">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="409" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A409" t="s">
+        <v>600</v>
+      </c>
+      <c r="B409" t="s">
+        <v>604</v>
+      </c>
+      <c r="C409">
+        <v>1</v>
+      </c>
+      <c r="D409" t="s">
+        <v>2</v>
+      </c>
+      <c r="E409" t="s">
+        <v>605</v>
+      </c>
+      <c r="F409" s="1">
+        <v>46157</v>
+      </c>
+      <c r="G409" s="1">
+        <v>46157</v>
+      </c>
+      <c r="H409">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="410" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A410" t="s">
+        <v>600</v>
+      </c>
+      <c r="B410" t="s">
+        <v>606</v>
+      </c>
+      <c r="C410">
+        <v>1</v>
+      </c>
+      <c r="D410" t="s">
+        <v>2</v>
+      </c>
+      <c r="E410" t="s">
+        <v>607</v>
+      </c>
+      <c r="F410" s="1">
+        <v>46168</v>
+      </c>
+      <c r="G410" s="1">
+        <v>46170</v>
+      </c>
+      <c r="H410">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="411" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A411" t="s">
+        <v>600</v>
+      </c>
+      <c r="B411" t="s">
+        <v>608</v>
+      </c>
+      <c r="C411">
+        <v>1</v>
+      </c>
+      <c r="D411" t="s">
+        <v>2</v>
+      </c>
+      <c r="E411" t="s">
+        <v>605</v>
+      </c>
+      <c r="F411" s="1">
+        <v>46244</v>
+      </c>
+      <c r="G411" s="1">
+        <v>46244</v>
+      </c>
+      <c r="H411">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="412" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A412" t="s">
+        <v>600</v>
+      </c>
+      <c r="B412" t="s">
+        <v>609</v>
+      </c>
+      <c r="C412">
+        <v>1</v>
+      </c>
+      <c r="D412" t="s">
+        <v>2</v>
+      </c>
+      <c r="E412" t="s">
+        <v>605</v>
+      </c>
+      <c r="F412" s="1">
         <v>46247</v>
       </c>
-      <c r="G382" s="1">
+      <c r="G412" s="1">
         <v>46247</v>
       </c>
-      <c r="H382">
+      <c r="H412">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="413" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A413" t="s">
+        <v>600</v>
+      </c>
+      <c r="B413" t="s">
+        <v>610</v>
+      </c>
+      <c r="C413">
+        <v>1</v>
+      </c>
+      <c r="D413" t="s">
+        <v>2</v>
+      </c>
+      <c r="E413" t="s">
+        <v>602</v>
+      </c>
+      <c r="F413" s="1">
+        <v>46247</v>
+      </c>
+      <c r="G413" s="1">
+        <v>46247</v>
+      </c>
+      <c r="H413">
         <v>1</v>
       </c>
     </row>

--- a/Data_ERP/Pedidos Transmicion.xlsx
+++ b/Data_ERP/Pedidos Transmicion.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sistema_Logistico_Peirano\Data_ERP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B4EFB909-474F-4E10-BB73-C318614B7764}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EB73F151-0BDB-4C8B-9D49-936DB92B223C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="26505" yWindow="3765" windowWidth="15375" windowHeight="8325" xr2:uid="{21F14381-FDC1-4C09-82D0-525EE40A7AFB}"/>
+    <workbookView xWindow="26505" yWindow="3765" windowWidth="15375" windowHeight="8325" xr2:uid="{47E7BEC0-358C-4974-A742-FE88DFB517F1}"/>
   </bookViews>
   <sheets>
     <sheet name="transmicion" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1656" uniqueCount="619">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1536" uniqueCount="573">
   <si>
     <t>0001</t>
   </si>
@@ -721,12 +721,6 @@
     <t>CORRALON AVENIDA S.A.S.</t>
   </si>
   <si>
-    <t xml:space="preserve">  213562</t>
-  </si>
-  <si>
-    <t>COMERCIAL O.R.O. S.A.</t>
-  </si>
-  <si>
     <t xml:space="preserve">  213569</t>
   </si>
   <si>
@@ -835,9 +829,6 @@
     <t>ABELSON S.A.</t>
   </si>
   <si>
-    <t xml:space="preserve">  213725</t>
-  </si>
-  <si>
     <t xml:space="preserve">  213727</t>
   </si>
   <si>
@@ -886,9 +877,6 @@
     <t xml:space="preserve">  213775</t>
   </si>
   <si>
-    <t xml:space="preserve">  213776</t>
-  </si>
-  <si>
     <t xml:space="preserve">  213778</t>
   </si>
   <si>
@@ -907,12 +895,6 @@
     <t xml:space="preserve">  213791</t>
   </si>
   <si>
-    <t xml:space="preserve">  213794</t>
-  </si>
-  <si>
-    <t>ALVEAR SANITARIOS S.R.L.</t>
-  </si>
-  <si>
     <t xml:space="preserve">  213798</t>
   </si>
   <si>
@@ -928,12 +910,6 @@
     <t xml:space="preserve">  213811</t>
   </si>
   <si>
-    <t xml:space="preserve">  213812</t>
-  </si>
-  <si>
-    <t>FERNANDEZ GUILLERMO S. -SANITARIOS FAM</t>
-  </si>
-  <si>
     <t xml:space="preserve">  213813</t>
   </si>
   <si>
@@ -943,9 +919,6 @@
     <t xml:space="preserve">  213818</t>
   </si>
   <si>
-    <t xml:space="preserve">  213819</t>
-  </si>
-  <si>
     <t xml:space="preserve">  213827</t>
   </si>
   <si>
@@ -988,480 +961,345 @@
     <t xml:space="preserve">  213861</t>
   </si>
   <si>
-    <t xml:space="preserve">  213864</t>
+    <t xml:space="preserve">  213866</t>
+  </si>
+  <si>
+    <t>ZINGALV GALVANIZADOS Y ZINC S.R.L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213869</t>
+  </si>
+  <si>
+    <t>DI STABILE E HIJOS S.A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213872</t>
+  </si>
+  <si>
+    <t>FERNANDEZ GONZALO M.-SANITARIOS FERNANDEZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213873</t>
+  </si>
+  <si>
+    <t>FIUMANI MATIAS EZEQUIEL - SANITARIOS MARQUEZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213874</t>
+  </si>
+  <si>
+    <t>COSTA CALCAGNO SRL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213876</t>
+  </si>
+  <si>
+    <t>ARDISSONE MARIO JAVIER -SANIT. ARDISSONE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213877</t>
+  </si>
+  <si>
+    <t>LISOTTO ROQUE Y LISOTTO ROBERTO SH -LISOTTO SANIT.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213895</t>
+  </si>
+  <si>
+    <t>COMERCIALIZADORA Y CONSTRUCTORA LANUS SA  CYCLA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213896</t>
+  </si>
+  <si>
+    <t>TRIPOLI ARNALDO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213902</t>
+  </si>
+  <si>
+    <t>MERMOZ S.A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213907</t>
+  </si>
+  <si>
+    <t>SAN MONTE ALMO SA - TEIXEIRA POCAS SANITARIOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213910</t>
+  </si>
+  <si>
+    <t>STM LOMAS DE CONCRETO SA - STM HOME</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213932</t>
+  </si>
+  <si>
+    <t>SANICENTRO S.A. SANITARIOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213946</t>
+  </si>
+  <si>
+    <t>BETOMAT S.R.L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213952</t>
+  </si>
+  <si>
+    <t>LEIRO JOAQUIN C. - EL GASIFICADOR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213954</t>
+  </si>
+  <si>
+    <t>ARNALDO BUYATTI E HIJOS S.A. -BUYATTI MATERIALES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213957</t>
+  </si>
+  <si>
+    <t>SANITARIOS AXANTRA S.R.L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213965</t>
+  </si>
+  <si>
+    <t>SUPERMAT CENTRAL S.A.S.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213971</t>
+  </si>
+  <si>
+    <t>TODO CAÑO DE MIGUEL ESPECHE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213976</t>
+  </si>
+  <si>
+    <t>GRUPO GRIFO LINC.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213977</t>
+  </si>
+  <si>
+    <t>PRIATEL PISOS S.R.L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213980</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213984</t>
+  </si>
+  <si>
+    <t>EL CAÑADON  S.R.L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213985</t>
+  </si>
+  <si>
+    <t>BALCARCE 54 S.A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213987</t>
+  </si>
+  <si>
+    <t>EMPRESA MAYORISTA INDUSTRIAL SRL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213988</t>
+  </si>
+  <si>
+    <t>SANTIANO LILIANA NOEMI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213990</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  213998</t>
+  </si>
+  <si>
+    <t>CMM ARGENTINA SA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214002</t>
+  </si>
+  <si>
+    <t>MG PINHEL S.R.L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214003</t>
+  </si>
+  <si>
+    <t>TUBONOR S.A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214004</t>
+  </si>
+  <si>
+    <t>SANITARIOS TARAGUI S.R.L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214005</t>
+  </si>
+  <si>
+    <t>CASA FERRALIC SRL - MARMOLERIA PATAGONICA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214008</t>
+  </si>
+  <si>
+    <t>FEDAN S.A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214009</t>
+  </si>
+  <si>
+    <t>ANSBOR S.R.L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214013</t>
+  </si>
+  <si>
+    <t>BRUNETTI ADRIANA NOEMI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214016</t>
+  </si>
+  <si>
+    <t>DIMA BAÑOS &amp; COCINAS S.R.L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214017</t>
+  </si>
+  <si>
+    <t>OCHIUZZO ALBINO JUAN - DISTRIMAR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214020</t>
   </si>
   <si>
     <t>GILI Y CIA SRL</t>
   </si>
   <si>
-    <t xml:space="preserve">  213865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213866</t>
-  </si>
-  <si>
-    <t>ZINGALV GALVANIZADOS Y ZINC S.R.L.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213869</t>
-  </si>
-  <si>
-    <t>DI STABILE E HIJOS S.A.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213872</t>
-  </si>
-  <si>
-    <t>FERNANDEZ GONZALO M.-SANITARIOS FERNANDEZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213873</t>
-  </si>
-  <si>
-    <t>FIUMANI MATIAS EZEQUIEL - SANITARIOS MARQUEZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213874</t>
-  </si>
-  <si>
-    <t>COSTA CALCAGNO SRL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213876</t>
-  </si>
-  <si>
-    <t>ARDISSONE MARIO JAVIER -SANIT. ARDISSONE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213877</t>
-  </si>
-  <si>
-    <t>LISOTTO ROQUE Y LISOTTO ROBERTO SH -LISOTTO SANIT.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213878</t>
-  </si>
-  <si>
-    <t>DARSIE Y CIA. SACI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213879</t>
-  </si>
-  <si>
-    <t>TOTAL 25 SANITARIOS S.A.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213888</t>
-  </si>
-  <si>
-    <t>BRASIL CERAMICAS S.R.L.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213889</t>
-  </si>
-  <si>
-    <t>SACE SRL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213890</t>
-  </si>
-  <si>
-    <t>VICTOR NADIA ANTONELA -SANTIANO CONSTRUCCIONES</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213891</t>
-  </si>
-  <si>
-    <t>GILLI FAUDIN LUIS V. -GILCOMAT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213895</t>
-  </si>
-  <si>
-    <t>COMERCIALIZADORA Y CONSTRUCTORA LANUS SA  CYCLA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213896</t>
-  </si>
-  <si>
-    <t>TRIPOLI ARNALDO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213898</t>
-  </si>
-  <si>
-    <t>ABATEDAGA PABLO D.J.-CONECTANDO INST. SANIT.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213900</t>
-  </si>
-  <si>
-    <t>PIGNATARO M,PIGNATARO P,PIGNATARO D S.H.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213902</t>
-  </si>
-  <si>
-    <t>MERMOZ S.A.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213907</t>
-  </si>
-  <si>
-    <t>SAN MONTE ALMO SA - TEIXEIRA POCAS SANITARIOS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213910</t>
-  </si>
-  <si>
-    <t>STM LOMAS DE CONCRETO SA - STM HOME</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213920</t>
-  </si>
-  <si>
-    <t>LA FERRETERIA S.A.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213930</t>
-  </si>
-  <si>
-    <t>NUEVA CASA SA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213932</t>
-  </si>
-  <si>
-    <t>SANICENTRO S.A. SANITARIOS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213936</t>
-  </si>
-  <si>
-    <t>SUPERFICIES S.R.L.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213941</t>
-  </si>
-  <si>
-    <t>SUCESION DE ARMITANO ALBERTO JUAN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213946</t>
-  </si>
-  <si>
-    <t>BETOMAT S.R.L.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213951</t>
-  </si>
-  <si>
-    <t>GARABITO MATERIALES S.R.L.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213952</t>
-  </si>
-  <si>
-    <t>LEIRO JOAQUIN C. - EL GASIFICADOR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213954</t>
-  </si>
-  <si>
-    <t>ARNALDO BUYATTI E HIJOS S.A. -BUYATTI MATERIALES</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213957</t>
-  </si>
-  <si>
-    <t>SANITARIOS AXANTRA S.R.L.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213960</t>
-  </si>
-  <si>
-    <t>DOS RIZZO S. A.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213961</t>
-  </si>
-  <si>
-    <t>SUPERMAT CENTRAL S.A.S.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213970</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213971</t>
-  </si>
-  <si>
-    <t>TODO CAÑO DE MIGUEL ESPECHE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213974</t>
-  </si>
-  <si>
-    <t>BERGIA SEBASTIAN R Y BERGIA S.R. SH -HIDRONORTE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213976</t>
-  </si>
-  <si>
-    <t>GRUPO GRIFO LINC.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213977</t>
-  </si>
-  <si>
-    <t>PRIATEL PISOS S.R.L.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213980</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213984</t>
-  </si>
-  <si>
-    <t>EL CAÑADON  S.R.L.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213985</t>
-  </si>
-  <si>
-    <t>BALCARCE 54 S.A.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213987</t>
-  </si>
-  <si>
-    <t>EMPRESA MAYORISTA INDUSTRIAL SRL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213988</t>
-  </si>
-  <si>
-    <t>SANTIANO LILIANA NOEMI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213990</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  213998</t>
-  </si>
-  <si>
-    <t>CMM ARGENTINA SA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214002</t>
-  </si>
-  <si>
-    <t>MG PINHEL S.R.L.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214003</t>
-  </si>
-  <si>
-    <t>TUBONOR S.A.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214004</t>
-  </si>
-  <si>
-    <t>SANITARIOS TARAGUI S.R.L.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214005</t>
-  </si>
-  <si>
-    <t>CASA FERRALIC SRL - MARMOLERIA PATAGONICA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214008</t>
-  </si>
-  <si>
-    <t>FEDAN S.A.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214009</t>
-  </si>
-  <si>
-    <t>ANSBOR S.R.L.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214010</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214013</t>
-  </si>
-  <si>
-    <t>BRUNETTI ADRIANA NOEMI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214016</t>
-  </si>
-  <si>
-    <t>DIMA BAÑOS &amp; COCINAS S.R.L.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214017</t>
-  </si>
-  <si>
-    <t>OCHIUZZO ALBINO JUAN - DISTRIMAR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214020</t>
-  </si>
-  <si>
     <t xml:space="preserve">  214021</t>
   </si>
   <si>
@@ -1492,9 +1330,6 @@
     <t xml:space="preserve">  214027</t>
   </si>
   <si>
-    <t xml:space="preserve">  214028</t>
-  </si>
-  <si>
     <t xml:space="preserve">  214029</t>
   </si>
   <si>
@@ -1642,6 +1477,36 @@
     <t xml:space="preserve">  214072</t>
   </si>
   <si>
+    <t xml:space="preserve">  214075</t>
+  </si>
+  <si>
+    <t>EL MUNDO DEL PLOMERO S.R.L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214080</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214081</t>
+  </si>
+  <si>
+    <t>ACUSCIEL S.A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214082</t>
+  </si>
+  <si>
     <t>0004</t>
   </si>
   <si>
@@ -1741,6 +1606,15 @@
     <t xml:space="preserve">    2823</t>
   </si>
   <si>
+    <t xml:space="preserve">    2824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    2825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    2826</t>
+  </si>
+  <si>
     <t>4444</t>
   </si>
   <si>
@@ -1807,19 +1681,7 @@
     <t xml:space="preserve">    1998</t>
   </si>
   <si>
-    <t xml:space="preserve">    2074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    2237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    2238</t>
-  </si>
-  <si>
     <t xml:space="preserve">    2240</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    2241</t>
   </si>
   <si>
     <t>9999</t>
@@ -2326,34 +2188,34 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD0089AF-CB57-41EE-88AE-69B2B29B9461}">
-  <dimension ref="A1:H413"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6F16584-8BB3-4654-BFD6-B70690C133B9}">
+  <dimension ref="A1:H383"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
-        <v>611</v>
+        <v>565</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>612</v>
+        <v>566</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>613</v>
+        <v>567</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>614</v>
+        <v>568</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>615</v>
+        <v>569</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>616</v>
+        <v>570</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>617</v>
+        <v>571</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>618</v>
+        <v>572</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
@@ -5071,7 +4933,7 @@
         <v>1</v>
       </c>
       <c r="D106" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E106" t="s">
         <v>89</v>
@@ -5083,7 +4945,7 @@
         <v>46252</v>
       </c>
       <c r="H106">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.2">
@@ -5981,19 +5843,19 @@
         <v>1</v>
       </c>
       <c r="D141" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E141" t="s">
-        <v>234</v>
+        <v>85</v>
       </c>
       <c r="F141" s="1">
         <v>46245</v>
       </c>
       <c r="G141" s="1">
-        <v>46252</v>
+        <v>46246</v>
       </c>
       <c r="H141">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.2">
@@ -6001,7 +5863,7 @@
         <v>0</v>
       </c>
       <c r="B142" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C142">
         <v>1</v>
@@ -6016,7 +5878,7 @@
         <v>46245</v>
       </c>
       <c r="G142" s="1">
-        <v>46246</v>
+        <v>46245</v>
       </c>
       <c r="H142">
         <v>0</v>
@@ -6027,7 +5889,7 @@
         <v>0</v>
       </c>
       <c r="B143" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C143">
         <v>1</v>
@@ -6053,25 +5915,25 @@
         <v>0</v>
       </c>
       <c r="B144" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C144">
         <v>1</v>
       </c>
       <c r="D144" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E144" t="s">
-        <v>85</v>
+        <v>39</v>
       </c>
       <c r="F144" s="1">
         <v>46245</v>
       </c>
       <c r="G144" s="1">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="H144">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.2">
@@ -6079,16 +5941,16 @@
         <v>0</v>
       </c>
       <c r="B145" t="s">
+        <v>237</v>
+      </c>
+      <c r="C145">
+        <v>1</v>
+      </c>
+      <c r="D145" t="s">
+        <v>2</v>
+      </c>
+      <c r="E145" t="s">
         <v>238</v>
-      </c>
-      <c r="C145">
-        <v>1</v>
-      </c>
-      <c r="D145" t="s">
-        <v>2</v>
-      </c>
-      <c r="E145" t="s">
-        <v>39</v>
       </c>
       <c r="F145" s="1">
         <v>46245</v>
@@ -6097,7 +5959,7 @@
         <v>46246</v>
       </c>
       <c r="H145">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.2">
@@ -6114,16 +5976,16 @@
         <v>2</v>
       </c>
       <c r="E146" t="s">
-        <v>240</v>
+        <v>27</v>
       </c>
       <c r="F146" s="1">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="G146" s="1">
-        <v>46246</v>
+        <v>46252</v>
       </c>
       <c r="H146">
-        <v>8</v>
+        <v>19</v>
       </c>
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.2">
@@ -6131,7 +5993,7 @@
         <v>0</v>
       </c>
       <c r="B147" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C147">
         <v>1</v>
@@ -6140,7 +6002,7 @@
         <v>2</v>
       </c>
       <c r="E147" t="s">
-        <v>27</v>
+        <v>190</v>
       </c>
       <c r="F147" s="1">
         <v>46246</v>
@@ -6149,7 +6011,7 @@
         <v>46252</v>
       </c>
       <c r="H147">
-        <v>19</v>
+        <v>4</v>
       </c>
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.2">
@@ -6157,7 +6019,7 @@
         <v>0</v>
       </c>
       <c r="B148" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C148">
         <v>1</v>
@@ -6166,16 +6028,16 @@
         <v>2</v>
       </c>
       <c r="E148" t="s">
-        <v>190</v>
+        <v>66</v>
       </c>
       <c r="F148" s="1">
         <v>46246</v>
       </c>
       <c r="G148" s="1">
-        <v>46252</v>
+        <v>46247</v>
       </c>
       <c r="H148">
-        <v>4</v>
+        <v>21</v>
       </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.2">
@@ -6183,25 +6045,25 @@
         <v>0</v>
       </c>
       <c r="B149" t="s">
+        <v>242</v>
+      </c>
+      <c r="C149">
+        <v>1</v>
+      </c>
+      <c r="D149" t="s">
+        <v>2</v>
+      </c>
+      <c r="E149" t="s">
         <v>243</v>
-      </c>
-      <c r="C149">
-        <v>1</v>
-      </c>
-      <c r="D149" t="s">
-        <v>2</v>
-      </c>
-      <c r="E149" t="s">
-        <v>66</v>
       </c>
       <c r="F149" s="1">
         <v>46246</v>
       </c>
       <c r="G149" s="1">
-        <v>46247</v>
+        <v>46252</v>
       </c>
       <c r="H149">
-        <v>21</v>
+        <v>2</v>
       </c>
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.2">
@@ -6218,7 +6080,7 @@
         <v>2</v>
       </c>
       <c r="E150" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="F150" s="1">
         <v>46246</v>
@@ -6227,7 +6089,7 @@
         <v>46252</v>
       </c>
       <c r="H150">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.2">
@@ -6235,25 +6097,25 @@
         <v>0</v>
       </c>
       <c r="B151" t="s">
+        <v>245</v>
+      </c>
+      <c r="C151">
+        <v>1</v>
+      </c>
+      <c r="D151" t="s">
+        <v>2</v>
+      </c>
+      <c r="E151" t="s">
         <v>246</v>
-      </c>
-      <c r="C151">
-        <v>1</v>
-      </c>
-      <c r="D151" t="s">
-        <v>2</v>
-      </c>
-      <c r="E151" t="s">
-        <v>245</v>
       </c>
       <c r="F151" s="1">
         <v>46246</v>
       </c>
       <c r="G151" s="1">
-        <v>46252</v>
+        <v>46247</v>
       </c>
       <c r="H151">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.2">
@@ -6276,7 +6138,7 @@
         <v>46246</v>
       </c>
       <c r="G152" s="1">
-        <v>46247</v>
+        <v>46252</v>
       </c>
       <c r="H152">
         <v>4</v>
@@ -6290,22 +6152,22 @@
         <v>249</v>
       </c>
       <c r="C153">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D153" t="s">
         <v>2</v>
       </c>
       <c r="E153" t="s">
-        <v>250</v>
+        <v>104</v>
       </c>
       <c r="F153" s="1">
         <v>46246</v>
       </c>
       <c r="G153" s="1">
-        <v>46252</v>
+        <v>46247</v>
       </c>
       <c r="H153">
-        <v>4</v>
+        <v>46</v>
       </c>
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.2">
@@ -6313,25 +6175,25 @@
         <v>0</v>
       </c>
       <c r="B154" t="s">
+        <v>250</v>
+      </c>
+      <c r="C154">
+        <v>1</v>
+      </c>
+      <c r="D154" t="s">
+        <v>2</v>
+      </c>
+      <c r="E154" t="s">
         <v>251</v>
-      </c>
-      <c r="C154">
-        <v>2</v>
-      </c>
-      <c r="D154" t="s">
-        <v>2</v>
-      </c>
-      <c r="E154" t="s">
-        <v>104</v>
       </c>
       <c r="F154" s="1">
         <v>46246</v>
       </c>
       <c r="G154" s="1">
-        <v>46247</v>
+        <v>46252</v>
       </c>
       <c r="H154">
-        <v>46</v>
+        <v>5</v>
       </c>
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.2">
@@ -6345,7 +6207,7 @@
         <v>1</v>
       </c>
       <c r="D155" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E155" t="s">
         <v>253</v>
@@ -6357,7 +6219,7 @@
         <v>46252</v>
       </c>
       <c r="H155">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.2">
@@ -6371,10 +6233,10 @@
         <v>1</v>
       </c>
       <c r="D156" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E156" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="F156" s="1">
         <v>46246</v>
@@ -6383,7 +6245,7 @@
         <v>46252</v>
       </c>
       <c r="H156">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.2">
@@ -6391,7 +6253,7 @@
         <v>0</v>
       </c>
       <c r="B157" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C157">
         <v>1</v>
@@ -6400,10 +6262,10 @@
         <v>12</v>
       </c>
       <c r="E157" t="s">
-        <v>255</v>
+        <v>27</v>
       </c>
       <c r="F157" s="1">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="G157" s="1">
         <v>46252</v>
@@ -6417,7 +6279,7 @@
         <v>0</v>
       </c>
       <c r="B158" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C158">
         <v>1</v>
@@ -6443,7 +6305,7 @@
         <v>0</v>
       </c>
       <c r="B159" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C159">
         <v>1</v>
@@ -6469,7 +6331,7 @@
         <v>0</v>
       </c>
       <c r="B160" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C160">
         <v>1</v>
@@ -6495,7 +6357,7 @@
         <v>0</v>
       </c>
       <c r="B161" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C161">
         <v>1</v>
@@ -6521,7 +6383,7 @@
         <v>0</v>
       </c>
       <c r="B162" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C162">
         <v>1</v>
@@ -6547,7 +6409,7 @@
         <v>0</v>
       </c>
       <c r="B163" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C163">
         <v>1</v>
@@ -6573,7 +6435,7 @@
         <v>0</v>
       </c>
       <c r="B164" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C164">
         <v>1</v>
@@ -6599,10 +6461,10 @@
         <v>0</v>
       </c>
       <c r="B165" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C165">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D165" t="s">
         <v>12</v>
@@ -6625,10 +6487,10 @@
         <v>0</v>
       </c>
       <c r="B166" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C166">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D166" t="s">
         <v>12</v>
@@ -6651,7 +6513,7 @@
         <v>0</v>
       </c>
       <c r="B167" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C167">
         <v>1</v>
@@ -6677,16 +6539,16 @@
         <v>0</v>
       </c>
       <c r="B168" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C168">
         <v>1</v>
       </c>
       <c r="D168" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E168" t="s">
-        <v>27</v>
+        <v>253</v>
       </c>
       <c r="F168" s="1">
         <v>46247</v>
@@ -6695,7 +6557,7 @@
         <v>46252</v>
       </c>
       <c r="H168">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.2">
@@ -6703,16 +6565,16 @@
         <v>0</v>
       </c>
       <c r="B169" t="s">
+        <v>267</v>
+      </c>
+      <c r="C169">
+        <v>1</v>
+      </c>
+      <c r="D169" t="s">
+        <v>2</v>
+      </c>
+      <c r="E169" t="s">
         <v>268</v>
-      </c>
-      <c r="C169">
-        <v>1</v>
-      </c>
-      <c r="D169" t="s">
-        <v>12</v>
-      </c>
-      <c r="E169" t="s">
-        <v>255</v>
       </c>
       <c r="F169" s="1">
         <v>46247</v>
@@ -6721,7 +6583,7 @@
         <v>46252</v>
       </c>
       <c r="H169">
-        <v>0</v>
+        <v>36</v>
       </c>
     </row>
     <row r="170" spans="1:8" x14ac:dyDescent="0.2">
@@ -6738,7 +6600,7 @@
         <v>2</v>
       </c>
       <c r="E170" t="s">
-        <v>270</v>
+        <v>223</v>
       </c>
       <c r="F170" s="1">
         <v>46247</v>
@@ -6747,7 +6609,7 @@
         <v>46252</v>
       </c>
       <c r="H170">
-        <v>36</v>
+        <v>42</v>
       </c>
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.2">
@@ -6755,25 +6617,25 @@
         <v>0</v>
       </c>
       <c r="B171" t="s">
+        <v>270</v>
+      </c>
+      <c r="C171">
+        <v>1</v>
+      </c>
+      <c r="D171" t="s">
+        <v>5</v>
+      </c>
+      <c r="E171" t="s">
         <v>271</v>
-      </c>
-      <c r="C171">
-        <v>1</v>
-      </c>
-      <c r="D171" t="s">
-        <v>2</v>
-      </c>
-      <c r="E171" t="s">
-        <v>132</v>
       </c>
       <c r="F171" s="1">
         <v>46247</v>
       </c>
       <c r="G171" s="1">
-        <v>46252</v>
+        <v>46247</v>
       </c>
       <c r="H171">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.2">
@@ -6790,7 +6652,7 @@
         <v>2</v>
       </c>
       <c r="E172" t="s">
-        <v>223</v>
+        <v>273</v>
       </c>
       <c r="F172" s="1">
         <v>46247</v>
@@ -6799,7 +6661,7 @@
         <v>46252</v>
       </c>
       <c r="H172">
-        <v>42</v>
+        <v>2</v>
       </c>
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.2">
@@ -6807,22 +6669,22 @@
         <v>0</v>
       </c>
       <c r="B173" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C173">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D173" t="s">
         <v>5</v>
       </c>
       <c r="E173" t="s">
-        <v>274</v>
+        <v>143</v>
       </c>
       <c r="F173" s="1">
         <v>46247</v>
       </c>
       <c r="G173" s="1">
-        <v>46247</v>
+        <v>46252</v>
       </c>
       <c r="H173">
         <v>0</v>
@@ -6839,7 +6701,7 @@
         <v>1</v>
       </c>
       <c r="D174" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E174" t="s">
         <v>276</v>
@@ -6851,7 +6713,7 @@
         <v>46252</v>
       </c>
       <c r="H174">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="175" spans="1:8" x14ac:dyDescent="0.2">
@@ -6862,19 +6724,19 @@
         <v>277</v>
       </c>
       <c r="C175">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D175" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E175" t="s">
-        <v>143</v>
+        <v>278</v>
       </c>
       <c r="F175" s="1">
         <v>46247</v>
       </c>
       <c r="G175" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="H175">
         <v>0</v>
@@ -6885,16 +6747,16 @@
         <v>0</v>
       </c>
       <c r="B176" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C176">
         <v>1</v>
       </c>
       <c r="D176" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E176" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F176" s="1">
         <v>46247</v>
@@ -6903,7 +6765,7 @@
         <v>46252</v>
       </c>
       <c r="H176">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="177" spans="1:8" x14ac:dyDescent="0.2">
@@ -6911,25 +6773,25 @@
         <v>0</v>
       </c>
       <c r="B177" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C177">
         <v>1</v>
       </c>
       <c r="D177" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E177" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F177" s="1">
         <v>46247</v>
       </c>
       <c r="G177" s="1">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="H177">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="178" spans="1:8" x14ac:dyDescent="0.2">
@@ -6937,7 +6799,7 @@
         <v>0</v>
       </c>
       <c r="B178" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C178">
         <v>1</v>
@@ -6946,16 +6808,16 @@
         <v>2</v>
       </c>
       <c r="E178" t="s">
-        <v>283</v>
+        <v>27</v>
       </c>
       <c r="F178" s="1">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="G178" s="1">
         <v>46252</v>
       </c>
       <c r="H178">
-        <v>20</v>
+        <v>1</v>
       </c>
     </row>
     <row r="179" spans="1:8" x14ac:dyDescent="0.2">
@@ -6972,16 +6834,16 @@
         <v>2</v>
       </c>
       <c r="E179" t="s">
-        <v>285</v>
+        <v>13</v>
       </c>
       <c r="F179" s="1">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="G179" s="1">
         <v>46252</v>
       </c>
       <c r="H179">
-        <v>3</v>
+        <v>17</v>
       </c>
     </row>
     <row r="180" spans="1:8" x14ac:dyDescent="0.2">
@@ -6989,16 +6851,16 @@
         <v>0</v>
       </c>
       <c r="B180" t="s">
+        <v>285</v>
+      </c>
+      <c r="C180">
+        <v>1</v>
+      </c>
+      <c r="D180" t="s">
+        <v>2</v>
+      </c>
+      <c r="E180" t="s">
         <v>286</v>
-      </c>
-      <c r="C180">
-        <v>1</v>
-      </c>
-      <c r="D180" t="s">
-        <v>2</v>
-      </c>
-      <c r="E180" t="s">
-        <v>27</v>
       </c>
       <c r="F180" s="1">
         <v>46248</v>
@@ -7007,7 +6869,7 @@
         <v>46252</v>
       </c>
       <c r="H180">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="181" spans="1:8" x14ac:dyDescent="0.2">
@@ -7024,7 +6886,7 @@
         <v>2</v>
       </c>
       <c r="E181" t="s">
-        <v>13</v>
+        <v>288</v>
       </c>
       <c r="F181" s="1">
         <v>46248</v>
@@ -7033,7 +6895,7 @@
         <v>46252</v>
       </c>
       <c r="H181">
-        <v>17</v>
+        <v>1</v>
       </c>
     </row>
     <row r="182" spans="1:8" x14ac:dyDescent="0.2">
@@ -7041,16 +6903,16 @@
         <v>0</v>
       </c>
       <c r="B182" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C182">
         <v>1</v>
       </c>
       <c r="D182" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E182" t="s">
-        <v>13</v>
+        <v>72</v>
       </c>
       <c r="F182" s="1">
         <v>46248</v>
@@ -7059,7 +6921,7 @@
         <v>46252</v>
       </c>
       <c r="H182">
-        <v>42</v>
+        <v>0</v>
       </c>
     </row>
     <row r="183" spans="1:8" x14ac:dyDescent="0.2">
@@ -7067,16 +6929,16 @@
         <v>0</v>
       </c>
       <c r="B183" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C183">
         <v>1</v>
       </c>
       <c r="D183" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E183" t="s">
-        <v>290</v>
+        <v>72</v>
       </c>
       <c r="F183" s="1">
         <v>46248</v>
@@ -7085,7 +6947,7 @@
         <v>46252</v>
       </c>
       <c r="H183">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="184" spans="1:8" x14ac:dyDescent="0.2">
@@ -7099,10 +6961,10 @@
         <v>1</v>
       </c>
       <c r="D184" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E184" t="s">
-        <v>292</v>
+        <v>127</v>
       </c>
       <c r="F184" s="1">
         <v>46248</v>
@@ -7111,7 +6973,7 @@
         <v>46252</v>
       </c>
       <c r="H184">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="185" spans="1:8" x14ac:dyDescent="0.2">
@@ -7119,7 +6981,7 @@
         <v>0</v>
       </c>
       <c r="B185" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C185">
         <v>1</v>
@@ -7128,7 +6990,7 @@
         <v>12</v>
       </c>
       <c r="E185" t="s">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="F185" s="1">
         <v>46248</v>
@@ -7145,16 +7007,16 @@
         <v>0</v>
       </c>
       <c r="B186" t="s">
+        <v>293</v>
+      </c>
+      <c r="C186">
+        <v>1</v>
+      </c>
+      <c r="D186" t="s">
+        <v>12</v>
+      </c>
+      <c r="E186" t="s">
         <v>294</v>
-      </c>
-      <c r="C186">
-        <v>1</v>
-      </c>
-      <c r="D186" t="s">
-        <v>12</v>
-      </c>
-      <c r="E186" t="s">
-        <v>72</v>
       </c>
       <c r="F186" s="1">
         <v>46248</v>
@@ -7177,10 +7039,10 @@
         <v>1</v>
       </c>
       <c r="D187" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E187" t="s">
-        <v>296</v>
+        <v>85</v>
       </c>
       <c r="F187" s="1">
         <v>46248</v>
@@ -7189,7 +7051,7 @@
         <v>46252</v>
       </c>
       <c r="H187">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="188" spans="1:8" x14ac:dyDescent="0.2">
@@ -7197,16 +7059,16 @@
         <v>0</v>
       </c>
       <c r="B188" t="s">
+        <v>296</v>
+      </c>
+      <c r="C188">
+        <v>1</v>
+      </c>
+      <c r="D188" t="s">
+        <v>12</v>
+      </c>
+      <c r="E188" t="s">
         <v>297</v>
-      </c>
-      <c r="C188">
-        <v>1</v>
-      </c>
-      <c r="D188" t="s">
-        <v>12</v>
-      </c>
-      <c r="E188" t="s">
-        <v>127</v>
       </c>
       <c r="F188" s="1">
         <v>46248</v>
@@ -7229,10 +7091,10 @@
         <v>1</v>
       </c>
       <c r="D189" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E189" t="s">
-        <v>127</v>
+        <v>35</v>
       </c>
       <c r="F189" s="1">
         <v>46248</v>
@@ -7241,7 +7103,7 @@
         <v>46252</v>
       </c>
       <c r="H189">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="190" spans="1:8" x14ac:dyDescent="0.2">
@@ -7255,7 +7117,7 @@
         <v>1</v>
       </c>
       <c r="D190" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E190" t="s">
         <v>300</v>
@@ -7267,7 +7129,7 @@
         <v>46252</v>
       </c>
       <c r="H190">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="191" spans="1:8" x14ac:dyDescent="0.2">
@@ -7281,10 +7143,10 @@
         <v>1</v>
       </c>
       <c r="D191" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E191" t="s">
-        <v>85</v>
+        <v>302</v>
       </c>
       <c r="F191" s="1">
         <v>46248</v>
@@ -7293,7 +7155,7 @@
         <v>46252</v>
       </c>
       <c r="H191">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="192" spans="1:8" x14ac:dyDescent="0.2">
@@ -7301,16 +7163,16 @@
         <v>0</v>
       </c>
       <c r="B192" t="s">
+        <v>303</v>
+      </c>
+      <c r="C192">
+        <v>1</v>
+      </c>
+      <c r="D192" t="s">
+        <v>5</v>
+      </c>
+      <c r="E192" t="s">
         <v>302</v>
-      </c>
-      <c r="C192">
-        <v>1</v>
-      </c>
-      <c r="D192" t="s">
-        <v>2</v>
-      </c>
-      <c r="E192" t="s">
-        <v>303</v>
       </c>
       <c r="F192" s="1">
         <v>46248</v>
@@ -7319,7 +7181,7 @@
         <v>46252</v>
       </c>
       <c r="H192">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="193" spans="1:8" x14ac:dyDescent="0.2">
@@ -7333,7 +7195,7 @@
         <v>1</v>
       </c>
       <c r="D193" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E193" t="s">
         <v>305</v>
@@ -7345,7 +7207,7 @@
         <v>46252</v>
       </c>
       <c r="H193">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="194" spans="1:8" x14ac:dyDescent="0.2">
@@ -7362,7 +7224,7 @@
         <v>2</v>
       </c>
       <c r="E194" t="s">
-        <v>35</v>
+        <v>117</v>
       </c>
       <c r="F194" s="1">
         <v>46248</v>
@@ -7371,7 +7233,7 @@
         <v>46252</v>
       </c>
       <c r="H194">
-        <v>6</v>
+        <v>136</v>
       </c>
     </row>
     <row r="195" spans="1:8" x14ac:dyDescent="0.2">
@@ -7385,10 +7247,10 @@
         <v>1</v>
       </c>
       <c r="D195" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E195" t="s">
-        <v>35</v>
+        <v>143</v>
       </c>
       <c r="F195" s="1">
         <v>46248</v>
@@ -7397,7 +7259,7 @@
         <v>46252</v>
       </c>
       <c r="H195">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="196" spans="1:8" x14ac:dyDescent="0.2">
@@ -7411,7 +7273,7 @@
         <v>1</v>
       </c>
       <c r="D196" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E196" t="s">
         <v>309</v>
@@ -7423,7 +7285,7 @@
         <v>46252</v>
       </c>
       <c r="H196">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="197" spans="1:8" x14ac:dyDescent="0.2">
@@ -7449,7 +7311,7 @@
         <v>46252</v>
       </c>
       <c r="H197">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="198" spans="1:8" x14ac:dyDescent="0.2">
@@ -7463,10 +7325,10 @@
         <v>1</v>
       </c>
       <c r="D198" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E198" t="s">
-        <v>311</v>
+        <v>157</v>
       </c>
       <c r="F198" s="1">
         <v>46248</v>
@@ -7475,7 +7337,7 @@
         <v>46252</v>
       </c>
       <c r="H198">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="199" spans="1:8" x14ac:dyDescent="0.2">
@@ -7489,7 +7351,7 @@
         <v>1</v>
       </c>
       <c r="D199" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E199" t="s">
         <v>314</v>
@@ -7501,7 +7363,7 @@
         <v>46252</v>
       </c>
       <c r="H199">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="200" spans="1:8" x14ac:dyDescent="0.2">
@@ -7515,10 +7377,10 @@
         <v>1</v>
       </c>
       <c r="D200" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E200" t="s">
-        <v>117</v>
+        <v>316</v>
       </c>
       <c r="F200" s="1">
         <v>46248</v>
@@ -7527,7 +7389,7 @@
         <v>46252</v>
       </c>
       <c r="H200">
-        <v>136</v>
+        <v>0</v>
       </c>
     </row>
     <row r="201" spans="1:8" x14ac:dyDescent="0.2">
@@ -7535,25 +7397,25 @@
         <v>0</v>
       </c>
       <c r="B201" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C201">
         <v>1</v>
       </c>
       <c r="D201" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E201" t="s">
-        <v>143</v>
+        <v>79</v>
       </c>
       <c r="F201" s="1">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="G201" s="1">
         <v>46252</v>
       </c>
       <c r="H201">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="202" spans="1:8" x14ac:dyDescent="0.2">
@@ -7561,25 +7423,25 @@
         <v>0</v>
       </c>
       <c r="B202" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C202">
         <v>1</v>
       </c>
       <c r="D202" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E202" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F202" s="1">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="G202" s="1">
         <v>46252</v>
       </c>
       <c r="H202">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="203" spans="1:8" x14ac:dyDescent="0.2">
@@ -7587,7 +7449,7 @@
         <v>0</v>
       </c>
       <c r="B203" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C203">
         <v>1</v>
@@ -7596,16 +7458,16 @@
         <v>2</v>
       </c>
       <c r="E203" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F203" s="1">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="G203" s="1">
         <v>46252</v>
       </c>
       <c r="H203">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="204" spans="1:8" x14ac:dyDescent="0.2">
@@ -7613,7 +7475,7 @@
         <v>0</v>
       </c>
       <c r="B204" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C204">
         <v>1</v>
@@ -7622,10 +7484,10 @@
         <v>2</v>
       </c>
       <c r="E204" t="s">
-        <v>157</v>
+        <v>323</v>
       </c>
       <c r="F204" s="1">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="G204" s="1">
         <v>46252</v>
@@ -7639,7 +7501,7 @@
         <v>0</v>
       </c>
       <c r="B205" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C205">
         <v>1</v>
@@ -7651,13 +7513,13 @@
         <v>323</v>
       </c>
       <c r="F205" s="1">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="G205" s="1">
         <v>46252</v>
       </c>
       <c r="H205">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="206" spans="1:8" x14ac:dyDescent="0.2">
@@ -7665,25 +7527,25 @@
         <v>0</v>
       </c>
       <c r="B206" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C206">
         <v>1</v>
       </c>
       <c r="D206" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E206" t="s">
-        <v>296</v>
+        <v>326</v>
       </c>
       <c r="F206" s="1">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="G206" s="1">
         <v>46252</v>
       </c>
       <c r="H206">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="207" spans="1:8" x14ac:dyDescent="0.2">
@@ -7691,25 +7553,25 @@
         <v>0</v>
       </c>
       <c r="B207" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="C207">
         <v>1</v>
       </c>
       <c r="D207" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E207" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="F207" s="1">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="G207" s="1">
         <v>46252</v>
       </c>
       <c r="H207">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="208" spans="1:8" x14ac:dyDescent="0.2">
@@ -7717,7 +7579,7 @@
         <v>0</v>
       </c>
       <c r="B208" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C208">
         <v>1</v>
@@ -7726,10 +7588,10 @@
         <v>12</v>
       </c>
       <c r="E208" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="F208" s="1">
-        <v>46248</v>
+        <v>46252</v>
       </c>
       <c r="G208" s="1">
         <v>46252</v>
@@ -7743,7 +7605,7 @@
         <v>0</v>
       </c>
       <c r="B209" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C209">
         <v>1</v>
@@ -7752,16 +7614,16 @@
         <v>2</v>
       </c>
       <c r="E209" t="s">
-        <v>79</v>
+        <v>332</v>
       </c>
       <c r="F209" s="1">
-        <v>46249</v>
+        <v>46252</v>
       </c>
       <c r="G209" s="1">
         <v>46252</v>
       </c>
       <c r="H209">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="210" spans="1:8" x14ac:dyDescent="0.2">
@@ -7769,7 +7631,7 @@
         <v>0</v>
       </c>
       <c r="B210" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="C210">
         <v>1</v>
@@ -7778,16 +7640,16 @@
         <v>2</v>
       </c>
       <c r="E210" t="s">
-        <v>331</v>
+        <v>13</v>
       </c>
       <c r="F210" s="1">
-        <v>46249</v>
+        <v>46252</v>
       </c>
       <c r="G210" s="1">
         <v>46252</v>
       </c>
       <c r="H210">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="211" spans="1:8" x14ac:dyDescent="0.2">
@@ -7795,25 +7657,25 @@
         <v>0</v>
       </c>
       <c r="B211" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="C211">
         <v>1</v>
       </c>
       <c r="D211" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E211" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="F211" s="1">
-        <v>46249</v>
+        <v>46252</v>
       </c>
       <c r="G211" s="1">
         <v>46252</v>
       </c>
       <c r="H211">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="212" spans="1:8" x14ac:dyDescent="0.2">
@@ -7821,7 +7683,7 @@
         <v>0</v>
       </c>
       <c r="B212" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="C212">
         <v>1</v>
@@ -7830,10 +7692,10 @@
         <v>12</v>
       </c>
       <c r="E212" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="F212" s="1">
-        <v>46249</v>
+        <v>46252</v>
       </c>
       <c r="G212" s="1">
         <v>46252</v>
@@ -7847,7 +7709,7 @@
         <v>0</v>
       </c>
       <c r="B213" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="C213">
         <v>1</v>
@@ -7856,10 +7718,10 @@
         <v>12</v>
       </c>
       <c r="E213" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="F213" s="1">
-        <v>46249</v>
+        <v>46252</v>
       </c>
       <c r="G213" s="1">
         <v>46252</v>
@@ -7873,7 +7735,7 @@
         <v>0</v>
       </c>
       <c r="B214" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="C214">
         <v>1</v>
@@ -7882,10 +7744,10 @@
         <v>12</v>
       </c>
       <c r="E214" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F214" s="1">
-        <v>46249</v>
+        <v>46252</v>
       </c>
       <c r="G214" s="1">
         <v>46252</v>
@@ -7899,7 +7761,7 @@
         <v>0</v>
       </c>
       <c r="B215" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="C215">
         <v>1</v>
@@ -7908,10 +7770,10 @@
         <v>12</v>
       </c>
       <c r="E215" t="s">
-        <v>340</v>
+        <v>72</v>
       </c>
       <c r="F215" s="1">
-        <v>46249</v>
+        <v>46252</v>
       </c>
       <c r="G215" s="1">
         <v>46252</v>
@@ -7925,7 +7787,7 @@
         <v>0</v>
       </c>
       <c r="B216" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C216">
         <v>1</v>
@@ -7934,10 +7796,10 @@
         <v>2</v>
       </c>
       <c r="E216" t="s">
-        <v>342</v>
+        <v>33</v>
       </c>
       <c r="F216" s="1">
-        <v>46249</v>
+        <v>46252</v>
       </c>
       <c r="G216" s="1">
         <v>46252</v>
@@ -7957,19 +7819,19 @@
         <v>1</v>
       </c>
       <c r="D217" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E217" t="s">
-        <v>344</v>
+        <v>268</v>
       </c>
       <c r="F217" s="1">
-        <v>46249</v>
+        <v>46252</v>
       </c>
       <c r="G217" s="1">
         <v>46252</v>
       </c>
       <c r="H217">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="218" spans="1:8" x14ac:dyDescent="0.2">
@@ -7977,16 +7839,16 @@
         <v>0</v>
       </c>
       <c r="B218" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C218">
         <v>1</v>
       </c>
       <c r="D218" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E218" t="s">
-        <v>346</v>
+        <v>66</v>
       </c>
       <c r="F218" s="1">
         <v>46252</v>
@@ -7995,7 +7857,7 @@
         <v>46252</v>
       </c>
       <c r="H218">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="219" spans="1:8" x14ac:dyDescent="0.2">
@@ -8003,7 +7865,7 @@
         <v>0</v>
       </c>
       <c r="B219" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C219">
         <v>1</v>
@@ -8012,7 +7874,7 @@
         <v>2</v>
       </c>
       <c r="E219" t="s">
-        <v>348</v>
+        <v>13</v>
       </c>
       <c r="F219" s="1">
         <v>46252</v>
@@ -8021,7 +7883,7 @@
         <v>46252</v>
       </c>
       <c r="H219">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="220" spans="1:8" x14ac:dyDescent="0.2">
@@ -8029,7 +7891,7 @@
         <v>0</v>
       </c>
       <c r="B220" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="C220">
         <v>1</v>
@@ -8038,7 +7900,7 @@
         <v>2</v>
       </c>
       <c r="E220" t="s">
-        <v>350</v>
+        <v>13</v>
       </c>
       <c r="F220" s="1">
         <v>46252</v>
@@ -8047,7 +7909,7 @@
         <v>46252</v>
       </c>
       <c r="H220">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="221" spans="1:8" x14ac:dyDescent="0.2">
@@ -8055,7 +7917,7 @@
         <v>0</v>
       </c>
       <c r="B221" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="C221">
         <v>1</v>
@@ -8064,7 +7926,7 @@
         <v>2</v>
       </c>
       <c r="E221" t="s">
-        <v>352</v>
+        <v>13</v>
       </c>
       <c r="F221" s="1">
         <v>46252</v>
@@ -8073,7 +7935,7 @@
         <v>46252</v>
       </c>
       <c r="H221">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="222" spans="1:8" x14ac:dyDescent="0.2">
@@ -8081,7 +7943,7 @@
         <v>0</v>
       </c>
       <c r="B222" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="C222">
         <v>1</v>
@@ -8090,7 +7952,7 @@
         <v>12</v>
       </c>
       <c r="E222" t="s">
-        <v>354</v>
+        <v>55</v>
       </c>
       <c r="F222" s="1">
         <v>46252</v>
@@ -8107,16 +7969,16 @@
         <v>0</v>
       </c>
       <c r="B223" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="C223">
         <v>1</v>
       </c>
       <c r="D223" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E223" t="s">
-        <v>356</v>
+        <v>70</v>
       </c>
       <c r="F223" s="1">
         <v>46252</v>
@@ -8125,7 +7987,7 @@
         <v>46252</v>
       </c>
       <c r="H223">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="224" spans="1:8" x14ac:dyDescent="0.2">
@@ -8133,16 +7995,16 @@
         <v>0</v>
       </c>
       <c r="B224" t="s">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="C224">
         <v>1</v>
       </c>
       <c r="D224" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E224" t="s">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="F224" s="1">
         <v>46252</v>
@@ -8151,7 +8013,7 @@
         <v>46252</v>
       </c>
       <c r="H224">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="225" spans="1:8" x14ac:dyDescent="0.2">
@@ -8159,25 +8021,25 @@
         <v>0</v>
       </c>
       <c r="B225" t="s">
-        <v>359</v>
+        <v>352</v>
       </c>
       <c r="C225">
         <v>1</v>
       </c>
       <c r="D225" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E225" t="s">
-        <v>360</v>
+        <v>85</v>
       </c>
       <c r="F225" s="1">
         <v>46252</v>
       </c>
       <c r="G225" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="H225">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="226" spans="1:8" x14ac:dyDescent="0.2">
@@ -8185,25 +8047,25 @@
         <v>0</v>
       </c>
       <c r="B226" t="s">
-        <v>361</v>
+        <v>353</v>
       </c>
       <c r="C226">
         <v>1</v>
       </c>
       <c r="D226" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E226" t="s">
-        <v>13</v>
+        <v>280</v>
       </c>
       <c r="F226" s="1">
         <v>46252</v>
       </c>
       <c r="G226" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="H226">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="227" spans="1:8" x14ac:dyDescent="0.2">
@@ -8211,7 +8073,7 @@
         <v>0</v>
       </c>
       <c r="B227" t="s">
-        <v>362</v>
+        <v>354</v>
       </c>
       <c r="C227">
         <v>1</v>
@@ -8220,13 +8082,13 @@
         <v>12</v>
       </c>
       <c r="E227" t="s">
-        <v>363</v>
+        <v>163</v>
       </c>
       <c r="F227" s="1">
         <v>46252</v>
       </c>
       <c r="G227" s="1">
-        <v>46252</v>
+        <v>46254</v>
       </c>
       <c r="H227">
         <v>0</v>
@@ -8237,25 +8099,25 @@
         <v>0</v>
       </c>
       <c r="B228" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="C228">
         <v>1</v>
       </c>
       <c r="D228" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E228" t="s">
-        <v>365</v>
+        <v>176</v>
       </c>
       <c r="F228" s="1">
         <v>46252</v>
       </c>
       <c r="G228" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="H228">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="229" spans="1:8" x14ac:dyDescent="0.2">
@@ -8263,16 +8125,16 @@
         <v>0</v>
       </c>
       <c r="B229" t="s">
-        <v>366</v>
+        <v>356</v>
       </c>
       <c r="C229">
         <v>1</v>
       </c>
       <c r="D229" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E229" t="s">
-        <v>367</v>
+        <v>178</v>
       </c>
       <c r="F229" s="1">
         <v>46252</v>
@@ -8281,7 +8143,7 @@
         <v>46252</v>
       </c>
       <c r="H229">
-        <v>0</v>
+        <v>21</v>
       </c>
     </row>
     <row r="230" spans="1:8" x14ac:dyDescent="0.2">
@@ -8289,16 +8151,16 @@
         <v>0</v>
       </c>
       <c r="B230" t="s">
-        <v>368</v>
+        <v>357</v>
       </c>
       <c r="C230">
         <v>1</v>
       </c>
       <c r="D230" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E230" t="s">
-        <v>367</v>
+        <v>15</v>
       </c>
       <c r="F230" s="1">
         <v>46252</v>
@@ -8307,7 +8169,7 @@
         <v>46252</v>
       </c>
       <c r="H230">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="231" spans="1:8" x14ac:dyDescent="0.2">
@@ -8315,7 +8177,7 @@
         <v>0</v>
       </c>
       <c r="B231" t="s">
-        <v>369</v>
+        <v>358</v>
       </c>
       <c r="C231">
         <v>1</v>
@@ -8324,7 +8186,7 @@
         <v>12</v>
       </c>
       <c r="E231" t="s">
-        <v>72</v>
+        <v>359</v>
       </c>
       <c r="F231" s="1">
         <v>46252</v>
@@ -8341,16 +8203,16 @@
         <v>0</v>
       </c>
       <c r="B232" t="s">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="C232">
         <v>1</v>
       </c>
       <c r="D232" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E232" t="s">
-        <v>33</v>
+        <v>134</v>
       </c>
       <c r="F232" s="1">
         <v>46252</v>
@@ -8359,7 +8221,7 @@
         <v>46252</v>
       </c>
       <c r="H232">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="233" spans="1:8" x14ac:dyDescent="0.2">
@@ -8367,16 +8229,16 @@
         <v>0</v>
       </c>
       <c r="B233" t="s">
-        <v>371</v>
+        <v>361</v>
       </c>
       <c r="C233">
         <v>1</v>
       </c>
       <c r="D233" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E233" t="s">
-        <v>240</v>
+        <v>134</v>
       </c>
       <c r="F233" s="1">
         <v>46252</v>
@@ -8385,7 +8247,7 @@
         <v>46252</v>
       </c>
       <c r="H233">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="234" spans="1:8" x14ac:dyDescent="0.2">
@@ -8393,25 +8255,25 @@
         <v>0</v>
       </c>
       <c r="B234" t="s">
-        <v>372</v>
+        <v>362</v>
       </c>
       <c r="C234">
         <v>1</v>
       </c>
       <c r="D234" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E234" t="s">
-        <v>373</v>
+        <v>363</v>
       </c>
       <c r="F234" s="1">
         <v>46252</v>
       </c>
       <c r="G234" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="H234">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="235" spans="1:8" x14ac:dyDescent="0.2">
@@ -8419,25 +8281,25 @@
         <v>0</v>
       </c>
       <c r="B235" t="s">
-        <v>374</v>
+        <v>364</v>
       </c>
       <c r="C235">
         <v>1</v>
       </c>
       <c r="D235" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E235" t="s">
-        <v>270</v>
+        <v>365</v>
       </c>
       <c r="F235" s="1">
         <v>46252</v>
       </c>
       <c r="G235" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="H235">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="236" spans="1:8" x14ac:dyDescent="0.2">
@@ -8445,25 +8307,25 @@
         <v>0</v>
       </c>
       <c r="B236" t="s">
-        <v>375</v>
+        <v>366</v>
       </c>
       <c r="C236">
         <v>1</v>
       </c>
       <c r="D236" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E236" t="s">
-        <v>66</v>
+        <v>367</v>
       </c>
       <c r="F236" s="1">
         <v>46252</v>
       </c>
       <c r="G236" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="H236">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="237" spans="1:8" x14ac:dyDescent="0.2">
@@ -8471,7 +8333,7 @@
         <v>0</v>
       </c>
       <c r="B237" t="s">
-        <v>376</v>
+        <v>368</v>
       </c>
       <c r="C237">
         <v>1</v>
@@ -8480,16 +8342,16 @@
         <v>2</v>
       </c>
       <c r="E237" t="s">
-        <v>13</v>
+        <v>253</v>
       </c>
       <c r="F237" s="1">
         <v>46252</v>
       </c>
       <c r="G237" s="1">
-        <v>46252</v>
+        <v>46254</v>
       </c>
       <c r="H237">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="238" spans="1:8" x14ac:dyDescent="0.2">
@@ -8497,7 +8359,7 @@
         <v>0</v>
       </c>
       <c r="B238" t="s">
-        <v>377</v>
+        <v>369</v>
       </c>
       <c r="C238">
         <v>1</v>
@@ -8506,7 +8368,7 @@
         <v>2</v>
       </c>
       <c r="E238" t="s">
-        <v>13</v>
+        <v>323</v>
       </c>
       <c r="F238" s="1">
         <v>46252</v>
@@ -8523,25 +8385,25 @@
         <v>0</v>
       </c>
       <c r="B239" t="s">
-        <v>378</v>
+        <v>370</v>
       </c>
       <c r="C239">
         <v>1</v>
       </c>
       <c r="D239" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E239" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="F239" s="1">
         <v>46252</v>
       </c>
       <c r="G239" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="H239">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="240" spans="1:8" x14ac:dyDescent="0.2">
@@ -8549,25 +8411,25 @@
         <v>0</v>
       </c>
       <c r="B240" t="s">
-        <v>379</v>
+        <v>372</v>
       </c>
       <c r="C240">
         <v>1</v>
       </c>
       <c r="D240" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E240" t="s">
-        <v>13</v>
+        <v>373</v>
       </c>
       <c r="F240" s="1">
         <v>46252</v>
       </c>
       <c r="G240" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="H240">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="241" spans="1:8" x14ac:dyDescent="0.2">
@@ -8575,7 +8437,7 @@
         <v>0</v>
       </c>
       <c r="B241" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
       <c r="C241">
         <v>1</v>
@@ -8584,13 +8446,13 @@
         <v>12</v>
       </c>
       <c r="E241" t="s">
-        <v>55</v>
+        <v>373</v>
       </c>
       <c r="F241" s="1">
         <v>46252</v>
       </c>
       <c r="G241" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="H241">
         <v>0</v>
@@ -8601,7 +8463,7 @@
         <v>0</v>
       </c>
       <c r="B242" t="s">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="C242">
         <v>1</v>
@@ -8610,16 +8472,16 @@
         <v>2</v>
       </c>
       <c r="E242" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="F242" s="1">
         <v>46252</v>
       </c>
       <c r="G242" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="H242">
-        <v>3</v>
+        <v>33</v>
       </c>
     </row>
     <row r="243" spans="1:8" x14ac:dyDescent="0.2">
@@ -8627,25 +8489,25 @@
         <v>0</v>
       </c>
       <c r="B243" t="s">
-        <v>383</v>
+        <v>377</v>
       </c>
       <c r="C243">
         <v>1</v>
       </c>
       <c r="D243" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E243" t="s">
-        <v>70</v>
+        <v>378</v>
       </c>
       <c r="F243" s="1">
         <v>46252</v>
       </c>
       <c r="G243" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="H243">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="244" spans="1:8" x14ac:dyDescent="0.2">
@@ -8653,7 +8515,7 @@
         <v>0</v>
       </c>
       <c r="B244" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="C244">
         <v>1</v>
@@ -8662,13 +8524,13 @@
         <v>12</v>
       </c>
       <c r="E244" t="s">
-        <v>385</v>
+        <v>219</v>
       </c>
       <c r="F244" s="1">
         <v>46252</v>
       </c>
       <c r="G244" s="1">
-        <v>46252</v>
+        <v>46254</v>
       </c>
       <c r="H244">
         <v>0</v>
@@ -8679,7 +8541,7 @@
         <v>0</v>
       </c>
       <c r="B245" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="C245">
         <v>1</v>
@@ -8688,7 +8550,7 @@
         <v>12</v>
       </c>
       <c r="E245" t="s">
-        <v>85</v>
+        <v>219</v>
       </c>
       <c r="F245" s="1">
         <v>46252</v>
@@ -8705,7 +8567,7 @@
         <v>0</v>
       </c>
       <c r="B246" t="s">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="C246">
         <v>1</v>
@@ -8714,13 +8576,13 @@
         <v>12</v>
       </c>
       <c r="E246" t="s">
-        <v>283</v>
+        <v>136</v>
       </c>
       <c r="F246" s="1">
         <v>46252</v>
       </c>
       <c r="G246" s="1">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="H246">
         <v>0</v>
@@ -8731,25 +8593,25 @@
         <v>0</v>
       </c>
       <c r="B247" t="s">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="C247">
         <v>1</v>
       </c>
       <c r="D247" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E247" t="s">
-        <v>389</v>
+        <v>136</v>
       </c>
       <c r="F247" s="1">
         <v>46252</v>
       </c>
       <c r="G247" s="1">
-        <v>46252</v>
+        <v>46254</v>
       </c>
       <c r="H247">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="248" spans="1:8" x14ac:dyDescent="0.2">
@@ -8757,7 +8619,7 @@
         <v>0</v>
       </c>
       <c r="B248" t="s">
-        <v>390</v>
+        <v>383</v>
       </c>
       <c r="C248">
         <v>1</v>
@@ -8766,13 +8628,13 @@
         <v>12</v>
       </c>
       <c r="E248" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="F248" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="G248" s="1">
-        <v>46254</v>
+        <v>46253</v>
       </c>
       <c r="H248">
         <v>0</v>
@@ -8783,25 +8645,25 @@
         <v>0</v>
       </c>
       <c r="B249" t="s">
-        <v>391</v>
+        <v>384</v>
       </c>
       <c r="C249">
         <v>1</v>
       </c>
       <c r="D249" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E249" t="s">
-        <v>176</v>
+        <v>167</v>
       </c>
       <c r="F249" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="G249" s="1">
         <v>46253</v>
       </c>
       <c r="H249">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="250" spans="1:8" x14ac:dyDescent="0.2">
@@ -8809,25 +8671,25 @@
         <v>0</v>
       </c>
       <c r="B250" t="s">
-        <v>392</v>
+        <v>385</v>
       </c>
       <c r="C250">
         <v>1</v>
       </c>
       <c r="D250" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E250" t="s">
-        <v>393</v>
+        <v>386</v>
       </c>
       <c r="F250" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="G250" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="H250">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="251" spans="1:8" x14ac:dyDescent="0.2">
@@ -8835,25 +8697,25 @@
         <v>0</v>
       </c>
       <c r="B251" t="s">
-        <v>394</v>
+        <v>387</v>
       </c>
       <c r="C251">
         <v>1</v>
       </c>
       <c r="D251" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E251" t="s">
-        <v>178</v>
+        <v>388</v>
       </c>
       <c r="F251" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="G251" s="1">
-        <v>46252</v>
+        <v>46254</v>
       </c>
       <c r="H251">
-        <v>21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="252" spans="1:8" x14ac:dyDescent="0.2">
@@ -8861,25 +8723,25 @@
         <v>0</v>
       </c>
       <c r="B252" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="C252">
         <v>1</v>
       </c>
       <c r="D252" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E252" t="s">
-        <v>15</v>
+        <v>390</v>
       </c>
       <c r="F252" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="G252" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="H252">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="253" spans="1:8" x14ac:dyDescent="0.2">
@@ -8887,22 +8749,22 @@
         <v>0</v>
       </c>
       <c r="B253" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="C253">
         <v>1</v>
       </c>
       <c r="D253" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E253" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="F253" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="G253" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="H253">
         <v>0</v>
@@ -8913,7 +8775,7 @@
         <v>0</v>
       </c>
       <c r="B254" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="C254">
         <v>1</v>
@@ -8922,13 +8784,13 @@
         <v>12</v>
       </c>
       <c r="E254" t="s">
-        <v>134</v>
+        <v>27</v>
       </c>
       <c r="F254" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="G254" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="H254">
         <v>0</v>
@@ -8939,25 +8801,25 @@
         <v>0</v>
       </c>
       <c r="B255" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="C255">
         <v>1</v>
       </c>
       <c r="D255" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E255" t="s">
-        <v>134</v>
+        <v>27</v>
       </c>
       <c r="F255" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="G255" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="H255">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="256" spans="1:8" x14ac:dyDescent="0.2">
@@ -8965,7 +8827,7 @@
         <v>0</v>
       </c>
       <c r="B256" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="C256">
         <v>1</v>
@@ -8974,16 +8836,16 @@
         <v>2</v>
       </c>
       <c r="E256" t="s">
-        <v>401</v>
+        <v>27</v>
       </c>
       <c r="F256" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="G256" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="H256">
-        <v>24</v>
+        <v>2</v>
       </c>
     </row>
     <row r="257" spans="1:8" x14ac:dyDescent="0.2">
@@ -8991,25 +8853,25 @@
         <v>0</v>
       </c>
       <c r="B257" t="s">
-        <v>402</v>
+        <v>396</v>
       </c>
       <c r="C257">
         <v>1</v>
       </c>
       <c r="D257" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E257" t="s">
-        <v>403</v>
+        <v>271</v>
       </c>
       <c r="F257" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="G257" s="1">
         <v>46253</v>
       </c>
       <c r="H257">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="258" spans="1:8" x14ac:dyDescent="0.2">
@@ -9017,7 +8879,7 @@
         <v>0</v>
       </c>
       <c r="B258" t="s">
-        <v>404</v>
+        <v>397</v>
       </c>
       <c r="C258">
         <v>1</v>
@@ -9026,16 +8888,16 @@
         <v>2</v>
       </c>
       <c r="E258" t="s">
-        <v>405</v>
+        <v>124</v>
       </c>
       <c r="F258" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="G258" s="1">
         <v>46253</v>
       </c>
       <c r="H258">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="259" spans="1:8" x14ac:dyDescent="0.2">
@@ -9043,7 +8905,7 @@
         <v>0</v>
       </c>
       <c r="B259" t="s">
-        <v>406</v>
+        <v>398</v>
       </c>
       <c r="C259">
         <v>1</v>
@@ -9052,16 +8914,16 @@
         <v>2</v>
       </c>
       <c r="E259" t="s">
-        <v>296</v>
+        <v>124</v>
       </c>
       <c r="F259" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="G259" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="H259">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="260" spans="1:8" x14ac:dyDescent="0.2">
@@ -9069,25 +8931,25 @@
         <v>0</v>
       </c>
       <c r="B260" t="s">
-        <v>407</v>
+        <v>399</v>
       </c>
       <c r="C260">
         <v>1</v>
       </c>
       <c r="D260" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E260" t="s">
-        <v>408</v>
+        <v>13</v>
       </c>
       <c r="F260" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="G260" s="1">
         <v>46253</v>
       </c>
       <c r="H260">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="261" spans="1:8" x14ac:dyDescent="0.2">
@@ -9095,25 +8957,25 @@
         <v>0</v>
       </c>
       <c r="B261" t="s">
-        <v>409</v>
+        <v>400</v>
       </c>
       <c r="C261">
         <v>1</v>
       </c>
       <c r="D261" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E261" t="s">
-        <v>255</v>
+        <v>401</v>
       </c>
       <c r="F261" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="G261" s="1">
-        <v>46254</v>
+        <v>46253</v>
       </c>
       <c r="H261">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="262" spans="1:8" x14ac:dyDescent="0.2">
@@ -9121,25 +8983,25 @@
         <v>0</v>
       </c>
       <c r="B262" t="s">
-        <v>410</v>
+        <v>402</v>
       </c>
       <c r="C262">
         <v>1</v>
       </c>
       <c r="D262" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E262" t="s">
-        <v>335</v>
+        <v>66</v>
       </c>
       <c r="F262" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="G262" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="H262">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="263" spans="1:8" x14ac:dyDescent="0.2">
@@ -9147,25 +9009,25 @@
         <v>0</v>
       </c>
       <c r="B263" t="s">
-        <v>411</v>
+        <v>403</v>
       </c>
       <c r="C263">
         <v>1</v>
       </c>
       <c r="D263" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E263" t="s">
-        <v>412</v>
+        <v>146</v>
       </c>
       <c r="F263" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="G263" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="H263">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="264" spans="1:8" x14ac:dyDescent="0.2">
@@ -9173,25 +9035,25 @@
         <v>0</v>
       </c>
       <c r="B264" t="s">
-        <v>413</v>
+        <v>404</v>
       </c>
       <c r="C264">
         <v>1</v>
       </c>
       <c r="D264" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E264" t="s">
-        <v>414</v>
+        <v>405</v>
       </c>
       <c r="F264" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="G264" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="H264">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="265" spans="1:8" x14ac:dyDescent="0.2">
@@ -9199,25 +9061,25 @@
         <v>0</v>
       </c>
       <c r="B265" t="s">
-        <v>415</v>
+        <v>406</v>
       </c>
       <c r="C265">
         <v>1</v>
       </c>
       <c r="D265" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E265" t="s">
-        <v>414</v>
+        <v>407</v>
       </c>
       <c r="F265" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="G265" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="H265">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="266" spans="1:8" x14ac:dyDescent="0.2">
@@ -9225,7 +9087,7 @@
         <v>0</v>
       </c>
       <c r="B266" t="s">
-        <v>416</v>
+        <v>408</v>
       </c>
       <c r="C266">
         <v>1</v>
@@ -9234,10 +9096,10 @@
         <v>12</v>
       </c>
       <c r="E266" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="F266" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="G266" s="1">
         <v>46253</v>
@@ -9251,25 +9113,25 @@
         <v>0</v>
       </c>
       <c r="B267" t="s">
-        <v>417</v>
+        <v>410</v>
       </c>
       <c r="C267">
         <v>1</v>
       </c>
       <c r="D267" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E267" t="s">
-        <v>192</v>
+        <v>411</v>
       </c>
       <c r="F267" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="G267" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="H267">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="268" spans="1:8" x14ac:dyDescent="0.2">
@@ -9277,25 +9139,25 @@
         <v>0</v>
       </c>
       <c r="B268" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="C268">
         <v>1</v>
       </c>
       <c r="D268" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E268" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="F268" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="G268" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="H268">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="269" spans="1:8" x14ac:dyDescent="0.2">
@@ -9303,25 +9165,25 @@
         <v>0</v>
       </c>
       <c r="B269" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="C269">
         <v>1</v>
       </c>
       <c r="D269" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E269" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="F269" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="G269" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="H269">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="270" spans="1:8" x14ac:dyDescent="0.2">
@@ -9329,25 +9191,25 @@
         <v>0</v>
       </c>
       <c r="B270" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="C270">
         <v>1</v>
       </c>
       <c r="D270" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E270" t="s">
-        <v>414</v>
+        <v>359</v>
       </c>
       <c r="F270" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="G270" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="H270">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="271" spans="1:8" x14ac:dyDescent="0.2">
@@ -9355,25 +9217,25 @@
         <v>0</v>
       </c>
       <c r="B271" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="C271">
         <v>1</v>
       </c>
       <c r="D271" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E271" t="s">
-        <v>422</v>
+        <v>122</v>
       </c>
       <c r="F271" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="G271" s="1">
         <v>46253</v>
       </c>
       <c r="H271">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="272" spans="1:8" x14ac:dyDescent="0.2">
@@ -9381,7 +9243,7 @@
         <v>0</v>
       </c>
       <c r="B272" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="C272">
         <v>1</v>
@@ -9390,10 +9252,10 @@
         <v>12</v>
       </c>
       <c r="E272" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="F272" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="G272" s="1">
         <v>46253</v>
@@ -9407,25 +9269,25 @@
         <v>0</v>
       </c>
       <c r="B273" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="C273">
         <v>1</v>
       </c>
       <c r="D273" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E273" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="F273" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="G273" s="1">
         <v>46253</v>
       </c>
       <c r="H273">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="274" spans="1:8" x14ac:dyDescent="0.2">
@@ -9433,7 +9295,7 @@
         <v>0</v>
       </c>
       <c r="B274" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="C274">
         <v>1</v>
@@ -9442,16 +9304,16 @@
         <v>2</v>
       </c>
       <c r="E274" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="F274" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="G274" s="1">
         <v>46253</v>
       </c>
       <c r="H274">
-        <v>33</v>
+        <v>4</v>
       </c>
     </row>
     <row r="275" spans="1:8" x14ac:dyDescent="0.2">
@@ -9459,7 +9321,7 @@
         <v>0</v>
       </c>
       <c r="B275" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="C275">
         <v>1</v>
@@ -9468,10 +9330,10 @@
         <v>12</v>
       </c>
       <c r="E275" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="F275" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="G275" s="1">
         <v>46253</v>
@@ -9485,25 +9347,25 @@
         <v>0</v>
       </c>
       <c r="B276" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="C276">
         <v>1</v>
       </c>
       <c r="D276" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E276" t="s">
-        <v>219</v>
+        <v>323</v>
       </c>
       <c r="F276" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="G276" s="1">
-        <v>46254</v>
+        <v>46253</v>
       </c>
       <c r="H276">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="277" spans="1:8" x14ac:dyDescent="0.2">
@@ -9511,7 +9373,7 @@
         <v>0</v>
       </c>
       <c r="B277" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="C277">
         <v>1</v>
@@ -9520,13 +9382,13 @@
         <v>12</v>
       </c>
       <c r="E277" t="s">
-        <v>219</v>
+        <v>17</v>
       </c>
       <c r="F277" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="G277" s="1">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="H277">
         <v>0</v>
@@ -9537,7 +9399,7 @@
         <v>0</v>
       </c>
       <c r="B278" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="C278">
         <v>1</v>
@@ -9546,13 +9408,13 @@
         <v>12</v>
       </c>
       <c r="E278" t="s">
-        <v>136</v>
+        <v>429</v>
       </c>
       <c r="F278" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="G278" s="1">
-        <v>46254</v>
+        <v>46253</v>
       </c>
       <c r="H278">
         <v>0</v>
@@ -9563,7 +9425,7 @@
         <v>0</v>
       </c>
       <c r="B279" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="C279">
         <v>1</v>
@@ -9572,13 +9434,13 @@
         <v>12</v>
       </c>
       <c r="E279" t="s">
-        <v>136</v>
+        <v>431</v>
       </c>
       <c r="F279" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="G279" s="1">
-        <v>46254</v>
+        <v>46253</v>
       </c>
       <c r="H279">
         <v>0</v>
@@ -9589,7 +9451,7 @@
         <v>0</v>
       </c>
       <c r="B280" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C280">
         <v>1</v>
@@ -9598,7 +9460,7 @@
         <v>12</v>
       </c>
       <c r="E280" t="s">
-        <v>167</v>
+        <v>141</v>
       </c>
       <c r="F280" s="1">
         <v>46253</v>
@@ -9615,16 +9477,16 @@
         <v>0</v>
       </c>
       <c r="B281" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="C281">
         <v>1</v>
       </c>
       <c r="D281" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E281" t="s">
-        <v>167</v>
+        <v>434</v>
       </c>
       <c r="F281" s="1">
         <v>46253</v>
@@ -9633,7 +9495,7 @@
         <v>46253</v>
       </c>
       <c r="H281">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="282" spans="1:8" x14ac:dyDescent="0.2">
@@ -9641,7 +9503,7 @@
         <v>0</v>
       </c>
       <c r="B282" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C282">
         <v>1</v>
@@ -9650,7 +9512,7 @@
         <v>12</v>
       </c>
       <c r="E282" t="s">
-        <v>437</v>
+        <v>359</v>
       </c>
       <c r="F282" s="1">
         <v>46253</v>
@@ -9667,7 +9529,7 @@
         <v>0</v>
       </c>
       <c r="B283" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C283">
         <v>1</v>
@@ -9676,13 +9538,13 @@
         <v>12</v>
       </c>
       <c r="E283" t="s">
-        <v>439</v>
+        <v>27</v>
       </c>
       <c r="F283" s="1">
         <v>46253</v>
       </c>
       <c r="G283" s="1">
-        <v>46254</v>
+        <v>46253</v>
       </c>
       <c r="H283">
         <v>0</v>
@@ -9693,7 +9555,7 @@
         <v>0</v>
       </c>
       <c r="B284" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="C284">
         <v>1</v>
@@ -9702,7 +9564,7 @@
         <v>12</v>
       </c>
       <c r="E284" t="s">
-        <v>441</v>
+        <v>27</v>
       </c>
       <c r="F284" s="1">
         <v>46253</v>
@@ -9719,16 +9581,16 @@
         <v>0</v>
       </c>
       <c r="B285" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="C285">
         <v>1</v>
       </c>
       <c r="D285" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E285" t="s">
-        <v>443</v>
+        <v>27</v>
       </c>
       <c r="F285" s="1">
         <v>46253</v>
@@ -9745,7 +9607,7 @@
         <v>0</v>
       </c>
       <c r="B286" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="C286">
         <v>1</v>
@@ -9771,7 +9633,7 @@
         <v>0</v>
       </c>
       <c r="B287" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="C287">
         <v>1</v>
@@ -9797,13 +9659,13 @@
         <v>0</v>
       </c>
       <c r="B288" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="C288">
         <v>1</v>
       </c>
       <c r="D288" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E288" t="s">
         <v>27</v>
@@ -9815,7 +9677,7 @@
         <v>46253</v>
       </c>
       <c r="H288">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="289" spans="1:8" x14ac:dyDescent="0.2">
@@ -9823,16 +9685,16 @@
         <v>0</v>
       </c>
       <c r="B289" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="C289">
         <v>1</v>
       </c>
       <c r="D289" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E289" t="s">
-        <v>274</v>
+        <v>27</v>
       </c>
       <c r="F289" s="1">
         <v>46253</v>
@@ -9841,7 +9703,7 @@
         <v>46253</v>
       </c>
       <c r="H289">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="290" spans="1:8" x14ac:dyDescent="0.2">
@@ -9849,16 +9711,16 @@
         <v>0</v>
       </c>
       <c r="B290" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="C290">
         <v>1</v>
       </c>
       <c r="D290" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E290" t="s">
-        <v>124</v>
+        <v>27</v>
       </c>
       <c r="F290" s="1">
         <v>46253</v>
@@ -9867,7 +9729,7 @@
         <v>46253</v>
       </c>
       <c r="H290">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="291" spans="1:8" x14ac:dyDescent="0.2">
@@ -9875,16 +9737,16 @@
         <v>0</v>
       </c>
       <c r="B291" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
       <c r="C291">
         <v>1</v>
       </c>
       <c r="D291" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E291" t="s">
-        <v>124</v>
+        <v>445</v>
       </c>
       <c r="F291" s="1">
         <v>46253</v>
@@ -9893,7 +9755,7 @@
         <v>46253</v>
       </c>
       <c r="H291">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="292" spans="1:8" x14ac:dyDescent="0.2">
@@ -9901,16 +9763,16 @@
         <v>0</v>
       </c>
       <c r="B292" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="C292">
         <v>1</v>
       </c>
       <c r="D292" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E292" t="s">
-        <v>57</v>
+        <v>447</v>
       </c>
       <c r="F292" s="1">
         <v>46253</v>
@@ -9919,7 +9781,7 @@
         <v>46253</v>
       </c>
       <c r="H292">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="293" spans="1:8" x14ac:dyDescent="0.2">
@@ -9927,7 +9789,7 @@
         <v>0</v>
       </c>
       <c r="B293" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="C293">
         <v>1</v>
@@ -9936,7 +9798,7 @@
         <v>12</v>
       </c>
       <c r="E293" t="s">
-        <v>13</v>
+        <v>449</v>
       </c>
       <c r="F293" s="1">
         <v>46253</v>
@@ -9953,16 +9815,16 @@
         <v>0</v>
       </c>
       <c r="B294" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="C294">
         <v>1</v>
       </c>
       <c r="D294" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E294" t="s">
-        <v>10</v>
+        <v>451</v>
       </c>
       <c r="F294" s="1">
         <v>46253</v>
@@ -9971,7 +9833,7 @@
         <v>46253</v>
       </c>
       <c r="H294">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="295" spans="1:8" x14ac:dyDescent="0.2">
@@ -9979,17 +9841,17 @@
         <v>0</v>
       </c>
       <c r="B295" t="s">
+        <v>452</v>
+      </c>
+      <c r="C295">
+        <v>1</v>
+      </c>
+      <c r="D295" t="s">
+        <v>12</v>
+      </c>
+      <c r="E295" t="s">
         <v>453</v>
       </c>
-      <c r="C295">
-        <v>1</v>
-      </c>
-      <c r="D295" t="s">
-        <v>2</v>
-      </c>
-      <c r="E295" t="s">
-        <v>454</v>
-      </c>
       <c r="F295" s="1">
         <v>46253</v>
       </c>
@@ -9997,7 +9859,7 @@
         <v>46253</v>
       </c>
       <c r="H295">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="296" spans="1:8" x14ac:dyDescent="0.2">
@@ -10005,7 +9867,7 @@
         <v>0</v>
       </c>
       <c r="B296" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C296">
         <v>1</v>
@@ -10014,7 +9876,7 @@
         <v>12</v>
       </c>
       <c r="E296" t="s">
-        <v>66</v>
+        <v>388</v>
       </c>
       <c r="F296" s="1">
         <v>46253</v>
@@ -10031,25 +9893,25 @@
         <v>0</v>
       </c>
       <c r="B297" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C297">
         <v>1</v>
       </c>
       <c r="D297" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E297" t="s">
-        <v>146</v>
+        <v>300</v>
       </c>
       <c r="F297" s="1">
         <v>46253</v>
       </c>
       <c r="G297" s="1">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="H297">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="298" spans="1:8" x14ac:dyDescent="0.2">
@@ -10057,22 +9919,22 @@
         <v>0</v>
       </c>
       <c r="B298" t="s">
+        <v>456</v>
+      </c>
+      <c r="C298">
+        <v>1</v>
+      </c>
+      <c r="D298" t="s">
+        <v>12</v>
+      </c>
+      <c r="E298" t="s">
         <v>457</v>
       </c>
-      <c r="C298">
-        <v>1</v>
-      </c>
-      <c r="D298" t="s">
-        <v>12</v>
-      </c>
-      <c r="E298" t="s">
-        <v>458</v>
-      </c>
       <c r="F298" s="1">
         <v>46253</v>
       </c>
       <c r="G298" s="1">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="H298">
         <v>0</v>
@@ -10083,7 +9945,7 @@
         <v>0</v>
       </c>
       <c r="B299" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C299">
         <v>1</v>
@@ -10092,13 +9954,13 @@
         <v>12</v>
       </c>
       <c r="E299" t="s">
-        <v>460</v>
+        <v>21</v>
       </c>
       <c r="F299" s="1">
         <v>46253</v>
       </c>
       <c r="G299" s="1">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="H299">
         <v>0</v>
@@ -10109,7 +9971,7 @@
         <v>0</v>
       </c>
       <c r="B300" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="C300">
         <v>1</v>
@@ -10118,13 +9980,13 @@
         <v>12</v>
       </c>
       <c r="E300" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="F300" s="1">
         <v>46253</v>
       </c>
       <c r="G300" s="1">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="H300">
         <v>0</v>
@@ -10135,7 +9997,7 @@
         <v>0</v>
       </c>
       <c r="B301" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="C301">
         <v>1</v>
@@ -10144,13 +10006,13 @@
         <v>12</v>
       </c>
       <c r="E301" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="F301" s="1">
         <v>46253</v>
       </c>
       <c r="G301" s="1">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="H301">
         <v>0</v>
@@ -10161,25 +10023,25 @@
         <v>0</v>
       </c>
       <c r="B302" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="C302">
         <v>1</v>
       </c>
       <c r="D302" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E302" t="s">
-        <v>292</v>
+        <v>463</v>
       </c>
       <c r="F302" s="1">
         <v>46253</v>
       </c>
       <c r="G302" s="1">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="H302">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="303" spans="1:8" x14ac:dyDescent="0.2">
@@ -10187,7 +10049,7 @@
         <v>0</v>
       </c>
       <c r="B303" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="C303">
         <v>1</v>
@@ -10196,13 +10058,13 @@
         <v>12</v>
       </c>
       <c r="E303" t="s">
-        <v>467</v>
+        <v>53</v>
       </c>
       <c r="F303" s="1">
         <v>46253</v>
       </c>
       <c r="G303" s="1">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="H303">
         <v>0</v>
@@ -10213,7 +10075,7 @@
         <v>0</v>
       </c>
       <c r="B304" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="C304">
         <v>1</v>
@@ -10222,13 +10084,13 @@
         <v>12</v>
       </c>
       <c r="E304" t="s">
-        <v>469</v>
+        <v>53</v>
       </c>
       <c r="F304" s="1">
         <v>46253</v>
       </c>
       <c r="G304" s="1">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="H304">
         <v>0</v>
@@ -10239,7 +10101,7 @@
         <v>0</v>
       </c>
       <c r="B305" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="C305">
         <v>1</v>
@@ -10248,13 +10110,13 @@
         <v>12</v>
       </c>
       <c r="E305" t="s">
-        <v>397</v>
+        <v>53</v>
       </c>
       <c r="F305" s="1">
         <v>46253</v>
       </c>
       <c r="G305" s="1">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="H305">
         <v>0</v>
@@ -10265,7 +10127,7 @@
         <v>0</v>
       </c>
       <c r="B306" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="C306">
         <v>1</v>
@@ -10274,13 +10136,13 @@
         <v>12</v>
       </c>
       <c r="E306" t="s">
-        <v>122</v>
+        <v>19</v>
       </c>
       <c r="F306" s="1">
         <v>46253</v>
       </c>
       <c r="G306" s="1">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="H306">
         <v>0</v>
@@ -10291,7 +10153,7 @@
         <v>0</v>
       </c>
       <c r="B307" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="C307">
         <v>1</v>
@@ -10300,13 +10162,13 @@
         <v>12</v>
       </c>
       <c r="E307" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="F307" s="1">
         <v>46253</v>
       </c>
       <c r="G307" s="1">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="H307">
         <v>0</v>
@@ -10317,25 +10179,25 @@
         <v>0</v>
       </c>
       <c r="B308" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="C308">
         <v>1</v>
       </c>
       <c r="D308" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E308" t="s">
-        <v>296</v>
+        <v>471</v>
       </c>
       <c r="F308" s="1">
         <v>46253</v>
       </c>
       <c r="G308" s="1">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="H308">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="309" spans="1:8" x14ac:dyDescent="0.2">
@@ -10343,7 +10205,7 @@
         <v>0</v>
       </c>
       <c r="B309" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="C309">
         <v>1</v>
@@ -10352,13 +10214,13 @@
         <v>12</v>
       </c>
       <c r="E309" t="s">
-        <v>476</v>
+        <v>309</v>
       </c>
       <c r="F309" s="1">
         <v>46253</v>
       </c>
       <c r="G309" s="1">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="H309">
         <v>0</v>
@@ -10369,25 +10231,25 @@
         <v>0</v>
       </c>
       <c r="B310" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="C310">
         <v>1</v>
       </c>
       <c r="D310" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E310" t="s">
-        <v>478</v>
+        <v>134</v>
       </c>
       <c r="F310" s="1">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="G310" s="1">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="H310">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="311" spans="1:8" x14ac:dyDescent="0.2">
@@ -10395,7 +10257,7 @@
         <v>0</v>
       </c>
       <c r="B311" t="s">
-        <v>479</v>
+        <v>474</v>
       </c>
       <c r="C311">
         <v>1</v>
@@ -10404,13 +10266,13 @@
         <v>12</v>
       </c>
       <c r="E311" t="s">
-        <v>323</v>
+        <v>70</v>
       </c>
       <c r="F311" s="1">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="G311" s="1">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="H311">
         <v>0</v>
@@ -10421,25 +10283,25 @@
         <v>0</v>
       </c>
       <c r="B312" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="C312">
         <v>1</v>
       </c>
       <c r="D312" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E312" t="s">
-        <v>335</v>
+        <v>476</v>
       </c>
       <c r="F312" s="1">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="G312" s="1">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="H312">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="313" spans="1:8" x14ac:dyDescent="0.2">
@@ -10447,25 +10309,25 @@
         <v>0</v>
       </c>
       <c r="B313" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="C313">
         <v>1</v>
       </c>
       <c r="D313" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E313" t="s">
-        <v>17</v>
+        <v>478</v>
       </c>
       <c r="F313" s="1">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="G313" s="1">
         <v>46254</v>
       </c>
       <c r="H313">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="314" spans="1:8" x14ac:dyDescent="0.2">
@@ -10473,7 +10335,7 @@
         <v>0</v>
       </c>
       <c r="B314" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="C314">
         <v>1</v>
@@ -10482,13 +10344,13 @@
         <v>12</v>
       </c>
       <c r="E314" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="F314" s="1">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="G314" s="1">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="H314">
         <v>0</v>
@@ -10499,7 +10361,7 @@
         <v>0</v>
       </c>
       <c r="B315" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="C315">
         <v>1</v>
@@ -10508,13 +10370,13 @@
         <v>12</v>
       </c>
       <c r="E315" t="s">
-        <v>485</v>
+        <v>124</v>
       </c>
       <c r="F315" s="1">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="G315" s="1">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="H315">
         <v>0</v>
@@ -10525,7 +10387,7 @@
         <v>0</v>
       </c>
       <c r="B316" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="C316">
         <v>1</v>
@@ -10534,13 +10396,13 @@
         <v>12</v>
       </c>
       <c r="E316" t="s">
-        <v>141</v>
+        <v>27</v>
       </c>
       <c r="F316" s="1">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="G316" s="1">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="H316">
         <v>0</v>
@@ -10551,25 +10413,25 @@
         <v>0</v>
       </c>
       <c r="B317" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="C317">
         <v>1</v>
       </c>
       <c r="D317" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E317" t="s">
-        <v>488</v>
+        <v>27</v>
       </c>
       <c r="F317" s="1">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="G317" s="1">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="H317">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="318" spans="1:8" x14ac:dyDescent="0.2">
@@ -10577,7 +10439,7 @@
         <v>0</v>
       </c>
       <c r="B318" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="C318">
         <v>1</v>
@@ -10586,13 +10448,13 @@
         <v>12</v>
       </c>
       <c r="E318" t="s">
-        <v>397</v>
+        <v>27</v>
       </c>
       <c r="F318" s="1">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="G318" s="1">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="H318">
         <v>0</v>
@@ -10603,25 +10465,25 @@
         <v>0</v>
       </c>
       <c r="B319" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="C319">
         <v>1</v>
       </c>
       <c r="D319" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E319" t="s">
-        <v>382</v>
+        <v>486</v>
       </c>
       <c r="F319" s="1">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="G319" s="1">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="H319">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="320" spans="1:8" x14ac:dyDescent="0.2">
@@ -10629,7 +10491,7 @@
         <v>0</v>
       </c>
       <c r="B320" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="C320">
         <v>1</v>
@@ -10638,13 +10500,13 @@
         <v>12</v>
       </c>
       <c r="E320" t="s">
-        <v>27</v>
+        <v>486</v>
       </c>
       <c r="F320" s="1">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="G320" s="1">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="H320">
         <v>0</v>
@@ -10655,7 +10517,7 @@
         <v>0</v>
       </c>
       <c r="B321" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="C321">
         <v>1</v>
@@ -10664,13 +10526,13 @@
         <v>12</v>
       </c>
       <c r="E321" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="F321" s="1">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="G321" s="1">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="H321">
         <v>0</v>
@@ -10681,7 +10543,7 @@
         <v>0</v>
       </c>
       <c r="B322" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="C322">
         <v>1</v>
@@ -10690,13 +10552,13 @@
         <v>12</v>
       </c>
       <c r="E322" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="F322" s="1">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="G322" s="1">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="H322">
         <v>0</v>
@@ -10707,7 +10569,7 @@
         <v>0</v>
       </c>
       <c r="B323" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="C323">
         <v>1</v>
@@ -10716,13 +10578,13 @@
         <v>12</v>
       </c>
       <c r="E323" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="F323" s="1">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="G323" s="1">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="H323">
         <v>0</v>
@@ -10733,7 +10595,7 @@
         <v>0</v>
       </c>
       <c r="B324" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="C324">
         <v>1</v>
@@ -10742,13 +10604,13 @@
         <v>12</v>
       </c>
       <c r="E324" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="F324" s="1">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="G324" s="1">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="H324">
         <v>0</v>
@@ -10759,7 +10621,7 @@
         <v>0</v>
       </c>
       <c r="B325" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="C325">
         <v>1</v>
@@ -10768,13 +10630,13 @@
         <v>12</v>
       </c>
       <c r="E325" t="s">
-        <v>27</v>
+        <v>493</v>
       </c>
       <c r="F325" s="1">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="G325" s="1">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="H325">
         <v>0</v>
@@ -10785,7 +10647,7 @@
         <v>0</v>
       </c>
       <c r="B326" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="C326">
         <v>1</v>
@@ -10794,13 +10656,13 @@
         <v>12</v>
       </c>
       <c r="E326" t="s">
-        <v>27</v>
+        <v>96</v>
       </c>
       <c r="F326" s="1">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="G326" s="1">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="H326">
         <v>0</v>
@@ -10808,51 +10670,51 @@
     </row>
     <row r="327" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A327" t="s">
-        <v>0</v>
+        <v>495</v>
       </c>
       <c r="B327" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="C327">
         <v>1</v>
       </c>
       <c r="D327" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E327" t="s">
-        <v>27</v>
+        <v>302</v>
       </c>
       <c r="F327" s="1">
-        <v>46253</v>
+        <v>46148</v>
       </c>
       <c r="G327" s="1">
-        <v>46253</v>
+        <v>46149</v>
       </c>
       <c r="H327">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="328" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A328" t="s">
-        <v>0</v>
+        <v>497</v>
       </c>
       <c r="B328" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C328">
         <v>1</v>
       </c>
       <c r="D328" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E328" t="s">
-        <v>500</v>
+        <v>30</v>
       </c>
       <c r="F328" s="1">
-        <v>46253</v>
+        <v>46133</v>
       </c>
       <c r="G328" s="1">
-        <v>46253</v>
+        <v>46134</v>
       </c>
       <c r="H328">
         <v>0</v>
@@ -10860,25 +10722,25 @@
     </row>
     <row r="329" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A329" t="s">
-        <v>0</v>
+        <v>497</v>
       </c>
       <c r="B329" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C329">
         <v>1</v>
       </c>
       <c r="D329" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E329" t="s">
-        <v>502</v>
+        <v>30</v>
       </c>
       <c r="F329" s="1">
-        <v>46253</v>
+        <v>46134</v>
       </c>
       <c r="G329" s="1">
-        <v>46253</v>
+        <v>46134</v>
       </c>
       <c r="H329">
         <v>0</v>
@@ -10886,25 +10748,25 @@
     </row>
     <row r="330" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A330" t="s">
-        <v>0</v>
+        <v>497</v>
       </c>
       <c r="B330" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="C330">
         <v>1</v>
       </c>
       <c r="D330" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E330" t="s">
-        <v>504</v>
+        <v>15</v>
       </c>
       <c r="F330" s="1">
-        <v>46253</v>
+        <v>46156</v>
       </c>
       <c r="G330" s="1">
-        <v>46253</v>
+        <v>46156</v>
       </c>
       <c r="H330">
         <v>0</v>
@@ -10912,51 +10774,51 @@
     </row>
     <row r="331" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A331" t="s">
-        <v>0</v>
+        <v>497</v>
       </c>
       <c r="B331" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="C331">
         <v>1</v>
       </c>
       <c r="D331" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E331" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="F331" s="1">
-        <v>46253</v>
+        <v>46195</v>
       </c>
       <c r="G331" s="1">
-        <v>46253</v>
+        <v>46195</v>
       </c>
       <c r="H331">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="332" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A332" t="s">
-        <v>0</v>
+        <v>497</v>
       </c>
       <c r="B332" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="C332">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D332" t="s">
         <v>12</v>
       </c>
       <c r="E332" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="F332" s="1">
-        <v>46253</v>
+        <v>46206</v>
       </c>
       <c r="G332" s="1">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="H332">
         <v>0</v>
@@ -10964,285 +10826,285 @@
     </row>
     <row r="333" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A333" t="s">
-        <v>0</v>
+        <v>497</v>
       </c>
       <c r="B333" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="C333">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D333" t="s">
-        <v>12</v>
+        <v>68</v>
       </c>
       <c r="E333" t="s">
-        <v>439</v>
+        <v>506</v>
       </c>
       <c r="F333" s="1">
-        <v>46253</v>
+        <v>46209</v>
       </c>
       <c r="G333" s="1">
-        <v>46253</v>
+        <v>46218</v>
       </c>
       <c r="H333">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="334" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A334" t="s">
-        <v>0</v>
+        <v>497</v>
       </c>
       <c r="B334" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="C334">
         <v>1</v>
       </c>
       <c r="D334" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E334" t="s">
-        <v>309</v>
+        <v>508</v>
       </c>
       <c r="F334" s="1">
-        <v>46253</v>
+        <v>46213</v>
       </c>
       <c r="G334" s="1">
-        <v>46254</v>
+        <v>46213</v>
       </c>
       <c r="H334">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="335" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A335" t="s">
-        <v>0</v>
+        <v>497</v>
       </c>
       <c r="B335" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="C335">
         <v>1</v>
       </c>
       <c r="D335" t="s">
-        <v>12</v>
+        <v>68</v>
       </c>
       <c r="E335" t="s">
-        <v>512</v>
+        <v>223</v>
       </c>
       <c r="F335" s="1">
-        <v>46253</v>
+        <v>46213</v>
       </c>
       <c r="G335" s="1">
-        <v>46254</v>
+        <v>46216</v>
       </c>
       <c r="H335">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="336" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A336" t="s">
-        <v>0</v>
+        <v>497</v>
       </c>
       <c r="B336" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="C336">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D336" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E336" t="s">
-        <v>21</v>
+        <v>96</v>
       </c>
       <c r="F336" s="1">
-        <v>46253</v>
+        <v>46220</v>
       </c>
       <c r="G336" s="1">
-        <v>46254</v>
+        <v>46231</v>
       </c>
       <c r="H336">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="337" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A337" t="s">
-        <v>0</v>
+        <v>497</v>
       </c>
       <c r="B337" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C337">
         <v>1</v>
       </c>
       <c r="D337" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E337" t="s">
-        <v>515</v>
+        <v>502</v>
       </c>
       <c r="F337" s="1">
-        <v>46253</v>
+        <v>46223</v>
       </c>
       <c r="G337" s="1">
-        <v>46254</v>
+        <v>46223</v>
       </c>
       <c r="H337">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="338" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A338" t="s">
-        <v>0</v>
+        <v>497</v>
       </c>
       <c r="B338" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="C338">
         <v>1</v>
       </c>
       <c r="D338" t="s">
-        <v>12</v>
+        <v>68</v>
       </c>
       <c r="E338" t="s">
-        <v>515</v>
+        <v>223</v>
       </c>
       <c r="F338" s="1">
-        <v>46253</v>
+        <v>46224</v>
       </c>
       <c r="G338" s="1">
-        <v>46254</v>
+        <v>46224</v>
       </c>
       <c r="H338">
-        <v>0</v>
+        <v>26</v>
       </c>
     </row>
     <row r="339" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A339" t="s">
-        <v>0</v>
+        <v>497</v>
       </c>
       <c r="B339" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="C339">
         <v>1</v>
       </c>
       <c r="D339" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E339" t="s">
-        <v>518</v>
+        <v>502</v>
       </c>
       <c r="F339" s="1">
-        <v>46253</v>
+        <v>46230</v>
       </c>
       <c r="G339" s="1">
-        <v>46254</v>
+        <v>46231</v>
       </c>
       <c r="H339">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="340" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A340" t="s">
-        <v>0</v>
+        <v>497</v>
       </c>
       <c r="B340" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="C340">
         <v>1</v>
       </c>
       <c r="D340" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E340" t="s">
-        <v>53</v>
+        <v>96</v>
       </c>
       <c r="F340" s="1">
-        <v>46253</v>
+        <v>46232</v>
       </c>
       <c r="G340" s="1">
-        <v>46254</v>
+        <v>46233</v>
       </c>
       <c r="H340">
-        <v>0</v>
+        <v>126</v>
       </c>
     </row>
     <row r="341" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A341" t="s">
-        <v>0</v>
+        <v>497</v>
       </c>
       <c r="B341" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="C341">
         <v>1</v>
       </c>
       <c r="D341" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E341" t="s">
-        <v>53</v>
+        <v>96</v>
       </c>
       <c r="F341" s="1">
-        <v>46253</v>
+        <v>46232</v>
       </c>
       <c r="G341" s="1">
-        <v>46254</v>
+        <v>46233</v>
       </c>
       <c r="H341">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="342" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A342" t="s">
-        <v>0</v>
+        <v>497</v>
       </c>
       <c r="B342" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="C342">
         <v>1</v>
       </c>
       <c r="D342" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E342" t="s">
-        <v>53</v>
+        <v>223</v>
       </c>
       <c r="F342" s="1">
-        <v>46253</v>
+        <v>46238</v>
       </c>
       <c r="G342" s="1">
-        <v>46254</v>
+        <v>46239</v>
       </c>
       <c r="H342">
-        <v>0</v>
+        <v>117</v>
       </c>
     </row>
     <row r="343" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A343" t="s">
-        <v>0</v>
+        <v>497</v>
       </c>
       <c r="B343" t="s">
-        <v>522</v>
+        <v>517</v>
       </c>
       <c r="C343">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D343" t="s">
         <v>12</v>
       </c>
       <c r="E343" t="s">
-        <v>19</v>
+        <v>504</v>
       </c>
       <c r="F343" s="1">
-        <v>46253</v>
+        <v>46239</v>
       </c>
       <c r="G343" s="1">
-        <v>46254</v>
+        <v>46252</v>
       </c>
       <c r="H343">
         <v>0</v>
@@ -11250,25 +11112,25 @@
     </row>
     <row r="344" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A344" t="s">
-        <v>0</v>
+        <v>497</v>
       </c>
       <c r="B344" t="s">
-        <v>523</v>
+        <v>518</v>
       </c>
       <c r="C344">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D344" t="s">
         <v>12</v>
       </c>
       <c r="E344" t="s">
-        <v>524</v>
+        <v>504</v>
       </c>
       <c r="F344" s="1">
-        <v>46253</v>
+        <v>46239</v>
       </c>
       <c r="G344" s="1">
-        <v>46254</v>
+        <v>46252</v>
       </c>
       <c r="H344">
         <v>0</v>
@@ -11276,36 +11138,36 @@
     </row>
     <row r="345" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A345" t="s">
-        <v>0</v>
+        <v>497</v>
       </c>
       <c r="B345" t="s">
-        <v>525</v>
+        <v>519</v>
       </c>
       <c r="C345">
         <v>1</v>
       </c>
       <c r="D345" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E345" t="s">
-        <v>526</v>
+        <v>30</v>
       </c>
       <c r="F345" s="1">
-        <v>46253</v>
+        <v>46247</v>
       </c>
       <c r="G345" s="1">
-        <v>46254</v>
+        <v>46252</v>
       </c>
       <c r="H345">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="346" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A346" t="s">
-        <v>0</v>
+        <v>497</v>
       </c>
       <c r="B346" t="s">
-        <v>527</v>
+        <v>520</v>
       </c>
       <c r="C346">
         <v>1</v>
@@ -11314,13 +11176,13 @@
         <v>12</v>
       </c>
       <c r="E346" t="s">
-        <v>318</v>
+        <v>335</v>
       </c>
       <c r="F346" s="1">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="G346" s="1">
-        <v>46254</v>
+        <v>46252</v>
       </c>
       <c r="H346">
         <v>0</v>
@@ -11328,10 +11190,10 @@
     </row>
     <row r="347" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A347" t="s">
-        <v>0</v>
+        <v>497</v>
       </c>
       <c r="B347" t="s">
-        <v>528</v>
+        <v>521</v>
       </c>
       <c r="C347">
         <v>1</v>
@@ -11343,10 +11205,10 @@
         <v>134</v>
       </c>
       <c r="F347" s="1">
-        <v>46254</v>
+        <v>46252</v>
       </c>
       <c r="G347" s="1">
-        <v>46254</v>
+        <v>46252</v>
       </c>
       <c r="H347">
         <v>0</v>
@@ -11354,25 +11216,25 @@
     </row>
     <row r="348" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A348" t="s">
-        <v>0</v>
+        <v>497</v>
       </c>
       <c r="B348" t="s">
-        <v>529</v>
+        <v>522</v>
       </c>
       <c r="C348">
         <v>1</v>
       </c>
       <c r="D348" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E348" t="s">
-        <v>70</v>
+        <v>523</v>
       </c>
       <c r="F348" s="1">
-        <v>46254</v>
+        <v>46253</v>
       </c>
       <c r="G348" s="1">
-        <v>46254</v>
+        <v>46253</v>
       </c>
       <c r="H348">
         <v>0</v>
@@ -11380,10 +11242,10 @@
     </row>
     <row r="349" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A349" t="s">
-        <v>0</v>
+        <v>497</v>
       </c>
       <c r="B349" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="C349">
         <v>1</v>
@@ -11392,10 +11254,10 @@
         <v>12</v>
       </c>
       <c r="E349" t="s">
-        <v>531</v>
+        <v>223</v>
       </c>
       <c r="F349" s="1">
-        <v>46254</v>
+        <v>46253</v>
       </c>
       <c r="G349" s="1">
         <v>46254</v>
@@ -11406,10 +11268,10 @@
     </row>
     <row r="350" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A350" t="s">
-        <v>0</v>
+        <v>497</v>
       </c>
       <c r="B350" t="s">
-        <v>532</v>
+        <v>525</v>
       </c>
       <c r="C350">
         <v>1</v>
@@ -11418,13 +11280,13 @@
         <v>12</v>
       </c>
       <c r="E350" t="s">
-        <v>533</v>
+        <v>409</v>
       </c>
       <c r="F350" s="1">
-        <v>46254</v>
+        <v>46253</v>
       </c>
       <c r="G350" s="1">
-        <v>46254</v>
+        <v>46253</v>
       </c>
       <c r="H350">
         <v>0</v>
@@ -11432,10 +11294,10 @@
     </row>
     <row r="351" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A351" t="s">
-        <v>0</v>
+        <v>497</v>
       </c>
       <c r="B351" t="s">
-        <v>534</v>
+        <v>526</v>
       </c>
       <c r="C351">
         <v>1</v>
@@ -11444,13 +11306,13 @@
         <v>12</v>
       </c>
       <c r="E351" t="s">
-        <v>535</v>
+        <v>141</v>
       </c>
       <c r="F351" s="1">
-        <v>46254</v>
+        <v>46253</v>
       </c>
       <c r="G351" s="1">
-        <v>46254</v>
+        <v>46253</v>
       </c>
       <c r="H351">
         <v>0</v>
@@ -11458,10 +11320,10 @@
     </row>
     <row r="352" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A352" t="s">
-        <v>0</v>
+        <v>497</v>
       </c>
       <c r="B352" t="s">
-        <v>536</v>
+        <v>527</v>
       </c>
       <c r="C352">
         <v>1</v>
@@ -11470,10 +11332,10 @@
         <v>12</v>
       </c>
       <c r="E352" t="s">
-        <v>124</v>
+        <v>463</v>
       </c>
       <c r="F352" s="1">
-        <v>46254</v>
+        <v>46253</v>
       </c>
       <c r="G352" s="1">
         <v>46254</v>
@@ -11484,10 +11346,10 @@
     </row>
     <row r="353" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A353" t="s">
-        <v>0</v>
+        <v>497</v>
       </c>
       <c r="B353" t="s">
-        <v>537</v>
+        <v>528</v>
       </c>
       <c r="C353">
         <v>1</v>
@@ -11496,7 +11358,7 @@
         <v>12</v>
       </c>
       <c r="E353" t="s">
-        <v>27</v>
+        <v>486</v>
       </c>
       <c r="F353" s="1">
         <v>46254</v>
@@ -11510,10 +11372,10 @@
     </row>
     <row r="354" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A354" t="s">
-        <v>0</v>
+        <v>497</v>
       </c>
       <c r="B354" t="s">
-        <v>538</v>
+        <v>529</v>
       </c>
       <c r="C354">
         <v>1</v>
@@ -11522,7 +11384,7 @@
         <v>12</v>
       </c>
       <c r="E354" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="F354" s="1">
         <v>46254</v>
@@ -11536,10 +11398,10 @@
     </row>
     <row r="355" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A355" t="s">
-        <v>0</v>
+        <v>497</v>
       </c>
       <c r="B355" t="s">
-        <v>539</v>
+        <v>530</v>
       </c>
       <c r="C355">
         <v>1</v>
@@ -11548,7 +11410,7 @@
         <v>12</v>
       </c>
       <c r="E355" t="s">
-        <v>27</v>
+        <v>96</v>
       </c>
       <c r="F355" s="1">
         <v>46254</v>
@@ -11562,36 +11424,36 @@
     </row>
     <row r="356" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A356" t="s">
-        <v>540</v>
+        <v>531</v>
       </c>
       <c r="B356" t="s">
-        <v>541</v>
+        <v>532</v>
       </c>
       <c r="C356">
         <v>1</v>
       </c>
       <c r="D356" t="s">
-        <v>2</v>
+        <v>68</v>
       </c>
       <c r="E356" t="s">
-        <v>311</v>
+        <v>533</v>
       </c>
       <c r="F356" s="1">
-        <v>46148</v>
+        <v>46063</v>
       </c>
       <c r="G356" s="1">
-        <v>46149</v>
+        <v>46064</v>
       </c>
       <c r="H356">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="357" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A357" t="s">
-        <v>542</v>
+        <v>531</v>
       </c>
       <c r="B357" t="s">
-        <v>543</v>
+        <v>534</v>
       </c>
       <c r="C357">
         <v>1</v>
@@ -11600,13 +11462,13 @@
         <v>5</v>
       </c>
       <c r="E357" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="F357" s="1">
-        <v>46133</v>
+        <v>46113</v>
       </c>
       <c r="G357" s="1">
-        <v>46134</v>
+        <v>46125</v>
       </c>
       <c r="H357">
         <v>0</v>
@@ -11614,62 +11476,62 @@
     </row>
     <row r="358" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A358" t="s">
-        <v>542</v>
+        <v>531</v>
       </c>
       <c r="B358" t="s">
-        <v>544</v>
+        <v>535</v>
       </c>
       <c r="C358">
         <v>1</v>
       </c>
       <c r="D358" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E358" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="F358" s="1">
-        <v>46134</v>
+        <v>46125</v>
       </c>
       <c r="G358" s="1">
-        <v>46134</v>
+        <v>46125</v>
       </c>
       <c r="H358">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="359" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A359" t="s">
-        <v>542</v>
+        <v>531</v>
       </c>
       <c r="B359" t="s">
-        <v>545</v>
+        <v>536</v>
       </c>
       <c r="C359">
         <v>1</v>
       </c>
       <c r="D359" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E359" t="s">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="F359" s="1">
-        <v>46156</v>
+        <v>46126</v>
       </c>
       <c r="G359" s="1">
-        <v>46156</v>
+        <v>46126</v>
       </c>
       <c r="H359">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="360" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A360" t="s">
-        <v>542</v>
+        <v>531</v>
       </c>
       <c r="B360" t="s">
-        <v>546</v>
+        <v>537</v>
       </c>
       <c r="C360">
         <v>1</v>
@@ -11678,206 +11540,206 @@
         <v>2</v>
       </c>
       <c r="E360" t="s">
-        <v>547</v>
+        <v>41</v>
       </c>
       <c r="F360" s="1">
-        <v>46195</v>
+        <v>46126</v>
       </c>
       <c r="G360" s="1">
-        <v>46195</v>
+        <v>46126</v>
       </c>
       <c r="H360">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="361" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A361" t="s">
-        <v>542</v>
+        <v>531</v>
       </c>
       <c r="B361" t="s">
-        <v>548</v>
+        <v>538</v>
       </c>
       <c r="C361">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D361" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E361" t="s">
-        <v>549</v>
+        <v>41</v>
       </c>
       <c r="F361" s="1">
-        <v>46206</v>
+        <v>46128</v>
       </c>
       <c r="G361" s="1">
-        <v>46252</v>
+        <v>46128</v>
       </c>
       <c r="H361">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="362" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A362" t="s">
-        <v>542</v>
+        <v>531</v>
       </c>
       <c r="B362" t="s">
-        <v>550</v>
+        <v>539</v>
       </c>
       <c r="C362">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D362" t="s">
-        <v>68</v>
+        <v>5</v>
       </c>
       <c r="E362" t="s">
-        <v>551</v>
+        <v>41</v>
       </c>
       <c r="F362" s="1">
-        <v>46209</v>
+        <v>46132</v>
       </c>
       <c r="G362" s="1">
-        <v>46218</v>
+        <v>46132</v>
       </c>
       <c r="H362">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="363" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A363" t="s">
-        <v>542</v>
+        <v>531</v>
       </c>
       <c r="B363" t="s">
-        <v>552</v>
+        <v>540</v>
       </c>
       <c r="C363">
         <v>1</v>
       </c>
       <c r="D363" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E363" t="s">
-        <v>553</v>
+        <v>41</v>
       </c>
       <c r="F363" s="1">
-        <v>46213</v>
+        <v>46161</v>
       </c>
       <c r="G363" s="1">
-        <v>46213</v>
+        <v>46161</v>
       </c>
       <c r="H363">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="364" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A364" t="s">
-        <v>542</v>
+        <v>531</v>
       </c>
       <c r="B364" t="s">
-        <v>554</v>
+        <v>541</v>
       </c>
       <c r="C364">
         <v>1</v>
       </c>
       <c r="D364" t="s">
-        <v>68</v>
+        <v>2</v>
       </c>
       <c r="E364" t="s">
-        <v>223</v>
+        <v>41</v>
       </c>
       <c r="F364" s="1">
-        <v>46213</v>
+        <v>46174</v>
       </c>
       <c r="G364" s="1">
-        <v>46216</v>
+        <v>46174</v>
       </c>
       <c r="H364">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="365" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A365" t="s">
+        <v>531</v>
+      </c>
+      <c r="B365" t="s">
         <v>542</v>
       </c>
-      <c r="B365" t="s">
-        <v>555</v>
-      </c>
       <c r="C365">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D365" t="s">
         <v>2</v>
       </c>
       <c r="E365" t="s">
-        <v>96</v>
+        <v>41</v>
       </c>
       <c r="F365" s="1">
-        <v>46220</v>
+        <v>46174</v>
       </c>
       <c r="G365" s="1">
-        <v>46231</v>
+        <v>46174</v>
       </c>
       <c r="H365">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="366" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A366" t="s">
-        <v>542</v>
+        <v>531</v>
       </c>
       <c r="B366" t="s">
-        <v>556</v>
+        <v>543</v>
       </c>
       <c r="C366">
         <v>1</v>
       </c>
       <c r="D366" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E366" t="s">
-        <v>547</v>
+        <v>41</v>
       </c>
       <c r="F366" s="1">
-        <v>46223</v>
+        <v>46195</v>
       </c>
       <c r="G366" s="1">
-        <v>46223</v>
+        <v>46252</v>
       </c>
       <c r="H366">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="367" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A367" t="s">
-        <v>542</v>
+        <v>531</v>
       </c>
       <c r="B367" t="s">
-        <v>557</v>
+        <v>544</v>
       </c>
       <c r="C367">
         <v>1</v>
       </c>
       <c r="D367" t="s">
-        <v>68</v>
+        <v>5</v>
       </c>
       <c r="E367" t="s">
-        <v>223</v>
+        <v>41</v>
       </c>
       <c r="F367" s="1">
-        <v>46224</v>
+        <v>46210</v>
       </c>
       <c r="G367" s="1">
-        <v>46224</v>
+        <v>46210</v>
       </c>
       <c r="H367">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="368" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A368" t="s">
-        <v>542</v>
+        <v>531</v>
       </c>
       <c r="B368" t="s">
-        <v>558</v>
+        <v>545</v>
       </c>
       <c r="C368">
         <v>1</v>
@@ -11886,114 +11748,114 @@
         <v>2</v>
       </c>
       <c r="E368" t="s">
-        <v>547</v>
+        <v>41</v>
       </c>
       <c r="F368" s="1">
-        <v>46230</v>
+        <v>46213</v>
       </c>
       <c r="G368" s="1">
-        <v>46231</v>
+        <v>46213</v>
       </c>
       <c r="H368">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="369" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A369" t="s">
-        <v>542</v>
+        <v>531</v>
       </c>
       <c r="B369" t="s">
-        <v>559</v>
+        <v>546</v>
       </c>
       <c r="C369">
         <v>1</v>
       </c>
       <c r="D369" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E369" t="s">
-        <v>96</v>
+        <v>41</v>
       </c>
       <c r="F369" s="1">
-        <v>46232</v>
+        <v>46218</v>
       </c>
       <c r="G369" s="1">
-        <v>46233</v>
+        <v>46252</v>
       </c>
       <c r="H369">
-        <v>126</v>
+        <v>0</v>
       </c>
     </row>
     <row r="370" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A370" t="s">
-        <v>542</v>
+        <v>531</v>
       </c>
       <c r="B370" t="s">
-        <v>560</v>
+        <v>547</v>
       </c>
       <c r="C370">
         <v>1</v>
       </c>
       <c r="D370" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E370" t="s">
-        <v>96</v>
+        <v>55</v>
       </c>
       <c r="F370" s="1">
-        <v>46232</v>
+        <v>46226</v>
       </c>
       <c r="G370" s="1">
-        <v>46233</v>
+        <v>46226</v>
       </c>
       <c r="H370">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="371" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A371" t="s">
-        <v>542</v>
+        <v>531</v>
       </c>
       <c r="B371" t="s">
-        <v>561</v>
+        <v>548</v>
       </c>
       <c r="C371">
         <v>1</v>
       </c>
       <c r="D371" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E371" t="s">
-        <v>223</v>
+        <v>41</v>
       </c>
       <c r="F371" s="1">
-        <v>46238</v>
+        <v>46227</v>
       </c>
       <c r="G371" s="1">
-        <v>46239</v>
+        <v>46252</v>
       </c>
       <c r="H371">
-        <v>117</v>
+        <v>0</v>
       </c>
     </row>
     <row r="372" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A372" t="s">
-        <v>542</v>
+        <v>531</v>
       </c>
       <c r="B372" t="s">
-        <v>562</v>
+        <v>549</v>
       </c>
       <c r="C372">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D372" t="s">
         <v>12</v>
       </c>
       <c r="E372" t="s">
-        <v>549</v>
+        <v>41</v>
       </c>
       <c r="F372" s="1">
-        <v>46239</v>
+        <v>46227</v>
       </c>
       <c r="G372" s="1">
         <v>46252</v>
@@ -12004,25 +11866,25 @@
     </row>
     <row r="373" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A373" t="s">
-        <v>542</v>
+        <v>531</v>
       </c>
       <c r="B373" t="s">
-        <v>563</v>
+        <v>550</v>
       </c>
       <c r="C373">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D373" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E373" t="s">
-        <v>549</v>
+        <v>41</v>
       </c>
       <c r="F373" s="1">
-        <v>46239</v>
+        <v>46227</v>
       </c>
       <c r="G373" s="1">
-        <v>46252</v>
+        <v>46228</v>
       </c>
       <c r="H373">
         <v>0</v>
@@ -12030,51 +11892,51 @@
     </row>
     <row r="374" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A374" t="s">
-        <v>542</v>
+        <v>531</v>
       </c>
       <c r="B374" t="s">
-        <v>564</v>
+        <v>551</v>
       </c>
       <c r="C374">
         <v>1</v>
       </c>
       <c r="D374" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E374" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F374" s="1">
-        <v>46247</v>
+        <v>46230</v>
       </c>
       <c r="G374" s="1">
         <v>46252</v>
       </c>
       <c r="H374">
-        <v>29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="375" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A375" t="s">
-        <v>542</v>
+        <v>531</v>
       </c>
       <c r="B375" t="s">
-        <v>565</v>
+        <v>552</v>
       </c>
       <c r="C375">
         <v>1</v>
       </c>
       <c r="D375" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E375" t="s">
-        <v>363</v>
+        <v>41</v>
       </c>
       <c r="F375" s="1">
-        <v>46252</v>
+        <v>46231</v>
       </c>
       <c r="G375" s="1">
-        <v>46252</v>
+        <v>46231</v>
       </c>
       <c r="H375">
         <v>0</v>
@@ -12082,10 +11944,10 @@
     </row>
     <row r="376" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A376" t="s">
-        <v>542</v>
+        <v>531</v>
       </c>
       <c r="B376" t="s">
-        <v>566</v>
+        <v>553</v>
       </c>
       <c r="C376">
         <v>1</v>
@@ -12094,13 +11956,13 @@
         <v>12</v>
       </c>
       <c r="E376" t="s">
-        <v>134</v>
+        <v>41</v>
       </c>
       <c r="F376" s="1">
-        <v>46252</v>
+        <v>46254</v>
       </c>
       <c r="G376" s="1">
-        <v>46252</v>
+        <v>46254</v>
       </c>
       <c r="H376">
         <v>0</v>
@@ -12108,963 +11970,183 @@
     </row>
     <row r="377" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A377" t="s">
-        <v>542</v>
+        <v>554</v>
       </c>
       <c r="B377" t="s">
-        <v>567</v>
+        <v>555</v>
       </c>
       <c r="C377">
         <v>1</v>
       </c>
       <c r="D377" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E377" t="s">
-        <v>568</v>
+        <v>556</v>
       </c>
       <c r="F377" s="1">
-        <v>46253</v>
+        <v>46083</v>
       </c>
       <c r="G377" s="1">
-        <v>46253</v>
+        <v>46084</v>
       </c>
       <c r="H377">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="378" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A378" t="s">
-        <v>542</v>
+        <v>554</v>
       </c>
       <c r="B378" t="s">
-        <v>569</v>
+        <v>557</v>
       </c>
       <c r="C378">
         <v>1</v>
       </c>
       <c r="D378" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E378" t="s">
-        <v>223</v>
+        <v>556</v>
       </c>
       <c r="F378" s="1">
-        <v>46253</v>
+        <v>46132</v>
       </c>
       <c r="G378" s="1">
-        <v>46254</v>
+        <v>46133</v>
       </c>
       <c r="H378">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="379" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A379" t="s">
-        <v>542</v>
+        <v>554</v>
       </c>
       <c r="B379" t="s">
-        <v>570</v>
+        <v>558</v>
       </c>
       <c r="C379">
         <v>1</v>
       </c>
       <c r="D379" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E379" t="s">
-        <v>462</v>
+        <v>559</v>
       </c>
       <c r="F379" s="1">
-        <v>46253</v>
+        <v>46157</v>
       </c>
       <c r="G379" s="1">
-        <v>46253</v>
+        <v>46157</v>
       </c>
       <c r="H379">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="380" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A380" t="s">
-        <v>542</v>
+        <v>554</v>
       </c>
       <c r="B380" t="s">
-        <v>571</v>
+        <v>560</v>
       </c>
       <c r="C380">
         <v>1</v>
       </c>
       <c r="D380" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E380" t="s">
-        <v>141</v>
+        <v>561</v>
       </c>
       <c r="F380" s="1">
-        <v>46253</v>
+        <v>46168</v>
       </c>
       <c r="G380" s="1">
-        <v>46253</v>
+        <v>46170</v>
       </c>
       <c r="H380">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="381" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A381" t="s">
-        <v>542</v>
+        <v>554</v>
       </c>
       <c r="B381" t="s">
-        <v>572</v>
+        <v>562</v>
       </c>
       <c r="C381">
         <v>1</v>
       </c>
       <c r="D381" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E381" t="s">
-        <v>518</v>
+        <v>559</v>
       </c>
       <c r="F381" s="1">
-        <v>46253</v>
+        <v>46244</v>
       </c>
       <c r="G381" s="1">
-        <v>46254</v>
+        <v>46244</v>
       </c>
       <c r="H381">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="382" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A382" t="s">
-        <v>573</v>
+        <v>554</v>
       </c>
       <c r="B382" t="s">
-        <v>574</v>
+        <v>563</v>
       </c>
       <c r="C382">
         <v>1</v>
       </c>
       <c r="D382" t="s">
-        <v>68</v>
+        <v>2</v>
       </c>
       <c r="E382" t="s">
-        <v>575</v>
+        <v>559</v>
       </c>
       <c r="F382" s="1">
-        <v>46063</v>
+        <v>46247</v>
       </c>
       <c r="G382" s="1">
-        <v>46064</v>
+        <v>46247</v>
       </c>
       <c r="H382">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="383" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A383" t="s">
-        <v>573</v>
+        <v>554</v>
       </c>
       <c r="B383" t="s">
-        <v>576</v>
+        <v>564</v>
       </c>
       <c r="C383">
         <v>1</v>
       </c>
       <c r="D383" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E383" t="s">
-        <v>41</v>
+        <v>556</v>
       </c>
       <c r="F383" s="1">
-        <v>46113</v>
+        <v>46247</v>
       </c>
       <c r="G383" s="1">
-        <v>46125</v>
+        <v>46247</v>
       </c>
       <c r="H383">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="384" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A384" t="s">
-        <v>573</v>
-      </c>
-      <c r="B384" t="s">
-        <v>577</v>
-      </c>
-      <c r="C384">
-        <v>1</v>
-      </c>
-      <c r="D384" t="s">
-        <v>2</v>
-      </c>
-      <c r="E384" t="s">
-        <v>41</v>
-      </c>
-      <c r="F384" s="1">
-        <v>46125</v>
-      </c>
-      <c r="G384" s="1">
-        <v>46125</v>
-      </c>
-      <c r="H384">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="385" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A385" t="s">
-        <v>573</v>
-      </c>
-      <c r="B385" t="s">
-        <v>578</v>
-      </c>
-      <c r="C385">
-        <v>1</v>
-      </c>
-      <c r="D385" t="s">
-        <v>2</v>
-      </c>
-      <c r="E385" t="s">
-        <v>41</v>
-      </c>
-      <c r="F385" s="1">
-        <v>46126</v>
-      </c>
-      <c r="G385" s="1">
-        <v>46126</v>
-      </c>
-      <c r="H385">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="386" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A386" t="s">
-        <v>573</v>
-      </c>
-      <c r="B386" t="s">
-        <v>579</v>
-      </c>
-      <c r="C386">
-        <v>1</v>
-      </c>
-      <c r="D386" t="s">
-        <v>2</v>
-      </c>
-      <c r="E386" t="s">
-        <v>41</v>
-      </c>
-      <c r="F386" s="1">
-        <v>46126</v>
-      </c>
-      <c r="G386" s="1">
-        <v>46126</v>
-      </c>
-      <c r="H386">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="387" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A387" t="s">
-        <v>573</v>
-      </c>
-      <c r="B387" t="s">
-        <v>580</v>
-      </c>
-      <c r="C387">
-        <v>1</v>
-      </c>
-      <c r="D387" t="s">
-        <v>2</v>
-      </c>
-      <c r="E387" t="s">
-        <v>41</v>
-      </c>
-      <c r="F387" s="1">
-        <v>46128</v>
-      </c>
-      <c r="G387" s="1">
-        <v>46128</v>
-      </c>
-      <c r="H387">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="388" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A388" t="s">
-        <v>573</v>
-      </c>
-      <c r="B388" t="s">
-        <v>581</v>
-      </c>
-      <c r="C388">
-        <v>1</v>
-      </c>
-      <c r="D388" t="s">
-        <v>5</v>
-      </c>
-      <c r="E388" t="s">
-        <v>41</v>
-      </c>
-      <c r="F388" s="1">
-        <v>46132</v>
-      </c>
-      <c r="G388" s="1">
-        <v>46132</v>
-      </c>
-      <c r="H388">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="389" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A389" t="s">
-        <v>573</v>
-      </c>
-      <c r="B389" t="s">
-        <v>582</v>
-      </c>
-      <c r="C389">
-        <v>1</v>
-      </c>
-      <c r="D389" t="s">
-        <v>2</v>
-      </c>
-      <c r="E389" t="s">
-        <v>41</v>
-      </c>
-      <c r="F389" s="1">
-        <v>46161</v>
-      </c>
-      <c r="G389" s="1">
-        <v>46161</v>
-      </c>
-      <c r="H389">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="390" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A390" t="s">
-        <v>573</v>
-      </c>
-      <c r="B390" t="s">
-        <v>583</v>
-      </c>
-      <c r="C390">
-        <v>1</v>
-      </c>
-      <c r="D390" t="s">
-        <v>2</v>
-      </c>
-      <c r="E390" t="s">
-        <v>41</v>
-      </c>
-      <c r="F390" s="1">
-        <v>46174</v>
-      </c>
-      <c r="G390" s="1">
-        <v>46174</v>
-      </c>
-      <c r="H390">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="391" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A391" t="s">
-        <v>573</v>
-      </c>
-      <c r="B391" t="s">
-        <v>584</v>
-      </c>
-      <c r="C391">
-        <v>1</v>
-      </c>
-      <c r="D391" t="s">
-        <v>2</v>
-      </c>
-      <c r="E391" t="s">
-        <v>41</v>
-      </c>
-      <c r="F391" s="1">
-        <v>46174</v>
-      </c>
-      <c r="G391" s="1">
-        <v>46174</v>
-      </c>
-      <c r="H391">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="392" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A392" t="s">
-        <v>573</v>
-      </c>
-      <c r="B392" t="s">
-        <v>585</v>
-      </c>
-      <c r="C392">
-        <v>1</v>
-      </c>
-      <c r="D392" t="s">
-        <v>12</v>
-      </c>
-      <c r="E392" t="s">
-        <v>41</v>
-      </c>
-      <c r="F392" s="1">
-        <v>46195</v>
-      </c>
-      <c r="G392" s="1">
-        <v>46252</v>
-      </c>
-      <c r="H392">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="393" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A393" t="s">
-        <v>573</v>
-      </c>
-      <c r="B393" t="s">
-        <v>586</v>
-      </c>
-      <c r="C393">
-        <v>1</v>
-      </c>
-      <c r="D393" t="s">
-        <v>5</v>
-      </c>
-      <c r="E393" t="s">
-        <v>41</v>
-      </c>
-      <c r="F393" s="1">
-        <v>46210</v>
-      </c>
-      <c r="G393" s="1">
-        <v>46210</v>
-      </c>
-      <c r="H393">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="394" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A394" t="s">
-        <v>573</v>
-      </c>
-      <c r="B394" t="s">
-        <v>587</v>
-      </c>
-      <c r="C394">
-        <v>1</v>
-      </c>
-      <c r="D394" t="s">
-        <v>2</v>
-      </c>
-      <c r="E394" t="s">
-        <v>41</v>
-      </c>
-      <c r="F394" s="1">
-        <v>46213</v>
-      </c>
-      <c r="G394" s="1">
-        <v>46213</v>
-      </c>
-      <c r="H394">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="395" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A395" t="s">
-        <v>573</v>
-      </c>
-      <c r="B395" t="s">
-        <v>588</v>
-      </c>
-      <c r="C395">
-        <v>1</v>
-      </c>
-      <c r="D395" t="s">
-        <v>12</v>
-      </c>
-      <c r="E395" t="s">
-        <v>41</v>
-      </c>
-      <c r="F395" s="1">
-        <v>46218</v>
-      </c>
-      <c r="G395" s="1">
-        <v>46252</v>
-      </c>
-      <c r="H395">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="396" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A396" t="s">
-        <v>573</v>
-      </c>
-      <c r="B396" t="s">
-        <v>589</v>
-      </c>
-      <c r="C396">
-        <v>1</v>
-      </c>
-      <c r="D396" t="s">
-        <v>5</v>
-      </c>
-      <c r="E396" t="s">
-        <v>55</v>
-      </c>
-      <c r="F396" s="1">
-        <v>46226</v>
-      </c>
-      <c r="G396" s="1">
-        <v>46226</v>
-      </c>
-      <c r="H396">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="397" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A397" t="s">
-        <v>573</v>
-      </c>
-      <c r="B397" t="s">
-        <v>590</v>
-      </c>
-      <c r="C397">
-        <v>1</v>
-      </c>
-      <c r="D397" t="s">
-        <v>12</v>
-      </c>
-      <c r="E397" t="s">
-        <v>41</v>
-      </c>
-      <c r="F397" s="1">
-        <v>46227</v>
-      </c>
-      <c r="G397" s="1">
-        <v>46252</v>
-      </c>
-      <c r="H397">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="398" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A398" t="s">
-        <v>573</v>
-      </c>
-      <c r="B398" t="s">
-        <v>591</v>
-      </c>
-      <c r="C398">
-        <v>1</v>
-      </c>
-      <c r="D398" t="s">
-        <v>12</v>
-      </c>
-      <c r="E398" t="s">
-        <v>41</v>
-      </c>
-      <c r="F398" s="1">
-        <v>46227</v>
-      </c>
-      <c r="G398" s="1">
-        <v>46252</v>
-      </c>
-      <c r="H398">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="399" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A399" t="s">
-        <v>573</v>
-      </c>
-      <c r="B399" t="s">
-        <v>592</v>
-      </c>
-      <c r="C399">
-        <v>1</v>
-      </c>
-      <c r="D399" t="s">
-        <v>5</v>
-      </c>
-      <c r="E399" t="s">
-        <v>41</v>
-      </c>
-      <c r="F399" s="1">
-        <v>46227</v>
-      </c>
-      <c r="G399" s="1">
-        <v>46228</v>
-      </c>
-      <c r="H399">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="400" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A400" t="s">
-        <v>573</v>
-      </c>
-      <c r="B400" t="s">
-        <v>593</v>
-      </c>
-      <c r="C400">
-        <v>1</v>
-      </c>
-      <c r="D400" t="s">
-        <v>12</v>
-      </c>
-      <c r="E400" t="s">
-        <v>55</v>
-      </c>
-      <c r="F400" s="1">
-        <v>46230</v>
-      </c>
-      <c r="G400" s="1">
-        <v>46252</v>
-      </c>
-      <c r="H400">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="401" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A401" t="s">
-        <v>573</v>
-      </c>
-      <c r="B401" t="s">
-        <v>594</v>
-      </c>
-      <c r="C401">
-        <v>1</v>
-      </c>
-      <c r="D401" t="s">
-        <v>5</v>
-      </c>
-      <c r="E401" t="s">
-        <v>41</v>
-      </c>
-      <c r="F401" s="1">
-        <v>46231</v>
-      </c>
-      <c r="G401" s="1">
-        <v>46231</v>
-      </c>
-      <c r="H401">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="402" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A402" t="s">
-        <v>573</v>
-      </c>
-      <c r="B402" t="s">
-        <v>595</v>
-      </c>
-      <c r="C402">
-        <v>1</v>
-      </c>
-      <c r="D402" t="s">
-        <v>5</v>
-      </c>
-      <c r="E402" t="s">
-        <v>41</v>
-      </c>
-      <c r="F402" s="1">
-        <v>46237</v>
-      </c>
-      <c r="G402" s="1">
-        <v>46237</v>
-      </c>
-      <c r="H402">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="403" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A403" t="s">
-        <v>573</v>
-      </c>
-      <c r="B403" t="s">
-        <v>596</v>
-      </c>
-      <c r="C403">
-        <v>1</v>
-      </c>
-      <c r="D403" t="s">
-        <v>12</v>
-      </c>
-      <c r="E403" t="s">
-        <v>41</v>
-      </c>
-      <c r="F403" s="1">
-        <v>46254</v>
-      </c>
-      <c r="G403" s="1">
-        <v>46254</v>
-      </c>
-      <c r="H403">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="404" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A404" t="s">
-        <v>573</v>
-      </c>
-      <c r="B404" t="s">
-        <v>597</v>
-      </c>
-      <c r="C404">
-        <v>1</v>
-      </c>
-      <c r="D404" t="s">
-        <v>12</v>
-      </c>
-      <c r="E404" t="s">
-        <v>41</v>
-      </c>
-      <c r="F404" s="1">
-        <v>46254</v>
-      </c>
-      <c r="G404" s="1">
-        <v>46254</v>
-      </c>
-      <c r="H404">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="405" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A405" t="s">
-        <v>573</v>
-      </c>
-      <c r="B405" t="s">
-        <v>598</v>
-      </c>
-      <c r="C405">
-        <v>1</v>
-      </c>
-      <c r="D405" t="s">
-        <v>12</v>
-      </c>
-      <c r="E405" t="s">
-        <v>41</v>
-      </c>
-      <c r="F405" s="1">
-        <v>46254</v>
-      </c>
-      <c r="G405" s="1">
-        <v>46254</v>
-      </c>
-      <c r="H405">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="406" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A406" t="s">
-        <v>573</v>
-      </c>
-      <c r="B406" t="s">
-        <v>599</v>
-      </c>
-      <c r="C406">
-        <v>1</v>
-      </c>
-      <c r="D406" t="s">
-        <v>12</v>
-      </c>
-      <c r="E406" t="s">
-        <v>41</v>
-      </c>
-      <c r="F406" s="1">
-        <v>46254</v>
-      </c>
-      <c r="G406" s="1">
-        <v>46254</v>
-      </c>
-      <c r="H406">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="407" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A407" t="s">
-        <v>600</v>
-      </c>
-      <c r="B407" t="s">
-        <v>601</v>
-      </c>
-      <c r="C407">
-        <v>1</v>
-      </c>
-      <c r="D407" t="s">
-        <v>2</v>
-      </c>
-      <c r="E407" t="s">
-        <v>602</v>
-      </c>
-      <c r="F407" s="1">
-        <v>46083</v>
-      </c>
-      <c r="G407" s="1">
-        <v>46084</v>
-      </c>
-      <c r="H407">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="408" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A408" t="s">
-        <v>600</v>
-      </c>
-      <c r="B408" t="s">
-        <v>603</v>
-      </c>
-      <c r="C408">
-        <v>1</v>
-      </c>
-      <c r="D408" t="s">
-        <v>2</v>
-      </c>
-      <c r="E408" t="s">
-        <v>602</v>
-      </c>
-      <c r="F408" s="1">
-        <v>46132</v>
-      </c>
-      <c r="G408" s="1">
-        <v>46133</v>
-      </c>
-      <c r="H408">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="409" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A409" t="s">
-        <v>600</v>
-      </c>
-      <c r="B409" t="s">
-        <v>604</v>
-      </c>
-      <c r="C409">
-        <v>1</v>
-      </c>
-      <c r="D409" t="s">
-        <v>2</v>
-      </c>
-      <c r="E409" t="s">
-        <v>605</v>
-      </c>
-      <c r="F409" s="1">
-        <v>46157</v>
-      </c>
-      <c r="G409" s="1">
-        <v>46157</v>
-      </c>
-      <c r="H409">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="410" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A410" t="s">
-        <v>600</v>
-      </c>
-      <c r="B410" t="s">
-        <v>606</v>
-      </c>
-      <c r="C410">
-        <v>1</v>
-      </c>
-      <c r="D410" t="s">
-        <v>2</v>
-      </c>
-      <c r="E410" t="s">
-        <v>607</v>
-      </c>
-      <c r="F410" s="1">
-        <v>46168</v>
-      </c>
-      <c r="G410" s="1">
-        <v>46170</v>
-      </c>
-      <c r="H410">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="411" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A411" t="s">
-        <v>600</v>
-      </c>
-      <c r="B411" t="s">
-        <v>608</v>
-      </c>
-      <c r="C411">
-        <v>1</v>
-      </c>
-      <c r="D411" t="s">
-        <v>2</v>
-      </c>
-      <c r="E411" t="s">
-        <v>605</v>
-      </c>
-      <c r="F411" s="1">
-        <v>46244</v>
-      </c>
-      <c r="G411" s="1">
-        <v>46244</v>
-      </c>
-      <c r="H411">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="412" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A412" t="s">
-        <v>600</v>
-      </c>
-      <c r="B412" t="s">
-        <v>609</v>
-      </c>
-      <c r="C412">
-        <v>1</v>
-      </c>
-      <c r="D412" t="s">
-        <v>2</v>
-      </c>
-      <c r="E412" t="s">
-        <v>605</v>
-      </c>
-      <c r="F412" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G412" s="1">
-        <v>46247</v>
-      </c>
-      <c r="H412">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="413" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A413" t="s">
-        <v>600</v>
-      </c>
-      <c r="B413" t="s">
-        <v>610</v>
-      </c>
-      <c r="C413">
-        <v>1</v>
-      </c>
-      <c r="D413" t="s">
-        <v>2</v>
-      </c>
-      <c r="E413" t="s">
-        <v>602</v>
-      </c>
-      <c r="F413" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G413" s="1">
-        <v>46247</v>
-      </c>
-      <c r="H413">
         <v>1</v>
       </c>
     </row>

--- a/Data_ERP/Pedidos Transmicion.xlsx
+++ b/Data_ERP/Pedidos Transmicion.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sistema_Logistico_Peirano\Data_ERP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B4807645-4B7E-4130-A269-E87177540A11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C2A20913-C271-47CC-A699-8D2BECE761B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="26505" yWindow="3765" windowWidth="15375" windowHeight="8325" xr2:uid="{40F9090B-8D9B-41B8-A15B-2B4B52674418}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{3F966780-C724-4E90-A737-9EE2B961DE5B}"/>
   </bookViews>
   <sheets>
     <sheet name="transmicion" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1352" uniqueCount="512">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1464" uniqueCount="554">
   <si>
     <t>0001</t>
   </si>
@@ -919,6 +919,9 @@
     <t xml:space="preserve">  213911</t>
   </si>
   <si>
+    <t xml:space="preserve">  213912</t>
+  </si>
+  <si>
     <t xml:space="preserve">  213914</t>
   </si>
   <si>
@@ -952,6 +955,9 @@
     <t xml:space="preserve">  213938</t>
   </si>
   <si>
+    <t xml:space="preserve">  213944</t>
+  </si>
+  <si>
     <t xml:space="preserve">  213946</t>
   </si>
   <si>
@@ -1321,12 +1327,129 @@
     <t>PIAZZA JOSE ALBERTO</t>
   </si>
   <si>
+    <t xml:space="preserve">  214087</t>
+  </si>
+  <si>
+    <t>SURVALMEDA CONSTRUCCIONES S. A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214089</t>
+  </si>
+  <si>
+    <t>PRIATEL PISOS S.R.L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214091</t>
+  </si>
+  <si>
+    <t>BELINDA S.R.L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214093</t>
+  </si>
+  <si>
+    <t>NICUESA E HIJOS S.R.L. -SANIT. NICUESA E HIJOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214095</t>
+  </si>
+  <si>
+    <t>BOLONDI JORGE A.-CORRALON MAILIN MADERAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214098</t>
+  </si>
+  <si>
+    <t>FICO HORACIO JAVIER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214099</t>
+  </si>
+  <si>
     <t xml:space="preserve">  214101</t>
   </si>
   <si>
     <t>TRIPOLI CARLOS L.</t>
   </si>
   <si>
+    <t xml:space="preserve">  214105</t>
+  </si>
+  <si>
+    <t>GILLI FAUDIN LUIS V. -GILCOMAT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214108</t>
+  </si>
+  <si>
+    <t>EDEN SANITARIOS S.R.L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214109</t>
+  </si>
+  <si>
+    <t>FANTINI FERNANDO ARIEL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214113</t>
+  </si>
+  <si>
+    <t>RA S.H. DE ALFONSO RUBEN Y POZZUTO CARLOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214115</t>
+  </si>
+  <si>
+    <t>UCCELI GABRIEL A.-SANITARIOS GABRIEL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214116</t>
+  </si>
+  <si>
+    <t>SCHEYER CARINA E,KOLB ESTEBAN H S.H.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214117</t>
+  </si>
+  <si>
+    <t>WELSH L Y HAUF E. -SANITARIOS DE LA COSTA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214119</t>
+  </si>
+  <si>
+    <t>TUBOPLAST SRL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214121</t>
+  </si>
+  <si>
     <t>0004</t>
   </si>
   <si>
@@ -1429,6 +1552,9 @@
     <t xml:space="preserve">    2826</t>
   </si>
   <si>
+    <t xml:space="preserve">    2829</t>
+  </si>
+  <si>
     <t>4444</t>
   </si>
   <si>
@@ -1498,7 +1624,7 @@
     <t xml:space="preserve">    2240</t>
   </si>
   <si>
-    <t xml:space="preserve">    2244</t>
+    <t xml:space="preserve">    2247</t>
   </si>
   <si>
     <t>9999</t>
@@ -2005,34 +2131,34 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{767F6232-E645-4A39-BF9A-057190255A70}">
-  <dimension ref="A1:H337"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E418CEC2-71E4-477F-B2C9-1ADD17A8D4DA}">
+  <dimension ref="A1:H365"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
-        <v>504</v>
+        <v>546</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>505</v>
+        <v>547</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>506</v>
+        <v>548</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>507</v>
+        <v>549</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>508</v>
+        <v>550</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>509</v>
+        <v>551</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>510</v>
+        <v>552</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>511</v>
+        <v>553</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
@@ -6781,13 +6907,13 @@
         <v>56</v>
       </c>
       <c r="E184" t="s">
-        <v>72</v>
+        <v>297</v>
       </c>
       <c r="F184" s="1">
         <v>46252</v>
       </c>
       <c r="G184" s="1">
-        <v>46252</v>
+        <v>46254</v>
       </c>
       <c r="H184">
         <v>0</v>
@@ -6807,7 +6933,7 @@
         <v>56</v>
       </c>
       <c r="E185" t="s">
-        <v>249</v>
+        <v>72</v>
       </c>
       <c r="F185" s="1">
         <v>46252</v>
@@ -6833,7 +6959,7 @@
         <v>56</v>
       </c>
       <c r="E186" t="s">
-        <v>66</v>
+        <v>249</v>
       </c>
       <c r="F186" s="1">
         <v>46252</v>
@@ -6859,7 +6985,7 @@
         <v>56</v>
       </c>
       <c r="E187" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="F187" s="1">
         <v>46252</v>
@@ -6885,7 +7011,7 @@
         <v>56</v>
       </c>
       <c r="E188" t="s">
-        <v>70</v>
+        <v>54</v>
       </c>
       <c r="F188" s="1">
         <v>46252</v>
@@ -6911,7 +7037,7 @@
         <v>56</v>
       </c>
       <c r="E189" t="s">
-        <v>305</v>
+        <v>70</v>
       </c>
       <c r="F189" s="1">
         <v>46252</v>
@@ -6928,22 +7054,22 @@
         <v>0</v>
       </c>
       <c r="B190" t="s">
+        <v>305</v>
+      </c>
+      <c r="C190">
+        <v>1</v>
+      </c>
+      <c r="D190" t="s">
+        <v>56</v>
+      </c>
+      <c r="E190" t="s">
         <v>306</v>
-      </c>
-      <c r="C190">
-        <v>1</v>
-      </c>
-      <c r="D190" t="s">
-        <v>56</v>
-      </c>
-      <c r="E190" t="s">
-        <v>83</v>
       </c>
       <c r="F190" s="1">
         <v>46252</v>
       </c>
       <c r="G190" s="1">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="H190">
         <v>0</v>
@@ -6963,7 +7089,7 @@
         <v>56</v>
       </c>
       <c r="E191" t="s">
-        <v>259</v>
+        <v>83</v>
       </c>
       <c r="F191" s="1">
         <v>46252</v>
@@ -6989,13 +7115,13 @@
         <v>56</v>
       </c>
       <c r="E192" t="s">
-        <v>159</v>
+        <v>259</v>
       </c>
       <c r="F192" s="1">
         <v>46252</v>
       </c>
       <c r="G192" s="1">
-        <v>46254</v>
+        <v>46253</v>
       </c>
       <c r="H192">
         <v>0</v>
@@ -7012,19 +7138,19 @@
         <v>1</v>
       </c>
       <c r="D193" t="s">
-        <v>2</v>
+        <v>56</v>
       </c>
       <c r="E193" t="s">
-        <v>172</v>
+        <v>159</v>
       </c>
       <c r="F193" s="1">
         <v>46252</v>
       </c>
       <c r="G193" s="1">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="H193">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="194" spans="1:8" x14ac:dyDescent="0.2">
@@ -7038,19 +7164,19 @@
         <v>1</v>
       </c>
       <c r="D194" t="s">
-        <v>56</v>
+        <v>2</v>
       </c>
       <c r="E194" t="s">
-        <v>311</v>
+        <v>172</v>
       </c>
       <c r="F194" s="1">
         <v>46252</v>
       </c>
       <c r="G194" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="H194">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="195" spans="1:8" x14ac:dyDescent="0.2">
@@ -7058,7 +7184,7 @@
         <v>0</v>
       </c>
       <c r="B195" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C195">
         <v>1</v>
@@ -7067,13 +7193,13 @@
         <v>56</v>
       </c>
       <c r="E195" t="s">
-        <v>132</v>
+        <v>174</v>
       </c>
       <c r="F195" s="1">
         <v>46252</v>
       </c>
       <c r="G195" s="1">
-        <v>46252</v>
+        <v>46254</v>
       </c>
       <c r="H195">
         <v>0</v>
@@ -7084,16 +7210,16 @@
         <v>0</v>
       </c>
       <c r="B196" t="s">
+        <v>312</v>
+      </c>
+      <c r="C196">
+        <v>1</v>
+      </c>
+      <c r="D196" t="s">
+        <v>56</v>
+      </c>
+      <c r="E196" t="s">
         <v>313</v>
-      </c>
-      <c r="C196">
-        <v>1</v>
-      </c>
-      <c r="D196" t="s">
-        <v>56</v>
-      </c>
-      <c r="E196" t="s">
-        <v>132</v>
       </c>
       <c r="F196" s="1">
         <v>46252</v>
@@ -7119,13 +7245,13 @@
         <v>56</v>
       </c>
       <c r="E197" t="s">
-        <v>315</v>
+        <v>132</v>
       </c>
       <c r="F197" s="1">
         <v>46252</v>
       </c>
       <c r="G197" s="1">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="H197">
         <v>0</v>
@@ -7136,25 +7262,25 @@
         <v>0</v>
       </c>
       <c r="B198" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C198">
         <v>1</v>
       </c>
       <c r="D198" t="s">
-        <v>2</v>
+        <v>56</v>
       </c>
       <c r="E198" t="s">
-        <v>317</v>
+        <v>132</v>
       </c>
       <c r="F198" s="1">
         <v>46252</v>
       </c>
       <c r="G198" s="1">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="H198">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="199" spans="1:8" x14ac:dyDescent="0.2">
@@ -7162,16 +7288,16 @@
         <v>0</v>
       </c>
       <c r="B199" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C199">
         <v>1</v>
       </c>
       <c r="D199" t="s">
-        <v>2</v>
+        <v>56</v>
       </c>
       <c r="E199" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="F199" s="1">
         <v>46252</v>
@@ -7180,7 +7306,7 @@
         <v>46253</v>
       </c>
       <c r="H199">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="200" spans="1:8" x14ac:dyDescent="0.2">
@@ -7188,7 +7314,7 @@
         <v>0</v>
       </c>
       <c r="B200" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C200">
         <v>1</v>
@@ -7197,16 +7323,16 @@
         <v>2</v>
       </c>
       <c r="E200" t="s">
-        <v>236</v>
+        <v>319</v>
       </c>
       <c r="F200" s="1">
         <v>46252</v>
       </c>
       <c r="G200" s="1">
-        <v>46254</v>
+        <v>46253</v>
       </c>
       <c r="H200">
-        <v>1</v>
+        <v>16</v>
       </c>
     </row>
     <row r="201" spans="1:8" x14ac:dyDescent="0.2">
@@ -7214,16 +7340,16 @@
         <v>0</v>
       </c>
       <c r="B201" t="s">
+        <v>320</v>
+      </c>
+      <c r="C201">
+        <v>1</v>
+      </c>
+      <c r="D201" t="s">
+        <v>2</v>
+      </c>
+      <c r="E201" t="s">
         <v>321</v>
-      </c>
-      <c r="C201">
-        <v>1</v>
-      </c>
-      <c r="D201" t="s">
-        <v>56</v>
-      </c>
-      <c r="E201" t="s">
-        <v>322</v>
       </c>
       <c r="F201" s="1">
         <v>46252</v>
@@ -7232,7 +7358,7 @@
         <v>46253</v>
       </c>
       <c r="H201">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="202" spans="1:8" x14ac:dyDescent="0.2">
@@ -7240,25 +7366,25 @@
         <v>0</v>
       </c>
       <c r="B202" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C202">
         <v>1</v>
       </c>
       <c r="D202" t="s">
-        <v>56</v>
+        <v>2</v>
       </c>
       <c r="E202" t="s">
-        <v>324</v>
+        <v>236</v>
       </c>
       <c r="F202" s="1">
         <v>46252</v>
       </c>
       <c r="G202" s="1">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="H202">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="203" spans="1:8" x14ac:dyDescent="0.2">
@@ -7266,7 +7392,7 @@
         <v>0</v>
       </c>
       <c r="B203" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C203">
         <v>1</v>
@@ -7292,22 +7418,22 @@
         <v>0</v>
       </c>
       <c r="B204" t="s">
+        <v>325</v>
+      </c>
+      <c r="C204">
+        <v>1</v>
+      </c>
+      <c r="D204" t="s">
+        <v>56</v>
+      </c>
+      <c r="E204" t="s">
         <v>326</v>
-      </c>
-      <c r="C204">
-        <v>1</v>
-      </c>
-      <c r="D204" t="s">
-        <v>56</v>
-      </c>
-      <c r="E204" t="s">
-        <v>204</v>
       </c>
       <c r="F204" s="1">
         <v>46252</v>
       </c>
       <c r="G204" s="1">
-        <v>46254</v>
+        <v>46253</v>
       </c>
       <c r="H204">
         <v>0</v>
@@ -7324,10 +7450,10 @@
         <v>1</v>
       </c>
       <c r="D205" t="s">
-        <v>56</v>
+        <v>2</v>
       </c>
       <c r="E205" t="s">
-        <v>204</v>
+        <v>326</v>
       </c>
       <c r="F205" s="1">
         <v>46252</v>
@@ -7336,7 +7462,7 @@
         <v>46253</v>
       </c>
       <c r="H205">
-        <v>0</v>
+        <v>52</v>
       </c>
     </row>
     <row r="206" spans="1:8" x14ac:dyDescent="0.2">
@@ -7353,7 +7479,7 @@
         <v>56</v>
       </c>
       <c r="E206" t="s">
-        <v>134</v>
+        <v>204</v>
       </c>
       <c r="F206" s="1">
         <v>46252</v>
@@ -7379,13 +7505,13 @@
         <v>56</v>
       </c>
       <c r="E207" t="s">
-        <v>134</v>
+        <v>204</v>
       </c>
       <c r="F207" s="1">
         <v>46252</v>
       </c>
       <c r="G207" s="1">
-        <v>46254</v>
+        <v>46253</v>
       </c>
       <c r="H207">
         <v>0</v>
@@ -7405,13 +7531,13 @@
         <v>56</v>
       </c>
       <c r="E208" t="s">
-        <v>163</v>
+        <v>134</v>
       </c>
       <c r="F208" s="1">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="G208" s="1">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="H208">
         <v>0</v>
@@ -7431,13 +7557,13 @@
         <v>56</v>
       </c>
       <c r="E209" t="s">
-        <v>163</v>
+        <v>134</v>
       </c>
       <c r="F209" s="1">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="G209" s="1">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="H209">
         <v>0</v>
@@ -7457,7 +7583,7 @@
         <v>56</v>
       </c>
       <c r="E210" t="s">
-        <v>333</v>
+        <v>163</v>
       </c>
       <c r="F210" s="1">
         <v>46253</v>
@@ -7474,25 +7600,25 @@
         <v>0</v>
       </c>
       <c r="B211" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C211">
         <v>1</v>
       </c>
       <c r="D211" t="s">
-        <v>56</v>
+        <v>2</v>
       </c>
       <c r="E211" t="s">
-        <v>335</v>
+        <v>163</v>
       </c>
       <c r="F211" s="1">
         <v>46253</v>
       </c>
       <c r="G211" s="1">
-        <v>46254</v>
+        <v>46253</v>
       </c>
       <c r="H211">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="212" spans="1:8" x14ac:dyDescent="0.2">
@@ -7500,7 +7626,7 @@
         <v>0</v>
       </c>
       <c r="B212" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C212">
         <v>1</v>
@@ -7509,7 +7635,7 @@
         <v>56</v>
       </c>
       <c r="E212" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="F212" s="1">
         <v>46253</v>
@@ -7526,22 +7652,22 @@
         <v>0</v>
       </c>
       <c r="B213" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C213">
         <v>1</v>
       </c>
       <c r="D213" t="s">
-        <v>5</v>
+        <v>56</v>
       </c>
       <c r="E213" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="F213" s="1">
         <v>46253</v>
       </c>
       <c r="G213" s="1">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="H213">
         <v>0</v>
@@ -7552,16 +7678,16 @@
         <v>0</v>
       </c>
       <c r="B214" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C214">
         <v>1</v>
       </c>
       <c r="D214" t="s">
-        <v>56</v>
+        <v>2</v>
       </c>
       <c r="E214" t="s">
-        <v>26</v>
+        <v>339</v>
       </c>
       <c r="F214" s="1">
         <v>46253</v>
@@ -7570,7 +7696,7 @@
         <v>46253</v>
       </c>
       <c r="H214">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="215" spans="1:8" x14ac:dyDescent="0.2">
@@ -7578,16 +7704,16 @@
         <v>0</v>
       </c>
       <c r="B215" t="s">
+        <v>340</v>
+      </c>
+      <c r="C215">
+        <v>1</v>
+      </c>
+      <c r="D215" t="s">
+        <v>5</v>
+      </c>
+      <c r="E215" t="s">
         <v>341</v>
-      </c>
-      <c r="C215">
-        <v>1</v>
-      </c>
-      <c r="D215" t="s">
-        <v>2</v>
-      </c>
-      <c r="E215" t="s">
-        <v>26</v>
       </c>
       <c r="F215" s="1">
         <v>46253</v>
@@ -7596,7 +7722,7 @@
         <v>46253</v>
       </c>
       <c r="H215">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="216" spans="1:8" x14ac:dyDescent="0.2">
@@ -7610,7 +7736,7 @@
         <v>1</v>
       </c>
       <c r="D216" t="s">
-        <v>2</v>
+        <v>56</v>
       </c>
       <c r="E216" t="s">
         <v>26</v>
@@ -7622,7 +7748,7 @@
         <v>46253</v>
       </c>
       <c r="H216">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="217" spans="1:8" x14ac:dyDescent="0.2">
@@ -7639,7 +7765,7 @@
         <v>2</v>
       </c>
       <c r="E217" t="s">
-        <v>122</v>
+        <v>26</v>
       </c>
       <c r="F217" s="1">
         <v>46253</v>
@@ -7648,7 +7774,7 @@
         <v>46253</v>
       </c>
       <c r="H217">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="218" spans="1:8" x14ac:dyDescent="0.2">
@@ -7665,7 +7791,7 @@
         <v>2</v>
       </c>
       <c r="E218" t="s">
-        <v>122</v>
+        <v>26</v>
       </c>
       <c r="F218" s="1">
         <v>46253</v>
@@ -7691,7 +7817,7 @@
         <v>2</v>
       </c>
       <c r="E219" t="s">
-        <v>346</v>
+        <v>122</v>
       </c>
       <c r="F219" s="1">
         <v>46253</v>
@@ -7700,7 +7826,7 @@
         <v>46253</v>
       </c>
       <c r="H219">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="220" spans="1:8" x14ac:dyDescent="0.2">
@@ -7708,16 +7834,16 @@
         <v>0</v>
       </c>
       <c r="B220" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C220">
         <v>1</v>
       </c>
       <c r="D220" t="s">
-        <v>56</v>
+        <v>2</v>
       </c>
       <c r="E220" t="s">
-        <v>66</v>
+        <v>122</v>
       </c>
       <c r="F220" s="1">
         <v>46253</v>
@@ -7726,7 +7852,7 @@
         <v>46253</v>
       </c>
       <c r="H220">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="221" spans="1:8" x14ac:dyDescent="0.2">
@@ -7734,16 +7860,16 @@
         <v>0</v>
       </c>
       <c r="B221" t="s">
+        <v>347</v>
+      </c>
+      <c r="C221">
+        <v>1</v>
+      </c>
+      <c r="D221" t="s">
+        <v>2</v>
+      </c>
+      <c r="E221" t="s">
         <v>348</v>
-      </c>
-      <c r="C221">
-        <v>1</v>
-      </c>
-      <c r="D221" t="s">
-        <v>56</v>
-      </c>
-      <c r="E221" t="s">
-        <v>144</v>
       </c>
       <c r="F221" s="1">
         <v>46253</v>
@@ -7752,7 +7878,7 @@
         <v>46253</v>
       </c>
       <c r="H221">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="222" spans="1:8" x14ac:dyDescent="0.2">
@@ -7769,7 +7895,7 @@
         <v>56</v>
       </c>
       <c r="E222" t="s">
-        <v>350</v>
+        <v>66</v>
       </c>
       <c r="F222" s="1">
         <v>46253</v>
@@ -7786,7 +7912,7 @@
         <v>0</v>
       </c>
       <c r="B223" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C223">
         <v>1</v>
@@ -7795,7 +7921,7 @@
         <v>56</v>
       </c>
       <c r="E223" t="s">
-        <v>352</v>
+        <v>144</v>
       </c>
       <c r="F223" s="1">
         <v>46253</v>
@@ -7812,16 +7938,16 @@
         <v>0</v>
       </c>
       <c r="B224" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C224">
         <v>1</v>
       </c>
       <c r="D224" t="s">
-        <v>2</v>
+        <v>56</v>
       </c>
       <c r="E224" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="F224" s="1">
         <v>46253</v>
@@ -7830,7 +7956,7 @@
         <v>46253</v>
       </c>
       <c r="H224">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="225" spans="1:8" x14ac:dyDescent="0.2">
@@ -7838,7 +7964,7 @@
         <v>0</v>
       </c>
       <c r="B225" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C225">
         <v>1</v>
@@ -7847,7 +7973,7 @@
         <v>56</v>
       </c>
       <c r="E225" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="F225" s="1">
         <v>46253</v>
@@ -7864,16 +7990,16 @@
         <v>0</v>
       </c>
       <c r="B226" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C226">
         <v>1</v>
       </c>
       <c r="D226" t="s">
-        <v>56</v>
+        <v>2</v>
       </c>
       <c r="E226" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="F226" s="1">
         <v>46253</v>
@@ -7882,7 +8008,7 @@
         <v>46253</v>
       </c>
       <c r="H226">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="227" spans="1:8" x14ac:dyDescent="0.2">
@@ -7890,7 +8016,7 @@
         <v>0</v>
       </c>
       <c r="B227" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C227">
         <v>1</v>
@@ -7899,7 +8025,7 @@
         <v>56</v>
       </c>
       <c r="E227" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="F227" s="1">
         <v>46253</v>
@@ -7916,7 +8042,7 @@
         <v>0</v>
       </c>
       <c r="B228" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C228">
         <v>1</v>
@@ -7925,7 +8051,7 @@
         <v>56</v>
       </c>
       <c r="E228" t="s">
-        <v>311</v>
+        <v>360</v>
       </c>
       <c r="F228" s="1">
         <v>46253</v>
@@ -7942,16 +8068,16 @@
         <v>0</v>
       </c>
       <c r="B229" t="s">
+        <v>361</v>
+      </c>
+      <c r="C229">
+        <v>1</v>
+      </c>
+      <c r="D229" t="s">
+        <v>56</v>
+      </c>
+      <c r="E229" t="s">
         <v>362</v>
-      </c>
-      <c r="C229">
-        <v>1</v>
-      </c>
-      <c r="D229" t="s">
-        <v>56</v>
-      </c>
-      <c r="E229" t="s">
-        <v>363</v>
       </c>
       <c r="F229" s="1">
         <v>46253</v>
@@ -7968,7 +8094,7 @@
         <v>0</v>
       </c>
       <c r="B230" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C230">
         <v>1</v>
@@ -7977,7 +8103,7 @@
         <v>56</v>
       </c>
       <c r="E230" t="s">
-        <v>365</v>
+        <v>313</v>
       </c>
       <c r="F230" s="1">
         <v>46253</v>
@@ -7994,7 +8120,7 @@
         <v>0</v>
       </c>
       <c r="B231" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C231">
         <v>1</v>
@@ -8003,13 +8129,13 @@
         <v>56</v>
       </c>
       <c r="E231" t="s">
-        <v>16</v>
+        <v>365</v>
       </c>
       <c r="F231" s="1">
         <v>46253</v>
       </c>
       <c r="G231" s="1">
-        <v>46254</v>
+        <v>46253</v>
       </c>
       <c r="H231">
         <v>0</v>
@@ -8020,16 +8146,16 @@
         <v>0</v>
       </c>
       <c r="B232" t="s">
+        <v>366</v>
+      </c>
+      <c r="C232">
+        <v>1</v>
+      </c>
+      <c r="D232" t="s">
+        <v>56</v>
+      </c>
+      <c r="E232" t="s">
         <v>367</v>
-      </c>
-      <c r="C232">
-        <v>1</v>
-      </c>
-      <c r="D232" t="s">
-        <v>56</v>
-      </c>
-      <c r="E232" t="s">
-        <v>368</v>
       </c>
       <c r="F232" s="1">
         <v>46253</v>
@@ -8046,7 +8172,7 @@
         <v>0</v>
       </c>
       <c r="B233" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C233">
         <v>1</v>
@@ -8055,13 +8181,13 @@
         <v>56</v>
       </c>
       <c r="E233" t="s">
-        <v>370</v>
+        <v>16</v>
       </c>
       <c r="F233" s="1">
         <v>46253</v>
       </c>
       <c r="G233" s="1">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="H233">
         <v>0</v>
@@ -8072,7 +8198,7 @@
         <v>0</v>
       </c>
       <c r="B234" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C234">
         <v>1</v>
@@ -8081,7 +8207,7 @@
         <v>56</v>
       </c>
       <c r="E234" t="s">
-        <v>139</v>
+        <v>370</v>
       </c>
       <c r="F234" s="1">
         <v>46253</v>
@@ -8098,16 +8224,16 @@
         <v>0</v>
       </c>
       <c r="B235" t="s">
+        <v>371</v>
+      </c>
+      <c r="C235">
+        <v>1</v>
+      </c>
+      <c r="D235" t="s">
+        <v>56</v>
+      </c>
+      <c r="E235" t="s">
         <v>372</v>
-      </c>
-      <c r="C235">
-        <v>1</v>
-      </c>
-      <c r="D235" t="s">
-        <v>56</v>
-      </c>
-      <c r="E235" t="s">
-        <v>311</v>
       </c>
       <c r="F235" s="1">
         <v>46253</v>
@@ -8133,7 +8259,7 @@
         <v>56</v>
       </c>
       <c r="E236" t="s">
-        <v>26</v>
+        <v>139</v>
       </c>
       <c r="F236" s="1">
         <v>46253</v>
@@ -8159,7 +8285,7 @@
         <v>56</v>
       </c>
       <c r="E237" t="s">
-        <v>26</v>
+        <v>313</v>
       </c>
       <c r="F237" s="1">
         <v>46253</v>
@@ -8338,10 +8464,10 @@
         <v>1</v>
       </c>
       <c r="D244" t="s">
-        <v>2</v>
+        <v>56</v>
       </c>
       <c r="E244" t="s">
-        <v>382</v>
+        <v>26</v>
       </c>
       <c r="F244" s="1">
         <v>46253</v>
@@ -8350,7 +8476,7 @@
         <v>46253</v>
       </c>
       <c r="H244">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="245" spans="1:8" x14ac:dyDescent="0.2">
@@ -8358,7 +8484,7 @@
         <v>0</v>
       </c>
       <c r="B245" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C245">
         <v>1</v>
@@ -8367,7 +8493,7 @@
         <v>56</v>
       </c>
       <c r="E245" t="s">
-        <v>384</v>
+        <v>26</v>
       </c>
       <c r="F245" s="1">
         <v>46253</v>
@@ -8384,16 +8510,16 @@
         <v>0</v>
       </c>
       <c r="B246" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="C246">
         <v>1</v>
       </c>
       <c r="D246" t="s">
-        <v>56</v>
+        <v>2</v>
       </c>
       <c r="E246" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="F246" s="1">
         <v>46253</v>
@@ -8402,7 +8528,7 @@
         <v>46253</v>
       </c>
       <c r="H246">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="247" spans="1:8" x14ac:dyDescent="0.2">
@@ -8410,16 +8536,16 @@
         <v>0</v>
       </c>
       <c r="B247" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C247">
         <v>1</v>
       </c>
       <c r="D247" t="s">
-        <v>2</v>
+        <v>56</v>
       </c>
       <c r="E247" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="F247" s="1">
         <v>46253</v>
@@ -8428,7 +8554,7 @@
         <v>46253</v>
       </c>
       <c r="H247">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="248" spans="1:8" x14ac:dyDescent="0.2">
@@ -8436,16 +8562,16 @@
         <v>0</v>
       </c>
       <c r="B248" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C248">
         <v>1</v>
       </c>
       <c r="D248" t="s">
-        <v>2</v>
+        <v>56</v>
       </c>
       <c r="E248" t="s">
-        <v>335</v>
+        <v>388</v>
       </c>
       <c r="F248" s="1">
         <v>46253</v>
@@ -8454,7 +8580,7 @@
         <v>46253</v>
       </c>
       <c r="H248">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="249" spans="1:8" x14ac:dyDescent="0.2">
@@ -8462,25 +8588,25 @@
         <v>0</v>
       </c>
       <c r="B249" t="s">
+        <v>389</v>
+      </c>
+      <c r="C249">
+        <v>1</v>
+      </c>
+      <c r="D249" t="s">
+        <v>2</v>
+      </c>
+      <c r="E249" t="s">
         <v>390</v>
-      </c>
-      <c r="C249">
-        <v>1</v>
-      </c>
-      <c r="D249" t="s">
-        <v>56</v>
-      </c>
-      <c r="E249" t="s">
-        <v>391</v>
       </c>
       <c r="F249" s="1">
         <v>46253</v>
       </c>
       <c r="G249" s="1">
-        <v>46254</v>
+        <v>46253</v>
       </c>
       <c r="H249">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="250" spans="1:8" x14ac:dyDescent="0.2">
@@ -8488,25 +8614,25 @@
         <v>0</v>
       </c>
       <c r="B250" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C250">
         <v>1</v>
       </c>
       <c r="D250" t="s">
-        <v>56</v>
+        <v>2</v>
       </c>
       <c r="E250" t="s">
-        <v>20</v>
+        <v>337</v>
       </c>
       <c r="F250" s="1">
         <v>46253</v>
       </c>
       <c r="G250" s="1">
-        <v>46254</v>
+        <v>46253</v>
       </c>
       <c r="H250">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="251" spans="1:8" x14ac:dyDescent="0.2">
@@ -8514,16 +8640,16 @@
         <v>0</v>
       </c>
       <c r="B251" t="s">
+        <v>392</v>
+      </c>
+      <c r="C251">
+        <v>1</v>
+      </c>
+      <c r="D251" t="s">
+        <v>56</v>
+      </c>
+      <c r="E251" t="s">
         <v>393</v>
-      </c>
-      <c r="C251">
-        <v>1</v>
-      </c>
-      <c r="D251" t="s">
-        <v>56</v>
-      </c>
-      <c r="E251" t="s">
-        <v>394</v>
       </c>
       <c r="F251" s="1">
         <v>46253</v>
@@ -8540,7 +8666,7 @@
         <v>0</v>
       </c>
       <c r="B252" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C252">
         <v>1</v>
@@ -8549,7 +8675,7 @@
         <v>56</v>
       </c>
       <c r="E252" t="s">
-        <v>394</v>
+        <v>20</v>
       </c>
       <c r="F252" s="1">
         <v>46253</v>
@@ -8566,16 +8692,16 @@
         <v>0</v>
       </c>
       <c r="B253" t="s">
+        <v>395</v>
+      </c>
+      <c r="C253">
+        <v>1</v>
+      </c>
+      <c r="D253" t="s">
+        <v>56</v>
+      </c>
+      <c r="E253" t="s">
         <v>396</v>
-      </c>
-      <c r="C253">
-        <v>1</v>
-      </c>
-      <c r="D253" t="s">
-        <v>56</v>
-      </c>
-      <c r="E253" t="s">
-        <v>397</v>
       </c>
       <c r="F253" s="1">
         <v>46253</v>
@@ -8592,7 +8718,7 @@
         <v>0</v>
       </c>
       <c r="B254" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C254">
         <v>1</v>
@@ -8601,7 +8727,7 @@
         <v>56</v>
       </c>
       <c r="E254" t="s">
-        <v>52</v>
+        <v>396</v>
       </c>
       <c r="F254" s="1">
         <v>46253</v>
@@ -8618,16 +8744,16 @@
         <v>0</v>
       </c>
       <c r="B255" t="s">
+        <v>398</v>
+      </c>
+      <c r="C255">
+        <v>1</v>
+      </c>
+      <c r="D255" t="s">
+        <v>56</v>
+      </c>
+      <c r="E255" t="s">
         <v>399</v>
-      </c>
-      <c r="C255">
-        <v>1</v>
-      </c>
-      <c r="D255" t="s">
-        <v>56</v>
-      </c>
-      <c r="E255" t="s">
-        <v>52</v>
       </c>
       <c r="F255" s="1">
         <v>46253</v>
@@ -8679,7 +8805,7 @@
         <v>56</v>
       </c>
       <c r="E257" t="s">
-        <v>18</v>
+        <v>52</v>
       </c>
       <c r="F257" s="1">
         <v>46253</v>
@@ -8705,7 +8831,7 @@
         <v>56</v>
       </c>
       <c r="E258" t="s">
-        <v>403</v>
+        <v>52</v>
       </c>
       <c r="F258" s="1">
         <v>46253</v>
@@ -8722,16 +8848,16 @@
         <v>0</v>
       </c>
       <c r="B259" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C259">
         <v>1</v>
       </c>
       <c r="D259" t="s">
-        <v>5</v>
+        <v>56</v>
       </c>
       <c r="E259" t="s">
-        <v>405</v>
+        <v>18</v>
       </c>
       <c r="F259" s="1">
         <v>46253</v>
@@ -8748,7 +8874,7 @@
         <v>0</v>
       </c>
       <c r="B260" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="C260">
         <v>1</v>
@@ -8757,7 +8883,7 @@
         <v>56</v>
       </c>
       <c r="E260" t="s">
-        <v>281</v>
+        <v>405</v>
       </c>
       <c r="F260" s="1">
         <v>46253</v>
@@ -8774,19 +8900,19 @@
         <v>0</v>
       </c>
       <c r="B261" t="s">
+        <v>406</v>
+      </c>
+      <c r="C261">
+        <v>2</v>
+      </c>
+      <c r="D261" t="s">
+        <v>56</v>
+      </c>
+      <c r="E261" t="s">
         <v>407</v>
       </c>
-      <c r="C261">
-        <v>1</v>
-      </c>
-      <c r="D261" t="s">
-        <v>56</v>
-      </c>
-      <c r="E261" t="s">
-        <v>132</v>
-      </c>
       <c r="F261" s="1">
-        <v>46254</v>
+        <v>46253</v>
       </c>
       <c r="G261" s="1">
         <v>46254</v>
@@ -8809,10 +8935,10 @@
         <v>56</v>
       </c>
       <c r="E262" t="s">
-        <v>70</v>
+        <v>281</v>
       </c>
       <c r="F262" s="1">
-        <v>46254</v>
+        <v>46253</v>
       </c>
       <c r="G262" s="1">
         <v>46254</v>
@@ -8835,7 +8961,7 @@
         <v>56</v>
       </c>
       <c r="E263" t="s">
-        <v>410</v>
+        <v>132</v>
       </c>
       <c r="F263" s="1">
         <v>46254</v>
@@ -8852,16 +8978,16 @@
         <v>0</v>
       </c>
       <c r="B264" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C264">
         <v>1</v>
       </c>
       <c r="D264" t="s">
-        <v>2</v>
+        <v>56</v>
       </c>
       <c r="E264" t="s">
-        <v>412</v>
+        <v>70</v>
       </c>
       <c r="F264" s="1">
         <v>46254</v>
@@ -8870,7 +8996,7 @@
         <v>46254</v>
       </c>
       <c r="H264">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="265" spans="1:8" x14ac:dyDescent="0.2">
@@ -8878,7 +9004,7 @@
         <v>0</v>
       </c>
       <c r="B265" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C265">
         <v>1</v>
@@ -8887,7 +9013,7 @@
         <v>56</v>
       </c>
       <c r="E265" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="F265" s="1">
         <v>46254</v>
@@ -8904,16 +9030,16 @@
         <v>0</v>
       </c>
       <c r="B266" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="C266">
         <v>1</v>
       </c>
       <c r="D266" t="s">
-        <v>56</v>
+        <v>2</v>
       </c>
       <c r="E266" t="s">
-        <v>122</v>
+        <v>414</v>
       </c>
       <c r="F266" s="1">
         <v>46254</v>
@@ -8922,7 +9048,7 @@
         <v>46254</v>
       </c>
       <c r="H266">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="267" spans="1:8" x14ac:dyDescent="0.2">
@@ -8930,16 +9056,16 @@
         <v>0</v>
       </c>
       <c r="B267" t="s">
+        <v>415</v>
+      </c>
+      <c r="C267">
+        <v>1</v>
+      </c>
+      <c r="D267" t="s">
+        <v>56</v>
+      </c>
+      <c r="E267" t="s">
         <v>416</v>
-      </c>
-      <c r="C267">
-        <v>1</v>
-      </c>
-      <c r="D267" t="s">
-        <v>56</v>
-      </c>
-      <c r="E267" t="s">
-        <v>26</v>
       </c>
       <c r="F267" s="1">
         <v>46254</v>
@@ -8965,7 +9091,7 @@
         <v>56</v>
       </c>
       <c r="E268" t="s">
-        <v>26</v>
+        <v>122</v>
       </c>
       <c r="F268" s="1">
         <v>46254</v>
@@ -9017,7 +9143,7 @@
         <v>56</v>
       </c>
       <c r="E270" t="s">
-        <v>420</v>
+        <v>26</v>
       </c>
       <c r="F270" s="1">
         <v>46254</v>
@@ -9034,7 +9160,7 @@
         <v>0</v>
       </c>
       <c r="B271" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C271">
         <v>1</v>
@@ -9043,7 +9169,7 @@
         <v>56</v>
       </c>
       <c r="E271" t="s">
-        <v>420</v>
+        <v>26</v>
       </c>
       <c r="F271" s="1">
         <v>46254</v>
@@ -9060,16 +9186,16 @@
         <v>0</v>
       </c>
       <c r="B272" t="s">
+        <v>421</v>
+      </c>
+      <c r="C272">
+        <v>1</v>
+      </c>
+      <c r="D272" t="s">
+        <v>56</v>
+      </c>
+      <c r="E272" t="s">
         <v>422</v>
-      </c>
-      <c r="C272">
-        <v>1</v>
-      </c>
-      <c r="D272" t="s">
-        <v>56</v>
-      </c>
-      <c r="E272" t="s">
-        <v>14</v>
       </c>
       <c r="F272" s="1">
         <v>46254</v>
@@ -9095,7 +9221,7 @@
         <v>56</v>
       </c>
       <c r="E273" t="s">
-        <v>34</v>
+        <v>422</v>
       </c>
       <c r="F273" s="1">
         <v>46254</v>
@@ -9121,7 +9247,7 @@
         <v>56</v>
       </c>
       <c r="E274" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F274" s="1">
         <v>46254</v>
@@ -9147,7 +9273,7 @@
         <v>56</v>
       </c>
       <c r="E275" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="F275" s="1">
         <v>46254</v>
@@ -9173,7 +9299,7 @@
         <v>56</v>
       </c>
       <c r="E276" t="s">
-        <v>427</v>
+        <v>12</v>
       </c>
       <c r="F276" s="1">
         <v>46254</v>
@@ -9190,7 +9316,7 @@
         <v>0</v>
       </c>
       <c r="B277" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C277">
         <v>1</v>
@@ -9199,7 +9325,7 @@
         <v>56</v>
       </c>
       <c r="E277" t="s">
-        <v>94</v>
+        <v>12</v>
       </c>
       <c r="F277" s="1">
         <v>46254</v>
@@ -9216,16 +9342,16 @@
         <v>0</v>
       </c>
       <c r="B278" t="s">
+        <v>428</v>
+      </c>
+      <c r="C278">
+        <v>1</v>
+      </c>
+      <c r="D278" t="s">
+        <v>56</v>
+      </c>
+      <c r="E278" t="s">
         <v>429</v>
-      </c>
-      <c r="C278">
-        <v>1</v>
-      </c>
-      <c r="D278" t="s">
-        <v>56</v>
-      </c>
-      <c r="E278" t="s">
-        <v>430</v>
       </c>
       <c r="F278" s="1">
         <v>46254</v>
@@ -9242,16 +9368,16 @@
         <v>0</v>
       </c>
       <c r="B279" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C279">
         <v>1</v>
       </c>
       <c r="D279" t="s">
-        <v>5</v>
+        <v>56</v>
       </c>
       <c r="E279" t="s">
-        <v>432</v>
+        <v>94</v>
       </c>
       <c r="F279" s="1">
         <v>46254</v>
@@ -9268,7 +9394,7 @@
         <v>0</v>
       </c>
       <c r="B280" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="C280">
         <v>1</v>
@@ -9277,7 +9403,7 @@
         <v>56</v>
       </c>
       <c r="E280" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="F280" s="1">
         <v>46254</v>
@@ -9291,51 +9417,51 @@
     </row>
     <row r="281" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A281" t="s">
-        <v>435</v>
+        <v>0</v>
       </c>
       <c r="B281" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C281">
         <v>1</v>
       </c>
       <c r="D281" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E281" t="s">
-        <v>275</v>
+        <v>434</v>
       </c>
       <c r="F281" s="1">
-        <v>46148</v>
+        <v>46254</v>
       </c>
       <c r="G281" s="1">
-        <v>46149</v>
+        <v>46254</v>
       </c>
       <c r="H281">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="282" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A282" t="s">
-        <v>437</v>
+        <v>0</v>
       </c>
       <c r="B282" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="C282">
         <v>1</v>
       </c>
       <c r="D282" t="s">
-        <v>5</v>
+        <v>56</v>
       </c>
       <c r="E282" t="s">
-        <v>29</v>
+        <v>436</v>
       </c>
       <c r="F282" s="1">
-        <v>46133</v>
+        <v>46254</v>
       </c>
       <c r="G282" s="1">
-        <v>46134</v>
+        <v>46254</v>
       </c>
       <c r="H282">
         <v>0</v>
@@ -9343,25 +9469,25 @@
     </row>
     <row r="283" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A283" t="s">
+        <v>0</v>
+      </c>
+      <c r="B283" t="s">
         <v>437</v>
       </c>
-      <c r="B283" t="s">
-        <v>439</v>
-      </c>
       <c r="C283">
         <v>1</v>
       </c>
       <c r="D283" t="s">
-        <v>5</v>
+        <v>56</v>
       </c>
       <c r="E283" t="s">
-        <v>29</v>
+        <v>438</v>
       </c>
       <c r="F283" s="1">
-        <v>46134</v>
+        <v>46254</v>
       </c>
       <c r="G283" s="1">
-        <v>46134</v>
+        <v>46254</v>
       </c>
       <c r="H283">
         <v>0</v>
@@ -9369,25 +9495,25 @@
     </row>
     <row r="284" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A284" t="s">
-        <v>437</v>
+        <v>0</v>
       </c>
       <c r="B284" t="s">
+        <v>439</v>
+      </c>
+      <c r="C284">
+        <v>1</v>
+      </c>
+      <c r="D284" t="s">
+        <v>56</v>
+      </c>
+      <c r="E284" t="s">
         <v>440</v>
       </c>
-      <c r="C284">
-        <v>1</v>
-      </c>
-      <c r="D284" t="s">
-        <v>5</v>
-      </c>
-      <c r="E284" t="s">
-        <v>14</v>
-      </c>
       <c r="F284" s="1">
-        <v>46156</v>
+        <v>46254</v>
       </c>
       <c r="G284" s="1">
-        <v>46156</v>
+        <v>46254</v>
       </c>
       <c r="H284">
         <v>0</v>
@@ -9395,7 +9521,7 @@
     </row>
     <row r="285" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A285" t="s">
-        <v>437</v>
+        <v>0</v>
       </c>
       <c r="B285" t="s">
         <v>441</v>
@@ -9404,30 +9530,30 @@
         <v>1</v>
       </c>
       <c r="D285" t="s">
-        <v>2</v>
+        <v>56</v>
       </c>
       <c r="E285" t="s">
-        <v>434</v>
+        <v>54</v>
       </c>
       <c r="F285" s="1">
-        <v>46195</v>
+        <v>46254</v>
       </c>
       <c r="G285" s="1">
-        <v>46195</v>
+        <v>46254</v>
       </c>
       <c r="H285">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="286" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A286" t="s">
-        <v>437</v>
+        <v>0</v>
       </c>
       <c r="B286" t="s">
         <v>442</v>
       </c>
       <c r="C286">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D286" t="s">
         <v>56</v>
@@ -9436,10 +9562,10 @@
         <v>443</v>
       </c>
       <c r="F286" s="1">
-        <v>46206</v>
+        <v>46254</v>
       </c>
       <c r="G286" s="1">
-        <v>46252</v>
+        <v>46254</v>
       </c>
       <c r="H286">
         <v>0</v>
@@ -9447,51 +9573,51 @@
     </row>
     <row r="287" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A287" t="s">
-        <v>437</v>
+        <v>0</v>
       </c>
       <c r="B287" t="s">
         <v>444</v>
       </c>
       <c r="C287">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D287" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="E287" t="s">
-        <v>445</v>
+        <v>12</v>
       </c>
       <c r="F287" s="1">
-        <v>46209</v>
+        <v>46254</v>
       </c>
       <c r="G287" s="1">
-        <v>46218</v>
+        <v>46254</v>
       </c>
       <c r="H287">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="288" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A288" t="s">
-        <v>437</v>
+        <v>0</v>
       </c>
       <c r="B288" t="s">
+        <v>445</v>
+      </c>
+      <c r="C288">
+        <v>1</v>
+      </c>
+      <c r="D288" t="s">
+        <v>56</v>
+      </c>
+      <c r="E288" t="s">
         <v>446</v>
       </c>
-      <c r="C288">
-        <v>1</v>
-      </c>
-      <c r="D288" t="s">
-        <v>5</v>
-      </c>
-      <c r="E288" t="s">
-        <v>447</v>
-      </c>
       <c r="F288" s="1">
-        <v>46213</v>
+        <v>46254</v>
       </c>
       <c r="G288" s="1">
-        <v>46213</v>
+        <v>46254</v>
       </c>
       <c r="H288">
         <v>0</v>
@@ -9499,85 +9625,85 @@
     </row>
     <row r="289" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A289" t="s">
-        <v>437</v>
+        <v>0</v>
       </c>
       <c r="B289" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C289">
         <v>1</v>
       </c>
       <c r="D289" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="E289" t="s">
-        <v>208</v>
+        <v>3</v>
       </c>
       <c r="F289" s="1">
-        <v>46213</v>
+        <v>46254</v>
       </c>
       <c r="G289" s="1">
-        <v>46216</v>
+        <v>46254</v>
       </c>
       <c r="H289">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="290" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A290" t="s">
-        <v>437</v>
+        <v>0</v>
       </c>
       <c r="B290" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C290">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D290" t="s">
-        <v>2</v>
+        <v>56</v>
       </c>
       <c r="E290" t="s">
-        <v>94</v>
+        <v>57</v>
       </c>
       <c r="F290" s="1">
-        <v>46220</v>
+        <v>46254</v>
       </c>
       <c r="G290" s="1">
-        <v>46231</v>
+        <v>46254</v>
       </c>
       <c r="H290">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="291" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A291" t="s">
-        <v>437</v>
+        <v>0</v>
       </c>
       <c r="B291" t="s">
+        <v>449</v>
+      </c>
+      <c r="C291">
+        <v>1</v>
+      </c>
+      <c r="D291" t="s">
+        <v>56</v>
+      </c>
+      <c r="E291" t="s">
         <v>450</v>
       </c>
-      <c r="C291">
-        <v>1</v>
-      </c>
-      <c r="D291" t="s">
-        <v>2</v>
-      </c>
-      <c r="E291" t="s">
-        <v>434</v>
-      </c>
       <c r="F291" s="1">
-        <v>46223</v>
+        <v>46254</v>
       </c>
       <c r="G291" s="1">
-        <v>46223</v>
+        <v>46254</v>
       </c>
       <c r="H291">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="292" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A292" t="s">
-        <v>437</v>
+        <v>0</v>
       </c>
       <c r="B292" t="s">
         <v>451</v>
@@ -9586,24 +9712,24 @@
         <v>1</v>
       </c>
       <c r="D292" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="E292" t="s">
-        <v>208</v>
+        <v>132</v>
       </c>
       <c r="F292" s="1">
-        <v>46224</v>
+        <v>46254</v>
       </c>
       <c r="G292" s="1">
-        <v>46224</v>
+        <v>46254</v>
       </c>
       <c r="H292">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="293" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A293" t="s">
-        <v>437</v>
+        <v>0</v>
       </c>
       <c r="B293" t="s">
         <v>452</v>
@@ -9612,120 +9738,120 @@
         <v>1</v>
       </c>
       <c r="D293" t="s">
-        <v>2</v>
+        <v>56</v>
       </c>
       <c r="E293" t="s">
-        <v>434</v>
+        <v>453</v>
       </c>
       <c r="F293" s="1">
-        <v>46230</v>
+        <v>46254</v>
       </c>
       <c r="G293" s="1">
-        <v>46231</v>
+        <v>46254</v>
       </c>
       <c r="H293">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="294" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A294" t="s">
-        <v>437</v>
+        <v>0</v>
       </c>
       <c r="B294" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C294">
         <v>1</v>
       </c>
       <c r="D294" t="s">
-        <v>2</v>
+        <v>56</v>
       </c>
       <c r="E294" t="s">
-        <v>94</v>
+        <v>455</v>
       </c>
       <c r="F294" s="1">
-        <v>46232</v>
+        <v>46254</v>
       </c>
       <c r="G294" s="1">
-        <v>46233</v>
+        <v>46254</v>
       </c>
       <c r="H294">
-        <v>126</v>
+        <v>0</v>
       </c>
     </row>
     <row r="295" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A295" t="s">
-        <v>437</v>
+        <v>0</v>
       </c>
       <c r="B295" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="C295">
         <v>1</v>
       </c>
       <c r="D295" t="s">
-        <v>2</v>
+        <v>56</v>
       </c>
       <c r="E295" t="s">
-        <v>94</v>
+        <v>283</v>
       </c>
       <c r="F295" s="1">
-        <v>46232</v>
+        <v>46254</v>
       </c>
       <c r="G295" s="1">
-        <v>46233</v>
+        <v>46254</v>
       </c>
       <c r="H295">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="296" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A296" t="s">
-        <v>437</v>
+        <v>0</v>
       </c>
       <c r="B296" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="C296">
         <v>1</v>
       </c>
       <c r="D296" t="s">
-        <v>2</v>
+        <v>56</v>
       </c>
       <c r="E296" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="F296" s="1">
-        <v>46238</v>
+        <v>46254</v>
       </c>
       <c r="G296" s="1">
-        <v>46239</v>
+        <v>46254</v>
       </c>
       <c r="H296">
-        <v>117</v>
+        <v>0</v>
       </c>
     </row>
     <row r="297" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A297" t="s">
-        <v>437</v>
+        <v>0</v>
       </c>
       <c r="B297" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="C297">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D297" t="s">
         <v>56</v>
       </c>
       <c r="E297" t="s">
-        <v>443</v>
+        <v>459</v>
       </c>
       <c r="F297" s="1">
-        <v>46239</v>
+        <v>46254</v>
       </c>
       <c r="G297" s="1">
-        <v>46252</v>
+        <v>46254</v>
       </c>
       <c r="H297">
         <v>0</v>
@@ -9733,25 +9859,25 @@
     </row>
     <row r="298" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A298" t="s">
-        <v>437</v>
+        <v>0</v>
       </c>
       <c r="B298" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="C298">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D298" t="s">
         <v>56</v>
       </c>
       <c r="E298" t="s">
-        <v>443</v>
+        <v>461</v>
       </c>
       <c r="F298" s="1">
-        <v>46239</v>
+        <v>46254</v>
       </c>
       <c r="G298" s="1">
-        <v>46252</v>
+        <v>46254</v>
       </c>
       <c r="H298">
         <v>0</v>
@@ -9759,36 +9885,36 @@
     </row>
     <row r="299" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A299" t="s">
-        <v>437</v>
+        <v>0</v>
       </c>
       <c r="B299" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="C299">
         <v>1</v>
       </c>
       <c r="D299" t="s">
-        <v>2</v>
+        <v>56</v>
       </c>
       <c r="E299" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="F299" s="1">
-        <v>46247</v>
+        <v>46254</v>
       </c>
       <c r="G299" s="1">
-        <v>46252</v>
+        <v>46254</v>
       </c>
       <c r="H299">
-        <v>29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="300" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A300" t="s">
-        <v>437</v>
+        <v>0</v>
       </c>
       <c r="B300" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="C300">
         <v>1</v>
@@ -9797,13 +9923,13 @@
         <v>56</v>
       </c>
       <c r="E300" t="s">
-        <v>293</v>
+        <v>464</v>
       </c>
       <c r="F300" s="1">
-        <v>46252</v>
+        <v>46254</v>
       </c>
       <c r="G300" s="1">
-        <v>46252</v>
+        <v>46254</v>
       </c>
       <c r="H300">
         <v>0</v>
@@ -9811,10 +9937,10 @@
     </row>
     <row r="301" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A301" t="s">
-        <v>437</v>
+        <v>0</v>
       </c>
       <c r="B301" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C301">
         <v>1</v>
@@ -9823,13 +9949,13 @@
         <v>56</v>
       </c>
       <c r="E301" t="s">
-        <v>132</v>
+        <v>161</v>
       </c>
       <c r="F301" s="1">
-        <v>46252</v>
+        <v>46254</v>
       </c>
       <c r="G301" s="1">
-        <v>46252</v>
+        <v>46254</v>
       </c>
       <c r="H301">
         <v>0</v>
@@ -9837,25 +9963,25 @@
     </row>
     <row r="302" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A302" t="s">
-        <v>437</v>
+        <v>0</v>
       </c>
       <c r="B302" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="C302">
         <v>1</v>
       </c>
       <c r="D302" t="s">
-        <v>5</v>
+        <v>56</v>
       </c>
       <c r="E302" t="s">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="F302" s="1">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="G302" s="1">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="H302">
         <v>0</v>
@@ -9863,36 +9989,36 @@
     </row>
     <row r="303" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A303" t="s">
-        <v>437</v>
+        <v>0</v>
       </c>
       <c r="B303" t="s">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="C303">
         <v>1</v>
       </c>
       <c r="D303" t="s">
-        <v>2</v>
+        <v>56</v>
       </c>
       <c r="E303" t="s">
-        <v>208</v>
+        <v>469</v>
       </c>
       <c r="F303" s="1">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="G303" s="1">
         <v>46254</v>
       </c>
       <c r="H303">
-        <v>105</v>
+        <v>0</v>
       </c>
     </row>
     <row r="304" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A304" t="s">
-        <v>437</v>
+        <v>0</v>
       </c>
       <c r="B304" t="s">
-        <v>464</v>
+        <v>470</v>
       </c>
       <c r="C304">
         <v>1</v>
@@ -9901,13 +10027,13 @@
         <v>56</v>
       </c>
       <c r="E304" t="s">
-        <v>139</v>
+        <v>471</v>
       </c>
       <c r="F304" s="1">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="G304" s="1">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="H304">
         <v>0</v>
@@ -9915,10 +10041,10 @@
     </row>
     <row r="305" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A305" t="s">
-        <v>437</v>
+        <v>0</v>
       </c>
       <c r="B305" t="s">
-        <v>465</v>
+        <v>472</v>
       </c>
       <c r="C305">
         <v>1</v>
@@ -9927,10 +10053,10 @@
         <v>56</v>
       </c>
       <c r="E305" t="s">
-        <v>397</v>
+        <v>384</v>
       </c>
       <c r="F305" s="1">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="G305" s="1">
         <v>46254</v>
@@ -9941,10 +10067,10 @@
     </row>
     <row r="306" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A306" t="s">
-        <v>437</v>
+        <v>0</v>
       </c>
       <c r="B306" t="s">
-        <v>466</v>
+        <v>473</v>
       </c>
       <c r="C306">
         <v>1</v>
@@ -9953,7 +10079,7 @@
         <v>56</v>
       </c>
       <c r="E306" t="s">
-        <v>420</v>
+        <v>474</v>
       </c>
       <c r="F306" s="1">
         <v>46254</v>
@@ -9967,10 +10093,10 @@
     </row>
     <row r="307" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A307" t="s">
-        <v>437</v>
+        <v>0</v>
       </c>
       <c r="B307" t="s">
-        <v>467</v>
+        <v>475</v>
       </c>
       <c r="C307">
         <v>1</v>
@@ -9979,7 +10105,7 @@
         <v>56</v>
       </c>
       <c r="E307" t="s">
-        <v>14</v>
+        <v>388</v>
       </c>
       <c r="F307" s="1">
         <v>46254</v>
@@ -9993,62 +10119,62 @@
     </row>
     <row r="308" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A308" t="s">
-        <v>437</v>
+        <v>476</v>
       </c>
       <c r="B308" t="s">
-        <v>468</v>
+        <v>477</v>
       </c>
       <c r="C308">
         <v>1</v>
       </c>
       <c r="D308" t="s">
-        <v>56</v>
+        <v>2</v>
       </c>
       <c r="E308" t="s">
-        <v>94</v>
+        <v>275</v>
       </c>
       <c r="F308" s="1">
-        <v>46254</v>
+        <v>46148</v>
       </c>
       <c r="G308" s="1">
-        <v>46254</v>
+        <v>46149</v>
       </c>
       <c r="H308">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="309" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A309" t="s">
-        <v>469</v>
+        <v>478</v>
       </c>
       <c r="B309" t="s">
-        <v>470</v>
+        <v>479</v>
       </c>
       <c r="C309">
         <v>1</v>
       </c>
       <c r="D309" t="s">
-        <v>68</v>
+        <v>5</v>
       </c>
       <c r="E309" t="s">
-        <v>471</v>
+        <v>29</v>
       </c>
       <c r="F309" s="1">
-        <v>46063</v>
+        <v>46133</v>
       </c>
       <c r="G309" s="1">
-        <v>46064</v>
+        <v>46134</v>
       </c>
       <c r="H309">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="310" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A310" t="s">
-        <v>469</v>
+        <v>478</v>
       </c>
       <c r="B310" t="s">
-        <v>472</v>
+        <v>480</v>
       </c>
       <c r="C310">
         <v>1</v>
@@ -10057,13 +10183,13 @@
         <v>5</v>
       </c>
       <c r="E310" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="F310" s="1">
-        <v>46113</v>
+        <v>46134</v>
       </c>
       <c r="G310" s="1">
-        <v>46125</v>
+        <v>46134</v>
       </c>
       <c r="H310">
         <v>0</v>
@@ -10071,36 +10197,36 @@
     </row>
     <row r="311" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A311" t="s">
-        <v>469</v>
+        <v>478</v>
       </c>
       <c r="B311" t="s">
-        <v>473</v>
+        <v>481</v>
       </c>
       <c r="C311">
         <v>1</v>
       </c>
       <c r="D311" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E311" t="s">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="F311" s="1">
-        <v>46125</v>
+        <v>46156</v>
       </c>
       <c r="G311" s="1">
-        <v>46125</v>
+        <v>46156</v>
       </c>
       <c r="H311">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="312" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A312" t="s">
-        <v>469</v>
+        <v>478</v>
       </c>
       <c r="B312" t="s">
-        <v>474</v>
+        <v>482</v>
       </c>
       <c r="C312">
         <v>1</v>
@@ -10109,65 +10235,65 @@
         <v>2</v>
       </c>
       <c r="E312" t="s">
-        <v>40</v>
+        <v>453</v>
       </c>
       <c r="F312" s="1">
-        <v>46126</v>
+        <v>46195</v>
       </c>
       <c r="G312" s="1">
-        <v>46126</v>
+        <v>46195</v>
       </c>
       <c r="H312">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="313" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A313" t="s">
-        <v>469</v>
+        <v>478</v>
       </c>
       <c r="B313" t="s">
-        <v>475</v>
+        <v>483</v>
       </c>
       <c r="C313">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D313" t="s">
-        <v>2</v>
+        <v>56</v>
       </c>
       <c r="E313" t="s">
-        <v>40</v>
+        <v>484</v>
       </c>
       <c r="F313" s="1">
-        <v>46126</v>
+        <v>46206</v>
       </c>
       <c r="G313" s="1">
-        <v>46126</v>
+        <v>46252</v>
       </c>
       <c r="H313">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="314" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A314" t="s">
-        <v>469</v>
+        <v>478</v>
       </c>
       <c r="B314" t="s">
-        <v>476</v>
+        <v>485</v>
       </c>
       <c r="C314">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D314" t="s">
-        <v>2</v>
+        <v>68</v>
       </c>
       <c r="E314" t="s">
-        <v>40</v>
+        <v>486</v>
       </c>
       <c r="F314" s="1">
-        <v>46128</v>
+        <v>46209</v>
       </c>
       <c r="G314" s="1">
-        <v>46128</v>
+        <v>46218</v>
       </c>
       <c r="H314">
         <v>1</v>
@@ -10175,10 +10301,10 @@
     </row>
     <row r="315" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A315" t="s">
-        <v>469</v>
+        <v>478</v>
       </c>
       <c r="B315" t="s">
-        <v>477</v>
+        <v>487</v>
       </c>
       <c r="C315">
         <v>1</v>
@@ -10187,13 +10313,13 @@
         <v>5</v>
       </c>
       <c r="E315" t="s">
-        <v>40</v>
+        <v>488</v>
       </c>
       <c r="F315" s="1">
-        <v>46132</v>
+        <v>46213</v>
       </c>
       <c r="G315" s="1">
-        <v>46132</v>
+        <v>46213</v>
       </c>
       <c r="H315">
         <v>0</v>
@@ -10201,62 +10327,62 @@
     </row>
     <row r="316" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A316" t="s">
-        <v>469</v>
+        <v>478</v>
       </c>
       <c r="B316" t="s">
-        <v>478</v>
+        <v>489</v>
       </c>
       <c r="C316">
         <v>1</v>
       </c>
       <c r="D316" t="s">
-        <v>2</v>
+        <v>68</v>
       </c>
       <c r="E316" t="s">
-        <v>40</v>
+        <v>208</v>
       </c>
       <c r="F316" s="1">
-        <v>46161</v>
+        <v>46213</v>
       </c>
       <c r="G316" s="1">
-        <v>46161</v>
+        <v>46216</v>
       </c>
       <c r="H316">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="317" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A317" t="s">
-        <v>469</v>
+        <v>478</v>
       </c>
       <c r="B317" t="s">
-        <v>479</v>
+        <v>490</v>
       </c>
       <c r="C317">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D317" t="s">
         <v>2</v>
       </c>
       <c r="E317" t="s">
-        <v>40</v>
+        <v>94</v>
       </c>
       <c r="F317" s="1">
-        <v>46174</v>
+        <v>46220</v>
       </c>
       <c r="G317" s="1">
-        <v>46174</v>
+        <v>46231</v>
       </c>
       <c r="H317">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="318" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A318" t="s">
-        <v>469</v>
+        <v>478</v>
       </c>
       <c r="B318" t="s">
-        <v>480</v>
+        <v>491</v>
       </c>
       <c r="C318">
         <v>1</v>
@@ -10265,76 +10391,76 @@
         <v>2</v>
       </c>
       <c r="E318" t="s">
-        <v>40</v>
+        <v>453</v>
       </c>
       <c r="F318" s="1">
-        <v>46174</v>
+        <v>46223</v>
       </c>
       <c r="G318" s="1">
-        <v>46174</v>
+        <v>46223</v>
       </c>
       <c r="H318">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="319" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A319" t="s">
-        <v>469</v>
+        <v>478</v>
       </c>
       <c r="B319" t="s">
-        <v>481</v>
+        <v>492</v>
       </c>
       <c r="C319">
         <v>1</v>
       </c>
       <c r="D319" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="E319" t="s">
-        <v>40</v>
+        <v>208</v>
       </c>
       <c r="F319" s="1">
-        <v>46195</v>
+        <v>46224</v>
       </c>
       <c r="G319" s="1">
-        <v>46252</v>
+        <v>46224</v>
       </c>
       <c r="H319">
-        <v>0</v>
+        <v>26</v>
       </c>
     </row>
     <row r="320" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A320" t="s">
-        <v>469</v>
+        <v>478</v>
       </c>
       <c r="B320" t="s">
-        <v>482</v>
+        <v>493</v>
       </c>
       <c r="C320">
         <v>1</v>
       </c>
       <c r="D320" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E320" t="s">
-        <v>40</v>
+        <v>453</v>
       </c>
       <c r="F320" s="1">
-        <v>46210</v>
+        <v>46230</v>
       </c>
       <c r="G320" s="1">
-        <v>46210</v>
+        <v>46231</v>
       </c>
       <c r="H320">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="321" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A321" t="s">
-        <v>469</v>
+        <v>478</v>
       </c>
       <c r="B321" t="s">
-        <v>483</v>
+        <v>494</v>
       </c>
       <c r="C321">
         <v>1</v>
@@ -10343,88 +10469,88 @@
         <v>2</v>
       </c>
       <c r="E321" t="s">
-        <v>40</v>
+        <v>94</v>
       </c>
       <c r="F321" s="1">
-        <v>46213</v>
+        <v>46232</v>
       </c>
       <c r="G321" s="1">
-        <v>46213</v>
+        <v>46233</v>
       </c>
       <c r="H321">
-        <v>1</v>
+        <v>126</v>
       </c>
     </row>
     <row r="322" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A322" t="s">
-        <v>469</v>
+        <v>478</v>
       </c>
       <c r="B322" t="s">
-        <v>484</v>
+        <v>495</v>
       </c>
       <c r="C322">
         <v>1</v>
       </c>
       <c r="D322" t="s">
-        <v>56</v>
+        <v>2</v>
       </c>
       <c r="E322" t="s">
-        <v>40</v>
+        <v>94</v>
       </c>
       <c r="F322" s="1">
-        <v>46218</v>
+        <v>46232</v>
       </c>
       <c r="G322" s="1">
-        <v>46252</v>
+        <v>46233</v>
       </c>
       <c r="H322">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="323" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A323" t="s">
-        <v>469</v>
+        <v>478</v>
       </c>
       <c r="B323" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="C323">
         <v>1</v>
       </c>
       <c r="D323" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E323" t="s">
-        <v>54</v>
+        <v>208</v>
       </c>
       <c r="F323" s="1">
-        <v>46226</v>
+        <v>46238</v>
       </c>
       <c r="G323" s="1">
-        <v>46226</v>
+        <v>46239</v>
       </c>
       <c r="H323">
-        <v>0</v>
+        <v>117</v>
       </c>
     </row>
     <row r="324" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A324" t="s">
-        <v>469</v>
+        <v>478</v>
       </c>
       <c r="B324" t="s">
-        <v>486</v>
+        <v>497</v>
       </c>
       <c r="C324">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D324" t="s">
         <v>56</v>
       </c>
       <c r="E324" t="s">
-        <v>40</v>
+        <v>484</v>
       </c>
       <c r="F324" s="1">
-        <v>46227</v>
+        <v>46239</v>
       </c>
       <c r="G324" s="1">
         <v>46252</v>
@@ -10435,22 +10561,22 @@
     </row>
     <row r="325" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A325" t="s">
-        <v>469</v>
+        <v>478</v>
       </c>
       <c r="B325" t="s">
-        <v>487</v>
+        <v>498</v>
       </c>
       <c r="C325">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D325" t="s">
         <v>56</v>
       </c>
       <c r="E325" t="s">
-        <v>40</v>
+        <v>484</v>
       </c>
       <c r="F325" s="1">
-        <v>46227</v>
+        <v>46239</v>
       </c>
       <c r="G325" s="1">
         <v>46252</v>
@@ -10461,36 +10587,36 @@
     </row>
     <row r="326" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A326" t="s">
-        <v>469</v>
+        <v>478</v>
       </c>
       <c r="B326" t="s">
-        <v>488</v>
+        <v>499</v>
       </c>
       <c r="C326">
         <v>1</v>
       </c>
       <c r="D326" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E326" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="F326" s="1">
-        <v>46227</v>
+        <v>46247</v>
       </c>
       <c r="G326" s="1">
-        <v>46228</v>
+        <v>46252</v>
       </c>
       <c r="H326">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="327" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A327" t="s">
-        <v>469</v>
+        <v>478</v>
       </c>
       <c r="B327" t="s">
-        <v>489</v>
+        <v>500</v>
       </c>
       <c r="C327">
         <v>1</v>
@@ -10499,10 +10625,10 @@
         <v>56</v>
       </c>
       <c r="E327" t="s">
-        <v>54</v>
+        <v>293</v>
       </c>
       <c r="F327" s="1">
-        <v>46230</v>
+        <v>46252</v>
       </c>
       <c r="G327" s="1">
         <v>46252</v>
@@ -10513,25 +10639,25 @@
     </row>
     <row r="328" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A328" t="s">
-        <v>469</v>
+        <v>478</v>
       </c>
       <c r="B328" t="s">
-        <v>490</v>
+        <v>501</v>
       </c>
       <c r="C328">
         <v>1</v>
       </c>
       <c r="D328" t="s">
-        <v>5</v>
+        <v>56</v>
       </c>
       <c r="E328" t="s">
-        <v>40</v>
+        <v>132</v>
       </c>
       <c r="F328" s="1">
-        <v>46231</v>
+        <v>46252</v>
       </c>
       <c r="G328" s="1">
-        <v>46231</v>
+        <v>46252</v>
       </c>
       <c r="H328">
         <v>0</v>
@@ -10539,25 +10665,25 @@
     </row>
     <row r="329" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A329" t="s">
-        <v>469</v>
+        <v>478</v>
       </c>
       <c r="B329" t="s">
-        <v>491</v>
+        <v>502</v>
       </c>
       <c r="C329">
         <v>1</v>
       </c>
       <c r="D329" t="s">
-        <v>56</v>
+        <v>5</v>
       </c>
       <c r="E329" t="s">
-        <v>40</v>
+        <v>503</v>
       </c>
       <c r="F329" s="1">
-        <v>46254</v>
+        <v>46253</v>
       </c>
       <c r="G329" s="1">
-        <v>46254</v>
+        <v>46253</v>
       </c>
       <c r="H329">
         <v>0</v>
@@ -10565,209 +10691,937 @@
     </row>
     <row r="330" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A330" t="s">
-        <v>469</v>
+        <v>478</v>
       </c>
       <c r="B330" t="s">
-        <v>492</v>
+        <v>504</v>
       </c>
       <c r="C330">
         <v>1</v>
       </c>
       <c r="D330" t="s">
-        <v>56</v>
+        <v>2</v>
       </c>
       <c r="E330" t="s">
-        <v>40</v>
+        <v>208</v>
       </c>
       <c r="F330" s="1">
-        <v>46254</v>
+        <v>46253</v>
       </c>
       <c r="G330" s="1">
         <v>46254</v>
       </c>
       <c r="H330">
-        <v>0</v>
+        <v>105</v>
       </c>
     </row>
     <row r="331" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A331" t="s">
-        <v>493</v>
+        <v>478</v>
       </c>
       <c r="B331" t="s">
-        <v>494</v>
+        <v>505</v>
       </c>
       <c r="C331">
         <v>1</v>
       </c>
       <c r="D331" t="s">
-        <v>2</v>
+        <v>56</v>
       </c>
       <c r="E331" t="s">
-        <v>495</v>
+        <v>139</v>
       </c>
       <c r="F331" s="1">
-        <v>46083</v>
+        <v>46253</v>
       </c>
       <c r="G331" s="1">
-        <v>46084</v>
+        <v>46253</v>
       </c>
       <c r="H331">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="332" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A332" t="s">
-        <v>493</v>
+        <v>478</v>
       </c>
       <c r="B332" t="s">
-        <v>496</v>
+        <v>506</v>
       </c>
       <c r="C332">
         <v>1</v>
       </c>
       <c r="D332" t="s">
-        <v>2</v>
+        <v>56</v>
       </c>
       <c r="E332" t="s">
-        <v>495</v>
+        <v>399</v>
       </c>
       <c r="F332" s="1">
-        <v>46132</v>
+        <v>46253</v>
       </c>
       <c r="G332" s="1">
-        <v>46133</v>
+        <v>46254</v>
       </c>
       <c r="H332">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="333" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A333" t="s">
-        <v>493</v>
+        <v>478</v>
       </c>
       <c r="B333" t="s">
-        <v>497</v>
+        <v>507</v>
       </c>
       <c r="C333">
         <v>1</v>
       </c>
       <c r="D333" t="s">
-        <v>2</v>
+        <v>56</v>
       </c>
       <c r="E333" t="s">
-        <v>498</v>
+        <v>422</v>
       </c>
       <c r="F333" s="1">
-        <v>46157</v>
+        <v>46254</v>
       </c>
       <c r="G333" s="1">
-        <v>46157</v>
+        <v>46254</v>
       </c>
       <c r="H333">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="334" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A334" t="s">
-        <v>493</v>
+        <v>478</v>
       </c>
       <c r="B334" t="s">
-        <v>499</v>
+        <v>508</v>
       </c>
       <c r="C334">
         <v>1</v>
       </c>
       <c r="D334" t="s">
-        <v>2</v>
+        <v>56</v>
       </c>
       <c r="E334" t="s">
-        <v>500</v>
+        <v>14</v>
       </c>
       <c r="F334" s="1">
-        <v>46168</v>
+        <v>46254</v>
       </c>
       <c r="G334" s="1">
-        <v>46170</v>
+        <v>46254</v>
       </c>
       <c r="H334">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="335" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A335" t="s">
-        <v>493</v>
+        <v>478</v>
       </c>
       <c r="B335" t="s">
-        <v>501</v>
+        <v>509</v>
       </c>
       <c r="C335">
         <v>1</v>
       </c>
       <c r="D335" t="s">
-        <v>2</v>
+        <v>56</v>
       </c>
       <c r="E335" t="s">
-        <v>498</v>
+        <v>94</v>
       </c>
       <c r="F335" s="1">
-        <v>46244</v>
+        <v>46254</v>
       </c>
       <c r="G335" s="1">
-        <v>46244</v>
+        <v>46254</v>
       </c>
       <c r="H335">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="336" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A336" t="s">
-        <v>493</v>
+        <v>478</v>
       </c>
       <c r="B336" t="s">
-        <v>502</v>
+        <v>510</v>
       </c>
       <c r="C336">
         <v>1</v>
       </c>
       <c r="D336" t="s">
-        <v>2</v>
+        <v>56</v>
       </c>
       <c r="E336" t="s">
-        <v>498</v>
+        <v>461</v>
       </c>
       <c r="F336" s="1">
-        <v>46247</v>
+        <v>46254</v>
       </c>
       <c r="G336" s="1">
-        <v>46247</v>
+        <v>46254</v>
       </c>
       <c r="H336">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="337" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A337" t="s">
-        <v>493</v>
+        <v>511</v>
       </c>
       <c r="B337" t="s">
-        <v>503</v>
+        <v>512</v>
       </c>
       <c r="C337">
         <v>1</v>
       </c>
       <c r="D337" t="s">
-        <v>2</v>
+        <v>68</v>
       </c>
       <c r="E337" t="s">
-        <v>495</v>
+        <v>513</v>
       </c>
       <c r="F337" s="1">
+        <v>46063</v>
+      </c>
+      <c r="G337" s="1">
+        <v>46064</v>
+      </c>
+      <c r="H337">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="338" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A338" t="s">
+        <v>511</v>
+      </c>
+      <c r="B338" t="s">
+        <v>514</v>
+      </c>
+      <c r="C338">
+        <v>1</v>
+      </c>
+      <c r="D338" t="s">
+        <v>5</v>
+      </c>
+      <c r="E338" t="s">
+        <v>40</v>
+      </c>
+      <c r="F338" s="1">
+        <v>46113</v>
+      </c>
+      <c r="G338" s="1">
+        <v>46125</v>
+      </c>
+      <c r="H338">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="339" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A339" t="s">
+        <v>511</v>
+      </c>
+      <c r="B339" t="s">
+        <v>515</v>
+      </c>
+      <c r="C339">
+        <v>1</v>
+      </c>
+      <c r="D339" t="s">
+        <v>2</v>
+      </c>
+      <c r="E339" t="s">
+        <v>40</v>
+      </c>
+      <c r="F339" s="1">
+        <v>46125</v>
+      </c>
+      <c r="G339" s="1">
+        <v>46125</v>
+      </c>
+      <c r="H339">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="340" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A340" t="s">
+        <v>511</v>
+      </c>
+      <c r="B340" t="s">
+        <v>516</v>
+      </c>
+      <c r="C340">
+        <v>1</v>
+      </c>
+      <c r="D340" t="s">
+        <v>2</v>
+      </c>
+      <c r="E340" t="s">
+        <v>40</v>
+      </c>
+      <c r="F340" s="1">
+        <v>46126</v>
+      </c>
+      <c r="G340" s="1">
+        <v>46126</v>
+      </c>
+      <c r="H340">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="341" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A341" t="s">
+        <v>511</v>
+      </c>
+      <c r="B341" t="s">
+        <v>517</v>
+      </c>
+      <c r="C341">
+        <v>1</v>
+      </c>
+      <c r="D341" t="s">
+        <v>2</v>
+      </c>
+      <c r="E341" t="s">
+        <v>40</v>
+      </c>
+      <c r="F341" s="1">
+        <v>46126</v>
+      </c>
+      <c r="G341" s="1">
+        <v>46126</v>
+      </c>
+      <c r="H341">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="342" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A342" t="s">
+        <v>511</v>
+      </c>
+      <c r="B342" t="s">
+        <v>518</v>
+      </c>
+      <c r="C342">
+        <v>1</v>
+      </c>
+      <c r="D342" t="s">
+        <v>2</v>
+      </c>
+      <c r="E342" t="s">
+        <v>40</v>
+      </c>
+      <c r="F342" s="1">
+        <v>46128</v>
+      </c>
+      <c r="G342" s="1">
+        <v>46128</v>
+      </c>
+      <c r="H342">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="343" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A343" t="s">
+        <v>511</v>
+      </c>
+      <c r="B343" t="s">
+        <v>519</v>
+      </c>
+      <c r="C343">
+        <v>1</v>
+      </c>
+      <c r="D343" t="s">
+        <v>5</v>
+      </c>
+      <c r="E343" t="s">
+        <v>40</v>
+      </c>
+      <c r="F343" s="1">
+        <v>46132</v>
+      </c>
+      <c r="G343" s="1">
+        <v>46132</v>
+      </c>
+      <c r="H343">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="344" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A344" t="s">
+        <v>511</v>
+      </c>
+      <c r="B344" t="s">
+        <v>520</v>
+      </c>
+      <c r="C344">
+        <v>1</v>
+      </c>
+      <c r="D344" t="s">
+        <v>2</v>
+      </c>
+      <c r="E344" t="s">
+        <v>40</v>
+      </c>
+      <c r="F344" s="1">
+        <v>46161</v>
+      </c>
+      <c r="G344" s="1">
+        <v>46161</v>
+      </c>
+      <c r="H344">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="345" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A345" t="s">
+        <v>511</v>
+      </c>
+      <c r="B345" t="s">
+        <v>521</v>
+      </c>
+      <c r="C345">
+        <v>1</v>
+      </c>
+      <c r="D345" t="s">
+        <v>2</v>
+      </c>
+      <c r="E345" t="s">
+        <v>40</v>
+      </c>
+      <c r="F345" s="1">
+        <v>46174</v>
+      </c>
+      <c r="G345" s="1">
+        <v>46174</v>
+      </c>
+      <c r="H345">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="346" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A346" t="s">
+        <v>511</v>
+      </c>
+      <c r="B346" t="s">
+        <v>522</v>
+      </c>
+      <c r="C346">
+        <v>1</v>
+      </c>
+      <c r="D346" t="s">
+        <v>2</v>
+      </c>
+      <c r="E346" t="s">
+        <v>40</v>
+      </c>
+      <c r="F346" s="1">
+        <v>46174</v>
+      </c>
+      <c r="G346" s="1">
+        <v>46174</v>
+      </c>
+      <c r="H346">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="347" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A347" t="s">
+        <v>511</v>
+      </c>
+      <c r="B347" t="s">
+        <v>523</v>
+      </c>
+      <c r="C347">
+        <v>1</v>
+      </c>
+      <c r="D347" t="s">
+        <v>56</v>
+      </c>
+      <c r="E347" t="s">
+        <v>40</v>
+      </c>
+      <c r="F347" s="1">
+        <v>46195</v>
+      </c>
+      <c r="G347" s="1">
+        <v>46252</v>
+      </c>
+      <c r="H347">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="348" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A348" t="s">
+        <v>511</v>
+      </c>
+      <c r="B348" t="s">
+        <v>524</v>
+      </c>
+      <c r="C348">
+        <v>1</v>
+      </c>
+      <c r="D348" t="s">
+        <v>5</v>
+      </c>
+      <c r="E348" t="s">
+        <v>40</v>
+      </c>
+      <c r="F348" s="1">
+        <v>46210</v>
+      </c>
+      <c r="G348" s="1">
+        <v>46210</v>
+      </c>
+      <c r="H348">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="349" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A349" t="s">
+        <v>511</v>
+      </c>
+      <c r="B349" t="s">
+        <v>525</v>
+      </c>
+      <c r="C349">
+        <v>1</v>
+      </c>
+      <c r="D349" t="s">
+        <v>2</v>
+      </c>
+      <c r="E349" t="s">
+        <v>40</v>
+      </c>
+      <c r="F349" s="1">
+        <v>46213</v>
+      </c>
+      <c r="G349" s="1">
+        <v>46213</v>
+      </c>
+      <c r="H349">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="350" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A350" t="s">
+        <v>511</v>
+      </c>
+      <c r="B350" t="s">
+        <v>526</v>
+      </c>
+      <c r="C350">
+        <v>1</v>
+      </c>
+      <c r="D350" t="s">
+        <v>56</v>
+      </c>
+      <c r="E350" t="s">
+        <v>40</v>
+      </c>
+      <c r="F350" s="1">
+        <v>46218</v>
+      </c>
+      <c r="G350" s="1">
+        <v>46252</v>
+      </c>
+      <c r="H350">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="351" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A351" t="s">
+        <v>511</v>
+      </c>
+      <c r="B351" t="s">
+        <v>527</v>
+      </c>
+      <c r="C351">
+        <v>1</v>
+      </c>
+      <c r="D351" t="s">
+        <v>5</v>
+      </c>
+      <c r="E351" t="s">
+        <v>54</v>
+      </c>
+      <c r="F351" s="1">
+        <v>46226</v>
+      </c>
+      <c r="G351" s="1">
+        <v>46226</v>
+      </c>
+      <c r="H351">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="352" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A352" t="s">
+        <v>511</v>
+      </c>
+      <c r="B352" t="s">
+        <v>528</v>
+      </c>
+      <c r="C352">
+        <v>1</v>
+      </c>
+      <c r="D352" t="s">
+        <v>56</v>
+      </c>
+      <c r="E352" t="s">
+        <v>40</v>
+      </c>
+      <c r="F352" s="1">
+        <v>46227</v>
+      </c>
+      <c r="G352" s="1">
+        <v>46252</v>
+      </c>
+      <c r="H352">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="353" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A353" t="s">
+        <v>511</v>
+      </c>
+      <c r="B353" t="s">
+        <v>529</v>
+      </c>
+      <c r="C353">
+        <v>1</v>
+      </c>
+      <c r="D353" t="s">
+        <v>56</v>
+      </c>
+      <c r="E353" t="s">
+        <v>40</v>
+      </c>
+      <c r="F353" s="1">
+        <v>46227</v>
+      </c>
+      <c r="G353" s="1">
+        <v>46252</v>
+      </c>
+      <c r="H353">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="354" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A354" t="s">
+        <v>511</v>
+      </c>
+      <c r="B354" t="s">
+        <v>530</v>
+      </c>
+      <c r="C354">
+        <v>1</v>
+      </c>
+      <c r="D354" t="s">
+        <v>5</v>
+      </c>
+      <c r="E354" t="s">
+        <v>40</v>
+      </c>
+      <c r="F354" s="1">
+        <v>46227</v>
+      </c>
+      <c r="G354" s="1">
+        <v>46228</v>
+      </c>
+      <c r="H354">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="355" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A355" t="s">
+        <v>511</v>
+      </c>
+      <c r="B355" t="s">
+        <v>531</v>
+      </c>
+      <c r="C355">
+        <v>1</v>
+      </c>
+      <c r="D355" t="s">
+        <v>56</v>
+      </c>
+      <c r="E355" t="s">
+        <v>54</v>
+      </c>
+      <c r="F355" s="1">
+        <v>46230</v>
+      </c>
+      <c r="G355" s="1">
+        <v>46252</v>
+      </c>
+      <c r="H355">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="356" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A356" t="s">
+        <v>511</v>
+      </c>
+      <c r="B356" t="s">
+        <v>532</v>
+      </c>
+      <c r="C356">
+        <v>1</v>
+      </c>
+      <c r="D356" t="s">
+        <v>5</v>
+      </c>
+      <c r="E356" t="s">
+        <v>40</v>
+      </c>
+      <c r="F356" s="1">
+        <v>46231</v>
+      </c>
+      <c r="G356" s="1">
+        <v>46231</v>
+      </c>
+      <c r="H356">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="357" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A357" t="s">
+        <v>511</v>
+      </c>
+      <c r="B357" t="s">
+        <v>533</v>
+      </c>
+      <c r="C357">
+        <v>1</v>
+      </c>
+      <c r="D357" t="s">
+        <v>56</v>
+      </c>
+      <c r="E357" t="s">
+        <v>40</v>
+      </c>
+      <c r="F357" s="1">
+        <v>46254</v>
+      </c>
+      <c r="G357" s="1">
+        <v>46254</v>
+      </c>
+      <c r="H357">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="358" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A358" t="s">
+        <v>511</v>
+      </c>
+      <c r="B358" t="s">
+        <v>534</v>
+      </c>
+      <c r="C358">
+        <v>1</v>
+      </c>
+      <c r="D358" t="s">
+        <v>56</v>
+      </c>
+      <c r="E358" t="s">
+        <v>40</v>
+      </c>
+      <c r="F358" s="1">
+        <v>46254</v>
+      </c>
+      <c r="G358" s="1">
+        <v>46254</v>
+      </c>
+      <c r="H358">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="359" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A359" t="s">
+        <v>535</v>
+      </c>
+      <c r="B359" t="s">
+        <v>536</v>
+      </c>
+      <c r="C359">
+        <v>1</v>
+      </c>
+      <c r="D359" t="s">
+        <v>2</v>
+      </c>
+      <c r="E359" t="s">
+        <v>537</v>
+      </c>
+      <c r="F359" s="1">
+        <v>46083</v>
+      </c>
+      <c r="G359" s="1">
+        <v>46084</v>
+      </c>
+      <c r="H359">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="360" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A360" t="s">
+        <v>535</v>
+      </c>
+      <c r="B360" t="s">
+        <v>538</v>
+      </c>
+      <c r="C360">
+        <v>1</v>
+      </c>
+      <c r="D360" t="s">
+        <v>2</v>
+      </c>
+      <c r="E360" t="s">
+        <v>537</v>
+      </c>
+      <c r="F360" s="1">
+        <v>46132</v>
+      </c>
+      <c r="G360" s="1">
+        <v>46133</v>
+      </c>
+      <c r="H360">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="361" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A361" t="s">
+        <v>535</v>
+      </c>
+      <c r="B361" t="s">
+        <v>539</v>
+      </c>
+      <c r="C361">
+        <v>1</v>
+      </c>
+      <c r="D361" t="s">
+        <v>2</v>
+      </c>
+      <c r="E361" t="s">
+        <v>540</v>
+      </c>
+      <c r="F361" s="1">
+        <v>46157</v>
+      </c>
+      <c r="G361" s="1">
+        <v>46157</v>
+      </c>
+      <c r="H361">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="362" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A362" t="s">
+        <v>535</v>
+      </c>
+      <c r="B362" t="s">
+        <v>541</v>
+      </c>
+      <c r="C362">
+        <v>1</v>
+      </c>
+      <c r="D362" t="s">
+        <v>2</v>
+      </c>
+      <c r="E362" t="s">
+        <v>542</v>
+      </c>
+      <c r="F362" s="1">
+        <v>46168</v>
+      </c>
+      <c r="G362" s="1">
+        <v>46170</v>
+      </c>
+      <c r="H362">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="363" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A363" t="s">
+        <v>535</v>
+      </c>
+      <c r="B363" t="s">
+        <v>543</v>
+      </c>
+      <c r="C363">
+        <v>1</v>
+      </c>
+      <c r="D363" t="s">
+        <v>2</v>
+      </c>
+      <c r="E363" t="s">
+        <v>540</v>
+      </c>
+      <c r="F363" s="1">
+        <v>46244</v>
+      </c>
+      <c r="G363" s="1">
+        <v>46244</v>
+      </c>
+      <c r="H363">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="364" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A364" t="s">
+        <v>535</v>
+      </c>
+      <c r="B364" t="s">
+        <v>544</v>
+      </c>
+      <c r="C364">
+        <v>1</v>
+      </c>
+      <c r="D364" t="s">
+        <v>2</v>
+      </c>
+      <c r="E364" t="s">
+        <v>540</v>
+      </c>
+      <c r="F364" s="1">
         <v>46247</v>
       </c>
-      <c r="G337" s="1">
+      <c r="G364" s="1">
         <v>46247</v>
       </c>
-      <c r="H337">
+      <c r="H364">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="365" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A365" t="s">
+        <v>535</v>
+      </c>
+      <c r="B365" t="s">
+        <v>545</v>
+      </c>
+      <c r="C365">
+        <v>1</v>
+      </c>
+      <c r="D365" t="s">
+        <v>2</v>
+      </c>
+      <c r="E365" t="s">
+        <v>537</v>
+      </c>
+      <c r="F365" s="1">
+        <v>46247</v>
+      </c>
+      <c r="G365" s="1">
+        <v>46247</v>
+      </c>
+      <c r="H365">
         <v>1</v>
       </c>
     </row>

--- a/Data_ERP/Pedidos Transmicion.xlsx
+++ b/Data_ERP/Pedidos Transmicion.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sistema_Logistico_Peirano\Data_ERP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C2A20913-C271-47CC-A699-8D2BECE761B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9AB404C2-F1AE-49EA-BD41-CC52B66ACD6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{3F966780-C724-4E90-A737-9EE2B961DE5B}"/>
+    <workbookView xWindow="26505" yWindow="3765" windowWidth="15375" windowHeight="8325" xr2:uid="{190D1A81-71E9-4756-9E1B-E75968853F8B}"/>
   </bookViews>
   <sheets>
     <sheet name="transmicion" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1464" uniqueCount="554">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1588" uniqueCount="597">
   <si>
     <t>0001</t>
   </si>
@@ -1069,6 +1069,9 @@
     <t>CMM ARGENTINA SA</t>
   </si>
   <si>
+    <t xml:space="preserve">  213999</t>
+  </si>
+  <si>
     <t xml:space="preserve">  214000</t>
   </si>
   <si>
@@ -1378,6 +1381,9 @@
     <t xml:space="preserve">  214099</t>
   </si>
   <si>
+    <t xml:space="preserve">  214100</t>
+  </si>
+  <si>
     <t xml:space="preserve">  214101</t>
   </si>
   <si>
@@ -1447,9 +1453,117 @@
     <t>TUBOPLAST SRL</t>
   </si>
   <si>
+    <t xml:space="preserve">  214120</t>
+  </si>
+  <si>
     <t xml:space="preserve">  214121</t>
   </si>
   <si>
+    <t xml:space="preserve">  214122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214123</t>
+  </si>
+  <si>
+    <t>PERALTA DANIEL -SANIT. DAPER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214126</t>
+  </si>
+  <si>
+    <t>VALDEZ HUGO A -DEL SUR MATERIALES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214127</t>
+  </si>
+  <si>
+    <t>SANITARIOS SANJUAN S.R.L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214128</t>
+  </si>
+  <si>
+    <t>LOSAMIL CONSTRUCCIONES S.A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214129</t>
+  </si>
+  <si>
+    <t>DE GIORGIO V,DE GIORGIO G,DE GIORGIO S,DE GIORGIO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214130</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214136</t>
+  </si>
+  <si>
+    <t>NESGAMET S.A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214137</t>
+  </si>
+  <si>
+    <t>SANITARIOS YERBAL DE LUIS TALAMONA Y OSCAR TALAMON</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214138</t>
+  </si>
+  <si>
+    <t>INTERMARBLE S.R.L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214142</t>
+  </si>
+  <si>
+    <t>DECORMAT S.R.L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214144</t>
+  </si>
+  <si>
+    <t>CASA CASMMA SRL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214148</t>
+  </si>
+  <si>
+    <t>PARDO MATERIALES SA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214150</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214151</t>
+  </si>
+  <si>
+    <t>VILLALBA MARIANO</t>
+  </si>
+  <si>
     <t>0004</t>
   </si>
   <si>
@@ -1540,21 +1654,36 @@
     <t xml:space="preserve">    2822</t>
   </si>
   <si>
-    <t xml:space="preserve">    2823</t>
-  </si>
-  <si>
     <t xml:space="preserve">    2824</t>
   </si>
   <si>
-    <t xml:space="preserve">    2825</t>
-  </si>
-  <si>
     <t xml:space="preserve">    2826</t>
   </si>
   <si>
+    <t xml:space="preserve">    2828</t>
+  </si>
+  <si>
     <t xml:space="preserve">    2829</t>
   </si>
   <si>
+    <t xml:space="preserve">    2830</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    2831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    2832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    2834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    2835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    2836</t>
+  </si>
+  <si>
     <t>4444</t>
   </si>
   <si>
@@ -1624,7 +1753,7 @@
     <t xml:space="preserve">    2240</t>
   </si>
   <si>
-    <t xml:space="preserve">    2247</t>
+    <t xml:space="preserve">    2254</t>
   </si>
   <si>
     <t>9999</t>
@@ -2131,34 +2260,34 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E418CEC2-71E4-477F-B2C9-1ADD17A8D4DA}">
-  <dimension ref="A1:H365"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C9B5CD1-D75A-4780-8000-E5B6EBE21ABB}">
+  <dimension ref="A1:H396"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
-        <v>546</v>
+        <v>589</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>547</v>
+        <v>590</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>548</v>
+        <v>591</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>549</v>
+        <v>592</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>550</v>
+        <v>593</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>551</v>
+        <v>594</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>552</v>
+        <v>595</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>553</v>
+        <v>596</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
@@ -6644,7 +6773,7 @@
         <v>1</v>
       </c>
       <c r="D174" t="s">
-        <v>56</v>
+        <v>2</v>
       </c>
       <c r="E174" t="s">
         <v>281</v>
@@ -6656,7 +6785,7 @@
         <v>46252</v>
       </c>
       <c r="H174">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="175" spans="1:8" x14ac:dyDescent="0.2">
@@ -6904,7 +7033,7 @@
         <v>1</v>
       </c>
       <c r="D184" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="E184" t="s">
         <v>297</v>
@@ -6916,7 +7045,7 @@
         <v>46254</v>
       </c>
       <c r="H184">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="185" spans="1:8" x14ac:dyDescent="0.2">
@@ -7398,7 +7527,7 @@
         <v>1</v>
       </c>
       <c r="D203" t="s">
-        <v>56</v>
+        <v>2</v>
       </c>
       <c r="E203" t="s">
         <v>324</v>
@@ -7410,7 +7539,7 @@
         <v>46253</v>
       </c>
       <c r="H203">
-        <v>0</v>
+        <v>22</v>
       </c>
     </row>
     <row r="204" spans="1:8" x14ac:dyDescent="0.2">
@@ -7424,7 +7553,7 @@
         <v>1</v>
       </c>
       <c r="D204" t="s">
-        <v>56</v>
+        <v>2</v>
       </c>
       <c r="E204" t="s">
         <v>326</v>
@@ -7436,7 +7565,7 @@
         <v>46253</v>
       </c>
       <c r="H204">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="205" spans="1:8" x14ac:dyDescent="0.2">
@@ -7528,7 +7657,7 @@
         <v>1</v>
       </c>
       <c r="D208" t="s">
-        <v>56</v>
+        <v>2</v>
       </c>
       <c r="E208" t="s">
         <v>134</v>
@@ -7540,7 +7669,7 @@
         <v>46254</v>
       </c>
       <c r="H208">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="209" spans="1:8" x14ac:dyDescent="0.2">
@@ -7554,7 +7683,7 @@
         <v>1</v>
       </c>
       <c r="D209" t="s">
-        <v>56</v>
+        <v>2</v>
       </c>
       <c r="E209" t="s">
         <v>134</v>
@@ -7566,7 +7695,7 @@
         <v>46254</v>
       </c>
       <c r="H209">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="210" spans="1:8" x14ac:dyDescent="0.2">
@@ -7580,7 +7709,7 @@
         <v>1</v>
       </c>
       <c r="D210" t="s">
-        <v>56</v>
+        <v>2</v>
       </c>
       <c r="E210" t="s">
         <v>163</v>
@@ -7592,7 +7721,7 @@
         <v>46253</v>
       </c>
       <c r="H210">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="211" spans="1:8" x14ac:dyDescent="0.2">
@@ -7895,13 +8024,13 @@
         <v>56</v>
       </c>
       <c r="E222" t="s">
-        <v>66</v>
+        <v>34</v>
       </c>
       <c r="F222" s="1">
         <v>46253</v>
       </c>
       <c r="G222" s="1">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="H222">
         <v>0</v>
@@ -7918,10 +8047,10 @@
         <v>1</v>
       </c>
       <c r="D223" t="s">
-        <v>56</v>
+        <v>2</v>
       </c>
       <c r="E223" t="s">
-        <v>144</v>
+        <v>66</v>
       </c>
       <c r="F223" s="1">
         <v>46253</v>
@@ -7930,7 +8059,7 @@
         <v>46253</v>
       </c>
       <c r="H223">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="224" spans="1:8" x14ac:dyDescent="0.2">
@@ -7944,10 +8073,10 @@
         <v>1</v>
       </c>
       <c r="D224" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="E224" t="s">
-        <v>352</v>
+        <v>144</v>
       </c>
       <c r="F224" s="1">
         <v>46253</v>
@@ -7956,7 +8085,7 @@
         <v>46253</v>
       </c>
       <c r="H224">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="225" spans="1:8" x14ac:dyDescent="0.2">
@@ -7964,16 +8093,16 @@
         <v>0</v>
       </c>
       <c r="B225" t="s">
+        <v>352</v>
+      </c>
+      <c r="C225">
+        <v>1</v>
+      </c>
+      <c r="D225" t="s">
+        <v>56</v>
+      </c>
+      <c r="E225" t="s">
         <v>353</v>
-      </c>
-      <c r="C225">
-        <v>1</v>
-      </c>
-      <c r="D225" t="s">
-        <v>56</v>
-      </c>
-      <c r="E225" t="s">
-        <v>354</v>
       </c>
       <c r="F225" s="1">
         <v>46253</v>
@@ -7990,16 +8119,16 @@
         <v>0</v>
       </c>
       <c r="B226" t="s">
+        <v>354</v>
+      </c>
+      <c r="C226">
+        <v>1</v>
+      </c>
+      <c r="D226" t="s">
+        <v>56</v>
+      </c>
+      <c r="E226" t="s">
         <v>355</v>
-      </c>
-      <c r="C226">
-        <v>1</v>
-      </c>
-      <c r="D226" t="s">
-        <v>2</v>
-      </c>
-      <c r="E226" t="s">
-        <v>356</v>
       </c>
       <c r="F226" s="1">
         <v>46253</v>
@@ -8008,7 +8137,7 @@
         <v>46253</v>
       </c>
       <c r="H226">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="227" spans="1:8" x14ac:dyDescent="0.2">
@@ -8016,16 +8145,16 @@
         <v>0</v>
       </c>
       <c r="B227" t="s">
+        <v>356</v>
+      </c>
+      <c r="C227">
+        <v>1</v>
+      </c>
+      <c r="D227" t="s">
+        <v>2</v>
+      </c>
+      <c r="E227" t="s">
         <v>357</v>
-      </c>
-      <c r="C227">
-        <v>1</v>
-      </c>
-      <c r="D227" t="s">
-        <v>56</v>
-      </c>
-      <c r="E227" t="s">
-        <v>358</v>
       </c>
       <c r="F227" s="1">
         <v>46253</v>
@@ -8034,7 +8163,7 @@
         <v>46253</v>
       </c>
       <c r="H227">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="228" spans="1:8" x14ac:dyDescent="0.2">
@@ -8042,16 +8171,16 @@
         <v>0</v>
       </c>
       <c r="B228" t="s">
+        <v>358</v>
+      </c>
+      <c r="C228">
+        <v>1</v>
+      </c>
+      <c r="D228" t="s">
+        <v>56</v>
+      </c>
+      <c r="E228" t="s">
         <v>359</v>
-      </c>
-      <c r="C228">
-        <v>1</v>
-      </c>
-      <c r="D228" t="s">
-        <v>56</v>
-      </c>
-      <c r="E228" t="s">
-        <v>360</v>
       </c>
       <c r="F228" s="1">
         <v>46253</v>
@@ -8068,16 +8197,16 @@
         <v>0</v>
       </c>
       <c r="B229" t="s">
+        <v>360</v>
+      </c>
+      <c r="C229">
+        <v>1</v>
+      </c>
+      <c r="D229" t="s">
+        <v>56</v>
+      </c>
+      <c r="E229" t="s">
         <v>361</v>
-      </c>
-      <c r="C229">
-        <v>1</v>
-      </c>
-      <c r="D229" t="s">
-        <v>56</v>
-      </c>
-      <c r="E229" t="s">
-        <v>362</v>
       </c>
       <c r="F229" s="1">
         <v>46253</v>
@@ -8094,16 +8223,16 @@
         <v>0</v>
       </c>
       <c r="B230" t="s">
+        <v>362</v>
+      </c>
+      <c r="C230">
+        <v>1</v>
+      </c>
+      <c r="D230" t="s">
+        <v>56</v>
+      </c>
+      <c r="E230" t="s">
         <v>363</v>
-      </c>
-      <c r="C230">
-        <v>1</v>
-      </c>
-      <c r="D230" t="s">
-        <v>56</v>
-      </c>
-      <c r="E230" t="s">
-        <v>313</v>
       </c>
       <c r="F230" s="1">
         <v>46253</v>
@@ -8129,7 +8258,7 @@
         <v>56</v>
       </c>
       <c r="E231" t="s">
-        <v>365</v>
+        <v>313</v>
       </c>
       <c r="F231" s="1">
         <v>46253</v>
@@ -8146,16 +8275,16 @@
         <v>0</v>
       </c>
       <c r="B232" t="s">
+        <v>365</v>
+      </c>
+      <c r="C232">
+        <v>1</v>
+      </c>
+      <c r="D232" t="s">
+        <v>56</v>
+      </c>
+      <c r="E232" t="s">
         <v>366</v>
-      </c>
-      <c r="C232">
-        <v>1</v>
-      </c>
-      <c r="D232" t="s">
-        <v>56</v>
-      </c>
-      <c r="E232" t="s">
-        <v>367</v>
       </c>
       <c r="F232" s="1">
         <v>46253</v>
@@ -8172,22 +8301,22 @@
         <v>0</v>
       </c>
       <c r="B233" t="s">
+        <v>367</v>
+      </c>
+      <c r="C233">
+        <v>1</v>
+      </c>
+      <c r="D233" t="s">
+        <v>56</v>
+      </c>
+      <c r="E233" t="s">
         <v>368</v>
-      </c>
-      <c r="C233">
-        <v>1</v>
-      </c>
-      <c r="D233" t="s">
-        <v>56</v>
-      </c>
-      <c r="E233" t="s">
-        <v>16</v>
       </c>
       <c r="F233" s="1">
         <v>46253</v>
       </c>
       <c r="G233" s="1">
-        <v>46254</v>
+        <v>46253</v>
       </c>
       <c r="H233">
         <v>0</v>
@@ -8207,13 +8336,13 @@
         <v>56</v>
       </c>
       <c r="E234" t="s">
-        <v>370</v>
+        <v>16</v>
       </c>
       <c r="F234" s="1">
         <v>46253</v>
       </c>
       <c r="G234" s="1">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="H234">
         <v>0</v>
@@ -8224,16 +8353,16 @@
         <v>0</v>
       </c>
       <c r="B235" t="s">
+        <v>370</v>
+      </c>
+      <c r="C235">
+        <v>1</v>
+      </c>
+      <c r="D235" t="s">
+        <v>2</v>
+      </c>
+      <c r="E235" t="s">
         <v>371</v>
-      </c>
-      <c r="C235">
-        <v>1</v>
-      </c>
-      <c r="D235" t="s">
-        <v>56</v>
-      </c>
-      <c r="E235" t="s">
-        <v>372</v>
       </c>
       <c r="F235" s="1">
         <v>46253</v>
@@ -8242,7 +8371,7 @@
         <v>46253</v>
       </c>
       <c r="H235">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="236" spans="1:8" x14ac:dyDescent="0.2">
@@ -8250,16 +8379,16 @@
         <v>0</v>
       </c>
       <c r="B236" t="s">
+        <v>372</v>
+      </c>
+      <c r="C236">
+        <v>1</v>
+      </c>
+      <c r="D236" t="s">
+        <v>56</v>
+      </c>
+      <c r="E236" t="s">
         <v>373</v>
-      </c>
-      <c r="C236">
-        <v>1</v>
-      </c>
-      <c r="D236" t="s">
-        <v>56</v>
-      </c>
-      <c r="E236" t="s">
-        <v>139</v>
       </c>
       <c r="F236" s="1">
         <v>46253</v>
@@ -8285,7 +8414,7 @@
         <v>56</v>
       </c>
       <c r="E237" t="s">
-        <v>313</v>
+        <v>139</v>
       </c>
       <c r="F237" s="1">
         <v>46253</v>
@@ -8311,7 +8440,7 @@
         <v>56</v>
       </c>
       <c r="E238" t="s">
-        <v>26</v>
+        <v>313</v>
       </c>
       <c r="F238" s="1">
         <v>46253</v>
@@ -8516,10 +8645,10 @@
         <v>1</v>
       </c>
       <c r="D246" t="s">
-        <v>2</v>
+        <v>56</v>
       </c>
       <c r="E246" t="s">
-        <v>384</v>
+        <v>26</v>
       </c>
       <c r="F246" s="1">
         <v>46253</v>
@@ -8528,7 +8657,7 @@
         <v>46253</v>
       </c>
       <c r="H246">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="247" spans="1:8" x14ac:dyDescent="0.2">
@@ -8536,16 +8665,16 @@
         <v>0</v>
       </c>
       <c r="B247" t="s">
+        <v>384</v>
+      </c>
+      <c r="C247">
+        <v>1</v>
+      </c>
+      <c r="D247" t="s">
+        <v>2</v>
+      </c>
+      <c r="E247" t="s">
         <v>385</v>
-      </c>
-      <c r="C247">
-        <v>1</v>
-      </c>
-      <c r="D247" t="s">
-        <v>56</v>
-      </c>
-      <c r="E247" t="s">
-        <v>386</v>
       </c>
       <c r="F247" s="1">
         <v>46253</v>
@@ -8554,7 +8683,7 @@
         <v>46253</v>
       </c>
       <c r="H247">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="248" spans="1:8" x14ac:dyDescent="0.2">
@@ -8562,16 +8691,16 @@
         <v>0</v>
       </c>
       <c r="B248" t="s">
+        <v>386</v>
+      </c>
+      <c r="C248">
+        <v>1</v>
+      </c>
+      <c r="D248" t="s">
+        <v>56</v>
+      </c>
+      <c r="E248" t="s">
         <v>387</v>
-      </c>
-      <c r="C248">
-        <v>1</v>
-      </c>
-      <c r="D248" t="s">
-        <v>56</v>
-      </c>
-      <c r="E248" t="s">
-        <v>388</v>
       </c>
       <c r="F248" s="1">
         <v>46253</v>
@@ -8588,16 +8717,16 @@
         <v>0</v>
       </c>
       <c r="B249" t="s">
+        <v>388</v>
+      </c>
+      <c r="C249">
+        <v>1</v>
+      </c>
+      <c r="D249" t="s">
+        <v>56</v>
+      </c>
+      <c r="E249" t="s">
         <v>389</v>
-      </c>
-      <c r="C249">
-        <v>1</v>
-      </c>
-      <c r="D249" t="s">
-        <v>2</v>
-      </c>
-      <c r="E249" t="s">
-        <v>390</v>
       </c>
       <c r="F249" s="1">
         <v>46253</v>
@@ -8606,7 +8735,7 @@
         <v>46253</v>
       </c>
       <c r="H249">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="250" spans="1:8" x14ac:dyDescent="0.2">
@@ -8614,16 +8743,16 @@
         <v>0</v>
       </c>
       <c r="B250" t="s">
+        <v>390</v>
+      </c>
+      <c r="C250">
+        <v>1</v>
+      </c>
+      <c r="D250" t="s">
+        <v>2</v>
+      </c>
+      <c r="E250" t="s">
         <v>391</v>
-      </c>
-      <c r="C250">
-        <v>1</v>
-      </c>
-      <c r="D250" t="s">
-        <v>2</v>
-      </c>
-      <c r="E250" t="s">
-        <v>337</v>
       </c>
       <c r="F250" s="1">
         <v>46253</v>
@@ -8632,7 +8761,7 @@
         <v>46253</v>
       </c>
       <c r="H250">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="251" spans="1:8" x14ac:dyDescent="0.2">
@@ -8646,19 +8775,19 @@
         <v>1</v>
       </c>
       <c r="D251" t="s">
-        <v>56</v>
+        <v>2</v>
       </c>
       <c r="E251" t="s">
-        <v>393</v>
+        <v>337</v>
       </c>
       <c r="F251" s="1">
         <v>46253</v>
       </c>
       <c r="G251" s="1">
-        <v>46254</v>
+        <v>46253</v>
       </c>
       <c r="H251">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="252" spans="1:8" x14ac:dyDescent="0.2">
@@ -8666,16 +8795,16 @@
         <v>0</v>
       </c>
       <c r="B252" t="s">
+        <v>393</v>
+      </c>
+      <c r="C252">
+        <v>1</v>
+      </c>
+      <c r="D252" t="s">
+        <v>68</v>
+      </c>
+      <c r="E252" t="s">
         <v>394</v>
-      </c>
-      <c r="C252">
-        <v>1</v>
-      </c>
-      <c r="D252" t="s">
-        <v>56</v>
-      </c>
-      <c r="E252" t="s">
-        <v>20</v>
       </c>
       <c r="F252" s="1">
         <v>46253</v>
@@ -8684,7 +8813,7 @@
         <v>46254</v>
       </c>
       <c r="H252">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="253" spans="1:8" x14ac:dyDescent="0.2">
@@ -8701,7 +8830,7 @@
         <v>56</v>
       </c>
       <c r="E253" t="s">
-        <v>396</v>
+        <v>20</v>
       </c>
       <c r="F253" s="1">
         <v>46253</v>
@@ -8718,16 +8847,16 @@
         <v>0</v>
       </c>
       <c r="B254" t="s">
+        <v>396</v>
+      </c>
+      <c r="C254">
+        <v>1</v>
+      </c>
+      <c r="D254" t="s">
+        <v>2</v>
+      </c>
+      <c r="E254" t="s">
         <v>397</v>
-      </c>
-      <c r="C254">
-        <v>1</v>
-      </c>
-      <c r="D254" t="s">
-        <v>56</v>
-      </c>
-      <c r="E254" t="s">
-        <v>396</v>
       </c>
       <c r="F254" s="1">
         <v>46253</v>
@@ -8736,7 +8865,7 @@
         <v>46254</v>
       </c>
       <c r="H254">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="255" spans="1:8" x14ac:dyDescent="0.2">
@@ -8750,10 +8879,10 @@
         <v>1</v>
       </c>
       <c r="D255" t="s">
-        <v>56</v>
+        <v>2</v>
       </c>
       <c r="E255" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="F255" s="1">
         <v>46253</v>
@@ -8762,7 +8891,7 @@
         <v>46254</v>
       </c>
       <c r="H255">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="256" spans="1:8" x14ac:dyDescent="0.2">
@@ -8770,16 +8899,16 @@
         <v>0</v>
       </c>
       <c r="B256" t="s">
+        <v>399</v>
+      </c>
+      <c r="C256">
+        <v>1</v>
+      </c>
+      <c r="D256" t="s">
+        <v>2</v>
+      </c>
+      <c r="E256" t="s">
         <v>400</v>
-      </c>
-      <c r="C256">
-        <v>1</v>
-      </c>
-      <c r="D256" t="s">
-        <v>56</v>
-      </c>
-      <c r="E256" t="s">
-        <v>52</v>
       </c>
       <c r="F256" s="1">
         <v>46253</v>
@@ -8788,7 +8917,7 @@
         <v>46254</v>
       </c>
       <c r="H256">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="257" spans="1:8" x14ac:dyDescent="0.2">
@@ -8802,7 +8931,7 @@
         <v>1</v>
       </c>
       <c r="D257" t="s">
-        <v>56</v>
+        <v>2</v>
       </c>
       <c r="E257" t="s">
         <v>52</v>
@@ -8814,7 +8943,7 @@
         <v>46254</v>
       </c>
       <c r="H257">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="258" spans="1:8" x14ac:dyDescent="0.2">
@@ -8828,7 +8957,7 @@
         <v>1</v>
       </c>
       <c r="D258" t="s">
-        <v>56</v>
+        <v>2</v>
       </c>
       <c r="E258" t="s">
         <v>52</v>
@@ -8840,7 +8969,7 @@
         <v>46254</v>
       </c>
       <c r="H258">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="259" spans="1:8" x14ac:dyDescent="0.2">
@@ -8857,7 +8986,7 @@
         <v>56</v>
       </c>
       <c r="E259" t="s">
-        <v>18</v>
+        <v>52</v>
       </c>
       <c r="F259" s="1">
         <v>46253</v>
@@ -8880,10 +9009,10 @@
         <v>1</v>
       </c>
       <c r="D260" t="s">
-        <v>56</v>
+        <v>2</v>
       </c>
       <c r="E260" t="s">
-        <v>405</v>
+        <v>18</v>
       </c>
       <c r="F260" s="1">
         <v>46253</v>
@@ -8892,7 +9021,7 @@
         <v>46254</v>
       </c>
       <c r="H260">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="261" spans="1:8" x14ac:dyDescent="0.2">
@@ -8900,16 +9029,16 @@
         <v>0</v>
       </c>
       <c r="B261" t="s">
+        <v>405</v>
+      </c>
+      <c r="C261">
+        <v>1</v>
+      </c>
+      <c r="D261" t="s">
+        <v>56</v>
+      </c>
+      <c r="E261" t="s">
         <v>406</v>
-      </c>
-      <c r="C261">
-        <v>2</v>
-      </c>
-      <c r="D261" t="s">
-        <v>56</v>
-      </c>
-      <c r="E261" t="s">
-        <v>407</v>
       </c>
       <c r="F261" s="1">
         <v>46253</v>
@@ -8926,16 +9055,16 @@
         <v>0</v>
       </c>
       <c r="B262" t="s">
+        <v>407</v>
+      </c>
+      <c r="C262">
+        <v>2</v>
+      </c>
+      <c r="D262" t="s">
+        <v>56</v>
+      </c>
+      <c r="E262" t="s">
         <v>408</v>
-      </c>
-      <c r="C262">
-        <v>1</v>
-      </c>
-      <c r="D262" t="s">
-        <v>56</v>
-      </c>
-      <c r="E262" t="s">
-        <v>281</v>
       </c>
       <c r="F262" s="1">
         <v>46253</v>
@@ -8958,19 +9087,19 @@
         <v>1</v>
       </c>
       <c r="D263" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="E263" t="s">
-        <v>132</v>
+        <v>281</v>
       </c>
       <c r="F263" s="1">
-        <v>46254</v>
+        <v>46253</v>
       </c>
       <c r="G263" s="1">
         <v>46254</v>
       </c>
       <c r="H263">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="264" spans="1:8" x14ac:dyDescent="0.2">
@@ -8987,7 +9116,7 @@
         <v>56</v>
       </c>
       <c r="E264" t="s">
-        <v>70</v>
+        <v>132</v>
       </c>
       <c r="F264" s="1">
         <v>46254</v>
@@ -9013,7 +9142,7 @@
         <v>56</v>
       </c>
       <c r="E265" t="s">
-        <v>412</v>
+        <v>70</v>
       </c>
       <c r="F265" s="1">
         <v>46254</v>
@@ -9030,17 +9159,17 @@
         <v>0</v>
       </c>
       <c r="B266" t="s">
+        <v>412</v>
+      </c>
+      <c r="C266">
+        <v>1</v>
+      </c>
+      <c r="D266" t="s">
+        <v>56</v>
+      </c>
+      <c r="E266" t="s">
         <v>413</v>
       </c>
-      <c r="C266">
-        <v>1</v>
-      </c>
-      <c r="D266" t="s">
-        <v>2</v>
-      </c>
-      <c r="E266" t="s">
-        <v>414</v>
-      </c>
       <c r="F266" s="1">
         <v>46254</v>
       </c>
@@ -9048,7 +9177,7 @@
         <v>46254</v>
       </c>
       <c r="H266">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="267" spans="1:8" x14ac:dyDescent="0.2">
@@ -9056,17 +9185,17 @@
         <v>0</v>
       </c>
       <c r="B267" t="s">
+        <v>414</v>
+      </c>
+      <c r="C267">
+        <v>1</v>
+      </c>
+      <c r="D267" t="s">
+        <v>2</v>
+      </c>
+      <c r="E267" t="s">
         <v>415</v>
       </c>
-      <c r="C267">
-        <v>1</v>
-      </c>
-      <c r="D267" t="s">
-        <v>56</v>
-      </c>
-      <c r="E267" t="s">
-        <v>416</v>
-      </c>
       <c r="F267" s="1">
         <v>46254</v>
       </c>
@@ -9074,7 +9203,7 @@
         <v>46254</v>
       </c>
       <c r="H267">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="268" spans="1:8" x14ac:dyDescent="0.2">
@@ -9082,16 +9211,16 @@
         <v>0</v>
       </c>
       <c r="B268" t="s">
+        <v>416</v>
+      </c>
+      <c r="C268">
+        <v>1</v>
+      </c>
+      <c r="D268" t="s">
+        <v>56</v>
+      </c>
+      <c r="E268" t="s">
         <v>417</v>
-      </c>
-      <c r="C268">
-        <v>1</v>
-      </c>
-      <c r="D268" t="s">
-        <v>56</v>
-      </c>
-      <c r="E268" t="s">
-        <v>122</v>
       </c>
       <c r="F268" s="1">
         <v>46254</v>
@@ -9117,7 +9246,7 @@
         <v>56</v>
       </c>
       <c r="E269" t="s">
-        <v>26</v>
+        <v>122</v>
       </c>
       <c r="F269" s="1">
         <v>46254</v>
@@ -9195,7 +9324,7 @@
         <v>56</v>
       </c>
       <c r="E272" t="s">
-        <v>422</v>
+        <v>26</v>
       </c>
       <c r="F272" s="1">
         <v>46254</v>
@@ -9212,16 +9341,16 @@
         <v>0</v>
       </c>
       <c r="B273" t="s">
+        <v>422</v>
+      </c>
+      <c r="C273">
+        <v>1</v>
+      </c>
+      <c r="D273" t="s">
+        <v>56</v>
+      </c>
+      <c r="E273" t="s">
         <v>423</v>
-      </c>
-      <c r="C273">
-        <v>1</v>
-      </c>
-      <c r="D273" t="s">
-        <v>56</v>
-      </c>
-      <c r="E273" t="s">
-        <v>422</v>
       </c>
       <c r="F273" s="1">
         <v>46254</v>
@@ -9247,7 +9376,7 @@
         <v>56</v>
       </c>
       <c r="E274" t="s">
-        <v>14</v>
+        <v>423</v>
       </c>
       <c r="F274" s="1">
         <v>46254</v>
@@ -9270,10 +9399,10 @@
         <v>1</v>
       </c>
       <c r="D275" t="s">
-        <v>56</v>
+        <v>2</v>
       </c>
       <c r="E275" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="F275" s="1">
         <v>46254</v>
@@ -9282,7 +9411,7 @@
         <v>46254</v>
       </c>
       <c r="H275">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="276" spans="1:8" x14ac:dyDescent="0.2">
@@ -9299,7 +9428,7 @@
         <v>56</v>
       </c>
       <c r="E276" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="F276" s="1">
         <v>46254</v>
@@ -9351,7 +9480,7 @@
         <v>56</v>
       </c>
       <c r="E278" t="s">
-        <v>429</v>
+        <v>12</v>
       </c>
       <c r="F278" s="1">
         <v>46254</v>
@@ -9368,16 +9497,16 @@
         <v>0</v>
       </c>
       <c r="B279" t="s">
+        <v>429</v>
+      </c>
+      <c r="C279">
+        <v>1</v>
+      </c>
+      <c r="D279" t="s">
+        <v>56</v>
+      </c>
+      <c r="E279" t="s">
         <v>430</v>
-      </c>
-      <c r="C279">
-        <v>1</v>
-      </c>
-      <c r="D279" t="s">
-        <v>56</v>
-      </c>
-      <c r="E279" t="s">
-        <v>94</v>
       </c>
       <c r="F279" s="1">
         <v>46254</v>
@@ -9403,7 +9532,7 @@
         <v>56</v>
       </c>
       <c r="E280" t="s">
-        <v>432</v>
+        <v>94</v>
       </c>
       <c r="F280" s="1">
         <v>46254</v>
@@ -9420,16 +9549,16 @@
         <v>0</v>
       </c>
       <c r="B281" t="s">
+        <v>432</v>
+      </c>
+      <c r="C281">
+        <v>1</v>
+      </c>
+      <c r="D281" t="s">
+        <v>56</v>
+      </c>
+      <c r="E281" t="s">
         <v>433</v>
-      </c>
-      <c r="C281">
-        <v>1</v>
-      </c>
-      <c r="D281" t="s">
-        <v>5</v>
-      </c>
-      <c r="E281" t="s">
-        <v>434</v>
       </c>
       <c r="F281" s="1">
         <v>46254</v>
@@ -9446,16 +9575,16 @@
         <v>0</v>
       </c>
       <c r="B282" t="s">
+        <v>434</v>
+      </c>
+      <c r="C282">
+        <v>1</v>
+      </c>
+      <c r="D282" t="s">
+        <v>5</v>
+      </c>
+      <c r="E282" t="s">
         <v>435</v>
-      </c>
-      <c r="C282">
-        <v>1</v>
-      </c>
-      <c r="D282" t="s">
-        <v>56</v>
-      </c>
-      <c r="E282" t="s">
-        <v>436</v>
       </c>
       <c r="F282" s="1">
         <v>46254</v>
@@ -9472,16 +9601,16 @@
         <v>0</v>
       </c>
       <c r="B283" t="s">
+        <v>436</v>
+      </c>
+      <c r="C283">
+        <v>1</v>
+      </c>
+      <c r="D283" t="s">
+        <v>56</v>
+      </c>
+      <c r="E283" t="s">
         <v>437</v>
-      </c>
-      <c r="C283">
-        <v>1</v>
-      </c>
-      <c r="D283" t="s">
-        <v>56</v>
-      </c>
-      <c r="E283" t="s">
-        <v>438</v>
       </c>
       <c r="F283" s="1">
         <v>46254</v>
@@ -9498,16 +9627,16 @@
         <v>0</v>
       </c>
       <c r="B284" t="s">
+        <v>438</v>
+      </c>
+      <c r="C284">
+        <v>1</v>
+      </c>
+      <c r="D284" t="s">
+        <v>56</v>
+      </c>
+      <c r="E284" t="s">
         <v>439</v>
-      </c>
-      <c r="C284">
-        <v>1</v>
-      </c>
-      <c r="D284" t="s">
-        <v>56</v>
-      </c>
-      <c r="E284" t="s">
-        <v>440</v>
       </c>
       <c r="F284" s="1">
         <v>46254</v>
@@ -9524,16 +9653,16 @@
         <v>0</v>
       </c>
       <c r="B285" t="s">
+        <v>440</v>
+      </c>
+      <c r="C285">
+        <v>1</v>
+      </c>
+      <c r="D285" t="s">
+        <v>56</v>
+      </c>
+      <c r="E285" t="s">
         <v>441</v>
-      </c>
-      <c r="C285">
-        <v>1</v>
-      </c>
-      <c r="D285" t="s">
-        <v>56</v>
-      </c>
-      <c r="E285" t="s">
-        <v>54</v>
       </c>
       <c r="F285" s="1">
         <v>46254</v>
@@ -9559,7 +9688,7 @@
         <v>56</v>
       </c>
       <c r="E286" t="s">
-        <v>443</v>
+        <v>54</v>
       </c>
       <c r="F286" s="1">
         <v>46254</v>
@@ -9576,16 +9705,16 @@
         <v>0</v>
       </c>
       <c r="B287" t="s">
+        <v>443</v>
+      </c>
+      <c r="C287">
+        <v>1</v>
+      </c>
+      <c r="D287" t="s">
+        <v>56</v>
+      </c>
+      <c r="E287" t="s">
         <v>444</v>
-      </c>
-      <c r="C287">
-        <v>1</v>
-      </c>
-      <c r="D287" t="s">
-        <v>56</v>
-      </c>
-      <c r="E287" t="s">
-        <v>12</v>
       </c>
       <c r="F287" s="1">
         <v>46254</v>
@@ -9611,7 +9740,7 @@
         <v>56</v>
       </c>
       <c r="E288" t="s">
-        <v>446</v>
+        <v>12</v>
       </c>
       <c r="F288" s="1">
         <v>46254</v>
@@ -9628,16 +9757,16 @@
         <v>0</v>
       </c>
       <c r="B289" t="s">
+        <v>446</v>
+      </c>
+      <c r="C289">
+        <v>1</v>
+      </c>
+      <c r="D289" t="s">
+        <v>56</v>
+      </c>
+      <c r="E289" t="s">
         <v>447</v>
-      </c>
-      <c r="C289">
-        <v>1</v>
-      </c>
-      <c r="D289" t="s">
-        <v>56</v>
-      </c>
-      <c r="E289" t="s">
-        <v>3</v>
       </c>
       <c r="F289" s="1">
         <v>46254</v>
@@ -9663,7 +9792,7 @@
         <v>56</v>
       </c>
       <c r="E290" t="s">
-        <v>57</v>
+        <v>3</v>
       </c>
       <c r="F290" s="1">
         <v>46254</v>
@@ -9689,7 +9818,7 @@
         <v>56</v>
       </c>
       <c r="E291" t="s">
-        <v>450</v>
+        <v>57</v>
       </c>
       <c r="F291" s="1">
         <v>46254</v>
@@ -9706,16 +9835,16 @@
         <v>0</v>
       </c>
       <c r="B292" t="s">
+        <v>450</v>
+      </c>
+      <c r="C292">
+        <v>1</v>
+      </c>
+      <c r="D292" t="s">
+        <v>56</v>
+      </c>
+      <c r="E292" t="s">
         <v>451</v>
-      </c>
-      <c r="C292">
-        <v>1</v>
-      </c>
-      <c r="D292" t="s">
-        <v>56</v>
-      </c>
-      <c r="E292" t="s">
-        <v>132</v>
       </c>
       <c r="F292" s="1">
         <v>46254</v>
@@ -9741,7 +9870,7 @@
         <v>56</v>
       </c>
       <c r="E293" t="s">
-        <v>453</v>
+        <v>132</v>
       </c>
       <c r="F293" s="1">
         <v>46254</v>
@@ -9758,7 +9887,7 @@
         <v>0</v>
       </c>
       <c r="B294" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C294">
         <v>1</v>
@@ -9767,13 +9896,13 @@
         <v>56</v>
       </c>
       <c r="E294" t="s">
-        <v>455</v>
+        <v>281</v>
       </c>
       <c r="F294" s="1">
         <v>46254</v>
       </c>
       <c r="G294" s="1">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="H294">
         <v>0</v>
@@ -9784,16 +9913,16 @@
         <v>0</v>
       </c>
       <c r="B295" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="C295">
         <v>1</v>
       </c>
       <c r="D295" t="s">
-        <v>56</v>
+        <v>2</v>
       </c>
       <c r="E295" t="s">
-        <v>283</v>
+        <v>455</v>
       </c>
       <c r="F295" s="1">
         <v>46254</v>
@@ -9802,7 +9931,7 @@
         <v>46254</v>
       </c>
       <c r="H295">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="296" spans="1:8" x14ac:dyDescent="0.2">
@@ -9810,16 +9939,16 @@
         <v>0</v>
       </c>
       <c r="B296" t="s">
+        <v>456</v>
+      </c>
+      <c r="C296">
+        <v>1</v>
+      </c>
+      <c r="D296" t="s">
+        <v>56</v>
+      </c>
+      <c r="E296" t="s">
         <v>457</v>
-      </c>
-      <c r="C296">
-        <v>1</v>
-      </c>
-      <c r="D296" t="s">
-        <v>56</v>
-      </c>
-      <c r="E296" t="s">
-        <v>217</v>
       </c>
       <c r="F296" s="1">
         <v>46254</v>
@@ -9845,7 +9974,7 @@
         <v>56</v>
       </c>
       <c r="E297" t="s">
-        <v>459</v>
+        <v>283</v>
       </c>
       <c r="F297" s="1">
         <v>46254</v>
@@ -9862,7 +9991,7 @@
         <v>0</v>
       </c>
       <c r="B298" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C298">
         <v>1</v>
@@ -9871,7 +10000,7 @@
         <v>56</v>
       </c>
       <c r="E298" t="s">
-        <v>461</v>
+        <v>217</v>
       </c>
       <c r="F298" s="1">
         <v>46254</v>
@@ -9888,7 +10017,7 @@
         <v>0</v>
       </c>
       <c r="B299" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="C299">
         <v>1</v>
@@ -9897,7 +10026,7 @@
         <v>56</v>
       </c>
       <c r="E299" t="s">
-        <v>12</v>
+        <v>461</v>
       </c>
       <c r="F299" s="1">
         <v>46254</v>
@@ -9914,16 +10043,16 @@
         <v>0</v>
       </c>
       <c r="B300" t="s">
+        <v>462</v>
+      </c>
+      <c r="C300">
+        <v>1</v>
+      </c>
+      <c r="D300" t="s">
+        <v>56</v>
+      </c>
+      <c r="E300" t="s">
         <v>463</v>
-      </c>
-      <c r="C300">
-        <v>1</v>
-      </c>
-      <c r="D300" t="s">
-        <v>56</v>
-      </c>
-      <c r="E300" t="s">
-        <v>464</v>
       </c>
       <c r="F300" s="1">
         <v>46254</v>
@@ -9940,7 +10069,7 @@
         <v>0</v>
       </c>
       <c r="B301" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C301">
         <v>1</v>
@@ -9949,7 +10078,7 @@
         <v>56</v>
       </c>
       <c r="E301" t="s">
-        <v>161</v>
+        <v>12</v>
       </c>
       <c r="F301" s="1">
         <v>46254</v>
@@ -9966,16 +10095,16 @@
         <v>0</v>
       </c>
       <c r="B302" t="s">
+        <v>465</v>
+      </c>
+      <c r="C302">
+        <v>1</v>
+      </c>
+      <c r="D302" t="s">
+        <v>56</v>
+      </c>
+      <c r="E302" t="s">
         <v>466</v>
-      </c>
-      <c r="C302">
-        <v>1</v>
-      </c>
-      <c r="D302" t="s">
-        <v>56</v>
-      </c>
-      <c r="E302" t="s">
-        <v>467</v>
       </c>
       <c r="F302" s="1">
         <v>46254</v>
@@ -9992,7 +10121,7 @@
         <v>0</v>
       </c>
       <c r="B303" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C303">
         <v>1</v>
@@ -10001,7 +10130,7 @@
         <v>56</v>
       </c>
       <c r="E303" t="s">
-        <v>469</v>
+        <v>161</v>
       </c>
       <c r="F303" s="1">
         <v>46254</v>
@@ -10018,7 +10147,7 @@
         <v>0</v>
       </c>
       <c r="B304" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="C304">
         <v>1</v>
@@ -10027,7 +10156,7 @@
         <v>56</v>
       </c>
       <c r="E304" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="F304" s="1">
         <v>46254</v>
@@ -10044,7 +10173,7 @@
         <v>0</v>
       </c>
       <c r="B305" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="C305">
         <v>1</v>
@@ -10053,7 +10182,7 @@
         <v>56</v>
       </c>
       <c r="E305" t="s">
-        <v>384</v>
+        <v>471</v>
       </c>
       <c r="F305" s="1">
         <v>46254</v>
@@ -10070,16 +10199,16 @@
         <v>0</v>
       </c>
       <c r="B306" t="s">
+        <v>472</v>
+      </c>
+      <c r="C306">
+        <v>1</v>
+      </c>
+      <c r="D306" t="s">
+        <v>56</v>
+      </c>
+      <c r="E306" t="s">
         <v>473</v>
-      </c>
-      <c r="C306">
-        <v>1</v>
-      </c>
-      <c r="D306" t="s">
-        <v>56</v>
-      </c>
-      <c r="E306" t="s">
-        <v>474</v>
       </c>
       <c r="F306" s="1">
         <v>46254</v>
@@ -10096,7 +10225,7 @@
         <v>0</v>
       </c>
       <c r="B307" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C307">
         <v>1</v>
@@ -10105,7 +10234,7 @@
         <v>56</v>
       </c>
       <c r="E307" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="F307" s="1">
         <v>46254</v>
@@ -10119,51 +10248,51 @@
     </row>
     <row r="308" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A308" t="s">
+        <v>0</v>
+      </c>
+      <c r="B308" t="s">
+        <v>475</v>
+      </c>
+      <c r="C308">
+        <v>1</v>
+      </c>
+      <c r="D308" t="s">
+        <v>56</v>
+      </c>
+      <c r="E308" t="s">
         <v>476</v>
       </c>
-      <c r="B308" t="s">
-        <v>477</v>
-      </c>
-      <c r="C308">
-        <v>1</v>
-      </c>
-      <c r="D308" t="s">
-        <v>2</v>
-      </c>
-      <c r="E308" t="s">
-        <v>275</v>
-      </c>
       <c r="F308" s="1">
-        <v>46148</v>
+        <v>46254</v>
       </c>
       <c r="G308" s="1">
-        <v>46149</v>
+        <v>46254</v>
       </c>
       <c r="H308">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="309" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A309" t="s">
-        <v>478</v>
+        <v>0</v>
       </c>
       <c r="B309" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="C309">
         <v>1</v>
       </c>
       <c r="D309" t="s">
-        <v>5</v>
+        <v>56</v>
       </c>
       <c r="E309" t="s">
-        <v>29</v>
+        <v>100</v>
       </c>
       <c r="F309" s="1">
-        <v>46133</v>
+        <v>46254</v>
       </c>
       <c r="G309" s="1">
-        <v>46134</v>
+        <v>46255</v>
       </c>
       <c r="H309">
         <v>0</v>
@@ -10171,25 +10300,25 @@
     </row>
     <row r="310" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A310" t="s">
+        <v>0</v>
+      </c>
+      <c r="B310" t="s">
         <v>478</v>
       </c>
-      <c r="B310" t="s">
-        <v>480</v>
-      </c>
       <c r="C310">
         <v>1</v>
       </c>
       <c r="D310" t="s">
-        <v>5</v>
+        <v>56</v>
       </c>
       <c r="E310" t="s">
-        <v>29</v>
+        <v>389</v>
       </c>
       <c r="F310" s="1">
-        <v>46134</v>
+        <v>46254</v>
       </c>
       <c r="G310" s="1">
-        <v>46134</v>
+        <v>46254</v>
       </c>
       <c r="H310">
         <v>0</v>
@@ -10197,25 +10326,25 @@
     </row>
     <row r="311" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A311" t="s">
-        <v>478</v>
+        <v>0</v>
       </c>
       <c r="B311" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="C311">
         <v>1</v>
       </c>
       <c r="D311" t="s">
-        <v>5</v>
+        <v>56</v>
       </c>
       <c r="E311" t="s">
-        <v>14</v>
+        <v>100</v>
       </c>
       <c r="F311" s="1">
-        <v>46156</v>
+        <v>46254</v>
       </c>
       <c r="G311" s="1">
-        <v>46156</v>
+        <v>46255</v>
       </c>
       <c r="H311">
         <v>0</v>
@@ -10223,51 +10352,51 @@
     </row>
     <row r="312" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A312" t="s">
-        <v>478</v>
+        <v>0</v>
       </c>
       <c r="B312" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="C312">
         <v>1</v>
       </c>
       <c r="D312" t="s">
-        <v>2</v>
+        <v>56</v>
       </c>
       <c r="E312" t="s">
-        <v>453</v>
+        <v>481</v>
       </c>
       <c r="F312" s="1">
-        <v>46195</v>
+        <v>46254</v>
       </c>
       <c r="G312" s="1">
-        <v>46195</v>
+        <v>46255</v>
       </c>
       <c r="H312">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="313" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A313" t="s">
-        <v>478</v>
+        <v>0</v>
       </c>
       <c r="B313" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C313">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D313" t="s">
         <v>56</v>
       </c>
       <c r="E313" t="s">
-        <v>484</v>
+        <v>249</v>
       </c>
       <c r="F313" s="1">
-        <v>46206</v>
+        <v>46254</v>
       </c>
       <c r="G313" s="1">
-        <v>46252</v>
+        <v>46255</v>
       </c>
       <c r="H313">
         <v>0</v>
@@ -10275,51 +10404,51 @@
     </row>
     <row r="314" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A314" t="s">
-        <v>478</v>
+        <v>0</v>
       </c>
       <c r="B314" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="C314">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D314" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="E314" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="F314" s="1">
-        <v>46209</v>
+        <v>46254</v>
       </c>
       <c r="G314" s="1">
-        <v>46218</v>
+        <v>46255</v>
       </c>
       <c r="H314">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="315" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A315" t="s">
-        <v>478</v>
+        <v>0</v>
       </c>
       <c r="B315" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="C315">
         <v>1</v>
       </c>
       <c r="D315" t="s">
-        <v>5</v>
+        <v>56</v>
       </c>
       <c r="E315" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="F315" s="1">
-        <v>46213</v>
+        <v>46254</v>
       </c>
       <c r="G315" s="1">
-        <v>46213</v>
+        <v>46255</v>
       </c>
       <c r="H315">
         <v>0</v>
@@ -10327,59 +10456,59 @@
     </row>
     <row r="316" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A316" t="s">
-        <v>478</v>
+        <v>0</v>
       </c>
       <c r="B316" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="C316">
         <v>1</v>
       </c>
       <c r="D316" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="E316" t="s">
-        <v>208</v>
+        <v>488</v>
       </c>
       <c r="F316" s="1">
-        <v>46213</v>
+        <v>46254</v>
       </c>
       <c r="G316" s="1">
-        <v>46216</v>
+        <v>46255</v>
       </c>
       <c r="H316">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="317" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A317" t="s">
-        <v>478</v>
+        <v>0</v>
       </c>
       <c r="B317" t="s">
+        <v>489</v>
+      </c>
+      <c r="C317">
+        <v>1</v>
+      </c>
+      <c r="D317" t="s">
+        <v>56</v>
+      </c>
+      <c r="E317" t="s">
         <v>490</v>
       </c>
-      <c r="C317">
-        <v>3</v>
-      </c>
-      <c r="D317" t="s">
-        <v>2</v>
-      </c>
-      <c r="E317" t="s">
-        <v>94</v>
-      </c>
       <c r="F317" s="1">
-        <v>46220</v>
+        <v>46254</v>
       </c>
       <c r="G317" s="1">
-        <v>46231</v>
+        <v>46255</v>
       </c>
       <c r="H317">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="318" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A318" t="s">
-        <v>478</v>
+        <v>0</v>
       </c>
       <c r="B318" t="s">
         <v>491</v>
@@ -10388,24 +10517,24 @@
         <v>1</v>
       </c>
       <c r="D318" t="s">
-        <v>2</v>
+        <v>56</v>
       </c>
       <c r="E318" t="s">
-        <v>453</v>
+        <v>490</v>
       </c>
       <c r="F318" s="1">
-        <v>46223</v>
+        <v>46254</v>
       </c>
       <c r="G318" s="1">
-        <v>46223</v>
+        <v>46255</v>
       </c>
       <c r="H318">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="319" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A319" t="s">
-        <v>478</v>
+        <v>0</v>
       </c>
       <c r="B319" t="s">
         <v>492</v>
@@ -10414,24 +10543,24 @@
         <v>1</v>
       </c>
       <c r="D319" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="E319" t="s">
-        <v>208</v>
+        <v>188</v>
       </c>
       <c r="F319" s="1">
-        <v>46224</v>
+        <v>46254</v>
       </c>
       <c r="G319" s="1">
-        <v>46224</v>
+        <v>46255</v>
       </c>
       <c r="H319">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="320" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A320" t="s">
-        <v>478</v>
+        <v>0</v>
       </c>
       <c r="B320" t="s">
         <v>493</v>
@@ -10440,24 +10569,24 @@
         <v>1</v>
       </c>
       <c r="D320" t="s">
-        <v>2</v>
+        <v>56</v>
       </c>
       <c r="E320" t="s">
-        <v>453</v>
+        <v>490</v>
       </c>
       <c r="F320" s="1">
-        <v>46230</v>
+        <v>46254</v>
       </c>
       <c r="G320" s="1">
-        <v>46231</v>
+        <v>46255</v>
       </c>
       <c r="H320">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="321" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A321" t="s">
-        <v>478</v>
+        <v>0</v>
       </c>
       <c r="B321" t="s">
         <v>494</v>
@@ -10466,94 +10595,94 @@
         <v>1</v>
       </c>
       <c r="D321" t="s">
-        <v>2</v>
+        <v>56</v>
       </c>
       <c r="E321" t="s">
-        <v>94</v>
+        <v>495</v>
       </c>
       <c r="F321" s="1">
-        <v>46232</v>
+        <v>46254</v>
       </c>
       <c r="G321" s="1">
-        <v>46233</v>
+        <v>46255</v>
       </c>
       <c r="H321">
-        <v>126</v>
+        <v>0</v>
       </c>
     </row>
     <row r="322" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A322" t="s">
-        <v>478</v>
+        <v>0</v>
       </c>
       <c r="B322" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C322">
         <v>1</v>
       </c>
       <c r="D322" t="s">
-        <v>2</v>
+        <v>56</v>
       </c>
       <c r="E322" t="s">
-        <v>94</v>
+        <v>497</v>
       </c>
       <c r="F322" s="1">
-        <v>46232</v>
+        <v>46254</v>
       </c>
       <c r="G322" s="1">
-        <v>46233</v>
+        <v>46255</v>
       </c>
       <c r="H322">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="323" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A323" t="s">
-        <v>478</v>
+        <v>0</v>
       </c>
       <c r="B323" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C323">
         <v>1</v>
       </c>
       <c r="D323" t="s">
-        <v>2</v>
+        <v>56</v>
       </c>
       <c r="E323" t="s">
-        <v>208</v>
+        <v>499</v>
       </c>
       <c r="F323" s="1">
-        <v>46238</v>
+        <v>46254</v>
       </c>
       <c r="G323" s="1">
-        <v>46239</v>
+        <v>46255</v>
       </c>
       <c r="H323">
-        <v>117</v>
+        <v>0</v>
       </c>
     </row>
     <row r="324" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A324" t="s">
-        <v>478</v>
+        <v>0</v>
       </c>
       <c r="B324" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="C324">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D324" t="s">
         <v>56</v>
       </c>
       <c r="E324" t="s">
-        <v>484</v>
+        <v>261</v>
       </c>
       <c r="F324" s="1">
-        <v>46239</v>
+        <v>46254</v>
       </c>
       <c r="G324" s="1">
-        <v>46252</v>
+        <v>46255</v>
       </c>
       <c r="H324">
         <v>0</v>
@@ -10561,25 +10690,25 @@
     </row>
     <row r="325" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A325" t="s">
-        <v>478</v>
+        <v>0</v>
       </c>
       <c r="B325" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="C325">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D325" t="s">
         <v>56</v>
       </c>
       <c r="E325" t="s">
-        <v>484</v>
+        <v>257</v>
       </c>
       <c r="F325" s="1">
-        <v>46239</v>
+        <v>46254</v>
       </c>
       <c r="G325" s="1">
-        <v>46252</v>
+        <v>46255</v>
       </c>
       <c r="H325">
         <v>0</v>
@@ -10587,36 +10716,36 @@
     </row>
     <row r="326" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A326" t="s">
-        <v>478</v>
+        <v>0</v>
       </c>
       <c r="B326" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="C326">
         <v>1</v>
       </c>
       <c r="D326" t="s">
-        <v>2</v>
+        <v>56</v>
       </c>
       <c r="E326" t="s">
-        <v>29</v>
+        <v>503</v>
       </c>
       <c r="F326" s="1">
-        <v>46247</v>
+        <v>46254</v>
       </c>
       <c r="G326" s="1">
-        <v>46252</v>
+        <v>46255</v>
       </c>
       <c r="H326">
-        <v>29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="327" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A327" t="s">
-        <v>478</v>
+        <v>0</v>
       </c>
       <c r="B327" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="C327">
         <v>1</v>
@@ -10625,13 +10754,13 @@
         <v>56</v>
       </c>
       <c r="E327" t="s">
-        <v>293</v>
+        <v>505</v>
       </c>
       <c r="F327" s="1">
-        <v>46252</v>
+        <v>46254</v>
       </c>
       <c r="G327" s="1">
-        <v>46252</v>
+        <v>46255</v>
       </c>
       <c r="H327">
         <v>0</v>
@@ -10639,10 +10768,10 @@
     </row>
     <row r="328" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A328" t="s">
-        <v>478</v>
+        <v>0</v>
       </c>
       <c r="B328" t="s">
-        <v>501</v>
+        <v>506</v>
       </c>
       <c r="C328">
         <v>1</v>
@@ -10651,13 +10780,13 @@
         <v>56</v>
       </c>
       <c r="E328" t="s">
-        <v>132</v>
+        <v>503</v>
       </c>
       <c r="F328" s="1">
-        <v>46252</v>
+        <v>46254</v>
       </c>
       <c r="G328" s="1">
-        <v>46252</v>
+        <v>46255</v>
       </c>
       <c r="H328">
         <v>0</v>
@@ -10665,25 +10794,25 @@
     </row>
     <row r="329" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A329" t="s">
-        <v>478</v>
+        <v>0</v>
       </c>
       <c r="B329" t="s">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c r="C329">
         <v>1</v>
       </c>
       <c r="D329" t="s">
-        <v>5</v>
+        <v>56</v>
       </c>
       <c r="E329" t="s">
-        <v>503</v>
+        <v>293</v>
       </c>
       <c r="F329" s="1">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="G329" s="1">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="H329">
         <v>0</v>
@@ -10691,36 +10820,36 @@
     </row>
     <row r="330" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A330" t="s">
-        <v>478</v>
+        <v>0</v>
       </c>
       <c r="B330" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="C330">
         <v>1</v>
       </c>
       <c r="D330" t="s">
-        <v>2</v>
+        <v>56</v>
       </c>
       <c r="E330" t="s">
-        <v>208</v>
+        <v>509</v>
       </c>
       <c r="F330" s="1">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="G330" s="1">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="H330">
-        <v>105</v>
+        <v>0</v>
       </c>
     </row>
     <row r="331" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A331" t="s">
-        <v>478</v>
+        <v>0</v>
       </c>
       <c r="B331" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="C331">
         <v>1</v>
@@ -10729,13 +10858,13 @@
         <v>56</v>
       </c>
       <c r="E331" t="s">
-        <v>139</v>
+        <v>12</v>
       </c>
       <c r="F331" s="1">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="G331" s="1">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="H331">
         <v>0</v>
@@ -10743,10 +10872,10 @@
     </row>
     <row r="332" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A332" t="s">
-        <v>478</v>
+        <v>0</v>
       </c>
       <c r="B332" t="s">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="C332">
         <v>1</v>
@@ -10755,13 +10884,13 @@
         <v>56</v>
       </c>
       <c r="E332" t="s">
-        <v>399</v>
+        <v>26</v>
       </c>
       <c r="F332" s="1">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="G332" s="1">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="H332">
         <v>0</v>
@@ -10769,10 +10898,10 @@
     </row>
     <row r="333" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A333" t="s">
-        <v>478</v>
+        <v>0</v>
       </c>
       <c r="B333" t="s">
-        <v>507</v>
+        <v>512</v>
       </c>
       <c r="C333">
         <v>1</v>
@@ -10781,13 +10910,13 @@
         <v>56</v>
       </c>
       <c r="E333" t="s">
-        <v>422</v>
+        <v>513</v>
       </c>
       <c r="F333" s="1">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="G333" s="1">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="H333">
         <v>0</v>
@@ -10795,51 +10924,51 @@
     </row>
     <row r="334" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A334" t="s">
-        <v>478</v>
+        <v>514</v>
       </c>
       <c r="B334" t="s">
-        <v>508</v>
+        <v>515</v>
       </c>
       <c r="C334">
         <v>1</v>
       </c>
       <c r="D334" t="s">
-        <v>56</v>
+        <v>2</v>
       </c>
       <c r="E334" t="s">
-        <v>14</v>
+        <v>275</v>
       </c>
       <c r="F334" s="1">
-        <v>46254</v>
+        <v>46148</v>
       </c>
       <c r="G334" s="1">
-        <v>46254</v>
+        <v>46149</v>
       </c>
       <c r="H334">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="335" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A335" t="s">
-        <v>478</v>
+        <v>516</v>
       </c>
       <c r="B335" t="s">
-        <v>509</v>
+        <v>517</v>
       </c>
       <c r="C335">
         <v>1</v>
       </c>
       <c r="D335" t="s">
-        <v>56</v>
+        <v>5</v>
       </c>
       <c r="E335" t="s">
-        <v>94</v>
+        <v>29</v>
       </c>
       <c r="F335" s="1">
-        <v>46254</v>
+        <v>46133</v>
       </c>
       <c r="G335" s="1">
-        <v>46254</v>
+        <v>46134</v>
       </c>
       <c r="H335">
         <v>0</v>
@@ -10847,25 +10976,25 @@
     </row>
     <row r="336" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A336" t="s">
-        <v>478</v>
+        <v>516</v>
       </c>
       <c r="B336" t="s">
-        <v>510</v>
+        <v>518</v>
       </c>
       <c r="C336">
         <v>1</v>
       </c>
       <c r="D336" t="s">
-        <v>56</v>
+        <v>5</v>
       </c>
       <c r="E336" t="s">
-        <v>461</v>
+        <v>29</v>
       </c>
       <c r="F336" s="1">
-        <v>46254</v>
+        <v>46134</v>
       </c>
       <c r="G336" s="1">
-        <v>46254</v>
+        <v>46134</v>
       </c>
       <c r="H336">
         <v>0</v>
@@ -10873,103 +11002,103 @@
     </row>
     <row r="337" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A337" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="B337" t="s">
-        <v>512</v>
+        <v>519</v>
       </c>
       <c r="C337">
         <v>1</v>
       </c>
       <c r="D337" t="s">
-        <v>68</v>
+        <v>5</v>
       </c>
       <c r="E337" t="s">
-        <v>513</v>
+        <v>14</v>
       </c>
       <c r="F337" s="1">
-        <v>46063</v>
+        <v>46156</v>
       </c>
       <c r="G337" s="1">
-        <v>46064</v>
+        <v>46156</v>
       </c>
       <c r="H337">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="338" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A338" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="B338" t="s">
-        <v>514</v>
+        <v>520</v>
       </c>
       <c r="C338">
         <v>1</v>
       </c>
       <c r="D338" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E338" t="s">
-        <v>40</v>
+        <v>455</v>
       </c>
       <c r="F338" s="1">
-        <v>46113</v>
+        <v>46195</v>
       </c>
       <c r="G338" s="1">
-        <v>46125</v>
+        <v>46195</v>
       </c>
       <c r="H338">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="339" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A339" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="B339" t="s">
-        <v>515</v>
+        <v>521</v>
       </c>
       <c r="C339">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D339" t="s">
-        <v>2</v>
+        <v>56</v>
       </c>
       <c r="E339" t="s">
-        <v>40</v>
+        <v>522</v>
       </c>
       <c r="F339" s="1">
-        <v>46125</v>
+        <v>46206</v>
       </c>
       <c r="G339" s="1">
-        <v>46125</v>
+        <v>46252</v>
       </c>
       <c r="H339">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="340" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A340" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="B340" t="s">
-        <v>516</v>
+        <v>523</v>
       </c>
       <c r="C340">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D340" t="s">
-        <v>2</v>
+        <v>68</v>
       </c>
       <c r="E340" t="s">
-        <v>40</v>
+        <v>524</v>
       </c>
       <c r="F340" s="1">
-        <v>46126</v>
+        <v>46209</v>
       </c>
       <c r="G340" s="1">
-        <v>46126</v>
+        <v>46218</v>
       </c>
       <c r="H340">
         <v>1</v>
@@ -10977,88 +11106,88 @@
     </row>
     <row r="341" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A341" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="B341" t="s">
-        <v>517</v>
+        <v>525</v>
       </c>
       <c r="C341">
         <v>1</v>
       </c>
       <c r="D341" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E341" t="s">
-        <v>40</v>
+        <v>526</v>
       </c>
       <c r="F341" s="1">
-        <v>46126</v>
+        <v>46213</v>
       </c>
       <c r="G341" s="1">
-        <v>46126</v>
+        <v>46213</v>
       </c>
       <c r="H341">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="342" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A342" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="B342" t="s">
-        <v>518</v>
+        <v>527</v>
       </c>
       <c r="C342">
         <v>1</v>
       </c>
       <c r="D342" t="s">
-        <v>2</v>
+        <v>68</v>
       </c>
       <c r="E342" t="s">
-        <v>40</v>
+        <v>208</v>
       </c>
       <c r="F342" s="1">
-        <v>46128</v>
+        <v>46213</v>
       </c>
       <c r="G342" s="1">
-        <v>46128</v>
+        <v>46216</v>
       </c>
       <c r="H342">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="343" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A343" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="B343" t="s">
-        <v>519</v>
+        <v>528</v>
       </c>
       <c r="C343">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D343" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E343" t="s">
-        <v>40</v>
+        <v>94</v>
       </c>
       <c r="F343" s="1">
-        <v>46132</v>
+        <v>46220</v>
       </c>
       <c r="G343" s="1">
-        <v>46132</v>
+        <v>46231</v>
       </c>
       <c r="H343">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="344" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A344" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="B344" t="s">
-        <v>520</v>
+        <v>529</v>
       </c>
       <c r="C344">
         <v>1</v>
@@ -11067,50 +11196,50 @@
         <v>2</v>
       </c>
       <c r="E344" t="s">
-        <v>40</v>
+        <v>455</v>
       </c>
       <c r="F344" s="1">
-        <v>46161</v>
+        <v>46223</v>
       </c>
       <c r="G344" s="1">
-        <v>46161</v>
+        <v>46223</v>
       </c>
       <c r="H344">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="345" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A345" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="B345" t="s">
-        <v>521</v>
+        <v>530</v>
       </c>
       <c r="C345">
         <v>1</v>
       </c>
       <c r="D345" t="s">
-        <v>2</v>
+        <v>68</v>
       </c>
       <c r="E345" t="s">
-        <v>40</v>
+        <v>208</v>
       </c>
       <c r="F345" s="1">
-        <v>46174</v>
+        <v>46224</v>
       </c>
       <c r="G345" s="1">
-        <v>46174</v>
+        <v>46224</v>
       </c>
       <c r="H345">
-        <v>1</v>
+        <v>26</v>
       </c>
     </row>
     <row r="346" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A346" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="B346" t="s">
-        <v>522</v>
+        <v>531</v>
       </c>
       <c r="C346">
         <v>1</v>
@@ -11119,76 +11248,76 @@
         <v>2</v>
       </c>
       <c r="E346" t="s">
-        <v>40</v>
+        <v>455</v>
       </c>
       <c r="F346" s="1">
-        <v>46174</v>
+        <v>46230</v>
       </c>
       <c r="G346" s="1">
-        <v>46174</v>
+        <v>46231</v>
       </c>
       <c r="H346">
-        <v>1</v>
+        <v>18</v>
       </c>
     </row>
     <row r="347" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A347" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="B347" t="s">
-        <v>523</v>
+        <v>532</v>
       </c>
       <c r="C347">
         <v>1</v>
       </c>
       <c r="D347" t="s">
-        <v>56</v>
+        <v>2</v>
       </c>
       <c r="E347" t="s">
-        <v>40</v>
+        <v>94</v>
       </c>
       <c r="F347" s="1">
-        <v>46195</v>
+        <v>46232</v>
       </c>
       <c r="G347" s="1">
-        <v>46252</v>
+        <v>46233</v>
       </c>
       <c r="H347">
-        <v>0</v>
+        <v>126</v>
       </c>
     </row>
     <row r="348" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A348" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="B348" t="s">
-        <v>524</v>
+        <v>533</v>
       </c>
       <c r="C348">
         <v>1</v>
       </c>
       <c r="D348" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E348" t="s">
-        <v>40</v>
+        <v>94</v>
       </c>
       <c r="F348" s="1">
-        <v>46210</v>
+        <v>46232</v>
       </c>
       <c r="G348" s="1">
-        <v>46210</v>
+        <v>46233</v>
       </c>
       <c r="H348">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="349" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A349" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="B349" t="s">
-        <v>525</v>
+        <v>534</v>
       </c>
       <c r="C349">
         <v>1</v>
@@ -11197,36 +11326,36 @@
         <v>2</v>
       </c>
       <c r="E349" t="s">
-        <v>40</v>
+        <v>208</v>
       </c>
       <c r="F349" s="1">
-        <v>46213</v>
+        <v>46238</v>
       </c>
       <c r="G349" s="1">
-        <v>46213</v>
+        <v>46239</v>
       </c>
       <c r="H349">
-        <v>1</v>
+        <v>117</v>
       </c>
     </row>
     <row r="350" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A350" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="B350" t="s">
-        <v>526</v>
+        <v>535</v>
       </c>
       <c r="C350">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D350" t="s">
         <v>56</v>
       </c>
       <c r="E350" t="s">
-        <v>40</v>
+        <v>522</v>
       </c>
       <c r="F350" s="1">
-        <v>46218</v>
+        <v>46239</v>
       </c>
       <c r="G350" s="1">
         <v>46252</v>
@@ -11237,25 +11366,25 @@
     </row>
     <row r="351" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A351" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="B351" t="s">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="C351">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D351" t="s">
-        <v>5</v>
+        <v>56</v>
       </c>
       <c r="E351" t="s">
-        <v>54</v>
+        <v>522</v>
       </c>
       <c r="F351" s="1">
-        <v>46226</v>
+        <v>46239</v>
       </c>
       <c r="G351" s="1">
-        <v>46226</v>
+        <v>46252</v>
       </c>
       <c r="H351">
         <v>0</v>
@@ -11263,36 +11392,36 @@
     </row>
     <row r="352" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A352" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="B352" t="s">
-        <v>528</v>
+        <v>537</v>
       </c>
       <c r="C352">
         <v>1</v>
       </c>
       <c r="D352" t="s">
-        <v>56</v>
+        <v>2</v>
       </c>
       <c r="E352" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="F352" s="1">
-        <v>46227</v>
+        <v>46247</v>
       </c>
       <c r="G352" s="1">
         <v>46252</v>
       </c>
       <c r="H352">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="353" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A353" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="B353" t="s">
-        <v>529</v>
+        <v>538</v>
       </c>
       <c r="C353">
         <v>1</v>
@@ -11301,10 +11430,10 @@
         <v>56</v>
       </c>
       <c r="E353" t="s">
-        <v>40</v>
+        <v>293</v>
       </c>
       <c r="F353" s="1">
-        <v>46227</v>
+        <v>46252</v>
       </c>
       <c r="G353" s="1">
         <v>46252</v>
@@ -11315,25 +11444,25 @@
     </row>
     <row r="354" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A354" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="B354" t="s">
-        <v>530</v>
+        <v>539</v>
       </c>
       <c r="C354">
         <v>1</v>
       </c>
       <c r="D354" t="s">
-        <v>5</v>
+        <v>56</v>
       </c>
       <c r="E354" t="s">
-        <v>40</v>
+        <v>132</v>
       </c>
       <c r="F354" s="1">
-        <v>46227</v>
+        <v>46252</v>
       </c>
       <c r="G354" s="1">
-        <v>46228</v>
+        <v>46252</v>
       </c>
       <c r="H354">
         <v>0</v>
@@ -11341,25 +11470,25 @@
     </row>
     <row r="355" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A355" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="B355" t="s">
-        <v>531</v>
+        <v>540</v>
       </c>
       <c r="C355">
         <v>1</v>
       </c>
       <c r="D355" t="s">
-        <v>56</v>
+        <v>5</v>
       </c>
       <c r="E355" t="s">
-        <v>54</v>
+        <v>541</v>
       </c>
       <c r="F355" s="1">
-        <v>46230</v>
+        <v>46253</v>
       </c>
       <c r="G355" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="H355">
         <v>0</v>
@@ -11367,36 +11496,36 @@
     </row>
     <row r="356" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A356" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="B356" t="s">
-        <v>532</v>
+        <v>542</v>
       </c>
       <c r="C356">
         <v>1</v>
       </c>
       <c r="D356" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E356" t="s">
-        <v>40</v>
+        <v>208</v>
       </c>
       <c r="F356" s="1">
-        <v>46231</v>
+        <v>46253</v>
       </c>
       <c r="G356" s="1">
-        <v>46231</v>
+        <v>46254</v>
       </c>
       <c r="H356">
-        <v>0</v>
+        <v>105</v>
       </c>
     </row>
     <row r="357" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A357" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="B357" t="s">
-        <v>533</v>
+        <v>543</v>
       </c>
       <c r="C357">
         <v>1</v>
@@ -11405,13 +11534,13 @@
         <v>56</v>
       </c>
       <c r="E357" t="s">
-        <v>40</v>
+        <v>139</v>
       </c>
       <c r="F357" s="1">
-        <v>46254</v>
+        <v>46253</v>
       </c>
       <c r="G357" s="1">
-        <v>46254</v>
+        <v>46253</v>
       </c>
       <c r="H357">
         <v>0</v>
@@ -11419,10 +11548,10 @@
     </row>
     <row r="358" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A358" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="B358" t="s">
-        <v>534</v>
+        <v>544</v>
       </c>
       <c r="C358">
         <v>1</v>
@@ -11431,7 +11560,7 @@
         <v>56</v>
       </c>
       <c r="E358" t="s">
-        <v>40</v>
+        <v>423</v>
       </c>
       <c r="F358" s="1">
         <v>46254</v>
@@ -11445,183 +11574,989 @@
     </row>
     <row r="359" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A359" t="s">
-        <v>535</v>
+        <v>516</v>
       </c>
       <c r="B359" t="s">
-        <v>536</v>
+        <v>545</v>
       </c>
       <c r="C359">
         <v>1</v>
       </c>
       <c r="D359" t="s">
-        <v>2</v>
+        <v>56</v>
       </c>
       <c r="E359" t="s">
-        <v>537</v>
+        <v>94</v>
       </c>
       <c r="F359" s="1">
-        <v>46083</v>
+        <v>46254</v>
       </c>
       <c r="G359" s="1">
-        <v>46084</v>
+        <v>46254</v>
       </c>
       <c r="H359">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="360" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A360" t="s">
-        <v>535</v>
+        <v>516</v>
       </c>
       <c r="B360" t="s">
-        <v>538</v>
+        <v>546</v>
       </c>
       <c r="C360">
         <v>1</v>
       </c>
       <c r="D360" t="s">
-        <v>2</v>
+        <v>56</v>
       </c>
       <c r="E360" t="s">
-        <v>537</v>
+        <v>98</v>
       </c>
       <c r="F360" s="1">
-        <v>46132</v>
+        <v>46254</v>
       </c>
       <c r="G360" s="1">
-        <v>46133</v>
+        <v>46255</v>
       </c>
       <c r="H360">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="361" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A361" t="s">
-        <v>535</v>
+        <v>516</v>
       </c>
       <c r="B361" t="s">
-        <v>539</v>
+        <v>547</v>
       </c>
       <c r="C361">
         <v>1</v>
       </c>
       <c r="D361" t="s">
-        <v>2</v>
+        <v>56</v>
       </c>
       <c r="E361" t="s">
-        <v>540</v>
+        <v>463</v>
       </c>
       <c r="F361" s="1">
-        <v>46157</v>
+        <v>46254</v>
       </c>
       <c r="G361" s="1">
-        <v>46157</v>
+        <v>46254</v>
       </c>
       <c r="H361">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="362" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A362" t="s">
-        <v>535</v>
+        <v>516</v>
       </c>
       <c r="B362" t="s">
-        <v>541</v>
+        <v>548</v>
       </c>
       <c r="C362">
         <v>1</v>
       </c>
       <c r="D362" t="s">
-        <v>2</v>
+        <v>56</v>
       </c>
       <c r="E362" t="s">
-        <v>542</v>
+        <v>98</v>
       </c>
       <c r="F362" s="1">
-        <v>46168</v>
+        <v>46254</v>
       </c>
       <c r="G362" s="1">
-        <v>46170</v>
+        <v>46255</v>
       </c>
       <c r="H362">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="363" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A363" t="s">
-        <v>535</v>
+        <v>516</v>
       </c>
       <c r="B363" t="s">
-        <v>543</v>
+        <v>549</v>
       </c>
       <c r="C363">
         <v>1</v>
       </c>
       <c r="D363" t="s">
-        <v>2</v>
+        <v>56</v>
       </c>
       <c r="E363" t="s">
-        <v>540</v>
+        <v>100</v>
       </c>
       <c r="F363" s="1">
-        <v>46244</v>
+        <v>46254</v>
       </c>
       <c r="G363" s="1">
-        <v>46244</v>
+        <v>46255</v>
       </c>
       <c r="H363">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="364" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A364" t="s">
-        <v>535</v>
+        <v>516</v>
       </c>
       <c r="B364" t="s">
-        <v>544</v>
+        <v>550</v>
       </c>
       <c r="C364">
         <v>1</v>
       </c>
       <c r="D364" t="s">
-        <v>2</v>
+        <v>56</v>
       </c>
       <c r="E364" t="s">
-        <v>540</v>
+        <v>110</v>
       </c>
       <c r="F364" s="1">
-        <v>46247</v>
+        <v>46254</v>
       </c>
       <c r="G364" s="1">
-        <v>46247</v>
+        <v>46255</v>
       </c>
       <c r="H364">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="365" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A365" t="s">
-        <v>535</v>
+        <v>516</v>
       </c>
       <c r="B365" t="s">
-        <v>545</v>
+        <v>551</v>
       </c>
       <c r="C365">
         <v>1</v>
       </c>
       <c r="D365" t="s">
-        <v>2</v>
+        <v>56</v>
       </c>
       <c r="E365" t="s">
-        <v>537</v>
+        <v>110</v>
       </c>
       <c r="F365" s="1">
+        <v>46254</v>
+      </c>
+      <c r="G365" s="1">
+        <v>46255</v>
+      </c>
+      <c r="H365">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="366" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A366" t="s">
+        <v>516</v>
+      </c>
+      <c r="B366" t="s">
+        <v>552</v>
+      </c>
+      <c r="C366">
+        <v>1</v>
+      </c>
+      <c r="D366" t="s">
+        <v>56</v>
+      </c>
+      <c r="E366" t="s">
+        <v>503</v>
+      </c>
+      <c r="F366" s="1">
+        <v>46254</v>
+      </c>
+      <c r="G366" s="1">
+        <v>46255</v>
+      </c>
+      <c r="H366">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="367" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A367" t="s">
+        <v>516</v>
+      </c>
+      <c r="B367" t="s">
+        <v>553</v>
+      </c>
+      <c r="C367">
+        <v>1</v>
+      </c>
+      <c r="D367" t="s">
+        <v>56</v>
+      </c>
+      <c r="E367" t="s">
+        <v>503</v>
+      </c>
+      <c r="F367" s="1">
+        <v>46254</v>
+      </c>
+      <c r="G367" s="1">
+        <v>46255</v>
+      </c>
+      <c r="H367">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="368" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A368" t="s">
+        <v>554</v>
+      </c>
+      <c r="B368" t="s">
+        <v>555</v>
+      </c>
+      <c r="C368">
+        <v>1</v>
+      </c>
+      <c r="D368" t="s">
+        <v>68</v>
+      </c>
+      <c r="E368" t="s">
+        <v>556</v>
+      </c>
+      <c r="F368" s="1">
+        <v>46063</v>
+      </c>
+      <c r="G368" s="1">
+        <v>46064</v>
+      </c>
+      <c r="H368">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="369" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A369" t="s">
+        <v>554</v>
+      </c>
+      <c r="B369" t="s">
+        <v>557</v>
+      </c>
+      <c r="C369">
+        <v>1</v>
+      </c>
+      <c r="D369" t="s">
+        <v>5</v>
+      </c>
+      <c r="E369" t="s">
+        <v>40</v>
+      </c>
+      <c r="F369" s="1">
+        <v>46113</v>
+      </c>
+      <c r="G369" s="1">
+        <v>46125</v>
+      </c>
+      <c r="H369">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="370" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A370" t="s">
+        <v>554</v>
+      </c>
+      <c r="B370" t="s">
+        <v>558</v>
+      </c>
+      <c r="C370">
+        <v>1</v>
+      </c>
+      <c r="D370" t="s">
+        <v>2</v>
+      </c>
+      <c r="E370" t="s">
+        <v>40</v>
+      </c>
+      <c r="F370" s="1">
+        <v>46125</v>
+      </c>
+      <c r="G370" s="1">
+        <v>46125</v>
+      </c>
+      <c r="H370">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="371" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A371" t="s">
+        <v>554</v>
+      </c>
+      <c r="B371" t="s">
+        <v>559</v>
+      </c>
+      <c r="C371">
+        <v>1</v>
+      </c>
+      <c r="D371" t="s">
+        <v>2</v>
+      </c>
+      <c r="E371" t="s">
+        <v>40</v>
+      </c>
+      <c r="F371" s="1">
+        <v>46126</v>
+      </c>
+      <c r="G371" s="1">
+        <v>46126</v>
+      </c>
+      <c r="H371">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="372" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A372" t="s">
+        <v>554</v>
+      </c>
+      <c r="B372" t="s">
+        <v>560</v>
+      </c>
+      <c r="C372">
+        <v>1</v>
+      </c>
+      <c r="D372" t="s">
+        <v>2</v>
+      </c>
+      <c r="E372" t="s">
+        <v>40</v>
+      </c>
+      <c r="F372" s="1">
+        <v>46126</v>
+      </c>
+      <c r="G372" s="1">
+        <v>46126</v>
+      </c>
+      <c r="H372">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="373" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A373" t="s">
+        <v>554</v>
+      </c>
+      <c r="B373" t="s">
+        <v>561</v>
+      </c>
+      <c r="C373">
+        <v>1</v>
+      </c>
+      <c r="D373" t="s">
+        <v>2</v>
+      </c>
+      <c r="E373" t="s">
+        <v>40</v>
+      </c>
+      <c r="F373" s="1">
+        <v>46128</v>
+      </c>
+      <c r="G373" s="1">
+        <v>46128</v>
+      </c>
+      <c r="H373">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="374" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A374" t="s">
+        <v>554</v>
+      </c>
+      <c r="B374" t="s">
+        <v>562</v>
+      </c>
+      <c r="C374">
+        <v>1</v>
+      </c>
+      <c r="D374" t="s">
+        <v>5</v>
+      </c>
+      <c r="E374" t="s">
+        <v>40</v>
+      </c>
+      <c r="F374" s="1">
+        <v>46132</v>
+      </c>
+      <c r="G374" s="1">
+        <v>46132</v>
+      </c>
+      <c r="H374">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="375" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A375" t="s">
+        <v>554</v>
+      </c>
+      <c r="B375" t="s">
+        <v>563</v>
+      </c>
+      <c r="C375">
+        <v>1</v>
+      </c>
+      <c r="D375" t="s">
+        <v>2</v>
+      </c>
+      <c r="E375" t="s">
+        <v>40</v>
+      </c>
+      <c r="F375" s="1">
+        <v>46161</v>
+      </c>
+      <c r="G375" s="1">
+        <v>46161</v>
+      </c>
+      <c r="H375">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="376" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A376" t="s">
+        <v>554</v>
+      </c>
+      <c r="B376" t="s">
+        <v>564</v>
+      </c>
+      <c r="C376">
+        <v>1</v>
+      </c>
+      <c r="D376" t="s">
+        <v>2</v>
+      </c>
+      <c r="E376" t="s">
+        <v>40</v>
+      </c>
+      <c r="F376" s="1">
+        <v>46174</v>
+      </c>
+      <c r="G376" s="1">
+        <v>46174</v>
+      </c>
+      <c r="H376">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="377" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A377" t="s">
+        <v>554</v>
+      </c>
+      <c r="B377" t="s">
+        <v>565</v>
+      </c>
+      <c r="C377">
+        <v>1</v>
+      </c>
+      <c r="D377" t="s">
+        <v>2</v>
+      </c>
+      <c r="E377" t="s">
+        <v>40</v>
+      </c>
+      <c r="F377" s="1">
+        <v>46174</v>
+      </c>
+      <c r="G377" s="1">
+        <v>46174</v>
+      </c>
+      <c r="H377">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="378" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A378" t="s">
+        <v>554</v>
+      </c>
+      <c r="B378" t="s">
+        <v>566</v>
+      </c>
+      <c r="C378">
+        <v>1</v>
+      </c>
+      <c r="D378" t="s">
+        <v>56</v>
+      </c>
+      <c r="E378" t="s">
+        <v>40</v>
+      </c>
+      <c r="F378" s="1">
+        <v>46195</v>
+      </c>
+      <c r="G378" s="1">
+        <v>46252</v>
+      </c>
+      <c r="H378">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="379" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A379" t="s">
+        <v>554</v>
+      </c>
+      <c r="B379" t="s">
+        <v>567</v>
+      </c>
+      <c r="C379">
+        <v>1</v>
+      </c>
+      <c r="D379" t="s">
+        <v>5</v>
+      </c>
+      <c r="E379" t="s">
+        <v>40</v>
+      </c>
+      <c r="F379" s="1">
+        <v>46210</v>
+      </c>
+      <c r="G379" s="1">
+        <v>46210</v>
+      </c>
+      <c r="H379">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="380" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A380" t="s">
+        <v>554</v>
+      </c>
+      <c r="B380" t="s">
+        <v>568</v>
+      </c>
+      <c r="C380">
+        <v>1</v>
+      </c>
+      <c r="D380" t="s">
+        <v>2</v>
+      </c>
+      <c r="E380" t="s">
+        <v>40</v>
+      </c>
+      <c r="F380" s="1">
+        <v>46213</v>
+      </c>
+      <c r="G380" s="1">
+        <v>46213</v>
+      </c>
+      <c r="H380">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="381" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A381" t="s">
+        <v>554</v>
+      </c>
+      <c r="B381" t="s">
+        <v>569</v>
+      </c>
+      <c r="C381">
+        <v>1</v>
+      </c>
+      <c r="D381" t="s">
+        <v>56</v>
+      </c>
+      <c r="E381" t="s">
+        <v>40</v>
+      </c>
+      <c r="F381" s="1">
+        <v>46218</v>
+      </c>
+      <c r="G381" s="1">
+        <v>46252</v>
+      </c>
+      <c r="H381">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="382" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A382" t="s">
+        <v>554</v>
+      </c>
+      <c r="B382" t="s">
+        <v>570</v>
+      </c>
+      <c r="C382">
+        <v>1</v>
+      </c>
+      <c r="D382" t="s">
+        <v>5</v>
+      </c>
+      <c r="E382" t="s">
+        <v>54</v>
+      </c>
+      <c r="F382" s="1">
+        <v>46226</v>
+      </c>
+      <c r="G382" s="1">
+        <v>46226</v>
+      </c>
+      <c r="H382">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="383" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A383" t="s">
+        <v>554</v>
+      </c>
+      <c r="B383" t="s">
+        <v>571</v>
+      </c>
+      <c r="C383">
+        <v>1</v>
+      </c>
+      <c r="D383" t="s">
+        <v>56</v>
+      </c>
+      <c r="E383" t="s">
+        <v>40</v>
+      </c>
+      <c r="F383" s="1">
+        <v>46227</v>
+      </c>
+      <c r="G383" s="1">
+        <v>46252</v>
+      </c>
+      <c r="H383">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="384" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A384" t="s">
+        <v>554</v>
+      </c>
+      <c r="B384" t="s">
+        <v>572</v>
+      </c>
+      <c r="C384">
+        <v>1</v>
+      </c>
+      <c r="D384" t="s">
+        <v>56</v>
+      </c>
+      <c r="E384" t="s">
+        <v>40</v>
+      </c>
+      <c r="F384" s="1">
+        <v>46227</v>
+      </c>
+      <c r="G384" s="1">
+        <v>46252</v>
+      </c>
+      <c r="H384">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="385" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A385" t="s">
+        <v>554</v>
+      </c>
+      <c r="B385" t="s">
+        <v>573</v>
+      </c>
+      <c r="C385">
+        <v>1</v>
+      </c>
+      <c r="D385" t="s">
+        <v>5</v>
+      </c>
+      <c r="E385" t="s">
+        <v>40</v>
+      </c>
+      <c r="F385" s="1">
+        <v>46227</v>
+      </c>
+      <c r="G385" s="1">
+        <v>46228</v>
+      </c>
+      <c r="H385">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="386" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A386" t="s">
+        <v>554</v>
+      </c>
+      <c r="B386" t="s">
+        <v>574</v>
+      </c>
+      <c r="C386">
+        <v>1</v>
+      </c>
+      <c r="D386" t="s">
+        <v>56</v>
+      </c>
+      <c r="E386" t="s">
+        <v>54</v>
+      </c>
+      <c r="F386" s="1">
+        <v>46230</v>
+      </c>
+      <c r="G386" s="1">
+        <v>46252</v>
+      </c>
+      <c r="H386">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="387" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A387" t="s">
+        <v>554</v>
+      </c>
+      <c r="B387" t="s">
+        <v>575</v>
+      </c>
+      <c r="C387">
+        <v>1</v>
+      </c>
+      <c r="D387" t="s">
+        <v>5</v>
+      </c>
+      <c r="E387" t="s">
+        <v>40</v>
+      </c>
+      <c r="F387" s="1">
+        <v>46231</v>
+      </c>
+      <c r="G387" s="1">
+        <v>46231</v>
+      </c>
+      <c r="H387">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="388" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A388" t="s">
+        <v>554</v>
+      </c>
+      <c r="B388" t="s">
+        <v>576</v>
+      </c>
+      <c r="C388">
+        <v>1</v>
+      </c>
+      <c r="D388" t="s">
+        <v>5</v>
+      </c>
+      <c r="E388" t="s">
+        <v>40</v>
+      </c>
+      <c r="F388" s="1">
+        <v>46254</v>
+      </c>
+      <c r="G388" s="1">
+        <v>46254</v>
+      </c>
+      <c r="H388">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="389" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A389" t="s">
+        <v>554</v>
+      </c>
+      <c r="B389" t="s">
+        <v>577</v>
+      </c>
+      <c r="C389">
+        <v>1</v>
+      </c>
+      <c r="D389" t="s">
+        <v>56</v>
+      </c>
+      <c r="E389" t="s">
+        <v>40</v>
+      </c>
+      <c r="F389" s="1">
+        <v>46255</v>
+      </c>
+      <c r="G389" s="1">
+        <v>46255</v>
+      </c>
+      <c r="H389">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="390" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A390" t="s">
+        <v>578</v>
+      </c>
+      <c r="B390" t="s">
+        <v>579</v>
+      </c>
+      <c r="C390">
+        <v>1</v>
+      </c>
+      <c r="D390" t="s">
+        <v>2</v>
+      </c>
+      <c r="E390" t="s">
+        <v>580</v>
+      </c>
+      <c r="F390" s="1">
+        <v>46083</v>
+      </c>
+      <c r="G390" s="1">
+        <v>46084</v>
+      </c>
+      <c r="H390">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="391" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A391" t="s">
+        <v>578</v>
+      </c>
+      <c r="B391" t="s">
+        <v>581</v>
+      </c>
+      <c r="C391">
+        <v>1</v>
+      </c>
+      <c r="D391" t="s">
+        <v>2</v>
+      </c>
+      <c r="E391" t="s">
+        <v>580</v>
+      </c>
+      <c r="F391" s="1">
+        <v>46132</v>
+      </c>
+      <c r="G391" s="1">
+        <v>46133</v>
+      </c>
+      <c r="H391">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="392" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A392" t="s">
+        <v>578</v>
+      </c>
+      <c r="B392" t="s">
+        <v>582</v>
+      </c>
+      <c r="C392">
+        <v>1</v>
+      </c>
+      <c r="D392" t="s">
+        <v>2</v>
+      </c>
+      <c r="E392" t="s">
+        <v>583</v>
+      </c>
+      <c r="F392" s="1">
+        <v>46157</v>
+      </c>
+      <c r="G392" s="1">
+        <v>46157</v>
+      </c>
+      <c r="H392">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="393" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A393" t="s">
+        <v>578</v>
+      </c>
+      <c r="B393" t="s">
+        <v>584</v>
+      </c>
+      <c r="C393">
+        <v>1</v>
+      </c>
+      <c r="D393" t="s">
+        <v>2</v>
+      </c>
+      <c r="E393" t="s">
+        <v>585</v>
+      </c>
+      <c r="F393" s="1">
+        <v>46168</v>
+      </c>
+      <c r="G393" s="1">
+        <v>46170</v>
+      </c>
+      <c r="H393">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="394" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A394" t="s">
+        <v>578</v>
+      </c>
+      <c r="B394" t="s">
+        <v>586</v>
+      </c>
+      <c r="C394">
+        <v>1</v>
+      </c>
+      <c r="D394" t="s">
+        <v>2</v>
+      </c>
+      <c r="E394" t="s">
+        <v>583</v>
+      </c>
+      <c r="F394" s="1">
+        <v>46244</v>
+      </c>
+      <c r="G394" s="1">
+        <v>46244</v>
+      </c>
+      <c r="H394">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="395" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A395" t="s">
+        <v>578</v>
+      </c>
+      <c r="B395" t="s">
+        <v>587</v>
+      </c>
+      <c r="C395">
+        <v>1</v>
+      </c>
+      <c r="D395" t="s">
+        <v>2</v>
+      </c>
+      <c r="E395" t="s">
+        <v>583</v>
+      </c>
+      <c r="F395" s="1">
         <v>46247</v>
       </c>
-      <c r="G365" s="1">
+      <c r="G395" s="1">
         <v>46247</v>
       </c>
-      <c r="H365">
+      <c r="H395">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="396" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A396" t="s">
+        <v>578</v>
+      </c>
+      <c r="B396" t="s">
+        <v>588</v>
+      </c>
+      <c r="C396">
+        <v>1</v>
+      </c>
+      <c r="D396" t="s">
+        <v>2</v>
+      </c>
+      <c r="E396" t="s">
+        <v>580</v>
+      </c>
+      <c r="F396" s="1">
+        <v>46247</v>
+      </c>
+      <c r="G396" s="1">
+        <v>46247</v>
+      </c>
+      <c r="H396">
         <v>1</v>
       </c>
     </row>

--- a/Data_ERP/Pedidos Transmicion.xlsx
+++ b/Data_ERP/Pedidos Transmicion.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sistema_Logistico_Peirano\Data_ERP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E55C8A46-0CD1-4E8F-AA00-A330D50EA55B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0BE52C57-FF3A-43EE-AD9F-B2B8F15C1584}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="27195" yWindow="4455" windowWidth="15375" windowHeight="8325" xr2:uid="{CE17D439-2207-4B04-856E-C2DA8F3F9AB0}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{F3EF298B-41C7-4855-832E-4E769876D2B9}"/>
   </bookViews>
   <sheets>
     <sheet name="transmicion" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2062" uniqueCount="815">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2042" uniqueCount="811">
   <si>
     <t>0001</t>
   </si>
@@ -1741,6 +1741,9 @@
     <t>DECORMAT S.R.L.</t>
   </si>
   <si>
+    <t xml:space="preserve">  214143</t>
+  </si>
+  <si>
     <t xml:space="preserve">  214144</t>
   </si>
   <si>
@@ -2014,15 +2017,18 @@
     <t xml:space="preserve">  214203</t>
   </si>
   <si>
+    <t xml:space="preserve">  214204</t>
+  </si>
+  <si>
+    <t>TB02</t>
+  </si>
+  <si>
+    <t>IT BROKERS S.A.</t>
+  </si>
+  <si>
     <t xml:space="preserve">  214205</t>
   </si>
   <si>
-    <t>TB02</t>
-  </si>
-  <si>
-    <t>IT BROKERS S.A.</t>
-  </si>
-  <si>
     <t xml:space="preserve">  214206</t>
   </si>
   <si>
@@ -2110,9 +2116,6 @@
     <t xml:space="preserve">  214222</t>
   </si>
   <si>
-    <t xml:space="preserve">  214223</t>
-  </si>
-  <si>
     <t xml:space="preserve">  214224</t>
   </si>
   <si>
@@ -2275,15 +2278,9 @@
     <t xml:space="preserve">    2827</t>
   </si>
   <si>
-    <t xml:space="preserve">    2828</t>
-  </si>
-  <si>
     <t xml:space="preserve">    2829</t>
   </si>
   <si>
-    <t xml:space="preserve">    2830</t>
-  </si>
-  <si>
     <t xml:space="preserve">    2831</t>
   </si>
   <si>
@@ -2317,9 +2314,6 @@
     <t>VARIOS</t>
   </si>
   <si>
-    <t xml:space="preserve">    2841</t>
-  </si>
-  <si>
     <t>4444</t>
   </si>
   <si>
@@ -2393,12 +2387,6 @@
   </si>
   <si>
     <t xml:space="preserve">    2258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    2260</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    2261</t>
   </si>
   <si>
     <t>9999</t>
@@ -2914,31 +2902,31 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BA96046-D851-4BB7-B8CA-2F6FDF561BF7}">
-  <dimension ref="A1:G412"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE68528F-9967-494B-98A8-1493F02C3C69}">
+  <dimension ref="A1:G408"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
+        <v>804</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>805</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>806</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>807</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>808</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>809</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>810</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>811</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>812</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>813</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>814</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
@@ -6537,7 +6525,7 @@
         <v>363</v>
       </c>
       <c r="C158" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D158" t="s">
         <v>364</v>
@@ -7664,7 +7652,7 @@
         <v>454</v>
       </c>
       <c r="C207" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D207" t="s">
         <v>455</v>
@@ -7917,7 +7905,7 @@
         <v>475</v>
       </c>
       <c r="C218" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D218" t="s">
         <v>16</v>
@@ -8124,7 +8112,7 @@
         <v>492</v>
       </c>
       <c r="C227" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D227" t="s">
         <v>493</v>
@@ -8193,7 +8181,7 @@
         <v>499</v>
       </c>
       <c r="C230" t="s">
-        <v>80</v>
+        <v>6</v>
       </c>
       <c r="D230" t="s">
         <v>138</v>
@@ -8699,7 +8687,7 @@
         <v>545</v>
       </c>
       <c r="C252" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D252" t="s">
         <v>546</v>
@@ -8722,7 +8710,7 @@
         <v>548</v>
       </c>
       <c r="C253" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D253" t="s">
         <v>546</v>
@@ -8768,7 +8756,7 @@
         <v>550</v>
       </c>
       <c r="C255" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D255" t="s">
         <v>546</v>
@@ -9024,16 +9012,16 @@
         <v>80</v>
       </c>
       <c r="D266" t="s">
-        <v>574</v>
+        <v>337</v>
       </c>
       <c r="E266" t="s">
-        <v>575</v>
+        <v>338</v>
       </c>
       <c r="F266" s="1">
         <v>46254</v>
       </c>
       <c r="G266" s="1">
-        <v>46255</v>
+        <v>46256</v>
       </c>
     </row>
     <row r="267" spans="1:7" x14ac:dyDescent="0.2">
@@ -9041,16 +9029,16 @@
         <v>0</v>
       </c>
       <c r="B267" t="s">
+        <v>574</v>
+      </c>
+      <c r="C267" t="s">
+        <v>80</v>
+      </c>
+      <c r="D267" t="s">
+        <v>575</v>
+      </c>
+      <c r="E267" t="s">
         <v>576</v>
-      </c>
-      <c r="C267" t="s">
-        <v>80</v>
-      </c>
-      <c r="D267" t="s">
-        <v>571</v>
-      </c>
-      <c r="E267" t="s">
-        <v>572</v>
       </c>
       <c r="F267" s="1">
         <v>46254</v>
@@ -9067,13 +9055,13 @@
         <v>577</v>
       </c>
       <c r="C268" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D268" t="s">
-        <v>216</v>
+        <v>571</v>
       </c>
       <c r="E268" t="s">
-        <v>217</v>
+        <v>572</v>
       </c>
       <c r="F268" s="1">
         <v>46254</v>
@@ -9090,13 +9078,13 @@
         <v>578</v>
       </c>
       <c r="C269" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D269" t="s">
-        <v>579</v>
+        <v>216</v>
       </c>
       <c r="E269" t="s">
-        <v>580</v>
+        <v>217</v>
       </c>
       <c r="F269" s="1">
         <v>46254</v>
@@ -9110,19 +9098,19 @@
         <v>0</v>
       </c>
       <c r="B270" t="s">
+        <v>579</v>
+      </c>
+      <c r="C270" t="s">
+        <v>80</v>
+      </c>
+      <c r="D270" t="s">
+        <v>580</v>
+      </c>
+      <c r="E270" t="s">
         <v>581</v>
       </c>
-      <c r="C270" t="s">
-        <v>80</v>
-      </c>
-      <c r="D270" t="s">
-        <v>16</v>
-      </c>
-      <c r="E270" t="s">
-        <v>17</v>
-      </c>
       <c r="F270" s="1">
-        <v>46255</v>
+        <v>46254</v>
       </c>
       <c r="G270" s="1">
         <v>46255</v>
@@ -9136,13 +9124,13 @@
         <v>582</v>
       </c>
       <c r="C271" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D271" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="E271" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F271" s="1">
         <v>46255</v>
@@ -9159,13 +9147,13 @@
         <v>583</v>
       </c>
       <c r="C272" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D272" t="s">
-        <v>584</v>
+        <v>37</v>
       </c>
       <c r="E272" t="s">
-        <v>585</v>
+        <v>38</v>
       </c>
       <c r="F272" s="1">
         <v>46255</v>
@@ -9179,16 +9167,16 @@
         <v>0</v>
       </c>
       <c r="B273" t="s">
+        <v>584</v>
+      </c>
+      <c r="C273" t="s">
+        <v>2</v>
+      </c>
+      <c r="D273" t="s">
+        <v>585</v>
+      </c>
+      <c r="E273" t="s">
         <v>586</v>
-      </c>
-      <c r="C273" t="s">
-        <v>80</v>
-      </c>
-      <c r="D273" t="s">
-        <v>587</v>
-      </c>
-      <c r="E273" t="s">
-        <v>588</v>
       </c>
       <c r="F273" s="1">
         <v>46255</v>
@@ -9202,16 +9190,16 @@
         <v>0</v>
       </c>
       <c r="B274" t="s">
+        <v>587</v>
+      </c>
+      <c r="C274" t="s">
+        <v>80</v>
+      </c>
+      <c r="D274" t="s">
+        <v>588</v>
+      </c>
+      <c r="E274" t="s">
         <v>589</v>
-      </c>
-      <c r="C274" t="s">
-        <v>80</v>
-      </c>
-      <c r="D274" t="s">
-        <v>98</v>
-      </c>
-      <c r="E274" t="s">
-        <v>99</v>
       </c>
       <c r="F274" s="1">
         <v>46255</v>
@@ -9231,10 +9219,10 @@
         <v>80</v>
       </c>
       <c r="D275" t="s">
-        <v>219</v>
+        <v>98</v>
       </c>
       <c r="E275" t="s">
-        <v>220</v>
+        <v>99</v>
       </c>
       <c r="F275" s="1">
         <v>46255</v>
@@ -9277,10 +9265,10 @@
         <v>80</v>
       </c>
       <c r="D277" t="s">
-        <v>593</v>
+        <v>219</v>
       </c>
       <c r="E277" t="s">
-        <v>594</v>
+        <v>220</v>
       </c>
       <c r="F277" s="1">
         <v>46255</v>
@@ -9294,16 +9282,16 @@
         <v>0</v>
       </c>
       <c r="B278" t="s">
+        <v>593</v>
+      </c>
+      <c r="C278" t="s">
+        <v>80</v>
+      </c>
+      <c r="D278" t="s">
+        <v>594</v>
+      </c>
+      <c r="E278" t="s">
         <v>595</v>
-      </c>
-      <c r="C278" t="s">
-        <v>80</v>
-      </c>
-      <c r="D278" t="s">
-        <v>16</v>
-      </c>
-      <c r="E278" t="s">
-        <v>17</v>
       </c>
       <c r="F278" s="1">
         <v>46255</v>
@@ -9323,10 +9311,10 @@
         <v>80</v>
       </c>
       <c r="D279" t="s">
-        <v>337</v>
+        <v>16</v>
       </c>
       <c r="E279" t="s">
-        <v>338</v>
+        <v>17</v>
       </c>
       <c r="F279" s="1">
         <v>46255</v>
@@ -9346,10 +9334,10 @@
         <v>80</v>
       </c>
       <c r="D280" t="s">
-        <v>435</v>
+        <v>337</v>
       </c>
       <c r="E280" t="s">
-        <v>436</v>
+        <v>338</v>
       </c>
       <c r="F280" s="1">
         <v>46255</v>
@@ -9369,10 +9357,10 @@
         <v>80</v>
       </c>
       <c r="D281" t="s">
-        <v>599</v>
+        <v>435</v>
       </c>
       <c r="E281" t="s">
-        <v>600</v>
+        <v>436</v>
       </c>
       <c r="F281" s="1">
         <v>46255</v>
@@ -9386,16 +9374,16 @@
         <v>0</v>
       </c>
       <c r="B282" t="s">
+        <v>599</v>
+      </c>
+      <c r="C282" t="s">
+        <v>80</v>
+      </c>
+      <c r="D282" t="s">
+        <v>600</v>
+      </c>
+      <c r="E282" t="s">
         <v>601</v>
-      </c>
-      <c r="C282" t="s">
-        <v>80</v>
-      </c>
-      <c r="D282" t="s">
-        <v>599</v>
-      </c>
-      <c r="E282" t="s">
-        <v>600</v>
       </c>
       <c r="F282" s="1">
         <v>46255</v>
@@ -9415,10 +9403,10 @@
         <v>80</v>
       </c>
       <c r="D283" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="E283" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="F283" s="1">
         <v>46255</v>
@@ -9432,16 +9420,16 @@
         <v>0</v>
       </c>
       <c r="B284" t="s">
+        <v>603</v>
+      </c>
+      <c r="C284" t="s">
+        <v>80</v>
+      </c>
+      <c r="D284" t="s">
+        <v>604</v>
+      </c>
+      <c r="E284" t="s">
         <v>605</v>
-      </c>
-      <c r="C284" t="s">
-        <v>80</v>
-      </c>
-      <c r="D284" t="s">
-        <v>422</v>
-      </c>
-      <c r="E284" t="s">
-        <v>423</v>
       </c>
       <c r="F284" s="1">
         <v>46255</v>
@@ -9484,10 +9472,10 @@
         <v>80</v>
       </c>
       <c r="D286" t="s">
-        <v>367</v>
+        <v>422</v>
       </c>
       <c r="E286" t="s">
-        <v>368</v>
+        <v>423</v>
       </c>
       <c r="F286" s="1">
         <v>46255</v>
@@ -9530,10 +9518,10 @@
         <v>80</v>
       </c>
       <c r="D288" t="s">
-        <v>610</v>
+        <v>367</v>
       </c>
       <c r="E288" t="s">
-        <v>611</v>
+        <v>368</v>
       </c>
       <c r="F288" s="1">
         <v>46255</v>
@@ -9547,16 +9535,16 @@
         <v>0</v>
       </c>
       <c r="B289" t="s">
+        <v>610</v>
+      </c>
+      <c r="C289" t="s">
+        <v>80</v>
+      </c>
+      <c r="D289" t="s">
+        <v>611</v>
+      </c>
+      <c r="E289" t="s">
         <v>612</v>
-      </c>
-      <c r="C289" t="s">
-        <v>80</v>
-      </c>
-      <c r="D289" t="s">
-        <v>429</v>
-      </c>
-      <c r="E289" t="s">
-        <v>430</v>
       </c>
       <c r="F289" s="1">
         <v>46255</v>
@@ -9599,10 +9587,10 @@
         <v>80</v>
       </c>
       <c r="D291" t="s">
-        <v>348</v>
+        <v>429</v>
       </c>
       <c r="E291" t="s">
-        <v>349</v>
+        <v>430</v>
       </c>
       <c r="F291" s="1">
         <v>46255</v>
@@ -9622,10 +9610,10 @@
         <v>80</v>
       </c>
       <c r="D292" t="s">
-        <v>616</v>
+        <v>348</v>
       </c>
       <c r="E292" t="s">
-        <v>617</v>
+        <v>349</v>
       </c>
       <c r="F292" s="1">
         <v>46255</v>
@@ -9639,16 +9627,16 @@
         <v>0</v>
       </c>
       <c r="B293" t="s">
+        <v>616</v>
+      </c>
+      <c r="C293" t="s">
+        <v>80</v>
+      </c>
+      <c r="D293" t="s">
+        <v>617</v>
+      </c>
+      <c r="E293" t="s">
         <v>618</v>
-      </c>
-      <c r="C293" t="s">
-        <v>80</v>
-      </c>
-      <c r="D293" t="s">
-        <v>7</v>
-      </c>
-      <c r="E293" t="s">
-        <v>8</v>
       </c>
       <c r="F293" s="1">
         <v>46255</v>
@@ -9668,10 +9656,10 @@
         <v>80</v>
       </c>
       <c r="D294" t="s">
-        <v>101</v>
+        <v>7</v>
       </c>
       <c r="E294" t="s">
-        <v>102</v>
+        <v>8</v>
       </c>
       <c r="F294" s="1">
         <v>46255</v>
@@ -9691,10 +9679,10 @@
         <v>80</v>
       </c>
       <c r="D295" t="s">
-        <v>381</v>
+        <v>101</v>
       </c>
       <c r="E295" t="s">
-        <v>382</v>
+        <v>102</v>
       </c>
       <c r="F295" s="1">
         <v>46255</v>
@@ -9714,10 +9702,10 @@
         <v>80</v>
       </c>
       <c r="D296" t="s">
-        <v>599</v>
+        <v>381</v>
       </c>
       <c r="E296" t="s">
-        <v>600</v>
+        <v>382</v>
       </c>
       <c r="F296" s="1">
         <v>46255</v>
@@ -9737,10 +9725,10 @@
         <v>80</v>
       </c>
       <c r="D297" t="s">
-        <v>381</v>
+        <v>600</v>
       </c>
       <c r="E297" t="s">
-        <v>382</v>
+        <v>601</v>
       </c>
       <c r="F297" s="1">
         <v>46255</v>
@@ -9760,10 +9748,10 @@
         <v>80</v>
       </c>
       <c r="D298" t="s">
-        <v>624</v>
+        <v>381</v>
       </c>
       <c r="E298" t="s">
-        <v>625</v>
+        <v>382</v>
       </c>
       <c r="F298" s="1">
         <v>46255</v>
@@ -9777,16 +9765,16 @@
         <v>0</v>
       </c>
       <c r="B299" t="s">
+        <v>624</v>
+      </c>
+      <c r="C299" t="s">
+        <v>80</v>
+      </c>
+      <c r="D299" t="s">
+        <v>625</v>
+      </c>
+      <c r="E299" t="s">
         <v>626</v>
-      </c>
-      <c r="C299" t="s">
-        <v>80</v>
-      </c>
-      <c r="D299" t="s">
-        <v>224</v>
-      </c>
-      <c r="E299" t="s">
-        <v>225</v>
       </c>
       <c r="F299" s="1">
         <v>46255</v>
@@ -9806,10 +9794,10 @@
         <v>80</v>
       </c>
       <c r="D300" t="s">
-        <v>74</v>
+        <v>224</v>
       </c>
       <c r="E300" t="s">
-        <v>75</v>
+        <v>225</v>
       </c>
       <c r="F300" s="1">
         <v>46255</v>
@@ -9829,10 +9817,10 @@
         <v>80</v>
       </c>
       <c r="D301" t="s">
-        <v>629</v>
+        <v>74</v>
       </c>
       <c r="E301" t="s">
-        <v>630</v>
+        <v>75</v>
       </c>
       <c r="F301" s="1">
         <v>46255</v>
@@ -9846,16 +9834,16 @@
         <v>0</v>
       </c>
       <c r="B302" t="s">
+        <v>629</v>
+      </c>
+      <c r="C302" t="s">
+        <v>80</v>
+      </c>
+      <c r="D302" t="s">
+        <v>630</v>
+      </c>
+      <c r="E302" t="s">
         <v>631</v>
-      </c>
-      <c r="C302" t="s">
-        <v>80</v>
-      </c>
-      <c r="D302" t="s">
-        <v>632</v>
-      </c>
-      <c r="E302" t="s">
-        <v>633</v>
       </c>
       <c r="F302" s="1">
         <v>46255</v>
@@ -9869,16 +9857,16 @@
         <v>0</v>
       </c>
       <c r="B303" t="s">
+        <v>632</v>
+      </c>
+      <c r="C303" t="s">
+        <v>80</v>
+      </c>
+      <c r="D303" t="s">
+        <v>633</v>
+      </c>
+      <c r="E303" t="s">
         <v>634</v>
-      </c>
-      <c r="C303" t="s">
-        <v>80</v>
-      </c>
-      <c r="D303" t="s">
-        <v>373</v>
-      </c>
-      <c r="E303" t="s">
-        <v>374</v>
       </c>
       <c r="F303" s="1">
         <v>46255</v>
@@ -9898,10 +9886,10 @@
         <v>80</v>
       </c>
       <c r="D304" t="s">
-        <v>48</v>
+        <v>373</v>
       </c>
       <c r="E304" t="s">
-        <v>49</v>
+        <v>374</v>
       </c>
       <c r="F304" s="1">
         <v>46255</v>
@@ -9921,10 +9909,10 @@
         <v>80</v>
       </c>
       <c r="D305" t="s">
-        <v>373</v>
+        <v>48</v>
       </c>
       <c r="E305" t="s">
-        <v>374</v>
+        <v>49</v>
       </c>
       <c r="F305" s="1">
         <v>46255</v>
@@ -9944,10 +9932,10 @@
         <v>80</v>
       </c>
       <c r="D306" t="s">
-        <v>638</v>
+        <v>373</v>
       </c>
       <c r="E306" t="s">
-        <v>639</v>
+        <v>374</v>
       </c>
       <c r="F306" s="1">
         <v>46255</v>
@@ -9961,16 +9949,16 @@
         <v>0</v>
       </c>
       <c r="B307" t="s">
+        <v>638</v>
+      </c>
+      <c r="C307" t="s">
+        <v>80</v>
+      </c>
+      <c r="D307" t="s">
+        <v>639</v>
+      </c>
+      <c r="E307" t="s">
         <v>640</v>
-      </c>
-      <c r="C307" t="s">
-        <v>80</v>
-      </c>
-      <c r="D307" t="s">
-        <v>638</v>
-      </c>
-      <c r="E307" t="s">
-        <v>639</v>
       </c>
       <c r="F307" s="1">
         <v>46255</v>
@@ -9990,10 +9978,10 @@
         <v>80</v>
       </c>
       <c r="D308" t="s">
-        <v>373</v>
+        <v>639</v>
       </c>
       <c r="E308" t="s">
-        <v>374</v>
+        <v>640</v>
       </c>
       <c r="F308" s="1">
         <v>46255</v>
@@ -10013,10 +10001,10 @@
         <v>80</v>
       </c>
       <c r="D309" t="s">
-        <v>643</v>
+        <v>373</v>
       </c>
       <c r="E309" t="s">
-        <v>644</v>
+        <v>374</v>
       </c>
       <c r="F309" s="1">
         <v>46255</v>
@@ -10030,16 +10018,16 @@
         <v>0</v>
       </c>
       <c r="B310" t="s">
+        <v>643</v>
+      </c>
+      <c r="C310" t="s">
+        <v>80</v>
+      </c>
+      <c r="D310" t="s">
+        <v>644</v>
+      </c>
+      <c r="E310" t="s">
         <v>645</v>
-      </c>
-      <c r="C310" t="s">
-        <v>80</v>
-      </c>
-      <c r="D310" t="s">
-        <v>646</v>
-      </c>
-      <c r="E310" t="s">
-        <v>647</v>
       </c>
       <c r="F310" s="1">
         <v>46255</v>
@@ -10053,16 +10041,16 @@
         <v>0</v>
       </c>
       <c r="B311" t="s">
+        <v>646</v>
+      </c>
+      <c r="C311" t="s">
+        <v>80</v>
+      </c>
+      <c r="D311" t="s">
+        <v>647</v>
+      </c>
+      <c r="E311" t="s">
         <v>648</v>
-      </c>
-      <c r="C311" t="s">
-        <v>80</v>
-      </c>
-      <c r="D311" t="s">
-        <v>101</v>
-      </c>
-      <c r="E311" t="s">
-        <v>102</v>
       </c>
       <c r="F311" s="1">
         <v>46255</v>
@@ -10082,10 +10070,10 @@
         <v>80</v>
       </c>
       <c r="D312" t="s">
-        <v>147</v>
+        <v>101</v>
       </c>
       <c r="E312" t="s">
-        <v>148</v>
+        <v>102</v>
       </c>
       <c r="F312" s="1">
         <v>46255</v>
@@ -10105,10 +10093,10 @@
         <v>80</v>
       </c>
       <c r="D313" t="s">
-        <v>355</v>
+        <v>147</v>
       </c>
       <c r="E313" t="s">
-        <v>356</v>
+        <v>148</v>
       </c>
       <c r="F313" s="1">
         <v>46255</v>
@@ -10128,10 +10116,10 @@
         <v>80</v>
       </c>
       <c r="D314" t="s">
-        <v>652</v>
+        <v>355</v>
       </c>
       <c r="E314" t="s">
-        <v>653</v>
+        <v>356</v>
       </c>
       <c r="F314" s="1">
         <v>46255</v>
@@ -10145,16 +10133,16 @@
         <v>0</v>
       </c>
       <c r="B315" t="s">
+        <v>652</v>
+      </c>
+      <c r="C315" t="s">
+        <v>80</v>
+      </c>
+      <c r="D315" t="s">
+        <v>653</v>
+      </c>
+      <c r="E315" t="s">
         <v>654</v>
-      </c>
-      <c r="C315" t="s">
-        <v>80</v>
-      </c>
-      <c r="D315" t="s">
-        <v>138</v>
-      </c>
-      <c r="E315" t="s">
-        <v>139</v>
       </c>
       <c r="F315" s="1">
         <v>46255</v>
@@ -10174,10 +10162,10 @@
         <v>80</v>
       </c>
       <c r="D316" t="s">
-        <v>652</v>
+        <v>138</v>
       </c>
       <c r="E316" t="s">
-        <v>653</v>
+        <v>139</v>
       </c>
       <c r="F316" s="1">
         <v>46255</v>
@@ -10197,10 +10185,10 @@
         <v>80</v>
       </c>
       <c r="D317" t="s">
-        <v>355</v>
+        <v>653</v>
       </c>
       <c r="E317" t="s">
-        <v>356</v>
+        <v>654</v>
       </c>
       <c r="F317" s="1">
         <v>46255</v>
@@ -10220,10 +10208,10 @@
         <v>80</v>
       </c>
       <c r="D318" t="s">
-        <v>658</v>
+        <v>355</v>
       </c>
       <c r="E318" t="s">
-        <v>659</v>
+        <v>356</v>
       </c>
       <c r="F318" s="1">
         <v>46255</v>
@@ -10237,16 +10225,16 @@
         <v>0</v>
       </c>
       <c r="B319" t="s">
+        <v>658</v>
+      </c>
+      <c r="C319" t="s">
+        <v>80</v>
+      </c>
+      <c r="D319" t="s">
+        <v>659</v>
+      </c>
+      <c r="E319" t="s">
         <v>660</v>
-      </c>
-      <c r="C319" t="s">
-        <v>80</v>
-      </c>
-      <c r="D319" t="s">
-        <v>661</v>
-      </c>
-      <c r="E319" t="s">
-        <v>662</v>
       </c>
       <c r="F319" s="1">
         <v>46255</v>
@@ -10260,16 +10248,16 @@
         <v>0</v>
       </c>
       <c r="B320" t="s">
+        <v>661</v>
+      </c>
+      <c r="C320" t="s">
+        <v>80</v>
+      </c>
+      <c r="D320" t="s">
+        <v>662</v>
+      </c>
+      <c r="E320" t="s">
         <v>663</v>
-      </c>
-      <c r="C320" t="s">
-        <v>80</v>
-      </c>
-      <c r="D320" t="s">
-        <v>181</v>
-      </c>
-      <c r="E320" t="s">
-        <v>182</v>
       </c>
       <c r="F320" s="1">
         <v>46255</v>
@@ -10289,10 +10277,10 @@
         <v>80</v>
       </c>
       <c r="D321" t="s">
-        <v>665</v>
+        <v>181</v>
       </c>
       <c r="E321" t="s">
-        <v>666</v>
+        <v>182</v>
       </c>
       <c r="F321" s="1">
         <v>46255</v>
@@ -10306,22 +10294,22 @@
         <v>0</v>
       </c>
       <c r="B322" t="s">
+        <v>665</v>
+      </c>
+      <c r="C322" t="s">
+        <v>80</v>
+      </c>
+      <c r="D322" t="s">
+        <v>666</v>
+      </c>
+      <c r="E322" t="s">
         <v>667</v>
       </c>
-      <c r="C322" t="s">
-        <v>80</v>
-      </c>
-      <c r="D322" t="s">
-        <v>668</v>
-      </c>
-      <c r="E322" t="s">
-        <v>669</v>
-      </c>
       <c r="F322" s="1">
         <v>46255</v>
       </c>
       <c r="G322" s="1">
-        <v>46255</v>
+        <v>46256</v>
       </c>
     </row>
     <row r="323" spans="1:7" x14ac:dyDescent="0.2">
@@ -10329,16 +10317,16 @@
         <v>0</v>
       </c>
       <c r="B323" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="C323" t="s">
         <v>80</v>
       </c>
       <c r="D323" t="s">
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="E323" t="s">
-        <v>672</v>
+        <v>667</v>
       </c>
       <c r="F323" s="1">
         <v>46255</v>
@@ -10352,16 +10340,16 @@
         <v>0</v>
       </c>
       <c r="B324" t="s">
-        <v>673</v>
+        <v>669</v>
       </c>
       <c r="C324" t="s">
         <v>80</v>
       </c>
       <c r="D324" t="s">
-        <v>674</v>
+        <v>670</v>
       </c>
       <c r="E324" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
       <c r="F324" s="1">
         <v>46255</v>
@@ -10375,16 +10363,16 @@
         <v>0</v>
       </c>
       <c r="B325" t="s">
-        <v>676</v>
+        <v>672</v>
       </c>
       <c r="C325" t="s">
         <v>80</v>
       </c>
       <c r="D325" t="s">
-        <v>337</v>
+        <v>673</v>
       </c>
       <c r="E325" t="s">
-        <v>338</v>
+        <v>674</v>
       </c>
       <c r="F325" s="1">
         <v>46255</v>
@@ -10398,16 +10386,16 @@
         <v>0</v>
       </c>
       <c r="B326" t="s">
+        <v>675</v>
+      </c>
+      <c r="C326" t="s">
+        <v>80</v>
+      </c>
+      <c r="D326" t="s">
+        <v>676</v>
+      </c>
+      <c r="E326" t="s">
         <v>677</v>
-      </c>
-      <c r="C326" t="s">
-        <v>80</v>
-      </c>
-      <c r="D326" t="s">
-        <v>678</v>
-      </c>
-      <c r="E326" t="s">
-        <v>679</v>
       </c>
       <c r="F326" s="1">
         <v>46255</v>
@@ -10421,16 +10409,16 @@
         <v>0</v>
       </c>
       <c r="B327" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="C327" t="s">
         <v>80</v>
       </c>
       <c r="D327" t="s">
-        <v>678</v>
+        <v>337</v>
       </c>
       <c r="E327" t="s">
-        <v>679</v>
+        <v>338</v>
       </c>
       <c r="F327" s="1">
         <v>46255</v>
@@ -10444,16 +10432,16 @@
         <v>0</v>
       </c>
       <c r="B328" t="s">
+        <v>679</v>
+      </c>
+      <c r="C328" t="s">
+        <v>80</v>
+      </c>
+      <c r="D328" t="s">
+        <v>680</v>
+      </c>
+      <c r="E328" t="s">
         <v>681</v>
-      </c>
-      <c r="C328" t="s">
-        <v>80</v>
-      </c>
-      <c r="D328" t="s">
-        <v>682</v>
-      </c>
-      <c r="E328" t="s">
-        <v>683</v>
       </c>
       <c r="F328" s="1">
         <v>46255</v>
@@ -10467,16 +10455,16 @@
         <v>0</v>
       </c>
       <c r="B329" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="C329" t="s">
         <v>80</v>
       </c>
       <c r="D329" t="s">
-        <v>685</v>
+        <v>680</v>
       </c>
       <c r="E329" t="s">
-        <v>686</v>
+        <v>681</v>
       </c>
       <c r="F329" s="1">
         <v>46255</v>
@@ -10490,16 +10478,16 @@
         <v>0</v>
       </c>
       <c r="B330" t="s">
-        <v>687</v>
+        <v>683</v>
       </c>
       <c r="C330" t="s">
         <v>80</v>
       </c>
       <c r="D330" t="s">
-        <v>688</v>
+        <v>684</v>
       </c>
       <c r="E330" t="s">
-        <v>689</v>
+        <v>685</v>
       </c>
       <c r="F330" s="1">
         <v>46255</v>
@@ -10513,16 +10501,16 @@
         <v>0</v>
       </c>
       <c r="B331" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="C331" t="s">
         <v>80</v>
       </c>
       <c r="D331" t="s">
-        <v>138</v>
+        <v>687</v>
       </c>
       <c r="E331" t="s">
-        <v>139</v>
+        <v>688</v>
       </c>
       <c r="F331" s="1">
         <v>46255</v>
@@ -10536,16 +10524,16 @@
         <v>0</v>
       </c>
       <c r="B332" t="s">
+        <v>689</v>
+      </c>
+      <c r="C332" t="s">
+        <v>80</v>
+      </c>
+      <c r="D332" t="s">
+        <v>690</v>
+      </c>
+      <c r="E332" t="s">
         <v>691</v>
-      </c>
-      <c r="C332" t="s">
-        <v>80</v>
-      </c>
-      <c r="D332" t="s">
-        <v>98</v>
-      </c>
-      <c r="E332" t="s">
-        <v>99</v>
       </c>
       <c r="F332" s="1">
         <v>46255</v>
@@ -10565,10 +10553,10 @@
         <v>80</v>
       </c>
       <c r="D333" t="s">
-        <v>593</v>
+        <v>138</v>
       </c>
       <c r="E333" t="s">
-        <v>594</v>
+        <v>139</v>
       </c>
       <c r="F333" s="1">
         <v>46255</v>
@@ -10588,10 +10576,10 @@
         <v>80</v>
       </c>
       <c r="D334" t="s">
-        <v>25</v>
+        <v>98</v>
       </c>
       <c r="E334" t="s">
-        <v>26</v>
+        <v>99</v>
       </c>
       <c r="F334" s="1">
         <v>46255</v>
@@ -10611,10 +10599,10 @@
         <v>80</v>
       </c>
       <c r="D335" t="s">
-        <v>37</v>
+        <v>594</v>
       </c>
       <c r="E335" t="s">
-        <v>38</v>
+        <v>595</v>
       </c>
       <c r="F335" s="1">
         <v>46255</v>
@@ -10634,10 +10622,10 @@
         <v>80</v>
       </c>
       <c r="D336" t="s">
-        <v>351</v>
+        <v>25</v>
       </c>
       <c r="E336" t="s">
-        <v>352</v>
+        <v>26</v>
       </c>
       <c r="F336" s="1">
         <v>46255</v>
@@ -10657,10 +10645,10 @@
         <v>80</v>
       </c>
       <c r="D337" t="s">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="E337" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F337" s="1">
         <v>46255</v>
@@ -10680,10 +10668,10 @@
         <v>80</v>
       </c>
       <c r="D338" t="s">
-        <v>698</v>
+        <v>351</v>
       </c>
       <c r="E338" t="s">
-        <v>699</v>
+        <v>352</v>
       </c>
       <c r="F338" s="1">
         <v>46255</v>
@@ -10697,16 +10685,16 @@
         <v>0</v>
       </c>
       <c r="B339" t="s">
+        <v>698</v>
+      </c>
+      <c r="C339" t="s">
+        <v>80</v>
+      </c>
+      <c r="D339" t="s">
+        <v>699</v>
+      </c>
+      <c r="E339" t="s">
         <v>700</v>
-      </c>
-      <c r="C339" t="s">
-        <v>80</v>
-      </c>
-      <c r="D339" t="s">
-        <v>701</v>
-      </c>
-      <c r="E339" t="s">
-        <v>702</v>
       </c>
       <c r="F339" s="1">
         <v>46255</v>
@@ -10720,16 +10708,16 @@
         <v>0</v>
       </c>
       <c r="B340" t="s">
+        <v>701</v>
+      </c>
+      <c r="C340" t="s">
+        <v>80</v>
+      </c>
+      <c r="D340" t="s">
+        <v>702</v>
+      </c>
+      <c r="E340" t="s">
         <v>703</v>
-      </c>
-      <c r="C340" t="s">
-        <v>80</v>
-      </c>
-      <c r="D340" t="s">
-        <v>400</v>
-      </c>
-      <c r="E340" t="s">
-        <v>401</v>
       </c>
       <c r="F340" s="1">
         <v>46255</v>
@@ -10749,10 +10737,10 @@
         <v>80</v>
       </c>
       <c r="D341" t="s">
-        <v>705</v>
+        <v>400</v>
       </c>
       <c r="E341" t="s">
-        <v>706</v>
+        <v>401</v>
       </c>
       <c r="F341" s="1">
         <v>46255</v>
@@ -10766,16 +10754,16 @@
         <v>0</v>
       </c>
       <c r="B342" t="s">
+        <v>705</v>
+      </c>
+      <c r="C342" t="s">
+        <v>80</v>
+      </c>
+      <c r="D342" t="s">
+        <v>706</v>
+      </c>
+      <c r="E342" t="s">
         <v>707</v>
-      </c>
-      <c r="C342" t="s">
-        <v>80</v>
-      </c>
-      <c r="D342" t="s">
-        <v>526</v>
-      </c>
-      <c r="E342" t="s">
-        <v>527</v>
       </c>
       <c r="F342" s="1">
         <v>46255</v>
@@ -10795,10 +10783,10 @@
         <v>80</v>
       </c>
       <c r="D343" t="s">
-        <v>709</v>
+        <v>526</v>
       </c>
       <c r="E343" t="s">
-        <v>710</v>
+        <v>527</v>
       </c>
       <c r="F343" s="1">
         <v>46255</v>
@@ -10812,16 +10800,16 @@
         <v>0</v>
       </c>
       <c r="B344" t="s">
+        <v>709</v>
+      </c>
+      <c r="C344" t="s">
+        <v>80</v>
+      </c>
+      <c r="D344" t="s">
+        <v>710</v>
+      </c>
+      <c r="E344" t="s">
         <v>711</v>
-      </c>
-      <c r="C344" t="s">
-        <v>80</v>
-      </c>
-      <c r="D344" t="s">
-        <v>403</v>
-      </c>
-      <c r="E344" t="s">
-        <v>404</v>
       </c>
       <c r="F344" s="1">
         <v>46255</v>
@@ -10841,10 +10829,10 @@
         <v>80</v>
       </c>
       <c r="D345" t="s">
-        <v>713</v>
+        <v>403</v>
       </c>
       <c r="E345" t="s">
-        <v>714</v>
+        <v>404</v>
       </c>
       <c r="F345" s="1">
         <v>46255</v>
@@ -10858,16 +10846,16 @@
         <v>0</v>
       </c>
       <c r="B346" t="s">
+        <v>713</v>
+      </c>
+      <c r="C346" t="s">
+        <v>80</v>
+      </c>
+      <c r="D346" t="s">
+        <v>714</v>
+      </c>
+      <c r="E346" t="s">
         <v>715</v>
-      </c>
-      <c r="C346" t="s">
-        <v>80</v>
-      </c>
-      <c r="D346" t="s">
-        <v>16</v>
-      </c>
-      <c r="E346" t="s">
-        <v>17</v>
       </c>
       <c r="F346" s="1">
         <v>46255</v>
@@ -10878,53 +10866,53 @@
     </row>
     <row r="347" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A347" t="s">
+        <v>0</v>
+      </c>
+      <c r="B347" t="s">
         <v>716</v>
       </c>
-      <c r="B347" t="s">
-        <v>717</v>
-      </c>
       <c r="C347" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D347" t="s">
-        <v>348</v>
+        <v>16</v>
       </c>
       <c r="E347" t="s">
-        <v>349</v>
+        <v>17</v>
       </c>
       <c r="F347" s="1">
-        <v>46148</v>
+        <v>46255</v>
       </c>
       <c r="G347" s="1">
-        <v>46149</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="348" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A348" t="s">
+        <v>717</v>
+      </c>
+      <c r="B348" t="s">
         <v>718</v>
       </c>
-      <c r="B348" t="s">
-        <v>719</v>
-      </c>
       <c r="C348" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D348" t="s">
-        <v>41</v>
+        <v>348</v>
       </c>
       <c r="E348" t="s">
-        <v>42</v>
+        <v>349</v>
       </c>
       <c r="F348" s="1">
-        <v>46133</v>
+        <v>46148</v>
       </c>
       <c r="G348" s="1">
-        <v>46134</v>
+        <v>46149</v>
       </c>
     </row>
     <row r="349" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A349" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="B349" t="s">
         <v>720</v>
@@ -10939,7 +10927,7 @@
         <v>42</v>
       </c>
       <c r="F349" s="1">
-        <v>46134</v>
+        <v>46133</v>
       </c>
       <c r="G349" s="1">
         <v>46134</v>
@@ -10947,7 +10935,7 @@
     </row>
     <row r="350" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A350" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="B350" t="s">
         <v>721</v>
@@ -10956,159 +10944,159 @@
         <v>6</v>
       </c>
       <c r="D350" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="E350" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="F350" s="1">
-        <v>46156</v>
+        <v>46134</v>
       </c>
       <c r="G350" s="1">
-        <v>46156</v>
+        <v>46134</v>
       </c>
     </row>
     <row r="351" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A351" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="B351" t="s">
         <v>722</v>
       </c>
       <c r="C351" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D351" t="s">
-        <v>723</v>
+        <v>19</v>
       </c>
       <c r="E351" t="s">
-        <v>724</v>
+        <v>20</v>
       </c>
       <c r="F351" s="1">
-        <v>46195</v>
+        <v>46156</v>
       </c>
       <c r="G351" s="1">
-        <v>46195</v>
+        <v>46156</v>
       </c>
     </row>
     <row r="352" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A352" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="B352" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="C352" t="s">
         <v>2</v>
       </c>
       <c r="D352" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="E352" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="F352" s="1">
-        <v>46206</v>
+        <v>46195</v>
       </c>
       <c r="G352" s="1">
-        <v>46252</v>
+        <v>46195</v>
       </c>
     </row>
     <row r="353" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A353" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="B353" t="s">
+        <v>726</v>
+      </c>
+      <c r="C353" t="s">
+        <v>2</v>
+      </c>
+      <c r="D353" t="s">
+        <v>727</v>
+      </c>
+      <c r="E353" t="s">
         <v>728</v>
       </c>
-      <c r="C353" t="s">
-        <v>96</v>
-      </c>
-      <c r="D353" t="s">
-        <v>729</v>
-      </c>
-      <c r="E353" t="s">
-        <v>730</v>
-      </c>
       <c r="F353" s="1">
-        <v>46209</v>
+        <v>46206</v>
       </c>
       <c r="G353" s="1">
-        <v>46218</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="354" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A354" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="B354" t="s">
+        <v>729</v>
+      </c>
+      <c r="C354" t="s">
+        <v>96</v>
+      </c>
+      <c r="D354" t="s">
+        <v>730</v>
+      </c>
+      <c r="E354" t="s">
         <v>731</v>
       </c>
-      <c r="C354" t="s">
-        <v>6</v>
-      </c>
-      <c r="D354" t="s">
-        <v>732</v>
-      </c>
-      <c r="E354" t="s">
-        <v>733</v>
-      </c>
       <c r="F354" s="1">
-        <v>46213</v>
+        <v>46209</v>
       </c>
       <c r="G354" s="1">
-        <v>46213</v>
+        <v>46218</v>
       </c>
     </row>
     <row r="355" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A355" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="B355" t="s">
+        <v>732</v>
+      </c>
+      <c r="C355" t="s">
+        <v>6</v>
+      </c>
+      <c r="D355" t="s">
+        <v>733</v>
+      </c>
+      <c r="E355" t="s">
         <v>734</v>
-      </c>
-      <c r="C355" t="s">
-        <v>96</v>
-      </c>
-      <c r="D355" t="s">
-        <v>735</v>
-      </c>
-      <c r="E355" t="s">
-        <v>736</v>
       </c>
       <c r="F355" s="1">
         <v>46213</v>
       </c>
       <c r="G355" s="1">
-        <v>46216</v>
+        <v>46213</v>
       </c>
     </row>
     <row r="356" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A356" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="B356" t="s">
+        <v>735</v>
+      </c>
+      <c r="C356" t="s">
+        <v>96</v>
+      </c>
+      <c r="D356" t="s">
+        <v>736</v>
+      </c>
+      <c r="E356" t="s">
         <v>737</v>
       </c>
-      <c r="C356" t="s">
-        <v>2</v>
-      </c>
-      <c r="D356" t="s">
-        <v>133</v>
-      </c>
-      <c r="E356" t="s">
-        <v>134</v>
-      </c>
       <c r="F356" s="1">
-        <v>46220</v>
+        <v>46213</v>
       </c>
       <c r="G356" s="1">
-        <v>46231</v>
+        <v>46216</v>
       </c>
     </row>
     <row r="357" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A357" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="B357" t="s">
         <v>738</v>
@@ -11117,67 +11105,67 @@
         <v>2</v>
       </c>
       <c r="D357" t="s">
-        <v>723</v>
+        <v>133</v>
       </c>
       <c r="E357" t="s">
-        <v>724</v>
+        <v>134</v>
       </c>
       <c r="F357" s="1">
-        <v>46223</v>
+        <v>46220</v>
       </c>
       <c r="G357" s="1">
-        <v>46223</v>
+        <v>46231</v>
       </c>
     </row>
     <row r="358" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A358" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="B358" t="s">
         <v>739</v>
       </c>
       <c r="C358" t="s">
-        <v>96</v>
+        <v>2</v>
       </c>
       <c r="D358" t="s">
-        <v>735</v>
+        <v>724</v>
       </c>
       <c r="E358" t="s">
-        <v>736</v>
+        <v>725</v>
       </c>
       <c r="F358" s="1">
-        <v>46224</v>
+        <v>46223</v>
       </c>
       <c r="G358" s="1">
-        <v>46224</v>
+        <v>46223</v>
       </c>
     </row>
     <row r="359" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A359" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="B359" t="s">
         <v>740</v>
       </c>
       <c r="C359" t="s">
-        <v>2</v>
+        <v>96</v>
       </c>
       <c r="D359" t="s">
-        <v>723</v>
+        <v>736</v>
       </c>
       <c r="E359" t="s">
-        <v>724</v>
+        <v>737</v>
       </c>
       <c r="F359" s="1">
-        <v>46230</v>
+        <v>46224</v>
       </c>
       <c r="G359" s="1">
-        <v>46231</v>
+        <v>46224</v>
       </c>
     </row>
     <row r="360" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A360" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="B360" t="s">
         <v>741</v>
@@ -11186,21 +11174,21 @@
         <v>2</v>
       </c>
       <c r="D360" t="s">
-        <v>133</v>
+        <v>724</v>
       </c>
       <c r="E360" t="s">
-        <v>134</v>
+        <v>725</v>
       </c>
       <c r="F360" s="1">
-        <v>46232</v>
+        <v>46230</v>
       </c>
       <c r="G360" s="1">
-        <v>46233</v>
+        <v>46231</v>
       </c>
     </row>
     <row r="361" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A361" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="B361" t="s">
         <v>742</v>
@@ -11223,7 +11211,7 @@
     </row>
     <row r="362" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A362" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="B362" t="s">
         <v>743</v>
@@ -11232,21 +11220,21 @@
         <v>2</v>
       </c>
       <c r="D362" t="s">
-        <v>735</v>
+        <v>133</v>
       </c>
       <c r="E362" t="s">
-        <v>736</v>
+        <v>134</v>
       </c>
       <c r="F362" s="1">
-        <v>46238</v>
+        <v>46232</v>
       </c>
       <c r="G362" s="1">
-        <v>46239</v>
+        <v>46233</v>
       </c>
     </row>
     <row r="363" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A363" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="B363" t="s">
         <v>744</v>
@@ -11255,82 +11243,82 @@
         <v>2</v>
       </c>
       <c r="D363" t="s">
-        <v>41</v>
+        <v>736</v>
       </c>
       <c r="E363" t="s">
-        <v>42</v>
+        <v>737</v>
       </c>
       <c r="F363" s="1">
-        <v>46247</v>
+        <v>46238</v>
       </c>
       <c r="G363" s="1">
-        <v>46252</v>
+        <v>46239</v>
       </c>
     </row>
     <row r="364" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A364" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="B364" t="s">
         <v>745</v>
       </c>
       <c r="C364" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D364" t="s">
-        <v>746</v>
+        <v>41</v>
       </c>
       <c r="E364" t="s">
-        <v>747</v>
+        <v>42</v>
       </c>
       <c r="F364" s="1">
-        <v>46253</v>
+        <v>46247</v>
       </c>
       <c r="G364" s="1">
-        <v>46253</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="365" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A365" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="B365" t="s">
+        <v>746</v>
+      </c>
+      <c r="C365" t="s">
+        <v>6</v>
+      </c>
+      <c r="D365" t="s">
+        <v>747</v>
+      </c>
+      <c r="E365" t="s">
         <v>748</v>
-      </c>
-      <c r="C365" t="s">
-        <v>2</v>
-      </c>
-      <c r="D365" t="s">
-        <v>735</v>
-      </c>
-      <c r="E365" t="s">
-        <v>736</v>
       </c>
       <c r="F365" s="1">
         <v>46253</v>
       </c>
       <c r="G365" s="1">
-        <v>46254</v>
+        <v>46253</v>
       </c>
     </row>
     <row r="366" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A366" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="B366" t="s">
         <v>749</v>
       </c>
       <c r="C366" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D366" t="s">
-        <v>472</v>
+        <v>736</v>
       </c>
       <c r="E366" t="s">
-        <v>473</v>
+        <v>737</v>
       </c>
       <c r="F366" s="1">
-        <v>46254</v>
+        <v>46253</v>
       </c>
       <c r="G366" s="1">
         <v>46254</v>
@@ -11338,7 +11326,7 @@
     </row>
     <row r="367" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A367" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="B367" t="s">
         <v>750</v>
@@ -11347,21 +11335,21 @@
         <v>80</v>
       </c>
       <c r="D367" t="s">
-        <v>735</v>
+        <v>472</v>
       </c>
       <c r="E367" t="s">
-        <v>736</v>
+        <v>473</v>
       </c>
       <c r="F367" s="1">
         <v>46254</v>
       </c>
       <c r="G367" s="1">
-        <v>46255</v>
+        <v>46254</v>
       </c>
     </row>
     <row r="368" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A368" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="B368" t="s">
         <v>751</v>
@@ -11370,10 +11358,10 @@
         <v>80</v>
       </c>
       <c r="D368" t="s">
-        <v>138</v>
+        <v>736</v>
       </c>
       <c r="E368" t="s">
-        <v>139</v>
+        <v>737</v>
       </c>
       <c r="F368" s="1">
         <v>46254</v>
@@ -11384,7 +11372,7 @@
     </row>
     <row r="369" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A369" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="B369" t="s">
         <v>752</v>
@@ -11407,7 +11395,7 @@
     </row>
     <row r="370" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A370" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="B370" t="s">
         <v>753</v>
@@ -11416,10 +11404,10 @@
         <v>80</v>
       </c>
       <c r="D370" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="E370" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="F370" s="1">
         <v>46254</v>
@@ -11430,7 +11418,7 @@
     </row>
     <row r="371" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A371" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="B371" t="s">
         <v>754</v>
@@ -11439,10 +11427,10 @@
         <v>80</v>
       </c>
       <c r="D371" t="s">
-        <v>141</v>
+        <v>156</v>
       </c>
       <c r="E371" t="s">
-        <v>142</v>
+        <v>157</v>
       </c>
       <c r="F371" s="1">
         <v>46254</v>
@@ -11453,7 +11441,7 @@
     </row>
     <row r="372" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A372" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="B372" t="s">
         <v>755</v>
@@ -11476,7 +11464,7 @@
     </row>
     <row r="373" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A373" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="B373" t="s">
         <v>756</v>
@@ -11499,7 +11487,7 @@
     </row>
     <row r="374" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A374" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="B374" t="s">
         <v>757</v>
@@ -11508,10 +11496,10 @@
         <v>80</v>
       </c>
       <c r="D374" t="s">
-        <v>156</v>
+        <v>571</v>
       </c>
       <c r="E374" t="s">
-        <v>157</v>
+        <v>572</v>
       </c>
       <c r="F374" s="1">
         <v>46254</v>
@@ -11522,7 +11510,7 @@
     </row>
     <row r="375" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A375" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="B375" t="s">
         <v>758</v>
@@ -11545,7 +11533,7 @@
     </row>
     <row r="376" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A376" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="B376" t="s">
         <v>759</v>
@@ -11554,13 +11542,13 @@
         <v>80</v>
       </c>
       <c r="D376" t="s">
-        <v>571</v>
+        <v>373</v>
       </c>
       <c r="E376" t="s">
-        <v>572</v>
+        <v>374</v>
       </c>
       <c r="F376" s="1">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="G376" s="1">
         <v>46255</v>
@@ -11568,7 +11556,7 @@
     </row>
     <row r="377" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A377" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="B377" t="s">
         <v>760</v>
@@ -11591,7 +11579,7 @@
     </row>
     <row r="378" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A378" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="B378" t="s">
         <v>761</v>
@@ -11600,10 +11588,10 @@
         <v>80</v>
       </c>
       <c r="D378" t="s">
-        <v>373</v>
+        <v>762</v>
       </c>
       <c r="E378" t="s">
-        <v>374</v>
+        <v>763</v>
       </c>
       <c r="F378" s="1">
         <v>46255</v>
@@ -11614,82 +11602,82 @@
     </row>
     <row r="379" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A379" t="s">
-        <v>718</v>
+        <v>764</v>
       </c>
       <c r="B379" t="s">
-        <v>762</v>
+        <v>765</v>
       </c>
       <c r="C379" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="D379" t="s">
-        <v>763</v>
+        <v>766</v>
       </c>
       <c r="E379" t="s">
-        <v>764</v>
+        <v>767</v>
       </c>
       <c r="F379" s="1">
-        <v>46255</v>
+        <v>46063</v>
       </c>
       <c r="G379" s="1">
-        <v>46255</v>
+        <v>46064</v>
       </c>
     </row>
     <row r="380" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A380" t="s">
-        <v>718</v>
+        <v>764</v>
       </c>
       <c r="B380" t="s">
-        <v>765</v>
+        <v>768</v>
       </c>
       <c r="C380" t="s">
-        <v>80</v>
+        <v>6</v>
       </c>
       <c r="D380" t="s">
-        <v>698</v>
+        <v>57</v>
       </c>
       <c r="E380" t="s">
-        <v>699</v>
+        <v>58</v>
       </c>
       <c r="F380" s="1">
-        <v>46255</v>
+        <v>46113</v>
       </c>
       <c r="G380" s="1">
-        <v>46255</v>
+        <v>46125</v>
       </c>
     </row>
     <row r="381" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A381" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="B381" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="C381" t="s">
-        <v>96</v>
+        <v>2</v>
       </c>
       <c r="D381" t="s">
-        <v>768</v>
+        <v>57</v>
       </c>
       <c r="E381" t="s">
-        <v>769</v>
+        <v>58</v>
       </c>
       <c r="F381" s="1">
-        <v>46063</v>
+        <v>46125</v>
       </c>
       <c r="G381" s="1">
-        <v>46064</v>
+        <v>46125</v>
       </c>
     </row>
     <row r="382" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A382" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="B382" t="s">
         <v>770</v>
       </c>
       <c r="C382" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D382" t="s">
         <v>57</v>
@@ -11698,15 +11686,15 @@
         <v>58</v>
       </c>
       <c r="F382" s="1">
-        <v>46113</v>
+        <v>46126</v>
       </c>
       <c r="G382" s="1">
-        <v>46125</v>
+        <v>46126</v>
       </c>
     </row>
     <row r="383" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A383" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="B383" t="s">
         <v>771</v>
@@ -11721,15 +11709,15 @@
         <v>58</v>
       </c>
       <c r="F383" s="1">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="G383" s="1">
-        <v>46125</v>
+        <v>46126</v>
       </c>
     </row>
     <row r="384" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A384" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="B384" t="s">
         <v>772</v>
@@ -11744,21 +11732,21 @@
         <v>58</v>
       </c>
       <c r="F384" s="1">
-        <v>46126</v>
+        <v>46128</v>
       </c>
       <c r="G384" s="1">
-        <v>46126</v>
+        <v>46128</v>
       </c>
     </row>
     <row r="385" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A385" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="B385" t="s">
         <v>773</v>
       </c>
       <c r="C385" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D385" t="s">
         <v>57</v>
@@ -11767,15 +11755,15 @@
         <v>58</v>
       </c>
       <c r="F385" s="1">
-        <v>46126</v>
+        <v>46132</v>
       </c>
       <c r="G385" s="1">
-        <v>46126</v>
+        <v>46132</v>
       </c>
     </row>
     <row r="386" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A386" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="B386" t="s">
         <v>774</v>
@@ -11790,21 +11778,21 @@
         <v>58</v>
       </c>
       <c r="F386" s="1">
-        <v>46128</v>
+        <v>46161</v>
       </c>
       <c r="G386" s="1">
-        <v>46128</v>
+        <v>46161</v>
       </c>
     </row>
     <row r="387" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A387" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="B387" t="s">
         <v>775</v>
       </c>
       <c r="C387" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D387" t="s">
         <v>57</v>
@@ -11813,15 +11801,15 @@
         <v>58</v>
       </c>
       <c r="F387" s="1">
-        <v>46132</v>
+        <v>46174</v>
       </c>
       <c r="G387" s="1">
-        <v>46132</v>
+        <v>46174</v>
       </c>
     </row>
     <row r="388" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A388" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="B388" t="s">
         <v>776</v>
@@ -11836,21 +11824,21 @@
         <v>58</v>
       </c>
       <c r="F388" s="1">
-        <v>46161</v>
+        <v>46174</v>
       </c>
       <c r="G388" s="1">
-        <v>46161</v>
+        <v>46174</v>
       </c>
     </row>
     <row r="389" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A389" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="B389" t="s">
         <v>777</v>
       </c>
       <c r="C389" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D389" t="s">
         <v>57</v>
@@ -11859,21 +11847,21 @@
         <v>58</v>
       </c>
       <c r="F389" s="1">
-        <v>46174</v>
+        <v>46195</v>
       </c>
       <c r="G389" s="1">
-        <v>46174</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="390" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A390" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="B390" t="s">
         <v>778</v>
       </c>
       <c r="C390" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D390" t="s">
         <v>57</v>
@@ -11882,21 +11870,21 @@
         <v>58</v>
       </c>
       <c r="F390" s="1">
-        <v>46174</v>
+        <v>46210</v>
       </c>
       <c r="G390" s="1">
-        <v>46174</v>
+        <v>46210</v>
       </c>
     </row>
     <row r="391" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A391" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="B391" t="s">
         <v>779</v>
       </c>
       <c r="C391" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D391" t="s">
         <v>57</v>
@@ -11905,21 +11893,21 @@
         <v>58</v>
       </c>
       <c r="F391" s="1">
-        <v>46195</v>
+        <v>46213</v>
       </c>
       <c r="G391" s="1">
-        <v>46252</v>
+        <v>46213</v>
       </c>
     </row>
     <row r="392" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A392" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="B392" t="s">
         <v>780</v>
       </c>
       <c r="C392" t="s">
-        <v>6</v>
+        <v>80</v>
       </c>
       <c r="D392" t="s">
         <v>57</v>
@@ -11928,38 +11916,38 @@
         <v>58</v>
       </c>
       <c r="F392" s="1">
-        <v>46210</v>
+        <v>46218</v>
       </c>
       <c r="G392" s="1">
-        <v>46210</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="393" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A393" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="B393" t="s">
         <v>781</v>
       </c>
       <c r="C393" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D393" t="s">
-        <v>57</v>
+        <v>77</v>
       </c>
       <c r="E393" t="s">
-        <v>58</v>
+        <v>78</v>
       </c>
       <c r="F393" s="1">
-        <v>46213</v>
+        <v>46226</v>
       </c>
       <c r="G393" s="1">
-        <v>46213</v>
+        <v>46226</v>
       </c>
     </row>
     <row r="394" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A394" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="B394" t="s">
         <v>782</v>
@@ -11974,7 +11962,7 @@
         <v>58</v>
       </c>
       <c r="F394" s="1">
-        <v>46218</v>
+        <v>46227</v>
       </c>
       <c r="G394" s="1">
         <v>46252</v>
@@ -11982,36 +11970,36 @@
     </row>
     <row r="395" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A395" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="B395" t="s">
         <v>783</v>
       </c>
       <c r="C395" t="s">
-        <v>6</v>
+        <v>80</v>
       </c>
       <c r="D395" t="s">
-        <v>77</v>
+        <v>57</v>
       </c>
       <c r="E395" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="F395" s="1">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="G395" s="1">
-        <v>46226</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="396" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A396" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="B396" t="s">
         <v>784</v>
       </c>
       <c r="C396" t="s">
-        <v>80</v>
+        <v>6</v>
       </c>
       <c r="D396" t="s">
         <v>57</v>
@@ -12023,12 +12011,12 @@
         <v>46227</v>
       </c>
       <c r="G396" s="1">
-        <v>46252</v>
+        <v>46228</v>
       </c>
     </row>
     <row r="397" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A397" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="B397" t="s">
         <v>785</v>
@@ -12037,13 +12025,13 @@
         <v>80</v>
       </c>
       <c r="D397" t="s">
-        <v>57</v>
+        <v>77</v>
       </c>
       <c r="E397" t="s">
-        <v>58</v>
+        <v>78</v>
       </c>
       <c r="F397" s="1">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="G397" s="1">
         <v>46252</v>
@@ -12051,7 +12039,7 @@
     </row>
     <row r="398" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A398" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="B398" t="s">
         <v>786</v>
@@ -12066,44 +12054,44 @@
         <v>58</v>
       </c>
       <c r="F398" s="1">
-        <v>46227</v>
+        <v>46231</v>
       </c>
       <c r="G398" s="1">
-        <v>46228</v>
+        <v>46231</v>
       </c>
     </row>
     <row r="399" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A399" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="B399" t="s">
         <v>787</v>
       </c>
       <c r="C399" t="s">
-        <v>80</v>
+        <v>6</v>
       </c>
       <c r="D399" t="s">
-        <v>77</v>
+        <v>57</v>
       </c>
       <c r="E399" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="F399" s="1">
-        <v>46230</v>
+        <v>46254</v>
       </c>
       <c r="G399" s="1">
-        <v>46252</v>
+        <v>46254</v>
       </c>
     </row>
     <row r="400" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A400" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="B400" t="s">
         <v>788</v>
       </c>
       <c r="C400" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D400" t="s">
         <v>57</v>
@@ -12112,110 +12100,110 @@
         <v>58</v>
       </c>
       <c r="F400" s="1">
-        <v>46231</v>
+        <v>46255</v>
       </c>
       <c r="G400" s="1">
-        <v>46231</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="401" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A401" t="s">
-        <v>766</v>
+        <v>789</v>
       </c>
       <c r="B401" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="C401" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D401" t="s">
-        <v>57</v>
+        <v>791</v>
       </c>
       <c r="E401" t="s">
-        <v>58</v>
+        <v>792</v>
       </c>
       <c r="F401" s="1">
-        <v>46254</v>
+        <v>46083</v>
       </c>
       <c r="G401" s="1">
-        <v>46254</v>
+        <v>46084</v>
       </c>
     </row>
     <row r="402" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A402" t="s">
-        <v>766</v>
+        <v>789</v>
       </c>
       <c r="B402" t="s">
-        <v>790</v>
+        <v>793</v>
       </c>
       <c r="C402" t="s">
         <v>2</v>
       </c>
       <c r="D402" t="s">
-        <v>57</v>
+        <v>791</v>
       </c>
       <c r="E402" t="s">
-        <v>58</v>
+        <v>792</v>
       </c>
       <c r="F402" s="1">
-        <v>46255</v>
+        <v>46132</v>
       </c>
       <c r="G402" s="1">
-        <v>46255</v>
+        <v>46133</v>
       </c>
     </row>
     <row r="403" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A403" t="s">
-        <v>766</v>
+        <v>789</v>
       </c>
       <c r="B403" t="s">
-        <v>791</v>
+        <v>794</v>
       </c>
       <c r="C403" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D403" t="s">
-        <v>57</v>
+        <v>795</v>
       </c>
       <c r="E403" t="s">
-        <v>58</v>
+        <v>796</v>
       </c>
       <c r="F403" s="1">
-        <v>46255</v>
+        <v>46157</v>
       </c>
       <c r="G403" s="1">
-        <v>46255</v>
+        <v>46157</v>
       </c>
     </row>
     <row r="404" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A404" t="s">
-        <v>766</v>
+        <v>789</v>
       </c>
       <c r="B404" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="C404" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D404" t="s">
-        <v>57</v>
+        <v>798</v>
       </c>
       <c r="E404" t="s">
-        <v>58</v>
+        <v>799</v>
       </c>
       <c r="F404" s="1">
-        <v>46255</v>
+        <v>46168</v>
       </c>
       <c r="G404" s="1">
-        <v>46255</v>
+        <v>46170</v>
       </c>
     </row>
     <row r="405" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A405" t="s">
-        <v>793</v>
+        <v>789</v>
       </c>
       <c r="B405" t="s">
-        <v>794</v>
+        <v>800</v>
       </c>
       <c r="C405" t="s">
         <v>2</v>
@@ -12227,18 +12215,18 @@
         <v>796</v>
       </c>
       <c r="F405" s="1">
-        <v>46083</v>
+        <v>46244</v>
       </c>
       <c r="G405" s="1">
-        <v>46084</v>
+        <v>46244</v>
       </c>
     </row>
     <row r="406" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A406" t="s">
-        <v>793</v>
+        <v>789</v>
       </c>
       <c r="B406" t="s">
-        <v>797</v>
+        <v>801</v>
       </c>
       <c r="C406" t="s">
         <v>2</v>
@@ -12250,147 +12238,55 @@
         <v>796</v>
       </c>
       <c r="F406" s="1">
-        <v>46132</v>
+        <v>46247</v>
       </c>
       <c r="G406" s="1">
-        <v>46133</v>
+        <v>46247</v>
       </c>
     </row>
     <row r="407" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A407" t="s">
-        <v>793</v>
+        <v>789</v>
       </c>
       <c r="B407" t="s">
-        <v>798</v>
+        <v>802</v>
       </c>
       <c r="C407" t="s">
         <v>2</v>
       </c>
       <c r="D407" t="s">
-        <v>799</v>
+        <v>791</v>
       </c>
       <c r="E407" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="F407" s="1">
-        <v>46157</v>
+        <v>46247</v>
       </c>
       <c r="G407" s="1">
-        <v>46157</v>
+        <v>46247</v>
       </c>
     </row>
     <row r="408" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A408" t="s">
-        <v>793</v>
+        <v>789</v>
       </c>
       <c r="B408" t="s">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="C408" t="s">
         <v>2</v>
       </c>
       <c r="D408" t="s">
-        <v>802</v>
+        <v>795</v>
       </c>
       <c r="E408" t="s">
-        <v>803</v>
+        <v>796</v>
       </c>
       <c r="F408" s="1">
-        <v>46168</v>
+        <v>46255</v>
       </c>
       <c r="G408" s="1">
-        <v>46170</v>
-      </c>
-    </row>
-    <row r="409" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A409" t="s">
-        <v>793</v>
-      </c>
-      <c r="B409" t="s">
-        <v>804</v>
-      </c>
-      <c r="C409" t="s">
-        <v>2</v>
-      </c>
-      <c r="D409" t="s">
-        <v>799</v>
-      </c>
-      <c r="E409" t="s">
-        <v>800</v>
-      </c>
-      <c r="F409" s="1">
-        <v>46244</v>
-      </c>
-      <c r="G409" s="1">
-        <v>46244</v>
-      </c>
-    </row>
-    <row r="410" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A410" t="s">
-        <v>793</v>
-      </c>
-      <c r="B410" t="s">
-        <v>805</v>
-      </c>
-      <c r="C410" t="s">
-        <v>2</v>
-      </c>
-      <c r="D410" t="s">
-        <v>799</v>
-      </c>
-      <c r="E410" t="s">
-        <v>800</v>
-      </c>
-      <c r="F410" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G410" s="1">
-        <v>46247</v>
-      </c>
-    </row>
-    <row r="411" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A411" t="s">
-        <v>793</v>
-      </c>
-      <c r="B411" t="s">
-        <v>806</v>
-      </c>
-      <c r="C411" t="s">
-        <v>2</v>
-      </c>
-      <c r="D411" t="s">
-        <v>795</v>
-      </c>
-      <c r="E411" t="s">
-        <v>796</v>
-      </c>
-      <c r="F411" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G411" s="1">
-        <v>46247</v>
-      </c>
-    </row>
-    <row r="412" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A412" t="s">
-        <v>793</v>
-      </c>
-      <c r="B412" t="s">
-        <v>807</v>
-      </c>
-      <c r="C412" t="s">
-        <v>80</v>
-      </c>
-      <c r="D412" t="s">
-        <v>799</v>
-      </c>
-      <c r="E412" t="s">
-        <v>800</v>
-      </c>
-      <c r="F412" s="1">
-        <v>46255</v>
-      </c>
-      <c r="G412" s="1">
         <v>46255</v>
       </c>
     </row>

--- a/Data_ERP/Pedidos Transmicion.xlsx
+++ b/Data_ERP/Pedidos Transmicion.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sistema_Logistico_Peirano\Data_ERP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0BE52C57-FF3A-43EE-AD9F-B2B8F15C1584}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AB45E4D7-CE10-464F-B45D-39C448998075}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{F3EF298B-41C7-4855-832E-4E769876D2B9}"/>
   </bookViews>

--- a/Data_ERP/Pedidos Transmicion.xlsx
+++ b/Data_ERP/Pedidos Transmicion.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sistema_Logistico_Peirano\Data_ERP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AB45E4D7-CE10-464F-B45D-39C448998075}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{10939395-A6DD-4ACD-AB43-4D5C57B7B5A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{F3EF298B-41C7-4855-832E-4E769876D2B9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{0727CCF8-8CE0-49D7-BD56-52BD225F092C}"/>
   </bookViews>
   <sheets>
     <sheet name="transmicion" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2042" uniqueCount="811">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2057" uniqueCount="816">
   <si>
     <t>0001</t>
   </si>
@@ -904,6 +904,15 @@
     <t>CORRALON AVENIDA S.A.S.</t>
   </si>
   <si>
+    <t xml:space="preserve">  213553</t>
+  </si>
+  <si>
+    <t>CM57</t>
+  </si>
+  <si>
+    <t>CELESIA MARIANO T-SANITARIOS LARRALDE 1724</t>
+  </si>
+  <si>
     <t xml:space="preserve">  213569</t>
   </si>
   <si>
@@ -1975,7 +1984,13 @@
     <t xml:space="preserve">  214193</t>
   </si>
   <si>
+    <t xml:space="preserve">  214194</t>
+  </si>
+  <si>
     <t xml:space="preserve">  214195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214196</t>
   </si>
   <si>
     <t xml:space="preserve">  214197</t>
@@ -2902,31 +2917,31 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE68528F-9967-494B-98A8-1493F02C3C69}">
-  <dimension ref="A1:G408"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DBD66A9-C2DF-412C-8C5C-367A117D8A73}">
+  <dimension ref="A1:G411"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
-        <v>804</v>
+        <v>809</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>805</v>
+        <v>810</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>806</v>
+        <v>811</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>807</v>
+        <v>812</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>808</v>
+        <v>813</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>809</v>
+        <v>814</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>810</v>
+        <v>815</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
@@ -5628,19 +5643,19 @@
         <v>294</v>
       </c>
       <c r="C119" t="s">
-        <v>6</v>
+        <v>80</v>
       </c>
       <c r="D119" t="s">
-        <v>117</v>
+        <v>295</v>
       </c>
       <c r="E119" t="s">
-        <v>118</v>
+        <v>296</v>
       </c>
       <c r="F119" s="1">
         <v>46245</v>
       </c>
       <c r="G119" s="1">
-        <v>46246</v>
+        <v>46256</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.2">
@@ -5648,7 +5663,7 @@
         <v>0</v>
       </c>
       <c r="B120" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C120" t="s">
         <v>6</v>
@@ -5663,7 +5678,7 @@
         <v>46245</v>
       </c>
       <c r="G120" s="1">
-        <v>46245</v>
+        <v>46246</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.2">
@@ -5671,7 +5686,7 @@
         <v>0</v>
       </c>
       <c r="B121" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C121" t="s">
         <v>6</v>
@@ -5694,22 +5709,22 @@
         <v>0</v>
       </c>
       <c r="B122" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="C122" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D122" t="s">
-        <v>54</v>
+        <v>117</v>
       </c>
       <c r="E122" t="s">
-        <v>55</v>
+        <v>118</v>
       </c>
       <c r="F122" s="1">
         <v>46245</v>
       </c>
       <c r="G122" s="1">
-        <v>46246</v>
+        <v>46245</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.2">
@@ -5717,16 +5732,16 @@
         <v>0</v>
       </c>
       <c r="B123" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C123" t="s">
         <v>2</v>
       </c>
       <c r="D123" t="s">
-        <v>299</v>
+        <v>54</v>
       </c>
       <c r="E123" t="s">
-        <v>300</v>
+        <v>55</v>
       </c>
       <c r="F123" s="1">
         <v>46245</v>
@@ -5746,16 +5761,16 @@
         <v>2</v>
       </c>
       <c r="D124" t="s">
-        <v>37</v>
+        <v>302</v>
       </c>
       <c r="E124" t="s">
-        <v>38</v>
+        <v>303</v>
       </c>
       <c r="F124" s="1">
+        <v>46245</v>
+      </c>
+      <c r="G124" s="1">
         <v>46246</v>
-      </c>
-      <c r="G124" s="1">
-        <v>46252</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.2">
@@ -5763,16 +5778,16 @@
         <v>0</v>
       </c>
       <c r="B125" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C125" t="s">
         <v>2</v>
       </c>
       <c r="D125" t="s">
-        <v>253</v>
+        <v>37</v>
       </c>
       <c r="E125" t="s">
-        <v>254</v>
+        <v>38</v>
       </c>
       <c r="F125" s="1">
         <v>46246</v>
@@ -5786,22 +5801,22 @@
         <v>0</v>
       </c>
       <c r="B126" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="C126" t="s">
         <v>2</v>
       </c>
       <c r="D126" t="s">
-        <v>93</v>
+        <v>253</v>
       </c>
       <c r="E126" t="s">
-        <v>94</v>
+        <v>254</v>
       </c>
       <c r="F126" s="1">
         <v>46246</v>
       </c>
       <c r="G126" s="1">
-        <v>46247</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.2">
@@ -5809,22 +5824,22 @@
         <v>0</v>
       </c>
       <c r="B127" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="C127" t="s">
         <v>2</v>
       </c>
       <c r="D127" t="s">
-        <v>305</v>
+        <v>93</v>
       </c>
       <c r="E127" t="s">
-        <v>306</v>
+        <v>94</v>
       </c>
       <c r="F127" s="1">
         <v>46246</v>
       </c>
       <c r="G127" s="1">
-        <v>46252</v>
+        <v>46247</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.2">
@@ -5838,10 +5853,10 @@
         <v>2</v>
       </c>
       <c r="D128" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="E128" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="F128" s="1">
         <v>46246</v>
@@ -5855,22 +5870,22 @@
         <v>0</v>
       </c>
       <c r="B129" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="C129" t="s">
         <v>2</v>
       </c>
       <c r="D129" t="s">
+        <v>308</v>
+      </c>
+      <c r="E129" t="s">
         <v>309</v>
-      </c>
-      <c r="E129" t="s">
-        <v>310</v>
       </c>
       <c r="F129" s="1">
         <v>46246</v>
       </c>
       <c r="G129" s="1">
-        <v>46247</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.2">
@@ -5893,7 +5908,7 @@
         <v>46246</v>
       </c>
       <c r="G130" s="1">
-        <v>46252</v>
+        <v>46247</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.2">
@@ -5904,19 +5919,19 @@
         <v>314</v>
       </c>
       <c r="C131" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D131" t="s">
-        <v>144</v>
+        <v>315</v>
       </c>
       <c r="E131" t="s">
-        <v>145</v>
+        <v>316</v>
       </c>
       <c r="F131" s="1">
         <v>46246</v>
       </c>
       <c r="G131" s="1">
-        <v>46247</v>
+        <v>46256</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.2">
@@ -5924,22 +5939,22 @@
         <v>0</v>
       </c>
       <c r="B132" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="C132" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D132" t="s">
-        <v>37</v>
+        <v>144</v>
       </c>
       <c r="E132" t="s">
-        <v>38</v>
+        <v>145</v>
       </c>
       <c r="F132" s="1">
+        <v>46246</v>
+      </c>
+      <c r="G132" s="1">
         <v>46247</v>
-      </c>
-      <c r="G132" s="1">
-        <v>46252</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.2">
@@ -5947,7 +5962,7 @@
         <v>0</v>
       </c>
       <c r="B133" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C133" t="s">
         <v>80</v>
@@ -5970,7 +5985,7 @@
         <v>0</v>
       </c>
       <c r="B134" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="C134" t="s">
         <v>80</v>
@@ -5993,7 +6008,7 @@
         <v>0</v>
       </c>
       <c r="B135" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C135" t="s">
         <v>80</v>
@@ -6016,7 +6031,7 @@
         <v>0</v>
       </c>
       <c r="B136" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="C136" t="s">
         <v>80</v>
@@ -6039,7 +6054,7 @@
         <v>0</v>
       </c>
       <c r="B137" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="C137" t="s">
         <v>80</v>
@@ -6062,7 +6077,7 @@
         <v>0</v>
       </c>
       <c r="B138" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="C138" t="s">
         <v>80</v>
@@ -6085,7 +6100,7 @@
         <v>0</v>
       </c>
       <c r="B139" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C139" t="s">
         <v>80</v>
@@ -6108,7 +6123,7 @@
         <v>0</v>
       </c>
       <c r="B140" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="C140" t="s">
         <v>80</v>
@@ -6131,7 +6146,7 @@
         <v>0</v>
       </c>
       <c r="B141" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C141" t="s">
         <v>80</v>
@@ -6154,7 +6169,7 @@
         <v>0</v>
       </c>
       <c r="B142" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="C142" t="s">
         <v>80</v>
@@ -6177,16 +6192,16 @@
         <v>0</v>
       </c>
       <c r="B143" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C143" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D143" t="s">
-        <v>327</v>
+        <v>37</v>
       </c>
       <c r="E143" t="s">
-        <v>328</v>
+        <v>38</v>
       </c>
       <c r="F143" s="1">
         <v>46247</v>
@@ -6203,7 +6218,7 @@
         <v>329</v>
       </c>
       <c r="C144" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D144" t="s">
         <v>330</v>
@@ -6215,7 +6230,7 @@
         <v>46247</v>
       </c>
       <c r="G144" s="1">
-        <v>46247</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.2">
@@ -6229,16 +6244,16 @@
         <v>6</v>
       </c>
       <c r="D145" t="s">
-        <v>200</v>
+        <v>333</v>
       </c>
       <c r="E145" t="s">
-        <v>201</v>
+        <v>334</v>
       </c>
       <c r="F145" s="1">
         <v>46247</v>
       </c>
       <c r="G145" s="1">
-        <v>46252</v>
+        <v>46247</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.2">
@@ -6246,16 +6261,16 @@
         <v>0</v>
       </c>
       <c r="B146" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="C146" t="s">
-        <v>80</v>
+        <v>6</v>
       </c>
       <c r="D146" t="s">
-        <v>334</v>
+        <v>200</v>
       </c>
       <c r="E146" t="s">
-        <v>335</v>
+        <v>201</v>
       </c>
       <c r="F146" s="1">
         <v>46247</v>
@@ -6284,7 +6299,7 @@
         <v>46247</v>
       </c>
       <c r="G147" s="1">
-        <v>46253</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.2">
@@ -6295,7 +6310,7 @@
         <v>339</v>
       </c>
       <c r="C148" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D148" t="s">
         <v>340</v>
@@ -6307,7 +6322,7 @@
         <v>46247</v>
       </c>
       <c r="G148" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.2">
@@ -6327,7 +6342,7 @@
         <v>344</v>
       </c>
       <c r="F149" s="1">
-        <v>46248</v>
+        <v>46247</v>
       </c>
       <c r="G149" s="1">
         <v>46252</v>
@@ -6341,13 +6356,13 @@
         <v>345</v>
       </c>
       <c r="C150" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D150" t="s">
-        <v>117</v>
+        <v>346</v>
       </c>
       <c r="E150" t="s">
-        <v>118</v>
+        <v>347</v>
       </c>
       <c r="F150" s="1">
         <v>46248</v>
@@ -6361,16 +6376,16 @@
         <v>0</v>
       </c>
       <c r="B151" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C151" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D151" t="s">
-        <v>48</v>
+        <v>117</v>
       </c>
       <c r="E151" t="s">
-        <v>49</v>
+        <v>118</v>
       </c>
       <c r="F151" s="1">
         <v>46248</v>
@@ -6384,16 +6399,16 @@
         <v>0</v>
       </c>
       <c r="B152" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="C152" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D152" t="s">
-        <v>348</v>
+        <v>48</v>
       </c>
       <c r="E152" t="s">
-        <v>349</v>
+        <v>49</v>
       </c>
       <c r="F152" s="1">
         <v>46248</v>
@@ -6410,7 +6425,7 @@
         <v>350</v>
       </c>
       <c r="C153" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D153" t="s">
         <v>351</v>
@@ -6436,10 +6451,10 @@
         <v>2</v>
       </c>
       <c r="D154" t="s">
-        <v>163</v>
+        <v>354</v>
       </c>
       <c r="E154" t="s">
-        <v>164</v>
+        <v>355</v>
       </c>
       <c r="F154" s="1">
         <v>46248</v>
@@ -6453,16 +6468,16 @@
         <v>0</v>
       </c>
       <c r="B155" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C155" t="s">
         <v>2</v>
       </c>
       <c r="D155" t="s">
-        <v>355</v>
+        <v>163</v>
       </c>
       <c r="E155" t="s">
-        <v>356</v>
+        <v>164</v>
       </c>
       <c r="F155" s="1">
         <v>46248</v>
@@ -6479,7 +6494,7 @@
         <v>357</v>
       </c>
       <c r="C156" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D156" t="s">
         <v>358</v>
@@ -6511,7 +6526,7 @@
         <v>362</v>
       </c>
       <c r="F157" s="1">
-        <v>46252</v>
+        <v>46248</v>
       </c>
       <c r="G157" s="1">
         <v>46252</v>
@@ -6525,7 +6540,7 @@
         <v>363</v>
       </c>
       <c r="C158" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D158" t="s">
         <v>364</v>
@@ -6537,7 +6552,7 @@
         <v>46252</v>
       </c>
       <c r="G158" s="1">
-        <v>46255</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.2">
@@ -6560,7 +6575,7 @@
         <v>46252</v>
       </c>
       <c r="G159" s="1">
-        <v>46254</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.2">
@@ -6571,19 +6586,19 @@
         <v>369</v>
       </c>
       <c r="C160" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D160" t="s">
-        <v>327</v>
+        <v>370</v>
       </c>
       <c r="E160" t="s">
-        <v>328</v>
+        <v>371</v>
       </c>
       <c r="F160" s="1">
         <v>46252</v>
       </c>
       <c r="G160" s="1">
-        <v>46252</v>
+        <v>46254</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.2">
@@ -6591,16 +6606,16 @@
         <v>0</v>
       </c>
       <c r="B161" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="C161" t="s">
         <v>80</v>
       </c>
       <c r="D161" t="s">
-        <v>77</v>
+        <v>330</v>
       </c>
       <c r="E161" t="s">
-        <v>78</v>
+        <v>331</v>
       </c>
       <c r="F161" s="1">
         <v>46252</v>
@@ -6614,16 +6629,16 @@
         <v>0</v>
       </c>
       <c r="B162" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C162" t="s">
         <v>80</v>
       </c>
       <c r="D162" t="s">
-        <v>98</v>
+        <v>77</v>
       </c>
       <c r="E162" t="s">
-        <v>99</v>
+        <v>78</v>
       </c>
       <c r="F162" s="1">
         <v>46252</v>
@@ -6637,16 +6652,16 @@
         <v>0</v>
       </c>
       <c r="B163" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="C163" t="s">
         <v>80</v>
       </c>
       <c r="D163" t="s">
-        <v>373</v>
+        <v>98</v>
       </c>
       <c r="E163" t="s">
-        <v>374</v>
+        <v>99</v>
       </c>
       <c r="F163" s="1">
         <v>46252</v>
@@ -6666,16 +6681,16 @@
         <v>80</v>
       </c>
       <c r="D164" t="s">
-        <v>117</v>
+        <v>376</v>
       </c>
       <c r="E164" t="s">
-        <v>118</v>
+        <v>377</v>
       </c>
       <c r="F164" s="1">
         <v>46252</v>
       </c>
       <c r="G164" s="1">
-        <v>46253</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.2">
@@ -6683,16 +6698,16 @@
         <v>0</v>
       </c>
       <c r="B165" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="C165" t="s">
         <v>80</v>
       </c>
       <c r="D165" t="s">
-        <v>340</v>
+        <v>117</v>
       </c>
       <c r="E165" t="s">
-        <v>341</v>
+        <v>118</v>
       </c>
       <c r="F165" s="1">
         <v>46252</v>
@@ -6706,22 +6721,22 @@
         <v>0</v>
       </c>
       <c r="B166" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="C166" t="s">
         <v>80</v>
       </c>
       <c r="D166" t="s">
-        <v>224</v>
+        <v>343</v>
       </c>
       <c r="E166" t="s">
-        <v>225</v>
+        <v>344</v>
       </c>
       <c r="F166" s="1">
         <v>46252</v>
       </c>
       <c r="G166" s="1">
-        <v>46254</v>
+        <v>46253</v>
       </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.2">
@@ -6729,22 +6744,22 @@
         <v>0</v>
       </c>
       <c r="B167" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="C167" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D167" t="s">
-        <v>243</v>
+        <v>224</v>
       </c>
       <c r="E167" t="s">
-        <v>244</v>
+        <v>225</v>
       </c>
       <c r="F167" s="1">
         <v>46252</v>
       </c>
       <c r="G167" s="1">
-        <v>46253</v>
+        <v>46254</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.2">
@@ -6752,22 +6767,22 @@
         <v>0</v>
       </c>
       <c r="B168" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="C168" t="s">
         <v>2</v>
       </c>
       <c r="D168" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="E168" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="F168" s="1">
         <v>46252</v>
       </c>
       <c r="G168" s="1">
-        <v>46254</v>
+        <v>46253</v>
       </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.2">
@@ -6775,22 +6790,22 @@
         <v>0</v>
       </c>
       <c r="B169" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="C169" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D169" t="s">
-        <v>381</v>
+        <v>246</v>
       </c>
       <c r="E169" t="s">
-        <v>382</v>
+        <v>247</v>
       </c>
       <c r="F169" s="1">
         <v>46252</v>
       </c>
       <c r="G169" s="1">
-        <v>46252</v>
+        <v>46254</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.2">
@@ -6801,7 +6816,7 @@
         <v>383</v>
       </c>
       <c r="C170" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D170" t="s">
         <v>384</v>
@@ -6813,7 +6828,7 @@
         <v>46252</v>
       </c>
       <c r="G170" s="1">
-        <v>46253</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.2">
@@ -6882,7 +6897,7 @@
         <v>46252</v>
       </c>
       <c r="G173" s="1">
-        <v>46254</v>
+        <v>46253</v>
       </c>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.2">
@@ -6893,13 +6908,13 @@
         <v>395</v>
       </c>
       <c r="C174" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D174" t="s">
-        <v>276</v>
+        <v>396</v>
       </c>
       <c r="E174" t="s">
-        <v>277</v>
+        <v>397</v>
       </c>
       <c r="F174" s="1">
         <v>46252</v>
@@ -6913,7 +6928,7 @@
         <v>0</v>
       </c>
       <c r="B175" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="C175" t="s">
         <v>80</v>
@@ -6928,7 +6943,7 @@
         <v>46252</v>
       </c>
       <c r="G175" s="1">
-        <v>46253</v>
+        <v>46254</v>
       </c>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.2">
@@ -6936,22 +6951,22 @@
         <v>0</v>
       </c>
       <c r="B176" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="C176" t="s">
         <v>80</v>
       </c>
       <c r="D176" t="s">
-        <v>190</v>
+        <v>276</v>
       </c>
       <c r="E176" t="s">
-        <v>191</v>
+        <v>277</v>
       </c>
       <c r="F176" s="1">
         <v>46252</v>
       </c>
       <c r="G176" s="1">
-        <v>46255</v>
+        <v>46253</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.2">
@@ -6959,7 +6974,7 @@
         <v>0</v>
       </c>
       <c r="B177" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="C177" t="s">
         <v>80</v>
@@ -6982,22 +6997,22 @@
         <v>0</v>
       </c>
       <c r="B178" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="C178" t="s">
         <v>80</v>
       </c>
       <c r="D178" t="s">
-        <v>400</v>
+        <v>190</v>
       </c>
       <c r="E178" t="s">
-        <v>401</v>
+        <v>191</v>
       </c>
       <c r="F178" s="1">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="G178" s="1">
-        <v>46253</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.2">
@@ -7008,7 +7023,7 @@
         <v>402</v>
       </c>
       <c r="C179" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D179" t="s">
         <v>403</v>
@@ -7020,7 +7035,7 @@
         <v>46253</v>
       </c>
       <c r="G179" s="1">
-        <v>46254</v>
+        <v>46253</v>
       </c>
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.2">
@@ -7031,7 +7046,7 @@
         <v>405</v>
       </c>
       <c r="C180" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D180" t="s">
         <v>406</v>
@@ -7043,7 +7058,7 @@
         <v>46253</v>
       </c>
       <c r="G180" s="1">
-        <v>46253</v>
+        <v>46254</v>
       </c>
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.2">
@@ -7054,13 +7069,13 @@
         <v>408</v>
       </c>
       <c r="C181" t="s">
-        <v>80</v>
+        <v>6</v>
       </c>
       <c r="D181" t="s">
-        <v>37</v>
+        <v>409</v>
       </c>
       <c r="E181" t="s">
-        <v>38</v>
+        <v>410</v>
       </c>
       <c r="F181" s="1">
         <v>46253</v>
@@ -7074,10 +7089,10 @@
         <v>0</v>
       </c>
       <c r="B182" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="C182" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D182" t="s">
         <v>37</v>
@@ -7097,7 +7112,7 @@
         <v>0</v>
       </c>
       <c r="B183" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C183" t="s">
         <v>2</v>
@@ -7120,22 +7135,22 @@
         <v>0</v>
       </c>
       <c r="B184" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C184" t="s">
         <v>2</v>
       </c>
       <c r="D184" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="E184" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="F184" s="1">
         <v>46253</v>
       </c>
       <c r="G184" s="1">
-        <v>46255</v>
+        <v>46253</v>
       </c>
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.2">
@@ -7143,22 +7158,22 @@
         <v>0</v>
       </c>
       <c r="B185" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="C185" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D185" t="s">
-        <v>413</v>
+        <v>48</v>
       </c>
       <c r="E185" t="s">
-        <v>414</v>
+        <v>49</v>
       </c>
       <c r="F185" s="1">
         <v>46253</v>
       </c>
       <c r="G185" s="1">
-        <v>46253</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.2">
@@ -7264,10 +7279,10 @@
         <v>80</v>
       </c>
       <c r="D190" t="s">
-        <v>381</v>
+        <v>428</v>
       </c>
       <c r="E190" t="s">
-        <v>382</v>
+        <v>429</v>
       </c>
       <c r="F190" s="1">
         <v>46253</v>
@@ -7281,16 +7296,16 @@
         <v>0</v>
       </c>
       <c r="B191" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="C191" t="s">
         <v>80</v>
       </c>
       <c r="D191" t="s">
-        <v>429</v>
+        <v>384</v>
       </c>
       <c r="E191" t="s">
-        <v>430</v>
+        <v>385</v>
       </c>
       <c r="F191" s="1">
         <v>46253</v>
@@ -7356,10 +7371,10 @@
         <v>80</v>
       </c>
       <c r="D194" t="s">
-        <v>37</v>
+        <v>438</v>
       </c>
       <c r="E194" t="s">
-        <v>38</v>
+        <v>439</v>
       </c>
       <c r="F194" s="1">
         <v>46253</v>
@@ -7373,7 +7388,7 @@
         <v>0</v>
       </c>
       <c r="B195" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="C195" t="s">
         <v>80</v>
@@ -7396,7 +7411,7 @@
         <v>0</v>
       </c>
       <c r="B196" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="C196" t="s">
         <v>80</v>
@@ -7419,7 +7434,7 @@
         <v>0</v>
       </c>
       <c r="B197" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="C197" t="s">
         <v>80</v>
@@ -7442,7 +7457,7 @@
         <v>0</v>
       </c>
       <c r="B198" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="C198" t="s">
         <v>80</v>
@@ -7465,7 +7480,7 @@
         <v>0</v>
       </c>
       <c r="B199" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="C199" t="s">
         <v>80</v>
@@ -7488,7 +7503,7 @@
         <v>0</v>
       </c>
       <c r="B200" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C200" t="s">
         <v>80</v>
@@ -7511,7 +7526,7 @@
         <v>0</v>
       </c>
       <c r="B201" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="C201" t="s">
         <v>80</v>
@@ -7534,16 +7549,16 @@
         <v>0</v>
       </c>
       <c r="B202" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="C202" t="s">
         <v>80</v>
       </c>
       <c r="D202" t="s">
-        <v>446</v>
+        <v>37</v>
       </c>
       <c r="E202" t="s">
-        <v>447</v>
+        <v>38</v>
       </c>
       <c r="F202" s="1">
         <v>46253</v>
@@ -7586,16 +7601,16 @@
         <v>80</v>
       </c>
       <c r="D204" t="s">
-        <v>7</v>
+        <v>452</v>
       </c>
       <c r="E204" t="s">
-        <v>8</v>
+        <v>453</v>
       </c>
       <c r="F204" s="1">
         <v>46253</v>
       </c>
       <c r="G204" s="1">
-        <v>46255</v>
+        <v>46253</v>
       </c>
     </row>
     <row r="205" spans="1:7" x14ac:dyDescent="0.2">
@@ -7603,7 +7618,7 @@
         <v>0</v>
       </c>
       <c r="B205" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="C205" t="s">
         <v>80</v>
@@ -7626,22 +7641,22 @@
         <v>0</v>
       </c>
       <c r="B206" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="C206" t="s">
         <v>80</v>
       </c>
       <c r="D206" t="s">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="E206" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="F206" s="1">
         <v>46253</v>
       </c>
       <c r="G206" s="1">
-        <v>46254</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="207" spans="1:7" x14ac:dyDescent="0.2">
@@ -7649,16 +7664,16 @@
         <v>0</v>
       </c>
       <c r="B207" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="C207" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D207" t="s">
-        <v>455</v>
+        <v>28</v>
       </c>
       <c r="E207" t="s">
-        <v>456</v>
+        <v>29</v>
       </c>
       <c r="F207" s="1">
         <v>46253</v>
@@ -7675,16 +7690,16 @@
         <v>457</v>
       </c>
       <c r="C208" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D208" t="s">
-        <v>98</v>
+        <v>458</v>
       </c>
       <c r="E208" t="s">
-        <v>99</v>
+        <v>459</v>
       </c>
       <c r="F208" s="1">
-        <v>46254</v>
+        <v>46253</v>
       </c>
       <c r="G208" s="1">
         <v>46254</v>
@@ -7695,16 +7710,16 @@
         <v>0</v>
       </c>
       <c r="B209" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="C209" t="s">
         <v>80</v>
       </c>
       <c r="D209" t="s">
-        <v>459</v>
+        <v>98</v>
       </c>
       <c r="E209" t="s">
-        <v>460</v>
+        <v>99</v>
       </c>
       <c r="F209" s="1">
         <v>46254</v>
@@ -7721,7 +7736,7 @@
         <v>461</v>
       </c>
       <c r="C210" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D210" t="s">
         <v>462</v>
@@ -7744,7 +7759,7 @@
         <v>464</v>
       </c>
       <c r="C211" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D211" t="s">
         <v>465</v>
@@ -7770,10 +7785,10 @@
         <v>80</v>
       </c>
       <c r="D212" t="s">
-        <v>173</v>
+        <v>468</v>
       </c>
       <c r="E212" t="s">
-        <v>174</v>
+        <v>469</v>
       </c>
       <c r="F212" s="1">
         <v>46254</v>
@@ -7787,16 +7802,16 @@
         <v>0</v>
       </c>
       <c r="B213" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="C213" t="s">
         <v>80</v>
       </c>
       <c r="D213" t="s">
-        <v>37</v>
+        <v>173</v>
       </c>
       <c r="E213" t="s">
-        <v>38</v>
+        <v>174</v>
       </c>
       <c r="F213" s="1">
         <v>46254</v>
@@ -7810,10 +7825,10 @@
         <v>0</v>
       </c>
       <c r="B214" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="C214" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D214" t="s">
         <v>37</v>
@@ -7833,10 +7848,10 @@
         <v>0</v>
       </c>
       <c r="B215" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="C215" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D215" t="s">
         <v>37</v>
@@ -7856,16 +7871,16 @@
         <v>0</v>
       </c>
       <c r="B216" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C216" t="s">
         <v>80</v>
       </c>
       <c r="D216" t="s">
-        <v>472</v>
+        <v>37</v>
       </c>
       <c r="E216" t="s">
-        <v>473</v>
+        <v>38</v>
       </c>
       <c r="F216" s="1">
         <v>46254</v>
@@ -7885,10 +7900,10 @@
         <v>80</v>
       </c>
       <c r="D217" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="E217" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="F217" s="1">
         <v>46254</v>
@@ -7902,16 +7917,16 @@
         <v>0</v>
       </c>
       <c r="B218" t="s">
+        <v>477</v>
+      </c>
+      <c r="C218" t="s">
+        <v>80</v>
+      </c>
+      <c r="D218" t="s">
         <v>475</v>
       </c>
-      <c r="C218" t="s">
-        <v>2</v>
-      </c>
-      <c r="D218" t="s">
-        <v>16</v>
-      </c>
       <c r="E218" t="s">
-        <v>17</v>
+        <v>476</v>
       </c>
       <c r="F218" s="1">
         <v>46254</v>
@@ -7925,10 +7940,10 @@
         <v>0</v>
       </c>
       <c r="B219" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="C219" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D219" t="s">
         <v>16</v>
@@ -7948,16 +7963,16 @@
         <v>0</v>
       </c>
       <c r="B220" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="C220" t="s">
         <v>80</v>
       </c>
       <c r="D220" t="s">
-        <v>478</v>
+        <v>16</v>
       </c>
       <c r="E220" t="s">
-        <v>479</v>
+        <v>17</v>
       </c>
       <c r="F220" s="1">
         <v>46254</v>
@@ -7977,16 +7992,16 @@
         <v>80</v>
       </c>
       <c r="D221" t="s">
-        <v>194</v>
+        <v>481</v>
       </c>
       <c r="E221" t="s">
-        <v>195</v>
+        <v>482</v>
       </c>
       <c r="F221" s="1">
         <v>46254</v>
       </c>
       <c r="G221" s="1">
-        <v>46255</v>
+        <v>46254</v>
       </c>
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.2">
@@ -7994,22 +8009,22 @@
         <v>0</v>
       </c>
       <c r="B222" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C222" t="s">
         <v>80</v>
       </c>
       <c r="D222" t="s">
-        <v>482</v>
+        <v>194</v>
       </c>
       <c r="E222" t="s">
-        <v>483</v>
+        <v>195</v>
       </c>
       <c r="F222" s="1">
         <v>46254</v>
       </c>
       <c r="G222" s="1">
-        <v>46254</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="223" spans="1:7" x14ac:dyDescent="0.2">
@@ -8020,7 +8035,7 @@
         <v>484</v>
       </c>
       <c r="C223" t="s">
-        <v>6</v>
+        <v>80</v>
       </c>
       <c r="D223" t="s">
         <v>485</v>
@@ -8043,7 +8058,7 @@
         <v>487</v>
       </c>
       <c r="C224" t="s">
-        <v>80</v>
+        <v>6</v>
       </c>
       <c r="D224" t="s">
         <v>488</v>
@@ -8069,10 +8084,10 @@
         <v>80</v>
       </c>
       <c r="D225" t="s">
-        <v>77</v>
+        <v>491</v>
       </c>
       <c r="E225" t="s">
-        <v>78</v>
+        <v>492</v>
       </c>
       <c r="F225" s="1">
         <v>46254</v>
@@ -8086,16 +8101,16 @@
         <v>0</v>
       </c>
       <c r="B226" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="C226" t="s">
         <v>80</v>
       </c>
       <c r="D226" t="s">
-        <v>16</v>
+        <v>77</v>
       </c>
       <c r="E226" t="s">
-        <v>17</v>
+        <v>78</v>
       </c>
       <c r="F226" s="1">
         <v>46254</v>
@@ -8109,16 +8124,16 @@
         <v>0</v>
       </c>
       <c r="B227" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="C227" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D227" t="s">
-        <v>493</v>
+        <v>16</v>
       </c>
       <c r="E227" t="s">
-        <v>494</v>
+        <v>17</v>
       </c>
       <c r="F227" s="1">
         <v>46254</v>
@@ -8135,13 +8150,13 @@
         <v>495</v>
       </c>
       <c r="C228" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D228" t="s">
-        <v>3</v>
+        <v>496</v>
       </c>
       <c r="E228" t="s">
-        <v>4</v>
+        <v>497</v>
       </c>
       <c r="F228" s="1">
         <v>46254</v>
@@ -8155,22 +8170,22 @@
         <v>0</v>
       </c>
       <c r="B229" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C229" t="s">
         <v>80</v>
       </c>
       <c r="D229" t="s">
-        <v>497</v>
+        <v>3</v>
       </c>
       <c r="E229" t="s">
-        <v>498</v>
+        <v>4</v>
       </c>
       <c r="F229" s="1">
         <v>46254</v>
       </c>
       <c r="G229" s="1">
-        <v>46255</v>
+        <v>46254</v>
       </c>
     </row>
     <row r="230" spans="1:7" x14ac:dyDescent="0.2">
@@ -8181,13 +8196,13 @@
         <v>499</v>
       </c>
       <c r="C230" t="s">
-        <v>6</v>
+        <v>80</v>
       </c>
       <c r="D230" t="s">
-        <v>138</v>
+        <v>500</v>
       </c>
       <c r="E230" t="s">
-        <v>139</v>
+        <v>501</v>
       </c>
       <c r="F230" s="1">
         <v>46254</v>
@@ -8201,22 +8216,22 @@
         <v>0</v>
       </c>
       <c r="B231" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="C231" t="s">
         <v>80</v>
       </c>
       <c r="D231" t="s">
-        <v>501</v>
+        <v>138</v>
       </c>
       <c r="E231" t="s">
-        <v>502</v>
+        <v>139</v>
       </c>
       <c r="F231" s="1">
         <v>46254</v>
       </c>
       <c r="G231" s="1">
-        <v>46255</v>
+        <v>46256</v>
       </c>
     </row>
     <row r="232" spans="1:7" x14ac:dyDescent="0.2">
@@ -8230,16 +8245,16 @@
         <v>80</v>
       </c>
       <c r="D232" t="s">
-        <v>355</v>
+        <v>504</v>
       </c>
       <c r="E232" t="s">
-        <v>356</v>
+        <v>505</v>
       </c>
       <c r="F232" s="1">
         <v>46254</v>
       </c>
       <c r="G232" s="1">
-        <v>46254</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="233" spans="1:7" x14ac:dyDescent="0.2">
@@ -8247,16 +8262,16 @@
         <v>0</v>
       </c>
       <c r="B233" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="C233" t="s">
         <v>80</v>
       </c>
       <c r="D233" t="s">
-        <v>292</v>
+        <v>358</v>
       </c>
       <c r="E233" t="s">
-        <v>293</v>
+        <v>359</v>
       </c>
       <c r="F233" s="1">
         <v>46254</v>
@@ -8270,16 +8285,16 @@
         <v>0</v>
       </c>
       <c r="B234" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="C234" t="s">
         <v>80</v>
       </c>
       <c r="D234" t="s">
-        <v>506</v>
+        <v>292</v>
       </c>
       <c r="E234" t="s">
-        <v>507</v>
+        <v>293</v>
       </c>
       <c r="F234" s="1">
         <v>46254</v>
@@ -8296,7 +8311,7 @@
         <v>508</v>
       </c>
       <c r="C235" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D235" t="s">
         <v>509</v>
@@ -8308,7 +8323,7 @@
         <v>46254</v>
       </c>
       <c r="G235" s="1">
-        <v>46255</v>
+        <v>46254</v>
       </c>
     </row>
     <row r="236" spans="1:7" x14ac:dyDescent="0.2">
@@ -8319,19 +8334,19 @@
         <v>511</v>
       </c>
       <c r="C236" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D236" t="s">
-        <v>16</v>
+        <v>512</v>
       </c>
       <c r="E236" t="s">
-        <v>17</v>
+        <v>513</v>
       </c>
       <c r="F236" s="1">
         <v>46254</v>
       </c>
       <c r="G236" s="1">
-        <v>46254</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.2">
@@ -8339,22 +8354,22 @@
         <v>0</v>
       </c>
       <c r="B237" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="C237" t="s">
         <v>80</v>
       </c>
       <c r="D237" t="s">
-        <v>138</v>
+        <v>16</v>
       </c>
       <c r="E237" t="s">
-        <v>139</v>
+        <v>17</v>
       </c>
       <c r="F237" s="1">
         <v>46254</v>
       </c>
       <c r="G237" s="1">
-        <v>46255</v>
+        <v>46254</v>
       </c>
     </row>
     <row r="238" spans="1:7" x14ac:dyDescent="0.2">
@@ -8362,22 +8377,22 @@
         <v>0</v>
       </c>
       <c r="B238" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="C238" t="s">
         <v>80</v>
       </c>
       <c r="D238" t="s">
-        <v>514</v>
+        <v>138</v>
       </c>
       <c r="E238" t="s">
-        <v>515</v>
+        <v>139</v>
       </c>
       <c r="F238" s="1">
         <v>46254</v>
       </c>
       <c r="G238" s="1">
-        <v>46254</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="239" spans="1:7" x14ac:dyDescent="0.2">
@@ -8483,16 +8498,16 @@
         <v>80</v>
       </c>
       <c r="D243" t="s">
-        <v>141</v>
+        <v>529</v>
       </c>
       <c r="E243" t="s">
-        <v>142</v>
+        <v>530</v>
       </c>
       <c r="F243" s="1">
         <v>46254</v>
       </c>
       <c r="G243" s="1">
-        <v>46255</v>
+        <v>46254</v>
       </c>
     </row>
     <row r="244" spans="1:7" x14ac:dyDescent="0.2">
@@ -8500,22 +8515,22 @@
         <v>0</v>
       </c>
       <c r="B244" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="C244" t="s">
         <v>80</v>
       </c>
       <c r="D244" t="s">
-        <v>449</v>
+        <v>141</v>
       </c>
       <c r="E244" t="s">
-        <v>450</v>
+        <v>142</v>
       </c>
       <c r="F244" s="1">
         <v>46254</v>
       </c>
       <c r="G244" s="1">
-        <v>46254</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="245" spans="1:7" x14ac:dyDescent="0.2">
@@ -8523,22 +8538,22 @@
         <v>0</v>
       </c>
       <c r="B245" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="C245" t="s">
         <v>80</v>
       </c>
       <c r="D245" t="s">
-        <v>141</v>
+        <v>452</v>
       </c>
       <c r="E245" t="s">
-        <v>142</v>
+        <v>453</v>
       </c>
       <c r="F245" s="1">
         <v>46254</v>
       </c>
       <c r="G245" s="1">
-        <v>46255</v>
+        <v>46254</v>
       </c>
     </row>
     <row r="246" spans="1:7" x14ac:dyDescent="0.2">
@@ -8546,16 +8561,16 @@
         <v>0</v>
       </c>
       <c r="B246" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="C246" t="s">
         <v>80</v>
       </c>
       <c r="D246" t="s">
-        <v>532</v>
+        <v>141</v>
       </c>
       <c r="E246" t="s">
-        <v>533</v>
+        <v>142</v>
       </c>
       <c r="F246" s="1">
         <v>46254</v>
@@ -8575,10 +8590,10 @@
         <v>80</v>
       </c>
       <c r="D247" t="s">
-        <v>19</v>
+        <v>535</v>
       </c>
       <c r="E247" t="s">
-        <v>20</v>
+        <v>536</v>
       </c>
       <c r="F247" s="1">
         <v>46254</v>
@@ -8592,16 +8607,16 @@
         <v>0</v>
       </c>
       <c r="B248" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="C248" t="s">
         <v>80</v>
       </c>
       <c r="D248" t="s">
-        <v>327</v>
+        <v>19</v>
       </c>
       <c r="E248" t="s">
-        <v>328</v>
+        <v>20</v>
       </c>
       <c r="F248" s="1">
         <v>46254</v>
@@ -8615,16 +8630,16 @@
         <v>0</v>
       </c>
       <c r="B249" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="C249" t="s">
         <v>80</v>
       </c>
       <c r="D249" t="s">
-        <v>537</v>
+        <v>330</v>
       </c>
       <c r="E249" t="s">
-        <v>538</v>
+        <v>331</v>
       </c>
       <c r="F249" s="1">
         <v>46254</v>
@@ -8687,7 +8702,7 @@
         <v>545</v>
       </c>
       <c r="C252" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D252" t="s">
         <v>546</v>
@@ -8713,10 +8728,10 @@
         <v>2</v>
       </c>
       <c r="D253" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="E253" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="F253" s="1">
         <v>46254</v>
@@ -8730,16 +8745,16 @@
         <v>0</v>
       </c>
       <c r="B254" t="s">
+        <v>551</v>
+      </c>
+      <c r="C254" t="s">
+        <v>2</v>
+      </c>
+      <c r="D254" t="s">
         <v>549</v>
       </c>
-      <c r="C254" t="s">
-        <v>80</v>
-      </c>
-      <c r="D254" t="s">
-        <v>259</v>
-      </c>
       <c r="E254" t="s">
-        <v>260</v>
+        <v>550</v>
       </c>
       <c r="F254" s="1">
         <v>46254</v>
@@ -8753,16 +8768,16 @@
         <v>0</v>
       </c>
       <c r="B255" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="C255" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D255" t="s">
-        <v>546</v>
+        <v>259</v>
       </c>
       <c r="E255" t="s">
-        <v>547</v>
+        <v>260</v>
       </c>
       <c r="F255" s="1">
         <v>46254</v>
@@ -8776,16 +8791,16 @@
         <v>0</v>
       </c>
       <c r="B256" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="C256" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D256" t="s">
-        <v>259</v>
+        <v>549</v>
       </c>
       <c r="E256" t="s">
-        <v>260</v>
+        <v>550</v>
       </c>
       <c r="F256" s="1">
         <v>46254</v>
@@ -8799,16 +8814,16 @@
         <v>0</v>
       </c>
       <c r="B257" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="C257" t="s">
         <v>80</v>
       </c>
       <c r="D257" t="s">
-        <v>156</v>
+        <v>259</v>
       </c>
       <c r="E257" t="s">
-        <v>157</v>
+        <v>260</v>
       </c>
       <c r="F257" s="1">
         <v>46254</v>
@@ -8822,16 +8837,16 @@
         <v>0</v>
       </c>
       <c r="B258" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="C258" t="s">
         <v>80</v>
       </c>
       <c r="D258" t="s">
-        <v>554</v>
+        <v>156</v>
       </c>
       <c r="E258" t="s">
-        <v>555</v>
+        <v>157</v>
       </c>
       <c r="F258" s="1">
         <v>46254</v>
@@ -8943,10 +8958,10 @@
         <v>80</v>
       </c>
       <c r="D263" t="s">
-        <v>156</v>
+        <v>569</v>
       </c>
       <c r="E263" t="s">
-        <v>157</v>
+        <v>570</v>
       </c>
       <c r="F263" s="1">
         <v>46254</v>
@@ -8960,16 +8975,16 @@
         <v>0</v>
       </c>
       <c r="B264" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="C264" t="s">
         <v>80</v>
       </c>
       <c r="D264" t="s">
-        <v>337</v>
+        <v>156</v>
       </c>
       <c r="E264" t="s">
-        <v>338</v>
+        <v>157</v>
       </c>
       <c r="F264" s="1">
         <v>46254</v>
@@ -8983,16 +8998,16 @@
         <v>0</v>
       </c>
       <c r="B265" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="C265" t="s">
         <v>80</v>
       </c>
       <c r="D265" t="s">
-        <v>571</v>
+        <v>340</v>
       </c>
       <c r="E265" t="s">
-        <v>572</v>
+        <v>341</v>
       </c>
       <c r="F265" s="1">
         <v>46254</v>
@@ -9012,16 +9027,16 @@
         <v>80</v>
       </c>
       <c r="D266" t="s">
-        <v>337</v>
+        <v>574</v>
       </c>
       <c r="E266" t="s">
-        <v>338</v>
+        <v>575</v>
       </c>
       <c r="F266" s="1">
         <v>46254</v>
       </c>
       <c r="G266" s="1">
-        <v>46256</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="267" spans="1:7" x14ac:dyDescent="0.2">
@@ -9029,22 +9044,22 @@
         <v>0</v>
       </c>
       <c r="B267" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="C267" t="s">
         <v>80</v>
       </c>
       <c r="D267" t="s">
-        <v>575</v>
+        <v>340</v>
       </c>
       <c r="E267" t="s">
-        <v>576</v>
+        <v>341</v>
       </c>
       <c r="F267" s="1">
         <v>46254</v>
       </c>
       <c r="G267" s="1">
-        <v>46255</v>
+        <v>46256</v>
       </c>
     </row>
     <row r="268" spans="1:7" x14ac:dyDescent="0.2">
@@ -9058,10 +9073,10 @@
         <v>80</v>
       </c>
       <c r="D268" t="s">
-        <v>571</v>
+        <v>578</v>
       </c>
       <c r="E268" t="s">
-        <v>572</v>
+        <v>579</v>
       </c>
       <c r="F268" s="1">
         <v>46254</v>
@@ -9075,16 +9090,16 @@
         <v>0</v>
       </c>
       <c r="B269" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="C269" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D269" t="s">
-        <v>216</v>
+        <v>574</v>
       </c>
       <c r="E269" t="s">
-        <v>217</v>
+        <v>575</v>
       </c>
       <c r="F269" s="1">
         <v>46254</v>
@@ -9098,16 +9113,16 @@
         <v>0</v>
       </c>
       <c r="B270" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="C270" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D270" t="s">
-        <v>580</v>
+        <v>216</v>
       </c>
       <c r="E270" t="s">
-        <v>581</v>
+        <v>217</v>
       </c>
       <c r="F270" s="1">
         <v>46254</v>
@@ -9127,13 +9142,13 @@
         <v>80</v>
       </c>
       <c r="D271" t="s">
-        <v>16</v>
+        <v>583</v>
       </c>
       <c r="E271" t="s">
-        <v>17</v>
+        <v>584</v>
       </c>
       <c r="F271" s="1">
-        <v>46255</v>
+        <v>46254</v>
       </c>
       <c r="G271" s="1">
         <v>46255</v>
@@ -9144,16 +9159,16 @@
         <v>0</v>
       </c>
       <c r="B272" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="C272" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D272" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="E272" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F272" s="1">
         <v>46255</v>
@@ -9167,16 +9182,16 @@
         <v>0</v>
       </c>
       <c r="B273" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="C273" t="s">
         <v>2</v>
       </c>
       <c r="D273" t="s">
-        <v>585</v>
+        <v>37</v>
       </c>
       <c r="E273" t="s">
-        <v>586</v>
+        <v>38</v>
       </c>
       <c r="F273" s="1">
         <v>46255</v>
@@ -9193,7 +9208,7 @@
         <v>587</v>
       </c>
       <c r="C274" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D274" t="s">
         <v>588</v>
@@ -9219,10 +9234,10 @@
         <v>80</v>
       </c>
       <c r="D275" t="s">
-        <v>98</v>
+        <v>591</v>
       </c>
       <c r="E275" t="s">
-        <v>99</v>
+        <v>592</v>
       </c>
       <c r="F275" s="1">
         <v>46255</v>
@@ -9236,16 +9251,16 @@
         <v>0</v>
       </c>
       <c r="B276" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="C276" t="s">
         <v>80</v>
       </c>
       <c r="D276" t="s">
-        <v>219</v>
+        <v>98</v>
       </c>
       <c r="E276" t="s">
-        <v>220</v>
+        <v>99</v>
       </c>
       <c r="F276" s="1">
         <v>46255</v>
@@ -9259,7 +9274,7 @@
         <v>0</v>
       </c>
       <c r="B277" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="C277" t="s">
         <v>80</v>
@@ -9282,16 +9297,16 @@
         <v>0</v>
       </c>
       <c r="B278" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="C278" t="s">
         <v>80</v>
       </c>
       <c r="D278" t="s">
-        <v>594</v>
+        <v>219</v>
       </c>
       <c r="E278" t="s">
-        <v>595</v>
+        <v>220</v>
       </c>
       <c r="F278" s="1">
         <v>46255</v>
@@ -9311,10 +9326,10 @@
         <v>80</v>
       </c>
       <c r="D279" t="s">
-        <v>16</v>
+        <v>597</v>
       </c>
       <c r="E279" t="s">
-        <v>17</v>
+        <v>598</v>
       </c>
       <c r="F279" s="1">
         <v>46255</v>
@@ -9328,16 +9343,16 @@
         <v>0</v>
       </c>
       <c r="B280" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="C280" t="s">
         <v>80</v>
       </c>
       <c r="D280" t="s">
-        <v>337</v>
+        <v>16</v>
       </c>
       <c r="E280" t="s">
-        <v>338</v>
+        <v>17</v>
       </c>
       <c r="F280" s="1">
         <v>46255</v>
@@ -9351,16 +9366,16 @@
         <v>0</v>
       </c>
       <c r="B281" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="C281" t="s">
         <v>80</v>
       </c>
       <c r="D281" t="s">
-        <v>435</v>
+        <v>340</v>
       </c>
       <c r="E281" t="s">
-        <v>436</v>
+        <v>341</v>
       </c>
       <c r="F281" s="1">
         <v>46255</v>
@@ -9374,16 +9389,16 @@
         <v>0</v>
       </c>
       <c r="B282" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="C282" t="s">
         <v>80</v>
       </c>
       <c r="D282" t="s">
-        <v>600</v>
+        <v>438</v>
       </c>
       <c r="E282" t="s">
-        <v>601</v>
+        <v>439</v>
       </c>
       <c r="F282" s="1">
         <v>46255</v>
@@ -9403,10 +9418,10 @@
         <v>80</v>
       </c>
       <c r="D283" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="E283" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="F283" s="1">
         <v>46255</v>
@@ -9420,16 +9435,16 @@
         <v>0</v>
       </c>
       <c r="B284" t="s">
+        <v>605</v>
+      </c>
+      <c r="C284" t="s">
+        <v>80</v>
+      </c>
+      <c r="D284" t="s">
         <v>603</v>
       </c>
-      <c r="C284" t="s">
-        <v>80</v>
-      </c>
-      <c r="D284" t="s">
+      <c r="E284" t="s">
         <v>604</v>
-      </c>
-      <c r="E284" t="s">
-        <v>605</v>
       </c>
       <c r="F284" s="1">
         <v>46255</v>
@@ -9449,10 +9464,10 @@
         <v>80</v>
       </c>
       <c r="D285" t="s">
-        <v>422</v>
+        <v>607</v>
       </c>
       <c r="E285" t="s">
-        <v>423</v>
+        <v>608</v>
       </c>
       <c r="F285" s="1">
         <v>46255</v>
@@ -9466,16 +9481,16 @@
         <v>0</v>
       </c>
       <c r="B286" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="C286" t="s">
         <v>80</v>
       </c>
       <c r="D286" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="E286" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="F286" s="1">
         <v>46255</v>
@@ -9489,16 +9504,16 @@
         <v>0</v>
       </c>
       <c r="B287" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="C287" t="s">
         <v>80</v>
       </c>
       <c r="D287" t="s">
-        <v>367</v>
+        <v>425</v>
       </c>
       <c r="E287" t="s">
-        <v>368</v>
+        <v>426</v>
       </c>
       <c r="F287" s="1">
         <v>46255</v>
@@ -9512,16 +9527,16 @@
         <v>0</v>
       </c>
       <c r="B288" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="C288" t="s">
         <v>80</v>
       </c>
       <c r="D288" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="E288" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="F288" s="1">
         <v>46255</v>
@@ -9535,16 +9550,16 @@
         <v>0</v>
       </c>
       <c r="B289" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="C289" t="s">
         <v>80</v>
       </c>
       <c r="D289" t="s">
-        <v>611</v>
+        <v>370</v>
       </c>
       <c r="E289" t="s">
-        <v>612</v>
+        <v>371</v>
       </c>
       <c r="F289" s="1">
         <v>46255</v>
@@ -9564,10 +9579,10 @@
         <v>80</v>
       </c>
       <c r="D290" t="s">
-        <v>429</v>
+        <v>614</v>
       </c>
       <c r="E290" t="s">
-        <v>430</v>
+        <v>615</v>
       </c>
       <c r="F290" s="1">
         <v>46255</v>
@@ -9581,16 +9596,16 @@
         <v>0</v>
       </c>
       <c r="B291" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="C291" t="s">
         <v>80</v>
       </c>
       <c r="D291" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="E291" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="F291" s="1">
         <v>46255</v>
@@ -9604,16 +9619,16 @@
         <v>0</v>
       </c>
       <c r="B292" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="C292" t="s">
         <v>80</v>
       </c>
       <c r="D292" t="s">
-        <v>348</v>
+        <v>432</v>
       </c>
       <c r="E292" t="s">
-        <v>349</v>
+        <v>433</v>
       </c>
       <c r="F292" s="1">
         <v>46255</v>
@@ -9627,16 +9642,16 @@
         <v>0</v>
       </c>
       <c r="B293" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="C293" t="s">
         <v>80</v>
       </c>
       <c r="D293" t="s">
-        <v>617</v>
+        <v>351</v>
       </c>
       <c r="E293" t="s">
-        <v>618</v>
+        <v>352</v>
       </c>
       <c r="F293" s="1">
         <v>46255</v>
@@ -9656,10 +9671,10 @@
         <v>80</v>
       </c>
       <c r="D294" t="s">
-        <v>7</v>
+        <v>620</v>
       </c>
       <c r="E294" t="s">
-        <v>8</v>
+        <v>621</v>
       </c>
       <c r="F294" s="1">
         <v>46255</v>
@@ -9673,16 +9688,16 @@
         <v>0</v>
       </c>
       <c r="B295" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="C295" t="s">
         <v>80</v>
       </c>
       <c r="D295" t="s">
-        <v>101</v>
+        <v>7</v>
       </c>
       <c r="E295" t="s">
-        <v>102</v>
+        <v>8</v>
       </c>
       <c r="F295" s="1">
         <v>46255</v>
@@ -9696,16 +9711,16 @@
         <v>0</v>
       </c>
       <c r="B296" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="C296" t="s">
         <v>80</v>
       </c>
       <c r="D296" t="s">
-        <v>381</v>
+        <v>101</v>
       </c>
       <c r="E296" t="s">
-        <v>382</v>
+        <v>102</v>
       </c>
       <c r="F296" s="1">
         <v>46255</v>
@@ -9719,16 +9734,16 @@
         <v>0</v>
       </c>
       <c r="B297" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="C297" t="s">
         <v>80</v>
       </c>
       <c r="D297" t="s">
-        <v>600</v>
+        <v>384</v>
       </c>
       <c r="E297" t="s">
-        <v>601</v>
+        <v>385</v>
       </c>
       <c r="F297" s="1">
         <v>46255</v>
@@ -9742,16 +9757,16 @@
         <v>0</v>
       </c>
       <c r="B298" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="C298" t="s">
         <v>80</v>
       </c>
       <c r="D298" t="s">
-        <v>381</v>
+        <v>603</v>
       </c>
       <c r="E298" t="s">
-        <v>382</v>
+        <v>604</v>
       </c>
       <c r="F298" s="1">
         <v>46255</v>
@@ -9765,16 +9780,16 @@
         <v>0</v>
       </c>
       <c r="B299" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="C299" t="s">
         <v>80</v>
       </c>
       <c r="D299" t="s">
-        <v>625</v>
+        <v>384</v>
       </c>
       <c r="E299" t="s">
-        <v>626</v>
+        <v>385</v>
       </c>
       <c r="F299" s="1">
         <v>46255</v>
@@ -9794,10 +9809,10 @@
         <v>80</v>
       </c>
       <c r="D300" t="s">
-        <v>224</v>
+        <v>628</v>
       </c>
       <c r="E300" t="s">
-        <v>225</v>
+        <v>629</v>
       </c>
       <c r="F300" s="1">
         <v>46255</v>
@@ -9811,16 +9826,16 @@
         <v>0</v>
       </c>
       <c r="B301" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="C301" t="s">
         <v>80</v>
       </c>
       <c r="D301" t="s">
-        <v>74</v>
+        <v>224</v>
       </c>
       <c r="E301" t="s">
-        <v>75</v>
+        <v>225</v>
       </c>
       <c r="F301" s="1">
         <v>46255</v>
@@ -9834,16 +9849,16 @@
         <v>0</v>
       </c>
       <c r="B302" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="C302" t="s">
         <v>80</v>
       </c>
       <c r="D302" t="s">
-        <v>630</v>
+        <v>74</v>
       </c>
       <c r="E302" t="s">
-        <v>631</v>
+        <v>75</v>
       </c>
       <c r="F302" s="1">
         <v>46255</v>
@@ -9886,10 +9901,10 @@
         <v>80</v>
       </c>
       <c r="D304" t="s">
-        <v>373</v>
+        <v>636</v>
       </c>
       <c r="E304" t="s">
-        <v>374</v>
+        <v>637</v>
       </c>
       <c r="F304" s="1">
         <v>46255</v>
@@ -9903,16 +9918,16 @@
         <v>0</v>
       </c>
       <c r="B305" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="C305" t="s">
         <v>80</v>
       </c>
       <c r="D305" t="s">
-        <v>48</v>
+        <v>376</v>
       </c>
       <c r="E305" t="s">
-        <v>49</v>
+        <v>377</v>
       </c>
       <c r="F305" s="1">
         <v>46255</v>
@@ -9926,16 +9941,16 @@
         <v>0</v>
       </c>
       <c r="B306" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="C306" t="s">
         <v>80</v>
       </c>
       <c r="D306" t="s">
-        <v>373</v>
+        <v>48</v>
       </c>
       <c r="E306" t="s">
-        <v>374</v>
+        <v>49</v>
       </c>
       <c r="F306" s="1">
         <v>46255</v>
@@ -9949,16 +9964,16 @@
         <v>0</v>
       </c>
       <c r="B307" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="C307" t="s">
         <v>80</v>
       </c>
       <c r="D307" t="s">
-        <v>639</v>
+        <v>376</v>
       </c>
       <c r="E307" t="s">
-        <v>640</v>
+        <v>377</v>
       </c>
       <c r="F307" s="1">
         <v>46255</v>
@@ -9978,10 +9993,10 @@
         <v>80</v>
       </c>
       <c r="D308" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="E308" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="F308" s="1">
         <v>46255</v>
@@ -9995,16 +10010,16 @@
         <v>0</v>
       </c>
       <c r="B309" t="s">
+        <v>644</v>
+      </c>
+      <c r="C309" t="s">
+        <v>80</v>
+      </c>
+      <c r="D309" t="s">
         <v>642</v>
       </c>
-      <c r="C309" t="s">
-        <v>80</v>
-      </c>
-      <c r="D309" t="s">
-        <v>373</v>
-      </c>
       <c r="E309" t="s">
-        <v>374</v>
+        <v>643</v>
       </c>
       <c r="F309" s="1">
         <v>46255</v>
@@ -10018,16 +10033,16 @@
         <v>0</v>
       </c>
       <c r="B310" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="C310" t="s">
         <v>80</v>
       </c>
       <c r="D310" t="s">
-        <v>644</v>
+        <v>376</v>
       </c>
       <c r="E310" t="s">
-        <v>645</v>
+        <v>377</v>
       </c>
       <c r="F310" s="1">
         <v>46255</v>
@@ -10070,10 +10085,10 @@
         <v>80</v>
       </c>
       <c r="D312" t="s">
-        <v>101</v>
+        <v>650</v>
       </c>
       <c r="E312" t="s">
-        <v>102</v>
+        <v>651</v>
       </c>
       <c r="F312" s="1">
         <v>46255</v>
@@ -10087,16 +10102,16 @@
         <v>0</v>
       </c>
       <c r="B313" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="C313" t="s">
         <v>80</v>
       </c>
       <c r="D313" t="s">
-        <v>147</v>
+        <v>101</v>
       </c>
       <c r="E313" t="s">
-        <v>148</v>
+        <v>102</v>
       </c>
       <c r="F313" s="1">
         <v>46255</v>
@@ -10110,16 +10125,16 @@
         <v>0</v>
       </c>
       <c r="B314" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="C314" t="s">
         <v>80</v>
       </c>
       <c r="D314" t="s">
-        <v>355</v>
+        <v>147</v>
       </c>
       <c r="E314" t="s">
-        <v>356</v>
+        <v>148</v>
       </c>
       <c r="F314" s="1">
         <v>46255</v>
@@ -10133,22 +10148,22 @@
         <v>0</v>
       </c>
       <c r="B315" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="C315" t="s">
         <v>80</v>
       </c>
       <c r="D315" t="s">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="E315" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="F315" s="1">
         <v>46255</v>
       </c>
       <c r="G315" s="1">
-        <v>46255</v>
+        <v>46256</v>
       </c>
     </row>
     <row r="316" spans="1:7" x14ac:dyDescent="0.2">
@@ -10162,10 +10177,10 @@
         <v>80</v>
       </c>
       <c r="D316" t="s">
-        <v>138</v>
+        <v>358</v>
       </c>
       <c r="E316" t="s">
-        <v>139</v>
+        <v>359</v>
       </c>
       <c r="F316" s="1">
         <v>46255</v>
@@ -10185,16 +10200,16 @@
         <v>80</v>
       </c>
       <c r="D317" t="s">
-        <v>653</v>
+        <v>16</v>
       </c>
       <c r="E317" t="s">
-        <v>654</v>
+        <v>17</v>
       </c>
       <c r="F317" s="1">
         <v>46255</v>
       </c>
       <c r="G317" s="1">
-        <v>46255</v>
+        <v>46256</v>
       </c>
     </row>
     <row r="318" spans="1:7" x14ac:dyDescent="0.2">
@@ -10208,10 +10223,10 @@
         <v>80</v>
       </c>
       <c r="D318" t="s">
-        <v>355</v>
+        <v>658</v>
       </c>
       <c r="E318" t="s">
-        <v>356</v>
+        <v>659</v>
       </c>
       <c r="F318" s="1">
         <v>46255</v>
@@ -10225,16 +10240,16 @@
         <v>0</v>
       </c>
       <c r="B319" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="C319" t="s">
         <v>80</v>
       </c>
       <c r="D319" t="s">
-        <v>659</v>
+        <v>138</v>
       </c>
       <c r="E319" t="s">
-        <v>660</v>
+        <v>139</v>
       </c>
       <c r="F319" s="1">
         <v>46255</v>
@@ -10254,10 +10269,10 @@
         <v>80</v>
       </c>
       <c r="D320" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="E320" t="s">
-        <v>663</v>
+        <v>659</v>
       </c>
       <c r="F320" s="1">
         <v>46255</v>
@@ -10271,16 +10286,16 @@
         <v>0</v>
       </c>
       <c r="B321" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="C321" t="s">
         <v>80</v>
       </c>
       <c r="D321" t="s">
-        <v>181</v>
+        <v>358</v>
       </c>
       <c r="E321" t="s">
-        <v>182</v>
+        <v>359</v>
       </c>
       <c r="F321" s="1">
         <v>46255</v>
@@ -10294,22 +10309,22 @@
         <v>0</v>
       </c>
       <c r="B322" t="s">
+        <v>663</v>
+      </c>
+      <c r="C322" t="s">
+        <v>80</v>
+      </c>
+      <c r="D322" t="s">
+        <v>664</v>
+      </c>
+      <c r="E322" t="s">
         <v>665</v>
       </c>
-      <c r="C322" t="s">
-        <v>80</v>
-      </c>
-      <c r="D322" t="s">
-        <v>666</v>
-      </c>
-      <c r="E322" t="s">
-        <v>667</v>
-      </c>
       <c r="F322" s="1">
         <v>46255</v>
       </c>
       <c r="G322" s="1">
-        <v>46256</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="323" spans="1:7" x14ac:dyDescent="0.2">
@@ -10317,16 +10332,16 @@
         <v>0</v>
       </c>
       <c r="B323" t="s">
+        <v>666</v>
+      </c>
+      <c r="C323" t="s">
+        <v>80</v>
+      </c>
+      <c r="D323" t="s">
+        <v>667</v>
+      </c>
+      <c r="E323" t="s">
         <v>668</v>
-      </c>
-      <c r="C323" t="s">
-        <v>80</v>
-      </c>
-      <c r="D323" t="s">
-        <v>666</v>
-      </c>
-      <c r="E323" t="s">
-        <v>667</v>
       </c>
       <c r="F323" s="1">
         <v>46255</v>
@@ -10346,10 +10361,10 @@
         <v>80</v>
       </c>
       <c r="D324" t="s">
-        <v>670</v>
+        <v>181</v>
       </c>
       <c r="E324" t="s">
-        <v>671</v>
+        <v>182</v>
       </c>
       <c r="F324" s="1">
         <v>46255</v>
@@ -10363,22 +10378,22 @@
         <v>0</v>
       </c>
       <c r="B325" t="s">
+        <v>670</v>
+      </c>
+      <c r="C325" t="s">
+        <v>80</v>
+      </c>
+      <c r="D325" t="s">
+        <v>671</v>
+      </c>
+      <c r="E325" t="s">
         <v>672</v>
       </c>
-      <c r="C325" t="s">
-        <v>80</v>
-      </c>
-      <c r="D325" t="s">
-        <v>673</v>
-      </c>
-      <c r="E325" t="s">
-        <v>674</v>
-      </c>
       <c r="F325" s="1">
         <v>46255</v>
       </c>
       <c r="G325" s="1">
-        <v>46255</v>
+        <v>46256</v>
       </c>
     </row>
     <row r="326" spans="1:7" x14ac:dyDescent="0.2">
@@ -10386,16 +10401,16 @@
         <v>0</v>
       </c>
       <c r="B326" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="C326" t="s">
         <v>80</v>
       </c>
       <c r="D326" t="s">
-        <v>676</v>
+        <v>671</v>
       </c>
       <c r="E326" t="s">
-        <v>677</v>
+        <v>672</v>
       </c>
       <c r="F326" s="1">
         <v>46255</v>
@@ -10409,16 +10424,16 @@
         <v>0</v>
       </c>
       <c r="B327" t="s">
-        <v>678</v>
+        <v>674</v>
       </c>
       <c r="C327" t="s">
         <v>80</v>
       </c>
       <c r="D327" t="s">
-        <v>337</v>
+        <v>675</v>
       </c>
       <c r="E327" t="s">
-        <v>338</v>
+        <v>676</v>
       </c>
       <c r="F327" s="1">
         <v>46255</v>
@@ -10432,16 +10447,16 @@
         <v>0</v>
       </c>
       <c r="B328" t="s">
+        <v>677</v>
+      </c>
+      <c r="C328" t="s">
+        <v>80</v>
+      </c>
+      <c r="D328" t="s">
+        <v>678</v>
+      </c>
+      <c r="E328" t="s">
         <v>679</v>
-      </c>
-      <c r="C328" t="s">
-        <v>80</v>
-      </c>
-      <c r="D328" t="s">
-        <v>680</v>
-      </c>
-      <c r="E328" t="s">
-        <v>681</v>
       </c>
       <c r="F328" s="1">
         <v>46255</v>
@@ -10455,16 +10470,16 @@
         <v>0</v>
       </c>
       <c r="B329" t="s">
+        <v>680</v>
+      </c>
+      <c r="C329" t="s">
+        <v>80</v>
+      </c>
+      <c r="D329" t="s">
+        <v>681</v>
+      </c>
+      <c r="E329" t="s">
         <v>682</v>
-      </c>
-      <c r="C329" t="s">
-        <v>80</v>
-      </c>
-      <c r="D329" t="s">
-        <v>680</v>
-      </c>
-      <c r="E329" t="s">
-        <v>681</v>
       </c>
       <c r="F329" s="1">
         <v>46255</v>
@@ -10484,10 +10499,10 @@
         <v>80</v>
       </c>
       <c r="D330" t="s">
-        <v>684</v>
+        <v>340</v>
       </c>
       <c r="E330" t="s">
-        <v>685</v>
+        <v>341</v>
       </c>
       <c r="F330" s="1">
         <v>46255</v>
@@ -10501,16 +10516,16 @@
         <v>0</v>
       </c>
       <c r="B331" t="s">
+        <v>684</v>
+      </c>
+      <c r="C331" t="s">
+        <v>80</v>
+      </c>
+      <c r="D331" t="s">
+        <v>685</v>
+      </c>
+      <c r="E331" t="s">
         <v>686</v>
-      </c>
-      <c r="C331" t="s">
-        <v>80</v>
-      </c>
-      <c r="D331" t="s">
-        <v>687</v>
-      </c>
-      <c r="E331" t="s">
-        <v>688</v>
       </c>
       <c r="F331" s="1">
         <v>46255</v>
@@ -10524,16 +10539,16 @@
         <v>0</v>
       </c>
       <c r="B332" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="C332" t="s">
         <v>80</v>
       </c>
       <c r="D332" t="s">
-        <v>690</v>
+        <v>685</v>
       </c>
       <c r="E332" t="s">
-        <v>691</v>
+        <v>686</v>
       </c>
       <c r="F332" s="1">
         <v>46255</v>
@@ -10547,16 +10562,16 @@
         <v>0</v>
       </c>
       <c r="B333" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="C333" t="s">
         <v>80</v>
       </c>
       <c r="D333" t="s">
-        <v>138</v>
+        <v>689</v>
       </c>
       <c r="E333" t="s">
-        <v>139</v>
+        <v>690</v>
       </c>
       <c r="F333" s="1">
         <v>46255</v>
@@ -10570,16 +10585,16 @@
         <v>0</v>
       </c>
       <c r="B334" t="s">
+        <v>691</v>
+      </c>
+      <c r="C334" t="s">
+        <v>80</v>
+      </c>
+      <c r="D334" t="s">
+        <v>692</v>
+      </c>
+      <c r="E334" t="s">
         <v>693</v>
-      </c>
-      <c r="C334" t="s">
-        <v>80</v>
-      </c>
-      <c r="D334" t="s">
-        <v>98</v>
-      </c>
-      <c r="E334" t="s">
-        <v>99</v>
       </c>
       <c r="F334" s="1">
         <v>46255</v>
@@ -10599,10 +10614,10 @@
         <v>80</v>
       </c>
       <c r="D335" t="s">
-        <v>594</v>
+        <v>695</v>
       </c>
       <c r="E335" t="s">
-        <v>595</v>
+        <v>696</v>
       </c>
       <c r="F335" s="1">
         <v>46255</v>
@@ -10616,16 +10631,16 @@
         <v>0</v>
       </c>
       <c r="B336" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="C336" t="s">
         <v>80</v>
       </c>
       <c r="D336" t="s">
-        <v>25</v>
+        <v>138</v>
       </c>
       <c r="E336" t="s">
-        <v>26</v>
+        <v>139</v>
       </c>
       <c r="F336" s="1">
         <v>46255</v>
@@ -10639,16 +10654,16 @@
         <v>0</v>
       </c>
       <c r="B337" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="C337" t="s">
         <v>80</v>
       </c>
       <c r="D337" t="s">
-        <v>37</v>
+        <v>98</v>
       </c>
       <c r="E337" t="s">
-        <v>38</v>
+        <v>99</v>
       </c>
       <c r="F337" s="1">
         <v>46255</v>
@@ -10662,16 +10677,16 @@
         <v>0</v>
       </c>
       <c r="B338" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="C338" t="s">
         <v>80</v>
       </c>
       <c r="D338" t="s">
-        <v>351</v>
+        <v>597</v>
       </c>
       <c r="E338" t="s">
-        <v>352</v>
+        <v>598</v>
       </c>
       <c r="F338" s="1">
         <v>46255</v>
@@ -10685,16 +10700,16 @@
         <v>0</v>
       </c>
       <c r="B339" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="C339" t="s">
         <v>80</v>
       </c>
       <c r="D339" t="s">
-        <v>699</v>
+        <v>25</v>
       </c>
       <c r="E339" t="s">
-        <v>700</v>
+        <v>26</v>
       </c>
       <c r="F339" s="1">
         <v>46255</v>
@@ -10714,10 +10729,10 @@
         <v>80</v>
       </c>
       <c r="D340" t="s">
-        <v>702</v>
+        <v>37</v>
       </c>
       <c r="E340" t="s">
-        <v>703</v>
+        <v>38</v>
       </c>
       <c r="F340" s="1">
         <v>46255</v>
@@ -10731,16 +10746,16 @@
         <v>0</v>
       </c>
       <c r="B341" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="C341" t="s">
         <v>80</v>
       </c>
       <c r="D341" t="s">
-        <v>400</v>
+        <v>354</v>
       </c>
       <c r="E341" t="s">
-        <v>401</v>
+        <v>355</v>
       </c>
       <c r="F341" s="1">
         <v>46255</v>
@@ -10754,16 +10769,16 @@
         <v>0</v>
       </c>
       <c r="B342" t="s">
+        <v>703</v>
+      </c>
+      <c r="C342" t="s">
+        <v>80</v>
+      </c>
+      <c r="D342" t="s">
+        <v>704</v>
+      </c>
+      <c r="E342" t="s">
         <v>705</v>
-      </c>
-      <c r="C342" t="s">
-        <v>80</v>
-      </c>
-      <c r="D342" t="s">
-        <v>706</v>
-      </c>
-      <c r="E342" t="s">
-        <v>707</v>
       </c>
       <c r="F342" s="1">
         <v>46255</v>
@@ -10777,16 +10792,16 @@
         <v>0</v>
       </c>
       <c r="B343" t="s">
+        <v>706</v>
+      </c>
+      <c r="C343" t="s">
+        <v>80</v>
+      </c>
+      <c r="D343" t="s">
+        <v>707</v>
+      </c>
+      <c r="E343" t="s">
         <v>708</v>
-      </c>
-      <c r="C343" t="s">
-        <v>80</v>
-      </c>
-      <c r="D343" t="s">
-        <v>526</v>
-      </c>
-      <c r="E343" t="s">
-        <v>527</v>
       </c>
       <c r="F343" s="1">
         <v>46255</v>
@@ -10806,10 +10821,10 @@
         <v>80</v>
       </c>
       <c r="D344" t="s">
-        <v>710</v>
+        <v>403</v>
       </c>
       <c r="E344" t="s">
-        <v>711</v>
+        <v>404</v>
       </c>
       <c r="F344" s="1">
         <v>46255</v>
@@ -10823,16 +10838,16 @@
         <v>0</v>
       </c>
       <c r="B345" t="s">
+        <v>710</v>
+      </c>
+      <c r="C345" t="s">
+        <v>80</v>
+      </c>
+      <c r="D345" t="s">
+        <v>711</v>
+      </c>
+      <c r="E345" t="s">
         <v>712</v>
-      </c>
-      <c r="C345" t="s">
-        <v>80</v>
-      </c>
-      <c r="D345" t="s">
-        <v>403</v>
-      </c>
-      <c r="E345" t="s">
-        <v>404</v>
       </c>
       <c r="F345" s="1">
         <v>46255</v>
@@ -10852,10 +10867,10 @@
         <v>80</v>
       </c>
       <c r="D346" t="s">
-        <v>714</v>
+        <v>529</v>
       </c>
       <c r="E346" t="s">
-        <v>715</v>
+        <v>530</v>
       </c>
       <c r="F346" s="1">
         <v>46255</v>
@@ -10869,16 +10884,16 @@
         <v>0</v>
       </c>
       <c r="B347" t="s">
+        <v>714</v>
+      </c>
+      <c r="C347" t="s">
+        <v>80</v>
+      </c>
+      <c r="D347" t="s">
+        <v>715</v>
+      </c>
+      <c r="E347" t="s">
         <v>716</v>
-      </c>
-      <c r="C347" t="s">
-        <v>80</v>
-      </c>
-      <c r="D347" t="s">
-        <v>16</v>
-      </c>
-      <c r="E347" t="s">
-        <v>17</v>
       </c>
       <c r="F347" s="1">
         <v>46255</v>
@@ -10889,260 +10904,260 @@
     </row>
     <row r="348" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A348" t="s">
+        <v>0</v>
+      </c>
+      <c r="B348" t="s">
         <v>717</v>
       </c>
-      <c r="B348" t="s">
-        <v>718</v>
-      </c>
       <c r="C348" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D348" t="s">
-        <v>348</v>
+        <v>406</v>
       </c>
       <c r="E348" t="s">
-        <v>349</v>
+        <v>407</v>
       </c>
       <c r="F348" s="1">
-        <v>46148</v>
+        <v>46255</v>
       </c>
       <c r="G348" s="1">
-        <v>46149</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="349" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A349" t="s">
+        <v>0</v>
+      </c>
+      <c r="B349" t="s">
+        <v>718</v>
+      </c>
+      <c r="C349" t="s">
+        <v>80</v>
+      </c>
+      <c r="D349" t="s">
         <v>719</v>
       </c>
-      <c r="B349" t="s">
+      <c r="E349" t="s">
         <v>720</v>
       </c>
-      <c r="C349" t="s">
-        <v>6</v>
-      </c>
-      <c r="D349" t="s">
-        <v>41</v>
-      </c>
-      <c r="E349" t="s">
-        <v>42</v>
-      </c>
       <c r="F349" s="1">
-        <v>46133</v>
+        <v>46255</v>
       </c>
       <c r="G349" s="1">
-        <v>46134</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="350" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A350" t="s">
-        <v>719</v>
+        <v>0</v>
       </c>
       <c r="B350" t="s">
         <v>721</v>
       </c>
       <c r="C350" t="s">
-        <v>6</v>
+        <v>80</v>
       </c>
       <c r="D350" t="s">
-        <v>41</v>
+        <v>16</v>
       </c>
       <c r="E350" t="s">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="F350" s="1">
-        <v>46134</v>
+        <v>46255</v>
       </c>
       <c r="G350" s="1">
-        <v>46134</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="351" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A351" t="s">
-        <v>719</v>
+        <v>722</v>
       </c>
       <c r="B351" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="C351" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D351" t="s">
-        <v>19</v>
+        <v>351</v>
       </c>
       <c r="E351" t="s">
-        <v>20</v>
+        <v>352</v>
       </c>
       <c r="F351" s="1">
-        <v>46156</v>
+        <v>46148</v>
       </c>
       <c r="G351" s="1">
-        <v>46156</v>
+        <v>46149</v>
       </c>
     </row>
     <row r="352" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A352" t="s">
-        <v>719</v>
+        <v>724</v>
       </c>
       <c r="B352" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="C352" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D352" t="s">
-        <v>724</v>
+        <v>41</v>
       </c>
       <c r="E352" t="s">
-        <v>725</v>
+        <v>42</v>
       </c>
       <c r="F352" s="1">
-        <v>46195</v>
+        <v>46133</v>
       </c>
       <c r="G352" s="1">
-        <v>46195</v>
+        <v>46134</v>
       </c>
     </row>
     <row r="353" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A353" t="s">
-        <v>719</v>
+        <v>724</v>
       </c>
       <c r="B353" t="s">
         <v>726</v>
       </c>
       <c r="C353" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D353" t="s">
-        <v>727</v>
+        <v>41</v>
       </c>
       <c r="E353" t="s">
-        <v>728</v>
+        <v>42</v>
       </c>
       <c r="F353" s="1">
-        <v>46206</v>
+        <v>46134</v>
       </c>
       <c r="G353" s="1">
-        <v>46252</v>
+        <v>46134</v>
       </c>
     </row>
     <row r="354" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A354" t="s">
-        <v>719</v>
+        <v>724</v>
       </c>
       <c r="B354" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="C354" t="s">
-        <v>96</v>
+        <v>6</v>
       </c>
       <c r="D354" t="s">
-        <v>730</v>
+        <v>19</v>
       </c>
       <c r="E354" t="s">
-        <v>731</v>
+        <v>20</v>
       </c>
       <c r="F354" s="1">
-        <v>46209</v>
+        <v>46156</v>
       </c>
       <c r="G354" s="1">
-        <v>46218</v>
+        <v>46156</v>
       </c>
     </row>
     <row r="355" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A355" t="s">
-        <v>719</v>
+        <v>724</v>
       </c>
       <c r="B355" t="s">
-        <v>732</v>
+        <v>728</v>
       </c>
       <c r="C355" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D355" t="s">
-        <v>733</v>
+        <v>729</v>
       </c>
       <c r="E355" t="s">
-        <v>734</v>
+        <v>730</v>
       </c>
       <c r="F355" s="1">
-        <v>46213</v>
+        <v>46195</v>
       </c>
       <c r="G355" s="1">
-        <v>46213</v>
+        <v>46195</v>
       </c>
     </row>
     <row r="356" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A356" t="s">
-        <v>719</v>
+        <v>724</v>
       </c>
       <c r="B356" t="s">
-        <v>735</v>
+        <v>731</v>
       </c>
       <c r="C356" t="s">
-        <v>96</v>
+        <v>2</v>
       </c>
       <c r="D356" t="s">
-        <v>736</v>
+        <v>732</v>
       </c>
       <c r="E356" t="s">
-        <v>737</v>
+        <v>733</v>
       </c>
       <c r="F356" s="1">
-        <v>46213</v>
+        <v>46206</v>
       </c>
       <c r="G356" s="1">
-        <v>46216</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="357" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A357" t="s">
-        <v>719</v>
+        <v>724</v>
       </c>
       <c r="B357" t="s">
-        <v>738</v>
+        <v>734</v>
       </c>
       <c r="C357" t="s">
-        <v>2</v>
+        <v>96</v>
       </c>
       <c r="D357" t="s">
-        <v>133</v>
+        <v>735</v>
       </c>
       <c r="E357" t="s">
-        <v>134</v>
+        <v>736</v>
       </c>
       <c r="F357" s="1">
-        <v>46220</v>
+        <v>46209</v>
       </c>
       <c r="G357" s="1">
-        <v>46231</v>
+        <v>46218</v>
       </c>
     </row>
     <row r="358" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A358" t="s">
-        <v>719</v>
+        <v>724</v>
       </c>
       <c r="B358" t="s">
+        <v>737</v>
+      </c>
+      <c r="C358" t="s">
+        <v>6</v>
+      </c>
+      <c r="D358" t="s">
+        <v>738</v>
+      </c>
+      <c r="E358" t="s">
         <v>739</v>
       </c>
-      <c r="C358" t="s">
-        <v>2</v>
-      </c>
-      <c r="D358" t="s">
-        <v>724</v>
-      </c>
-      <c r="E358" t="s">
-        <v>725</v>
-      </c>
       <c r="F358" s="1">
-        <v>46223</v>
+        <v>46213</v>
       </c>
       <c r="G358" s="1">
-        <v>46223</v>
+        <v>46213</v>
       </c>
     </row>
     <row r="359" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A359" t="s">
-        <v>719</v>
+        <v>724</v>
       </c>
       <c r="B359" t="s">
         <v>740</v>
@@ -11151,36 +11166,36 @@
         <v>96</v>
       </c>
       <c r="D359" t="s">
-        <v>736</v>
+        <v>741</v>
       </c>
       <c r="E359" t="s">
-        <v>737</v>
+        <v>742</v>
       </c>
       <c r="F359" s="1">
-        <v>46224</v>
+        <v>46213</v>
       </c>
       <c r="G359" s="1">
-        <v>46224</v>
+        <v>46216</v>
       </c>
     </row>
     <row r="360" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A360" t="s">
-        <v>719</v>
+        <v>724</v>
       </c>
       <c r="B360" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="C360" t="s">
         <v>2</v>
       </c>
       <c r="D360" t="s">
-        <v>724</v>
+        <v>133</v>
       </c>
       <c r="E360" t="s">
-        <v>725</v>
+        <v>134</v>
       </c>
       <c r="F360" s="1">
-        <v>46230</v>
+        <v>46220</v>
       </c>
       <c r="G360" s="1">
         <v>46231</v>
@@ -11188,122 +11203,122 @@
     </row>
     <row r="361" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A361" t="s">
-        <v>719</v>
+        <v>724</v>
       </c>
       <c r="B361" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="C361" t="s">
         <v>2</v>
       </c>
       <c r="D361" t="s">
-        <v>133</v>
+        <v>729</v>
       </c>
       <c r="E361" t="s">
-        <v>134</v>
+        <v>730</v>
       </c>
       <c r="F361" s="1">
-        <v>46232</v>
+        <v>46223</v>
       </c>
       <c r="G361" s="1">
-        <v>46233</v>
+        <v>46223</v>
       </c>
     </row>
     <row r="362" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A362" t="s">
-        <v>719</v>
+        <v>724</v>
       </c>
       <c r="B362" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="C362" t="s">
-        <v>2</v>
+        <v>96</v>
       </c>
       <c r="D362" t="s">
-        <v>133</v>
+        <v>741</v>
       </c>
       <c r="E362" t="s">
-        <v>134</v>
+        <v>742</v>
       </c>
       <c r="F362" s="1">
-        <v>46232</v>
+        <v>46224</v>
       </c>
       <c r="G362" s="1">
-        <v>46233</v>
+        <v>46224</v>
       </c>
     </row>
     <row r="363" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A363" t="s">
-        <v>719</v>
+        <v>724</v>
       </c>
       <c r="B363" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="C363" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D363" t="s">
-        <v>736</v>
+        <v>729</v>
       </c>
       <c r="E363" t="s">
-        <v>737</v>
+        <v>730</v>
       </c>
       <c r="F363" s="1">
-        <v>46238</v>
+        <v>46230</v>
       </c>
       <c r="G363" s="1">
-        <v>46239</v>
+        <v>46256</v>
       </c>
     </row>
     <row r="364" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A364" t="s">
-        <v>719</v>
+        <v>724</v>
       </c>
       <c r="B364" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="C364" t="s">
         <v>2</v>
       </c>
       <c r="D364" t="s">
-        <v>41</v>
+        <v>133</v>
       </c>
       <c r="E364" t="s">
-        <v>42</v>
+        <v>134</v>
       </c>
       <c r="F364" s="1">
-        <v>46247</v>
+        <v>46232</v>
       </c>
       <c r="G364" s="1">
-        <v>46252</v>
+        <v>46233</v>
       </c>
     </row>
     <row r="365" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A365" t="s">
-        <v>719</v>
+        <v>724</v>
       </c>
       <c r="B365" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="C365" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D365" t="s">
-        <v>747</v>
+        <v>133</v>
       </c>
       <c r="E365" t="s">
-        <v>748</v>
+        <v>134</v>
       </c>
       <c r="F365" s="1">
-        <v>46253</v>
+        <v>46232</v>
       </c>
       <c r="G365" s="1">
-        <v>46253</v>
+        <v>46233</v>
       </c>
     </row>
     <row r="366" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A366" t="s">
-        <v>719</v>
+        <v>724</v>
       </c>
       <c r="B366" t="s">
         <v>749</v>
@@ -11312,82 +11327,82 @@
         <v>2</v>
       </c>
       <c r="D366" t="s">
-        <v>736</v>
+        <v>741</v>
       </c>
       <c r="E366" t="s">
-        <v>737</v>
+        <v>742</v>
       </c>
       <c r="F366" s="1">
-        <v>46253</v>
+        <v>46238</v>
       </c>
       <c r="G366" s="1">
-        <v>46254</v>
+        <v>46239</v>
       </c>
     </row>
     <row r="367" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A367" t="s">
-        <v>719</v>
+        <v>724</v>
       </c>
       <c r="B367" t="s">
         <v>750</v>
       </c>
       <c r="C367" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D367" t="s">
-        <v>472</v>
+        <v>41</v>
       </c>
       <c r="E367" t="s">
-        <v>473</v>
+        <v>42</v>
       </c>
       <c r="F367" s="1">
-        <v>46254</v>
+        <v>46247</v>
       </c>
       <c r="G367" s="1">
-        <v>46254</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="368" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A368" t="s">
-        <v>719</v>
+        <v>724</v>
       </c>
       <c r="B368" t="s">
         <v>751</v>
       </c>
       <c r="C368" t="s">
-        <v>80</v>
+        <v>6</v>
       </c>
       <c r="D368" t="s">
-        <v>736</v>
+        <v>752</v>
       </c>
       <c r="E368" t="s">
-        <v>737</v>
+        <v>753</v>
       </c>
       <c r="F368" s="1">
-        <v>46254</v>
+        <v>46253</v>
       </c>
       <c r="G368" s="1">
-        <v>46255</v>
+        <v>46253</v>
       </c>
     </row>
     <row r="369" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A369" t="s">
-        <v>719</v>
+        <v>724</v>
       </c>
       <c r="B369" t="s">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="C369" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D369" t="s">
-        <v>506</v>
+        <v>741</v>
       </c>
       <c r="E369" t="s">
-        <v>507</v>
+        <v>742</v>
       </c>
       <c r="F369" s="1">
-        <v>46254</v>
+        <v>46253</v>
       </c>
       <c r="G369" s="1">
         <v>46254</v>
@@ -11395,42 +11410,42 @@
     </row>
     <row r="370" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A370" t="s">
-        <v>719</v>
+        <v>724</v>
       </c>
       <c r="B370" t="s">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="C370" t="s">
         <v>80</v>
       </c>
       <c r="D370" t="s">
-        <v>141</v>
+        <v>475</v>
       </c>
       <c r="E370" t="s">
-        <v>142</v>
+        <v>476</v>
       </c>
       <c r="F370" s="1">
         <v>46254</v>
       </c>
       <c r="G370" s="1">
-        <v>46255</v>
+        <v>46254</v>
       </c>
     </row>
     <row r="371" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A371" t="s">
-        <v>719</v>
+        <v>724</v>
       </c>
       <c r="B371" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="C371" t="s">
         <v>80</v>
       </c>
       <c r="D371" t="s">
-        <v>156</v>
+        <v>741</v>
       </c>
       <c r="E371" t="s">
-        <v>157</v>
+        <v>742</v>
       </c>
       <c r="F371" s="1">
         <v>46254</v>
@@ -11441,42 +11456,42 @@
     </row>
     <row r="372" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A372" t="s">
-        <v>719</v>
+        <v>724</v>
       </c>
       <c r="B372" t="s">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="C372" t="s">
         <v>80</v>
       </c>
       <c r="D372" t="s">
-        <v>156</v>
+        <v>509</v>
       </c>
       <c r="E372" t="s">
-        <v>157</v>
+        <v>510</v>
       </c>
       <c r="F372" s="1">
         <v>46254</v>
       </c>
       <c r="G372" s="1">
-        <v>46255</v>
+        <v>46254</v>
       </c>
     </row>
     <row r="373" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A373" t="s">
-        <v>719</v>
+        <v>724</v>
       </c>
       <c r="B373" t="s">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="C373" t="s">
         <v>80</v>
       </c>
       <c r="D373" t="s">
-        <v>156</v>
+        <v>141</v>
       </c>
       <c r="E373" t="s">
-        <v>157</v>
+        <v>142</v>
       </c>
       <c r="F373" s="1">
         <v>46254</v>
@@ -11487,19 +11502,19 @@
     </row>
     <row r="374" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A374" t="s">
-        <v>719</v>
+        <v>724</v>
       </c>
       <c r="B374" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="C374" t="s">
         <v>80</v>
       </c>
       <c r="D374" t="s">
-        <v>571</v>
+        <v>156</v>
       </c>
       <c r="E374" t="s">
-        <v>572</v>
+        <v>157</v>
       </c>
       <c r="F374" s="1">
         <v>46254</v>
@@ -11510,19 +11525,19 @@
     </row>
     <row r="375" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A375" t="s">
-        <v>719</v>
+        <v>724</v>
       </c>
       <c r="B375" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="C375" t="s">
         <v>80</v>
       </c>
       <c r="D375" t="s">
-        <v>571</v>
+        <v>156</v>
       </c>
       <c r="E375" t="s">
-        <v>572</v>
+        <v>157</v>
       </c>
       <c r="F375" s="1">
         <v>46254</v>
@@ -11533,22 +11548,22 @@
     </row>
     <row r="376" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A376" t="s">
-        <v>719</v>
+        <v>724</v>
       </c>
       <c r="B376" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="C376" t="s">
         <v>80</v>
       </c>
       <c r="D376" t="s">
-        <v>373</v>
+        <v>156</v>
       </c>
       <c r="E376" t="s">
-        <v>374</v>
+        <v>157</v>
       </c>
       <c r="F376" s="1">
-        <v>46255</v>
+        <v>46254</v>
       </c>
       <c r="G376" s="1">
         <v>46255</v>
@@ -11556,22 +11571,22 @@
     </row>
     <row r="377" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A377" t="s">
-        <v>719</v>
+        <v>724</v>
       </c>
       <c r="B377" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="C377" t="s">
         <v>80</v>
       </c>
       <c r="D377" t="s">
-        <v>373</v>
+        <v>574</v>
       </c>
       <c r="E377" t="s">
-        <v>374</v>
+        <v>575</v>
       </c>
       <c r="F377" s="1">
-        <v>46255</v>
+        <v>46254</v>
       </c>
       <c r="G377" s="1">
         <v>46255</v>
@@ -11579,22 +11594,22 @@
     </row>
     <row r="378" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A378" t="s">
-        <v>719</v>
+        <v>724</v>
       </c>
       <c r="B378" t="s">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="C378" t="s">
         <v>80</v>
       </c>
       <c r="D378" t="s">
-        <v>762</v>
+        <v>574</v>
       </c>
       <c r="E378" t="s">
-        <v>763</v>
+        <v>575</v>
       </c>
       <c r="F378" s="1">
-        <v>46255</v>
+        <v>46254</v>
       </c>
       <c r="G378" s="1">
         <v>46255</v>
@@ -11602,105 +11617,105 @@
     </row>
     <row r="379" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A379" t="s">
+        <v>724</v>
+      </c>
+      <c r="B379" t="s">
         <v>764</v>
       </c>
-      <c r="B379" t="s">
-        <v>765</v>
-      </c>
       <c r="C379" t="s">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="D379" t="s">
-        <v>766</v>
+        <v>376</v>
       </c>
       <c r="E379" t="s">
-        <v>767</v>
+        <v>377</v>
       </c>
       <c r="F379" s="1">
-        <v>46063</v>
+        <v>46255</v>
       </c>
       <c r="G379" s="1">
-        <v>46064</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="380" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A380" t="s">
-        <v>764</v>
+        <v>724</v>
       </c>
       <c r="B380" t="s">
-        <v>768</v>
+        <v>765</v>
       </c>
       <c r="C380" t="s">
-        <v>6</v>
+        <v>80</v>
       </c>
       <c r="D380" t="s">
-        <v>57</v>
+        <v>376</v>
       </c>
       <c r="E380" t="s">
-        <v>58</v>
+        <v>377</v>
       </c>
       <c r="F380" s="1">
-        <v>46113</v>
+        <v>46255</v>
       </c>
       <c r="G380" s="1">
-        <v>46125</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="381" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A381" t="s">
-        <v>764</v>
+        <v>724</v>
       </c>
       <c r="B381" t="s">
-        <v>769</v>
+        <v>766</v>
       </c>
       <c r="C381" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D381" t="s">
-        <v>57</v>
+        <v>767</v>
       </c>
       <c r="E381" t="s">
-        <v>58</v>
+        <v>768</v>
       </c>
       <c r="F381" s="1">
-        <v>46125</v>
+        <v>46255</v>
       </c>
       <c r="G381" s="1">
-        <v>46125</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="382" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A382" t="s">
-        <v>764</v>
+        <v>769</v>
       </c>
       <c r="B382" t="s">
         <v>770</v>
       </c>
       <c r="C382" t="s">
-        <v>2</v>
+        <v>96</v>
       </c>
       <c r="D382" t="s">
-        <v>57</v>
+        <v>771</v>
       </c>
       <c r="E382" t="s">
-        <v>58</v>
+        <v>772</v>
       </c>
       <c r="F382" s="1">
-        <v>46126</v>
+        <v>46063</v>
       </c>
       <c r="G382" s="1">
-        <v>46126</v>
+        <v>46064</v>
       </c>
     </row>
     <row r="383" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A383" t="s">
-        <v>764</v>
+        <v>769</v>
       </c>
       <c r="B383" t="s">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="C383" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D383" t="s">
         <v>57</v>
@@ -11709,18 +11724,18 @@
         <v>58</v>
       </c>
       <c r="F383" s="1">
-        <v>46126</v>
+        <v>46113</v>
       </c>
       <c r="G383" s="1">
-        <v>46126</v>
+        <v>46125</v>
       </c>
     </row>
     <row r="384" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A384" t="s">
-        <v>764</v>
+        <v>769</v>
       </c>
       <c r="B384" t="s">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="C384" t="s">
         <v>2</v>
@@ -11732,21 +11747,21 @@
         <v>58</v>
       </c>
       <c r="F384" s="1">
-        <v>46128</v>
+        <v>46125</v>
       </c>
       <c r="G384" s="1">
-        <v>46128</v>
+        <v>46125</v>
       </c>
     </row>
     <row r="385" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A385" t="s">
-        <v>764</v>
+        <v>769</v>
       </c>
       <c r="B385" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="C385" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D385" t="s">
         <v>57</v>
@@ -11755,18 +11770,18 @@
         <v>58</v>
       </c>
       <c r="F385" s="1">
-        <v>46132</v>
+        <v>46126</v>
       </c>
       <c r="G385" s="1">
-        <v>46132</v>
+        <v>46126</v>
       </c>
     </row>
     <row r="386" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A386" t="s">
-        <v>764</v>
+        <v>769</v>
       </c>
       <c r="B386" t="s">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="C386" t="s">
         <v>2</v>
@@ -11778,18 +11793,18 @@
         <v>58</v>
       </c>
       <c r="F386" s="1">
-        <v>46161</v>
+        <v>46126</v>
       </c>
       <c r="G386" s="1">
-        <v>46161</v>
+        <v>46126</v>
       </c>
     </row>
     <row r="387" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A387" t="s">
-        <v>764</v>
+        <v>769</v>
       </c>
       <c r="B387" t="s">
-        <v>775</v>
+        <v>777</v>
       </c>
       <c r="C387" t="s">
         <v>2</v>
@@ -11801,21 +11816,21 @@
         <v>58</v>
       </c>
       <c r="F387" s="1">
-        <v>46174</v>
+        <v>46128</v>
       </c>
       <c r="G387" s="1">
-        <v>46174</v>
+        <v>46128</v>
       </c>
     </row>
     <row r="388" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A388" t="s">
-        <v>764</v>
+        <v>769</v>
       </c>
       <c r="B388" t="s">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="C388" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D388" t="s">
         <v>57</v>
@@ -11824,21 +11839,21 @@
         <v>58</v>
       </c>
       <c r="F388" s="1">
-        <v>46174</v>
+        <v>46132</v>
       </c>
       <c r="G388" s="1">
-        <v>46174</v>
+        <v>46132</v>
       </c>
     </row>
     <row r="389" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A389" t="s">
-        <v>764</v>
+        <v>769</v>
       </c>
       <c r="B389" t="s">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="C389" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D389" t="s">
         <v>57</v>
@@ -11847,21 +11862,21 @@
         <v>58</v>
       </c>
       <c r="F389" s="1">
-        <v>46195</v>
+        <v>46161</v>
       </c>
       <c r="G389" s="1">
-        <v>46252</v>
+        <v>46161</v>
       </c>
     </row>
     <row r="390" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A390" t="s">
-        <v>764</v>
+        <v>769</v>
       </c>
       <c r="B390" t="s">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="C390" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D390" t="s">
         <v>57</v>
@@ -11870,18 +11885,18 @@
         <v>58</v>
       </c>
       <c r="F390" s="1">
-        <v>46210</v>
+        <v>46174</v>
       </c>
       <c r="G390" s="1">
-        <v>46210</v>
+        <v>46174</v>
       </c>
     </row>
     <row r="391" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A391" t="s">
-        <v>764</v>
+        <v>769</v>
       </c>
       <c r="B391" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="C391" t="s">
         <v>2</v>
@@ -11893,18 +11908,18 @@
         <v>58</v>
       </c>
       <c r="F391" s="1">
-        <v>46213</v>
+        <v>46174</v>
       </c>
       <c r="G391" s="1">
-        <v>46213</v>
+        <v>46174</v>
       </c>
     </row>
     <row r="392" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A392" t="s">
-        <v>764</v>
+        <v>769</v>
       </c>
       <c r="B392" t="s">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="C392" t="s">
         <v>80</v>
@@ -11916,7 +11931,7 @@
         <v>58</v>
       </c>
       <c r="F392" s="1">
-        <v>46218</v>
+        <v>46195</v>
       </c>
       <c r="G392" s="1">
         <v>46252</v>
@@ -11924,36 +11939,36 @@
     </row>
     <row r="393" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A393" t="s">
-        <v>764</v>
+        <v>769</v>
       </c>
       <c r="B393" t="s">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="C393" t="s">
         <v>6</v>
       </c>
       <c r="D393" t="s">
-        <v>77</v>
+        <v>57</v>
       </c>
       <c r="E393" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="F393" s="1">
-        <v>46226</v>
+        <v>46210</v>
       </c>
       <c r="G393" s="1">
-        <v>46226</v>
+        <v>46210</v>
       </c>
     </row>
     <row r="394" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A394" t="s">
-        <v>764</v>
+        <v>769</v>
       </c>
       <c r="B394" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="C394" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D394" t="s">
         <v>57</v>
@@ -11962,18 +11977,18 @@
         <v>58</v>
       </c>
       <c r="F394" s="1">
-        <v>46227</v>
+        <v>46213</v>
       </c>
       <c r="G394" s="1">
-        <v>46252</v>
+        <v>46213</v>
       </c>
     </row>
     <row r="395" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A395" t="s">
-        <v>764</v>
+        <v>769</v>
       </c>
       <c r="B395" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="C395" t="s">
         <v>80</v>
@@ -11985,7 +12000,7 @@
         <v>58</v>
       </c>
       <c r="F395" s="1">
-        <v>46227</v>
+        <v>46218</v>
       </c>
       <c r="G395" s="1">
         <v>46252</v>
@@ -11993,45 +12008,45 @@
     </row>
     <row r="396" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A396" t="s">
-        <v>764</v>
+        <v>769</v>
       </c>
       <c r="B396" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="C396" t="s">
         <v>6</v>
       </c>
       <c r="D396" t="s">
-        <v>57</v>
+        <v>77</v>
       </c>
       <c r="E396" t="s">
-        <v>58</v>
+        <v>78</v>
       </c>
       <c r="F396" s="1">
-        <v>46227</v>
+        <v>46226</v>
       </c>
       <c r="G396" s="1">
-        <v>46228</v>
+        <v>46226</v>
       </c>
     </row>
     <row r="397" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A397" t="s">
-        <v>764</v>
+        <v>769</v>
       </c>
       <c r="B397" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="C397" t="s">
         <v>80</v>
       </c>
       <c r="D397" t="s">
-        <v>77</v>
+        <v>57</v>
       </c>
       <c r="E397" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="F397" s="1">
-        <v>46230</v>
+        <v>46227</v>
       </c>
       <c r="G397" s="1">
         <v>46252</v>
@@ -12039,13 +12054,13 @@
     </row>
     <row r="398" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A398" t="s">
-        <v>764</v>
+        <v>769</v>
       </c>
       <c r="B398" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="C398" t="s">
-        <v>6</v>
+        <v>80</v>
       </c>
       <c r="D398" t="s">
         <v>57</v>
@@ -12054,18 +12069,18 @@
         <v>58</v>
       </c>
       <c r="F398" s="1">
-        <v>46231</v>
+        <v>46227</v>
       </c>
       <c r="G398" s="1">
-        <v>46231</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="399" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A399" t="s">
-        <v>764</v>
+        <v>769</v>
       </c>
       <c r="B399" t="s">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="C399" t="s">
         <v>6</v>
@@ -12077,176 +12092,176 @@
         <v>58</v>
       </c>
       <c r="F399" s="1">
-        <v>46254</v>
+        <v>46227</v>
       </c>
       <c r="G399" s="1">
-        <v>46254</v>
+        <v>46228</v>
       </c>
     </row>
     <row r="400" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A400" t="s">
-        <v>764</v>
+        <v>769</v>
       </c>
       <c r="B400" t="s">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="C400" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D400" t="s">
-        <v>57</v>
+        <v>77</v>
       </c>
       <c r="E400" t="s">
-        <v>58</v>
+        <v>78</v>
       </c>
       <c r="F400" s="1">
-        <v>46255</v>
+        <v>46230</v>
       </c>
       <c r="G400" s="1">
-        <v>46255</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="401" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A401" t="s">
-        <v>789</v>
+        <v>769</v>
       </c>
       <c r="B401" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="C401" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D401" t="s">
-        <v>791</v>
+        <v>57</v>
       </c>
       <c r="E401" t="s">
-        <v>792</v>
+        <v>58</v>
       </c>
       <c r="F401" s="1">
-        <v>46083</v>
+        <v>46231</v>
       </c>
       <c r="G401" s="1">
-        <v>46084</v>
+        <v>46231</v>
       </c>
     </row>
     <row r="402" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A402" t="s">
-        <v>789</v>
+        <v>769</v>
       </c>
       <c r="B402" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="C402" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D402" t="s">
-        <v>791</v>
+        <v>57</v>
       </c>
       <c r="E402" t="s">
-        <v>792</v>
+        <v>58</v>
       </c>
       <c r="F402" s="1">
-        <v>46132</v>
+        <v>46254</v>
       </c>
       <c r="G402" s="1">
-        <v>46133</v>
+        <v>46254</v>
       </c>
     </row>
     <row r="403" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A403" t="s">
-        <v>789</v>
+        <v>769</v>
       </c>
       <c r="B403" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="C403" t="s">
         <v>2</v>
       </c>
       <c r="D403" t="s">
-        <v>795</v>
+        <v>57</v>
       </c>
       <c r="E403" t="s">
-        <v>796</v>
+        <v>58</v>
       </c>
       <c r="F403" s="1">
-        <v>46157</v>
+        <v>46255</v>
       </c>
       <c r="G403" s="1">
-        <v>46157</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="404" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A404" t="s">
-        <v>789</v>
+        <v>794</v>
       </c>
       <c r="B404" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="C404" t="s">
         <v>2</v>
       </c>
       <c r="D404" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="E404" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="F404" s="1">
-        <v>46168</v>
+        <v>46083</v>
       </c>
       <c r="G404" s="1">
-        <v>46170</v>
+        <v>46084</v>
       </c>
     </row>
     <row r="405" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A405" t="s">
-        <v>789</v>
+        <v>794</v>
       </c>
       <c r="B405" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="C405" t="s">
         <v>2</v>
       </c>
       <c r="D405" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="E405" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="F405" s="1">
-        <v>46244</v>
+        <v>46132</v>
       </c>
       <c r="G405" s="1">
-        <v>46244</v>
+        <v>46133</v>
       </c>
     </row>
     <row r="406" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A406" t="s">
-        <v>789</v>
+        <v>794</v>
       </c>
       <c r="B406" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="C406" t="s">
         <v>2</v>
       </c>
       <c r="D406" t="s">
-        <v>795</v>
+        <v>800</v>
       </c>
       <c r="E406" t="s">
-        <v>796</v>
+        <v>801</v>
       </c>
       <c r="F406" s="1">
-        <v>46247</v>
+        <v>46157</v>
       </c>
       <c r="G406" s="1">
-        <v>46247</v>
+        <v>46157</v>
       </c>
     </row>
     <row r="407" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A407" t="s">
-        <v>789</v>
+        <v>794</v>
       </c>
       <c r="B407" t="s">
         <v>802</v>
@@ -12255,38 +12270,107 @@
         <v>2</v>
       </c>
       <c r="D407" t="s">
-        <v>791</v>
+        <v>803</v>
       </c>
       <c r="E407" t="s">
-        <v>792</v>
+        <v>804</v>
       </c>
       <c r="F407" s="1">
-        <v>46247</v>
+        <v>46168</v>
       </c>
       <c r="G407" s="1">
-        <v>46247</v>
+        <v>46170</v>
       </c>
     </row>
     <row r="408" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A408" t="s">
-        <v>789</v>
+        <v>794</v>
       </c>
       <c r="B408" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="C408" t="s">
         <v>2</v>
       </c>
       <c r="D408" t="s">
-        <v>795</v>
+        <v>800</v>
       </c>
       <c r="E408" t="s">
+        <v>801</v>
+      </c>
+      <c r="F408" s="1">
+        <v>46244</v>
+      </c>
+      <c r="G408" s="1">
+        <v>46244</v>
+      </c>
+    </row>
+    <row r="409" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A409" t="s">
+        <v>794</v>
+      </c>
+      <c r="B409" t="s">
+        <v>806</v>
+      </c>
+      <c r="C409" t="s">
+        <v>2</v>
+      </c>
+      <c r="D409" t="s">
+        <v>800</v>
+      </c>
+      <c r="E409" t="s">
+        <v>801</v>
+      </c>
+      <c r="F409" s="1">
+        <v>46247</v>
+      </c>
+      <c r="G409" s="1">
+        <v>46247</v>
+      </c>
+    </row>
+    <row r="410" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A410" t="s">
+        <v>794</v>
+      </c>
+      <c r="B410" t="s">
+        <v>807</v>
+      </c>
+      <c r="C410" t="s">
+        <v>2</v>
+      </c>
+      <c r="D410" t="s">
         <v>796</v>
       </c>
-      <c r="F408" s="1">
-        <v>46255</v>
-      </c>
-      <c r="G408" s="1">
+      <c r="E410" t="s">
+        <v>797</v>
+      </c>
+      <c r="F410" s="1">
+        <v>46247</v>
+      </c>
+      <c r="G410" s="1">
+        <v>46247</v>
+      </c>
+    </row>
+    <row r="411" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A411" t="s">
+        <v>794</v>
+      </c>
+      <c r="B411" t="s">
+        <v>808</v>
+      </c>
+      <c r="C411" t="s">
+        <v>2</v>
+      </c>
+      <c r="D411" t="s">
+        <v>800</v>
+      </c>
+      <c r="E411" t="s">
+        <v>801</v>
+      </c>
+      <c r="F411" s="1">
+        <v>46255</v>
+      </c>
+      <c r="G411" s="1">
         <v>46255</v>
       </c>
     </row>

--- a/Data_ERP/Pedidos Transmicion.xlsx
+++ b/Data_ERP/Pedidos Transmicion.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sistema_Logistico_Peirano\Data_ERP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{10939395-A6DD-4ACD-AB43-4D5C57B7B5A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3B7C429F-80BB-4528-844A-EF115329784E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{0727CCF8-8CE0-49D7-BD56-52BD225F092C}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="15375" windowHeight="8325" xr2:uid="{3336A967-536E-497A-9EE5-06074FC30E3B}"/>
   </bookViews>
   <sheets>
     <sheet name="transmicion" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2057" uniqueCount="816">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2202" uniqueCount="863">
   <si>
     <t>0001</t>
   </si>
@@ -1390,9 +1390,21 @@
     <t xml:space="preserve">  214048</t>
   </si>
   <si>
+    <t xml:space="preserve">  214049</t>
+  </si>
+  <si>
     <t xml:space="preserve">  214051</t>
   </si>
   <si>
+    <t xml:space="preserve">  214052</t>
+  </si>
+  <si>
+    <t>SS41</t>
+  </si>
+  <si>
+    <t>SANITARIOS SANJUAN S.R.L.</t>
+  </si>
+  <si>
     <t xml:space="preserve">  214062</t>
   </si>
   <si>
@@ -1540,6 +1552,9 @@
     <t>GILLI FAUDIN LUIS V. -GILCOMAT</t>
   </si>
   <si>
+    <t xml:space="preserve">  214104</t>
+  </si>
+  <si>
     <t xml:space="preserve">  214106</t>
   </si>
   <si>
@@ -1651,12 +1666,6 @@
     <t xml:space="preserve">  214127</t>
   </si>
   <si>
-    <t>SS41</t>
-  </si>
-  <si>
-    <t>SANITARIOS SANJUAN S.R.L.</t>
-  </si>
-  <si>
     <t xml:space="preserve">  214128</t>
   </si>
   <si>
@@ -2140,6 +2149,15 @@
     <t>VARELA MARIA ISABEL</t>
   </si>
   <si>
+    <t xml:space="preserve">  214226</t>
+  </si>
+  <si>
+    <t>KP01</t>
+  </si>
+  <si>
+    <t>KROMACOLOR PINTURERIAS S.R.L.</t>
+  </si>
+  <si>
     <t xml:space="preserve">  214227</t>
   </si>
   <si>
@@ -2188,6 +2206,144 @@
     <t xml:space="preserve">  214234</t>
   </si>
   <si>
+    <t xml:space="preserve">  214235</t>
+  </si>
+  <si>
+    <t>SG13</t>
+  </si>
+  <si>
+    <t>SANITARIOS GAONA S.A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214238</t>
+  </si>
+  <si>
+    <t>RT04</t>
+  </si>
+  <si>
+    <t>REY DEL TANQUE S.R.L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214240</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214242</t>
+  </si>
+  <si>
+    <t>GG20</t>
+  </si>
+  <si>
+    <t>GRUPO GALU S.A.  - SANITARIOS MITRE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214245</t>
+  </si>
+  <si>
+    <t>IC16</t>
+  </si>
+  <si>
+    <t>EL IMPERIO DEL CERAMICO S.R.L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214246</t>
+  </si>
+  <si>
+    <t>LM17</t>
+  </si>
+  <si>
+    <t>LUCERO MIRIAM ELIZABETH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214247</t>
+  </si>
+  <si>
+    <t>DP09</t>
+  </si>
+  <si>
+    <t>DEL PRADO SERGIO A. -SANIT GAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214249</t>
+  </si>
+  <si>
+    <t>KA07</t>
+  </si>
+  <si>
+    <t>KASA S.R.L. -KASA SANITARIOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214250</t>
+  </si>
+  <si>
+    <t>VG06</t>
+  </si>
+  <si>
+    <t>VICTOR GULLO S.R.L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214252</t>
+  </si>
+  <si>
+    <t>TC11</t>
+  </si>
+  <si>
+    <t>TRIPOLI CARLOS L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214253</t>
+  </si>
+  <si>
+    <t>T1</t>
+  </si>
+  <si>
+    <t>TRIPOLI ARNALDO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214260</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214263</t>
+  </si>
+  <si>
     <t>0004</t>
   </si>
   <si>
@@ -2209,12 +2365,6 @@
     <t xml:space="preserve">    2593</t>
   </si>
   <si>
-    <t>TC11</t>
-  </si>
-  <si>
-    <t>TRIPOLI CARLOS L.</t>
-  </si>
-  <si>
     <t xml:space="preserve">    2645</t>
   </si>
   <si>
@@ -2293,24 +2443,9 @@
     <t xml:space="preserve">    2827</t>
   </si>
   <si>
-    <t xml:space="preserve">    2829</t>
-  </si>
-  <si>
     <t xml:space="preserve">    2831</t>
   </si>
   <si>
-    <t xml:space="preserve">    2832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    2833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    2834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    2835</t>
-  </si>
-  <si>
     <t xml:space="preserve">    2836</t>
   </si>
   <si>
@@ -2320,13 +2455,10 @@
     <t xml:space="preserve">    2838</t>
   </si>
   <si>
-    <t xml:space="preserve">    2840</t>
-  </si>
-  <si>
-    <t>PA01</t>
-  </si>
-  <si>
-    <t>VARIOS</t>
+    <t xml:space="preserve">    2842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    2844</t>
   </si>
   <si>
     <t>4444</t>
@@ -2402,6 +2534,15 @@
   </si>
   <si>
     <t xml:space="preserve">    2258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    2266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    2267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    2273</t>
   </si>
   <si>
     <t>9999</t>
@@ -2917,31 +3058,31 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DBD66A9-C2DF-412C-8C5C-367A117D8A73}">
-  <dimension ref="A1:G411"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C63A934D-BD17-43E1-9345-0B0244A63800}">
+  <dimension ref="A1:G440"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
-        <v>809</v>
+        <v>856</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>810</v>
+        <v>857</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>811</v>
+        <v>858</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>812</v>
+        <v>859</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>813</v>
+        <v>860</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>814</v>
+        <v>861</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>815</v>
+        <v>862</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
@@ -6310,7 +6451,7 @@
         <v>339</v>
       </c>
       <c r="C148" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D148" t="s">
         <v>340</v>
@@ -6379,7 +6520,7 @@
         <v>348</v>
       </c>
       <c r="C151" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D151" t="s">
         <v>117</v>
@@ -6517,7 +6658,7 @@
         <v>360</v>
       </c>
       <c r="C157" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D157" t="s">
         <v>361</v>
@@ -6609,7 +6750,7 @@
         <v>372</v>
       </c>
       <c r="C161" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D161" t="s">
         <v>330</v>
@@ -6701,7 +6842,7 @@
         <v>378</v>
       </c>
       <c r="C165" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D165" t="s">
         <v>117</v>
@@ -6816,7 +6957,7 @@
         <v>383</v>
       </c>
       <c r="C170" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D170" t="s">
         <v>384</v>
@@ -7276,7 +7417,7 @@
         <v>427</v>
       </c>
       <c r="C190" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D190" t="s">
         <v>428</v>
@@ -7299,7 +7440,7 @@
         <v>430</v>
       </c>
       <c r="C191" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D191" t="s">
         <v>384</v>
@@ -7322,7 +7463,7 @@
         <v>431</v>
       </c>
       <c r="C192" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D192" t="s">
         <v>432</v>
@@ -7368,7 +7509,7 @@
         <v>437</v>
       </c>
       <c r="C194" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D194" t="s">
         <v>438</v>
@@ -7670,16 +7811,16 @@
         <v>80</v>
       </c>
       <c r="D207" t="s">
-        <v>28</v>
+        <v>346</v>
       </c>
       <c r="E207" t="s">
-        <v>29</v>
+        <v>347</v>
       </c>
       <c r="F207" s="1">
         <v>46253</v>
       </c>
       <c r="G207" s="1">
-        <v>46254</v>
+        <v>46258</v>
       </c>
     </row>
     <row r="208" spans="1:7" x14ac:dyDescent="0.2">
@@ -7690,13 +7831,13 @@
         <v>457</v>
       </c>
       <c r="C208" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D208" t="s">
-        <v>458</v>
+        <v>28</v>
       </c>
       <c r="E208" t="s">
-        <v>459</v>
+        <v>29</v>
       </c>
       <c r="F208" s="1">
         <v>46253</v>
@@ -7710,22 +7851,22 @@
         <v>0</v>
       </c>
       <c r="B209" t="s">
+        <v>458</v>
+      </c>
+      <c r="C209" t="s">
+        <v>80</v>
+      </c>
+      <c r="D209" t="s">
+        <v>459</v>
+      </c>
+      <c r="E209" t="s">
         <v>460</v>
       </c>
-      <c r="C209" t="s">
-        <v>80</v>
-      </c>
-      <c r="D209" t="s">
-        <v>98</v>
-      </c>
-      <c r="E209" t="s">
-        <v>99</v>
-      </c>
       <c r="F209" s="1">
-        <v>46254</v>
+        <v>46253</v>
       </c>
       <c r="G209" s="1">
-        <v>46254</v>
+        <v>46258</v>
       </c>
     </row>
     <row r="210" spans="1:7" x14ac:dyDescent="0.2">
@@ -7736,7 +7877,7 @@
         <v>461</v>
       </c>
       <c r="C210" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D210" t="s">
         <v>462</v>
@@ -7745,7 +7886,7 @@
         <v>463</v>
       </c>
       <c r="F210" s="1">
-        <v>46254</v>
+        <v>46253</v>
       </c>
       <c r="G210" s="1">
         <v>46254</v>
@@ -7759,13 +7900,13 @@
         <v>464</v>
       </c>
       <c r="C211" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D211" t="s">
-        <v>465</v>
+        <v>98</v>
       </c>
       <c r="E211" t="s">
-        <v>466</v>
+        <v>99</v>
       </c>
       <c r="F211" s="1">
         <v>46254</v>
@@ -7779,16 +7920,16 @@
         <v>0</v>
       </c>
       <c r="B212" t="s">
+        <v>465</v>
+      </c>
+      <c r="C212" t="s">
+        <v>80</v>
+      </c>
+      <c r="D212" t="s">
+        <v>466</v>
+      </c>
+      <c r="E212" t="s">
         <v>467</v>
-      </c>
-      <c r="C212" t="s">
-        <v>80</v>
-      </c>
-      <c r="D212" t="s">
-        <v>468</v>
-      </c>
-      <c r="E212" t="s">
-        <v>469</v>
       </c>
       <c r="F212" s="1">
         <v>46254</v>
@@ -7802,16 +7943,16 @@
         <v>0</v>
       </c>
       <c r="B213" t="s">
+        <v>468</v>
+      </c>
+      <c r="C213" t="s">
+        <v>2</v>
+      </c>
+      <c r="D213" t="s">
+        <v>469</v>
+      </c>
+      <c r="E213" t="s">
         <v>470</v>
-      </c>
-      <c r="C213" t="s">
-        <v>80</v>
-      </c>
-      <c r="D213" t="s">
-        <v>173</v>
-      </c>
-      <c r="E213" t="s">
-        <v>174</v>
       </c>
       <c r="F213" s="1">
         <v>46254</v>
@@ -7831,10 +7972,10 @@
         <v>80</v>
       </c>
       <c r="D214" t="s">
-        <v>37</v>
+        <v>472</v>
       </c>
       <c r="E214" t="s">
-        <v>38</v>
+        <v>473</v>
       </c>
       <c r="F214" s="1">
         <v>46254</v>
@@ -7848,16 +7989,16 @@
         <v>0</v>
       </c>
       <c r="B215" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="C215" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D215" t="s">
-        <v>37</v>
+        <v>173</v>
       </c>
       <c r="E215" t="s">
-        <v>38</v>
+        <v>174</v>
       </c>
       <c r="F215" s="1">
         <v>46254</v>
@@ -7871,7 +8012,7 @@
         <v>0</v>
       </c>
       <c r="B216" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="C216" t="s">
         <v>80</v>
@@ -7894,16 +8035,16 @@
         <v>0</v>
       </c>
       <c r="B217" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="C217" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D217" t="s">
-        <v>475</v>
+        <v>37</v>
       </c>
       <c r="E217" t="s">
-        <v>476</v>
+        <v>38</v>
       </c>
       <c r="F217" s="1">
         <v>46254</v>
@@ -7923,10 +8064,10 @@
         <v>80</v>
       </c>
       <c r="D218" t="s">
-        <v>475</v>
+        <v>37</v>
       </c>
       <c r="E218" t="s">
-        <v>476</v>
+        <v>38</v>
       </c>
       <c r="F218" s="1">
         <v>46254</v>
@@ -7943,13 +8084,13 @@
         <v>478</v>
       </c>
       <c r="C219" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D219" t="s">
-        <v>16</v>
+        <v>479</v>
       </c>
       <c r="E219" t="s">
-        <v>17</v>
+        <v>480</v>
       </c>
       <c r="F219" s="1">
         <v>46254</v>
@@ -7963,16 +8104,16 @@
         <v>0</v>
       </c>
       <c r="B220" t="s">
+        <v>481</v>
+      </c>
+      <c r="C220" t="s">
+        <v>80</v>
+      </c>
+      <c r="D220" t="s">
         <v>479</v>
       </c>
-      <c r="C220" t="s">
-        <v>80</v>
-      </c>
-      <c r="D220" t="s">
-        <v>16</v>
-      </c>
       <c r="E220" t="s">
-        <v>17</v>
+        <v>480</v>
       </c>
       <c r="F220" s="1">
         <v>46254</v>
@@ -7986,16 +8127,16 @@
         <v>0</v>
       </c>
       <c r="B221" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="C221" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D221" t="s">
-        <v>481</v>
+        <v>16</v>
       </c>
       <c r="E221" t="s">
-        <v>482</v>
+        <v>17</v>
       </c>
       <c r="F221" s="1">
         <v>46254</v>
@@ -8015,16 +8156,16 @@
         <v>80</v>
       </c>
       <c r="D222" t="s">
-        <v>194</v>
+        <v>16</v>
       </c>
       <c r="E222" t="s">
-        <v>195</v>
+        <v>17</v>
       </c>
       <c r="F222" s="1">
         <v>46254</v>
       </c>
       <c r="G222" s="1">
-        <v>46255</v>
+        <v>46254</v>
       </c>
     </row>
     <row r="223" spans="1:7" x14ac:dyDescent="0.2">
@@ -8058,19 +8199,19 @@
         <v>487</v>
       </c>
       <c r="C224" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D224" t="s">
-        <v>488</v>
+        <v>194</v>
       </c>
       <c r="E224" t="s">
-        <v>489</v>
+        <v>195</v>
       </c>
       <c r="F224" s="1">
         <v>46254</v>
       </c>
       <c r="G224" s="1">
-        <v>46254</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.2">
@@ -8078,16 +8219,16 @@
         <v>0</v>
       </c>
       <c r="B225" t="s">
+        <v>488</v>
+      </c>
+      <c r="C225" t="s">
+        <v>80</v>
+      </c>
+      <c r="D225" t="s">
+        <v>489</v>
+      </c>
+      <c r="E225" t="s">
         <v>490</v>
-      </c>
-      <c r="C225" t="s">
-        <v>80</v>
-      </c>
-      <c r="D225" t="s">
-        <v>491</v>
-      </c>
-      <c r="E225" t="s">
-        <v>492</v>
       </c>
       <c r="F225" s="1">
         <v>46254</v>
@@ -8101,16 +8242,16 @@
         <v>0</v>
       </c>
       <c r="B226" t="s">
+        <v>491</v>
+      </c>
+      <c r="C226" t="s">
+        <v>6</v>
+      </c>
+      <c r="D226" t="s">
+        <v>492</v>
+      </c>
+      <c r="E226" t="s">
         <v>493</v>
-      </c>
-      <c r="C226" t="s">
-        <v>80</v>
-      </c>
-      <c r="D226" t="s">
-        <v>77</v>
-      </c>
-      <c r="E226" t="s">
-        <v>78</v>
       </c>
       <c r="F226" s="1">
         <v>46254</v>
@@ -8130,10 +8271,10 @@
         <v>80</v>
       </c>
       <c r="D227" t="s">
-        <v>16</v>
+        <v>495</v>
       </c>
       <c r="E227" t="s">
-        <v>17</v>
+        <v>496</v>
       </c>
       <c r="F227" s="1">
         <v>46254</v>
@@ -8147,16 +8288,16 @@
         <v>0</v>
       </c>
       <c r="B228" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="C228" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D228" t="s">
-        <v>496</v>
+        <v>77</v>
       </c>
       <c r="E228" t="s">
-        <v>497</v>
+        <v>78</v>
       </c>
       <c r="F228" s="1">
         <v>46254</v>
@@ -8176,10 +8317,10 @@
         <v>80</v>
       </c>
       <c r="D229" t="s">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="E229" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="F229" s="1">
         <v>46254</v>
@@ -8196,7 +8337,7 @@
         <v>499</v>
       </c>
       <c r="C230" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D230" t="s">
         <v>500</v>
@@ -8208,7 +8349,7 @@
         <v>46254</v>
       </c>
       <c r="G230" s="1">
-        <v>46255</v>
+        <v>46254</v>
       </c>
     </row>
     <row r="231" spans="1:7" x14ac:dyDescent="0.2">
@@ -8222,16 +8363,16 @@
         <v>80</v>
       </c>
       <c r="D231" t="s">
-        <v>138</v>
+        <v>3</v>
       </c>
       <c r="E231" t="s">
-        <v>139</v>
+        <v>4</v>
       </c>
       <c r="F231" s="1">
         <v>46254</v>
       </c>
       <c r="G231" s="1">
-        <v>46256</v>
+        <v>46254</v>
       </c>
     </row>
     <row r="232" spans="1:7" x14ac:dyDescent="0.2">
@@ -8242,7 +8383,7 @@
         <v>503</v>
       </c>
       <c r="C232" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D232" t="s">
         <v>504</v>
@@ -8268,16 +8409,16 @@
         <v>80</v>
       </c>
       <c r="D233" t="s">
-        <v>358</v>
+        <v>138</v>
       </c>
       <c r="E233" t="s">
-        <v>359</v>
+        <v>139</v>
       </c>
       <c r="F233" s="1">
         <v>46254</v>
       </c>
       <c r="G233" s="1">
-        <v>46254</v>
+        <v>46256</v>
       </c>
     </row>
     <row r="234" spans="1:7" x14ac:dyDescent="0.2">
@@ -8291,16 +8432,16 @@
         <v>80</v>
       </c>
       <c r="D234" t="s">
-        <v>292</v>
+        <v>508</v>
       </c>
       <c r="E234" t="s">
-        <v>293</v>
+        <v>509</v>
       </c>
       <c r="F234" s="1">
         <v>46254</v>
       </c>
       <c r="G234" s="1">
-        <v>46254</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="235" spans="1:7" x14ac:dyDescent="0.2">
@@ -8308,22 +8449,22 @@
         <v>0</v>
       </c>
       <c r="B235" t="s">
+        <v>510</v>
+      </c>
+      <c r="C235" t="s">
+        <v>80</v>
+      </c>
+      <c r="D235" t="s">
         <v>508</v>
       </c>
-      <c r="C235" t="s">
-        <v>80</v>
-      </c>
-      <c r="D235" t="s">
+      <c r="E235" t="s">
         <v>509</v>
-      </c>
-      <c r="E235" t="s">
-        <v>510</v>
       </c>
       <c r="F235" s="1">
         <v>46254</v>
       </c>
       <c r="G235" s="1">
-        <v>46254</v>
+        <v>46258</v>
       </c>
     </row>
     <row r="236" spans="1:7" x14ac:dyDescent="0.2">
@@ -8334,19 +8475,19 @@
         <v>511</v>
       </c>
       <c r="C236" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D236" t="s">
-        <v>512</v>
+        <v>358</v>
       </c>
       <c r="E236" t="s">
-        <v>513</v>
+        <v>359</v>
       </c>
       <c r="F236" s="1">
         <v>46254</v>
       </c>
       <c r="G236" s="1">
-        <v>46255</v>
+        <v>46254</v>
       </c>
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.2">
@@ -8354,16 +8495,16 @@
         <v>0</v>
       </c>
       <c r="B237" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="C237" t="s">
         <v>80</v>
       </c>
       <c r="D237" t="s">
-        <v>16</v>
+        <v>292</v>
       </c>
       <c r="E237" t="s">
-        <v>17</v>
+        <v>293</v>
       </c>
       <c r="F237" s="1">
         <v>46254</v>
@@ -8377,22 +8518,22 @@
         <v>0</v>
       </c>
       <c r="B238" t="s">
+        <v>513</v>
+      </c>
+      <c r="C238" t="s">
+        <v>2</v>
+      </c>
+      <c r="D238" t="s">
+        <v>514</v>
+      </c>
+      <c r="E238" t="s">
         <v>515</v>
-      </c>
-      <c r="C238" t="s">
-        <v>80</v>
-      </c>
-      <c r="D238" t="s">
-        <v>138</v>
-      </c>
-      <c r="E238" t="s">
-        <v>139</v>
       </c>
       <c r="F238" s="1">
         <v>46254</v>
       </c>
       <c r="G238" s="1">
-        <v>46255</v>
+        <v>46254</v>
       </c>
     </row>
     <row r="239" spans="1:7" x14ac:dyDescent="0.2">
@@ -8403,7 +8544,7 @@
         <v>516</v>
       </c>
       <c r="C239" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D239" t="s">
         <v>517</v>
@@ -8415,7 +8556,7 @@
         <v>46254</v>
       </c>
       <c r="G239" s="1">
-        <v>46254</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="240" spans="1:7" x14ac:dyDescent="0.2">
@@ -8429,10 +8570,10 @@
         <v>80</v>
       </c>
       <c r="D240" t="s">
-        <v>520</v>
+        <v>16</v>
       </c>
       <c r="E240" t="s">
-        <v>521</v>
+        <v>17</v>
       </c>
       <c r="F240" s="1">
         <v>46254</v>
@@ -8446,22 +8587,22 @@
         <v>0</v>
       </c>
       <c r="B241" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="C241" t="s">
         <v>80</v>
       </c>
       <c r="D241" t="s">
-        <v>523</v>
+        <v>138</v>
       </c>
       <c r="E241" t="s">
-        <v>524</v>
+        <v>139</v>
       </c>
       <c r="F241" s="1">
         <v>46254</v>
       </c>
       <c r="G241" s="1">
-        <v>46254</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="242" spans="1:7" x14ac:dyDescent="0.2">
@@ -8469,16 +8610,16 @@
         <v>0</v>
       </c>
       <c r="B242" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="C242" t="s">
         <v>80</v>
       </c>
       <c r="D242" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="E242" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="F242" s="1">
         <v>46254</v>
@@ -8492,16 +8633,16 @@
         <v>0</v>
       </c>
       <c r="B243" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
       <c r="C243" t="s">
         <v>80</v>
       </c>
       <c r="D243" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="E243" t="s">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="F243" s="1">
         <v>46254</v>
@@ -8515,22 +8656,22 @@
         <v>0</v>
       </c>
       <c r="B244" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="C244" t="s">
         <v>80</v>
       </c>
       <c r="D244" t="s">
-        <v>141</v>
+        <v>528</v>
       </c>
       <c r="E244" t="s">
-        <v>142</v>
+        <v>529</v>
       </c>
       <c r="F244" s="1">
         <v>46254</v>
       </c>
       <c r="G244" s="1">
-        <v>46255</v>
+        <v>46254</v>
       </c>
     </row>
     <row r="245" spans="1:7" x14ac:dyDescent="0.2">
@@ -8538,16 +8679,16 @@
         <v>0</v>
       </c>
       <c r="B245" t="s">
+        <v>530</v>
+      </c>
+      <c r="C245" t="s">
+        <v>2</v>
+      </c>
+      <c r="D245" t="s">
+        <v>531</v>
+      </c>
+      <c r="E245" t="s">
         <v>532</v>
-      </c>
-      <c r="C245" t="s">
-        <v>80</v>
-      </c>
-      <c r="D245" t="s">
-        <v>452</v>
-      </c>
-      <c r="E245" t="s">
-        <v>453</v>
       </c>
       <c r="F245" s="1">
         <v>46254</v>
@@ -8567,16 +8708,16 @@
         <v>80</v>
       </c>
       <c r="D246" t="s">
-        <v>141</v>
+        <v>534</v>
       </c>
       <c r="E246" t="s">
-        <v>142</v>
+        <v>535</v>
       </c>
       <c r="F246" s="1">
         <v>46254</v>
       </c>
       <c r="G246" s="1">
-        <v>46255</v>
+        <v>46254</v>
       </c>
     </row>
     <row r="247" spans="1:7" x14ac:dyDescent="0.2">
@@ -8584,16 +8725,16 @@
         <v>0</v>
       </c>
       <c r="B247" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="C247" t="s">
         <v>80</v>
       </c>
       <c r="D247" t="s">
-        <v>535</v>
+        <v>141</v>
       </c>
       <c r="E247" t="s">
-        <v>536</v>
+        <v>142</v>
       </c>
       <c r="F247" s="1">
         <v>46254</v>
@@ -8613,16 +8754,16 @@
         <v>80</v>
       </c>
       <c r="D248" t="s">
-        <v>19</v>
+        <v>452</v>
       </c>
       <c r="E248" t="s">
-        <v>20</v>
+        <v>453</v>
       </c>
       <c r="F248" s="1">
         <v>46254</v>
       </c>
       <c r="G248" s="1">
-        <v>46255</v>
+        <v>46254</v>
       </c>
     </row>
     <row r="249" spans="1:7" x14ac:dyDescent="0.2">
@@ -8636,10 +8777,10 @@
         <v>80</v>
       </c>
       <c r="D249" t="s">
-        <v>330</v>
+        <v>141</v>
       </c>
       <c r="E249" t="s">
-        <v>331</v>
+        <v>142</v>
       </c>
       <c r="F249" s="1">
         <v>46254</v>
@@ -8679,13 +8820,13 @@
         <v>542</v>
       </c>
       <c r="C251" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D251" t="s">
-        <v>543</v>
+        <v>19</v>
       </c>
       <c r="E251" t="s">
-        <v>544</v>
+        <v>20</v>
       </c>
       <c r="F251" s="1">
         <v>46254</v>
@@ -8699,16 +8840,16 @@
         <v>0</v>
       </c>
       <c r="B252" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="C252" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D252" t="s">
-        <v>546</v>
+        <v>330</v>
       </c>
       <c r="E252" t="s">
-        <v>547</v>
+        <v>331</v>
       </c>
       <c r="F252" s="1">
         <v>46254</v>
@@ -8722,16 +8863,16 @@
         <v>0</v>
       </c>
       <c r="B253" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="C253" t="s">
         <v>2</v>
       </c>
       <c r="D253" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="E253" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="F253" s="1">
         <v>46254</v>
@@ -8745,16 +8886,16 @@
         <v>0</v>
       </c>
       <c r="B254" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="C254" t="s">
         <v>2</v>
       </c>
       <c r="D254" t="s">
-        <v>549</v>
+        <v>459</v>
       </c>
       <c r="E254" t="s">
-        <v>550</v>
+        <v>460</v>
       </c>
       <c r="F254" s="1">
         <v>46254</v>
@@ -8768,16 +8909,16 @@
         <v>0</v>
       </c>
       <c r="B255" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="C255" t="s">
         <v>80</v>
       </c>
       <c r="D255" t="s">
-        <v>259</v>
+        <v>549</v>
       </c>
       <c r="E255" t="s">
-        <v>260</v>
+        <v>550</v>
       </c>
       <c r="F255" s="1">
         <v>46254</v>
@@ -8791,16 +8932,16 @@
         <v>0</v>
       </c>
       <c r="B256" t="s">
+        <v>551</v>
+      </c>
+      <c r="C256" t="s">
+        <v>2</v>
+      </c>
+      <c r="D256" t="s">
+        <v>552</v>
+      </c>
+      <c r="E256" t="s">
         <v>553</v>
-      </c>
-      <c r="C256" t="s">
-        <v>2</v>
-      </c>
-      <c r="D256" t="s">
-        <v>549</v>
-      </c>
-      <c r="E256" t="s">
-        <v>550</v>
       </c>
       <c r="F256" s="1">
         <v>46254</v>
@@ -8817,13 +8958,13 @@
         <v>554</v>
       </c>
       <c r="C257" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D257" t="s">
-        <v>259</v>
+        <v>552</v>
       </c>
       <c r="E257" t="s">
-        <v>260</v>
+        <v>553</v>
       </c>
       <c r="F257" s="1">
         <v>46254</v>
@@ -8843,10 +8984,10 @@
         <v>80</v>
       </c>
       <c r="D258" t="s">
-        <v>156</v>
+        <v>259</v>
       </c>
       <c r="E258" t="s">
-        <v>157</v>
+        <v>260</v>
       </c>
       <c r="F258" s="1">
         <v>46254</v>
@@ -8863,13 +9004,13 @@
         <v>556</v>
       </c>
       <c r="C259" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D259" t="s">
-        <v>557</v>
+        <v>552</v>
       </c>
       <c r="E259" t="s">
-        <v>558</v>
+        <v>553</v>
       </c>
       <c r="F259" s="1">
         <v>46254</v>
@@ -8883,16 +9024,16 @@
         <v>0</v>
       </c>
       <c r="B260" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="C260" t="s">
         <v>80</v>
       </c>
       <c r="D260" t="s">
-        <v>560</v>
+        <v>259</v>
       </c>
       <c r="E260" t="s">
-        <v>561</v>
+        <v>260</v>
       </c>
       <c r="F260" s="1">
         <v>46254</v>
@@ -8906,16 +9047,16 @@
         <v>0</v>
       </c>
       <c r="B261" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="C261" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D261" t="s">
-        <v>563</v>
+        <v>156</v>
       </c>
       <c r="E261" t="s">
-        <v>564</v>
+        <v>157</v>
       </c>
       <c r="F261" s="1">
         <v>46254</v>
@@ -8929,16 +9070,16 @@
         <v>0</v>
       </c>
       <c r="B262" t="s">
-        <v>565</v>
+        <v>559</v>
       </c>
       <c r="C262" t="s">
         <v>80</v>
       </c>
       <c r="D262" t="s">
-        <v>566</v>
+        <v>560</v>
       </c>
       <c r="E262" t="s">
-        <v>567</v>
+        <v>561</v>
       </c>
       <c r="F262" s="1">
         <v>46254</v>
@@ -8952,16 +9093,16 @@
         <v>0</v>
       </c>
       <c r="B263" t="s">
-        <v>568</v>
+        <v>562</v>
       </c>
       <c r="C263" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D263" t="s">
-        <v>569</v>
+        <v>563</v>
       </c>
       <c r="E263" t="s">
-        <v>570</v>
+        <v>564</v>
       </c>
       <c r="F263" s="1">
         <v>46254</v>
@@ -8975,16 +9116,16 @@
         <v>0</v>
       </c>
       <c r="B264" t="s">
-        <v>571</v>
+        <v>565</v>
       </c>
       <c r="C264" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D264" t="s">
-        <v>156</v>
+        <v>566</v>
       </c>
       <c r="E264" t="s">
-        <v>157</v>
+        <v>567</v>
       </c>
       <c r="F264" s="1">
         <v>46254</v>
@@ -8998,16 +9139,16 @@
         <v>0</v>
       </c>
       <c r="B265" t="s">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="C265" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D265" t="s">
-        <v>340</v>
+        <v>569</v>
       </c>
       <c r="E265" t="s">
-        <v>341</v>
+        <v>570</v>
       </c>
       <c r="F265" s="1">
         <v>46254</v>
@@ -9021,16 +9162,16 @@
         <v>0</v>
       </c>
       <c r="B266" t="s">
+        <v>571</v>
+      </c>
+      <c r="C266" t="s">
+        <v>2</v>
+      </c>
+      <c r="D266" t="s">
+        <v>572</v>
+      </c>
+      <c r="E266" t="s">
         <v>573</v>
-      </c>
-      <c r="C266" t="s">
-        <v>80</v>
-      </c>
-      <c r="D266" t="s">
-        <v>574</v>
-      </c>
-      <c r="E266" t="s">
-        <v>575</v>
       </c>
       <c r="F266" s="1">
         <v>46254</v>
@@ -9044,22 +9185,22 @@
         <v>0</v>
       </c>
       <c r="B267" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C267" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D267" t="s">
-        <v>340</v>
+        <v>156</v>
       </c>
       <c r="E267" t="s">
-        <v>341</v>
+        <v>157</v>
       </c>
       <c r="F267" s="1">
         <v>46254</v>
       </c>
       <c r="G267" s="1">
-        <v>46256</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="268" spans="1:7" x14ac:dyDescent="0.2">
@@ -9067,16 +9208,16 @@
         <v>0</v>
       </c>
       <c r="B268" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="C268" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D268" t="s">
-        <v>578</v>
+        <v>340</v>
       </c>
       <c r="E268" t="s">
-        <v>579</v>
+        <v>341</v>
       </c>
       <c r="F268" s="1">
         <v>46254</v>
@@ -9090,16 +9231,16 @@
         <v>0</v>
       </c>
       <c r="B269" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="C269" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D269" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="E269" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="F269" s="1">
         <v>46254</v>
@@ -9113,22 +9254,22 @@
         <v>0</v>
       </c>
       <c r="B270" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="C270" t="s">
         <v>2</v>
       </c>
       <c r="D270" t="s">
-        <v>216</v>
+        <v>340</v>
       </c>
       <c r="E270" t="s">
-        <v>217</v>
+        <v>341</v>
       </c>
       <c r="F270" s="1">
         <v>46254</v>
       </c>
       <c r="G270" s="1">
-        <v>46255</v>
+        <v>46256</v>
       </c>
     </row>
     <row r="271" spans="1:7" x14ac:dyDescent="0.2">
@@ -9136,16 +9277,16 @@
         <v>0</v>
       </c>
       <c r="B271" t="s">
+        <v>580</v>
+      </c>
+      <c r="C271" t="s">
+        <v>2</v>
+      </c>
+      <c r="D271" t="s">
+        <v>581</v>
+      </c>
+      <c r="E271" t="s">
         <v>582</v>
-      </c>
-      <c r="C271" t="s">
-        <v>80</v>
-      </c>
-      <c r="D271" t="s">
-        <v>583</v>
-      </c>
-      <c r="E271" t="s">
-        <v>584</v>
       </c>
       <c r="F271" s="1">
         <v>46254</v>
@@ -9159,19 +9300,19 @@
         <v>0</v>
       </c>
       <c r="B272" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="C272" t="s">
         <v>80</v>
       </c>
       <c r="D272" t="s">
-        <v>16</v>
+        <v>577</v>
       </c>
       <c r="E272" t="s">
-        <v>17</v>
+        <v>578</v>
       </c>
       <c r="F272" s="1">
-        <v>46255</v>
+        <v>46254</v>
       </c>
       <c r="G272" s="1">
         <v>46255</v>
@@ -9182,19 +9323,19 @@
         <v>0</v>
       </c>
       <c r="B273" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="C273" t="s">
         <v>2</v>
       </c>
       <c r="D273" t="s">
-        <v>37</v>
+        <v>216</v>
       </c>
       <c r="E273" t="s">
-        <v>38</v>
+        <v>217</v>
       </c>
       <c r="F273" s="1">
-        <v>46255</v>
+        <v>46254</v>
       </c>
       <c r="G273" s="1">
         <v>46255</v>
@@ -9205,19 +9346,19 @@
         <v>0</v>
       </c>
       <c r="B274" t="s">
+        <v>585</v>
+      </c>
+      <c r="C274" t="s">
+        <v>80</v>
+      </c>
+      <c r="D274" t="s">
+        <v>586</v>
+      </c>
+      <c r="E274" t="s">
         <v>587</v>
       </c>
-      <c r="C274" t="s">
-        <v>2</v>
-      </c>
-      <c r="D274" t="s">
-        <v>588</v>
-      </c>
-      <c r="E274" t="s">
-        <v>589</v>
-      </c>
       <c r="F274" s="1">
-        <v>46255</v>
+        <v>46254</v>
       </c>
       <c r="G274" s="1">
         <v>46255</v>
@@ -9228,16 +9369,16 @@
         <v>0</v>
       </c>
       <c r="B275" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="C275" t="s">
         <v>80</v>
       </c>
       <c r="D275" t="s">
-        <v>591</v>
+        <v>16</v>
       </c>
       <c r="E275" t="s">
-        <v>592</v>
+        <v>17</v>
       </c>
       <c r="F275" s="1">
         <v>46255</v>
@@ -9251,16 +9392,16 @@
         <v>0</v>
       </c>
       <c r="B276" t="s">
-        <v>593</v>
+        <v>589</v>
       </c>
       <c r="C276" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D276" t="s">
-        <v>98</v>
+        <v>37</v>
       </c>
       <c r="E276" t="s">
-        <v>99</v>
+        <v>38</v>
       </c>
       <c r="F276" s="1">
         <v>46255</v>
@@ -9274,16 +9415,16 @@
         <v>0</v>
       </c>
       <c r="B277" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="C277" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D277" t="s">
-        <v>219</v>
+        <v>591</v>
       </c>
       <c r="E277" t="s">
-        <v>220</v>
+        <v>592</v>
       </c>
       <c r="F277" s="1">
         <v>46255</v>
@@ -9297,16 +9438,16 @@
         <v>0</v>
       </c>
       <c r="B278" t="s">
+        <v>593</v>
+      </c>
+      <c r="C278" t="s">
+        <v>2</v>
+      </c>
+      <c r="D278" t="s">
+        <v>594</v>
+      </c>
+      <c r="E278" t="s">
         <v>595</v>
-      </c>
-      <c r="C278" t="s">
-        <v>80</v>
-      </c>
-      <c r="D278" t="s">
-        <v>219</v>
-      </c>
-      <c r="E278" t="s">
-        <v>220</v>
       </c>
       <c r="F278" s="1">
         <v>46255</v>
@@ -9326,10 +9467,10 @@
         <v>80</v>
       </c>
       <c r="D279" t="s">
-        <v>597</v>
+        <v>98</v>
       </c>
       <c r="E279" t="s">
-        <v>598</v>
+        <v>99</v>
       </c>
       <c r="F279" s="1">
         <v>46255</v>
@@ -9343,16 +9484,16 @@
         <v>0</v>
       </c>
       <c r="B280" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="C280" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D280" t="s">
-        <v>16</v>
+        <v>219</v>
       </c>
       <c r="E280" t="s">
-        <v>17</v>
+        <v>220</v>
       </c>
       <c r="F280" s="1">
         <v>46255</v>
@@ -9366,16 +9507,16 @@
         <v>0</v>
       </c>
       <c r="B281" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="C281" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D281" t="s">
-        <v>340</v>
+        <v>219</v>
       </c>
       <c r="E281" t="s">
-        <v>341</v>
+        <v>220</v>
       </c>
       <c r="F281" s="1">
         <v>46255</v>
@@ -9389,16 +9530,16 @@
         <v>0</v>
       </c>
       <c r="B282" t="s">
+        <v>599</v>
+      </c>
+      <c r="C282" t="s">
+        <v>80</v>
+      </c>
+      <c r="D282" t="s">
+        <v>600</v>
+      </c>
+      <c r="E282" t="s">
         <v>601</v>
-      </c>
-      <c r="C282" t="s">
-        <v>80</v>
-      </c>
-      <c r="D282" t="s">
-        <v>438</v>
-      </c>
-      <c r="E282" t="s">
-        <v>439</v>
       </c>
       <c r="F282" s="1">
         <v>46255</v>
@@ -9418,10 +9559,10 @@
         <v>80</v>
       </c>
       <c r="D283" t="s">
-        <v>603</v>
+        <v>16</v>
       </c>
       <c r="E283" t="s">
-        <v>604</v>
+        <v>17</v>
       </c>
       <c r="F283" s="1">
         <v>46255</v>
@@ -9435,16 +9576,16 @@
         <v>0</v>
       </c>
       <c r="B284" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="C284" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D284" t="s">
-        <v>603</v>
+        <v>340</v>
       </c>
       <c r="E284" t="s">
-        <v>604</v>
+        <v>341</v>
       </c>
       <c r="F284" s="1">
         <v>46255</v>
@@ -9458,16 +9599,16 @@
         <v>0</v>
       </c>
       <c r="B285" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="C285" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D285" t="s">
-        <v>607</v>
+        <v>438</v>
       </c>
       <c r="E285" t="s">
-        <v>608</v>
+        <v>439</v>
       </c>
       <c r="F285" s="1">
         <v>46255</v>
@@ -9481,16 +9622,16 @@
         <v>0</v>
       </c>
       <c r="B286" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="C286" t="s">
         <v>80</v>
       </c>
       <c r="D286" t="s">
-        <v>425</v>
+        <v>606</v>
       </c>
       <c r="E286" t="s">
-        <v>426</v>
+        <v>607</v>
       </c>
       <c r="F286" s="1">
         <v>46255</v>
@@ -9504,16 +9645,16 @@
         <v>0</v>
       </c>
       <c r="B287" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="C287" t="s">
         <v>80</v>
       </c>
       <c r="D287" t="s">
-        <v>425</v>
+        <v>606</v>
       </c>
       <c r="E287" t="s">
-        <v>426</v>
+        <v>607</v>
       </c>
       <c r="F287" s="1">
         <v>46255</v>
@@ -9527,16 +9668,16 @@
         <v>0</v>
       </c>
       <c r="B288" t="s">
+        <v>609</v>
+      </c>
+      <c r="C288" t="s">
+        <v>2</v>
+      </c>
+      <c r="D288" t="s">
+        <v>610</v>
+      </c>
+      <c r="E288" t="s">
         <v>611</v>
-      </c>
-      <c r="C288" t="s">
-        <v>80</v>
-      </c>
-      <c r="D288" t="s">
-        <v>370</v>
-      </c>
-      <c r="E288" t="s">
-        <v>371</v>
       </c>
       <c r="F288" s="1">
         <v>46255</v>
@@ -9556,10 +9697,10 @@
         <v>80</v>
       </c>
       <c r="D289" t="s">
-        <v>370</v>
+        <v>425</v>
       </c>
       <c r="E289" t="s">
-        <v>371</v>
+        <v>426</v>
       </c>
       <c r="F289" s="1">
         <v>46255</v>
@@ -9579,10 +9720,10 @@
         <v>80</v>
       </c>
       <c r="D290" t="s">
-        <v>614</v>
+        <v>425</v>
       </c>
       <c r="E290" t="s">
-        <v>615</v>
+        <v>426</v>
       </c>
       <c r="F290" s="1">
         <v>46255</v>
@@ -9596,16 +9737,16 @@
         <v>0</v>
       </c>
       <c r="B291" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="C291" t="s">
         <v>80</v>
       </c>
       <c r="D291" t="s">
-        <v>432</v>
+        <v>370</v>
       </c>
       <c r="E291" t="s">
-        <v>433</v>
+        <v>371</v>
       </c>
       <c r="F291" s="1">
         <v>46255</v>
@@ -9619,16 +9760,16 @@
         <v>0</v>
       </c>
       <c r="B292" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="C292" t="s">
         <v>80</v>
       </c>
       <c r="D292" t="s">
-        <v>432</v>
+        <v>370</v>
       </c>
       <c r="E292" t="s">
-        <v>433</v>
+        <v>371</v>
       </c>
       <c r="F292" s="1">
         <v>46255</v>
@@ -9642,16 +9783,16 @@
         <v>0</v>
       </c>
       <c r="B293" t="s">
+        <v>616</v>
+      </c>
+      <c r="C293" t="s">
+        <v>80</v>
+      </c>
+      <c r="D293" t="s">
+        <v>617</v>
+      </c>
+      <c r="E293" t="s">
         <v>618</v>
-      </c>
-      <c r="C293" t="s">
-        <v>80</v>
-      </c>
-      <c r="D293" t="s">
-        <v>351</v>
-      </c>
-      <c r="E293" t="s">
-        <v>352</v>
       </c>
       <c r="F293" s="1">
         <v>46255</v>
@@ -9668,13 +9809,13 @@
         <v>619</v>
       </c>
       <c r="C294" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D294" t="s">
-        <v>620</v>
+        <v>432</v>
       </c>
       <c r="E294" t="s">
-        <v>621</v>
+        <v>433</v>
       </c>
       <c r="F294" s="1">
         <v>46255</v>
@@ -9688,16 +9829,16 @@
         <v>0</v>
       </c>
       <c r="B295" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="C295" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D295" t="s">
-        <v>7</v>
+        <v>432</v>
       </c>
       <c r="E295" t="s">
-        <v>8</v>
+        <v>433</v>
       </c>
       <c r="F295" s="1">
         <v>46255</v>
@@ -9711,16 +9852,16 @@
         <v>0</v>
       </c>
       <c r="B296" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="C296" t="s">
         <v>80</v>
       </c>
       <c r="D296" t="s">
-        <v>101</v>
+        <v>351</v>
       </c>
       <c r="E296" t="s">
-        <v>102</v>
+        <v>352</v>
       </c>
       <c r="F296" s="1">
         <v>46255</v>
@@ -9734,16 +9875,16 @@
         <v>0</v>
       </c>
       <c r="B297" t="s">
+        <v>622</v>
+      </c>
+      <c r="C297" t="s">
+        <v>2</v>
+      </c>
+      <c r="D297" t="s">
+        <v>623</v>
+      </c>
+      <c r="E297" t="s">
         <v>624</v>
-      </c>
-      <c r="C297" t="s">
-        <v>80</v>
-      </c>
-      <c r="D297" t="s">
-        <v>384</v>
-      </c>
-      <c r="E297" t="s">
-        <v>385</v>
       </c>
       <c r="F297" s="1">
         <v>46255</v>
@@ -9763,10 +9904,10 @@
         <v>80</v>
       </c>
       <c r="D298" t="s">
-        <v>603</v>
+        <v>7</v>
       </c>
       <c r="E298" t="s">
-        <v>604</v>
+        <v>8</v>
       </c>
       <c r="F298" s="1">
         <v>46255</v>
@@ -9786,10 +9927,10 @@
         <v>80</v>
       </c>
       <c r="D299" t="s">
-        <v>384</v>
+        <v>101</v>
       </c>
       <c r="E299" t="s">
-        <v>385</v>
+        <v>102</v>
       </c>
       <c r="F299" s="1">
         <v>46255</v>
@@ -9806,13 +9947,13 @@
         <v>627</v>
       </c>
       <c r="C300" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D300" t="s">
-        <v>628</v>
+        <v>384</v>
       </c>
       <c r="E300" t="s">
-        <v>629</v>
+        <v>385</v>
       </c>
       <c r="F300" s="1">
         <v>46255</v>
@@ -9826,16 +9967,16 @@
         <v>0</v>
       </c>
       <c r="B301" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="C301" t="s">
         <v>80</v>
       </c>
       <c r="D301" t="s">
-        <v>224</v>
+        <v>606</v>
       </c>
       <c r="E301" t="s">
-        <v>225</v>
+        <v>607</v>
       </c>
       <c r="F301" s="1">
         <v>46255</v>
@@ -9849,16 +9990,16 @@
         <v>0</v>
       </c>
       <c r="B302" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="C302" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D302" t="s">
-        <v>74</v>
+        <v>384</v>
       </c>
       <c r="E302" t="s">
-        <v>75</v>
+        <v>385</v>
       </c>
       <c r="F302" s="1">
         <v>46255</v>
@@ -9872,16 +10013,16 @@
         <v>0</v>
       </c>
       <c r="B303" t="s">
+        <v>630</v>
+      </c>
+      <c r="C303" t="s">
+        <v>2</v>
+      </c>
+      <c r="D303" t="s">
+        <v>631</v>
+      </c>
+      <c r="E303" t="s">
         <v>632</v>
-      </c>
-      <c r="C303" t="s">
-        <v>80</v>
-      </c>
-      <c r="D303" t="s">
-        <v>633</v>
-      </c>
-      <c r="E303" t="s">
-        <v>634</v>
       </c>
       <c r="F303" s="1">
         <v>46255</v>
@@ -9895,16 +10036,16 @@
         <v>0</v>
       </c>
       <c r="B304" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="C304" t="s">
         <v>80</v>
       </c>
       <c r="D304" t="s">
-        <v>636</v>
+        <v>224</v>
       </c>
       <c r="E304" t="s">
-        <v>637</v>
+        <v>225</v>
       </c>
       <c r="F304" s="1">
         <v>46255</v>
@@ -9918,16 +10059,16 @@
         <v>0</v>
       </c>
       <c r="B305" t="s">
-        <v>638</v>
+        <v>634</v>
       </c>
       <c r="C305" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D305" t="s">
-        <v>376</v>
+        <v>74</v>
       </c>
       <c r="E305" t="s">
-        <v>377</v>
+        <v>75</v>
       </c>
       <c r="F305" s="1">
         <v>46255</v>
@@ -9941,16 +10082,16 @@
         <v>0</v>
       </c>
       <c r="B306" t="s">
-        <v>639</v>
+        <v>635</v>
       </c>
       <c r="C306" t="s">
         <v>80</v>
       </c>
       <c r="D306" t="s">
-        <v>48</v>
+        <v>636</v>
       </c>
       <c r="E306" t="s">
-        <v>49</v>
+        <v>637</v>
       </c>
       <c r="F306" s="1">
         <v>46255</v>
@@ -9964,16 +10105,16 @@
         <v>0</v>
       </c>
       <c r="B307" t="s">
+        <v>638</v>
+      </c>
+      <c r="C307" t="s">
+        <v>80</v>
+      </c>
+      <c r="D307" t="s">
+        <v>639</v>
+      </c>
+      <c r="E307" t="s">
         <v>640</v>
-      </c>
-      <c r="C307" t="s">
-        <v>80</v>
-      </c>
-      <c r="D307" t="s">
-        <v>376</v>
-      </c>
-      <c r="E307" t="s">
-        <v>377</v>
       </c>
       <c r="F307" s="1">
         <v>46255</v>
@@ -9993,10 +10134,10 @@
         <v>80</v>
       </c>
       <c r="D308" t="s">
-        <v>642</v>
+        <v>376</v>
       </c>
       <c r="E308" t="s">
-        <v>643</v>
+        <v>377</v>
       </c>
       <c r="F308" s="1">
         <v>46255</v>
@@ -10010,16 +10151,16 @@
         <v>0</v>
       </c>
       <c r="B309" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="C309" t="s">
         <v>80</v>
       </c>
       <c r="D309" t="s">
-        <v>642</v>
+        <v>48</v>
       </c>
       <c r="E309" t="s">
-        <v>643</v>
+        <v>49</v>
       </c>
       <c r="F309" s="1">
         <v>46255</v>
@@ -10033,7 +10174,7 @@
         <v>0</v>
       </c>
       <c r="B310" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="C310" t="s">
         <v>80</v>
@@ -10056,16 +10197,16 @@
         <v>0</v>
       </c>
       <c r="B311" t="s">
+        <v>644</v>
+      </c>
+      <c r="C311" t="s">
+        <v>80</v>
+      </c>
+      <c r="D311" t="s">
+        <v>645</v>
+      </c>
+      <c r="E311" t="s">
         <v>646</v>
-      </c>
-      <c r="C311" t="s">
-        <v>80</v>
-      </c>
-      <c r="D311" t="s">
-        <v>647</v>
-      </c>
-      <c r="E311" t="s">
-        <v>648</v>
       </c>
       <c r="F311" s="1">
         <v>46255</v>
@@ -10079,16 +10220,16 @@
         <v>0</v>
       </c>
       <c r="B312" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="C312" t="s">
         <v>80</v>
       </c>
       <c r="D312" t="s">
-        <v>650</v>
+        <v>645</v>
       </c>
       <c r="E312" t="s">
-        <v>651</v>
+        <v>646</v>
       </c>
       <c r="F312" s="1">
         <v>46255</v>
@@ -10102,16 +10243,16 @@
         <v>0</v>
       </c>
       <c r="B313" t="s">
-        <v>652</v>
+        <v>648</v>
       </c>
       <c r="C313" t="s">
         <v>80</v>
       </c>
       <c r="D313" t="s">
-        <v>101</v>
+        <v>376</v>
       </c>
       <c r="E313" t="s">
-        <v>102</v>
+        <v>377</v>
       </c>
       <c r="F313" s="1">
         <v>46255</v>
@@ -10125,16 +10266,16 @@
         <v>0</v>
       </c>
       <c r="B314" t="s">
-        <v>653</v>
+        <v>649</v>
       </c>
       <c r="C314" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D314" t="s">
-        <v>147</v>
+        <v>650</v>
       </c>
       <c r="E314" t="s">
-        <v>148</v>
+        <v>651</v>
       </c>
       <c r="F314" s="1">
         <v>46255</v>
@@ -10148,22 +10289,22 @@
         <v>0</v>
       </c>
       <c r="B315" t="s">
+        <v>652</v>
+      </c>
+      <c r="C315" t="s">
+        <v>2</v>
+      </c>
+      <c r="D315" t="s">
+        <v>653</v>
+      </c>
+      <c r="E315" t="s">
         <v>654</v>
       </c>
-      <c r="C315" t="s">
-        <v>80</v>
-      </c>
-      <c r="D315" t="s">
-        <v>650</v>
-      </c>
-      <c r="E315" t="s">
-        <v>651</v>
-      </c>
       <c r="F315" s="1">
         <v>46255</v>
       </c>
       <c r="G315" s="1">
-        <v>46256</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="316" spans="1:7" x14ac:dyDescent="0.2">
@@ -10177,10 +10318,10 @@
         <v>80</v>
       </c>
       <c r="D316" t="s">
-        <v>358</v>
+        <v>101</v>
       </c>
       <c r="E316" t="s">
-        <v>359</v>
+        <v>102</v>
       </c>
       <c r="F316" s="1">
         <v>46255</v>
@@ -10200,16 +10341,16 @@
         <v>80</v>
       </c>
       <c r="D317" t="s">
-        <v>16</v>
+        <v>147</v>
       </c>
       <c r="E317" t="s">
-        <v>17</v>
+        <v>148</v>
       </c>
       <c r="F317" s="1">
         <v>46255</v>
       </c>
       <c r="G317" s="1">
-        <v>46256</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="318" spans="1:7" x14ac:dyDescent="0.2">
@@ -10220,19 +10361,19 @@
         <v>657</v>
       </c>
       <c r="C318" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D318" t="s">
-        <v>658</v>
+        <v>653</v>
       </c>
       <c r="E318" t="s">
-        <v>659</v>
+        <v>654</v>
       </c>
       <c r="F318" s="1">
         <v>46255</v>
       </c>
       <c r="G318" s="1">
-        <v>46255</v>
+        <v>46256</v>
       </c>
     </row>
     <row r="319" spans="1:7" x14ac:dyDescent="0.2">
@@ -10240,16 +10381,16 @@
         <v>0</v>
       </c>
       <c r="B319" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="C319" t="s">
         <v>80</v>
       </c>
       <c r="D319" t="s">
-        <v>138</v>
+        <v>358</v>
       </c>
       <c r="E319" t="s">
-        <v>139</v>
+        <v>359</v>
       </c>
       <c r="F319" s="1">
         <v>46255</v>
@@ -10263,22 +10404,22 @@
         <v>0</v>
       </c>
       <c r="B320" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="C320" t="s">
         <v>80</v>
       </c>
       <c r="D320" t="s">
-        <v>658</v>
+        <v>16</v>
       </c>
       <c r="E320" t="s">
-        <v>659</v>
+        <v>17</v>
       </c>
       <c r="F320" s="1">
         <v>46255</v>
       </c>
       <c r="G320" s="1">
-        <v>46255</v>
+        <v>46256</v>
       </c>
     </row>
     <row r="321" spans="1:7" x14ac:dyDescent="0.2">
@@ -10286,16 +10427,16 @@
         <v>0</v>
       </c>
       <c r="B321" t="s">
+        <v>660</v>
+      </c>
+      <c r="C321" t="s">
+        <v>80</v>
+      </c>
+      <c r="D321" t="s">
+        <v>661</v>
+      </c>
+      <c r="E321" t="s">
         <v>662</v>
-      </c>
-      <c r="C321" t="s">
-        <v>80</v>
-      </c>
-      <c r="D321" t="s">
-        <v>358</v>
-      </c>
-      <c r="E321" t="s">
-        <v>359</v>
       </c>
       <c r="F321" s="1">
         <v>46255</v>
@@ -10315,10 +10456,10 @@
         <v>80</v>
       </c>
       <c r="D322" t="s">
-        <v>664</v>
+        <v>138</v>
       </c>
       <c r="E322" t="s">
-        <v>665</v>
+        <v>139</v>
       </c>
       <c r="F322" s="1">
         <v>46255</v>
@@ -10332,16 +10473,16 @@
         <v>0</v>
       </c>
       <c r="B323" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="C323" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D323" t="s">
-        <v>667</v>
+        <v>661</v>
       </c>
       <c r="E323" t="s">
-        <v>668</v>
+        <v>662</v>
       </c>
       <c r="F323" s="1">
         <v>46255</v>
@@ -10355,16 +10496,16 @@
         <v>0</v>
       </c>
       <c r="B324" t="s">
-        <v>669</v>
+        <v>665</v>
       </c>
       <c r="C324" t="s">
         <v>80</v>
       </c>
       <c r="D324" t="s">
-        <v>181</v>
+        <v>358</v>
       </c>
       <c r="E324" t="s">
-        <v>182</v>
+        <v>359</v>
       </c>
       <c r="F324" s="1">
         <v>46255</v>
@@ -10378,22 +10519,22 @@
         <v>0</v>
       </c>
       <c r="B325" t="s">
-        <v>670</v>
+        <v>666</v>
       </c>
       <c r="C325" t="s">
         <v>80</v>
       </c>
       <c r="D325" t="s">
-        <v>671</v>
+        <v>667</v>
       </c>
       <c r="E325" t="s">
-        <v>672</v>
+        <v>668</v>
       </c>
       <c r="F325" s="1">
         <v>46255</v>
       </c>
       <c r="G325" s="1">
-        <v>46256</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="326" spans="1:7" x14ac:dyDescent="0.2">
@@ -10401,16 +10542,16 @@
         <v>0</v>
       </c>
       <c r="B326" t="s">
-        <v>673</v>
+        <v>669</v>
       </c>
       <c r="C326" t="s">
         <v>80</v>
       </c>
       <c r="D326" t="s">
+        <v>670</v>
+      </c>
+      <c r="E326" t="s">
         <v>671</v>
-      </c>
-      <c r="E326" t="s">
-        <v>672</v>
       </c>
       <c r="F326" s="1">
         <v>46255</v>
@@ -10424,16 +10565,16 @@
         <v>0</v>
       </c>
       <c r="B327" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="C327" t="s">
         <v>80</v>
       </c>
       <c r="D327" t="s">
-        <v>675</v>
+        <v>181</v>
       </c>
       <c r="E327" t="s">
-        <v>676</v>
+        <v>182</v>
       </c>
       <c r="F327" s="1">
         <v>46255</v>
@@ -10447,22 +10588,22 @@
         <v>0</v>
       </c>
       <c r="B328" t="s">
-        <v>677</v>
+        <v>673</v>
       </c>
       <c r="C328" t="s">
         <v>80</v>
       </c>
       <c r="D328" t="s">
-        <v>678</v>
+        <v>674</v>
       </c>
       <c r="E328" t="s">
-        <v>679</v>
+        <v>675</v>
       </c>
       <c r="F328" s="1">
         <v>46255</v>
       </c>
       <c r="G328" s="1">
-        <v>46255</v>
+        <v>46256</v>
       </c>
     </row>
     <row r="329" spans="1:7" x14ac:dyDescent="0.2">
@@ -10470,16 +10611,16 @@
         <v>0</v>
       </c>
       <c r="B329" t="s">
-        <v>680</v>
+        <v>676</v>
       </c>
       <c r="C329" t="s">
         <v>80</v>
       </c>
       <c r="D329" t="s">
-        <v>681</v>
+        <v>674</v>
       </c>
       <c r="E329" t="s">
-        <v>682</v>
+        <v>675</v>
       </c>
       <c r="F329" s="1">
         <v>46255</v>
@@ -10493,16 +10634,16 @@
         <v>0</v>
       </c>
       <c r="B330" t="s">
-        <v>683</v>
+        <v>677</v>
       </c>
       <c r="C330" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D330" t="s">
-        <v>340</v>
+        <v>678</v>
       </c>
       <c r="E330" t="s">
-        <v>341</v>
+        <v>679</v>
       </c>
       <c r="F330" s="1">
         <v>46255</v>
@@ -10516,16 +10657,16 @@
         <v>0</v>
       </c>
       <c r="B331" t="s">
-        <v>684</v>
+        <v>680</v>
       </c>
       <c r="C331" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D331" t="s">
-        <v>685</v>
+        <v>681</v>
       </c>
       <c r="E331" t="s">
-        <v>686</v>
+        <v>682</v>
       </c>
       <c r="F331" s="1">
         <v>46255</v>
@@ -10539,16 +10680,16 @@
         <v>0</v>
       </c>
       <c r="B332" t="s">
-        <v>687</v>
+        <v>683</v>
       </c>
       <c r="C332" t="s">
         <v>80</v>
       </c>
       <c r="D332" t="s">
+        <v>684</v>
+      </c>
+      <c r="E332" t="s">
         <v>685</v>
-      </c>
-      <c r="E332" t="s">
-        <v>686</v>
       </c>
       <c r="F332" s="1">
         <v>46255</v>
@@ -10562,16 +10703,16 @@
         <v>0</v>
       </c>
       <c r="B333" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="C333" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D333" t="s">
-        <v>689</v>
+        <v>340</v>
       </c>
       <c r="E333" t="s">
-        <v>690</v>
+        <v>341</v>
       </c>
       <c r="F333" s="1">
         <v>46255</v>
@@ -10585,16 +10726,16 @@
         <v>0</v>
       </c>
       <c r="B334" t="s">
-        <v>691</v>
+        <v>687</v>
       </c>
       <c r="C334" t="s">
         <v>80</v>
       </c>
       <c r="D334" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="E334" t="s">
-        <v>693</v>
+        <v>689</v>
       </c>
       <c r="F334" s="1">
         <v>46255</v>
@@ -10608,16 +10749,16 @@
         <v>0</v>
       </c>
       <c r="B335" t="s">
-        <v>694</v>
+        <v>690</v>
       </c>
       <c r="C335" t="s">
         <v>80</v>
       </c>
       <c r="D335" t="s">
-        <v>695</v>
+        <v>688</v>
       </c>
       <c r="E335" t="s">
-        <v>696</v>
+        <v>689</v>
       </c>
       <c r="F335" s="1">
         <v>46255</v>
@@ -10631,16 +10772,16 @@
         <v>0</v>
       </c>
       <c r="B336" t="s">
-        <v>697</v>
+        <v>691</v>
       </c>
       <c r="C336" t="s">
         <v>80</v>
       </c>
       <c r="D336" t="s">
-        <v>138</v>
+        <v>692</v>
       </c>
       <c r="E336" t="s">
-        <v>139</v>
+        <v>693</v>
       </c>
       <c r="F336" s="1">
         <v>46255</v>
@@ -10654,16 +10795,16 @@
         <v>0</v>
       </c>
       <c r="B337" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
       <c r="C337" t="s">
         <v>80</v>
       </c>
       <c r="D337" t="s">
-        <v>98</v>
+        <v>695</v>
       </c>
       <c r="E337" t="s">
-        <v>99</v>
+        <v>696</v>
       </c>
       <c r="F337" s="1">
         <v>46255</v>
@@ -10677,16 +10818,16 @@
         <v>0</v>
       </c>
       <c r="B338" t="s">
+        <v>697</v>
+      </c>
+      <c r="C338" t="s">
+        <v>2</v>
+      </c>
+      <c r="D338" t="s">
+        <v>698</v>
+      </c>
+      <c r="E338" t="s">
         <v>699</v>
-      </c>
-      <c r="C338" t="s">
-        <v>80</v>
-      </c>
-      <c r="D338" t="s">
-        <v>597</v>
-      </c>
-      <c r="E338" t="s">
-        <v>598</v>
       </c>
       <c r="F338" s="1">
         <v>46255</v>
@@ -10706,10 +10847,10 @@
         <v>80</v>
       </c>
       <c r="D339" t="s">
-        <v>25</v>
+        <v>138</v>
       </c>
       <c r="E339" t="s">
-        <v>26</v>
+        <v>139</v>
       </c>
       <c r="F339" s="1">
         <v>46255</v>
@@ -10729,10 +10870,10 @@
         <v>80</v>
       </c>
       <c r="D340" t="s">
-        <v>37</v>
+        <v>98</v>
       </c>
       <c r="E340" t="s">
-        <v>38</v>
+        <v>99</v>
       </c>
       <c r="F340" s="1">
         <v>46255</v>
@@ -10752,10 +10893,10 @@
         <v>80</v>
       </c>
       <c r="D341" t="s">
-        <v>354</v>
+        <v>600</v>
       </c>
       <c r="E341" t="s">
-        <v>355</v>
+        <v>601</v>
       </c>
       <c r="F341" s="1">
         <v>46255</v>
@@ -10772,13 +10913,13 @@
         <v>703</v>
       </c>
       <c r="C342" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D342" t="s">
-        <v>704</v>
+        <v>25</v>
       </c>
       <c r="E342" t="s">
-        <v>705</v>
+        <v>26</v>
       </c>
       <c r="F342" s="1">
         <v>46255</v>
@@ -10792,16 +10933,16 @@
         <v>0</v>
       </c>
       <c r="B343" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="C343" t="s">
         <v>80</v>
       </c>
       <c r="D343" t="s">
-        <v>707</v>
+        <v>37</v>
       </c>
       <c r="E343" t="s">
-        <v>708</v>
+        <v>38</v>
       </c>
       <c r="F343" s="1">
         <v>46255</v>
@@ -10815,16 +10956,16 @@
         <v>0</v>
       </c>
       <c r="B344" t="s">
-        <v>709</v>
+        <v>705</v>
       </c>
       <c r="C344" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D344" t="s">
-        <v>403</v>
+        <v>354</v>
       </c>
       <c r="E344" t="s">
-        <v>404</v>
+        <v>355</v>
       </c>
       <c r="F344" s="1">
         <v>46255</v>
@@ -10838,16 +10979,16 @@
         <v>0</v>
       </c>
       <c r="B345" t="s">
-        <v>710</v>
+        <v>706</v>
       </c>
       <c r="C345" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D345" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="E345" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="F345" s="1">
         <v>46255</v>
@@ -10861,22 +11002,22 @@
         <v>0</v>
       </c>
       <c r="B346" t="s">
-        <v>713</v>
+        <v>709</v>
       </c>
       <c r="C346" t="s">
         <v>80</v>
       </c>
       <c r="D346" t="s">
-        <v>529</v>
+        <v>710</v>
       </c>
       <c r="E346" t="s">
-        <v>530</v>
+        <v>711</v>
       </c>
       <c r="F346" s="1">
         <v>46255</v>
       </c>
       <c r="G346" s="1">
-        <v>46255</v>
+        <v>46258</v>
       </c>
     </row>
     <row r="347" spans="1:7" x14ac:dyDescent="0.2">
@@ -10884,16 +11025,16 @@
         <v>0</v>
       </c>
       <c r="B347" t="s">
+        <v>712</v>
+      </c>
+      <c r="C347" t="s">
+        <v>80</v>
+      </c>
+      <c r="D347" t="s">
+        <v>713</v>
+      </c>
+      <c r="E347" t="s">
         <v>714</v>
-      </c>
-      <c r="C347" t="s">
-        <v>80</v>
-      </c>
-      <c r="D347" t="s">
-        <v>715</v>
-      </c>
-      <c r="E347" t="s">
-        <v>716</v>
       </c>
       <c r="F347" s="1">
         <v>46255</v>
@@ -10907,16 +11048,16 @@
         <v>0</v>
       </c>
       <c r="B348" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="C348" t="s">
         <v>80</v>
       </c>
       <c r="D348" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="E348" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="F348" s="1">
         <v>46255</v>
@@ -10930,16 +11071,16 @@
         <v>0</v>
       </c>
       <c r="B349" t="s">
+        <v>716</v>
+      </c>
+      <c r="C349" t="s">
+        <v>2</v>
+      </c>
+      <c r="D349" t="s">
+        <v>717</v>
+      </c>
+      <c r="E349" t="s">
         <v>718</v>
-      </c>
-      <c r="C349" t="s">
-        <v>80</v>
-      </c>
-      <c r="D349" t="s">
-        <v>719</v>
-      </c>
-      <c r="E349" t="s">
-        <v>720</v>
       </c>
       <c r="F349" s="1">
         <v>46255</v>
@@ -10953,16 +11094,16 @@
         <v>0</v>
       </c>
       <c r="B350" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="C350" t="s">
         <v>80</v>
       </c>
       <c r="D350" t="s">
-        <v>16</v>
+        <v>534</v>
       </c>
       <c r="E350" t="s">
-        <v>17</v>
+        <v>535</v>
       </c>
       <c r="F350" s="1">
         <v>46255</v>
@@ -10973,105 +11114,105 @@
     </row>
     <row r="351" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A351" t="s">
+        <v>0</v>
+      </c>
+      <c r="B351" t="s">
+        <v>720</v>
+      </c>
+      <c r="C351" t="s">
+        <v>80</v>
+      </c>
+      <c r="D351" t="s">
+        <v>721</v>
+      </c>
+      <c r="E351" t="s">
         <v>722</v>
       </c>
-      <c r="B351" t="s">
-        <v>723</v>
-      </c>
-      <c r="C351" t="s">
-        <v>2</v>
-      </c>
-      <c r="D351" t="s">
-        <v>351</v>
-      </c>
-      <c r="E351" t="s">
-        <v>352</v>
-      </c>
       <c r="F351" s="1">
-        <v>46148</v>
+        <v>46255</v>
       </c>
       <c r="G351" s="1">
-        <v>46149</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="352" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A352" t="s">
-        <v>724</v>
+        <v>0</v>
       </c>
       <c r="B352" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="C352" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D352" t="s">
-        <v>41</v>
+        <v>406</v>
       </c>
       <c r="E352" t="s">
-        <v>42</v>
+        <v>407</v>
       </c>
       <c r="F352" s="1">
-        <v>46133</v>
+        <v>46255</v>
       </c>
       <c r="G352" s="1">
-        <v>46134</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="353" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A353" t="s">
+        <v>0</v>
+      </c>
+      <c r="B353" t="s">
         <v>724</v>
       </c>
-      <c r="B353" t="s">
+      <c r="C353" t="s">
+        <v>2</v>
+      </c>
+      <c r="D353" t="s">
+        <v>725</v>
+      </c>
+      <c r="E353" t="s">
         <v>726</v>
       </c>
-      <c r="C353" t="s">
-        <v>6</v>
-      </c>
-      <c r="D353" t="s">
-        <v>41</v>
-      </c>
-      <c r="E353" t="s">
-        <v>42</v>
-      </c>
       <c r="F353" s="1">
-        <v>46134</v>
+        <v>46255</v>
       </c>
       <c r="G353" s="1">
-        <v>46134</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="354" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A354" t="s">
-        <v>724</v>
+        <v>0</v>
       </c>
       <c r="B354" t="s">
         <v>727</v>
       </c>
       <c r="C354" t="s">
-        <v>6</v>
+        <v>80</v>
       </c>
       <c r="D354" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E354" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F354" s="1">
-        <v>46156</v>
+        <v>46255</v>
       </c>
       <c r="G354" s="1">
-        <v>46156</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="355" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A355" t="s">
-        <v>724</v>
+        <v>0</v>
       </c>
       <c r="B355" t="s">
         <v>728</v>
       </c>
       <c r="C355" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D355" t="s">
         <v>729</v>
@@ -11080,547 +11221,547 @@
         <v>730</v>
       </c>
       <c r="F355" s="1">
-        <v>46195</v>
+        <v>46255</v>
       </c>
       <c r="G355" s="1">
-        <v>46195</v>
+        <v>46258</v>
       </c>
     </row>
     <row r="356" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A356" t="s">
-        <v>724</v>
+        <v>0</v>
       </c>
       <c r="B356" t="s">
         <v>731</v>
       </c>
       <c r="C356" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D356" t="s">
-        <v>732</v>
+        <v>729</v>
       </c>
       <c r="E356" t="s">
-        <v>733</v>
+        <v>730</v>
       </c>
       <c r="F356" s="1">
-        <v>46206</v>
+        <v>46255</v>
       </c>
       <c r="G356" s="1">
-        <v>46252</v>
+        <v>46258</v>
       </c>
     </row>
     <row r="357" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A357" t="s">
-        <v>724</v>
+        <v>0</v>
       </c>
       <c r="B357" t="s">
+        <v>732</v>
+      </c>
+      <c r="C357" t="s">
+        <v>80</v>
+      </c>
+      <c r="D357" t="s">
+        <v>733</v>
+      </c>
+      <c r="E357" t="s">
         <v>734</v>
       </c>
-      <c r="C357" t="s">
-        <v>96</v>
-      </c>
-      <c r="D357" t="s">
-        <v>735</v>
-      </c>
-      <c r="E357" t="s">
-        <v>736</v>
-      </c>
       <c r="F357" s="1">
-        <v>46209</v>
+        <v>46255</v>
       </c>
       <c r="G357" s="1">
-        <v>46218</v>
+        <v>46258</v>
       </c>
     </row>
     <row r="358" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A358" t="s">
-        <v>724</v>
+        <v>0</v>
       </c>
       <c r="B358" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="C358" t="s">
-        <v>6</v>
+        <v>80</v>
       </c>
       <c r="D358" t="s">
-        <v>738</v>
+        <v>586</v>
       </c>
       <c r="E358" t="s">
-        <v>739</v>
+        <v>587</v>
       </c>
       <c r="F358" s="1">
-        <v>46213</v>
+        <v>46255</v>
       </c>
       <c r="G358" s="1">
-        <v>46213</v>
+        <v>46258</v>
       </c>
     </row>
     <row r="359" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A359" t="s">
-        <v>724</v>
+        <v>0</v>
       </c>
       <c r="B359" t="s">
-        <v>740</v>
+        <v>736</v>
       </c>
       <c r="C359" t="s">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="D359" t="s">
-        <v>741</v>
+        <v>586</v>
       </c>
       <c r="E359" t="s">
-        <v>742</v>
+        <v>587</v>
       </c>
       <c r="F359" s="1">
-        <v>46213</v>
+        <v>46255</v>
       </c>
       <c r="G359" s="1">
-        <v>46216</v>
+        <v>46258</v>
       </c>
     </row>
     <row r="360" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A360" t="s">
-        <v>724</v>
+        <v>0</v>
       </c>
       <c r="B360" t="s">
-        <v>743</v>
+        <v>737</v>
       </c>
       <c r="C360" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D360" t="s">
-        <v>133</v>
+        <v>738</v>
       </c>
       <c r="E360" t="s">
-        <v>134</v>
+        <v>739</v>
       </c>
       <c r="F360" s="1">
-        <v>46220</v>
+        <v>46255</v>
       </c>
       <c r="G360" s="1">
-        <v>46231</v>
+        <v>46258</v>
       </c>
     </row>
     <row r="361" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A361" t="s">
-        <v>724</v>
+        <v>0</v>
       </c>
       <c r="B361" t="s">
-        <v>744</v>
+        <v>740</v>
       </c>
       <c r="C361" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D361" t="s">
-        <v>729</v>
+        <v>224</v>
       </c>
       <c r="E361" t="s">
-        <v>730</v>
+        <v>225</v>
       </c>
       <c r="F361" s="1">
-        <v>46223</v>
+        <v>46255</v>
       </c>
       <c r="G361" s="1">
-        <v>46223</v>
+        <v>46258</v>
       </c>
     </row>
     <row r="362" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A362" t="s">
-        <v>724</v>
+        <v>0</v>
       </c>
       <c r="B362" t="s">
-        <v>745</v>
+        <v>741</v>
       </c>
       <c r="C362" t="s">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="D362" t="s">
-        <v>741</v>
+        <v>147</v>
       </c>
       <c r="E362" t="s">
-        <v>742</v>
+        <v>148</v>
       </c>
       <c r="F362" s="1">
-        <v>46224</v>
+        <v>46255</v>
       </c>
       <c r="G362" s="1">
-        <v>46224</v>
+        <v>46258</v>
       </c>
     </row>
     <row r="363" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A363" t="s">
-        <v>724</v>
+        <v>0</v>
       </c>
       <c r="B363" t="s">
-        <v>746</v>
+        <v>742</v>
       </c>
       <c r="C363" t="s">
         <v>80</v>
       </c>
       <c r="D363" t="s">
-        <v>729</v>
+        <v>743</v>
       </c>
       <c r="E363" t="s">
-        <v>730</v>
+        <v>744</v>
       </c>
       <c r="F363" s="1">
-        <v>46230</v>
+        <v>46255</v>
       </c>
       <c r="G363" s="1">
-        <v>46256</v>
+        <v>46258</v>
       </c>
     </row>
     <row r="364" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A364" t="s">
-        <v>724</v>
+        <v>0</v>
       </c>
       <c r="B364" t="s">
+        <v>745</v>
+      </c>
+      <c r="C364" t="s">
+        <v>80</v>
+      </c>
+      <c r="D364" t="s">
+        <v>746</v>
+      </c>
+      <c r="E364" t="s">
         <v>747</v>
       </c>
-      <c r="C364" t="s">
-        <v>2</v>
-      </c>
-      <c r="D364" t="s">
-        <v>133</v>
-      </c>
-      <c r="E364" t="s">
-        <v>134</v>
-      </c>
       <c r="F364" s="1">
-        <v>46232</v>
+        <v>46256</v>
       </c>
       <c r="G364" s="1">
-        <v>46233</v>
+        <v>46258</v>
       </c>
     </row>
     <row r="365" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A365" t="s">
-        <v>724</v>
+        <v>0</v>
       </c>
       <c r="B365" t="s">
         <v>748</v>
       </c>
       <c r="C365" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D365" t="s">
-        <v>133</v>
+        <v>749</v>
       </c>
       <c r="E365" t="s">
-        <v>134</v>
+        <v>750</v>
       </c>
       <c r="F365" s="1">
-        <v>46232</v>
+        <v>46256</v>
       </c>
       <c r="G365" s="1">
-        <v>46233</v>
+        <v>46258</v>
       </c>
     </row>
     <row r="366" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A366" t="s">
-        <v>724</v>
+        <v>0</v>
       </c>
       <c r="B366" t="s">
+        <v>751</v>
+      </c>
+      <c r="C366" t="s">
+        <v>80</v>
+      </c>
+      <c r="D366" t="s">
         <v>749</v>
       </c>
-      <c r="C366" t="s">
-        <v>2</v>
-      </c>
-      <c r="D366" t="s">
-        <v>741</v>
-      </c>
       <c r="E366" t="s">
-        <v>742</v>
+        <v>750</v>
       </c>
       <c r="F366" s="1">
-        <v>46238</v>
+        <v>46256</v>
       </c>
       <c r="G366" s="1">
-        <v>46239</v>
+        <v>46258</v>
       </c>
     </row>
     <row r="367" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A367" t="s">
-        <v>724</v>
+        <v>0</v>
       </c>
       <c r="B367" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="C367" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D367" t="s">
-        <v>41</v>
+        <v>753</v>
       </c>
       <c r="E367" t="s">
-        <v>42</v>
+        <v>754</v>
       </c>
       <c r="F367" s="1">
-        <v>46247</v>
+        <v>46257</v>
       </c>
       <c r="G367" s="1">
-        <v>46252</v>
+        <v>46258</v>
       </c>
     </row>
     <row r="368" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A368" t="s">
-        <v>724</v>
+        <v>0</v>
       </c>
       <c r="B368" t="s">
-        <v>751</v>
+        <v>755</v>
       </c>
       <c r="C368" t="s">
-        <v>6</v>
+        <v>80</v>
       </c>
       <c r="D368" t="s">
-        <v>752</v>
+        <v>756</v>
       </c>
       <c r="E368" t="s">
-        <v>753</v>
+        <v>757</v>
       </c>
       <c r="F368" s="1">
-        <v>46253</v>
+        <v>46257</v>
       </c>
       <c r="G368" s="1">
-        <v>46253</v>
+        <v>46258</v>
       </c>
     </row>
     <row r="369" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A369" t="s">
-        <v>724</v>
+        <v>0</v>
       </c>
       <c r="B369" t="s">
-        <v>754</v>
+        <v>758</v>
       </c>
       <c r="C369" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D369" t="s">
-        <v>741</v>
+        <v>98</v>
       </c>
       <c r="E369" t="s">
-        <v>742</v>
+        <v>99</v>
       </c>
       <c r="F369" s="1">
-        <v>46253</v>
+        <v>46258</v>
       </c>
       <c r="G369" s="1">
-        <v>46254</v>
+        <v>46258</v>
       </c>
     </row>
     <row r="370" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A370" t="s">
-        <v>724</v>
+        <v>0</v>
       </c>
       <c r="B370" t="s">
-        <v>755</v>
+        <v>759</v>
       </c>
       <c r="C370" t="s">
         <v>80</v>
       </c>
       <c r="D370" t="s">
-        <v>475</v>
+        <v>760</v>
       </c>
       <c r="E370" t="s">
-        <v>476</v>
+        <v>761</v>
       </c>
       <c r="F370" s="1">
-        <v>46254</v>
+        <v>46258</v>
       </c>
       <c r="G370" s="1">
-        <v>46254</v>
+        <v>46258</v>
       </c>
     </row>
     <row r="371" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A371" t="s">
-        <v>724</v>
+        <v>0</v>
       </c>
       <c r="B371" t="s">
-        <v>756</v>
+        <v>762</v>
       </c>
       <c r="C371" t="s">
         <v>80</v>
       </c>
       <c r="D371" t="s">
-        <v>741</v>
+        <v>763</v>
       </c>
       <c r="E371" t="s">
-        <v>742</v>
+        <v>764</v>
       </c>
       <c r="F371" s="1">
-        <v>46254</v>
+        <v>46258</v>
       </c>
       <c r="G371" s="1">
-        <v>46255</v>
+        <v>46258</v>
       </c>
     </row>
     <row r="372" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A372" t="s">
-        <v>724</v>
+        <v>0</v>
       </c>
       <c r="B372" t="s">
-        <v>757</v>
+        <v>765</v>
       </c>
       <c r="C372" t="s">
         <v>80</v>
       </c>
       <c r="D372" t="s">
-        <v>509</v>
+        <v>459</v>
       </c>
       <c r="E372" t="s">
-        <v>510</v>
+        <v>460</v>
       </c>
       <c r="F372" s="1">
-        <v>46254</v>
+        <v>46258</v>
       </c>
       <c r="G372" s="1">
-        <v>46254</v>
+        <v>46258</v>
       </c>
     </row>
     <row r="373" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A373" t="s">
-        <v>724</v>
+        <v>0</v>
       </c>
       <c r="B373" t="s">
-        <v>758</v>
+        <v>766</v>
       </c>
       <c r="C373" t="s">
         <v>80</v>
       </c>
       <c r="D373" t="s">
-        <v>141</v>
+        <v>508</v>
       </c>
       <c r="E373" t="s">
-        <v>142</v>
+        <v>509</v>
       </c>
       <c r="F373" s="1">
-        <v>46254</v>
+        <v>46258</v>
       </c>
       <c r="G373" s="1">
-        <v>46255</v>
+        <v>46258</v>
       </c>
     </row>
     <row r="374" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A374" t="s">
-        <v>724</v>
+        <v>0</v>
       </c>
       <c r="B374" t="s">
-        <v>759</v>
+        <v>767</v>
       </c>
       <c r="C374" t="s">
         <v>80</v>
       </c>
       <c r="D374" t="s">
-        <v>156</v>
+        <v>16</v>
       </c>
       <c r="E374" t="s">
-        <v>157</v>
+        <v>17</v>
       </c>
       <c r="F374" s="1">
-        <v>46254</v>
+        <v>46258</v>
       </c>
       <c r="G374" s="1">
-        <v>46255</v>
+        <v>46258</v>
       </c>
     </row>
     <row r="375" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A375" t="s">
-        <v>724</v>
+        <v>0</v>
       </c>
       <c r="B375" t="s">
-        <v>760</v>
+        <v>768</v>
       </c>
       <c r="C375" t="s">
         <v>80</v>
       </c>
       <c r="D375" t="s">
-        <v>156</v>
+        <v>387</v>
       </c>
       <c r="E375" t="s">
-        <v>157</v>
+        <v>388</v>
       </c>
       <c r="F375" s="1">
-        <v>46254</v>
+        <v>46258</v>
       </c>
       <c r="G375" s="1">
-        <v>46255</v>
+        <v>46258</v>
       </c>
     </row>
     <row r="376" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A376" t="s">
-        <v>724</v>
+        <v>0</v>
       </c>
       <c r="B376" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="C376" t="s">
         <v>80</v>
       </c>
       <c r="D376" t="s">
-        <v>156</v>
+        <v>522</v>
       </c>
       <c r="E376" t="s">
-        <v>157</v>
+        <v>523</v>
       </c>
       <c r="F376" s="1">
-        <v>46254</v>
+        <v>46258</v>
       </c>
       <c r="G376" s="1">
-        <v>46255</v>
+        <v>46258</v>
       </c>
     </row>
     <row r="377" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A377" t="s">
-        <v>724</v>
+        <v>0</v>
       </c>
       <c r="B377" t="s">
-        <v>762</v>
+        <v>770</v>
       </c>
       <c r="C377" t="s">
         <v>80</v>
       </c>
       <c r="D377" t="s">
-        <v>574</v>
+        <v>98</v>
       </c>
       <c r="E377" t="s">
-        <v>575</v>
+        <v>99</v>
       </c>
       <c r="F377" s="1">
-        <v>46254</v>
+        <v>46258</v>
       </c>
       <c r="G377" s="1">
-        <v>46255</v>
+        <v>46258</v>
       </c>
     </row>
     <row r="378" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A378" t="s">
-        <v>724</v>
+        <v>0</v>
       </c>
       <c r="B378" t="s">
-        <v>763</v>
+        <v>771</v>
       </c>
       <c r="C378" t="s">
         <v>80</v>
       </c>
       <c r="D378" t="s">
-        <v>574</v>
+        <v>98</v>
       </c>
       <c r="E378" t="s">
-        <v>575</v>
+        <v>99</v>
       </c>
       <c r="F378" s="1">
-        <v>46254</v>
+        <v>46258</v>
       </c>
       <c r="G378" s="1">
-        <v>46255</v>
+        <v>46258</v>
       </c>
     </row>
     <row r="379" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A379" t="s">
-        <v>724</v>
+        <v>0</v>
       </c>
       <c r="B379" t="s">
-        <v>764</v>
+        <v>772</v>
       </c>
       <c r="C379" t="s">
         <v>80</v>
@@ -11632,421 +11773,421 @@
         <v>377</v>
       </c>
       <c r="F379" s="1">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="G379" s="1">
-        <v>46255</v>
+        <v>46258</v>
       </c>
     </row>
     <row r="380" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A380" t="s">
-        <v>724</v>
+        <v>0</v>
       </c>
       <c r="B380" t="s">
-        <v>765</v>
+        <v>773</v>
       </c>
       <c r="C380" t="s">
         <v>80</v>
       </c>
       <c r="D380" t="s">
-        <v>376</v>
+        <v>746</v>
       </c>
       <c r="E380" t="s">
-        <v>377</v>
+        <v>747</v>
       </c>
       <c r="F380" s="1">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="G380" s="1">
-        <v>46255</v>
+        <v>46258</v>
       </c>
     </row>
     <row r="381" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A381" t="s">
-        <v>724</v>
+        <v>774</v>
       </c>
       <c r="B381" t="s">
-        <v>766</v>
+        <v>775</v>
       </c>
       <c r="C381" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D381" t="s">
-        <v>767</v>
+        <v>351</v>
       </c>
       <c r="E381" t="s">
-        <v>768</v>
+        <v>352</v>
       </c>
       <c r="F381" s="1">
-        <v>46255</v>
+        <v>46148</v>
       </c>
       <c r="G381" s="1">
-        <v>46255</v>
+        <v>46149</v>
       </c>
     </row>
     <row r="382" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A382" t="s">
-        <v>769</v>
+        <v>776</v>
       </c>
       <c r="B382" t="s">
-        <v>770</v>
+        <v>777</v>
       </c>
       <c r="C382" t="s">
-        <v>96</v>
+        <v>6</v>
       </c>
       <c r="D382" t="s">
-        <v>771</v>
+        <v>41</v>
       </c>
       <c r="E382" t="s">
-        <v>772</v>
+        <v>42</v>
       </c>
       <c r="F382" s="1">
-        <v>46063</v>
+        <v>46133</v>
       </c>
       <c r="G382" s="1">
-        <v>46064</v>
+        <v>46134</v>
       </c>
     </row>
     <row r="383" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A383" t="s">
-        <v>769</v>
+        <v>776</v>
       </c>
       <c r="B383" t="s">
-        <v>773</v>
+        <v>778</v>
       </c>
       <c r="C383" t="s">
         <v>6</v>
       </c>
       <c r="D383" t="s">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="E383" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="F383" s="1">
-        <v>46113</v>
+        <v>46134</v>
       </c>
       <c r="G383" s="1">
-        <v>46125</v>
+        <v>46134</v>
       </c>
     </row>
     <row r="384" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A384" t="s">
-        <v>769</v>
+        <v>776</v>
       </c>
       <c r="B384" t="s">
-        <v>774</v>
+        <v>779</v>
       </c>
       <c r="C384" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D384" t="s">
-        <v>57</v>
+        <v>19</v>
       </c>
       <c r="E384" t="s">
-        <v>58</v>
+        <v>20</v>
       </c>
       <c r="F384" s="1">
-        <v>46125</v>
+        <v>46156</v>
       </c>
       <c r="G384" s="1">
-        <v>46125</v>
+        <v>46156</v>
       </c>
     </row>
     <row r="385" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A385" t="s">
-        <v>769</v>
+        <v>776</v>
       </c>
       <c r="B385" t="s">
-        <v>775</v>
+        <v>780</v>
       </c>
       <c r="C385" t="s">
         <v>2</v>
       </c>
       <c r="D385" t="s">
-        <v>57</v>
+        <v>760</v>
       </c>
       <c r="E385" t="s">
-        <v>58</v>
+        <v>761</v>
       </c>
       <c r="F385" s="1">
-        <v>46126</v>
+        <v>46195</v>
       </c>
       <c r="G385" s="1">
-        <v>46126</v>
+        <v>46195</v>
       </c>
     </row>
     <row r="386" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A386" t="s">
-        <v>769</v>
+        <v>776</v>
       </c>
       <c r="B386" t="s">
-        <v>776</v>
+        <v>781</v>
       </c>
       <c r="C386" t="s">
         <v>2</v>
       </c>
       <c r="D386" t="s">
-        <v>57</v>
+        <v>782</v>
       </c>
       <c r="E386" t="s">
-        <v>58</v>
+        <v>783</v>
       </c>
       <c r="F386" s="1">
-        <v>46126</v>
+        <v>46206</v>
       </c>
       <c r="G386" s="1">
-        <v>46126</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="387" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A387" t="s">
-        <v>769</v>
+        <v>776</v>
       </c>
       <c r="B387" t="s">
-        <v>777</v>
+        <v>784</v>
       </c>
       <c r="C387" t="s">
-        <v>2</v>
+        <v>96</v>
       </c>
       <c r="D387" t="s">
-        <v>57</v>
+        <v>785</v>
       </c>
       <c r="E387" t="s">
-        <v>58</v>
+        <v>786</v>
       </c>
       <c r="F387" s="1">
-        <v>46128</v>
+        <v>46209</v>
       </c>
       <c r="G387" s="1">
-        <v>46128</v>
+        <v>46218</v>
       </c>
     </row>
     <row r="388" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A388" t="s">
-        <v>769</v>
+        <v>776</v>
       </c>
       <c r="B388" t="s">
-        <v>778</v>
+        <v>787</v>
       </c>
       <c r="C388" t="s">
         <v>6</v>
       </c>
       <c r="D388" t="s">
-        <v>57</v>
+        <v>788</v>
       </c>
       <c r="E388" t="s">
-        <v>58</v>
+        <v>789</v>
       </c>
       <c r="F388" s="1">
-        <v>46132</v>
+        <v>46213</v>
       </c>
       <c r="G388" s="1">
-        <v>46132</v>
+        <v>46213</v>
       </c>
     </row>
     <row r="389" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A389" t="s">
-        <v>769</v>
+        <v>776</v>
       </c>
       <c r="B389" t="s">
-        <v>779</v>
+        <v>790</v>
       </c>
       <c r="C389" t="s">
-        <v>2</v>
+        <v>96</v>
       </c>
       <c r="D389" t="s">
-        <v>57</v>
+        <v>791</v>
       </c>
       <c r="E389" t="s">
-        <v>58</v>
+        <v>792</v>
       </c>
       <c r="F389" s="1">
-        <v>46161</v>
+        <v>46213</v>
       </c>
       <c r="G389" s="1">
-        <v>46161</v>
+        <v>46216</v>
       </c>
     </row>
     <row r="390" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A390" t="s">
-        <v>769</v>
+        <v>776</v>
       </c>
       <c r="B390" t="s">
-        <v>780</v>
+        <v>793</v>
       </c>
       <c r="C390" t="s">
         <v>2</v>
       </c>
       <c r="D390" t="s">
-        <v>57</v>
+        <v>133</v>
       </c>
       <c r="E390" t="s">
-        <v>58</v>
+        <v>134</v>
       </c>
       <c r="F390" s="1">
-        <v>46174</v>
+        <v>46220</v>
       </c>
       <c r="G390" s="1">
-        <v>46174</v>
+        <v>46231</v>
       </c>
     </row>
     <row r="391" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A391" t="s">
-        <v>769</v>
+        <v>776</v>
       </c>
       <c r="B391" t="s">
-        <v>781</v>
+        <v>794</v>
       </c>
       <c r="C391" t="s">
         <v>2</v>
       </c>
       <c r="D391" t="s">
-        <v>57</v>
+        <v>760</v>
       </c>
       <c r="E391" t="s">
-        <v>58</v>
+        <v>761</v>
       </c>
       <c r="F391" s="1">
-        <v>46174</v>
+        <v>46223</v>
       </c>
       <c r="G391" s="1">
-        <v>46174</v>
+        <v>46223</v>
       </c>
     </row>
     <row r="392" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A392" t="s">
-        <v>769</v>
+        <v>776</v>
       </c>
       <c r="B392" t="s">
-        <v>782</v>
+        <v>795</v>
       </c>
       <c r="C392" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="D392" t="s">
-        <v>57</v>
+        <v>791</v>
       </c>
       <c r="E392" t="s">
-        <v>58</v>
+        <v>792</v>
       </c>
       <c r="F392" s="1">
-        <v>46195</v>
+        <v>46224</v>
       </c>
       <c r="G392" s="1">
-        <v>46252</v>
+        <v>46224</v>
       </c>
     </row>
     <row r="393" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A393" t="s">
-        <v>769</v>
+        <v>776</v>
       </c>
       <c r="B393" t="s">
-        <v>783</v>
+        <v>796</v>
       </c>
       <c r="C393" t="s">
-        <v>6</v>
+        <v>80</v>
       </c>
       <c r="D393" t="s">
-        <v>57</v>
+        <v>760</v>
       </c>
       <c r="E393" t="s">
-        <v>58</v>
+        <v>761</v>
       </c>
       <c r="F393" s="1">
-        <v>46210</v>
+        <v>46230</v>
       </c>
       <c r="G393" s="1">
-        <v>46210</v>
+        <v>46256</v>
       </c>
     </row>
     <row r="394" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A394" t="s">
-        <v>769</v>
+        <v>776</v>
       </c>
       <c r="B394" t="s">
-        <v>784</v>
+        <v>797</v>
       </c>
       <c r="C394" t="s">
         <v>2</v>
       </c>
       <c r="D394" t="s">
-        <v>57</v>
+        <v>133</v>
       </c>
       <c r="E394" t="s">
-        <v>58</v>
+        <v>134</v>
       </c>
       <c r="F394" s="1">
-        <v>46213</v>
+        <v>46232</v>
       </c>
       <c r="G394" s="1">
-        <v>46213</v>
+        <v>46233</v>
       </c>
     </row>
     <row r="395" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A395" t="s">
-        <v>769</v>
+        <v>776</v>
       </c>
       <c r="B395" t="s">
-        <v>785</v>
+        <v>798</v>
       </c>
       <c r="C395" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D395" t="s">
-        <v>57</v>
+        <v>133</v>
       </c>
       <c r="E395" t="s">
-        <v>58</v>
+        <v>134</v>
       </c>
       <c r="F395" s="1">
-        <v>46218</v>
+        <v>46232</v>
       </c>
       <c r="G395" s="1">
-        <v>46252</v>
+        <v>46233</v>
       </c>
     </row>
     <row r="396" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A396" t="s">
-        <v>769</v>
+        <v>776</v>
       </c>
       <c r="B396" t="s">
-        <v>786</v>
+        <v>799</v>
       </c>
       <c r="C396" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D396" t="s">
-        <v>77</v>
+        <v>791</v>
       </c>
       <c r="E396" t="s">
-        <v>78</v>
+        <v>792</v>
       </c>
       <c r="F396" s="1">
-        <v>46226</v>
+        <v>46238</v>
       </c>
       <c r="G396" s="1">
-        <v>46226</v>
+        <v>46239</v>
       </c>
     </row>
     <row r="397" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A397" t="s">
-        <v>769</v>
+        <v>776</v>
       </c>
       <c r="B397" t="s">
-        <v>787</v>
+        <v>800</v>
       </c>
       <c r="C397" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D397" t="s">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="E397" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="F397" s="1">
-        <v>46227</v>
+        <v>46247</v>
       </c>
       <c r="G397" s="1">
         <v>46252</v>
@@ -12054,137 +12195,137 @@
     </row>
     <row r="398" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A398" t="s">
-        <v>769</v>
+        <v>776</v>
       </c>
       <c r="B398" t="s">
-        <v>788</v>
+        <v>801</v>
       </c>
       <c r="C398" t="s">
-        <v>80</v>
+        <v>6</v>
       </c>
       <c r="D398" t="s">
-        <v>57</v>
+        <v>802</v>
       </c>
       <c r="E398" t="s">
-        <v>58</v>
+        <v>803</v>
       </c>
       <c r="F398" s="1">
-        <v>46227</v>
+        <v>46253</v>
       </c>
       <c r="G398" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
     </row>
     <row r="399" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A399" t="s">
-        <v>769</v>
+        <v>776</v>
       </c>
       <c r="B399" t="s">
-        <v>789</v>
+        <v>804</v>
       </c>
       <c r="C399" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D399" t="s">
-        <v>57</v>
+        <v>791</v>
       </c>
       <c r="E399" t="s">
-        <v>58</v>
+        <v>792</v>
       </c>
       <c r="F399" s="1">
-        <v>46227</v>
+        <v>46253</v>
       </c>
       <c r="G399" s="1">
-        <v>46228</v>
+        <v>46254</v>
       </c>
     </row>
     <row r="400" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A400" t="s">
-        <v>769</v>
+        <v>776</v>
       </c>
       <c r="B400" t="s">
-        <v>790</v>
+        <v>805</v>
       </c>
       <c r="C400" t="s">
         <v>80</v>
       </c>
       <c r="D400" t="s">
-        <v>77</v>
+        <v>479</v>
       </c>
       <c r="E400" t="s">
-        <v>78</v>
+        <v>480</v>
       </c>
       <c r="F400" s="1">
-        <v>46230</v>
+        <v>46254</v>
       </c>
       <c r="G400" s="1">
-        <v>46252</v>
+        <v>46254</v>
       </c>
     </row>
     <row r="401" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A401" t="s">
-        <v>769</v>
+        <v>776</v>
       </c>
       <c r="B401" t="s">
+        <v>806</v>
+      </c>
+      <c r="C401" t="s">
+        <v>80</v>
+      </c>
+      <c r="D401" t="s">
         <v>791</v>
       </c>
-      <c r="C401" t="s">
-        <v>6</v>
-      </c>
-      <c r="D401" t="s">
-        <v>57</v>
-      </c>
       <c r="E401" t="s">
-        <v>58</v>
+        <v>792</v>
       </c>
       <c r="F401" s="1">
-        <v>46231</v>
+        <v>46254</v>
       </c>
       <c r="G401" s="1">
-        <v>46231</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="402" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A402" t="s">
-        <v>769</v>
+        <v>776</v>
       </c>
       <c r="B402" t="s">
-        <v>792</v>
+        <v>807</v>
       </c>
       <c r="C402" t="s">
-        <v>6</v>
+        <v>80</v>
       </c>
       <c r="D402" t="s">
-        <v>57</v>
+        <v>141</v>
       </c>
       <c r="E402" t="s">
-        <v>58</v>
+        <v>142</v>
       </c>
       <c r="F402" s="1">
         <v>46254</v>
       </c>
       <c r="G402" s="1">
-        <v>46254</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="403" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A403" t="s">
-        <v>769</v>
+        <v>776</v>
       </c>
       <c r="B403" t="s">
-        <v>793</v>
+        <v>808</v>
       </c>
       <c r="C403" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D403" t="s">
-        <v>57</v>
+        <v>577</v>
       </c>
       <c r="E403" t="s">
-        <v>58</v>
+        <v>578</v>
       </c>
       <c r="F403" s="1">
-        <v>46255</v>
+        <v>46254</v>
       </c>
       <c r="G403" s="1">
         <v>46255</v>
@@ -12192,185 +12333,852 @@
     </row>
     <row r="404" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A404" t="s">
-        <v>794</v>
+        <v>776</v>
       </c>
       <c r="B404" t="s">
-        <v>795</v>
+        <v>809</v>
       </c>
       <c r="C404" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D404" t="s">
-        <v>796</v>
+        <v>376</v>
       </c>
       <c r="E404" t="s">
-        <v>797</v>
+        <v>377</v>
       </c>
       <c r="F404" s="1">
-        <v>46083</v>
+        <v>46255</v>
       </c>
       <c r="G404" s="1">
-        <v>46084</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="405" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A405" t="s">
-        <v>794</v>
+        <v>776</v>
       </c>
       <c r="B405" t="s">
-        <v>798</v>
+        <v>810</v>
       </c>
       <c r="C405" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D405" t="s">
-        <v>796</v>
+        <v>376</v>
       </c>
       <c r="E405" t="s">
-        <v>797</v>
+        <v>377</v>
       </c>
       <c r="F405" s="1">
-        <v>46132</v>
+        <v>46255</v>
       </c>
       <c r="G405" s="1">
-        <v>46133</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="406" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A406" t="s">
-        <v>794</v>
+        <v>776</v>
       </c>
       <c r="B406" t="s">
-        <v>799</v>
+        <v>811</v>
       </c>
       <c r="C406" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D406" t="s">
-        <v>800</v>
+        <v>586</v>
       </c>
       <c r="E406" t="s">
-        <v>801</v>
+        <v>587</v>
       </c>
       <c r="F406" s="1">
-        <v>46157</v>
+        <v>46255</v>
       </c>
       <c r="G406" s="1">
-        <v>46157</v>
+        <v>46258</v>
       </c>
     </row>
     <row r="407" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A407" t="s">
-        <v>794</v>
+        <v>776</v>
       </c>
       <c r="B407" t="s">
-        <v>802</v>
+        <v>812</v>
       </c>
       <c r="C407" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D407" t="s">
-        <v>803</v>
+        <v>376</v>
       </c>
       <c r="E407" t="s">
-        <v>804</v>
+        <v>377</v>
       </c>
       <c r="F407" s="1">
-        <v>46168</v>
+        <v>46258</v>
       </c>
       <c r="G407" s="1">
-        <v>46170</v>
+        <v>46258</v>
       </c>
     </row>
     <row r="408" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A408" t="s">
-        <v>794</v>
+        <v>813</v>
       </c>
       <c r="B408" t="s">
-        <v>805</v>
+        <v>814</v>
       </c>
       <c r="C408" t="s">
-        <v>2</v>
+        <v>96</v>
       </c>
       <c r="D408" t="s">
-        <v>800</v>
+        <v>815</v>
       </c>
       <c r="E408" t="s">
-        <v>801</v>
+        <v>816</v>
       </c>
       <c r="F408" s="1">
-        <v>46244</v>
+        <v>46063</v>
       </c>
       <c r="G408" s="1">
-        <v>46244</v>
+        <v>46064</v>
       </c>
     </row>
     <row r="409" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A409" t="s">
-        <v>794</v>
+        <v>813</v>
       </c>
       <c r="B409" t="s">
-        <v>806</v>
+        <v>817</v>
       </c>
       <c r="C409" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D409" t="s">
-        <v>800</v>
+        <v>57</v>
       </c>
       <c r="E409" t="s">
-        <v>801</v>
+        <v>58</v>
       </c>
       <c r="F409" s="1">
-        <v>46247</v>
+        <v>46113</v>
       </c>
       <c r="G409" s="1">
-        <v>46247</v>
+        <v>46125</v>
       </c>
     </row>
     <row r="410" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A410" t="s">
-        <v>794</v>
+        <v>813</v>
       </c>
       <c r="B410" t="s">
-        <v>807</v>
+        <v>818</v>
       </c>
       <c r="C410" t="s">
         <v>2</v>
       </c>
       <c r="D410" t="s">
-        <v>796</v>
+        <v>57</v>
       </c>
       <c r="E410" t="s">
-        <v>797</v>
+        <v>58</v>
       </c>
       <c r="F410" s="1">
-        <v>46247</v>
+        <v>46125</v>
       </c>
       <c r="G410" s="1">
-        <v>46247</v>
+        <v>46125</v>
       </c>
     </row>
     <row r="411" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A411" t="s">
-        <v>794</v>
+        <v>813</v>
       </c>
       <c r="B411" t="s">
-        <v>808</v>
+        <v>819</v>
       </c>
       <c r="C411" t="s">
         <v>2</v>
       </c>
       <c r="D411" t="s">
-        <v>800</v>
+        <v>57</v>
       </c>
       <c r="E411" t="s">
-        <v>801</v>
+        <v>58</v>
       </c>
       <c r="F411" s="1">
-        <v>46255</v>
+        <v>46126</v>
       </c>
       <c r="G411" s="1">
+        <v>46126</v>
+      </c>
+    </row>
+    <row r="412" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A412" t="s">
+        <v>813</v>
+      </c>
+      <c r="B412" t="s">
+        <v>820</v>
+      </c>
+      <c r="C412" t="s">
+        <v>2</v>
+      </c>
+      <c r="D412" t="s">
+        <v>57</v>
+      </c>
+      <c r="E412" t="s">
+        <v>58</v>
+      </c>
+      <c r="F412" s="1">
+        <v>46126</v>
+      </c>
+      <c r="G412" s="1">
+        <v>46126</v>
+      </c>
+    </row>
+    <row r="413" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A413" t="s">
+        <v>813</v>
+      </c>
+      <c r="B413" t="s">
+        <v>821</v>
+      </c>
+      <c r="C413" t="s">
+        <v>2</v>
+      </c>
+      <c r="D413" t="s">
+        <v>57</v>
+      </c>
+      <c r="E413" t="s">
+        <v>58</v>
+      </c>
+      <c r="F413" s="1">
+        <v>46128</v>
+      </c>
+      <c r="G413" s="1">
+        <v>46128</v>
+      </c>
+    </row>
+    <row r="414" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A414" t="s">
+        <v>813</v>
+      </c>
+      <c r="B414" t="s">
+        <v>822</v>
+      </c>
+      <c r="C414" t="s">
+        <v>6</v>
+      </c>
+      <c r="D414" t="s">
+        <v>57</v>
+      </c>
+      <c r="E414" t="s">
+        <v>58</v>
+      </c>
+      <c r="F414" s="1">
+        <v>46132</v>
+      </c>
+      <c r="G414" s="1">
+        <v>46132</v>
+      </c>
+    </row>
+    <row r="415" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A415" t="s">
+        <v>813</v>
+      </c>
+      <c r="B415" t="s">
+        <v>823</v>
+      </c>
+      <c r="C415" t="s">
+        <v>2</v>
+      </c>
+      <c r="D415" t="s">
+        <v>57</v>
+      </c>
+      <c r="E415" t="s">
+        <v>58</v>
+      </c>
+      <c r="F415" s="1">
+        <v>46161</v>
+      </c>
+      <c r="G415" s="1">
+        <v>46161</v>
+      </c>
+    </row>
+    <row r="416" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A416" t="s">
+        <v>813</v>
+      </c>
+      <c r="B416" t="s">
+        <v>824</v>
+      </c>
+      <c r="C416" t="s">
+        <v>2</v>
+      </c>
+      <c r="D416" t="s">
+        <v>57</v>
+      </c>
+      <c r="E416" t="s">
+        <v>58</v>
+      </c>
+      <c r="F416" s="1">
+        <v>46174</v>
+      </c>
+      <c r="G416" s="1">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="417" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A417" t="s">
+        <v>813</v>
+      </c>
+      <c r="B417" t="s">
+        <v>825</v>
+      </c>
+      <c r="C417" t="s">
+        <v>2</v>
+      </c>
+      <c r="D417" t="s">
+        <v>57</v>
+      </c>
+      <c r="E417" t="s">
+        <v>58</v>
+      </c>
+      <c r="F417" s="1">
+        <v>46174</v>
+      </c>
+      <c r="G417" s="1">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="418" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A418" t="s">
+        <v>813</v>
+      </c>
+      <c r="B418" t="s">
+        <v>826</v>
+      </c>
+      <c r="C418" t="s">
+        <v>80</v>
+      </c>
+      <c r="D418" t="s">
+        <v>57</v>
+      </c>
+      <c r="E418" t="s">
+        <v>58</v>
+      </c>
+      <c r="F418" s="1">
+        <v>46195</v>
+      </c>
+      <c r="G418" s="1">
+        <v>46252</v>
+      </c>
+    </row>
+    <row r="419" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A419" t="s">
+        <v>813</v>
+      </c>
+      <c r="B419" t="s">
+        <v>827</v>
+      </c>
+      <c r="C419" t="s">
+        <v>6</v>
+      </c>
+      <c r="D419" t="s">
+        <v>57</v>
+      </c>
+      <c r="E419" t="s">
+        <v>58</v>
+      </c>
+      <c r="F419" s="1">
+        <v>46210</v>
+      </c>
+      <c r="G419" s="1">
+        <v>46210</v>
+      </c>
+    </row>
+    <row r="420" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A420" t="s">
+        <v>813</v>
+      </c>
+      <c r="B420" t="s">
+        <v>828</v>
+      </c>
+      <c r="C420" t="s">
+        <v>2</v>
+      </c>
+      <c r="D420" t="s">
+        <v>57</v>
+      </c>
+      <c r="E420" t="s">
+        <v>58</v>
+      </c>
+      <c r="F420" s="1">
+        <v>46213</v>
+      </c>
+      <c r="G420" s="1">
+        <v>46213</v>
+      </c>
+    </row>
+    <row r="421" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A421" t="s">
+        <v>813</v>
+      </c>
+      <c r="B421" t="s">
+        <v>829</v>
+      </c>
+      <c r="C421" t="s">
+        <v>80</v>
+      </c>
+      <c r="D421" t="s">
+        <v>57</v>
+      </c>
+      <c r="E421" t="s">
+        <v>58</v>
+      </c>
+      <c r="F421" s="1">
+        <v>46218</v>
+      </c>
+      <c r="G421" s="1">
+        <v>46252</v>
+      </c>
+    </row>
+    <row r="422" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A422" t="s">
+        <v>813</v>
+      </c>
+      <c r="B422" t="s">
+        <v>830</v>
+      </c>
+      <c r="C422" t="s">
+        <v>6</v>
+      </c>
+      <c r="D422" t="s">
+        <v>77</v>
+      </c>
+      <c r="E422" t="s">
+        <v>78</v>
+      </c>
+      <c r="F422" s="1">
+        <v>46226</v>
+      </c>
+      <c r="G422" s="1">
+        <v>46226</v>
+      </c>
+    </row>
+    <row r="423" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A423" t="s">
+        <v>813</v>
+      </c>
+      <c r="B423" t="s">
+        <v>831</v>
+      </c>
+      <c r="C423" t="s">
+        <v>80</v>
+      </c>
+      <c r="D423" t="s">
+        <v>57</v>
+      </c>
+      <c r="E423" t="s">
+        <v>58</v>
+      </c>
+      <c r="F423" s="1">
+        <v>46227</v>
+      </c>
+      <c r="G423" s="1">
+        <v>46252</v>
+      </c>
+    </row>
+    <row r="424" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A424" t="s">
+        <v>813</v>
+      </c>
+      <c r="B424" t="s">
+        <v>832</v>
+      </c>
+      <c r="C424" t="s">
+        <v>80</v>
+      </c>
+      <c r="D424" t="s">
+        <v>57</v>
+      </c>
+      <c r="E424" t="s">
+        <v>58</v>
+      </c>
+      <c r="F424" s="1">
+        <v>46227</v>
+      </c>
+      <c r="G424" s="1">
+        <v>46252</v>
+      </c>
+    </row>
+    <row r="425" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A425" t="s">
+        <v>813</v>
+      </c>
+      <c r="B425" t="s">
+        <v>833</v>
+      </c>
+      <c r="C425" t="s">
+        <v>6</v>
+      </c>
+      <c r="D425" t="s">
+        <v>57</v>
+      </c>
+      <c r="E425" t="s">
+        <v>58</v>
+      </c>
+      <c r="F425" s="1">
+        <v>46227</v>
+      </c>
+      <c r="G425" s="1">
+        <v>46228</v>
+      </c>
+    </row>
+    <row r="426" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A426" t="s">
+        <v>813</v>
+      </c>
+      <c r="B426" t="s">
+        <v>834</v>
+      </c>
+      <c r="C426" t="s">
+        <v>80</v>
+      </c>
+      <c r="D426" t="s">
+        <v>77</v>
+      </c>
+      <c r="E426" t="s">
+        <v>78</v>
+      </c>
+      <c r="F426" s="1">
+        <v>46230</v>
+      </c>
+      <c r="G426" s="1">
+        <v>46252</v>
+      </c>
+    </row>
+    <row r="427" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A427" t="s">
+        <v>813</v>
+      </c>
+      <c r="B427" t="s">
+        <v>835</v>
+      </c>
+      <c r="C427" t="s">
+        <v>6</v>
+      </c>
+      <c r="D427" t="s">
+        <v>57</v>
+      </c>
+      <c r="E427" t="s">
+        <v>58</v>
+      </c>
+      <c r="F427" s="1">
+        <v>46231</v>
+      </c>
+      <c r="G427" s="1">
+        <v>46231</v>
+      </c>
+    </row>
+    <row r="428" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A428" t="s">
+        <v>813</v>
+      </c>
+      <c r="B428" t="s">
+        <v>836</v>
+      </c>
+      <c r="C428" t="s">
+        <v>6</v>
+      </c>
+      <c r="D428" t="s">
+        <v>57</v>
+      </c>
+      <c r="E428" t="s">
+        <v>58</v>
+      </c>
+      <c r="F428" s="1">
+        <v>46254</v>
+      </c>
+      <c r="G428" s="1">
+        <v>46254</v>
+      </c>
+    </row>
+    <row r="429" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A429" t="s">
+        <v>813</v>
+      </c>
+      <c r="B429" t="s">
+        <v>837</v>
+      </c>
+      <c r="C429" t="s">
+        <v>2</v>
+      </c>
+      <c r="D429" t="s">
+        <v>57</v>
+      </c>
+      <c r="E429" t="s">
+        <v>58</v>
+      </c>
+      <c r="F429" s="1">
+        <v>46255</v>
+      </c>
+      <c r="G429" s="1">
+        <v>46255</v>
+      </c>
+    </row>
+    <row r="430" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A430" t="s">
+        <v>813</v>
+      </c>
+      <c r="B430" t="s">
+        <v>838</v>
+      </c>
+      <c r="C430" t="s">
+        <v>80</v>
+      </c>
+      <c r="D430" t="s">
+        <v>57</v>
+      </c>
+      <c r="E430" t="s">
+        <v>58</v>
+      </c>
+      <c r="F430" s="1">
+        <v>46258</v>
+      </c>
+      <c r="G430" s="1">
+        <v>46258</v>
+      </c>
+    </row>
+    <row r="431" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A431" t="s">
+        <v>813</v>
+      </c>
+      <c r="B431" t="s">
+        <v>839</v>
+      </c>
+      <c r="C431" t="s">
+        <v>80</v>
+      </c>
+      <c r="D431" t="s">
+        <v>525</v>
+      </c>
+      <c r="E431" t="s">
+        <v>526</v>
+      </c>
+      <c r="F431" s="1">
+        <v>46258</v>
+      </c>
+      <c r="G431" s="1">
+        <v>46258</v>
+      </c>
+    </row>
+    <row r="432" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A432" t="s">
+        <v>813</v>
+      </c>
+      <c r="B432" t="s">
+        <v>840</v>
+      </c>
+      <c r="C432" t="s">
+        <v>80</v>
+      </c>
+      <c r="D432" t="s">
+        <v>57</v>
+      </c>
+      <c r="E432" t="s">
+        <v>58</v>
+      </c>
+      <c r="F432" s="1">
+        <v>46258</v>
+      </c>
+      <c r="G432" s="1">
+        <v>46258</v>
+      </c>
+    </row>
+    <row r="433" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A433" t="s">
+        <v>841</v>
+      </c>
+      <c r="B433" t="s">
+        <v>842</v>
+      </c>
+      <c r="C433" t="s">
+        <v>2</v>
+      </c>
+      <c r="D433" t="s">
+        <v>843</v>
+      </c>
+      <c r="E433" t="s">
+        <v>844</v>
+      </c>
+      <c r="F433" s="1">
+        <v>46083</v>
+      </c>
+      <c r="G433" s="1">
+        <v>46084</v>
+      </c>
+    </row>
+    <row r="434" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A434" t="s">
+        <v>841</v>
+      </c>
+      <c r="B434" t="s">
+        <v>845</v>
+      </c>
+      <c r="C434" t="s">
+        <v>2</v>
+      </c>
+      <c r="D434" t="s">
+        <v>843</v>
+      </c>
+      <c r="E434" t="s">
+        <v>844</v>
+      </c>
+      <c r="F434" s="1">
+        <v>46132</v>
+      </c>
+      <c r="G434" s="1">
+        <v>46133</v>
+      </c>
+    </row>
+    <row r="435" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A435" t="s">
+        <v>841</v>
+      </c>
+      <c r="B435" t="s">
+        <v>846</v>
+      </c>
+      <c r="C435" t="s">
+        <v>2</v>
+      </c>
+      <c r="D435" t="s">
+        <v>847</v>
+      </c>
+      <c r="E435" t="s">
+        <v>848</v>
+      </c>
+      <c r="F435" s="1">
+        <v>46157</v>
+      </c>
+      <c r="G435" s="1">
+        <v>46157</v>
+      </c>
+    </row>
+    <row r="436" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A436" t="s">
+        <v>841</v>
+      </c>
+      <c r="B436" t="s">
+        <v>849</v>
+      </c>
+      <c r="C436" t="s">
+        <v>2</v>
+      </c>
+      <c r="D436" t="s">
+        <v>850</v>
+      </c>
+      <c r="E436" t="s">
+        <v>851</v>
+      </c>
+      <c r="F436" s="1">
+        <v>46168</v>
+      </c>
+      <c r="G436" s="1">
+        <v>46170</v>
+      </c>
+    </row>
+    <row r="437" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A437" t="s">
+        <v>841</v>
+      </c>
+      <c r="B437" t="s">
+        <v>852</v>
+      </c>
+      <c r="C437" t="s">
+        <v>2</v>
+      </c>
+      <c r="D437" t="s">
+        <v>847</v>
+      </c>
+      <c r="E437" t="s">
+        <v>848</v>
+      </c>
+      <c r="F437" s="1">
+        <v>46244</v>
+      </c>
+      <c r="G437" s="1">
+        <v>46244</v>
+      </c>
+    </row>
+    <row r="438" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A438" t="s">
+        <v>841</v>
+      </c>
+      <c r="B438" t="s">
+        <v>853</v>
+      </c>
+      <c r="C438" t="s">
+        <v>2</v>
+      </c>
+      <c r="D438" t="s">
+        <v>847</v>
+      </c>
+      <c r="E438" t="s">
+        <v>848</v>
+      </c>
+      <c r="F438" s="1">
+        <v>46247</v>
+      </c>
+      <c r="G438" s="1">
+        <v>46247</v>
+      </c>
+    </row>
+    <row r="439" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A439" t="s">
+        <v>841</v>
+      </c>
+      <c r="B439" t="s">
+        <v>854</v>
+      </c>
+      <c r="C439" t="s">
+        <v>2</v>
+      </c>
+      <c r="D439" t="s">
+        <v>843</v>
+      </c>
+      <c r="E439" t="s">
+        <v>844</v>
+      </c>
+      <c r="F439" s="1">
+        <v>46247</v>
+      </c>
+      <c r="G439" s="1">
+        <v>46247</v>
+      </c>
+    </row>
+    <row r="440" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A440" t="s">
+        <v>841</v>
+      </c>
+      <c r="B440" t="s">
+        <v>855</v>
+      </c>
+      <c r="C440" t="s">
+        <v>2</v>
+      </c>
+      <c r="D440" t="s">
+        <v>847</v>
+      </c>
+      <c r="E440" t="s">
+        <v>848</v>
+      </c>
+      <c r="F440" s="1">
+        <v>46255</v>
+      </c>
+      <c r="G440" s="1">
         <v>46255</v>
       </c>
     </row>

--- a/Data_ERP/Pedidos Transmicion.xlsx
+++ b/Data_ERP/Pedidos Transmicion.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sistema_Logistico_Peirano\Data_ERP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3B7C429F-80BB-4528-844A-EF115329784E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{93E37392-37F1-43B5-91B5-4D05EBD99B87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1950" yWindow="1950" windowWidth="15375" windowHeight="8325" xr2:uid="{3336A967-536E-497A-9EE5-06074FC30E3B}"/>
   </bookViews>

--- a/Data_ERP/Pedidos Transmicion.xlsx
+++ b/Data_ERP/Pedidos Transmicion.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sistema_Logistico_Peirano\Data_ERP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8DE01029-B422-417C-93D1-43BF9A0DC94F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{328B48CC-EA18-4AE1-AC05-6F8E2E9B7123}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{0B2FB06A-CBC1-4C8D-8E20-58169CDD604B}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{50339531-E259-43D6-AA35-7093338C10F7}"/>
   </bookViews>
   <sheets>
     <sheet name="transmicion" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2317" uniqueCount="900">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2352" uniqueCount="915">
   <si>
     <t>0001</t>
   </si>
@@ -1291,6 +1291,15 @@
     <t xml:space="preserve">  214073</t>
   </si>
   <si>
+    <t xml:space="preserve">  214074</t>
+  </si>
+  <si>
+    <t>BL05</t>
+  </si>
+  <si>
+    <t>BAIGORRIA LEONARDO F.</t>
+  </si>
+  <si>
     <t xml:space="preserve">  214080</t>
   </si>
   <si>
@@ -2444,6 +2453,42 @@
   </si>
   <si>
     <t xml:space="preserve">  214426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214427</t>
+  </si>
+  <si>
+    <t>FE23</t>
+  </si>
+  <si>
+    <t>FERRIND S.A.S.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214429</t>
+  </si>
+  <si>
+    <t>CS53</t>
+  </si>
+  <si>
+    <t>CASTILLO SERGIO R- EM SER SANITARIOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214430</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214431</t>
+  </si>
+  <si>
+    <t>SG24</t>
+  </si>
+  <si>
+    <t>SANITARIOS GUELMIB S.R.L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214433</t>
   </si>
   <si>
     <t>0004</t>
@@ -3169,31 +3214,31 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87B7C5A8-D838-4896-ABD1-4D166ECD9BFD}">
-  <dimension ref="A1:G463"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{141D0937-3DD9-4892-85EB-40087C9D261C}">
+  <dimension ref="A1:G470"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
-        <v>893</v>
+        <v>908</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>894</v>
+        <v>909</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>895</v>
+        <v>910</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>896</v>
+        <v>911</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>897</v>
+        <v>912</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>898</v>
+        <v>913</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>899</v>
+        <v>914</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
@@ -7669,16 +7714,16 @@
         <v>80</v>
       </c>
       <c r="D196" t="s">
-        <v>16</v>
+        <v>424</v>
       </c>
       <c r="E196" t="s">
-        <v>17</v>
+        <v>425</v>
       </c>
       <c r="F196" s="1">
         <v>46254</v>
       </c>
       <c r="G196" s="1">
-        <v>46254</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.2">
@@ -7686,16 +7731,16 @@
         <v>0</v>
       </c>
       <c r="B197" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="C197" t="s">
         <v>80</v>
       </c>
       <c r="D197" t="s">
-        <v>425</v>
+        <v>16</v>
       </c>
       <c r="E197" t="s">
-        <v>426</v>
+        <v>17</v>
       </c>
       <c r="F197" s="1">
         <v>46254</v>
@@ -7712,7 +7757,7 @@
         <v>427</v>
       </c>
       <c r="C198" t="s">
-        <v>6</v>
+        <v>80</v>
       </c>
       <c r="D198" t="s">
         <v>428</v>
@@ -7735,13 +7780,13 @@
         <v>430</v>
       </c>
       <c r="C199" t="s">
-        <v>80</v>
+        <v>6</v>
       </c>
       <c r="D199" t="s">
-        <v>16</v>
+        <v>431</v>
       </c>
       <c r="E199" t="s">
-        <v>17</v>
+        <v>432</v>
       </c>
       <c r="F199" s="1">
         <v>46254</v>
@@ -7755,22 +7800,22 @@
         <v>0</v>
       </c>
       <c r="B200" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="C200" t="s">
         <v>80</v>
       </c>
       <c r="D200" t="s">
-        <v>138</v>
+        <v>16</v>
       </c>
       <c r="E200" t="s">
-        <v>139</v>
+        <v>17</v>
       </c>
       <c r="F200" s="1">
         <v>46254</v>
       </c>
       <c r="G200" s="1">
-        <v>46259</v>
+        <v>46254</v>
       </c>
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.2">
@@ -7778,22 +7823,22 @@
         <v>0</v>
       </c>
       <c r="B201" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="C201" t="s">
         <v>80</v>
       </c>
       <c r="D201" t="s">
-        <v>433</v>
+        <v>138</v>
       </c>
       <c r="E201" t="s">
-        <v>434</v>
+        <v>139</v>
       </c>
       <c r="F201" s="1">
         <v>46254</v>
       </c>
       <c r="G201" s="1">
-        <v>46258</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="202" spans="1:7" x14ac:dyDescent="0.2">
@@ -7807,16 +7852,16 @@
         <v>80</v>
       </c>
       <c r="D202" t="s">
-        <v>351</v>
+        <v>436</v>
       </c>
       <c r="E202" t="s">
-        <v>352</v>
+        <v>437</v>
       </c>
       <c r="F202" s="1">
         <v>46254</v>
       </c>
       <c r="G202" s="1">
-        <v>46254</v>
+        <v>46258</v>
       </c>
     </row>
     <row r="203" spans="1:7" x14ac:dyDescent="0.2">
@@ -7824,22 +7869,22 @@
         <v>0</v>
       </c>
       <c r="B203" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C203" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D203" t="s">
-        <v>437</v>
+        <v>351</v>
       </c>
       <c r="E203" t="s">
-        <v>438</v>
+        <v>352</v>
       </c>
       <c r="F203" s="1">
         <v>46254</v>
       </c>
       <c r="G203" s="1">
-        <v>46255</v>
+        <v>46254</v>
       </c>
     </row>
     <row r="204" spans="1:7" x14ac:dyDescent="0.2">
@@ -7850,19 +7895,19 @@
         <v>439</v>
       </c>
       <c r="C204" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D204" t="s">
-        <v>16</v>
+        <v>440</v>
       </c>
       <c r="E204" t="s">
-        <v>17</v>
+        <v>441</v>
       </c>
       <c r="F204" s="1">
         <v>46254</v>
       </c>
       <c r="G204" s="1">
-        <v>46254</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="205" spans="1:7" x14ac:dyDescent="0.2">
@@ -7870,22 +7915,22 @@
         <v>0</v>
       </c>
       <c r="B205" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="C205" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D205" t="s">
-        <v>138</v>
+        <v>16</v>
       </c>
       <c r="E205" t="s">
-        <v>139</v>
+        <v>17</v>
       </c>
       <c r="F205" s="1">
         <v>46254</v>
       </c>
       <c r="G205" s="1">
-        <v>46255</v>
+        <v>46254</v>
       </c>
     </row>
     <row r="206" spans="1:7" x14ac:dyDescent="0.2">
@@ -7893,22 +7938,22 @@
         <v>0</v>
       </c>
       <c r="B206" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="C206" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D206" t="s">
-        <v>442</v>
+        <v>138</v>
       </c>
       <c r="E206" t="s">
-        <v>443</v>
+        <v>139</v>
       </c>
       <c r="F206" s="1">
         <v>46254</v>
       </c>
       <c r="G206" s="1">
-        <v>46254</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="207" spans="1:7" x14ac:dyDescent="0.2">
@@ -7931,7 +7976,7 @@
         <v>46254</v>
       </c>
       <c r="G207" s="1">
-        <v>46255</v>
+        <v>46254</v>
       </c>
     </row>
     <row r="208" spans="1:7" x14ac:dyDescent="0.2">
@@ -7965,13 +8010,13 @@
         <v>450</v>
       </c>
       <c r="C209" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D209" t="s">
-        <v>212</v>
+        <v>451</v>
       </c>
       <c r="E209" t="s">
-        <v>213</v>
+        <v>452</v>
       </c>
       <c r="F209" s="1">
         <v>46254</v>
@@ -7985,16 +8030,16 @@
         <v>0</v>
       </c>
       <c r="B210" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="C210" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D210" t="s">
-        <v>452</v>
+        <v>212</v>
       </c>
       <c r="E210" t="s">
-        <v>453</v>
+        <v>213</v>
       </c>
       <c r="F210" s="1">
         <v>46254</v>
@@ -8014,13 +8059,13 @@
         <v>80</v>
       </c>
       <c r="D211" t="s">
-        <v>16</v>
+        <v>455</v>
       </c>
       <c r="E211" t="s">
-        <v>17</v>
+        <v>456</v>
       </c>
       <c r="F211" s="1">
-        <v>46255</v>
+        <v>46254</v>
       </c>
       <c r="G211" s="1">
         <v>46255</v>
@@ -8031,16 +8076,16 @@
         <v>0</v>
       </c>
       <c r="B212" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="C212" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D212" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="E212" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F212" s="1">
         <v>46255</v>
@@ -8054,16 +8099,16 @@
         <v>0</v>
       </c>
       <c r="B213" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="C213" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D213" t="s">
-        <v>457</v>
+        <v>37</v>
       </c>
       <c r="E213" t="s">
-        <v>458</v>
+        <v>38</v>
       </c>
       <c r="F213" s="1">
         <v>46255</v>
@@ -8083,10 +8128,10 @@
         <v>80</v>
       </c>
       <c r="D214" t="s">
-        <v>16</v>
+        <v>460</v>
       </c>
       <c r="E214" t="s">
-        <v>17</v>
+        <v>461</v>
       </c>
       <c r="F214" s="1">
         <v>46255</v>
@@ -8100,16 +8145,16 @@
         <v>0</v>
       </c>
       <c r="B215" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="C215" t="s">
         <v>80</v>
       </c>
       <c r="D215" t="s">
-        <v>461</v>
+        <v>16</v>
       </c>
       <c r="E215" t="s">
-        <v>462</v>
+        <v>17</v>
       </c>
       <c r="F215" s="1">
         <v>46255</v>
@@ -8129,10 +8174,10 @@
         <v>80</v>
       </c>
       <c r="D216" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="E216" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="F216" s="1">
         <v>46255</v>
@@ -8146,16 +8191,16 @@
         <v>0</v>
       </c>
       <c r="B217" t="s">
+        <v>466</v>
+      </c>
+      <c r="C217" t="s">
+        <v>80</v>
+      </c>
+      <c r="D217" t="s">
         <v>464</v>
       </c>
-      <c r="C217" t="s">
-        <v>80</v>
-      </c>
-      <c r="D217" t="s">
+      <c r="E217" t="s">
         <v>465</v>
-      </c>
-      <c r="E217" t="s">
-        <v>466</v>
       </c>
       <c r="F217" s="1">
         <v>46255</v>
@@ -8175,10 +8220,10 @@
         <v>80</v>
       </c>
       <c r="D218" t="s">
-        <v>354</v>
+        <v>468</v>
       </c>
       <c r="E218" t="s">
-        <v>355</v>
+        <v>469</v>
       </c>
       <c r="F218" s="1">
         <v>46255</v>
@@ -8192,7 +8237,7 @@
         <v>0</v>
       </c>
       <c r="B219" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="C219" t="s">
         <v>80</v>
@@ -8215,16 +8260,16 @@
         <v>0</v>
       </c>
       <c r="B220" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="C220" t="s">
         <v>80</v>
       </c>
       <c r="D220" t="s">
-        <v>470</v>
+        <v>354</v>
       </c>
       <c r="E220" t="s">
-        <v>471</v>
+        <v>355</v>
       </c>
       <c r="F220" s="1">
         <v>46255</v>
@@ -8244,10 +8289,10 @@
         <v>80</v>
       </c>
       <c r="D221" t="s">
-        <v>344</v>
+        <v>473</v>
       </c>
       <c r="E221" t="s">
-        <v>345</v>
+        <v>474</v>
       </c>
       <c r="F221" s="1">
         <v>46255</v>
@@ -8261,16 +8306,16 @@
         <v>0</v>
       </c>
       <c r="B222" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="C222" t="s">
         <v>80</v>
       </c>
       <c r="D222" t="s">
-        <v>7</v>
+        <v>344</v>
       </c>
       <c r="E222" t="s">
-        <v>8</v>
+        <v>345</v>
       </c>
       <c r="F222" s="1">
         <v>46255</v>
@@ -8284,16 +8329,16 @@
         <v>0</v>
       </c>
       <c r="B223" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="C223" t="s">
         <v>80</v>
       </c>
       <c r="D223" t="s">
-        <v>101</v>
+        <v>7</v>
       </c>
       <c r="E223" t="s">
-        <v>102</v>
+        <v>8</v>
       </c>
       <c r="F223" s="1">
         <v>46255</v>
@@ -8307,16 +8352,16 @@
         <v>0</v>
       </c>
       <c r="B224" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="C224" t="s">
         <v>80</v>
       </c>
       <c r="D224" t="s">
-        <v>461</v>
+        <v>101</v>
       </c>
       <c r="E224" t="s">
-        <v>462</v>
+        <v>102</v>
       </c>
       <c r="F224" s="1">
         <v>46255</v>
@@ -8330,16 +8375,16 @@
         <v>0</v>
       </c>
       <c r="B225" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="C225" t="s">
         <v>80</v>
       </c>
       <c r="D225" t="s">
-        <v>477</v>
+        <v>464</v>
       </c>
       <c r="E225" t="s">
-        <v>478</v>
+        <v>465</v>
       </c>
       <c r="F225" s="1">
         <v>46255</v>
@@ -8359,10 +8404,10 @@
         <v>80</v>
       </c>
       <c r="D226" t="s">
-        <v>48</v>
+        <v>480</v>
       </c>
       <c r="E226" t="s">
-        <v>49</v>
+        <v>481</v>
       </c>
       <c r="F226" s="1">
         <v>46255</v>
@@ -8376,22 +8421,22 @@
         <v>0</v>
       </c>
       <c r="B227" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="C227" t="s">
         <v>80</v>
       </c>
       <c r="D227" t="s">
-        <v>481</v>
+        <v>48</v>
       </c>
       <c r="E227" t="s">
-        <v>482</v>
+        <v>49</v>
       </c>
       <c r="F227" s="1">
         <v>46255</v>
       </c>
       <c r="G227" s="1">
-        <v>46259</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.2">
@@ -8405,10 +8450,10 @@
         <v>80</v>
       </c>
       <c r="D228" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="E228" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="F228" s="1">
         <v>46255</v>
@@ -8422,22 +8467,22 @@
         <v>0</v>
       </c>
       <c r="B229" t="s">
+        <v>486</v>
+      </c>
+      <c r="C229" t="s">
+        <v>80</v>
+      </c>
+      <c r="D229" t="s">
         <v>484</v>
       </c>
-      <c r="C229" t="s">
-        <v>80</v>
-      </c>
-      <c r="D229" t="s">
+      <c r="E229" t="s">
         <v>485</v>
-      </c>
-      <c r="E229" t="s">
-        <v>486</v>
       </c>
       <c r="F229" s="1">
         <v>46255</v>
       </c>
       <c r="G229" s="1">
-        <v>46255</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="230" spans="1:7" x14ac:dyDescent="0.2">
@@ -8451,10 +8496,10 @@
         <v>80</v>
       </c>
       <c r="D230" t="s">
-        <v>101</v>
+        <v>488</v>
       </c>
       <c r="E230" t="s">
-        <v>102</v>
+        <v>489</v>
       </c>
       <c r="F230" s="1">
         <v>46255</v>
@@ -8468,16 +8513,16 @@
         <v>0</v>
       </c>
       <c r="B231" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="C231" t="s">
         <v>80</v>
       </c>
       <c r="D231" t="s">
-        <v>351</v>
+        <v>101</v>
       </c>
       <c r="E231" t="s">
-        <v>352</v>
+        <v>102</v>
       </c>
       <c r="F231" s="1">
         <v>46255</v>
@@ -8491,22 +8536,22 @@
         <v>0</v>
       </c>
       <c r="B232" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="C232" t="s">
         <v>80</v>
       </c>
       <c r="D232" t="s">
-        <v>16</v>
+        <v>351</v>
       </c>
       <c r="E232" t="s">
-        <v>17</v>
+        <v>352</v>
       </c>
       <c r="F232" s="1">
         <v>46255</v>
       </c>
       <c r="G232" s="1">
-        <v>46256</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="233" spans="1:7" x14ac:dyDescent="0.2">
@@ -8514,22 +8559,22 @@
         <v>0</v>
       </c>
       <c r="B233" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="C233" t="s">
         <v>80</v>
       </c>
       <c r="D233" t="s">
-        <v>351</v>
+        <v>16</v>
       </c>
       <c r="E233" t="s">
-        <v>352</v>
+        <v>17</v>
       </c>
       <c r="F233" s="1">
         <v>46255</v>
       </c>
       <c r="G233" s="1">
-        <v>46255</v>
+        <v>46256</v>
       </c>
     </row>
     <row r="234" spans="1:7" x14ac:dyDescent="0.2">
@@ -8537,16 +8582,16 @@
         <v>0</v>
       </c>
       <c r="B234" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="C234" t="s">
         <v>80</v>
       </c>
       <c r="D234" t="s">
-        <v>492</v>
+        <v>351</v>
       </c>
       <c r="E234" t="s">
-        <v>493</v>
+        <v>352</v>
       </c>
       <c r="F234" s="1">
         <v>46255</v>
@@ -8589,10 +8634,10 @@
         <v>80</v>
       </c>
       <c r="D236" t="s">
-        <v>177</v>
+        <v>498</v>
       </c>
       <c r="E236" t="s">
-        <v>178</v>
+        <v>499</v>
       </c>
       <c r="F236" s="1">
         <v>46255</v>
@@ -8606,16 +8651,16 @@
         <v>0</v>
       </c>
       <c r="B237" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="C237" t="s">
         <v>80</v>
       </c>
       <c r="D237" t="s">
-        <v>499</v>
+        <v>177</v>
       </c>
       <c r="E237" t="s">
-        <v>500</v>
+        <v>178</v>
       </c>
       <c r="F237" s="1">
         <v>46255</v>
@@ -8658,10 +8703,10 @@
         <v>80</v>
       </c>
       <c r="D239" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="E239" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="F239" s="1">
         <v>46255</v>
@@ -8675,16 +8720,16 @@
         <v>0</v>
       </c>
       <c r="B240" t="s">
+        <v>507</v>
+      </c>
+      <c r="C240" t="s">
+        <v>80</v>
+      </c>
+      <c r="D240" t="s">
         <v>505</v>
       </c>
-      <c r="C240" t="s">
-        <v>80</v>
-      </c>
-      <c r="D240" t="s">
+      <c r="E240" t="s">
         <v>506</v>
-      </c>
-      <c r="E240" t="s">
-        <v>507</v>
       </c>
       <c r="F240" s="1">
         <v>46255</v>
@@ -8727,10 +8772,10 @@
         <v>80</v>
       </c>
       <c r="D242" t="s">
-        <v>457</v>
+        <v>512</v>
       </c>
       <c r="E242" t="s">
-        <v>458</v>
+        <v>513</v>
       </c>
       <c r="F242" s="1">
         <v>46255</v>
@@ -8744,16 +8789,16 @@
         <v>0</v>
       </c>
       <c r="B243" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="C243" t="s">
         <v>80</v>
       </c>
       <c r="D243" t="s">
-        <v>37</v>
+        <v>460</v>
       </c>
       <c r="E243" t="s">
-        <v>38</v>
+        <v>461</v>
       </c>
       <c r="F243" s="1">
         <v>46255</v>
@@ -8767,22 +8812,22 @@
         <v>0</v>
       </c>
       <c r="B244" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="C244" t="s">
         <v>80</v>
       </c>
       <c r="D244" t="s">
-        <v>514</v>
+        <v>37</v>
       </c>
       <c r="E244" t="s">
-        <v>515</v>
+        <v>38</v>
       </c>
       <c r="F244" s="1">
         <v>46255</v>
       </c>
       <c r="G244" s="1">
-        <v>46258</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="245" spans="1:7" x14ac:dyDescent="0.2">
@@ -8805,7 +8850,7 @@
         <v>46255</v>
       </c>
       <c r="G245" s="1">
-        <v>46255</v>
+        <v>46258</v>
       </c>
     </row>
     <row r="246" spans="1:7" x14ac:dyDescent="0.2">
@@ -8865,10 +8910,10 @@
         <v>80</v>
       </c>
       <c r="D248" t="s">
-        <v>16</v>
+        <v>526</v>
       </c>
       <c r="E248" t="s">
-        <v>17</v>
+        <v>527</v>
       </c>
       <c r="F248" s="1">
         <v>46255</v>
@@ -8882,22 +8927,22 @@
         <v>0</v>
       </c>
       <c r="B249" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="C249" t="s">
         <v>80</v>
       </c>
       <c r="D249" t="s">
-        <v>527</v>
+        <v>16</v>
       </c>
       <c r="E249" t="s">
-        <v>528</v>
+        <v>17</v>
       </c>
       <c r="F249" s="1">
         <v>46255</v>
       </c>
       <c r="G249" s="1">
-        <v>46258</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="250" spans="1:7" x14ac:dyDescent="0.2">
@@ -8911,10 +8956,10 @@
         <v>80</v>
       </c>
       <c r="D250" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="E250" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="F250" s="1">
         <v>46255</v>
@@ -8928,16 +8973,16 @@
         <v>0</v>
       </c>
       <c r="B251" t="s">
+        <v>532</v>
+      </c>
+      <c r="C251" t="s">
+        <v>80</v>
+      </c>
+      <c r="D251" t="s">
         <v>530</v>
       </c>
-      <c r="C251" t="s">
-        <v>80</v>
-      </c>
-      <c r="D251" t="s">
+      <c r="E251" t="s">
         <v>531</v>
-      </c>
-      <c r="E251" t="s">
-        <v>532</v>
       </c>
       <c r="F251" s="1">
         <v>46255</v>
@@ -9003,10 +9048,10 @@
         <v>80</v>
       </c>
       <c r="D254" t="s">
-        <v>452</v>
+        <v>540</v>
       </c>
       <c r="E254" t="s">
-        <v>453</v>
+        <v>541</v>
       </c>
       <c r="F254" s="1">
         <v>46255</v>
@@ -9020,16 +9065,16 @@
         <v>0</v>
       </c>
       <c r="B255" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="C255" t="s">
         <v>80</v>
       </c>
       <c r="D255" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="E255" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="F255" s="1">
         <v>46255</v>
@@ -9043,16 +9088,16 @@
         <v>0</v>
       </c>
       <c r="B256" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="C256" t="s">
         <v>80</v>
       </c>
       <c r="D256" t="s">
-        <v>537</v>
+        <v>455</v>
       </c>
       <c r="E256" t="s">
-        <v>538</v>
+        <v>456</v>
       </c>
       <c r="F256" s="1">
         <v>46255</v>
@@ -9066,19 +9111,19 @@
         <v>0</v>
       </c>
       <c r="B257" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="C257" t="s">
         <v>80</v>
       </c>
       <c r="D257" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="E257" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="F257" s="1">
-        <v>46257</v>
+        <v>46255</v>
       </c>
       <c r="G257" s="1">
         <v>46258</v>
@@ -9101,7 +9146,7 @@
         <v>547</v>
       </c>
       <c r="F258" s="1">
-        <v>46258</v>
+        <v>46257</v>
       </c>
       <c r="G258" s="1">
         <v>46258</v>
@@ -9141,10 +9186,10 @@
         <v>80</v>
       </c>
       <c r="D260" t="s">
-        <v>413</v>
+        <v>552</v>
       </c>
       <c r="E260" t="s">
-        <v>414</v>
+        <v>553</v>
       </c>
       <c r="F260" s="1">
         <v>46258</v>
@@ -9158,16 +9203,16 @@
         <v>0</v>
       </c>
       <c r="B261" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="C261" t="s">
         <v>80</v>
       </c>
       <c r="D261" t="s">
-        <v>433</v>
+        <v>413</v>
       </c>
       <c r="E261" t="s">
-        <v>434</v>
+        <v>414</v>
       </c>
       <c r="F261" s="1">
         <v>46258</v>
@@ -9181,16 +9226,16 @@
         <v>0</v>
       </c>
       <c r="B262" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="C262" t="s">
         <v>80</v>
       </c>
       <c r="D262" t="s">
-        <v>361</v>
+        <v>436</v>
       </c>
       <c r="E262" t="s">
-        <v>362</v>
+        <v>437</v>
       </c>
       <c r="F262" s="1">
         <v>46258</v>
@@ -9204,16 +9249,16 @@
         <v>0</v>
       </c>
       <c r="B263" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="C263" t="s">
         <v>80</v>
       </c>
       <c r="D263" t="s">
-        <v>442</v>
+        <v>361</v>
       </c>
       <c r="E263" t="s">
-        <v>443</v>
+        <v>362</v>
       </c>
       <c r="F263" s="1">
         <v>46258</v>
@@ -9227,22 +9272,22 @@
         <v>0</v>
       </c>
       <c r="B264" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="C264" t="s">
         <v>80</v>
       </c>
       <c r="D264" t="s">
-        <v>556</v>
+        <v>445</v>
       </c>
       <c r="E264" t="s">
-        <v>557</v>
+        <v>446</v>
       </c>
       <c r="F264" s="1">
         <v>46258</v>
       </c>
       <c r="G264" s="1">
-        <v>46259</v>
+        <v>46258</v>
       </c>
     </row>
     <row r="265" spans="1:7" x14ac:dyDescent="0.2">
@@ -9256,16 +9301,16 @@
         <v>80</v>
       </c>
       <c r="D265" t="s">
-        <v>230</v>
+        <v>559</v>
       </c>
       <c r="E265" t="s">
-        <v>231</v>
+        <v>560</v>
       </c>
       <c r="F265" s="1">
         <v>46258</v>
       </c>
       <c r="G265" s="1">
-        <v>46258</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="266" spans="1:7" x14ac:dyDescent="0.2">
@@ -9273,16 +9318,16 @@
         <v>0</v>
       </c>
       <c r="B266" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="C266" t="s">
         <v>80</v>
       </c>
       <c r="D266" t="s">
-        <v>560</v>
+        <v>230</v>
       </c>
       <c r="E266" t="s">
-        <v>561</v>
+        <v>231</v>
       </c>
       <c r="F266" s="1">
         <v>46258</v>
@@ -9311,7 +9356,7 @@
         <v>46258</v>
       </c>
       <c r="G267" s="1">
-        <v>46259</v>
+        <v>46258</v>
       </c>
     </row>
     <row r="268" spans="1:7" x14ac:dyDescent="0.2">
@@ -9325,16 +9370,16 @@
         <v>80</v>
       </c>
       <c r="D268" t="s">
-        <v>336</v>
+        <v>566</v>
       </c>
       <c r="E268" t="s">
-        <v>337</v>
+        <v>567</v>
       </c>
       <c r="F268" s="1">
         <v>46258</v>
       </c>
       <c r="G268" s="1">
-        <v>46258</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="269" spans="1:7" x14ac:dyDescent="0.2">
@@ -9342,16 +9387,16 @@
         <v>0</v>
       </c>
       <c r="B269" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="C269" t="s">
         <v>80</v>
       </c>
       <c r="D269" t="s">
-        <v>567</v>
+        <v>336</v>
       </c>
       <c r="E269" t="s">
-        <v>568</v>
+        <v>337</v>
       </c>
       <c r="F269" s="1">
         <v>46258</v>
@@ -9371,10 +9416,10 @@
         <v>80</v>
       </c>
       <c r="D270" t="s">
-        <v>448</v>
+        <v>570</v>
       </c>
       <c r="E270" t="s">
-        <v>449</v>
+        <v>571</v>
       </c>
       <c r="F270" s="1">
         <v>46258</v>
@@ -9388,16 +9433,16 @@
         <v>0</v>
       </c>
       <c r="B271" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="C271" t="s">
         <v>80</v>
       </c>
       <c r="D271" t="s">
-        <v>183</v>
+        <v>451</v>
       </c>
       <c r="E271" t="s">
-        <v>184</v>
+        <v>452</v>
       </c>
       <c r="F271" s="1">
         <v>46258</v>
@@ -9411,16 +9456,16 @@
         <v>0</v>
       </c>
       <c r="B272" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="C272" t="s">
-        <v>6</v>
+        <v>80</v>
       </c>
       <c r="D272" t="s">
-        <v>572</v>
+        <v>183</v>
       </c>
       <c r="E272" t="s">
-        <v>573</v>
+        <v>184</v>
       </c>
       <c r="F272" s="1">
         <v>46258</v>
@@ -9437,7 +9482,7 @@
         <v>574</v>
       </c>
       <c r="C273" t="s">
-        <v>80</v>
+        <v>6</v>
       </c>
       <c r="D273" t="s">
         <v>575</v>
@@ -9509,10 +9554,10 @@
         <v>80</v>
       </c>
       <c r="D276" t="s">
-        <v>351</v>
+        <v>584</v>
       </c>
       <c r="E276" t="s">
-        <v>352</v>
+        <v>585</v>
       </c>
       <c r="F276" s="1">
         <v>46258</v>
@@ -9526,7 +9571,7 @@
         <v>0</v>
       </c>
       <c r="B277" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="C277" t="s">
         <v>80</v>
@@ -9549,16 +9594,16 @@
         <v>0</v>
       </c>
       <c r="B278" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="C278" t="s">
         <v>80</v>
       </c>
       <c r="D278" t="s">
-        <v>586</v>
+        <v>351</v>
       </c>
       <c r="E278" t="s">
-        <v>587</v>
+        <v>352</v>
       </c>
       <c r="F278" s="1">
         <v>46258</v>
@@ -9578,10 +9623,10 @@
         <v>80</v>
       </c>
       <c r="D279" t="s">
-        <v>48</v>
+        <v>589</v>
       </c>
       <c r="E279" t="s">
-        <v>49</v>
+        <v>590</v>
       </c>
       <c r="F279" s="1">
         <v>46258</v>
@@ -9595,16 +9640,16 @@
         <v>0</v>
       </c>
       <c r="B280" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="C280" t="s">
         <v>80</v>
       </c>
       <c r="D280" t="s">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="E280" t="s">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="F280" s="1">
         <v>46258</v>
@@ -9618,16 +9663,16 @@
         <v>0</v>
       </c>
       <c r="B281" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="C281" t="s">
         <v>80</v>
       </c>
       <c r="D281" t="s">
-        <v>591</v>
+        <v>16</v>
       </c>
       <c r="E281" t="s">
-        <v>592</v>
+        <v>17</v>
       </c>
       <c r="F281" s="1">
         <v>46258</v>
@@ -9647,10 +9692,10 @@
         <v>80</v>
       </c>
       <c r="D282" t="s">
-        <v>16</v>
+        <v>594</v>
       </c>
       <c r="E282" t="s">
-        <v>17</v>
+        <v>595</v>
       </c>
       <c r="F282" s="1">
         <v>46258</v>
@@ -9664,16 +9709,16 @@
         <v>0</v>
       </c>
       <c r="B283" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="C283" t="s">
         <v>80</v>
       </c>
       <c r="D283" t="s">
-        <v>591</v>
+        <v>16</v>
       </c>
       <c r="E283" t="s">
-        <v>592</v>
+        <v>17</v>
       </c>
       <c r="F283" s="1">
         <v>46258</v>
@@ -9687,22 +9732,22 @@
         <v>0</v>
       </c>
       <c r="B284" t="s">
+        <v>597</v>
+      </c>
+      <c r="C284" t="s">
+        <v>80</v>
+      </c>
+      <c r="D284" t="s">
+        <v>594</v>
+      </c>
+      <c r="E284" t="s">
         <v>595</v>
       </c>
-      <c r="C284" t="s">
-        <v>80</v>
-      </c>
-      <c r="D284" t="s">
-        <v>596</v>
-      </c>
-      <c r="E284" t="s">
-        <v>597</v>
-      </c>
       <c r="F284" s="1">
         <v>46258</v>
       </c>
       <c r="G284" s="1">
-        <v>46259</v>
+        <v>46258</v>
       </c>
     </row>
     <row r="285" spans="1:7" x14ac:dyDescent="0.2">
@@ -9725,7 +9770,7 @@
         <v>46258</v>
       </c>
       <c r="G285" s="1">
-        <v>46258</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="286" spans="1:7" x14ac:dyDescent="0.2">
@@ -9739,16 +9784,16 @@
         <v>80</v>
       </c>
       <c r="D286" t="s">
-        <v>344</v>
+        <v>602</v>
       </c>
       <c r="E286" t="s">
-        <v>345</v>
+        <v>603</v>
       </c>
       <c r="F286" s="1">
         <v>46258</v>
       </c>
       <c r="G286" s="1">
-        <v>46259</v>
+        <v>46258</v>
       </c>
     </row>
     <row r="287" spans="1:7" x14ac:dyDescent="0.2">
@@ -9756,22 +9801,22 @@
         <v>0</v>
       </c>
       <c r="B287" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="C287" t="s">
         <v>80</v>
       </c>
       <c r="D287" t="s">
-        <v>170</v>
+        <v>344</v>
       </c>
       <c r="E287" t="s">
-        <v>171</v>
+        <v>345</v>
       </c>
       <c r="F287" s="1">
         <v>46258</v>
       </c>
       <c r="G287" s="1">
-        <v>46258</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="288" spans="1:7" x14ac:dyDescent="0.2">
@@ -9779,16 +9824,16 @@
         <v>0</v>
       </c>
       <c r="B288" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="C288" t="s">
         <v>80</v>
       </c>
       <c r="D288" t="s">
-        <v>461</v>
+        <v>170</v>
       </c>
       <c r="E288" t="s">
-        <v>462</v>
+        <v>171</v>
       </c>
       <c r="F288" s="1">
         <v>46258</v>
@@ -9802,16 +9847,16 @@
         <v>0</v>
       </c>
       <c r="B289" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="C289" t="s">
         <v>80</v>
       </c>
       <c r="D289" t="s">
-        <v>481</v>
+        <v>464</v>
       </c>
       <c r="E289" t="s">
-        <v>482</v>
+        <v>465</v>
       </c>
       <c r="F289" s="1">
         <v>46258</v>
@@ -9825,16 +9870,16 @@
         <v>0</v>
       </c>
       <c r="B290" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="C290" t="s">
         <v>80</v>
       </c>
       <c r="D290" t="s">
-        <v>546</v>
+        <v>484</v>
       </c>
       <c r="E290" t="s">
-        <v>547</v>
+        <v>485</v>
       </c>
       <c r="F290" s="1">
         <v>46258</v>
@@ -9848,16 +9893,16 @@
         <v>0</v>
       </c>
       <c r="B291" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="C291" t="s">
         <v>80</v>
       </c>
       <c r="D291" t="s">
-        <v>581</v>
+        <v>549</v>
       </c>
       <c r="E291" t="s">
-        <v>582</v>
+        <v>550</v>
       </c>
       <c r="F291" s="1">
         <v>46258</v>
@@ -9871,16 +9916,16 @@
         <v>0</v>
       </c>
       <c r="B292" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="C292" t="s">
         <v>80</v>
       </c>
       <c r="D292" t="s">
-        <v>7</v>
+        <v>584</v>
       </c>
       <c r="E292" t="s">
-        <v>8</v>
+        <v>585</v>
       </c>
       <c r="F292" s="1">
         <v>46258</v>
@@ -9894,16 +9939,16 @@
         <v>0</v>
       </c>
       <c r="B293" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="C293" t="s">
         <v>80</v>
       </c>
       <c r="D293" t="s">
-        <v>609</v>
+        <v>7</v>
       </c>
       <c r="E293" t="s">
-        <v>610</v>
+        <v>8</v>
       </c>
       <c r="F293" s="1">
         <v>46258</v>
@@ -9923,10 +9968,10 @@
         <v>80</v>
       </c>
       <c r="D294" t="s">
-        <v>392</v>
+        <v>612</v>
       </c>
       <c r="E294" t="s">
-        <v>393</v>
+        <v>613</v>
       </c>
       <c r="F294" s="1">
         <v>46258</v>
@@ -9940,16 +9985,16 @@
         <v>0</v>
       </c>
       <c r="B295" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="C295" t="s">
         <v>80</v>
       </c>
       <c r="D295" t="s">
-        <v>613</v>
+        <v>392</v>
       </c>
       <c r="E295" t="s">
-        <v>614</v>
+        <v>393</v>
       </c>
       <c r="F295" s="1">
         <v>46258</v>
@@ -9978,7 +10023,7 @@
         <v>46258</v>
       </c>
       <c r="G296" s="1">
-        <v>46259</v>
+        <v>46258</v>
       </c>
     </row>
     <row r="297" spans="1:7" x14ac:dyDescent="0.2">
@@ -10001,7 +10046,7 @@
         <v>46258</v>
       </c>
       <c r="G297" s="1">
-        <v>46258</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="298" spans="1:7" x14ac:dyDescent="0.2">
@@ -10070,7 +10115,7 @@
         <v>46258</v>
       </c>
       <c r="G300" s="1">
-        <v>46259</v>
+        <v>46258</v>
       </c>
     </row>
     <row r="301" spans="1:7" x14ac:dyDescent="0.2">
@@ -10093,7 +10138,7 @@
         <v>46258</v>
       </c>
       <c r="G301" s="1">
-        <v>46258</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="302" spans="1:7" x14ac:dyDescent="0.2">
@@ -10130,10 +10175,10 @@
         <v>80</v>
       </c>
       <c r="D303" t="s">
-        <v>344</v>
+        <v>637</v>
       </c>
       <c r="E303" t="s">
-        <v>345</v>
+        <v>638</v>
       </c>
       <c r="F303" s="1">
         <v>46258</v>
@@ -10147,16 +10192,16 @@
         <v>0</v>
       </c>
       <c r="B304" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="C304" t="s">
         <v>80</v>
       </c>
       <c r="D304" t="s">
-        <v>638</v>
+        <v>344</v>
       </c>
       <c r="E304" t="s">
-        <v>639</v>
+        <v>345</v>
       </c>
       <c r="F304" s="1">
         <v>46258</v>
@@ -10176,16 +10221,16 @@
         <v>80</v>
       </c>
       <c r="D305" t="s">
-        <v>295</v>
+        <v>641</v>
       </c>
       <c r="E305" t="s">
-        <v>296</v>
+        <v>642</v>
       </c>
       <c r="F305" s="1">
         <v>46258</v>
       </c>
       <c r="G305" s="1">
-        <v>46259</v>
+        <v>46258</v>
       </c>
     </row>
     <row r="306" spans="1:7" x14ac:dyDescent="0.2">
@@ -10193,22 +10238,22 @@
         <v>0</v>
       </c>
       <c r="B306" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="C306" t="s">
         <v>80</v>
       </c>
       <c r="D306" t="s">
-        <v>642</v>
+        <v>295</v>
       </c>
       <c r="E306" t="s">
-        <v>643</v>
+        <v>296</v>
       </c>
       <c r="F306" s="1">
         <v>46258</v>
       </c>
       <c r="G306" s="1">
-        <v>46258</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="307" spans="1:7" x14ac:dyDescent="0.2">
@@ -10245,10 +10290,10 @@
         <v>80</v>
       </c>
       <c r="D308" t="s">
-        <v>477</v>
+        <v>648</v>
       </c>
       <c r="E308" t="s">
-        <v>478</v>
+        <v>649</v>
       </c>
       <c r="F308" s="1">
         <v>46258</v>
@@ -10262,16 +10307,16 @@
         <v>0</v>
       </c>
       <c r="B309" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="C309" t="s">
         <v>80</v>
       </c>
       <c r="D309" t="s">
-        <v>649</v>
+        <v>480</v>
       </c>
       <c r="E309" t="s">
-        <v>650</v>
+        <v>481</v>
       </c>
       <c r="F309" s="1">
         <v>46258</v>
@@ -10314,10 +10359,10 @@
         <v>80</v>
       </c>
       <c r="D311" t="s">
-        <v>649</v>
+        <v>655</v>
       </c>
       <c r="E311" t="s">
-        <v>650</v>
+        <v>656</v>
       </c>
       <c r="F311" s="1">
         <v>46258</v>
@@ -10331,16 +10376,16 @@
         <v>0</v>
       </c>
       <c r="B312" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="C312" t="s">
         <v>80</v>
       </c>
       <c r="D312" t="s">
-        <v>656</v>
+        <v>652</v>
       </c>
       <c r="E312" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="F312" s="1">
         <v>46258</v>
@@ -10406,10 +10451,10 @@
         <v>80</v>
       </c>
       <c r="D315" t="s">
-        <v>652</v>
+        <v>665</v>
       </c>
       <c r="E315" t="s">
-        <v>653</v>
+        <v>666</v>
       </c>
       <c r="F315" s="1">
         <v>46258</v>
@@ -10423,22 +10468,22 @@
         <v>0</v>
       </c>
       <c r="B316" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="C316" t="s">
-        <v>6</v>
+        <v>80</v>
       </c>
       <c r="D316" t="s">
-        <v>662</v>
+        <v>655</v>
       </c>
       <c r="E316" t="s">
-        <v>663</v>
+        <v>656</v>
       </c>
       <c r="F316" s="1">
         <v>46258</v>
       </c>
       <c r="G316" s="1">
-        <v>46259</v>
+        <v>46258</v>
       </c>
     </row>
     <row r="317" spans="1:7" x14ac:dyDescent="0.2">
@@ -10446,22 +10491,22 @@
         <v>0</v>
       </c>
       <c r="B317" t="s">
+        <v>668</v>
+      </c>
+      <c r="C317" t="s">
+        <v>6</v>
+      </c>
+      <c r="D317" t="s">
+        <v>665</v>
+      </c>
+      <c r="E317" t="s">
         <v>666</v>
       </c>
-      <c r="C317" t="s">
-        <v>80</v>
-      </c>
-      <c r="D317" t="s">
-        <v>667</v>
-      </c>
-      <c r="E317" t="s">
-        <v>668</v>
-      </c>
       <c r="F317" s="1">
         <v>46258</v>
       </c>
       <c r="G317" s="1">
-        <v>46258</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="318" spans="1:7" x14ac:dyDescent="0.2">
@@ -10475,10 +10520,10 @@
         <v>80</v>
       </c>
       <c r="D318" t="s">
-        <v>652</v>
+        <v>670</v>
       </c>
       <c r="E318" t="s">
-        <v>653</v>
+        <v>671</v>
       </c>
       <c r="F318" s="1">
         <v>46258</v>
@@ -10492,22 +10537,22 @@
         <v>0</v>
       </c>
       <c r="B319" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="C319" t="s">
         <v>80</v>
       </c>
       <c r="D319" t="s">
-        <v>667</v>
+        <v>655</v>
       </c>
       <c r="E319" t="s">
-        <v>668</v>
+        <v>656</v>
       </c>
       <c r="F319" s="1">
         <v>46258</v>
       </c>
       <c r="G319" s="1">
-        <v>46259</v>
+        <v>46258</v>
       </c>
     </row>
     <row r="320" spans="1:7" x14ac:dyDescent="0.2">
@@ -10515,16 +10560,16 @@
         <v>0</v>
       </c>
       <c r="B320" t="s">
+        <v>673</v>
+      </c>
+      <c r="C320" t="s">
+        <v>80</v>
+      </c>
+      <c r="D320" t="s">
+        <v>670</v>
+      </c>
+      <c r="E320" t="s">
         <v>671</v>
-      </c>
-      <c r="C320" t="s">
-        <v>80</v>
-      </c>
-      <c r="D320" t="s">
-        <v>672</v>
-      </c>
-      <c r="E320" t="s">
-        <v>673</v>
       </c>
       <c r="F320" s="1">
         <v>46258</v>
@@ -10553,7 +10598,7 @@
         <v>46258</v>
       </c>
       <c r="G321" s="1">
-        <v>46258</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="322" spans="1:7" x14ac:dyDescent="0.2">
@@ -10590,16 +10635,16 @@
         <v>80</v>
       </c>
       <c r="D323" t="s">
-        <v>662</v>
+        <v>681</v>
       </c>
       <c r="E323" t="s">
-        <v>663</v>
+        <v>682</v>
       </c>
       <c r="F323" s="1">
         <v>46258</v>
       </c>
       <c r="G323" s="1">
-        <v>46259</v>
+        <v>46258</v>
       </c>
     </row>
     <row r="324" spans="1:7" x14ac:dyDescent="0.2">
@@ -10607,22 +10652,22 @@
         <v>0</v>
       </c>
       <c r="B324" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="C324" t="s">
         <v>80</v>
       </c>
       <c r="D324" t="s">
-        <v>682</v>
+        <v>665</v>
       </c>
       <c r="E324" t="s">
-        <v>683</v>
+        <v>666</v>
       </c>
       <c r="F324" s="1">
         <v>46258</v>
       </c>
       <c r="G324" s="1">
-        <v>46258</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="325" spans="1:7" x14ac:dyDescent="0.2">
@@ -10636,10 +10681,10 @@
         <v>80</v>
       </c>
       <c r="D325" t="s">
-        <v>16</v>
+        <v>685</v>
       </c>
       <c r="E325" t="s">
-        <v>17</v>
+        <v>686</v>
       </c>
       <c r="F325" s="1">
         <v>46258</v>
@@ -10653,16 +10698,16 @@
         <v>0</v>
       </c>
       <c r="B326" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="C326" t="s">
         <v>80</v>
       </c>
       <c r="D326" t="s">
-        <v>682</v>
+        <v>16</v>
       </c>
       <c r="E326" t="s">
-        <v>683</v>
+        <v>17</v>
       </c>
       <c r="F326" s="1">
         <v>46258</v>
@@ -10676,22 +10721,22 @@
         <v>0</v>
       </c>
       <c r="B327" t="s">
+        <v>688</v>
+      </c>
+      <c r="C327" t="s">
+        <v>80</v>
+      </c>
+      <c r="D327" t="s">
+        <v>685</v>
+      </c>
+      <c r="E327" t="s">
         <v>686</v>
       </c>
-      <c r="C327" t="s">
-        <v>80</v>
-      </c>
-      <c r="D327" t="s">
-        <v>262</v>
-      </c>
-      <c r="E327" t="s">
-        <v>263</v>
-      </c>
       <c r="F327" s="1">
         <v>46258</v>
       </c>
       <c r="G327" s="1">
-        <v>46259</v>
+        <v>46258</v>
       </c>
     </row>
     <row r="328" spans="1:7" x14ac:dyDescent="0.2">
@@ -10699,16 +10744,16 @@
         <v>0</v>
       </c>
       <c r="B328" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="C328" t="s">
         <v>80</v>
       </c>
       <c r="D328" t="s">
-        <v>688</v>
+        <v>262</v>
       </c>
       <c r="E328" t="s">
-        <v>689</v>
+        <v>263</v>
       </c>
       <c r="F328" s="1">
         <v>46258</v>
@@ -10728,10 +10773,10 @@
         <v>80</v>
       </c>
       <c r="D329" t="s">
-        <v>367</v>
+        <v>691</v>
       </c>
       <c r="E329" t="s">
-        <v>368</v>
+        <v>692</v>
       </c>
       <c r="F329" s="1">
         <v>46258</v>
@@ -10745,16 +10790,16 @@
         <v>0</v>
       </c>
       <c r="B330" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="C330" t="s">
         <v>80</v>
       </c>
       <c r="D330" t="s">
-        <v>457</v>
+        <v>367</v>
       </c>
       <c r="E330" t="s">
-        <v>458</v>
+        <v>368</v>
       </c>
       <c r="F330" s="1">
         <v>46258</v>
@@ -10768,16 +10813,16 @@
         <v>0</v>
       </c>
       <c r="B331" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="C331" t="s">
         <v>80</v>
       </c>
       <c r="D331" t="s">
-        <v>693</v>
+        <v>460</v>
       </c>
       <c r="E331" t="s">
-        <v>694</v>
+        <v>461</v>
       </c>
       <c r="F331" s="1">
         <v>46258</v>
@@ -10797,10 +10842,10 @@
         <v>80</v>
       </c>
       <c r="D332" t="s">
-        <v>326</v>
+        <v>696</v>
       </c>
       <c r="E332" t="s">
-        <v>327</v>
+        <v>697</v>
       </c>
       <c r="F332" s="1">
         <v>46258</v>
@@ -10814,7 +10859,7 @@
         <v>0</v>
       </c>
       <c r="B333" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="C333" t="s">
         <v>80</v>
@@ -10837,16 +10882,16 @@
         <v>0</v>
       </c>
       <c r="B334" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="C334" t="s">
         <v>80</v>
       </c>
       <c r="D334" t="s">
-        <v>698</v>
+        <v>326</v>
       </c>
       <c r="E334" t="s">
-        <v>699</v>
+        <v>327</v>
       </c>
       <c r="F334" s="1">
         <v>46258</v>
@@ -10872,7 +10917,7 @@
         <v>702</v>
       </c>
       <c r="F335" s="1">
-        <v>46259</v>
+        <v>46258</v>
       </c>
       <c r="G335" s="1">
         <v>46259</v>
@@ -10889,10 +10934,10 @@
         <v>80</v>
       </c>
       <c r="D336" t="s">
-        <v>638</v>
+        <v>704</v>
       </c>
       <c r="E336" t="s">
-        <v>639</v>
+        <v>705</v>
       </c>
       <c r="F336" s="1">
         <v>46259</v>
@@ -10906,16 +10951,16 @@
         <v>0</v>
       </c>
       <c r="B337" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="C337" t="s">
         <v>80</v>
       </c>
       <c r="D337" t="s">
-        <v>546</v>
+        <v>641</v>
       </c>
       <c r="E337" t="s">
-        <v>547</v>
+        <v>642</v>
       </c>
       <c r="F337" s="1">
         <v>46259</v>
@@ -10929,16 +10974,16 @@
         <v>0</v>
       </c>
       <c r="B338" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="C338" t="s">
-        <v>6</v>
+        <v>80</v>
       </c>
       <c r="D338" t="s">
-        <v>133</v>
+        <v>549</v>
       </c>
       <c r="E338" t="s">
-        <v>134</v>
+        <v>550</v>
       </c>
       <c r="F338" s="1">
         <v>46259</v>
@@ -10952,16 +10997,16 @@
         <v>0</v>
       </c>
       <c r="B339" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="C339" t="s">
-        <v>80</v>
+        <v>6</v>
       </c>
       <c r="D339" t="s">
-        <v>98</v>
+        <v>133</v>
       </c>
       <c r="E339" t="s">
-        <v>99</v>
+        <v>134</v>
       </c>
       <c r="F339" s="1">
         <v>46259</v>
@@ -10975,16 +11020,16 @@
         <v>0</v>
       </c>
       <c r="B340" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="C340" t="s">
         <v>80</v>
       </c>
       <c r="D340" t="s">
-        <v>133</v>
+        <v>98</v>
       </c>
       <c r="E340" t="s">
-        <v>134</v>
+        <v>99</v>
       </c>
       <c r="F340" s="1">
         <v>46259</v>
@@ -10998,16 +11043,16 @@
         <v>0</v>
       </c>
       <c r="B341" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="C341" t="s">
         <v>80</v>
       </c>
       <c r="D341" t="s">
-        <v>709</v>
+        <v>133</v>
       </c>
       <c r="E341" t="s">
-        <v>710</v>
+        <v>134</v>
       </c>
       <c r="F341" s="1">
         <v>46259</v>
@@ -11027,10 +11072,10 @@
         <v>80</v>
       </c>
       <c r="D342" t="s">
-        <v>347</v>
+        <v>712</v>
       </c>
       <c r="E342" t="s">
-        <v>348</v>
+        <v>713</v>
       </c>
       <c r="F342" s="1">
         <v>46259</v>
@@ -11044,16 +11089,16 @@
         <v>0</v>
       </c>
       <c r="B343" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="C343" t="s">
         <v>80</v>
       </c>
       <c r="D343" t="s">
-        <v>37</v>
+        <v>347</v>
       </c>
       <c r="E343" t="s">
-        <v>38</v>
+        <v>348</v>
       </c>
       <c r="F343" s="1">
         <v>46259</v>
@@ -11067,7 +11112,7 @@
         <v>0</v>
       </c>
       <c r="B344" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="C344" t="s">
         <v>80</v>
@@ -11090,7 +11135,7 @@
         <v>0</v>
       </c>
       <c r="B345" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="C345" t="s">
         <v>80</v>
@@ -11113,7 +11158,7 @@
         <v>0</v>
       </c>
       <c r="B346" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="C346" t="s">
         <v>80</v>
@@ -11136,16 +11181,16 @@
         <v>0</v>
       </c>
       <c r="B347" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="C347" t="s">
         <v>80</v>
       </c>
       <c r="D347" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="E347" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="F347" s="1">
         <v>46259</v>
@@ -11159,16 +11204,16 @@
         <v>0</v>
       </c>
       <c r="B348" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="C348" t="s">
         <v>80</v>
       </c>
       <c r="D348" t="s">
-        <v>433</v>
+        <v>16</v>
       </c>
       <c r="E348" t="s">
-        <v>434</v>
+        <v>17</v>
       </c>
       <c r="F348" s="1">
         <v>46259</v>
@@ -11182,16 +11227,16 @@
         <v>0</v>
       </c>
       <c r="B349" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="C349" t="s">
         <v>80</v>
       </c>
       <c r="D349" t="s">
-        <v>98</v>
+        <v>436</v>
       </c>
       <c r="E349" t="s">
-        <v>99</v>
+        <v>437</v>
       </c>
       <c r="F349" s="1">
         <v>46259</v>
@@ -11205,16 +11250,16 @@
         <v>0</v>
       </c>
       <c r="B350" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="C350" t="s">
         <v>80</v>
       </c>
       <c r="D350" t="s">
-        <v>720</v>
+        <v>98</v>
       </c>
       <c r="E350" t="s">
-        <v>721</v>
+        <v>99</v>
       </c>
       <c r="F350" s="1">
         <v>46259</v>
@@ -11234,10 +11279,10 @@
         <v>80</v>
       </c>
       <c r="D351" t="s">
-        <v>344</v>
+        <v>723</v>
       </c>
       <c r="E351" t="s">
-        <v>345</v>
+        <v>724</v>
       </c>
       <c r="F351" s="1">
         <v>46259</v>
@@ -11251,16 +11296,16 @@
         <v>0</v>
       </c>
       <c r="B352" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="C352" t="s">
         <v>80</v>
       </c>
       <c r="D352" t="s">
-        <v>638</v>
+        <v>344</v>
       </c>
       <c r="E352" t="s">
-        <v>639</v>
+        <v>345</v>
       </c>
       <c r="F352" s="1">
         <v>46259</v>
@@ -11274,16 +11319,16 @@
         <v>0</v>
       </c>
       <c r="B353" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="C353" t="s">
         <v>80</v>
       </c>
       <c r="D353" t="s">
-        <v>336</v>
+        <v>641</v>
       </c>
       <c r="E353" t="s">
-        <v>337</v>
+        <v>642</v>
       </c>
       <c r="F353" s="1">
         <v>46259</v>
@@ -11297,16 +11342,16 @@
         <v>0</v>
       </c>
       <c r="B354" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="C354" t="s">
         <v>80</v>
       </c>
       <c r="D354" t="s">
-        <v>726</v>
+        <v>336</v>
       </c>
       <c r="E354" t="s">
-        <v>727</v>
+        <v>337</v>
       </c>
       <c r="F354" s="1">
         <v>46259</v>
@@ -11349,10 +11394,10 @@
         <v>80</v>
       </c>
       <c r="D356" t="s">
-        <v>329</v>
+        <v>732</v>
       </c>
       <c r="E356" t="s">
-        <v>330</v>
+        <v>733</v>
       </c>
       <c r="F356" s="1">
         <v>46259</v>
@@ -11366,16 +11411,16 @@
         <v>0</v>
       </c>
       <c r="B357" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="C357" t="s">
         <v>80</v>
       </c>
       <c r="D357" t="s">
-        <v>177</v>
+        <v>329</v>
       </c>
       <c r="E357" t="s">
-        <v>178</v>
+        <v>330</v>
       </c>
       <c r="F357" s="1">
         <v>46259</v>
@@ -11389,16 +11434,16 @@
         <v>0</v>
       </c>
       <c r="B358" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="C358" t="s">
         <v>80</v>
       </c>
       <c r="D358" t="s">
-        <v>734</v>
+        <v>177</v>
       </c>
       <c r="E358" t="s">
-        <v>735</v>
+        <v>178</v>
       </c>
       <c r="F358" s="1">
         <v>46259</v>
@@ -11418,10 +11463,10 @@
         <v>80</v>
       </c>
       <c r="D359" t="s">
-        <v>183</v>
+        <v>737</v>
       </c>
       <c r="E359" t="s">
-        <v>184</v>
+        <v>738</v>
       </c>
       <c r="F359" s="1">
         <v>46259</v>
@@ -11435,16 +11480,16 @@
         <v>0</v>
       </c>
       <c r="B360" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="C360" t="s">
         <v>80</v>
       </c>
       <c r="D360" t="s">
-        <v>738</v>
+        <v>183</v>
       </c>
       <c r="E360" t="s">
-        <v>739</v>
+        <v>184</v>
       </c>
       <c r="F360" s="1">
         <v>46259</v>
@@ -11510,10 +11555,10 @@
         <v>80</v>
       </c>
       <c r="D363" t="s">
-        <v>285</v>
+        <v>747</v>
       </c>
       <c r="E363" t="s">
-        <v>286</v>
+        <v>748</v>
       </c>
       <c r="F363" s="1">
         <v>46259</v>
@@ -11527,16 +11572,16 @@
         <v>0</v>
       </c>
       <c r="B364" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="C364" t="s">
         <v>80</v>
       </c>
       <c r="D364" t="s">
-        <v>236</v>
+        <v>285</v>
       </c>
       <c r="E364" t="s">
-        <v>237</v>
+        <v>286</v>
       </c>
       <c r="F364" s="1">
         <v>46259</v>
@@ -11550,16 +11595,16 @@
         <v>0</v>
       </c>
       <c r="B365" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="C365" t="s">
         <v>80</v>
       </c>
       <c r="D365" t="s">
-        <v>672</v>
+        <v>236</v>
       </c>
       <c r="E365" t="s">
-        <v>673</v>
+        <v>237</v>
       </c>
       <c r="F365" s="1">
         <v>46259</v>
@@ -11573,16 +11618,16 @@
         <v>0</v>
       </c>
       <c r="B366" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="C366" t="s">
         <v>80</v>
       </c>
       <c r="D366" t="s">
-        <v>750</v>
+        <v>675</v>
       </c>
       <c r="E366" t="s">
-        <v>751</v>
+        <v>676</v>
       </c>
       <c r="F366" s="1">
         <v>46259</v>
@@ -11602,10 +11647,10 @@
         <v>80</v>
       </c>
       <c r="D367" t="s">
-        <v>634</v>
+        <v>753</v>
       </c>
       <c r="E367" t="s">
-        <v>635</v>
+        <v>754</v>
       </c>
       <c r="F367" s="1">
         <v>46259</v>
@@ -11619,16 +11664,16 @@
         <v>0</v>
       </c>
       <c r="B368" t="s">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="C368" t="s">
         <v>80</v>
       </c>
       <c r="D368" t="s">
-        <v>754</v>
+        <v>637</v>
       </c>
       <c r="E368" t="s">
-        <v>755</v>
+        <v>638</v>
       </c>
       <c r="F368" s="1">
         <v>46259</v>
@@ -11648,10 +11693,10 @@
         <v>80</v>
       </c>
       <c r="D369" t="s">
-        <v>452</v>
+        <v>757</v>
       </c>
       <c r="E369" t="s">
-        <v>453</v>
+        <v>758</v>
       </c>
       <c r="F369" s="1">
         <v>46259</v>
@@ -11665,16 +11710,16 @@
         <v>0</v>
       </c>
       <c r="B370" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="C370" t="s">
         <v>80</v>
       </c>
       <c r="D370" t="s">
-        <v>81</v>
+        <v>455</v>
       </c>
       <c r="E370" t="s">
-        <v>82</v>
+        <v>456</v>
       </c>
       <c r="F370" s="1">
         <v>46259</v>
@@ -11688,16 +11733,16 @@
         <v>0</v>
       </c>
       <c r="B371" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="C371" t="s">
         <v>80</v>
       </c>
       <c r="D371" t="s">
-        <v>759</v>
+        <v>81</v>
       </c>
       <c r="E371" t="s">
-        <v>760</v>
+        <v>82</v>
       </c>
       <c r="F371" s="1">
         <v>46259</v>
@@ -11717,10 +11762,10 @@
         <v>80</v>
       </c>
       <c r="D372" t="s">
-        <v>239</v>
+        <v>762</v>
       </c>
       <c r="E372" t="s">
-        <v>240</v>
+        <v>763</v>
       </c>
       <c r="F372" s="1">
         <v>46259</v>
@@ -11734,16 +11779,16 @@
         <v>0</v>
       </c>
       <c r="B373" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="C373" t="s">
         <v>80</v>
       </c>
       <c r="D373" t="s">
-        <v>763</v>
+        <v>239</v>
       </c>
       <c r="E373" t="s">
-        <v>764</v>
+        <v>240</v>
       </c>
       <c r="F373" s="1">
         <v>46259</v>
@@ -11763,10 +11808,10 @@
         <v>80</v>
       </c>
       <c r="D374" t="s">
-        <v>531</v>
+        <v>766</v>
       </c>
       <c r="E374" t="s">
-        <v>532</v>
+        <v>767</v>
       </c>
       <c r="F374" s="1">
         <v>46259</v>
@@ -11780,16 +11825,16 @@
         <v>0</v>
       </c>
       <c r="B375" t="s">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="C375" t="s">
         <v>80</v>
       </c>
       <c r="D375" t="s">
-        <v>767</v>
+        <v>534</v>
       </c>
       <c r="E375" t="s">
-        <v>768</v>
+        <v>535</v>
       </c>
       <c r="F375" s="1">
         <v>46259</v>
@@ -11809,10 +11854,10 @@
         <v>80</v>
       </c>
       <c r="D376" t="s">
-        <v>242</v>
+        <v>770</v>
       </c>
       <c r="E376" t="s">
-        <v>243</v>
+        <v>771</v>
       </c>
       <c r="F376" s="1">
         <v>46259</v>
@@ -11826,16 +11871,16 @@
         <v>0</v>
       </c>
       <c r="B377" t="s">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="C377" t="s">
         <v>80</v>
       </c>
       <c r="D377" t="s">
-        <v>596</v>
+        <v>242</v>
       </c>
       <c r="E377" t="s">
-        <v>597</v>
+        <v>243</v>
       </c>
       <c r="F377" s="1">
         <v>46259</v>
@@ -11849,16 +11894,16 @@
         <v>0</v>
       </c>
       <c r="B378" t="s">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="C378" t="s">
         <v>80</v>
       </c>
       <c r="D378" t="s">
-        <v>465</v>
+        <v>599</v>
       </c>
       <c r="E378" t="s">
-        <v>466</v>
+        <v>600</v>
       </c>
       <c r="F378" s="1">
         <v>46259</v>
@@ -11872,16 +11917,16 @@
         <v>0</v>
       </c>
       <c r="B379" t="s">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="C379" t="s">
         <v>80</v>
       </c>
       <c r="D379" t="s">
-        <v>98</v>
+        <v>468</v>
       </c>
       <c r="E379" t="s">
-        <v>99</v>
+        <v>469</v>
       </c>
       <c r="F379" s="1">
         <v>46259</v>
@@ -11895,16 +11940,16 @@
         <v>0</v>
       </c>
       <c r="B380" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="C380" t="s">
         <v>80</v>
       </c>
       <c r="D380" t="s">
-        <v>774</v>
+        <v>98</v>
       </c>
       <c r="E380" t="s">
-        <v>775</v>
+        <v>99</v>
       </c>
       <c r="F380" s="1">
         <v>46259</v>
@@ -11947,10 +11992,10 @@
         <v>80</v>
       </c>
       <c r="D382" t="s">
-        <v>774</v>
+        <v>780</v>
       </c>
       <c r="E382" t="s">
-        <v>775</v>
+        <v>781</v>
       </c>
       <c r="F382" s="1">
         <v>46259</v>
@@ -11964,16 +12009,16 @@
         <v>0</v>
       </c>
       <c r="B383" t="s">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="C383" t="s">
         <v>80</v>
       </c>
       <c r="D383" t="s">
-        <v>361</v>
+        <v>777</v>
       </c>
       <c r="E383" t="s">
-        <v>362</v>
+        <v>778</v>
       </c>
       <c r="F383" s="1">
         <v>46259</v>
@@ -11987,16 +12032,16 @@
         <v>0</v>
       </c>
       <c r="B384" t="s">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="C384" t="s">
         <v>80</v>
       </c>
       <c r="D384" t="s">
-        <v>782</v>
+        <v>361</v>
       </c>
       <c r="E384" t="s">
-        <v>783</v>
+        <v>362</v>
       </c>
       <c r="F384" s="1">
         <v>46259</v>
@@ -12016,10 +12061,10 @@
         <v>80</v>
       </c>
       <c r="D385" t="s">
-        <v>622</v>
+        <v>785</v>
       </c>
       <c r="E385" t="s">
-        <v>623</v>
+        <v>786</v>
       </c>
       <c r="F385" s="1">
         <v>46259</v>
@@ -12033,16 +12078,16 @@
         <v>0</v>
       </c>
       <c r="B386" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="C386" t="s">
         <v>80</v>
       </c>
       <c r="D386" t="s">
-        <v>786</v>
+        <v>625</v>
       </c>
       <c r="E386" t="s">
-        <v>787</v>
+        <v>626</v>
       </c>
       <c r="F386" s="1">
         <v>46259</v>
@@ -12062,10 +12107,10 @@
         <v>80</v>
       </c>
       <c r="D387" t="s">
-        <v>351</v>
+        <v>789</v>
       </c>
       <c r="E387" t="s">
-        <v>352</v>
+        <v>790</v>
       </c>
       <c r="F387" s="1">
         <v>46259</v>
@@ -12079,7 +12124,7 @@
         <v>0</v>
       </c>
       <c r="B388" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="C388" t="s">
         <v>80</v>
@@ -12102,7 +12147,7 @@
         <v>0</v>
       </c>
       <c r="B389" t="s">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="C389" t="s">
         <v>80</v>
@@ -12125,16 +12170,16 @@
         <v>0</v>
       </c>
       <c r="B390" t="s">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="C390" t="s">
         <v>80</v>
       </c>
       <c r="D390" t="s">
-        <v>792</v>
+        <v>351</v>
       </c>
       <c r="E390" t="s">
-        <v>793</v>
+        <v>352</v>
       </c>
       <c r="F390" s="1">
         <v>46259</v>
@@ -12200,10 +12245,10 @@
         <v>80</v>
       </c>
       <c r="D393" t="s">
-        <v>147</v>
+        <v>801</v>
       </c>
       <c r="E393" t="s">
-        <v>148</v>
+        <v>802</v>
       </c>
       <c r="F393" s="1">
         <v>46259</v>
@@ -12217,16 +12262,16 @@
         <v>0</v>
       </c>
       <c r="B394" t="s">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="C394" t="s">
         <v>80</v>
       </c>
       <c r="D394" t="s">
-        <v>370</v>
+        <v>147</v>
       </c>
       <c r="E394" t="s">
-        <v>371</v>
+        <v>148</v>
       </c>
       <c r="F394" s="1">
         <v>46259</v>
@@ -12240,16 +12285,16 @@
         <v>0</v>
       </c>
       <c r="B395" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="C395" t="s">
         <v>80</v>
       </c>
       <c r="D395" t="s">
-        <v>803</v>
+        <v>370</v>
       </c>
       <c r="E395" t="s">
-        <v>804</v>
+        <v>371</v>
       </c>
       <c r="F395" s="1">
         <v>46259</v>
@@ -12269,10 +12314,10 @@
         <v>80</v>
       </c>
       <c r="D396" t="s">
-        <v>77</v>
+        <v>806</v>
       </c>
       <c r="E396" t="s">
-        <v>78</v>
+        <v>807</v>
       </c>
       <c r="F396" s="1">
         <v>46259</v>
@@ -12286,16 +12331,16 @@
         <v>0</v>
       </c>
       <c r="B397" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="C397" t="s">
         <v>80</v>
       </c>
       <c r="D397" t="s">
-        <v>164</v>
+        <v>77</v>
       </c>
       <c r="E397" t="s">
-        <v>165</v>
+        <v>78</v>
       </c>
       <c r="F397" s="1">
         <v>46259</v>
@@ -12309,16 +12354,16 @@
         <v>0</v>
       </c>
       <c r="B398" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="C398" t="s">
         <v>80</v>
       </c>
       <c r="D398" t="s">
-        <v>68</v>
+        <v>164</v>
       </c>
       <c r="E398" t="s">
-        <v>69</v>
+        <v>165</v>
       </c>
       <c r="F398" s="1">
         <v>46259</v>
@@ -12329,689 +12374,689 @@
     </row>
     <row r="399" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A399" t="s">
-        <v>808</v>
+        <v>0</v>
       </c>
       <c r="B399" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="C399" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D399" t="s">
-        <v>344</v>
+        <v>68</v>
       </c>
       <c r="E399" t="s">
-        <v>345</v>
+        <v>69</v>
       </c>
       <c r="F399" s="1">
-        <v>46148</v>
+        <v>46259</v>
       </c>
       <c r="G399" s="1">
-        <v>46149</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="400" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A400" t="s">
-        <v>810</v>
+        <v>0</v>
       </c>
       <c r="B400" t="s">
         <v>811</v>
       </c>
       <c r="C400" t="s">
-        <v>6</v>
+        <v>80</v>
       </c>
       <c r="D400" t="s">
-        <v>41</v>
+        <v>812</v>
       </c>
       <c r="E400" t="s">
-        <v>42</v>
+        <v>813</v>
       </c>
       <c r="F400" s="1">
-        <v>46133</v>
+        <v>46259</v>
       </c>
       <c r="G400" s="1">
-        <v>46134</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="401" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A401" t="s">
-        <v>810</v>
+        <v>0</v>
       </c>
       <c r="B401" t="s">
-        <v>812</v>
+        <v>814</v>
       </c>
       <c r="C401" t="s">
-        <v>6</v>
+        <v>80</v>
       </c>
       <c r="D401" t="s">
-        <v>41</v>
+        <v>815</v>
       </c>
       <c r="E401" t="s">
-        <v>42</v>
+        <v>816</v>
       </c>
       <c r="F401" s="1">
-        <v>46134</v>
+        <v>46259</v>
       </c>
       <c r="G401" s="1">
-        <v>46134</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="402" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A402" t="s">
-        <v>810</v>
+        <v>0</v>
       </c>
       <c r="B402" t="s">
-        <v>813</v>
+        <v>817</v>
       </c>
       <c r="C402" t="s">
-        <v>6</v>
+        <v>80</v>
       </c>
       <c r="D402" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E402" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F402" s="1">
-        <v>46156</v>
+        <v>46259</v>
       </c>
       <c r="G402" s="1">
-        <v>46156</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="403" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A403" t="s">
-        <v>810</v>
+        <v>0</v>
       </c>
       <c r="B403" t="s">
-        <v>814</v>
+        <v>818</v>
       </c>
       <c r="C403" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D403" t="s">
-        <v>546</v>
+        <v>819</v>
       </c>
       <c r="E403" t="s">
-        <v>547</v>
+        <v>820</v>
       </c>
       <c r="F403" s="1">
-        <v>46195</v>
+        <v>46259</v>
       </c>
       <c r="G403" s="1">
-        <v>46195</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="404" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A404" t="s">
-        <v>810</v>
+        <v>0</v>
       </c>
       <c r="B404" t="s">
-        <v>815</v>
+        <v>821</v>
       </c>
       <c r="C404" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D404" t="s">
-        <v>798</v>
+        <v>370</v>
       </c>
       <c r="E404" t="s">
-        <v>799</v>
+        <v>371</v>
       </c>
       <c r="F404" s="1">
-        <v>46206</v>
+        <v>46259</v>
       </c>
       <c r="G404" s="1">
-        <v>46252</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="405" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A405" t="s">
-        <v>810</v>
+        <v>0</v>
       </c>
       <c r="B405" t="s">
-        <v>816</v>
+        <v>822</v>
       </c>
       <c r="C405" t="s">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="D405" t="s">
-        <v>817</v>
+        <v>186</v>
       </c>
       <c r="E405" t="s">
-        <v>818</v>
+        <v>187</v>
       </c>
       <c r="F405" s="1">
-        <v>46209</v>
+        <v>46259</v>
       </c>
       <c r="G405" s="1">
-        <v>46218</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="406" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A406" t="s">
-        <v>810</v>
+        <v>823</v>
       </c>
       <c r="B406" t="s">
-        <v>819</v>
+        <v>824</v>
       </c>
       <c r="C406" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D406" t="s">
-        <v>820</v>
+        <v>344</v>
       </c>
       <c r="E406" t="s">
-        <v>821</v>
+        <v>345</v>
       </c>
       <c r="F406" s="1">
-        <v>46213</v>
+        <v>46148</v>
       </c>
       <c r="G406" s="1">
-        <v>46213</v>
+        <v>46149</v>
       </c>
     </row>
     <row r="407" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A407" t="s">
-        <v>810</v>
+        <v>825</v>
       </c>
       <c r="B407" t="s">
-        <v>822</v>
+        <v>826</v>
       </c>
       <c r="C407" t="s">
-        <v>96</v>
+        <v>6</v>
       </c>
       <c r="D407" t="s">
-        <v>591</v>
+        <v>41</v>
       </c>
       <c r="E407" t="s">
-        <v>592</v>
+        <v>42</v>
       </c>
       <c r="F407" s="1">
-        <v>46213</v>
+        <v>46133</v>
       </c>
       <c r="G407" s="1">
-        <v>46216</v>
+        <v>46134</v>
       </c>
     </row>
     <row r="408" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A408" t="s">
-        <v>810</v>
+        <v>825</v>
       </c>
       <c r="B408" t="s">
-        <v>823</v>
+        <v>827</v>
       </c>
       <c r="C408" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D408" t="s">
-        <v>133</v>
+        <v>41</v>
       </c>
       <c r="E408" t="s">
-        <v>134</v>
+        <v>42</v>
       </c>
       <c r="F408" s="1">
-        <v>46220</v>
+        <v>46134</v>
       </c>
       <c r="G408" s="1">
-        <v>46231</v>
+        <v>46134</v>
       </c>
     </row>
     <row r="409" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A409" t="s">
-        <v>810</v>
+        <v>825</v>
       </c>
       <c r="B409" t="s">
-        <v>824</v>
+        <v>828</v>
       </c>
       <c r="C409" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D409" t="s">
-        <v>546</v>
+        <v>19</v>
       </c>
       <c r="E409" t="s">
-        <v>547</v>
+        <v>20</v>
       </c>
       <c r="F409" s="1">
-        <v>46223</v>
+        <v>46156</v>
       </c>
       <c r="G409" s="1">
-        <v>46223</v>
+        <v>46156</v>
       </c>
     </row>
     <row r="410" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A410" t="s">
-        <v>810</v>
+        <v>825</v>
       </c>
       <c r="B410" t="s">
-        <v>825</v>
+        <v>829</v>
       </c>
       <c r="C410" t="s">
-        <v>96</v>
+        <v>2</v>
       </c>
       <c r="D410" t="s">
-        <v>591</v>
+        <v>549</v>
       </c>
       <c r="E410" t="s">
-        <v>592</v>
+        <v>550</v>
       </c>
       <c r="F410" s="1">
-        <v>46224</v>
+        <v>46195</v>
       </c>
       <c r="G410" s="1">
-        <v>46224</v>
+        <v>46195</v>
       </c>
     </row>
     <row r="411" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A411" t="s">
-        <v>810</v>
+        <v>825</v>
       </c>
       <c r="B411" t="s">
-        <v>826</v>
+        <v>830</v>
       </c>
       <c r="C411" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D411" t="s">
-        <v>546</v>
+        <v>801</v>
       </c>
       <c r="E411" t="s">
-        <v>547</v>
+        <v>802</v>
       </c>
       <c r="F411" s="1">
-        <v>46230</v>
+        <v>46206</v>
       </c>
       <c r="G411" s="1">
-        <v>46256</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="412" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A412" t="s">
-        <v>810</v>
+        <v>825</v>
       </c>
       <c r="B412" t="s">
-        <v>827</v>
+        <v>831</v>
       </c>
       <c r="C412" t="s">
-        <v>2</v>
+        <v>96</v>
       </c>
       <c r="D412" t="s">
-        <v>133</v>
+        <v>832</v>
       </c>
       <c r="E412" t="s">
-        <v>134</v>
+        <v>833</v>
       </c>
       <c r="F412" s="1">
-        <v>46232</v>
+        <v>46209</v>
       </c>
       <c r="G412" s="1">
-        <v>46233</v>
+        <v>46218</v>
       </c>
     </row>
     <row r="413" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A413" t="s">
-        <v>810</v>
+        <v>825</v>
       </c>
       <c r="B413" t="s">
-        <v>828</v>
+        <v>834</v>
       </c>
       <c r="C413" t="s">
-        <v>80</v>
+        <v>6</v>
       </c>
       <c r="D413" t="s">
-        <v>133</v>
+        <v>835</v>
       </c>
       <c r="E413" t="s">
-        <v>134</v>
+        <v>836</v>
       </c>
       <c r="F413" s="1">
-        <v>46232</v>
+        <v>46213</v>
       </c>
       <c r="G413" s="1">
-        <v>46259</v>
+        <v>46213</v>
       </c>
     </row>
     <row r="414" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A414" t="s">
-        <v>810</v>
+        <v>825</v>
       </c>
       <c r="B414" t="s">
-        <v>829</v>
+        <v>837</v>
       </c>
       <c r="C414" t="s">
-        <v>2</v>
+        <v>96</v>
       </c>
       <c r="D414" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="E414" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="F414" s="1">
-        <v>46238</v>
+        <v>46213</v>
       </c>
       <c r="G414" s="1">
-        <v>46239</v>
+        <v>46216</v>
       </c>
     </row>
     <row r="415" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A415" t="s">
-        <v>810</v>
+        <v>825</v>
       </c>
       <c r="B415" t="s">
-        <v>830</v>
+        <v>838</v>
       </c>
       <c r="C415" t="s">
         <v>2</v>
       </c>
       <c r="D415" t="s">
-        <v>41</v>
+        <v>133</v>
       </c>
       <c r="E415" t="s">
-        <v>42</v>
+        <v>134</v>
       </c>
       <c r="F415" s="1">
-        <v>46247</v>
+        <v>46220</v>
       </c>
       <c r="G415" s="1">
-        <v>46252</v>
+        <v>46231</v>
       </c>
     </row>
     <row r="416" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A416" t="s">
-        <v>810</v>
+        <v>825</v>
       </c>
       <c r="B416" t="s">
-        <v>831</v>
+        <v>839</v>
       </c>
       <c r="C416" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D416" t="s">
-        <v>832</v>
+        <v>549</v>
       </c>
       <c r="E416" t="s">
-        <v>833</v>
+        <v>550</v>
       </c>
       <c r="F416" s="1">
-        <v>46253</v>
+        <v>46223</v>
       </c>
       <c r="G416" s="1">
-        <v>46253</v>
+        <v>46223</v>
       </c>
     </row>
     <row r="417" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A417" t="s">
-        <v>810</v>
+        <v>825</v>
       </c>
       <c r="B417" t="s">
-        <v>834</v>
+        <v>840</v>
       </c>
       <c r="C417" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="D417" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="E417" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="F417" s="1">
-        <v>46253</v>
+        <v>46224</v>
       </c>
       <c r="G417" s="1">
-        <v>46259</v>
+        <v>46224</v>
       </c>
     </row>
     <row r="418" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A418" t="s">
-        <v>810</v>
+        <v>825</v>
       </c>
       <c r="B418" t="s">
-        <v>835</v>
+        <v>841</v>
       </c>
       <c r="C418" t="s">
         <v>80</v>
       </c>
       <c r="D418" t="s">
-        <v>591</v>
+        <v>549</v>
       </c>
       <c r="E418" t="s">
-        <v>592</v>
+        <v>550</v>
       </c>
       <c r="F418" s="1">
-        <v>46254</v>
+        <v>46230</v>
       </c>
       <c r="G418" s="1">
-        <v>46255</v>
+        <v>46256</v>
       </c>
     </row>
     <row r="419" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A419" t="s">
-        <v>810</v>
+        <v>825</v>
       </c>
       <c r="B419" t="s">
-        <v>836</v>
+        <v>842</v>
       </c>
       <c r="C419" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D419" t="s">
-        <v>448</v>
+        <v>133</v>
       </c>
       <c r="E419" t="s">
-        <v>449</v>
+        <v>134</v>
       </c>
       <c r="F419" s="1">
-        <v>46254</v>
+        <v>46232</v>
       </c>
       <c r="G419" s="1">
-        <v>46255</v>
+        <v>46233</v>
       </c>
     </row>
     <row r="420" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A420" t="s">
-        <v>810</v>
+        <v>825</v>
       </c>
       <c r="B420" t="s">
-        <v>837</v>
+        <v>843</v>
       </c>
       <c r="C420" t="s">
         <v>80</v>
       </c>
       <c r="D420" t="s">
-        <v>452</v>
+        <v>133</v>
       </c>
       <c r="E420" t="s">
-        <v>453</v>
+        <v>134</v>
       </c>
       <c r="F420" s="1">
-        <v>46255</v>
+        <v>46232</v>
       </c>
       <c r="G420" s="1">
-        <v>46258</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="421" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A421" t="s">
-        <v>810</v>
+        <v>825</v>
       </c>
       <c r="B421" t="s">
-        <v>838</v>
+        <v>844</v>
       </c>
       <c r="C421" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D421" t="s">
-        <v>546</v>
+        <v>594</v>
       </c>
       <c r="E421" t="s">
-        <v>547</v>
+        <v>595</v>
       </c>
       <c r="F421" s="1">
-        <v>46258</v>
+        <v>46238</v>
       </c>
       <c r="G421" s="1">
-        <v>46259</v>
+        <v>46239</v>
       </c>
     </row>
     <row r="422" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A422" t="s">
-        <v>810</v>
+        <v>825</v>
       </c>
       <c r="B422" t="s">
-        <v>839</v>
+        <v>845</v>
       </c>
       <c r="C422" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D422" t="s">
-        <v>448</v>
+        <v>41</v>
       </c>
       <c r="E422" t="s">
-        <v>449</v>
+        <v>42</v>
       </c>
       <c r="F422" s="1">
-        <v>46258</v>
+        <v>46247</v>
       </c>
       <c r="G422" s="1">
-        <v>46258</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="423" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A423" t="s">
-        <v>810</v>
+        <v>825</v>
       </c>
       <c r="B423" t="s">
-        <v>840</v>
+        <v>846</v>
       </c>
       <c r="C423" t="s">
-        <v>80</v>
+        <v>6</v>
       </c>
       <c r="D423" t="s">
-        <v>591</v>
+        <v>847</v>
       </c>
       <c r="E423" t="s">
-        <v>592</v>
+        <v>848</v>
       </c>
       <c r="F423" s="1">
-        <v>46258</v>
+        <v>46253</v>
       </c>
       <c r="G423" s="1">
-        <v>46259</v>
+        <v>46253</v>
       </c>
     </row>
     <row r="424" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A424" t="s">
-        <v>810</v>
+        <v>825</v>
       </c>
       <c r="B424" t="s">
-        <v>841</v>
+        <v>849</v>
       </c>
       <c r="C424" t="s">
         <v>80</v>
       </c>
       <c r="D424" t="s">
-        <v>817</v>
+        <v>594</v>
       </c>
       <c r="E424" t="s">
-        <v>818</v>
+        <v>595</v>
       </c>
       <c r="F424" s="1">
-        <v>46258</v>
+        <v>46253</v>
       </c>
       <c r="G424" s="1">
-        <v>46258</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="425" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A425" t="s">
-        <v>810</v>
+        <v>825</v>
       </c>
       <c r="B425" t="s">
-        <v>842</v>
+        <v>850</v>
       </c>
       <c r="C425" t="s">
         <v>80</v>
       </c>
       <c r="D425" t="s">
-        <v>546</v>
+        <v>594</v>
       </c>
       <c r="E425" t="s">
-        <v>547</v>
+        <v>595</v>
       </c>
       <c r="F425" s="1">
-        <v>46258</v>
+        <v>46254</v>
       </c>
       <c r="G425" s="1">
-        <v>46258</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="426" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A426" t="s">
-        <v>810</v>
+        <v>825</v>
       </c>
       <c r="B426" t="s">
-        <v>843</v>
+        <v>851</v>
       </c>
       <c r="C426" t="s">
         <v>80</v>
       </c>
       <c r="D426" t="s">
-        <v>652</v>
+        <v>451</v>
       </c>
       <c r="E426" t="s">
-        <v>653</v>
+        <v>452</v>
       </c>
       <c r="F426" s="1">
-        <v>46258</v>
+        <v>46254</v>
       </c>
       <c r="G426" s="1">
-        <v>46258</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="427" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A427" t="s">
-        <v>810</v>
+        <v>825</v>
       </c>
       <c r="B427" t="s">
-        <v>844</v>
+        <v>852</v>
       </c>
       <c r="C427" t="s">
         <v>80</v>
       </c>
       <c r="D427" t="s">
-        <v>546</v>
+        <v>455</v>
       </c>
       <c r="E427" t="s">
-        <v>547</v>
+        <v>456</v>
       </c>
       <c r="F427" s="1">
-        <v>46259</v>
+        <v>46255</v>
       </c>
       <c r="G427" s="1">
-        <v>46259</v>
+        <v>46258</v>
       </c>
     </row>
     <row r="428" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A428" t="s">
-        <v>810</v>
+        <v>825</v>
       </c>
       <c r="B428" t="s">
-        <v>845</v>
+        <v>853</v>
       </c>
       <c r="C428" t="s">
         <v>80</v>
       </c>
       <c r="D428" t="s">
-        <v>133</v>
+        <v>549</v>
       </c>
       <c r="E428" t="s">
-        <v>134</v>
+        <v>550</v>
       </c>
       <c r="F428" s="1">
-        <v>46259</v>
+        <v>46258</v>
       </c>
       <c r="G428" s="1">
         <v>46259</v>
@@ -13019,45 +13064,45 @@
     </row>
     <row r="429" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A429" t="s">
-        <v>810</v>
+        <v>825</v>
       </c>
       <c r="B429" t="s">
-        <v>846</v>
+        <v>854</v>
       </c>
       <c r="C429" t="s">
         <v>80</v>
       </c>
       <c r="D429" t="s">
-        <v>133</v>
+        <v>451</v>
       </c>
       <c r="E429" t="s">
-        <v>134</v>
+        <v>452</v>
       </c>
       <c r="F429" s="1">
-        <v>46259</v>
+        <v>46258</v>
       </c>
       <c r="G429" s="1">
-        <v>46259</v>
+        <v>46258</v>
       </c>
     </row>
     <row r="430" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A430" t="s">
-        <v>810</v>
+        <v>825</v>
       </c>
       <c r="B430" t="s">
-        <v>847</v>
+        <v>855</v>
       </c>
       <c r="C430" t="s">
         <v>80</v>
       </c>
       <c r="D430" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="E430" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="F430" s="1">
-        <v>46259</v>
+        <v>46258</v>
       </c>
       <c r="G430" s="1">
         <v>46259</v>
@@ -13065,197 +13110,197 @@
     </row>
     <row r="431" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A431" t="s">
-        <v>848</v>
+        <v>825</v>
       </c>
       <c r="B431" t="s">
-        <v>849</v>
+        <v>856</v>
       </c>
       <c r="C431" t="s">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="D431" t="s">
-        <v>850</v>
+        <v>832</v>
       </c>
       <c r="E431" t="s">
-        <v>851</v>
+        <v>833</v>
       </c>
       <c r="F431" s="1">
-        <v>46063</v>
+        <v>46258</v>
       </c>
       <c r="G431" s="1">
-        <v>46064</v>
+        <v>46258</v>
       </c>
     </row>
     <row r="432" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A432" t="s">
-        <v>848</v>
+        <v>825</v>
       </c>
       <c r="B432" t="s">
-        <v>852</v>
+        <v>857</v>
       </c>
       <c r="C432" t="s">
-        <v>6</v>
+        <v>80</v>
       </c>
       <c r="D432" t="s">
-        <v>57</v>
+        <v>549</v>
       </c>
       <c r="E432" t="s">
-        <v>58</v>
+        <v>550</v>
       </c>
       <c r="F432" s="1">
-        <v>46113</v>
+        <v>46258</v>
       </c>
       <c r="G432" s="1">
-        <v>46125</v>
+        <v>46258</v>
       </c>
     </row>
     <row r="433" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A433" t="s">
-        <v>848</v>
+        <v>825</v>
       </c>
       <c r="B433" t="s">
-        <v>853</v>
+        <v>858</v>
       </c>
       <c r="C433" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D433" t="s">
-        <v>57</v>
+        <v>655</v>
       </c>
       <c r="E433" t="s">
-        <v>58</v>
+        <v>656</v>
       </c>
       <c r="F433" s="1">
-        <v>46125</v>
+        <v>46258</v>
       </c>
       <c r="G433" s="1">
-        <v>46125</v>
+        <v>46258</v>
       </c>
     </row>
     <row r="434" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A434" t="s">
-        <v>848</v>
+        <v>825</v>
       </c>
       <c r="B434" t="s">
-        <v>854</v>
+        <v>859</v>
       </c>
       <c r="C434" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D434" t="s">
-        <v>57</v>
+        <v>549</v>
       </c>
       <c r="E434" t="s">
-        <v>58</v>
+        <v>550</v>
       </c>
       <c r="F434" s="1">
-        <v>46126</v>
+        <v>46259</v>
       </c>
       <c r="G434" s="1">
-        <v>46126</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="435" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A435" t="s">
-        <v>848</v>
+        <v>825</v>
       </c>
       <c r="B435" t="s">
-        <v>855</v>
+        <v>860</v>
       </c>
       <c r="C435" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D435" t="s">
-        <v>57</v>
+        <v>133</v>
       </c>
       <c r="E435" t="s">
-        <v>58</v>
+        <v>134</v>
       </c>
       <c r="F435" s="1">
-        <v>46126</v>
+        <v>46259</v>
       </c>
       <c r="G435" s="1">
-        <v>46126</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="436" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A436" t="s">
-        <v>848</v>
+        <v>825</v>
       </c>
       <c r="B436" t="s">
-        <v>856</v>
+        <v>861</v>
       </c>
       <c r="C436" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D436" t="s">
-        <v>57</v>
+        <v>133</v>
       </c>
       <c r="E436" t="s">
-        <v>58</v>
+        <v>134</v>
       </c>
       <c r="F436" s="1">
-        <v>46128</v>
+        <v>46259</v>
       </c>
       <c r="G436" s="1">
-        <v>46128</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="437" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A437" t="s">
-        <v>848</v>
+        <v>825</v>
       </c>
       <c r="B437" t="s">
-        <v>857</v>
+        <v>862</v>
       </c>
       <c r="C437" t="s">
-        <v>6</v>
+        <v>80</v>
       </c>
       <c r="D437" t="s">
-        <v>57</v>
+        <v>594</v>
       </c>
       <c r="E437" t="s">
-        <v>58</v>
+        <v>595</v>
       </c>
       <c r="F437" s="1">
-        <v>46132</v>
+        <v>46259</v>
       </c>
       <c r="G437" s="1">
-        <v>46132</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="438" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A438" t="s">
-        <v>848</v>
+        <v>863</v>
       </c>
       <c r="B438" t="s">
-        <v>858</v>
+        <v>864</v>
       </c>
       <c r="C438" t="s">
-        <v>2</v>
+        <v>96</v>
       </c>
       <c r="D438" t="s">
-        <v>57</v>
+        <v>865</v>
       </c>
       <c r="E438" t="s">
-        <v>58</v>
+        <v>866</v>
       </c>
       <c r="F438" s="1">
-        <v>46161</v>
+        <v>46063</v>
       </c>
       <c r="G438" s="1">
-        <v>46161</v>
+        <v>46064</v>
       </c>
     </row>
     <row r="439" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A439" t="s">
-        <v>848</v>
+        <v>863</v>
       </c>
       <c r="B439" t="s">
-        <v>859</v>
+        <v>867</v>
       </c>
       <c r="C439" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D439" t="s">
         <v>57</v>
@@ -13264,18 +13309,18 @@
         <v>58</v>
       </c>
       <c r="F439" s="1">
-        <v>46174</v>
+        <v>46113</v>
       </c>
       <c r="G439" s="1">
-        <v>46174</v>
+        <v>46125</v>
       </c>
     </row>
     <row r="440" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A440" t="s">
-        <v>848</v>
+        <v>863</v>
       </c>
       <c r="B440" t="s">
-        <v>860</v>
+        <v>868</v>
       </c>
       <c r="C440" t="s">
         <v>2</v>
@@ -13287,21 +13332,21 @@
         <v>58</v>
       </c>
       <c r="F440" s="1">
-        <v>46174</v>
+        <v>46125</v>
       </c>
       <c r="G440" s="1">
-        <v>46174</v>
+        <v>46125</v>
       </c>
     </row>
     <row r="441" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A441" t="s">
-        <v>848</v>
+        <v>863</v>
       </c>
       <c r="B441" t="s">
-        <v>861</v>
+        <v>869</v>
       </c>
       <c r="C441" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D441" t="s">
         <v>57</v>
@@ -13310,21 +13355,21 @@
         <v>58</v>
       </c>
       <c r="F441" s="1">
-        <v>46195</v>
+        <v>46126</v>
       </c>
       <c r="G441" s="1">
-        <v>46252</v>
+        <v>46126</v>
       </c>
     </row>
     <row r="442" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A442" t="s">
-        <v>848</v>
+        <v>863</v>
       </c>
       <c r="B442" t="s">
-        <v>862</v>
+        <v>870</v>
       </c>
       <c r="C442" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D442" t="s">
         <v>57</v>
@@ -13333,18 +13378,18 @@
         <v>58</v>
       </c>
       <c r="F442" s="1">
-        <v>46210</v>
+        <v>46126</v>
       </c>
       <c r="G442" s="1">
-        <v>46210</v>
+        <v>46126</v>
       </c>
     </row>
     <row r="443" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A443" t="s">
-        <v>848</v>
+        <v>863</v>
       </c>
       <c r="B443" t="s">
-        <v>863</v>
+        <v>871</v>
       </c>
       <c r="C443" t="s">
         <v>2</v>
@@ -13356,21 +13401,21 @@
         <v>58</v>
       </c>
       <c r="F443" s="1">
-        <v>46213</v>
+        <v>46128</v>
       </c>
       <c r="G443" s="1">
-        <v>46213</v>
+        <v>46128</v>
       </c>
     </row>
     <row r="444" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A444" t="s">
-        <v>848</v>
+        <v>863</v>
       </c>
       <c r="B444" t="s">
-        <v>864</v>
+        <v>872</v>
       </c>
       <c r="C444" t="s">
-        <v>80</v>
+        <v>6</v>
       </c>
       <c r="D444" t="s">
         <v>57</v>
@@ -13379,44 +13424,44 @@
         <v>58</v>
       </c>
       <c r="F444" s="1">
-        <v>46218</v>
+        <v>46132</v>
       </c>
       <c r="G444" s="1">
-        <v>46252</v>
+        <v>46132</v>
       </c>
     </row>
     <row r="445" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A445" t="s">
-        <v>848</v>
+        <v>863</v>
       </c>
       <c r="B445" t="s">
-        <v>865</v>
+        <v>873</v>
       </c>
       <c r="C445" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D445" t="s">
-        <v>77</v>
+        <v>57</v>
       </c>
       <c r="E445" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="F445" s="1">
-        <v>46226</v>
+        <v>46161</v>
       </c>
       <c r="G445" s="1">
-        <v>46226</v>
+        <v>46161</v>
       </c>
     </row>
     <row r="446" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A446" t="s">
-        <v>848</v>
+        <v>863</v>
       </c>
       <c r="B446" t="s">
-        <v>866</v>
+        <v>874</v>
       </c>
       <c r="C446" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D446" t="s">
         <v>57</v>
@@ -13425,21 +13470,21 @@
         <v>58</v>
       </c>
       <c r="F446" s="1">
-        <v>46227</v>
+        <v>46174</v>
       </c>
       <c r="G446" s="1">
-        <v>46252</v>
+        <v>46174</v>
       </c>
     </row>
     <row r="447" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A447" t="s">
-        <v>848</v>
+        <v>863</v>
       </c>
       <c r="B447" t="s">
-        <v>867</v>
+        <v>875</v>
       </c>
       <c r="C447" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D447" t="s">
         <v>57</v>
@@ -13448,21 +13493,21 @@
         <v>58</v>
       </c>
       <c r="F447" s="1">
-        <v>46227</v>
+        <v>46174</v>
       </c>
       <c r="G447" s="1">
-        <v>46252</v>
+        <v>46174</v>
       </c>
     </row>
     <row r="448" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A448" t="s">
-        <v>848</v>
+        <v>863</v>
       </c>
       <c r="B448" t="s">
-        <v>868</v>
+        <v>876</v>
       </c>
       <c r="C448" t="s">
-        <v>6</v>
+        <v>80</v>
       </c>
       <c r="D448" t="s">
         <v>57</v>
@@ -13471,44 +13516,44 @@
         <v>58</v>
       </c>
       <c r="F448" s="1">
-        <v>46227</v>
+        <v>46195</v>
       </c>
       <c r="G448" s="1">
-        <v>46228</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="449" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A449" t="s">
-        <v>848</v>
+        <v>863</v>
       </c>
       <c r="B449" t="s">
-        <v>869</v>
+        <v>877</v>
       </c>
       <c r="C449" t="s">
-        <v>80</v>
+        <v>6</v>
       </c>
       <c r="D449" t="s">
-        <v>77</v>
+        <v>57</v>
       </c>
       <c r="E449" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="F449" s="1">
-        <v>46230</v>
+        <v>46210</v>
       </c>
       <c r="G449" s="1">
-        <v>46252</v>
+        <v>46210</v>
       </c>
     </row>
     <row r="450" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A450" t="s">
-        <v>848</v>
+        <v>863</v>
       </c>
       <c r="B450" t="s">
-        <v>870</v>
+        <v>878</v>
       </c>
       <c r="C450" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D450" t="s">
         <v>57</v>
@@ -13517,21 +13562,21 @@
         <v>58</v>
       </c>
       <c r="F450" s="1">
-        <v>46231</v>
+        <v>46213</v>
       </c>
       <c r="G450" s="1">
-        <v>46231</v>
+        <v>46213</v>
       </c>
     </row>
     <row r="451" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A451" t="s">
-        <v>848</v>
+        <v>863</v>
       </c>
       <c r="B451" t="s">
-        <v>871</v>
+        <v>879</v>
       </c>
       <c r="C451" t="s">
-        <v>6</v>
+        <v>80</v>
       </c>
       <c r="D451" t="s">
         <v>57</v>
@@ -13540,64 +13585,64 @@
         <v>58</v>
       </c>
       <c r="F451" s="1">
-        <v>46254</v>
+        <v>46218</v>
       </c>
       <c r="G451" s="1">
-        <v>46254</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="452" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A452" t="s">
-        <v>848</v>
+        <v>863</v>
       </c>
       <c r="B452" t="s">
-        <v>872</v>
+        <v>880</v>
       </c>
       <c r="C452" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D452" t="s">
-        <v>57</v>
+        <v>77</v>
       </c>
       <c r="E452" t="s">
-        <v>58</v>
+        <v>78</v>
       </c>
       <c r="F452" s="1">
-        <v>46255</v>
+        <v>46226</v>
       </c>
       <c r="G452" s="1">
-        <v>46255</v>
+        <v>46226</v>
       </c>
     </row>
     <row r="453" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A453" t="s">
-        <v>848</v>
+        <v>863</v>
       </c>
       <c r="B453" t="s">
-        <v>873</v>
+        <v>881</v>
       </c>
       <c r="C453" t="s">
         <v>80</v>
       </c>
       <c r="D453" t="s">
-        <v>874</v>
+        <v>57</v>
       </c>
       <c r="E453" t="s">
-        <v>875</v>
+        <v>58</v>
       </c>
       <c r="F453" s="1">
-        <v>46258</v>
+        <v>46227</v>
       </c>
       <c r="G453" s="1">
-        <v>46258</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="454" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A454" t="s">
-        <v>848</v>
+        <v>863</v>
       </c>
       <c r="B454" t="s">
-        <v>876</v>
+        <v>882</v>
       </c>
       <c r="C454" t="s">
         <v>80</v>
@@ -13609,216 +13654,377 @@
         <v>58</v>
       </c>
       <c r="F454" s="1">
-        <v>46259</v>
+        <v>46227</v>
       </c>
       <c r="G454" s="1">
-        <v>46259</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="455" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A455" t="s">
-        <v>877</v>
+        <v>863</v>
       </c>
       <c r="B455" t="s">
-        <v>878</v>
+        <v>883</v>
       </c>
       <c r="C455" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D455" t="s">
-        <v>879</v>
+        <v>57</v>
       </c>
       <c r="E455" t="s">
-        <v>880</v>
+        <v>58</v>
       </c>
       <c r="F455" s="1">
-        <v>46083</v>
+        <v>46227</v>
       </c>
       <c r="G455" s="1">
-        <v>46084</v>
+        <v>46228</v>
       </c>
     </row>
     <row r="456" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A456" t="s">
-        <v>877</v>
+        <v>863</v>
       </c>
       <c r="B456" t="s">
-        <v>881</v>
+        <v>884</v>
       </c>
       <c r="C456" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D456" t="s">
-        <v>879</v>
+        <v>77</v>
       </c>
       <c r="E456" t="s">
-        <v>880</v>
+        <v>78</v>
       </c>
       <c r="F456" s="1">
-        <v>46132</v>
+        <v>46230</v>
       </c>
       <c r="G456" s="1">
-        <v>46133</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="457" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A457" t="s">
-        <v>877</v>
+        <v>863</v>
       </c>
       <c r="B457" t="s">
-        <v>882</v>
+        <v>885</v>
       </c>
       <c r="C457" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D457" t="s">
-        <v>883</v>
+        <v>57</v>
       </c>
       <c r="E457" t="s">
-        <v>884</v>
+        <v>58</v>
       </c>
       <c r="F457" s="1">
-        <v>46157</v>
+        <v>46231</v>
       </c>
       <c r="G457" s="1">
-        <v>46157</v>
+        <v>46231</v>
       </c>
     </row>
     <row r="458" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A458" t="s">
-        <v>877</v>
+        <v>863</v>
       </c>
       <c r="B458" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="C458" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D458" t="s">
-        <v>886</v>
+        <v>57</v>
       </c>
       <c r="E458" t="s">
-        <v>887</v>
+        <v>58</v>
       </c>
       <c r="F458" s="1">
-        <v>46168</v>
+        <v>46254</v>
       </c>
       <c r="G458" s="1">
-        <v>46170</v>
+        <v>46254</v>
       </c>
     </row>
     <row r="459" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A459" t="s">
-        <v>877</v>
+        <v>863</v>
       </c>
       <c r="B459" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="C459" t="s">
         <v>2</v>
       </c>
       <c r="D459" t="s">
-        <v>883</v>
+        <v>57</v>
       </c>
       <c r="E459" t="s">
-        <v>884</v>
+        <v>58</v>
       </c>
       <c r="F459" s="1">
-        <v>46244</v>
+        <v>46255</v>
       </c>
       <c r="G459" s="1">
-        <v>46244</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="460" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A460" t="s">
-        <v>877</v>
+        <v>863</v>
       </c>
       <c r="B460" t="s">
+        <v>888</v>
+      </c>
+      <c r="C460" t="s">
+        <v>80</v>
+      </c>
+      <c r="D460" t="s">
         <v>889</v>
       </c>
-      <c r="C460" t="s">
-        <v>2</v>
-      </c>
-      <c r="D460" t="s">
-        <v>883</v>
-      </c>
       <c r="E460" t="s">
-        <v>884</v>
+        <v>890</v>
       </c>
       <c r="F460" s="1">
-        <v>46247</v>
+        <v>46258</v>
       </c>
       <c r="G460" s="1">
-        <v>46247</v>
+        <v>46258</v>
       </c>
     </row>
     <row r="461" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A461" t="s">
-        <v>877</v>
+        <v>863</v>
       </c>
       <c r="B461" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="C461" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D461" t="s">
-        <v>879</v>
+        <v>57</v>
       </c>
       <c r="E461" t="s">
-        <v>880</v>
+        <v>58</v>
       </c>
       <c r="F461" s="1">
-        <v>46247</v>
+        <v>46259</v>
       </c>
       <c r="G461" s="1">
-        <v>46247</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="462" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A462" t="s">
-        <v>877</v>
+        <v>892</v>
       </c>
       <c r="B462" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="C462" t="s">
         <v>2</v>
       </c>
       <c r="D462" t="s">
-        <v>883</v>
+        <v>894</v>
       </c>
       <c r="E462" t="s">
-        <v>884</v>
+        <v>895</v>
       </c>
       <c r="F462" s="1">
-        <v>46255</v>
+        <v>46083</v>
       </c>
       <c r="G462" s="1">
-        <v>46255</v>
+        <v>46084</v>
       </c>
     </row>
     <row r="463" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A463" t="s">
-        <v>877</v>
+        <v>892</v>
       </c>
       <c r="B463" t="s">
-        <v>892</v>
+        <v>896</v>
       </c>
       <c r="C463" t="s">
         <v>2</v>
       </c>
       <c r="D463" t="s">
-        <v>883</v>
+        <v>894</v>
       </c>
       <c r="E463" t="s">
-        <v>884</v>
+        <v>895</v>
       </c>
       <c r="F463" s="1">
-        <v>46258</v>
+        <v>46132</v>
       </c>
       <c r="G463" s="1">
+        <v>46133</v>
+      </c>
+    </row>
+    <row r="464" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A464" t="s">
+        <v>892</v>
+      </c>
+      <c r="B464" t="s">
+        <v>897</v>
+      </c>
+      <c r="C464" t="s">
+        <v>2</v>
+      </c>
+      <c r="D464" t="s">
+        <v>898</v>
+      </c>
+      <c r="E464" t="s">
+        <v>899</v>
+      </c>
+      <c r="F464" s="1">
+        <v>46157</v>
+      </c>
+      <c r="G464" s="1">
+        <v>46157</v>
+      </c>
+    </row>
+    <row r="465" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A465" t="s">
+        <v>892</v>
+      </c>
+      <c r="B465" t="s">
+        <v>900</v>
+      </c>
+      <c r="C465" t="s">
+        <v>2</v>
+      </c>
+      <c r="D465" t="s">
+        <v>901</v>
+      </c>
+      <c r="E465" t="s">
+        <v>902</v>
+      </c>
+      <c r="F465" s="1">
+        <v>46168</v>
+      </c>
+      <c r="G465" s="1">
+        <v>46170</v>
+      </c>
+    </row>
+    <row r="466" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A466" t="s">
+        <v>892</v>
+      </c>
+      <c r="B466" t="s">
+        <v>903</v>
+      </c>
+      <c r="C466" t="s">
+        <v>2</v>
+      </c>
+      <c r="D466" t="s">
+        <v>898</v>
+      </c>
+      <c r="E466" t="s">
+        <v>899</v>
+      </c>
+      <c r="F466" s="1">
+        <v>46244</v>
+      </c>
+      <c r="G466" s="1">
+        <v>46244</v>
+      </c>
+    </row>
+    <row r="467" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A467" t="s">
+        <v>892</v>
+      </c>
+      <c r="B467" t="s">
+        <v>904</v>
+      </c>
+      <c r="C467" t="s">
+        <v>2</v>
+      </c>
+      <c r="D467" t="s">
+        <v>898</v>
+      </c>
+      <c r="E467" t="s">
+        <v>899</v>
+      </c>
+      <c r="F467" s="1">
+        <v>46247</v>
+      </c>
+      <c r="G467" s="1">
+        <v>46247</v>
+      </c>
+    </row>
+    <row r="468" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A468" t="s">
+        <v>892</v>
+      </c>
+      <c r="B468" t="s">
+        <v>905</v>
+      </c>
+      <c r="C468" t="s">
+        <v>2</v>
+      </c>
+      <c r="D468" t="s">
+        <v>894</v>
+      </c>
+      <c r="E468" t="s">
+        <v>895</v>
+      </c>
+      <c r="F468" s="1">
+        <v>46247</v>
+      </c>
+      <c r="G468" s="1">
+        <v>46247</v>
+      </c>
+    </row>
+    <row r="469" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A469" t="s">
+        <v>892</v>
+      </c>
+      <c r="B469" t="s">
+        <v>906</v>
+      </c>
+      <c r="C469" t="s">
+        <v>2</v>
+      </c>
+      <c r="D469" t="s">
+        <v>898</v>
+      </c>
+      <c r="E469" t="s">
+        <v>899</v>
+      </c>
+      <c r="F469" s="1">
+        <v>46255</v>
+      </c>
+      <c r="G469" s="1">
+        <v>46255</v>
+      </c>
+    </row>
+    <row r="470" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A470" t="s">
+        <v>892</v>
+      </c>
+      <c r="B470" t="s">
+        <v>907</v>
+      </c>
+      <c r="C470" t="s">
+        <v>2</v>
+      </c>
+      <c r="D470" t="s">
+        <v>898</v>
+      </c>
+      <c r="E470" t="s">
+        <v>899</v>
+      </c>
+      <c r="F470" s="1">
+        <v>46258</v>
+      </c>
+      <c r="G470" s="1">
         <v>46258</v>
       </c>
     </row>

--- a/Data_ERP/Pedidos Transmicion.xlsx
+++ b/Data_ERP/Pedidos Transmicion.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sistema_Logistico_Peirano\Data_ERP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D01866F1-74B6-4C15-91A5-72FA84A23711}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B7B85198-59CD-4007-BF58-956C244C93EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="24885" yWindow="3735" windowWidth="15375" windowHeight="8325" xr2:uid="{1549ECF5-6776-44E5-B3E5-058874E2C2A1}"/>
   </bookViews>

--- a/Data_ERP/Pedidos Transmicion.xlsx
+++ b/Data_ERP/Pedidos Transmicion.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sistema_Logistico_Peirano\Data_ERP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6893485A-C7EC-406A-8182-48C93447AF7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DD7F434A-DB69-4DC2-875A-F31DFE1E35E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{A16D5544-A1FF-4F58-8B58-7EFD3B43616F}"/>
+    <workbookView xWindow="25230" yWindow="4080" windowWidth="15375" windowHeight="8325" xr2:uid="{55B95A94-176D-4463-8EC7-16775CAE43F3}"/>
   </bookViews>
   <sheets>
     <sheet name="transmicion" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2347" uniqueCount="890">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2277" uniqueCount="860">
   <si>
     <t>0001</t>
   </si>
@@ -1267,18 +1267,6 @@
     <t xml:space="preserve">  214166</t>
   </si>
   <si>
-    <t xml:space="preserve">  214167</t>
-  </si>
-  <si>
-    <t>BR08</t>
-  </si>
-  <si>
-    <t>BAEZ RAMON ANTONIO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214170</t>
-  </si>
-  <si>
     <t xml:space="preserve">  214173</t>
   </si>
   <si>
@@ -1294,15 +1282,6 @@
     <t xml:space="preserve">  214186</t>
   </si>
   <si>
-    <t xml:space="preserve">  214187</t>
-  </si>
-  <si>
-    <t>NE04</t>
-  </si>
-  <si>
-    <t>NEOMAT S.A.</t>
-  </si>
-  <si>
     <t xml:space="preserve">  214192</t>
   </si>
   <si>
@@ -1318,9 +1297,6 @@
     <t>SANITARIOS LUGANO S.R.L.</t>
   </si>
   <si>
-    <t xml:space="preserve">  214203</t>
-  </si>
-  <si>
     <t xml:space="preserve">  214214</t>
   </si>
   <si>
@@ -1369,15 +1345,6 @@
     <t xml:space="preserve">  214257</t>
   </si>
   <si>
-    <t xml:space="preserve">  214258</t>
-  </si>
-  <si>
-    <t>RA20</t>
-  </si>
-  <si>
-    <t>RA S.H. DE ALFONSO RUBEN Y POZZUTO CARLOS</t>
-  </si>
-  <si>
     <t xml:space="preserve">  214264</t>
   </si>
   <si>
@@ -1435,15 +1402,6 @@
     <t xml:space="preserve">  214292</t>
   </si>
   <si>
-    <t xml:space="preserve">  214293</t>
-  </si>
-  <si>
-    <t>DC16</t>
-  </si>
-  <si>
-    <t>DISEÑO Y CONSTRUCCION LEO SRL -CASA LEO</t>
-  </si>
-  <si>
     <t xml:space="preserve">  214294</t>
   </si>
   <si>
@@ -1468,7 +1426,133 @@
     <t>RAMIREZ CHRISTIAN J.G.-SANIMAR</t>
   </si>
   <si>
-    <t xml:space="preserve">  214319</t>
+    <t xml:space="preserve">  214320</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214325</t>
+  </si>
+  <si>
+    <t>SC33</t>
+  </si>
+  <si>
+    <t>SANITARIOS CAMPANA S.R.L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214332</t>
+  </si>
+  <si>
+    <t>ZE02</t>
+  </si>
+  <si>
+    <t>ZERAMIKO DE MARIA R.O.CABRERA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214335</t>
+  </si>
+  <si>
+    <t>VS08</t>
+  </si>
+  <si>
+    <t>VIAL SERVICIOS S.A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214336</t>
+  </si>
+  <si>
+    <t>CO42</t>
+  </si>
+  <si>
+    <t>COLADONATO FEDERICO N.-SANITARIOS CARUPA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214349</t>
+  </si>
+  <si>
+    <t>MA43</t>
+  </si>
+  <si>
+    <t>MARMOLERIA EL ARTESANO S.A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214350</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214352</t>
+  </si>
+  <si>
+    <t>DR01</t>
+  </si>
+  <si>
+    <t>DOMINGO RESTA Y CIA. SA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214353</t>
+  </si>
+  <si>
+    <t>ML16</t>
+  </si>
+  <si>
+    <t>MORINICO LEONEL E-MARKET FULL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214362</t>
+  </si>
+  <si>
+    <t>KO01</t>
+  </si>
+  <si>
+    <t>KOCUDEL S.A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214370</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214371</t>
+  </si>
+  <si>
+    <t>DL10</t>
+  </si>
+  <si>
+    <t>DE LOS ANDES S. A. S.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214373</t>
   </si>
   <si>
     <t>VM14</t>
@@ -1477,138 +1561,6 @@
     <t>VIESTI HNOS. SANITARIOS S. R. L.</t>
   </si>
   <si>
-    <t xml:space="preserve">  214320</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214325</t>
-  </si>
-  <si>
-    <t>SC33</t>
-  </si>
-  <si>
-    <t>SANITARIOS CAMPANA S.R.L.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214332</t>
-  </si>
-  <si>
-    <t>ZE02</t>
-  </si>
-  <si>
-    <t>ZERAMIKO DE MARIA R.O.CABRERA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214335</t>
-  </si>
-  <si>
-    <t>VS08</t>
-  </si>
-  <si>
-    <t>VIAL SERVICIOS S.A.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214336</t>
-  </si>
-  <si>
-    <t>CO42</t>
-  </si>
-  <si>
-    <t>COLADONATO FEDERICO N.-SANITARIOS CARUPA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214349</t>
-  </si>
-  <si>
-    <t>MA43</t>
-  </si>
-  <si>
-    <t>MARMOLERIA EL ARTESANO S.A.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214350</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214352</t>
-  </si>
-  <si>
-    <t>DR01</t>
-  </si>
-  <si>
-    <t>DOMINGO RESTA Y CIA. SA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214353</t>
-  </si>
-  <si>
-    <t>ML16</t>
-  </si>
-  <si>
-    <t>MORINICO LEONEL E-MARKET FULL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214362</t>
-  </si>
-  <si>
-    <t>KO01</t>
-  </si>
-  <si>
-    <t>KOCUDEL S.A.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214370</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214371</t>
-  </si>
-  <si>
-    <t>DL10</t>
-  </si>
-  <si>
-    <t>DE LOS ANDES S. A. S.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214373</t>
-  </si>
-  <si>
     <t xml:space="preserve">  214374</t>
   </si>
   <si>
@@ -1624,15 +1576,6 @@
     <t>GRUPO V S.R.L.</t>
   </si>
   <si>
-    <t xml:space="preserve">  214380</t>
-  </si>
-  <si>
-    <t>RF09</t>
-  </si>
-  <si>
-    <t>RAMOS FABIO H -MADERAS RAMOS</t>
-  </si>
-  <si>
     <t xml:space="preserve">  214381</t>
   </si>
   <si>
@@ -1696,9 +1639,6 @@
     <t xml:space="preserve">  214393</t>
   </si>
   <si>
-    <t xml:space="preserve">  214394</t>
-  </si>
-  <si>
     <t xml:space="preserve">  214395</t>
   </si>
   <si>
@@ -1759,9 +1699,6 @@
     <t>TOBA S.R.L.</t>
   </si>
   <si>
-    <t xml:space="preserve">  214408</t>
-  </si>
-  <si>
     <t xml:space="preserve">  214409</t>
   </si>
   <si>
@@ -1774,15 +1711,6 @@
     <t>BOTTIGLIERI S.R.L.</t>
   </si>
   <si>
-    <t xml:space="preserve">  214411</t>
-  </si>
-  <si>
-    <t>BA34</t>
-  </si>
-  <si>
-    <t>BALMAT S.R.L.</t>
-  </si>
-  <si>
     <t xml:space="preserve">  214412</t>
   </si>
   <si>
@@ -1810,15 +1738,6 @@
     <t>SAN MONTE ALMO SA - TEIXEIRA POCAS SANITARIOS</t>
   </si>
   <si>
-    <t xml:space="preserve">  214418</t>
-  </si>
-  <si>
-    <t>DH01</t>
-  </si>
-  <si>
-    <t>DEMARCHI HNOS.</t>
-  </si>
-  <si>
     <t xml:space="preserve">  214419</t>
   </si>
   <si>
@@ -1861,9 +1780,6 @@
     <t>SANITARIOS GUELMIB S.R.L.</t>
   </si>
   <si>
-    <t xml:space="preserve">  214432</t>
-  </si>
-  <si>
     <t xml:space="preserve">  214433</t>
   </si>
   <si>
@@ -1948,12 +1864,6 @@
     <t xml:space="preserve">  214466</t>
   </si>
   <si>
-    <t xml:space="preserve">  214467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214469</t>
-  </si>
-  <si>
     <t xml:space="preserve">  214470</t>
   </si>
   <si>
@@ -1978,9 +1888,6 @@
     <t xml:space="preserve">  214476</t>
   </si>
   <si>
-    <t xml:space="preserve">  214479</t>
-  </si>
-  <si>
     <t xml:space="preserve">  214480</t>
   </si>
   <si>
@@ -2029,18 +1936,18 @@
     <t>SANIFER VCP S.R.L.</t>
   </si>
   <si>
+    <t xml:space="preserve">  214486</t>
+  </si>
+  <si>
+    <t>ED04</t>
+  </si>
+  <si>
+    <t>EDIFICOR S.R.L.</t>
+  </si>
+  <si>
     <t xml:space="preserve">  214487</t>
   </si>
   <si>
-    <t xml:space="preserve">  214489</t>
-  </si>
-  <si>
-    <t>OA01</t>
-  </si>
-  <si>
-    <t>OCHIUZZO ALBINO JUAN - DISTRIMAR</t>
-  </si>
-  <si>
     <t xml:space="preserve">  214493</t>
   </si>
   <si>
@@ -2116,9 +2023,6 @@
     <t>FERNANDEZ AGUSTIN JOSE - GASTITO</t>
   </si>
   <si>
-    <t xml:space="preserve">  214515</t>
-  </si>
-  <si>
     <t xml:space="preserve">  214516</t>
   </si>
   <si>
@@ -2143,6 +2047,9 @@
     <t xml:space="preserve">  214521</t>
   </si>
   <si>
+    <t xml:space="preserve">  214522</t>
+  </si>
+  <si>
     <t xml:space="preserve">  214523</t>
   </si>
   <si>
@@ -2176,6 +2083,15 @@
     <t xml:space="preserve">  214533</t>
   </si>
   <si>
+    <t xml:space="preserve">  214534</t>
+  </si>
+  <si>
+    <t>RM20</t>
+  </si>
+  <si>
+    <t>ROSEBOON MIGUEL O. -M&amp;M SANITARIOS</t>
+  </si>
+  <si>
     <t xml:space="preserve">  214536</t>
   </si>
   <si>
@@ -2227,15 +2143,6 @@
     <t>BULFON GUILLERMO JESUS - SANIT. MATISA -</t>
   </si>
   <si>
-    <t xml:space="preserve">  214544</t>
-  </si>
-  <si>
-    <t>PA11</t>
-  </si>
-  <si>
-    <t>ANTONIO PREVEDELLO Y CIA S.R.L.</t>
-  </si>
-  <si>
     <t xml:space="preserve">  214545</t>
   </si>
   <si>
@@ -2248,19 +2155,16 @@
     <t>LA NORIA REVESIMIENTOS S.A.</t>
   </si>
   <si>
-    <t xml:space="preserve">  214548</t>
-  </si>
-  <si>
-    <t>AS17</t>
-  </si>
-  <si>
-    <t>AQUA SANITARIOS TANDIL S. R. L.</t>
-  </si>
-  <si>
     <t xml:space="preserve">  214549</t>
   </si>
   <si>
-    <t xml:space="preserve">  214550</t>
+    <t xml:space="preserve">  214551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214553</t>
   </si>
   <si>
     <t>DA03</t>
@@ -2269,15 +2173,6 @@
     <t>DARSIE Y CIA. SACI</t>
   </si>
   <si>
-    <t xml:space="preserve">  214551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214553</t>
-  </si>
-  <si>
     <t xml:space="preserve">  214554</t>
   </si>
   <si>
@@ -2308,10 +2203,7 @@
     <t xml:space="preserve">  214563</t>
   </si>
   <si>
-    <t>ED04</t>
-  </si>
-  <si>
-    <t>EDIFICOR S.R.L.</t>
+    <t xml:space="preserve">  214564</t>
   </si>
   <si>
     <t xml:space="preserve">  214565</t>
@@ -2371,6 +2263,9 @@
     <t xml:space="preserve">  214575</t>
   </si>
   <si>
+    <t xml:space="preserve">  214576</t>
+  </si>
+  <si>
     <t xml:space="preserve">  214577</t>
   </si>
   <si>
@@ -2395,6 +2290,9 @@
     <t xml:space="preserve">  214582</t>
   </si>
   <si>
+    <t xml:space="preserve">  214583</t>
+  </si>
+  <si>
     <t xml:space="preserve">  214584</t>
   </si>
   <si>
@@ -2407,12 +2305,33 @@
     <t>ALVARENGA VILLAR LUIS F.</t>
   </si>
   <si>
+    <t xml:space="preserve">  214587</t>
+  </si>
+  <si>
+    <t>UG01</t>
+  </si>
+  <si>
+    <t>UCCELI GABRIEL A.-SANITARIOS GABRIEL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214590</t>
+  </si>
+  <si>
     <t>0004</t>
   </si>
   <si>
     <t xml:space="preserve">      51</t>
   </si>
   <si>
+    <t xml:space="preserve">     111</t>
+  </si>
+  <si>
+    <t>LG10</t>
+  </si>
+  <si>
+    <t>LOPEZ GAS ONLINE S.A</t>
+  </si>
+  <si>
     <t>0008</t>
   </si>
   <si>
@@ -2500,9 +2419,6 @@
     <t xml:space="preserve">    2846</t>
   </si>
   <si>
-    <t xml:space="preserve">    2847</t>
-  </si>
-  <si>
     <t xml:space="preserve">    2849</t>
   </si>
   <si>
@@ -2608,19 +2524,13 @@
     <t xml:space="preserve">    2301</t>
   </si>
   <si>
-    <t xml:space="preserve">    2328</t>
-  </si>
-  <si>
-    <t>UG01</t>
-  </si>
-  <si>
-    <t>UCCELI GABRIEL A.-SANITARIOS GABRIEL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    2329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    2333</t>
+    <t xml:space="preserve">    2334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    2335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    2336</t>
   </si>
   <si>
     <t>9999</t>
@@ -3139,31 +3049,31 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00E00EDD-4524-4BA9-B1A4-C7D71D187DCB}">
-  <dimension ref="A1:G469"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C982E07-9753-4882-B88A-0A8DF07939F9}">
+  <dimension ref="A1:G455"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
-        <v>883</v>
+        <v>853</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>884</v>
+        <v>854</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>885</v>
+        <v>855</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>886</v>
+        <v>856</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>887</v>
+        <v>857</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>888</v>
+        <v>858</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>889</v>
+        <v>859</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
@@ -6969,7 +6879,7 @@
         <v>364</v>
       </c>
       <c r="C167" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D167" t="s">
         <v>37</v>
@@ -7015,7 +6925,7 @@
         <v>366</v>
       </c>
       <c r="C169" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D169" t="s">
         <v>37</v>
@@ -7685,10 +7595,10 @@
         <v>80</v>
       </c>
       <c r="D198" t="s">
-        <v>416</v>
+        <v>101</v>
       </c>
       <c r="E198" t="s">
-        <v>417</v>
+        <v>102</v>
       </c>
       <c r="F198" s="1">
         <v>46255</v>
@@ -7702,22 +7612,22 @@
         <v>0</v>
       </c>
       <c r="B199" t="s">
+        <v>416</v>
+      </c>
+      <c r="C199" t="s">
+        <v>2</v>
+      </c>
+      <c r="D199" t="s">
+        <v>417</v>
+      </c>
+      <c r="E199" t="s">
         <v>418</v>
-      </c>
-      <c r="C199" t="s">
-        <v>2</v>
-      </c>
-      <c r="D199" t="s">
-        <v>314</v>
-      </c>
-      <c r="E199" t="s">
-        <v>315</v>
       </c>
       <c r="F199" s="1">
         <v>46255</v>
       </c>
       <c r="G199" s="1">
-        <v>46255</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.2">
@@ -7731,16 +7641,16 @@
         <v>80</v>
       </c>
       <c r="D200" t="s">
-        <v>101</v>
+        <v>417</v>
       </c>
       <c r="E200" t="s">
-        <v>102</v>
+        <v>418</v>
       </c>
       <c r="F200" s="1">
         <v>46255</v>
       </c>
       <c r="G200" s="1">
-        <v>46255</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.2">
@@ -7751,19 +7661,19 @@
         <v>420</v>
       </c>
       <c r="C201" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D201" t="s">
-        <v>421</v>
+        <v>101</v>
       </c>
       <c r="E201" t="s">
-        <v>422</v>
+        <v>102</v>
       </c>
       <c r="F201" s="1">
         <v>46255</v>
       </c>
       <c r="G201" s="1">
-        <v>46259</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="202" spans="1:7" x14ac:dyDescent="0.2">
@@ -7771,22 +7681,22 @@
         <v>0</v>
       </c>
       <c r="B202" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="C202" t="s">
         <v>80</v>
       </c>
       <c r="D202" t="s">
-        <v>421</v>
+        <v>16</v>
       </c>
       <c r="E202" t="s">
-        <v>422</v>
+        <v>17</v>
       </c>
       <c r="F202" s="1">
         <v>46255</v>
       </c>
       <c r="G202" s="1">
-        <v>46259</v>
+        <v>46256</v>
       </c>
     </row>
     <row r="203" spans="1:7" x14ac:dyDescent="0.2">
@@ -7794,16 +7704,16 @@
         <v>0</v>
       </c>
       <c r="B203" t="s">
+        <v>422</v>
+      </c>
+      <c r="C203" t="s">
+        <v>2</v>
+      </c>
+      <c r="D203" t="s">
+        <v>423</v>
+      </c>
+      <c r="E203" t="s">
         <v>424</v>
-      </c>
-      <c r="C203" t="s">
-        <v>80</v>
-      </c>
-      <c r="D203" t="s">
-        <v>425</v>
-      </c>
-      <c r="E203" t="s">
-        <v>426</v>
       </c>
       <c r="F203" s="1">
         <v>46255</v>
@@ -7817,22 +7727,22 @@
         <v>0</v>
       </c>
       <c r="B204" t="s">
+        <v>425</v>
+      </c>
+      <c r="C204" t="s">
+        <v>2</v>
+      </c>
+      <c r="D204" t="s">
+        <v>426</v>
+      </c>
+      <c r="E204" t="s">
         <v>427</v>
-      </c>
-      <c r="C204" t="s">
-        <v>80</v>
-      </c>
-      <c r="D204" t="s">
-        <v>101</v>
-      </c>
-      <c r="E204" t="s">
-        <v>102</v>
       </c>
       <c r="F204" s="1">
         <v>46255</v>
       </c>
       <c r="G204" s="1">
-        <v>46255</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="205" spans="1:7" x14ac:dyDescent="0.2">
@@ -7846,16 +7756,16 @@
         <v>80</v>
       </c>
       <c r="D205" t="s">
-        <v>16</v>
+        <v>407</v>
       </c>
       <c r="E205" t="s">
-        <v>17</v>
+        <v>408</v>
       </c>
       <c r="F205" s="1">
         <v>46255</v>
       </c>
       <c r="G205" s="1">
-        <v>46256</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="206" spans="1:7" x14ac:dyDescent="0.2">
@@ -7869,10 +7779,10 @@
         <v>80</v>
       </c>
       <c r="D206" t="s">
-        <v>430</v>
+        <v>37</v>
       </c>
       <c r="E206" t="s">
-        <v>431</v>
+        <v>38</v>
       </c>
       <c r="F206" s="1">
         <v>46255</v>
@@ -7886,22 +7796,22 @@
         <v>0</v>
       </c>
       <c r="B207" t="s">
+        <v>430</v>
+      </c>
+      <c r="C207" t="s">
+        <v>2</v>
+      </c>
+      <c r="D207" t="s">
+        <v>431</v>
+      </c>
+      <c r="E207" t="s">
         <v>432</v>
-      </c>
-      <c r="C207" t="s">
-        <v>2</v>
-      </c>
-      <c r="D207" t="s">
-        <v>165</v>
-      </c>
-      <c r="E207" t="s">
-        <v>166</v>
       </c>
       <c r="F207" s="1">
         <v>46255</v>
       </c>
       <c r="G207" s="1">
-        <v>46255</v>
+        <v>46258</v>
       </c>
     </row>
     <row r="208" spans="1:7" x14ac:dyDescent="0.2">
@@ -7912,19 +7822,19 @@
         <v>433</v>
       </c>
       <c r="C208" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D208" t="s">
-        <v>434</v>
+        <v>16</v>
       </c>
       <c r="E208" t="s">
-        <v>435</v>
+        <v>17</v>
       </c>
       <c r="F208" s="1">
         <v>46255</v>
       </c>
       <c r="G208" s="1">
-        <v>46260</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="209" spans="1:7" x14ac:dyDescent="0.2">
@@ -7932,22 +7842,22 @@
         <v>0</v>
       </c>
       <c r="B209" t="s">
+        <v>434</v>
+      </c>
+      <c r="C209" t="s">
+        <v>80</v>
+      </c>
+      <c r="D209" t="s">
+        <v>435</v>
+      </c>
+      <c r="E209" t="s">
         <v>436</v>
-      </c>
-      <c r="C209" t="s">
-        <v>80</v>
-      </c>
-      <c r="D209" t="s">
-        <v>407</v>
-      </c>
-      <c r="E209" t="s">
-        <v>408</v>
       </c>
       <c r="F209" s="1">
         <v>46255</v>
       </c>
       <c r="G209" s="1">
-        <v>46255</v>
+        <v>46258</v>
       </c>
     </row>
     <row r="210" spans="1:7" x14ac:dyDescent="0.2">
@@ -7961,16 +7871,16 @@
         <v>80</v>
       </c>
       <c r="D210" t="s">
-        <v>37</v>
+        <v>402</v>
       </c>
       <c r="E210" t="s">
-        <v>38</v>
+        <v>403</v>
       </c>
       <c r="F210" s="1">
         <v>46255</v>
       </c>
       <c r="G210" s="1">
-        <v>46255</v>
+        <v>46258</v>
       </c>
     </row>
     <row r="211" spans="1:7" x14ac:dyDescent="0.2">
@@ -7981,13 +7891,13 @@
         <v>438</v>
       </c>
       <c r="C211" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D211" t="s">
-        <v>439</v>
+        <v>402</v>
       </c>
       <c r="E211" t="s">
-        <v>440</v>
+        <v>403</v>
       </c>
       <c r="F211" s="1">
         <v>46255</v>
@@ -8001,22 +7911,22 @@
         <v>0</v>
       </c>
       <c r="B212" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C212" t="s">
         <v>80</v>
       </c>
       <c r="D212" t="s">
-        <v>16</v>
+        <v>377</v>
       </c>
       <c r="E212" t="s">
-        <v>17</v>
+        <v>378</v>
       </c>
       <c r="F212" s="1">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="G212" s="1">
-        <v>46255</v>
+        <v>46258</v>
       </c>
     </row>
     <row r="213" spans="1:7" x14ac:dyDescent="0.2">
@@ -8024,19 +7934,19 @@
         <v>0</v>
       </c>
       <c r="B213" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="C213" t="s">
         <v>80</v>
       </c>
       <c r="D213" t="s">
-        <v>443</v>
+        <v>332</v>
       </c>
       <c r="E213" t="s">
-        <v>444</v>
+        <v>333</v>
       </c>
       <c r="F213" s="1">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="G213" s="1">
         <v>46258</v>
@@ -8047,22 +7957,22 @@
         <v>0</v>
       </c>
       <c r="B214" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="C214" t="s">
         <v>80</v>
       </c>
       <c r="D214" t="s">
-        <v>402</v>
+        <v>442</v>
       </c>
       <c r="E214" t="s">
-        <v>403</v>
+        <v>443</v>
       </c>
       <c r="F214" s="1">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="G214" s="1">
-        <v>46258</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="215" spans="1:7" x14ac:dyDescent="0.2">
@@ -8070,22 +7980,22 @@
         <v>0</v>
       </c>
       <c r="B215" t="s">
+        <v>444</v>
+      </c>
+      <c r="C215" t="s">
+        <v>80</v>
+      </c>
+      <c r="D215" t="s">
+        <v>445</v>
+      </c>
+      <c r="E215" t="s">
         <v>446</v>
       </c>
-      <c r="C215" t="s">
-        <v>80</v>
-      </c>
-      <c r="D215" t="s">
-        <v>402</v>
-      </c>
-      <c r="E215" t="s">
-        <v>403</v>
-      </c>
       <c r="F215" s="1">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="G215" s="1">
-        <v>46258</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="216" spans="1:7" x14ac:dyDescent="0.2">
@@ -8099,10 +8009,10 @@
         <v>80</v>
       </c>
       <c r="D216" t="s">
-        <v>377</v>
+        <v>171</v>
       </c>
       <c r="E216" t="s">
-        <v>378</v>
+        <v>172</v>
       </c>
       <c r="F216" s="1">
         <v>46258</v>
@@ -8119,13 +8029,13 @@
         <v>448</v>
       </c>
       <c r="C217" t="s">
-        <v>80</v>
+        <v>6</v>
       </c>
       <c r="D217" t="s">
-        <v>332</v>
+        <v>449</v>
       </c>
       <c r="E217" t="s">
-        <v>333</v>
+        <v>450</v>
       </c>
       <c r="F217" s="1">
         <v>46258</v>
@@ -8139,16 +8049,16 @@
         <v>0</v>
       </c>
       <c r="B218" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="C218" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D218" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="E218" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="F218" s="1">
         <v>46258</v>
@@ -8162,22 +8072,22 @@
         <v>0</v>
       </c>
       <c r="B219" t="s">
+        <v>454</v>
+      </c>
+      <c r="C219" t="s">
+        <v>2</v>
+      </c>
+      <c r="D219" t="s">
         <v>452</v>
       </c>
-      <c r="C219" t="s">
-        <v>80</v>
-      </c>
-      <c r="D219" t="s">
+      <c r="E219" t="s">
         <v>453</v>
-      </c>
-      <c r="E219" t="s">
-        <v>454</v>
       </c>
       <c r="F219" s="1">
         <v>46258</v>
       </c>
       <c r="G219" s="1">
-        <v>46259</v>
+        <v>46258</v>
       </c>
     </row>
     <row r="220" spans="1:7" x14ac:dyDescent="0.2">
@@ -8211,19 +8121,19 @@
         <v>458</v>
       </c>
       <c r="C221" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D221" t="s">
-        <v>171</v>
+        <v>314</v>
       </c>
       <c r="E221" t="s">
-        <v>172</v>
+        <v>315</v>
       </c>
       <c r="F221" s="1">
         <v>46258</v>
       </c>
       <c r="G221" s="1">
-        <v>46258</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.2">
@@ -8234,13 +8144,13 @@
         <v>459</v>
       </c>
       <c r="C222" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D222" t="s">
-        <v>460</v>
+        <v>158</v>
       </c>
       <c r="E222" t="s">
-        <v>461</v>
+        <v>159</v>
       </c>
       <c r="F222" s="1">
         <v>46258</v>
@@ -8254,16 +8164,16 @@
         <v>0</v>
       </c>
       <c r="B223" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="C223" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D223" t="s">
-        <v>463</v>
+        <v>417</v>
       </c>
       <c r="E223" t="s">
-        <v>464</v>
+        <v>418</v>
       </c>
       <c r="F223" s="1">
         <v>46258</v>
@@ -8277,16 +8187,16 @@
         <v>0</v>
       </c>
       <c r="B224" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="C224" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D224" t="s">
-        <v>463</v>
+        <v>359</v>
       </c>
       <c r="E224" t="s">
-        <v>464</v>
+        <v>360</v>
       </c>
       <c r="F224" s="1">
         <v>46258</v>
@@ -8300,16 +8210,16 @@
         <v>0</v>
       </c>
       <c r="B225" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="C225" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D225" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="E225" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="F225" s="1">
         <v>46258</v>
@@ -8323,16 +8233,16 @@
         <v>0</v>
       </c>
       <c r="B226" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="C226" t="s">
         <v>2</v>
       </c>
       <c r="D226" t="s">
-        <v>314</v>
+        <v>466</v>
       </c>
       <c r="E226" t="s">
-        <v>315</v>
+        <v>467</v>
       </c>
       <c r="F226" s="1">
         <v>46258</v>
@@ -8346,22 +8256,22 @@
         <v>0</v>
       </c>
       <c r="B227" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="C227" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D227" t="s">
-        <v>158</v>
+        <v>274</v>
       </c>
       <c r="E227" t="s">
-        <v>159</v>
+        <v>275</v>
       </c>
       <c r="F227" s="1">
         <v>46258</v>
       </c>
       <c r="G227" s="1">
-        <v>46258</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.2">
@@ -8369,16 +8279,16 @@
         <v>0</v>
       </c>
       <c r="B228" t="s">
+        <v>469</v>
+      </c>
+      <c r="C228" t="s">
+        <v>80</v>
+      </c>
+      <c r="D228" t="s">
+        <v>470</v>
+      </c>
+      <c r="E228" t="s">
         <v>471</v>
-      </c>
-      <c r="C228" t="s">
-        <v>2</v>
-      </c>
-      <c r="D228" t="s">
-        <v>472</v>
-      </c>
-      <c r="E228" t="s">
-        <v>473</v>
       </c>
       <c r="F228" s="1">
         <v>46258</v>
@@ -8392,16 +8302,16 @@
         <v>0</v>
       </c>
       <c r="B229" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="C229" t="s">
         <v>80</v>
       </c>
       <c r="D229" t="s">
-        <v>421</v>
+        <v>470</v>
       </c>
       <c r="E229" t="s">
-        <v>422</v>
+        <v>471</v>
       </c>
       <c r="F229" s="1">
         <v>46258</v>
@@ -8415,22 +8325,22 @@
         <v>0</v>
       </c>
       <c r="B230" t="s">
+        <v>473</v>
+      </c>
+      <c r="C230" t="s">
+        <v>80</v>
+      </c>
+      <c r="D230" t="s">
+        <v>474</v>
+      </c>
+      <c r="E230" t="s">
         <v>475</v>
-      </c>
-      <c r="C230" t="s">
-        <v>80</v>
-      </c>
-      <c r="D230" t="s">
-        <v>359</v>
-      </c>
-      <c r="E230" t="s">
-        <v>360</v>
       </c>
       <c r="F230" s="1">
         <v>46258</v>
       </c>
       <c r="G230" s="1">
-        <v>46258</v>
+        <v>46261</v>
       </c>
     </row>
     <row r="231" spans="1:7" x14ac:dyDescent="0.2">
@@ -8444,16 +8354,16 @@
         <v>80</v>
       </c>
       <c r="D231" t="s">
-        <v>477</v>
+        <v>470</v>
       </c>
       <c r="E231" t="s">
-        <v>478</v>
+        <v>471</v>
       </c>
       <c r="F231" s="1">
         <v>46258</v>
       </c>
       <c r="G231" s="1">
-        <v>46259</v>
+        <v>46258</v>
       </c>
     </row>
     <row r="232" spans="1:7" x14ac:dyDescent="0.2">
@@ -8461,16 +8371,16 @@
         <v>0</v>
       </c>
       <c r="B232" t="s">
+        <v>477</v>
+      </c>
+      <c r="C232" t="s">
+        <v>80</v>
+      </c>
+      <c r="D232" t="s">
+        <v>478</v>
+      </c>
+      <c r="E232" t="s">
         <v>479</v>
-      </c>
-      <c r="C232" t="s">
-        <v>2</v>
-      </c>
-      <c r="D232" t="s">
-        <v>480</v>
-      </c>
-      <c r="E232" t="s">
-        <v>481</v>
       </c>
       <c r="F232" s="1">
         <v>46258</v>
@@ -8484,22 +8394,22 @@
         <v>0</v>
       </c>
       <c r="B233" t="s">
+        <v>480</v>
+      </c>
+      <c r="C233" t="s">
+        <v>2</v>
+      </c>
+      <c r="D233" t="s">
+        <v>481</v>
+      </c>
+      <c r="E233" t="s">
         <v>482</v>
-      </c>
-      <c r="C233" t="s">
-        <v>2</v>
-      </c>
-      <c r="D233" t="s">
-        <v>483</v>
-      </c>
-      <c r="E233" t="s">
-        <v>484</v>
       </c>
       <c r="F233" s="1">
         <v>46258</v>
       </c>
       <c r="G233" s="1">
-        <v>46258</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="234" spans="1:7" x14ac:dyDescent="0.2">
@@ -8507,16 +8417,16 @@
         <v>0</v>
       </c>
       <c r="B234" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="C234" t="s">
         <v>80</v>
       </c>
       <c r="D234" t="s">
-        <v>274</v>
+        <v>474</v>
       </c>
       <c r="E234" t="s">
-        <v>275</v>
+        <v>475</v>
       </c>
       <c r="F234" s="1">
         <v>46258</v>
@@ -8530,22 +8440,22 @@
         <v>0</v>
       </c>
       <c r="B235" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="C235" t="s">
         <v>80</v>
       </c>
       <c r="D235" t="s">
-        <v>487</v>
+        <v>407</v>
       </c>
       <c r="E235" t="s">
-        <v>488</v>
+        <v>408</v>
       </c>
       <c r="F235" s="1">
         <v>46258</v>
       </c>
       <c r="G235" s="1">
-        <v>46258</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="236" spans="1:7" x14ac:dyDescent="0.2">
@@ -8553,22 +8463,22 @@
         <v>0</v>
       </c>
       <c r="B236" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="C236" t="s">
         <v>80</v>
       </c>
       <c r="D236" t="s">
+        <v>486</v>
+      </c>
+      <c r="E236" t="s">
         <v>487</v>
-      </c>
-      <c r="E236" t="s">
-        <v>488</v>
       </c>
       <c r="F236" s="1">
         <v>46258</v>
       </c>
       <c r="G236" s="1">
-        <v>46258</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.2">
@@ -8576,22 +8486,22 @@
         <v>0</v>
       </c>
       <c r="B237" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="C237" t="s">
         <v>80</v>
       </c>
       <c r="D237" t="s">
-        <v>491</v>
+        <v>299</v>
       </c>
       <c r="E237" t="s">
-        <v>492</v>
+        <v>300</v>
       </c>
       <c r="F237" s="1">
         <v>46258</v>
       </c>
       <c r="G237" s="1">
-        <v>46261</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="238" spans="1:7" x14ac:dyDescent="0.2">
@@ -8599,22 +8509,22 @@
         <v>0</v>
       </c>
       <c r="B238" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="C238" t="s">
         <v>80</v>
       </c>
       <c r="D238" t="s">
-        <v>487</v>
+        <v>299</v>
       </c>
       <c r="E238" t="s">
-        <v>488</v>
+        <v>300</v>
       </c>
       <c r="F238" s="1">
         <v>46258</v>
       </c>
       <c r="G238" s="1">
-        <v>46258</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="239" spans="1:7" x14ac:dyDescent="0.2">
@@ -8622,22 +8532,22 @@
         <v>0</v>
       </c>
       <c r="B239" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="C239" t="s">
         <v>80</v>
       </c>
       <c r="D239" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="E239" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="F239" s="1">
         <v>46258</v>
       </c>
       <c r="G239" s="1">
-        <v>46259</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="240" spans="1:7" x14ac:dyDescent="0.2">
@@ -8645,16 +8555,16 @@
         <v>0</v>
       </c>
       <c r="B240" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="C240" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D240" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="E240" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="F240" s="1">
         <v>46258</v>
@@ -8668,22 +8578,22 @@
         <v>0</v>
       </c>
       <c r="B241" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="C241" t="s">
         <v>80</v>
       </c>
       <c r="D241" t="s">
-        <v>491</v>
+        <v>127</v>
       </c>
       <c r="E241" t="s">
-        <v>492</v>
+        <v>128</v>
       </c>
       <c r="F241" s="1">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="G241" s="1">
-        <v>46259</v>
+        <v>46261</v>
       </c>
     </row>
     <row r="242" spans="1:7" x14ac:dyDescent="0.2">
@@ -8691,19 +8601,19 @@
         <v>0</v>
       </c>
       <c r="B242" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="C242" t="s">
         <v>80</v>
       </c>
       <c r="D242" t="s">
-        <v>407</v>
+        <v>98</v>
       </c>
       <c r="E242" t="s">
-        <v>408</v>
+        <v>99</v>
       </c>
       <c r="F242" s="1">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="G242" s="1">
         <v>46259</v>
@@ -8714,22 +8624,22 @@
         <v>0</v>
       </c>
       <c r="B243" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="C243" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D243" t="s">
-        <v>503</v>
+        <v>284</v>
       </c>
       <c r="E243" t="s">
-        <v>504</v>
+        <v>285</v>
       </c>
       <c r="F243" s="1">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="G243" s="1">
-        <v>46259</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="244" spans="1:7" x14ac:dyDescent="0.2">
@@ -8737,19 +8647,19 @@
         <v>0</v>
       </c>
       <c r="B244" t="s">
-        <v>505</v>
+        <v>499</v>
       </c>
       <c r="C244" t="s">
         <v>80</v>
       </c>
       <c r="D244" t="s">
-        <v>299</v>
+        <v>500</v>
       </c>
       <c r="E244" t="s">
-        <v>300</v>
+        <v>501</v>
       </c>
       <c r="F244" s="1">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="G244" s="1">
         <v>46259</v>
@@ -8760,19 +8670,19 @@
         <v>0</v>
       </c>
       <c r="B245" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="C245" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D245" t="s">
-        <v>299</v>
+        <v>37</v>
       </c>
       <c r="E245" t="s">
-        <v>300</v>
+        <v>38</v>
       </c>
       <c r="F245" s="1">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="G245" s="1">
         <v>46259</v>
@@ -8783,22 +8693,22 @@
         <v>0</v>
       </c>
       <c r="B246" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="C246" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D246" t="s">
-        <v>508</v>
+        <v>37</v>
       </c>
       <c r="E246" t="s">
-        <v>509</v>
+        <v>38</v>
       </c>
       <c r="F246" s="1">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="G246" s="1">
-        <v>46260</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="247" spans="1:7" x14ac:dyDescent="0.2">
@@ -8806,19 +8716,19 @@
         <v>0</v>
       </c>
       <c r="B247" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="C247" t="s">
-        <v>80</v>
+        <v>6</v>
       </c>
       <c r="D247" t="s">
-        <v>511</v>
+        <v>37</v>
       </c>
       <c r="E247" t="s">
-        <v>512</v>
+        <v>38</v>
       </c>
       <c r="F247" s="1">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="G247" s="1">
         <v>46259</v>
@@ -8829,22 +8739,22 @@
         <v>0</v>
       </c>
       <c r="B248" t="s">
-        <v>513</v>
+        <v>505</v>
       </c>
       <c r="C248" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D248" t="s">
-        <v>127</v>
+        <v>37</v>
       </c>
       <c r="E248" t="s">
-        <v>128</v>
+        <v>38</v>
       </c>
       <c r="F248" s="1">
         <v>46259</v>
       </c>
       <c r="G248" s="1">
-        <v>46261</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="249" spans="1:7" x14ac:dyDescent="0.2">
@@ -8852,7 +8762,7 @@
         <v>0</v>
       </c>
       <c r="B249" t="s">
-        <v>514</v>
+        <v>506</v>
       </c>
       <c r="C249" t="s">
         <v>80</v>
@@ -8875,22 +8785,22 @@
         <v>0</v>
       </c>
       <c r="B250" t="s">
-        <v>515</v>
+        <v>507</v>
       </c>
       <c r="C250" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D250" t="s">
-        <v>284</v>
+        <v>508</v>
       </c>
       <c r="E250" t="s">
-        <v>285</v>
+        <v>509</v>
       </c>
       <c r="F250" s="1">
         <v>46259</v>
       </c>
       <c r="G250" s="1">
-        <v>46260</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="251" spans="1:7" x14ac:dyDescent="0.2">
@@ -8898,16 +8808,16 @@
         <v>0</v>
       </c>
       <c r="B251" t="s">
-        <v>516</v>
+        <v>510</v>
       </c>
       <c r="C251" t="s">
-        <v>80</v>
+        <v>6</v>
       </c>
       <c r="D251" t="s">
-        <v>517</v>
+        <v>511</v>
       </c>
       <c r="E251" t="s">
-        <v>518</v>
+        <v>512</v>
       </c>
       <c r="F251" s="1">
         <v>46259</v>
@@ -8921,22 +8831,22 @@
         <v>0</v>
       </c>
       <c r="B252" t="s">
-        <v>519</v>
+        <v>513</v>
       </c>
       <c r="C252" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D252" t="s">
-        <v>37</v>
+        <v>105</v>
       </c>
       <c r="E252" t="s">
-        <v>38</v>
+        <v>106</v>
       </c>
       <c r="F252" s="1">
         <v>46259</v>
       </c>
       <c r="G252" s="1">
-        <v>46259</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="253" spans="1:7" x14ac:dyDescent="0.2">
@@ -8944,16 +8854,16 @@
         <v>0</v>
       </c>
       <c r="B253" t="s">
-        <v>520</v>
+        <v>514</v>
       </c>
       <c r="C253" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D253" t="s">
-        <v>37</v>
+        <v>306</v>
       </c>
       <c r="E253" t="s">
-        <v>38</v>
+        <v>307</v>
       </c>
       <c r="F253" s="1">
         <v>46259</v>
@@ -8967,16 +8877,16 @@
         <v>0</v>
       </c>
       <c r="B254" t="s">
-        <v>521</v>
+        <v>515</v>
       </c>
       <c r="C254" t="s">
-        <v>6</v>
+        <v>80</v>
       </c>
       <c r="D254" t="s">
-        <v>37</v>
+        <v>516</v>
       </c>
       <c r="E254" t="s">
-        <v>38</v>
+        <v>517</v>
       </c>
       <c r="F254" s="1">
         <v>46259</v>
@@ -8990,16 +8900,16 @@
         <v>0</v>
       </c>
       <c r="B255" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="C255" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D255" t="s">
-        <v>37</v>
+        <v>171</v>
       </c>
       <c r="E255" t="s">
-        <v>38</v>
+        <v>172</v>
       </c>
       <c r="F255" s="1">
         <v>46259</v>
@@ -9013,16 +8923,16 @@
         <v>0</v>
       </c>
       <c r="B256" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="C256" t="s">
         <v>80</v>
       </c>
       <c r="D256" t="s">
-        <v>393</v>
+        <v>520</v>
       </c>
       <c r="E256" t="s">
-        <v>394</v>
+        <v>521</v>
       </c>
       <c r="F256" s="1">
         <v>46259</v>
@@ -9036,16 +8946,16 @@
         <v>0</v>
       </c>
       <c r="B257" t="s">
+        <v>522</v>
+      </c>
+      <c r="C257" t="s">
+        <v>80</v>
+      </c>
+      <c r="D257" t="s">
+        <v>523</v>
+      </c>
+      <c r="E257" t="s">
         <v>524</v>
-      </c>
-      <c r="C257" t="s">
-        <v>80</v>
-      </c>
-      <c r="D257" t="s">
-        <v>98</v>
-      </c>
-      <c r="E257" t="s">
-        <v>99</v>
       </c>
       <c r="F257" s="1">
         <v>46259</v>
@@ -9085,13 +8995,13 @@
         <v>528</v>
       </c>
       <c r="C259" t="s">
-        <v>6</v>
+        <v>80</v>
       </c>
       <c r="D259" t="s">
-        <v>483</v>
+        <v>529</v>
       </c>
       <c r="E259" t="s">
-        <v>484</v>
+        <v>530</v>
       </c>
       <c r="F259" s="1">
         <v>46259</v>
@@ -9105,22 +9015,22 @@
         <v>0</v>
       </c>
       <c r="B260" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="C260" t="s">
         <v>80</v>
       </c>
       <c r="D260" t="s">
-        <v>105</v>
+        <v>532</v>
       </c>
       <c r="E260" t="s">
-        <v>106</v>
+        <v>533</v>
       </c>
       <c r="F260" s="1">
         <v>46259</v>
       </c>
       <c r="G260" s="1">
-        <v>46260</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="261" spans="1:7" x14ac:dyDescent="0.2">
@@ -9128,16 +9038,16 @@
         <v>0</v>
       </c>
       <c r="B261" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="C261" t="s">
         <v>80</v>
       </c>
       <c r="D261" t="s">
-        <v>306</v>
+        <v>535</v>
       </c>
       <c r="E261" t="s">
-        <v>307</v>
+        <v>536</v>
       </c>
       <c r="F261" s="1">
         <v>46259</v>
@@ -9151,16 +9061,16 @@
         <v>0</v>
       </c>
       <c r="B262" t="s">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="C262" t="s">
         <v>80</v>
       </c>
       <c r="D262" t="s">
-        <v>532</v>
+        <v>402</v>
       </c>
       <c r="E262" t="s">
-        <v>533</v>
+        <v>403</v>
       </c>
       <c r="F262" s="1">
         <v>46259</v>
@@ -9174,22 +9084,22 @@
         <v>0</v>
       </c>
       <c r="B263" t="s">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="C263" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D263" t="s">
-        <v>535</v>
+        <v>13</v>
       </c>
       <c r="E263" t="s">
-        <v>536</v>
+        <v>14</v>
       </c>
       <c r="F263" s="1">
         <v>46259</v>
       </c>
       <c r="G263" s="1">
-        <v>46259</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="264" spans="1:7" x14ac:dyDescent="0.2">
@@ -9197,16 +9107,16 @@
         <v>0</v>
       </c>
       <c r="B264" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="C264" t="s">
         <v>80</v>
       </c>
       <c r="D264" t="s">
-        <v>171</v>
+        <v>540</v>
       </c>
       <c r="E264" t="s">
-        <v>172</v>
+        <v>541</v>
       </c>
       <c r="F264" s="1">
         <v>46259</v>
@@ -9220,16 +9130,16 @@
         <v>0</v>
       </c>
       <c r="B265" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="C265" t="s">
         <v>80</v>
       </c>
       <c r="D265" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="E265" t="s">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="F265" s="1">
         <v>46259</v>
@@ -9243,16 +9153,16 @@
         <v>0</v>
       </c>
       <c r="B266" t="s">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="C266" t="s">
         <v>80</v>
       </c>
       <c r="D266" t="s">
-        <v>542</v>
+        <v>435</v>
       </c>
       <c r="E266" t="s">
-        <v>543</v>
+        <v>436</v>
       </c>
       <c r="F266" s="1">
         <v>46259</v>
@@ -9266,16 +9176,16 @@
         <v>0</v>
       </c>
       <c r="B267" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="C267" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D267" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="E267" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="F267" s="1">
         <v>46259</v>
@@ -9289,16 +9199,16 @@
         <v>0</v>
       </c>
       <c r="B268" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="C268" t="s">
         <v>80</v>
       </c>
       <c r="D268" t="s">
-        <v>548</v>
+        <v>456</v>
       </c>
       <c r="E268" t="s">
-        <v>549</v>
+        <v>457</v>
       </c>
       <c r="F268" s="1">
         <v>46259</v>
@@ -9318,10 +9228,10 @@
         <v>80</v>
       </c>
       <c r="D269" t="s">
-        <v>551</v>
+        <v>411</v>
       </c>
       <c r="E269" t="s">
-        <v>552</v>
+        <v>412</v>
       </c>
       <c r="F269" s="1">
         <v>46259</v>
@@ -9335,16 +9245,16 @@
         <v>0</v>
       </c>
       <c r="B270" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="C270" t="s">
         <v>80</v>
       </c>
       <c r="D270" t="s">
-        <v>554</v>
+        <v>98</v>
       </c>
       <c r="E270" t="s">
-        <v>555</v>
+        <v>99</v>
       </c>
       <c r="F270" s="1">
         <v>46259</v>
@@ -9358,16 +9268,16 @@
         <v>0</v>
       </c>
       <c r="B271" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="C271" t="s">
         <v>80</v>
       </c>
       <c r="D271" t="s">
-        <v>402</v>
+        <v>553</v>
       </c>
       <c r="E271" t="s">
-        <v>403</v>
+        <v>554</v>
       </c>
       <c r="F271" s="1">
         <v>46259</v>
@@ -9381,16 +9291,16 @@
         <v>0</v>
       </c>
       <c r="B272" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="C272" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D272" t="s">
-        <v>13</v>
+        <v>553</v>
       </c>
       <c r="E272" t="s">
-        <v>14</v>
+        <v>554</v>
       </c>
       <c r="F272" s="1">
         <v>46259</v>
@@ -9404,16 +9314,16 @@
         <v>0</v>
       </c>
       <c r="B273" t="s">
+        <v>556</v>
+      </c>
+      <c r="C273" t="s">
+        <v>80</v>
+      </c>
+      <c r="D273" t="s">
+        <v>557</v>
+      </c>
+      <c r="E273" t="s">
         <v>558</v>
-      </c>
-      <c r="C273" t="s">
-        <v>2</v>
-      </c>
-      <c r="D273" t="s">
-        <v>81</v>
-      </c>
-      <c r="E273" t="s">
-        <v>82</v>
       </c>
       <c r="F273" s="1">
         <v>46259</v>
@@ -9433,10 +9343,10 @@
         <v>80</v>
       </c>
       <c r="D274" t="s">
-        <v>560</v>
+        <v>332</v>
       </c>
       <c r="E274" t="s">
-        <v>561</v>
+        <v>333</v>
       </c>
       <c r="F274" s="1">
         <v>46259</v>
@@ -9450,16 +9360,16 @@
         <v>0</v>
       </c>
       <c r="B275" t="s">
+        <v>560</v>
+      </c>
+      <c r="C275" t="s">
+        <v>80</v>
+      </c>
+      <c r="D275" t="s">
+        <v>561</v>
+      </c>
+      <c r="E275" t="s">
         <v>562</v>
-      </c>
-      <c r="C275" t="s">
-        <v>80</v>
-      </c>
-      <c r="D275" t="s">
-        <v>563</v>
-      </c>
-      <c r="E275" t="s">
-        <v>564</v>
       </c>
       <c r="F275" s="1">
         <v>46259</v>
@@ -9473,16 +9383,16 @@
         <v>0</v>
       </c>
       <c r="B276" t="s">
+        <v>563</v>
+      </c>
+      <c r="C276" t="s">
+        <v>80</v>
+      </c>
+      <c r="D276" t="s">
+        <v>564</v>
+      </c>
+      <c r="E276" t="s">
         <v>565</v>
-      </c>
-      <c r="C276" t="s">
-        <v>80</v>
-      </c>
-      <c r="D276" t="s">
-        <v>443</v>
-      </c>
-      <c r="E276" t="s">
-        <v>444</v>
       </c>
       <c r="F276" s="1">
         <v>46259</v>
@@ -9499,7 +9409,7 @@
         <v>566</v>
       </c>
       <c r="C277" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D277" t="s">
         <v>567</v>
@@ -9511,7 +9421,7 @@
         <v>46259</v>
       </c>
       <c r="G277" s="1">
-        <v>46259</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="278" spans="1:7" x14ac:dyDescent="0.2">
@@ -9525,10 +9435,10 @@
         <v>80</v>
       </c>
       <c r="D278" t="s">
-        <v>467</v>
+        <v>570</v>
       </c>
       <c r="E278" t="s">
-        <v>468</v>
+        <v>571</v>
       </c>
       <c r="F278" s="1">
         <v>46259</v>
@@ -9542,16 +9452,16 @@
         <v>0</v>
       </c>
       <c r="B279" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="C279" t="s">
         <v>80</v>
       </c>
       <c r="D279" t="s">
-        <v>411</v>
+        <v>573</v>
       </c>
       <c r="E279" t="s">
-        <v>412</v>
+        <v>574</v>
       </c>
       <c r="F279" s="1">
         <v>46259</v>
@@ -9565,16 +9475,16 @@
         <v>0</v>
       </c>
       <c r="B280" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="C280" t="s">
         <v>80</v>
       </c>
       <c r="D280" t="s">
-        <v>98</v>
+        <v>135</v>
       </c>
       <c r="E280" t="s">
-        <v>99</v>
+        <v>136</v>
       </c>
       <c r="F280" s="1">
         <v>46259</v>
@@ -9588,22 +9498,22 @@
         <v>0</v>
       </c>
       <c r="B281" t="s">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="C281" t="s">
         <v>80</v>
       </c>
       <c r="D281" t="s">
-        <v>573</v>
+        <v>344</v>
       </c>
       <c r="E281" t="s">
-        <v>574</v>
+        <v>345</v>
       </c>
       <c r="F281" s="1">
         <v>46259</v>
       </c>
       <c r="G281" s="1">
-        <v>46259</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="282" spans="1:7" x14ac:dyDescent="0.2">
@@ -9611,22 +9521,22 @@
         <v>0</v>
       </c>
       <c r="B282" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="C282" t="s">
         <v>80</v>
       </c>
       <c r="D282" t="s">
-        <v>573</v>
+        <v>77</v>
       </c>
       <c r="E282" t="s">
-        <v>574</v>
+        <v>78</v>
       </c>
       <c r="F282" s="1">
         <v>46259</v>
       </c>
       <c r="G282" s="1">
-        <v>46260</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="283" spans="1:7" x14ac:dyDescent="0.2">
@@ -9634,16 +9544,16 @@
         <v>0</v>
       </c>
       <c r="B283" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="C283" t="s">
         <v>80</v>
       </c>
       <c r="D283" t="s">
-        <v>577</v>
+        <v>68</v>
       </c>
       <c r="E283" t="s">
-        <v>578</v>
+        <v>69</v>
       </c>
       <c r="F283" s="1">
         <v>46259</v>
@@ -9663,10 +9573,10 @@
         <v>80</v>
       </c>
       <c r="D284" t="s">
-        <v>573</v>
+        <v>580</v>
       </c>
       <c r="E284" t="s">
-        <v>574</v>
+        <v>581</v>
       </c>
       <c r="F284" s="1">
         <v>46259</v>
@@ -9680,16 +9590,16 @@
         <v>0</v>
       </c>
       <c r="B285" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="C285" t="s">
         <v>80</v>
       </c>
       <c r="D285" t="s">
-        <v>332</v>
+        <v>16</v>
       </c>
       <c r="E285" t="s">
-        <v>333</v>
+        <v>17</v>
       </c>
       <c r="F285" s="1">
         <v>46259</v>
@@ -9703,16 +9613,16 @@
         <v>0</v>
       </c>
       <c r="B286" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="C286" t="s">
         <v>80</v>
       </c>
       <c r="D286" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="E286" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="F286" s="1">
         <v>46259</v>
@@ -9726,16 +9636,16 @@
         <v>0</v>
       </c>
       <c r="B287" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="C287" t="s">
         <v>80</v>
       </c>
       <c r="D287" t="s">
-        <v>585</v>
+        <v>174</v>
       </c>
       <c r="E287" t="s">
-        <v>586</v>
+        <v>175</v>
       </c>
       <c r="F287" s="1">
         <v>46259</v>
@@ -9755,16 +9665,16 @@
         <v>80</v>
       </c>
       <c r="D288" t="s">
-        <v>588</v>
+        <v>28</v>
       </c>
       <c r="E288" t="s">
-        <v>589</v>
+        <v>29</v>
       </c>
       <c r="F288" s="1">
         <v>46259</v>
       </c>
       <c r="G288" s="1">
-        <v>46259</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="289" spans="1:7" x14ac:dyDescent="0.2">
@@ -9772,22 +9682,22 @@
         <v>0</v>
       </c>
       <c r="B289" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="C289" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D289" t="s">
-        <v>591</v>
+        <v>155</v>
       </c>
       <c r="E289" t="s">
-        <v>592</v>
+        <v>156</v>
       </c>
       <c r="F289" s="1">
         <v>46259</v>
       </c>
       <c r="G289" s="1">
-        <v>46260</v>
+        <v>46261</v>
       </c>
     </row>
     <row r="290" spans="1:7" x14ac:dyDescent="0.2">
@@ -9795,22 +9705,22 @@
         <v>0</v>
       </c>
       <c r="B290" t="s">
-        <v>593</v>
+        <v>589</v>
       </c>
       <c r="C290" t="s">
         <v>80</v>
       </c>
       <c r="D290" t="s">
-        <v>594</v>
+        <v>491</v>
       </c>
       <c r="E290" t="s">
-        <v>595</v>
+        <v>492</v>
       </c>
       <c r="F290" s="1">
         <v>46259</v>
       </c>
       <c r="G290" s="1">
-        <v>46259</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="291" spans="1:7" x14ac:dyDescent="0.2">
@@ -9818,22 +9728,22 @@
         <v>0</v>
       </c>
       <c r="B291" t="s">
-        <v>596</v>
+        <v>590</v>
       </c>
       <c r="C291" t="s">
         <v>80</v>
       </c>
       <c r="D291" t="s">
-        <v>597</v>
+        <v>591</v>
       </c>
       <c r="E291" t="s">
-        <v>598</v>
+        <v>592</v>
       </c>
       <c r="F291" s="1">
         <v>46259</v>
       </c>
       <c r="G291" s="1">
-        <v>46259</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="292" spans="1:7" x14ac:dyDescent="0.2">
@@ -9841,22 +9751,22 @@
         <v>0</v>
       </c>
       <c r="B292" t="s">
-        <v>599</v>
+        <v>593</v>
       </c>
       <c r="C292" t="s">
         <v>80</v>
       </c>
       <c r="D292" t="s">
-        <v>600</v>
+        <v>98</v>
       </c>
       <c r="E292" t="s">
-        <v>601</v>
+        <v>99</v>
       </c>
       <c r="F292" s="1">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="G292" s="1">
-        <v>46259</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="293" spans="1:7" x14ac:dyDescent="0.2">
@@ -9864,22 +9774,22 @@
         <v>0</v>
       </c>
       <c r="B293" t="s">
-        <v>602</v>
+        <v>594</v>
       </c>
       <c r="C293" t="s">
         <v>80</v>
       </c>
       <c r="D293" t="s">
-        <v>135</v>
+        <v>98</v>
       </c>
       <c r="E293" t="s">
-        <v>136</v>
+        <v>99</v>
       </c>
       <c r="F293" s="1">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="G293" s="1">
-        <v>46259</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="294" spans="1:7" x14ac:dyDescent="0.2">
@@ -9887,19 +9797,19 @@
         <v>0</v>
       </c>
       <c r="B294" t="s">
-        <v>603</v>
+        <v>595</v>
       </c>
       <c r="C294" t="s">
         <v>80</v>
       </c>
       <c r="D294" t="s">
-        <v>344</v>
+        <v>596</v>
       </c>
       <c r="E294" t="s">
-        <v>345</v>
+        <v>597</v>
       </c>
       <c r="F294" s="1">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="G294" s="1">
         <v>46260</v>
@@ -9910,22 +9820,22 @@
         <v>0</v>
       </c>
       <c r="B295" t="s">
-        <v>604</v>
+        <v>598</v>
       </c>
       <c r="C295" t="s">
         <v>80</v>
       </c>
       <c r="D295" t="s">
-        <v>77</v>
+        <v>599</v>
       </c>
       <c r="E295" t="s">
-        <v>78</v>
+        <v>600</v>
       </c>
       <c r="F295" s="1">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="G295" s="1">
-        <v>46259</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="296" spans="1:7" x14ac:dyDescent="0.2">
@@ -9933,22 +9843,22 @@
         <v>0</v>
       </c>
       <c r="B296" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="C296" t="s">
         <v>80</v>
       </c>
       <c r="D296" t="s">
-        <v>68</v>
+        <v>602</v>
       </c>
       <c r="E296" t="s">
-        <v>69</v>
+        <v>603</v>
       </c>
       <c r="F296" s="1">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="G296" s="1">
-        <v>46259</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="297" spans="1:7" x14ac:dyDescent="0.2">
@@ -9956,22 +9866,22 @@
         <v>0</v>
       </c>
       <c r="B297" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="C297" t="s">
         <v>80</v>
       </c>
       <c r="D297" t="s">
-        <v>607</v>
+        <v>16</v>
       </c>
       <c r="E297" t="s">
-        <v>608</v>
+        <v>17</v>
       </c>
       <c r="F297" s="1">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="G297" s="1">
-        <v>46259</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="298" spans="1:7" x14ac:dyDescent="0.2">
@@ -9979,22 +9889,22 @@
         <v>0</v>
       </c>
       <c r="B298" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="C298" t="s">
         <v>80</v>
       </c>
       <c r="D298" t="s">
-        <v>16</v>
+        <v>606</v>
       </c>
       <c r="E298" t="s">
-        <v>17</v>
+        <v>607</v>
       </c>
       <c r="F298" s="1">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="G298" s="1">
-        <v>46259</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="299" spans="1:7" x14ac:dyDescent="0.2">
@@ -10002,22 +9912,22 @@
         <v>0</v>
       </c>
       <c r="B299" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="C299" t="s">
         <v>80</v>
       </c>
       <c r="D299" t="s">
-        <v>611</v>
+        <v>606</v>
       </c>
       <c r="E299" t="s">
-        <v>612</v>
+        <v>607</v>
       </c>
       <c r="F299" s="1">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="G299" s="1">
-        <v>46259</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="300" spans="1:7" x14ac:dyDescent="0.2">
@@ -10025,22 +9935,22 @@
         <v>0</v>
       </c>
       <c r="B300" t="s">
-        <v>613</v>
+        <v>609</v>
       </c>
       <c r="C300" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D300" t="s">
-        <v>341</v>
+        <v>610</v>
       </c>
       <c r="E300" t="s">
-        <v>342</v>
+        <v>611</v>
       </c>
       <c r="F300" s="1">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="G300" s="1">
-        <v>46259</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="301" spans="1:7" x14ac:dyDescent="0.2">
@@ -10048,22 +9958,22 @@
         <v>0</v>
       </c>
       <c r="B301" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="C301" t="s">
         <v>80</v>
       </c>
       <c r="D301" t="s">
-        <v>174</v>
+        <v>599</v>
       </c>
       <c r="E301" t="s">
-        <v>175</v>
+        <v>600</v>
       </c>
       <c r="F301" s="1">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="G301" s="1">
-        <v>46259</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="302" spans="1:7" x14ac:dyDescent="0.2">
@@ -10071,19 +9981,19 @@
         <v>0</v>
       </c>
       <c r="B302" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="C302" t="s">
         <v>80</v>
       </c>
       <c r="D302" t="s">
-        <v>28</v>
+        <v>215</v>
       </c>
       <c r="E302" t="s">
-        <v>29</v>
+        <v>216</v>
       </c>
       <c r="F302" s="1">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="G302" s="1">
         <v>46260</v>
@@ -10094,22 +10004,22 @@
         <v>0</v>
       </c>
       <c r="B303" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="C303" t="s">
         <v>80</v>
       </c>
       <c r="D303" t="s">
-        <v>155</v>
+        <v>445</v>
       </c>
       <c r="E303" t="s">
-        <v>156</v>
+        <v>446</v>
       </c>
       <c r="F303" s="1">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="G303" s="1">
-        <v>46261</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="304" spans="1:7" x14ac:dyDescent="0.2">
@@ -10117,19 +10027,19 @@
         <v>0</v>
       </c>
       <c r="B304" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="C304" t="s">
         <v>80</v>
       </c>
       <c r="D304" t="s">
-        <v>508</v>
+        <v>491</v>
       </c>
       <c r="E304" t="s">
-        <v>509</v>
+        <v>492</v>
       </c>
       <c r="F304" s="1">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="G304" s="1">
         <v>46260</v>
@@ -10140,19 +10050,19 @@
         <v>0</v>
       </c>
       <c r="B305" t="s">
+        <v>616</v>
+      </c>
+      <c r="C305" t="s">
+        <v>80</v>
+      </c>
+      <c r="D305" t="s">
+        <v>617</v>
+      </c>
+      <c r="E305" t="s">
         <v>618</v>
       </c>
-      <c r="C305" t="s">
-        <v>80</v>
-      </c>
-      <c r="D305" t="s">
-        <v>619</v>
-      </c>
-      <c r="E305" t="s">
-        <v>620</v>
-      </c>
       <c r="F305" s="1">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="G305" s="1">
         <v>46260</v>
@@ -10163,16 +10073,16 @@
         <v>0</v>
       </c>
       <c r="B306" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="C306" t="s">
         <v>80</v>
       </c>
       <c r="D306" t="s">
-        <v>98</v>
+        <v>16</v>
       </c>
       <c r="E306" t="s">
-        <v>99</v>
+        <v>17</v>
       </c>
       <c r="F306" s="1">
         <v>46260</v>
@@ -10186,16 +10096,16 @@
         <v>0</v>
       </c>
       <c r="B307" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="C307" t="s">
         <v>80</v>
       </c>
       <c r="D307" t="s">
-        <v>98</v>
+        <v>16</v>
       </c>
       <c r="E307" t="s">
-        <v>99</v>
+        <v>17</v>
       </c>
       <c r="F307" s="1">
         <v>46260</v>
@@ -10209,22 +10119,22 @@
         <v>0</v>
       </c>
       <c r="B308" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="C308" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D308" t="s">
-        <v>624</v>
+        <v>132</v>
       </c>
       <c r="E308" t="s">
-        <v>625</v>
+        <v>133</v>
       </c>
       <c r="F308" s="1">
         <v>46260</v>
       </c>
       <c r="G308" s="1">
-        <v>46260</v>
+        <v>46261</v>
       </c>
     </row>
     <row r="309" spans="1:7" x14ac:dyDescent="0.2">
@@ -10232,16 +10142,16 @@
         <v>0</v>
       </c>
       <c r="B309" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="C309" t="s">
         <v>80</v>
       </c>
       <c r="D309" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="E309" t="s">
-        <v>628</v>
+        <v>624</v>
       </c>
       <c r="F309" s="1">
         <v>46260</v>
@@ -10255,16 +10165,16 @@
         <v>0</v>
       </c>
       <c r="B310" t="s">
-        <v>629</v>
+        <v>625</v>
       </c>
       <c r="C310" t="s">
         <v>80</v>
       </c>
       <c r="D310" t="s">
-        <v>630</v>
+        <v>626</v>
       </c>
       <c r="E310" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
       <c r="F310" s="1">
         <v>46260</v>
@@ -10278,16 +10188,16 @@
         <v>0</v>
       </c>
       <c r="B311" t="s">
-        <v>632</v>
+        <v>628</v>
       </c>
       <c r="C311" t="s">
         <v>80</v>
       </c>
       <c r="D311" t="s">
-        <v>16</v>
+        <v>629</v>
       </c>
       <c r="E311" t="s">
-        <v>17</v>
+        <v>630</v>
       </c>
       <c r="F311" s="1">
         <v>46260</v>
@@ -10301,16 +10211,16 @@
         <v>0</v>
       </c>
       <c r="B312" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="C312" t="s">
         <v>80</v>
       </c>
       <c r="D312" t="s">
-        <v>634</v>
+        <v>564</v>
       </c>
       <c r="E312" t="s">
-        <v>635</v>
+        <v>565</v>
       </c>
       <c r="F312" s="1">
         <v>46260</v>
@@ -10324,16 +10234,16 @@
         <v>0</v>
       </c>
       <c r="B313" t="s">
-        <v>636</v>
+        <v>632</v>
       </c>
       <c r="C313" t="s">
         <v>80</v>
       </c>
       <c r="D313" t="s">
+        <v>633</v>
+      </c>
+      <c r="E313" t="s">
         <v>634</v>
-      </c>
-      <c r="E313" t="s">
-        <v>635</v>
       </c>
       <c r="F313" s="1">
         <v>46260</v>
@@ -10347,16 +10257,16 @@
         <v>0</v>
       </c>
       <c r="B314" t="s">
+        <v>635</v>
+      </c>
+      <c r="C314" t="s">
+        <v>80</v>
+      </c>
+      <c r="D314" t="s">
+        <v>636</v>
+      </c>
+      <c r="E314" t="s">
         <v>637</v>
-      </c>
-      <c r="C314" t="s">
-        <v>80</v>
-      </c>
-      <c r="D314" t="s">
-        <v>638</v>
-      </c>
-      <c r="E314" t="s">
-        <v>639</v>
       </c>
       <c r="F314" s="1">
         <v>46260</v>
@@ -10370,22 +10280,22 @@
         <v>0</v>
       </c>
       <c r="B315" t="s">
+        <v>638</v>
+      </c>
+      <c r="C315" t="s">
+        <v>80</v>
+      </c>
+      <c r="D315" t="s">
+        <v>639</v>
+      </c>
+      <c r="E315" t="s">
         <v>640</v>
-      </c>
-      <c r="C315" t="s">
-        <v>80</v>
-      </c>
-      <c r="D315" t="s">
-        <v>627</v>
-      </c>
-      <c r="E315" t="s">
-        <v>628</v>
       </c>
       <c r="F315" s="1">
         <v>46260</v>
       </c>
       <c r="G315" s="1">
-        <v>46260</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="316" spans="1:7" x14ac:dyDescent="0.2">
@@ -10399,10 +10309,10 @@
         <v>80</v>
       </c>
       <c r="D316" t="s">
-        <v>215</v>
+        <v>359</v>
       </c>
       <c r="E316" t="s">
-        <v>216</v>
+        <v>360</v>
       </c>
       <c r="F316" s="1">
         <v>46260</v>
@@ -10419,13 +10329,13 @@
         <v>642</v>
       </c>
       <c r="C317" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D317" t="s">
-        <v>155</v>
+        <v>371</v>
       </c>
       <c r="E317" t="s">
-        <v>156</v>
+        <v>372</v>
       </c>
       <c r="F317" s="1">
         <v>46260</v>
@@ -10445,10 +10355,10 @@
         <v>80</v>
       </c>
       <c r="D318" t="s">
-        <v>430</v>
+        <v>101</v>
       </c>
       <c r="E318" t="s">
-        <v>431</v>
+        <v>102</v>
       </c>
       <c r="F318" s="1">
         <v>46260</v>
@@ -10468,10 +10378,10 @@
         <v>80</v>
       </c>
       <c r="D319" t="s">
-        <v>456</v>
+        <v>98</v>
       </c>
       <c r="E319" t="s">
-        <v>457</v>
+        <v>99</v>
       </c>
       <c r="F319" s="1">
         <v>46260</v>
@@ -10491,10 +10401,10 @@
         <v>80</v>
       </c>
       <c r="D320" t="s">
-        <v>508</v>
+        <v>161</v>
       </c>
       <c r="E320" t="s">
-        <v>509</v>
+        <v>162</v>
       </c>
       <c r="F320" s="1">
         <v>46260</v>
@@ -10537,10 +10447,10 @@
         <v>80</v>
       </c>
       <c r="D322" t="s">
-        <v>16</v>
+        <v>650</v>
       </c>
       <c r="E322" t="s">
-        <v>17</v>
+        <v>651</v>
       </c>
       <c r="F322" s="1">
         <v>46260</v>
@@ -10554,16 +10464,16 @@
         <v>0</v>
       </c>
       <c r="B323" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="C323" t="s">
         <v>80</v>
       </c>
       <c r="D323" t="s">
-        <v>16</v>
+        <v>653</v>
       </c>
       <c r="E323" t="s">
-        <v>17</v>
+        <v>654</v>
       </c>
       <c r="F323" s="1">
         <v>46260</v>
@@ -10577,22 +10487,22 @@
         <v>0</v>
       </c>
       <c r="B324" t="s">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="C324" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D324" t="s">
-        <v>132</v>
+        <v>656</v>
       </c>
       <c r="E324" t="s">
-        <v>133</v>
+        <v>657</v>
       </c>
       <c r="F324" s="1">
         <v>46260</v>
       </c>
       <c r="G324" s="1">
-        <v>46261</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="325" spans="1:7" x14ac:dyDescent="0.2">
@@ -10600,16 +10510,16 @@
         <v>0</v>
       </c>
       <c r="B325" t="s">
-        <v>652</v>
+        <v>658</v>
       </c>
       <c r="C325" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D325" t="s">
-        <v>19</v>
+        <v>659</v>
       </c>
       <c r="E325" t="s">
-        <v>20</v>
+        <v>660</v>
       </c>
       <c r="F325" s="1">
         <v>46260</v>
@@ -10623,16 +10533,16 @@
         <v>0</v>
       </c>
       <c r="B326" t="s">
-        <v>653</v>
+        <v>661</v>
       </c>
       <c r="C326" t="s">
         <v>80</v>
       </c>
       <c r="D326" t="s">
-        <v>654</v>
+        <v>659</v>
       </c>
       <c r="E326" t="s">
-        <v>655</v>
+        <v>660</v>
       </c>
       <c r="F326" s="1">
         <v>46260</v>
@@ -10646,16 +10556,16 @@
         <v>0</v>
       </c>
       <c r="B327" t="s">
-        <v>656</v>
+        <v>662</v>
       </c>
       <c r="C327" t="s">
         <v>80</v>
       </c>
       <c r="D327" t="s">
-        <v>657</v>
+        <v>626</v>
       </c>
       <c r="E327" t="s">
-        <v>658</v>
+        <v>627</v>
       </c>
       <c r="F327" s="1">
         <v>46260</v>
@@ -10669,16 +10579,16 @@
         <v>0</v>
       </c>
       <c r="B328" t="s">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="C328" t="s">
         <v>80</v>
       </c>
       <c r="D328" t="s">
-        <v>660</v>
+        <v>371</v>
       </c>
       <c r="E328" t="s">
-        <v>661</v>
+        <v>372</v>
       </c>
       <c r="F328" s="1">
         <v>46260</v>
@@ -10692,22 +10602,22 @@
         <v>0</v>
       </c>
       <c r="B329" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="C329" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D329" t="s">
-        <v>588</v>
+        <v>665</v>
       </c>
       <c r="E329" t="s">
-        <v>589</v>
+        <v>666</v>
       </c>
       <c r="F329" s="1">
         <v>46260</v>
       </c>
       <c r="G329" s="1">
-        <v>46260</v>
+        <v>46261</v>
       </c>
     </row>
     <row r="330" spans="1:7" x14ac:dyDescent="0.2">
@@ -10715,16 +10625,16 @@
         <v>0</v>
       </c>
       <c r="B330" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="C330" t="s">
         <v>80</v>
       </c>
       <c r="D330" t="s">
-        <v>664</v>
+        <v>16</v>
       </c>
       <c r="E330" t="s">
-        <v>665</v>
+        <v>17</v>
       </c>
       <c r="F330" s="1">
         <v>46260</v>
@@ -10738,22 +10648,22 @@
         <v>0</v>
       </c>
       <c r="B331" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="C331" t="s">
         <v>80</v>
       </c>
       <c r="D331" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="E331" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="F331" s="1">
         <v>46260</v>
       </c>
       <c r="G331" s="1">
-        <v>46260</v>
+        <v>46261</v>
       </c>
     </row>
     <row r="332" spans="1:7" x14ac:dyDescent="0.2">
@@ -10761,22 +10671,22 @@
         <v>0</v>
       </c>
       <c r="B332" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="C332" t="s">
         <v>80</v>
       </c>
       <c r="D332" t="s">
-        <v>359</v>
+        <v>3</v>
       </c>
       <c r="E332" t="s">
-        <v>360</v>
+        <v>4</v>
       </c>
       <c r="F332" s="1">
         <v>46260</v>
       </c>
       <c r="G332" s="1">
-        <v>46260</v>
+        <v>46261</v>
       </c>
     </row>
     <row r="333" spans="1:7" x14ac:dyDescent="0.2">
@@ -10784,22 +10694,22 @@
         <v>0</v>
       </c>
       <c r="B333" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="C333" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D333" t="s">
-        <v>671</v>
+        <v>16</v>
       </c>
       <c r="E333" t="s">
-        <v>672</v>
+        <v>17</v>
       </c>
       <c r="F333" s="1">
         <v>46260</v>
       </c>
       <c r="G333" s="1">
-        <v>46260</v>
+        <v>46261</v>
       </c>
     </row>
     <row r="334" spans="1:7" x14ac:dyDescent="0.2">
@@ -10813,16 +10723,16 @@
         <v>80</v>
       </c>
       <c r="D334" t="s">
-        <v>371</v>
+        <v>393</v>
       </c>
       <c r="E334" t="s">
-        <v>372</v>
+        <v>394</v>
       </c>
       <c r="F334" s="1">
         <v>46260</v>
       </c>
       <c r="G334" s="1">
-        <v>46260</v>
+        <v>46261</v>
       </c>
     </row>
     <row r="335" spans="1:7" x14ac:dyDescent="0.2">
@@ -10836,16 +10746,16 @@
         <v>80</v>
       </c>
       <c r="D335" t="s">
-        <v>101</v>
+        <v>19</v>
       </c>
       <c r="E335" t="s">
-        <v>102</v>
+        <v>20</v>
       </c>
       <c r="F335" s="1">
         <v>46260</v>
       </c>
       <c r="G335" s="1">
-        <v>46260</v>
+        <v>46261</v>
       </c>
     </row>
     <row r="336" spans="1:7" x14ac:dyDescent="0.2">
@@ -10859,16 +10769,16 @@
         <v>80</v>
       </c>
       <c r="D336" t="s">
-        <v>98</v>
+        <v>317</v>
       </c>
       <c r="E336" t="s">
-        <v>99</v>
+        <v>318</v>
       </c>
       <c r="F336" s="1">
         <v>46260</v>
       </c>
       <c r="G336" s="1">
-        <v>46260</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="337" spans="1:7" x14ac:dyDescent="0.2">
@@ -10882,16 +10792,16 @@
         <v>80</v>
       </c>
       <c r="D337" t="s">
-        <v>161</v>
+        <v>37</v>
       </c>
       <c r="E337" t="s">
-        <v>162</v>
+        <v>38</v>
       </c>
       <c r="F337" s="1">
         <v>46260</v>
       </c>
       <c r="G337" s="1">
-        <v>46260</v>
+        <v>46261</v>
       </c>
     </row>
     <row r="338" spans="1:7" x14ac:dyDescent="0.2">
@@ -10905,16 +10815,16 @@
         <v>80</v>
       </c>
       <c r="D338" t="s">
-        <v>678</v>
+        <v>37</v>
       </c>
       <c r="E338" t="s">
-        <v>679</v>
+        <v>38</v>
       </c>
       <c r="F338" s="1">
         <v>46260</v>
       </c>
       <c r="G338" s="1">
-        <v>46260</v>
+        <v>46261</v>
       </c>
     </row>
     <row r="339" spans="1:7" x14ac:dyDescent="0.2">
@@ -10922,22 +10832,22 @@
         <v>0</v>
       </c>
       <c r="B339" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="C339" t="s">
         <v>80</v>
       </c>
       <c r="D339" t="s">
-        <v>681</v>
+        <v>37</v>
       </c>
       <c r="E339" t="s">
-        <v>682</v>
+        <v>38</v>
       </c>
       <c r="F339" s="1">
         <v>46260</v>
       </c>
       <c r="G339" s="1">
-        <v>46260</v>
+        <v>46261</v>
       </c>
     </row>
     <row r="340" spans="1:7" x14ac:dyDescent="0.2">
@@ -10945,22 +10855,22 @@
         <v>0</v>
       </c>
       <c r="B340" t="s">
-        <v>683</v>
+        <v>679</v>
       </c>
       <c r="C340" t="s">
         <v>80</v>
       </c>
       <c r="D340" t="s">
-        <v>684</v>
+        <v>37</v>
       </c>
       <c r="E340" t="s">
-        <v>685</v>
+        <v>38</v>
       </c>
       <c r="F340" s="1">
         <v>46260</v>
       </c>
       <c r="G340" s="1">
-        <v>46260</v>
+        <v>46261</v>
       </c>
     </row>
     <row r="341" spans="1:7" x14ac:dyDescent="0.2">
@@ -10968,22 +10878,22 @@
         <v>0</v>
       </c>
       <c r="B341" t="s">
-        <v>686</v>
+        <v>680</v>
       </c>
       <c r="C341" t="s">
         <v>80</v>
       </c>
       <c r="D341" t="s">
-        <v>687</v>
+        <v>37</v>
       </c>
       <c r="E341" t="s">
-        <v>688</v>
+        <v>38</v>
       </c>
       <c r="F341" s="1">
         <v>46260</v>
       </c>
       <c r="G341" s="1">
-        <v>46260</v>
+        <v>46261</v>
       </c>
     </row>
     <row r="342" spans="1:7" x14ac:dyDescent="0.2">
@@ -10991,22 +10901,22 @@
         <v>0</v>
       </c>
       <c r="B342" t="s">
-        <v>689</v>
+        <v>681</v>
       </c>
       <c r="C342" t="s">
         <v>80</v>
       </c>
       <c r="D342" t="s">
-        <v>690</v>
+        <v>37</v>
       </c>
       <c r="E342" t="s">
-        <v>691</v>
+        <v>38</v>
       </c>
       <c r="F342" s="1">
         <v>46260</v>
       </c>
       <c r="G342" s="1">
-        <v>46260</v>
+        <v>46261</v>
       </c>
     </row>
     <row r="343" spans="1:7" x14ac:dyDescent="0.2">
@@ -11014,22 +10924,22 @@
         <v>0</v>
       </c>
       <c r="B343" t="s">
-        <v>692</v>
+        <v>682</v>
       </c>
       <c r="C343" t="s">
         <v>80</v>
       </c>
       <c r="D343" t="s">
-        <v>690</v>
+        <v>37</v>
       </c>
       <c r="E343" t="s">
-        <v>691</v>
+        <v>38</v>
       </c>
       <c r="F343" s="1">
         <v>46260</v>
       </c>
       <c r="G343" s="1">
-        <v>46260</v>
+        <v>46261</v>
       </c>
     </row>
     <row r="344" spans="1:7" x14ac:dyDescent="0.2">
@@ -11037,22 +10947,22 @@
         <v>0</v>
       </c>
       <c r="B344" t="s">
-        <v>693</v>
+        <v>683</v>
       </c>
       <c r="C344" t="s">
         <v>80</v>
       </c>
       <c r="D344" t="s">
-        <v>657</v>
+        <v>37</v>
       </c>
       <c r="E344" t="s">
-        <v>658</v>
+        <v>38</v>
       </c>
       <c r="F344" s="1">
         <v>46260</v>
       </c>
       <c r="G344" s="1">
-        <v>46260</v>
+        <v>46261</v>
       </c>
     </row>
     <row r="345" spans="1:7" x14ac:dyDescent="0.2">
@@ -11060,22 +10970,22 @@
         <v>0</v>
       </c>
       <c r="B345" t="s">
-        <v>694</v>
+        <v>684</v>
       </c>
       <c r="C345" t="s">
         <v>80</v>
       </c>
       <c r="D345" t="s">
-        <v>371</v>
+        <v>37</v>
       </c>
       <c r="E345" t="s">
-        <v>372</v>
+        <v>38</v>
       </c>
       <c r="F345" s="1">
         <v>46260</v>
       </c>
       <c r="G345" s="1">
-        <v>46260</v>
+        <v>46261</v>
       </c>
     </row>
     <row r="346" spans="1:7" x14ac:dyDescent="0.2">
@@ -11083,16 +10993,16 @@
         <v>0</v>
       </c>
       <c r="B346" t="s">
-        <v>695</v>
+        <v>685</v>
       </c>
       <c r="C346" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D346" t="s">
-        <v>696</v>
+        <v>37</v>
       </c>
       <c r="E346" t="s">
-        <v>697</v>
+        <v>38</v>
       </c>
       <c r="F346" s="1">
         <v>46260</v>
@@ -11106,22 +11016,22 @@
         <v>0</v>
       </c>
       <c r="B347" t="s">
-        <v>698</v>
+        <v>686</v>
       </c>
       <c r="C347" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D347" t="s">
-        <v>197</v>
+        <v>526</v>
       </c>
       <c r="E347" t="s">
-        <v>198</v>
+        <v>527</v>
       </c>
       <c r="F347" s="1">
         <v>46260</v>
       </c>
       <c r="G347" s="1">
-        <v>46260</v>
+        <v>46261</v>
       </c>
     </row>
     <row r="348" spans="1:7" x14ac:dyDescent="0.2">
@@ -11129,22 +11039,22 @@
         <v>0</v>
       </c>
       <c r="B348" t="s">
-        <v>699</v>
+        <v>687</v>
       </c>
       <c r="C348" t="s">
         <v>80</v>
       </c>
       <c r="D348" t="s">
-        <v>16</v>
+        <v>688</v>
       </c>
       <c r="E348" t="s">
-        <v>17</v>
+        <v>689</v>
       </c>
       <c r="F348" s="1">
         <v>46260</v>
       </c>
       <c r="G348" s="1">
-        <v>46260</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="349" spans="1:7" x14ac:dyDescent="0.2">
@@ -11152,16 +11062,16 @@
         <v>0</v>
       </c>
       <c r="B349" t="s">
-        <v>700</v>
+        <v>690</v>
       </c>
       <c r="C349" t="s">
         <v>80</v>
       </c>
       <c r="D349" t="s">
-        <v>701</v>
+        <v>691</v>
       </c>
       <c r="E349" t="s">
-        <v>702</v>
+        <v>692</v>
       </c>
       <c r="F349" s="1">
         <v>46260</v>
@@ -11175,16 +11085,16 @@
         <v>0</v>
       </c>
       <c r="B350" t="s">
-        <v>703</v>
+        <v>693</v>
       </c>
       <c r="C350" t="s">
         <v>80</v>
       </c>
       <c r="D350" t="s">
-        <v>3</v>
+        <v>694</v>
       </c>
       <c r="E350" t="s">
-        <v>4</v>
+        <v>695</v>
       </c>
       <c r="F350" s="1">
         <v>46260</v>
@@ -11198,16 +11108,16 @@
         <v>0</v>
       </c>
       <c r="B351" t="s">
-        <v>704</v>
+        <v>696</v>
       </c>
       <c r="C351" t="s">
         <v>80</v>
       </c>
       <c r="D351" t="s">
-        <v>16</v>
+        <v>697</v>
       </c>
       <c r="E351" t="s">
-        <v>17</v>
+        <v>698</v>
       </c>
       <c r="F351" s="1">
         <v>46260</v>
@@ -11221,16 +11131,16 @@
         <v>0</v>
       </c>
       <c r="B352" t="s">
-        <v>705</v>
+        <v>699</v>
       </c>
       <c r="C352" t="s">
         <v>80</v>
       </c>
       <c r="D352" t="s">
-        <v>393</v>
+        <v>25</v>
       </c>
       <c r="E352" t="s">
-        <v>394</v>
+        <v>26</v>
       </c>
       <c r="F352" s="1">
         <v>46260</v>
@@ -11244,19 +11154,19 @@
         <v>0</v>
       </c>
       <c r="B353" t="s">
-        <v>706</v>
+        <v>700</v>
       </c>
       <c r="C353" t="s">
         <v>80</v>
       </c>
       <c r="D353" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="E353" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="F353" s="1">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="G353" s="1">
         <v>46261</v>
@@ -11267,19 +11177,19 @@
         <v>0</v>
       </c>
       <c r="B354" t="s">
-        <v>707</v>
+        <v>701</v>
       </c>
       <c r="C354" t="s">
         <v>80</v>
       </c>
       <c r="D354" t="s">
-        <v>37</v>
+        <v>702</v>
       </c>
       <c r="E354" t="s">
-        <v>38</v>
+        <v>703</v>
       </c>
       <c r="F354" s="1">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="G354" s="1">
         <v>46261</v>
@@ -11290,19 +11200,19 @@
         <v>0</v>
       </c>
       <c r="B355" t="s">
-        <v>708</v>
+        <v>704</v>
       </c>
       <c r="C355" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D355" t="s">
-        <v>37</v>
+        <v>705</v>
       </c>
       <c r="E355" t="s">
-        <v>38</v>
+        <v>706</v>
       </c>
       <c r="F355" s="1">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="G355" s="1">
         <v>46261</v>
@@ -11313,19 +11223,19 @@
         <v>0</v>
       </c>
       <c r="B356" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="C356" t="s">
         <v>80</v>
       </c>
       <c r="D356" t="s">
-        <v>37</v>
+        <v>606</v>
       </c>
       <c r="E356" t="s">
-        <v>38</v>
+        <v>607</v>
       </c>
       <c r="F356" s="1">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="G356" s="1">
         <v>46261</v>
@@ -11336,19 +11246,19 @@
         <v>0</v>
       </c>
       <c r="B357" t="s">
+        <v>708</v>
+      </c>
+      <c r="C357" t="s">
+        <v>80</v>
+      </c>
+      <c r="D357" t="s">
+        <v>709</v>
+      </c>
+      <c r="E357" t="s">
         <v>710</v>
       </c>
-      <c r="C357" t="s">
-        <v>80</v>
-      </c>
-      <c r="D357" t="s">
-        <v>37</v>
-      </c>
-      <c r="E357" t="s">
-        <v>38</v>
-      </c>
       <c r="F357" s="1">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="G357" s="1">
         <v>46261</v>
@@ -11365,13 +11275,13 @@
         <v>80</v>
       </c>
       <c r="D358" t="s">
-        <v>37</v>
+        <v>470</v>
       </c>
       <c r="E358" t="s">
-        <v>38</v>
+        <v>471</v>
       </c>
       <c r="F358" s="1">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="G358" s="1">
         <v>46261</v>
@@ -11388,13 +11298,13 @@
         <v>80</v>
       </c>
       <c r="D359" t="s">
-        <v>37</v>
+        <v>93</v>
       </c>
       <c r="E359" t="s">
-        <v>38</v>
+        <v>94</v>
       </c>
       <c r="F359" s="1">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="G359" s="1">
         <v>46261</v>
@@ -11411,13 +11321,13 @@
         <v>80</v>
       </c>
       <c r="D360" t="s">
-        <v>37</v>
+        <v>93</v>
       </c>
       <c r="E360" t="s">
-        <v>38</v>
+        <v>94</v>
       </c>
       <c r="F360" s="1">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="G360" s="1">
         <v>46261</v>
@@ -11434,13 +11344,13 @@
         <v>80</v>
       </c>
       <c r="D361" t="s">
-        <v>37</v>
+        <v>715</v>
       </c>
       <c r="E361" t="s">
-        <v>38</v>
+        <v>716</v>
       </c>
       <c r="F361" s="1">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="G361" s="1">
         <v>46261</v>
@@ -11451,19 +11361,19 @@
         <v>0</v>
       </c>
       <c r="B362" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="C362" t="s">
         <v>80</v>
       </c>
       <c r="D362" t="s">
-        <v>37</v>
+        <v>402</v>
       </c>
       <c r="E362" t="s">
-        <v>38</v>
+        <v>403</v>
       </c>
       <c r="F362" s="1">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="G362" s="1">
         <v>46261</v>
@@ -11474,19 +11384,19 @@
         <v>0</v>
       </c>
       <c r="B363" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="C363" t="s">
         <v>80</v>
       </c>
       <c r="D363" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="E363" t="s">
-        <v>38</v>
+        <v>720</v>
       </c>
       <c r="F363" s="1">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="G363" s="1">
         <v>46261</v>
@@ -11497,19 +11407,19 @@
         <v>0</v>
       </c>
       <c r="B364" t="s">
-        <v>717</v>
+        <v>721</v>
       </c>
       <c r="C364" t="s">
         <v>80</v>
       </c>
       <c r="D364" t="s">
-        <v>545</v>
+        <v>449</v>
       </c>
       <c r="E364" t="s">
-        <v>546</v>
+        <v>450</v>
       </c>
       <c r="F364" s="1">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="G364" s="1">
         <v>46261</v>
@@ -11520,19 +11430,19 @@
         <v>0</v>
       </c>
       <c r="B365" t="s">
-        <v>718</v>
+        <v>722</v>
       </c>
       <c r="C365" t="s">
         <v>80</v>
       </c>
       <c r="D365" t="s">
-        <v>719</v>
+        <v>215</v>
       </c>
       <c r="E365" t="s">
-        <v>720</v>
+        <v>216</v>
       </c>
       <c r="F365" s="1">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="G365" s="1">
         <v>46261</v>
@@ -11543,19 +11453,19 @@
         <v>0</v>
       </c>
       <c r="B366" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="C366" t="s">
         <v>80</v>
       </c>
       <c r="D366" t="s">
-        <v>722</v>
+        <v>16</v>
       </c>
       <c r="E366" t="s">
-        <v>723</v>
+        <v>17</v>
       </c>
       <c r="F366" s="1">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="G366" s="1">
         <v>46261</v>
@@ -11569,16 +11479,16 @@
         <v>724</v>
       </c>
       <c r="C367" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D367" t="s">
-        <v>725</v>
+        <v>705</v>
       </c>
       <c r="E367" t="s">
-        <v>726</v>
+        <v>706</v>
       </c>
       <c r="F367" s="1">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="G367" s="1">
         <v>46261</v>
@@ -11589,19 +11499,19 @@
         <v>0</v>
       </c>
       <c r="B368" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="C368" t="s">
         <v>80</v>
       </c>
       <c r="D368" t="s">
-        <v>25</v>
+        <v>325</v>
       </c>
       <c r="E368" t="s">
-        <v>26</v>
+        <v>326</v>
       </c>
       <c r="F368" s="1">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="G368" s="1">
         <v>46261</v>
@@ -11612,16 +11522,16 @@
         <v>0</v>
       </c>
       <c r="B369" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="C369" t="s">
         <v>80</v>
       </c>
       <c r="D369" t="s">
-        <v>37</v>
+        <v>639</v>
       </c>
       <c r="E369" t="s">
-        <v>38</v>
+        <v>640</v>
       </c>
       <c r="F369" s="1">
         <v>46261</v>
@@ -11635,22 +11545,22 @@
         <v>0</v>
       </c>
       <c r="B370" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="C370" t="s">
         <v>80</v>
       </c>
       <c r="D370" t="s">
-        <v>730</v>
+        <v>411</v>
       </c>
       <c r="E370" t="s">
-        <v>731</v>
+        <v>412</v>
       </c>
       <c r="F370" s="1">
         <v>46261</v>
       </c>
       <c r="G370" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="371" spans="1:7" x14ac:dyDescent="0.2">
@@ -11658,16 +11568,16 @@
         <v>0</v>
       </c>
       <c r="B371" t="s">
-        <v>732</v>
+        <v>728</v>
       </c>
       <c r="C371" t="s">
         <v>80</v>
       </c>
       <c r="D371" t="s">
-        <v>733</v>
+        <v>456</v>
       </c>
       <c r="E371" t="s">
-        <v>734</v>
+        <v>457</v>
       </c>
       <c r="F371" s="1">
         <v>46261</v>
@@ -11681,16 +11591,16 @@
         <v>0</v>
       </c>
       <c r="B372" t="s">
-        <v>735</v>
+        <v>729</v>
       </c>
       <c r="C372" t="s">
         <v>80</v>
       </c>
       <c r="D372" t="s">
-        <v>736</v>
+        <v>101</v>
       </c>
       <c r="E372" t="s">
-        <v>737</v>
+        <v>102</v>
       </c>
       <c r="F372" s="1">
         <v>46261</v>
@@ -11704,16 +11614,16 @@
         <v>0</v>
       </c>
       <c r="B373" t="s">
-        <v>738</v>
+        <v>730</v>
       </c>
       <c r="C373" t="s">
         <v>80</v>
       </c>
       <c r="D373" t="s">
-        <v>634</v>
+        <v>101</v>
       </c>
       <c r="E373" t="s">
-        <v>635</v>
+        <v>102</v>
       </c>
       <c r="F373" s="1">
         <v>46261</v>
@@ -11727,16 +11637,16 @@
         <v>0</v>
       </c>
       <c r="B374" t="s">
-        <v>739</v>
+        <v>731</v>
       </c>
       <c r="C374" t="s">
         <v>80</v>
       </c>
       <c r="D374" t="s">
-        <v>740</v>
+        <v>732</v>
       </c>
       <c r="E374" t="s">
-        <v>741</v>
+        <v>733</v>
       </c>
       <c r="F374" s="1">
         <v>46261</v>
@@ -11750,16 +11660,16 @@
         <v>0</v>
       </c>
       <c r="B375" t="s">
-        <v>742</v>
+        <v>734</v>
       </c>
       <c r="C375" t="s">
         <v>80</v>
       </c>
       <c r="D375" t="s">
-        <v>743</v>
+        <v>74</v>
       </c>
       <c r="E375" t="s">
-        <v>744</v>
+        <v>75</v>
       </c>
       <c r="F375" s="1">
         <v>46261</v>
@@ -11773,16 +11683,16 @@
         <v>0</v>
       </c>
       <c r="B376" t="s">
-        <v>745</v>
+        <v>735</v>
       </c>
       <c r="C376" t="s">
         <v>80</v>
       </c>
       <c r="D376" t="s">
-        <v>487</v>
+        <v>736</v>
       </c>
       <c r="E376" t="s">
-        <v>488</v>
+        <v>737</v>
       </c>
       <c r="F376" s="1">
         <v>46261</v>
@@ -11796,16 +11706,16 @@
         <v>0</v>
       </c>
       <c r="B377" t="s">
-        <v>746</v>
+        <v>738</v>
       </c>
       <c r="C377" t="s">
         <v>80</v>
       </c>
       <c r="D377" t="s">
-        <v>747</v>
+        <v>101</v>
       </c>
       <c r="E377" t="s">
-        <v>748</v>
+        <v>102</v>
       </c>
       <c r="F377" s="1">
         <v>46261</v>
@@ -11819,16 +11729,16 @@
         <v>0</v>
       </c>
       <c r="B378" t="s">
-        <v>749</v>
+        <v>739</v>
       </c>
       <c r="C378" t="s">
         <v>80</v>
       </c>
       <c r="D378" t="s">
-        <v>93</v>
+        <v>740</v>
       </c>
       <c r="E378" t="s">
-        <v>94</v>
+        <v>741</v>
       </c>
       <c r="F378" s="1">
         <v>46261</v>
@@ -11842,16 +11752,16 @@
         <v>0</v>
       </c>
       <c r="B379" t="s">
-        <v>750</v>
+        <v>742</v>
       </c>
       <c r="C379" t="s">
         <v>80</v>
       </c>
       <c r="D379" t="s">
-        <v>93</v>
+        <v>158</v>
       </c>
       <c r="E379" t="s">
-        <v>94</v>
+        <v>159</v>
       </c>
       <c r="F379" s="1">
         <v>46261</v>
@@ -11865,16 +11775,16 @@
         <v>0</v>
       </c>
       <c r="B380" t="s">
-        <v>751</v>
+        <v>743</v>
       </c>
       <c r="C380" t="s">
         <v>80</v>
       </c>
       <c r="D380" t="s">
-        <v>747</v>
+        <v>744</v>
       </c>
       <c r="E380" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
       <c r="F380" s="1">
         <v>46261</v>
@@ -11888,16 +11798,16 @@
         <v>0</v>
       </c>
       <c r="B381" t="s">
-        <v>752</v>
+        <v>746</v>
       </c>
       <c r="C381" t="s">
         <v>80</v>
       </c>
       <c r="D381" t="s">
-        <v>402</v>
+        <v>744</v>
       </c>
       <c r="E381" t="s">
-        <v>403</v>
+        <v>745</v>
       </c>
       <c r="F381" s="1">
         <v>46261</v>
@@ -11911,22 +11821,22 @@
         <v>0</v>
       </c>
       <c r="B382" t="s">
-        <v>753</v>
+        <v>747</v>
       </c>
       <c r="C382" t="s">
         <v>80</v>
       </c>
       <c r="D382" t="s">
-        <v>754</v>
+        <v>200</v>
       </c>
       <c r="E382" t="s">
-        <v>755</v>
+        <v>201</v>
       </c>
       <c r="F382" s="1">
         <v>46261</v>
       </c>
       <c r="G382" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="383" spans="1:7" x14ac:dyDescent="0.2">
@@ -11934,16 +11844,16 @@
         <v>0</v>
       </c>
       <c r="B383" t="s">
-        <v>756</v>
+        <v>748</v>
       </c>
       <c r="C383" t="s">
         <v>80</v>
       </c>
       <c r="D383" t="s">
-        <v>460</v>
+        <v>200</v>
       </c>
       <c r="E383" t="s">
-        <v>461</v>
+        <v>201</v>
       </c>
       <c r="F383" s="1">
         <v>46261</v>
@@ -11957,16 +11867,16 @@
         <v>0</v>
       </c>
       <c r="B384" t="s">
-        <v>757</v>
+        <v>749</v>
       </c>
       <c r="C384" t="s">
         <v>80</v>
       </c>
       <c r="D384" t="s">
-        <v>215</v>
+        <v>81</v>
       </c>
       <c r="E384" t="s">
-        <v>216</v>
+        <v>82</v>
       </c>
       <c r="F384" s="1">
         <v>46261</v>
@@ -11980,16 +11890,16 @@
         <v>0</v>
       </c>
       <c r="B385" t="s">
-        <v>758</v>
+        <v>750</v>
       </c>
       <c r="C385" t="s">
         <v>80</v>
       </c>
       <c r="D385" t="s">
-        <v>16</v>
+        <v>751</v>
       </c>
       <c r="E385" t="s">
-        <v>17</v>
+        <v>752</v>
       </c>
       <c r="F385" s="1">
         <v>46261</v>
@@ -12003,16 +11913,16 @@
         <v>0</v>
       </c>
       <c r="B386" t="s">
-        <v>759</v>
+        <v>753</v>
       </c>
       <c r="C386" t="s">
         <v>80</v>
       </c>
       <c r="D386" t="s">
-        <v>733</v>
+        <v>470</v>
       </c>
       <c r="E386" t="s">
-        <v>734</v>
+        <v>471</v>
       </c>
       <c r="F386" s="1">
         <v>46261</v>
@@ -12026,16 +11936,16 @@
         <v>0</v>
       </c>
       <c r="B387" t="s">
-        <v>760</v>
+        <v>754</v>
       </c>
       <c r="C387" t="s">
         <v>80</v>
       </c>
       <c r="D387" t="s">
-        <v>325</v>
+        <v>470</v>
       </c>
       <c r="E387" t="s">
-        <v>326</v>
+        <v>471</v>
       </c>
       <c r="F387" s="1">
         <v>46261</v>
@@ -12049,16 +11959,16 @@
         <v>0</v>
       </c>
       <c r="B388" t="s">
-        <v>761</v>
+        <v>755</v>
       </c>
       <c r="C388" t="s">
         <v>80</v>
       </c>
       <c r="D388" t="s">
-        <v>762</v>
+        <v>393</v>
       </c>
       <c r="E388" t="s">
-        <v>763</v>
+        <v>394</v>
       </c>
       <c r="F388" s="1">
         <v>46261</v>
@@ -12072,22 +11982,22 @@
         <v>0</v>
       </c>
       <c r="B389" t="s">
-        <v>764</v>
+        <v>756</v>
       </c>
       <c r="C389" t="s">
         <v>80</v>
       </c>
       <c r="D389" t="s">
-        <v>467</v>
+        <v>250</v>
       </c>
       <c r="E389" t="s">
-        <v>468</v>
+        <v>251</v>
       </c>
       <c r="F389" s="1">
         <v>46261</v>
       </c>
       <c r="G389" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="390" spans="1:7" x14ac:dyDescent="0.2">
@@ -12095,16 +12005,16 @@
         <v>0</v>
       </c>
       <c r="B390" t="s">
-        <v>765</v>
+        <v>757</v>
       </c>
       <c r="C390" t="s">
         <v>80</v>
       </c>
       <c r="D390" t="s">
-        <v>101</v>
+        <v>470</v>
       </c>
       <c r="E390" t="s">
-        <v>102</v>
+        <v>471</v>
       </c>
       <c r="F390" s="1">
         <v>46261</v>
@@ -12118,16 +12028,16 @@
         <v>0</v>
       </c>
       <c r="B391" t="s">
-        <v>766</v>
+        <v>758</v>
       </c>
       <c r="C391" t="s">
         <v>80</v>
       </c>
       <c r="D391" t="s">
-        <v>101</v>
+        <v>759</v>
       </c>
       <c r="E391" t="s">
-        <v>102</v>
+        <v>760</v>
       </c>
       <c r="F391" s="1">
         <v>46261</v>
@@ -12141,22 +12051,22 @@
         <v>0</v>
       </c>
       <c r="B392" t="s">
-        <v>767</v>
+        <v>761</v>
       </c>
       <c r="C392" t="s">
         <v>80</v>
       </c>
       <c r="D392" t="s">
-        <v>768</v>
+        <v>762</v>
       </c>
       <c r="E392" t="s">
-        <v>769</v>
+        <v>763</v>
       </c>
       <c r="F392" s="1">
         <v>46261</v>
       </c>
       <c r="G392" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="393" spans="1:7" x14ac:dyDescent="0.2">
@@ -12164,401 +12074,401 @@
         <v>0</v>
       </c>
       <c r="B393" t="s">
-        <v>770</v>
+        <v>764</v>
       </c>
       <c r="C393" t="s">
         <v>80</v>
       </c>
       <c r="D393" t="s">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="E393" t="s">
-        <v>75</v>
+        <v>99</v>
       </c>
       <c r="F393" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="G393" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="394" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A394" t="s">
-        <v>0</v>
+        <v>765</v>
       </c>
       <c r="B394" t="s">
-        <v>771</v>
+        <v>766</v>
       </c>
       <c r="C394" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D394" t="s">
-        <v>772</v>
+        <v>314</v>
       </c>
       <c r="E394" t="s">
-        <v>773</v>
+        <v>315</v>
       </c>
       <c r="F394" s="1">
-        <v>46261</v>
+        <v>46148</v>
       </c>
       <c r="G394" s="1">
-        <v>46261</v>
+        <v>46149</v>
       </c>
     </row>
     <row r="395" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A395" t="s">
-        <v>0</v>
+        <v>765</v>
       </c>
       <c r="B395" t="s">
-        <v>774</v>
+        <v>767</v>
       </c>
       <c r="C395" t="s">
         <v>80</v>
       </c>
       <c r="D395" t="s">
-        <v>101</v>
+        <v>768</v>
       </c>
       <c r="E395" t="s">
-        <v>102</v>
+        <v>769</v>
       </c>
       <c r="F395" s="1">
-        <v>46261</v>
+        <v>46260</v>
       </c>
       <c r="G395" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="396" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A396" t="s">
-        <v>0</v>
+        <v>770</v>
       </c>
       <c r="B396" t="s">
-        <v>775</v>
+        <v>771</v>
       </c>
       <c r="C396" t="s">
-        <v>80</v>
+        <v>6</v>
       </c>
       <c r="D396" t="s">
-        <v>776</v>
+        <v>41</v>
       </c>
       <c r="E396" t="s">
-        <v>777</v>
+        <v>42</v>
       </c>
       <c r="F396" s="1">
-        <v>46261</v>
+        <v>46133</v>
       </c>
       <c r="G396" s="1">
-        <v>46261</v>
+        <v>46134</v>
       </c>
     </row>
     <row r="397" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A397" t="s">
-        <v>0</v>
+        <v>770</v>
       </c>
       <c r="B397" t="s">
-        <v>778</v>
+        <v>772</v>
       </c>
       <c r="C397" t="s">
-        <v>80</v>
+        <v>6</v>
       </c>
       <c r="D397" t="s">
-        <v>158</v>
+        <v>41</v>
       </c>
       <c r="E397" t="s">
-        <v>159</v>
+        <v>42</v>
       </c>
       <c r="F397" s="1">
-        <v>46261</v>
+        <v>46134</v>
       </c>
       <c r="G397" s="1">
-        <v>46261</v>
+        <v>46134</v>
       </c>
     </row>
     <row r="398" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A398" t="s">
-        <v>0</v>
+        <v>770</v>
       </c>
       <c r="B398" t="s">
-        <v>779</v>
+        <v>773</v>
       </c>
       <c r="C398" t="s">
-        <v>80</v>
+        <v>6</v>
       </c>
       <c r="D398" t="s">
-        <v>780</v>
+        <v>19</v>
       </c>
       <c r="E398" t="s">
-        <v>781</v>
+        <v>20</v>
       </c>
       <c r="F398" s="1">
-        <v>46261</v>
+        <v>46156</v>
       </c>
       <c r="G398" s="1">
-        <v>46261</v>
+        <v>46156</v>
       </c>
     </row>
     <row r="399" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A399" t="s">
-        <v>0</v>
+        <v>770</v>
       </c>
       <c r="B399" t="s">
-        <v>782</v>
+        <v>774</v>
       </c>
       <c r="C399" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D399" t="s">
-        <v>780</v>
+        <v>775</v>
       </c>
       <c r="E399" t="s">
-        <v>781</v>
+        <v>776</v>
       </c>
       <c r="F399" s="1">
-        <v>46261</v>
+        <v>46195</v>
       </c>
       <c r="G399" s="1">
-        <v>46261</v>
+        <v>46195</v>
       </c>
     </row>
     <row r="400" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A400" t="s">
-        <v>0</v>
+        <v>770</v>
       </c>
       <c r="B400" t="s">
-        <v>783</v>
+        <v>777</v>
       </c>
       <c r="C400" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D400" t="s">
-        <v>200</v>
+        <v>573</v>
       </c>
       <c r="E400" t="s">
-        <v>201</v>
+        <v>574</v>
       </c>
       <c r="F400" s="1">
-        <v>46261</v>
+        <v>46206</v>
       </c>
       <c r="G400" s="1">
-        <v>46261</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="401" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A401" t="s">
-        <v>0</v>
+        <v>770</v>
       </c>
       <c r="B401" t="s">
-        <v>784</v>
+        <v>778</v>
       </c>
       <c r="C401" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="D401" t="s">
-        <v>81</v>
+        <v>779</v>
       </c>
       <c r="E401" t="s">
-        <v>82</v>
+        <v>780</v>
       </c>
       <c r="F401" s="1">
-        <v>46261</v>
+        <v>46209</v>
       </c>
       <c r="G401" s="1">
-        <v>46261</v>
+        <v>46218</v>
       </c>
     </row>
     <row r="402" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A402" t="s">
-        <v>0</v>
+        <v>770</v>
       </c>
       <c r="B402" t="s">
-        <v>785</v>
+        <v>781</v>
       </c>
       <c r="C402" t="s">
-        <v>80</v>
+        <v>6</v>
       </c>
       <c r="D402" t="s">
-        <v>786</v>
+        <v>782</v>
       </c>
       <c r="E402" t="s">
-        <v>787</v>
+        <v>783</v>
       </c>
       <c r="F402" s="1">
-        <v>46261</v>
+        <v>46213</v>
       </c>
       <c r="G402" s="1">
-        <v>46261</v>
+        <v>46213</v>
       </c>
     </row>
     <row r="403" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A403" t="s">
-        <v>0</v>
+        <v>770</v>
       </c>
       <c r="B403" t="s">
-        <v>788</v>
+        <v>784</v>
       </c>
       <c r="C403" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="D403" t="s">
-        <v>487</v>
+        <v>452</v>
       </c>
       <c r="E403" t="s">
-        <v>488</v>
+        <v>453</v>
       </c>
       <c r="F403" s="1">
-        <v>46261</v>
+        <v>46213</v>
       </c>
       <c r="G403" s="1">
-        <v>46261</v>
+        <v>46216</v>
       </c>
     </row>
     <row r="404" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A404" t="s">
-        <v>0</v>
+        <v>770</v>
       </c>
       <c r="B404" t="s">
-        <v>789</v>
+        <v>785</v>
       </c>
       <c r="C404" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D404" t="s">
-        <v>487</v>
+        <v>127</v>
       </c>
       <c r="E404" t="s">
-        <v>488</v>
+        <v>128</v>
       </c>
       <c r="F404" s="1">
-        <v>46261</v>
+        <v>46220</v>
       </c>
       <c r="G404" s="1">
-        <v>46261</v>
+        <v>46231</v>
       </c>
     </row>
     <row r="405" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A405" t="s">
-        <v>0</v>
+        <v>770</v>
       </c>
       <c r="B405" t="s">
-        <v>790</v>
+        <v>786</v>
       </c>
       <c r="C405" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D405" t="s">
-        <v>393</v>
+        <v>775</v>
       </c>
       <c r="E405" t="s">
-        <v>394</v>
+        <v>776</v>
       </c>
       <c r="F405" s="1">
-        <v>46261</v>
+        <v>46223</v>
       </c>
       <c r="G405" s="1">
-        <v>46261</v>
+        <v>46223</v>
       </c>
     </row>
     <row r="406" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A406" t="s">
-        <v>0</v>
+        <v>770</v>
       </c>
       <c r="B406" t="s">
-        <v>791</v>
+        <v>787</v>
       </c>
       <c r="C406" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="D406" t="s">
-        <v>487</v>
+        <v>452</v>
       </c>
       <c r="E406" t="s">
-        <v>488</v>
+        <v>453</v>
       </c>
       <c r="F406" s="1">
-        <v>46261</v>
+        <v>46224</v>
       </c>
       <c r="G406" s="1">
-        <v>46261</v>
+        <v>46224</v>
       </c>
     </row>
     <row r="407" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A407" t="s">
-        <v>0</v>
+        <v>770</v>
       </c>
       <c r="B407" t="s">
-        <v>792</v>
+        <v>788</v>
       </c>
       <c r="C407" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D407" t="s">
-        <v>793</v>
+        <v>127</v>
       </c>
       <c r="E407" t="s">
-        <v>794</v>
+        <v>128</v>
       </c>
       <c r="F407" s="1">
-        <v>46261</v>
+        <v>46232</v>
       </c>
       <c r="G407" s="1">
-        <v>46261</v>
+        <v>46233</v>
       </c>
     </row>
     <row r="408" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A408" t="s">
-        <v>795</v>
+        <v>770</v>
       </c>
       <c r="B408" t="s">
-        <v>796</v>
+        <v>789</v>
       </c>
       <c r="C408" t="s">
         <v>2</v>
       </c>
       <c r="D408" t="s">
-        <v>314</v>
+        <v>127</v>
       </c>
       <c r="E408" t="s">
-        <v>315</v>
+        <v>128</v>
       </c>
       <c r="F408" s="1">
-        <v>46148</v>
+        <v>46232</v>
       </c>
       <c r="G408" s="1">
-        <v>46149</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="409" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A409" t="s">
-        <v>797</v>
+        <v>770</v>
       </c>
       <c r="B409" t="s">
-        <v>798</v>
+        <v>790</v>
       </c>
       <c r="C409" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D409" t="s">
-        <v>41</v>
+        <v>452</v>
       </c>
       <c r="E409" t="s">
-        <v>42</v>
+        <v>453</v>
       </c>
       <c r="F409" s="1">
-        <v>46133</v>
+        <v>46238</v>
       </c>
       <c r="G409" s="1">
-        <v>46134</v>
+        <v>46239</v>
       </c>
     </row>
     <row r="410" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A410" t="s">
-        <v>797</v>
+        <v>770</v>
       </c>
       <c r="B410" t="s">
-        <v>799</v>
+        <v>791</v>
       </c>
       <c r="C410" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D410" t="s">
         <v>41</v>
@@ -12567,156 +12477,156 @@
         <v>42</v>
       </c>
       <c r="F410" s="1">
-        <v>46134</v>
+        <v>46247</v>
       </c>
       <c r="G410" s="1">
-        <v>46134</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="411" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A411" t="s">
-        <v>797</v>
+        <v>770</v>
       </c>
       <c r="B411" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="C411" t="s">
         <v>6</v>
       </c>
       <c r="D411" t="s">
-        <v>19</v>
+        <v>793</v>
       </c>
       <c r="E411" t="s">
-        <v>20</v>
+        <v>794</v>
       </c>
       <c r="F411" s="1">
-        <v>46156</v>
+        <v>46253</v>
       </c>
       <c r="G411" s="1">
-        <v>46156</v>
+        <v>46253</v>
       </c>
     </row>
     <row r="412" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A412" t="s">
-        <v>797</v>
+        <v>770</v>
       </c>
       <c r="B412" t="s">
-        <v>801</v>
+        <v>795</v>
       </c>
       <c r="C412" t="s">
         <v>2</v>
       </c>
       <c r="D412" t="s">
-        <v>802</v>
+        <v>452</v>
       </c>
       <c r="E412" t="s">
-        <v>803</v>
+        <v>453</v>
       </c>
       <c r="F412" s="1">
-        <v>46195</v>
+        <v>46253</v>
       </c>
       <c r="G412" s="1">
-        <v>46195</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="413" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A413" t="s">
-        <v>797</v>
+        <v>770</v>
       </c>
       <c r="B413" t="s">
-        <v>804</v>
+        <v>796</v>
       </c>
       <c r="C413" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D413" t="s">
-        <v>600</v>
+        <v>402</v>
       </c>
       <c r="E413" t="s">
-        <v>601</v>
+        <v>403</v>
       </c>
       <c r="F413" s="1">
-        <v>46206</v>
+        <v>46255</v>
       </c>
       <c r="G413" s="1">
-        <v>46252</v>
+        <v>46258</v>
       </c>
     </row>
     <row r="414" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A414" t="s">
+        <v>770</v>
+      </c>
+      <c r="B414" t="s">
         <v>797</v>
       </c>
-      <c r="B414" t="s">
-        <v>805</v>
-      </c>
       <c r="C414" t="s">
-        <v>96</v>
+        <v>2</v>
       </c>
       <c r="D414" t="s">
-        <v>806</v>
+        <v>775</v>
       </c>
       <c r="E414" t="s">
-        <v>807</v>
+        <v>776</v>
       </c>
       <c r="F414" s="1">
-        <v>46209</v>
+        <v>46258</v>
       </c>
       <c r="G414" s="1">
-        <v>46218</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="415" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A415" t="s">
-        <v>797</v>
+        <v>770</v>
       </c>
       <c r="B415" t="s">
-        <v>808</v>
+        <v>798</v>
       </c>
       <c r="C415" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D415" t="s">
-        <v>809</v>
+        <v>452</v>
       </c>
       <c r="E415" t="s">
-        <v>810</v>
+        <v>453</v>
       </c>
       <c r="F415" s="1">
-        <v>46213</v>
+        <v>46258</v>
       </c>
       <c r="G415" s="1">
-        <v>46213</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="416" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A416" t="s">
-        <v>797</v>
+        <v>770</v>
       </c>
       <c r="B416" t="s">
-        <v>811</v>
+        <v>799</v>
       </c>
       <c r="C416" t="s">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="D416" t="s">
-        <v>463</v>
+        <v>470</v>
       </c>
       <c r="E416" t="s">
-        <v>464</v>
+        <v>471</v>
       </c>
       <c r="F416" s="1">
-        <v>46213</v>
+        <v>46258</v>
       </c>
       <c r="G416" s="1">
-        <v>46216</v>
+        <v>46258</v>
       </c>
     </row>
     <row r="417" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A417" t="s">
-        <v>797</v>
+        <v>770</v>
       </c>
       <c r="B417" t="s">
-        <v>812</v>
+        <v>800</v>
       </c>
       <c r="C417" t="s">
         <v>2</v>
@@ -12728,435 +12638,435 @@
         <v>128</v>
       </c>
       <c r="F417" s="1">
-        <v>46220</v>
+        <v>46259</v>
       </c>
       <c r="G417" s="1">
-        <v>46231</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="418" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A418" t="s">
-        <v>797</v>
+        <v>770</v>
       </c>
       <c r="B418" t="s">
-        <v>813</v>
+        <v>801</v>
       </c>
       <c r="C418" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D418" t="s">
-        <v>802</v>
+        <v>402</v>
       </c>
       <c r="E418" t="s">
-        <v>803</v>
+        <v>403</v>
       </c>
       <c r="F418" s="1">
-        <v>46223</v>
+        <v>46261</v>
       </c>
       <c r="G418" s="1">
-        <v>46223</v>
+        <v>46261</v>
       </c>
     </row>
     <row r="419" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A419" t="s">
-        <v>797</v>
+        <v>770</v>
       </c>
       <c r="B419" t="s">
-        <v>814</v>
+        <v>802</v>
       </c>
       <c r="C419" t="s">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="D419" t="s">
-        <v>463</v>
+        <v>803</v>
       </c>
       <c r="E419" t="s">
-        <v>464</v>
+        <v>804</v>
       </c>
       <c r="F419" s="1">
-        <v>46224</v>
+        <v>46261</v>
       </c>
       <c r="G419" s="1">
-        <v>46224</v>
+        <v>46261</v>
       </c>
     </row>
     <row r="420" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A420" t="s">
-        <v>797</v>
+        <v>770</v>
       </c>
       <c r="B420" t="s">
-        <v>815</v>
+        <v>805</v>
       </c>
       <c r="C420" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D420" t="s">
-        <v>127</v>
+        <v>806</v>
       </c>
       <c r="E420" t="s">
-        <v>128</v>
+        <v>807</v>
       </c>
       <c r="F420" s="1">
-        <v>46232</v>
+        <v>46261</v>
       </c>
       <c r="G420" s="1">
-        <v>46233</v>
+        <v>46261</v>
       </c>
     </row>
     <row r="421" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A421" t="s">
-        <v>797</v>
+        <v>808</v>
       </c>
       <c r="B421" t="s">
-        <v>816</v>
+        <v>809</v>
       </c>
       <c r="C421" t="s">
-        <v>2</v>
+        <v>96</v>
       </c>
       <c r="D421" t="s">
-        <v>127</v>
+        <v>810</v>
       </c>
       <c r="E421" t="s">
-        <v>128</v>
+        <v>811</v>
       </c>
       <c r="F421" s="1">
-        <v>46232</v>
+        <v>46063</v>
       </c>
       <c r="G421" s="1">
-        <v>46259</v>
+        <v>46064</v>
       </c>
     </row>
     <row r="422" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A422" t="s">
-        <v>797</v>
+        <v>808</v>
       </c>
       <c r="B422" t="s">
-        <v>817</v>
+        <v>812</v>
       </c>
       <c r="C422" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D422" t="s">
-        <v>463</v>
+        <v>57</v>
       </c>
       <c r="E422" t="s">
-        <v>464</v>
+        <v>58</v>
       </c>
       <c r="F422" s="1">
-        <v>46238</v>
+        <v>46113</v>
       </c>
       <c r="G422" s="1">
-        <v>46239</v>
+        <v>46125</v>
       </c>
     </row>
     <row r="423" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A423" t="s">
-        <v>797</v>
+        <v>808</v>
       </c>
       <c r="B423" t="s">
-        <v>818</v>
+        <v>813</v>
       </c>
       <c r="C423" t="s">
         <v>2</v>
       </c>
       <c r="D423" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="E423" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="F423" s="1">
-        <v>46247</v>
+        <v>46125</v>
       </c>
       <c r="G423" s="1">
-        <v>46252</v>
+        <v>46125</v>
       </c>
     </row>
     <row r="424" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A424" t="s">
-        <v>797</v>
+        <v>808</v>
       </c>
       <c r="B424" t="s">
-        <v>819</v>
+        <v>814</v>
       </c>
       <c r="C424" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D424" t="s">
-        <v>820</v>
+        <v>57</v>
       </c>
       <c r="E424" t="s">
-        <v>821</v>
+        <v>58</v>
       </c>
       <c r="F424" s="1">
-        <v>46253</v>
+        <v>46126</v>
       </c>
       <c r="G424" s="1">
-        <v>46253</v>
+        <v>46126</v>
       </c>
     </row>
     <row r="425" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A425" t="s">
-        <v>797</v>
+        <v>808</v>
       </c>
       <c r="B425" t="s">
-        <v>822</v>
+        <v>815</v>
       </c>
       <c r="C425" t="s">
         <v>2</v>
       </c>
       <c r="D425" t="s">
-        <v>463</v>
+        <v>57</v>
       </c>
       <c r="E425" t="s">
-        <v>464</v>
+        <v>58</v>
       </c>
       <c r="F425" s="1">
-        <v>46253</v>
+        <v>46126</v>
       </c>
       <c r="G425" s="1">
-        <v>46259</v>
+        <v>46126</v>
       </c>
     </row>
     <row r="426" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A426" t="s">
-        <v>797</v>
+        <v>808</v>
       </c>
       <c r="B426" t="s">
-        <v>823</v>
+        <v>816</v>
       </c>
       <c r="C426" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D426" t="s">
-        <v>402</v>
+        <v>57</v>
       </c>
       <c r="E426" t="s">
-        <v>403</v>
+        <v>58</v>
       </c>
       <c r="F426" s="1">
-        <v>46255</v>
+        <v>46128</v>
       </c>
       <c r="G426" s="1">
-        <v>46258</v>
+        <v>46128</v>
       </c>
     </row>
     <row r="427" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A427" t="s">
-        <v>797</v>
+        <v>808</v>
       </c>
       <c r="B427" t="s">
-        <v>824</v>
+        <v>817</v>
       </c>
       <c r="C427" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D427" t="s">
-        <v>802</v>
+        <v>57</v>
       </c>
       <c r="E427" t="s">
-        <v>803</v>
+        <v>58</v>
       </c>
       <c r="F427" s="1">
-        <v>46258</v>
+        <v>46132</v>
       </c>
       <c r="G427" s="1">
-        <v>46259</v>
+        <v>46132</v>
       </c>
     </row>
     <row r="428" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A428" t="s">
-        <v>797</v>
+        <v>808</v>
       </c>
       <c r="B428" t="s">
-        <v>825</v>
+        <v>818</v>
       </c>
       <c r="C428" t="s">
         <v>2</v>
       </c>
       <c r="D428" t="s">
-        <v>463</v>
+        <v>57</v>
       </c>
       <c r="E428" t="s">
-        <v>464</v>
+        <v>58</v>
       </c>
       <c r="F428" s="1">
-        <v>46258</v>
+        <v>46161</v>
       </c>
       <c r="G428" s="1">
-        <v>46259</v>
+        <v>46161</v>
       </c>
     </row>
     <row r="429" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A429" t="s">
-        <v>797</v>
+        <v>808</v>
       </c>
       <c r="B429" t="s">
-        <v>826</v>
+        <v>819</v>
       </c>
       <c r="C429" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D429" t="s">
-        <v>806</v>
+        <v>57</v>
       </c>
       <c r="E429" t="s">
-        <v>807</v>
+        <v>58</v>
       </c>
       <c r="F429" s="1">
-        <v>46258</v>
+        <v>46174</v>
       </c>
       <c r="G429" s="1">
-        <v>46258</v>
+        <v>46174</v>
       </c>
     </row>
     <row r="430" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A430" t="s">
-        <v>797</v>
+        <v>808</v>
       </c>
       <c r="B430" t="s">
-        <v>827</v>
+        <v>820</v>
       </c>
       <c r="C430" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D430" t="s">
-        <v>487</v>
+        <v>57</v>
       </c>
       <c r="E430" t="s">
-        <v>488</v>
+        <v>58</v>
       </c>
       <c r="F430" s="1">
-        <v>46258</v>
+        <v>46174</v>
       </c>
       <c r="G430" s="1">
-        <v>46258</v>
+        <v>46174</v>
       </c>
     </row>
     <row r="431" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A431" t="s">
-        <v>797</v>
+        <v>808</v>
       </c>
       <c r="B431" t="s">
-        <v>828</v>
+        <v>821</v>
       </c>
       <c r="C431" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D431" t="s">
-        <v>127</v>
+        <v>57</v>
       </c>
       <c r="E431" t="s">
-        <v>128</v>
+        <v>58</v>
       </c>
       <c r="F431" s="1">
-        <v>46259</v>
+        <v>46195</v>
       </c>
       <c r="G431" s="1">
-        <v>46259</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="432" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A432" t="s">
-        <v>797</v>
+        <v>808</v>
       </c>
       <c r="B432" t="s">
-        <v>829</v>
+        <v>822</v>
       </c>
       <c r="C432" t="s">
-        <v>80</v>
+        <v>6</v>
       </c>
       <c r="D432" t="s">
-        <v>402</v>
+        <v>57</v>
       </c>
       <c r="E432" t="s">
-        <v>403</v>
+        <v>58</v>
       </c>
       <c r="F432" s="1">
-        <v>46261</v>
+        <v>46210</v>
       </c>
       <c r="G432" s="1">
-        <v>46261</v>
+        <v>46210</v>
       </c>
     </row>
     <row r="433" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A433" t="s">
-        <v>797</v>
+        <v>808</v>
       </c>
       <c r="B433" t="s">
-        <v>830</v>
+        <v>823</v>
       </c>
       <c r="C433" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D433" t="s">
-        <v>831</v>
+        <v>57</v>
       </c>
       <c r="E433" t="s">
-        <v>832</v>
+        <v>58</v>
       </c>
       <c r="F433" s="1">
-        <v>46261</v>
+        <v>46213</v>
       </c>
       <c r="G433" s="1">
-        <v>46261</v>
+        <v>46213</v>
       </c>
     </row>
     <row r="434" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A434" t="s">
-        <v>797</v>
+        <v>808</v>
       </c>
       <c r="B434" t="s">
-        <v>833</v>
+        <v>824</v>
       </c>
       <c r="C434" t="s">
         <v>80</v>
       </c>
       <c r="D434" t="s">
-        <v>834</v>
+        <v>57</v>
       </c>
       <c r="E434" t="s">
-        <v>835</v>
+        <v>58</v>
       </c>
       <c r="F434" s="1">
-        <v>46261</v>
+        <v>46218</v>
       </c>
       <c r="G434" s="1">
-        <v>46261</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="435" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A435" t="s">
-        <v>836</v>
+        <v>808</v>
       </c>
       <c r="B435" t="s">
-        <v>837</v>
+        <v>825</v>
       </c>
       <c r="C435" t="s">
-        <v>96</v>
+        <v>6</v>
       </c>
       <c r="D435" t="s">
-        <v>838</v>
+        <v>77</v>
       </c>
       <c r="E435" t="s">
-        <v>839</v>
+        <v>78</v>
       </c>
       <c r="F435" s="1">
-        <v>46063</v>
+        <v>46226</v>
       </c>
       <c r="G435" s="1">
-        <v>46064</v>
+        <v>46226</v>
       </c>
     </row>
     <row r="436" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A436" t="s">
-        <v>836</v>
+        <v>808</v>
       </c>
       <c r="B436" t="s">
-        <v>840</v>
+        <v>826</v>
       </c>
       <c r="C436" t="s">
-        <v>6</v>
+        <v>80</v>
       </c>
       <c r="D436" t="s">
         <v>57</v>
@@ -13165,21 +13075,21 @@
         <v>58</v>
       </c>
       <c r="F436" s="1">
-        <v>46113</v>
+        <v>46227</v>
       </c>
       <c r="G436" s="1">
-        <v>46125</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="437" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A437" t="s">
-        <v>836</v>
+        <v>808</v>
       </c>
       <c r="B437" t="s">
-        <v>841</v>
+        <v>827</v>
       </c>
       <c r="C437" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D437" t="s">
         <v>57</v>
@@ -13188,21 +13098,21 @@
         <v>58</v>
       </c>
       <c r="F437" s="1">
-        <v>46125</v>
+        <v>46227</v>
       </c>
       <c r="G437" s="1">
-        <v>46125</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="438" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A438" t="s">
-        <v>836</v>
+        <v>808</v>
       </c>
       <c r="B438" t="s">
-        <v>842</v>
+        <v>828</v>
       </c>
       <c r="C438" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D438" t="s">
         <v>57</v>
@@ -13211,44 +13121,44 @@
         <v>58</v>
       </c>
       <c r="F438" s="1">
-        <v>46126</v>
+        <v>46227</v>
       </c>
       <c r="G438" s="1">
-        <v>46126</v>
+        <v>46228</v>
       </c>
     </row>
     <row r="439" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A439" t="s">
-        <v>836</v>
+        <v>808</v>
       </c>
       <c r="B439" t="s">
-        <v>843</v>
+        <v>829</v>
       </c>
       <c r="C439" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D439" t="s">
-        <v>57</v>
+        <v>77</v>
       </c>
       <c r="E439" t="s">
-        <v>58</v>
+        <v>78</v>
       </c>
       <c r="F439" s="1">
-        <v>46126</v>
+        <v>46230</v>
       </c>
       <c r="G439" s="1">
-        <v>46126</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="440" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A440" t="s">
-        <v>836</v>
+        <v>808</v>
       </c>
       <c r="B440" t="s">
-        <v>844</v>
+        <v>830</v>
       </c>
       <c r="C440" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D440" t="s">
         <v>57</v>
@@ -13257,18 +13167,18 @@
         <v>58</v>
       </c>
       <c r="F440" s="1">
-        <v>46128</v>
+        <v>46231</v>
       </c>
       <c r="G440" s="1">
-        <v>46128</v>
+        <v>46231</v>
       </c>
     </row>
     <row r="441" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A441" t="s">
-        <v>836</v>
+        <v>808</v>
       </c>
       <c r="B441" t="s">
-        <v>845</v>
+        <v>831</v>
       </c>
       <c r="C441" t="s">
         <v>6</v>
@@ -13280,18 +13190,18 @@
         <v>58</v>
       </c>
       <c r="F441" s="1">
-        <v>46132</v>
+        <v>46254</v>
       </c>
       <c r="G441" s="1">
-        <v>46132</v>
+        <v>46254</v>
       </c>
     </row>
     <row r="442" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A442" t="s">
-        <v>836</v>
+        <v>808</v>
       </c>
       <c r="B442" t="s">
-        <v>846</v>
+        <v>832</v>
       </c>
       <c r="C442" t="s">
         <v>2</v>
@@ -13303,21 +13213,21 @@
         <v>58</v>
       </c>
       <c r="F442" s="1">
-        <v>46161</v>
+        <v>46255</v>
       </c>
       <c r="G442" s="1">
-        <v>46161</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="443" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A443" t="s">
-        <v>836</v>
+        <v>808</v>
       </c>
       <c r="B443" t="s">
-        <v>847</v>
+        <v>833</v>
       </c>
       <c r="C443" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D443" t="s">
         <v>57</v>
@@ -13326,21 +13236,21 @@
         <v>58</v>
       </c>
       <c r="F443" s="1">
-        <v>46174</v>
+        <v>46260</v>
       </c>
       <c r="G443" s="1">
-        <v>46174</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="444" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A444" t="s">
-        <v>836</v>
+        <v>808</v>
       </c>
       <c r="B444" t="s">
-        <v>848</v>
+        <v>834</v>
       </c>
       <c r="C444" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D444" t="s">
         <v>57</v>
@@ -13349,18 +13259,18 @@
         <v>58</v>
       </c>
       <c r="F444" s="1">
-        <v>46174</v>
+        <v>46262</v>
       </c>
       <c r="G444" s="1">
-        <v>46174</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="445" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A445" t="s">
-        <v>836</v>
+        <v>808</v>
       </c>
       <c r="B445" t="s">
-        <v>849</v>
+        <v>835</v>
       </c>
       <c r="C445" t="s">
         <v>80</v>
@@ -13372,21 +13282,21 @@
         <v>58</v>
       </c>
       <c r="F445" s="1">
-        <v>46195</v>
+        <v>46262</v>
       </c>
       <c r="G445" s="1">
-        <v>46252</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="446" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A446" t="s">
+        <v>808</v>
+      </c>
+      <c r="B446" t="s">
         <v>836</v>
       </c>
-      <c r="B446" t="s">
-        <v>850</v>
-      </c>
       <c r="C446" t="s">
-        <v>6</v>
+        <v>80</v>
       </c>
       <c r="D446" t="s">
         <v>57</v>
@@ -13395,538 +13305,216 @@
         <v>58</v>
       </c>
       <c r="F446" s="1">
-        <v>46210</v>
+        <v>46262</v>
       </c>
       <c r="G446" s="1">
-        <v>46210</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="447" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A447" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="B447" t="s">
-        <v>851</v>
+        <v>838</v>
       </c>
       <c r="C447" t="s">
         <v>2</v>
       </c>
       <c r="D447" t="s">
-        <v>57</v>
+        <v>839</v>
       </c>
       <c r="E447" t="s">
-        <v>58</v>
+        <v>840</v>
       </c>
       <c r="F447" s="1">
-        <v>46213</v>
+        <v>46083</v>
       </c>
       <c r="G447" s="1">
-        <v>46213</v>
+        <v>46084</v>
       </c>
     </row>
     <row r="448" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A448" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="B448" t="s">
-        <v>852</v>
+        <v>841</v>
       </c>
       <c r="C448" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D448" t="s">
-        <v>57</v>
+        <v>839</v>
       </c>
       <c r="E448" t="s">
-        <v>58</v>
+        <v>840</v>
       </c>
       <c r="F448" s="1">
-        <v>46218</v>
+        <v>46132</v>
       </c>
       <c r="G448" s="1">
-        <v>46252</v>
+        <v>46133</v>
       </c>
     </row>
     <row r="449" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A449" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="B449" t="s">
-        <v>853</v>
+        <v>842</v>
       </c>
       <c r="C449" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D449" t="s">
-        <v>77</v>
+        <v>843</v>
       </c>
       <c r="E449" t="s">
-        <v>78</v>
+        <v>844</v>
       </c>
       <c r="F449" s="1">
-        <v>46226</v>
+        <v>46157</v>
       </c>
       <c r="G449" s="1">
-        <v>46226</v>
+        <v>46157</v>
       </c>
     </row>
     <row r="450" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A450" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="B450" t="s">
-        <v>854</v>
+        <v>845</v>
       </c>
       <c r="C450" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D450" t="s">
-        <v>57</v>
+        <v>846</v>
       </c>
       <c r="E450" t="s">
-        <v>58</v>
+        <v>847</v>
       </c>
       <c r="F450" s="1">
-        <v>46227</v>
+        <v>46168</v>
       </c>
       <c r="G450" s="1">
-        <v>46252</v>
+        <v>46170</v>
       </c>
     </row>
     <row r="451" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A451" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="B451" t="s">
-        <v>855</v>
+        <v>848</v>
       </c>
       <c r="C451" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D451" t="s">
-        <v>57</v>
+        <v>843</v>
       </c>
       <c r="E451" t="s">
-        <v>58</v>
+        <v>844</v>
       </c>
       <c r="F451" s="1">
-        <v>46227</v>
+        <v>46244</v>
       </c>
       <c r="G451" s="1">
-        <v>46252</v>
+        <v>46244</v>
       </c>
     </row>
     <row r="452" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A452" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="B452" t="s">
-        <v>856</v>
+        <v>849</v>
       </c>
       <c r="C452" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D452" t="s">
-        <v>57</v>
+        <v>843</v>
       </c>
       <c r="E452" t="s">
-        <v>58</v>
+        <v>844</v>
       </c>
       <c r="F452" s="1">
-        <v>46227</v>
+        <v>46247</v>
       </c>
       <c r="G452" s="1">
-        <v>46228</v>
+        <v>46247</v>
       </c>
     </row>
     <row r="453" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A453" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="B453" t="s">
-        <v>857</v>
+        <v>850</v>
       </c>
       <c r="C453" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D453" t="s">
-        <v>77</v>
+        <v>839</v>
       </c>
       <c r="E453" t="s">
-        <v>78</v>
+        <v>840</v>
       </c>
       <c r="F453" s="1">
-        <v>46230</v>
+        <v>46247</v>
       </c>
       <c r="G453" s="1">
-        <v>46252</v>
+        <v>46247</v>
       </c>
     </row>
     <row r="454" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A454" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="B454" t="s">
-        <v>858</v>
+        <v>851</v>
       </c>
       <c r="C454" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D454" t="s">
-        <v>57</v>
+        <v>843</v>
       </c>
       <c r="E454" t="s">
-        <v>58</v>
+        <v>844</v>
       </c>
       <c r="F454" s="1">
-        <v>46231</v>
+        <v>46255</v>
       </c>
       <c r="G454" s="1">
-        <v>46231</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="455" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A455" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="B455" t="s">
-        <v>859</v>
+        <v>852</v>
       </c>
       <c r="C455" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D455" t="s">
-        <v>57</v>
+        <v>843</v>
       </c>
       <c r="E455" t="s">
-        <v>58</v>
+        <v>844</v>
       </c>
       <c r="F455" s="1">
-        <v>46254</v>
+        <v>46258</v>
       </c>
       <c r="G455" s="1">
-        <v>46254</v>
-      </c>
-    </row>
-    <row r="456" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A456" t="s">
-        <v>836</v>
-      </c>
-      <c r="B456" t="s">
-        <v>860</v>
-      </c>
-      <c r="C456" t="s">
-        <v>2</v>
-      </c>
-      <c r="D456" t="s">
-        <v>57</v>
-      </c>
-      <c r="E456" t="s">
-        <v>58</v>
-      </c>
-      <c r="F456" s="1">
-        <v>46255</v>
-      </c>
-      <c r="G456" s="1">
-        <v>46255</v>
-      </c>
-    </row>
-    <row r="457" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A457" t="s">
-        <v>836</v>
-      </c>
-      <c r="B457" t="s">
-        <v>861</v>
-      </c>
-      <c r="C457" t="s">
-        <v>6</v>
-      </c>
-      <c r="D457" t="s">
-        <v>57</v>
-      </c>
-      <c r="E457" t="s">
-        <v>58</v>
-      </c>
-      <c r="F457" s="1">
-        <v>46260</v>
-      </c>
-      <c r="G457" s="1">
-        <v>46260</v>
-      </c>
-    </row>
-    <row r="458" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A458" t="s">
-        <v>836</v>
-      </c>
-      <c r="B458" t="s">
-        <v>862</v>
-      </c>
-      <c r="C458" t="s">
-        <v>80</v>
-      </c>
-      <c r="D458" t="s">
-        <v>863</v>
-      </c>
-      <c r="E458" t="s">
-        <v>864</v>
-      </c>
-      <c r="F458" s="1">
-        <v>46261</v>
-      </c>
-      <c r="G458" s="1">
-        <v>46261</v>
-      </c>
-    </row>
-    <row r="459" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A459" t="s">
-        <v>836</v>
-      </c>
-      <c r="B459" t="s">
-        <v>865</v>
-      </c>
-      <c r="C459" t="s">
-        <v>80</v>
-      </c>
-      <c r="D459" t="s">
-        <v>57</v>
-      </c>
-      <c r="E459" t="s">
-        <v>58</v>
-      </c>
-      <c r="F459" s="1">
-        <v>46261</v>
-      </c>
-      <c r="G459" s="1">
-        <v>46261</v>
-      </c>
-    </row>
-    <row r="460" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A460" t="s">
-        <v>836</v>
-      </c>
-      <c r="B460" t="s">
-        <v>866</v>
-      </c>
-      <c r="C460" t="s">
-        <v>80</v>
-      </c>
-      <c r="D460" t="s">
-        <v>57</v>
-      </c>
-      <c r="E460" t="s">
-        <v>58</v>
-      </c>
-      <c r="F460" s="1">
-        <v>46261</v>
-      </c>
-      <c r="G460" s="1">
-        <v>46261</v>
-      </c>
-    </row>
-    <row r="461" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A461" t="s">
-        <v>867</v>
-      </c>
-      <c r="B461" t="s">
-        <v>868</v>
-      </c>
-      <c r="C461" t="s">
-        <v>2</v>
-      </c>
-      <c r="D461" t="s">
-        <v>869</v>
-      </c>
-      <c r="E461" t="s">
-        <v>870</v>
-      </c>
-      <c r="F461" s="1">
-        <v>46083</v>
-      </c>
-      <c r="G461" s="1">
-        <v>46084</v>
-      </c>
-    </row>
-    <row r="462" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A462" t="s">
-        <v>867</v>
-      </c>
-      <c r="B462" t="s">
-        <v>871</v>
-      </c>
-      <c r="C462" t="s">
-        <v>2</v>
-      </c>
-      <c r="D462" t="s">
-        <v>869</v>
-      </c>
-      <c r="E462" t="s">
-        <v>870</v>
-      </c>
-      <c r="F462" s="1">
-        <v>46132</v>
-      </c>
-      <c r="G462" s="1">
-        <v>46133</v>
-      </c>
-    </row>
-    <row r="463" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A463" t="s">
-        <v>867</v>
-      </c>
-      <c r="B463" t="s">
-        <v>872</v>
-      </c>
-      <c r="C463" t="s">
-        <v>2</v>
-      </c>
-      <c r="D463" t="s">
-        <v>873</v>
-      </c>
-      <c r="E463" t="s">
-        <v>874</v>
-      </c>
-      <c r="F463" s="1">
-        <v>46157</v>
-      </c>
-      <c r="G463" s="1">
-        <v>46157</v>
-      </c>
-    </row>
-    <row r="464" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A464" t="s">
-        <v>867</v>
-      </c>
-      <c r="B464" t="s">
-        <v>875</v>
-      </c>
-      <c r="C464" t="s">
-        <v>2</v>
-      </c>
-      <c r="D464" t="s">
-        <v>876</v>
-      </c>
-      <c r="E464" t="s">
-        <v>877</v>
-      </c>
-      <c r="F464" s="1">
-        <v>46168</v>
-      </c>
-      <c r="G464" s="1">
-        <v>46170</v>
-      </c>
-    </row>
-    <row r="465" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A465" t="s">
-        <v>867</v>
-      </c>
-      <c r="B465" t="s">
-        <v>878</v>
-      </c>
-      <c r="C465" t="s">
-        <v>2</v>
-      </c>
-      <c r="D465" t="s">
-        <v>873</v>
-      </c>
-      <c r="E465" t="s">
-        <v>874</v>
-      </c>
-      <c r="F465" s="1">
-        <v>46244</v>
-      </c>
-      <c r="G465" s="1">
-        <v>46244</v>
-      </c>
-    </row>
-    <row r="466" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A466" t="s">
-        <v>867</v>
-      </c>
-      <c r="B466" t="s">
-        <v>879</v>
-      </c>
-      <c r="C466" t="s">
-        <v>2</v>
-      </c>
-      <c r="D466" t="s">
-        <v>873</v>
-      </c>
-      <c r="E466" t="s">
-        <v>874</v>
-      </c>
-      <c r="F466" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G466" s="1">
-        <v>46247</v>
-      </c>
-    </row>
-    <row r="467" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A467" t="s">
-        <v>867</v>
-      </c>
-      <c r="B467" t="s">
-        <v>880</v>
-      </c>
-      <c r="C467" t="s">
-        <v>2</v>
-      </c>
-      <c r="D467" t="s">
-        <v>869</v>
-      </c>
-      <c r="E467" t="s">
-        <v>870</v>
-      </c>
-      <c r="F467" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G467" s="1">
-        <v>46247</v>
-      </c>
-    </row>
-    <row r="468" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A468" t="s">
-        <v>867</v>
-      </c>
-      <c r="B468" t="s">
-        <v>881</v>
-      </c>
-      <c r="C468" t="s">
-        <v>2</v>
-      </c>
-      <c r="D468" t="s">
-        <v>873</v>
-      </c>
-      <c r="E468" t="s">
-        <v>874</v>
-      </c>
-      <c r="F468" s="1">
-        <v>46255</v>
-      </c>
-      <c r="G468" s="1">
-        <v>46255</v>
-      </c>
-    </row>
-    <row r="469" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A469" t="s">
-        <v>867</v>
-      </c>
-      <c r="B469" t="s">
-        <v>882</v>
-      </c>
-      <c r="C469" t="s">
-        <v>2</v>
-      </c>
-      <c r="D469" t="s">
-        <v>873</v>
-      </c>
-      <c r="E469" t="s">
-        <v>874</v>
-      </c>
-      <c r="F469" s="1">
-        <v>46258</v>
-      </c>
-      <c r="G469" s="1">
         <v>46258</v>
       </c>
     </row>

--- a/Data_ERP/Pedidos Transmicion.xlsx
+++ b/Data_ERP/Pedidos Transmicion.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sistema_Logistico_Peirano\Data_ERP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DD7F434A-DB69-4DC2-875A-F31DFE1E35E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BFCF6CEA-E211-44D0-9B14-95D9B4A65337}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25230" yWindow="4080" windowWidth="15375" windowHeight="8325" xr2:uid="{55B95A94-176D-4463-8EC7-16775CAE43F3}"/>
+    <workbookView xWindow="25230" yWindow="4080" windowWidth="15375" windowHeight="8325" xr2:uid="{0387AA51-D7FF-49B4-9616-210EF5E8A02F}"/>
   </bookViews>
   <sheets>
     <sheet name="transmicion" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2277" uniqueCount="860">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2192" uniqueCount="805">
   <si>
     <t>0001</t>
   </si>
@@ -1165,15 +1165,6 @@
     <t xml:space="preserve">  214073</t>
   </si>
   <si>
-    <t xml:space="preserve">  214074</t>
-  </si>
-  <si>
-    <t>BL05</t>
-  </si>
-  <si>
-    <t>BAIGORRIA LEONARDO F.</t>
-  </si>
-  <si>
     <t xml:space="preserve">  214080</t>
   </si>
   <si>
@@ -1225,7 +1216,661 @@
     <t xml:space="preserve">  214146</t>
   </si>
   <si>
-    <t xml:space="preserve">  214147</t>
+    <t xml:space="preserve">  214149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214150</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214164</t>
+  </si>
+  <si>
+    <t>FE15</t>
+  </si>
+  <si>
+    <t>FEDAN S.A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214184</t>
+  </si>
+  <si>
+    <t>SS42</t>
+  </si>
+  <si>
+    <t>SINCENCO SILVIO D -CASA SILVIO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214214</t>
+  </si>
+  <si>
+    <t>TS11</t>
+  </si>
+  <si>
+    <t>TODO SANITARIOS Y GAS S.R.L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214226</t>
+  </si>
+  <si>
+    <t>KP01</t>
+  </si>
+  <si>
+    <t>KROMACOLOR PINTURERIAS S.R.L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214237</t>
+  </si>
+  <si>
+    <t>DS15</t>
+  </si>
+  <si>
+    <t>DI STABILE E HIJOS S.A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214264</t>
+  </si>
+  <si>
+    <t>MA42</t>
+  </si>
+  <si>
+    <t>MAYOR S.A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214268</t>
+  </si>
+  <si>
+    <t>PL24</t>
+  </si>
+  <si>
+    <t>PLOMYGAS S.R.L. - PLOMIGAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214274</t>
+  </si>
+  <si>
+    <t>EF09</t>
+  </si>
+  <si>
+    <t>ETCHEVERS Y FARIAS S. CAP I SECC IV-BLANCO Y CASTR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214285</t>
+  </si>
+  <si>
+    <t>CO28</t>
+  </si>
+  <si>
+    <t>CONSTRUDISENO S.A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214289</t>
+  </si>
+  <si>
+    <t>ZZ02</t>
+  </si>
+  <si>
+    <t>ZINGALV GALVANIZADOS Y ZINC S.R.L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214309</t>
+  </si>
+  <si>
+    <t>FP04</t>
+  </si>
+  <si>
+    <t>FLUIDOS PATAGONIA S.A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214314</t>
+  </si>
+  <si>
+    <t>RC25</t>
+  </si>
+  <si>
+    <t>RAMIREZ CHRISTIAN J.G.-SANIMAR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214320</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214325</t>
+  </si>
+  <si>
+    <t>SC33</t>
+  </si>
+  <si>
+    <t>SANITARIOS CAMPANA S.R.L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214332</t>
+  </si>
+  <si>
+    <t>ZE02</t>
+  </si>
+  <si>
+    <t>ZERAMIKO DE MARIA R.O.CABRERA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214335</t>
+  </si>
+  <si>
+    <t>VS08</t>
+  </si>
+  <si>
+    <t>VIAL SERVICIOS S.A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214336</t>
+  </si>
+  <si>
+    <t>CO42</t>
+  </si>
+  <si>
+    <t>COLADONATO FEDERICO N.-SANITARIOS CARUPA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214350</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214352</t>
+  </si>
+  <si>
+    <t>DR01</t>
+  </si>
+  <si>
+    <t>DOMINGO RESTA Y CIA. SA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214353</t>
+  </si>
+  <si>
+    <t>ML16</t>
+  </si>
+  <si>
+    <t>MORINICO LEONEL E-MARKET FULL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214370</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214373</t>
+  </si>
+  <si>
+    <t>VM14</t>
+  </si>
+  <si>
+    <t>VIESTI HNOS. SANITARIOS S. R. L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214383</t>
+  </si>
+  <si>
+    <t>RR17</t>
+  </si>
+  <si>
+    <t>RAMOS REVESTIMIENTOS S.R.L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214390</t>
+  </si>
+  <si>
+    <t>IM05</t>
+  </si>
+  <si>
+    <t>IMEPHO S.A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214391</t>
+  </si>
+  <si>
+    <t>DG15</t>
+  </si>
+  <si>
+    <t>DISTRIBUIDORA GAY S.R.L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214395</t>
+  </si>
+  <si>
+    <t>MM43</t>
+  </si>
+  <si>
+    <t>MEZZACAPPA MIGUEL A -CASAMIKY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214406</t>
+  </si>
+  <si>
+    <t>SO06</t>
+  </si>
+  <si>
+    <t>SOLDASUR S.A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214412</t>
+  </si>
+  <si>
+    <t>EP08</t>
+  </si>
+  <si>
+    <t>EL MUNDO DEL PLOMERO S.R.L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214413</t>
+  </si>
+  <si>
+    <t>DG16</t>
+  </si>
+  <si>
+    <t>DEKKO GUALEGUAYCHU SRL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214417</t>
+  </si>
+  <si>
+    <t>TP01</t>
+  </si>
+  <si>
+    <t>SAN MONTE ALMO SA - TEIXEIRA POCAS SANITARIOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214420</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214430</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214446</t>
+  </si>
+  <si>
+    <t>LC20</t>
+  </si>
+  <si>
+    <t>BELFORTTI S.R.L. -LA CALERA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214450</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214452</t>
+  </si>
+  <si>
+    <t>GF01</t>
+  </si>
+  <si>
+    <t>GUIDOLI FLORIO S.R.L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214456</t>
+  </si>
+  <si>
+    <t>FE24</t>
+  </si>
+  <si>
+    <t>FEDAMIL S.A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214458</t>
+  </si>
+  <si>
+    <t>SA36</t>
+  </si>
+  <si>
+    <t>SAMOT S.A.S.  -SANIPLAST</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214470</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214481</t>
+  </si>
+  <si>
+    <t>BE13</t>
+  </si>
+  <si>
+    <t>BETOMAT S.R.L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214484</t>
+  </si>
+  <si>
+    <t>CP02</t>
+  </si>
+  <si>
+    <t>CASA PALM S.A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214485</t>
+  </si>
+  <si>
+    <t>SV08</t>
+  </si>
+  <si>
+    <t>SANIFER VCP S.R.L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214498</t>
+  </si>
+  <si>
+    <t>FC03</t>
+  </si>
+  <si>
+    <t>CHUAR S.R.L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214499</t>
+  </si>
+  <si>
+    <t>IC01</t>
+  </si>
+  <si>
+    <t>IMPORTADORA COMERCIAL FUEGUINA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214500</t>
+  </si>
+  <si>
+    <t>NP04</t>
+  </si>
+  <si>
+    <t>NEOMAT DE LA PATAGONIA S.A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214505</t>
+  </si>
+  <si>
+    <t>CJ35</t>
+  </si>
+  <si>
+    <t>CACERES JOSE A.- FERRETERIA CORRALON CACERES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214506</t>
+  </si>
+  <si>
+    <t>KN01</t>
+  </si>
+  <si>
+    <t>KALFAIAN HNOS. S.R.L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214513</t>
+  </si>
+  <si>
+    <t>FA32</t>
+  </si>
+  <si>
+    <t>FERNANDEZ AGUSTIN JOSE - GASTITO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214517</t>
+  </si>
+  <si>
+    <t>MH17</t>
+  </si>
+  <si>
+    <t>MALDONADO HECTOR H. -SANIT. MALDONADO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214530</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214534</t>
+  </si>
+  <si>
+    <t>RM20</t>
+  </si>
+  <si>
+    <t>ROSEBOON MIGUEL O. -M&amp;M SANITARIOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214536</t>
+  </si>
+  <si>
+    <t>PR20</t>
+  </si>
+  <si>
+    <t>PRADES S.A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214537</t>
+  </si>
+  <si>
+    <t>LR14</t>
+  </si>
+  <si>
+    <t>LA AGRICOLA REGIONAL COOPERATIVA LIMITADA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214538</t>
+  </si>
+  <si>
+    <t>NI04</t>
+  </si>
+  <si>
+    <t>NITUB SAIC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214540</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214547</t>
+  </si>
+  <si>
+    <t>LN02</t>
+  </si>
+  <si>
+    <t>LA NORIA REVESIMIENTOS S.A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214553</t>
+  </si>
+  <si>
+    <t>DA03</t>
+  </si>
+  <si>
+    <t>DARSIE Y CIA. SACI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214554</t>
   </si>
   <si>
     <t>ME36</t>
@@ -1234,511 +1879,316 @@
     <t>MERMOZ S.A.</t>
   </si>
   <si>
-    <t xml:space="preserve">  214149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214150</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214156</t>
-  </si>
-  <si>
-    <t>CY03</t>
-  </si>
-  <si>
-    <t>COMERCIALIZADORA Y CONSTRUCTORA LANUS SA  CYCLA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214164</t>
-  </si>
-  <si>
-    <t>FE15</t>
-  </si>
-  <si>
-    <t>FEDAN S.A.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214184</t>
-  </si>
-  <si>
-    <t>SS42</t>
-  </si>
-  <si>
-    <t>SINCENCO SILVIO D -CASA SILVIO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214201</t>
-  </si>
-  <si>
-    <t>SL13</t>
-  </si>
-  <si>
-    <t>SANITARIOS LUGANO S.R.L.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214214</t>
-  </si>
-  <si>
-    <t>TS11</t>
-  </si>
-  <si>
-    <t>TODO SANITARIOS Y GAS S.R.L.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214226</t>
-  </si>
-  <si>
-    <t>KP01</t>
-  </si>
-  <si>
-    <t>KROMACOLOR PINTURERIAS S.R.L.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214237</t>
-  </si>
-  <si>
-    <t>DS15</t>
-  </si>
-  <si>
-    <t>DI STABILE E HIJOS S.A.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214240</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214264</t>
-  </si>
-  <si>
-    <t>MA42</t>
-  </si>
-  <si>
-    <t>MAYOR S.A.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214268</t>
-  </si>
-  <si>
-    <t>PL24</t>
-  </si>
-  <si>
-    <t>PLOMYGAS S.R.L. - PLOMIGAS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214274</t>
-  </si>
-  <si>
-    <t>EF09</t>
-  </si>
-  <si>
-    <t>ETCHEVERS Y FARIAS S. CAP I SECC IV-BLANCO Y CASTR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214285</t>
-  </si>
-  <si>
-    <t>CO28</t>
-  </si>
-  <si>
-    <t>CONSTRUDISENO S.A.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214289</t>
-  </si>
-  <si>
-    <t>ZZ02</t>
-  </si>
-  <si>
-    <t>ZINGALV GALVANIZADOS Y ZINC S.R.L.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214309</t>
-  </si>
-  <si>
-    <t>FP04</t>
-  </si>
-  <si>
-    <t>FLUIDOS PATAGONIA S.A.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214314</t>
-  </si>
-  <si>
-    <t>RC25</t>
-  </si>
-  <si>
-    <t>RAMIREZ CHRISTIAN J.G.-SANIMAR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214320</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214325</t>
-  </si>
-  <si>
-    <t>SC33</t>
-  </si>
-  <si>
-    <t>SANITARIOS CAMPANA S.R.L.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214332</t>
-  </si>
-  <si>
-    <t>ZE02</t>
-  </si>
-  <si>
-    <t>ZERAMIKO DE MARIA R.O.CABRERA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214335</t>
-  </si>
-  <si>
-    <t>VS08</t>
-  </si>
-  <si>
-    <t>VIAL SERVICIOS S.A.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214336</t>
-  </si>
-  <si>
-    <t>CO42</t>
-  </si>
-  <si>
-    <t>COLADONATO FEDERICO N.-SANITARIOS CARUPA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214349</t>
-  </si>
-  <si>
-    <t>MA43</t>
-  </si>
-  <si>
-    <t>MARMOLERIA EL ARTESANO S.A.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214350</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214352</t>
-  </si>
-  <si>
-    <t>DR01</t>
-  </si>
-  <si>
-    <t>DOMINGO RESTA Y CIA. SA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214353</t>
-  </si>
-  <si>
-    <t>ML16</t>
-  </si>
-  <si>
-    <t>MORINICO LEONEL E-MARKET FULL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214362</t>
-  </si>
-  <si>
-    <t>KO01</t>
-  </si>
-  <si>
-    <t>KOCUDEL S.A.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214370</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214371</t>
-  </si>
-  <si>
-    <t>DL10</t>
-  </si>
-  <si>
-    <t>DE LOS ANDES S. A. S.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214373</t>
-  </si>
-  <si>
-    <t>VM14</t>
-  </si>
-  <si>
-    <t>VIESTI HNOS. SANITARIOS S. R. L.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214376</t>
-  </si>
-  <si>
-    <t>GV05</t>
-  </si>
-  <si>
-    <t>GRUPO V S.R.L.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214382</t>
-  </si>
-  <si>
-    <t>CL40</t>
-  </si>
-  <si>
-    <t>CLICK-ON S.A. -TIOSO HOGAR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214383</t>
-  </si>
-  <si>
-    <t>RR17</t>
-  </si>
-  <si>
-    <t>RAMOS REVESTIMIENTOS S.R.L.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214384</t>
-  </si>
-  <si>
-    <t>CC52</t>
-  </si>
-  <si>
-    <t>CHEN CHING MEI- SANITARIOS DANIEL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214389</t>
-  </si>
-  <si>
-    <t>ST16</t>
-  </si>
-  <si>
-    <t>SANITARIOS TARAGUI S.R.L.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214390</t>
-  </si>
-  <si>
-    <t>IM05</t>
-  </si>
-  <si>
-    <t>IMEPHO S.A.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214391</t>
-  </si>
-  <si>
-    <t>DG15</t>
-  </si>
-  <si>
-    <t>DISTRIBUIDORA GAY S.R.L.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214395</t>
-  </si>
-  <si>
-    <t>MM43</t>
-  </si>
-  <si>
-    <t>MEZZACAPPA MIGUEL A -CASAMIKY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214398</t>
-  </si>
-  <si>
-    <t>CS16</t>
-  </si>
-  <si>
-    <t>CERAMICOS Y SANITARIOS SAN LUIS SRL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214400</t>
-  </si>
-  <si>
-    <t>MO24</t>
-  </si>
-  <si>
-    <t>MOENCA SRL -JAQUE MATE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214405</t>
-  </si>
-  <si>
-    <t>SO06</t>
-  </si>
-  <si>
-    <t>SOLDASUR S.A.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214407</t>
-  </si>
-  <si>
-    <t>TO04</t>
-  </si>
-  <si>
-    <t>TOBA S.R.L.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214410</t>
-  </si>
-  <si>
-    <t>BO15</t>
-  </si>
-  <si>
-    <t>BOTTIGLIERI S.R.L.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214412</t>
-  </si>
-  <si>
-    <t>EP08</t>
-  </si>
-  <si>
-    <t>EL MUNDO DEL PLOMERO S.R.L.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214413</t>
-  </si>
-  <si>
-    <t>DG16</t>
-  </si>
-  <si>
-    <t>DEKKO GUALEGUAYCHU SRL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214417</t>
-  </si>
-  <si>
-    <t>TP01</t>
-  </si>
-  <si>
-    <t>SAN MONTE ALMO SA - TEIXEIRA POCAS SANITARIOS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214419</t>
+    <t xml:space="preserve">  214555</t>
+  </si>
+  <si>
+    <t>HC03</t>
+  </si>
+  <si>
+    <t>HIJOS DE RAFAEL CONTI S.A. - CONTI MATERIALES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214568</t>
+  </si>
+  <si>
+    <t>PE04</t>
+  </si>
+  <si>
+    <t>PERREN Y CIA. S.A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214570</t>
+  </si>
+  <si>
+    <t>NO09</t>
+  </si>
+  <si>
+    <t>NOCITO S.A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214572</t>
+  </si>
+  <si>
+    <t>SJ21</t>
+  </si>
+  <si>
+    <t>SANITARIOS JULICAM SRL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214574</t>
+  </si>
+  <si>
+    <t>TR22</t>
+  </si>
+  <si>
+    <t>TRITONIC S.A.S.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214580</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214585</t>
+  </si>
+  <si>
+    <t>AL24</t>
+  </si>
+  <si>
+    <t>ALVARENGA VILLAR LUIS F.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214587</t>
+  </si>
+  <si>
+    <t>UG01</t>
+  </si>
+  <si>
+    <t>UCCELI GABRIEL A.-SANITARIOS GABRIEL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214590</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214593</t>
+  </si>
+  <si>
+    <t>CM56</t>
+  </si>
+  <si>
+    <t>ISMARON S.A. -CASA MARTINEZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214600</t>
+  </si>
+  <si>
+    <t>QU03</t>
+  </si>
+  <si>
+    <t>QUBO S.A.S. - QUBO AMBIENTES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214602</t>
+  </si>
+  <si>
+    <t>VN02</t>
+  </si>
+  <si>
+    <t>VICTOR NADIA ANTONELA -SANTIANO CONSTRUCCIONES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214603</t>
+  </si>
+  <si>
+    <t>ZJ02</t>
+  </si>
+  <si>
+    <t>ZORZON JOANA M -SANTIANO CONSTRUCCIONES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214604</t>
+  </si>
+  <si>
+    <t>ES13</t>
+  </si>
+  <si>
+    <t>EDEN SANITARIOS S.R.L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214610</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214630</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214633</t>
+  </si>
+  <si>
+    <t>MM44</t>
+  </si>
+  <si>
+    <t>MOTTESI MATERIALES SA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214640</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214643</t>
+  </si>
+  <si>
+    <t>NS03</t>
+  </si>
+  <si>
+    <t>NESGAMET S.A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214646</t>
+  </si>
+  <si>
+    <t>QU01</t>
+  </si>
+  <si>
+    <t>QUEIJA S.A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214650</t>
+  </si>
+  <si>
+    <t>0004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      51</t>
+  </si>
+  <si>
+    <t xml:space="preserve">     111</t>
+  </si>
+  <si>
+    <t>LG10</t>
+  </si>
+  <si>
+    <t>LOPEZ GAS ONLINE S.A</t>
+  </si>
+  <si>
+    <t>0008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    2390</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    2391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    2474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    2593</t>
+  </si>
+  <si>
+    <t>TC11</t>
+  </si>
+  <si>
+    <t>TRIPOLI CARLOS L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    2645</t>
   </si>
   <si>
     <t>DA11</t>
@@ -1747,615 +2197,6 @@
     <t>DAFYS S.A.</t>
   </si>
   <si>
-    <t xml:space="preserve">  214420</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214427</t>
-  </si>
-  <si>
-    <t>FE23</t>
-  </si>
-  <si>
-    <t>FERRIND S.A.S.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214430</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214431</t>
-  </si>
-  <si>
-    <t>SG24</t>
-  </si>
-  <si>
-    <t>SANITARIOS GUELMIB S.R.L.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214446</t>
-  </si>
-  <si>
-    <t>LC20</t>
-  </si>
-  <si>
-    <t>BELFORTTI S.R.L. -LA CALERA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214450</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214452</t>
-  </si>
-  <si>
-    <t>GF01</t>
-  </si>
-  <si>
-    <t>GUIDOLI FLORIO S.R.L.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214453</t>
-  </si>
-  <si>
-    <t>VG04</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ NORBERTO Y GRANELLA JORGE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214456</t>
-  </si>
-  <si>
-    <t>FE24</t>
-  </si>
-  <si>
-    <t>FEDAMIL S.A.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214458</t>
-  </si>
-  <si>
-    <t>SA36</t>
-  </si>
-  <si>
-    <t>SAMOT S.A.S.  -SANIPLAST</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214460</t>
-  </si>
-  <si>
-    <t>DU04</t>
-  </si>
-  <si>
-    <t>DURANTE HNOS S R L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214470</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214473</t>
-  </si>
-  <si>
-    <t>LP11</t>
-  </si>
-  <si>
-    <t>SANITARIOS LA PRIMERA S.R.L.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214480</t>
-  </si>
-  <si>
-    <t>AG17</t>
-  </si>
-  <si>
-    <t>A G CHIBAN S.R.L.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214481</t>
-  </si>
-  <si>
-    <t>BE13</t>
-  </si>
-  <si>
-    <t>BETOMAT S.R.L.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214482</t>
-  </si>
-  <si>
-    <t>SU09</t>
-  </si>
-  <si>
-    <t>SUPERMAT CENTRAL S.A.S.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214484</t>
-  </si>
-  <si>
-    <t>CP02</t>
-  </si>
-  <si>
-    <t>CASA PALM S.A.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214485</t>
-  </si>
-  <si>
-    <t>SV08</t>
-  </si>
-  <si>
-    <t>SANIFER VCP S.R.L.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214486</t>
-  </si>
-  <si>
-    <t>ED04</t>
-  </si>
-  <si>
-    <t>EDIFICOR S.R.L.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214498</t>
-  </si>
-  <si>
-    <t>FC03</t>
-  </si>
-  <si>
-    <t>CHUAR S.R.L.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214499</t>
-  </si>
-  <si>
-    <t>IC01</t>
-  </si>
-  <si>
-    <t>IMPORTADORA COMERCIAL FUEGUINA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214500</t>
-  </si>
-  <si>
-    <t>NP04</t>
-  </si>
-  <si>
-    <t>NEOMAT DE LA PATAGONIA S.A.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214501</t>
-  </si>
-  <si>
-    <t>WA05</t>
-  </si>
-  <si>
-    <t>SUCESION DE WILLATOWSKI FELIX ALFREDO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214506</t>
-  </si>
-  <si>
-    <t>KN01</t>
-  </si>
-  <si>
-    <t>KALFAIAN HNOS. S.R.L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214513</t>
-  </si>
-  <si>
-    <t>FA32</t>
-  </si>
-  <si>
-    <t>FERNANDEZ AGUSTIN JOSE - GASTITO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214517</t>
-  </si>
-  <si>
-    <t>MH17</t>
-  </si>
-  <si>
-    <t>MALDONADO HECTOR H. -SANIT. MALDONADO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214520</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214530</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214534</t>
-  </si>
-  <si>
-    <t>RM20</t>
-  </si>
-  <si>
-    <t>ROSEBOON MIGUEL O. -M&amp;M SANITARIOS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214536</t>
-  </si>
-  <si>
-    <t>PR20</t>
-  </si>
-  <si>
-    <t>PRADES S.A.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214537</t>
-  </si>
-  <si>
-    <t>LR14</t>
-  </si>
-  <si>
-    <t>LA AGRICOLA REGIONAL COOPERATIVA LIMITADA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214538</t>
-  </si>
-  <si>
-    <t>NI04</t>
-  </si>
-  <si>
-    <t>NITUB SAIC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214540</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214541</t>
-  </si>
-  <si>
-    <t>FC16</t>
-  </si>
-  <si>
-    <t>FERNANDEZ CARLOS FEDERICO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214543</t>
-  </si>
-  <si>
-    <t>BG15</t>
-  </si>
-  <si>
-    <t>BULFON GUILLERMO JESUS - SANIT. MATISA -</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214547</t>
-  </si>
-  <si>
-    <t>LN02</t>
-  </si>
-  <si>
-    <t>LA NORIA REVESIMIENTOS S.A.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214553</t>
-  </si>
-  <si>
-    <t>DA03</t>
-  </si>
-  <si>
-    <t>DARSIE Y CIA. SACI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214555</t>
-  </si>
-  <si>
-    <t>HC03</t>
-  </si>
-  <si>
-    <t>HIJOS DE RAFAEL CONTI S.A. - CONTI MATERIALES</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214560</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214568</t>
-  </si>
-  <si>
-    <t>PE04</t>
-  </si>
-  <si>
-    <t>PERREN Y CIA. S.A.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214570</t>
-  </si>
-  <si>
-    <t>NO09</t>
-  </si>
-  <si>
-    <t>NOCITO S.A.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214572</t>
-  </si>
-  <si>
-    <t>SJ21</t>
-  </si>
-  <si>
-    <t>SANITARIOS JULICAM SRL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214574</t>
-  </si>
-  <si>
-    <t>TR22</t>
-  </si>
-  <si>
-    <t>TRITONIC S.A.S.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214579</t>
-  </si>
-  <si>
-    <t>RC10</t>
-  </si>
-  <si>
-    <t>RAN CO MATERIALES S.A.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214580</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214585</t>
-  </si>
-  <si>
-    <t>AL24</t>
-  </si>
-  <si>
-    <t>ALVARENGA VILLAR LUIS F.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214587</t>
-  </si>
-  <si>
-    <t>UG01</t>
-  </si>
-  <si>
-    <t>UCCELI GABRIEL A.-SANITARIOS GABRIEL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214590</t>
-  </si>
-  <si>
-    <t>0004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">      51</t>
-  </si>
-  <si>
-    <t xml:space="preserve">     111</t>
-  </si>
-  <si>
-    <t>LG10</t>
-  </si>
-  <si>
-    <t>LOPEZ GAS ONLINE S.A</t>
-  </si>
-  <si>
-    <t>0008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    2390</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    2391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    2474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    2593</t>
-  </si>
-  <si>
-    <t>TC11</t>
-  </si>
-  <si>
-    <t>TRIPOLI CARLOS L.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    2645</t>
-  </si>
-  <si>
     <t xml:space="preserve">    2652</t>
   </si>
   <si>
@@ -2410,9 +2251,6 @@
     <t xml:space="preserve">    2818</t>
   </si>
   <si>
-    <t xml:space="preserve">    2842</t>
-  </si>
-  <si>
     <t xml:space="preserve">    2843</t>
   </si>
   <si>
@@ -2425,18 +2263,6 @@
     <t xml:space="preserve">    2851</t>
   </si>
   <si>
-    <t xml:space="preserve">    2858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    2859</t>
-  </si>
-  <si>
-    <t>SM26</t>
-  </si>
-  <si>
-    <t>SANCHEZ M. Y NUÑEZ M. S.H. - SANITARIOS NUSAN</t>
-  </si>
-  <si>
     <t xml:space="preserve">    2860</t>
   </si>
   <si>
@@ -2446,6 +2272,12 @@
     <t>MATERIALES BASUALDO S.A.</t>
   </si>
   <si>
+    <t xml:space="preserve">    2862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    2863</t>
+  </si>
+  <si>
     <t>4444</t>
   </si>
   <si>
@@ -2533,6 +2365,15 @@
     <t xml:space="preserve">    2336</t>
   </si>
   <si>
+    <t xml:space="preserve">    2337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    2339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    2340</t>
+  </si>
+  <si>
     <t>9999</t>
   </si>
   <si>
@@ -2549,12 +2390,6 @@
   </si>
   <si>
     <t xml:space="preserve">      50</t>
-  </si>
-  <si>
-    <t>QU01</t>
-  </si>
-  <si>
-    <t>QUEIJA S.A</t>
   </si>
   <si>
     <t xml:space="preserve">      55</t>
@@ -3049,31 +2884,31 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C982E07-9753-4882-B88A-0A8DF07939F9}">
-  <dimension ref="A1:G455"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{961C53E3-9F57-4010-80CB-BC209C238E0C}">
+  <dimension ref="A1:G438"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
-        <v>853</v>
+        <v>798</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>854</v>
+        <v>799</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>855</v>
+        <v>800</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>856</v>
+        <v>801</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>857</v>
+        <v>802</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>858</v>
+        <v>803</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>859</v>
+        <v>804</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
@@ -6741,7 +6576,7 @@
         <v>356</v>
       </c>
       <c r="C161" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D161" t="s">
         <v>37</v>
@@ -6810,7 +6645,7 @@
         <v>361</v>
       </c>
       <c r="C164" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D164" t="s">
         <v>37</v>
@@ -6833,7 +6668,7 @@
         <v>362</v>
       </c>
       <c r="C165" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D165" t="s">
         <v>37</v>
@@ -6856,7 +6691,7 @@
         <v>363</v>
       </c>
       <c r="C166" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D166" t="s">
         <v>37</v>
@@ -6994,7 +6829,7 @@
         <v>369</v>
       </c>
       <c r="C172" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D172" t="s">
         <v>37</v>
@@ -7181,16 +7016,16 @@
         <v>80</v>
       </c>
       <c r="D180" t="s">
-        <v>382</v>
+        <v>16</v>
       </c>
       <c r="E180" t="s">
-        <v>383</v>
+        <v>17</v>
       </c>
       <c r="F180" s="1">
         <v>46254</v>
       </c>
       <c r="G180" s="1">
-        <v>46259</v>
+        <v>46254</v>
       </c>
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.2">
@@ -7198,16 +7033,16 @@
         <v>0</v>
       </c>
       <c r="B181" t="s">
+        <v>382</v>
+      </c>
+      <c r="C181" t="s">
+        <v>6</v>
+      </c>
+      <c r="D181" t="s">
+        <v>383</v>
+      </c>
+      <c r="E181" t="s">
         <v>384</v>
-      </c>
-      <c r="C181" t="s">
-        <v>80</v>
-      </c>
-      <c r="D181" t="s">
-        <v>16</v>
-      </c>
-      <c r="E181" t="s">
-        <v>17</v>
       </c>
       <c r="F181" s="1">
         <v>46254</v>
@@ -7224,13 +7059,13 @@
         <v>385</v>
       </c>
       <c r="C182" t="s">
-        <v>6</v>
+        <v>80</v>
       </c>
       <c r="D182" t="s">
-        <v>386</v>
+        <v>16</v>
       </c>
       <c r="E182" t="s">
-        <v>387</v>
+        <v>17</v>
       </c>
       <c r="F182" s="1">
         <v>46254</v>
@@ -7244,22 +7079,22 @@
         <v>0</v>
       </c>
       <c r="B183" t="s">
+        <v>386</v>
+      </c>
+      <c r="C183" t="s">
+        <v>80</v>
+      </c>
+      <c r="D183" t="s">
+        <v>387</v>
+      </c>
+      <c r="E183" t="s">
         <v>388</v>
-      </c>
-      <c r="C183" t="s">
-        <v>80</v>
-      </c>
-      <c r="D183" t="s">
-        <v>16</v>
-      </c>
-      <c r="E183" t="s">
-        <v>17</v>
       </c>
       <c r="F183" s="1">
         <v>46254</v>
       </c>
       <c r="G183" s="1">
-        <v>46254</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.2">
@@ -7270,7 +7105,7 @@
         <v>389</v>
       </c>
       <c r="C184" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D184" t="s">
         <v>390</v>
@@ -7282,7 +7117,7 @@
         <v>46254</v>
       </c>
       <c r="G184" s="1">
-        <v>46259</v>
+        <v>46258</v>
       </c>
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.2">
@@ -7305,7 +7140,7 @@
         <v>46254</v>
       </c>
       <c r="G185" s="1">
-        <v>46258</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.2">
@@ -7316,19 +7151,19 @@
         <v>395</v>
       </c>
       <c r="C186" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D186" t="s">
-        <v>396</v>
+        <v>16</v>
       </c>
       <c r="E186" t="s">
-        <v>397</v>
+        <v>17</v>
       </c>
       <c r="F186" s="1">
         <v>46254</v>
       </c>
       <c r="G186" s="1">
-        <v>46255</v>
+        <v>46254</v>
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.2">
@@ -7336,22 +7171,22 @@
         <v>0</v>
       </c>
       <c r="B187" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C187" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D187" t="s">
-        <v>16</v>
+        <v>387</v>
       </c>
       <c r="E187" t="s">
-        <v>17</v>
+        <v>388</v>
       </c>
       <c r="F187" s="1">
         <v>46254</v>
       </c>
       <c r="G187" s="1">
-        <v>46254</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.2">
@@ -7359,16 +7194,16 @@
         <v>0</v>
       </c>
       <c r="B188" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="C188" t="s">
         <v>2</v>
       </c>
       <c r="D188" t="s">
-        <v>390</v>
+        <v>197</v>
       </c>
       <c r="E188" t="s">
-        <v>391</v>
+        <v>198</v>
       </c>
       <c r="F188" s="1">
         <v>46254</v>
@@ -7382,19 +7217,19 @@
         <v>0</v>
       </c>
       <c r="B189" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="C189" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D189" t="s">
-        <v>197</v>
+        <v>16</v>
       </c>
       <c r="E189" t="s">
-        <v>198</v>
+        <v>17</v>
       </c>
       <c r="F189" s="1">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="G189" s="1">
         <v>46255</v>
@@ -7405,19 +7240,19 @@
         <v>0</v>
       </c>
       <c r="B190" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C190" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D190" t="s">
-        <v>402</v>
+        <v>37</v>
       </c>
       <c r="E190" t="s">
-        <v>403</v>
+        <v>38</v>
       </c>
       <c r="F190" s="1">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="G190" s="1">
         <v>46255</v>
@@ -7428,10 +7263,10 @@
         <v>0</v>
       </c>
       <c r="B191" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="C191" t="s">
-        <v>80</v>
+        <v>6</v>
       </c>
       <c r="D191" t="s">
         <v>16</v>
@@ -7451,16 +7286,16 @@
         <v>0</v>
       </c>
       <c r="B192" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="C192" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D192" t="s">
-        <v>37</v>
+        <v>402</v>
       </c>
       <c r="E192" t="s">
-        <v>38</v>
+        <v>403</v>
       </c>
       <c r="F192" s="1">
         <v>46255</v>
@@ -7474,16 +7309,16 @@
         <v>0</v>
       </c>
       <c r="B193" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="C193" t="s">
         <v>80</v>
       </c>
       <c r="D193" t="s">
-        <v>407</v>
+        <v>325</v>
       </c>
       <c r="E193" t="s">
-        <v>408</v>
+        <v>326</v>
       </c>
       <c r="F193" s="1">
         <v>46255</v>
@@ -7497,22 +7332,22 @@
         <v>0</v>
       </c>
       <c r="B194" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="C194" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D194" t="s">
-        <v>16</v>
+        <v>406</v>
       </c>
       <c r="E194" t="s">
-        <v>17</v>
+        <v>407</v>
       </c>
       <c r="F194" s="1">
         <v>46255</v>
       </c>
       <c r="G194" s="1">
-        <v>46255</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.2">
@@ -7520,22 +7355,22 @@
         <v>0</v>
       </c>
       <c r="B195" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C195" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D195" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="E195" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="F195" s="1">
         <v>46255</v>
       </c>
       <c r="G195" s="1">
-        <v>46255</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.2">
@@ -7543,22 +7378,22 @@
         <v>0</v>
       </c>
       <c r="B196" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="C196" t="s">
         <v>80</v>
       </c>
       <c r="D196" t="s">
-        <v>325</v>
+        <v>16</v>
       </c>
       <c r="E196" t="s">
-        <v>326</v>
+        <v>17</v>
       </c>
       <c r="F196" s="1">
         <v>46255</v>
       </c>
       <c r="G196" s="1">
-        <v>46255</v>
+        <v>46256</v>
       </c>
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.2">
@@ -7566,22 +7401,22 @@
         <v>0</v>
       </c>
       <c r="B197" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="C197" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D197" t="s">
-        <v>325</v>
+        <v>411</v>
       </c>
       <c r="E197" t="s">
-        <v>326</v>
+        <v>412</v>
       </c>
       <c r="F197" s="1">
         <v>46255</v>
       </c>
       <c r="G197" s="1">
-        <v>46255</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.2">
@@ -7589,16 +7424,16 @@
         <v>0</v>
       </c>
       <c r="B198" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="C198" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D198" t="s">
-        <v>101</v>
+        <v>37</v>
       </c>
       <c r="E198" t="s">
-        <v>102</v>
+        <v>38</v>
       </c>
       <c r="F198" s="1">
         <v>46255</v>
@@ -7612,22 +7447,22 @@
         <v>0</v>
       </c>
       <c r="B199" t="s">
+        <v>414</v>
+      </c>
+      <c r="C199" t="s">
+        <v>2</v>
+      </c>
+      <c r="D199" t="s">
+        <v>415</v>
+      </c>
+      <c r="E199" t="s">
         <v>416</v>
-      </c>
-      <c r="C199" t="s">
-        <v>2</v>
-      </c>
-      <c r="D199" t="s">
-        <v>417</v>
-      </c>
-      <c r="E199" t="s">
-        <v>418</v>
       </c>
       <c r="F199" s="1">
         <v>46255</v>
       </c>
       <c r="G199" s="1">
-        <v>46259</v>
+        <v>46258</v>
       </c>
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.2">
@@ -7635,22 +7470,22 @@
         <v>0</v>
       </c>
       <c r="B200" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C200" t="s">
         <v>80</v>
       </c>
       <c r="D200" t="s">
-        <v>417</v>
+        <v>16</v>
       </c>
       <c r="E200" t="s">
-        <v>418</v>
+        <v>17</v>
       </c>
       <c r="F200" s="1">
         <v>46255</v>
       </c>
       <c r="G200" s="1">
-        <v>46259</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.2">
@@ -7658,22 +7493,22 @@
         <v>0</v>
       </c>
       <c r="B201" t="s">
+        <v>418</v>
+      </c>
+      <c r="C201" t="s">
+        <v>80</v>
+      </c>
+      <c r="D201" t="s">
+        <v>419</v>
+      </c>
+      <c r="E201" t="s">
         <v>420</v>
-      </c>
-      <c r="C201" t="s">
-        <v>80</v>
-      </c>
-      <c r="D201" t="s">
-        <v>101</v>
-      </c>
-      <c r="E201" t="s">
-        <v>102</v>
       </c>
       <c r="F201" s="1">
         <v>46255</v>
       </c>
       <c r="G201" s="1">
-        <v>46255</v>
+        <v>46258</v>
       </c>
     </row>
     <row r="202" spans="1:7" x14ac:dyDescent="0.2">
@@ -7687,16 +7522,16 @@
         <v>80</v>
       </c>
       <c r="D202" t="s">
-        <v>16</v>
+        <v>377</v>
       </c>
       <c r="E202" t="s">
-        <v>17</v>
+        <v>378</v>
       </c>
       <c r="F202" s="1">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="G202" s="1">
-        <v>46256</v>
+        <v>46258</v>
       </c>
     </row>
     <row r="203" spans="1:7" x14ac:dyDescent="0.2">
@@ -7716,10 +7551,10 @@
         <v>424</v>
       </c>
       <c r="F203" s="1">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="G203" s="1">
-        <v>46255</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="204" spans="1:7" x14ac:dyDescent="0.2">
@@ -7730,7 +7565,7 @@
         <v>425</v>
       </c>
       <c r="C204" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D204" t="s">
         <v>426</v>
@@ -7739,10 +7574,10 @@
         <v>427</v>
       </c>
       <c r="F204" s="1">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="G204" s="1">
-        <v>46260</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="205" spans="1:7" x14ac:dyDescent="0.2">
@@ -7756,16 +7591,16 @@
         <v>80</v>
       </c>
       <c r="D205" t="s">
-        <v>407</v>
+        <v>171</v>
       </c>
       <c r="E205" t="s">
-        <v>408</v>
+        <v>172</v>
       </c>
       <c r="F205" s="1">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="G205" s="1">
-        <v>46255</v>
+        <v>46258</v>
       </c>
     </row>
     <row r="206" spans="1:7" x14ac:dyDescent="0.2">
@@ -7776,19 +7611,19 @@
         <v>429</v>
       </c>
       <c r="C206" t="s">
-        <v>80</v>
+        <v>6</v>
       </c>
       <c r="D206" t="s">
-        <v>37</v>
+        <v>430</v>
       </c>
       <c r="E206" t="s">
-        <v>38</v>
+        <v>431</v>
       </c>
       <c r="F206" s="1">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="G206" s="1">
-        <v>46255</v>
+        <v>46258</v>
       </c>
     </row>
     <row r="207" spans="1:7" x14ac:dyDescent="0.2">
@@ -7796,19 +7631,19 @@
         <v>0</v>
       </c>
       <c r="B207" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="C207" t="s">
         <v>2</v>
       </c>
       <c r="D207" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="E207" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="F207" s="1">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="G207" s="1">
         <v>46258</v>
@@ -7819,22 +7654,22 @@
         <v>0</v>
       </c>
       <c r="B208" t="s">
+        <v>435</v>
+      </c>
+      <c r="C208" t="s">
+        <v>2</v>
+      </c>
+      <c r="D208" t="s">
         <v>433</v>
       </c>
-      <c r="C208" t="s">
-        <v>80</v>
-      </c>
-      <c r="D208" t="s">
-        <v>16</v>
-      </c>
       <c r="E208" t="s">
-        <v>17</v>
+        <v>434</v>
       </c>
       <c r="F208" s="1">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="G208" s="1">
-        <v>46255</v>
+        <v>46258</v>
       </c>
     </row>
     <row r="209" spans="1:7" x14ac:dyDescent="0.2">
@@ -7842,22 +7677,22 @@
         <v>0</v>
       </c>
       <c r="B209" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="C209" t="s">
         <v>80</v>
       </c>
       <c r="D209" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="E209" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="F209" s="1">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="G209" s="1">
-        <v>46258</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="210" spans="1:7" x14ac:dyDescent="0.2">
@@ -7865,22 +7700,22 @@
         <v>0</v>
       </c>
       <c r="B210" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="C210" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D210" t="s">
-        <v>402</v>
+        <v>314</v>
       </c>
       <c r="E210" t="s">
-        <v>403</v>
+        <v>315</v>
       </c>
       <c r="F210" s="1">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="G210" s="1">
-        <v>46258</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="211" spans="1:7" x14ac:dyDescent="0.2">
@@ -7888,19 +7723,19 @@
         <v>0</v>
       </c>
       <c r="B211" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="C211" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D211" t="s">
-        <v>402</v>
+        <v>158</v>
       </c>
       <c r="E211" t="s">
-        <v>403</v>
+        <v>159</v>
       </c>
       <c r="F211" s="1">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="G211" s="1">
         <v>46258</v>
@@ -7911,16 +7746,16 @@
         <v>0</v>
       </c>
       <c r="B212" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="C212" t="s">
         <v>80</v>
       </c>
       <c r="D212" t="s">
-        <v>377</v>
+        <v>359</v>
       </c>
       <c r="E212" t="s">
-        <v>378</v>
+        <v>360</v>
       </c>
       <c r="F212" s="1">
         <v>46258</v>
@@ -7934,22 +7769,22 @@
         <v>0</v>
       </c>
       <c r="B213" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="C213" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D213" t="s">
-        <v>332</v>
+        <v>443</v>
       </c>
       <c r="E213" t="s">
-        <v>333</v>
+        <v>444</v>
       </c>
       <c r="F213" s="1">
         <v>46258</v>
       </c>
       <c r="G213" s="1">
-        <v>46258</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="214" spans="1:7" x14ac:dyDescent="0.2">
@@ -7957,16 +7792,16 @@
         <v>0</v>
       </c>
       <c r="B214" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="C214" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D214" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="E214" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="F214" s="1">
         <v>46258</v>
@@ -7980,16 +7815,16 @@
         <v>0</v>
       </c>
       <c r="B215" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="C215" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D215" t="s">
-        <v>445</v>
+        <v>274</v>
       </c>
       <c r="E215" t="s">
-        <v>446</v>
+        <v>275</v>
       </c>
       <c r="F215" s="1">
         <v>46258</v>
@@ -8003,16 +7838,16 @@
         <v>0</v>
       </c>
       <c r="B216" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C216" t="s">
         <v>80</v>
       </c>
       <c r="D216" t="s">
-        <v>171</v>
+        <v>450</v>
       </c>
       <c r="E216" t="s">
-        <v>172</v>
+        <v>451</v>
       </c>
       <c r="F216" s="1">
         <v>46258</v>
@@ -8026,16 +7861,16 @@
         <v>0</v>
       </c>
       <c r="B217" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="C217" t="s">
-        <v>6</v>
+        <v>80</v>
       </c>
       <c r="D217" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="E217" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="F217" s="1">
         <v>46258</v>
@@ -8049,22 +7884,22 @@
         <v>0</v>
       </c>
       <c r="B218" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="C218" t="s">
         <v>2</v>
       </c>
       <c r="D218" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="E218" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="F218" s="1">
         <v>46258</v>
       </c>
       <c r="G218" s="1">
-        <v>46258</v>
+        <v>46261</v>
       </c>
     </row>
     <row r="219" spans="1:7" x14ac:dyDescent="0.2">
@@ -8072,16 +7907,16 @@
         <v>0</v>
       </c>
       <c r="B219" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="C219" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D219" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="E219" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="F219" s="1">
         <v>46258</v>
@@ -8095,16 +7930,16 @@
         <v>0</v>
       </c>
       <c r="B220" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="C220" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D220" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="E220" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="F220" s="1">
         <v>46258</v>
@@ -8118,16 +7953,16 @@
         <v>0</v>
       </c>
       <c r="B221" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="C221" t="s">
         <v>2</v>
       </c>
       <c r="D221" t="s">
-        <v>314</v>
+        <v>461</v>
       </c>
       <c r="E221" t="s">
-        <v>315</v>
+        <v>462</v>
       </c>
       <c r="F221" s="1">
         <v>46258</v>
@@ -8141,22 +7976,22 @@
         <v>0</v>
       </c>
       <c r="B222" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="C222" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D222" t="s">
-        <v>158</v>
+        <v>454</v>
       </c>
       <c r="E222" t="s">
-        <v>159</v>
+        <v>455</v>
       </c>
       <c r="F222" s="1">
         <v>46258</v>
       </c>
       <c r="G222" s="1">
-        <v>46258</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="223" spans="1:7" x14ac:dyDescent="0.2">
@@ -8164,22 +7999,22 @@
         <v>0</v>
       </c>
       <c r="B223" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="C223" t="s">
         <v>80</v>
       </c>
       <c r="D223" t="s">
-        <v>417</v>
+        <v>299</v>
       </c>
       <c r="E223" t="s">
-        <v>418</v>
+        <v>300</v>
       </c>
       <c r="F223" s="1">
         <v>46258</v>
       </c>
       <c r="G223" s="1">
-        <v>46258</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="224" spans="1:7" x14ac:dyDescent="0.2">
@@ -8187,22 +8022,22 @@
         <v>0</v>
       </c>
       <c r="B224" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="C224" t="s">
         <v>80</v>
       </c>
       <c r="D224" t="s">
-        <v>359</v>
+        <v>299</v>
       </c>
       <c r="E224" t="s">
-        <v>360</v>
+        <v>300</v>
       </c>
       <c r="F224" s="1">
         <v>46258</v>
       </c>
       <c r="G224" s="1">
-        <v>46258</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.2">
@@ -8210,22 +8045,22 @@
         <v>0</v>
       </c>
       <c r="B225" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="C225" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D225" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="E225" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="F225" s="1">
         <v>46258</v>
       </c>
       <c r="G225" s="1">
-        <v>46259</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="226" spans="1:7" x14ac:dyDescent="0.2">
@@ -8233,16 +8068,16 @@
         <v>0</v>
       </c>
       <c r="B226" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="C226" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D226" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="E226" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="F226" s="1">
         <v>46258</v>
@@ -8256,22 +8091,22 @@
         <v>0</v>
       </c>
       <c r="B227" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="C227" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D227" t="s">
-        <v>274</v>
+        <v>127</v>
       </c>
       <c r="E227" t="s">
-        <v>275</v>
+        <v>128</v>
       </c>
       <c r="F227" s="1">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="G227" s="1">
-        <v>46259</v>
+        <v>46261</v>
       </c>
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.2">
@@ -8279,22 +8114,22 @@
         <v>0</v>
       </c>
       <c r="B228" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="C228" t="s">
         <v>80</v>
       </c>
       <c r="D228" t="s">
-        <v>470</v>
+        <v>98</v>
       </c>
       <c r="E228" t="s">
-        <v>471</v>
+        <v>99</v>
       </c>
       <c r="F228" s="1">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="G228" s="1">
-        <v>46258</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="229" spans="1:7" x14ac:dyDescent="0.2">
@@ -8302,22 +8137,22 @@
         <v>0</v>
       </c>
       <c r="B229" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="C229" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D229" t="s">
-        <v>470</v>
+        <v>284</v>
       </c>
       <c r="E229" t="s">
-        <v>471</v>
+        <v>285</v>
       </c>
       <c r="F229" s="1">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="G229" s="1">
-        <v>46258</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="230" spans="1:7" x14ac:dyDescent="0.2">
@@ -8325,22 +8160,22 @@
         <v>0</v>
       </c>
       <c r="B230" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="C230" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D230" t="s">
-        <v>474</v>
+        <v>37</v>
       </c>
       <c r="E230" t="s">
-        <v>475</v>
+        <v>38</v>
       </c>
       <c r="F230" s="1">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="G230" s="1">
-        <v>46261</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="231" spans="1:7" x14ac:dyDescent="0.2">
@@ -8351,19 +8186,19 @@
         <v>476</v>
       </c>
       <c r="C231" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D231" t="s">
-        <v>470</v>
+        <v>37</v>
       </c>
       <c r="E231" t="s">
-        <v>471</v>
+        <v>38</v>
       </c>
       <c r="F231" s="1">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="G231" s="1">
-        <v>46258</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="232" spans="1:7" x14ac:dyDescent="0.2">
@@ -8374,16 +8209,16 @@
         <v>477</v>
       </c>
       <c r="C232" t="s">
-        <v>80</v>
+        <v>6</v>
       </c>
       <c r="D232" t="s">
-        <v>478</v>
+        <v>37</v>
       </c>
       <c r="E232" t="s">
-        <v>479</v>
+        <v>38</v>
       </c>
       <c r="F232" s="1">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="G232" s="1">
         <v>46259</v>
@@ -8394,19 +8229,19 @@
         <v>0</v>
       </c>
       <c r="B233" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="C233" t="s">
         <v>2</v>
       </c>
       <c r="D233" t="s">
-        <v>481</v>
+        <v>37</v>
       </c>
       <c r="E233" t="s">
-        <v>482</v>
+        <v>38</v>
       </c>
       <c r="F233" s="1">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="G233" s="1">
         <v>46259</v>
@@ -8417,19 +8252,19 @@
         <v>0</v>
       </c>
       <c r="B234" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="C234" t="s">
         <v>80</v>
       </c>
       <c r="D234" t="s">
-        <v>474</v>
+        <v>98</v>
       </c>
       <c r="E234" t="s">
-        <v>475</v>
+        <v>99</v>
       </c>
       <c r="F234" s="1">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="G234" s="1">
         <v>46259</v>
@@ -8440,19 +8275,19 @@
         <v>0</v>
       </c>
       <c r="B235" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="C235" t="s">
-        <v>80</v>
+        <v>6</v>
       </c>
       <c r="D235" t="s">
-        <v>407</v>
+        <v>481</v>
       </c>
       <c r="E235" t="s">
-        <v>408</v>
+        <v>482</v>
       </c>
       <c r="F235" s="1">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="G235" s="1">
         <v>46259</v>
@@ -8463,22 +8298,22 @@
         <v>0</v>
       </c>
       <c r="B236" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="C236" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D236" t="s">
-        <v>486</v>
+        <v>105</v>
       </c>
       <c r="E236" t="s">
-        <v>487</v>
+        <v>106</v>
       </c>
       <c r="F236" s="1">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="G236" s="1">
-        <v>46259</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.2">
@@ -8486,19 +8321,19 @@
         <v>0</v>
       </c>
       <c r="B237" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="C237" t="s">
         <v>80</v>
       </c>
       <c r="D237" t="s">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="E237" t="s">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="F237" s="1">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="G237" s="1">
         <v>46259</v>
@@ -8509,19 +8344,19 @@
         <v>0</v>
       </c>
       <c r="B238" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="C238" t="s">
         <v>80</v>
       </c>
       <c r="D238" t="s">
-        <v>299</v>
+        <v>171</v>
       </c>
       <c r="E238" t="s">
-        <v>300</v>
+        <v>172</v>
       </c>
       <c r="F238" s="1">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="G238" s="1">
         <v>46259</v>
@@ -8532,22 +8367,22 @@
         <v>0</v>
       </c>
       <c r="B239" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="C239" t="s">
         <v>80</v>
       </c>
       <c r="D239" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="E239" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="F239" s="1">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="G239" s="1">
-        <v>46260</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="240" spans="1:7" x14ac:dyDescent="0.2">
@@ -8555,19 +8390,19 @@
         <v>0</v>
       </c>
       <c r="B240" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="C240" t="s">
         <v>80</v>
       </c>
       <c r="D240" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="E240" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="F240" s="1">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="G240" s="1">
         <v>46259</v>
@@ -8578,22 +8413,22 @@
         <v>0</v>
       </c>
       <c r="B241" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="C241" t="s">
         <v>80</v>
       </c>
       <c r="D241" t="s">
-        <v>127</v>
+        <v>493</v>
       </c>
       <c r="E241" t="s">
-        <v>128</v>
+        <v>494</v>
       </c>
       <c r="F241" s="1">
         <v>46259</v>
       </c>
       <c r="G241" s="1">
-        <v>46261</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="242" spans="1:7" x14ac:dyDescent="0.2">
@@ -8601,22 +8436,22 @@
         <v>0</v>
       </c>
       <c r="B242" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="C242" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D242" t="s">
-        <v>98</v>
+        <v>13</v>
       </c>
       <c r="E242" t="s">
-        <v>99</v>
+        <v>14</v>
       </c>
       <c r="F242" s="1">
         <v>46259</v>
       </c>
       <c r="G242" s="1">
-        <v>46259</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="243" spans="1:7" x14ac:dyDescent="0.2">
@@ -8624,22 +8459,22 @@
         <v>0</v>
       </c>
       <c r="B243" t="s">
+        <v>496</v>
+      </c>
+      <c r="C243" t="s">
+        <v>80</v>
+      </c>
+      <c r="D243" t="s">
+        <v>497</v>
+      </c>
+      <c r="E243" t="s">
         <v>498</v>
-      </c>
-      <c r="C243" t="s">
-        <v>2</v>
-      </c>
-      <c r="D243" t="s">
-        <v>284</v>
-      </c>
-      <c r="E243" t="s">
-        <v>285</v>
       </c>
       <c r="F243" s="1">
         <v>46259</v>
       </c>
       <c r="G243" s="1">
-        <v>46260</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="244" spans="1:7" x14ac:dyDescent="0.2">
@@ -8653,10 +8488,10 @@
         <v>80</v>
       </c>
       <c r="D244" t="s">
-        <v>500</v>
+        <v>419</v>
       </c>
       <c r="E244" t="s">
-        <v>501</v>
+        <v>420</v>
       </c>
       <c r="F244" s="1">
         <v>46259</v>
@@ -8670,16 +8505,16 @@
         <v>0</v>
       </c>
       <c r="B245" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="C245" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D245" t="s">
-        <v>37</v>
+        <v>437</v>
       </c>
       <c r="E245" t="s">
-        <v>38</v>
+        <v>438</v>
       </c>
       <c r="F245" s="1">
         <v>46259</v>
@@ -8693,16 +8528,16 @@
         <v>0</v>
       </c>
       <c r="B246" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="C246" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D246" t="s">
-        <v>37</v>
+        <v>402</v>
       </c>
       <c r="E246" t="s">
-        <v>38</v>
+        <v>403</v>
       </c>
       <c r="F246" s="1">
         <v>46259</v>
@@ -8716,16 +8551,16 @@
         <v>0</v>
       </c>
       <c r="B247" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="C247" t="s">
-        <v>6</v>
+        <v>80</v>
       </c>
       <c r="D247" t="s">
-        <v>37</v>
+        <v>98</v>
       </c>
       <c r="E247" t="s">
-        <v>38</v>
+        <v>99</v>
       </c>
       <c r="F247" s="1">
         <v>46259</v>
@@ -8739,22 +8574,22 @@
         <v>0</v>
       </c>
       <c r="B248" t="s">
+        <v>503</v>
+      </c>
+      <c r="C248" t="s">
+        <v>2</v>
+      </c>
+      <c r="D248" t="s">
+        <v>504</v>
+      </c>
+      <c r="E248" t="s">
         <v>505</v>
-      </c>
-      <c r="C248" t="s">
-        <v>2</v>
-      </c>
-      <c r="D248" t="s">
-        <v>37</v>
-      </c>
-      <c r="E248" t="s">
-        <v>38</v>
       </c>
       <c r="F248" s="1">
         <v>46259</v>
       </c>
       <c r="G248" s="1">
-        <v>46259</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="249" spans="1:7" x14ac:dyDescent="0.2">
@@ -8768,10 +8603,10 @@
         <v>80</v>
       </c>
       <c r="D249" t="s">
-        <v>98</v>
+        <v>507</v>
       </c>
       <c r="E249" t="s">
-        <v>99</v>
+        <v>508</v>
       </c>
       <c r="F249" s="1">
         <v>46259</v>
@@ -8785,22 +8620,22 @@
         <v>0</v>
       </c>
       <c r="B250" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="C250" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D250" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="E250" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="F250" s="1">
         <v>46259</v>
       </c>
       <c r="G250" s="1">
-        <v>46259</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="251" spans="1:7" x14ac:dyDescent="0.2">
@@ -8808,16 +8643,16 @@
         <v>0</v>
       </c>
       <c r="B251" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="C251" t="s">
-        <v>6</v>
+        <v>80</v>
       </c>
       <c r="D251" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="E251" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="F251" s="1">
         <v>46259</v>
@@ -8831,22 +8666,22 @@
         <v>0</v>
       </c>
       <c r="B252" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="C252" t="s">
         <v>80</v>
       </c>
       <c r="D252" t="s">
-        <v>105</v>
+        <v>135</v>
       </c>
       <c r="E252" t="s">
-        <v>106</v>
+        <v>136</v>
       </c>
       <c r="F252" s="1">
         <v>46259</v>
       </c>
       <c r="G252" s="1">
-        <v>46260</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="253" spans="1:7" x14ac:dyDescent="0.2">
@@ -8854,22 +8689,22 @@
         <v>0</v>
       </c>
       <c r="B253" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="C253" t="s">
         <v>80</v>
       </c>
       <c r="D253" t="s">
-        <v>306</v>
+        <v>344</v>
       </c>
       <c r="E253" t="s">
-        <v>307</v>
+        <v>345</v>
       </c>
       <c r="F253" s="1">
         <v>46259</v>
       </c>
       <c r="G253" s="1">
-        <v>46259</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="254" spans="1:7" x14ac:dyDescent="0.2">
@@ -8877,16 +8712,16 @@
         <v>0</v>
       </c>
       <c r="B254" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="C254" t="s">
         <v>80</v>
       </c>
       <c r="D254" t="s">
-        <v>516</v>
+        <v>77</v>
       </c>
       <c r="E254" t="s">
-        <v>517</v>
+        <v>78</v>
       </c>
       <c r="F254" s="1">
         <v>46259</v>
@@ -8906,10 +8741,10 @@
         <v>80</v>
       </c>
       <c r="D255" t="s">
-        <v>171</v>
+        <v>16</v>
       </c>
       <c r="E255" t="s">
-        <v>172</v>
+        <v>17</v>
       </c>
       <c r="F255" s="1">
         <v>46259</v>
@@ -8929,10 +8764,10 @@
         <v>80</v>
       </c>
       <c r="D256" t="s">
-        <v>520</v>
+        <v>174</v>
       </c>
       <c r="E256" t="s">
-        <v>521</v>
+        <v>175</v>
       </c>
       <c r="F256" s="1">
         <v>46259</v>
@@ -8946,22 +8781,22 @@
         <v>0</v>
       </c>
       <c r="B257" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="C257" t="s">
         <v>80</v>
       </c>
       <c r="D257" t="s">
-        <v>523</v>
+        <v>28</v>
       </c>
       <c r="E257" t="s">
-        <v>524</v>
+        <v>29</v>
       </c>
       <c r="F257" s="1">
         <v>46259</v>
       </c>
       <c r="G257" s="1">
-        <v>46259</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="258" spans="1:7" x14ac:dyDescent="0.2">
@@ -8969,22 +8804,22 @@
         <v>0</v>
       </c>
       <c r="B258" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="C258" t="s">
         <v>80</v>
       </c>
       <c r="D258" t="s">
-        <v>526</v>
+        <v>155</v>
       </c>
       <c r="E258" t="s">
-        <v>527</v>
+        <v>156</v>
       </c>
       <c r="F258" s="1">
         <v>46259</v>
       </c>
       <c r="G258" s="1">
-        <v>46259</v>
+        <v>46261</v>
       </c>
     </row>
     <row r="259" spans="1:7" x14ac:dyDescent="0.2">
@@ -8992,22 +8827,22 @@
         <v>0</v>
       </c>
       <c r="B259" t="s">
-        <v>528</v>
+        <v>522</v>
       </c>
       <c r="C259" t="s">
         <v>80</v>
       </c>
       <c r="D259" t="s">
-        <v>529</v>
+        <v>467</v>
       </c>
       <c r="E259" t="s">
-        <v>530</v>
+        <v>468</v>
       </c>
       <c r="F259" s="1">
         <v>46259</v>
       </c>
       <c r="G259" s="1">
-        <v>46259</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="260" spans="1:7" x14ac:dyDescent="0.2">
@@ -9015,22 +8850,22 @@
         <v>0</v>
       </c>
       <c r="B260" t="s">
-        <v>531</v>
+        <v>523</v>
       </c>
       <c r="C260" t="s">
         <v>80</v>
       </c>
       <c r="D260" t="s">
-        <v>532</v>
+        <v>524</v>
       </c>
       <c r="E260" t="s">
-        <v>533</v>
+        <v>525</v>
       </c>
       <c r="F260" s="1">
         <v>46259</v>
       </c>
       <c r="G260" s="1">
-        <v>46259</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="261" spans="1:7" x14ac:dyDescent="0.2">
@@ -9038,22 +8873,22 @@
         <v>0</v>
       </c>
       <c r="B261" t="s">
-        <v>534</v>
+        <v>526</v>
       </c>
       <c r="C261" t="s">
         <v>80</v>
       </c>
       <c r="D261" t="s">
-        <v>535</v>
+        <v>98</v>
       </c>
       <c r="E261" t="s">
-        <v>536</v>
+        <v>99</v>
       </c>
       <c r="F261" s="1">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="G261" s="1">
-        <v>46259</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="262" spans="1:7" x14ac:dyDescent="0.2">
@@ -9061,22 +8896,22 @@
         <v>0</v>
       </c>
       <c r="B262" t="s">
-        <v>537</v>
+        <v>527</v>
       </c>
       <c r="C262" t="s">
         <v>80</v>
       </c>
       <c r="D262" t="s">
-        <v>402</v>
+        <v>98</v>
       </c>
       <c r="E262" t="s">
-        <v>403</v>
+        <v>99</v>
       </c>
       <c r="F262" s="1">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="G262" s="1">
-        <v>46259</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="263" spans="1:7" x14ac:dyDescent="0.2">
@@ -9084,19 +8919,19 @@
         <v>0</v>
       </c>
       <c r="B263" t="s">
-        <v>538</v>
+        <v>528</v>
       </c>
       <c r="C263" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D263" t="s">
-        <v>13</v>
+        <v>529</v>
       </c>
       <c r="E263" t="s">
-        <v>14</v>
+        <v>530</v>
       </c>
       <c r="F263" s="1">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="G263" s="1">
         <v>46260</v>
@@ -9107,22 +8942,22 @@
         <v>0</v>
       </c>
       <c r="B264" t="s">
-        <v>539</v>
+        <v>531</v>
       </c>
       <c r="C264" t="s">
         <v>80</v>
       </c>
       <c r="D264" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E264" t="s">
-        <v>541</v>
+        <v>533</v>
       </c>
       <c r="F264" s="1">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="G264" s="1">
-        <v>46259</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="265" spans="1:7" x14ac:dyDescent="0.2">
@@ -9130,22 +8965,22 @@
         <v>0</v>
       </c>
       <c r="B265" t="s">
-        <v>542</v>
+        <v>534</v>
       </c>
       <c r="C265" t="s">
         <v>80</v>
       </c>
       <c r="D265" t="s">
-        <v>543</v>
+        <v>16</v>
       </c>
       <c r="E265" t="s">
-        <v>544</v>
+        <v>17</v>
       </c>
       <c r="F265" s="1">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="G265" s="1">
-        <v>46259</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="266" spans="1:7" x14ac:dyDescent="0.2">
@@ -9153,22 +8988,22 @@
         <v>0</v>
       </c>
       <c r="B266" t="s">
-        <v>545</v>
+        <v>535</v>
       </c>
       <c r="C266" t="s">
         <v>80</v>
       </c>
       <c r="D266" t="s">
-        <v>435</v>
+        <v>536</v>
       </c>
       <c r="E266" t="s">
-        <v>436</v>
+        <v>537</v>
       </c>
       <c r="F266" s="1">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="G266" s="1">
-        <v>46259</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="267" spans="1:7" x14ac:dyDescent="0.2">
@@ -9176,22 +9011,22 @@
         <v>0</v>
       </c>
       <c r="B267" t="s">
-        <v>546</v>
+        <v>538</v>
       </c>
       <c r="C267" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D267" t="s">
-        <v>547</v>
+        <v>536</v>
       </c>
       <c r="E267" t="s">
-        <v>548</v>
+        <v>537</v>
       </c>
       <c r="F267" s="1">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="G267" s="1">
-        <v>46259</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="268" spans="1:7" x14ac:dyDescent="0.2">
@@ -9199,22 +9034,22 @@
         <v>0</v>
       </c>
       <c r="B268" t="s">
-        <v>549</v>
+        <v>539</v>
       </c>
       <c r="C268" t="s">
         <v>80</v>
       </c>
       <c r="D268" t="s">
-        <v>456</v>
+        <v>426</v>
       </c>
       <c r="E268" t="s">
-        <v>457</v>
+        <v>427</v>
       </c>
       <c r="F268" s="1">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="G268" s="1">
-        <v>46259</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="269" spans="1:7" x14ac:dyDescent="0.2">
@@ -9222,22 +9057,22 @@
         <v>0</v>
       </c>
       <c r="B269" t="s">
-        <v>550</v>
+        <v>540</v>
       </c>
       <c r="C269" t="s">
         <v>80</v>
       </c>
       <c r="D269" t="s">
-        <v>411</v>
+        <v>467</v>
       </c>
       <c r="E269" t="s">
-        <v>412</v>
+        <v>468</v>
       </c>
       <c r="F269" s="1">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="G269" s="1">
-        <v>46259</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="270" spans="1:7" x14ac:dyDescent="0.2">
@@ -9245,22 +9080,22 @@
         <v>0</v>
       </c>
       <c r="B270" t="s">
-        <v>551</v>
+        <v>541</v>
       </c>
       <c r="C270" t="s">
         <v>80</v>
       </c>
       <c r="D270" t="s">
-        <v>98</v>
+        <v>16</v>
       </c>
       <c r="E270" t="s">
-        <v>99</v>
+        <v>17</v>
       </c>
       <c r="F270" s="1">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="G270" s="1">
-        <v>46259</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="271" spans="1:7" x14ac:dyDescent="0.2">
@@ -9268,22 +9103,22 @@
         <v>0</v>
       </c>
       <c r="B271" t="s">
-        <v>552</v>
+        <v>542</v>
       </c>
       <c r="C271" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D271" t="s">
-        <v>553</v>
+        <v>132</v>
       </c>
       <c r="E271" t="s">
-        <v>554</v>
+        <v>133</v>
       </c>
       <c r="F271" s="1">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="G271" s="1">
-        <v>46259</v>
+        <v>46261</v>
       </c>
     </row>
     <row r="272" spans="1:7" x14ac:dyDescent="0.2">
@@ -9291,19 +9126,19 @@
         <v>0</v>
       </c>
       <c r="B272" t="s">
-        <v>555</v>
+        <v>543</v>
       </c>
       <c r="C272" t="s">
         <v>80</v>
       </c>
       <c r="D272" t="s">
-        <v>553</v>
+        <v>544</v>
       </c>
       <c r="E272" t="s">
-        <v>554</v>
+        <v>545</v>
       </c>
       <c r="F272" s="1">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="G272" s="1">
         <v>46260</v>
@@ -9314,22 +9149,22 @@
         <v>0</v>
       </c>
       <c r="B273" t="s">
-        <v>556</v>
+        <v>546</v>
       </c>
       <c r="C273" t="s">
         <v>80</v>
       </c>
       <c r="D273" t="s">
-        <v>557</v>
+        <v>507</v>
       </c>
       <c r="E273" t="s">
-        <v>558</v>
+        <v>508</v>
       </c>
       <c r="F273" s="1">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="G273" s="1">
-        <v>46259</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="274" spans="1:7" x14ac:dyDescent="0.2">
@@ -9337,22 +9172,22 @@
         <v>0</v>
       </c>
       <c r="B274" t="s">
-        <v>559</v>
+        <v>547</v>
       </c>
       <c r="C274" t="s">
         <v>80</v>
       </c>
       <c r="D274" t="s">
-        <v>332</v>
+        <v>548</v>
       </c>
       <c r="E274" t="s">
-        <v>333</v>
+        <v>549</v>
       </c>
       <c r="F274" s="1">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="G274" s="1">
-        <v>46259</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="275" spans="1:7" x14ac:dyDescent="0.2">
@@ -9360,22 +9195,22 @@
         <v>0</v>
       </c>
       <c r="B275" t="s">
-        <v>560</v>
+        <v>550</v>
       </c>
       <c r="C275" t="s">
         <v>80</v>
       </c>
       <c r="D275" t="s">
-        <v>561</v>
+        <v>551</v>
       </c>
       <c r="E275" t="s">
-        <v>562</v>
+        <v>552</v>
       </c>
       <c r="F275" s="1">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="G275" s="1">
-        <v>46259</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="276" spans="1:7" x14ac:dyDescent="0.2">
@@ -9383,22 +9218,22 @@
         <v>0</v>
       </c>
       <c r="B276" t="s">
-        <v>563</v>
+        <v>553</v>
       </c>
       <c r="C276" t="s">
         <v>80</v>
       </c>
       <c r="D276" t="s">
-        <v>564</v>
+        <v>359</v>
       </c>
       <c r="E276" t="s">
-        <v>565</v>
+        <v>360</v>
       </c>
       <c r="F276" s="1">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="G276" s="1">
-        <v>46259</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="277" spans="1:7" x14ac:dyDescent="0.2">
@@ -9406,19 +9241,19 @@
         <v>0</v>
       </c>
       <c r="B277" t="s">
-        <v>566</v>
+        <v>554</v>
       </c>
       <c r="C277" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D277" t="s">
-        <v>567</v>
+        <v>371</v>
       </c>
       <c r="E277" t="s">
-        <v>568</v>
+        <v>372</v>
       </c>
       <c r="F277" s="1">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="G277" s="1">
         <v>46260</v>
@@ -9429,22 +9264,22 @@
         <v>0</v>
       </c>
       <c r="B278" t="s">
-        <v>569</v>
+        <v>555</v>
       </c>
       <c r="C278" t="s">
         <v>80</v>
       </c>
       <c r="D278" t="s">
-        <v>570</v>
+        <v>98</v>
       </c>
       <c r="E278" t="s">
-        <v>571</v>
+        <v>99</v>
       </c>
       <c r="F278" s="1">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="G278" s="1">
-        <v>46259</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="279" spans="1:7" x14ac:dyDescent="0.2">
@@ -9452,22 +9287,22 @@
         <v>0</v>
       </c>
       <c r="B279" t="s">
-        <v>572</v>
+        <v>556</v>
       </c>
       <c r="C279" t="s">
         <v>80</v>
       </c>
       <c r="D279" t="s">
-        <v>573</v>
+        <v>557</v>
       </c>
       <c r="E279" t="s">
-        <v>574</v>
+        <v>558</v>
       </c>
       <c r="F279" s="1">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="G279" s="1">
-        <v>46259</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="280" spans="1:7" x14ac:dyDescent="0.2">
@@ -9475,22 +9310,22 @@
         <v>0</v>
       </c>
       <c r="B280" t="s">
-        <v>575</v>
+        <v>559</v>
       </c>
       <c r="C280" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D280" t="s">
-        <v>135</v>
+        <v>560</v>
       </c>
       <c r="E280" t="s">
-        <v>136</v>
+        <v>561</v>
       </c>
       <c r="F280" s="1">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="G280" s="1">
-        <v>46259</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="281" spans="1:7" x14ac:dyDescent="0.2">
@@ -9498,19 +9333,19 @@
         <v>0</v>
       </c>
       <c r="B281" t="s">
-        <v>576</v>
+        <v>562</v>
       </c>
       <c r="C281" t="s">
         <v>80</v>
       </c>
       <c r="D281" t="s">
-        <v>344</v>
+        <v>563</v>
       </c>
       <c r="E281" t="s">
-        <v>345</v>
+        <v>564</v>
       </c>
       <c r="F281" s="1">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="G281" s="1">
         <v>46260</v>
@@ -9521,22 +9356,22 @@
         <v>0</v>
       </c>
       <c r="B282" t="s">
-        <v>577</v>
+        <v>565</v>
       </c>
       <c r="C282" t="s">
         <v>80</v>
       </c>
       <c r="D282" t="s">
-        <v>77</v>
+        <v>566</v>
       </c>
       <c r="E282" t="s">
-        <v>78</v>
+        <v>567</v>
       </c>
       <c r="F282" s="1">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="G282" s="1">
-        <v>46259</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="283" spans="1:7" x14ac:dyDescent="0.2">
@@ -9544,22 +9379,22 @@
         <v>0</v>
       </c>
       <c r="B283" t="s">
-        <v>578</v>
+        <v>568</v>
       </c>
       <c r="C283" t="s">
         <v>80</v>
       </c>
       <c r="D283" t="s">
-        <v>68</v>
+        <v>569</v>
       </c>
       <c r="E283" t="s">
-        <v>69</v>
+        <v>570</v>
       </c>
       <c r="F283" s="1">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="G283" s="1">
-        <v>46259</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="284" spans="1:7" x14ac:dyDescent="0.2">
@@ -9567,22 +9402,22 @@
         <v>0</v>
       </c>
       <c r="B284" t="s">
-        <v>579</v>
+        <v>571</v>
       </c>
       <c r="C284" t="s">
         <v>80</v>
       </c>
       <c r="D284" t="s">
-        <v>580</v>
+        <v>569</v>
       </c>
       <c r="E284" t="s">
-        <v>581</v>
+        <v>570</v>
       </c>
       <c r="F284" s="1">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="G284" s="1">
-        <v>46259</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="285" spans="1:7" x14ac:dyDescent="0.2">
@@ -9590,22 +9425,22 @@
         <v>0</v>
       </c>
       <c r="B285" t="s">
-        <v>582</v>
+        <v>572</v>
       </c>
       <c r="C285" t="s">
         <v>80</v>
       </c>
       <c r="D285" t="s">
-        <v>16</v>
+        <v>544</v>
       </c>
       <c r="E285" t="s">
-        <v>17</v>
+        <v>545</v>
       </c>
       <c r="F285" s="1">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="G285" s="1">
-        <v>46259</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="286" spans="1:7" x14ac:dyDescent="0.2">
@@ -9613,22 +9448,22 @@
         <v>0</v>
       </c>
       <c r="B286" t="s">
-        <v>583</v>
+        <v>573</v>
       </c>
       <c r="C286" t="s">
         <v>80</v>
       </c>
       <c r="D286" t="s">
-        <v>584</v>
+        <v>371</v>
       </c>
       <c r="E286" t="s">
-        <v>585</v>
+        <v>372</v>
       </c>
       <c r="F286" s="1">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="G286" s="1">
-        <v>46259</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="287" spans="1:7" x14ac:dyDescent="0.2">
@@ -9636,22 +9471,22 @@
         <v>0</v>
       </c>
       <c r="B287" t="s">
-        <v>586</v>
+        <v>574</v>
       </c>
       <c r="C287" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D287" t="s">
-        <v>174</v>
+        <v>575</v>
       </c>
       <c r="E287" t="s">
-        <v>175</v>
+        <v>576</v>
       </c>
       <c r="F287" s="1">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="G287" s="1">
-        <v>46259</v>
+        <v>46261</v>
       </c>
     </row>
     <row r="288" spans="1:7" x14ac:dyDescent="0.2">
@@ -9659,19 +9494,19 @@
         <v>0</v>
       </c>
       <c r="B288" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="C288" t="s">
         <v>80</v>
       </c>
       <c r="D288" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="E288" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="F288" s="1">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="G288" s="1">
         <v>46260</v>
@@ -9682,19 +9517,19 @@
         <v>0</v>
       </c>
       <c r="B289" t="s">
-        <v>588</v>
+        <v>578</v>
       </c>
       <c r="C289" t="s">
         <v>80</v>
       </c>
       <c r="D289" t="s">
-        <v>155</v>
+        <v>579</v>
       </c>
       <c r="E289" t="s">
-        <v>156</v>
+        <v>580</v>
       </c>
       <c r="F289" s="1">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="G289" s="1">
         <v>46261</v>
@@ -9705,22 +9540,22 @@
         <v>0</v>
       </c>
       <c r="B290" t="s">
-        <v>589</v>
+        <v>581</v>
       </c>
       <c r="C290" t="s">
         <v>80</v>
       </c>
       <c r="D290" t="s">
-        <v>491</v>
+        <v>16</v>
       </c>
       <c r="E290" t="s">
-        <v>492</v>
+        <v>17</v>
       </c>
       <c r="F290" s="1">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="G290" s="1">
-        <v>46260</v>
+        <v>46261</v>
       </c>
     </row>
     <row r="291" spans="1:7" x14ac:dyDescent="0.2">
@@ -9728,22 +9563,22 @@
         <v>0</v>
       </c>
       <c r="B291" t="s">
-        <v>590</v>
+        <v>582</v>
       </c>
       <c r="C291" t="s">
         <v>80</v>
       </c>
       <c r="D291" t="s">
-        <v>591</v>
+        <v>317</v>
       </c>
       <c r="E291" t="s">
-        <v>592</v>
+        <v>318</v>
       </c>
       <c r="F291" s="1">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="G291" s="1">
-        <v>46260</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="292" spans="1:7" x14ac:dyDescent="0.2">
@@ -9751,22 +9586,22 @@
         <v>0</v>
       </c>
       <c r="B292" t="s">
-        <v>593</v>
+        <v>583</v>
       </c>
       <c r="C292" t="s">
         <v>80</v>
       </c>
       <c r="D292" t="s">
-        <v>98</v>
+        <v>37</v>
       </c>
       <c r="E292" t="s">
-        <v>99</v>
+        <v>38</v>
       </c>
       <c r="F292" s="1">
         <v>46260</v>
       </c>
       <c r="G292" s="1">
-        <v>46260</v>
+        <v>46261</v>
       </c>
     </row>
     <row r="293" spans="1:7" x14ac:dyDescent="0.2">
@@ -9774,22 +9609,22 @@
         <v>0</v>
       </c>
       <c r="B293" t="s">
-        <v>594</v>
+        <v>584</v>
       </c>
       <c r="C293" t="s">
         <v>80</v>
       </c>
       <c r="D293" t="s">
-        <v>98</v>
+        <v>37</v>
       </c>
       <c r="E293" t="s">
-        <v>99</v>
+        <v>38</v>
       </c>
       <c r="F293" s="1">
         <v>46260</v>
       </c>
       <c r="G293" s="1">
-        <v>46260</v>
+        <v>46261</v>
       </c>
     </row>
     <row r="294" spans="1:7" x14ac:dyDescent="0.2">
@@ -9797,22 +9632,22 @@
         <v>0</v>
       </c>
       <c r="B294" t="s">
-        <v>595</v>
+        <v>585</v>
       </c>
       <c r="C294" t="s">
         <v>80</v>
       </c>
       <c r="D294" t="s">
-        <v>596</v>
+        <v>37</v>
       </c>
       <c r="E294" t="s">
-        <v>597</v>
+        <v>38</v>
       </c>
       <c r="F294" s="1">
         <v>46260</v>
       </c>
       <c r="G294" s="1">
-        <v>46260</v>
+        <v>46261</v>
       </c>
     </row>
     <row r="295" spans="1:7" x14ac:dyDescent="0.2">
@@ -9820,22 +9655,22 @@
         <v>0</v>
       </c>
       <c r="B295" t="s">
-        <v>598</v>
+        <v>586</v>
       </c>
       <c r="C295" t="s">
         <v>80</v>
       </c>
       <c r="D295" t="s">
-        <v>599</v>
+        <v>37</v>
       </c>
       <c r="E295" t="s">
-        <v>600</v>
+        <v>38</v>
       </c>
       <c r="F295" s="1">
         <v>46260</v>
       </c>
       <c r="G295" s="1">
-        <v>46260</v>
+        <v>46261</v>
       </c>
     </row>
     <row r="296" spans="1:7" x14ac:dyDescent="0.2">
@@ -9843,22 +9678,22 @@
         <v>0</v>
       </c>
       <c r="B296" t="s">
-        <v>601</v>
+        <v>587</v>
       </c>
       <c r="C296" t="s">
         <v>80</v>
       </c>
       <c r="D296" t="s">
-        <v>602</v>
+        <v>37</v>
       </c>
       <c r="E296" t="s">
-        <v>603</v>
+        <v>38</v>
       </c>
       <c r="F296" s="1">
         <v>46260</v>
       </c>
       <c r="G296" s="1">
-        <v>46260</v>
+        <v>46261</v>
       </c>
     </row>
     <row r="297" spans="1:7" x14ac:dyDescent="0.2">
@@ -9866,22 +9701,22 @@
         <v>0</v>
       </c>
       <c r="B297" t="s">
-        <v>604</v>
+        <v>588</v>
       </c>
       <c r="C297" t="s">
         <v>80</v>
       </c>
       <c r="D297" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="E297" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="F297" s="1">
         <v>46260</v>
       </c>
       <c r="G297" s="1">
-        <v>46260</v>
+        <v>46261</v>
       </c>
     </row>
     <row r="298" spans="1:7" x14ac:dyDescent="0.2">
@@ -9889,22 +9724,22 @@
         <v>0</v>
       </c>
       <c r="B298" t="s">
-        <v>605</v>
+        <v>589</v>
       </c>
       <c r="C298" t="s">
         <v>80</v>
       </c>
       <c r="D298" t="s">
-        <v>606</v>
+        <v>37</v>
       </c>
       <c r="E298" t="s">
-        <v>607</v>
+        <v>38</v>
       </c>
       <c r="F298" s="1">
         <v>46260</v>
       </c>
       <c r="G298" s="1">
-        <v>46260</v>
+        <v>46261</v>
       </c>
     </row>
     <row r="299" spans="1:7" x14ac:dyDescent="0.2">
@@ -9912,22 +9747,22 @@
         <v>0</v>
       </c>
       <c r="B299" t="s">
-        <v>608</v>
+        <v>590</v>
       </c>
       <c r="C299" t="s">
         <v>80</v>
       </c>
       <c r="D299" t="s">
-        <v>606</v>
+        <v>37</v>
       </c>
       <c r="E299" t="s">
-        <v>607</v>
+        <v>38</v>
       </c>
       <c r="F299" s="1">
         <v>46260</v>
       </c>
       <c r="G299" s="1">
-        <v>46260</v>
+        <v>46261</v>
       </c>
     </row>
     <row r="300" spans="1:7" x14ac:dyDescent="0.2">
@@ -9935,22 +9770,22 @@
         <v>0</v>
       </c>
       <c r="B300" t="s">
-        <v>609</v>
+        <v>591</v>
       </c>
       <c r="C300" t="s">
         <v>80</v>
       </c>
       <c r="D300" t="s">
-        <v>610</v>
+        <v>37</v>
       </c>
       <c r="E300" t="s">
-        <v>611</v>
+        <v>38</v>
       </c>
       <c r="F300" s="1">
         <v>46260</v>
       </c>
       <c r="G300" s="1">
-        <v>46260</v>
+        <v>46261</v>
       </c>
     </row>
     <row r="301" spans="1:7" x14ac:dyDescent="0.2">
@@ -9958,22 +9793,22 @@
         <v>0</v>
       </c>
       <c r="B301" t="s">
-        <v>612</v>
+        <v>592</v>
       </c>
       <c r="C301" t="s">
         <v>80</v>
       </c>
       <c r="D301" t="s">
-        <v>599</v>
+        <v>37</v>
       </c>
       <c r="E301" t="s">
-        <v>600</v>
+        <v>38</v>
       </c>
       <c r="F301" s="1">
         <v>46260</v>
       </c>
       <c r="G301" s="1">
-        <v>46260</v>
+        <v>46261</v>
       </c>
     </row>
     <row r="302" spans="1:7" x14ac:dyDescent="0.2">
@@ -9981,22 +9816,22 @@
         <v>0</v>
       </c>
       <c r="B302" t="s">
-        <v>613</v>
+        <v>593</v>
       </c>
       <c r="C302" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D302" t="s">
-        <v>215</v>
+        <v>594</v>
       </c>
       <c r="E302" t="s">
-        <v>216</v>
+        <v>595</v>
       </c>
       <c r="F302" s="1">
         <v>46260</v>
       </c>
       <c r="G302" s="1">
-        <v>46260</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="303" spans="1:7" x14ac:dyDescent="0.2">
@@ -10004,22 +9839,22 @@
         <v>0</v>
       </c>
       <c r="B303" t="s">
-        <v>614</v>
+        <v>596</v>
       </c>
       <c r="C303" t="s">
         <v>80</v>
       </c>
       <c r="D303" t="s">
-        <v>445</v>
+        <v>597</v>
       </c>
       <c r="E303" t="s">
-        <v>446</v>
+        <v>598</v>
       </c>
       <c r="F303" s="1">
         <v>46260</v>
       </c>
       <c r="G303" s="1">
-        <v>46260</v>
+        <v>46261</v>
       </c>
     </row>
     <row r="304" spans="1:7" x14ac:dyDescent="0.2">
@@ -10027,22 +9862,22 @@
         <v>0</v>
       </c>
       <c r="B304" t="s">
-        <v>615</v>
+        <v>599</v>
       </c>
       <c r="C304" t="s">
         <v>80</v>
       </c>
       <c r="D304" t="s">
-        <v>491</v>
+        <v>600</v>
       </c>
       <c r="E304" t="s">
-        <v>492</v>
+        <v>601</v>
       </c>
       <c r="F304" s="1">
         <v>46260</v>
       </c>
       <c r="G304" s="1">
-        <v>46260</v>
+        <v>46261</v>
       </c>
     </row>
     <row r="305" spans="1:7" x14ac:dyDescent="0.2">
@@ -10050,22 +9885,22 @@
         <v>0</v>
       </c>
       <c r="B305" t="s">
-        <v>616</v>
+        <v>602</v>
       </c>
       <c r="C305" t="s">
         <v>80</v>
       </c>
       <c r="D305" t="s">
-        <v>617</v>
+        <v>603</v>
       </c>
       <c r="E305" t="s">
-        <v>618</v>
+        <v>604</v>
       </c>
       <c r="F305" s="1">
         <v>46260</v>
       </c>
       <c r="G305" s="1">
-        <v>46260</v>
+        <v>46261</v>
       </c>
     </row>
     <row r="306" spans="1:7" x14ac:dyDescent="0.2">
@@ -10073,22 +9908,22 @@
         <v>0</v>
       </c>
       <c r="B306" t="s">
-        <v>619</v>
+        <v>605</v>
       </c>
       <c r="C306" t="s">
         <v>80</v>
       </c>
       <c r="D306" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="E306" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="F306" s="1">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="G306" s="1">
-        <v>46260</v>
+        <v>46261</v>
       </c>
     </row>
     <row r="307" spans="1:7" x14ac:dyDescent="0.2">
@@ -10096,22 +9931,22 @@
         <v>0</v>
       </c>
       <c r="B307" t="s">
-        <v>620</v>
+        <v>606</v>
       </c>
       <c r="C307" t="s">
         <v>80</v>
       </c>
       <c r="D307" t="s">
-        <v>16</v>
+        <v>536</v>
       </c>
       <c r="E307" t="s">
-        <v>17</v>
+        <v>537</v>
       </c>
       <c r="F307" s="1">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="G307" s="1">
-        <v>46260</v>
+        <v>46261</v>
       </c>
     </row>
     <row r="308" spans="1:7" x14ac:dyDescent="0.2">
@@ -10119,19 +9954,19 @@
         <v>0</v>
       </c>
       <c r="B308" t="s">
-        <v>621</v>
+        <v>607</v>
       </c>
       <c r="C308" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D308" t="s">
-        <v>132</v>
+        <v>608</v>
       </c>
       <c r="E308" t="s">
-        <v>133</v>
+        <v>609</v>
       </c>
       <c r="F308" s="1">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="G308" s="1">
         <v>46261</v>
@@ -10142,22 +9977,22 @@
         <v>0</v>
       </c>
       <c r="B309" t="s">
-        <v>622</v>
+        <v>610</v>
       </c>
       <c r="C309" t="s">
         <v>80</v>
       </c>
       <c r="D309" t="s">
-        <v>623</v>
+        <v>450</v>
       </c>
       <c r="E309" t="s">
-        <v>624</v>
+        <v>451</v>
       </c>
       <c r="F309" s="1">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="G309" s="1">
-        <v>46260</v>
+        <v>46261</v>
       </c>
     </row>
     <row r="310" spans="1:7" x14ac:dyDescent="0.2">
@@ -10165,22 +10000,22 @@
         <v>0</v>
       </c>
       <c r="B310" t="s">
-        <v>625</v>
+        <v>611</v>
       </c>
       <c r="C310" t="s">
         <v>80</v>
       </c>
       <c r="D310" t="s">
-        <v>626</v>
+        <v>93</v>
       </c>
       <c r="E310" t="s">
-        <v>627</v>
+        <v>94</v>
       </c>
       <c r="F310" s="1">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="G310" s="1">
-        <v>46260</v>
+        <v>46261</v>
       </c>
     </row>
     <row r="311" spans="1:7" x14ac:dyDescent="0.2">
@@ -10188,22 +10023,22 @@
         <v>0</v>
       </c>
       <c r="B311" t="s">
-        <v>628</v>
+        <v>612</v>
       </c>
       <c r="C311" t="s">
         <v>80</v>
       </c>
       <c r="D311" t="s">
-        <v>629</v>
+        <v>93</v>
       </c>
       <c r="E311" t="s">
-        <v>630</v>
+        <v>94</v>
       </c>
       <c r="F311" s="1">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="G311" s="1">
-        <v>46260</v>
+        <v>46261</v>
       </c>
     </row>
     <row r="312" spans="1:7" x14ac:dyDescent="0.2">
@@ -10211,22 +10046,22 @@
         <v>0</v>
       </c>
       <c r="B312" t="s">
-        <v>631</v>
+        <v>613</v>
       </c>
       <c r="C312" t="s">
         <v>80</v>
       </c>
       <c r="D312" t="s">
-        <v>564</v>
+        <v>614</v>
       </c>
       <c r="E312" t="s">
-        <v>565</v>
+        <v>615</v>
       </c>
       <c r="F312" s="1">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="G312" s="1">
-        <v>46260</v>
+        <v>46261</v>
       </c>
     </row>
     <row r="313" spans="1:7" x14ac:dyDescent="0.2">
@@ -10234,22 +10069,22 @@
         <v>0</v>
       </c>
       <c r="B313" t="s">
-        <v>632</v>
+        <v>616</v>
       </c>
       <c r="C313" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D313" t="s">
-        <v>633</v>
+        <v>617</v>
       </c>
       <c r="E313" t="s">
-        <v>634</v>
+        <v>618</v>
       </c>
       <c r="F313" s="1">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="G313" s="1">
-        <v>46260</v>
+        <v>46261</v>
       </c>
     </row>
     <row r="314" spans="1:7" x14ac:dyDescent="0.2">
@@ -10257,22 +10092,22 @@
         <v>0</v>
       </c>
       <c r="B314" t="s">
-        <v>635</v>
+        <v>619</v>
       </c>
       <c r="C314" t="s">
         <v>80</v>
       </c>
       <c r="D314" t="s">
-        <v>636</v>
+        <v>620</v>
       </c>
       <c r="E314" t="s">
-        <v>637</v>
+        <v>621</v>
       </c>
       <c r="F314" s="1">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="G314" s="1">
-        <v>46260</v>
+        <v>46261</v>
       </c>
     </row>
     <row r="315" spans="1:7" x14ac:dyDescent="0.2">
@@ -10280,22 +10115,22 @@
         <v>0</v>
       </c>
       <c r="B315" t="s">
-        <v>638</v>
+        <v>622</v>
       </c>
       <c r="C315" t="s">
         <v>80</v>
       </c>
       <c r="D315" t="s">
-        <v>639</v>
+        <v>430</v>
       </c>
       <c r="E315" t="s">
-        <v>640</v>
+        <v>431</v>
       </c>
       <c r="F315" s="1">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="G315" s="1">
-        <v>46262</v>
+        <v>46261</v>
       </c>
     </row>
     <row r="316" spans="1:7" x14ac:dyDescent="0.2">
@@ -10303,22 +10138,22 @@
         <v>0</v>
       </c>
       <c r="B316" t="s">
-        <v>641</v>
+        <v>623</v>
       </c>
       <c r="C316" t="s">
         <v>80</v>
       </c>
       <c r="D316" t="s">
-        <v>359</v>
+        <v>402</v>
       </c>
       <c r="E316" t="s">
-        <v>360</v>
+        <v>403</v>
       </c>
       <c r="F316" s="1">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="G316" s="1">
-        <v>46260</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="317" spans="1:7" x14ac:dyDescent="0.2">
@@ -10326,22 +10161,22 @@
         <v>0</v>
       </c>
       <c r="B317" t="s">
-        <v>642</v>
+        <v>624</v>
       </c>
       <c r="C317" t="s">
         <v>80</v>
       </c>
       <c r="D317" t="s">
-        <v>371</v>
+        <v>437</v>
       </c>
       <c r="E317" t="s">
-        <v>372</v>
+        <v>438</v>
       </c>
       <c r="F317" s="1">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="G317" s="1">
-        <v>46260</v>
+        <v>46261</v>
       </c>
     </row>
     <row r="318" spans="1:7" x14ac:dyDescent="0.2">
@@ -10349,7 +10184,7 @@
         <v>0</v>
       </c>
       <c r="B318" t="s">
-        <v>643</v>
+        <v>625</v>
       </c>
       <c r="C318" t="s">
         <v>80</v>
@@ -10361,10 +10196,10 @@
         <v>102</v>
       </c>
       <c r="F318" s="1">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="G318" s="1">
-        <v>46260</v>
+        <v>46261</v>
       </c>
     </row>
     <row r="319" spans="1:7" x14ac:dyDescent="0.2">
@@ -10372,22 +10207,22 @@
         <v>0</v>
       </c>
       <c r="B319" t="s">
-        <v>644</v>
+        <v>626</v>
       </c>
       <c r="C319" t="s">
         <v>80</v>
       </c>
       <c r="D319" t="s">
-        <v>98</v>
+        <v>627</v>
       </c>
       <c r="E319" t="s">
-        <v>99</v>
+        <v>628</v>
       </c>
       <c r="F319" s="1">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="G319" s="1">
-        <v>46260</v>
+        <v>46261</v>
       </c>
     </row>
     <row r="320" spans="1:7" x14ac:dyDescent="0.2">
@@ -10395,22 +10230,22 @@
         <v>0</v>
       </c>
       <c r="B320" t="s">
-        <v>645</v>
+        <v>629</v>
       </c>
       <c r="C320" t="s">
         <v>80</v>
       </c>
       <c r="D320" t="s">
-        <v>161</v>
+        <v>74</v>
       </c>
       <c r="E320" t="s">
-        <v>162</v>
+        <v>75</v>
       </c>
       <c r="F320" s="1">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="G320" s="1">
-        <v>46260</v>
+        <v>46261</v>
       </c>
     </row>
     <row r="321" spans="1:7" x14ac:dyDescent="0.2">
@@ -10418,22 +10253,22 @@
         <v>0</v>
       </c>
       <c r="B321" t="s">
-        <v>646</v>
+        <v>630</v>
       </c>
       <c r="C321" t="s">
         <v>80</v>
       </c>
       <c r="D321" t="s">
-        <v>647</v>
+        <v>631</v>
       </c>
       <c r="E321" t="s">
-        <v>648</v>
+        <v>632</v>
       </c>
       <c r="F321" s="1">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="G321" s="1">
-        <v>46260</v>
+        <v>46261</v>
       </c>
     </row>
     <row r="322" spans="1:7" x14ac:dyDescent="0.2">
@@ -10441,22 +10276,22 @@
         <v>0</v>
       </c>
       <c r="B322" t="s">
-        <v>649</v>
+        <v>633</v>
       </c>
       <c r="C322" t="s">
         <v>80</v>
       </c>
       <c r="D322" t="s">
-        <v>650</v>
+        <v>634</v>
       </c>
       <c r="E322" t="s">
-        <v>651</v>
+        <v>635</v>
       </c>
       <c r="F322" s="1">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="G322" s="1">
-        <v>46260</v>
+        <v>46261</v>
       </c>
     </row>
     <row r="323" spans="1:7" x14ac:dyDescent="0.2">
@@ -10464,22 +10299,22 @@
         <v>0</v>
       </c>
       <c r="B323" t="s">
-        <v>652</v>
+        <v>636</v>
       </c>
       <c r="C323" t="s">
         <v>80</v>
       </c>
       <c r="D323" t="s">
-        <v>653</v>
+        <v>158</v>
       </c>
       <c r="E323" t="s">
-        <v>654</v>
+        <v>159</v>
       </c>
       <c r="F323" s="1">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="G323" s="1">
-        <v>46260</v>
+        <v>46261</v>
       </c>
     </row>
     <row r="324" spans="1:7" x14ac:dyDescent="0.2">
@@ -10487,22 +10322,22 @@
         <v>0</v>
       </c>
       <c r="B324" t="s">
-        <v>655</v>
+        <v>637</v>
       </c>
       <c r="C324" t="s">
         <v>80</v>
       </c>
       <c r="D324" t="s">
-        <v>656</v>
+        <v>638</v>
       </c>
       <c r="E324" t="s">
-        <v>657</v>
+        <v>639</v>
       </c>
       <c r="F324" s="1">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="G324" s="1">
-        <v>46260</v>
+        <v>46261</v>
       </c>
     </row>
     <row r="325" spans="1:7" x14ac:dyDescent="0.2">
@@ -10510,22 +10345,22 @@
         <v>0</v>
       </c>
       <c r="B325" t="s">
-        <v>658</v>
+        <v>640</v>
       </c>
       <c r="C325" t="s">
         <v>80</v>
       </c>
       <c r="D325" t="s">
-        <v>659</v>
+        <v>638</v>
       </c>
       <c r="E325" t="s">
-        <v>660</v>
+        <v>639</v>
       </c>
       <c r="F325" s="1">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="G325" s="1">
-        <v>46260</v>
+        <v>46261</v>
       </c>
     </row>
     <row r="326" spans="1:7" x14ac:dyDescent="0.2">
@@ -10533,22 +10368,22 @@
         <v>0</v>
       </c>
       <c r="B326" t="s">
-        <v>661</v>
+        <v>641</v>
       </c>
       <c r="C326" t="s">
         <v>80</v>
       </c>
       <c r="D326" t="s">
-        <v>659</v>
+        <v>200</v>
       </c>
       <c r="E326" t="s">
-        <v>660</v>
+        <v>201</v>
       </c>
       <c r="F326" s="1">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="G326" s="1">
-        <v>46260</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="327" spans="1:7" x14ac:dyDescent="0.2">
@@ -10556,22 +10391,22 @@
         <v>0</v>
       </c>
       <c r="B327" t="s">
-        <v>662</v>
+        <v>642</v>
       </c>
       <c r="C327" t="s">
         <v>80</v>
       </c>
       <c r="D327" t="s">
-        <v>626</v>
+        <v>200</v>
       </c>
       <c r="E327" t="s">
-        <v>627</v>
+        <v>201</v>
       </c>
       <c r="F327" s="1">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="G327" s="1">
-        <v>46260</v>
+        <v>46261</v>
       </c>
     </row>
     <row r="328" spans="1:7" x14ac:dyDescent="0.2">
@@ -10579,22 +10414,22 @@
         <v>0</v>
       </c>
       <c r="B328" t="s">
-        <v>663</v>
+        <v>643</v>
       </c>
       <c r="C328" t="s">
         <v>80</v>
       </c>
       <c r="D328" t="s">
-        <v>371</v>
+        <v>450</v>
       </c>
       <c r="E328" t="s">
-        <v>372</v>
+        <v>451</v>
       </c>
       <c r="F328" s="1">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="G328" s="1">
-        <v>46260</v>
+        <v>46261</v>
       </c>
     </row>
     <row r="329" spans="1:7" x14ac:dyDescent="0.2">
@@ -10602,19 +10437,19 @@
         <v>0</v>
       </c>
       <c r="B329" t="s">
-        <v>664</v>
+        <v>644</v>
       </c>
       <c r="C329" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D329" t="s">
-        <v>665</v>
+        <v>450</v>
       </c>
       <c r="E329" t="s">
-        <v>666</v>
+        <v>451</v>
       </c>
       <c r="F329" s="1">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="G329" s="1">
         <v>46261</v>
@@ -10625,22 +10460,22 @@
         <v>0</v>
       </c>
       <c r="B330" t="s">
-        <v>667</v>
+        <v>645</v>
       </c>
       <c r="C330" t="s">
         <v>80</v>
       </c>
       <c r="D330" t="s">
-        <v>16</v>
+        <v>250</v>
       </c>
       <c r="E330" t="s">
-        <v>17</v>
+        <v>251</v>
       </c>
       <c r="F330" s="1">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="G330" s="1">
-        <v>46260</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="331" spans="1:7" x14ac:dyDescent="0.2">
@@ -10648,19 +10483,19 @@
         <v>0</v>
       </c>
       <c r="B331" t="s">
-        <v>668</v>
+        <v>646</v>
       </c>
       <c r="C331" t="s">
         <v>80</v>
       </c>
       <c r="D331" t="s">
-        <v>669</v>
+        <v>450</v>
       </c>
       <c r="E331" t="s">
-        <v>670</v>
+        <v>451</v>
       </c>
       <c r="F331" s="1">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="G331" s="1">
         <v>46261</v>
@@ -10671,19 +10506,19 @@
         <v>0</v>
       </c>
       <c r="B332" t="s">
-        <v>671</v>
+        <v>647</v>
       </c>
       <c r="C332" t="s">
         <v>80</v>
       </c>
       <c r="D332" t="s">
-        <v>3</v>
+        <v>648</v>
       </c>
       <c r="E332" t="s">
-        <v>4</v>
+        <v>649</v>
       </c>
       <c r="F332" s="1">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="G332" s="1">
         <v>46261</v>
@@ -10694,22 +10529,22 @@
         <v>0</v>
       </c>
       <c r="B333" t="s">
-        <v>672</v>
+        <v>650</v>
       </c>
       <c r="C333" t="s">
         <v>80</v>
       </c>
       <c r="D333" t="s">
-        <v>16</v>
+        <v>651</v>
       </c>
       <c r="E333" t="s">
-        <v>17</v>
+        <v>652</v>
       </c>
       <c r="F333" s="1">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="G333" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="334" spans="1:7" x14ac:dyDescent="0.2">
@@ -10717,22 +10552,22 @@
         <v>0</v>
       </c>
       <c r="B334" t="s">
-        <v>673</v>
+        <v>653</v>
       </c>
       <c r="C334" t="s">
         <v>80</v>
       </c>
       <c r="D334" t="s">
-        <v>393</v>
+        <v>98</v>
       </c>
       <c r="E334" t="s">
-        <v>394</v>
+        <v>99</v>
       </c>
       <c r="F334" s="1">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="G334" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="335" spans="1:7" x14ac:dyDescent="0.2">
@@ -10740,22 +10575,22 @@
         <v>0</v>
       </c>
       <c r="B335" t="s">
-        <v>674</v>
+        <v>654</v>
       </c>
       <c r="C335" t="s">
         <v>80</v>
       </c>
       <c r="D335" t="s">
-        <v>19</v>
+        <v>200</v>
       </c>
       <c r="E335" t="s">
-        <v>20</v>
+        <v>201</v>
       </c>
       <c r="F335" s="1">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="G335" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="336" spans="1:7" x14ac:dyDescent="0.2">
@@ -10763,19 +10598,19 @@
         <v>0</v>
       </c>
       <c r="B336" t="s">
-        <v>675</v>
+        <v>655</v>
       </c>
       <c r="C336" t="s">
         <v>80</v>
       </c>
       <c r="D336" t="s">
-        <v>317</v>
+        <v>656</v>
       </c>
       <c r="E336" t="s">
-        <v>318</v>
+        <v>657</v>
       </c>
       <c r="F336" s="1">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="G336" s="1">
         <v>46262</v>
@@ -10786,22 +10621,22 @@
         <v>0</v>
       </c>
       <c r="B337" t="s">
-        <v>676</v>
+        <v>658</v>
       </c>
       <c r="C337" t="s">
         <v>80</v>
       </c>
       <c r="D337" t="s">
-        <v>37</v>
+        <v>390</v>
       </c>
       <c r="E337" t="s">
-        <v>38</v>
+        <v>391</v>
       </c>
       <c r="F337" s="1">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="G337" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="338" spans="1:7" x14ac:dyDescent="0.2">
@@ -10809,22 +10644,22 @@
         <v>0</v>
       </c>
       <c r="B338" t="s">
-        <v>677</v>
+        <v>659</v>
       </c>
       <c r="C338" t="s">
         <v>80</v>
       </c>
       <c r="D338" t="s">
-        <v>37</v>
+        <v>656</v>
       </c>
       <c r="E338" t="s">
-        <v>38</v>
+        <v>657</v>
       </c>
       <c r="F338" s="1">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="G338" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="339" spans="1:7" x14ac:dyDescent="0.2">
@@ -10832,22 +10667,22 @@
         <v>0</v>
       </c>
       <c r="B339" t="s">
-        <v>678</v>
+        <v>660</v>
       </c>
       <c r="C339" t="s">
         <v>80</v>
       </c>
       <c r="D339" t="s">
-        <v>37</v>
+        <v>93</v>
       </c>
       <c r="E339" t="s">
-        <v>38</v>
+        <v>94</v>
       </c>
       <c r="F339" s="1">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="G339" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="340" spans="1:7" x14ac:dyDescent="0.2">
@@ -10855,7 +10690,7 @@
         <v>0</v>
       </c>
       <c r="B340" t="s">
-        <v>679</v>
+        <v>661</v>
       </c>
       <c r="C340" t="s">
         <v>80</v>
@@ -10867,10 +10702,10 @@
         <v>38</v>
       </c>
       <c r="F340" s="1">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="G340" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="341" spans="1:7" x14ac:dyDescent="0.2">
@@ -10878,7 +10713,7 @@
         <v>0</v>
       </c>
       <c r="B341" t="s">
-        <v>680</v>
+        <v>662</v>
       </c>
       <c r="C341" t="s">
         <v>80</v>
@@ -10890,10 +10725,10 @@
         <v>38</v>
       </c>
       <c r="F341" s="1">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="G341" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="342" spans="1:7" x14ac:dyDescent="0.2">
@@ -10901,22 +10736,22 @@
         <v>0</v>
       </c>
       <c r="B342" t="s">
-        <v>681</v>
+        <v>663</v>
       </c>
       <c r="C342" t="s">
         <v>80</v>
       </c>
       <c r="D342" t="s">
-        <v>37</v>
+        <v>664</v>
       </c>
       <c r="E342" t="s">
-        <v>38</v>
+        <v>665</v>
       </c>
       <c r="F342" s="1">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="G342" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="343" spans="1:7" x14ac:dyDescent="0.2">
@@ -10924,22 +10759,22 @@
         <v>0</v>
       </c>
       <c r="B343" t="s">
-        <v>682</v>
+        <v>666</v>
       </c>
       <c r="C343" t="s">
         <v>80</v>
       </c>
       <c r="D343" t="s">
-        <v>37</v>
+        <v>667</v>
       </c>
       <c r="E343" t="s">
-        <v>38</v>
+        <v>668</v>
       </c>
       <c r="F343" s="1">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="G343" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="344" spans="1:7" x14ac:dyDescent="0.2">
@@ -10947,22 +10782,22 @@
         <v>0</v>
       </c>
       <c r="B344" t="s">
-        <v>683</v>
+        <v>669</v>
       </c>
       <c r="C344" t="s">
         <v>80</v>
       </c>
       <c r="D344" t="s">
-        <v>37</v>
+        <v>670</v>
       </c>
       <c r="E344" t="s">
-        <v>38</v>
+        <v>671</v>
       </c>
       <c r="F344" s="1">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="G344" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="345" spans="1:7" x14ac:dyDescent="0.2">
@@ -10970,22 +10805,22 @@
         <v>0</v>
       </c>
       <c r="B345" t="s">
-        <v>684</v>
+        <v>672</v>
       </c>
       <c r="C345" t="s">
         <v>80</v>
       </c>
       <c r="D345" t="s">
-        <v>37</v>
+        <v>673</v>
       </c>
       <c r="E345" t="s">
-        <v>38</v>
+        <v>674</v>
       </c>
       <c r="F345" s="1">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="G345" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="346" spans="1:7" x14ac:dyDescent="0.2">
@@ -10993,22 +10828,22 @@
         <v>0</v>
       </c>
       <c r="B346" t="s">
-        <v>685</v>
+        <v>675</v>
       </c>
       <c r="C346" t="s">
         <v>80</v>
       </c>
       <c r="D346" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="E346" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F346" s="1">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="G346" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="347" spans="1:7" x14ac:dyDescent="0.2">
@@ -11016,22 +10851,22 @@
         <v>0</v>
       </c>
       <c r="B347" t="s">
-        <v>686</v>
+        <v>676</v>
       </c>
       <c r="C347" t="s">
         <v>80</v>
       </c>
       <c r="D347" t="s">
-        <v>526</v>
+        <v>16</v>
       </c>
       <c r="E347" t="s">
-        <v>527</v>
+        <v>17</v>
       </c>
       <c r="F347" s="1">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="G347" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="348" spans="1:7" x14ac:dyDescent="0.2">
@@ -11039,19 +10874,19 @@
         <v>0</v>
       </c>
       <c r="B348" t="s">
-        <v>687</v>
+        <v>677</v>
       </c>
       <c r="C348" t="s">
         <v>80</v>
       </c>
       <c r="D348" t="s">
-        <v>688</v>
+        <v>16</v>
       </c>
       <c r="E348" t="s">
-        <v>689</v>
+        <v>17</v>
       </c>
       <c r="F348" s="1">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="G348" s="1">
         <v>46262</v>
@@ -11062,22 +10897,22 @@
         <v>0</v>
       </c>
       <c r="B349" t="s">
-        <v>690</v>
+        <v>678</v>
       </c>
       <c r="C349" t="s">
         <v>80</v>
       </c>
       <c r="D349" t="s">
-        <v>691</v>
+        <v>87</v>
       </c>
       <c r="E349" t="s">
-        <v>692</v>
+        <v>88</v>
       </c>
       <c r="F349" s="1">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="G349" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="350" spans="1:7" x14ac:dyDescent="0.2">
@@ -11085,22 +10920,22 @@
         <v>0</v>
       </c>
       <c r="B350" t="s">
-        <v>693</v>
+        <v>679</v>
       </c>
       <c r="C350" t="s">
         <v>80</v>
       </c>
       <c r="D350" t="s">
-        <v>694</v>
+        <v>87</v>
       </c>
       <c r="E350" t="s">
-        <v>695</v>
+        <v>88</v>
       </c>
       <c r="F350" s="1">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="G350" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="351" spans="1:7" x14ac:dyDescent="0.2">
@@ -11108,22 +10943,22 @@
         <v>0</v>
       </c>
       <c r="B351" t="s">
-        <v>696</v>
+        <v>680</v>
       </c>
       <c r="C351" t="s">
         <v>80</v>
       </c>
       <c r="D351" t="s">
-        <v>697</v>
+        <v>205</v>
       </c>
       <c r="E351" t="s">
-        <v>698</v>
+        <v>206</v>
       </c>
       <c r="F351" s="1">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="G351" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="352" spans="1:7" x14ac:dyDescent="0.2">
@@ -11131,22 +10966,22 @@
         <v>0</v>
       </c>
       <c r="B352" t="s">
-        <v>699</v>
+        <v>681</v>
       </c>
       <c r="C352" t="s">
         <v>80</v>
       </c>
       <c r="D352" t="s">
-        <v>25</v>
+        <v>87</v>
       </c>
       <c r="E352" t="s">
-        <v>26</v>
+        <v>88</v>
       </c>
       <c r="F352" s="1">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="G352" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="353" spans="1:7" x14ac:dyDescent="0.2">
@@ -11154,22 +10989,22 @@
         <v>0</v>
       </c>
       <c r="B353" t="s">
-        <v>700</v>
+        <v>682</v>
       </c>
       <c r="C353" t="s">
         <v>80</v>
       </c>
       <c r="D353" t="s">
-        <v>37</v>
+        <v>87</v>
       </c>
       <c r="E353" t="s">
-        <v>38</v>
+        <v>88</v>
       </c>
       <c r="F353" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="G353" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="354" spans="1:7" x14ac:dyDescent="0.2">
@@ -11177,22 +11012,22 @@
         <v>0</v>
       </c>
       <c r="B354" t="s">
-        <v>701</v>
+        <v>683</v>
       </c>
       <c r="C354" t="s">
         <v>80</v>
       </c>
       <c r="D354" t="s">
-        <v>702</v>
+        <v>87</v>
       </c>
       <c r="E354" t="s">
-        <v>703</v>
+        <v>88</v>
       </c>
       <c r="F354" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="G354" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="355" spans="1:7" x14ac:dyDescent="0.2">
@@ -11200,22 +11035,22 @@
         <v>0</v>
       </c>
       <c r="B355" t="s">
-        <v>704</v>
+        <v>684</v>
       </c>
       <c r="C355" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D355" t="s">
-        <v>705</v>
+        <v>87</v>
       </c>
       <c r="E355" t="s">
-        <v>706</v>
+        <v>88</v>
       </c>
       <c r="F355" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="G355" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="356" spans="1:7" x14ac:dyDescent="0.2">
@@ -11223,22 +11058,22 @@
         <v>0</v>
       </c>
       <c r="B356" t="s">
-        <v>707</v>
+        <v>685</v>
       </c>
       <c r="C356" t="s">
         <v>80</v>
       </c>
       <c r="D356" t="s">
-        <v>606</v>
+        <v>87</v>
       </c>
       <c r="E356" t="s">
-        <v>607</v>
+        <v>88</v>
       </c>
       <c r="F356" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="G356" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="357" spans="1:7" x14ac:dyDescent="0.2">
@@ -11246,22 +11081,22 @@
         <v>0</v>
       </c>
       <c r="B357" t="s">
-        <v>708</v>
+        <v>686</v>
       </c>
       <c r="C357" t="s">
         <v>80</v>
       </c>
       <c r="D357" t="s">
-        <v>709</v>
+        <v>87</v>
       </c>
       <c r="E357" t="s">
-        <v>710</v>
+        <v>88</v>
       </c>
       <c r="F357" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="G357" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="358" spans="1:7" x14ac:dyDescent="0.2">
@@ -11269,22 +11104,22 @@
         <v>0</v>
       </c>
       <c r="B358" t="s">
-        <v>711</v>
+        <v>687</v>
       </c>
       <c r="C358" t="s">
         <v>80</v>
       </c>
       <c r="D358" t="s">
-        <v>470</v>
+        <v>87</v>
       </c>
       <c r="E358" t="s">
-        <v>471</v>
+        <v>88</v>
       </c>
       <c r="F358" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="G358" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="359" spans="1:7" x14ac:dyDescent="0.2">
@@ -11292,22 +11127,22 @@
         <v>0</v>
       </c>
       <c r="B359" t="s">
-        <v>712</v>
+        <v>688</v>
       </c>
       <c r="C359" t="s">
         <v>80</v>
       </c>
       <c r="D359" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="E359" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="F359" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="G359" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="360" spans="1:7" x14ac:dyDescent="0.2">
@@ -11315,22 +11150,22 @@
         <v>0</v>
       </c>
       <c r="B360" t="s">
-        <v>713</v>
+        <v>689</v>
       </c>
       <c r="C360" t="s">
         <v>80</v>
       </c>
       <c r="D360" t="s">
-        <v>93</v>
+        <v>284</v>
       </c>
       <c r="E360" t="s">
-        <v>94</v>
+        <v>285</v>
       </c>
       <c r="F360" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="G360" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="361" spans="1:7" x14ac:dyDescent="0.2">
@@ -11338,22 +11173,22 @@
         <v>0</v>
       </c>
       <c r="B361" t="s">
-        <v>714</v>
+        <v>690</v>
       </c>
       <c r="C361" t="s">
         <v>80</v>
       </c>
       <c r="D361" t="s">
-        <v>715</v>
+        <v>563</v>
       </c>
       <c r="E361" t="s">
-        <v>716</v>
+        <v>564</v>
       </c>
       <c r="F361" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="G361" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="362" spans="1:7" x14ac:dyDescent="0.2">
@@ -11361,22 +11196,22 @@
         <v>0</v>
       </c>
       <c r="B362" t="s">
-        <v>717</v>
+        <v>691</v>
       </c>
       <c r="C362" t="s">
         <v>80</v>
       </c>
       <c r="D362" t="s">
-        <v>402</v>
+        <v>692</v>
       </c>
       <c r="E362" t="s">
-        <v>403</v>
+        <v>693</v>
       </c>
       <c r="F362" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="G362" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="363" spans="1:7" x14ac:dyDescent="0.2">
@@ -11384,22 +11219,22 @@
         <v>0</v>
       </c>
       <c r="B363" t="s">
-        <v>718</v>
+        <v>694</v>
       </c>
       <c r="C363" t="s">
         <v>80</v>
       </c>
       <c r="D363" t="s">
-        <v>719</v>
+        <v>158</v>
       </c>
       <c r="E363" t="s">
-        <v>720</v>
+        <v>159</v>
       </c>
       <c r="F363" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="G363" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="364" spans="1:7" x14ac:dyDescent="0.2">
@@ -11407,22 +11242,22 @@
         <v>0</v>
       </c>
       <c r="B364" t="s">
-        <v>721</v>
+        <v>695</v>
       </c>
       <c r="C364" t="s">
         <v>80</v>
       </c>
       <c r="D364" t="s">
-        <v>449</v>
+        <v>93</v>
       </c>
       <c r="E364" t="s">
-        <v>450</v>
+        <v>94</v>
       </c>
       <c r="F364" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="G364" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="365" spans="1:7" x14ac:dyDescent="0.2">
@@ -11430,22 +11265,22 @@
         <v>0</v>
       </c>
       <c r="B365" t="s">
-        <v>722</v>
+        <v>696</v>
       </c>
       <c r="C365" t="s">
         <v>80</v>
       </c>
       <c r="D365" t="s">
-        <v>215</v>
+        <v>314</v>
       </c>
       <c r="E365" t="s">
-        <v>216</v>
+        <v>315</v>
       </c>
       <c r="F365" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="G365" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="366" spans="1:7" x14ac:dyDescent="0.2">
@@ -11453,22 +11288,22 @@
         <v>0</v>
       </c>
       <c r="B366" t="s">
-        <v>723</v>
+        <v>697</v>
       </c>
       <c r="C366" t="s">
         <v>80</v>
       </c>
       <c r="D366" t="s">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="E366" t="s">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="F366" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="G366" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="367" spans="1:7" x14ac:dyDescent="0.2">
@@ -11476,22 +11311,22 @@
         <v>0</v>
       </c>
       <c r="B367" t="s">
-        <v>724</v>
+        <v>698</v>
       </c>
       <c r="C367" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D367" t="s">
-        <v>705</v>
+        <v>16</v>
       </c>
       <c r="E367" t="s">
-        <v>706</v>
+        <v>17</v>
       </c>
       <c r="F367" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="G367" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="368" spans="1:7" x14ac:dyDescent="0.2">
@@ -11499,22 +11334,22 @@
         <v>0</v>
       </c>
       <c r="B368" t="s">
-        <v>725</v>
+        <v>699</v>
       </c>
       <c r="C368" t="s">
         <v>80</v>
       </c>
       <c r="D368" t="s">
-        <v>325</v>
+        <v>16</v>
       </c>
       <c r="E368" t="s">
-        <v>326</v>
+        <v>17</v>
       </c>
       <c r="F368" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="G368" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="369" spans="1:7" x14ac:dyDescent="0.2">
@@ -11522,22 +11357,22 @@
         <v>0</v>
       </c>
       <c r="B369" t="s">
-        <v>726</v>
+        <v>700</v>
       </c>
       <c r="C369" t="s">
         <v>80</v>
       </c>
       <c r="D369" t="s">
-        <v>639</v>
+        <v>701</v>
       </c>
       <c r="E369" t="s">
-        <v>640</v>
+        <v>702</v>
       </c>
       <c r="F369" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="G369" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="370" spans="1:7" x14ac:dyDescent="0.2">
@@ -11545,19 +11380,19 @@
         <v>0</v>
       </c>
       <c r="B370" t="s">
-        <v>727</v>
+        <v>703</v>
       </c>
       <c r="C370" t="s">
         <v>80</v>
       </c>
       <c r="D370" t="s">
-        <v>411</v>
+        <v>470</v>
       </c>
       <c r="E370" t="s">
-        <v>412</v>
+        <v>471</v>
       </c>
       <c r="F370" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="G370" s="1">
         <v>46262</v>
@@ -11568,22 +11403,22 @@
         <v>0</v>
       </c>
       <c r="B371" t="s">
-        <v>728</v>
+        <v>704</v>
       </c>
       <c r="C371" t="s">
         <v>80</v>
       </c>
       <c r="D371" t="s">
-        <v>456</v>
+        <v>705</v>
       </c>
       <c r="E371" t="s">
-        <v>457</v>
+        <v>706</v>
       </c>
       <c r="F371" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="G371" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="372" spans="1:7" x14ac:dyDescent="0.2">
@@ -11591,22 +11426,22 @@
         <v>0</v>
       </c>
       <c r="B372" t="s">
-        <v>729</v>
+        <v>707</v>
       </c>
       <c r="C372" t="s">
         <v>80</v>
       </c>
       <c r="D372" t="s">
-        <v>101</v>
+        <v>158</v>
       </c>
       <c r="E372" t="s">
-        <v>102</v>
+        <v>159</v>
       </c>
       <c r="F372" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="G372" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="373" spans="1:7" x14ac:dyDescent="0.2">
@@ -11614,22 +11449,22 @@
         <v>0</v>
       </c>
       <c r="B373" t="s">
-        <v>730</v>
+        <v>708</v>
       </c>
       <c r="C373" t="s">
         <v>80</v>
       </c>
       <c r="D373" t="s">
-        <v>101</v>
+        <v>158</v>
       </c>
       <c r="E373" t="s">
-        <v>102</v>
+        <v>159</v>
       </c>
       <c r="F373" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="G373" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="374" spans="1:7" x14ac:dyDescent="0.2">
@@ -11637,1114 +11472,1114 @@
         <v>0</v>
       </c>
       <c r="B374" t="s">
-        <v>731</v>
+        <v>709</v>
       </c>
       <c r="C374" t="s">
         <v>80</v>
       </c>
       <c r="D374" t="s">
-        <v>732</v>
+        <v>390</v>
       </c>
       <c r="E374" t="s">
-        <v>733</v>
+        <v>391</v>
       </c>
       <c r="F374" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="G374" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="375" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A375" t="s">
-        <v>0</v>
+        <v>710</v>
       </c>
       <c r="B375" t="s">
-        <v>734</v>
+        <v>711</v>
       </c>
       <c r="C375" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D375" t="s">
-        <v>74</v>
+        <v>314</v>
       </c>
       <c r="E375" t="s">
-        <v>75</v>
+        <v>315</v>
       </c>
       <c r="F375" s="1">
-        <v>46261</v>
+        <v>46148</v>
       </c>
       <c r="G375" s="1">
-        <v>46261</v>
+        <v>46149</v>
       </c>
     </row>
     <row r="376" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A376" t="s">
-        <v>0</v>
+        <v>710</v>
       </c>
       <c r="B376" t="s">
-        <v>735</v>
+        <v>712</v>
       </c>
       <c r="C376" t="s">
         <v>80</v>
       </c>
       <c r="D376" t="s">
-        <v>736</v>
+        <v>713</v>
       </c>
       <c r="E376" t="s">
-        <v>737</v>
+        <v>714</v>
       </c>
       <c r="F376" s="1">
-        <v>46261</v>
+        <v>46260</v>
       </c>
       <c r="G376" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="377" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A377" t="s">
-        <v>0</v>
+        <v>715</v>
       </c>
       <c r="B377" t="s">
-        <v>738</v>
+        <v>716</v>
       </c>
       <c r="C377" t="s">
-        <v>80</v>
+        <v>6</v>
       </c>
       <c r="D377" t="s">
-        <v>101</v>
+        <v>41</v>
       </c>
       <c r="E377" t="s">
-        <v>102</v>
+        <v>42</v>
       </c>
       <c r="F377" s="1">
-        <v>46261</v>
+        <v>46133</v>
       </c>
       <c r="G377" s="1">
-        <v>46261</v>
+        <v>46134</v>
       </c>
     </row>
     <row r="378" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A378" t="s">
-        <v>0</v>
+        <v>715</v>
       </c>
       <c r="B378" t="s">
-        <v>739</v>
+        <v>717</v>
       </c>
       <c r="C378" t="s">
-        <v>80</v>
+        <v>6</v>
       </c>
       <c r="D378" t="s">
-        <v>740</v>
+        <v>41</v>
       </c>
       <c r="E378" t="s">
-        <v>741</v>
+        <v>42</v>
       </c>
       <c r="F378" s="1">
-        <v>46261</v>
+        <v>46134</v>
       </c>
       <c r="G378" s="1">
-        <v>46261</v>
+        <v>46134</v>
       </c>
     </row>
     <row r="379" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A379" t="s">
-        <v>0</v>
+        <v>715</v>
       </c>
       <c r="B379" t="s">
-        <v>742</v>
+        <v>718</v>
       </c>
       <c r="C379" t="s">
-        <v>80</v>
+        <v>6</v>
       </c>
       <c r="D379" t="s">
-        <v>158</v>
+        <v>19</v>
       </c>
       <c r="E379" t="s">
-        <v>159</v>
+        <v>20</v>
       </c>
       <c r="F379" s="1">
-        <v>46261</v>
+        <v>46156</v>
       </c>
       <c r="G379" s="1">
-        <v>46261</v>
+        <v>46156</v>
       </c>
     </row>
     <row r="380" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A380" t="s">
-        <v>0</v>
+        <v>715</v>
       </c>
       <c r="B380" t="s">
-        <v>743</v>
+        <v>719</v>
       </c>
       <c r="C380" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D380" t="s">
-        <v>744</v>
+        <v>720</v>
       </c>
       <c r="E380" t="s">
-        <v>745</v>
+        <v>721</v>
       </c>
       <c r="F380" s="1">
-        <v>46261</v>
+        <v>46195</v>
       </c>
       <c r="G380" s="1">
-        <v>46261</v>
+        <v>46195</v>
       </c>
     </row>
     <row r="381" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A381" t="s">
-        <v>0</v>
+        <v>715</v>
       </c>
       <c r="B381" t="s">
-        <v>746</v>
+        <v>722</v>
       </c>
       <c r="C381" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D381" t="s">
-        <v>744</v>
+        <v>723</v>
       </c>
       <c r="E381" t="s">
-        <v>745</v>
+        <v>724</v>
       </c>
       <c r="F381" s="1">
-        <v>46261</v>
+        <v>46206</v>
       </c>
       <c r="G381" s="1">
-        <v>46261</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="382" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A382" t="s">
-        <v>0</v>
+        <v>715</v>
       </c>
       <c r="B382" t="s">
-        <v>747</v>
+        <v>725</v>
       </c>
       <c r="C382" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="D382" t="s">
-        <v>200</v>
+        <v>726</v>
       </c>
       <c r="E382" t="s">
-        <v>201</v>
+        <v>727</v>
       </c>
       <c r="F382" s="1">
-        <v>46261</v>
+        <v>46209</v>
       </c>
       <c r="G382" s="1">
-        <v>46262</v>
+        <v>46218</v>
       </c>
     </row>
     <row r="383" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A383" t="s">
-        <v>0</v>
+        <v>715</v>
       </c>
       <c r="B383" t="s">
-        <v>748</v>
+        <v>728</v>
       </c>
       <c r="C383" t="s">
-        <v>80</v>
+        <v>6</v>
       </c>
       <c r="D383" t="s">
-        <v>200</v>
+        <v>729</v>
       </c>
       <c r="E383" t="s">
-        <v>201</v>
+        <v>730</v>
       </c>
       <c r="F383" s="1">
-        <v>46261</v>
+        <v>46213</v>
       </c>
       <c r="G383" s="1">
-        <v>46261</v>
+        <v>46213</v>
       </c>
     </row>
     <row r="384" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A384" t="s">
-        <v>0</v>
+        <v>715</v>
       </c>
       <c r="B384" t="s">
-        <v>749</v>
+        <v>731</v>
       </c>
       <c r="C384" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="D384" t="s">
-        <v>81</v>
+        <v>433</v>
       </c>
       <c r="E384" t="s">
-        <v>82</v>
+        <v>434</v>
       </c>
       <c r="F384" s="1">
-        <v>46261</v>
+        <v>46213</v>
       </c>
       <c r="G384" s="1">
-        <v>46261</v>
+        <v>46216</v>
       </c>
     </row>
     <row r="385" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A385" t="s">
-        <v>0</v>
+        <v>715</v>
       </c>
       <c r="B385" t="s">
-        <v>750</v>
+        <v>732</v>
       </c>
       <c r="C385" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D385" t="s">
-        <v>751</v>
+        <v>127</v>
       </c>
       <c r="E385" t="s">
-        <v>752</v>
+        <v>128</v>
       </c>
       <c r="F385" s="1">
-        <v>46261</v>
+        <v>46220</v>
       </c>
       <c r="G385" s="1">
-        <v>46261</v>
+        <v>46231</v>
       </c>
     </row>
     <row r="386" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A386" t="s">
-        <v>0</v>
+        <v>715</v>
       </c>
       <c r="B386" t="s">
-        <v>753</v>
+        <v>733</v>
       </c>
       <c r="C386" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D386" t="s">
-        <v>470</v>
+        <v>720</v>
       </c>
       <c r="E386" t="s">
-        <v>471</v>
+        <v>721</v>
       </c>
       <c r="F386" s="1">
-        <v>46261</v>
+        <v>46223</v>
       </c>
       <c r="G386" s="1">
-        <v>46261</v>
+        <v>46223</v>
       </c>
     </row>
     <row r="387" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A387" t="s">
-        <v>0</v>
+        <v>715</v>
       </c>
       <c r="B387" t="s">
-        <v>754</v>
+        <v>734</v>
       </c>
       <c r="C387" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="D387" t="s">
-        <v>470</v>
+        <v>433</v>
       </c>
       <c r="E387" t="s">
-        <v>471</v>
+        <v>434</v>
       </c>
       <c r="F387" s="1">
-        <v>46261</v>
+        <v>46224</v>
       </c>
       <c r="G387" s="1">
-        <v>46261</v>
+        <v>46224</v>
       </c>
     </row>
     <row r="388" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A388" t="s">
-        <v>0</v>
+        <v>715</v>
       </c>
       <c r="B388" t="s">
-        <v>755</v>
+        <v>735</v>
       </c>
       <c r="C388" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D388" t="s">
-        <v>393</v>
+        <v>127</v>
       </c>
       <c r="E388" t="s">
-        <v>394</v>
+        <v>128</v>
       </c>
       <c r="F388" s="1">
-        <v>46261</v>
+        <v>46232</v>
       </c>
       <c r="G388" s="1">
-        <v>46261</v>
+        <v>46233</v>
       </c>
     </row>
     <row r="389" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A389" t="s">
-        <v>0</v>
+        <v>715</v>
       </c>
       <c r="B389" t="s">
-        <v>756</v>
+        <v>736</v>
       </c>
       <c r="C389" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D389" t="s">
-        <v>250</v>
+        <v>127</v>
       </c>
       <c r="E389" t="s">
-        <v>251</v>
+        <v>128</v>
       </c>
       <c r="F389" s="1">
-        <v>46261</v>
+        <v>46232</v>
       </c>
       <c r="G389" s="1">
-        <v>46262</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="390" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A390" t="s">
-        <v>0</v>
+        <v>715</v>
       </c>
       <c r="B390" t="s">
-        <v>757</v>
+        <v>737</v>
       </c>
       <c r="C390" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D390" t="s">
-        <v>470</v>
+        <v>433</v>
       </c>
       <c r="E390" t="s">
-        <v>471</v>
+        <v>434</v>
       </c>
       <c r="F390" s="1">
-        <v>46261</v>
+        <v>46238</v>
       </c>
       <c r="G390" s="1">
-        <v>46261</v>
+        <v>46239</v>
       </c>
     </row>
     <row r="391" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A391" t="s">
-        <v>0</v>
+        <v>715</v>
       </c>
       <c r="B391" t="s">
-        <v>758</v>
+        <v>738</v>
       </c>
       <c r="C391" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D391" t="s">
-        <v>759</v>
+        <v>41</v>
       </c>
       <c r="E391" t="s">
-        <v>760</v>
+        <v>42</v>
       </c>
       <c r="F391" s="1">
-        <v>46261</v>
+        <v>46247</v>
       </c>
       <c r="G391" s="1">
-        <v>46261</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="392" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A392" t="s">
-        <v>0</v>
+        <v>715</v>
       </c>
       <c r="B392" t="s">
-        <v>761</v>
+        <v>739</v>
       </c>
       <c r="C392" t="s">
-        <v>80</v>
+        <v>6</v>
       </c>
       <c r="D392" t="s">
-        <v>762</v>
+        <v>740</v>
       </c>
       <c r="E392" t="s">
-        <v>763</v>
+        <v>741</v>
       </c>
       <c r="F392" s="1">
-        <v>46261</v>
+        <v>46253</v>
       </c>
       <c r="G392" s="1">
-        <v>46262</v>
+        <v>46253</v>
       </c>
     </row>
     <row r="393" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A393" t="s">
-        <v>0</v>
+        <v>715</v>
       </c>
       <c r="B393" t="s">
-        <v>764</v>
+        <v>742</v>
       </c>
       <c r="C393" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D393" t="s">
-        <v>98</v>
+        <v>433</v>
       </c>
       <c r="E393" t="s">
-        <v>99</v>
+        <v>434</v>
       </c>
       <c r="F393" s="1">
-        <v>46262</v>
+        <v>46253</v>
       </c>
       <c r="G393" s="1">
-        <v>46262</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="394" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A394" t="s">
-        <v>765</v>
+        <v>715</v>
       </c>
       <c r="B394" t="s">
-        <v>766</v>
+        <v>743</v>
       </c>
       <c r="C394" t="s">
         <v>2</v>
       </c>
       <c r="D394" t="s">
-        <v>314</v>
+        <v>720</v>
       </c>
       <c r="E394" t="s">
-        <v>315</v>
+        <v>721</v>
       </c>
       <c r="F394" s="1">
-        <v>46148</v>
+        <v>46258</v>
       </c>
       <c r="G394" s="1">
-        <v>46149</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="395" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A395" t="s">
-        <v>765</v>
+        <v>715</v>
       </c>
       <c r="B395" t="s">
-        <v>767</v>
+        <v>744</v>
       </c>
       <c r="C395" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D395" t="s">
-        <v>768</v>
+        <v>433</v>
       </c>
       <c r="E395" t="s">
-        <v>769</v>
+        <v>434</v>
       </c>
       <c r="F395" s="1">
-        <v>46260</v>
+        <v>46258</v>
       </c>
       <c r="G395" s="1">
-        <v>46262</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="396" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A396" t="s">
-        <v>770</v>
+        <v>715</v>
       </c>
       <c r="B396" t="s">
-        <v>771</v>
+        <v>745</v>
       </c>
       <c r="C396" t="s">
-        <v>6</v>
+        <v>80</v>
       </c>
       <c r="D396" t="s">
-        <v>41</v>
+        <v>450</v>
       </c>
       <c r="E396" t="s">
-        <v>42</v>
+        <v>451</v>
       </c>
       <c r="F396" s="1">
-        <v>46133</v>
+        <v>46258</v>
       </c>
       <c r="G396" s="1">
-        <v>46134</v>
+        <v>46258</v>
       </c>
     </row>
     <row r="397" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A397" t="s">
-        <v>770</v>
+        <v>715</v>
       </c>
       <c r="B397" t="s">
-        <v>772</v>
+        <v>746</v>
       </c>
       <c r="C397" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D397" t="s">
-        <v>41</v>
+        <v>127</v>
       </c>
       <c r="E397" t="s">
-        <v>42</v>
+        <v>128</v>
       </c>
       <c r="F397" s="1">
-        <v>46134</v>
+        <v>46259</v>
       </c>
       <c r="G397" s="1">
-        <v>46134</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="398" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A398" t="s">
-        <v>770</v>
+        <v>715</v>
       </c>
       <c r="B398" t="s">
-        <v>773</v>
+        <v>747</v>
       </c>
       <c r="C398" t="s">
-        <v>6</v>
+        <v>80</v>
       </c>
       <c r="D398" t="s">
-        <v>19</v>
+        <v>748</v>
       </c>
       <c r="E398" t="s">
-        <v>20</v>
+        <v>749</v>
       </c>
       <c r="F398" s="1">
-        <v>46156</v>
+        <v>46261</v>
       </c>
       <c r="G398" s="1">
-        <v>46156</v>
+        <v>46261</v>
       </c>
     </row>
     <row r="399" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A399" t="s">
-        <v>770</v>
+        <v>715</v>
       </c>
       <c r="B399" t="s">
-        <v>774</v>
+        <v>750</v>
       </c>
       <c r="C399" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D399" t="s">
-        <v>775</v>
+        <v>433</v>
       </c>
       <c r="E399" t="s">
-        <v>776</v>
+        <v>434</v>
       </c>
       <c r="F399" s="1">
-        <v>46195</v>
+        <v>46262</v>
       </c>
       <c r="G399" s="1">
-        <v>46195</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="400" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A400" t="s">
-        <v>770</v>
+        <v>715</v>
       </c>
       <c r="B400" t="s">
-        <v>777</v>
+        <v>751</v>
       </c>
       <c r="C400" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D400" t="s">
-        <v>573</v>
+        <v>726</v>
       </c>
       <c r="E400" t="s">
-        <v>574</v>
+        <v>727</v>
       </c>
       <c r="F400" s="1">
-        <v>46206</v>
+        <v>46262</v>
       </c>
       <c r="G400" s="1">
-        <v>46252</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="401" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A401" t="s">
-        <v>770</v>
+        <v>752</v>
       </c>
       <c r="B401" t="s">
-        <v>778</v>
+        <v>753</v>
       </c>
       <c r="C401" t="s">
         <v>96</v>
       </c>
       <c r="D401" t="s">
-        <v>779</v>
+        <v>754</v>
       </c>
       <c r="E401" t="s">
-        <v>780</v>
+        <v>755</v>
       </c>
       <c r="F401" s="1">
-        <v>46209</v>
+        <v>46063</v>
       </c>
       <c r="G401" s="1">
-        <v>46218</v>
+        <v>46064</v>
       </c>
     </row>
     <row r="402" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A402" t="s">
-        <v>770</v>
+        <v>752</v>
       </c>
       <c r="B402" t="s">
-        <v>781</v>
+        <v>756</v>
       </c>
       <c r="C402" t="s">
         <v>6</v>
       </c>
       <c r="D402" t="s">
-        <v>782</v>
+        <v>57</v>
       </c>
       <c r="E402" t="s">
-        <v>783</v>
+        <v>58</v>
       </c>
       <c r="F402" s="1">
-        <v>46213</v>
+        <v>46113</v>
       </c>
       <c r="G402" s="1">
-        <v>46213</v>
+        <v>46125</v>
       </c>
     </row>
     <row r="403" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A403" t="s">
-        <v>770</v>
+        <v>752</v>
       </c>
       <c r="B403" t="s">
-        <v>784</v>
+        <v>757</v>
       </c>
       <c r="C403" t="s">
-        <v>96</v>
+        <v>2</v>
       </c>
       <c r="D403" t="s">
-        <v>452</v>
+        <v>57</v>
       </c>
       <c r="E403" t="s">
-        <v>453</v>
+        <v>58</v>
       </c>
       <c r="F403" s="1">
-        <v>46213</v>
+        <v>46125</v>
       </c>
       <c r="G403" s="1">
-        <v>46216</v>
+        <v>46125</v>
       </c>
     </row>
     <row r="404" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A404" t="s">
-        <v>770</v>
+        <v>752</v>
       </c>
       <c r="B404" t="s">
-        <v>785</v>
+        <v>758</v>
       </c>
       <c r="C404" t="s">
         <v>2</v>
       </c>
       <c r="D404" t="s">
-        <v>127</v>
+        <v>57</v>
       </c>
       <c r="E404" t="s">
-        <v>128</v>
+        <v>58</v>
       </c>
       <c r="F404" s="1">
-        <v>46220</v>
+        <v>46126</v>
       </c>
       <c r="G404" s="1">
-        <v>46231</v>
+        <v>46126</v>
       </c>
     </row>
     <row r="405" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A405" t="s">
-        <v>770</v>
+        <v>752</v>
       </c>
       <c r="B405" t="s">
-        <v>786</v>
+        <v>759</v>
       </c>
       <c r="C405" t="s">
         <v>2</v>
       </c>
       <c r="D405" t="s">
-        <v>775</v>
+        <v>57</v>
       </c>
       <c r="E405" t="s">
-        <v>776</v>
+        <v>58</v>
       </c>
       <c r="F405" s="1">
-        <v>46223</v>
+        <v>46126</v>
       </c>
       <c r="G405" s="1">
-        <v>46223</v>
+        <v>46126</v>
       </c>
     </row>
     <row r="406" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A406" t="s">
-        <v>770</v>
+        <v>752</v>
       </c>
       <c r="B406" t="s">
-        <v>787</v>
+        <v>760</v>
       </c>
       <c r="C406" t="s">
-        <v>96</v>
+        <v>2</v>
       </c>
       <c r="D406" t="s">
-        <v>452</v>
+        <v>57</v>
       </c>
       <c r="E406" t="s">
-        <v>453</v>
+        <v>58</v>
       </c>
       <c r="F406" s="1">
-        <v>46224</v>
+        <v>46128</v>
       </c>
       <c r="G406" s="1">
-        <v>46224</v>
+        <v>46128</v>
       </c>
     </row>
     <row r="407" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A407" t="s">
-        <v>770</v>
+        <v>752</v>
       </c>
       <c r="B407" t="s">
-        <v>788</v>
+        <v>761</v>
       </c>
       <c r="C407" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D407" t="s">
-        <v>127</v>
+        <v>57</v>
       </c>
       <c r="E407" t="s">
-        <v>128</v>
+        <v>58</v>
       </c>
       <c r="F407" s="1">
-        <v>46232</v>
+        <v>46132</v>
       </c>
       <c r="G407" s="1">
-        <v>46233</v>
+        <v>46132</v>
       </c>
     </row>
     <row r="408" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A408" t="s">
-        <v>770</v>
+        <v>752</v>
       </c>
       <c r="B408" t="s">
-        <v>789</v>
+        <v>762</v>
       </c>
       <c r="C408" t="s">
         <v>2</v>
       </c>
       <c r="D408" t="s">
-        <v>127</v>
+        <v>57</v>
       </c>
       <c r="E408" t="s">
-        <v>128</v>
+        <v>58</v>
       </c>
       <c r="F408" s="1">
-        <v>46232</v>
+        <v>46161</v>
       </c>
       <c r="G408" s="1">
-        <v>46259</v>
+        <v>46161</v>
       </c>
     </row>
     <row r="409" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A409" t="s">
-        <v>770</v>
+        <v>752</v>
       </c>
       <c r="B409" t="s">
-        <v>790</v>
+        <v>763</v>
       </c>
       <c r="C409" t="s">
         <v>2</v>
       </c>
       <c r="D409" t="s">
-        <v>452</v>
+        <v>57</v>
       </c>
       <c r="E409" t="s">
-        <v>453</v>
+        <v>58</v>
       </c>
       <c r="F409" s="1">
-        <v>46238</v>
+        <v>46174</v>
       </c>
       <c r="G409" s="1">
-        <v>46239</v>
+        <v>46174</v>
       </c>
     </row>
     <row r="410" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A410" t="s">
-        <v>770</v>
+        <v>752</v>
       </c>
       <c r="B410" t="s">
-        <v>791</v>
+        <v>764</v>
       </c>
       <c r="C410" t="s">
         <v>2</v>
       </c>
       <c r="D410" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="E410" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="F410" s="1">
-        <v>46247</v>
+        <v>46174</v>
       </c>
       <c r="G410" s="1">
-        <v>46252</v>
+        <v>46174</v>
       </c>
     </row>
     <row r="411" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A411" t="s">
-        <v>770</v>
+        <v>752</v>
       </c>
       <c r="B411" t="s">
-        <v>792</v>
+        <v>765</v>
       </c>
       <c r="C411" t="s">
-        <v>6</v>
+        <v>80</v>
       </c>
       <c r="D411" t="s">
-        <v>793</v>
+        <v>57</v>
       </c>
       <c r="E411" t="s">
-        <v>794</v>
+        <v>58</v>
       </c>
       <c r="F411" s="1">
-        <v>46253</v>
+        <v>46195</v>
       </c>
       <c r="G411" s="1">
-        <v>46253</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="412" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A412" t="s">
-        <v>770</v>
+        <v>752</v>
       </c>
       <c r="B412" t="s">
-        <v>795</v>
+        <v>766</v>
       </c>
       <c r="C412" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D412" t="s">
-        <v>452</v>
+        <v>57</v>
       </c>
       <c r="E412" t="s">
-        <v>453</v>
+        <v>58</v>
       </c>
       <c r="F412" s="1">
-        <v>46253</v>
+        <v>46210</v>
       </c>
       <c r="G412" s="1">
-        <v>46259</v>
+        <v>46210</v>
       </c>
     </row>
     <row r="413" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A413" t="s">
-        <v>770</v>
+        <v>752</v>
       </c>
       <c r="B413" t="s">
-        <v>796</v>
+        <v>767</v>
       </c>
       <c r="C413" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D413" t="s">
-        <v>402</v>
+        <v>57</v>
       </c>
       <c r="E413" t="s">
-        <v>403</v>
+        <v>58</v>
       </c>
       <c r="F413" s="1">
-        <v>46255</v>
+        <v>46213</v>
       </c>
       <c r="G413" s="1">
-        <v>46258</v>
+        <v>46213</v>
       </c>
     </row>
     <row r="414" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A414" t="s">
-        <v>770</v>
+        <v>752</v>
       </c>
       <c r="B414" t="s">
-        <v>797</v>
+        <v>768</v>
       </c>
       <c r="C414" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D414" t="s">
-        <v>775</v>
+        <v>57</v>
       </c>
       <c r="E414" t="s">
-        <v>776</v>
+        <v>58</v>
       </c>
       <c r="F414" s="1">
-        <v>46258</v>
+        <v>46218</v>
       </c>
       <c r="G414" s="1">
-        <v>46259</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="415" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A415" t="s">
-        <v>770</v>
+        <v>752</v>
       </c>
       <c r="B415" t="s">
-        <v>798</v>
+        <v>769</v>
       </c>
       <c r="C415" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D415" t="s">
-        <v>452</v>
+        <v>77</v>
       </c>
       <c r="E415" t="s">
-        <v>453</v>
+        <v>78</v>
       </c>
       <c r="F415" s="1">
-        <v>46258</v>
+        <v>46226</v>
       </c>
       <c r="G415" s="1">
-        <v>46259</v>
+        <v>46226</v>
       </c>
     </row>
     <row r="416" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A416" t="s">
+        <v>752</v>
+      </c>
+      <c r="B416" t="s">
         <v>770</v>
       </c>
-      <c r="B416" t="s">
-        <v>799</v>
-      </c>
       <c r="C416" t="s">
         <v>80</v>
       </c>
       <c r="D416" t="s">
-        <v>470</v>
+        <v>57</v>
       </c>
       <c r="E416" t="s">
-        <v>471</v>
+        <v>58</v>
       </c>
       <c r="F416" s="1">
-        <v>46258</v>
+        <v>46227</v>
       </c>
       <c r="G416" s="1">
-        <v>46258</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="417" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A417" t="s">
-        <v>770</v>
+        <v>752</v>
       </c>
       <c r="B417" t="s">
-        <v>800</v>
+        <v>771</v>
       </c>
       <c r="C417" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D417" t="s">
-        <v>127</v>
+        <v>57</v>
       </c>
       <c r="E417" t="s">
-        <v>128</v>
+        <v>58</v>
       </c>
       <c r="F417" s="1">
-        <v>46259</v>
+        <v>46227</v>
       </c>
       <c r="G417" s="1">
-        <v>46259</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="418" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A418" t="s">
-        <v>770</v>
+        <v>752</v>
       </c>
       <c r="B418" t="s">
-        <v>801</v>
+        <v>772</v>
       </c>
       <c r="C418" t="s">
-        <v>80</v>
+        <v>6</v>
       </c>
       <c r="D418" t="s">
-        <v>402</v>
+        <v>57</v>
       </c>
       <c r="E418" t="s">
-        <v>403</v>
+        <v>58</v>
       </c>
       <c r="F418" s="1">
-        <v>46261</v>
+        <v>46227</v>
       </c>
       <c r="G418" s="1">
-        <v>46261</v>
+        <v>46228</v>
       </c>
     </row>
     <row r="419" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A419" t="s">
-        <v>770</v>
+        <v>752</v>
       </c>
       <c r="B419" t="s">
-        <v>802</v>
+        <v>773</v>
       </c>
       <c r="C419" t="s">
         <v>80</v>
       </c>
       <c r="D419" t="s">
-        <v>803</v>
+        <v>77</v>
       </c>
       <c r="E419" t="s">
-        <v>804</v>
+        <v>78</v>
       </c>
       <c r="F419" s="1">
-        <v>46261</v>
+        <v>46230</v>
       </c>
       <c r="G419" s="1">
-        <v>46261</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="420" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A420" t="s">
-        <v>770</v>
+        <v>752</v>
       </c>
       <c r="B420" t="s">
-        <v>805</v>
+        <v>774</v>
       </c>
       <c r="C420" t="s">
-        <v>80</v>
+        <v>6</v>
       </c>
       <c r="D420" t="s">
-        <v>806</v>
+        <v>57</v>
       </c>
       <c r="E420" t="s">
-        <v>807</v>
+        <v>58</v>
       </c>
       <c r="F420" s="1">
-        <v>46261</v>
+        <v>46231</v>
       </c>
       <c r="G420" s="1">
-        <v>46261</v>
+        <v>46231</v>
       </c>
     </row>
     <row r="421" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A421" t="s">
-        <v>808</v>
+        <v>752</v>
       </c>
       <c r="B421" t="s">
-        <v>809</v>
+        <v>775</v>
       </c>
       <c r="C421" t="s">
-        <v>96</v>
+        <v>6</v>
       </c>
       <c r="D421" t="s">
-        <v>810</v>
+        <v>57</v>
       </c>
       <c r="E421" t="s">
-        <v>811</v>
+        <v>58</v>
       </c>
       <c r="F421" s="1">
-        <v>46063</v>
+        <v>46254</v>
       </c>
       <c r="G421" s="1">
-        <v>46064</v>
+        <v>46254</v>
       </c>
     </row>
     <row r="422" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A422" t="s">
-        <v>808</v>
+        <v>752</v>
       </c>
       <c r="B422" t="s">
-        <v>812</v>
+        <v>776</v>
       </c>
       <c r="C422" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D422" t="s">
         <v>57</v>
@@ -12753,21 +12588,21 @@
         <v>58</v>
       </c>
       <c r="F422" s="1">
-        <v>46113</v>
+        <v>46255</v>
       </c>
       <c r="G422" s="1">
-        <v>46125</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="423" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A423" t="s">
-        <v>808</v>
+        <v>752</v>
       </c>
       <c r="B423" t="s">
-        <v>813</v>
+        <v>777</v>
       </c>
       <c r="C423" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D423" t="s">
         <v>57</v>
@@ -12776,21 +12611,21 @@
         <v>58</v>
       </c>
       <c r="F423" s="1">
-        <v>46125</v>
+        <v>46260</v>
       </c>
       <c r="G423" s="1">
-        <v>46125</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="424" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A424" t="s">
-        <v>808</v>
+        <v>752</v>
       </c>
       <c r="B424" t="s">
-        <v>814</v>
+        <v>778</v>
       </c>
       <c r="C424" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D424" t="s">
         <v>57</v>
@@ -12799,21 +12634,21 @@
         <v>58</v>
       </c>
       <c r="F424" s="1">
-        <v>46126</v>
+        <v>46262</v>
       </c>
       <c r="G424" s="1">
-        <v>46126</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="425" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A425" t="s">
-        <v>808</v>
+        <v>752</v>
       </c>
       <c r="B425" t="s">
-        <v>815</v>
+        <v>779</v>
       </c>
       <c r="C425" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D425" t="s">
         <v>57</v>
@@ -12822,21 +12657,21 @@
         <v>58</v>
       </c>
       <c r="F425" s="1">
-        <v>46126</v>
+        <v>46262</v>
       </c>
       <c r="G425" s="1">
-        <v>46126</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="426" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A426" t="s">
-        <v>808</v>
+        <v>752</v>
       </c>
       <c r="B426" t="s">
-        <v>816</v>
+        <v>780</v>
       </c>
       <c r="C426" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D426" t="s">
         <v>57</v>
@@ -12845,21 +12680,21 @@
         <v>58</v>
       </c>
       <c r="F426" s="1">
-        <v>46128</v>
+        <v>46262</v>
       </c>
       <c r="G426" s="1">
-        <v>46128</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="427" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A427" t="s">
-        <v>808</v>
+        <v>752</v>
       </c>
       <c r="B427" t="s">
-        <v>817</v>
+        <v>781</v>
       </c>
       <c r="C427" t="s">
-        <v>6</v>
+        <v>80</v>
       </c>
       <c r="D427" t="s">
         <v>57</v>
@@ -12868,21 +12703,21 @@
         <v>58</v>
       </c>
       <c r="F427" s="1">
-        <v>46132</v>
+        <v>46262</v>
       </c>
       <c r="G427" s="1">
-        <v>46132</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="428" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A428" t="s">
-        <v>808</v>
+        <v>752</v>
       </c>
       <c r="B428" t="s">
-        <v>818</v>
+        <v>782</v>
       </c>
       <c r="C428" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D428" t="s">
         <v>57</v>
@@ -12891,21 +12726,21 @@
         <v>58</v>
       </c>
       <c r="F428" s="1">
-        <v>46161</v>
+        <v>46262</v>
       </c>
       <c r="G428" s="1">
-        <v>46161</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="429" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A429" t="s">
-        <v>808</v>
+        <v>752</v>
       </c>
       <c r="B429" t="s">
-        <v>819</v>
+        <v>783</v>
       </c>
       <c r="C429" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D429" t="s">
         <v>57</v>
@@ -12914,607 +12749,216 @@
         <v>58</v>
       </c>
       <c r="F429" s="1">
-        <v>46174</v>
+        <v>46262</v>
       </c>
       <c r="G429" s="1">
-        <v>46174</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="430" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A430" t="s">
-        <v>808</v>
+        <v>784</v>
       </c>
       <c r="B430" t="s">
-        <v>820</v>
+        <v>785</v>
       </c>
       <c r="C430" t="s">
         <v>2</v>
       </c>
       <c r="D430" t="s">
-        <v>57</v>
+        <v>786</v>
       </c>
       <c r="E430" t="s">
-        <v>58</v>
+        <v>787</v>
       </c>
       <c r="F430" s="1">
-        <v>46174</v>
+        <v>46083</v>
       </c>
       <c r="G430" s="1">
-        <v>46174</v>
+        <v>46084</v>
       </c>
     </row>
     <row r="431" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A431" t="s">
-        <v>808</v>
+        <v>784</v>
       </c>
       <c r="B431" t="s">
-        <v>821</v>
+        <v>788</v>
       </c>
       <c r="C431" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D431" t="s">
-        <v>57</v>
+        <v>786</v>
       </c>
       <c r="E431" t="s">
-        <v>58</v>
+        <v>787</v>
       </c>
       <c r="F431" s="1">
-        <v>46195</v>
+        <v>46132</v>
       </c>
       <c r="G431" s="1">
-        <v>46252</v>
+        <v>46133</v>
       </c>
     </row>
     <row r="432" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A432" t="s">
-        <v>808</v>
+        <v>784</v>
       </c>
       <c r="B432" t="s">
-        <v>822</v>
+        <v>789</v>
       </c>
       <c r="C432" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D432" t="s">
-        <v>57</v>
+        <v>705</v>
       </c>
       <c r="E432" t="s">
-        <v>58</v>
+        <v>706</v>
       </c>
       <c r="F432" s="1">
-        <v>46210</v>
+        <v>46157</v>
       </c>
       <c r="G432" s="1">
-        <v>46210</v>
+        <v>46157</v>
       </c>
     </row>
     <row r="433" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A433" t="s">
-        <v>808</v>
+        <v>784</v>
       </c>
       <c r="B433" t="s">
-        <v>823</v>
+        <v>790</v>
       </c>
       <c r="C433" t="s">
         <v>2</v>
       </c>
       <c r="D433" t="s">
-        <v>57</v>
+        <v>791</v>
       </c>
       <c r="E433" t="s">
-        <v>58</v>
+        <v>792</v>
       </c>
       <c r="F433" s="1">
-        <v>46213</v>
+        <v>46168</v>
       </c>
       <c r="G433" s="1">
-        <v>46213</v>
+        <v>46170</v>
       </c>
     </row>
     <row r="434" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A434" t="s">
-        <v>808</v>
+        <v>784</v>
       </c>
       <c r="B434" t="s">
-        <v>824</v>
+        <v>793</v>
       </c>
       <c r="C434" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D434" t="s">
-        <v>57</v>
+        <v>705</v>
       </c>
       <c r="E434" t="s">
-        <v>58</v>
+        <v>706</v>
       </c>
       <c r="F434" s="1">
-        <v>46218</v>
+        <v>46244</v>
       </c>
       <c r="G434" s="1">
-        <v>46252</v>
+        <v>46244</v>
       </c>
     </row>
     <row r="435" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A435" t="s">
-        <v>808</v>
+        <v>784</v>
       </c>
       <c r="B435" t="s">
-        <v>825</v>
+        <v>794</v>
       </c>
       <c r="C435" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D435" t="s">
-        <v>77</v>
+        <v>705</v>
       </c>
       <c r="E435" t="s">
-        <v>78</v>
+        <v>706</v>
       </c>
       <c r="F435" s="1">
-        <v>46226</v>
+        <v>46247</v>
       </c>
       <c r="G435" s="1">
-        <v>46226</v>
+        <v>46247</v>
       </c>
     </row>
     <row r="436" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A436" t="s">
-        <v>808</v>
+        <v>784</v>
       </c>
       <c r="B436" t="s">
-        <v>826</v>
+        <v>795</v>
       </c>
       <c r="C436" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D436" t="s">
-        <v>57</v>
+        <v>786</v>
       </c>
       <c r="E436" t="s">
-        <v>58</v>
+        <v>787</v>
       </c>
       <c r="F436" s="1">
-        <v>46227</v>
+        <v>46247</v>
       </c>
       <c r="G436" s="1">
-        <v>46252</v>
+        <v>46247</v>
       </c>
     </row>
     <row r="437" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A437" t="s">
-        <v>808</v>
+        <v>784</v>
       </c>
       <c r="B437" t="s">
-        <v>827</v>
+        <v>796</v>
       </c>
       <c r="C437" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D437" t="s">
-        <v>57</v>
+        <v>705</v>
       </c>
       <c r="E437" t="s">
-        <v>58</v>
+        <v>706</v>
       </c>
       <c r="F437" s="1">
-        <v>46227</v>
+        <v>46255</v>
       </c>
       <c r="G437" s="1">
-        <v>46252</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="438" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A438" t="s">
-        <v>808</v>
+        <v>784</v>
       </c>
       <c r="B438" t="s">
-        <v>828</v>
+        <v>797</v>
       </c>
       <c r="C438" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D438" t="s">
-        <v>57</v>
+        <v>705</v>
       </c>
       <c r="E438" t="s">
-        <v>58</v>
+        <v>706</v>
       </c>
       <c r="F438" s="1">
-        <v>46227</v>
+        <v>46258</v>
       </c>
       <c r="G438" s="1">
-        <v>46228</v>
-      </c>
-    </row>
-    <row r="439" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A439" t="s">
-        <v>808</v>
-      </c>
-      <c r="B439" t="s">
-        <v>829</v>
-      </c>
-      <c r="C439" t="s">
-        <v>80</v>
-      </c>
-      <c r="D439" t="s">
-        <v>77</v>
-      </c>
-      <c r="E439" t="s">
-        <v>78</v>
-      </c>
-      <c r="F439" s="1">
-        <v>46230</v>
-      </c>
-      <c r="G439" s="1">
-        <v>46252</v>
-      </c>
-    </row>
-    <row r="440" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A440" t="s">
-        <v>808</v>
-      </c>
-      <c r="B440" t="s">
-        <v>830</v>
-      </c>
-      <c r="C440" t="s">
-        <v>6</v>
-      </c>
-      <c r="D440" t="s">
-        <v>57</v>
-      </c>
-      <c r="E440" t="s">
-        <v>58</v>
-      </c>
-      <c r="F440" s="1">
-        <v>46231</v>
-      </c>
-      <c r="G440" s="1">
-        <v>46231</v>
-      </c>
-    </row>
-    <row r="441" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A441" t="s">
-        <v>808</v>
-      </c>
-      <c r="B441" t="s">
-        <v>831</v>
-      </c>
-      <c r="C441" t="s">
-        <v>6</v>
-      </c>
-      <c r="D441" t="s">
-        <v>57</v>
-      </c>
-      <c r="E441" t="s">
-        <v>58</v>
-      </c>
-      <c r="F441" s="1">
-        <v>46254</v>
-      </c>
-      <c r="G441" s="1">
-        <v>46254</v>
-      </c>
-    </row>
-    <row r="442" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A442" t="s">
-        <v>808</v>
-      </c>
-      <c r="B442" t="s">
-        <v>832</v>
-      </c>
-      <c r="C442" t="s">
-        <v>2</v>
-      </c>
-      <c r="D442" t="s">
-        <v>57</v>
-      </c>
-      <c r="E442" t="s">
-        <v>58</v>
-      </c>
-      <c r="F442" s="1">
-        <v>46255</v>
-      </c>
-      <c r="G442" s="1">
-        <v>46255</v>
-      </c>
-    </row>
-    <row r="443" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A443" t="s">
-        <v>808</v>
-      </c>
-      <c r="B443" t="s">
-        <v>833</v>
-      </c>
-      <c r="C443" t="s">
-        <v>6</v>
-      </c>
-      <c r="D443" t="s">
-        <v>57</v>
-      </c>
-      <c r="E443" t="s">
-        <v>58</v>
-      </c>
-      <c r="F443" s="1">
-        <v>46260</v>
-      </c>
-      <c r="G443" s="1">
-        <v>46260</v>
-      </c>
-    </row>
-    <row r="444" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A444" t="s">
-        <v>808</v>
-      </c>
-      <c r="B444" t="s">
-        <v>834</v>
-      </c>
-      <c r="C444" t="s">
-        <v>80</v>
-      </c>
-      <c r="D444" t="s">
-        <v>57</v>
-      </c>
-      <c r="E444" t="s">
-        <v>58</v>
-      </c>
-      <c r="F444" s="1">
-        <v>46262</v>
-      </c>
-      <c r="G444" s="1">
-        <v>46262</v>
-      </c>
-    </row>
-    <row r="445" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A445" t="s">
-        <v>808</v>
-      </c>
-      <c r="B445" t="s">
-        <v>835</v>
-      </c>
-      <c r="C445" t="s">
-        <v>80</v>
-      </c>
-      <c r="D445" t="s">
-        <v>57</v>
-      </c>
-      <c r="E445" t="s">
-        <v>58</v>
-      </c>
-      <c r="F445" s="1">
-        <v>46262</v>
-      </c>
-      <c r="G445" s="1">
-        <v>46262</v>
-      </c>
-    </row>
-    <row r="446" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A446" t="s">
-        <v>808</v>
-      </c>
-      <c r="B446" t="s">
-        <v>836</v>
-      </c>
-      <c r="C446" t="s">
-        <v>80</v>
-      </c>
-      <c r="D446" t="s">
-        <v>57</v>
-      </c>
-      <c r="E446" t="s">
-        <v>58</v>
-      </c>
-      <c r="F446" s="1">
-        <v>46262</v>
-      </c>
-      <c r="G446" s="1">
-        <v>46262</v>
-      </c>
-    </row>
-    <row r="447" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A447" t="s">
-        <v>837</v>
-      </c>
-      <c r="B447" t="s">
-        <v>838</v>
-      </c>
-      <c r="C447" t="s">
-        <v>2</v>
-      </c>
-      <c r="D447" t="s">
-        <v>839</v>
-      </c>
-      <c r="E447" t="s">
-        <v>840</v>
-      </c>
-      <c r="F447" s="1">
-        <v>46083</v>
-      </c>
-      <c r="G447" s="1">
-        <v>46084</v>
-      </c>
-    </row>
-    <row r="448" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A448" t="s">
-        <v>837</v>
-      </c>
-      <c r="B448" t="s">
-        <v>841</v>
-      </c>
-      <c r="C448" t="s">
-        <v>2</v>
-      </c>
-      <c r="D448" t="s">
-        <v>839</v>
-      </c>
-      <c r="E448" t="s">
-        <v>840</v>
-      </c>
-      <c r="F448" s="1">
-        <v>46132</v>
-      </c>
-      <c r="G448" s="1">
-        <v>46133</v>
-      </c>
-    </row>
-    <row r="449" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A449" t="s">
-        <v>837</v>
-      </c>
-      <c r="B449" t="s">
-        <v>842</v>
-      </c>
-      <c r="C449" t="s">
-        <v>2</v>
-      </c>
-      <c r="D449" t="s">
-        <v>843</v>
-      </c>
-      <c r="E449" t="s">
-        <v>844</v>
-      </c>
-      <c r="F449" s="1">
-        <v>46157</v>
-      </c>
-      <c r="G449" s="1">
-        <v>46157</v>
-      </c>
-    </row>
-    <row r="450" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A450" t="s">
-        <v>837</v>
-      </c>
-      <c r="B450" t="s">
-        <v>845</v>
-      </c>
-      <c r="C450" t="s">
-        <v>2</v>
-      </c>
-      <c r="D450" t="s">
-        <v>846</v>
-      </c>
-      <c r="E450" t="s">
-        <v>847</v>
-      </c>
-      <c r="F450" s="1">
-        <v>46168</v>
-      </c>
-      <c r="G450" s="1">
-        <v>46170</v>
-      </c>
-    </row>
-    <row r="451" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A451" t="s">
-        <v>837</v>
-      </c>
-      <c r="B451" t="s">
-        <v>848</v>
-      </c>
-      <c r="C451" t="s">
-        <v>2</v>
-      </c>
-      <c r="D451" t="s">
-        <v>843</v>
-      </c>
-      <c r="E451" t="s">
-        <v>844</v>
-      </c>
-      <c r="F451" s="1">
-        <v>46244</v>
-      </c>
-      <c r="G451" s="1">
-        <v>46244</v>
-      </c>
-    </row>
-    <row r="452" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A452" t="s">
-        <v>837</v>
-      </c>
-      <c r="B452" t="s">
-        <v>849</v>
-      </c>
-      <c r="C452" t="s">
-        <v>2</v>
-      </c>
-      <c r="D452" t="s">
-        <v>843</v>
-      </c>
-      <c r="E452" t="s">
-        <v>844</v>
-      </c>
-      <c r="F452" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G452" s="1">
-        <v>46247</v>
-      </c>
-    </row>
-    <row r="453" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A453" t="s">
-        <v>837</v>
-      </c>
-      <c r="B453" t="s">
-        <v>850</v>
-      </c>
-      <c r="C453" t="s">
-        <v>2</v>
-      </c>
-      <c r="D453" t="s">
-        <v>839</v>
-      </c>
-      <c r="E453" t="s">
-        <v>840</v>
-      </c>
-      <c r="F453" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G453" s="1">
-        <v>46247</v>
-      </c>
-    </row>
-    <row r="454" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A454" t="s">
-        <v>837</v>
-      </c>
-      <c r="B454" t="s">
-        <v>851</v>
-      </c>
-      <c r="C454" t="s">
-        <v>2</v>
-      </c>
-      <c r="D454" t="s">
-        <v>843</v>
-      </c>
-      <c r="E454" t="s">
-        <v>844</v>
-      </c>
-      <c r="F454" s="1">
-        <v>46255</v>
-      </c>
-      <c r="G454" s="1">
-        <v>46255</v>
-      </c>
-    </row>
-    <row r="455" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A455" t="s">
-        <v>837</v>
-      </c>
-      <c r="B455" t="s">
-        <v>852</v>
-      </c>
-      <c r="C455" t="s">
-        <v>2</v>
-      </c>
-      <c r="D455" t="s">
-        <v>843</v>
-      </c>
-      <c r="E455" t="s">
-        <v>844</v>
-      </c>
-      <c r="F455" s="1">
-        <v>46258</v>
-      </c>
-      <c r="G455" s="1">
         <v>46258</v>
       </c>
     </row>

--- a/Data_ERP/Pedidos Transmicion.xlsx
+++ b/Data_ERP/Pedidos Transmicion.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sistema_Logistico_Peirano\Data_ERP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BFCF6CEA-E211-44D0-9B14-95D9B4A65337}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E3389E81-2B0A-4D8B-B054-ABD39129DDCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25230" yWindow="4080" windowWidth="15375" windowHeight="8325" xr2:uid="{0387AA51-D7FF-49B4-9616-210EF5E8A02F}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{AC707633-82CA-4A69-8930-E54342FE1B21}"/>
   </bookViews>
   <sheets>
     <sheet name="transmicion" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2192" uniqueCount="805">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2152" uniqueCount="795">
   <si>
     <t>0001</t>
   </si>
@@ -2257,21 +2257,9 @@
     <t xml:space="preserve">    2846</t>
   </si>
   <si>
-    <t xml:space="preserve">    2849</t>
-  </si>
-  <si>
     <t xml:space="preserve">    2851</t>
   </si>
   <si>
-    <t xml:space="preserve">    2860</t>
-  </si>
-  <si>
-    <t>MB13</t>
-  </si>
-  <si>
-    <t>MATERIALES BASUALDO S.A.</t>
-  </si>
-  <si>
     <t xml:space="preserve">    2862</t>
   </si>
   <si>
@@ -2354,24 +2342,6 @@
   </si>
   <si>
     <t xml:space="preserve">    2301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    2334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    2335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    2336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    2337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    2339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    2340</t>
   </si>
   <si>
     <t>9999</t>
@@ -2884,31 +2854,31 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{961C53E3-9F57-4010-80CB-BC209C238E0C}">
-  <dimension ref="A1:G438"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2526AF24-EA90-4723-B15F-F71EC0F581FF}">
+  <dimension ref="A1:G430"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
-        <v>798</v>
+        <v>788</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>799</v>
+        <v>789</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>800</v>
+        <v>790</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>801</v>
+        <v>791</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>802</v>
+        <v>792</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>803</v>
+        <v>793</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>804</v>
+        <v>794</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
@@ -7013,7 +6983,7 @@
         <v>381</v>
       </c>
       <c r="C180" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D180" t="s">
         <v>16</v>
@@ -7059,7 +7029,7 @@
         <v>385</v>
       </c>
       <c r="C182" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D182" t="s">
         <v>16</v>
@@ -7151,7 +7121,7 @@
         <v>395</v>
       </c>
       <c r="C186" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D186" t="s">
         <v>16</v>
@@ -7220,7 +7190,7 @@
         <v>398</v>
       </c>
       <c r="C189" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D189" t="s">
         <v>16</v>
@@ -7381,7 +7351,7 @@
         <v>409</v>
       </c>
       <c r="C196" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D196" t="s">
         <v>16</v>
@@ -7473,7 +7443,7 @@
         <v>417</v>
       </c>
       <c r="C200" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D200" t="s">
         <v>16</v>
@@ -7496,7 +7466,7 @@
         <v>418</v>
       </c>
       <c r="C201" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D201" t="s">
         <v>419</v>
@@ -7519,7 +7489,7 @@
         <v>421</v>
       </c>
       <c r="C202" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D202" t="s">
         <v>377</v>
@@ -7588,7 +7558,7 @@
         <v>428</v>
       </c>
       <c r="C205" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D205" t="s">
         <v>171</v>
@@ -7680,7 +7650,7 @@
         <v>436</v>
       </c>
       <c r="C209" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D209" t="s">
         <v>437</v>
@@ -7841,7 +7811,7 @@
         <v>449</v>
       </c>
       <c r="C216" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D216" t="s">
         <v>450</v>
@@ -7910,7 +7880,7 @@
         <v>456</v>
       </c>
       <c r="C219" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D219" t="s">
         <v>450</v>
@@ -7979,7 +7949,7 @@
         <v>463</v>
       </c>
       <c r="C222" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D222" t="s">
         <v>454</v>
@@ -8002,7 +7972,7 @@
         <v>464</v>
       </c>
       <c r="C223" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D223" t="s">
         <v>299</v>
@@ -8048,7 +8018,7 @@
         <v>466</v>
       </c>
       <c r="C225" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D225" t="s">
         <v>467</v>
@@ -8071,7 +8041,7 @@
         <v>469</v>
       </c>
       <c r="C226" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D226" t="s">
         <v>470</v>
@@ -8393,7 +8363,7 @@
         <v>489</v>
       </c>
       <c r="C240" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D240" t="s">
         <v>490</v>
@@ -8485,7 +8455,7 @@
         <v>499</v>
       </c>
       <c r="C244" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D244" t="s">
         <v>419</v>
@@ -8508,7 +8478,7 @@
         <v>500</v>
       </c>
       <c r="C245" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D245" t="s">
         <v>437</v>
@@ -8830,7 +8800,7 @@
         <v>522</v>
       </c>
       <c r="C259" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D259" t="s">
         <v>467</v>
@@ -9014,7 +8984,7 @@
         <v>538</v>
       </c>
       <c r="C267" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D267" t="s">
         <v>536</v>
@@ -9037,7 +9007,7 @@
         <v>539</v>
       </c>
       <c r="C268" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D268" t="s">
         <v>426</v>
@@ -9060,7 +9030,7 @@
         <v>540</v>
       </c>
       <c r="C269" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D269" t="s">
         <v>467</v>
@@ -9083,7 +9053,7 @@
         <v>541</v>
       </c>
       <c r="C270" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D270" t="s">
         <v>16</v>
@@ -9129,7 +9099,7 @@
         <v>543</v>
       </c>
       <c r="C272" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D272" t="s">
         <v>544</v>
@@ -9175,7 +9145,7 @@
         <v>547</v>
       </c>
       <c r="C274" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D274" t="s">
         <v>548</v>
@@ -9198,7 +9168,7 @@
         <v>550</v>
       </c>
       <c r="C275" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D275" t="s">
         <v>551</v>
@@ -9290,7 +9260,7 @@
         <v>556</v>
       </c>
       <c r="C279" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D279" t="s">
         <v>557</v>
@@ -9336,7 +9306,7 @@
         <v>562</v>
       </c>
       <c r="C281" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D281" t="s">
         <v>563</v>
@@ -9842,7 +9812,7 @@
         <v>596</v>
       </c>
       <c r="C303" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D303" t="s">
         <v>597</v>
@@ -9865,7 +9835,7 @@
         <v>599</v>
       </c>
       <c r="C304" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D304" t="s">
         <v>600</v>
@@ -9980,7 +9950,7 @@
         <v>610</v>
       </c>
       <c r="C309" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D309" t="s">
         <v>450</v>
@@ -10003,7 +9973,7 @@
         <v>611</v>
       </c>
       <c r="C310" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D310" t="s">
         <v>93</v>
@@ -10026,7 +9996,7 @@
         <v>612</v>
       </c>
       <c r="C311" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D311" t="s">
         <v>93</v>
@@ -10095,7 +10065,7 @@
         <v>619</v>
       </c>
       <c r="C314" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D314" t="s">
         <v>620</v>
@@ -10118,7 +10088,7 @@
         <v>622</v>
       </c>
       <c r="C315" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D315" t="s">
         <v>430</v>
@@ -10187,7 +10157,7 @@
         <v>625</v>
       </c>
       <c r="C318" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D318" t="s">
         <v>101</v>
@@ -10417,7 +10387,7 @@
         <v>643</v>
       </c>
       <c r="C328" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D328" t="s">
         <v>450</v>
@@ -10440,7 +10410,7 @@
         <v>644</v>
       </c>
       <c r="C329" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D329" t="s">
         <v>450</v>
@@ -10486,7 +10456,7 @@
         <v>646</v>
       </c>
       <c r="C331" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D331" t="s">
         <v>450</v>
@@ -10578,7 +10548,7 @@
         <v>654</v>
       </c>
       <c r="C335" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D335" t="s">
         <v>200</v>
@@ -10808,7 +10778,7 @@
         <v>672</v>
       </c>
       <c r="C345" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D345" t="s">
         <v>673</v>
@@ -11383,7 +11353,7 @@
         <v>703</v>
       </c>
       <c r="C370" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D370" t="s">
         <v>470</v>
@@ -11981,19 +11951,19 @@
         <v>745</v>
       </c>
       <c r="C396" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D396" t="s">
-        <v>450</v>
+        <v>127</v>
       </c>
       <c r="E396" t="s">
-        <v>451</v>
+        <v>128</v>
       </c>
       <c r="F396" s="1">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="G396" s="1">
-        <v>46258</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="397" spans="1:7" x14ac:dyDescent="0.2">
@@ -12004,19 +11974,19 @@
         <v>746</v>
       </c>
       <c r="C397" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D397" t="s">
-        <v>127</v>
+        <v>433</v>
       </c>
       <c r="E397" t="s">
-        <v>128</v>
+        <v>434</v>
       </c>
       <c r="F397" s="1">
-        <v>46259</v>
+        <v>46262</v>
       </c>
       <c r="G397" s="1">
-        <v>46259</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="398" spans="1:7" x14ac:dyDescent="0.2">
@@ -12030,96 +12000,96 @@
         <v>80</v>
       </c>
       <c r="D398" t="s">
-        <v>748</v>
+        <v>726</v>
       </c>
       <c r="E398" t="s">
-        <v>749</v>
+        <v>727</v>
       </c>
       <c r="F398" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="G398" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="399" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A399" t="s">
-        <v>715</v>
+        <v>748</v>
       </c>
       <c r="B399" t="s">
+        <v>749</v>
+      </c>
+      <c r="C399" t="s">
+        <v>96</v>
+      </c>
+      <c r="D399" t="s">
         <v>750</v>
       </c>
-      <c r="C399" t="s">
-        <v>80</v>
-      </c>
-      <c r="D399" t="s">
-        <v>433</v>
-      </c>
       <c r="E399" t="s">
-        <v>434</v>
+        <v>751</v>
       </c>
       <c r="F399" s="1">
-        <v>46262</v>
+        <v>46063</v>
       </c>
       <c r="G399" s="1">
-        <v>46262</v>
+        <v>46064</v>
       </c>
     </row>
     <row r="400" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A400" t="s">
-        <v>715</v>
+        <v>748</v>
       </c>
       <c r="B400" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="C400" t="s">
-        <v>80</v>
+        <v>6</v>
       </c>
       <c r="D400" t="s">
-        <v>726</v>
+        <v>57</v>
       </c>
       <c r="E400" t="s">
-        <v>727</v>
+        <v>58</v>
       </c>
       <c r="F400" s="1">
-        <v>46262</v>
+        <v>46113</v>
       </c>
       <c r="G400" s="1">
-        <v>46262</v>
+        <v>46125</v>
       </c>
     </row>
     <row r="401" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A401" t="s">
-        <v>752</v>
+        <v>748</v>
       </c>
       <c r="B401" t="s">
         <v>753</v>
       </c>
       <c r="C401" t="s">
-        <v>96</v>
+        <v>2</v>
       </c>
       <c r="D401" t="s">
-        <v>754</v>
+        <v>57</v>
       </c>
       <c r="E401" t="s">
-        <v>755</v>
+        <v>58</v>
       </c>
       <c r="F401" s="1">
-        <v>46063</v>
+        <v>46125</v>
       </c>
       <c r="G401" s="1">
-        <v>46064</v>
+        <v>46125</v>
       </c>
     </row>
     <row r="402" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A402" t="s">
-        <v>752</v>
+        <v>748</v>
       </c>
       <c r="B402" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="C402" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D402" t="s">
         <v>57</v>
@@ -12128,18 +12098,18 @@
         <v>58</v>
       </c>
       <c r="F402" s="1">
-        <v>46113</v>
+        <v>46126</v>
       </c>
       <c r="G402" s="1">
-        <v>46125</v>
+        <v>46126</v>
       </c>
     </row>
     <row r="403" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A403" t="s">
-        <v>752</v>
+        <v>748</v>
       </c>
       <c r="B403" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="C403" t="s">
         <v>2</v>
@@ -12151,18 +12121,18 @@
         <v>58</v>
       </c>
       <c r="F403" s="1">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="G403" s="1">
-        <v>46125</v>
+        <v>46126</v>
       </c>
     </row>
     <row r="404" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A404" t="s">
-        <v>752</v>
+        <v>748</v>
       </c>
       <c r="B404" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="C404" t="s">
         <v>2</v>
@@ -12174,21 +12144,21 @@
         <v>58</v>
       </c>
       <c r="F404" s="1">
-        <v>46126</v>
+        <v>46128</v>
       </c>
       <c r="G404" s="1">
-        <v>46126</v>
+        <v>46128</v>
       </c>
     </row>
     <row r="405" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A405" t="s">
-        <v>752</v>
+        <v>748</v>
       </c>
       <c r="B405" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="C405" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D405" t="s">
         <v>57</v>
@@ -12197,18 +12167,18 @@
         <v>58</v>
       </c>
       <c r="F405" s="1">
-        <v>46126</v>
+        <v>46132</v>
       </c>
       <c r="G405" s="1">
-        <v>46126</v>
+        <v>46132</v>
       </c>
     </row>
     <row r="406" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A406" t="s">
-        <v>752</v>
+        <v>748</v>
       </c>
       <c r="B406" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="C406" t="s">
         <v>2</v>
@@ -12220,21 +12190,21 @@
         <v>58</v>
       </c>
       <c r="F406" s="1">
-        <v>46128</v>
+        <v>46161</v>
       </c>
       <c r="G406" s="1">
-        <v>46128</v>
+        <v>46161</v>
       </c>
     </row>
     <row r="407" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A407" t="s">
-        <v>752</v>
+        <v>748</v>
       </c>
       <c r="B407" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="C407" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D407" t="s">
         <v>57</v>
@@ -12243,18 +12213,18 @@
         <v>58</v>
       </c>
       <c r="F407" s="1">
-        <v>46132</v>
+        <v>46174</v>
       </c>
       <c r="G407" s="1">
-        <v>46132</v>
+        <v>46174</v>
       </c>
     </row>
     <row r="408" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A408" t="s">
-        <v>752</v>
+        <v>748</v>
       </c>
       <c r="B408" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="C408" t="s">
         <v>2</v>
@@ -12266,21 +12236,21 @@
         <v>58</v>
       </c>
       <c r="F408" s="1">
-        <v>46161</v>
+        <v>46174</v>
       </c>
       <c r="G408" s="1">
-        <v>46161</v>
+        <v>46174</v>
       </c>
     </row>
     <row r="409" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A409" t="s">
-        <v>752</v>
+        <v>748</v>
       </c>
       <c r="B409" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="C409" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D409" t="s">
         <v>57</v>
@@ -12289,21 +12259,21 @@
         <v>58</v>
       </c>
       <c r="F409" s="1">
-        <v>46174</v>
+        <v>46195</v>
       </c>
       <c r="G409" s="1">
-        <v>46174</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="410" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A410" t="s">
-        <v>752</v>
+        <v>748</v>
       </c>
       <c r="B410" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="C410" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D410" t="s">
         <v>57</v>
@@ -12312,21 +12282,21 @@
         <v>58</v>
       </c>
       <c r="F410" s="1">
-        <v>46174</v>
+        <v>46210</v>
       </c>
       <c r="G410" s="1">
-        <v>46174</v>
+        <v>46210</v>
       </c>
     </row>
     <row r="411" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A411" t="s">
-        <v>752</v>
+        <v>748</v>
       </c>
       <c r="B411" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="C411" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D411" t="s">
         <v>57</v>
@@ -12335,21 +12305,21 @@
         <v>58</v>
       </c>
       <c r="F411" s="1">
-        <v>46195</v>
+        <v>46213</v>
       </c>
       <c r="G411" s="1">
-        <v>46252</v>
+        <v>46213</v>
       </c>
     </row>
     <row r="412" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A412" t="s">
-        <v>752</v>
+        <v>748</v>
       </c>
       <c r="B412" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="C412" t="s">
-        <v>6</v>
+        <v>80</v>
       </c>
       <c r="D412" t="s">
         <v>57</v>
@@ -12358,41 +12328,41 @@
         <v>58</v>
       </c>
       <c r="F412" s="1">
-        <v>46210</v>
+        <v>46218</v>
       </c>
       <c r="G412" s="1">
-        <v>46210</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="413" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A413" t="s">
-        <v>752</v>
+        <v>748</v>
       </c>
       <c r="B413" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="C413" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D413" t="s">
-        <v>57</v>
+        <v>77</v>
       </c>
       <c r="E413" t="s">
-        <v>58</v>
+        <v>78</v>
       </c>
       <c r="F413" s="1">
-        <v>46213</v>
+        <v>46226</v>
       </c>
       <c r="G413" s="1">
-        <v>46213</v>
+        <v>46226</v>
       </c>
     </row>
     <row r="414" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A414" t="s">
-        <v>752</v>
+        <v>748</v>
       </c>
       <c r="B414" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="C414" t="s">
         <v>80</v>
@@ -12404,7 +12374,7 @@
         <v>58</v>
       </c>
       <c r="F414" s="1">
-        <v>46218</v>
+        <v>46227</v>
       </c>
       <c r="G414" s="1">
         <v>46252</v>
@@ -12412,36 +12382,36 @@
     </row>
     <row r="415" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A415" t="s">
-        <v>752</v>
+        <v>748</v>
       </c>
       <c r="B415" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="C415" t="s">
-        <v>6</v>
+        <v>80</v>
       </c>
       <c r="D415" t="s">
-        <v>77</v>
+        <v>57</v>
       </c>
       <c r="E415" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="F415" s="1">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="G415" s="1">
-        <v>46226</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="416" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A416" t="s">
-        <v>752</v>
+        <v>748</v>
       </c>
       <c r="B416" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="C416" t="s">
-        <v>80</v>
+        <v>6</v>
       </c>
       <c r="D416" t="s">
         <v>57</v>
@@ -12453,27 +12423,27 @@
         <v>46227</v>
       </c>
       <c r="G416" s="1">
-        <v>46252</v>
+        <v>46228</v>
       </c>
     </row>
     <row r="417" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A417" t="s">
-        <v>752</v>
+        <v>748</v>
       </c>
       <c r="B417" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="C417" t="s">
         <v>80</v>
       </c>
       <c r="D417" t="s">
-        <v>57</v>
+        <v>77</v>
       </c>
       <c r="E417" t="s">
-        <v>58</v>
+        <v>78</v>
       </c>
       <c r="F417" s="1">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="G417" s="1">
         <v>46252</v>
@@ -12481,10 +12451,10 @@
     </row>
     <row r="418" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A418" t="s">
-        <v>752</v>
+        <v>748</v>
       </c>
       <c r="B418" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="C418" t="s">
         <v>6</v>
@@ -12496,44 +12466,44 @@
         <v>58</v>
       </c>
       <c r="F418" s="1">
-        <v>46227</v>
+        <v>46231</v>
       </c>
       <c r="G418" s="1">
-        <v>46228</v>
+        <v>46231</v>
       </c>
     </row>
     <row r="419" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A419" t="s">
-        <v>752</v>
+        <v>748</v>
       </c>
       <c r="B419" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="C419" t="s">
-        <v>80</v>
+        <v>6</v>
       </c>
       <c r="D419" t="s">
-        <v>77</v>
+        <v>57</v>
       </c>
       <c r="E419" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="F419" s="1">
-        <v>46230</v>
+        <v>46254</v>
       </c>
       <c r="G419" s="1">
-        <v>46252</v>
+        <v>46254</v>
       </c>
     </row>
     <row r="420" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A420" t="s">
-        <v>752</v>
+        <v>748</v>
       </c>
       <c r="B420" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="C420" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D420" t="s">
         <v>57</v>
@@ -12542,18 +12512,18 @@
         <v>58</v>
       </c>
       <c r="F420" s="1">
-        <v>46231</v>
+        <v>46255</v>
       </c>
       <c r="G420" s="1">
-        <v>46231</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="421" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A421" t="s">
-        <v>752</v>
+        <v>748</v>
       </c>
       <c r="B421" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="C421" t="s">
         <v>6</v>
@@ -12565,400 +12535,216 @@
         <v>58</v>
       </c>
       <c r="F421" s="1">
-        <v>46254</v>
+        <v>46260</v>
       </c>
       <c r="G421" s="1">
-        <v>46254</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="422" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A422" t="s">
-        <v>752</v>
+        <v>774</v>
       </c>
       <c r="B422" t="s">
+        <v>775</v>
+      </c>
+      <c r="C422" t="s">
+        <v>2</v>
+      </c>
+      <c r="D422" t="s">
         <v>776</v>
       </c>
-      <c r="C422" t="s">
-        <v>2</v>
-      </c>
-      <c r="D422" t="s">
-        <v>57</v>
-      </c>
       <c r="E422" t="s">
-        <v>58</v>
+        <v>777</v>
       </c>
       <c r="F422" s="1">
-        <v>46255</v>
+        <v>46083</v>
       </c>
       <c r="G422" s="1">
-        <v>46255</v>
+        <v>46084</v>
       </c>
     </row>
     <row r="423" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A423" t="s">
-        <v>752</v>
+        <v>774</v>
       </c>
       <c r="B423" t="s">
+        <v>778</v>
+      </c>
+      <c r="C423" t="s">
+        <v>2</v>
+      </c>
+      <c r="D423" t="s">
+        <v>776</v>
+      </c>
+      <c r="E423" t="s">
         <v>777</v>
       </c>
-      <c r="C423" t="s">
-        <v>6</v>
-      </c>
-      <c r="D423" t="s">
-        <v>57</v>
-      </c>
-      <c r="E423" t="s">
-        <v>58</v>
-      </c>
       <c r="F423" s="1">
-        <v>46260</v>
+        <v>46132</v>
       </c>
       <c r="G423" s="1">
-        <v>46260</v>
+        <v>46133</v>
       </c>
     </row>
     <row r="424" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A424" t="s">
-        <v>752</v>
+        <v>774</v>
       </c>
       <c r="B424" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="C424" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D424" t="s">
-        <v>57</v>
+        <v>705</v>
       </c>
       <c r="E424" t="s">
-        <v>58</v>
+        <v>706</v>
       </c>
       <c r="F424" s="1">
-        <v>46262</v>
+        <v>46157</v>
       </c>
       <c r="G424" s="1">
-        <v>46262</v>
+        <v>46157</v>
       </c>
     </row>
     <row r="425" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A425" t="s">
-        <v>752</v>
+        <v>774</v>
       </c>
       <c r="B425" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="C425" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D425" t="s">
-        <v>57</v>
+        <v>781</v>
       </c>
       <c r="E425" t="s">
-        <v>58</v>
+        <v>782</v>
       </c>
       <c r="F425" s="1">
-        <v>46262</v>
+        <v>46168</v>
       </c>
       <c r="G425" s="1">
-        <v>46262</v>
+        <v>46170</v>
       </c>
     </row>
     <row r="426" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A426" t="s">
-        <v>752</v>
+        <v>774</v>
       </c>
       <c r="B426" t="s">
-        <v>780</v>
+        <v>783</v>
       </c>
       <c r="C426" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D426" t="s">
-        <v>57</v>
+        <v>705</v>
       </c>
       <c r="E426" t="s">
-        <v>58</v>
+        <v>706</v>
       </c>
       <c r="F426" s="1">
-        <v>46262</v>
+        <v>46244</v>
       </c>
       <c r="G426" s="1">
-        <v>46262</v>
+        <v>46244</v>
       </c>
     </row>
     <row r="427" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A427" t="s">
-        <v>752</v>
+        <v>774</v>
       </c>
       <c r="B427" t="s">
-        <v>781</v>
+        <v>784</v>
       </c>
       <c r="C427" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D427" t="s">
-        <v>57</v>
+        <v>705</v>
       </c>
       <c r="E427" t="s">
-        <v>58</v>
+        <v>706</v>
       </c>
       <c r="F427" s="1">
-        <v>46262</v>
+        <v>46247</v>
       </c>
       <c r="G427" s="1">
-        <v>46262</v>
+        <v>46247</v>
       </c>
     </row>
     <row r="428" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A428" t="s">
-        <v>752</v>
+        <v>774</v>
       </c>
       <c r="B428" t="s">
-        <v>782</v>
+        <v>785</v>
       </c>
       <c r="C428" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D428" t="s">
-        <v>57</v>
+        <v>776</v>
       </c>
       <c r="E428" t="s">
-        <v>58</v>
+        <v>777</v>
       </c>
       <c r="F428" s="1">
-        <v>46262</v>
+        <v>46247</v>
       </c>
       <c r="G428" s="1">
-        <v>46262</v>
+        <v>46247</v>
       </c>
     </row>
     <row r="429" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A429" t="s">
-        <v>752</v>
+        <v>774</v>
       </c>
       <c r="B429" t="s">
-        <v>783</v>
+        <v>786</v>
       </c>
       <c r="C429" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D429" t="s">
-        <v>57</v>
+        <v>705</v>
       </c>
       <c r="E429" t="s">
-        <v>58</v>
+        <v>706</v>
       </c>
       <c r="F429" s="1">
-        <v>46262</v>
+        <v>46255</v>
       </c>
       <c r="G429" s="1">
-        <v>46262</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="430" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A430" t="s">
-        <v>784</v>
+        <v>774</v>
       </c>
       <c r="B430" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="C430" t="s">
         <v>2</v>
       </c>
       <c r="D430" t="s">
-        <v>786</v>
+        <v>705</v>
       </c>
       <c r="E430" t="s">
-        <v>787</v>
+        <v>706</v>
       </c>
       <c r="F430" s="1">
-        <v>46083</v>
+        <v>46258</v>
       </c>
       <c r="G430" s="1">
-        <v>46084</v>
-      </c>
-    </row>
-    <row r="431" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A431" t="s">
-        <v>784</v>
-      </c>
-      <c r="B431" t="s">
-        <v>788</v>
-      </c>
-      <c r="C431" t="s">
-        <v>2</v>
-      </c>
-      <c r="D431" t="s">
-        <v>786</v>
-      </c>
-      <c r="E431" t="s">
-        <v>787</v>
-      </c>
-      <c r="F431" s="1">
-        <v>46132</v>
-      </c>
-      <c r="G431" s="1">
-        <v>46133</v>
-      </c>
-    </row>
-    <row r="432" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A432" t="s">
-        <v>784</v>
-      </c>
-      <c r="B432" t="s">
-        <v>789</v>
-      </c>
-      <c r="C432" t="s">
-        <v>2</v>
-      </c>
-      <c r="D432" t="s">
-        <v>705</v>
-      </c>
-      <c r="E432" t="s">
-        <v>706</v>
-      </c>
-      <c r="F432" s="1">
-        <v>46157</v>
-      </c>
-      <c r="G432" s="1">
-        <v>46157</v>
-      </c>
-    </row>
-    <row r="433" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A433" t="s">
-        <v>784</v>
-      </c>
-      <c r="B433" t="s">
-        <v>790</v>
-      </c>
-      <c r="C433" t="s">
-        <v>2</v>
-      </c>
-      <c r="D433" t="s">
-        <v>791</v>
-      </c>
-      <c r="E433" t="s">
-        <v>792</v>
-      </c>
-      <c r="F433" s="1">
-        <v>46168</v>
-      </c>
-      <c r="G433" s="1">
-        <v>46170</v>
-      </c>
-    </row>
-    <row r="434" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A434" t="s">
-        <v>784</v>
-      </c>
-      <c r="B434" t="s">
-        <v>793</v>
-      </c>
-      <c r="C434" t="s">
-        <v>2</v>
-      </c>
-      <c r="D434" t="s">
-        <v>705</v>
-      </c>
-      <c r="E434" t="s">
-        <v>706</v>
-      </c>
-      <c r="F434" s="1">
-        <v>46244</v>
-      </c>
-      <c r="G434" s="1">
-        <v>46244</v>
-      </c>
-    </row>
-    <row r="435" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A435" t="s">
-        <v>784</v>
-      </c>
-      <c r="B435" t="s">
-        <v>794</v>
-      </c>
-      <c r="C435" t="s">
-        <v>2</v>
-      </c>
-      <c r="D435" t="s">
-        <v>705</v>
-      </c>
-      <c r="E435" t="s">
-        <v>706</v>
-      </c>
-      <c r="F435" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G435" s="1">
-        <v>46247</v>
-      </c>
-    </row>
-    <row r="436" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A436" t="s">
-        <v>784</v>
-      </c>
-      <c r="B436" t="s">
-        <v>795</v>
-      </c>
-      <c r="C436" t="s">
-        <v>2</v>
-      </c>
-      <c r="D436" t="s">
-        <v>786</v>
-      </c>
-      <c r="E436" t="s">
-        <v>787</v>
-      </c>
-      <c r="F436" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G436" s="1">
-        <v>46247</v>
-      </c>
-    </row>
-    <row r="437" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A437" t="s">
-        <v>784</v>
-      </c>
-      <c r="B437" t="s">
-        <v>796</v>
-      </c>
-      <c r="C437" t="s">
-        <v>2</v>
-      </c>
-      <c r="D437" t="s">
-        <v>705</v>
-      </c>
-      <c r="E437" t="s">
-        <v>706</v>
-      </c>
-      <c r="F437" s="1">
-        <v>46255</v>
-      </c>
-      <c r="G437" s="1">
-        <v>46255</v>
-      </c>
-    </row>
-    <row r="438" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A438" t="s">
-        <v>784</v>
-      </c>
-      <c r="B438" t="s">
-        <v>797</v>
-      </c>
-      <c r="C438" t="s">
-        <v>2</v>
-      </c>
-      <c r="D438" t="s">
-        <v>705</v>
-      </c>
-      <c r="E438" t="s">
-        <v>706</v>
-      </c>
-      <c r="F438" s="1">
-        <v>46258</v>
-      </c>
-      <c r="G438" s="1">
         <v>46258</v>
       </c>
     </row>

--- a/Data_ERP/Pedidos Transmicion.xlsx
+++ b/Data_ERP/Pedidos Transmicion.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sistema_Logistico_Peirano\Data_ERP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E3389E81-2B0A-4D8B-B054-ABD39129DDCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{303668A2-2658-4F90-9A34-0C0C221CB841}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{AC707633-82CA-4A69-8930-E54342FE1B21}"/>
   </bookViews>

--- a/Data_ERP/Pedidos Transmicion.xlsx
+++ b/Data_ERP/Pedidos Transmicion.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sistema_Logistico_Peirano\Data_ERP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A2E9F0C5-C782-4752-A821-E1F0EDA9110E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{388DDAE7-6A08-46C9-AD33-EFB362FCE2E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{37546D58-28C8-4CE7-A8A5-5A3426FC2AB1}"/>
+    <workbookView xWindow="26955" yWindow="5805" windowWidth="15375" windowHeight="8325" xr2:uid="{4A4BF3F3-49D1-4E03-BE66-B5DF973415CF}"/>
   </bookViews>
   <sheets>
     <sheet name="transmicion" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2117" uniqueCount="838">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2067" uniqueCount="826">
   <si>
     <t>0001</t>
   </si>
@@ -859,15 +859,6 @@
     <t xml:space="preserve">  213634</t>
   </si>
   <si>
-    <t xml:space="preserve">  213648</t>
-  </si>
-  <si>
-    <t>VC09</t>
-  </si>
-  <si>
-    <t>VICENTELLI CARLOS ROBERTO - CASA DIVI</t>
-  </si>
-  <si>
     <t xml:space="preserve">  213668</t>
   </si>
   <si>
@@ -1060,9 +1051,6 @@
     <t xml:space="preserve">  214030</t>
   </si>
   <si>
-    <t xml:space="preserve">  214047</t>
-  </si>
-  <si>
     <t xml:space="preserve">  214048</t>
   </si>
   <si>
@@ -1150,6 +1138,15 @@
     <t>TODO SANITARIOS Y GAS S.R.L.</t>
   </si>
   <si>
+    <t xml:space="preserve">  214225</t>
+  </si>
+  <si>
+    <t>VM08</t>
+  </si>
+  <si>
+    <t>VARELA MARIA ISABEL</t>
+  </si>
+  <si>
     <t xml:space="preserve">  214226</t>
   </si>
   <si>
@@ -1207,6 +1204,15 @@
     <t>RAMIREZ CHRISTIAN J.G.-SANIMAR</t>
   </si>
   <si>
+    <t xml:space="preserve">  214318</t>
+  </si>
+  <si>
+    <t>MA06</t>
+  </si>
+  <si>
+    <t>MARTINO S.A.</t>
+  </si>
+  <si>
     <t xml:space="preserve">  214320</t>
   </si>
   <si>
@@ -1297,15 +1303,6 @@
     <t xml:space="preserve">  214444</t>
   </si>
   <si>
-    <t xml:space="preserve">  214456</t>
-  </si>
-  <si>
-    <t>FE24</t>
-  </si>
-  <si>
-    <t>FEDAMIL S.A.</t>
-  </si>
-  <si>
     <t xml:space="preserve">  214461</t>
   </si>
   <si>
@@ -1318,15 +1315,6 @@
     <t xml:space="preserve">  214476</t>
   </si>
   <si>
-    <t xml:space="preserve">  214506</t>
-  </si>
-  <si>
-    <t>KN01</t>
-  </si>
-  <si>
-    <t>KALFAIAN HNOS. S.R.L</t>
-  </si>
-  <si>
     <t xml:space="preserve">  214513</t>
   </si>
   <si>
@@ -1405,48 +1393,12 @@
     <t xml:space="preserve">  214564</t>
   </si>
   <si>
-    <t xml:space="preserve">  214568</t>
-  </si>
-  <si>
-    <t>PE04</t>
-  </si>
-  <si>
-    <t>PERREN Y CIA. S.A.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214572</t>
-  </si>
-  <si>
-    <t>SJ21</t>
-  </si>
-  <si>
-    <t>SANITARIOS JULICAM SRL</t>
-  </si>
-  <si>
     <t xml:space="preserve">  214576</t>
   </si>
   <si>
     <t xml:space="preserve">  214583</t>
   </si>
   <si>
-    <t xml:space="preserve">  214585</t>
-  </si>
-  <si>
-    <t>AL24</t>
-  </si>
-  <si>
-    <t>ALVARENGA VILLAR LUIS F.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214587</t>
-  </si>
-  <si>
-    <t>UG01</t>
-  </si>
-  <si>
-    <t>UCCELI GABRIEL A.-SANITARIOS GABRIEL</t>
-  </si>
-  <si>
     <t xml:space="preserve">  214588</t>
   </si>
   <si>
@@ -1456,6 +1408,9 @@
     <t xml:space="preserve">  214598</t>
   </si>
   <si>
+    <t xml:space="preserve">  214599</t>
+  </si>
+  <si>
     <t xml:space="preserve">  214606</t>
   </si>
   <si>
@@ -1474,9 +1429,6 @@
     <t xml:space="preserve">  214626</t>
   </si>
   <si>
-    <t xml:space="preserve">  214629</t>
-  </si>
-  <si>
     <t xml:space="preserve">  214636</t>
   </si>
   <si>
@@ -1516,21 +1468,6 @@
     <t xml:space="preserve">  214652</t>
   </si>
   <si>
-    <t xml:space="preserve">  214654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214656</t>
-  </si>
-  <si>
-    <t>SA72</t>
-  </si>
-  <si>
-    <t>SANI 3 S.R.L</t>
-  </si>
-  <si>
     <t xml:space="preserve">  214664</t>
   </si>
   <si>
@@ -1552,15 +1489,6 @@
     <t xml:space="preserve">  214666</t>
   </si>
   <si>
-    <t xml:space="preserve">  214668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214670</t>
-  </si>
-  <si>
     <t xml:space="preserve">  214672</t>
   </si>
   <si>
@@ -1573,18 +1501,6 @@
     <t xml:space="preserve">  214673</t>
   </si>
   <si>
-    <t xml:space="preserve">  214674</t>
-  </si>
-  <si>
-    <t>SG13</t>
-  </si>
-  <si>
-    <t>SANITARIOS GAONA S.A.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214675</t>
-  </si>
-  <si>
     <t xml:space="preserve">  214676</t>
   </si>
   <si>
@@ -1609,9 +1525,6 @@
     <t>DI STABILE E HIJOS S.A.</t>
   </si>
   <si>
-    <t xml:space="preserve">  214680</t>
-  </si>
-  <si>
     <t xml:space="preserve">  214681</t>
   </si>
   <si>
@@ -1621,33 +1534,6 @@
     <t>LUQUE SANITARIOS S.R.L.</t>
   </si>
   <si>
-    <t xml:space="preserve">  214683</t>
-  </si>
-  <si>
-    <t>AA05</t>
-  </si>
-  <si>
-    <t>SANITARIOS ALVAREZ SOC. LEY 19550 CAP. I SECCION I</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214687</t>
-  </si>
-  <si>
-    <t>BG15</t>
-  </si>
-  <si>
-    <t>BULFON GUILLERMO JESUS - SANIT. MATISA -</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214688</t>
-  </si>
-  <si>
-    <t>IN15</t>
-  </si>
-  <si>
-    <t>INTERMARBLE S.R.L.</t>
-  </si>
-  <si>
     <t xml:space="preserve">  214689</t>
   </si>
   <si>
@@ -1678,33 +1564,9 @@
     <t>TRIPOLI ARNALDO</t>
   </si>
   <si>
-    <t xml:space="preserve">  214695</t>
-  </si>
-  <si>
-    <t>GG26</t>
-  </si>
-  <si>
-    <t>GUERRERO EMILIO G. Y GUERRERO MATIA SH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214698</t>
-  </si>
-  <si>
     <t xml:space="preserve">  214699</t>
   </si>
   <si>
-    <t xml:space="preserve">  214700</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214701</t>
-  </si>
-  <si>
     <t xml:space="preserve">  214703</t>
   </si>
   <si>
@@ -1732,6 +1594,9 @@
     <t>CLICK-ON S.A. -TIOSO HOGAR</t>
   </si>
   <si>
+    <t xml:space="preserve">  214709</t>
+  </si>
+  <si>
     <t xml:space="preserve">  214713</t>
   </si>
   <si>
@@ -1759,7 +1624,316 @@
     <t>NICUESA E HIJOS S.R.L. -SANIT. NICUESA E HIJOS</t>
   </si>
   <si>
-    <t xml:space="preserve">  214720</t>
+    <t xml:space="preserve">  214724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214730</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214742</t>
+  </si>
+  <si>
+    <t>RR12</t>
+  </si>
+  <si>
+    <t>RIOS MARIA JOSE Y RIOS MARIA FERNANDA S.H.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214743</t>
+  </si>
+  <si>
+    <t>SL13</t>
+  </si>
+  <si>
+    <t>SANITARIOS LUGANO S.R.L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214745</t>
+  </si>
+  <si>
+    <t>ZZ02</t>
+  </si>
+  <si>
+    <t>ZINGALV GALVANIZADOS Y ZINC S.R.L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214746</t>
+  </si>
+  <si>
+    <t>RR17</t>
+  </si>
+  <si>
+    <t>RAMOS REVESTIMIENTOS S.R.L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214756</t>
+  </si>
+  <si>
+    <t>ME44</t>
+  </si>
+  <si>
+    <t>MERDUN S.R.L. -EL FARO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214758</t>
+  </si>
+  <si>
+    <t>HE09</t>
+  </si>
+  <si>
+    <t>HARGUINDEGUY ELIZABETH M -CASA FRANCO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214761</t>
+  </si>
+  <si>
+    <t>DR14</t>
+  </si>
+  <si>
+    <t>DREC SAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214767</t>
+  </si>
+  <si>
+    <t>OA01</t>
+  </si>
+  <si>
+    <t>OCHIUZZO ALBINO JUAN - DISTRIMAR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214769</t>
+  </si>
+  <si>
+    <t>CO28</t>
+  </si>
+  <si>
+    <t>CONSTRUDISENO S.A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214772</t>
+  </si>
+  <si>
+    <t>SV09</t>
+  </si>
+  <si>
+    <t>SANTIANO &amp; VICTOR S.R.L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214775</t>
+  </si>
+  <si>
+    <t>NM04</t>
+  </si>
+  <si>
+    <t>NEO MATERIALES S.A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214779</t>
+  </si>
+  <si>
+    <t>FG17</t>
+  </si>
+  <si>
+    <t>FERNANDEZ GONZALO M.-SANITARIOS FERNANDEZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214780</t>
+  </si>
+  <si>
+    <t>PA29</t>
+  </si>
+  <si>
+    <t>PIRILLI ALEJANDRO ANTONIO - DIECI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214787</t>
+  </si>
+  <si>
+    <t>FC03</t>
+  </si>
+  <si>
+    <t>CHUAR S.R.L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214789</t>
+  </si>
+  <si>
+    <t>ZV02</t>
+  </si>
+  <si>
+    <t>ZALAZAR VICTOR ANDRES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214790</t>
+  </si>
+  <si>
+    <t>AP11</t>
+  </si>
+  <si>
+    <t>ABASTECIMIENTOS PLASTICOS S.R.L. -ABAS PLAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214799</t>
+  </si>
+  <si>
+    <t>SS46</t>
+  </si>
+  <si>
+    <t>SANTAELLA SANTIAGO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214802</t>
+  </si>
+  <si>
+    <t>EC13</t>
+  </si>
+  <si>
+    <t>EL CAÑADON  S.R.L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214804</t>
+  </si>
+  <si>
+    <t>SG20</t>
+  </si>
+  <si>
+    <t>SANCHEZ OSVALDO D. Y GIANNINI GUILLERMO SH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214808</t>
+  </si>
+  <si>
+    <t>FE26</t>
+  </si>
+  <si>
+    <t>FEMEN S.A. - CENTRO DE MATERIALES -</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214809</t>
+  </si>
+  <si>
+    <t>GS16</t>
+  </si>
+  <si>
+    <t>GRAMMATICO SERGIO A -SANITARIOS ALVEAR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214810</t>
+  </si>
+  <si>
+    <t>DB15</t>
+  </si>
+  <si>
+    <t>DEL BELLO MARIELA -FERRETERIA TIENDA LUME</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214812</t>
+  </si>
+  <si>
+    <t>DC18</t>
+  </si>
+  <si>
+    <t>DI CARLO SEBASTIAN F -DI CARLO SANIT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214813</t>
+  </si>
+  <si>
+    <t>VA12</t>
+  </si>
+  <si>
+    <t>VALEANT S.R.L.-SANITARIOS TITO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214836</t>
+  </si>
+  <si>
+    <t>MA56</t>
+  </si>
+  <si>
+    <t>MORAL ANTONIO A. -COMERCIAL 3 DE MAYO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214852</t>
+  </si>
+  <si>
+    <t>CP19</t>
+  </si>
+  <si>
+    <t>CERAMICOS PELLEGRINI S.R.L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214853</t>
+  </si>
+  <si>
+    <t>HO06</t>
+  </si>
+  <si>
+    <t>HORLIT S.R.L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214858</t>
+  </si>
+  <si>
+    <t>PI09</t>
+  </si>
+  <si>
+    <t>PIETRO INSTALACIONES AGUA Y GAS S.R.L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214861</t>
   </si>
   <si>
     <t>SA40</t>
@@ -1768,196 +1942,37 @@
     <t>SANICENTRO S.A. SANITARIOS</t>
   </si>
   <si>
-    <t xml:space="preserve">  214722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214727</t>
-  </si>
-  <si>
-    <t>SR24</t>
-  </si>
-  <si>
-    <t>SAKER REYNOSO E -SANITARIOS EL TIO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214730</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214731</t>
-  </si>
-  <si>
-    <t>DA32</t>
-  </si>
-  <si>
-    <t>D AVIS DANIEL DAVID -CASA DAVID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214738</t>
-  </si>
-  <si>
-    <t>HU03</t>
-  </si>
-  <si>
-    <t>HURA S.A.S.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214740</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214742</t>
-  </si>
-  <si>
-    <t>RR12</t>
-  </si>
-  <si>
-    <t>RIOS MARIA JOSE Y RIOS MARIA FERNANDA S.H.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214743</t>
-  </si>
-  <si>
-    <t>SL13</t>
-  </si>
-  <si>
-    <t>SANITARIOS LUGANO S.R.L.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214745</t>
-  </si>
-  <si>
-    <t>ZZ02</t>
-  </si>
-  <si>
-    <t>ZINGALV GALVANIZADOS Y ZINC S.R.L.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214746</t>
-  </si>
-  <si>
-    <t>RR17</t>
-  </si>
-  <si>
-    <t>RAMOS REVESTIMIENTOS S.R.L.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214756</t>
-  </si>
-  <si>
-    <t>ME44</t>
-  </si>
-  <si>
-    <t>MERDUN S.R.L. -EL FARO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214758</t>
-  </si>
-  <si>
-    <t>HE09</t>
-  </si>
-  <si>
-    <t>HARGUINDEGUY ELIZABETH M -CASA FRANCO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214760</t>
-  </si>
-  <si>
-    <t>SO05</t>
-  </si>
-  <si>
-    <t>SANTOS OSCAR FERNANDO - ARGUAY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214761</t>
-  </si>
-  <si>
-    <t>DR14</t>
-  </si>
-  <si>
-    <t>DREC SAS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214766</t>
-  </si>
-  <si>
-    <t>CR26</t>
-  </si>
-  <si>
-    <t>CARLOS CARTIER M Y ROSANA GERARDI SH-SANITARIOS RC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214767</t>
-  </si>
-  <si>
-    <t>OA01</t>
-  </si>
-  <si>
-    <t>OCHIUZZO ALBINO JUAN - DISTRIMAR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214768</t>
+    <t xml:space="preserve">  214863</t>
+  </si>
+  <si>
+    <t>SA73</t>
+  </si>
+  <si>
+    <t>SANITARIOS ADUCCI ADROGUE S.R.L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214866</t>
+  </si>
+  <si>
+    <t>AS18</t>
+  </si>
+  <si>
+    <t>ALVEAR SANITARIOS S.R.L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214869</t>
   </si>
   <si>
     <t>BR08</t>
@@ -1966,187 +1981,163 @@
     <t>BAEZ RAMON ANTONIO</t>
   </si>
   <si>
-    <t xml:space="preserve">  214769</t>
-  </si>
-  <si>
-    <t>CO28</t>
-  </si>
-  <si>
-    <t>CONSTRUDISENO S.A.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214770</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214774</t>
-  </si>
-  <si>
-    <t>HL02</t>
-  </si>
-  <si>
-    <t>HEREDIA LEONARDO A - FERRETERIA HEREDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214775</t>
-  </si>
-  <si>
-    <t>NM04</t>
-  </si>
-  <si>
-    <t>NEO MATERIALES S.A.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214779</t>
-  </si>
-  <si>
-    <t>FG17</t>
-  </si>
-  <si>
-    <t>FERNANDEZ GONZALO M.-SANITARIOS FERNANDEZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214780</t>
-  </si>
-  <si>
-    <t>PA29</t>
-  </si>
-  <si>
-    <t>PIRILLI ALEJANDRO ANTONIO - DIECI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214781</t>
-  </si>
-  <si>
-    <t>NE04</t>
-  </si>
-  <si>
-    <t>NEOMAT S.A.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214783</t>
-  </si>
-  <si>
-    <t>CQ01</t>
-  </si>
-  <si>
-    <t>CAMARGO QUISPE VICENTE - MATERIALES CAMARGO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214784</t>
-  </si>
-  <si>
-    <t>AG04</t>
-  </si>
-  <si>
-    <t>AGUA Y GAS SRL.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214786</t>
-  </si>
-  <si>
-    <t>PL16</t>
-  </si>
-  <si>
-    <t>PLASTISUR S.R.L.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214787</t>
-  </si>
-  <si>
-    <t>FC03</t>
-  </si>
-  <si>
-    <t>CHUAR S.R.L.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214789</t>
-  </si>
-  <si>
-    <t>ZV02</t>
-  </si>
-  <si>
-    <t>ZALAZAR VICTOR ANDRES</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214790</t>
-  </si>
-  <si>
-    <t>AP11</t>
-  </si>
-  <si>
-    <t>ABASTECIMIENTOS PLASTICOS S.R.L. -ABAS PLAS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214792</t>
-  </si>
-  <si>
-    <t>EP08</t>
-  </si>
-  <si>
-    <t>EL MUNDO DEL PLOMERO S.R.L.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214793</t>
-  </si>
-  <si>
-    <t>JG08</t>
-  </si>
-  <si>
-    <t>JOSE LUIS GONZALEZ S A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214794</t>
-  </si>
-  <si>
-    <t>BR18</t>
-  </si>
-  <si>
-    <t>BRAZZOLA ROBERTO O. Y BRAZZOLA JUAN SH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214795</t>
-  </si>
-  <si>
-    <t>BO15</t>
-  </si>
-  <si>
-    <t>BOTTIGLIERI S.R.L.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214796</t>
-  </si>
-  <si>
-    <t>WL01</t>
-  </si>
-  <si>
-    <t>WELSH L Y HAUF E. -SANITARIOS DE LA COSTA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214797</t>
-  </si>
-  <si>
-    <t>SC28</t>
-  </si>
-  <si>
-    <t>SANITARIOS CAROSIO S.A.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214798</t>
+    <t xml:space="preserve">  214870</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214872</t>
+  </si>
+  <si>
+    <t>DB14</t>
+  </si>
+  <si>
+    <t>DIMA BAÑOS &amp; COCINAS S.R.L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214873</t>
+  </si>
+  <si>
+    <t>MH19</t>
+  </si>
+  <si>
+    <t>MATERIALES LOS HERMANOS Z4 S.R.L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214874</t>
+  </si>
+  <si>
+    <t>IC01</t>
+  </si>
+  <si>
+    <t>IMPORTADORA COMERCIAL FUEGUINA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214877</t>
+  </si>
+  <si>
+    <t>MS03</t>
+  </si>
+  <si>
+    <t>MATERIALES SUR S.A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214878</t>
+  </si>
+  <si>
+    <t>FE27</t>
+  </si>
+  <si>
+    <t>FERREFAZ S.R.L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214880</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214882</t>
+  </si>
+  <si>
+    <t>DF09</t>
+  </si>
+  <si>
+    <t>DICATARINA F.Y FITSZIMONS M. -KONECTA MERCEDES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214883</t>
+  </si>
+  <si>
+    <t>KI01</t>
+  </si>
+  <si>
+    <t>KONECTA INSUMOS SANITARIOS S.R.L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214890</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214893</t>
+  </si>
+  <si>
+    <t>WM02</t>
+  </si>
+  <si>
+    <t>WILEJTO MARCOS M. -ISA SANITARIOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214894</t>
+  </si>
+  <si>
+    <t>BN01</t>
+  </si>
+  <si>
+    <t>BARBOSA NESTOR AGUSTIN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214895</t>
+  </si>
+  <si>
+    <t>CF13</t>
+  </si>
+  <si>
+    <t>CAPRI FERNANDO GABRIEL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214896</t>
+  </si>
+  <si>
+    <t>LM17</t>
+  </si>
+  <si>
+    <t>LUCERO MIRIAM ELIZABETH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214898</t>
+  </si>
+  <si>
+    <t>ED04</t>
+  </si>
+  <si>
+    <t>EDIFICOR S.R.L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214899</t>
+  </si>
+  <si>
+    <t>SD30</t>
+  </si>
+  <si>
+    <t>SANITARIOS D AMBROSIO S.R.L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214900</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214902</t>
   </si>
   <si>
     <t>GI01</t>
@@ -2155,100 +2146,91 @@
     <t>GILI Y CIA SRL</t>
   </si>
   <si>
-    <t xml:space="preserve">  214799</t>
-  </si>
-  <si>
-    <t>SS46</t>
-  </si>
-  <si>
-    <t>SANTAELLA SANTIAGO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214800</t>
-  </si>
-  <si>
-    <t>TC01</t>
-  </si>
-  <si>
-    <t>TODO CAÑO DE MIGUEL ESPECHE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214802</t>
-  </si>
-  <si>
-    <t>EC13</t>
-  </si>
-  <si>
-    <t>EL CAÑADON  S.R.L.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214803</t>
-  </si>
-  <si>
-    <t>DR13</t>
-  </si>
-  <si>
-    <t>DOS RIZZO S. A.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214808</t>
-  </si>
-  <si>
-    <t>FE26</t>
-  </si>
-  <si>
-    <t>FEMEN S.A. - CENTRO DE MATERIALES -</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214809</t>
-  </si>
-  <si>
-    <t>GS16</t>
-  </si>
-  <si>
-    <t>GRAMMATICO SERGIO A -SANITARIOS ALVEAR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214810</t>
-  </si>
-  <si>
-    <t>DB15</t>
-  </si>
-  <si>
-    <t>DEL BELLO MARIELA -FERRETERIA TIENDA LUME</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214812</t>
-  </si>
-  <si>
-    <t>DC18</t>
-  </si>
-  <si>
-    <t>DI CARLO SEBASTIAN F -DI CARLO SANIT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214813</t>
-  </si>
-  <si>
-    <t>VA12</t>
-  </si>
-  <si>
-    <t>VALEANT S.R.L.-SANITARIOS TITO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  214816</t>
+    <t xml:space="preserve">  214903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214905</t>
+  </si>
+  <si>
+    <t>MR20</t>
+  </si>
+  <si>
+    <t>MANNARINO FEDERICO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214906</t>
+  </si>
+  <si>
+    <t>EC11</t>
+  </si>
+  <si>
+    <t>ES-COR DESIGN S.R.L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214910</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214914</t>
+  </si>
+  <si>
+    <t>ES13</t>
+  </si>
+  <si>
+    <t>EDEN SANITARIOS S.R.L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214915</t>
+  </si>
+  <si>
+    <t>SJ04</t>
+  </si>
+  <si>
+    <t>SANITARIOS JOSE C. PAZ S A E F</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214917</t>
+  </si>
+  <si>
+    <t>SV08</t>
+  </si>
+  <si>
+    <t>SANIFER VCP S.R.L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214919</t>
+  </si>
+  <si>
+    <t>LB03</t>
+  </si>
+  <si>
+    <t>LORES JOSE M. Y BRIGGEN DANiEL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214923</t>
   </si>
   <si>
     <t>0004</t>
@@ -2356,31 +2338,19 @@
     <t xml:space="preserve">    2862</t>
   </si>
   <si>
-    <t xml:space="preserve">    2868</t>
-  </si>
-  <si>
     <t xml:space="preserve">    2869</t>
   </si>
   <si>
-    <t xml:space="preserve">    2870</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    2872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    2873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    2874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    2875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    2876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    2877</t>
+    <t xml:space="preserve">    2880</t>
+  </si>
+  <si>
+    <t>FV10</t>
+  </si>
+  <si>
+    <t>FIDEICOMISO INMOBILIARIO VIVRE ANDES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    2881</t>
   </si>
   <si>
     <t>4444</t>
@@ -2461,10 +2431,7 @@
     <t xml:space="preserve">    2301</t>
   </si>
   <si>
-    <t xml:space="preserve">    2362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    2364</t>
+    <t xml:space="preserve">    2379</t>
   </si>
   <si>
     <t>9999</t>
@@ -2510,9 +2477,6 @@
   </si>
   <si>
     <t xml:space="preserve">      86</t>
-  </si>
-  <si>
-    <t xml:space="preserve">      87</t>
   </si>
   <si>
     <t>Puesto</t>
@@ -2983,31 +2947,31 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{465441C0-8E6F-492F-A73D-3376E1E82F72}">
-  <dimension ref="A1:G423"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49F20F2A-A25C-4861-83EF-B1A777B1036E}">
+  <dimension ref="A1:G413"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
-        <v>831</v>
+        <v>819</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>832</v>
+        <v>820</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>833</v>
+        <v>821</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>834</v>
+        <v>822</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>835</v>
+        <v>823</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>836</v>
+        <v>824</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>837</v>
+        <v>825</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
@@ -5698,7 +5662,7 @@
         <v>46246</v>
       </c>
       <c r="G118" s="1">
-        <v>46261</v>
+        <v>46247</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.2">
@@ -5712,10 +5676,10 @@
         <v>2</v>
       </c>
       <c r="D119" t="s">
-        <v>283</v>
+        <v>132</v>
       </c>
       <c r="E119" t="s">
-        <v>284</v>
+        <v>133</v>
       </c>
       <c r="F119" s="1">
         <v>46246</v>
@@ -5729,22 +5693,22 @@
         <v>0</v>
       </c>
       <c r="B120" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C120" t="s">
         <v>2</v>
       </c>
       <c r="D120" t="s">
-        <v>132</v>
+        <v>37</v>
       </c>
       <c r="E120" t="s">
-        <v>133</v>
+        <v>38</v>
       </c>
       <c r="F120" s="1">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="G120" s="1">
-        <v>46247</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.2">
@@ -5752,16 +5716,16 @@
         <v>0</v>
       </c>
       <c r="B121" t="s">
+        <v>284</v>
+      </c>
+      <c r="C121" t="s">
+        <v>2</v>
+      </c>
+      <c r="D121" t="s">
+        <v>285</v>
+      </c>
+      <c r="E121" t="s">
         <v>286</v>
-      </c>
-      <c r="C121" t="s">
-        <v>2</v>
-      </c>
-      <c r="D121" t="s">
-        <v>37</v>
-      </c>
-      <c r="E121" t="s">
-        <v>38</v>
       </c>
       <c r="F121" s="1">
         <v>46247</v>
@@ -5778,7 +5742,7 @@
         <v>287</v>
       </c>
       <c r="C122" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D122" t="s">
         <v>288</v>
@@ -5790,7 +5754,7 @@
         <v>46247</v>
       </c>
       <c r="G122" s="1">
-        <v>46252</v>
+        <v>46247</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.2">
@@ -5801,19 +5765,19 @@
         <v>290</v>
       </c>
       <c r="C123" t="s">
-        <v>6</v>
+        <v>80</v>
       </c>
       <c r="D123" t="s">
-        <v>291</v>
+        <v>184</v>
       </c>
       <c r="E123" t="s">
-        <v>292</v>
+        <v>185</v>
       </c>
       <c r="F123" s="1">
         <v>46247</v>
       </c>
       <c r="G123" s="1">
-        <v>46247</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.2">
@@ -5821,16 +5785,16 @@
         <v>0</v>
       </c>
       <c r="B124" t="s">
+        <v>291</v>
+      </c>
+      <c r="C124" t="s">
+        <v>2</v>
+      </c>
+      <c r="D124" t="s">
+        <v>292</v>
+      </c>
+      <c r="E124" t="s">
         <v>293</v>
-      </c>
-      <c r="C124" t="s">
-        <v>6</v>
-      </c>
-      <c r="D124" t="s">
-        <v>184</v>
-      </c>
-      <c r="E124" t="s">
-        <v>185</v>
       </c>
       <c r="F124" s="1">
         <v>46247</v>
@@ -5856,7 +5820,7 @@
         <v>296</v>
       </c>
       <c r="F125" s="1">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="G125" s="1">
         <v>46252</v>
@@ -5873,10 +5837,10 @@
         <v>2</v>
       </c>
       <c r="D126" t="s">
-        <v>298</v>
+        <v>114</v>
       </c>
       <c r="E126" t="s">
-        <v>299</v>
+        <v>115</v>
       </c>
       <c r="F126" s="1">
         <v>46248</v>
@@ -5890,16 +5854,16 @@
         <v>0</v>
       </c>
       <c r="B127" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C127" t="s">
         <v>2</v>
       </c>
       <c r="D127" t="s">
-        <v>114</v>
+        <v>48</v>
       </c>
       <c r="E127" t="s">
-        <v>115</v>
+        <v>49</v>
       </c>
       <c r="F127" s="1">
         <v>46248</v>
@@ -5913,16 +5877,16 @@
         <v>0</v>
       </c>
       <c r="B128" t="s">
+        <v>299</v>
+      </c>
+      <c r="C128" t="s">
+        <v>6</v>
+      </c>
+      <c r="D128" t="s">
+        <v>300</v>
+      </c>
+      <c r="E128" t="s">
         <v>301</v>
-      </c>
-      <c r="C128" t="s">
-        <v>2</v>
-      </c>
-      <c r="D128" t="s">
-        <v>48</v>
-      </c>
-      <c r="E128" t="s">
-        <v>49</v>
       </c>
       <c r="F128" s="1">
         <v>46248</v>
@@ -5939,7 +5903,7 @@
         <v>302</v>
       </c>
       <c r="C129" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D129" t="s">
         <v>303</v>
@@ -5965,10 +5929,10 @@
         <v>2</v>
       </c>
       <c r="D130" t="s">
-        <v>306</v>
+        <v>148</v>
       </c>
       <c r="E130" t="s">
-        <v>307</v>
+        <v>149</v>
       </c>
       <c r="F130" s="1">
         <v>46248</v>
@@ -5982,16 +5946,16 @@
         <v>0</v>
       </c>
       <c r="B131" t="s">
+        <v>306</v>
+      </c>
+      <c r="C131" t="s">
+        <v>2</v>
+      </c>
+      <c r="D131" t="s">
+        <v>307</v>
+      </c>
+      <c r="E131" t="s">
         <v>308</v>
-      </c>
-      <c r="C131" t="s">
-        <v>2</v>
-      </c>
-      <c r="D131" t="s">
-        <v>148</v>
-      </c>
-      <c r="E131" t="s">
-        <v>149</v>
       </c>
       <c r="F131" s="1">
         <v>46248</v>
@@ -6017,10 +5981,10 @@
         <v>311</v>
       </c>
       <c r="F132" s="1">
-        <v>46248</v>
+        <v>46252</v>
       </c>
       <c r="G132" s="1">
-        <v>46252</v>
+        <v>46254</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.2">
@@ -6034,16 +5998,16 @@
         <v>2</v>
       </c>
       <c r="D133" t="s">
-        <v>313</v>
+        <v>114</v>
       </c>
       <c r="E133" t="s">
-        <v>314</v>
+        <v>115</v>
       </c>
       <c r="F133" s="1">
         <v>46252</v>
       </c>
       <c r="G133" s="1">
-        <v>46254</v>
+        <v>46253</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.2">
@@ -6051,22 +6015,22 @@
         <v>0</v>
       </c>
       <c r="B134" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C134" t="s">
         <v>2</v>
       </c>
       <c r="D134" t="s">
-        <v>114</v>
+        <v>205</v>
       </c>
       <c r="E134" t="s">
-        <v>115</v>
+        <v>206</v>
       </c>
       <c r="F134" s="1">
         <v>46252</v>
       </c>
       <c r="G134" s="1">
-        <v>46253</v>
+        <v>46254</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.2">
@@ -6074,22 +6038,22 @@
         <v>0</v>
       </c>
       <c r="B135" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C135" t="s">
         <v>2</v>
       </c>
       <c r="D135" t="s">
-        <v>205</v>
+        <v>224</v>
       </c>
       <c r="E135" t="s">
-        <v>206</v>
+        <v>225</v>
       </c>
       <c r="F135" s="1">
         <v>46252</v>
       </c>
       <c r="G135" s="1">
-        <v>46254</v>
+        <v>46253</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.2">
@@ -6097,22 +6061,22 @@
         <v>0</v>
       </c>
       <c r="B136" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C136" t="s">
         <v>2</v>
       </c>
       <c r="D136" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E136" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="F136" s="1">
         <v>46252</v>
       </c>
       <c r="G136" s="1">
-        <v>46253</v>
+        <v>46254</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.2">
@@ -6120,22 +6084,22 @@
         <v>0</v>
       </c>
       <c r="B137" t="s">
+        <v>316</v>
+      </c>
+      <c r="C137" t="s">
+        <v>2</v>
+      </c>
+      <c r="D137" t="s">
+        <v>317</v>
+      </c>
+      <c r="E137" t="s">
         <v>318</v>
-      </c>
-      <c r="C137" t="s">
-        <v>2</v>
-      </c>
-      <c r="D137" t="s">
-        <v>227</v>
-      </c>
-      <c r="E137" t="s">
-        <v>228</v>
       </c>
       <c r="F137" s="1">
         <v>46252</v>
       </c>
       <c r="G137" s="1">
-        <v>46254</v>
+        <v>46253</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.2">
@@ -6181,7 +6145,7 @@
         <v>46252</v>
       </c>
       <c r="G139" s="1">
-        <v>46253</v>
+        <v>46254</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.2">
@@ -6192,7 +6156,7 @@
         <v>325</v>
       </c>
       <c r="C140" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D140" t="s">
         <v>326</v>
@@ -6204,7 +6168,7 @@
         <v>46252</v>
       </c>
       <c r="G140" s="1">
-        <v>46254</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.2">
@@ -6215,13 +6179,13 @@
         <v>328</v>
       </c>
       <c r="C141" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D141" t="s">
-        <v>329</v>
+        <v>81</v>
       </c>
       <c r="E141" t="s">
-        <v>330</v>
+        <v>82</v>
       </c>
       <c r="F141" s="1">
         <v>46252</v>
@@ -6235,22 +6199,22 @@
         <v>0</v>
       </c>
       <c r="B142" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C142" t="s">
         <v>2</v>
       </c>
       <c r="D142" t="s">
-        <v>81</v>
+        <v>257</v>
       </c>
       <c r="E142" t="s">
-        <v>82</v>
+        <v>258</v>
       </c>
       <c r="F142" s="1">
         <v>46252</v>
       </c>
       <c r="G142" s="1">
-        <v>46259</v>
+        <v>46254</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.2">
@@ -6258,22 +6222,22 @@
         <v>0</v>
       </c>
       <c r="B143" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C143" t="s">
         <v>2</v>
       </c>
       <c r="D143" t="s">
-        <v>257</v>
+        <v>174</v>
       </c>
       <c r="E143" t="s">
-        <v>258</v>
+        <v>175</v>
       </c>
       <c r="F143" s="1">
         <v>46252</v>
       </c>
       <c r="G143" s="1">
-        <v>46254</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.2">
@@ -6281,7 +6245,7 @@
         <v>0</v>
       </c>
       <c r="B144" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C144" t="s">
         <v>2</v>
@@ -6304,22 +6268,22 @@
         <v>0</v>
       </c>
       <c r="B145" t="s">
+        <v>332</v>
+      </c>
+      <c r="C145" t="s">
+        <v>2</v>
+      </c>
+      <c r="D145" t="s">
+        <v>333</v>
+      </c>
+      <c r="E145" t="s">
         <v>334</v>
       </c>
-      <c r="C145" t="s">
-        <v>2</v>
-      </c>
-      <c r="D145" t="s">
-        <v>174</v>
-      </c>
-      <c r="E145" t="s">
-        <v>175</v>
-      </c>
       <c r="F145" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="G145" s="1">
-        <v>46255</v>
+        <v>46254</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.2">
@@ -6330,7 +6294,7 @@
         <v>335</v>
       </c>
       <c r="C146" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D146" t="s">
         <v>336</v>
@@ -6342,7 +6306,7 @@
         <v>46253</v>
       </c>
       <c r="G146" s="1">
-        <v>46254</v>
+        <v>46253</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.2">
@@ -6353,19 +6317,19 @@
         <v>338</v>
       </c>
       <c r="C147" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D147" t="s">
-        <v>339</v>
+        <v>48</v>
       </c>
       <c r="E147" t="s">
-        <v>340</v>
+        <v>49</v>
       </c>
       <c r="F147" s="1">
         <v>46253</v>
       </c>
       <c r="G147" s="1">
-        <v>46253</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.2">
@@ -6373,22 +6337,22 @@
         <v>0</v>
       </c>
       <c r="B148" t="s">
+        <v>339</v>
+      </c>
+      <c r="C148" t="s">
+        <v>2</v>
+      </c>
+      <c r="D148" t="s">
+        <v>340</v>
+      </c>
+      <c r="E148" t="s">
         <v>341</v>
-      </c>
-      <c r="C148" t="s">
-        <v>2</v>
-      </c>
-      <c r="D148" t="s">
-        <v>48</v>
-      </c>
-      <c r="E148" t="s">
-        <v>49</v>
       </c>
       <c r="F148" s="1">
         <v>46253</v>
       </c>
       <c r="G148" s="1">
-        <v>46255</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.2">
@@ -6402,10 +6366,10 @@
         <v>2</v>
       </c>
       <c r="D149" t="s">
-        <v>343</v>
+        <v>37</v>
       </c>
       <c r="E149" t="s">
-        <v>344</v>
+        <v>38</v>
       </c>
       <c r="F149" s="1">
         <v>46253</v>
@@ -6419,22 +6383,22 @@
         <v>0</v>
       </c>
       <c r="B150" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C150" t="s">
         <v>2</v>
       </c>
       <c r="D150" t="s">
-        <v>37</v>
+        <v>7</v>
       </c>
       <c r="E150" t="s">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="F150" s="1">
         <v>46253</v>
       </c>
       <c r="G150" s="1">
-        <v>46259</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.2">
@@ -6442,22 +6406,22 @@
         <v>0</v>
       </c>
       <c r="B151" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="C151" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D151" t="s">
-        <v>7</v>
+        <v>295</v>
       </c>
       <c r="E151" t="s">
-        <v>8</v>
+        <v>296</v>
       </c>
       <c r="F151" s="1">
         <v>46253</v>
       </c>
       <c r="G151" s="1">
-        <v>46261</v>
+        <v>46258</v>
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.2">
@@ -6465,22 +6429,22 @@
         <v>0</v>
       </c>
       <c r="B152" t="s">
+        <v>345</v>
+      </c>
+      <c r="C152" t="s">
+        <v>2</v>
+      </c>
+      <c r="D152" t="s">
+        <v>346</v>
+      </c>
+      <c r="E152" t="s">
         <v>347</v>
-      </c>
-      <c r="C152" t="s">
-        <v>2</v>
-      </c>
-      <c r="D152" t="s">
-        <v>7</v>
-      </c>
-      <c r="E152" t="s">
-        <v>8</v>
       </c>
       <c r="F152" s="1">
         <v>46253</v>
       </c>
       <c r="G152" s="1">
-        <v>46255</v>
+        <v>46258</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.2">
@@ -6494,16 +6458,16 @@
         <v>2</v>
       </c>
       <c r="D153" t="s">
-        <v>298</v>
+        <v>37</v>
       </c>
       <c r="E153" t="s">
-        <v>299</v>
+        <v>38</v>
       </c>
       <c r="F153" s="1">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="G153" s="1">
-        <v>46258</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.2">
@@ -6514,7 +6478,7 @@
         <v>349</v>
       </c>
       <c r="C154" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D154" t="s">
         <v>350</v>
@@ -6523,10 +6487,10 @@
         <v>351</v>
       </c>
       <c r="F154" s="1">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="G154" s="1">
-        <v>46258</v>
+        <v>46254</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.2">
@@ -6537,13 +6501,13 @@
         <v>352</v>
       </c>
       <c r="C155" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D155" t="s">
-        <v>37</v>
+        <v>353</v>
       </c>
       <c r="E155" t="s">
-        <v>38</v>
+        <v>354</v>
       </c>
       <c r="F155" s="1">
         <v>46254</v>
@@ -6557,22 +6521,22 @@
         <v>0</v>
       </c>
       <c r="B156" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="C156" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D156" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="E156" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="F156" s="1">
         <v>46254</v>
       </c>
       <c r="G156" s="1">
-        <v>46254</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.2">
@@ -6580,22 +6544,22 @@
         <v>0</v>
       </c>
       <c r="B157" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="C157" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D157" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="E157" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="F157" s="1">
         <v>46254</v>
       </c>
       <c r="G157" s="1">
-        <v>46259</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.2">
@@ -6609,10 +6573,10 @@
         <v>2</v>
       </c>
       <c r="D158" t="s">
-        <v>360</v>
+        <v>197</v>
       </c>
       <c r="E158" t="s">
-        <v>361</v>
+        <v>198</v>
       </c>
       <c r="F158" s="1">
         <v>46254</v>
@@ -6626,19 +6590,19 @@
         <v>0</v>
       </c>
       <c r="B159" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C159" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D159" t="s">
-        <v>357</v>
+        <v>16</v>
       </c>
       <c r="E159" t="s">
-        <v>358</v>
+        <v>17</v>
       </c>
       <c r="F159" s="1">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="G159" s="1">
         <v>46255</v>
@@ -6649,19 +6613,19 @@
         <v>0</v>
       </c>
       <c r="B160" t="s">
+        <v>361</v>
+      </c>
+      <c r="C160" t="s">
+        <v>80</v>
+      </c>
+      <c r="D160" t="s">
+        <v>362</v>
+      </c>
+      <c r="E160" t="s">
         <v>363</v>
       </c>
-      <c r="C160" t="s">
-        <v>2</v>
-      </c>
-      <c r="D160" t="s">
-        <v>197</v>
-      </c>
-      <c r="E160" t="s">
-        <v>198</v>
-      </c>
       <c r="F160" s="1">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="G160" s="1">
         <v>46255</v>
@@ -6675,13 +6639,13 @@
         <v>364</v>
       </c>
       <c r="C161" t="s">
-        <v>6</v>
+        <v>80</v>
       </c>
       <c r="D161" t="s">
-        <v>16</v>
+        <v>310</v>
       </c>
       <c r="E161" t="s">
-        <v>17</v>
+        <v>311</v>
       </c>
       <c r="F161" s="1">
         <v>46255</v>
@@ -6698,7 +6662,7 @@
         <v>365</v>
       </c>
       <c r="C162" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D162" t="s">
         <v>366</v>
@@ -6710,7 +6674,7 @@
         <v>46255</v>
       </c>
       <c r="G162" s="1">
-        <v>46255</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.2">
@@ -6721,19 +6685,19 @@
         <v>368</v>
       </c>
       <c r="C163" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D163" t="s">
-        <v>313</v>
+        <v>366</v>
       </c>
       <c r="E163" t="s">
-        <v>314</v>
+        <v>367</v>
       </c>
       <c r="F163" s="1">
         <v>46255</v>
       </c>
       <c r="G163" s="1">
-        <v>46255</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.2">
@@ -6744,7 +6708,7 @@
         <v>369</v>
       </c>
       <c r="C164" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D164" t="s">
         <v>370</v>
@@ -6756,7 +6720,7 @@
         <v>46255</v>
       </c>
       <c r="G164" s="1">
-        <v>46259</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.2">
@@ -6770,16 +6734,16 @@
         <v>2</v>
       </c>
       <c r="D165" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="E165" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="F165" s="1">
         <v>46255</v>
       </c>
       <c r="G165" s="1">
-        <v>46259</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.2">
@@ -6787,22 +6751,22 @@
         <v>0</v>
       </c>
       <c r="B166" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="C166" t="s">
         <v>2</v>
       </c>
       <c r="D166" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="E166" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="F166" s="1">
         <v>46255</v>
       </c>
       <c r="G166" s="1">
-        <v>46260</v>
+        <v>46258</v>
       </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.2">
@@ -6810,22 +6774,22 @@
         <v>0</v>
       </c>
       <c r="B167" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="C167" t="s">
         <v>2</v>
       </c>
       <c r="D167" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="E167" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="F167" s="1">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="G167" s="1">
-        <v>46258</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.2">
@@ -6833,16 +6797,16 @@
         <v>0</v>
       </c>
       <c r="B168" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="C168" t="s">
         <v>2</v>
       </c>
       <c r="D168" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="E168" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="F168" s="1">
         <v>46258</v>
@@ -6856,22 +6820,22 @@
         <v>0</v>
       </c>
       <c r="B169" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="C169" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D169" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="E169" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="F169" s="1">
         <v>46258</v>
       </c>
       <c r="G169" s="1">
-        <v>46259</v>
+        <v>46258</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.2">
@@ -6879,22 +6843,22 @@
         <v>0</v>
       </c>
       <c r="B170" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="C170" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D170" t="s">
-        <v>386</v>
+        <v>300</v>
       </c>
       <c r="E170" t="s">
-        <v>387</v>
+        <v>301</v>
       </c>
       <c r="F170" s="1">
         <v>46258</v>
       </c>
       <c r="G170" s="1">
-        <v>46258</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.2">
@@ -6908,10 +6872,10 @@
         <v>2</v>
       </c>
       <c r="D171" t="s">
-        <v>303</v>
+        <v>389</v>
       </c>
       <c r="E171" t="s">
-        <v>304</v>
+        <v>390</v>
       </c>
       <c r="F171" s="1">
         <v>46258</v>
@@ -6925,16 +6889,16 @@
         <v>0</v>
       </c>
       <c r="B172" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C172" t="s">
         <v>2</v>
       </c>
       <c r="D172" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="E172" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="F172" s="1">
         <v>46258</v>
@@ -6948,22 +6912,22 @@
         <v>0</v>
       </c>
       <c r="B173" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C173" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D173" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="E173" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="F173" s="1">
         <v>46258</v>
       </c>
       <c r="G173" s="1">
-        <v>46259</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.2">
@@ -6971,7 +6935,7 @@
         <v>0</v>
       </c>
       <c r="B174" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C174" t="s">
         <v>2</v>
@@ -6994,16 +6958,16 @@
         <v>0</v>
       </c>
       <c r="B175" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="C175" t="s">
         <v>2</v>
       </c>
       <c r="D175" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="E175" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="F175" s="1">
         <v>46258</v>
@@ -7017,16 +6981,16 @@
         <v>0</v>
       </c>
       <c r="B176" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="C176" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D176" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="E176" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="F176" s="1">
         <v>46258</v>
@@ -7040,16 +7004,16 @@
         <v>0</v>
       </c>
       <c r="B177" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="C177" t="s">
         <v>2</v>
       </c>
       <c r="D177" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="E177" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="F177" s="1">
         <v>46258</v>
@@ -7063,16 +7027,16 @@
         <v>0</v>
       </c>
       <c r="B178" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="C178" t="s">
         <v>2</v>
       </c>
       <c r="D178" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="E178" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="F178" s="1">
         <v>46258</v>
@@ -7086,7 +7050,7 @@
         <v>0</v>
       </c>
       <c r="B179" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="C179" t="s">
         <v>80</v>
@@ -7109,16 +7073,16 @@
         <v>0</v>
       </c>
       <c r="B180" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="C180" t="s">
         <v>2</v>
       </c>
       <c r="D180" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="E180" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="F180" s="1">
         <v>46259</v>
@@ -7132,7 +7096,7 @@
         <v>0</v>
       </c>
       <c r="B181" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C181" t="s">
         <v>2</v>
@@ -7155,7 +7119,7 @@
         <v>0</v>
       </c>
       <c r="B182" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C182" t="s">
         <v>6</v>
@@ -7178,16 +7142,16 @@
         <v>0</v>
       </c>
       <c r="B183" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="C183" t="s">
         <v>6</v>
       </c>
       <c r="D183" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="E183" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="F183" s="1">
         <v>46259</v>
@@ -7201,7 +7165,7 @@
         <v>0</v>
       </c>
       <c r="B184" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="C184" t="s">
         <v>2</v>
@@ -7224,7 +7188,7 @@
         <v>0</v>
       </c>
       <c r="B185" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="C185" t="s">
         <v>2</v>
@@ -7247,16 +7211,16 @@
         <v>0</v>
       </c>
       <c r="B186" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="C186" t="s">
         <v>2</v>
       </c>
       <c r="D186" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="E186" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="F186" s="1">
         <v>46259</v>
@@ -7270,16 +7234,16 @@
         <v>0</v>
       </c>
       <c r="B187" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="C187" t="s">
         <v>2</v>
       </c>
       <c r="D187" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="E187" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="F187" s="1">
         <v>46259</v>
@@ -7293,7 +7257,7 @@
         <v>0</v>
       </c>
       <c r="B188" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C188" t="s">
         <v>80</v>
@@ -7316,7 +7280,7 @@
         <v>0</v>
       </c>
       <c r="B189" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="C189" t="s">
         <v>80</v>
@@ -7339,22 +7303,22 @@
         <v>0</v>
       </c>
       <c r="B190" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="C190" t="s">
         <v>80</v>
       </c>
       <c r="D190" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="E190" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="F190" s="1">
         <v>46260</v>
       </c>
       <c r="G190" s="1">
-        <v>46260</v>
+        <v>46265</v>
       </c>
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.2">
@@ -7362,22 +7326,22 @@
         <v>0</v>
       </c>
       <c r="B191" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="C191" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D191" t="s">
-        <v>429</v>
+        <v>132</v>
       </c>
       <c r="E191" t="s">
-        <v>430</v>
+        <v>133</v>
       </c>
       <c r="F191" s="1">
         <v>46260</v>
       </c>
       <c r="G191" s="1">
-        <v>46265</v>
+        <v>46261</v>
       </c>
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.2">
@@ -7391,10 +7355,10 @@
         <v>2</v>
       </c>
       <c r="D192" t="s">
-        <v>132</v>
+        <v>432</v>
       </c>
       <c r="E192" t="s">
-        <v>133</v>
+        <v>433</v>
       </c>
       <c r="F192" s="1">
         <v>46260</v>
@@ -7408,16 +7372,16 @@
         <v>0</v>
       </c>
       <c r="B193" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="C193" t="s">
         <v>80</v>
       </c>
       <c r="D193" t="s">
-        <v>433</v>
+        <v>16</v>
       </c>
       <c r="E193" t="s">
-        <v>434</v>
+        <v>17</v>
       </c>
       <c r="F193" s="1">
         <v>46260</v>
@@ -7434,7 +7398,7 @@
         <v>435</v>
       </c>
       <c r="C194" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D194" t="s">
         <v>436</v>
@@ -7460,16 +7424,16 @@
         <v>80</v>
       </c>
       <c r="D195" t="s">
-        <v>16</v>
+        <v>303</v>
       </c>
       <c r="E195" t="s">
-        <v>17</v>
+        <v>304</v>
       </c>
       <c r="F195" s="1">
         <v>46260</v>
       </c>
       <c r="G195" s="1">
-        <v>46260</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.2">
@@ -7483,10 +7447,10 @@
         <v>80</v>
       </c>
       <c r="D196" t="s">
-        <v>440</v>
+        <v>37</v>
       </c>
       <c r="E196" t="s">
-        <v>441</v>
+        <v>38</v>
       </c>
       <c r="F196" s="1">
         <v>46260</v>
@@ -7500,22 +7464,22 @@
         <v>0</v>
       </c>
       <c r="B197" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="C197" t="s">
         <v>80</v>
       </c>
       <c r="D197" t="s">
-        <v>306</v>
+        <v>37</v>
       </c>
       <c r="E197" t="s">
-        <v>307</v>
+        <v>38</v>
       </c>
       <c r="F197" s="1">
         <v>46260</v>
       </c>
       <c r="G197" s="1">
-        <v>46262</v>
+        <v>46261</v>
       </c>
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.2">
@@ -7523,7 +7487,7 @@
         <v>0</v>
       </c>
       <c r="B198" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="C198" t="s">
         <v>80</v>
@@ -7546,7 +7510,7 @@
         <v>0</v>
       </c>
       <c r="B199" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="C199" t="s">
         <v>80</v>
@@ -7569,10 +7533,10 @@
         <v>0</v>
       </c>
       <c r="B200" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="C200" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D200" t="s">
         <v>37</v>
@@ -7592,7 +7556,7 @@
         <v>0</v>
       </c>
       <c r="B201" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="C201" t="s">
         <v>80</v>
@@ -7615,10 +7579,10 @@
         <v>0</v>
       </c>
       <c r="B202" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="C202" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D202" t="s">
         <v>37</v>
@@ -7638,7 +7602,7 @@
         <v>0</v>
       </c>
       <c r="B203" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="C203" t="s">
         <v>80</v>
@@ -7661,7 +7625,7 @@
         <v>0</v>
       </c>
       <c r="B204" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="C204" t="s">
         <v>80</v>
@@ -7684,7 +7648,7 @@
         <v>0</v>
       </c>
       <c r="B205" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="C205" t="s">
         <v>80</v>
@@ -7707,22 +7671,22 @@
         <v>0</v>
       </c>
       <c r="B206" t="s">
+        <v>449</v>
+      </c>
+      <c r="C206" t="s">
+        <v>2</v>
+      </c>
+      <c r="D206" t="s">
+        <v>450</v>
+      </c>
+      <c r="E206" t="s">
         <v>451</v>
-      </c>
-      <c r="C206" t="s">
-        <v>80</v>
-      </c>
-      <c r="D206" t="s">
-        <v>37</v>
-      </c>
-      <c r="E206" t="s">
-        <v>38</v>
       </c>
       <c r="F206" s="1">
         <v>46260</v>
       </c>
       <c r="G206" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="207" spans="1:7" x14ac:dyDescent="0.2">
@@ -7733,7 +7697,7 @@
         <v>452</v>
       </c>
       <c r="C207" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D207" t="s">
         <v>37</v>
@@ -7742,7 +7706,7 @@
         <v>38</v>
       </c>
       <c r="F207" s="1">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="G207" s="1">
         <v>46261</v>
@@ -7756,7 +7720,7 @@
         <v>453</v>
       </c>
       <c r="C208" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D208" t="s">
         <v>454</v>
@@ -7765,10 +7729,10 @@
         <v>455</v>
       </c>
       <c r="F208" s="1">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="G208" s="1">
-        <v>46262</v>
+        <v>46261</v>
       </c>
     </row>
     <row r="209" spans="1:7" x14ac:dyDescent="0.2">
@@ -7779,19 +7743,19 @@
         <v>456</v>
       </c>
       <c r="C209" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D209" t="s">
-        <v>37</v>
+        <v>362</v>
       </c>
       <c r="E209" t="s">
-        <v>38</v>
+        <v>363</v>
       </c>
       <c r="F209" s="1">
         <v>46261</v>
       </c>
       <c r="G209" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="210" spans="1:7" x14ac:dyDescent="0.2">
@@ -7802,19 +7766,19 @@
         <v>457</v>
       </c>
       <c r="C210" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D210" t="s">
-        <v>458</v>
+        <v>200</v>
       </c>
       <c r="E210" t="s">
-        <v>459</v>
+        <v>201</v>
       </c>
       <c r="F210" s="1">
         <v>46261</v>
       </c>
       <c r="G210" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="211" spans="1:7" x14ac:dyDescent="0.2">
@@ -7822,16 +7786,16 @@
         <v>0</v>
       </c>
       <c r="B211" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="C211" t="s">
         <v>2</v>
       </c>
       <c r="D211" t="s">
-        <v>366</v>
+        <v>250</v>
       </c>
       <c r="E211" t="s">
-        <v>367</v>
+        <v>251</v>
       </c>
       <c r="F211" s="1">
         <v>46261</v>
@@ -7845,22 +7809,22 @@
         <v>0</v>
       </c>
       <c r="B212" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="C212" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D212" t="s">
-        <v>462</v>
+        <v>98</v>
       </c>
       <c r="E212" t="s">
-        <v>463</v>
+        <v>99</v>
       </c>
       <c r="F212" s="1">
         <v>46261</v>
       </c>
       <c r="G212" s="1">
-        <v>46261</v>
+        <v>46265</v>
       </c>
     </row>
     <row r="213" spans="1:7" x14ac:dyDescent="0.2">
@@ -7868,22 +7832,22 @@
         <v>0</v>
       </c>
       <c r="B213" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="C213" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D213" t="s">
-        <v>465</v>
+        <v>37</v>
       </c>
       <c r="E213" t="s">
-        <v>466</v>
+        <v>38</v>
       </c>
       <c r="F213" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="G213" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="214" spans="1:7" x14ac:dyDescent="0.2">
@@ -7891,19 +7855,19 @@
         <v>0</v>
       </c>
       <c r="B214" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="C214" t="s">
         <v>2</v>
       </c>
       <c r="D214" t="s">
-        <v>200</v>
+        <v>37</v>
       </c>
       <c r="E214" t="s">
-        <v>201</v>
+        <v>38</v>
       </c>
       <c r="F214" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="G214" s="1">
         <v>46262</v>
@@ -7914,22 +7878,22 @@
         <v>0</v>
       </c>
       <c r="B215" t="s">
-        <v>468</v>
+        <v>462</v>
       </c>
       <c r="C215" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D215" t="s">
-        <v>250</v>
+        <v>37</v>
       </c>
       <c r="E215" t="s">
-        <v>251</v>
+        <v>38</v>
       </c>
       <c r="F215" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="G215" s="1">
-        <v>46262</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="216" spans="1:7" x14ac:dyDescent="0.2">
@@ -7937,22 +7901,22 @@
         <v>0</v>
       </c>
       <c r="B216" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="C216" t="s">
         <v>80</v>
       </c>
       <c r="D216" t="s">
-        <v>470</v>
+        <v>16</v>
       </c>
       <c r="E216" t="s">
-        <v>471</v>
+        <v>17</v>
       </c>
       <c r="F216" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="G216" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="217" spans="1:7" x14ac:dyDescent="0.2">
@@ -7960,19 +7924,19 @@
         <v>0</v>
       </c>
       <c r="B217" t="s">
-        <v>472</v>
+        <v>464</v>
       </c>
       <c r="C217" t="s">
-        <v>80</v>
+        <v>6</v>
       </c>
       <c r="D217" t="s">
-        <v>473</v>
+        <v>87</v>
       </c>
       <c r="E217" t="s">
-        <v>474</v>
+        <v>88</v>
       </c>
       <c r="F217" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="G217" s="1">
         <v>46262</v>
@@ -7983,22 +7947,22 @@
         <v>0</v>
       </c>
       <c r="B218" t="s">
-        <v>475</v>
+        <v>465</v>
       </c>
       <c r="C218" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D218" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="E218" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="F218" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="G218" s="1">
-        <v>46265</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="219" spans="1:7" x14ac:dyDescent="0.2">
@@ -8006,16 +7970,16 @@
         <v>0</v>
       </c>
       <c r="B219" t="s">
-        <v>476</v>
+        <v>466</v>
       </c>
       <c r="C219" t="s">
-        <v>80</v>
+        <v>6</v>
       </c>
       <c r="D219" t="s">
-        <v>37</v>
+        <v>87</v>
       </c>
       <c r="E219" t="s">
-        <v>38</v>
+        <v>88</v>
       </c>
       <c r="F219" s="1">
         <v>46262</v>
@@ -8029,16 +7993,16 @@
         <v>0</v>
       </c>
       <c r="B220" t="s">
-        <v>477</v>
+        <v>467</v>
       </c>
       <c r="C220" t="s">
         <v>80</v>
       </c>
       <c r="D220" t="s">
-        <v>37</v>
+        <v>87</v>
       </c>
       <c r="E220" t="s">
-        <v>38</v>
+        <v>88</v>
       </c>
       <c r="F220" s="1">
         <v>46262</v>
@@ -8052,16 +8016,16 @@
         <v>0</v>
       </c>
       <c r="B221" t="s">
-        <v>478</v>
+        <v>468</v>
       </c>
       <c r="C221" t="s">
         <v>80</v>
       </c>
       <c r="D221" t="s">
-        <v>16</v>
+        <v>87</v>
       </c>
       <c r="E221" t="s">
-        <v>17</v>
+        <v>88</v>
       </c>
       <c r="F221" s="1">
         <v>46262</v>
@@ -8075,16 +8039,16 @@
         <v>0</v>
       </c>
       <c r="B222" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="C222" t="s">
         <v>80</v>
       </c>
       <c r="D222" t="s">
-        <v>87</v>
+        <v>300</v>
       </c>
       <c r="E222" t="s">
-        <v>88</v>
+        <v>301</v>
       </c>
       <c r="F222" s="1">
         <v>46262</v>
@@ -8098,22 +8062,22 @@
         <v>0</v>
       </c>
       <c r="B223" t="s">
-        <v>480</v>
+        <v>470</v>
       </c>
       <c r="C223" t="s">
         <v>80</v>
       </c>
       <c r="D223" t="s">
-        <v>87</v>
+        <v>48</v>
       </c>
       <c r="E223" t="s">
-        <v>88</v>
+        <v>49</v>
       </c>
       <c r="F223" s="1">
         <v>46262</v>
       </c>
       <c r="G223" s="1">
-        <v>46262</v>
+        <v>46265</v>
       </c>
     </row>
     <row r="224" spans="1:7" x14ac:dyDescent="0.2">
@@ -8121,16 +8085,16 @@
         <v>0</v>
       </c>
       <c r="B224" t="s">
-        <v>481</v>
+        <v>471</v>
       </c>
       <c r="C224" t="s">
         <v>80</v>
       </c>
       <c r="D224" t="s">
-        <v>87</v>
+        <v>48</v>
       </c>
       <c r="E224" t="s">
-        <v>88</v>
+        <v>49</v>
       </c>
       <c r="F224" s="1">
         <v>46262</v>
@@ -8144,16 +8108,16 @@
         <v>0</v>
       </c>
       <c r="B225" t="s">
-        <v>482</v>
+        <v>472</v>
       </c>
       <c r="C225" t="s">
         <v>80</v>
       </c>
       <c r="D225" t="s">
-        <v>87</v>
+        <v>16</v>
       </c>
       <c r="E225" t="s">
-        <v>88</v>
+        <v>17</v>
       </c>
       <c r="F225" s="1">
         <v>46262</v>
@@ -8167,22 +8131,22 @@
         <v>0</v>
       </c>
       <c r="B226" t="s">
-        <v>483</v>
+        <v>473</v>
       </c>
       <c r="C226" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D226" t="s">
-        <v>87</v>
+        <v>114</v>
       </c>
       <c r="E226" t="s">
-        <v>88</v>
+        <v>115</v>
       </c>
       <c r="F226" s="1">
         <v>46262</v>
       </c>
       <c r="G226" s="1">
-        <v>46262</v>
+        <v>46265</v>
       </c>
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.2">
@@ -8190,22 +8154,22 @@
         <v>0</v>
       </c>
       <c r="B227" t="s">
-        <v>484</v>
+        <v>474</v>
       </c>
       <c r="C227" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D227" t="s">
-        <v>87</v>
+        <v>114</v>
       </c>
       <c r="E227" t="s">
-        <v>88</v>
+        <v>115</v>
       </c>
       <c r="F227" s="1">
         <v>46262</v>
       </c>
       <c r="G227" s="1">
-        <v>46262</v>
+        <v>46265</v>
       </c>
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.2">
@@ -8213,22 +8177,22 @@
         <v>0</v>
       </c>
       <c r="B228" t="s">
-        <v>485</v>
+        <v>475</v>
       </c>
       <c r="C228" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D228" t="s">
-        <v>303</v>
+        <v>476</v>
       </c>
       <c r="E228" t="s">
-        <v>304</v>
+        <v>477</v>
       </c>
       <c r="F228" s="1">
         <v>46262</v>
       </c>
       <c r="G228" s="1">
-        <v>46262</v>
+        <v>46265</v>
       </c>
     </row>
     <row r="229" spans="1:7" x14ac:dyDescent="0.2">
@@ -8236,16 +8200,16 @@
         <v>0</v>
       </c>
       <c r="B229" t="s">
-        <v>486</v>
+        <v>478</v>
       </c>
       <c r="C229" t="s">
         <v>80</v>
       </c>
       <c r="D229" t="s">
-        <v>48</v>
+        <v>479</v>
       </c>
       <c r="E229" t="s">
-        <v>49</v>
+        <v>480</v>
       </c>
       <c r="F229" s="1">
         <v>46262</v>
@@ -8259,22 +8223,22 @@
         <v>0</v>
       </c>
       <c r="B230" t="s">
-        <v>487</v>
+        <v>481</v>
       </c>
       <c r="C230" t="s">
         <v>80</v>
       </c>
       <c r="D230" t="s">
-        <v>48</v>
+        <v>479</v>
       </c>
       <c r="E230" t="s">
-        <v>49</v>
+        <v>480</v>
       </c>
       <c r="F230" s="1">
         <v>46262</v>
       </c>
       <c r="G230" s="1">
-        <v>46262</v>
+        <v>46265</v>
       </c>
     </row>
     <row r="231" spans="1:7" x14ac:dyDescent="0.2">
@@ -8282,22 +8246,22 @@
         <v>0</v>
       </c>
       <c r="B231" t="s">
-        <v>488</v>
+        <v>482</v>
       </c>
       <c r="C231" t="s">
         <v>80</v>
       </c>
       <c r="D231" t="s">
-        <v>16</v>
+        <v>483</v>
       </c>
       <c r="E231" t="s">
-        <v>17</v>
+        <v>484</v>
       </c>
       <c r="F231" s="1">
         <v>46262</v>
       </c>
       <c r="G231" s="1">
-        <v>46262</v>
+        <v>46265</v>
       </c>
     </row>
     <row r="232" spans="1:7" x14ac:dyDescent="0.2">
@@ -8305,16 +8269,16 @@
         <v>0</v>
       </c>
       <c r="B232" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="C232" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D232" t="s">
-        <v>114</v>
+        <v>486</v>
       </c>
       <c r="E232" t="s">
-        <v>115</v>
+        <v>487</v>
       </c>
       <c r="F232" s="1">
         <v>46262</v>
@@ -8328,16 +8292,16 @@
         <v>0</v>
       </c>
       <c r="B233" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="C233" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D233" t="s">
-        <v>114</v>
+        <v>16</v>
       </c>
       <c r="E233" t="s">
-        <v>115</v>
+        <v>17</v>
       </c>
       <c r="F233" s="1">
         <v>46262</v>
@@ -8351,16 +8315,16 @@
         <v>0</v>
       </c>
       <c r="B234" t="s">
+        <v>489</v>
+      </c>
+      <c r="C234" t="s">
+        <v>80</v>
+      </c>
+      <c r="D234" t="s">
+        <v>490</v>
+      </c>
+      <c r="E234" t="s">
         <v>491</v>
-      </c>
-      <c r="C234" t="s">
-        <v>2</v>
-      </c>
-      <c r="D234" t="s">
-        <v>492</v>
-      </c>
-      <c r="E234" t="s">
-        <v>493</v>
       </c>
       <c r="F234" s="1">
         <v>46262</v>
@@ -8374,16 +8338,16 @@
         <v>0</v>
       </c>
       <c r="B235" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="C235" t="s">
         <v>80</v>
       </c>
       <c r="D235" t="s">
-        <v>495</v>
+        <v>132</v>
       </c>
       <c r="E235" t="s">
-        <v>496</v>
+        <v>133</v>
       </c>
       <c r="F235" s="1">
         <v>46262</v>
@@ -8397,16 +8361,16 @@
         <v>0</v>
       </c>
       <c r="B236" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="C236" t="s">
         <v>80</v>
       </c>
       <c r="D236" t="s">
-        <v>495</v>
+        <v>197</v>
       </c>
       <c r="E236" t="s">
-        <v>496</v>
+        <v>198</v>
       </c>
       <c r="F236" s="1">
         <v>46262</v>
@@ -8420,16 +8384,16 @@
         <v>0</v>
       </c>
       <c r="B237" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="C237" t="s">
         <v>80</v>
       </c>
       <c r="D237" t="s">
-        <v>433</v>
+        <v>197</v>
       </c>
       <c r="E237" t="s">
-        <v>434</v>
+        <v>198</v>
       </c>
       <c r="F237" s="1">
         <v>46262</v>
@@ -8443,16 +8407,16 @@
         <v>0</v>
       </c>
       <c r="B238" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="C238" t="s">
         <v>80</v>
       </c>
       <c r="D238" t="s">
-        <v>93</v>
+        <v>496</v>
       </c>
       <c r="E238" t="s">
-        <v>94</v>
+        <v>497</v>
       </c>
       <c r="F238" s="1">
         <v>46262</v>
@@ -8466,16 +8430,16 @@
         <v>0</v>
       </c>
       <c r="B239" t="s">
+        <v>498</v>
+      </c>
+      <c r="C239" t="s">
+        <v>80</v>
+      </c>
+      <c r="D239" t="s">
+        <v>499</v>
+      </c>
+      <c r="E239" t="s">
         <v>500</v>
-      </c>
-      <c r="C239" t="s">
-        <v>2</v>
-      </c>
-      <c r="D239" t="s">
-        <v>501</v>
-      </c>
-      <c r="E239" t="s">
-        <v>502</v>
       </c>
       <c r="F239" s="1">
         <v>46262</v>
@@ -8489,16 +8453,16 @@
         <v>0</v>
       </c>
       <c r="B240" t="s">
+        <v>501</v>
+      </c>
+      <c r="C240" t="s">
+        <v>80</v>
+      </c>
+      <c r="D240" t="s">
+        <v>502</v>
+      </c>
+      <c r="E240" t="s">
         <v>503</v>
-      </c>
-      <c r="C240" t="s">
-        <v>80</v>
-      </c>
-      <c r="D240" t="s">
-        <v>504</v>
-      </c>
-      <c r="E240" t="s">
-        <v>505</v>
       </c>
       <c r="F240" s="1">
         <v>46262</v>
@@ -8512,19 +8476,19 @@
         <v>0</v>
       </c>
       <c r="B241" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="C241" t="s">
         <v>80</v>
       </c>
       <c r="D241" t="s">
-        <v>507</v>
+        <v>486</v>
       </c>
       <c r="E241" t="s">
-        <v>508</v>
+        <v>487</v>
       </c>
       <c r="F241" s="1">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="G241" s="1">
         <v>46265</v>
@@ -8535,19 +8499,19 @@
         <v>0</v>
       </c>
       <c r="B242" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="C242" t="s">
         <v>80</v>
       </c>
       <c r="D242" t="s">
-        <v>16</v>
+        <v>506</v>
       </c>
       <c r="E242" t="s">
-        <v>17</v>
+        <v>507</v>
       </c>
       <c r="F242" s="1">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="G242" s="1">
         <v>46265</v>
@@ -8558,19 +8522,19 @@
         <v>0</v>
       </c>
       <c r="B243" t="s">
+        <v>508</v>
+      </c>
+      <c r="C243" t="s">
+        <v>2</v>
+      </c>
+      <c r="D243" t="s">
+        <v>509</v>
+      </c>
+      <c r="E243" t="s">
         <v>510</v>
       </c>
-      <c r="C243" t="s">
-        <v>2</v>
-      </c>
-      <c r="D243" t="s">
-        <v>501</v>
-      </c>
-      <c r="E243" t="s">
-        <v>502</v>
-      </c>
       <c r="F243" s="1">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="G243" s="1">
         <v>46265</v>
@@ -8587,13 +8551,13 @@
         <v>2</v>
       </c>
       <c r="D244" t="s">
-        <v>501</v>
+        <v>512</v>
       </c>
       <c r="E244" t="s">
-        <v>502</v>
+        <v>513</v>
       </c>
       <c r="F244" s="1">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="G244" s="1">
         <v>46265</v>
@@ -8604,19 +8568,19 @@
         <v>0</v>
       </c>
       <c r="B245" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="C245" t="s">
         <v>2</v>
       </c>
       <c r="D245" t="s">
-        <v>501</v>
+        <v>257</v>
       </c>
       <c r="E245" t="s">
-        <v>502</v>
+        <v>258</v>
       </c>
       <c r="F245" s="1">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="G245" s="1">
         <v>46265</v>
@@ -8627,19 +8591,19 @@
         <v>0</v>
       </c>
       <c r="B246" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="C246" t="s">
         <v>80</v>
       </c>
       <c r="D246" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="E246" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="F246" s="1">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="G246" s="1">
         <v>46265</v>
@@ -8650,19 +8614,19 @@
         <v>0</v>
       </c>
       <c r="B247" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="C247" t="s">
         <v>80</v>
       </c>
       <c r="D247" t="s">
-        <v>132</v>
+        <v>519</v>
       </c>
       <c r="E247" t="s">
-        <v>133</v>
+        <v>520</v>
       </c>
       <c r="F247" s="1">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="G247" s="1">
         <v>46265</v>
@@ -8673,19 +8637,19 @@
         <v>0</v>
       </c>
       <c r="B248" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="C248" t="s">
         <v>80</v>
       </c>
       <c r="D248" t="s">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="E248" t="s">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="F248" s="1">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="G248" s="1">
         <v>46265</v>
@@ -8696,22 +8660,22 @@
         <v>0</v>
       </c>
       <c r="B249" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="C249" t="s">
         <v>80</v>
       </c>
       <c r="D249" t="s">
-        <v>518</v>
+        <v>171</v>
       </c>
       <c r="E249" t="s">
-        <v>519</v>
+        <v>172</v>
       </c>
       <c r="F249" s="1">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="G249" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="250" spans="1:7" x14ac:dyDescent="0.2">
@@ -8719,19 +8683,19 @@
         <v>0</v>
       </c>
       <c r="B250" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="C250" t="s">
         <v>80</v>
       </c>
       <c r="D250" t="s">
-        <v>197</v>
+        <v>16</v>
       </c>
       <c r="E250" t="s">
-        <v>198</v>
+        <v>17</v>
       </c>
       <c r="F250" s="1">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="G250" s="1">
         <v>46265</v>
@@ -8742,19 +8706,19 @@
         <v>0</v>
       </c>
       <c r="B251" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="C251" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D251" t="s">
-        <v>197</v>
+        <v>41</v>
       </c>
       <c r="E251" t="s">
-        <v>198</v>
+        <v>42</v>
       </c>
       <c r="F251" s="1">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="G251" s="1">
         <v>46265</v>
@@ -8765,19 +8729,19 @@
         <v>0</v>
       </c>
       <c r="B252" t="s">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="C252" t="s">
         <v>80</v>
       </c>
       <c r="D252" t="s">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="E252" t="s">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="F252" s="1">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="G252" s="1">
         <v>46265</v>
@@ -8788,19 +8752,19 @@
         <v>0</v>
       </c>
       <c r="B253" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="C253" t="s">
         <v>80</v>
       </c>
       <c r="D253" t="s">
-        <v>527</v>
+        <v>522</v>
       </c>
       <c r="E253" t="s">
-        <v>528</v>
+        <v>523</v>
       </c>
       <c r="F253" s="1">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="G253" s="1">
         <v>46265</v>
@@ -8811,19 +8775,19 @@
         <v>0</v>
       </c>
       <c r="B254" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="C254" t="s">
         <v>80</v>
       </c>
       <c r="D254" t="s">
-        <v>429</v>
+        <v>532</v>
       </c>
       <c r="E254" t="s">
-        <v>430</v>
+        <v>533</v>
       </c>
       <c r="F254" s="1">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="G254" s="1">
         <v>46265</v>
@@ -8834,19 +8798,19 @@
         <v>0</v>
       </c>
       <c r="B255" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="C255" t="s">
         <v>80</v>
       </c>
       <c r="D255" t="s">
-        <v>531</v>
+        <v>200</v>
       </c>
       <c r="E255" t="s">
-        <v>532</v>
+        <v>201</v>
       </c>
       <c r="F255" s="1">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="G255" s="1">
         <v>46265</v>
@@ -8857,19 +8821,19 @@
         <v>0</v>
       </c>
       <c r="B256" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="C256" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D256" t="s">
-        <v>534</v>
+        <v>84</v>
       </c>
       <c r="E256" t="s">
-        <v>535</v>
+        <v>85</v>
       </c>
       <c r="F256" s="1">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="G256" s="1">
         <v>46265</v>
@@ -8886,13 +8850,13 @@
         <v>80</v>
       </c>
       <c r="D257" t="s">
-        <v>537</v>
+        <v>81</v>
       </c>
       <c r="E257" t="s">
-        <v>538</v>
+        <v>82</v>
       </c>
       <c r="F257" s="1">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="G257" s="1">
         <v>46265</v>
@@ -8903,19 +8867,19 @@
         <v>0</v>
       </c>
       <c r="B258" t="s">
+        <v>537</v>
+      </c>
+      <c r="C258" t="s">
+        <v>80</v>
+      </c>
+      <c r="D258" t="s">
+        <v>538</v>
+      </c>
+      <c r="E258" t="s">
         <v>539</v>
       </c>
-      <c r="C258" t="s">
-        <v>80</v>
-      </c>
-      <c r="D258" t="s">
-        <v>540</v>
-      </c>
-      <c r="E258" t="s">
-        <v>541</v>
-      </c>
       <c r="F258" s="1">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="G258" s="1">
         <v>46265</v>
@@ -8926,19 +8890,19 @@
         <v>0</v>
       </c>
       <c r="B259" t="s">
+        <v>540</v>
+      </c>
+      <c r="C259" t="s">
+        <v>80</v>
+      </c>
+      <c r="D259" t="s">
+        <v>541</v>
+      </c>
+      <c r="E259" t="s">
         <v>542</v>
       </c>
-      <c r="C259" t="s">
-        <v>80</v>
-      </c>
-      <c r="D259" t="s">
-        <v>507</v>
-      </c>
-      <c r="E259" t="s">
-        <v>508</v>
-      </c>
       <c r="F259" s="1">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="G259" s="1">
         <v>46265</v>
@@ -8952,16 +8916,16 @@
         <v>543</v>
       </c>
       <c r="C260" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D260" t="s">
-        <v>544</v>
+        <v>19</v>
       </c>
       <c r="E260" t="s">
-        <v>545</v>
+        <v>20</v>
       </c>
       <c r="F260" s="1">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="G260" s="1">
         <v>46265</v>
@@ -8972,16 +8936,16 @@
         <v>0</v>
       </c>
       <c r="B261" t="s">
+        <v>544</v>
+      </c>
+      <c r="C261" t="s">
+        <v>80</v>
+      </c>
+      <c r="D261" t="s">
+        <v>545</v>
+      </c>
+      <c r="E261" t="s">
         <v>546</v>
-      </c>
-      <c r="C261" t="s">
-        <v>80</v>
-      </c>
-      <c r="D261" t="s">
-        <v>547</v>
-      </c>
-      <c r="E261" t="s">
-        <v>548</v>
       </c>
       <c r="F261" s="1">
         <v>46265</v>
@@ -8995,16 +8959,16 @@
         <v>0</v>
       </c>
       <c r="B262" t="s">
+        <v>547</v>
+      </c>
+      <c r="C262" t="s">
+        <v>80</v>
+      </c>
+      <c r="D262" t="s">
+        <v>548</v>
+      </c>
+      <c r="E262" t="s">
         <v>549</v>
-      </c>
-      <c r="C262" t="s">
-        <v>80</v>
-      </c>
-      <c r="D262" t="s">
-        <v>550</v>
-      </c>
-      <c r="E262" t="s">
-        <v>551</v>
       </c>
       <c r="F262" s="1">
         <v>46265</v>
@@ -9018,16 +8982,16 @@
         <v>0</v>
       </c>
       <c r="B263" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="C263" t="s">
         <v>80</v>
       </c>
       <c r="D263" t="s">
-        <v>553</v>
+        <v>340</v>
       </c>
       <c r="E263" t="s">
-        <v>554</v>
+        <v>341</v>
       </c>
       <c r="F263" s="1">
         <v>46265</v>
@@ -9041,16 +9005,16 @@
         <v>0</v>
       </c>
       <c r="B264" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="C264" t="s">
         <v>80</v>
       </c>
       <c r="D264" t="s">
-        <v>61</v>
+        <v>101</v>
       </c>
       <c r="E264" t="s">
-        <v>62</v>
+        <v>102</v>
       </c>
       <c r="F264" s="1">
         <v>46265</v>
@@ -9064,16 +9028,16 @@
         <v>0</v>
       </c>
       <c r="B265" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="C265" t="s">
         <v>80</v>
       </c>
       <c r="D265" t="s">
-        <v>224</v>
+        <v>553</v>
       </c>
       <c r="E265" t="s">
-        <v>225</v>
+        <v>554</v>
       </c>
       <c r="F265" s="1">
         <v>46265</v>
@@ -9087,16 +9051,16 @@
         <v>0</v>
       </c>
       <c r="B266" t="s">
+        <v>555</v>
+      </c>
+      <c r="C266" t="s">
+        <v>80</v>
+      </c>
+      <c r="D266" t="s">
+        <v>556</v>
+      </c>
+      <c r="E266" t="s">
         <v>557</v>
-      </c>
-      <c r="C266" t="s">
-        <v>80</v>
-      </c>
-      <c r="D266" t="s">
-        <v>429</v>
-      </c>
-      <c r="E266" t="s">
-        <v>430</v>
       </c>
       <c r="F266" s="1">
         <v>46265</v>
@@ -9116,10 +9080,10 @@
         <v>80</v>
       </c>
       <c r="D267" t="s">
-        <v>257</v>
+        <v>161</v>
       </c>
       <c r="E267" t="s">
-        <v>258</v>
+        <v>162</v>
       </c>
       <c r="F267" s="1">
         <v>46265</v>
@@ -9139,10 +9103,10 @@
         <v>80</v>
       </c>
       <c r="D268" t="s">
-        <v>257</v>
+        <v>560</v>
       </c>
       <c r="E268" t="s">
-        <v>258</v>
+        <v>561</v>
       </c>
       <c r="F268" s="1">
         <v>46265</v>
@@ -9156,16 +9120,16 @@
         <v>0</v>
       </c>
       <c r="B269" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="C269" t="s">
         <v>80</v>
       </c>
       <c r="D269" t="s">
-        <v>473</v>
+        <v>93</v>
       </c>
       <c r="E269" t="s">
-        <v>474</v>
+        <v>94</v>
       </c>
       <c r="F269" s="1">
         <v>46265</v>
@@ -9179,16 +9143,16 @@
         <v>0</v>
       </c>
       <c r="B270" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="C270" t="s">
         <v>80</v>
       </c>
       <c r="D270" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="E270" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="F270" s="1">
         <v>46265</v>
@@ -9202,16 +9166,16 @@
         <v>0</v>
       </c>
       <c r="B271" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="C271" t="s">
         <v>80</v>
       </c>
       <c r="D271" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="E271" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="F271" s="1">
         <v>46265</v>
@@ -9225,16 +9189,16 @@
         <v>0</v>
       </c>
       <c r="B272" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="C272" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D272" t="s">
-        <v>568</v>
+        <v>41</v>
       </c>
       <c r="E272" t="s">
-        <v>569</v>
+        <v>42</v>
       </c>
       <c r="F272" s="1">
         <v>46265</v>
@@ -9254,16 +9218,16 @@
         <v>80</v>
       </c>
       <c r="D273" t="s">
-        <v>16</v>
+        <v>571</v>
       </c>
       <c r="E273" t="s">
-        <v>17</v>
+        <v>572</v>
       </c>
       <c r="F273" s="1">
         <v>46265</v>
       </c>
       <c r="G273" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="274" spans="1:7" x14ac:dyDescent="0.2">
@@ -9271,16 +9235,16 @@
         <v>0</v>
       </c>
       <c r="B274" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="C274" t="s">
         <v>80</v>
       </c>
       <c r="D274" t="s">
-        <v>41</v>
+        <v>574</v>
       </c>
       <c r="E274" t="s">
-        <v>42</v>
+        <v>575</v>
       </c>
       <c r="F274" s="1">
         <v>46265</v>
@@ -9294,16 +9258,16 @@
         <v>0</v>
       </c>
       <c r="B275" t="s">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="C275" t="s">
         <v>80</v>
       </c>
       <c r="D275" t="s">
-        <v>573</v>
+        <v>155</v>
       </c>
       <c r="E275" t="s">
-        <v>574</v>
+        <v>156</v>
       </c>
       <c r="F275" s="1">
         <v>46265</v>
@@ -9317,16 +9281,16 @@
         <v>0</v>
       </c>
       <c r="B276" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="C276" t="s">
         <v>80</v>
       </c>
       <c r="D276" t="s">
-        <v>568</v>
+        <v>578</v>
       </c>
       <c r="E276" t="s">
-        <v>569</v>
+        <v>579</v>
       </c>
       <c r="F276" s="1">
         <v>46265</v>
@@ -9340,16 +9304,16 @@
         <v>0</v>
       </c>
       <c r="B277" t="s">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="C277" t="s">
         <v>80</v>
       </c>
       <c r="D277" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="E277" t="s">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="F277" s="1">
         <v>46265</v>
@@ -9363,16 +9327,16 @@
         <v>0</v>
       </c>
       <c r="B278" t="s">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="C278" t="s">
         <v>80</v>
       </c>
       <c r="D278" t="s">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="E278" t="s">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="F278" s="1">
         <v>46265</v>
@@ -9386,16 +9350,16 @@
         <v>0</v>
       </c>
       <c r="B279" t="s">
-        <v>582</v>
+        <v>586</v>
       </c>
       <c r="C279" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D279" t="s">
-        <v>93</v>
+        <v>420</v>
       </c>
       <c r="E279" t="s">
-        <v>94</v>
+        <v>421</v>
       </c>
       <c r="F279" s="1">
         <v>46265</v>
@@ -9409,16 +9373,16 @@
         <v>0</v>
       </c>
       <c r="B280" t="s">
-        <v>583</v>
+        <v>587</v>
       </c>
       <c r="C280" t="s">
         <v>80</v>
       </c>
       <c r="D280" t="s">
-        <v>93</v>
+        <v>588</v>
       </c>
       <c r="E280" t="s">
-        <v>94</v>
+        <v>589</v>
       </c>
       <c r="F280" s="1">
         <v>46265</v>
@@ -9432,16 +9396,16 @@
         <v>0</v>
       </c>
       <c r="B281" t="s">
-        <v>584</v>
+        <v>590</v>
       </c>
       <c r="C281" t="s">
         <v>80</v>
       </c>
       <c r="D281" t="s">
-        <v>200</v>
+        <v>591</v>
       </c>
       <c r="E281" t="s">
-        <v>201</v>
+        <v>592</v>
       </c>
       <c r="F281" s="1">
         <v>46265</v>
@@ -9455,16 +9419,16 @@
         <v>0</v>
       </c>
       <c r="B282" t="s">
-        <v>585</v>
+        <v>593</v>
       </c>
       <c r="C282" t="s">
         <v>80</v>
       </c>
       <c r="D282" t="s">
-        <v>93</v>
+        <v>594</v>
       </c>
       <c r="E282" t="s">
-        <v>94</v>
+        <v>595</v>
       </c>
       <c r="F282" s="1">
         <v>46265</v>
@@ -9478,16 +9442,16 @@
         <v>0</v>
       </c>
       <c r="B283" t="s">
-        <v>586</v>
+        <v>596</v>
       </c>
       <c r="C283" t="s">
         <v>80</v>
       </c>
       <c r="D283" t="s">
-        <v>205</v>
+        <v>597</v>
       </c>
       <c r="E283" t="s">
-        <v>206</v>
+        <v>598</v>
       </c>
       <c r="F283" s="1">
         <v>46265</v>
@@ -9501,22 +9465,22 @@
         <v>0</v>
       </c>
       <c r="B284" t="s">
-        <v>587</v>
+        <v>599</v>
       </c>
       <c r="C284" t="s">
         <v>80</v>
       </c>
       <c r="D284" t="s">
-        <v>588</v>
+        <v>600</v>
       </c>
       <c r="E284" t="s">
-        <v>589</v>
+        <v>601</v>
       </c>
       <c r="F284" s="1">
         <v>46265</v>
       </c>
       <c r="G284" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="285" spans="1:7" x14ac:dyDescent="0.2">
@@ -9524,16 +9488,16 @@
         <v>0</v>
       </c>
       <c r="B285" t="s">
-        <v>590</v>
+        <v>602</v>
       </c>
       <c r="C285" t="s">
         <v>80</v>
       </c>
       <c r="D285" t="s">
-        <v>93</v>
+        <v>528</v>
       </c>
       <c r="E285" t="s">
-        <v>94</v>
+        <v>529</v>
       </c>
       <c r="F285" s="1">
         <v>46265</v>
@@ -9547,16 +9511,16 @@
         <v>0</v>
       </c>
       <c r="B286" t="s">
-        <v>591</v>
+        <v>603</v>
       </c>
       <c r="C286" t="s">
         <v>80</v>
       </c>
       <c r="D286" t="s">
-        <v>93</v>
+        <v>490</v>
       </c>
       <c r="E286" t="s">
-        <v>94</v>
+        <v>491</v>
       </c>
       <c r="F286" s="1">
         <v>46265</v>
@@ -9570,16 +9534,16 @@
         <v>0</v>
       </c>
       <c r="B287" t="s">
-        <v>592</v>
+        <v>604</v>
       </c>
       <c r="C287" t="s">
         <v>80</v>
       </c>
       <c r="D287" t="s">
-        <v>84</v>
+        <v>605</v>
       </c>
       <c r="E287" t="s">
-        <v>85</v>
+        <v>606</v>
       </c>
       <c r="F287" s="1">
         <v>46265</v>
@@ -9593,16 +9557,16 @@
         <v>0</v>
       </c>
       <c r="B288" t="s">
-        <v>593</v>
+        <v>607</v>
       </c>
       <c r="C288" t="s">
         <v>80</v>
       </c>
       <c r="D288" t="s">
-        <v>594</v>
+        <v>608</v>
       </c>
       <c r="E288" t="s">
-        <v>595</v>
+        <v>609</v>
       </c>
       <c r="F288" s="1">
         <v>46265</v>
@@ -9616,16 +9580,16 @@
         <v>0</v>
       </c>
       <c r="B289" t="s">
-        <v>596</v>
+        <v>610</v>
       </c>
       <c r="C289" t="s">
         <v>80</v>
       </c>
       <c r="D289" t="s">
-        <v>16</v>
+        <v>611</v>
       </c>
       <c r="E289" t="s">
-        <v>17</v>
+        <v>612</v>
       </c>
       <c r="F289" s="1">
         <v>46265</v>
@@ -9639,16 +9603,16 @@
         <v>0</v>
       </c>
       <c r="B290" t="s">
-        <v>597</v>
+        <v>613</v>
       </c>
       <c r="C290" t="s">
         <v>80</v>
       </c>
       <c r="D290" t="s">
-        <v>598</v>
+        <v>614</v>
       </c>
       <c r="E290" t="s">
-        <v>599</v>
+        <v>615</v>
       </c>
       <c r="F290" s="1">
         <v>46265</v>
@@ -9662,16 +9626,16 @@
         <v>0</v>
       </c>
       <c r="B291" t="s">
-        <v>600</v>
+        <v>616</v>
       </c>
       <c r="C291" t="s">
         <v>80</v>
       </c>
       <c r="D291" t="s">
-        <v>403</v>
+        <v>617</v>
       </c>
       <c r="E291" t="s">
-        <v>404</v>
+        <v>618</v>
       </c>
       <c r="F291" s="1">
         <v>46265</v>
@@ -9685,16 +9649,16 @@
         <v>0</v>
       </c>
       <c r="B292" t="s">
-        <v>601</v>
+        <v>619</v>
       </c>
       <c r="C292" t="s">
         <v>80</v>
       </c>
       <c r="D292" t="s">
-        <v>81</v>
+        <v>37</v>
       </c>
       <c r="E292" t="s">
-        <v>82</v>
+        <v>38</v>
       </c>
       <c r="F292" s="1">
         <v>46265</v>
@@ -9708,16 +9672,16 @@
         <v>0</v>
       </c>
       <c r="B293" t="s">
-        <v>602</v>
+        <v>620</v>
       </c>
       <c r="C293" t="s">
         <v>80</v>
       </c>
       <c r="D293" t="s">
-        <v>603</v>
+        <v>37</v>
       </c>
       <c r="E293" t="s">
-        <v>604</v>
+        <v>38</v>
       </c>
       <c r="F293" s="1">
         <v>46265</v>
@@ -9731,22 +9695,22 @@
         <v>0</v>
       </c>
       <c r="B294" t="s">
-        <v>605</v>
+        <v>621</v>
       </c>
       <c r="C294" t="s">
         <v>80</v>
       </c>
       <c r="D294" t="s">
-        <v>606</v>
+        <v>622</v>
       </c>
       <c r="E294" t="s">
-        <v>607</v>
+        <v>623</v>
       </c>
       <c r="F294" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="G294" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="295" spans="1:7" x14ac:dyDescent="0.2">
@@ -9754,22 +9718,22 @@
         <v>0</v>
       </c>
       <c r="B295" t="s">
-        <v>608</v>
+        <v>624</v>
       </c>
       <c r="C295" t="s">
         <v>80</v>
       </c>
       <c r="D295" t="s">
-        <v>19</v>
+        <v>541</v>
       </c>
       <c r="E295" t="s">
-        <v>20</v>
+        <v>542</v>
       </c>
       <c r="F295" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="G295" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="296" spans="1:7" x14ac:dyDescent="0.2">
@@ -9777,22 +9741,22 @@
         <v>0</v>
       </c>
       <c r="B296" t="s">
-        <v>609</v>
+        <v>625</v>
       </c>
       <c r="C296" t="s">
         <v>80</v>
       </c>
       <c r="D296" t="s">
-        <v>610</v>
+        <v>626</v>
       </c>
       <c r="E296" t="s">
-        <v>611</v>
+        <v>627</v>
       </c>
       <c r="F296" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="G296" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="297" spans="1:7" x14ac:dyDescent="0.2">
@@ -9800,22 +9764,22 @@
         <v>0</v>
       </c>
       <c r="B297" t="s">
-        <v>612</v>
+        <v>628</v>
       </c>
       <c r="C297" t="s">
         <v>80</v>
       </c>
       <c r="D297" t="s">
-        <v>613</v>
+        <v>629</v>
       </c>
       <c r="E297" t="s">
-        <v>614</v>
+        <v>630</v>
       </c>
       <c r="F297" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="G297" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="298" spans="1:7" x14ac:dyDescent="0.2">
@@ -9823,22 +9787,22 @@
         <v>0</v>
       </c>
       <c r="B298" t="s">
-        <v>615</v>
+        <v>631</v>
       </c>
       <c r="C298" t="s">
         <v>80</v>
       </c>
       <c r="D298" t="s">
-        <v>310</v>
+        <v>16</v>
       </c>
       <c r="E298" t="s">
-        <v>311</v>
+        <v>17</v>
       </c>
       <c r="F298" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="G298" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="299" spans="1:7" x14ac:dyDescent="0.2">
@@ -9846,22 +9810,22 @@
         <v>0</v>
       </c>
       <c r="B299" t="s">
-        <v>616</v>
+        <v>632</v>
       </c>
       <c r="C299" t="s">
         <v>80</v>
       </c>
       <c r="D299" t="s">
-        <v>310</v>
+        <v>205</v>
       </c>
       <c r="E299" t="s">
-        <v>311</v>
+        <v>206</v>
       </c>
       <c r="F299" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="G299" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="300" spans="1:7" x14ac:dyDescent="0.2">
@@ -9869,22 +9833,22 @@
         <v>0</v>
       </c>
       <c r="B300" t="s">
-        <v>617</v>
+        <v>633</v>
       </c>
       <c r="C300" t="s">
         <v>80</v>
       </c>
       <c r="D300" t="s">
-        <v>343</v>
+        <v>634</v>
       </c>
       <c r="E300" t="s">
-        <v>344</v>
+        <v>635</v>
       </c>
       <c r="F300" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="G300" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="301" spans="1:7" x14ac:dyDescent="0.2">
@@ -9892,22 +9856,22 @@
         <v>0</v>
       </c>
       <c r="B301" t="s">
-        <v>618</v>
+        <v>636</v>
       </c>
       <c r="C301" t="s">
         <v>80</v>
       </c>
       <c r="D301" t="s">
-        <v>7</v>
+        <v>127</v>
       </c>
       <c r="E301" t="s">
-        <v>8</v>
+        <v>128</v>
       </c>
       <c r="F301" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="G301" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="302" spans="1:7" x14ac:dyDescent="0.2">
@@ -9915,22 +9879,22 @@
         <v>0</v>
       </c>
       <c r="B302" t="s">
-        <v>619</v>
+        <v>637</v>
       </c>
       <c r="C302" t="s">
         <v>80</v>
       </c>
       <c r="D302" t="s">
-        <v>7</v>
+        <v>638</v>
       </c>
       <c r="E302" t="s">
-        <v>8</v>
+        <v>639</v>
       </c>
       <c r="F302" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="G302" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="303" spans="1:7" x14ac:dyDescent="0.2">
@@ -9938,22 +9902,22 @@
         <v>0</v>
       </c>
       <c r="B303" t="s">
-        <v>620</v>
+        <v>640</v>
       </c>
       <c r="C303" t="s">
         <v>80</v>
       </c>
       <c r="D303" t="s">
-        <v>7</v>
+        <v>641</v>
       </c>
       <c r="E303" t="s">
-        <v>8</v>
+        <v>642</v>
       </c>
       <c r="F303" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="G303" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="304" spans="1:7" x14ac:dyDescent="0.2">
@@ -9961,22 +9925,22 @@
         <v>0</v>
       </c>
       <c r="B304" t="s">
-        <v>621</v>
+        <v>643</v>
       </c>
       <c r="C304" t="s">
         <v>80</v>
       </c>
       <c r="D304" t="s">
-        <v>101</v>
+        <v>340</v>
       </c>
       <c r="E304" t="s">
-        <v>102</v>
+        <v>341</v>
       </c>
       <c r="F304" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="G304" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="305" spans="1:7" x14ac:dyDescent="0.2">
@@ -9984,22 +9948,22 @@
         <v>0</v>
       </c>
       <c r="B305" t="s">
-        <v>622</v>
+        <v>644</v>
       </c>
       <c r="C305" t="s">
         <v>80</v>
       </c>
       <c r="D305" t="s">
-        <v>623</v>
+        <v>560</v>
       </c>
       <c r="E305" t="s">
-        <v>624</v>
+        <v>561</v>
       </c>
       <c r="F305" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="G305" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="306" spans="1:7" x14ac:dyDescent="0.2">
@@ -10007,22 +9971,22 @@
         <v>0</v>
       </c>
       <c r="B306" t="s">
-        <v>625</v>
+        <v>645</v>
       </c>
       <c r="C306" t="s">
         <v>80</v>
       </c>
       <c r="D306" t="s">
-        <v>598</v>
+        <v>646</v>
       </c>
       <c r="E306" t="s">
-        <v>599</v>
+        <v>647</v>
       </c>
       <c r="F306" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="G306" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="307" spans="1:7" x14ac:dyDescent="0.2">
@@ -10030,22 +9994,22 @@
         <v>0</v>
       </c>
       <c r="B307" t="s">
-        <v>626</v>
+        <v>648</v>
       </c>
       <c r="C307" t="s">
         <v>80</v>
       </c>
       <c r="D307" t="s">
-        <v>627</v>
+        <v>45</v>
       </c>
       <c r="E307" t="s">
-        <v>628</v>
+        <v>46</v>
       </c>
       <c r="F307" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="G307" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="308" spans="1:7" x14ac:dyDescent="0.2">
@@ -10053,22 +10017,22 @@
         <v>0</v>
       </c>
       <c r="B308" t="s">
-        <v>629</v>
+        <v>649</v>
       </c>
       <c r="C308" t="s">
         <v>80</v>
       </c>
       <c r="D308" t="s">
-        <v>161</v>
+        <v>310</v>
       </c>
       <c r="E308" t="s">
-        <v>162</v>
+        <v>311</v>
       </c>
       <c r="F308" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="G308" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="309" spans="1:7" x14ac:dyDescent="0.2">
@@ -10076,22 +10040,22 @@
         <v>0</v>
       </c>
       <c r="B309" t="s">
-        <v>630</v>
+        <v>650</v>
       </c>
       <c r="C309" t="s">
         <v>80</v>
       </c>
       <c r="D309" t="s">
-        <v>631</v>
+        <v>651</v>
       </c>
       <c r="E309" t="s">
-        <v>632</v>
+        <v>652</v>
       </c>
       <c r="F309" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="G309" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="310" spans="1:7" x14ac:dyDescent="0.2">
@@ -10099,22 +10063,22 @@
         <v>0</v>
       </c>
       <c r="B310" t="s">
-        <v>633</v>
+        <v>653</v>
       </c>
       <c r="C310" t="s">
         <v>80</v>
       </c>
       <c r="D310" t="s">
-        <v>634</v>
+        <v>101</v>
       </c>
       <c r="E310" t="s">
-        <v>635</v>
+        <v>102</v>
       </c>
       <c r="F310" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="G310" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="311" spans="1:7" x14ac:dyDescent="0.2">
@@ -10122,22 +10086,22 @@
         <v>0</v>
       </c>
       <c r="B311" t="s">
-        <v>636</v>
+        <v>654</v>
       </c>
       <c r="C311" t="s">
         <v>80</v>
       </c>
       <c r="D311" t="s">
-        <v>390</v>
+        <v>655</v>
       </c>
       <c r="E311" t="s">
-        <v>391</v>
+        <v>656</v>
       </c>
       <c r="F311" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="G311" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="312" spans="1:7" x14ac:dyDescent="0.2">
@@ -10145,22 +10109,22 @@
         <v>0</v>
       </c>
       <c r="B312" t="s">
-        <v>637</v>
+        <v>657</v>
       </c>
       <c r="C312" t="s">
         <v>80</v>
       </c>
       <c r="D312" t="s">
-        <v>3</v>
+        <v>658</v>
       </c>
       <c r="E312" t="s">
-        <v>4</v>
+        <v>659</v>
       </c>
       <c r="F312" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="G312" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="313" spans="1:7" x14ac:dyDescent="0.2">
@@ -10168,22 +10132,22 @@
         <v>0</v>
       </c>
       <c r="B313" t="s">
-        <v>638</v>
+        <v>660</v>
       </c>
       <c r="C313" t="s">
         <v>80</v>
       </c>
       <c r="D313" t="s">
-        <v>93</v>
+        <v>661</v>
       </c>
       <c r="E313" t="s">
-        <v>94</v>
+        <v>662</v>
       </c>
       <c r="F313" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="G313" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="314" spans="1:7" x14ac:dyDescent="0.2">
@@ -10191,22 +10155,22 @@
         <v>0</v>
       </c>
       <c r="B314" t="s">
-        <v>639</v>
+        <v>663</v>
       </c>
       <c r="C314" t="s">
         <v>80</v>
       </c>
       <c r="D314" t="s">
-        <v>640</v>
+        <v>661</v>
       </c>
       <c r="E314" t="s">
-        <v>641</v>
+        <v>662</v>
       </c>
       <c r="F314" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="G314" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="315" spans="1:7" x14ac:dyDescent="0.2">
@@ -10214,22 +10178,22 @@
         <v>0</v>
       </c>
       <c r="B315" t="s">
-        <v>642</v>
+        <v>664</v>
       </c>
       <c r="C315" t="s">
         <v>80</v>
       </c>
       <c r="D315" t="s">
-        <v>643</v>
+        <v>665</v>
       </c>
       <c r="E315" t="s">
-        <v>644</v>
+        <v>666</v>
       </c>
       <c r="F315" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="G315" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="316" spans="1:7" x14ac:dyDescent="0.2">
@@ -10237,22 +10201,22 @@
         <v>0</v>
       </c>
       <c r="B316" t="s">
-        <v>645</v>
+        <v>667</v>
       </c>
       <c r="C316" t="s">
         <v>80</v>
       </c>
       <c r="D316" t="s">
-        <v>646</v>
+        <v>668</v>
       </c>
       <c r="E316" t="s">
-        <v>647</v>
+        <v>669</v>
       </c>
       <c r="F316" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="G316" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="317" spans="1:7" x14ac:dyDescent="0.2">
@@ -10260,22 +10224,22 @@
         <v>0</v>
       </c>
       <c r="B317" t="s">
-        <v>648</v>
+        <v>670</v>
       </c>
       <c r="C317" t="s">
         <v>80</v>
       </c>
       <c r="D317" t="s">
-        <v>649</v>
+        <v>668</v>
       </c>
       <c r="E317" t="s">
-        <v>650</v>
+        <v>669</v>
       </c>
       <c r="F317" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="G317" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="318" spans="1:7" x14ac:dyDescent="0.2">
@@ -10283,22 +10247,22 @@
         <v>0</v>
       </c>
       <c r="B318" t="s">
-        <v>651</v>
+        <v>671</v>
       </c>
       <c r="C318" t="s">
         <v>80</v>
       </c>
       <c r="D318" t="s">
-        <v>646</v>
+        <v>288</v>
       </c>
       <c r="E318" t="s">
-        <v>647</v>
+        <v>289</v>
       </c>
       <c r="F318" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="G318" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="319" spans="1:7" x14ac:dyDescent="0.2">
@@ -10306,22 +10270,22 @@
         <v>0</v>
       </c>
       <c r="B319" t="s">
-        <v>652</v>
+        <v>672</v>
       </c>
       <c r="C319" t="s">
         <v>80</v>
       </c>
       <c r="D319" t="s">
-        <v>41</v>
+        <v>673</v>
       </c>
       <c r="E319" t="s">
-        <v>42</v>
+        <v>674</v>
       </c>
       <c r="F319" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="G319" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="320" spans="1:7" x14ac:dyDescent="0.2">
@@ -10329,22 +10293,22 @@
         <v>0</v>
       </c>
       <c r="B320" t="s">
-        <v>653</v>
+        <v>675</v>
       </c>
       <c r="C320" t="s">
         <v>80</v>
       </c>
       <c r="D320" t="s">
-        <v>654</v>
+        <v>676</v>
       </c>
       <c r="E320" t="s">
-        <v>655</v>
+        <v>677</v>
       </c>
       <c r="F320" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="G320" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="321" spans="1:7" x14ac:dyDescent="0.2">
@@ -10352,22 +10316,22 @@
         <v>0</v>
       </c>
       <c r="B321" t="s">
-        <v>656</v>
+        <v>678</v>
       </c>
       <c r="C321" t="s">
         <v>80</v>
       </c>
       <c r="D321" t="s">
-        <v>657</v>
+        <v>184</v>
       </c>
       <c r="E321" t="s">
-        <v>658</v>
+        <v>185</v>
       </c>
       <c r="F321" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="G321" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="322" spans="1:7" x14ac:dyDescent="0.2">
@@ -10375,22 +10339,22 @@
         <v>0</v>
       </c>
       <c r="B322" t="s">
-        <v>659</v>
+        <v>679</v>
       </c>
       <c r="C322" t="s">
         <v>80</v>
       </c>
       <c r="D322" t="s">
-        <v>155</v>
+        <v>655</v>
       </c>
       <c r="E322" t="s">
-        <v>156</v>
+        <v>656</v>
       </c>
       <c r="F322" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="G322" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="323" spans="1:7" x14ac:dyDescent="0.2">
@@ -10398,22 +10362,22 @@
         <v>0</v>
       </c>
       <c r="B323" t="s">
-        <v>660</v>
+        <v>680</v>
       </c>
       <c r="C323" t="s">
         <v>80</v>
       </c>
       <c r="D323" t="s">
-        <v>661</v>
+        <v>215</v>
       </c>
       <c r="E323" t="s">
-        <v>662</v>
+        <v>216</v>
       </c>
       <c r="F323" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="G323" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="324" spans="1:7" x14ac:dyDescent="0.2">
@@ -10421,22 +10385,22 @@
         <v>0</v>
       </c>
       <c r="B324" t="s">
-        <v>663</v>
+        <v>681</v>
       </c>
       <c r="C324" t="s">
         <v>80</v>
       </c>
       <c r="D324" t="s">
-        <v>664</v>
+        <v>81</v>
       </c>
       <c r="E324" t="s">
-        <v>665</v>
+        <v>82</v>
       </c>
       <c r="F324" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="G324" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="325" spans="1:7" x14ac:dyDescent="0.2">
@@ -10444,22 +10408,22 @@
         <v>0</v>
       </c>
       <c r="B325" t="s">
-        <v>666</v>
+        <v>682</v>
       </c>
       <c r="C325" t="s">
         <v>80</v>
       </c>
       <c r="D325" t="s">
-        <v>667</v>
+        <v>81</v>
       </c>
       <c r="E325" t="s">
-        <v>668</v>
+        <v>82</v>
       </c>
       <c r="F325" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="G325" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="326" spans="1:7" x14ac:dyDescent="0.2">
@@ -10467,22 +10431,22 @@
         <v>0</v>
       </c>
       <c r="B326" t="s">
-        <v>669</v>
+        <v>683</v>
       </c>
       <c r="C326" t="s">
         <v>80</v>
       </c>
       <c r="D326" t="s">
-        <v>667</v>
+        <v>81</v>
       </c>
       <c r="E326" t="s">
-        <v>668</v>
+        <v>82</v>
       </c>
       <c r="F326" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="G326" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="327" spans="1:7" x14ac:dyDescent="0.2">
@@ -10490,22 +10454,22 @@
         <v>0</v>
       </c>
       <c r="B327" t="s">
-        <v>670</v>
+        <v>684</v>
       </c>
       <c r="C327" t="s">
         <v>80</v>
       </c>
       <c r="D327" t="s">
-        <v>671</v>
+        <v>685</v>
       </c>
       <c r="E327" t="s">
-        <v>672</v>
+        <v>686</v>
       </c>
       <c r="F327" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="G327" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="328" spans="1:7" x14ac:dyDescent="0.2">
@@ -10513,22 +10477,22 @@
         <v>0</v>
       </c>
       <c r="B328" t="s">
-        <v>673</v>
+        <v>687</v>
       </c>
       <c r="C328" t="s">
         <v>80</v>
       </c>
       <c r="D328" t="s">
-        <v>674</v>
+        <v>688</v>
       </c>
       <c r="E328" t="s">
-        <v>675</v>
+        <v>689</v>
       </c>
       <c r="F328" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="G328" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="329" spans="1:7" x14ac:dyDescent="0.2">
@@ -10536,22 +10500,22 @@
         <v>0</v>
       </c>
       <c r="B329" t="s">
-        <v>676</v>
+        <v>690</v>
       </c>
       <c r="C329" t="s">
         <v>80</v>
       </c>
       <c r="D329" t="s">
-        <v>677</v>
+        <v>691</v>
       </c>
       <c r="E329" t="s">
-        <v>678</v>
+        <v>692</v>
       </c>
       <c r="F329" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="G329" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="330" spans="1:7" x14ac:dyDescent="0.2">
@@ -10559,22 +10523,22 @@
         <v>0</v>
       </c>
       <c r="B330" t="s">
-        <v>679</v>
+        <v>693</v>
       </c>
       <c r="C330" t="s">
         <v>80</v>
       </c>
       <c r="D330" t="s">
-        <v>680</v>
+        <v>694</v>
       </c>
       <c r="E330" t="s">
-        <v>681</v>
+        <v>695</v>
       </c>
       <c r="F330" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="G330" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="331" spans="1:7" x14ac:dyDescent="0.2">
@@ -10582,22 +10546,22 @@
         <v>0</v>
       </c>
       <c r="B331" t="s">
-        <v>682</v>
+        <v>696</v>
       </c>
       <c r="C331" t="s">
         <v>80</v>
       </c>
       <c r="D331" t="s">
-        <v>418</v>
+        <v>13</v>
       </c>
       <c r="E331" t="s">
-        <v>419</v>
+        <v>14</v>
       </c>
       <c r="F331" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="G331" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="332" spans="1:7" x14ac:dyDescent="0.2">
@@ -10605,22 +10569,22 @@
         <v>0</v>
       </c>
       <c r="B332" t="s">
-        <v>683</v>
+        <v>697</v>
       </c>
       <c r="C332" t="s">
         <v>80</v>
       </c>
       <c r="D332" t="s">
-        <v>684</v>
+        <v>698</v>
       </c>
       <c r="E332" t="s">
-        <v>685</v>
+        <v>699</v>
       </c>
       <c r="F332" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="G332" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="333" spans="1:7" x14ac:dyDescent="0.2">
@@ -10628,22 +10592,22 @@
         <v>0</v>
       </c>
       <c r="B333" t="s">
-        <v>686</v>
+        <v>700</v>
       </c>
       <c r="C333" t="s">
         <v>80</v>
       </c>
       <c r="D333" t="s">
-        <v>687</v>
+        <v>701</v>
       </c>
       <c r="E333" t="s">
-        <v>688</v>
+        <v>702</v>
       </c>
       <c r="F333" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="G333" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="334" spans="1:7" x14ac:dyDescent="0.2">
@@ -10651,22 +10615,22 @@
         <v>0</v>
       </c>
       <c r="B334" t="s">
-        <v>689</v>
+        <v>703</v>
       </c>
       <c r="C334" t="s">
         <v>80</v>
       </c>
       <c r="D334" t="s">
-        <v>64</v>
+        <v>581</v>
       </c>
       <c r="E334" t="s">
-        <v>65</v>
+        <v>582</v>
       </c>
       <c r="F334" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="G334" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="335" spans="1:7" x14ac:dyDescent="0.2">
@@ -10674,22 +10638,22 @@
         <v>0</v>
       </c>
       <c r="B335" t="s">
-        <v>690</v>
+        <v>704</v>
       </c>
       <c r="C335" t="s">
         <v>80</v>
       </c>
       <c r="D335" t="s">
-        <v>691</v>
+        <v>665</v>
       </c>
       <c r="E335" t="s">
-        <v>692</v>
+        <v>666</v>
       </c>
       <c r="F335" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="G335" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="336" spans="1:7" x14ac:dyDescent="0.2">
@@ -10697,22 +10661,22 @@
         <v>0</v>
       </c>
       <c r="B336" t="s">
-        <v>693</v>
+        <v>705</v>
       </c>
       <c r="C336" t="s">
         <v>80</v>
       </c>
       <c r="D336" t="s">
-        <v>694</v>
+        <v>706</v>
       </c>
       <c r="E336" t="s">
-        <v>695</v>
+        <v>707</v>
       </c>
       <c r="F336" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="G336" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="337" spans="1:7" x14ac:dyDescent="0.2">
@@ -10720,22 +10684,22 @@
         <v>0</v>
       </c>
       <c r="B337" t="s">
-        <v>696</v>
+        <v>708</v>
       </c>
       <c r="C337" t="s">
         <v>80</v>
       </c>
       <c r="D337" t="s">
-        <v>697</v>
+        <v>320</v>
       </c>
       <c r="E337" t="s">
-        <v>698</v>
+        <v>321</v>
       </c>
       <c r="F337" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="G337" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="338" spans="1:7" x14ac:dyDescent="0.2">
@@ -10743,22 +10707,22 @@
         <v>0</v>
       </c>
       <c r="B338" t="s">
-        <v>699</v>
+        <v>709</v>
       </c>
       <c r="C338" t="s">
         <v>80</v>
       </c>
       <c r="D338" t="s">
-        <v>700</v>
+        <v>454</v>
       </c>
       <c r="E338" t="s">
-        <v>701</v>
+        <v>455</v>
       </c>
       <c r="F338" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="G338" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="339" spans="1:7" x14ac:dyDescent="0.2">
@@ -10766,22 +10730,22 @@
         <v>0</v>
       </c>
       <c r="B339" t="s">
-        <v>702</v>
+        <v>710</v>
       </c>
       <c r="C339" t="s">
         <v>80</v>
       </c>
       <c r="D339" t="s">
-        <v>703</v>
+        <v>711</v>
       </c>
       <c r="E339" t="s">
-        <v>704</v>
+        <v>712</v>
       </c>
       <c r="F339" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="G339" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="340" spans="1:7" x14ac:dyDescent="0.2">
@@ -10789,22 +10753,22 @@
         <v>0</v>
       </c>
       <c r="B340" t="s">
-        <v>705</v>
+        <v>713</v>
       </c>
       <c r="C340" t="s">
         <v>80</v>
       </c>
       <c r="D340" t="s">
-        <v>706</v>
+        <v>714</v>
       </c>
       <c r="E340" t="s">
-        <v>707</v>
+        <v>715</v>
       </c>
       <c r="F340" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="G340" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="341" spans="1:7" x14ac:dyDescent="0.2">
@@ -10812,22 +10776,22 @@
         <v>0</v>
       </c>
       <c r="B341" t="s">
-        <v>708</v>
+        <v>716</v>
       </c>
       <c r="C341" t="s">
         <v>80</v>
       </c>
       <c r="D341" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="E341" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="F341" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="G341" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="342" spans="1:7" x14ac:dyDescent="0.2">
@@ -10835,22 +10799,22 @@
         <v>0</v>
       </c>
       <c r="B342" t="s">
-        <v>711</v>
+        <v>717</v>
       </c>
       <c r="C342" t="s">
         <v>80</v>
       </c>
       <c r="D342" t="s">
-        <v>712</v>
+        <v>292</v>
       </c>
       <c r="E342" t="s">
-        <v>713</v>
+        <v>293</v>
       </c>
       <c r="F342" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="G342" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="343" spans="1:7" x14ac:dyDescent="0.2">
@@ -10858,22 +10822,22 @@
         <v>0</v>
       </c>
       <c r="B343" t="s">
-        <v>714</v>
+        <v>718</v>
       </c>
       <c r="C343" t="s">
         <v>80</v>
       </c>
       <c r="D343" t="s">
-        <v>715</v>
+        <v>300</v>
       </c>
       <c r="E343" t="s">
-        <v>716</v>
+        <v>301</v>
       </c>
       <c r="F343" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="G343" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="344" spans="1:7" x14ac:dyDescent="0.2">
@@ -10881,22 +10845,22 @@
         <v>0</v>
       </c>
       <c r="B344" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="C344" t="s">
         <v>80</v>
       </c>
       <c r="D344" t="s">
-        <v>718</v>
+        <v>362</v>
       </c>
       <c r="E344" t="s">
-        <v>719</v>
+        <v>363</v>
       </c>
       <c r="F344" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="G344" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="345" spans="1:7" x14ac:dyDescent="0.2">
@@ -10910,16 +10874,16 @@
         <v>80</v>
       </c>
       <c r="D345" t="s">
-        <v>721</v>
+        <v>161</v>
       </c>
       <c r="E345" t="s">
-        <v>722</v>
+        <v>162</v>
       </c>
       <c r="F345" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="G345" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="346" spans="1:7" x14ac:dyDescent="0.2">
@@ -10927,22 +10891,22 @@
         <v>0</v>
       </c>
       <c r="B346" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="C346" t="s">
         <v>80</v>
       </c>
       <c r="D346" t="s">
-        <v>573</v>
+        <v>74</v>
       </c>
       <c r="E346" t="s">
-        <v>574</v>
+        <v>75</v>
       </c>
       <c r="F346" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="G346" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="347" spans="1:7" x14ac:dyDescent="0.2">
@@ -10950,22 +10914,22 @@
         <v>0</v>
       </c>
       <c r="B347" t="s">
+        <v>722</v>
+      </c>
+      <c r="C347" t="s">
+        <v>80</v>
+      </c>
+      <c r="D347" t="s">
+        <v>723</v>
+      </c>
+      <c r="E347" t="s">
         <v>724</v>
       </c>
-      <c r="C347" t="s">
-        <v>80</v>
-      </c>
-      <c r="D347" t="s">
-        <v>514</v>
-      </c>
-      <c r="E347" t="s">
-        <v>515</v>
-      </c>
       <c r="F347" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="G347" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="348" spans="1:7" x14ac:dyDescent="0.2">
@@ -10985,10 +10949,10 @@
         <v>727</v>
       </c>
       <c r="F348" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="G348" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="349" spans="1:7" x14ac:dyDescent="0.2">
@@ -11002,16 +10966,16 @@
         <v>80</v>
       </c>
       <c r="D349" t="s">
-        <v>729</v>
+        <v>726</v>
       </c>
       <c r="E349" t="s">
-        <v>730</v>
+        <v>727</v>
       </c>
       <c r="F349" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="G349" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="350" spans="1:7" x14ac:dyDescent="0.2">
@@ -11019,22 +10983,22 @@
         <v>0</v>
       </c>
       <c r="B350" t="s">
+        <v>729</v>
+      </c>
+      <c r="C350" t="s">
+        <v>80</v>
+      </c>
+      <c r="D350" t="s">
+        <v>730</v>
+      </c>
+      <c r="E350" t="s">
         <v>731</v>
       </c>
-      <c r="C350" t="s">
-        <v>80</v>
-      </c>
-      <c r="D350" t="s">
-        <v>732</v>
-      </c>
-      <c r="E350" t="s">
-        <v>733</v>
-      </c>
       <c r="F350" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="G350" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="351" spans="1:7" x14ac:dyDescent="0.2">
@@ -11042,22 +11006,22 @@
         <v>0</v>
       </c>
       <c r="B351" t="s">
+        <v>732</v>
+      </c>
+      <c r="C351" t="s">
+        <v>80</v>
+      </c>
+      <c r="D351" t="s">
+        <v>733</v>
+      </c>
+      <c r="E351" t="s">
         <v>734</v>
       </c>
-      <c r="C351" t="s">
-        <v>80</v>
-      </c>
-      <c r="D351" t="s">
-        <v>366</v>
-      </c>
-      <c r="E351" t="s">
-        <v>367</v>
-      </c>
       <c r="F351" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="G351" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="352" spans="1:7" x14ac:dyDescent="0.2">
@@ -11071,16 +11035,16 @@
         <v>80</v>
       </c>
       <c r="D352" t="s">
-        <v>736</v>
+        <v>87</v>
       </c>
       <c r="E352" t="s">
-        <v>737</v>
+        <v>88</v>
       </c>
       <c r="F352" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="G352" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="353" spans="1:7" x14ac:dyDescent="0.2">
@@ -11088,217 +11052,217 @@
         <v>0</v>
       </c>
       <c r="B353" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="C353" t="s">
         <v>80</v>
       </c>
       <c r="D353" t="s">
-        <v>739</v>
+        <v>87</v>
       </c>
       <c r="E353" t="s">
-        <v>740</v>
+        <v>88</v>
       </c>
       <c r="F353" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="G353" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="354" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A354" t="s">
-        <v>0</v>
+        <v>737</v>
       </c>
       <c r="B354" t="s">
-        <v>741</v>
+        <v>738</v>
       </c>
       <c r="C354" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D354" t="s">
-        <v>37</v>
+        <v>300</v>
       </c>
       <c r="E354" t="s">
-        <v>38</v>
+        <v>301</v>
       </c>
       <c r="F354" s="1">
-        <v>46265</v>
+        <v>46148</v>
       </c>
       <c r="G354" s="1">
-        <v>46265</v>
+        <v>46149</v>
       </c>
     </row>
     <row r="355" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A355" t="s">
-        <v>0</v>
+        <v>737</v>
       </c>
       <c r="B355" t="s">
-        <v>742</v>
+        <v>739</v>
       </c>
       <c r="C355" t="s">
         <v>80</v>
       </c>
       <c r="D355" t="s">
-        <v>37</v>
+        <v>740</v>
       </c>
       <c r="E355" t="s">
-        <v>38</v>
+        <v>741</v>
       </c>
       <c r="F355" s="1">
-        <v>46265</v>
+        <v>46260</v>
       </c>
       <c r="G355" s="1">
-        <v>46265</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="356" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A356" t="s">
+        <v>742</v>
+      </c>
+      <c r="B356" t="s">
         <v>743</v>
       </c>
-      <c r="B356" t="s">
-        <v>744</v>
-      </c>
       <c r="C356" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D356" t="s">
-        <v>303</v>
+        <v>41</v>
       </c>
       <c r="E356" t="s">
-        <v>304</v>
+        <v>42</v>
       </c>
       <c r="F356" s="1">
-        <v>46148</v>
+        <v>46133</v>
       </c>
       <c r="G356" s="1">
-        <v>46149</v>
+        <v>46134</v>
       </c>
     </row>
     <row r="357" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A357" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="B357" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="C357" t="s">
-        <v>80</v>
+        <v>6</v>
       </c>
       <c r="D357" t="s">
-        <v>746</v>
+        <v>41</v>
       </c>
       <c r="E357" t="s">
-        <v>747</v>
+        <v>42</v>
       </c>
       <c r="F357" s="1">
-        <v>46260</v>
+        <v>46134</v>
       </c>
       <c r="G357" s="1">
-        <v>46262</v>
+        <v>46134</v>
       </c>
     </row>
     <row r="358" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A358" t="s">
-        <v>748</v>
+        <v>742</v>
       </c>
       <c r="B358" t="s">
-        <v>749</v>
+        <v>745</v>
       </c>
       <c r="C358" t="s">
         <v>6</v>
       </c>
       <c r="D358" t="s">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="E358" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="F358" s="1">
-        <v>46133</v>
+        <v>46156</v>
       </c>
       <c r="G358" s="1">
-        <v>46134</v>
+        <v>46156</v>
       </c>
     </row>
     <row r="359" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A359" t="s">
-        <v>748</v>
+        <v>742</v>
       </c>
       <c r="B359" t="s">
-        <v>750</v>
+        <v>746</v>
       </c>
       <c r="C359" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D359" t="s">
-        <v>41</v>
+        <v>509</v>
       </c>
       <c r="E359" t="s">
-        <v>42</v>
+        <v>510</v>
       </c>
       <c r="F359" s="1">
-        <v>46134</v>
+        <v>46195</v>
       </c>
       <c r="G359" s="1">
-        <v>46134</v>
+        <v>46195</v>
       </c>
     </row>
     <row r="360" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A360" t="s">
+        <v>742</v>
+      </c>
+      <c r="B360" t="s">
+        <v>747</v>
+      </c>
+      <c r="C360" t="s">
+        <v>2</v>
+      </c>
+      <c r="D360" t="s">
         <v>748</v>
       </c>
-      <c r="B360" t="s">
-        <v>751</v>
-      </c>
-      <c r="C360" t="s">
-        <v>6</v>
-      </c>
-      <c r="D360" t="s">
-        <v>19</v>
-      </c>
       <c r="E360" t="s">
-        <v>20</v>
+        <v>749</v>
       </c>
       <c r="F360" s="1">
-        <v>46156</v>
+        <v>46206</v>
       </c>
       <c r="G360" s="1">
-        <v>46156</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="361" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A361" t="s">
-        <v>748</v>
+        <v>742</v>
       </c>
       <c r="B361" t="s">
+        <v>750</v>
+      </c>
+      <c r="C361" t="s">
+        <v>96</v>
+      </c>
+      <c r="D361" t="s">
+        <v>751</v>
+      </c>
+      <c r="E361" t="s">
         <v>752</v>
       </c>
-      <c r="C361" t="s">
-        <v>2</v>
-      </c>
-      <c r="D361" t="s">
-        <v>547</v>
-      </c>
-      <c r="E361" t="s">
-        <v>548</v>
-      </c>
       <c r="F361" s="1">
-        <v>46195</v>
+        <v>46209</v>
       </c>
       <c r="G361" s="1">
-        <v>46195</v>
+        <v>46218</v>
       </c>
     </row>
     <row r="362" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A362" t="s">
-        <v>748</v>
+        <v>742</v>
       </c>
       <c r="B362" t="s">
         <v>753</v>
       </c>
       <c r="C362" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D362" t="s">
         <v>754</v>
@@ -11307,15 +11271,15 @@
         <v>755</v>
       </c>
       <c r="F362" s="1">
-        <v>46206</v>
+        <v>46213</v>
       </c>
       <c r="G362" s="1">
-        <v>46252</v>
+        <v>46213</v>
       </c>
     </row>
     <row r="363" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A363" t="s">
-        <v>748</v>
+        <v>742</v>
       </c>
       <c r="B363" t="s">
         <v>756</v>
@@ -11324,266 +11288,266 @@
         <v>96</v>
       </c>
       <c r="D363" t="s">
-        <v>757</v>
+        <v>567</v>
       </c>
       <c r="E363" t="s">
-        <v>758</v>
+        <v>568</v>
       </c>
       <c r="F363" s="1">
-        <v>46209</v>
+        <v>46213</v>
       </c>
       <c r="G363" s="1">
-        <v>46218</v>
+        <v>46216</v>
       </c>
     </row>
     <row r="364" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A364" t="s">
-        <v>748</v>
+        <v>742</v>
       </c>
       <c r="B364" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="C364" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D364" t="s">
-        <v>760</v>
+        <v>127</v>
       </c>
       <c r="E364" t="s">
-        <v>761</v>
+        <v>128</v>
       </c>
       <c r="F364" s="1">
-        <v>46213</v>
+        <v>46220</v>
       </c>
       <c r="G364" s="1">
-        <v>46213</v>
+        <v>46231</v>
       </c>
     </row>
     <row r="365" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A365" t="s">
-        <v>748</v>
+        <v>742</v>
       </c>
       <c r="B365" t="s">
-        <v>762</v>
+        <v>758</v>
       </c>
       <c r="C365" t="s">
-        <v>96</v>
+        <v>2</v>
       </c>
       <c r="D365" t="s">
-        <v>649</v>
+        <v>509</v>
       </c>
       <c r="E365" t="s">
-        <v>650</v>
+        <v>510</v>
       </c>
       <c r="F365" s="1">
-        <v>46213</v>
+        <v>46223</v>
       </c>
       <c r="G365" s="1">
-        <v>46216</v>
+        <v>46223</v>
       </c>
     </row>
     <row r="366" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A366" t="s">
-        <v>748</v>
+        <v>742</v>
       </c>
       <c r="B366" t="s">
-        <v>763</v>
+        <v>759</v>
       </c>
       <c r="C366" t="s">
-        <v>2</v>
+        <v>96</v>
       </c>
       <c r="D366" t="s">
-        <v>127</v>
+        <v>567</v>
       </c>
       <c r="E366" t="s">
-        <v>128</v>
+        <v>568</v>
       </c>
       <c r="F366" s="1">
-        <v>46220</v>
+        <v>46224</v>
       </c>
       <c r="G366" s="1">
-        <v>46231</v>
+        <v>46224</v>
       </c>
     </row>
     <row r="367" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A367" t="s">
-        <v>748</v>
+        <v>742</v>
       </c>
       <c r="B367" t="s">
-        <v>764</v>
+        <v>760</v>
       </c>
       <c r="C367" t="s">
         <v>2</v>
       </c>
       <c r="D367" t="s">
-        <v>547</v>
+        <v>127</v>
       </c>
       <c r="E367" t="s">
-        <v>548</v>
+        <v>128</v>
       </c>
       <c r="F367" s="1">
-        <v>46223</v>
+        <v>46232</v>
       </c>
       <c r="G367" s="1">
-        <v>46223</v>
+        <v>46233</v>
       </c>
     </row>
     <row r="368" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A368" t="s">
-        <v>748</v>
+        <v>742</v>
       </c>
       <c r="B368" t="s">
-        <v>765</v>
+        <v>761</v>
       </c>
       <c r="C368" t="s">
-        <v>96</v>
+        <v>2</v>
       </c>
       <c r="D368" t="s">
-        <v>649</v>
+        <v>127</v>
       </c>
       <c r="E368" t="s">
-        <v>650</v>
+        <v>128</v>
       </c>
       <c r="F368" s="1">
-        <v>46224</v>
+        <v>46232</v>
       </c>
       <c r="G368" s="1">
-        <v>46224</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="369" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A369" t="s">
-        <v>748</v>
+        <v>742</v>
       </c>
       <c r="B369" t="s">
-        <v>766</v>
+        <v>762</v>
       </c>
       <c r="C369" t="s">
         <v>2</v>
       </c>
       <c r="D369" t="s">
-        <v>127</v>
+        <v>567</v>
       </c>
       <c r="E369" t="s">
-        <v>128</v>
+        <v>568</v>
       </c>
       <c r="F369" s="1">
-        <v>46232</v>
+        <v>46238</v>
       </c>
       <c r="G369" s="1">
-        <v>46233</v>
+        <v>46239</v>
       </c>
     </row>
     <row r="370" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A370" t="s">
-        <v>748</v>
+        <v>742</v>
       </c>
       <c r="B370" t="s">
-        <v>767</v>
+        <v>763</v>
       </c>
       <c r="C370" t="s">
         <v>2</v>
       </c>
       <c r="D370" t="s">
-        <v>127</v>
+        <v>41</v>
       </c>
       <c r="E370" t="s">
-        <v>128</v>
+        <v>42</v>
       </c>
       <c r="F370" s="1">
-        <v>46232</v>
+        <v>46247</v>
       </c>
       <c r="G370" s="1">
-        <v>46259</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="371" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A371" t="s">
-        <v>748</v>
+        <v>742</v>
       </c>
       <c r="B371" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
       <c r="C371" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D371" t="s">
-        <v>649</v>
+        <v>765</v>
       </c>
       <c r="E371" t="s">
-        <v>650</v>
+        <v>766</v>
       </c>
       <c r="F371" s="1">
-        <v>46238</v>
+        <v>46253</v>
       </c>
       <c r="G371" s="1">
-        <v>46239</v>
+        <v>46253</v>
       </c>
     </row>
     <row r="372" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A372" t="s">
-        <v>748</v>
+        <v>742</v>
       </c>
       <c r="B372" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="C372" t="s">
         <v>2</v>
       </c>
       <c r="D372" t="s">
-        <v>41</v>
+        <v>567</v>
       </c>
       <c r="E372" t="s">
-        <v>42</v>
+        <v>568</v>
       </c>
       <c r="F372" s="1">
-        <v>46247</v>
+        <v>46253</v>
       </c>
       <c r="G372" s="1">
-        <v>46252</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="373" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A373" t="s">
-        <v>748</v>
+        <v>742</v>
       </c>
       <c r="B373" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="C373" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D373" t="s">
-        <v>771</v>
+        <v>509</v>
       </c>
       <c r="E373" t="s">
-        <v>772</v>
+        <v>510</v>
       </c>
       <c r="F373" s="1">
-        <v>46253</v>
+        <v>46258</v>
       </c>
       <c r="G373" s="1">
-        <v>46253</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="374" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A374" t="s">
-        <v>748</v>
+        <v>742</v>
       </c>
       <c r="B374" t="s">
-        <v>773</v>
+        <v>769</v>
       </c>
       <c r="C374" t="s">
         <v>2</v>
       </c>
       <c r="D374" t="s">
-        <v>649</v>
+        <v>567</v>
       </c>
       <c r="E374" t="s">
-        <v>650</v>
+        <v>568</v>
       </c>
       <c r="F374" s="1">
-        <v>46253</v>
+        <v>46258</v>
       </c>
       <c r="G374" s="1">
         <v>46259</v>
@@ -11591,22 +11555,22 @@
     </row>
     <row r="375" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A375" t="s">
-        <v>748</v>
+        <v>742</v>
       </c>
       <c r="B375" t="s">
-        <v>774</v>
+        <v>770</v>
       </c>
       <c r="C375" t="s">
         <v>2</v>
       </c>
       <c r="D375" t="s">
-        <v>547</v>
+        <v>127</v>
       </c>
       <c r="E375" t="s">
-        <v>548</v>
+        <v>128</v>
       </c>
       <c r="F375" s="1">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="G375" s="1">
         <v>46259</v>
@@ -11614,312 +11578,312 @@
     </row>
     <row r="376" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A376" t="s">
-        <v>748</v>
+        <v>742</v>
       </c>
       <c r="B376" t="s">
-        <v>775</v>
+        <v>771</v>
       </c>
       <c r="C376" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D376" t="s">
-        <v>649</v>
+        <v>567</v>
       </c>
       <c r="E376" t="s">
-        <v>650</v>
+        <v>568</v>
       </c>
       <c r="F376" s="1">
-        <v>46258</v>
+        <v>46262</v>
       </c>
       <c r="G376" s="1">
-        <v>46259</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="377" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A377" t="s">
-        <v>748</v>
+        <v>742</v>
       </c>
       <c r="B377" t="s">
-        <v>776</v>
+        <v>772</v>
       </c>
       <c r="C377" t="s">
         <v>2</v>
       </c>
       <c r="D377" t="s">
-        <v>127</v>
+        <v>509</v>
       </c>
       <c r="E377" t="s">
-        <v>128</v>
+        <v>510</v>
       </c>
       <c r="F377" s="1">
-        <v>46259</v>
+        <v>46265</v>
       </c>
       <c r="G377" s="1">
-        <v>46259</v>
+        <v>46265</v>
       </c>
     </row>
     <row r="378" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A378" t="s">
-        <v>748</v>
+        <v>742</v>
       </c>
       <c r="B378" t="s">
-        <v>777</v>
+        <v>773</v>
       </c>
       <c r="C378" t="s">
         <v>80</v>
       </c>
       <c r="D378" t="s">
-        <v>649</v>
+        <v>774</v>
       </c>
       <c r="E378" t="s">
-        <v>650</v>
+        <v>775</v>
       </c>
       <c r="F378" s="1">
-        <v>46262</v>
+        <v>46266</v>
       </c>
       <c r="G378" s="1">
-        <v>46262</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="379" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A379" t="s">
-        <v>748</v>
+        <v>742</v>
       </c>
       <c r="B379" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="C379" t="s">
         <v>80</v>
       </c>
       <c r="D379" t="s">
-        <v>547</v>
+        <v>638</v>
       </c>
       <c r="E379" t="s">
-        <v>548</v>
+        <v>639</v>
       </c>
       <c r="F379" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="G379" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="380" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A380" t="s">
-        <v>748</v>
+        <v>777</v>
       </c>
       <c r="B380" t="s">
+        <v>778</v>
+      </c>
+      <c r="C380" t="s">
+        <v>96</v>
+      </c>
+      <c r="D380" t="s">
         <v>779</v>
       </c>
-      <c r="C380" t="s">
-        <v>80</v>
-      </c>
-      <c r="D380" t="s">
-        <v>547</v>
-      </c>
       <c r="E380" t="s">
-        <v>548</v>
+        <v>780</v>
       </c>
       <c r="F380" s="1">
-        <v>46265</v>
+        <v>46063</v>
       </c>
       <c r="G380" s="1">
-        <v>46265</v>
+        <v>46064</v>
       </c>
     </row>
     <row r="381" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A381" t="s">
-        <v>748</v>
+        <v>777</v>
       </c>
       <c r="B381" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="C381" t="s">
-        <v>80</v>
+        <v>6</v>
       </c>
       <c r="D381" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="E381" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="F381" s="1">
-        <v>46265</v>
+        <v>46113</v>
       </c>
       <c r="G381" s="1">
-        <v>46265</v>
+        <v>46125</v>
       </c>
     </row>
     <row r="382" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A382" t="s">
-        <v>748</v>
+        <v>777</v>
       </c>
       <c r="B382" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="C382" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D382" t="s">
-        <v>580</v>
+        <v>57</v>
       </c>
       <c r="E382" t="s">
-        <v>581</v>
+        <v>58</v>
       </c>
       <c r="F382" s="1">
-        <v>46265</v>
+        <v>46125</v>
       </c>
       <c r="G382" s="1">
-        <v>46265</v>
+        <v>46125</v>
       </c>
     </row>
     <row r="383" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A383" t="s">
-        <v>748</v>
+        <v>777</v>
       </c>
       <c r="B383" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="C383" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D383" t="s">
-        <v>84</v>
+        <v>57</v>
       </c>
       <c r="E383" t="s">
-        <v>85</v>
+        <v>58</v>
       </c>
       <c r="F383" s="1">
-        <v>46265</v>
+        <v>46126</v>
       </c>
       <c r="G383" s="1">
-        <v>46265</v>
+        <v>46126</v>
       </c>
     </row>
     <row r="384" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A384" t="s">
-        <v>748</v>
+        <v>777</v>
       </c>
       <c r="B384" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="C384" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D384" t="s">
-        <v>598</v>
+        <v>57</v>
       </c>
       <c r="E384" t="s">
-        <v>599</v>
+        <v>58</v>
       </c>
       <c r="F384" s="1">
-        <v>46265</v>
+        <v>46126</v>
       </c>
       <c r="G384" s="1">
-        <v>46265</v>
+        <v>46126</v>
       </c>
     </row>
     <row r="385" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A385" t="s">
-        <v>748</v>
+        <v>777</v>
       </c>
       <c r="B385" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="C385" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D385" t="s">
-        <v>598</v>
+        <v>57</v>
       </c>
       <c r="E385" t="s">
-        <v>599</v>
+        <v>58</v>
       </c>
       <c r="F385" s="1">
-        <v>46265</v>
+        <v>46128</v>
       </c>
       <c r="G385" s="1">
-        <v>46265</v>
+        <v>46128</v>
       </c>
     </row>
     <row r="386" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A386" t="s">
-        <v>748</v>
+        <v>777</v>
       </c>
       <c r="B386" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="C386" t="s">
-        <v>80</v>
+        <v>6</v>
       </c>
       <c r="D386" t="s">
-        <v>310</v>
+        <v>57</v>
       </c>
       <c r="E386" t="s">
-        <v>311</v>
+        <v>58</v>
       </c>
       <c r="F386" s="1">
-        <v>46265</v>
+        <v>46132</v>
       </c>
       <c r="G386" s="1">
-        <v>46265</v>
+        <v>46132</v>
       </c>
     </row>
     <row r="387" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A387" t="s">
-        <v>748</v>
+        <v>777</v>
       </c>
       <c r="B387" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="C387" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D387" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="E387" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="F387" s="1">
-        <v>46265</v>
+        <v>46161</v>
       </c>
       <c r="G387" s="1">
-        <v>46265</v>
+        <v>46161</v>
       </c>
     </row>
     <row r="388" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A388" t="s">
-        <v>787</v>
+        <v>777</v>
       </c>
       <c r="B388" t="s">
         <v>788</v>
       </c>
       <c r="C388" t="s">
-        <v>96</v>
+        <v>2</v>
       </c>
       <c r="D388" t="s">
-        <v>789</v>
+        <v>57</v>
       </c>
       <c r="E388" t="s">
-        <v>790</v>
+        <v>58</v>
       </c>
       <c r="F388" s="1">
-        <v>46063</v>
+        <v>46174</v>
       </c>
       <c r="G388" s="1">
-        <v>46064</v>
+        <v>46174</v>
       </c>
     </row>
     <row r="389" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A389" t="s">
-        <v>787</v>
+        <v>777</v>
       </c>
       <c r="B389" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="C389" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D389" t="s">
         <v>57</v>
@@ -11928,21 +11892,21 @@
         <v>58</v>
       </c>
       <c r="F389" s="1">
-        <v>46113</v>
+        <v>46174</v>
       </c>
       <c r="G389" s="1">
-        <v>46125</v>
+        <v>46174</v>
       </c>
     </row>
     <row r="390" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A390" t="s">
-        <v>787</v>
+        <v>777</v>
       </c>
       <c r="B390" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="C390" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D390" t="s">
         <v>57</v>
@@ -11951,21 +11915,21 @@
         <v>58</v>
       </c>
       <c r="F390" s="1">
-        <v>46125</v>
+        <v>46195</v>
       </c>
       <c r="G390" s="1">
-        <v>46125</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="391" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A391" t="s">
-        <v>787</v>
+        <v>777</v>
       </c>
       <c r="B391" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="C391" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D391" t="s">
         <v>57</v>
@@ -11974,18 +11938,18 @@
         <v>58</v>
       </c>
       <c r="F391" s="1">
-        <v>46126</v>
+        <v>46210</v>
       </c>
       <c r="G391" s="1">
-        <v>46126</v>
+        <v>46210</v>
       </c>
     </row>
     <row r="392" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A392" t="s">
-        <v>787</v>
+        <v>777</v>
       </c>
       <c r="B392" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="C392" t="s">
         <v>2</v>
@@ -11997,21 +11961,21 @@
         <v>58</v>
       </c>
       <c r="F392" s="1">
-        <v>46126</v>
+        <v>46213</v>
       </c>
       <c r="G392" s="1">
-        <v>46126</v>
+        <v>46213</v>
       </c>
     </row>
     <row r="393" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A393" t="s">
-        <v>787</v>
+        <v>777</v>
       </c>
       <c r="B393" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="C393" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D393" t="s">
         <v>57</v>
@@ -12020,44 +11984,44 @@
         <v>58</v>
       </c>
       <c r="F393" s="1">
-        <v>46128</v>
+        <v>46218</v>
       </c>
       <c r="G393" s="1">
-        <v>46128</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="394" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A394" t="s">
-        <v>787</v>
+        <v>777</v>
       </c>
       <c r="B394" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="C394" t="s">
         <v>6</v>
       </c>
       <c r="D394" t="s">
-        <v>57</v>
+        <v>77</v>
       </c>
       <c r="E394" t="s">
-        <v>58</v>
+        <v>78</v>
       </c>
       <c r="F394" s="1">
-        <v>46132</v>
+        <v>46226</v>
       </c>
       <c r="G394" s="1">
-        <v>46132</v>
+        <v>46226</v>
       </c>
     </row>
     <row r="395" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A395" t="s">
-        <v>787</v>
+        <v>777</v>
       </c>
       <c r="B395" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="C395" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D395" t="s">
         <v>57</v>
@@ -12066,21 +12030,21 @@
         <v>58</v>
       </c>
       <c r="F395" s="1">
-        <v>46161</v>
+        <v>46227</v>
       </c>
       <c r="G395" s="1">
-        <v>46161</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="396" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A396" t="s">
-        <v>787</v>
+        <v>777</v>
       </c>
       <c r="B396" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="C396" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D396" t="s">
         <v>57</v>
@@ -12089,21 +12053,21 @@
         <v>58</v>
       </c>
       <c r="F396" s="1">
-        <v>46174</v>
+        <v>46227</v>
       </c>
       <c r="G396" s="1">
-        <v>46174</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="397" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A397" t="s">
-        <v>787</v>
+        <v>777</v>
       </c>
       <c r="B397" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="C397" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D397" t="s">
         <v>57</v>
@@ -12112,30 +12076,30 @@
         <v>58</v>
       </c>
       <c r="F397" s="1">
-        <v>46174</v>
+        <v>46227</v>
       </c>
       <c r="G397" s="1">
-        <v>46174</v>
+        <v>46228</v>
       </c>
     </row>
     <row r="398" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A398" t="s">
-        <v>787</v>
+        <v>777</v>
       </c>
       <c r="B398" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="C398" t="s">
         <v>80</v>
       </c>
       <c r="D398" t="s">
-        <v>57</v>
+        <v>77</v>
       </c>
       <c r="E398" t="s">
-        <v>58</v>
+        <v>78</v>
       </c>
       <c r="F398" s="1">
-        <v>46195</v>
+        <v>46230</v>
       </c>
       <c r="G398" s="1">
         <v>46252</v>
@@ -12143,10 +12107,10 @@
     </row>
     <row r="399" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A399" t="s">
-        <v>787</v>
+        <v>777</v>
       </c>
       <c r="B399" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="C399" t="s">
         <v>6</v>
@@ -12158,21 +12122,21 @@
         <v>58</v>
       </c>
       <c r="F399" s="1">
-        <v>46210</v>
+        <v>46231</v>
       </c>
       <c r="G399" s="1">
-        <v>46210</v>
+        <v>46231</v>
       </c>
     </row>
     <row r="400" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A400" t="s">
-        <v>787</v>
+        <v>777</v>
       </c>
       <c r="B400" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="C400" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D400" t="s">
         <v>57</v>
@@ -12181,21 +12145,21 @@
         <v>58</v>
       </c>
       <c r="F400" s="1">
-        <v>46213</v>
+        <v>46254</v>
       </c>
       <c r="G400" s="1">
-        <v>46213</v>
+        <v>46254</v>
       </c>
     </row>
     <row r="401" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A401" t="s">
-        <v>787</v>
+        <v>777</v>
       </c>
       <c r="B401" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="C401" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D401" t="s">
         <v>57</v>
@@ -12204,41 +12168,41 @@
         <v>58</v>
       </c>
       <c r="F401" s="1">
-        <v>46218</v>
+        <v>46255</v>
       </c>
       <c r="G401" s="1">
-        <v>46252</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="402" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A402" t="s">
-        <v>787</v>
+        <v>777</v>
       </c>
       <c r="B402" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="C402" t="s">
         <v>6</v>
       </c>
       <c r="D402" t="s">
-        <v>77</v>
+        <v>57</v>
       </c>
       <c r="E402" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="F402" s="1">
-        <v>46226</v>
+        <v>46260</v>
       </c>
       <c r="G402" s="1">
-        <v>46226</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="403" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A403" t="s">
-        <v>787</v>
+        <v>777</v>
       </c>
       <c r="B403" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="C403" t="s">
         <v>80</v>
@@ -12250,469 +12214,239 @@
         <v>58</v>
       </c>
       <c r="F403" s="1">
-        <v>46227</v>
+        <v>46266</v>
       </c>
       <c r="G403" s="1">
-        <v>46252</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="404" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A404" t="s">
-        <v>787</v>
+        <v>804</v>
       </c>
       <c r="B404" t="s">
+        <v>805</v>
+      </c>
+      <c r="C404" t="s">
+        <v>2</v>
+      </c>
+      <c r="D404" t="s">
         <v>806</v>
       </c>
-      <c r="C404" t="s">
-        <v>80</v>
-      </c>
-      <c r="D404" t="s">
-        <v>57</v>
-      </c>
       <c r="E404" t="s">
-        <v>58</v>
+        <v>807</v>
       </c>
       <c r="F404" s="1">
-        <v>46227</v>
+        <v>46083</v>
       </c>
       <c r="G404" s="1">
-        <v>46252</v>
+        <v>46084</v>
       </c>
     </row>
     <row r="405" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A405" t="s">
-        <v>787</v>
+        <v>804</v>
       </c>
       <c r="B405" t="s">
+        <v>808</v>
+      </c>
+      <c r="C405" t="s">
+        <v>2</v>
+      </c>
+      <c r="D405" t="s">
+        <v>806</v>
+      </c>
+      <c r="E405" t="s">
         <v>807</v>
       </c>
-      <c r="C405" t="s">
-        <v>6</v>
-      </c>
-      <c r="D405" t="s">
-        <v>57</v>
-      </c>
-      <c r="E405" t="s">
-        <v>58</v>
-      </c>
       <c r="F405" s="1">
-        <v>46227</v>
+        <v>46132</v>
       </c>
       <c r="G405" s="1">
-        <v>46228</v>
+        <v>46133</v>
       </c>
     </row>
     <row r="406" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A406" t="s">
-        <v>787</v>
+        <v>804</v>
       </c>
       <c r="B406" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="C406" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D406" t="s">
-        <v>77</v>
+        <v>483</v>
       </c>
       <c r="E406" t="s">
-        <v>78</v>
+        <v>484</v>
       </c>
       <c r="F406" s="1">
-        <v>46230</v>
+        <v>46157</v>
       </c>
       <c r="G406" s="1">
-        <v>46252</v>
+        <v>46157</v>
       </c>
     </row>
     <row r="407" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A407" t="s">
-        <v>787</v>
+        <v>804</v>
       </c>
       <c r="B407" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="C407" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D407" t="s">
-        <v>57</v>
+        <v>811</v>
       </c>
       <c r="E407" t="s">
-        <v>58</v>
+        <v>812</v>
       </c>
       <c r="F407" s="1">
-        <v>46231</v>
+        <v>46168</v>
       </c>
       <c r="G407" s="1">
-        <v>46231</v>
+        <v>46170</v>
       </c>
     </row>
     <row r="408" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A408" t="s">
-        <v>787</v>
+        <v>804</v>
       </c>
       <c r="B408" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
       <c r="C408" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D408" t="s">
-        <v>57</v>
+        <v>483</v>
       </c>
       <c r="E408" t="s">
-        <v>58</v>
+        <v>484</v>
       </c>
       <c r="F408" s="1">
-        <v>46254</v>
+        <v>46244</v>
       </c>
       <c r="G408" s="1">
-        <v>46254</v>
+        <v>46244</v>
       </c>
     </row>
     <row r="409" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A409" t="s">
-        <v>787</v>
+        <v>804</v>
       </c>
       <c r="B409" t="s">
-        <v>811</v>
+        <v>814</v>
       </c>
       <c r="C409" t="s">
         <v>2</v>
       </c>
       <c r="D409" t="s">
-        <v>57</v>
+        <v>483</v>
       </c>
       <c r="E409" t="s">
-        <v>58</v>
+        <v>484</v>
       </c>
       <c r="F409" s="1">
-        <v>46255</v>
+        <v>46247</v>
       </c>
       <c r="G409" s="1">
-        <v>46255</v>
+        <v>46247</v>
       </c>
     </row>
     <row r="410" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A410" t="s">
-        <v>787</v>
+        <v>804</v>
       </c>
       <c r="B410" t="s">
-        <v>812</v>
+        <v>815</v>
       </c>
       <c r="C410" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D410" t="s">
-        <v>57</v>
+        <v>806</v>
       </c>
       <c r="E410" t="s">
-        <v>58</v>
+        <v>807</v>
       </c>
       <c r="F410" s="1">
-        <v>46260</v>
+        <v>46247</v>
       </c>
       <c r="G410" s="1">
-        <v>46260</v>
+        <v>46247</v>
       </c>
     </row>
     <row r="411" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A411" t="s">
-        <v>787</v>
+        <v>804</v>
       </c>
       <c r="B411" t="s">
-        <v>813</v>
+        <v>816</v>
       </c>
       <c r="C411" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D411" t="s">
-        <v>57</v>
+        <v>483</v>
       </c>
       <c r="E411" t="s">
-        <v>58</v>
+        <v>484</v>
       </c>
       <c r="F411" s="1">
-        <v>46265</v>
+        <v>46255</v>
       </c>
       <c r="G411" s="1">
-        <v>46265</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="412" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A412" t="s">
-        <v>787</v>
+        <v>804</v>
       </c>
       <c r="B412" t="s">
-        <v>814</v>
+        <v>817</v>
       </c>
       <c r="C412" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D412" t="s">
-        <v>57</v>
+        <v>483</v>
       </c>
       <c r="E412" t="s">
-        <v>58</v>
+        <v>484</v>
       </c>
       <c r="F412" s="1">
-        <v>46265</v>
+        <v>46258</v>
       </c>
       <c r="G412" s="1">
-        <v>46265</v>
+        <v>46258</v>
       </c>
     </row>
     <row r="413" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A413" t="s">
-        <v>815</v>
+        <v>804</v>
       </c>
       <c r="B413" t="s">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="C413" t="s">
         <v>2</v>
       </c>
       <c r="D413" t="s">
-        <v>817</v>
+        <v>483</v>
       </c>
       <c r="E413" t="s">
-        <v>818</v>
+        <v>484</v>
       </c>
       <c r="F413" s="1">
-        <v>46083</v>
+        <v>46262</v>
       </c>
       <c r="G413" s="1">
-        <v>46084</v>
-      </c>
-    </row>
-    <row r="414" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A414" t="s">
-        <v>815</v>
-      </c>
-      <c r="B414" t="s">
-        <v>819</v>
-      </c>
-      <c r="C414" t="s">
-        <v>2</v>
-      </c>
-      <c r="D414" t="s">
-        <v>817</v>
-      </c>
-      <c r="E414" t="s">
-        <v>818</v>
-      </c>
-      <c r="F414" s="1">
-        <v>46132</v>
-      </c>
-      <c r="G414" s="1">
-        <v>46133</v>
-      </c>
-    </row>
-    <row r="415" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A415" t="s">
-        <v>815</v>
-      </c>
-      <c r="B415" t="s">
-        <v>820</v>
-      </c>
-      <c r="C415" t="s">
-        <v>2</v>
-      </c>
-      <c r="D415" t="s">
-        <v>504</v>
-      </c>
-      <c r="E415" t="s">
-        <v>505</v>
-      </c>
-      <c r="F415" s="1">
-        <v>46157</v>
-      </c>
-      <c r="G415" s="1">
-        <v>46157</v>
-      </c>
-    </row>
-    <row r="416" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A416" t="s">
-        <v>815</v>
-      </c>
-      <c r="B416" t="s">
-        <v>821</v>
-      </c>
-      <c r="C416" t="s">
-        <v>2</v>
-      </c>
-      <c r="D416" t="s">
-        <v>822</v>
-      </c>
-      <c r="E416" t="s">
-        <v>823</v>
-      </c>
-      <c r="F416" s="1">
-        <v>46168</v>
-      </c>
-      <c r="G416" s="1">
-        <v>46170</v>
-      </c>
-    </row>
-    <row r="417" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A417" t="s">
-        <v>815</v>
-      </c>
-      <c r="B417" t="s">
-        <v>824</v>
-      </c>
-      <c r="C417" t="s">
-        <v>2</v>
-      </c>
-      <c r="D417" t="s">
-        <v>504</v>
-      </c>
-      <c r="E417" t="s">
-        <v>505</v>
-      </c>
-      <c r="F417" s="1">
-        <v>46244</v>
-      </c>
-      <c r="G417" s="1">
-        <v>46244</v>
-      </c>
-    </row>
-    <row r="418" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A418" t="s">
-        <v>815</v>
-      </c>
-      <c r="B418" t="s">
-        <v>825</v>
-      </c>
-      <c r="C418" t="s">
-        <v>2</v>
-      </c>
-      <c r="D418" t="s">
-        <v>504</v>
-      </c>
-      <c r="E418" t="s">
-        <v>505</v>
-      </c>
-      <c r="F418" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G418" s="1">
-        <v>46247</v>
-      </c>
-    </row>
-    <row r="419" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A419" t="s">
-        <v>815</v>
-      </c>
-      <c r="B419" t="s">
-        <v>826</v>
-      </c>
-      <c r="C419" t="s">
-        <v>2</v>
-      </c>
-      <c r="D419" t="s">
-        <v>817</v>
-      </c>
-      <c r="E419" t="s">
-        <v>818</v>
-      </c>
-      <c r="F419" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G419" s="1">
-        <v>46247</v>
-      </c>
-    </row>
-    <row r="420" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A420" t="s">
-        <v>815</v>
-      </c>
-      <c r="B420" t="s">
-        <v>827</v>
-      </c>
-      <c r="C420" t="s">
-        <v>2</v>
-      </c>
-      <c r="D420" t="s">
-        <v>504</v>
-      </c>
-      <c r="E420" t="s">
-        <v>505</v>
-      </c>
-      <c r="F420" s="1">
-        <v>46255</v>
-      </c>
-      <c r="G420" s="1">
-        <v>46255</v>
-      </c>
-    </row>
-    <row r="421" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A421" t="s">
-        <v>815</v>
-      </c>
-      <c r="B421" t="s">
-        <v>828</v>
-      </c>
-      <c r="C421" t="s">
-        <v>2</v>
-      </c>
-      <c r="D421" t="s">
-        <v>504</v>
-      </c>
-      <c r="E421" t="s">
-        <v>505</v>
-      </c>
-      <c r="F421" s="1">
-        <v>46258</v>
-      </c>
-      <c r="G421" s="1">
-        <v>46258</v>
-      </c>
-    </row>
-    <row r="422" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A422" t="s">
-        <v>815</v>
-      </c>
-      <c r="B422" t="s">
-        <v>829</v>
-      </c>
-      <c r="C422" t="s">
-        <v>2</v>
-      </c>
-      <c r="D422" t="s">
-        <v>504</v>
-      </c>
-      <c r="E422" t="s">
-        <v>505</v>
-      </c>
-      <c r="F422" s="1">
-        <v>46262</v>
-      </c>
-      <c r="G422" s="1">
-        <v>46265</v>
-      </c>
-    </row>
-    <row r="423" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A423" t="s">
-        <v>815</v>
-      </c>
-      <c r="B423" t="s">
-        <v>830</v>
-      </c>
-      <c r="C423" t="s">
-        <v>80</v>
-      </c>
-      <c r="D423" t="s">
-        <v>16</v>
-      </c>
-      <c r="E423" t="s">
-        <v>17</v>
-      </c>
-      <c r="F423" s="1">
-        <v>46265</v>
-      </c>
-      <c r="G423" s="1">
         <v>46265</v>
       </c>
     </row>

--- a/Data_ERP/Pedidos Transmicion.xlsx
+++ b/Data_ERP/Pedidos Transmicion.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sistema_Logistico_Peirano\Data_ERP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C6164A87-FBA9-4F13-99BA-10BF71C303AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{38E4C223-29D0-43E9-A0CB-76138F0DED7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{FBD716CC-5FD5-4122-BE97-14E62155AC82}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{66E3F89A-E5B5-45B9-97A0-0FEE46956870}"/>
   </bookViews>
   <sheets>
     <sheet name="transmicion" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2377" uniqueCount="916">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2502" uniqueCount="953">
   <si>
     <t>0001</t>
   </si>
@@ -1456,15 +1456,6 @@
     <t xml:space="preserve">  214677</t>
   </si>
   <si>
-    <t xml:space="preserve">  214678</t>
-  </si>
-  <si>
-    <t>MO24</t>
-  </si>
-  <si>
-    <t>MOENCA SRL -JAQUE MATE</t>
-  </si>
-  <si>
     <t xml:space="preserve">  214679</t>
   </si>
   <si>
@@ -1633,27 +1624,9 @@
     <t xml:space="preserve">  214759</t>
   </si>
   <si>
-    <t xml:space="preserve">  214761</t>
-  </si>
-  <si>
-    <t>DR14</t>
-  </si>
-  <si>
-    <t>DREC SAS</t>
-  </si>
-  <si>
     <t xml:space="preserve">  214763</t>
   </si>
   <si>
-    <t xml:space="preserve">  214767</t>
-  </si>
-  <si>
-    <t>OA01</t>
-  </si>
-  <si>
-    <t>OCHIUZZO ALBINO JUAN - DISTRIMAR</t>
-  </si>
-  <si>
     <t xml:space="preserve">  214771</t>
   </si>
   <si>
@@ -1687,6 +1660,15 @@
     <t>WALTER CARLOS A. -EL FUERTE MATERIALES</t>
   </si>
   <si>
+    <t xml:space="preserve">  214778</t>
+  </si>
+  <si>
+    <t>GA31</t>
+  </si>
+  <si>
+    <t>GALBAHIA S.R.L.</t>
+  </si>
+  <si>
     <t xml:space="preserve">  214779</t>
   </si>
   <si>
@@ -1705,6 +1687,9 @@
     <t>PIRILLI ALEJANDRO ANTONIO - DIECI</t>
   </si>
   <si>
+    <t xml:space="preserve">  214785</t>
+  </si>
+  <si>
     <t xml:space="preserve">  214787</t>
   </si>
   <si>
@@ -1723,6 +1708,15 @@
     <t>ABASTECIMIENTOS PLASTICOS S.R.L. -ABAS PLAS</t>
   </si>
   <si>
+    <t xml:space="preserve">  214805</t>
+  </si>
+  <si>
+    <t>ZJ02</t>
+  </si>
+  <si>
+    <t>ZORZON JOANA M -SANTIANO CONSTRUCCIONES</t>
+  </si>
+  <si>
     <t xml:space="preserve">  214807</t>
   </si>
   <si>
@@ -1777,9 +1771,33 @@
     <t xml:space="preserve">  214816</t>
   </si>
   <si>
+    <t xml:space="preserve">  214818</t>
+  </si>
+  <si>
+    <t>RA22</t>
+  </si>
+  <si>
+    <t>RENUS ALFREDO R. -HERRAJES ARENALES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214819</t>
+  </si>
+  <si>
+    <t>GC13</t>
+  </si>
+  <si>
+    <t>GOMEZ CONSTRUSHOP S.A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  214822</t>
+  </si>
+  <si>
     <t xml:space="preserve">  214823</t>
   </si>
   <si>
+    <t xml:space="preserve">  214824</t>
+  </si>
+  <si>
     <t xml:space="preserve">  214825</t>
   </si>
   <si>
@@ -2017,6 +2035,15 @@
     <t xml:space="preserve">  214928</t>
   </si>
   <si>
+    <t xml:space="preserve">  214929</t>
+  </si>
+  <si>
+    <t>VG04</t>
+  </si>
+  <si>
+    <t>VELAZQUEZ NORBERTO Y GRANELLA JORGE</t>
+  </si>
+  <si>
     <t xml:space="preserve">  214930</t>
   </si>
   <si>
@@ -2185,15 +2212,6 @@
     <t xml:space="preserve">  214970</t>
   </si>
   <si>
-    <t xml:space="preserve">  214971</t>
-  </si>
-  <si>
-    <t>SG13</t>
-  </si>
-  <si>
-    <t>SANITARIOS GAONA S.A.</t>
-  </si>
-  <si>
     <t xml:space="preserve">  214973</t>
   </si>
   <si>
@@ -2473,6 +2491,96 @@
     <t>CATALANO PATRICIA L-SANITARIOS MRM</t>
   </si>
   <si>
+    <t xml:space="preserve">  215037</t>
+  </si>
+  <si>
+    <t>SC33</t>
+  </si>
+  <si>
+    <t>SANITARIOS CAMPANA S.R.L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  215038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  215041</t>
+  </si>
+  <si>
+    <t>CF15</t>
+  </si>
+  <si>
+    <t>COMPAGNUCCI FEDERICO -FERRET. LA OBRA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  215042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  215045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  215046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  215048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  215049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  215050</t>
+  </si>
+  <si>
+    <t>VM15</t>
+  </si>
+  <si>
+    <t>VILANOVA DE MEIA S.R.L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  215051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  215052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  215054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  215056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  215058</t>
+  </si>
+  <si>
+    <t>CS36</t>
+  </si>
+  <si>
+    <t>CREDITO SALADILLO S.R.L.-CENTROMAT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  215059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  215060</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  215061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  215062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  215064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  215066</t>
+  </si>
+  <si>
+    <t>AP09</t>
+  </si>
+  <si>
+    <t>ABATEDAGA PABLO D.J.-CONECTANDO INST. SANIT.</t>
+  </si>
+  <si>
     <t>0004</t>
   </si>
   <si>
@@ -2618,6 +2726,9 @@
   </si>
   <si>
     <t xml:space="preserve">    2891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    2893</t>
   </si>
   <si>
     <t>4444</t>
@@ -3217,31 +3328,31 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72274407-B343-4CE7-AF9F-198FE6B21ED9}">
-  <dimension ref="A1:G475"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D73B85AB-3341-4AE4-9572-B9CAB7B28833}">
+  <dimension ref="A1:G500"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
-        <v>909</v>
+        <v>946</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>910</v>
+        <v>947</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>911</v>
+        <v>948</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>912</v>
+        <v>949</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>913</v>
+        <v>950</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>914</v>
+        <v>951</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>915</v>
+        <v>952</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
@@ -7553,7 +7664,7 @@
         <v>422</v>
       </c>
       <c r="C189" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D189" t="s">
         <v>423</v>
@@ -7565,7 +7676,7 @@
         <v>46260</v>
       </c>
       <c r="G189" s="1">
-        <v>46261</v>
+        <v>46267</v>
       </c>
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.2">
@@ -8289,7 +8400,7 @@
         <v>462</v>
       </c>
       <c r="C221" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D221" t="s">
         <v>463</v>
@@ -8301,7 +8412,7 @@
         <v>46262</v>
       </c>
       <c r="G221" s="1">
-        <v>46265</v>
+        <v>46267</v>
       </c>
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.2">
@@ -8473,7 +8584,7 @@
         <v>478</v>
       </c>
       <c r="C229" t="s">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="D229" t="s">
         <v>479</v>
@@ -8499,13 +8610,13 @@
         <v>80</v>
       </c>
       <c r="D230" t="s">
-        <v>482</v>
+        <v>469</v>
       </c>
       <c r="E230" t="s">
-        <v>483</v>
+        <v>470</v>
       </c>
       <c r="F230" s="1">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="G230" s="1">
         <v>46265</v>
@@ -8516,16 +8627,16 @@
         <v>0</v>
       </c>
       <c r="B231" t="s">
+        <v>482</v>
+      </c>
+      <c r="C231" t="s">
+        <v>80</v>
+      </c>
+      <c r="D231" t="s">
+        <v>483</v>
+      </c>
+      <c r="E231" t="s">
         <v>484</v>
-      </c>
-      <c r="C231" t="s">
-        <v>80</v>
-      </c>
-      <c r="D231" t="s">
-        <v>469</v>
-      </c>
-      <c r="E231" t="s">
-        <v>470</v>
       </c>
       <c r="F231" s="1">
         <v>46263</v>
@@ -8542,7 +8653,7 @@
         <v>485</v>
       </c>
       <c r="C232" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D232" t="s">
         <v>486</v>
@@ -8551,7 +8662,7 @@
         <v>487</v>
       </c>
       <c r="F232" s="1">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="G232" s="1">
         <v>46265</v>
@@ -8591,10 +8702,10 @@
         <v>2</v>
       </c>
       <c r="D234" t="s">
-        <v>492</v>
+        <v>257</v>
       </c>
       <c r="E234" t="s">
-        <v>493</v>
+        <v>258</v>
       </c>
       <c r="F234" s="1">
         <v>46265</v>
@@ -8608,16 +8719,16 @@
         <v>0</v>
       </c>
       <c r="B235" t="s">
+        <v>492</v>
+      </c>
+      <c r="C235" t="s">
+        <v>80</v>
+      </c>
+      <c r="D235" t="s">
+        <v>493</v>
+      </c>
+      <c r="E235" t="s">
         <v>494</v>
-      </c>
-      <c r="C235" t="s">
-        <v>2</v>
-      </c>
-      <c r="D235" t="s">
-        <v>257</v>
-      </c>
-      <c r="E235" t="s">
-        <v>258</v>
       </c>
       <c r="F235" s="1">
         <v>46265</v>
@@ -8680,19 +8791,19 @@
         <v>501</v>
       </c>
       <c r="C238" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D238" t="s">
-        <v>502</v>
+        <v>171</v>
       </c>
       <c r="E238" t="s">
-        <v>503</v>
+        <v>172</v>
       </c>
       <c r="F238" s="1">
         <v>46265</v>
       </c>
       <c r="G238" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="239" spans="1:7" x14ac:dyDescent="0.2">
@@ -8700,22 +8811,22 @@
         <v>0</v>
       </c>
       <c r="B239" t="s">
+        <v>502</v>
+      </c>
+      <c r="C239" t="s">
+        <v>80</v>
+      </c>
+      <c r="D239" t="s">
+        <v>503</v>
+      </c>
+      <c r="E239" t="s">
         <v>504</v>
-      </c>
-      <c r="C239" t="s">
-        <v>2</v>
-      </c>
-      <c r="D239" t="s">
-        <v>171</v>
-      </c>
-      <c r="E239" t="s">
-        <v>172</v>
       </c>
       <c r="F239" s="1">
         <v>46265</v>
       </c>
       <c r="G239" s="1">
-        <v>46266</v>
+        <v>46267</v>
       </c>
     </row>
     <row r="240" spans="1:7" x14ac:dyDescent="0.2">
@@ -8729,16 +8840,16 @@
         <v>80</v>
       </c>
       <c r="D240" t="s">
-        <v>506</v>
+        <v>16</v>
       </c>
       <c r="E240" t="s">
-        <v>507</v>
+        <v>17</v>
       </c>
       <c r="F240" s="1">
         <v>46265</v>
       </c>
       <c r="G240" s="1">
-        <v>46267</v>
+        <v>46265</v>
       </c>
     </row>
     <row r="241" spans="1:7" x14ac:dyDescent="0.2">
@@ -8746,16 +8857,16 @@
         <v>0</v>
       </c>
       <c r="B241" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="C241" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D241" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="E241" t="s">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="F241" s="1">
         <v>46265</v>
@@ -8769,16 +8880,16 @@
         <v>0</v>
       </c>
       <c r="B242" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="C242" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D242" t="s">
-        <v>41</v>
+        <v>499</v>
       </c>
       <c r="E242" t="s">
-        <v>42</v>
+        <v>500</v>
       </c>
       <c r="F242" s="1">
         <v>46265</v>
@@ -8792,16 +8903,16 @@
         <v>0</v>
       </c>
       <c r="B243" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="C243" t="s">
         <v>80</v>
       </c>
       <c r="D243" t="s">
-        <v>502</v>
+        <v>200</v>
       </c>
       <c r="E243" t="s">
-        <v>503</v>
+        <v>201</v>
       </c>
       <c r="F243" s="1">
         <v>46265</v>
@@ -8815,16 +8926,16 @@
         <v>0</v>
       </c>
       <c r="B244" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="C244" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D244" t="s">
-        <v>200</v>
+        <v>84</v>
       </c>
       <c r="E244" t="s">
-        <v>201</v>
+        <v>85</v>
       </c>
       <c r="F244" s="1">
         <v>46265</v>
@@ -8838,22 +8949,22 @@
         <v>0</v>
       </c>
       <c r="B245" t="s">
+        <v>510</v>
+      </c>
+      <c r="C245" t="s">
+        <v>80</v>
+      </c>
+      <c r="D245" t="s">
+        <v>511</v>
+      </c>
+      <c r="E245" t="s">
         <v>512</v>
-      </c>
-      <c r="C245" t="s">
-        <v>2</v>
-      </c>
-      <c r="D245" t="s">
-        <v>84</v>
-      </c>
-      <c r="E245" t="s">
-        <v>85</v>
       </c>
       <c r="F245" s="1">
         <v>46265</v>
       </c>
       <c r="G245" s="1">
-        <v>46265</v>
+        <v>46267</v>
       </c>
     </row>
     <row r="246" spans="1:7" x14ac:dyDescent="0.2">
@@ -8864,13 +8975,13 @@
         <v>513</v>
       </c>
       <c r="C246" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D246" t="s">
-        <v>514</v>
+        <v>48</v>
       </c>
       <c r="E246" t="s">
-        <v>515</v>
+        <v>49</v>
       </c>
       <c r="F246" s="1">
         <v>46265</v>
@@ -8884,22 +8995,22 @@
         <v>0</v>
       </c>
       <c r="B247" t="s">
+        <v>514</v>
+      </c>
+      <c r="C247" t="s">
+        <v>80</v>
+      </c>
+      <c r="D247" t="s">
+        <v>515</v>
+      </c>
+      <c r="E247" t="s">
         <v>516</v>
-      </c>
-      <c r="C247" t="s">
-        <v>2</v>
-      </c>
-      <c r="D247" t="s">
-        <v>48</v>
-      </c>
-      <c r="E247" t="s">
-        <v>49</v>
       </c>
       <c r="F247" s="1">
         <v>46265</v>
       </c>
       <c r="G247" s="1">
-        <v>46267</v>
+        <v>46265</v>
       </c>
     </row>
     <row r="248" spans="1:7" x14ac:dyDescent="0.2">
@@ -8910,13 +9021,13 @@
         <v>517</v>
       </c>
       <c r="C248" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D248" t="s">
-        <v>518</v>
+        <v>19</v>
       </c>
       <c r="E248" t="s">
-        <v>519</v>
+        <v>20</v>
       </c>
       <c r="F248" s="1">
         <v>46265</v>
@@ -8930,16 +9041,16 @@
         <v>0</v>
       </c>
       <c r="B249" t="s">
+        <v>518</v>
+      </c>
+      <c r="C249" t="s">
+        <v>80</v>
+      </c>
+      <c r="D249" t="s">
+        <v>519</v>
+      </c>
+      <c r="E249" t="s">
         <v>520</v>
-      </c>
-      <c r="C249" t="s">
-        <v>2</v>
-      </c>
-      <c r="D249" t="s">
-        <v>19</v>
-      </c>
-      <c r="E249" t="s">
-        <v>20</v>
       </c>
       <c r="F249" s="1">
         <v>46265</v>
@@ -8982,10 +9093,10 @@
         <v>80</v>
       </c>
       <c r="D251" t="s">
-        <v>525</v>
+        <v>340</v>
       </c>
       <c r="E251" t="s">
-        <v>526</v>
+        <v>341</v>
       </c>
       <c r="F251" s="1">
         <v>46265</v>
@@ -8999,22 +9110,22 @@
         <v>0</v>
       </c>
       <c r="B252" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="C252" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D252" t="s">
-        <v>340</v>
+        <v>7</v>
       </c>
       <c r="E252" t="s">
-        <v>341</v>
+        <v>8</v>
       </c>
       <c r="F252" s="1">
         <v>46265</v>
       </c>
       <c r="G252" s="1">
-        <v>46265</v>
+        <v>46267</v>
       </c>
     </row>
     <row r="253" spans="1:7" x14ac:dyDescent="0.2">
@@ -9022,16 +9133,16 @@
         <v>0</v>
       </c>
       <c r="B253" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="C253" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D253" t="s">
-        <v>7</v>
+        <v>101</v>
       </c>
       <c r="E253" t="s">
-        <v>8</v>
+        <v>102</v>
       </c>
       <c r="F253" s="1">
         <v>46265</v>
@@ -9045,22 +9156,22 @@
         <v>0</v>
       </c>
       <c r="B254" t="s">
+        <v>527</v>
+      </c>
+      <c r="C254" t="s">
+        <v>80</v>
+      </c>
+      <c r="D254" t="s">
+        <v>528</v>
+      </c>
+      <c r="E254" t="s">
         <v>529</v>
-      </c>
-      <c r="C254" t="s">
-        <v>80</v>
-      </c>
-      <c r="D254" t="s">
-        <v>101</v>
-      </c>
-      <c r="E254" t="s">
-        <v>102</v>
       </c>
       <c r="F254" s="1">
         <v>46265</v>
       </c>
       <c r="G254" s="1">
-        <v>46267</v>
+        <v>46265</v>
       </c>
     </row>
     <row r="255" spans="1:7" x14ac:dyDescent="0.2">
@@ -9097,10 +9208,10 @@
         <v>80</v>
       </c>
       <c r="D256" t="s">
-        <v>534</v>
+        <v>161</v>
       </c>
       <c r="E256" t="s">
-        <v>535</v>
+        <v>162</v>
       </c>
       <c r="F256" s="1">
         <v>46265</v>
@@ -9114,22 +9225,22 @@
         <v>0</v>
       </c>
       <c r="B257" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="C257" t="s">
         <v>80</v>
       </c>
       <c r="D257" t="s">
-        <v>161</v>
+        <v>93</v>
       </c>
       <c r="E257" t="s">
-        <v>162</v>
+        <v>94</v>
       </c>
       <c r="F257" s="1">
         <v>46265</v>
       </c>
       <c r="G257" s="1">
-        <v>46265</v>
+        <v>46267</v>
       </c>
     </row>
     <row r="258" spans="1:7" x14ac:dyDescent="0.2">
@@ -9137,16 +9248,16 @@
         <v>0</v>
       </c>
       <c r="B258" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="C258" t="s">
-        <v>96</v>
+        <v>2</v>
       </c>
       <c r="D258" t="s">
-        <v>538</v>
+        <v>41</v>
       </c>
       <c r="E258" t="s">
-        <v>539</v>
+        <v>42</v>
       </c>
       <c r="F258" s="1">
         <v>46265</v>
@@ -9160,16 +9271,16 @@
         <v>0</v>
       </c>
       <c r="B259" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="C259" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D259" t="s">
-        <v>93</v>
+        <v>537</v>
       </c>
       <c r="E259" t="s">
-        <v>94</v>
+        <v>538</v>
       </c>
       <c r="F259" s="1">
         <v>46265</v>
@@ -9183,16 +9294,16 @@
         <v>0</v>
       </c>
       <c r="B260" t="s">
+        <v>539</v>
+      </c>
+      <c r="C260" t="s">
+        <v>80</v>
+      </c>
+      <c r="D260" t="s">
+        <v>540</v>
+      </c>
+      <c r="E260" t="s">
         <v>541</v>
-      </c>
-      <c r="C260" t="s">
-        <v>96</v>
-      </c>
-      <c r="D260" t="s">
-        <v>542</v>
-      </c>
-      <c r="E260" t="s">
-        <v>543</v>
       </c>
       <c r="F260" s="1">
         <v>46265</v>
@@ -9206,16 +9317,16 @@
         <v>0</v>
       </c>
       <c r="B261" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="C261" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D261" t="s">
-        <v>41</v>
+        <v>155</v>
       </c>
       <c r="E261" t="s">
-        <v>42</v>
+        <v>156</v>
       </c>
       <c r="F261" s="1">
         <v>46265</v>
@@ -9229,16 +9340,16 @@
         <v>0</v>
       </c>
       <c r="B262" t="s">
+        <v>543</v>
+      </c>
+      <c r="C262" t="s">
+        <v>80</v>
+      </c>
+      <c r="D262" t="s">
+        <v>544</v>
+      </c>
+      <c r="E262" t="s">
         <v>545</v>
-      </c>
-      <c r="C262" t="s">
-        <v>80</v>
-      </c>
-      <c r="D262" t="s">
-        <v>546</v>
-      </c>
-      <c r="E262" t="s">
-        <v>547</v>
       </c>
       <c r="F262" s="1">
         <v>46265</v>
@@ -9252,22 +9363,22 @@
         <v>0</v>
       </c>
       <c r="B263" t="s">
+        <v>546</v>
+      </c>
+      <c r="C263" t="s">
+        <v>80</v>
+      </c>
+      <c r="D263" t="s">
+        <v>547</v>
+      </c>
+      <c r="E263" t="s">
         <v>548</v>
-      </c>
-      <c r="C263" t="s">
-        <v>80</v>
-      </c>
-      <c r="D263" t="s">
-        <v>549</v>
-      </c>
-      <c r="E263" t="s">
-        <v>550</v>
       </c>
       <c r="F263" s="1">
         <v>46265</v>
       </c>
       <c r="G263" s="1">
-        <v>46265</v>
+        <v>46267</v>
       </c>
     </row>
     <row r="264" spans="1:7" x14ac:dyDescent="0.2">
@@ -9275,16 +9386,16 @@
         <v>0</v>
       </c>
       <c r="B264" t="s">
+        <v>549</v>
+      </c>
+      <c r="C264" t="s">
+        <v>80</v>
+      </c>
+      <c r="D264" t="s">
+        <v>550</v>
+      </c>
+      <c r="E264" t="s">
         <v>551</v>
-      </c>
-      <c r="C264" t="s">
-        <v>80</v>
-      </c>
-      <c r="D264" t="s">
-        <v>155</v>
-      </c>
-      <c r="E264" t="s">
-        <v>156</v>
       </c>
       <c r="F264" s="1">
         <v>46265</v>
@@ -9313,7 +9424,7 @@
         <v>46265</v>
       </c>
       <c r="G265" s="1">
-        <v>46267</v>
+        <v>46265</v>
       </c>
     </row>
     <row r="266" spans="1:7" x14ac:dyDescent="0.2">
@@ -9327,16 +9438,16 @@
         <v>80</v>
       </c>
       <c r="D266" t="s">
-        <v>556</v>
+        <v>168</v>
       </c>
       <c r="E266" t="s">
-        <v>557</v>
+        <v>169</v>
       </c>
       <c r="F266" s="1">
         <v>46265</v>
       </c>
       <c r="G266" s="1">
-        <v>46265</v>
+        <v>46267</v>
       </c>
     </row>
     <row r="267" spans="1:7" x14ac:dyDescent="0.2">
@@ -9344,16 +9455,16 @@
         <v>0</v>
       </c>
       <c r="B267" t="s">
+        <v>556</v>
+      </c>
+      <c r="C267" t="s">
+        <v>80</v>
+      </c>
+      <c r="D267" t="s">
+        <v>557</v>
+      </c>
+      <c r="E267" t="s">
         <v>558</v>
-      </c>
-      <c r="C267" t="s">
-        <v>80</v>
-      </c>
-      <c r="D267" t="s">
-        <v>559</v>
-      </c>
-      <c r="E267" t="s">
-        <v>560</v>
       </c>
       <c r="F267" s="1">
         <v>46265</v>
@@ -9367,16 +9478,16 @@
         <v>0</v>
       </c>
       <c r="B268" t="s">
+        <v>559</v>
+      </c>
+      <c r="C268" t="s">
+        <v>80</v>
+      </c>
+      <c r="D268" t="s">
+        <v>560</v>
+      </c>
+      <c r="E268" t="s">
         <v>561</v>
-      </c>
-      <c r="C268" t="s">
-        <v>80</v>
-      </c>
-      <c r="D268" t="s">
-        <v>562</v>
-      </c>
-      <c r="E268" t="s">
-        <v>563</v>
       </c>
       <c r="F268" s="1">
         <v>46265</v>
@@ -9390,22 +9501,22 @@
         <v>0</v>
       </c>
       <c r="B269" t="s">
+        <v>562</v>
+      </c>
+      <c r="C269" t="s">
+        <v>80</v>
+      </c>
+      <c r="D269" t="s">
+        <v>563</v>
+      </c>
+      <c r="E269" t="s">
         <v>564</v>
-      </c>
-      <c r="C269" t="s">
-        <v>80</v>
-      </c>
-      <c r="D269" t="s">
-        <v>565</v>
-      </c>
-      <c r="E269" t="s">
-        <v>566</v>
       </c>
       <c r="F269" s="1">
         <v>46265</v>
       </c>
       <c r="G269" s="1">
-        <v>46265</v>
+        <v>46267</v>
       </c>
     </row>
     <row r="270" spans="1:7" x14ac:dyDescent="0.2">
@@ -9413,7 +9524,7 @@
         <v>0</v>
       </c>
       <c r="B270" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="C270" t="s">
         <v>80</v>
@@ -9436,16 +9547,16 @@
         <v>0</v>
       </c>
       <c r="B271" t="s">
+        <v>566</v>
+      </c>
+      <c r="C271" t="s">
+        <v>80</v>
+      </c>
+      <c r="D271" t="s">
+        <v>567</v>
+      </c>
+      <c r="E271" t="s">
         <v>568</v>
-      </c>
-      <c r="C271" t="s">
-        <v>80</v>
-      </c>
-      <c r="D271" t="s">
-        <v>569</v>
-      </c>
-      <c r="E271" t="s">
-        <v>570</v>
       </c>
       <c r="F271" s="1">
         <v>46265</v>
@@ -9459,16 +9570,16 @@
         <v>0</v>
       </c>
       <c r="B272" t="s">
+        <v>569</v>
+      </c>
+      <c r="C272" t="s">
+        <v>80</v>
+      </c>
+      <c r="D272" t="s">
+        <v>570</v>
+      </c>
+      <c r="E272" t="s">
         <v>571</v>
-      </c>
-      <c r="C272" t="s">
-        <v>80</v>
-      </c>
-      <c r="D272" t="s">
-        <v>572</v>
-      </c>
-      <c r="E272" t="s">
-        <v>573</v>
       </c>
       <c r="F272" s="1">
         <v>46265</v>
@@ -9482,16 +9593,16 @@
         <v>0</v>
       </c>
       <c r="B273" t="s">
+        <v>572</v>
+      </c>
+      <c r="C273" t="s">
+        <v>2</v>
+      </c>
+      <c r="D273" t="s">
+        <v>573</v>
+      </c>
+      <c r="E273" t="s">
         <v>574</v>
-      </c>
-      <c r="C273" t="s">
-        <v>80</v>
-      </c>
-      <c r="D273" t="s">
-        <v>575</v>
-      </c>
-      <c r="E273" t="s">
-        <v>576</v>
       </c>
       <c r="F273" s="1">
         <v>46265</v>
@@ -9505,16 +9616,16 @@
         <v>0</v>
       </c>
       <c r="B274" t="s">
+        <v>575</v>
+      </c>
+      <c r="C274" t="s">
+        <v>80</v>
+      </c>
+      <c r="D274" t="s">
+        <v>576</v>
+      </c>
+      <c r="E274" t="s">
         <v>577</v>
-      </c>
-      <c r="C274" t="s">
-        <v>80</v>
-      </c>
-      <c r="D274" t="s">
-        <v>578</v>
-      </c>
-      <c r="E274" t="s">
-        <v>579</v>
       </c>
       <c r="F274" s="1">
         <v>46265</v>
@@ -9528,16 +9639,16 @@
         <v>0</v>
       </c>
       <c r="B275" t="s">
+        <v>578</v>
+      </c>
+      <c r="C275" t="s">
+        <v>80</v>
+      </c>
+      <c r="D275" t="s">
+        <v>579</v>
+      </c>
+      <c r="E275" t="s">
         <v>580</v>
-      </c>
-      <c r="C275" t="s">
-        <v>80</v>
-      </c>
-      <c r="D275" t="s">
-        <v>581</v>
-      </c>
-      <c r="E275" t="s">
-        <v>582</v>
       </c>
       <c r="F275" s="1">
         <v>46265</v>
@@ -9551,7 +9662,7 @@
         <v>0</v>
       </c>
       <c r="B276" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="C276" t="s">
         <v>2</v>
@@ -9574,7 +9685,7 @@
         <v>0</v>
       </c>
       <c r="B277" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="C277" t="s">
         <v>80</v>
@@ -9597,16 +9708,16 @@
         <v>0</v>
       </c>
       <c r="B278" t="s">
+        <v>583</v>
+      </c>
+      <c r="C278" t="s">
+        <v>80</v>
+      </c>
+      <c r="D278" t="s">
+        <v>584</v>
+      </c>
+      <c r="E278" t="s">
         <v>585</v>
-      </c>
-      <c r="C278" t="s">
-        <v>80</v>
-      </c>
-      <c r="D278" t="s">
-        <v>227</v>
-      </c>
-      <c r="E278" t="s">
-        <v>228</v>
       </c>
       <c r="F278" s="1">
         <v>46265</v>
@@ -9626,10 +9737,10 @@
         <v>80</v>
       </c>
       <c r="D279" t="s">
-        <v>227</v>
+        <v>587</v>
       </c>
       <c r="E279" t="s">
-        <v>228</v>
+        <v>588</v>
       </c>
       <c r="F279" s="1">
         <v>46265</v>
@@ -9643,16 +9754,16 @@
         <v>0</v>
       </c>
       <c r="B280" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="C280" t="s">
         <v>80</v>
       </c>
       <c r="D280" t="s">
-        <v>588</v>
+        <v>346</v>
       </c>
       <c r="E280" t="s">
-        <v>589</v>
+        <v>347</v>
       </c>
       <c r="F280" s="1">
         <v>46265</v>
@@ -9672,10 +9783,10 @@
         <v>80</v>
       </c>
       <c r="D281" t="s">
-        <v>205</v>
+        <v>227</v>
       </c>
       <c r="E281" t="s">
-        <v>206</v>
+        <v>228</v>
       </c>
       <c r="F281" s="1">
         <v>46265</v>
@@ -9695,10 +9806,10 @@
         <v>80</v>
       </c>
       <c r="D282" t="s">
-        <v>205</v>
+        <v>285</v>
       </c>
       <c r="E282" t="s">
-        <v>206</v>
+        <v>286</v>
       </c>
       <c r="F282" s="1">
         <v>46265</v>
@@ -9715,16 +9826,16 @@
         <v>592</v>
       </c>
       <c r="C283" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D283" t="s">
-        <v>489</v>
+        <v>227</v>
       </c>
       <c r="E283" t="s">
-        <v>490</v>
+        <v>228</v>
       </c>
       <c r="F283" s="1">
-        <v>46266</v>
+        <v>46265</v>
       </c>
       <c r="G283" s="1">
         <v>46267</v>
@@ -9741,13 +9852,13 @@
         <v>80</v>
       </c>
       <c r="D284" t="s">
-        <v>98</v>
+        <v>594</v>
       </c>
       <c r="E284" t="s">
-        <v>99</v>
+        <v>595</v>
       </c>
       <c r="F284" s="1">
-        <v>46266</v>
+        <v>46265</v>
       </c>
       <c r="G284" s="1">
         <v>46267</v>
@@ -9758,19 +9869,19 @@
         <v>0</v>
       </c>
       <c r="B285" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="C285" t="s">
         <v>80</v>
       </c>
       <c r="D285" t="s">
-        <v>174</v>
+        <v>205</v>
       </c>
       <c r="E285" t="s">
-        <v>175</v>
+        <v>206</v>
       </c>
       <c r="F285" s="1">
-        <v>46266</v>
+        <v>46265</v>
       </c>
       <c r="G285" s="1">
         <v>46267</v>
@@ -9781,19 +9892,19 @@
         <v>0</v>
       </c>
       <c r="B286" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="C286" t="s">
         <v>80</v>
       </c>
       <c r="D286" t="s">
-        <v>596</v>
+        <v>205</v>
       </c>
       <c r="E286" t="s">
-        <v>597</v>
+        <v>206</v>
       </c>
       <c r="F286" s="1">
-        <v>46266</v>
+        <v>46265</v>
       </c>
       <c r="G286" s="1">
         <v>46267</v>
@@ -9807,13 +9918,13 @@
         <v>598</v>
       </c>
       <c r="C287" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D287" t="s">
-        <v>599</v>
+        <v>486</v>
       </c>
       <c r="E287" t="s">
-        <v>600</v>
+        <v>487</v>
       </c>
       <c r="F287" s="1">
         <v>46266</v>
@@ -9827,16 +9938,16 @@
         <v>0</v>
       </c>
       <c r="B288" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="C288" t="s">
         <v>80</v>
       </c>
       <c r="D288" t="s">
-        <v>602</v>
+        <v>98</v>
       </c>
       <c r="E288" t="s">
-        <v>603</v>
+        <v>99</v>
       </c>
       <c r="F288" s="1">
         <v>46266</v>
@@ -9850,16 +9961,16 @@
         <v>0</v>
       </c>
       <c r="B289" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="C289" t="s">
         <v>80</v>
       </c>
       <c r="D289" t="s">
-        <v>605</v>
+        <v>174</v>
       </c>
       <c r="E289" t="s">
-        <v>606</v>
+        <v>175</v>
       </c>
       <c r="F289" s="1">
         <v>46266</v>
@@ -9873,22 +9984,22 @@
         <v>0</v>
       </c>
       <c r="B290" t="s">
-        <v>607</v>
+        <v>601</v>
       </c>
       <c r="C290" t="s">
         <v>80</v>
       </c>
       <c r="D290" t="s">
-        <v>16</v>
+        <v>602</v>
       </c>
       <c r="E290" t="s">
-        <v>17</v>
+        <v>603</v>
       </c>
       <c r="F290" s="1">
         <v>46266</v>
       </c>
       <c r="G290" s="1">
-        <v>46266</v>
+        <v>46267</v>
       </c>
     </row>
     <row r="291" spans="1:7" x14ac:dyDescent="0.2">
@@ -9896,22 +10007,22 @@
         <v>0</v>
       </c>
       <c r="B291" t="s">
-        <v>608</v>
+        <v>604</v>
       </c>
       <c r="C291" t="s">
         <v>80</v>
       </c>
       <c r="D291" t="s">
-        <v>205</v>
+        <v>605</v>
       </c>
       <c r="E291" t="s">
-        <v>206</v>
+        <v>606</v>
       </c>
       <c r="F291" s="1">
         <v>46266</v>
       </c>
       <c r="G291" s="1">
-        <v>46266</v>
+        <v>46267</v>
       </c>
     </row>
     <row r="292" spans="1:7" x14ac:dyDescent="0.2">
@@ -9919,22 +10030,22 @@
         <v>0</v>
       </c>
       <c r="B292" t="s">
+        <v>607</v>
+      </c>
+      <c r="C292" t="s">
+        <v>80</v>
+      </c>
+      <c r="D292" t="s">
+        <v>608</v>
+      </c>
+      <c r="E292" t="s">
         <v>609</v>
-      </c>
-      <c r="C292" t="s">
-        <v>80</v>
-      </c>
-      <c r="D292" t="s">
-        <v>610</v>
-      </c>
-      <c r="E292" t="s">
-        <v>611</v>
       </c>
       <c r="F292" s="1">
         <v>46266</v>
       </c>
       <c r="G292" s="1">
-        <v>46266</v>
+        <v>46267</v>
       </c>
     </row>
     <row r="293" spans="1:7" x14ac:dyDescent="0.2">
@@ -9942,22 +10053,22 @@
         <v>0</v>
       </c>
       <c r="B293" t="s">
+        <v>610</v>
+      </c>
+      <c r="C293" t="s">
+        <v>80</v>
+      </c>
+      <c r="D293" t="s">
+        <v>611</v>
+      </c>
+      <c r="E293" t="s">
         <v>612</v>
-      </c>
-      <c r="C293" t="s">
-        <v>80</v>
-      </c>
-      <c r="D293" t="s">
-        <v>127</v>
-      </c>
-      <c r="E293" t="s">
-        <v>128</v>
       </c>
       <c r="F293" s="1">
         <v>46266</v>
       </c>
       <c r="G293" s="1">
-        <v>46266</v>
+        <v>46267</v>
       </c>
     </row>
     <row r="294" spans="1:7" x14ac:dyDescent="0.2">
@@ -9971,10 +10082,10 @@
         <v>80</v>
       </c>
       <c r="D294" t="s">
-        <v>614</v>
+        <v>16</v>
       </c>
       <c r="E294" t="s">
-        <v>615</v>
+        <v>17</v>
       </c>
       <c r="F294" s="1">
         <v>46266</v>
@@ -9988,16 +10099,16 @@
         <v>0</v>
       </c>
       <c r="B295" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="C295" t="s">
         <v>80</v>
       </c>
       <c r="D295" t="s">
-        <v>340</v>
+        <v>205</v>
       </c>
       <c r="E295" t="s">
-        <v>341</v>
+        <v>206</v>
       </c>
       <c r="F295" s="1">
         <v>46266</v>
@@ -10011,16 +10122,16 @@
         <v>0</v>
       </c>
       <c r="B296" t="s">
+        <v>615</v>
+      </c>
+      <c r="C296" t="s">
+        <v>80</v>
+      </c>
+      <c r="D296" t="s">
+        <v>616</v>
+      </c>
+      <c r="E296" t="s">
         <v>617</v>
-      </c>
-      <c r="C296" t="s">
-        <v>80</v>
-      </c>
-      <c r="D296" t="s">
-        <v>45</v>
-      </c>
-      <c r="E296" t="s">
-        <v>46</v>
       </c>
       <c r="F296" s="1">
         <v>46266</v>
@@ -10040,10 +10151,10 @@
         <v>80</v>
       </c>
       <c r="D297" t="s">
-        <v>310</v>
+        <v>127</v>
       </c>
       <c r="E297" t="s">
-        <v>311</v>
+        <v>128</v>
       </c>
       <c r="F297" s="1">
         <v>46266</v>
@@ -10063,10 +10174,10 @@
         <v>80</v>
       </c>
       <c r="D298" t="s">
-        <v>101</v>
+        <v>620</v>
       </c>
       <c r="E298" t="s">
-        <v>102</v>
+        <v>621</v>
       </c>
       <c r="F298" s="1">
         <v>46266</v>
@@ -10080,22 +10191,22 @@
         <v>0</v>
       </c>
       <c r="B299" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="C299" t="s">
         <v>80</v>
       </c>
       <c r="D299" t="s">
-        <v>101</v>
+        <v>340</v>
       </c>
       <c r="E299" t="s">
-        <v>102</v>
+        <v>341</v>
       </c>
       <c r="F299" s="1">
         <v>46266</v>
       </c>
       <c r="G299" s="1">
-        <v>46267</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="300" spans="1:7" x14ac:dyDescent="0.2">
@@ -10103,22 +10214,22 @@
         <v>0</v>
       </c>
       <c r="B300" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="C300" t="s">
         <v>80</v>
       </c>
       <c r="D300" t="s">
-        <v>148</v>
+        <v>45</v>
       </c>
       <c r="E300" t="s">
-        <v>149</v>
+        <v>46</v>
       </c>
       <c r="F300" s="1">
         <v>46266</v>
       </c>
       <c r="G300" s="1">
-        <v>46267</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="301" spans="1:7" x14ac:dyDescent="0.2">
@@ -10126,16 +10237,16 @@
         <v>0</v>
       </c>
       <c r="B301" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="C301" t="s">
         <v>80</v>
       </c>
       <c r="D301" t="s">
-        <v>623</v>
+        <v>310</v>
       </c>
       <c r="E301" t="s">
-        <v>624</v>
+        <v>311</v>
       </c>
       <c r="F301" s="1">
         <v>46266</v>
@@ -10155,10 +10266,10 @@
         <v>80</v>
       </c>
       <c r="D302" t="s">
-        <v>626</v>
+        <v>101</v>
       </c>
       <c r="E302" t="s">
-        <v>627</v>
+        <v>102</v>
       </c>
       <c r="F302" s="1">
         <v>46266</v>
@@ -10172,22 +10283,22 @@
         <v>0</v>
       </c>
       <c r="B303" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="C303" t="s">
         <v>80</v>
       </c>
       <c r="D303" t="s">
-        <v>184</v>
+        <v>101</v>
       </c>
       <c r="E303" t="s">
-        <v>185</v>
+        <v>102</v>
       </c>
       <c r="F303" s="1">
         <v>46266</v>
       </c>
       <c r="G303" s="1">
-        <v>46266</v>
+        <v>46267</v>
       </c>
     </row>
     <row r="304" spans="1:7" x14ac:dyDescent="0.2">
@@ -10195,16 +10306,16 @@
         <v>0</v>
       </c>
       <c r="B304" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="C304" t="s">
         <v>80</v>
       </c>
       <c r="D304" t="s">
-        <v>132</v>
+        <v>148</v>
       </c>
       <c r="E304" t="s">
-        <v>133</v>
+        <v>149</v>
       </c>
       <c r="F304" s="1">
         <v>46266</v>
@@ -10218,16 +10329,16 @@
         <v>0</v>
       </c>
       <c r="B305" t="s">
+        <v>628</v>
+      </c>
+      <c r="C305" t="s">
+        <v>80</v>
+      </c>
+      <c r="D305" t="s">
+        <v>629</v>
+      </c>
+      <c r="E305" t="s">
         <v>630</v>
-      </c>
-      <c r="C305" t="s">
-        <v>80</v>
-      </c>
-      <c r="D305" t="s">
-        <v>631</v>
-      </c>
-      <c r="E305" t="s">
-        <v>632</v>
       </c>
       <c r="F305" s="1">
         <v>46266</v>
@@ -10241,16 +10352,16 @@
         <v>0</v>
       </c>
       <c r="B306" t="s">
+        <v>631</v>
+      </c>
+      <c r="C306" t="s">
+        <v>80</v>
+      </c>
+      <c r="D306" t="s">
+        <v>632</v>
+      </c>
+      <c r="E306" t="s">
         <v>633</v>
-      </c>
-      <c r="C306" t="s">
-        <v>96</v>
-      </c>
-      <c r="D306" t="s">
-        <v>634</v>
-      </c>
-      <c r="E306" t="s">
-        <v>635</v>
       </c>
       <c r="F306" s="1">
         <v>46266</v>
@@ -10264,16 +10375,16 @@
         <v>0</v>
       </c>
       <c r="B307" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="C307" t="s">
         <v>80</v>
       </c>
       <c r="D307" t="s">
-        <v>559</v>
+        <v>184</v>
       </c>
       <c r="E307" t="s">
-        <v>560</v>
+        <v>185</v>
       </c>
       <c r="F307" s="1">
         <v>46266</v>
@@ -10287,22 +10398,22 @@
         <v>0</v>
       </c>
       <c r="B308" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="C308" t="s">
         <v>80</v>
       </c>
       <c r="D308" t="s">
-        <v>623</v>
+        <v>132</v>
       </c>
       <c r="E308" t="s">
-        <v>624</v>
+        <v>133</v>
       </c>
       <c r="F308" s="1">
         <v>46266</v>
       </c>
       <c r="G308" s="1">
-        <v>46266</v>
+        <v>46267</v>
       </c>
     </row>
     <row r="309" spans="1:7" x14ac:dyDescent="0.2">
@@ -10310,16 +10421,16 @@
         <v>0</v>
       </c>
       <c r="B309" t="s">
+        <v>636</v>
+      </c>
+      <c r="C309" t="s">
+        <v>80</v>
+      </c>
+      <c r="D309" t="s">
+        <v>637</v>
+      </c>
+      <c r="E309" t="s">
         <v>638</v>
-      </c>
-      <c r="C309" t="s">
-        <v>80</v>
-      </c>
-      <c r="D309" t="s">
-        <v>639</v>
-      </c>
-      <c r="E309" t="s">
-        <v>640</v>
       </c>
       <c r="F309" s="1">
         <v>46266</v>
@@ -10333,16 +10444,16 @@
         <v>0</v>
       </c>
       <c r="B310" t="s">
+        <v>639</v>
+      </c>
+      <c r="C310" t="s">
+        <v>96</v>
+      </c>
+      <c r="D310" t="s">
+        <v>640</v>
+      </c>
+      <c r="E310" t="s">
         <v>641</v>
-      </c>
-      <c r="C310" t="s">
-        <v>80</v>
-      </c>
-      <c r="D310" t="s">
-        <v>639</v>
-      </c>
-      <c r="E310" t="s">
-        <v>640</v>
       </c>
       <c r="F310" s="1">
         <v>46266</v>
@@ -10362,10 +10473,10 @@
         <v>80</v>
       </c>
       <c r="D311" t="s">
-        <v>161</v>
+        <v>553</v>
       </c>
       <c r="E311" t="s">
-        <v>162</v>
+        <v>554</v>
       </c>
       <c r="F311" s="1">
         <v>46266</v>
@@ -10385,10 +10496,10 @@
         <v>80</v>
       </c>
       <c r="D312" t="s">
-        <v>644</v>
+        <v>629</v>
       </c>
       <c r="E312" t="s">
-        <v>645</v>
+        <v>630</v>
       </c>
       <c r="F312" s="1">
         <v>46266</v>
@@ -10402,16 +10513,16 @@
         <v>0</v>
       </c>
       <c r="B313" t="s">
+        <v>644</v>
+      </c>
+      <c r="C313" t="s">
+        <v>80</v>
+      </c>
+      <c r="D313" t="s">
+        <v>645</v>
+      </c>
+      <c r="E313" t="s">
         <v>646</v>
-      </c>
-      <c r="C313" t="s">
-        <v>80</v>
-      </c>
-      <c r="D313" t="s">
-        <v>647</v>
-      </c>
-      <c r="E313" t="s">
-        <v>648</v>
       </c>
       <c r="F313" s="1">
         <v>46266</v>
@@ -10425,16 +10536,16 @@
         <v>0</v>
       </c>
       <c r="B314" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="C314" t="s">
         <v>80</v>
       </c>
       <c r="D314" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="E314" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="F314" s="1">
         <v>46266</v>
@@ -10448,22 +10559,22 @@
         <v>0</v>
       </c>
       <c r="B315" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="C315" t="s">
         <v>80</v>
       </c>
       <c r="D315" t="s">
-        <v>117</v>
+        <v>161</v>
       </c>
       <c r="E315" t="s">
-        <v>118</v>
+        <v>162</v>
       </c>
       <c r="F315" s="1">
         <v>46266</v>
       </c>
       <c r="G315" s="1">
-        <v>46267</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="316" spans="1:7" x14ac:dyDescent="0.2">
@@ -10471,16 +10582,16 @@
         <v>0</v>
       </c>
       <c r="B316" t="s">
+        <v>649</v>
+      </c>
+      <c r="C316" t="s">
+        <v>80</v>
+      </c>
+      <c r="D316" t="s">
+        <v>650</v>
+      </c>
+      <c r="E316" t="s">
         <v>651</v>
-      </c>
-      <c r="C316" t="s">
-        <v>80</v>
-      </c>
-      <c r="D316" t="s">
-        <v>652</v>
-      </c>
-      <c r="E316" t="s">
-        <v>653</v>
       </c>
       <c r="F316" s="1">
         <v>46266</v>
@@ -10494,16 +10605,16 @@
         <v>0</v>
       </c>
       <c r="B317" t="s">
+        <v>652</v>
+      </c>
+      <c r="C317" t="s">
+        <v>80</v>
+      </c>
+      <c r="D317" t="s">
+        <v>653</v>
+      </c>
+      <c r="E317" t="s">
         <v>654</v>
-      </c>
-      <c r="C317" t="s">
-        <v>2</v>
-      </c>
-      <c r="D317" t="s">
-        <v>87</v>
-      </c>
-      <c r="E317" t="s">
-        <v>88</v>
       </c>
       <c r="F317" s="1">
         <v>46266</v>
@@ -10523,16 +10634,16 @@
         <v>80</v>
       </c>
       <c r="D318" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="E318" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="F318" s="1">
         <v>46266</v>
       </c>
       <c r="G318" s="1">
-        <v>46267</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="319" spans="1:7" x14ac:dyDescent="0.2">
@@ -10540,22 +10651,22 @@
         <v>0</v>
       </c>
       <c r="B319" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="C319" t="s">
         <v>2</v>
       </c>
       <c r="D319" t="s">
-        <v>87</v>
+        <v>117</v>
       </c>
       <c r="E319" t="s">
-        <v>88</v>
+        <v>118</v>
       </c>
       <c r="F319" s="1">
         <v>46266</v>
       </c>
       <c r="G319" s="1">
-        <v>46266</v>
+        <v>46267</v>
       </c>
     </row>
     <row r="320" spans="1:7" x14ac:dyDescent="0.2">
@@ -10563,22 +10674,22 @@
         <v>0</v>
       </c>
       <c r="B320" t="s">
+        <v>657</v>
+      </c>
+      <c r="C320" t="s">
+        <v>80</v>
+      </c>
+      <c r="D320" t="s">
+        <v>658</v>
+      </c>
+      <c r="E320" t="s">
         <v>659</v>
-      </c>
-      <c r="C320" t="s">
-        <v>80</v>
-      </c>
-      <c r="D320" t="s">
-        <v>660</v>
-      </c>
-      <c r="E320" t="s">
-        <v>661</v>
       </c>
       <c r="F320" s="1">
         <v>46266</v>
       </c>
       <c r="G320" s="1">
-        <v>46267</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="321" spans="1:7" x14ac:dyDescent="0.2">
@@ -10586,10 +10697,10 @@
         <v>0</v>
       </c>
       <c r="B321" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="C321" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D321" t="s">
         <v>87</v>
@@ -10601,7 +10712,7 @@
         <v>46266</v>
       </c>
       <c r="G321" s="1">
-        <v>46267</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="322" spans="1:7" x14ac:dyDescent="0.2">
@@ -10609,16 +10720,16 @@
         <v>0</v>
       </c>
       <c r="B322" t="s">
+        <v>661</v>
+      </c>
+      <c r="C322" t="s">
+        <v>80</v>
+      </c>
+      <c r="D322" t="s">
+        <v>662</v>
+      </c>
+      <c r="E322" t="s">
         <v>663</v>
-      </c>
-      <c r="C322" t="s">
-        <v>80</v>
-      </c>
-      <c r="D322" t="s">
-        <v>578</v>
-      </c>
-      <c r="E322" t="s">
-        <v>579</v>
       </c>
       <c r="F322" s="1">
         <v>46266</v>
@@ -10635,7 +10746,7 @@
         <v>664</v>
       </c>
       <c r="C323" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D323" t="s">
         <v>87</v>
@@ -10647,7 +10758,7 @@
         <v>46266</v>
       </c>
       <c r="G323" s="1">
-        <v>46267</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="324" spans="1:7" x14ac:dyDescent="0.2">
@@ -10661,10 +10772,10 @@
         <v>80</v>
       </c>
       <c r="D324" t="s">
-        <v>87</v>
+        <v>666</v>
       </c>
       <c r="E324" t="s">
-        <v>88</v>
+        <v>667</v>
       </c>
       <c r="F324" s="1">
         <v>46266</v>
@@ -10678,7 +10789,7 @@
         <v>0</v>
       </c>
       <c r="B325" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="C325" t="s">
         <v>80</v>
@@ -10701,16 +10812,16 @@
         <v>0</v>
       </c>
       <c r="B326" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="C326" t="s">
         <v>80</v>
       </c>
       <c r="D326" t="s">
-        <v>668</v>
+        <v>576</v>
       </c>
       <c r="E326" t="s">
-        <v>669</v>
+        <v>577</v>
       </c>
       <c r="F326" s="1">
         <v>46266</v>
@@ -10730,10 +10841,10 @@
         <v>80</v>
       </c>
       <c r="D327" t="s">
-        <v>671</v>
+        <v>87</v>
       </c>
       <c r="E327" t="s">
-        <v>672</v>
+        <v>88</v>
       </c>
       <c r="F327" s="1">
         <v>46266</v>
@@ -10747,16 +10858,16 @@
         <v>0</v>
       </c>
       <c r="B328" t="s">
+        <v>671</v>
+      </c>
+      <c r="C328" t="s">
+        <v>80</v>
+      </c>
+      <c r="D328" t="s">
+        <v>672</v>
+      </c>
+      <c r="E328" t="s">
         <v>673</v>
-      </c>
-      <c r="C328" t="s">
-        <v>80</v>
-      </c>
-      <c r="D328" t="s">
-        <v>674</v>
-      </c>
-      <c r="E328" t="s">
-        <v>675</v>
       </c>
       <c r="F328" s="1">
         <v>46266</v>
@@ -10770,16 +10881,16 @@
         <v>0</v>
       </c>
       <c r="B329" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="C329" t="s">
         <v>80</v>
       </c>
       <c r="D329" t="s">
-        <v>221</v>
+        <v>87</v>
       </c>
       <c r="E329" t="s">
-        <v>222</v>
+        <v>88</v>
       </c>
       <c r="F329" s="1">
         <v>46266</v>
@@ -10793,16 +10904,16 @@
         <v>0</v>
       </c>
       <c r="B330" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="C330" t="s">
         <v>80</v>
       </c>
       <c r="D330" t="s">
-        <v>323</v>
+        <v>87</v>
       </c>
       <c r="E330" t="s">
-        <v>324</v>
+        <v>88</v>
       </c>
       <c r="F330" s="1">
         <v>46266</v>
@@ -10816,16 +10927,16 @@
         <v>0</v>
       </c>
       <c r="B331" t="s">
+        <v>676</v>
+      </c>
+      <c r="C331" t="s">
+        <v>80</v>
+      </c>
+      <c r="D331" t="s">
+        <v>677</v>
+      </c>
+      <c r="E331" t="s">
         <v>678</v>
-      </c>
-      <c r="C331" t="s">
-        <v>80</v>
-      </c>
-      <c r="D331" t="s">
-        <v>48</v>
-      </c>
-      <c r="E331" t="s">
-        <v>49</v>
       </c>
       <c r="F331" s="1">
         <v>46266</v>
@@ -10891,10 +11002,10 @@
         <v>80</v>
       </c>
       <c r="D334" t="s">
-        <v>686</v>
+        <v>221</v>
       </c>
       <c r="E334" t="s">
-        <v>687</v>
+        <v>222</v>
       </c>
       <c r="F334" s="1">
         <v>46266</v>
@@ -10908,16 +11019,16 @@
         <v>0</v>
       </c>
       <c r="B335" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="C335" t="s">
         <v>80</v>
       </c>
       <c r="D335" t="s">
-        <v>689</v>
+        <v>323</v>
       </c>
       <c r="E335" t="s">
-        <v>690</v>
+        <v>324</v>
       </c>
       <c r="F335" s="1">
         <v>46266</v>
@@ -10931,16 +11042,16 @@
         <v>0</v>
       </c>
       <c r="B336" t="s">
-        <v>691</v>
+        <v>687</v>
       </c>
       <c r="C336" t="s">
         <v>80</v>
       </c>
       <c r="D336" t="s">
-        <v>463</v>
+        <v>48</v>
       </c>
       <c r="E336" t="s">
-        <v>464</v>
+        <v>49</v>
       </c>
       <c r="F336" s="1">
         <v>46266</v>
@@ -10954,16 +11065,16 @@
         <v>0</v>
       </c>
       <c r="B337" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="C337" t="s">
         <v>80</v>
       </c>
       <c r="D337" t="s">
-        <v>463</v>
+        <v>689</v>
       </c>
       <c r="E337" t="s">
-        <v>464</v>
+        <v>690</v>
       </c>
       <c r="F337" s="1">
         <v>46266</v>
@@ -10977,16 +11088,16 @@
         <v>0</v>
       </c>
       <c r="B338" t="s">
+        <v>691</v>
+      </c>
+      <c r="C338" t="s">
+        <v>80</v>
+      </c>
+      <c r="D338" t="s">
+        <v>692</v>
+      </c>
+      <c r="E338" t="s">
         <v>693</v>
-      </c>
-      <c r="C338" t="s">
-        <v>80</v>
-      </c>
-      <c r="D338" t="s">
-        <v>502</v>
-      </c>
-      <c r="E338" t="s">
-        <v>503</v>
       </c>
       <c r="F338" s="1">
         <v>46266</v>
@@ -11052,10 +11163,10 @@
         <v>80</v>
       </c>
       <c r="D341" t="s">
-        <v>588</v>
+        <v>463</v>
       </c>
       <c r="E341" t="s">
-        <v>589</v>
+        <v>464</v>
       </c>
       <c r="F341" s="1">
         <v>46266</v>
@@ -11075,10 +11186,10 @@
         <v>80</v>
       </c>
       <c r="D342" t="s">
-        <v>111</v>
+        <v>463</v>
       </c>
       <c r="E342" t="s">
-        <v>112</v>
+        <v>464</v>
       </c>
       <c r="F342" s="1">
         <v>46266</v>
@@ -11098,10 +11209,10 @@
         <v>80</v>
       </c>
       <c r="D343" t="s">
-        <v>114</v>
+        <v>499</v>
       </c>
       <c r="E343" t="s">
-        <v>115</v>
+        <v>500</v>
       </c>
       <c r="F343" s="1">
         <v>46266</v>
@@ -11121,10 +11232,10 @@
         <v>80</v>
       </c>
       <c r="D344" t="s">
-        <v>114</v>
+        <v>704</v>
       </c>
       <c r="E344" t="s">
-        <v>115</v>
+        <v>705</v>
       </c>
       <c r="F344" s="1">
         <v>46266</v>
@@ -11138,16 +11249,16 @@
         <v>0</v>
       </c>
       <c r="B345" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="C345" t="s">
         <v>80</v>
       </c>
       <c r="D345" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="E345" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="F345" s="1">
         <v>46266</v>
@@ -11161,16 +11272,16 @@
         <v>0</v>
       </c>
       <c r="B346" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="C346" t="s">
         <v>80</v>
       </c>
       <c r="D346" t="s">
-        <v>144</v>
+        <v>594</v>
       </c>
       <c r="E346" t="s">
-        <v>145</v>
+        <v>595</v>
       </c>
       <c r="F346" s="1">
         <v>46266</v>
@@ -11184,16 +11295,16 @@
         <v>0</v>
       </c>
       <c r="B347" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="C347" t="s">
         <v>80</v>
       </c>
       <c r="D347" t="s">
-        <v>709</v>
+        <v>111</v>
       </c>
       <c r="E347" t="s">
-        <v>710</v>
+        <v>112</v>
       </c>
       <c r="F347" s="1">
         <v>46266</v>
@@ -11213,10 +11324,10 @@
         <v>80</v>
       </c>
       <c r="D348" t="s">
-        <v>709</v>
+        <v>114</v>
       </c>
       <c r="E348" t="s">
-        <v>710</v>
+        <v>115</v>
       </c>
       <c r="F348" s="1">
         <v>46266</v>
@@ -11236,10 +11347,10 @@
         <v>80</v>
       </c>
       <c r="D349" t="s">
-        <v>396</v>
+        <v>114</v>
       </c>
       <c r="E349" t="s">
-        <v>397</v>
+        <v>115</v>
       </c>
       <c r="F349" s="1">
         <v>46266</v>
@@ -11259,10 +11370,10 @@
         <v>80</v>
       </c>
       <c r="D350" t="s">
-        <v>280</v>
+        <v>714</v>
       </c>
       <c r="E350" t="s">
-        <v>281</v>
+        <v>715</v>
       </c>
       <c r="F350" s="1">
         <v>46266</v>
@@ -11276,16 +11387,16 @@
         <v>0</v>
       </c>
       <c r="B351" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="C351" t="s">
         <v>80</v>
       </c>
       <c r="D351" t="s">
-        <v>280</v>
+        <v>144</v>
       </c>
       <c r="E351" t="s">
-        <v>281</v>
+        <v>145</v>
       </c>
       <c r="F351" s="1">
         <v>46266</v>
@@ -11299,16 +11410,16 @@
         <v>0</v>
       </c>
       <c r="B352" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="C352" t="s">
         <v>80</v>
       </c>
       <c r="D352" t="s">
-        <v>280</v>
+        <v>718</v>
       </c>
       <c r="E352" t="s">
-        <v>281</v>
+        <v>719</v>
       </c>
       <c r="F352" s="1">
         <v>46266</v>
@@ -11322,16 +11433,16 @@
         <v>0</v>
       </c>
       <c r="B353" t="s">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="C353" t="s">
         <v>80</v>
       </c>
       <c r="D353" t="s">
-        <v>237</v>
+        <v>718</v>
       </c>
       <c r="E353" t="s">
-        <v>238</v>
+        <v>719</v>
       </c>
       <c r="F353" s="1">
         <v>46266</v>
@@ -11345,16 +11456,16 @@
         <v>0</v>
       </c>
       <c r="B354" t="s">
-        <v>717</v>
+        <v>721</v>
       </c>
       <c r="C354" t="s">
         <v>80</v>
       </c>
       <c r="D354" t="s">
-        <v>184</v>
+        <v>396</v>
       </c>
       <c r="E354" t="s">
-        <v>185</v>
+        <v>397</v>
       </c>
       <c r="F354" s="1">
         <v>46266</v>
@@ -11368,16 +11479,16 @@
         <v>0</v>
       </c>
       <c r="B355" t="s">
-        <v>718</v>
+        <v>722</v>
       </c>
       <c r="C355" t="s">
         <v>80</v>
       </c>
       <c r="D355" t="s">
-        <v>13</v>
+        <v>280</v>
       </c>
       <c r="E355" t="s">
-        <v>14</v>
+        <v>281</v>
       </c>
       <c r="F355" s="1">
         <v>46266</v>
@@ -11391,16 +11502,16 @@
         <v>0</v>
       </c>
       <c r="B356" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
       <c r="C356" t="s">
         <v>80</v>
       </c>
       <c r="D356" t="s">
-        <v>13</v>
+        <v>280</v>
       </c>
       <c r="E356" t="s">
-        <v>14</v>
+        <v>281</v>
       </c>
       <c r="F356" s="1">
         <v>46266</v>
@@ -11414,16 +11525,16 @@
         <v>0</v>
       </c>
       <c r="B357" t="s">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="C357" t="s">
         <v>80</v>
       </c>
       <c r="D357" t="s">
-        <v>482</v>
+        <v>280</v>
       </c>
       <c r="E357" t="s">
-        <v>483</v>
+        <v>281</v>
       </c>
       <c r="F357" s="1">
         <v>46266</v>
@@ -11437,16 +11548,16 @@
         <v>0</v>
       </c>
       <c r="B358" t="s">
-        <v>721</v>
+        <v>725</v>
       </c>
       <c r="C358" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D358" t="s">
-        <v>722</v>
+        <v>237</v>
       </c>
       <c r="E358" t="s">
-        <v>723</v>
+        <v>238</v>
       </c>
       <c r="F358" s="1">
         <v>46266</v>
@@ -11460,16 +11571,16 @@
         <v>0</v>
       </c>
       <c r="B359" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="C359" t="s">
         <v>80</v>
       </c>
       <c r="D359" t="s">
-        <v>197</v>
+        <v>184</v>
       </c>
       <c r="E359" t="s">
-        <v>198</v>
+        <v>185</v>
       </c>
       <c r="F359" s="1">
         <v>46266</v>
@@ -11483,16 +11594,16 @@
         <v>0</v>
       </c>
       <c r="B360" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="C360" t="s">
         <v>80</v>
       </c>
       <c r="D360" t="s">
-        <v>171</v>
+        <v>13</v>
       </c>
       <c r="E360" t="s">
-        <v>172</v>
+        <v>14</v>
       </c>
       <c r="F360" s="1">
         <v>46266</v>
@@ -11506,16 +11617,16 @@
         <v>0</v>
       </c>
       <c r="B361" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="C361" t="s">
         <v>80</v>
       </c>
       <c r="D361" t="s">
-        <v>674</v>
+        <v>13</v>
       </c>
       <c r="E361" t="s">
-        <v>675</v>
+        <v>14</v>
       </c>
       <c r="F361" s="1">
         <v>46266</v>
@@ -11529,16 +11640,16 @@
         <v>0</v>
       </c>
       <c r="B362" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="C362" t="s">
         <v>80</v>
       </c>
       <c r="D362" t="s">
-        <v>108</v>
+        <v>479</v>
       </c>
       <c r="E362" t="s">
-        <v>109</v>
+        <v>480</v>
       </c>
       <c r="F362" s="1">
         <v>46266</v>
@@ -11552,19 +11663,19 @@
         <v>0</v>
       </c>
       <c r="B363" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="C363" t="s">
         <v>80</v>
       </c>
       <c r="D363" t="s">
-        <v>729</v>
+        <v>197</v>
       </c>
       <c r="E363" t="s">
-        <v>730</v>
+        <v>198</v>
       </c>
       <c r="F363" s="1">
-        <v>46267</v>
+        <v>46266</v>
       </c>
       <c r="G363" s="1">
         <v>46267</v>
@@ -11581,13 +11692,13 @@
         <v>80</v>
       </c>
       <c r="D364" t="s">
-        <v>732</v>
+        <v>171</v>
       </c>
       <c r="E364" t="s">
-        <v>733</v>
+        <v>172</v>
       </c>
       <c r="F364" s="1">
-        <v>46267</v>
+        <v>46266</v>
       </c>
       <c r="G364" s="1">
         <v>46267</v>
@@ -11598,19 +11709,19 @@
         <v>0</v>
       </c>
       <c r="B365" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="C365" t="s">
         <v>80</v>
       </c>
       <c r="D365" t="s">
-        <v>735</v>
+        <v>683</v>
       </c>
       <c r="E365" t="s">
-        <v>736</v>
+        <v>684</v>
       </c>
       <c r="F365" s="1">
-        <v>46267</v>
+        <v>46266</v>
       </c>
       <c r="G365" s="1">
         <v>46267</v>
@@ -11621,19 +11732,19 @@
         <v>0</v>
       </c>
       <c r="B366" t="s">
-        <v>737</v>
+        <v>733</v>
       </c>
       <c r="C366" t="s">
         <v>80</v>
       </c>
       <c r="D366" t="s">
-        <v>234</v>
+        <v>108</v>
       </c>
       <c r="E366" t="s">
-        <v>235</v>
+        <v>109</v>
       </c>
       <c r="F366" s="1">
-        <v>46267</v>
+        <v>46266</v>
       </c>
       <c r="G366" s="1">
         <v>46267</v>
@@ -11644,16 +11755,16 @@
         <v>0</v>
       </c>
       <c r="B367" t="s">
-        <v>738</v>
+        <v>734</v>
       </c>
       <c r="C367" t="s">
         <v>80</v>
       </c>
       <c r="D367" t="s">
-        <v>739</v>
+        <v>735</v>
       </c>
       <c r="E367" t="s">
-        <v>740</v>
+        <v>736</v>
       </c>
       <c r="F367" s="1">
         <v>46267</v>
@@ -11667,16 +11778,16 @@
         <v>0</v>
       </c>
       <c r="B368" t="s">
-        <v>741</v>
+        <v>737</v>
       </c>
       <c r="C368" t="s">
         <v>80</v>
       </c>
       <c r="D368" t="s">
-        <v>742</v>
+        <v>738</v>
       </c>
       <c r="E368" t="s">
-        <v>743</v>
+        <v>739</v>
       </c>
       <c r="F368" s="1">
         <v>46267</v>
@@ -11690,16 +11801,16 @@
         <v>0</v>
       </c>
       <c r="B369" t="s">
-        <v>744</v>
+        <v>740</v>
       </c>
       <c r="C369" t="s">
         <v>80</v>
       </c>
       <c r="D369" t="s">
+        <v>741</v>
+      </c>
+      <c r="E369" t="s">
         <v>742</v>
-      </c>
-      <c r="E369" t="s">
-        <v>743</v>
       </c>
       <c r="F369" s="1">
         <v>46267</v>
@@ -11713,16 +11824,16 @@
         <v>0</v>
       </c>
       <c r="B370" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="C370" t="s">
         <v>80</v>
       </c>
       <c r="D370" t="s">
-        <v>211</v>
+        <v>234</v>
       </c>
       <c r="E370" t="s">
-        <v>212</v>
+        <v>235</v>
       </c>
       <c r="F370" s="1">
         <v>46267</v>
@@ -11736,16 +11847,16 @@
         <v>0</v>
       </c>
       <c r="B371" t="s">
+        <v>744</v>
+      </c>
+      <c r="C371" t="s">
+        <v>80</v>
+      </c>
+      <c r="D371" t="s">
+        <v>745</v>
+      </c>
+      <c r="E371" t="s">
         <v>746</v>
-      </c>
-      <c r="C371" t="s">
-        <v>80</v>
-      </c>
-      <c r="D371" t="s">
-        <v>747</v>
-      </c>
-      <c r="E371" t="s">
-        <v>748</v>
       </c>
       <c r="F371" s="1">
         <v>46267</v>
@@ -11759,16 +11870,16 @@
         <v>0</v>
       </c>
       <c r="B372" t="s">
+        <v>747</v>
+      </c>
+      <c r="C372" t="s">
+        <v>80</v>
+      </c>
+      <c r="D372" t="s">
+        <v>748</v>
+      </c>
+      <c r="E372" t="s">
         <v>749</v>
-      </c>
-      <c r="C372" t="s">
-        <v>80</v>
-      </c>
-      <c r="D372" t="s">
-        <v>750</v>
-      </c>
-      <c r="E372" t="s">
-        <v>751</v>
       </c>
       <c r="F372" s="1">
         <v>46267</v>
@@ -11782,16 +11893,16 @@
         <v>0</v>
       </c>
       <c r="B373" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="C373" t="s">
         <v>80</v>
       </c>
       <c r="D373" t="s">
-        <v>3</v>
+        <v>748</v>
       </c>
       <c r="E373" t="s">
-        <v>4</v>
+        <v>749</v>
       </c>
       <c r="F373" s="1">
         <v>46267</v>
@@ -11805,16 +11916,16 @@
         <v>0</v>
       </c>
       <c r="B374" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="C374" t="s">
         <v>80</v>
       </c>
       <c r="D374" t="s">
-        <v>754</v>
+        <v>211</v>
       </c>
       <c r="E374" t="s">
-        <v>755</v>
+        <v>212</v>
       </c>
       <c r="F374" s="1">
         <v>46267</v>
@@ -11828,16 +11939,16 @@
         <v>0</v>
       </c>
       <c r="B375" t="s">
-        <v>756</v>
+        <v>752</v>
       </c>
       <c r="C375" t="s">
         <v>80</v>
       </c>
       <c r="D375" t="s">
+        <v>753</v>
+      </c>
+      <c r="E375" t="s">
         <v>754</v>
-      </c>
-      <c r="E375" t="s">
-        <v>755</v>
       </c>
       <c r="F375" s="1">
         <v>46267</v>
@@ -11851,16 +11962,16 @@
         <v>0</v>
       </c>
       <c r="B376" t="s">
+        <v>755</v>
+      </c>
+      <c r="C376" t="s">
+        <v>80</v>
+      </c>
+      <c r="D376" t="s">
+        <v>756</v>
+      </c>
+      <c r="E376" t="s">
         <v>757</v>
-      </c>
-      <c r="C376" t="s">
-        <v>80</v>
-      </c>
-      <c r="D376" t="s">
-        <v>758</v>
-      </c>
-      <c r="E376" t="s">
-        <v>759</v>
       </c>
       <c r="F376" s="1">
         <v>46267</v>
@@ -11874,16 +11985,16 @@
         <v>0</v>
       </c>
       <c r="B377" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="C377" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D377" t="s">
-        <v>492</v>
+        <v>3</v>
       </c>
       <c r="E377" t="s">
-        <v>493</v>
+        <v>4</v>
       </c>
       <c r="F377" s="1">
         <v>46267</v>
@@ -11897,16 +12008,16 @@
         <v>0</v>
       </c>
       <c r="B378" t="s">
+        <v>759</v>
+      </c>
+      <c r="C378" t="s">
+        <v>80</v>
+      </c>
+      <c r="D378" t="s">
+        <v>760</v>
+      </c>
+      <c r="E378" t="s">
         <v>761</v>
-      </c>
-      <c r="C378" t="s">
-        <v>80</v>
-      </c>
-      <c r="D378" t="s">
-        <v>762</v>
-      </c>
-      <c r="E378" t="s">
-        <v>763</v>
       </c>
       <c r="F378" s="1">
         <v>46267</v>
@@ -11920,16 +12031,16 @@
         <v>0</v>
       </c>
       <c r="B379" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="C379" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D379" t="s">
-        <v>489</v>
+        <v>760</v>
       </c>
       <c r="E379" t="s">
-        <v>490</v>
+        <v>761</v>
       </c>
       <c r="F379" s="1">
         <v>46267</v>
@@ -11943,16 +12054,16 @@
         <v>0</v>
       </c>
       <c r="B380" t="s">
+        <v>763</v>
+      </c>
+      <c r="C380" t="s">
+        <v>80</v>
+      </c>
+      <c r="D380" t="s">
+        <v>764</v>
+      </c>
+      <c r="E380" t="s">
         <v>765</v>
-      </c>
-      <c r="C380" t="s">
-        <v>2</v>
-      </c>
-      <c r="D380" t="s">
-        <v>492</v>
-      </c>
-      <c r="E380" t="s">
-        <v>493</v>
       </c>
       <c r="F380" s="1">
         <v>46267</v>
@@ -11969,13 +12080,13 @@
         <v>766</v>
       </c>
       <c r="C381" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D381" t="s">
-        <v>93</v>
+        <v>489</v>
       </c>
       <c r="E381" t="s">
-        <v>94</v>
+        <v>490</v>
       </c>
       <c r="F381" s="1">
         <v>46267</v>
@@ -11995,10 +12106,10 @@
         <v>80</v>
       </c>
       <c r="D382" t="s">
-        <v>37</v>
+        <v>768</v>
       </c>
       <c r="E382" t="s">
-        <v>38</v>
+        <v>769</v>
       </c>
       <c r="F382" s="1">
         <v>46267</v>
@@ -12012,16 +12123,16 @@
         <v>0</v>
       </c>
       <c r="B383" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="C383" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D383" t="s">
-        <v>37</v>
+        <v>486</v>
       </c>
       <c r="E383" t="s">
-        <v>38</v>
+        <v>487</v>
       </c>
       <c r="F383" s="1">
         <v>46267</v>
@@ -12035,16 +12146,16 @@
         <v>0</v>
       </c>
       <c r="B384" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="C384" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D384" t="s">
-        <v>37</v>
+        <v>489</v>
       </c>
       <c r="E384" t="s">
-        <v>38</v>
+        <v>490</v>
       </c>
       <c r="F384" s="1">
         <v>46267</v>
@@ -12058,16 +12169,16 @@
         <v>0</v>
       </c>
       <c r="B385" t="s">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="C385" t="s">
         <v>80</v>
       </c>
       <c r="D385" t="s">
-        <v>37</v>
+        <v>93</v>
       </c>
       <c r="E385" t="s">
-        <v>38</v>
+        <v>94</v>
       </c>
       <c r="F385" s="1">
         <v>46267</v>
@@ -12081,7 +12192,7 @@
         <v>0</v>
       </c>
       <c r="B386" t="s">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="C386" t="s">
         <v>80</v>
@@ -12104,7 +12215,7 @@
         <v>0</v>
       </c>
       <c r="B387" t="s">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="C387" t="s">
         <v>80</v>
@@ -12127,7 +12238,7 @@
         <v>0</v>
       </c>
       <c r="B388" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="C388" t="s">
         <v>80</v>
@@ -12150,16 +12261,16 @@
         <v>0</v>
       </c>
       <c r="B389" t="s">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="C389" t="s">
         <v>80</v>
       </c>
       <c r="D389" t="s">
-        <v>775</v>
+        <v>37</v>
       </c>
       <c r="E389" t="s">
-        <v>776</v>
+        <v>38</v>
       </c>
       <c r="F389" s="1">
         <v>46267</v>
@@ -12179,10 +12290,10 @@
         <v>80</v>
       </c>
       <c r="D390" t="s">
-        <v>778</v>
+        <v>37</v>
       </c>
       <c r="E390" t="s">
-        <v>779</v>
+        <v>38</v>
       </c>
       <c r="F390" s="1">
         <v>46267</v>
@@ -12196,7 +12307,7 @@
         <v>0</v>
       </c>
       <c r="B391" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="C391" t="s">
         <v>80</v>
@@ -12219,16 +12330,16 @@
         <v>0</v>
       </c>
       <c r="B392" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="C392" t="s">
         <v>80</v>
       </c>
       <c r="D392" t="s">
-        <v>782</v>
+        <v>37</v>
       </c>
       <c r="E392" t="s">
-        <v>783</v>
+        <v>38</v>
       </c>
       <c r="F392" s="1">
         <v>46267</v>
@@ -12242,16 +12353,16 @@
         <v>0</v>
       </c>
       <c r="B393" t="s">
-        <v>784</v>
+        <v>780</v>
       </c>
       <c r="C393" t="s">
         <v>80</v>
       </c>
       <c r="D393" t="s">
-        <v>785</v>
+        <v>781</v>
       </c>
       <c r="E393" t="s">
-        <v>786</v>
+        <v>782</v>
       </c>
       <c r="F393" s="1">
         <v>46267</v>
@@ -12265,16 +12376,16 @@
         <v>0</v>
       </c>
       <c r="B394" t="s">
-        <v>787</v>
+        <v>783</v>
       </c>
       <c r="C394" t="s">
         <v>80</v>
       </c>
       <c r="D394" t="s">
-        <v>292</v>
+        <v>784</v>
       </c>
       <c r="E394" t="s">
-        <v>293</v>
+        <v>785</v>
       </c>
       <c r="F394" s="1">
         <v>46267</v>
@@ -12288,16 +12399,16 @@
         <v>0</v>
       </c>
       <c r="B395" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="C395" t="s">
         <v>80</v>
       </c>
       <c r="D395" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="E395" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="F395" s="1">
         <v>46267</v>
@@ -12311,16 +12422,16 @@
         <v>0</v>
       </c>
       <c r="B396" t="s">
+        <v>787</v>
+      </c>
+      <c r="C396" t="s">
+        <v>80</v>
+      </c>
+      <c r="D396" t="s">
+        <v>788</v>
+      </c>
+      <c r="E396" t="s">
         <v>789</v>
-      </c>
-      <c r="C396" t="s">
-        <v>80</v>
-      </c>
-      <c r="D396" t="s">
-        <v>790</v>
-      </c>
-      <c r="E396" t="s">
-        <v>791</v>
       </c>
       <c r="F396" s="1">
         <v>46267</v>
@@ -12334,16 +12445,16 @@
         <v>0</v>
       </c>
       <c r="B397" t="s">
+        <v>790</v>
+      </c>
+      <c r="C397" t="s">
+        <v>80</v>
+      </c>
+      <c r="D397" t="s">
+        <v>791</v>
+      </c>
+      <c r="E397" t="s">
         <v>792</v>
-      </c>
-      <c r="C397" t="s">
-        <v>80</v>
-      </c>
-      <c r="D397" t="s">
-        <v>793</v>
-      </c>
-      <c r="E397" t="s">
-        <v>794</v>
       </c>
       <c r="F397" s="1">
         <v>46267</v>
@@ -12357,16 +12468,16 @@
         <v>0</v>
       </c>
       <c r="B398" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="C398" t="s">
         <v>80</v>
       </c>
       <c r="D398" t="s">
-        <v>16</v>
+        <v>292</v>
       </c>
       <c r="E398" t="s">
-        <v>17</v>
+        <v>293</v>
       </c>
       <c r="F398" s="1">
         <v>46267</v>
@@ -12380,16 +12491,16 @@
         <v>0</v>
       </c>
       <c r="B399" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="C399" t="s">
         <v>80</v>
       </c>
       <c r="D399" t="s">
-        <v>797</v>
+        <v>16</v>
       </c>
       <c r="E399" t="s">
-        <v>798</v>
+        <v>17</v>
       </c>
       <c r="F399" s="1">
         <v>46267</v>
@@ -12403,16 +12514,16 @@
         <v>0</v>
       </c>
       <c r="B400" t="s">
-        <v>799</v>
+        <v>795</v>
       </c>
       <c r="C400" t="s">
         <v>80</v>
       </c>
       <c r="D400" t="s">
-        <v>800</v>
+        <v>796</v>
       </c>
       <c r="E400" t="s">
-        <v>801</v>
+        <v>797</v>
       </c>
       <c r="F400" s="1">
         <v>46267</v>
@@ -12426,16 +12537,16 @@
         <v>0</v>
       </c>
       <c r="B401" t="s">
-        <v>802</v>
+        <v>798</v>
       </c>
       <c r="C401" t="s">
         <v>80</v>
       </c>
       <c r="D401" t="s">
-        <v>37</v>
+        <v>799</v>
       </c>
       <c r="E401" t="s">
-        <v>38</v>
+        <v>800</v>
       </c>
       <c r="F401" s="1">
         <v>46267</v>
@@ -12449,16 +12560,16 @@
         <v>0</v>
       </c>
       <c r="B402" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="C402" t="s">
         <v>80</v>
       </c>
       <c r="D402" t="s">
-        <v>602</v>
+        <v>16</v>
       </c>
       <c r="E402" t="s">
-        <v>603</v>
+        <v>17</v>
       </c>
       <c r="F402" s="1">
         <v>46267</v>
@@ -12472,16 +12583,16 @@
         <v>0</v>
       </c>
       <c r="B403" t="s">
+        <v>802</v>
+      </c>
+      <c r="C403" t="s">
+        <v>80</v>
+      </c>
+      <c r="D403" t="s">
+        <v>803</v>
+      </c>
+      <c r="E403" t="s">
         <v>804</v>
-      </c>
-      <c r="C403" t="s">
-        <v>80</v>
-      </c>
-      <c r="D403" t="s">
-        <v>805</v>
-      </c>
-      <c r="E403" t="s">
-        <v>806</v>
       </c>
       <c r="F403" s="1">
         <v>46267</v>
@@ -12495,16 +12606,16 @@
         <v>0</v>
       </c>
       <c r="B404" t="s">
+        <v>805</v>
+      </c>
+      <c r="C404" t="s">
+        <v>80</v>
+      </c>
+      <c r="D404" t="s">
+        <v>806</v>
+      </c>
+      <c r="E404" t="s">
         <v>807</v>
-      </c>
-      <c r="C404" t="s">
-        <v>80</v>
-      </c>
-      <c r="D404" t="s">
-        <v>93</v>
-      </c>
-      <c r="E404" t="s">
-        <v>94</v>
       </c>
       <c r="F404" s="1">
         <v>46267</v>
@@ -12524,10 +12635,10 @@
         <v>80</v>
       </c>
       <c r="D405" t="s">
-        <v>809</v>
+        <v>37</v>
       </c>
       <c r="E405" t="s">
-        <v>810</v>
+        <v>38</v>
       </c>
       <c r="F405" s="1">
         <v>46267</v>
@@ -12541,16 +12652,16 @@
         <v>0</v>
       </c>
       <c r="B406" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="C406" t="s">
         <v>80</v>
       </c>
       <c r="D406" t="s">
-        <v>812</v>
+        <v>608</v>
       </c>
       <c r="E406" t="s">
-        <v>813</v>
+        <v>609</v>
       </c>
       <c r="F406" s="1">
         <v>46267</v>
@@ -12564,16 +12675,16 @@
         <v>0</v>
       </c>
       <c r="B407" t="s">
-        <v>814</v>
+        <v>810</v>
       </c>
       <c r="C407" t="s">
         <v>80</v>
       </c>
       <c r="D407" t="s">
-        <v>815</v>
+        <v>811</v>
       </c>
       <c r="E407" t="s">
-        <v>816</v>
+        <v>812</v>
       </c>
       <c r="F407" s="1">
         <v>46267</v>
@@ -12584,151 +12695,151 @@
     </row>
     <row r="408" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A408" t="s">
-        <v>817</v>
+        <v>0</v>
       </c>
       <c r="B408" t="s">
-        <v>818</v>
+        <v>813</v>
       </c>
       <c r="C408" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D408" t="s">
-        <v>300</v>
+        <v>93</v>
       </c>
       <c r="E408" t="s">
-        <v>301</v>
+        <v>94</v>
       </c>
       <c r="F408" s="1">
-        <v>46148</v>
+        <v>46267</v>
       </c>
       <c r="G408" s="1">
-        <v>46149</v>
+        <v>46267</v>
       </c>
     </row>
     <row r="409" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A409" t="s">
-        <v>817</v>
+        <v>0</v>
       </c>
       <c r="B409" t="s">
-        <v>819</v>
+        <v>814</v>
       </c>
       <c r="C409" t="s">
         <v>80</v>
       </c>
       <c r="D409" t="s">
-        <v>820</v>
+        <v>815</v>
       </c>
       <c r="E409" t="s">
-        <v>821</v>
+        <v>816</v>
       </c>
       <c r="F409" s="1">
-        <v>46260</v>
+        <v>46267</v>
       </c>
       <c r="G409" s="1">
-        <v>46262</v>
+        <v>46267</v>
       </c>
     </row>
     <row r="410" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A410" t="s">
-        <v>822</v>
+        <v>0</v>
       </c>
       <c r="B410" t="s">
-        <v>823</v>
+        <v>817</v>
       </c>
       <c r="C410" t="s">
-        <v>6</v>
+        <v>80</v>
       </c>
       <c r="D410" t="s">
-        <v>41</v>
+        <v>818</v>
       </c>
       <c r="E410" t="s">
-        <v>42</v>
+        <v>819</v>
       </c>
       <c r="F410" s="1">
-        <v>46133</v>
+        <v>46267</v>
       </c>
       <c r="G410" s="1">
-        <v>46134</v>
+        <v>46267</v>
       </c>
     </row>
     <row r="411" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A411" t="s">
+        <v>0</v>
+      </c>
+      <c r="B411" t="s">
+        <v>820</v>
+      </c>
+      <c r="C411" t="s">
+        <v>80</v>
+      </c>
+      <c r="D411" t="s">
+        <v>821</v>
+      </c>
+      <c r="E411" t="s">
         <v>822</v>
       </c>
-      <c r="B411" t="s">
-        <v>824</v>
-      </c>
-      <c r="C411" t="s">
-        <v>6</v>
-      </c>
-      <c r="D411" t="s">
-        <v>41</v>
-      </c>
-      <c r="E411" t="s">
-        <v>42</v>
-      </c>
       <c r="F411" s="1">
-        <v>46134</v>
+        <v>46267</v>
       </c>
       <c r="G411" s="1">
-        <v>46134</v>
+        <v>46267</v>
       </c>
     </row>
     <row r="412" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A412" t="s">
-        <v>822</v>
+        <v>0</v>
       </c>
       <c r="B412" t="s">
+        <v>823</v>
+      </c>
+      <c r="C412" t="s">
+        <v>80</v>
+      </c>
+      <c r="D412" t="s">
+        <v>824</v>
+      </c>
+      <c r="E412" t="s">
         <v>825</v>
       </c>
-      <c r="C412" t="s">
-        <v>6</v>
-      </c>
-      <c r="D412" t="s">
-        <v>19</v>
-      </c>
-      <c r="E412" t="s">
-        <v>20</v>
-      </c>
       <c r="F412" s="1">
-        <v>46156</v>
+        <v>46267</v>
       </c>
       <c r="G412" s="1">
-        <v>46156</v>
+        <v>46267</v>
       </c>
     </row>
     <row r="413" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A413" t="s">
-        <v>822</v>
+        <v>0</v>
       </c>
       <c r="B413" t="s">
         <v>826</v>
       </c>
       <c r="C413" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D413" t="s">
-        <v>489</v>
+        <v>824</v>
       </c>
       <c r="E413" t="s">
-        <v>490</v>
+        <v>825</v>
       </c>
       <c r="F413" s="1">
-        <v>46195</v>
+        <v>46267</v>
       </c>
       <c r="G413" s="1">
-        <v>46195</v>
+        <v>46267</v>
       </c>
     </row>
     <row r="414" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A414" t="s">
-        <v>822</v>
+        <v>0</v>
       </c>
       <c r="B414" t="s">
         <v>827</v>
       </c>
       <c r="C414" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D414" t="s">
         <v>828</v>
@@ -12737,306 +12848,306 @@
         <v>829</v>
       </c>
       <c r="F414" s="1">
-        <v>46206</v>
+        <v>46267</v>
       </c>
       <c r="G414" s="1">
-        <v>46252</v>
+        <v>46267</v>
       </c>
     </row>
     <row r="415" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A415" t="s">
-        <v>822</v>
+        <v>0</v>
       </c>
       <c r="B415" t="s">
         <v>830</v>
       </c>
       <c r="C415" t="s">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="D415" t="s">
-        <v>831</v>
+        <v>714</v>
       </c>
       <c r="E415" t="s">
-        <v>832</v>
+        <v>715</v>
       </c>
       <c r="F415" s="1">
-        <v>46209</v>
+        <v>46267</v>
       </c>
       <c r="G415" s="1">
-        <v>46218</v>
+        <v>46267</v>
       </c>
     </row>
     <row r="416" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A416" t="s">
-        <v>822</v>
+        <v>0</v>
       </c>
       <c r="B416" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="C416" t="s">
-        <v>6</v>
+        <v>80</v>
       </c>
       <c r="D416" t="s">
-        <v>834</v>
+        <v>155</v>
       </c>
       <c r="E416" t="s">
-        <v>835</v>
+        <v>156</v>
       </c>
       <c r="F416" s="1">
-        <v>46213</v>
+        <v>46267</v>
       </c>
       <c r="G416" s="1">
-        <v>46213</v>
+        <v>46267</v>
       </c>
     </row>
     <row r="417" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A417" t="s">
-        <v>822</v>
+        <v>0</v>
       </c>
       <c r="B417" t="s">
-        <v>836</v>
+        <v>832</v>
       </c>
       <c r="C417" t="s">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="D417" t="s">
-        <v>837</v>
+        <v>608</v>
       </c>
       <c r="E417" t="s">
-        <v>838</v>
+        <v>609</v>
       </c>
       <c r="F417" s="1">
-        <v>46213</v>
+        <v>46267</v>
       </c>
       <c r="G417" s="1">
-        <v>46216</v>
+        <v>46267</v>
       </c>
     </row>
     <row r="418" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A418" t="s">
-        <v>822</v>
+        <v>0</v>
       </c>
       <c r="B418" t="s">
-        <v>839</v>
+        <v>833</v>
       </c>
       <c r="C418" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D418" t="s">
-        <v>127</v>
+        <v>155</v>
       </c>
       <c r="E418" t="s">
-        <v>128</v>
+        <v>156</v>
       </c>
       <c r="F418" s="1">
-        <v>46220</v>
+        <v>46267</v>
       </c>
       <c r="G418" s="1">
-        <v>46231</v>
+        <v>46267</v>
       </c>
     </row>
     <row r="419" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A419" t="s">
-        <v>822</v>
+        <v>0</v>
       </c>
       <c r="B419" t="s">
-        <v>840</v>
+        <v>834</v>
       </c>
       <c r="C419" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D419" t="s">
-        <v>489</v>
+        <v>37</v>
       </c>
       <c r="E419" t="s">
-        <v>490</v>
+        <v>38</v>
       </c>
       <c r="F419" s="1">
-        <v>46223</v>
+        <v>46267</v>
       </c>
       <c r="G419" s="1">
-        <v>46223</v>
+        <v>46267</v>
       </c>
     </row>
     <row r="420" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A420" t="s">
-        <v>822</v>
+        <v>0</v>
       </c>
       <c r="B420" t="s">
-        <v>841</v>
+        <v>835</v>
       </c>
       <c r="C420" t="s">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="D420" t="s">
+        <v>836</v>
+      </c>
+      <c r="E420" t="s">
         <v>837</v>
       </c>
-      <c r="E420" t="s">
-        <v>838</v>
-      </c>
       <c r="F420" s="1">
-        <v>46224</v>
+        <v>46267</v>
       </c>
       <c r="G420" s="1">
-        <v>46224</v>
+        <v>46267</v>
       </c>
     </row>
     <row r="421" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A421" t="s">
-        <v>822</v>
+        <v>0</v>
       </c>
       <c r="B421" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
       <c r="C421" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D421" t="s">
-        <v>127</v>
+        <v>37</v>
       </c>
       <c r="E421" t="s">
-        <v>128</v>
+        <v>38</v>
       </c>
       <c r="F421" 